--- a/Templates/Tables/StringInfo/StrTable.xlsx
+++ b/Templates/Tables/StringInfo/StrTable.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="303">
   <si>
     <t>ID</t>
   </si>
@@ -37,7 +37,7 @@
     <t>에디터를 종료하시겠습니까?</t>
   </si>
   <si>
-    <t>Are you sure you want to quit the editor?</t>
+    <t>Do you want to quit the editor?</t>
   </si>
   <si>
     <t>EDITOR_REMOVE_LP_MSG</t>
@@ -49,7 +49,7 @@
     <t>레벨을 제거하시겠습니까?</t>
   </si>
   <si>
-    <t>Are you sure you want to remove the level?</t>
+    <t>Do you want to remove the level?</t>
   </si>
   <si>
     <t>EDITOR_REMOVE_SP_MSG</t>
@@ -61,7 +61,7 @@
     <t>스테이지를 제거하시겠습니까?</t>
   </si>
   <si>
-    <t>Are you sure you want to remove the stage?</t>
+    <t>Do you want to remove the stage?</t>
   </si>
   <si>
     <t>EDITOR_REMOVE_CP_MSG</t>
@@ -73,7 +73,7 @@
     <t>챕터를 제거하시겠습니까?</t>
   </si>
   <si>
-    <t>Are you sure you want to remove the chapter?</t>
+    <t>Do you want to remove the chapter?</t>
   </si>
   <si>
     <t>QUIT_P_MSG</t>
@@ -85,7 +85,7 @@
     <t>게임을 종료하시겠습니까?</t>
   </si>
   <si>
-    <t>Are you sure you want to quit the game?</t>
+    <t>Do you want to quit the game?</t>
   </si>
   <si>
     <t>UPDATE_P_MSG</t>
@@ -100,16 +100,28 @@
     <t>A new version has been released.\nWould you like to update it?</t>
   </si>
   <si>
+    <t>LOAD_P_MSG</t>
+  </si>
+  <si>
+    <t>로드 팝업 메세지</t>
+  </si>
+  <si>
+    <t>진행 상황을 로드하시겠습니까?\n&lt;color=#ff0000ff&gt;&lt;size=24&gt;(로드 시 현재 진행 상황은 복구 할 수 없습니다)&lt;/size&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Do you want to load progress?\n&lt;color=#ff0000ff&gt;&lt;size=24&gt;(When loading, current progress cannot be recovered)&lt;/size&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
     <t>SAVE_P_MSG</t>
   </si>
   <si>
     <t>저장 팝업 메세지</t>
   </si>
   <si>
-    <t>LOAD_P_MSG</t>
+    <t>진행 상황을 저장하시겠습니까?\n&lt;color=#ff0000ff&gt;&lt;size=24&gt;(저장 시 이전 진행 상황은 복구 할 수 없습니다)&lt;/size&gt;&lt;/color&gt;</t>
   </si>
   <si>
-    <t>로드 팝업 메세지</t>
+    <t>Do you want to save progress?\n&lt;color=#ff0000ff&gt;&lt;size=24&gt;(When saving, previous progress cannot be recovered)&lt;/size&gt;&lt;/color&gt;</t>
   </si>
   <si>
     <t>AGREE_P_SERVICES_TITLE</t>
@@ -175,58 +187,58 @@
     <t>약관 동의 팝업 개인 정보 버튼 텍스트</t>
   </si>
   <si>
-    <t>DESC_P_TITLE</t>
+    <t>TRACKING_DP_TITLE</t>
   </si>
   <si>
-    <t>설명 팝업 제목</t>
+    <t>추적 설명 팝업 제목</t>
   </si>
   <si>
     <t>알림</t>
   </si>
   <si>
-    <t>DESC_P_MSG</t>
+    <t>TRACKING_DP_MSG</t>
   </si>
   <si>
-    <t>설명 팝업 메세지</t>
+    <t>추적 설명 팝업 메세지</t>
   </si>
   <si>
-    <t>추적 허용</t>
+    <t>앱 추적을 승인\n해주세요</t>
   </si>
   <si>
     <t>Allow tracking on the\nnext screen for</t>
   </si>
   <si>
-    <t>DESC_P_DESC_MSG_01</t>
+    <t>TRACKING_DP_DESC_MSG_01</t>
   </si>
   <si>
-    <t>설명 팝업 설명 메세지 1</t>
+    <t>추적 설명 팝업 설명 메세지 1</t>
   </si>
   <si>
-    <t>∙ 특별한 프로모션을 제공해\n드립니다.</t>
+    <t>∙ 특별한 프로모션을 제공해\n드립니다</t>
   </si>
   <si>
     <t>∙ Special offers and promotions\njust for you</t>
   </si>
   <si>
-    <t>DESC_P_DESC_MSG_02</t>
+    <t>TRACKING_DP_DESC_MSG_02</t>
   </si>
   <si>
-    <t>설명 팝업 설명 메세지 2</t>
+    <t>추적 설명 팝업 설명 메세지 2</t>
   </si>
   <si>
-    <t>∙ 관심사에 맞는 광고를 보여\n드립니다.</t>
+    <t>∙ 관심사에 맞는 광고를 보여\n드립니다</t>
   </si>
   <si>
     <t>∙ Advertisements that match\nyour interests</t>
   </si>
   <si>
-    <t>DESC_P_DESC_MSG_03</t>
+    <t>TRACKING_DP_DESC_MSG_03</t>
   </si>
   <si>
-    <t>설명 팝업 설명 메세지 3</t>
+    <t>추적 설명 팝업 설명 메세지 3</t>
   </si>
   <si>
-    <t>∙ 개인화 된 경험이 향상 시켜\n드립니다.</t>
+    <t>∙ 개인화 된 경험을 향상 시켜\n드립니다</t>
   </si>
   <si>
     <t>∙ An improved personalized\nexperience over time</t>
@@ -250,7 +262,7 @@
     <t>공용 로그인 성공 메세지</t>
   </si>
   <si>
-    <t>로그인했습니다.</t>
+    <t>로그인했습니다</t>
   </si>
   <si>
     <t>You have successfully login</t>
@@ -262,7 +274,7 @@
     <t>공용 로그인 실패 메세지</t>
   </si>
   <si>
-    <t>로그인에 실패했습니다.</t>
+    <t>로그인에 실패했습니다</t>
   </si>
   <si>
     <t>You have failed to login</t>
@@ -274,7 +286,7 @@
     <t>공용 로그아웃 성공 메세지</t>
   </si>
   <si>
-    <t>로그아웃했습니다.</t>
+    <t>로그아웃했습니다</t>
   </si>
   <si>
     <t>You have successfully logout</t>
@@ -286,7 +298,7 @@
     <t>공용 로그아웃 실패 메세지</t>
   </si>
   <si>
-    <t>로그아웃에 실패했습니다.</t>
+    <t>로그아웃에 실패했습니다</t>
   </si>
   <si>
     <t>You have failed to logout</t>
@@ -298,10 +310,10 @@
     <t>공용 로드 성공 메세지</t>
   </si>
   <si>
-    <t>진행 상황을 로드했습니다.</t>
+    <t>진행 상황을 로드했습니다</t>
   </si>
   <si>
-    <t>You have successfully loaded progress.</t>
+    <t>You have successfully loaded progress</t>
   </si>
   <si>
     <t>COMMON_LOAD_FAIL_MSG</t>
@@ -310,10 +322,10 @@
     <t>공용 로드 실패 메세지</t>
   </si>
   <si>
-    <t>진행 상황 로드에 실패했습니다.</t>
+    <t>진행 상황 로드에 실패했습니다</t>
   </si>
   <si>
-    <t>You have failed to load progress.</t>
+    <t>You have failed to load progress</t>
   </si>
   <si>
     <t>COMMON_SAVE_SUCCESS_MSG</t>
@@ -322,10 +334,10 @@
     <t>공용 저장 성공 메세지</t>
   </si>
   <si>
-    <t>진행 상황을 저장했습니다.</t>
+    <t>진행 상황을 저장했습니다</t>
   </si>
   <si>
-    <t>You have successfully saved progress.</t>
+    <t>You have successfully saved progress</t>
   </si>
   <si>
     <t>COMMON_SAVE_FAIL_MSG</t>
@@ -334,10 +346,10 @@
     <t>공용 저장 실패 메세지</t>
   </si>
   <si>
-    <t>진행 상황 저장에 실패했습니다.</t>
+    <t>진행 상황 저장에 실패했습니다</t>
   </si>
   <si>
-    <t>You have failed to save progress.</t>
+    <t>You have failed to save progress</t>
   </si>
   <si>
     <t>COMMON_PURCHASE_SUCCESS_MSG</t>
@@ -346,10 +358,10 @@
     <t>공용 결제 성공 메세지</t>
   </si>
   <si>
-    <t>해당 상품을 구입했습니다.</t>
+    <t>해당 상품을 구입했습니다</t>
   </si>
   <si>
-    <t>You have successfully purchased this product.</t>
+    <t>You have successfully purchased this product</t>
   </si>
   <si>
     <t>COMMON_PURCHASE_FAIL_MSG</t>
@@ -358,10 +370,10 @@
     <t>공용 결제 실패 메세지</t>
   </si>
   <si>
-    <t>해당 상품 구입에 실패했습니다.</t>
+    <t>해당 상품 구입에 실패했습니다</t>
   </si>
   <si>
-    <t>You have failed to purchase this product.</t>
+    <t>You have failed to purchase this product</t>
   </si>
   <si>
     <t>COMMON_RESTORE_SUCCESS_MSG</t>
@@ -370,10 +382,10 @@
     <t>공용 복원 성공 메세지</t>
   </si>
   <si>
-    <t>상품을 복원했습니다.</t>
+    <t>상품을 복원했습니다</t>
   </si>
   <si>
-    <t>The product has been restored.</t>
+    <t>The product has been restored</t>
   </si>
   <si>
     <t>COMMON_RESTORE_FAIL_MSG</t>
@@ -382,10 +394,10 @@
     <t>공용 복원 실패 메세지</t>
   </si>
   <si>
-    <t>상품 복원에 실패했습니다.</t>
+    <t>상품 복원에 실패했습니다</t>
   </si>
   <si>
-    <t>Failed to restore the product.</t>
+    <t>Failed to restore the product</t>
   </si>
   <si>
     <t>COMMON_OK_TEXT</t>
@@ -424,6 +436,18 @@
     <t>Agree</t>
   </si>
   <si>
+    <t>COMMON_RESULT_TEXT</t>
+  </si>
+  <si>
+    <t>공용 결과 텍스트</t>
+  </si>
+  <si>
+    <t>결과</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
     <t>COMMON_GET_TEXT</t>
   </si>
   <si>
@@ -436,6 +460,30 @@
     <t>Get</t>
   </si>
   <si>
+    <t>COMMON_STORE_TEXT</t>
+  </si>
+  <si>
+    <t>공용 상점 텍스트</t>
+  </si>
+  <si>
+    <t>상점</t>
+  </si>
+  <si>
+    <t>Store</t>
+  </si>
+  <si>
+    <t>COMMON_EVENT_TEXT</t>
+  </si>
+  <si>
+    <t>공용 이벤트 텍스트</t>
+  </si>
+  <si>
+    <t>이벤트</t>
+  </si>
+  <si>
+    <t>Event</t>
+  </si>
+  <si>
     <t>COMMON_NEXT_TEXT</t>
   </si>
   <si>
@@ -446,6 +494,42 @@
   </si>
   <si>
     <t>Next</t>
+  </si>
+  <si>
+    <t>COMMON_HOME_TEXT</t>
+  </si>
+  <si>
+    <t>공용 홈 텍스트</t>
+  </si>
+  <si>
+    <t>홈</t>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>COMMON_PLAY_TEXT</t>
+  </si>
+  <si>
+    <t>공용 플레이 텍스트</t>
+  </si>
+  <si>
+    <t>플레이</t>
+  </si>
+  <si>
+    <t>Play</t>
+  </si>
+  <si>
+    <t>COMMON_RETRY_TEXT</t>
+  </si>
+  <si>
+    <t>공용 재시도 텍스트</t>
+  </si>
+  <si>
+    <t>재시도</t>
+  </si>
+  <si>
+    <t>Retry</t>
   </si>
   <si>
     <t>COMMON_LEAVE_TEXT</t>
@@ -484,6 +568,30 @@
     <t>Login</t>
   </si>
   <si>
+    <t>COMMON_APPLE_LOGIN_TEXT</t>
+  </si>
+  <si>
+    <t>공용 애플 로그인 텍스트</t>
+  </si>
+  <si>
+    <t>애플 로그인</t>
+  </si>
+  <si>
+    <t>Sign in with Apple</t>
+  </si>
+  <si>
+    <t>COMMON_FACEBOOK_LOGIN_TEXT</t>
+  </si>
+  <si>
+    <t>공용 페이스 북 로그인</t>
+  </si>
+  <si>
+    <t>페이스 북 로그인</t>
+  </si>
+  <si>
+    <t>Sign in with Facebook</t>
+  </si>
+  <si>
     <t>COMMON_LOGOUT_TEXT</t>
   </si>
   <si>
@@ -494,6 +602,30 @@
   </si>
   <si>
     <t>Logout</t>
+  </si>
+  <si>
+    <t>COMMON_DISCONNECT_TEXT</t>
+  </si>
+  <si>
+    <t>공용 연결 해제 텍스트</t>
+  </si>
+  <si>
+    <t>연결 해제</t>
+  </si>
+  <si>
+    <t>Disconnect</t>
+  </si>
+  <si>
+    <t>COMMON_LOAD_TEXT</t>
+  </si>
+  <si>
+    <t>공용 로드 텍스트</t>
+  </si>
+  <si>
+    <t>불러오기</t>
+  </si>
+  <si>
+    <t>Load</t>
   </si>
   <si>
     <t>COMMON_SAVE_TEXT</t>
@@ -508,19 +640,19 @@
     <t>Save</t>
   </si>
   <si>
-    <t>COMMON_LOAD_TEXT</t>
+    <t>COMMON_CONTINUE_TEXT</t>
   </si>
   <si>
-    <t>공용 로드 텍스트</t>
+    <t>공용 이어하기 텍스트</t>
   </si>
   <si>
-    <t>불러오기</t>
+    <t>이어하기</t>
   </si>
   <si>
-    <t>Load</t>
+    <t>Continue</t>
   </si>
   <si>
-    <t>COMMON_NOTICE_TEXT</t>
+    <t>COMMON_NOTI_TEXT</t>
   </si>
   <si>
     <t>공용 알림 텍스트</t>
@@ -562,7 +694,7 @@
     <t>BGM</t>
   </si>
   <si>
-    <t>COMMON_FX_SND_TEXT</t>
+    <t>COMMON_FX_SNDS_TEXT</t>
   </si>
   <si>
     <t>공용 효과음 텍스트</t>
@@ -634,6 +766,42 @@
     <t>Chapter</t>
   </si>
   <si>
+    <t>COMMON_LEVEL_NUM_TEXT_FMT</t>
+  </si>
+  <si>
+    <t>공용 레벨 번호 텍스트 형식</t>
+  </si>
+  <si>
+    <t>레벨 {0}</t>
+  </si>
+  <si>
+    <t>Level {0}</t>
+  </si>
+  <si>
+    <t>COMMON_STAGE_NUM_TEXT_FMT</t>
+  </si>
+  <si>
+    <t>공용 스테이지 번호 텍스트 형식</t>
+  </si>
+  <si>
+    <t>스테이지 {0}</t>
+  </si>
+  <si>
+    <t>Stage {0}</t>
+  </si>
+  <si>
+    <t>COMMON_CHAPTER_NUM_TEXT_FMT</t>
+  </si>
+  <si>
+    <t>공용 챕터 번호 텍스트 형식</t>
+  </si>
+  <si>
+    <t>챕터 {0}</t>
+  </si>
+  <si>
+    <t>Chapter {0}</t>
+  </si>
+  <si>
     <t>COMMON_LEVEL_PAGE_TEXT_FMT</t>
   </si>
   <si>
@@ -674,12 +842,6 @@
   </si>
   <si>
     <t>상점 팝업 타이틀</t>
-  </si>
-  <si>
-    <t>상점</t>
-  </si>
-  <si>
-    <t>Store</t>
   </si>
   <si>
     <t>SETTINGS_P_TITLE</t>
@@ -747,6 +909,18 @@
   <si>
     <t>Sale Coins</t>
   </si>
+  <si>
+    <t>CONTINUE_P_TITLE</t>
+  </si>
+  <si>
+    <t>이어하기 팝업 타이틀</t>
+  </si>
+  <si>
+    <t>RESULT_P_TITLE</t>
+  </si>
+  <si>
+    <t>결과 팝업 제목</t>
+  </si>
 </sst>
 </file>
 
@@ -762,10 +936,10 @@
       <color theme="1"/>
       <name val="Arial"/>
     </font>
-    <font/>
     <font>
       <name val="Arial"/>
     </font>
+    <font/>
   </fonts>
   <fills count="6">
     <fill>
@@ -857,90 +1031,184 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="63">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="2" fillId="3" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="3" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf borderId="2" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="5" fillId="3" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="6" fillId="3" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="3" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="3" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf borderId="2" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="3" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="4" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="4" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="4" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="6" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="7" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="7" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="8" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="2" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="2" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="2" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="3" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="4" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="5" fillId="4" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="4" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="4" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="6" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="7" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="7" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="7" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="8" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="2" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="2" fillId="5" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="5" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="5" fillId="5" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="5" fillId="5" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="6" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="5" fillId="5" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="7" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="7" fillId="5" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="5" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="6" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="7" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="7" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="7" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="7" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="8" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1157,8 +1425,8 @@
     <col customWidth="1" min="1" max="1" width="37.71"/>
     <col customWidth="1" min="2" max="2" width="14.43"/>
     <col customWidth="1" min="3" max="3" width="29.0"/>
-    <col customWidth="1" min="4" max="4" width="59.14"/>
-    <col customWidth="1" min="5" max="5" width="54.71"/>
+    <col customWidth="1" min="4" max="4" width="98.14"/>
+    <col customWidth="1" min="5" max="5" width="112.0"/>
     <col customWidth="1" min="6" max="6" width="14.43"/>
   </cols>
   <sheetData>
@@ -1207,2842 +1475,3000 @@
       <c r="B2" s="4">
         <v>0.0</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="4"/>
-      <c r="Z2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+      <c r="U2" s="5"/>
+      <c r="V2" s="5"/>
+      <c r="W2" s="5"/>
+      <c r="X2" s="5"/>
+      <c r="Y2" s="5"/>
+      <c r="Z2" s="6"/>
     </row>
     <row r="3" ht="15.0" customHeight="1">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="8">
         <v>0.0</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
-      <c r="U3" s="7"/>
-      <c r="V3" s="7"/>
-      <c r="W3" s="7"/>
-      <c r="X3" s="7"/>
-      <c r="Y3" s="7"/>
-      <c r="Z3" s="9"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="10"/>
+      <c r="U3" s="10"/>
+      <c r="V3" s="10"/>
+      <c r="W3" s="10"/>
+      <c r="X3" s="10"/>
+      <c r="Y3" s="10"/>
+      <c r="Z3" s="11"/>
     </row>
     <row r="4" ht="15.0" customHeight="1">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="8">
         <v>0.0</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="7"/>
-      <c r="T4" s="7"/>
-      <c r="U4" s="7"/>
-      <c r="V4" s="7"/>
-      <c r="W4" s="7"/>
-      <c r="X4" s="7"/>
-      <c r="Y4" s="7"/>
-      <c r="Z4" s="9"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
+      <c r="S4" s="10"/>
+      <c r="T4" s="10"/>
+      <c r="U4" s="10"/>
+      <c r="V4" s="10"/>
+      <c r="W4" s="10"/>
+      <c r="X4" s="10"/>
+      <c r="Y4" s="10"/>
+      <c r="Z4" s="11"/>
     </row>
     <row r="5" ht="15.0" customHeight="1">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="8">
         <v>0.0</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="7"/>
-      <c r="S5" s="7"/>
-      <c r="T5" s="7"/>
-      <c r="U5" s="7"/>
-      <c r="V5" s="7"/>
-      <c r="W5" s="7"/>
-      <c r="X5" s="7"/>
-      <c r="Y5" s="7"/>
-      <c r="Z5" s="9"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="10"/>
+      <c r="S5" s="10"/>
+      <c r="T5" s="10"/>
+      <c r="U5" s="10"/>
+      <c r="V5" s="10"/>
+      <c r="W5" s="10"/>
+      <c r="X5" s="10"/>
+      <c r="Y5" s="10"/>
+      <c r="Z5" s="11"/>
     </row>
     <row r="6" ht="15.0" customHeight="1">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="8">
         <v>0.0</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="7"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="7"/>
-      <c r="T6" s="7"/>
-      <c r="U6" s="7"/>
-      <c r="V6" s="7"/>
-      <c r="W6" s="7"/>
-      <c r="X6" s="7"/>
-      <c r="Y6" s="7"/>
-      <c r="Z6" s="9"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="10"/>
+      <c r="R6" s="10"/>
+      <c r="S6" s="10"/>
+      <c r="T6" s="10"/>
+      <c r="U6" s="10"/>
+      <c r="V6" s="10"/>
+      <c r="W6" s="10"/>
+      <c r="X6" s="10"/>
+      <c r="Y6" s="10"/>
+      <c r="Z6" s="11"/>
     </row>
     <row r="7" ht="15.0" customHeight="1">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="8">
         <v>0.0</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="7"/>
-      <c r="R7" s="7"/>
-      <c r="S7" s="7"/>
-      <c r="T7" s="7"/>
-      <c r="U7" s="7"/>
-      <c r="V7" s="7"/>
-      <c r="W7" s="7"/>
-      <c r="X7" s="7"/>
-      <c r="Y7" s="7"/>
-      <c r="Z7" s="9"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="10"/>
+      <c r="S7" s="10"/>
+      <c r="T7" s="10"/>
+      <c r="U7" s="10"/>
+      <c r="V7" s="10"/>
+      <c r="W7" s="10"/>
+      <c r="X7" s="10"/>
+      <c r="Y7" s="10"/>
+      <c r="Z7" s="11"/>
     </row>
     <row r="8" ht="15.0" customHeight="1">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="13">
         <v>0.0</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
-      <c r="P8" s="7"/>
-      <c r="Q8" s="7"/>
-      <c r="R8" s="7"/>
-      <c r="S8" s="7"/>
-      <c r="T8" s="7"/>
-      <c r="U8" s="7"/>
-      <c r="V8" s="7"/>
-      <c r="W8" s="7"/>
-      <c r="X8" s="7"/>
-      <c r="Y8" s="7"/>
-      <c r="Z8" s="9"/>
+      <c r="D8" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10"/>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="10"/>
+      <c r="S8" s="10"/>
+      <c r="T8" s="10"/>
+      <c r="U8" s="10"/>
+      <c r="V8" s="10"/>
+      <c r="W8" s="10"/>
+      <c r="X8" s="10"/>
+      <c r="Y8" s="10"/>
+      <c r="Z8" s="15"/>
     </row>
     <row r="9" ht="15.0" customHeight="1">
-      <c r="A9" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="8">
+      <c r="A9" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="13">
         <v>0.0</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7"/>
-      <c r="P9" s="7"/>
-      <c r="Q9" s="7"/>
-      <c r="R9" s="7"/>
-      <c r="S9" s="7"/>
-      <c r="T9" s="7"/>
-      <c r="U9" s="7"/>
-      <c r="V9" s="7"/>
-      <c r="W9" s="7"/>
-      <c r="X9" s="7"/>
-      <c r="Y9" s="7"/>
-      <c r="Z9" s="9"/>
+      <c r="C9" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="10"/>
+      <c r="R9" s="10"/>
+      <c r="S9" s="10"/>
+      <c r="T9" s="10"/>
+      <c r="U9" s="10"/>
+      <c r="V9" s="10"/>
+      <c r="W9" s="10"/>
+      <c r="X9" s="10"/>
+      <c r="Y9" s="10"/>
+      <c r="Z9" s="15"/>
     </row>
     <row r="10" ht="15.0" customHeight="1">
-      <c r="A10" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="7">
+      <c r="A10" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="8">
         <v>0.0</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
-      <c r="O10" s="7"/>
-      <c r="P10" s="7"/>
-      <c r="Q10" s="7"/>
-      <c r="R10" s="7"/>
-      <c r="S10" s="7"/>
-      <c r="T10" s="7"/>
-      <c r="U10" s="7"/>
-      <c r="V10" s="7"/>
-      <c r="W10" s="7"/>
-      <c r="X10" s="7"/>
-      <c r="Y10" s="7"/>
-      <c r="Z10" s="9"/>
+      <c r="C10" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="10"/>
+      <c r="S10" s="10"/>
+      <c r="T10" s="10"/>
+      <c r="U10" s="10"/>
+      <c r="V10" s="10"/>
+      <c r="W10" s="10"/>
+      <c r="X10" s="10"/>
+      <c r="Y10" s="10"/>
+      <c r="Z10" s="11"/>
     </row>
     <row r="11" ht="15.0" customHeight="1">
-      <c r="A11" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" s="7">
+      <c r="A11" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="8">
         <v>0.0</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E11" s="7" t="s">
+      <c r="C11" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="10"/>
+      <c r="P11" s="10"/>
+      <c r="Q11" s="10"/>
+      <c r="R11" s="10"/>
+      <c r="S11" s="10"/>
+      <c r="T11" s="10"/>
+      <c r="U11" s="10"/>
+      <c r="V11" s="10"/>
+      <c r="W11" s="10"/>
+      <c r="X11" s="10"/>
+      <c r="Y11" s="10"/>
+      <c r="Z11" s="11"/>
+    </row>
+    <row r="12" ht="15.0" customHeight="1">
+      <c r="A12" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="10"/>
+      <c r="P12" s="10"/>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="10"/>
+      <c r="S12" s="10"/>
+      <c r="T12" s="10"/>
+      <c r="U12" s="10"/>
+      <c r="V12" s="10"/>
+      <c r="W12" s="10"/>
+      <c r="X12" s="10"/>
+      <c r="Y12" s="10"/>
+      <c r="Z12" s="11"/>
+    </row>
+    <row r="13" ht="15.0" customHeight="1">
+      <c r="A13" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="10"/>
+      <c r="P13" s="10"/>
+      <c r="Q13" s="10"/>
+      <c r="R13" s="10"/>
+      <c r="S13" s="10"/>
+      <c r="T13" s="10"/>
+      <c r="U13" s="10"/>
+      <c r="V13" s="10"/>
+      <c r="W13" s="10"/>
+      <c r="X13" s="10"/>
+      <c r="Y13" s="10"/>
+      <c r="Z13" s="11"/>
+    </row>
+    <row r="14" ht="15.0" customHeight="1">
+      <c r="A14" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="10"/>
+      <c r="R14" s="10"/>
+      <c r="S14" s="10"/>
+      <c r="T14" s="10"/>
+      <c r="U14" s="10"/>
+      <c r="V14" s="10"/>
+      <c r="W14" s="10"/>
+      <c r="X14" s="10"/>
+      <c r="Y14" s="10"/>
+      <c r="Z14" s="11"/>
+    </row>
+    <row r="15" ht="15.0" customHeight="1">
+      <c r="A15" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="7"/>
-      <c r="O11" s="7"/>
-      <c r="P11" s="7"/>
-      <c r="Q11" s="7"/>
-      <c r="R11" s="7"/>
-      <c r="S11" s="7"/>
-      <c r="T11" s="7"/>
-      <c r="U11" s="7"/>
-      <c r="V11" s="7"/>
-      <c r="W11" s="7"/>
-      <c r="X11" s="7"/>
-      <c r="Y11" s="7"/>
-      <c r="Z11" s="9"/>
-    </row>
-    <row r="12" ht="15.0" customHeight="1">
-      <c r="A12" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="7">
+      <c r="E15" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="10"/>
+      <c r="P15" s="10"/>
+      <c r="Q15" s="10"/>
+      <c r="R15" s="10"/>
+      <c r="S15" s="10"/>
+      <c r="T15" s="10"/>
+      <c r="U15" s="10"/>
+      <c r="V15" s="10"/>
+      <c r="W15" s="10"/>
+      <c r="X15" s="10"/>
+      <c r="Y15" s="10"/>
+      <c r="Z15" s="11"/>
+    </row>
+    <row r="16" ht="15.0" customHeight="1">
+      <c r="A16" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" s="8">
         <v>0.0</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
-      <c r="P12" s="7"/>
-      <c r="Q12" s="7"/>
-      <c r="R12" s="7"/>
-      <c r="S12" s="7"/>
-      <c r="T12" s="7"/>
-      <c r="U12" s="7"/>
-      <c r="V12" s="7"/>
-      <c r="W12" s="7"/>
-      <c r="X12" s="7"/>
-      <c r="Y12" s="7"/>
-      <c r="Z12" s="9"/>
-    </row>
-    <row r="13" ht="15.0" customHeight="1">
-      <c r="A13" s="10" t="s">
+      <c r="C16" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="7">
+      <c r="E16" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="10"/>
+      <c r="O16" s="10"/>
+      <c r="P16" s="10"/>
+      <c r="Q16" s="10"/>
+      <c r="R16" s="10"/>
+      <c r="S16" s="10"/>
+      <c r="T16" s="10"/>
+      <c r="U16" s="10"/>
+      <c r="V16" s="10"/>
+      <c r="W16" s="10"/>
+      <c r="X16" s="10"/>
+      <c r="Y16" s="10"/>
+      <c r="Z16" s="11"/>
+    </row>
+    <row r="17" ht="15.0" customHeight="1">
+      <c r="A17" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17" s="8">
         <v>0.0</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="7"/>
-      <c r="R13" s="7"/>
-      <c r="S13" s="7"/>
-      <c r="T13" s="7"/>
-      <c r="U13" s="7"/>
-      <c r="V13" s="7"/>
-      <c r="W13" s="7"/>
-      <c r="X13" s="7"/>
-      <c r="Y13" s="7"/>
-      <c r="Z13" s="9"/>
-    </row>
-    <row r="14" ht="15.0" customHeight="1">
-      <c r="A14" s="10" t="s">
+      <c r="C17" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B14" s="7">
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="10"/>
+      <c r="P17" s="10"/>
+      <c r="Q17" s="10"/>
+      <c r="R17" s="10"/>
+      <c r="S17" s="10"/>
+      <c r="T17" s="10"/>
+      <c r="U17" s="10"/>
+      <c r="V17" s="10"/>
+      <c r="W17" s="10"/>
+      <c r="X17" s="10"/>
+      <c r="Y17" s="10"/>
+      <c r="Z17" s="11"/>
+    </row>
+    <row r="18" ht="15.0" customHeight="1">
+      <c r="A18" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="8">
         <v>0.0</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
-      <c r="O14" s="7"/>
-      <c r="P14" s="7"/>
-      <c r="Q14" s="7"/>
-      <c r="R14" s="7"/>
-      <c r="S14" s="7"/>
-      <c r="T14" s="7"/>
-      <c r="U14" s="7"/>
-      <c r="V14" s="7"/>
-      <c r="W14" s="7"/>
-      <c r="X14" s="7"/>
-      <c r="Y14" s="7"/>
-      <c r="Z14" s="9"/>
-    </row>
-    <row r="15" ht="15.0" customHeight="1">
-      <c r="A15" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" s="7">
+      <c r="C18" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="10"/>
+      <c r="P18" s="10"/>
+      <c r="Q18" s="10"/>
+      <c r="R18" s="10"/>
+      <c r="S18" s="10"/>
+      <c r="T18" s="10"/>
+      <c r="U18" s="10"/>
+      <c r="V18" s="10"/>
+      <c r="W18" s="10"/>
+      <c r="X18" s="10"/>
+      <c r="Y18" s="10"/>
+      <c r="Z18" s="11"/>
+    </row>
+    <row r="19" ht="15.0" customHeight="1">
+      <c r="A19" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="B19" s="8">
         <v>0.0</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
-      <c r="P15" s="7"/>
-      <c r="Q15" s="7"/>
-      <c r="R15" s="7"/>
-      <c r="S15" s="7"/>
-      <c r="T15" s="7"/>
-      <c r="U15" s="7"/>
-      <c r="V15" s="7"/>
-      <c r="W15" s="7"/>
-      <c r="X15" s="7"/>
-      <c r="Y15" s="7"/>
-      <c r="Z15" s="9"/>
-    </row>
-    <row r="16" ht="15.0" customHeight="1">
-      <c r="A16" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B16" s="7">
+      <c r="C19" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="10"/>
+      <c r="O19" s="10"/>
+      <c r="P19" s="10"/>
+      <c r="Q19" s="10"/>
+      <c r="R19" s="10"/>
+      <c r="S19" s="10"/>
+      <c r="T19" s="10"/>
+      <c r="U19" s="10"/>
+      <c r="V19" s="10"/>
+      <c r="W19" s="10"/>
+      <c r="X19" s="10"/>
+      <c r="Y19" s="10"/>
+      <c r="Z19" s="11"/>
+    </row>
+    <row r="20" ht="15.0" customHeight="1">
+      <c r="A20" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="8">
         <v>0.0</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="7"/>
-      <c r="Q16" s="7"/>
-      <c r="R16" s="7"/>
-      <c r="S16" s="7"/>
-      <c r="T16" s="7"/>
-      <c r="U16" s="7"/>
-      <c r="V16" s="7"/>
-      <c r="W16" s="7"/>
-      <c r="X16" s="7"/>
-      <c r="Y16" s="7"/>
-      <c r="Z16" s="9"/>
-    </row>
-    <row r="17" ht="15.0" customHeight="1">
-      <c r="A17" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="B17" s="7">
+      <c r="C20" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="10"/>
+      <c r="R20" s="10"/>
+      <c r="S20" s="10"/>
+      <c r="T20" s="10"/>
+      <c r="U20" s="10"/>
+      <c r="V20" s="10"/>
+      <c r="W20" s="10"/>
+      <c r="X20" s="10"/>
+      <c r="Y20" s="10"/>
+      <c r="Z20" s="11"/>
+    </row>
+    <row r="21" ht="15.0" customHeight="1">
+      <c r="A21" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" s="8">
         <v>0.0</v>
       </c>
-      <c r="C17" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="7"/>
-      <c r="O17" s="7"/>
-      <c r="P17" s="7"/>
-      <c r="Q17" s="7"/>
-      <c r="R17" s="7"/>
-      <c r="S17" s="7"/>
-      <c r="T17" s="7"/>
-      <c r="U17" s="7"/>
-      <c r="V17" s="7"/>
-      <c r="W17" s="7"/>
-      <c r="X17" s="7"/>
-      <c r="Y17" s="7"/>
-      <c r="Z17" s="9"/>
-    </row>
-    <row r="18" ht="15.0" customHeight="1">
-      <c r="A18" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="B18" s="7">
+      <c r="C21" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="10"/>
+      <c r="P21" s="10"/>
+      <c r="Q21" s="10"/>
+      <c r="R21" s="10"/>
+      <c r="S21" s="10"/>
+      <c r="T21" s="10"/>
+      <c r="U21" s="10"/>
+      <c r="V21" s="10"/>
+      <c r="W21" s="10"/>
+      <c r="X21" s="10"/>
+      <c r="Y21" s="10"/>
+      <c r="Z21" s="11"/>
+    </row>
+    <row r="22" ht="15.0" customHeight="1">
+      <c r="A22" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="B22" s="18">
         <v>0.0</v>
       </c>
-      <c r="C18" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E18" s="7" t="s">
+      <c r="C22" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="19"/>
+      <c r="L22" s="19"/>
+      <c r="M22" s="19"/>
+      <c r="N22" s="19"/>
+      <c r="O22" s="19"/>
+      <c r="P22" s="19"/>
+      <c r="Q22" s="19"/>
+      <c r="R22" s="19"/>
+      <c r="S22" s="19"/>
+      <c r="T22" s="19"/>
+      <c r="U22" s="19"/>
+      <c r="V22" s="19"/>
+      <c r="W22" s="19"/>
+      <c r="X22" s="19"/>
+      <c r="Y22" s="19"/>
+      <c r="Z22" s="20"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="B23" s="22">
+        <v>0.0</v>
+      </c>
+      <c r="C23" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="D23" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="E23" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="F23" s="24"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="24"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="24"/>
+      <c r="M23" s="24"/>
+      <c r="N23" s="24"/>
+      <c r="O23" s="24"/>
+      <c r="P23" s="24"/>
+      <c r="Q23" s="24"/>
+      <c r="R23" s="24"/>
+      <c r="S23" s="24"/>
+      <c r="T23" s="24"/>
+      <c r="U23" s="24"/>
+      <c r="V23" s="24"/>
+      <c r="W23" s="24"/>
+      <c r="X23" s="24"/>
+      <c r="Y23" s="24"/>
+      <c r="Z23" s="25"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B24" s="27">
+        <v>0.0</v>
+      </c>
+      <c r="C24" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="D24" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="E24" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="F24" s="29"/>
+      <c r="G24" s="29"/>
+      <c r="H24" s="29"/>
+      <c r="I24" s="29"/>
+      <c r="J24" s="29"/>
+      <c r="K24" s="29"/>
+      <c r="L24" s="29"/>
+      <c r="M24" s="29"/>
+      <c r="N24" s="29"/>
+      <c r="O24" s="29"/>
+      <c r="P24" s="29"/>
+      <c r="Q24" s="29"/>
+      <c r="R24" s="29"/>
+      <c r="S24" s="29"/>
+      <c r="T24" s="29"/>
+      <c r="U24" s="29"/>
+      <c r="V24" s="29"/>
+      <c r="W24" s="29"/>
+      <c r="X24" s="29"/>
+      <c r="Y24" s="29"/>
+      <c r="Z24" s="30"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B25" s="27">
+        <v>0.0</v>
+      </c>
+      <c r="C25" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="D25" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="E25" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29"/>
+      <c r="I25" s="29"/>
+      <c r="J25" s="29"/>
+      <c r="K25" s="29"/>
+      <c r="L25" s="29"/>
+      <c r="M25" s="29"/>
+      <c r="N25" s="29"/>
+      <c r="O25" s="29"/>
+      <c r="P25" s="29"/>
+      <c r="Q25" s="29"/>
+      <c r="R25" s="29"/>
+      <c r="S25" s="29"/>
+      <c r="T25" s="29"/>
+      <c r="U25" s="29"/>
+      <c r="V25" s="29"/>
+      <c r="W25" s="29"/>
+      <c r="X25" s="29"/>
+      <c r="Y25" s="29"/>
+      <c r="Z25" s="30"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="B26" s="27">
+        <v>0.0</v>
+      </c>
+      <c r="C26" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="D26" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="E26" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="F26" s="29"/>
+      <c r="G26" s="29"/>
+      <c r="H26" s="29"/>
+      <c r="I26" s="29"/>
+      <c r="J26" s="29"/>
+      <c r="K26" s="29"/>
+      <c r="L26" s="29"/>
+      <c r="M26" s="29"/>
+      <c r="N26" s="29"/>
+      <c r="O26" s="29"/>
+      <c r="P26" s="29"/>
+      <c r="Q26" s="29"/>
+      <c r="R26" s="29"/>
+      <c r="S26" s="29"/>
+      <c r="T26" s="29"/>
+      <c r="U26" s="29"/>
+      <c r="V26" s="29"/>
+      <c r="W26" s="29"/>
+      <c r="X26" s="29"/>
+      <c r="Y26" s="29"/>
+      <c r="Z26" s="30"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="B27" s="27">
+        <v>0.0</v>
+      </c>
+      <c r="C27" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="D27" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="E27" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29"/>
+      <c r="I27" s="29"/>
+      <c r="J27" s="29"/>
+      <c r="K27" s="29"/>
+      <c r="L27" s="29"/>
+      <c r="M27" s="29"/>
+      <c r="N27" s="29"/>
+      <c r="O27" s="29"/>
+      <c r="P27" s="29"/>
+      <c r="Q27" s="29"/>
+      <c r="R27" s="29"/>
+      <c r="S27" s="29"/>
+      <c r="T27" s="29"/>
+      <c r="U27" s="29"/>
+      <c r="V27" s="29"/>
+      <c r="W27" s="29"/>
+      <c r="X27" s="29"/>
+      <c r="Y27" s="29"/>
+      <c r="Z27" s="30"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="B28" s="27">
+        <v>0.0</v>
+      </c>
+      <c r="C28" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="D28" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="E28" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="29"/>
+      <c r="I28" s="29"/>
+      <c r="J28" s="29"/>
+      <c r="K28" s="29"/>
+      <c r="L28" s="29"/>
+      <c r="M28" s="29"/>
+      <c r="N28" s="29"/>
+      <c r="O28" s="29"/>
+      <c r="P28" s="29"/>
+      <c r="Q28" s="29"/>
+      <c r="R28" s="29"/>
+      <c r="S28" s="29"/>
+      <c r="T28" s="29"/>
+      <c r="U28" s="29"/>
+      <c r="V28" s="29"/>
+      <c r="W28" s="29"/>
+      <c r="X28" s="29"/>
+      <c r="Y28" s="29"/>
+      <c r="Z28" s="30"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="B29" s="27">
+        <v>0.0</v>
+      </c>
+      <c r="C29" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="D29" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="E29" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="F29" s="29"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="29"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="29"/>
+      <c r="K29" s="29"/>
+      <c r="L29" s="29"/>
+      <c r="M29" s="29"/>
+      <c r="N29" s="29"/>
+      <c r="O29" s="29"/>
+      <c r="P29" s="29"/>
+      <c r="Q29" s="29"/>
+      <c r="R29" s="29"/>
+      <c r="S29" s="29"/>
+      <c r="T29" s="29"/>
+      <c r="U29" s="29"/>
+      <c r="V29" s="29"/>
+      <c r="W29" s="29"/>
+      <c r="X29" s="29"/>
+      <c r="Y29" s="29"/>
+      <c r="Z29" s="30"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="B30" s="27">
+        <v>0.0</v>
+      </c>
+      <c r="C30" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="D30" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="E30" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="29"/>
+      <c r="I30" s="29"/>
+      <c r="J30" s="29"/>
+      <c r="K30" s="29"/>
+      <c r="L30" s="29"/>
+      <c r="M30" s="29"/>
+      <c r="N30" s="29"/>
+      <c r="O30" s="29"/>
+      <c r="P30" s="29"/>
+      <c r="Q30" s="29"/>
+      <c r="R30" s="29"/>
+      <c r="S30" s="29"/>
+      <c r="T30" s="29"/>
+      <c r="U30" s="29"/>
+      <c r="V30" s="29"/>
+      <c r="W30" s="29"/>
+      <c r="X30" s="29"/>
+      <c r="Y30" s="29"/>
+      <c r="Z30" s="30"/>
+    </row>
+    <row r="31" ht="15.0" customHeight="1">
+      <c r="A31" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="B31" s="31">
+        <v>0.0</v>
+      </c>
+      <c r="C31" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="D31" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="E31" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="F31" s="32"/>
+      <c r="G31" s="32"/>
+      <c r="H31" s="32"/>
+      <c r="I31" s="32"/>
+      <c r="J31" s="32"/>
+      <c r="K31" s="32"/>
+      <c r="L31" s="32"/>
+      <c r="M31" s="32"/>
+      <c r="N31" s="32"/>
+      <c r="O31" s="32"/>
+      <c r="P31" s="32"/>
+      <c r="Q31" s="32"/>
+      <c r="R31" s="32"/>
+      <c r="S31" s="32"/>
+      <c r="T31" s="32"/>
+      <c r="U31" s="32"/>
+      <c r="V31" s="32"/>
+      <c r="W31" s="32"/>
+      <c r="X31" s="32"/>
+      <c r="Y31" s="32"/>
+      <c r="Z31" s="30"/>
+    </row>
+    <row r="32" ht="15.0" customHeight="1">
+      <c r="A32" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="B32" s="31">
+        <v>0.0</v>
+      </c>
+      <c r="C32" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="D32" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="E32" s="32" t="s">
+        <v>120</v>
+      </c>
+      <c r="F32" s="32"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="32"/>
+      <c r="J32" s="32"/>
+      <c r="K32" s="32"/>
+      <c r="L32" s="32"/>
+      <c r="M32" s="32"/>
+      <c r="N32" s="32"/>
+      <c r="O32" s="32"/>
+      <c r="P32" s="32"/>
+      <c r="Q32" s="32"/>
+      <c r="R32" s="32"/>
+      <c r="S32" s="32"/>
+      <c r="T32" s="32"/>
+      <c r="U32" s="32"/>
+      <c r="V32" s="32"/>
+      <c r="W32" s="32"/>
+      <c r="X32" s="32"/>
+      <c r="Y32" s="32"/>
+      <c r="Z32" s="30"/>
+    </row>
+    <row r="33" ht="15.0" customHeight="1">
+      <c r="A33" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="B33" s="31">
+        <v>0.0</v>
+      </c>
+      <c r="C33" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="D33" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="E33" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="F33" s="32"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="32"/>
+      <c r="J33" s="32"/>
+      <c r="K33" s="32"/>
+      <c r="L33" s="32"/>
+      <c r="M33" s="32"/>
+      <c r="N33" s="32"/>
+      <c r="O33" s="32"/>
+      <c r="P33" s="32"/>
+      <c r="Q33" s="32"/>
+      <c r="R33" s="32"/>
+      <c r="S33" s="32"/>
+      <c r="T33" s="32"/>
+      <c r="U33" s="32"/>
+      <c r="V33" s="32"/>
+      <c r="W33" s="32"/>
+      <c r="X33" s="32"/>
+      <c r="Y33" s="32"/>
+      <c r="Z33" s="30"/>
+    </row>
+    <row r="34" ht="15.0" customHeight="1">
+      <c r="A34" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="B34" s="31">
+        <v>0.0</v>
+      </c>
+      <c r="C34" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="D34" s="32" t="s">
+        <v>127</v>
+      </c>
+      <c r="E34" s="32" t="s">
+        <v>128</v>
+      </c>
+      <c r="F34" s="32"/>
+      <c r="G34" s="32"/>
+      <c r="H34" s="32"/>
+      <c r="I34" s="32"/>
+      <c r="J34" s="32"/>
+      <c r="K34" s="32"/>
+      <c r="L34" s="32"/>
+      <c r="M34" s="32"/>
+      <c r="N34" s="32"/>
+      <c r="O34" s="32"/>
+      <c r="P34" s="32"/>
+      <c r="Q34" s="32"/>
+      <c r="R34" s="32"/>
+      <c r="S34" s="32"/>
+      <c r="T34" s="32"/>
+      <c r="U34" s="32"/>
+      <c r="V34" s="32"/>
+      <c r="W34" s="32"/>
+      <c r="X34" s="32"/>
+      <c r="Y34" s="32"/>
+      <c r="Z34" s="30"/>
+    </row>
+    <row r="35" ht="15.0" customHeight="1">
+      <c r="A35" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="B35" s="31">
+        <v>0.0</v>
+      </c>
+      <c r="C35" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="D35" s="32" t="s">
+        <v>131</v>
+      </c>
+      <c r="E35" s="32" t="s">
+        <v>132</v>
+      </c>
+      <c r="F35" s="32"/>
+      <c r="G35" s="32"/>
+      <c r="H35" s="32"/>
+      <c r="I35" s="32"/>
+      <c r="J35" s="32"/>
+      <c r="K35" s="32"/>
+      <c r="L35" s="32"/>
+      <c r="M35" s="32"/>
+      <c r="N35" s="32"/>
+      <c r="O35" s="32"/>
+      <c r="P35" s="32"/>
+      <c r="Q35" s="32"/>
+      <c r="R35" s="32"/>
+      <c r="S35" s="32"/>
+      <c r="T35" s="32"/>
+      <c r="U35" s="32"/>
+      <c r="V35" s="32"/>
+      <c r="W35" s="32"/>
+      <c r="X35" s="32"/>
+      <c r="Y35" s="32"/>
+      <c r="Z35" s="30"/>
+    </row>
+    <row r="36" ht="15.0" customHeight="1">
+      <c r="A36" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="B36" s="31">
+        <v>0.0</v>
+      </c>
+      <c r="C36" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="D36" s="32" t="s">
+        <v>135</v>
+      </c>
+      <c r="E36" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="32"/>
+      <c r="I36" s="32"/>
+      <c r="J36" s="32"/>
+      <c r="K36" s="32"/>
+      <c r="L36" s="32"/>
+      <c r="M36" s="32"/>
+      <c r="N36" s="32"/>
+      <c r="O36" s="32"/>
+      <c r="P36" s="32"/>
+      <c r="Q36" s="32"/>
+      <c r="R36" s="32"/>
+      <c r="S36" s="32"/>
+      <c r="T36" s="32"/>
+      <c r="U36" s="32"/>
+      <c r="V36" s="32"/>
+      <c r="W36" s="32"/>
+      <c r="X36" s="32"/>
+      <c r="Y36" s="32"/>
+      <c r="Z36" s="30"/>
+    </row>
+    <row r="37" ht="15.0" customHeight="1">
+      <c r="A37" s="26" t="s">
+        <v>137</v>
+      </c>
+      <c r="B37" s="31">
+        <v>0.0</v>
+      </c>
+      <c r="C37" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="D37" s="32" t="s">
+        <v>139</v>
+      </c>
+      <c r="E37" s="32" t="s">
+        <v>140</v>
+      </c>
+      <c r="F37" s="32"/>
+      <c r="G37" s="32"/>
+      <c r="H37" s="32"/>
+      <c r="I37" s="32"/>
+      <c r="J37" s="32"/>
+      <c r="K37" s="32"/>
+      <c r="L37" s="32"/>
+      <c r="M37" s="32"/>
+      <c r="N37" s="32"/>
+      <c r="O37" s="32"/>
+      <c r="P37" s="32"/>
+      <c r="Q37" s="32"/>
+      <c r="R37" s="32"/>
+      <c r="S37" s="32"/>
+      <c r="T37" s="32"/>
+      <c r="U37" s="32"/>
+      <c r="V37" s="32"/>
+      <c r="W37" s="32"/>
+      <c r="X37" s="32"/>
+      <c r="Y37" s="32"/>
+      <c r="Z37" s="30"/>
+    </row>
+    <row r="38" ht="15.0" customHeight="1">
+      <c r="A38" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="B38" s="27">
+        <v>0.0</v>
+      </c>
+      <c r="C38" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="D38" s="28" t="s">
+        <v>143</v>
+      </c>
+      <c r="E38" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="F38" s="29"/>
+      <c r="G38" s="29"/>
+      <c r="H38" s="29"/>
+      <c r="I38" s="29"/>
+      <c r="J38" s="29"/>
+      <c r="K38" s="29"/>
+      <c r="L38" s="29"/>
+      <c r="M38" s="29"/>
+      <c r="N38" s="29"/>
+      <c r="O38" s="29"/>
+      <c r="P38" s="29"/>
+      <c r="Q38" s="29"/>
+      <c r="R38" s="29"/>
+      <c r="S38" s="29"/>
+      <c r="T38" s="29"/>
+      <c r="U38" s="29"/>
+      <c r="V38" s="29"/>
+      <c r="W38" s="29"/>
+      <c r="X38" s="29"/>
+      <c r="Y38" s="29"/>
+      <c r="Z38" s="30"/>
+    </row>
+    <row r="39" ht="15.0" customHeight="1">
+      <c r="A39" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="B39" s="27">
+        <v>0.0</v>
+      </c>
+      <c r="C39" s="28" t="s">
+        <v>146</v>
+      </c>
+      <c r="D39" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="E39" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="F39" s="29"/>
+      <c r="G39" s="29"/>
+      <c r="H39" s="29"/>
+      <c r="I39" s="29"/>
+      <c r="J39" s="29"/>
+      <c r="K39" s="29"/>
+      <c r="L39" s="29"/>
+      <c r="M39" s="29"/>
+      <c r="N39" s="29"/>
+      <c r="O39" s="29"/>
+      <c r="P39" s="29"/>
+      <c r="Q39" s="29"/>
+      <c r="R39" s="29"/>
+      <c r="S39" s="29"/>
+      <c r="T39" s="29"/>
+      <c r="U39" s="29"/>
+      <c r="V39" s="29"/>
+      <c r="W39" s="29"/>
+      <c r="X39" s="29"/>
+      <c r="Y39" s="29"/>
+      <c r="Z39" s="30"/>
+    </row>
+    <row r="40" ht="15.0" customHeight="1">
+      <c r="A40" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="B40" s="27">
+        <v>0.0</v>
+      </c>
+      <c r="C40" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="D40" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="E40" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="F40" s="29"/>
+      <c r="G40" s="29"/>
+      <c r="H40" s="29"/>
+      <c r="I40" s="29"/>
+      <c r="J40" s="29"/>
+      <c r="K40" s="29"/>
+      <c r="L40" s="29"/>
+      <c r="M40" s="29"/>
+      <c r="N40" s="29"/>
+      <c r="O40" s="29"/>
+      <c r="P40" s="29"/>
+      <c r="Q40" s="29"/>
+      <c r="R40" s="29"/>
+      <c r="S40" s="29"/>
+      <c r="T40" s="29"/>
+      <c r="U40" s="29"/>
+      <c r="V40" s="29"/>
+      <c r="W40" s="29"/>
+      <c r="X40" s="29"/>
+      <c r="Y40" s="29"/>
+      <c r="Z40" s="30"/>
+    </row>
+    <row r="41" ht="15.0" customHeight="1">
+      <c r="A41" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="B41" s="27">
+        <v>0.0</v>
+      </c>
+      <c r="C41" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="D41" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="E41" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="F41" s="29"/>
+      <c r="G41" s="29"/>
+      <c r="H41" s="29"/>
+      <c r="I41" s="29"/>
+      <c r="J41" s="29"/>
+      <c r="K41" s="29"/>
+      <c r="L41" s="29"/>
+      <c r="M41" s="29"/>
+      <c r="N41" s="29"/>
+      <c r="O41" s="29"/>
+      <c r="P41" s="29"/>
+      <c r="Q41" s="29"/>
+      <c r="R41" s="29"/>
+      <c r="S41" s="29"/>
+      <c r="T41" s="29"/>
+      <c r="U41" s="29"/>
+      <c r="V41" s="29"/>
+      <c r="W41" s="29"/>
+      <c r="X41" s="29"/>
+      <c r="Y41" s="29"/>
+      <c r="Z41" s="30"/>
+    </row>
+    <row r="42" ht="15.0" customHeight="1">
+      <c r="A42" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="B42" s="27">
+        <v>0.0</v>
+      </c>
+      <c r="C42" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="D42" s="28" t="s">
+        <v>159</v>
+      </c>
+      <c r="E42" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="F42" s="29"/>
+      <c r="G42" s="29"/>
+      <c r="H42" s="29"/>
+      <c r="I42" s="29"/>
+      <c r="J42" s="29"/>
+      <c r="K42" s="29"/>
+      <c r="L42" s="29"/>
+      <c r="M42" s="29"/>
+      <c r="N42" s="29"/>
+      <c r="O42" s="29"/>
+      <c r="P42" s="29"/>
+      <c r="Q42" s="29"/>
+      <c r="R42" s="29"/>
+      <c r="S42" s="29"/>
+      <c r="T42" s="29"/>
+      <c r="U42" s="29"/>
+      <c r="V42" s="29"/>
+      <c r="W42" s="29"/>
+      <c r="X42" s="29"/>
+      <c r="Y42" s="29"/>
+      <c r="Z42" s="30"/>
+    </row>
+    <row r="43" ht="15.0" customHeight="1">
+      <c r="A43" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="B43" s="27">
+        <v>0.0</v>
+      </c>
+      <c r="C43" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="D43" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="E43" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="F43" s="29"/>
+      <c r="G43" s="29"/>
+      <c r="H43" s="29"/>
+      <c r="I43" s="29"/>
+      <c r="J43" s="29"/>
+      <c r="K43" s="29"/>
+      <c r="L43" s="29"/>
+      <c r="M43" s="29"/>
+      <c r="N43" s="29"/>
+      <c r="O43" s="29"/>
+      <c r="P43" s="29"/>
+      <c r="Q43" s="29"/>
+      <c r="R43" s="29"/>
+      <c r="S43" s="29"/>
+      <c r="T43" s="29"/>
+      <c r="U43" s="29"/>
+      <c r="V43" s="29"/>
+      <c r="W43" s="29"/>
+      <c r="X43" s="29"/>
+      <c r="Y43" s="29"/>
+      <c r="Z43" s="30"/>
+    </row>
+    <row r="44" ht="15.0" customHeight="1">
+      <c r="A44" s="26" t="s">
+        <v>165</v>
+      </c>
+      <c r="B44" s="27">
+        <v>0.0</v>
+      </c>
+      <c r="C44" s="28" t="s">
+        <v>166</v>
+      </c>
+      <c r="D44" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="E44" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="F44" s="29"/>
+      <c r="G44" s="29"/>
+      <c r="H44" s="29"/>
+      <c r="I44" s="29"/>
+      <c r="J44" s="29"/>
+      <c r="K44" s="29"/>
+      <c r="L44" s="29"/>
+      <c r="M44" s="29"/>
+      <c r="N44" s="29"/>
+      <c r="O44" s="29"/>
+      <c r="P44" s="29"/>
+      <c r="Q44" s="29"/>
+      <c r="R44" s="29"/>
+      <c r="S44" s="29"/>
+      <c r="T44" s="29"/>
+      <c r="U44" s="29"/>
+      <c r="V44" s="29"/>
+      <c r="W44" s="29"/>
+      <c r="X44" s="29"/>
+      <c r="Y44" s="29"/>
+      <c r="Z44" s="30"/>
+    </row>
+    <row r="45" ht="15.0" customHeight="1">
+      <c r="A45" s="26" t="s">
+        <v>169</v>
+      </c>
+      <c r="B45" s="27">
+        <v>0.0</v>
+      </c>
+      <c r="C45" s="28" t="s">
+        <v>170</v>
+      </c>
+      <c r="D45" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="E45" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="F45" s="29"/>
+      <c r="G45" s="29"/>
+      <c r="H45" s="29"/>
+      <c r="I45" s="29"/>
+      <c r="J45" s="29"/>
+      <c r="K45" s="29"/>
+      <c r="L45" s="29"/>
+      <c r="M45" s="29"/>
+      <c r="N45" s="29"/>
+      <c r="O45" s="29"/>
+      <c r="P45" s="29"/>
+      <c r="Q45" s="29"/>
+      <c r="R45" s="29"/>
+      <c r="S45" s="29"/>
+      <c r="T45" s="29"/>
+      <c r="U45" s="29"/>
+      <c r="V45" s="29"/>
+      <c r="W45" s="29"/>
+      <c r="X45" s="29"/>
+      <c r="Y45" s="29"/>
+      <c r="Z45" s="30"/>
+    </row>
+    <row r="46" ht="15.0" customHeight="1">
+      <c r="A46" s="26" t="s">
+        <v>173</v>
+      </c>
+      <c r="B46" s="27">
+        <v>0.0</v>
+      </c>
+      <c r="C46" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="D46" s="28" t="s">
+        <v>175</v>
+      </c>
+      <c r="E46" s="28" t="s">
+        <v>176</v>
+      </c>
+      <c r="F46" s="29"/>
+      <c r="G46" s="29"/>
+      <c r="H46" s="29"/>
+      <c r="I46" s="29"/>
+      <c r="J46" s="29"/>
+      <c r="K46" s="29"/>
+      <c r="L46" s="29"/>
+      <c r="M46" s="29"/>
+      <c r="N46" s="29"/>
+      <c r="O46" s="29"/>
+      <c r="P46" s="29"/>
+      <c r="Q46" s="29"/>
+      <c r="R46" s="29"/>
+      <c r="S46" s="29"/>
+      <c r="T46" s="29"/>
+      <c r="U46" s="29"/>
+      <c r="V46" s="29"/>
+      <c r="W46" s="29"/>
+      <c r="X46" s="29"/>
+      <c r="Y46" s="29"/>
+      <c r="Z46" s="30"/>
+    </row>
+    <row r="47" ht="15.0" customHeight="1">
+      <c r="A47" s="26" t="s">
+        <v>177</v>
+      </c>
+      <c r="B47" s="27">
+        <v>0.0</v>
+      </c>
+      <c r="C47" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="D47" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="E47" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="F47" s="29"/>
+      <c r="G47" s="29"/>
+      <c r="H47" s="29"/>
+      <c r="I47" s="29"/>
+      <c r="J47" s="29"/>
+      <c r="K47" s="29"/>
+      <c r="L47" s="29"/>
+      <c r="M47" s="29"/>
+      <c r="N47" s="29"/>
+      <c r="O47" s="29"/>
+      <c r="P47" s="29"/>
+      <c r="Q47" s="29"/>
+      <c r="R47" s="29"/>
+      <c r="S47" s="29"/>
+      <c r="T47" s="29"/>
+      <c r="U47" s="29"/>
+      <c r="V47" s="29"/>
+      <c r="W47" s="29"/>
+      <c r="X47" s="29"/>
+      <c r="Y47" s="29"/>
+      <c r="Z47" s="30"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="26" t="s">
+        <v>181</v>
+      </c>
+      <c r="B48" s="27">
+        <v>0.0</v>
+      </c>
+      <c r="C48" s="28" t="s">
+        <v>182</v>
+      </c>
+      <c r="D48" s="28" t="s">
+        <v>183</v>
+      </c>
+      <c r="E48" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="F48" s="29"/>
+      <c r="G48" s="29"/>
+      <c r="H48" s="29"/>
+      <c r="I48" s="29"/>
+      <c r="J48" s="29"/>
+      <c r="K48" s="29"/>
+      <c r="L48" s="29"/>
+      <c r="M48" s="29"/>
+      <c r="N48" s="29"/>
+      <c r="O48" s="29"/>
+      <c r="P48" s="29"/>
+      <c r="Q48" s="29"/>
+      <c r="R48" s="29"/>
+      <c r="S48" s="29"/>
+      <c r="T48" s="29"/>
+      <c r="U48" s="29"/>
+      <c r="V48" s="29"/>
+      <c r="W48" s="29"/>
+      <c r="X48" s="29"/>
+      <c r="Y48" s="29"/>
+      <c r="Z48" s="30"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="B49" s="27">
+        <v>0.0</v>
+      </c>
+      <c r="C49" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="D49" s="28" t="s">
+        <v>187</v>
+      </c>
+      <c r="E49" s="28" t="s">
+        <v>188</v>
+      </c>
+      <c r="F49" s="29"/>
+      <c r="G49" s="29"/>
+      <c r="H49" s="29"/>
+      <c r="I49" s="29"/>
+      <c r="J49" s="29"/>
+      <c r="K49" s="29"/>
+      <c r="L49" s="29"/>
+      <c r="M49" s="29"/>
+      <c r="N49" s="29"/>
+      <c r="O49" s="29"/>
+      <c r="P49" s="29"/>
+      <c r="Q49" s="29"/>
+      <c r="R49" s="29"/>
+      <c r="S49" s="29"/>
+      <c r="T49" s="29"/>
+      <c r="U49" s="29"/>
+      <c r="V49" s="29"/>
+      <c r="W49" s="29"/>
+      <c r="X49" s="29"/>
+      <c r="Y49" s="29"/>
+      <c r="Z49" s="30"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="26" t="s">
+        <v>189</v>
+      </c>
+      <c r="B50" s="27">
+        <v>0.0</v>
+      </c>
+      <c r="C50" s="28" t="s">
+        <v>190</v>
+      </c>
+      <c r="D50" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="E50" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="F50" s="29"/>
+      <c r="G50" s="29"/>
+      <c r="H50" s="29"/>
+      <c r="I50" s="29"/>
+      <c r="J50" s="29"/>
+      <c r="K50" s="29"/>
+      <c r="L50" s="29"/>
+      <c r="M50" s="29"/>
+      <c r="N50" s="29"/>
+      <c r="O50" s="29"/>
+      <c r="P50" s="29"/>
+      <c r="Q50" s="29"/>
+      <c r="R50" s="29"/>
+      <c r="S50" s="29"/>
+      <c r="T50" s="29"/>
+      <c r="U50" s="29"/>
+      <c r="V50" s="29"/>
+      <c r="W50" s="29"/>
+      <c r="X50" s="29"/>
+      <c r="Y50" s="29"/>
+      <c r="Z50" s="30"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="26" t="s">
+        <v>193</v>
+      </c>
+      <c r="B51" s="27">
+        <v>0.0</v>
+      </c>
+      <c r="C51" s="28" t="s">
+        <v>194</v>
+      </c>
+      <c r="D51" s="28" t="s">
+        <v>195</v>
+      </c>
+      <c r="E51" s="28" t="s">
+        <v>196</v>
+      </c>
+      <c r="F51" s="29"/>
+      <c r="G51" s="29"/>
+      <c r="H51" s="29"/>
+      <c r="I51" s="29"/>
+      <c r="J51" s="29"/>
+      <c r="K51" s="29"/>
+      <c r="L51" s="29"/>
+      <c r="M51" s="29"/>
+      <c r="N51" s="29"/>
+      <c r="O51" s="29"/>
+      <c r="P51" s="29"/>
+      <c r="Q51" s="29"/>
+      <c r="R51" s="29"/>
+      <c r="S51" s="29"/>
+      <c r="T51" s="29"/>
+      <c r="U51" s="29"/>
+      <c r="V51" s="29"/>
+      <c r="W51" s="29"/>
+      <c r="X51" s="29"/>
+      <c r="Y51" s="29"/>
+      <c r="Z51" s="30"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="B52" s="27">
+        <v>0.0</v>
+      </c>
+      <c r="C52" s="28" t="s">
+        <v>198</v>
+      </c>
+      <c r="D52" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="E52" s="28" t="s">
+        <v>200</v>
+      </c>
+      <c r="F52" s="29"/>
+      <c r="G52" s="29"/>
+      <c r="H52" s="29"/>
+      <c r="I52" s="29"/>
+      <c r="J52" s="29"/>
+      <c r="K52" s="29"/>
+      <c r="L52" s="29"/>
+      <c r="M52" s="29"/>
+      <c r="N52" s="29"/>
+      <c r="O52" s="29"/>
+      <c r="P52" s="29"/>
+      <c r="Q52" s="29"/>
+      <c r="R52" s="29"/>
+      <c r="S52" s="29"/>
+      <c r="T52" s="29"/>
+      <c r="U52" s="29"/>
+      <c r="V52" s="29"/>
+      <c r="W52" s="29"/>
+      <c r="X52" s="29"/>
+      <c r="Y52" s="29"/>
+      <c r="Z52" s="30"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="26" t="s">
+        <v>201</v>
+      </c>
+      <c r="B53" s="27">
+        <v>0.0</v>
+      </c>
+      <c r="C53" s="28" t="s">
+        <v>202</v>
+      </c>
+      <c r="D53" s="28" t="s">
+        <v>203</v>
+      </c>
+      <c r="E53" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="F53" s="29"/>
+      <c r="G53" s="29"/>
+      <c r="H53" s="29"/>
+      <c r="I53" s="29"/>
+      <c r="J53" s="29"/>
+      <c r="K53" s="29"/>
+      <c r="L53" s="29"/>
+      <c r="M53" s="29"/>
+      <c r="N53" s="29"/>
+      <c r="O53" s="29"/>
+      <c r="P53" s="29"/>
+      <c r="Q53" s="29"/>
+      <c r="R53" s="29"/>
+      <c r="S53" s="29"/>
+      <c r="T53" s="29"/>
+      <c r="U53" s="29"/>
+      <c r="V53" s="29"/>
+      <c r="W53" s="29"/>
+      <c r="X53" s="29"/>
+      <c r="Y53" s="29"/>
+      <c r="Z53" s="30"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="26" t="s">
+        <v>205</v>
+      </c>
+      <c r="B54" s="27">
+        <v>0.0</v>
+      </c>
+      <c r="C54" s="28" t="s">
+        <v>206</v>
+      </c>
+      <c r="D54" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="E54" s="28" t="s">
+        <v>208</v>
+      </c>
+      <c r="F54" s="29"/>
+      <c r="G54" s="29"/>
+      <c r="H54" s="29"/>
+      <c r="I54" s="29"/>
+      <c r="J54" s="29"/>
+      <c r="K54" s="29"/>
+      <c r="L54" s="29"/>
+      <c r="M54" s="29"/>
+      <c r="N54" s="29"/>
+      <c r="O54" s="29"/>
+      <c r="P54" s="29"/>
+      <c r="Q54" s="29"/>
+      <c r="R54" s="29"/>
+      <c r="S54" s="29"/>
+      <c r="T54" s="29"/>
+      <c r="U54" s="29"/>
+      <c r="V54" s="29"/>
+      <c r="W54" s="29"/>
+      <c r="X54" s="29"/>
+      <c r="Y54" s="29"/>
+      <c r="Z54" s="30"/>
+    </row>
+    <row r="55" ht="15.0" customHeight="1">
+      <c r="A55" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="B55" s="27">
+        <v>0.0</v>
+      </c>
+      <c r="C55" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="D55" s="28" t="s">
+        <v>211</v>
+      </c>
+      <c r="E55" s="28" t="s">
+        <v>212</v>
+      </c>
+      <c r="F55" s="29"/>
+      <c r="G55" s="29"/>
+      <c r="H55" s="29"/>
+      <c r="I55" s="29"/>
+      <c r="J55" s="29"/>
+      <c r="K55" s="29"/>
+      <c r="L55" s="29"/>
+      <c r="M55" s="29"/>
+      <c r="N55" s="29"/>
+      <c r="O55" s="29"/>
+      <c r="P55" s="29"/>
+      <c r="Q55" s="29"/>
+      <c r="R55" s="29"/>
+      <c r="S55" s="29"/>
+      <c r="T55" s="29"/>
+      <c r="U55" s="29"/>
+      <c r="V55" s="29"/>
+      <c r="W55" s="29"/>
+      <c r="X55" s="29"/>
+      <c r="Y55" s="29"/>
+      <c r="Z55" s="30"/>
+    </row>
+    <row r="56" ht="15.0" customHeight="1">
+      <c r="A56" s="33" t="s">
+        <v>213</v>
+      </c>
+      <c r="B56" s="27">
+        <v>0.0</v>
+      </c>
+      <c r="C56" s="28" t="s">
+        <v>214</v>
+      </c>
+      <c r="D56" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="7"/>
-      <c r="O18" s="7"/>
-      <c r="P18" s="7"/>
-      <c r="Q18" s="7"/>
-      <c r="R18" s="7"/>
-      <c r="S18" s="7"/>
-      <c r="T18" s="7"/>
-      <c r="U18" s="7"/>
-      <c r="V18" s="7"/>
-      <c r="W18" s="7"/>
-      <c r="X18" s="7"/>
-      <c r="Y18" s="7"/>
-      <c r="Z18" s="9"/>
-    </row>
-    <row r="19" ht="15.0" customHeight="1">
-      <c r="A19" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="B19" s="7">
+      <c r="E56" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="F56" s="29"/>
+      <c r="G56" s="29"/>
+      <c r="H56" s="29"/>
+      <c r="I56" s="29"/>
+      <c r="J56" s="29"/>
+      <c r="K56" s="29"/>
+      <c r="L56" s="29"/>
+      <c r="M56" s="29"/>
+      <c r="N56" s="29"/>
+      <c r="O56" s="29"/>
+      <c r="P56" s="29"/>
+      <c r="Q56" s="29"/>
+      <c r="R56" s="29"/>
+      <c r="S56" s="29"/>
+      <c r="T56" s="29"/>
+      <c r="U56" s="29"/>
+      <c r="V56" s="29"/>
+      <c r="W56" s="29"/>
+      <c r="X56" s="29"/>
+      <c r="Y56" s="29"/>
+      <c r="Z56" s="30"/>
+    </row>
+    <row r="57" ht="15.0" customHeight="1">
+      <c r="A57" s="26" t="s">
+        <v>215</v>
+      </c>
+      <c r="B57" s="27">
         <v>0.0</v>
       </c>
-      <c r="C19" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="7"/>
-      <c r="N19" s="7"/>
-      <c r="O19" s="7"/>
-      <c r="P19" s="7"/>
-      <c r="Q19" s="7"/>
-      <c r="R19" s="7"/>
-      <c r="S19" s="7"/>
-      <c r="T19" s="7"/>
-      <c r="U19" s="7"/>
-      <c r="V19" s="7"/>
-      <c r="W19" s="7"/>
-      <c r="X19" s="7"/>
-      <c r="Y19" s="7"/>
-      <c r="Z19" s="9"/>
-    </row>
-    <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B20" s="7">
+      <c r="C57" s="28" t="s">
+        <v>216</v>
+      </c>
+      <c r="D57" s="28" t="s">
+        <v>217</v>
+      </c>
+      <c r="E57" s="34" t="s">
+        <v>218</v>
+      </c>
+      <c r="F57" s="29"/>
+      <c r="G57" s="29"/>
+      <c r="H57" s="29"/>
+      <c r="I57" s="29"/>
+      <c r="J57" s="29"/>
+      <c r="K57" s="29"/>
+      <c r="L57" s="29"/>
+      <c r="M57" s="29"/>
+      <c r="N57" s="29"/>
+      <c r="O57" s="29"/>
+      <c r="P57" s="29"/>
+      <c r="Q57" s="29"/>
+      <c r="R57" s="29"/>
+      <c r="S57" s="29"/>
+      <c r="T57" s="29"/>
+      <c r="U57" s="29"/>
+      <c r="V57" s="29"/>
+      <c r="W57" s="29"/>
+      <c r="X57" s="29"/>
+      <c r="Y57" s="29"/>
+      <c r="Z57" s="30"/>
+    </row>
+    <row r="58" ht="15.0" customHeight="1">
+      <c r="A58" s="26" t="s">
+        <v>219</v>
+      </c>
+      <c r="B58" s="27">
         <v>0.0</v>
       </c>
-      <c r="C20" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7"/>
-      <c r="N20" s="7"/>
-      <c r="O20" s="7"/>
-      <c r="P20" s="7"/>
-      <c r="Q20" s="7"/>
-      <c r="R20" s="7"/>
-      <c r="S20" s="7"/>
-      <c r="T20" s="7"/>
-      <c r="U20" s="7"/>
-      <c r="V20" s="7"/>
-      <c r="W20" s="7"/>
-      <c r="X20" s="7"/>
-      <c r="Y20" s="7"/>
-      <c r="Z20" s="9"/>
-    </row>
-    <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="B21" s="7">
+      <c r="C58" s="28" t="s">
+        <v>220</v>
+      </c>
+      <c r="D58" s="28" t="s">
+        <v>221</v>
+      </c>
+      <c r="E58" s="34" t="s">
+        <v>222</v>
+      </c>
+      <c r="F58" s="29"/>
+      <c r="G58" s="29"/>
+      <c r="H58" s="29"/>
+      <c r="I58" s="29"/>
+      <c r="J58" s="29"/>
+      <c r="K58" s="29"/>
+      <c r="L58" s="29"/>
+      <c r="M58" s="29"/>
+      <c r="N58" s="29"/>
+      <c r="O58" s="29"/>
+      <c r="P58" s="29"/>
+      <c r="Q58" s="29"/>
+      <c r="R58" s="29"/>
+      <c r="S58" s="29"/>
+      <c r="T58" s="29"/>
+      <c r="U58" s="29"/>
+      <c r="V58" s="29"/>
+      <c r="W58" s="29"/>
+      <c r="X58" s="29"/>
+      <c r="Y58" s="29"/>
+      <c r="Z58" s="30"/>
+    </row>
+    <row r="59" ht="15.0" customHeight="1">
+      <c r="A59" s="26" t="s">
+        <v>223</v>
+      </c>
+      <c r="B59" s="27">
         <v>0.0</v>
       </c>
-      <c r="C21" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="7"/>
-      <c r="N21" s="7"/>
-      <c r="O21" s="7"/>
-      <c r="P21" s="7"/>
-      <c r="Q21" s="7"/>
-      <c r="R21" s="7"/>
-      <c r="S21" s="7"/>
-      <c r="T21" s="7"/>
-      <c r="U21" s="7"/>
-      <c r="V21" s="7"/>
-      <c r="W21" s="7"/>
-      <c r="X21" s="7"/>
-      <c r="Y21" s="7"/>
-      <c r="Z21" s="9"/>
-    </row>
-    <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="B22" s="12">
-        <v>0.0</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="12"/>
-      <c r="K22" s="12"/>
-      <c r="L22" s="12"/>
-      <c r="M22" s="12"/>
-      <c r="N22" s="12"/>
-      <c r="O22" s="12"/>
-      <c r="P22" s="12"/>
-      <c r="Q22" s="12"/>
-      <c r="R22" s="12"/>
-      <c r="S22" s="12"/>
-      <c r="T22" s="12"/>
-      <c r="U22" s="12"/>
-      <c r="V22" s="12"/>
-      <c r="W22" s="12"/>
-      <c r="X22" s="12"/>
-      <c r="Y22" s="12"/>
-      <c r="Z22" s="13"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="B23" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="D23" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="E23" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="16"/>
-      <c r="J23" s="16"/>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="16"/>
-      <c r="O23" s="16"/>
-      <c r="P23" s="16"/>
-      <c r="Q23" s="16"/>
-      <c r="R23" s="16"/>
-      <c r="S23" s="16"/>
-      <c r="T23" s="16"/>
-      <c r="U23" s="16"/>
-      <c r="V23" s="16"/>
-      <c r="W23" s="16"/>
-      <c r="X23" s="16"/>
-      <c r="Y23" s="16"/>
-      <c r="Z23" s="17"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="B24" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="D24" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="E24" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="16"/>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="16"/>
-      <c r="O24" s="16"/>
-      <c r="P24" s="16"/>
-      <c r="Q24" s="16"/>
-      <c r="R24" s="16"/>
-      <c r="S24" s="16"/>
-      <c r="T24" s="16"/>
-      <c r="U24" s="16"/>
-      <c r="V24" s="16"/>
-      <c r="W24" s="16"/>
-      <c r="X24" s="16"/>
-      <c r="Y24" s="16"/>
-      <c r="Z24" s="17"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="B25" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="D25" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="E25" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
-      <c r="J25" s="16"/>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="16"/>
-      <c r="O25" s="16"/>
-      <c r="P25" s="16"/>
-      <c r="Q25" s="16"/>
-      <c r="R25" s="16"/>
-      <c r="S25" s="16"/>
-      <c r="T25" s="16"/>
-      <c r="U25" s="16"/>
-      <c r="V25" s="16"/>
-      <c r="W25" s="16"/>
-      <c r="X25" s="16"/>
-      <c r="Y25" s="16"/>
-      <c r="Z25" s="17"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="B26" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="D26" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="16"/>
-      <c r="J26" s="16"/>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="16"/>
-      <c r="O26" s="16"/>
-      <c r="P26" s="16"/>
-      <c r="Q26" s="16"/>
-      <c r="R26" s="16"/>
-      <c r="S26" s="16"/>
-      <c r="T26" s="16"/>
-      <c r="U26" s="16"/>
-      <c r="V26" s="16"/>
-      <c r="W26" s="16"/>
-      <c r="X26" s="16"/>
-      <c r="Y26" s="16"/>
-      <c r="Z26" s="17"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="B27" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C27" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="D27" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="E27" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="16"/>
-      <c r="J27" s="16"/>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="16"/>
-      <c r="O27" s="16"/>
-      <c r="P27" s="16"/>
-      <c r="Q27" s="16"/>
-      <c r="R27" s="16"/>
-      <c r="S27" s="16"/>
-      <c r="T27" s="16"/>
-      <c r="U27" s="16"/>
-      <c r="V27" s="16"/>
-      <c r="W27" s="16"/>
-      <c r="X27" s="16"/>
-      <c r="Y27" s="16"/>
-      <c r="Z27" s="17"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="B28" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="D28" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="E28" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="16"/>
-      <c r="J28" s="16"/>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="16"/>
-      <c r="O28" s="16"/>
-      <c r="P28" s="16"/>
-      <c r="Q28" s="16"/>
-      <c r="R28" s="16"/>
-      <c r="S28" s="16"/>
-      <c r="T28" s="16"/>
-      <c r="U28" s="16"/>
-      <c r="V28" s="16"/>
-      <c r="W28" s="16"/>
-      <c r="X28" s="16"/>
-      <c r="Y28" s="16"/>
-      <c r="Z28" s="17"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="B29" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C29" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="D29" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="E29" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="F29" s="16"/>
-      <c r="G29" s="16"/>
-      <c r="H29" s="16"/>
-      <c r="I29" s="16"/>
-      <c r="J29" s="16"/>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="16"/>
-      <c r="O29" s="16"/>
-      <c r="P29" s="16"/>
-      <c r="Q29" s="16"/>
-      <c r="R29" s="16"/>
-      <c r="S29" s="16"/>
-      <c r="T29" s="16"/>
-      <c r="U29" s="16"/>
-      <c r="V29" s="16"/>
-      <c r="W29" s="16"/>
-      <c r="X29" s="16"/>
-      <c r="Y29" s="16"/>
-      <c r="Z29" s="17"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="B30" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C30" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="E30" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="F30" s="16"/>
-      <c r="G30" s="16"/>
-      <c r="H30" s="16"/>
-      <c r="I30" s="16"/>
-      <c r="J30" s="16"/>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="16"/>
-      <c r="O30" s="16"/>
-      <c r="P30" s="16"/>
-      <c r="Q30" s="16"/>
-      <c r="R30" s="16"/>
-      <c r="S30" s="16"/>
-      <c r="T30" s="16"/>
-      <c r="U30" s="16"/>
-      <c r="V30" s="16"/>
-      <c r="W30" s="16"/>
-      <c r="X30" s="16"/>
-      <c r="Y30" s="16"/>
-      <c r="Z30" s="17"/>
-    </row>
-    <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="B31" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="C31" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="D31" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="E31" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="19"/>
-      <c r="J31" s="19"/>
-      <c r="K31" s="19"/>
-      <c r="L31" s="19"/>
-      <c r="M31" s="19"/>
-      <c r="N31" s="19"/>
-      <c r="O31" s="19"/>
-      <c r="P31" s="19"/>
-      <c r="Q31" s="19"/>
-      <c r="R31" s="19"/>
-      <c r="S31" s="19"/>
-      <c r="T31" s="19"/>
-      <c r="U31" s="19"/>
-      <c r="V31" s="19"/>
-      <c r="W31" s="19"/>
-      <c r="X31" s="19"/>
-      <c r="Y31" s="19"/>
-      <c r="Z31" s="17"/>
-    </row>
-    <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="B32" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="C32" s="20" t="s">
-        <v>114</v>
-      </c>
-      <c r="D32" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="E32" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="19"/>
-      <c r="J32" s="19"/>
-      <c r="K32" s="19"/>
-      <c r="L32" s="19"/>
-      <c r="M32" s="19"/>
-      <c r="N32" s="19"/>
-      <c r="O32" s="19"/>
-      <c r="P32" s="19"/>
-      <c r="Q32" s="19"/>
-      <c r="R32" s="19"/>
-      <c r="S32" s="19"/>
-      <c r="T32" s="19"/>
-      <c r="U32" s="19"/>
-      <c r="V32" s="19"/>
-      <c r="W32" s="19"/>
-      <c r="X32" s="19"/>
-      <c r="Y32" s="19"/>
-      <c r="Z32" s="17"/>
-    </row>
-    <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="B33" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="C33" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="D33" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="E33" s="23" t="s">
-        <v>120</v>
-      </c>
-      <c r="F33" s="23"/>
-      <c r="G33" s="23"/>
-      <c r="H33" s="23"/>
-      <c r="I33" s="23"/>
-      <c r="J33" s="23"/>
-      <c r="K33" s="23"/>
-      <c r="L33" s="23"/>
-      <c r="M33" s="23"/>
-      <c r="N33" s="23"/>
-      <c r="O33" s="23"/>
-      <c r="P33" s="23"/>
-      <c r="Q33" s="23"/>
-      <c r="R33" s="23"/>
-      <c r="S33" s="23"/>
-      <c r="T33" s="23"/>
-      <c r="U33" s="23"/>
-      <c r="V33" s="23"/>
-      <c r="W33" s="23"/>
-      <c r="X33" s="23"/>
-      <c r="Y33" s="23"/>
-      <c r="Z33" s="17"/>
-    </row>
-    <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="B34" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="C34" s="22" t="s">
-        <v>122</v>
-      </c>
-      <c r="D34" s="23" t="s">
-        <v>123</v>
-      </c>
-      <c r="E34" s="23" t="s">
-        <v>124</v>
-      </c>
-      <c r="F34" s="23"/>
-      <c r="G34" s="23"/>
-      <c r="H34" s="23"/>
-      <c r="I34" s="23"/>
-      <c r="J34" s="23"/>
-      <c r="K34" s="23"/>
-      <c r="L34" s="23"/>
-      <c r="M34" s="23"/>
-      <c r="N34" s="23"/>
-      <c r="O34" s="23"/>
-      <c r="P34" s="23"/>
-      <c r="Q34" s="23"/>
-      <c r="R34" s="23"/>
-      <c r="S34" s="23"/>
-      <c r="T34" s="23"/>
-      <c r="U34" s="23"/>
-      <c r="V34" s="23"/>
-      <c r="W34" s="23"/>
-      <c r="X34" s="23"/>
-      <c r="Y34" s="23"/>
-      <c r="Z34" s="17"/>
-    </row>
-    <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="B35" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="C35" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="D35" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="E35" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="F35" s="19"/>
-      <c r="G35" s="19"/>
-      <c r="H35" s="19"/>
-      <c r="I35" s="19"/>
-      <c r="J35" s="19"/>
-      <c r="K35" s="19"/>
-      <c r="L35" s="19"/>
-      <c r="M35" s="19"/>
-      <c r="N35" s="19"/>
-      <c r="O35" s="19"/>
-      <c r="P35" s="19"/>
-      <c r="Q35" s="19"/>
-      <c r="R35" s="19"/>
-      <c r="S35" s="19"/>
-      <c r="T35" s="19"/>
-      <c r="U35" s="19"/>
-      <c r="V35" s="19"/>
-      <c r="W35" s="19"/>
-      <c r="X35" s="19"/>
-      <c r="Y35" s="19"/>
-      <c r="Z35" s="17"/>
-    </row>
-    <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="B36" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="C36" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="D36" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="E36" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="F36" s="19"/>
-      <c r="G36" s="19"/>
-      <c r="H36" s="19"/>
-      <c r="I36" s="19"/>
-      <c r="J36" s="19"/>
-      <c r="K36" s="19"/>
-      <c r="L36" s="19"/>
-      <c r="M36" s="19"/>
-      <c r="N36" s="19"/>
-      <c r="O36" s="19"/>
-      <c r="P36" s="19"/>
-      <c r="Q36" s="19"/>
-      <c r="R36" s="19"/>
-      <c r="S36" s="19"/>
-      <c r="T36" s="19"/>
-      <c r="U36" s="19"/>
-      <c r="V36" s="19"/>
-      <c r="W36" s="19"/>
-      <c r="X36" s="19"/>
-      <c r="Y36" s="19"/>
-      <c r="Z36" s="17"/>
-    </row>
-    <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="B37" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="C37" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="D37" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="E37" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="F37" s="19"/>
-      <c r="G37" s="19"/>
-      <c r="H37" s="19"/>
-      <c r="I37" s="19"/>
-      <c r="J37" s="19"/>
-      <c r="K37" s="19"/>
-      <c r="L37" s="19"/>
-      <c r="M37" s="19"/>
-      <c r="N37" s="19"/>
-      <c r="O37" s="19"/>
-      <c r="P37" s="19"/>
-      <c r="Q37" s="19"/>
-      <c r="R37" s="19"/>
-      <c r="S37" s="19"/>
-      <c r="T37" s="19"/>
-      <c r="U37" s="19"/>
-      <c r="V37" s="19"/>
-      <c r="W37" s="19"/>
-      <c r="X37" s="19"/>
-      <c r="Y37" s="19"/>
-      <c r="Z37" s="17"/>
-    </row>
-    <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="B38" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C38" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="D38" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="E38" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="F38" s="16"/>
-      <c r="G38" s="16"/>
-      <c r="H38" s="16"/>
-      <c r="I38" s="16"/>
-      <c r="J38" s="16"/>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="16"/>
-      <c r="O38" s="16"/>
-      <c r="P38" s="16"/>
-      <c r="Q38" s="16"/>
-      <c r="R38" s="16"/>
-      <c r="S38" s="16"/>
-      <c r="T38" s="16"/>
-      <c r="U38" s="16"/>
-      <c r="V38" s="16"/>
-      <c r="W38" s="16"/>
-      <c r="X38" s="16"/>
-      <c r="Y38" s="16"/>
-      <c r="Z38" s="17"/>
-    </row>
-    <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="B39" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C39" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="D39" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="E39" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="F39" s="16"/>
-      <c r="G39" s="16"/>
-      <c r="H39" s="16"/>
-      <c r="I39" s="16"/>
-      <c r="J39" s="16"/>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="16"/>
-      <c r="O39" s="16"/>
-      <c r="P39" s="16"/>
-      <c r="Q39" s="16"/>
-      <c r="R39" s="16"/>
-      <c r="S39" s="16"/>
-      <c r="T39" s="16"/>
-      <c r="U39" s="16"/>
-      <c r="V39" s="16"/>
-      <c r="W39" s="16"/>
-      <c r="X39" s="16"/>
-      <c r="Y39" s="16"/>
-      <c r="Z39" s="17"/>
-    </row>
-    <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="B40" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C40" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="D40" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="E40" s="15" t="s">
-        <v>148</v>
-      </c>
-      <c r="F40" s="16"/>
-      <c r="G40" s="16"/>
-      <c r="H40" s="16"/>
-      <c r="I40" s="16"/>
-      <c r="J40" s="16"/>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="16"/>
-      <c r="O40" s="16"/>
-      <c r="P40" s="16"/>
-      <c r="Q40" s="16"/>
-      <c r="R40" s="16"/>
-      <c r="S40" s="16"/>
-      <c r="T40" s="16"/>
-      <c r="U40" s="16"/>
-      <c r="V40" s="16"/>
-      <c r="W40" s="16"/>
-      <c r="X40" s="16"/>
-      <c r="Y40" s="16"/>
-      <c r="Z40" s="17"/>
-    </row>
-    <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="24" t="s">
-        <v>149</v>
-      </c>
-      <c r="B41" s="25">
-        <v>0.0</v>
-      </c>
-      <c r="C41" s="26" t="s">
-        <v>150</v>
-      </c>
-      <c r="D41" s="26" t="s">
-        <v>151</v>
-      </c>
-      <c r="E41" s="26" t="s">
-        <v>152</v>
-      </c>
-      <c r="F41" s="27"/>
-      <c r="G41" s="27"/>
-      <c r="H41" s="27"/>
-      <c r="I41" s="27"/>
-      <c r="J41" s="27"/>
-      <c r="K41" s="27"/>
-      <c r="L41" s="27"/>
-      <c r="M41" s="27"/>
-      <c r="N41" s="27"/>
-      <c r="O41" s="27"/>
-      <c r="P41" s="27"/>
-      <c r="Q41" s="27"/>
-      <c r="R41" s="27"/>
-      <c r="S41" s="27"/>
-      <c r="T41" s="27"/>
-      <c r="U41" s="27"/>
-      <c r="V41" s="27"/>
-      <c r="W41" s="27"/>
-      <c r="X41" s="27"/>
-      <c r="Y41" s="27"/>
-      <c r="Z41" s="28"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="14" t="s">
-        <v>153</v>
-      </c>
-      <c r="B42" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C42" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="D42" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="E42" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="F42" s="16"/>
-      <c r="G42" s="16"/>
-      <c r="H42" s="16"/>
-      <c r="I42" s="16"/>
-      <c r="J42" s="16"/>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="16"/>
-      <c r="O42" s="16"/>
-      <c r="P42" s="16"/>
-      <c r="Q42" s="16"/>
-      <c r="R42" s="16"/>
-      <c r="S42" s="16"/>
-      <c r="T42" s="16"/>
-      <c r="U42" s="16"/>
-      <c r="V42" s="16"/>
-      <c r="W42" s="16"/>
-      <c r="X42" s="16"/>
-      <c r="Y42" s="16"/>
-      <c r="Z42" s="17"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="14" t="s">
-        <v>157</v>
-      </c>
-      <c r="B43" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C43" s="15" t="s">
-        <v>158</v>
-      </c>
-      <c r="D43" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="E43" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="F43" s="16"/>
-      <c r="G43" s="16"/>
-      <c r="H43" s="16"/>
-      <c r="I43" s="16"/>
-      <c r="J43" s="16"/>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="16"/>
-      <c r="O43" s="16"/>
-      <c r="P43" s="16"/>
-      <c r="Q43" s="16"/>
-      <c r="R43" s="16"/>
-      <c r="S43" s="16"/>
-      <c r="T43" s="16"/>
-      <c r="U43" s="16"/>
-      <c r="V43" s="16"/>
-      <c r="W43" s="16"/>
-      <c r="X43" s="16"/>
-      <c r="Y43" s="16"/>
-      <c r="Z43" s="17"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="B44" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C44" s="15" t="s">
-        <v>162</v>
-      </c>
-      <c r="D44" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="E44" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="F44" s="16"/>
-      <c r="G44" s="16"/>
-      <c r="H44" s="16"/>
-      <c r="I44" s="16"/>
-      <c r="J44" s="16"/>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="16"/>
-      <c r="O44" s="16"/>
-      <c r="P44" s="16"/>
-      <c r="Q44" s="16"/>
-      <c r="R44" s="16"/>
-      <c r="S44" s="16"/>
-      <c r="T44" s="16"/>
-      <c r="U44" s="16"/>
-      <c r="V44" s="16"/>
-      <c r="W44" s="16"/>
-      <c r="X44" s="16"/>
-      <c r="Y44" s="16"/>
-      <c r="Z44" s="17"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="B45" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C45" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="D45" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="E45" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="F45" s="16"/>
-      <c r="G45" s="16"/>
-      <c r="H45" s="16"/>
-      <c r="I45" s="16"/>
-      <c r="J45" s="16"/>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="16"/>
-      <c r="O45" s="16"/>
-      <c r="P45" s="16"/>
-      <c r="Q45" s="16"/>
-      <c r="R45" s="16"/>
-      <c r="S45" s="16"/>
-      <c r="T45" s="16"/>
-      <c r="U45" s="16"/>
-      <c r="V45" s="16"/>
-      <c r="W45" s="16"/>
-      <c r="X45" s="16"/>
-      <c r="Y45" s="16"/>
-      <c r="Z45" s="17"/>
-    </row>
-    <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="B46" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C46" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="D46" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="E46" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="F46" s="16"/>
-      <c r="G46" s="16"/>
-      <c r="H46" s="16"/>
-      <c r="I46" s="16"/>
-      <c r="J46" s="16"/>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="16"/>
-      <c r="O46" s="16"/>
-      <c r="P46" s="16"/>
-      <c r="Q46" s="16"/>
-      <c r="R46" s="16"/>
-      <c r="S46" s="16"/>
-      <c r="T46" s="16"/>
-      <c r="U46" s="16"/>
-      <c r="V46" s="16"/>
-      <c r="W46" s="16"/>
-      <c r="X46" s="16"/>
-      <c r="Y46" s="16"/>
-      <c r="Z46" s="17"/>
-    </row>
-    <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="B47" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C47" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="D47" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="E47" s="15" t="s">
-        <v>174</v>
-      </c>
-      <c r="F47" s="16"/>
-      <c r="G47" s="16"/>
-      <c r="H47" s="16"/>
-      <c r="I47" s="16"/>
-      <c r="J47" s="16"/>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="16"/>
-      <c r="O47" s="16"/>
-      <c r="P47" s="16"/>
-      <c r="Q47" s="16"/>
-      <c r="R47" s="16"/>
-      <c r="S47" s="16"/>
-      <c r="T47" s="16"/>
-      <c r="U47" s="16"/>
-      <c r="V47" s="16"/>
-      <c r="W47" s="16"/>
-      <c r="X47" s="16"/>
-      <c r="Y47" s="16"/>
-      <c r="Z47" s="17"/>
-    </row>
-    <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="B48" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C48" s="15" t="s">
-        <v>176</v>
-      </c>
-      <c r="D48" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="E48" s="15" t="s">
-        <v>178</v>
-      </c>
-      <c r="F48" s="16"/>
-      <c r="G48" s="16"/>
-      <c r="H48" s="16"/>
-      <c r="I48" s="16"/>
-      <c r="J48" s="16"/>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="16"/>
-      <c r="O48" s="16"/>
-      <c r="P48" s="16"/>
-      <c r="Q48" s="16"/>
-      <c r="R48" s="16"/>
-      <c r="S48" s="16"/>
-      <c r="T48" s="16"/>
-      <c r="U48" s="16"/>
-      <c r="V48" s="16"/>
-      <c r="W48" s="16"/>
-      <c r="X48" s="16"/>
-      <c r="Y48" s="16"/>
-      <c r="Z48" s="17"/>
-    </row>
-    <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="B49" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C49" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="D49" s="15" t="s">
-        <v>181</v>
-      </c>
-      <c r="E49" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="F49" s="16"/>
-      <c r="G49" s="16"/>
-      <c r="H49" s="16"/>
-      <c r="I49" s="16"/>
-      <c r="J49" s="16"/>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="16"/>
-      <c r="O49" s="16"/>
-      <c r="P49" s="16"/>
-      <c r="Q49" s="16"/>
-      <c r="R49" s="16"/>
-      <c r="S49" s="16"/>
-      <c r="T49" s="16"/>
-      <c r="U49" s="16"/>
-      <c r="V49" s="16"/>
-      <c r="W49" s="16"/>
-      <c r="X49" s="16"/>
-      <c r="Y49" s="16"/>
-      <c r="Z49" s="17"/>
-    </row>
-    <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="14" t="s">
-        <v>183</v>
-      </c>
-      <c r="B50" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C50" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="D50" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="E50" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="F50" s="16"/>
-      <c r="G50" s="16"/>
-      <c r="H50" s="16"/>
-      <c r="I50" s="16"/>
-      <c r="J50" s="16"/>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="16"/>
-      <c r="O50" s="16"/>
-      <c r="P50" s="16"/>
-      <c r="Q50" s="16"/>
-      <c r="R50" s="16"/>
-      <c r="S50" s="16"/>
-      <c r="T50" s="16"/>
-      <c r="U50" s="16"/>
-      <c r="V50" s="16"/>
-      <c r="W50" s="16"/>
-      <c r="X50" s="16"/>
-      <c r="Y50" s="16"/>
-      <c r="Z50" s="17"/>
-    </row>
-    <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B51" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C51" s="15" t="s">
-        <v>188</v>
-      </c>
-      <c r="D51" s="15" t="s">
-        <v>189</v>
-      </c>
-      <c r="E51" s="15" t="s">
-        <v>190</v>
-      </c>
-      <c r="F51" s="16"/>
-      <c r="G51" s="16"/>
-      <c r="H51" s="16"/>
-      <c r="I51" s="16"/>
-      <c r="J51" s="16"/>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="16"/>
-      <c r="O51" s="16"/>
-      <c r="P51" s="16"/>
-      <c r="Q51" s="16"/>
-      <c r="R51" s="16"/>
-      <c r="S51" s="16"/>
-      <c r="T51" s="16"/>
-      <c r="U51" s="16"/>
-      <c r="V51" s="16"/>
-      <c r="W51" s="16"/>
-      <c r="X51" s="16"/>
-      <c r="Y51" s="16"/>
-      <c r="Z51" s="17"/>
-    </row>
-    <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="B52" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C52" s="15" t="s">
-        <v>192</v>
-      </c>
-      <c r="D52" s="15" t="s">
-        <v>193</v>
-      </c>
-      <c r="E52" s="15" t="s">
-        <v>194</v>
-      </c>
-      <c r="F52" s="16"/>
-      <c r="G52" s="16"/>
-      <c r="H52" s="16"/>
-      <c r="I52" s="16"/>
-      <c r="J52" s="16"/>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="16"/>
-      <c r="O52" s="16"/>
-      <c r="P52" s="16"/>
-      <c r="Q52" s="16"/>
-      <c r="R52" s="16"/>
-      <c r="S52" s="16"/>
-      <c r="T52" s="16"/>
-      <c r="U52" s="16"/>
-      <c r="V52" s="16"/>
-      <c r="W52" s="16"/>
-      <c r="X52" s="16"/>
-      <c r="Y52" s="16"/>
-      <c r="Z52" s="17"/>
-    </row>
-    <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="B53" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C53" s="15" t="s">
-        <v>196</v>
-      </c>
-      <c r="D53" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="E53" s="15" t="s">
-        <v>198</v>
-      </c>
-      <c r="F53" s="16"/>
-      <c r="G53" s="16"/>
-      <c r="H53" s="16"/>
-      <c r="I53" s="16"/>
-      <c r="J53" s="16"/>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
-      <c r="N53" s="16"/>
-      <c r="O53" s="16"/>
-      <c r="P53" s="16"/>
-      <c r="Q53" s="16"/>
-      <c r="R53" s="16"/>
-      <c r="S53" s="16"/>
-      <c r="T53" s="16"/>
-      <c r="U53" s="16"/>
-      <c r="V53" s="16"/>
-      <c r="W53" s="16"/>
-      <c r="X53" s="16"/>
-      <c r="Y53" s="16"/>
-      <c r="Z53" s="17"/>
-    </row>
-    <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="B54" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C54" s="15" t="s">
-        <v>200</v>
-      </c>
-      <c r="D54" s="15" t="s">
-        <v>201</v>
-      </c>
-      <c r="E54" s="15" t="s">
-        <v>202</v>
-      </c>
-      <c r="F54" s="16"/>
-      <c r="G54" s="16"/>
-      <c r="H54" s="16"/>
-      <c r="I54" s="16"/>
-      <c r="J54" s="16"/>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
-      <c r="N54" s="16"/>
-      <c r="O54" s="16"/>
-      <c r="P54" s="16"/>
-      <c r="Q54" s="16"/>
-      <c r="R54" s="16"/>
-      <c r="S54" s="16"/>
-      <c r="T54" s="16"/>
-      <c r="U54" s="16"/>
-      <c r="V54" s="16"/>
-      <c r="W54" s="16"/>
-      <c r="X54" s="16"/>
-      <c r="Y54" s="16"/>
-      <c r="Z54" s="17"/>
-    </row>
-    <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="14" t="s">
-        <v>203</v>
-      </c>
-      <c r="B55" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C55" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="D55" s="15" t="s">
-        <v>205</v>
-      </c>
-      <c r="E55" s="15" t="s">
-        <v>206</v>
-      </c>
-      <c r="F55" s="16"/>
-      <c r="G55" s="16"/>
-      <c r="H55" s="16"/>
-      <c r="I55" s="16"/>
-      <c r="J55" s="16"/>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
-      <c r="N55" s="16"/>
-      <c r="O55" s="16"/>
-      <c r="P55" s="16"/>
-      <c r="Q55" s="16"/>
-      <c r="R55" s="16"/>
-      <c r="S55" s="16"/>
-      <c r="T55" s="16"/>
-      <c r="U55" s="16"/>
-      <c r="V55" s="16"/>
-      <c r="W55" s="16"/>
-      <c r="X55" s="16"/>
-      <c r="Y55" s="16"/>
-      <c r="Z55" s="17"/>
-    </row>
-    <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="B56" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C56" s="15" t="s">
-        <v>208</v>
-      </c>
-      <c r="D56" s="15" t="s">
-        <v>209</v>
-      </c>
-      <c r="E56" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="F56" s="16"/>
-      <c r="G56" s="16"/>
-      <c r="H56" s="16"/>
-      <c r="I56" s="16"/>
-      <c r="J56" s="16"/>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
-      <c r="N56" s="16"/>
-      <c r="O56" s="16"/>
-      <c r="P56" s="16"/>
-      <c r="Q56" s="16"/>
-      <c r="R56" s="16"/>
-      <c r="S56" s="16"/>
-      <c r="T56" s="16"/>
-      <c r="U56" s="16"/>
-      <c r="V56" s="16"/>
-      <c r="W56" s="16"/>
-      <c r="X56" s="16"/>
-      <c r="Y56" s="16"/>
-      <c r="Z56" s="17"/>
-    </row>
-    <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="14" t="s">
-        <v>211</v>
-      </c>
-      <c r="B57" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C57" s="15" t="s">
-        <v>212</v>
-      </c>
-      <c r="D57" s="15" t="s">
-        <v>213</v>
-      </c>
-      <c r="E57" s="15" t="s">
-        <v>214</v>
-      </c>
-      <c r="F57" s="16"/>
-      <c r="G57" s="16"/>
-      <c r="H57" s="16"/>
-      <c r="I57" s="16"/>
-      <c r="J57" s="16"/>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
-      <c r="N57" s="16"/>
-      <c r="O57" s="16"/>
-      <c r="P57" s="16"/>
-      <c r="Q57" s="16"/>
-      <c r="R57" s="16"/>
-      <c r="S57" s="16"/>
-      <c r="T57" s="16"/>
-      <c r="U57" s="16"/>
-      <c r="V57" s="16"/>
-      <c r="W57" s="16"/>
-      <c r="X57" s="16"/>
-      <c r="Y57" s="16"/>
-      <c r="Z57" s="17"/>
-    </row>
-    <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="14" t="s">
-        <v>215</v>
-      </c>
-      <c r="B58" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C58" s="15" t="s">
-        <v>216</v>
-      </c>
-      <c r="D58" s="15" t="s">
-        <v>217</v>
-      </c>
-      <c r="E58" s="15" t="s">
-        <v>218</v>
-      </c>
-      <c r="F58" s="16"/>
-      <c r="G58" s="16"/>
-      <c r="H58" s="16"/>
-      <c r="I58" s="16"/>
-      <c r="J58" s="16"/>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
-      <c r="N58" s="16"/>
-      <c r="O58" s="16"/>
-      <c r="P58" s="16"/>
-      <c r="Q58" s="16"/>
-      <c r="R58" s="16"/>
-      <c r="S58" s="16"/>
-      <c r="T58" s="16"/>
-      <c r="U58" s="16"/>
-      <c r="V58" s="16"/>
-      <c r="W58" s="16"/>
-      <c r="X58" s="16"/>
-      <c r="Y58" s="16"/>
-      <c r="Z58" s="17"/>
-    </row>
-    <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="29" t="s">
-        <v>219</v>
-      </c>
-      <c r="B59" s="30">
-        <v>0.0</v>
-      </c>
-      <c r="C59" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="D59" s="30" t="s">
-        <v>221</v>
-      </c>
-      <c r="E59" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="F59" s="31"/>
-      <c r="G59" s="31"/>
-      <c r="H59" s="31"/>
-      <c r="I59" s="31"/>
-      <c r="J59" s="31"/>
-      <c r="K59" s="31"/>
-      <c r="L59" s="31"/>
-      <c r="M59" s="31"/>
-      <c r="N59" s="31"/>
-      <c r="O59" s="31"/>
-      <c r="P59" s="31"/>
-      <c r="Q59" s="31"/>
-      <c r="R59" s="31"/>
-      <c r="S59" s="31"/>
-      <c r="T59" s="31"/>
-      <c r="U59" s="31"/>
-      <c r="V59" s="31"/>
-      <c r="W59" s="31"/>
-      <c r="X59" s="31"/>
-      <c r="Y59" s="31"/>
-      <c r="Z59" s="32"/>
+      <c r="C59" s="28" t="s">
+        <v>224</v>
+      </c>
+      <c r="D59" s="28" t="s">
+        <v>225</v>
+      </c>
+      <c r="E59" s="28" t="s">
+        <v>226</v>
+      </c>
+      <c r="F59" s="29"/>
+      <c r="G59" s="29"/>
+      <c r="H59" s="29"/>
+      <c r="I59" s="29"/>
+      <c r="J59" s="29"/>
+      <c r="K59" s="29"/>
+      <c r="L59" s="29"/>
+      <c r="M59" s="29"/>
+      <c r="N59" s="29"/>
+      <c r="O59" s="29"/>
+      <c r="P59" s="29"/>
+      <c r="Q59" s="29"/>
+      <c r="R59" s="29"/>
+      <c r="S59" s="29"/>
+      <c r="T59" s="29"/>
+      <c r="U59" s="29"/>
+      <c r="V59" s="29"/>
+      <c r="W59" s="29"/>
+      <c r="X59" s="29"/>
+      <c r="Y59" s="29"/>
+      <c r="Z59" s="30"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="33" t="s">
-        <v>223</v>
-      </c>
-      <c r="B60" s="34">
+        <v>227</v>
+      </c>
+      <c r="B60" s="27">
         <v>0.0</v>
       </c>
-      <c r="C60" s="34" t="s">
-        <v>224</v>
-      </c>
-      <c r="D60" s="34" t="s">
-        <v>225</v>
-      </c>
-      <c r="E60" s="34" t="s">
-        <v>226</v>
-      </c>
-      <c r="F60" s="35"/>
-      <c r="G60" s="35"/>
-      <c r="H60" s="35"/>
-      <c r="I60" s="35"/>
-      <c r="J60" s="35"/>
-      <c r="K60" s="35"/>
-      <c r="L60" s="35"/>
-      <c r="M60" s="35"/>
-      <c r="N60" s="35"/>
-      <c r="O60" s="35"/>
-      <c r="P60" s="35"/>
-      <c r="Q60" s="35"/>
-      <c r="R60" s="35"/>
-      <c r="S60" s="35"/>
-      <c r="T60" s="35"/>
-      <c r="U60" s="35"/>
-      <c r="V60" s="35"/>
-      <c r="W60" s="35"/>
-      <c r="X60" s="35"/>
-      <c r="Y60" s="35"/>
-      <c r="Z60" s="36"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="33" t="s">
-        <v>227</v>
-      </c>
-      <c r="B61" s="34">
+      <c r="C60" s="28" t="s">
+        <v>228</v>
+      </c>
+      <c r="D60" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="E60" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="F60" s="29"/>
+      <c r="G60" s="29"/>
+      <c r="H60" s="29"/>
+      <c r="I60" s="29"/>
+      <c r="J60" s="29"/>
+      <c r="K60" s="29"/>
+      <c r="L60" s="29"/>
+      <c r="M60" s="29"/>
+      <c r="N60" s="29"/>
+      <c r="O60" s="29"/>
+      <c r="P60" s="29"/>
+      <c r="Q60" s="29"/>
+      <c r="R60" s="29"/>
+      <c r="S60" s="29"/>
+      <c r="T60" s="29"/>
+      <c r="U60" s="29"/>
+      <c r="V60" s="29"/>
+      <c r="W60" s="29"/>
+      <c r="X60" s="29"/>
+      <c r="Y60" s="29"/>
+      <c r="Z60" s="30"/>
+    </row>
+    <row r="61" ht="15.0" customHeight="1">
+      <c r="A61" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="B61" s="27">
         <v>0.0</v>
       </c>
-      <c r="C61" s="34" t="s">
-        <v>228</v>
-      </c>
-      <c r="D61" s="34" t="s">
+      <c r="C61" s="28" t="s">
+        <v>232</v>
+      </c>
+      <c r="D61" s="28" t="s">
+        <v>233</v>
+      </c>
+      <c r="E61" s="28" t="s">
+        <v>234</v>
+      </c>
+      <c r="F61" s="29"/>
+      <c r="G61" s="29"/>
+      <c r="H61" s="29"/>
+      <c r="I61" s="29"/>
+      <c r="J61" s="29"/>
+      <c r="K61" s="29"/>
+      <c r="L61" s="29"/>
+      <c r="M61" s="29"/>
+      <c r="N61" s="29"/>
+      <c r="O61" s="29"/>
+      <c r="P61" s="29"/>
+      <c r="Q61" s="29"/>
+      <c r="R61" s="29"/>
+      <c r="S61" s="29"/>
+      <c r="T61" s="29"/>
+      <c r="U61" s="29"/>
+      <c r="V61" s="29"/>
+      <c r="W61" s="29"/>
+      <c r="X61" s="29"/>
+      <c r="Y61" s="29"/>
+      <c r="Z61" s="30"/>
+    </row>
+    <row r="62" ht="15.0" customHeight="1">
+      <c r="A62" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="B62" s="27">
+        <v>0.0</v>
+      </c>
+      <c r="C62" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="D62" s="28" t="s">
+        <v>237</v>
+      </c>
+      <c r="E62" s="28" t="s">
+        <v>238</v>
+      </c>
+      <c r="F62" s="29"/>
+      <c r="G62" s="29"/>
+      <c r="H62" s="29"/>
+      <c r="I62" s="29"/>
+      <c r="J62" s="29"/>
+      <c r="K62" s="29"/>
+      <c r="L62" s="29"/>
+      <c r="M62" s="29"/>
+      <c r="N62" s="29"/>
+      <c r="O62" s="29"/>
+      <c r="P62" s="29"/>
+      <c r="Q62" s="29"/>
+      <c r="R62" s="29"/>
+      <c r="S62" s="29"/>
+      <c r="T62" s="29"/>
+      <c r="U62" s="29"/>
+      <c r="V62" s="29"/>
+      <c r="W62" s="29"/>
+      <c r="X62" s="29"/>
+      <c r="Y62" s="29"/>
+      <c r="Z62" s="30"/>
+    </row>
+    <row r="63" ht="15.0" customHeight="1">
+      <c r="A63" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="B63" s="27">
+        <v>0.0</v>
+      </c>
+      <c r="C63" s="28" t="s">
+        <v>240</v>
+      </c>
+      <c r="D63" s="28" t="s">
+        <v>241</v>
+      </c>
+      <c r="E63" s="28" t="s">
+        <v>242</v>
+      </c>
+      <c r="F63" s="29"/>
+      <c r="G63" s="29"/>
+      <c r="H63" s="29"/>
+      <c r="I63" s="29"/>
+      <c r="J63" s="29"/>
+      <c r="K63" s="29"/>
+      <c r="L63" s="29"/>
+      <c r="M63" s="29"/>
+      <c r="N63" s="29"/>
+      <c r="O63" s="29"/>
+      <c r="P63" s="29"/>
+      <c r="Q63" s="29"/>
+      <c r="R63" s="29"/>
+      <c r="S63" s="29"/>
+      <c r="T63" s="29"/>
+      <c r="U63" s="29"/>
+      <c r="V63" s="29"/>
+      <c r="W63" s="29"/>
+      <c r="X63" s="29"/>
+      <c r="Y63" s="29"/>
+      <c r="Z63" s="30"/>
+    </row>
+    <row r="64" ht="15.0" customHeight="1">
+      <c r="A64" s="26" t="s">
+        <v>243</v>
+      </c>
+      <c r="B64" s="27">
+        <v>0.0</v>
+      </c>
+      <c r="C64" s="28" t="s">
+        <v>244</v>
+      </c>
+      <c r="D64" s="28" t="s">
+        <v>245</v>
+      </c>
+      <c r="E64" s="28" t="s">
+        <v>246</v>
+      </c>
+      <c r="F64" s="29"/>
+      <c r="G64" s="29"/>
+      <c r="H64" s="29"/>
+      <c r="I64" s="29"/>
+      <c r="J64" s="29"/>
+      <c r="K64" s="29"/>
+      <c r="L64" s="29"/>
+      <c r="M64" s="29"/>
+      <c r="N64" s="29"/>
+      <c r="O64" s="29"/>
+      <c r="P64" s="29"/>
+      <c r="Q64" s="29"/>
+      <c r="R64" s="29"/>
+      <c r="S64" s="29"/>
+      <c r="T64" s="29"/>
+      <c r="U64" s="29"/>
+      <c r="V64" s="29"/>
+      <c r="W64" s="29"/>
+      <c r="X64" s="29"/>
+      <c r="Y64" s="29"/>
+      <c r="Z64" s="30"/>
+    </row>
+    <row r="65" ht="15.0" customHeight="1">
+      <c r="A65" s="26" t="s">
+        <v>247</v>
+      </c>
+      <c r="B65" s="27">
+        <v>0.0</v>
+      </c>
+      <c r="C65" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="D65" s="28" t="s">
+        <v>249</v>
+      </c>
+      <c r="E65" s="28" t="s">
+        <v>250</v>
+      </c>
+      <c r="F65" s="29"/>
+      <c r="G65" s="29"/>
+      <c r="H65" s="29"/>
+      <c r="I65" s="29"/>
+      <c r="J65" s="29"/>
+      <c r="K65" s="29"/>
+      <c r="L65" s="29"/>
+      <c r="M65" s="29"/>
+      <c r="N65" s="29"/>
+      <c r="O65" s="29"/>
+      <c r="P65" s="29"/>
+      <c r="Q65" s="29"/>
+      <c r="R65" s="29"/>
+      <c r="S65" s="29"/>
+      <c r="T65" s="29"/>
+      <c r="U65" s="29"/>
+      <c r="V65" s="29"/>
+      <c r="W65" s="29"/>
+      <c r="X65" s="29"/>
+      <c r="Y65" s="29"/>
+      <c r="Z65" s="30"/>
+    </row>
+    <row r="66" ht="15.0" customHeight="1">
+      <c r="A66" s="33" t="s">
+        <v>251</v>
+      </c>
+      <c r="B66" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="C66" s="34" t="s">
+        <v>252</v>
+      </c>
+      <c r="D66" s="34" t="s">
+        <v>253</v>
+      </c>
+      <c r="E66" s="34" t="s">
+        <v>254</v>
+      </c>
+      <c r="F66" s="36"/>
+      <c r="G66" s="36"/>
+      <c r="H66" s="36"/>
+      <c r="I66" s="36"/>
+      <c r="J66" s="36"/>
+      <c r="K66" s="36"/>
+      <c r="L66" s="36"/>
+      <c r="M66" s="36"/>
+      <c r="N66" s="36"/>
+      <c r="O66" s="36"/>
+      <c r="P66" s="36"/>
+      <c r="Q66" s="36"/>
+      <c r="R66" s="36"/>
+      <c r="S66" s="36"/>
+      <c r="T66" s="36"/>
+      <c r="U66" s="36"/>
+      <c r="V66" s="36"/>
+      <c r="W66" s="36"/>
+      <c r="X66" s="36"/>
+      <c r="Y66" s="36"/>
+      <c r="Z66" s="37"/>
+    </row>
+    <row r="67" ht="15.0" customHeight="1">
+      <c r="A67" s="33" t="s">
+        <v>255</v>
+      </c>
+      <c r="B67" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="C67" s="34" t="s">
+        <v>256</v>
+      </c>
+      <c r="D67" s="34" t="s">
+        <v>257</v>
+      </c>
+      <c r="E67" s="34" t="s">
+        <v>258</v>
+      </c>
+      <c r="F67" s="36"/>
+      <c r="G67" s="36"/>
+      <c r="H67" s="36"/>
+      <c r="I67" s="36"/>
+      <c r="J67" s="36"/>
+      <c r="K67" s="36"/>
+      <c r="L67" s="36"/>
+      <c r="M67" s="36"/>
+      <c r="N67" s="36"/>
+      <c r="O67" s="36"/>
+      <c r="P67" s="36"/>
+      <c r="Q67" s="36"/>
+      <c r="R67" s="36"/>
+      <c r="S67" s="36"/>
+      <c r="T67" s="36"/>
+      <c r="U67" s="36"/>
+      <c r="V67" s="36"/>
+      <c r="W67" s="36"/>
+      <c r="X67" s="36"/>
+      <c r="Y67" s="36"/>
+      <c r="Z67" s="37"/>
+    </row>
+    <row r="68" ht="15.0" customHeight="1">
+      <c r="A68" s="33" t="s">
+        <v>259</v>
+      </c>
+      <c r="B68" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="C68" s="34" t="s">
+        <v>260</v>
+      </c>
+      <c r="D68" s="34" t="s">
+        <v>261</v>
+      </c>
+      <c r="E68" s="34" t="s">
+        <v>262</v>
+      </c>
+      <c r="F68" s="36"/>
+      <c r="G68" s="36"/>
+      <c r="H68" s="36"/>
+      <c r="I68" s="36"/>
+      <c r="J68" s="36"/>
+      <c r="K68" s="36"/>
+      <c r="L68" s="36"/>
+      <c r="M68" s="36"/>
+      <c r="N68" s="36"/>
+      <c r="O68" s="36"/>
+      <c r="P68" s="36"/>
+      <c r="Q68" s="36"/>
+      <c r="R68" s="36"/>
+      <c r="S68" s="36"/>
+      <c r="T68" s="36"/>
+      <c r="U68" s="36"/>
+      <c r="V68" s="36"/>
+      <c r="W68" s="36"/>
+      <c r="X68" s="36"/>
+      <c r="Y68" s="36"/>
+      <c r="Z68" s="37"/>
+    </row>
+    <row r="69" ht="15.0" customHeight="1">
+      <c r="A69" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="B69" s="27">
+        <v>0.0</v>
+      </c>
+      <c r="C69" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="D69" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="E69" s="28" t="s">
+        <v>266</v>
+      </c>
+      <c r="F69" s="29"/>
+      <c r="G69" s="29"/>
+      <c r="H69" s="29"/>
+      <c r="I69" s="29"/>
+      <c r="J69" s="29"/>
+      <c r="K69" s="29"/>
+      <c r="L69" s="29"/>
+      <c r="M69" s="29"/>
+      <c r="N69" s="29"/>
+      <c r="O69" s="29"/>
+      <c r="P69" s="29"/>
+      <c r="Q69" s="29"/>
+      <c r="R69" s="29"/>
+      <c r="S69" s="29"/>
+      <c r="T69" s="29"/>
+      <c r="U69" s="29"/>
+      <c r="V69" s="29"/>
+      <c r="W69" s="29"/>
+      <c r="X69" s="29"/>
+      <c r="Y69" s="29"/>
+      <c r="Z69" s="30"/>
+    </row>
+    <row r="70" ht="15.0" customHeight="1">
+      <c r="A70" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="B70" s="27">
+        <v>0.0</v>
+      </c>
+      <c r="C70" s="28" t="s">
+        <v>268</v>
+      </c>
+      <c r="D70" s="28" t="s">
+        <v>269</v>
+      </c>
+      <c r="E70" s="28" t="s">
+        <v>270</v>
+      </c>
+      <c r="F70" s="29"/>
+      <c r="G70" s="29"/>
+      <c r="H70" s="29"/>
+      <c r="I70" s="29"/>
+      <c r="J70" s="29"/>
+      <c r="K70" s="29"/>
+      <c r="L70" s="29"/>
+      <c r="M70" s="29"/>
+      <c r="N70" s="29"/>
+      <c r="O70" s="29"/>
+      <c r="P70" s="29"/>
+      <c r="Q70" s="29"/>
+      <c r="R70" s="29"/>
+      <c r="S70" s="29"/>
+      <c r="T70" s="29"/>
+      <c r="U70" s="29"/>
+      <c r="V70" s="29"/>
+      <c r="W70" s="29"/>
+      <c r="X70" s="29"/>
+      <c r="Y70" s="29"/>
+      <c r="Z70" s="30"/>
+    </row>
+    <row r="71" ht="15.0" customHeight="1">
+      <c r="A71" s="38" t="s">
+        <v>271</v>
+      </c>
+      <c r="B71" s="39">
+        <v>0.0</v>
+      </c>
+      <c r="C71" s="40" t="s">
+        <v>272</v>
+      </c>
+      <c r="D71" s="40" t="s">
+        <v>273</v>
+      </c>
+      <c r="E71" s="40" t="s">
+        <v>274</v>
+      </c>
+      <c r="F71" s="41"/>
+      <c r="G71" s="41"/>
+      <c r="H71" s="41"/>
+      <c r="I71" s="41"/>
+      <c r="J71" s="41"/>
+      <c r="K71" s="41"/>
+      <c r="L71" s="41"/>
+      <c r="M71" s="41"/>
+      <c r="N71" s="41"/>
+      <c r="O71" s="41"/>
+      <c r="P71" s="41"/>
+      <c r="Q71" s="41"/>
+      <c r="R71" s="41"/>
+      <c r="S71" s="41"/>
+      <c r="T71" s="41"/>
+      <c r="U71" s="41"/>
+      <c r="V71" s="41"/>
+      <c r="W71" s="41"/>
+      <c r="X71" s="41"/>
+      <c r="Y71" s="41"/>
+      <c r="Z71" s="42"/>
+    </row>
+    <row r="72" ht="15.0" customHeight="1">
+      <c r="A72" s="43" t="s">
+        <v>275</v>
+      </c>
+      <c r="B72" s="44">
+        <v>0.0</v>
+      </c>
+      <c r="C72" s="44" t="s">
+        <v>276</v>
+      </c>
+      <c r="D72" s="44" t="s">
         <v>151</v>
       </c>
-      <c r="E61" s="34" t="s">
+      <c r="E72" s="44" t="s">
         <v>152</v>
       </c>
-      <c r="F61" s="35"/>
-      <c r="G61" s="35"/>
-      <c r="H61" s="35"/>
-      <c r="I61" s="35"/>
-      <c r="J61" s="35"/>
-      <c r="K61" s="35"/>
-      <c r="L61" s="35"/>
-      <c r="M61" s="35"/>
-      <c r="N61" s="35"/>
-      <c r="O61" s="35"/>
-      <c r="P61" s="35"/>
-      <c r="Q61" s="35"/>
-      <c r="R61" s="35"/>
-      <c r="S61" s="35"/>
-      <c r="T61" s="35"/>
-      <c r="U61" s="35"/>
-      <c r="V61" s="35"/>
-      <c r="W61" s="35"/>
-      <c r="X61" s="35"/>
-      <c r="Y61" s="35"/>
-      <c r="Z61" s="36"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="33" t="s">
-        <v>229</v>
-      </c>
-      <c r="B62" s="34">
+      <c r="F72" s="45"/>
+      <c r="G72" s="45"/>
+      <c r="H72" s="45"/>
+      <c r="I72" s="45"/>
+      <c r="J72" s="45"/>
+      <c r="K72" s="45"/>
+      <c r="L72" s="45"/>
+      <c r="M72" s="45"/>
+      <c r="N72" s="45"/>
+      <c r="O72" s="45"/>
+      <c r="P72" s="45"/>
+      <c r="Q72" s="45"/>
+      <c r="R72" s="45"/>
+      <c r="S72" s="45"/>
+      <c r="T72" s="45"/>
+      <c r="U72" s="45"/>
+      <c r="V72" s="45"/>
+      <c r="W72" s="45"/>
+      <c r="X72" s="45"/>
+      <c r="Y72" s="45"/>
+      <c r="Z72" s="46"/>
+    </row>
+    <row r="73" ht="15.0" customHeight="1">
+      <c r="A73" s="47" t="s">
+        <v>277</v>
+      </c>
+      <c r="B73" s="48">
         <v>0.0</v>
       </c>
-      <c r="C62" s="34" t="s">
-        <v>230</v>
-      </c>
-      <c r="D62" s="34" t="s">
-        <v>231</v>
-      </c>
-      <c r="E62" s="34" t="s">
-        <v>232</v>
-      </c>
-      <c r="F62" s="35"/>
-      <c r="G62" s="35"/>
-      <c r="H62" s="35"/>
-      <c r="I62" s="35"/>
-      <c r="J62" s="35"/>
-      <c r="K62" s="35"/>
-      <c r="L62" s="35"/>
-      <c r="M62" s="35"/>
-      <c r="N62" s="35"/>
-      <c r="O62" s="35"/>
-      <c r="P62" s="35"/>
-      <c r="Q62" s="35"/>
-      <c r="R62" s="35"/>
-      <c r="S62" s="35"/>
-      <c r="T62" s="35"/>
-      <c r="U62" s="35"/>
-      <c r="V62" s="35"/>
-      <c r="W62" s="35"/>
-      <c r="X62" s="35"/>
-      <c r="Y62" s="35"/>
-      <c r="Z62" s="36"/>
-    </row>
-    <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="33" t="s">
-        <v>233</v>
-      </c>
-      <c r="B63" s="34">
+      <c r="C73" s="48" t="s">
+        <v>278</v>
+      </c>
+      <c r="D73" s="48" t="s">
+        <v>279</v>
+      </c>
+      <c r="E73" s="48" t="s">
+        <v>280</v>
+      </c>
+      <c r="F73" s="49"/>
+      <c r="G73" s="49"/>
+      <c r="H73" s="49"/>
+      <c r="I73" s="49"/>
+      <c r="J73" s="49"/>
+      <c r="K73" s="49"/>
+      <c r="L73" s="49"/>
+      <c r="M73" s="49"/>
+      <c r="N73" s="49"/>
+      <c r="O73" s="49"/>
+      <c r="P73" s="49"/>
+      <c r="Q73" s="49"/>
+      <c r="R73" s="49"/>
+      <c r="S73" s="49"/>
+      <c r="T73" s="49"/>
+      <c r="U73" s="49"/>
+      <c r="V73" s="49"/>
+      <c r="W73" s="49"/>
+      <c r="X73" s="49"/>
+      <c r="Y73" s="49"/>
+      <c r="Z73" s="50"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="47" t="s">
+        <v>281</v>
+      </c>
+      <c r="B74" s="48">
         <v>0.0</v>
       </c>
-      <c r="C63" s="34" t="s">
-        <v>234</v>
-      </c>
-      <c r="D63" s="34" t="s">
-        <v>235</v>
-      </c>
-      <c r="E63" s="34" t="s">
-        <v>236</v>
-      </c>
-      <c r="F63" s="35"/>
-      <c r="G63" s="35"/>
-      <c r="H63" s="35"/>
-      <c r="I63" s="35"/>
-      <c r="J63" s="35"/>
-      <c r="K63" s="35"/>
-      <c r="L63" s="35"/>
-      <c r="M63" s="35"/>
-      <c r="N63" s="35"/>
-      <c r="O63" s="35"/>
-      <c r="P63" s="35"/>
-      <c r="Q63" s="35"/>
-      <c r="R63" s="35"/>
-      <c r="S63" s="35"/>
-      <c r="T63" s="35"/>
-      <c r="U63" s="35"/>
-      <c r="V63" s="35"/>
-      <c r="W63" s="35"/>
-      <c r="X63" s="35"/>
-      <c r="Y63" s="35"/>
-      <c r="Z63" s="36"/>
-    </row>
-    <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="33" t="s">
-        <v>237</v>
-      </c>
-      <c r="B64" s="34">
+      <c r="C74" s="48" t="s">
+        <v>282</v>
+      </c>
+      <c r="D74" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="E74" s="48" t="s">
+        <v>180</v>
+      </c>
+      <c r="F74" s="49"/>
+      <c r="G74" s="49"/>
+      <c r="H74" s="49"/>
+      <c r="I74" s="49"/>
+      <c r="J74" s="49"/>
+      <c r="K74" s="49"/>
+      <c r="L74" s="49"/>
+      <c r="M74" s="49"/>
+      <c r="N74" s="49"/>
+      <c r="O74" s="49"/>
+      <c r="P74" s="49"/>
+      <c r="Q74" s="49"/>
+      <c r="R74" s="49"/>
+      <c r="S74" s="49"/>
+      <c r="T74" s="49"/>
+      <c r="U74" s="49"/>
+      <c r="V74" s="49"/>
+      <c r="W74" s="49"/>
+      <c r="X74" s="49"/>
+      <c r="Y74" s="49"/>
+      <c r="Z74" s="50"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="47" t="s">
+        <v>283</v>
+      </c>
+      <c r="B75" s="48">
         <v>0.0</v>
       </c>
-      <c r="C64" s="34" t="s">
-        <v>238</v>
-      </c>
-      <c r="D64" s="34" t="s">
-        <v>239</v>
-      </c>
-      <c r="E64" s="34" t="s">
-        <v>240</v>
-      </c>
-      <c r="F64" s="35"/>
-      <c r="G64" s="35"/>
-      <c r="H64" s="35"/>
-      <c r="I64" s="35"/>
-      <c r="J64" s="35"/>
-      <c r="K64" s="35"/>
-      <c r="L64" s="35"/>
-      <c r="M64" s="35"/>
-      <c r="N64" s="35"/>
-      <c r="O64" s="35"/>
-      <c r="P64" s="35"/>
-      <c r="Q64" s="35"/>
-      <c r="R64" s="35"/>
-      <c r="S64" s="35"/>
-      <c r="T64" s="35"/>
-      <c r="U64" s="35"/>
-      <c r="V64" s="35"/>
-      <c r="W64" s="35"/>
-      <c r="X64" s="35"/>
-      <c r="Y64" s="35"/>
-      <c r="Z64" s="36"/>
-    </row>
-    <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="37" t="s">
-        <v>241</v>
-      </c>
-      <c r="B65" s="38">
+      <c r="C75" s="48" t="s">
+        <v>284</v>
+      </c>
+      <c r="D75" s="48" t="s">
+        <v>285</v>
+      </c>
+      <c r="E75" s="48" t="s">
+        <v>286</v>
+      </c>
+      <c r="F75" s="49"/>
+      <c r="G75" s="49"/>
+      <c r="H75" s="49"/>
+      <c r="I75" s="49"/>
+      <c r="J75" s="49"/>
+      <c r="K75" s="49"/>
+      <c r="L75" s="49"/>
+      <c r="M75" s="49"/>
+      <c r="N75" s="49"/>
+      <c r="O75" s="49"/>
+      <c r="P75" s="49"/>
+      <c r="Q75" s="49"/>
+      <c r="R75" s="49"/>
+      <c r="S75" s="49"/>
+      <c r="T75" s="49"/>
+      <c r="U75" s="49"/>
+      <c r="V75" s="49"/>
+      <c r="W75" s="49"/>
+      <c r="X75" s="49"/>
+      <c r="Y75" s="49"/>
+      <c r="Z75" s="50"/>
+    </row>
+    <row r="76" ht="15.0" customHeight="1">
+      <c r="A76" s="47" t="s">
+        <v>287</v>
+      </c>
+      <c r="B76" s="48">
         <v>0.0</v>
       </c>
-      <c r="C65" s="38" t="s">
-        <v>242</v>
-      </c>
-      <c r="D65" s="38" t="s">
-        <v>243</v>
-      </c>
-      <c r="E65" s="38" t="s">
-        <v>244</v>
-      </c>
-      <c r="F65" s="39"/>
-      <c r="G65" s="39"/>
-      <c r="H65" s="39"/>
-      <c r="I65" s="39"/>
-      <c r="J65" s="39"/>
-      <c r="K65" s="39"/>
-      <c r="L65" s="39"/>
-      <c r="M65" s="39"/>
-      <c r="N65" s="39"/>
-      <c r="O65" s="39"/>
-      <c r="P65" s="39"/>
-      <c r="Q65" s="39"/>
-      <c r="R65" s="39"/>
-      <c r="S65" s="39"/>
-      <c r="T65" s="39"/>
-      <c r="U65" s="39"/>
-      <c r="V65" s="39"/>
-      <c r="W65" s="39"/>
-      <c r="X65" s="39"/>
-      <c r="Y65" s="39"/>
-      <c r="Z65" s="40"/>
-    </row>
-    <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="2"/>
-      <c r="B66" s="2"/>
-      <c r="C66" s="2"/>
-      <c r="D66" s="2"/>
-      <c r="E66" s="2"/>
-      <c r="F66" s="2"/>
-      <c r="G66" s="2"/>
-      <c r="H66" s="2"/>
-      <c r="I66" s="2"/>
-      <c r="J66" s="2"/>
-      <c r="K66" s="2"/>
-      <c r="L66" s="2"/>
-      <c r="M66" s="2"/>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
-      <c r="P66" s="2"/>
-      <c r="Q66" s="2"/>
-      <c r="R66" s="2"/>
-      <c r="S66" s="2"/>
-      <c r="T66" s="2"/>
-      <c r="U66" s="2"/>
-      <c r="V66" s="2"/>
-      <c r="W66" s="2"/>
-      <c r="X66" s="2"/>
-      <c r="Y66" s="2"/>
-      <c r="Z66" s="2"/>
-    </row>
-    <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="2"/>
-      <c r="B67" s="2"/>
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="2"/>
-      <c r="F67" s="2"/>
-      <c r="G67" s="2"/>
-      <c r="H67" s="2"/>
-      <c r="I67" s="2"/>
-      <c r="J67" s="2"/>
-      <c r="K67" s="2"/>
-      <c r="L67" s="2"/>
-      <c r="M67" s="2"/>
-      <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
-      <c r="P67" s="2"/>
-      <c r="Q67" s="2"/>
-      <c r="R67" s="2"/>
-      <c r="S67" s="2"/>
-      <c r="T67" s="2"/>
-      <c r="U67" s="2"/>
-      <c r="V67" s="2"/>
-      <c r="W67" s="2"/>
-      <c r="X67" s="2"/>
-      <c r="Y67" s="2"/>
-      <c r="Z67" s="2"/>
-    </row>
-    <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="2"/>
-      <c r="B68" s="2"/>
-      <c r="C68" s="2"/>
-      <c r="D68" s="2"/>
-      <c r="E68" s="2"/>
-      <c r="F68" s="2"/>
-      <c r="G68" s="2"/>
-      <c r="H68" s="2"/>
-      <c r="I68" s="2"/>
-      <c r="J68" s="2"/>
-      <c r="K68" s="2"/>
-      <c r="L68" s="2"/>
-      <c r="M68" s="2"/>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
-      <c r="P68" s="2"/>
-      <c r="Q68" s="2"/>
-      <c r="R68" s="2"/>
-      <c r="S68" s="2"/>
-      <c r="T68" s="2"/>
-      <c r="U68" s="2"/>
-      <c r="V68" s="2"/>
-      <c r="W68" s="2"/>
-      <c r="X68" s="2"/>
-      <c r="Y68" s="2"/>
-      <c r="Z68" s="2"/>
-    </row>
-    <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="2"/>
-      <c r="B69" s="2"/>
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
-      <c r="E69" s="2"/>
-      <c r="F69" s="2"/>
-      <c r="G69" s="2"/>
-      <c r="H69" s="2"/>
-      <c r="I69" s="2"/>
-      <c r="J69" s="2"/>
-      <c r="K69" s="2"/>
-      <c r="L69" s="2"/>
-      <c r="M69" s="2"/>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
-      <c r="P69" s="2"/>
-      <c r="Q69" s="2"/>
-      <c r="R69" s="2"/>
-      <c r="S69" s="2"/>
-      <c r="T69" s="2"/>
-      <c r="U69" s="2"/>
-      <c r="V69" s="2"/>
-      <c r="W69" s="2"/>
-      <c r="X69" s="2"/>
-      <c r="Y69" s="2"/>
-      <c r="Z69" s="2"/>
-    </row>
-    <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="2"/>
-      <c r="B70" s="2"/>
-      <c r="C70" s="2"/>
-      <c r="D70" s="2"/>
-      <c r="E70" s="2"/>
-      <c r="F70" s="2"/>
-      <c r="G70" s="2"/>
-      <c r="H70" s="2"/>
-      <c r="I70" s="2"/>
-      <c r="J70" s="2"/>
-      <c r="K70" s="2"/>
-      <c r="L70" s="2"/>
-      <c r="M70" s="2"/>
-      <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
-      <c r="P70" s="2"/>
-      <c r="Q70" s="2"/>
-      <c r="R70" s="2"/>
-      <c r="S70" s="2"/>
-      <c r="T70" s="2"/>
-      <c r="U70" s="2"/>
-      <c r="V70" s="2"/>
-      <c r="W70" s="2"/>
-      <c r="X70" s="2"/>
-      <c r="Y70" s="2"/>
-      <c r="Z70" s="2"/>
-    </row>
-    <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="2"/>
-      <c r="B71" s="2"/>
-      <c r="C71" s="2"/>
-      <c r="D71" s="2"/>
-      <c r="E71" s="2"/>
-      <c r="F71" s="2"/>
-      <c r="G71" s="2"/>
-      <c r="H71" s="2"/>
-      <c r="I71" s="2"/>
-      <c r="J71" s="2"/>
-      <c r="K71" s="2"/>
-      <c r="L71" s="2"/>
-      <c r="M71" s="2"/>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
-      <c r="P71" s="2"/>
-      <c r="Q71" s="2"/>
-      <c r="R71" s="2"/>
-      <c r="S71" s="2"/>
-      <c r="T71" s="2"/>
-      <c r="U71" s="2"/>
-      <c r="V71" s="2"/>
-      <c r="W71" s="2"/>
-      <c r="X71" s="2"/>
-      <c r="Y71" s="2"/>
-      <c r="Z71" s="2"/>
-    </row>
-    <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="2"/>
-      <c r="B72" s="2"/>
-      <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
-      <c r="F72" s="2"/>
-      <c r="G72" s="2"/>
-      <c r="H72" s="2"/>
-      <c r="I72" s="2"/>
-      <c r="J72" s="2"/>
-      <c r="K72" s="2"/>
-      <c r="L72" s="2"/>
-      <c r="M72" s="2"/>
-      <c r="N72" s="2"/>
-      <c r="O72" s="2"/>
-      <c r="P72" s="2"/>
-      <c r="Q72" s="2"/>
-      <c r="R72" s="2"/>
-      <c r="S72" s="2"/>
-      <c r="T72" s="2"/>
-      <c r="U72" s="2"/>
-      <c r="V72" s="2"/>
-      <c r="W72" s="2"/>
-      <c r="X72" s="2"/>
-      <c r="Y72" s="2"/>
-      <c r="Z72" s="2"/>
-    </row>
-    <row r="73" ht="15.0" customHeight="1">
-      <c r="A73" s="2"/>
-      <c r="B73" s="2"/>
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
-      <c r="F73" s="2"/>
-      <c r="G73" s="2"/>
-      <c r="H73" s="2"/>
-      <c r="I73" s="2"/>
-      <c r="J73" s="2"/>
-      <c r="K73" s="2"/>
-      <c r="L73" s="2"/>
-      <c r="M73" s="2"/>
-      <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
-      <c r="P73" s="2"/>
-      <c r="Q73" s="2"/>
-      <c r="R73" s="2"/>
-      <c r="S73" s="2"/>
-      <c r="T73" s="2"/>
-      <c r="U73" s="2"/>
-      <c r="V73" s="2"/>
-      <c r="W73" s="2"/>
-      <c r="X73" s="2"/>
-      <c r="Y73" s="2"/>
-      <c r="Z73" s="2"/>
-    </row>
-    <row r="74" ht="15.0" customHeight="1">
-      <c r="A74" s="2"/>
-      <c r="B74" s="2"/>
-      <c r="C74" s="2"/>
-      <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
-      <c r="F74" s="2"/>
-      <c r="G74" s="2"/>
-      <c r="H74" s="2"/>
-      <c r="I74" s="2"/>
-      <c r="J74" s="2"/>
-      <c r="K74" s="2"/>
-      <c r="L74" s="2"/>
-      <c r="M74" s="2"/>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
-      <c r="P74" s="2"/>
-      <c r="Q74" s="2"/>
-      <c r="R74" s="2"/>
-      <c r="S74" s="2"/>
-      <c r="T74" s="2"/>
-      <c r="U74" s="2"/>
-      <c r="V74" s="2"/>
-      <c r="W74" s="2"/>
-      <c r="X74" s="2"/>
-      <c r="Y74" s="2"/>
-      <c r="Z74" s="2"/>
-    </row>
-    <row r="75" ht="15.0" customHeight="1">
-      <c r="A75" s="2"/>
-      <c r="B75" s="2"/>
-      <c r="C75" s="2"/>
-      <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
-      <c r="F75" s="2"/>
-      <c r="G75" s="2"/>
-      <c r="H75" s="2"/>
-      <c r="I75" s="2"/>
-      <c r="J75" s="2"/>
-      <c r="K75" s="2"/>
-      <c r="L75" s="2"/>
-      <c r="M75" s="2"/>
-      <c r="N75" s="2"/>
-      <c r="O75" s="2"/>
-      <c r="P75" s="2"/>
-      <c r="Q75" s="2"/>
-      <c r="R75" s="2"/>
-      <c r="S75" s="2"/>
-      <c r="T75" s="2"/>
-      <c r="U75" s="2"/>
-      <c r="V75" s="2"/>
-      <c r="W75" s="2"/>
-      <c r="X75" s="2"/>
-      <c r="Y75" s="2"/>
-      <c r="Z75" s="2"/>
-    </row>
-    <row r="76" ht="15.0" customHeight="1">
-      <c r="A76" s="2"/>
-      <c r="B76" s="2"/>
-      <c r="C76" s="2"/>
-      <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
-      <c r="F76" s="2"/>
-      <c r="G76" s="2"/>
-      <c r="H76" s="2"/>
-      <c r="I76" s="2"/>
-      <c r="J76" s="2"/>
-      <c r="K76" s="2"/>
-      <c r="L76" s="2"/>
-      <c r="M76" s="2"/>
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
-      <c r="P76" s="2"/>
-      <c r="Q76" s="2"/>
-      <c r="R76" s="2"/>
-      <c r="S76" s="2"/>
-      <c r="T76" s="2"/>
-      <c r="U76" s="2"/>
-      <c r="V76" s="2"/>
-      <c r="W76" s="2"/>
-      <c r="X76" s="2"/>
-      <c r="Y76" s="2"/>
-      <c r="Z76" s="2"/>
+      <c r="C76" s="48" t="s">
+        <v>288</v>
+      </c>
+      <c r="D76" s="48" t="s">
+        <v>289</v>
+      </c>
+      <c r="E76" s="48" t="s">
+        <v>290</v>
+      </c>
+      <c r="F76" s="49"/>
+      <c r="G76" s="49"/>
+      <c r="H76" s="49"/>
+      <c r="I76" s="49"/>
+      <c r="J76" s="49"/>
+      <c r="K76" s="49"/>
+      <c r="L76" s="49"/>
+      <c r="M76" s="49"/>
+      <c r="N76" s="49"/>
+      <c r="O76" s="49"/>
+      <c r="P76" s="49"/>
+      <c r="Q76" s="49"/>
+      <c r="R76" s="49"/>
+      <c r="S76" s="49"/>
+      <c r="T76" s="49"/>
+      <c r="U76" s="49"/>
+      <c r="V76" s="49"/>
+      <c r="W76" s="49"/>
+      <c r="X76" s="49"/>
+      <c r="Y76" s="49"/>
+      <c r="Z76" s="50"/>
     </row>
     <row r="77" ht="15.0" customHeight="1">
-      <c r="A77" s="2"/>
-      <c r="B77" s="2"/>
-      <c r="C77" s="2"/>
-      <c r="D77" s="2"/>
-      <c r="E77" s="2"/>
-      <c r="F77" s="2"/>
-      <c r="G77" s="2"/>
-      <c r="H77" s="2"/>
-      <c r="I77" s="2"/>
-      <c r="J77" s="2"/>
-      <c r="K77" s="2"/>
-      <c r="L77" s="2"/>
-      <c r="M77" s="2"/>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
-      <c r="P77" s="2"/>
-      <c r="Q77" s="2"/>
-      <c r="R77" s="2"/>
-      <c r="S77" s="2"/>
-      <c r="T77" s="2"/>
-      <c r="U77" s="2"/>
-      <c r="V77" s="2"/>
-      <c r="W77" s="2"/>
-      <c r="X77" s="2"/>
-      <c r="Y77" s="2"/>
-      <c r="Z77" s="2"/>
+      <c r="A77" s="47" t="s">
+        <v>291</v>
+      </c>
+      <c r="B77" s="48">
+        <v>0.0</v>
+      </c>
+      <c r="C77" s="48" t="s">
+        <v>292</v>
+      </c>
+      <c r="D77" s="48" t="s">
+        <v>293</v>
+      </c>
+      <c r="E77" s="48" t="s">
+        <v>294</v>
+      </c>
+      <c r="F77" s="49"/>
+      <c r="G77" s="49"/>
+      <c r="H77" s="49"/>
+      <c r="I77" s="49"/>
+      <c r="J77" s="49"/>
+      <c r="K77" s="49"/>
+      <c r="L77" s="49"/>
+      <c r="M77" s="49"/>
+      <c r="N77" s="49"/>
+      <c r="O77" s="49"/>
+      <c r="P77" s="49"/>
+      <c r="Q77" s="49"/>
+      <c r="R77" s="49"/>
+      <c r="S77" s="49"/>
+      <c r="T77" s="49"/>
+      <c r="U77" s="49"/>
+      <c r="V77" s="49"/>
+      <c r="W77" s="49"/>
+      <c r="X77" s="49"/>
+      <c r="Y77" s="49"/>
+      <c r="Z77" s="50"/>
     </row>
     <row r="78" ht="15.0" customHeight="1">
-      <c r="A78" s="2"/>
-      <c r="B78" s="2"/>
-      <c r="C78" s="2"/>
-      <c r="D78" s="2"/>
-      <c r="E78" s="2"/>
-      <c r="F78" s="2"/>
-      <c r="G78" s="2"/>
-      <c r="H78" s="2"/>
-      <c r="I78" s="2"/>
-      <c r="J78" s="2"/>
-      <c r="K78" s="2"/>
-      <c r="L78" s="2"/>
-      <c r="M78" s="2"/>
-      <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
-      <c r="P78" s="2"/>
-      <c r="Q78" s="2"/>
-      <c r="R78" s="2"/>
-      <c r="S78" s="2"/>
-      <c r="T78" s="2"/>
-      <c r="U78" s="2"/>
-      <c r="V78" s="2"/>
-      <c r="W78" s="2"/>
-      <c r="X78" s="2"/>
-      <c r="Y78" s="2"/>
-      <c r="Z78" s="2"/>
+      <c r="A78" s="47" t="s">
+        <v>295</v>
+      </c>
+      <c r="B78" s="48">
+        <v>0.0</v>
+      </c>
+      <c r="C78" s="48" t="s">
+        <v>296</v>
+      </c>
+      <c r="D78" s="48" t="s">
+        <v>297</v>
+      </c>
+      <c r="E78" s="48" t="s">
+        <v>298</v>
+      </c>
+      <c r="F78" s="49"/>
+      <c r="G78" s="49"/>
+      <c r="H78" s="49"/>
+      <c r="I78" s="49"/>
+      <c r="J78" s="49"/>
+      <c r="K78" s="49"/>
+      <c r="L78" s="49"/>
+      <c r="M78" s="49"/>
+      <c r="N78" s="49"/>
+      <c r="O78" s="49"/>
+      <c r="P78" s="49"/>
+      <c r="Q78" s="49"/>
+      <c r="R78" s="49"/>
+      <c r="S78" s="49"/>
+      <c r="T78" s="49"/>
+      <c r="U78" s="49"/>
+      <c r="V78" s="49"/>
+      <c r="W78" s="49"/>
+      <c r="X78" s="49"/>
+      <c r="Y78" s="49"/>
+      <c r="Z78" s="50"/>
     </row>
     <row r="79" ht="15.0" customHeight="1">
-      <c r="A79" s="2"/>
-      <c r="B79" s="2"/>
-      <c r="C79" s="2"/>
-      <c r="D79" s="2"/>
-      <c r="E79" s="2"/>
-      <c r="F79" s="2"/>
-      <c r="G79" s="2"/>
-      <c r="H79" s="2"/>
-      <c r="I79" s="2"/>
-      <c r="J79" s="2"/>
-      <c r="K79" s="2"/>
-      <c r="L79" s="2"/>
-      <c r="M79" s="2"/>
-      <c r="N79" s="2"/>
-      <c r="O79" s="2"/>
-      <c r="P79" s="2"/>
-      <c r="Q79" s="2"/>
-      <c r="R79" s="2"/>
-      <c r="S79" s="2"/>
-      <c r="T79" s="2"/>
-      <c r="U79" s="2"/>
-      <c r="V79" s="2"/>
-      <c r="W79" s="2"/>
-      <c r="X79" s="2"/>
-      <c r="Y79" s="2"/>
-      <c r="Z79" s="2"/>
+      <c r="A79" s="51" t="s">
+        <v>299</v>
+      </c>
+      <c r="B79" s="52">
+        <v>0.0</v>
+      </c>
+      <c r="C79" s="53" t="s">
+        <v>300</v>
+      </c>
+      <c r="D79" s="54" t="s">
+        <v>211</v>
+      </c>
+      <c r="E79" s="54" t="s">
+        <v>212</v>
+      </c>
+      <c r="F79" s="55"/>
+      <c r="G79" s="55"/>
+      <c r="H79" s="55"/>
+      <c r="I79" s="55"/>
+      <c r="J79" s="55"/>
+      <c r="K79" s="55"/>
+      <c r="L79" s="55"/>
+      <c r="M79" s="55"/>
+      <c r="N79" s="55"/>
+      <c r="O79" s="55"/>
+      <c r="P79" s="55"/>
+      <c r="Q79" s="55"/>
+      <c r="R79" s="55"/>
+      <c r="S79" s="55"/>
+      <c r="T79" s="55"/>
+      <c r="U79" s="55"/>
+      <c r="V79" s="55"/>
+      <c r="W79" s="55"/>
+      <c r="X79" s="55"/>
+      <c r="Y79" s="55"/>
+      <c r="Z79" s="56"/>
     </row>
     <row r="80" ht="15.0" customHeight="1">
-      <c r="A80" s="2"/>
-      <c r="B80" s="2"/>
-      <c r="C80" s="2"/>
-      <c r="D80" s="2"/>
-      <c r="E80" s="2"/>
-      <c r="F80" s="2"/>
-      <c r="G80" s="2"/>
-      <c r="H80" s="2"/>
-      <c r="I80" s="2"/>
-      <c r="J80" s="2"/>
-      <c r="K80" s="2"/>
-      <c r="L80" s="2"/>
-      <c r="M80" s="2"/>
-      <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
-      <c r="P80" s="2"/>
-      <c r="Q80" s="2"/>
-      <c r="R80" s="2"/>
-      <c r="S80" s="2"/>
-      <c r="T80" s="2"/>
-      <c r="U80" s="2"/>
-      <c r="V80" s="2"/>
-      <c r="W80" s="2"/>
-      <c r="X80" s="2"/>
-      <c r="Y80" s="2"/>
-      <c r="Z80" s="2"/>
+      <c r="A80" s="57" t="s">
+        <v>301</v>
+      </c>
+      <c r="B80" s="58">
+        <v>0.0</v>
+      </c>
+      <c r="C80" s="59" t="s">
+        <v>302</v>
+      </c>
+      <c r="D80" s="60" t="s">
+        <v>143</v>
+      </c>
+      <c r="E80" s="60" t="s">
+        <v>144</v>
+      </c>
+      <c r="F80" s="61"/>
+      <c r="G80" s="61"/>
+      <c r="H80" s="61"/>
+      <c r="I80" s="61"/>
+      <c r="J80" s="61"/>
+      <c r="K80" s="61"/>
+      <c r="L80" s="61"/>
+      <c r="M80" s="61"/>
+      <c r="N80" s="61"/>
+      <c r="O80" s="61"/>
+      <c r="P80" s="61"/>
+      <c r="Q80" s="61"/>
+      <c r="R80" s="61"/>
+      <c r="S80" s="61"/>
+      <c r="T80" s="61"/>
+      <c r="U80" s="61"/>
+      <c r="V80" s="61"/>
+      <c r="W80" s="61"/>
+      <c r="X80" s="61"/>
+      <c r="Y80" s="61"/>
+      <c r="Z80" s="62"/>
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="2"/>
@@ -8776,7 +9202,7 @@
       <c r="Y249" s="2"/>
       <c r="Z249" s="2"/>
     </row>
-    <row r="250" ht="15.75" customHeight="1">
+    <row r="250" ht="15.0" customHeight="1">
       <c r="A250" s="2"/>
       <c r="B250" s="2"/>
       <c r="C250" s="2"/>
@@ -8804,7 +9230,7 @@
       <c r="Y250" s="2"/>
       <c r="Z250" s="2"/>
     </row>
-    <row r="251" ht="15.75" customHeight="1">
+    <row r="251" ht="15.0" customHeight="1">
       <c r="A251" s="2"/>
       <c r="B251" s="2"/>
       <c r="C251" s="2"/>
@@ -8832,7 +9258,7 @@
       <c r="Y251" s="2"/>
       <c r="Z251" s="2"/>
     </row>
-    <row r="252" ht="15.75" customHeight="1">
+    <row r="252" ht="15.0" customHeight="1">
       <c r="A252" s="2"/>
       <c r="B252" s="2"/>
       <c r="C252" s="2"/>
@@ -8860,7 +9286,7 @@
       <c r="Y252" s="2"/>
       <c r="Z252" s="2"/>
     </row>
-    <row r="253" ht="15.75" customHeight="1">
+    <row r="253" ht="15.0" customHeight="1">
       <c r="A253" s="2"/>
       <c r="B253" s="2"/>
       <c r="C253" s="2"/>
@@ -8888,7 +9314,7 @@
       <c r="Y253" s="2"/>
       <c r="Z253" s="2"/>
     </row>
-    <row r="254" ht="15.75" customHeight="1">
+    <row r="254" ht="15.0" customHeight="1">
       <c r="A254" s="2"/>
       <c r="B254" s="2"/>
       <c r="C254" s="2"/>
@@ -8916,7 +9342,7 @@
       <c r="Y254" s="2"/>
       <c r="Z254" s="2"/>
     </row>
-    <row r="255" ht="15.75" customHeight="1">
+    <row r="255" ht="15.0" customHeight="1">
       <c r="A255" s="2"/>
       <c r="B255" s="2"/>
       <c r="C255" s="2"/>
@@ -8944,7 +9370,7 @@
       <c r="Y255" s="2"/>
       <c r="Z255" s="2"/>
     </row>
-    <row r="256" ht="15.75" customHeight="1">
+    <row r="256" ht="15.0" customHeight="1">
       <c r="A256" s="2"/>
       <c r="B256" s="2"/>
       <c r="C256" s="2"/>
@@ -8972,7 +9398,7 @@
       <c r="Y256" s="2"/>
       <c r="Z256" s="2"/>
     </row>
-    <row r="257" ht="15.75" customHeight="1">
+    <row r="257" ht="15.0" customHeight="1">
       <c r="A257" s="2"/>
       <c r="B257" s="2"/>
       <c r="C257" s="2"/>
@@ -9000,7 +9426,7 @@
       <c r="Y257" s="2"/>
       <c r="Z257" s="2"/>
     </row>
-    <row r="258" ht="15.75" customHeight="1">
+    <row r="258" ht="15.0" customHeight="1">
       <c r="A258" s="2"/>
       <c r="B258" s="2"/>
       <c r="C258" s="2"/>
@@ -9028,7 +9454,7 @@
       <c r="Y258" s="2"/>
       <c r="Z258" s="2"/>
     </row>
-    <row r="259" ht="15.75" customHeight="1">
+    <row r="259" ht="15.0" customHeight="1">
       <c r="A259" s="2"/>
       <c r="B259" s="2"/>
       <c r="C259" s="2"/>
@@ -9056,7 +9482,7 @@
       <c r="Y259" s="2"/>
       <c r="Z259" s="2"/>
     </row>
-    <row r="260" ht="15.75" customHeight="1">
+    <row r="260" ht="15.0" customHeight="1">
       <c r="A260" s="2"/>
       <c r="B260" s="2"/>
       <c r="C260" s="2"/>
@@ -9084,7 +9510,7 @@
       <c r="Y260" s="2"/>
       <c r="Z260" s="2"/>
     </row>
-    <row r="261" ht="15.75" customHeight="1">
+    <row r="261" ht="15.0" customHeight="1">
       <c r="A261" s="2"/>
       <c r="B261" s="2"/>
       <c r="C261" s="2"/>
@@ -9112,7 +9538,7 @@
       <c r="Y261" s="2"/>
       <c r="Z261" s="2"/>
     </row>
-    <row r="262" ht="15.75" customHeight="1">
+    <row r="262" ht="15.0" customHeight="1">
       <c r="A262" s="2"/>
       <c r="B262" s="2"/>
       <c r="C262" s="2"/>
@@ -9140,7 +9566,7 @@
       <c r="Y262" s="2"/>
       <c r="Z262" s="2"/>
     </row>
-    <row r="263" ht="15.75" customHeight="1">
+    <row r="263" ht="15.0" customHeight="1">
       <c r="A263" s="2"/>
       <c r="B263" s="2"/>
       <c r="C263" s="2"/>
@@ -9168,7 +9594,7 @@
       <c r="Y263" s="2"/>
       <c r="Z263" s="2"/>
     </row>
-    <row r="264" ht="15.75" customHeight="1">
+    <row r="264" ht="15.0" customHeight="1">
       <c r="A264" s="2"/>
       <c r="B264" s="2"/>
       <c r="C264" s="2"/>
@@ -30420,6 +30846,426 @@
       <c r="Y1022" s="2"/>
       <c r="Z1022" s="2"/>
     </row>
+    <row r="1023" ht="15.75" customHeight="1">
+      <c r="A1023" s="2"/>
+      <c r="B1023" s="2"/>
+      <c r="C1023" s="2"/>
+      <c r="D1023" s="2"/>
+      <c r="E1023" s="2"/>
+      <c r="F1023" s="2"/>
+      <c r="G1023" s="2"/>
+      <c r="H1023" s="2"/>
+      <c r="I1023" s="2"/>
+      <c r="J1023" s="2"/>
+      <c r="K1023" s="2"/>
+      <c r="L1023" s="2"/>
+      <c r="M1023" s="2"/>
+      <c r="N1023" s="2"/>
+      <c r="O1023" s="2"/>
+      <c r="P1023" s="2"/>
+      <c r="Q1023" s="2"/>
+      <c r="R1023" s="2"/>
+      <c r="S1023" s="2"/>
+      <c r="T1023" s="2"/>
+      <c r="U1023" s="2"/>
+      <c r="V1023" s="2"/>
+      <c r="W1023" s="2"/>
+      <c r="X1023" s="2"/>
+      <c r="Y1023" s="2"/>
+      <c r="Z1023" s="2"/>
+    </row>
+    <row r="1024" ht="15.75" customHeight="1">
+      <c r="A1024" s="2"/>
+      <c r="B1024" s="2"/>
+      <c r="C1024" s="2"/>
+      <c r="D1024" s="2"/>
+      <c r="E1024" s="2"/>
+      <c r="F1024" s="2"/>
+      <c r="G1024" s="2"/>
+      <c r="H1024" s="2"/>
+      <c r="I1024" s="2"/>
+      <c r="J1024" s="2"/>
+      <c r="K1024" s="2"/>
+      <c r="L1024" s="2"/>
+      <c r="M1024" s="2"/>
+      <c r="N1024" s="2"/>
+      <c r="O1024" s="2"/>
+      <c r="P1024" s="2"/>
+      <c r="Q1024" s="2"/>
+      <c r="R1024" s="2"/>
+      <c r="S1024" s="2"/>
+      <c r="T1024" s="2"/>
+      <c r="U1024" s="2"/>
+      <c r="V1024" s="2"/>
+      <c r="W1024" s="2"/>
+      <c r="X1024" s="2"/>
+      <c r="Y1024" s="2"/>
+      <c r="Z1024" s="2"/>
+    </row>
+    <row r="1025" ht="15.75" customHeight="1">
+      <c r="A1025" s="2"/>
+      <c r="B1025" s="2"/>
+      <c r="C1025" s="2"/>
+      <c r="D1025" s="2"/>
+      <c r="E1025" s="2"/>
+      <c r="F1025" s="2"/>
+      <c r="G1025" s="2"/>
+      <c r="H1025" s="2"/>
+      <c r="I1025" s="2"/>
+      <c r="J1025" s="2"/>
+      <c r="K1025" s="2"/>
+      <c r="L1025" s="2"/>
+      <c r="M1025" s="2"/>
+      <c r="N1025" s="2"/>
+      <c r="O1025" s="2"/>
+      <c r="P1025" s="2"/>
+      <c r="Q1025" s="2"/>
+      <c r="R1025" s="2"/>
+      <c r="S1025" s="2"/>
+      <c r="T1025" s="2"/>
+      <c r="U1025" s="2"/>
+      <c r="V1025" s="2"/>
+      <c r="W1025" s="2"/>
+      <c r="X1025" s="2"/>
+      <c r="Y1025" s="2"/>
+      <c r="Z1025" s="2"/>
+    </row>
+    <row r="1026" ht="15.75" customHeight="1">
+      <c r="A1026" s="2"/>
+      <c r="B1026" s="2"/>
+      <c r="C1026" s="2"/>
+      <c r="D1026" s="2"/>
+      <c r="E1026" s="2"/>
+      <c r="F1026" s="2"/>
+      <c r="G1026" s="2"/>
+      <c r="H1026" s="2"/>
+      <c r="I1026" s="2"/>
+      <c r="J1026" s="2"/>
+      <c r="K1026" s="2"/>
+      <c r="L1026" s="2"/>
+      <c r="M1026" s="2"/>
+      <c r="N1026" s="2"/>
+      <c r="O1026" s="2"/>
+      <c r="P1026" s="2"/>
+      <c r="Q1026" s="2"/>
+      <c r="R1026" s="2"/>
+      <c r="S1026" s="2"/>
+      <c r="T1026" s="2"/>
+      <c r="U1026" s="2"/>
+      <c r="V1026" s="2"/>
+      <c r="W1026" s="2"/>
+      <c r="X1026" s="2"/>
+      <c r="Y1026" s="2"/>
+      <c r="Z1026" s="2"/>
+    </row>
+    <row r="1027" ht="15.75" customHeight="1">
+      <c r="A1027" s="2"/>
+      <c r="B1027" s="2"/>
+      <c r="C1027" s="2"/>
+      <c r="D1027" s="2"/>
+      <c r="E1027" s="2"/>
+      <c r="F1027" s="2"/>
+      <c r="G1027" s="2"/>
+      <c r="H1027" s="2"/>
+      <c r="I1027" s="2"/>
+      <c r="J1027" s="2"/>
+      <c r="K1027" s="2"/>
+      <c r="L1027" s="2"/>
+      <c r="M1027" s="2"/>
+      <c r="N1027" s="2"/>
+      <c r="O1027" s="2"/>
+      <c r="P1027" s="2"/>
+      <c r="Q1027" s="2"/>
+      <c r="R1027" s="2"/>
+      <c r="S1027" s="2"/>
+      <c r="T1027" s="2"/>
+      <c r="U1027" s="2"/>
+      <c r="V1027" s="2"/>
+      <c r="W1027" s="2"/>
+      <c r="X1027" s="2"/>
+      <c r="Y1027" s="2"/>
+      <c r="Z1027" s="2"/>
+    </row>
+    <row r="1028" ht="15.75" customHeight="1">
+      <c r="A1028" s="2"/>
+      <c r="B1028" s="2"/>
+      <c r="C1028" s="2"/>
+      <c r="D1028" s="2"/>
+      <c r="E1028" s="2"/>
+      <c r="F1028" s="2"/>
+      <c r="G1028" s="2"/>
+      <c r="H1028" s="2"/>
+      <c r="I1028" s="2"/>
+      <c r="J1028" s="2"/>
+      <c r="K1028" s="2"/>
+      <c r="L1028" s="2"/>
+      <c r="M1028" s="2"/>
+      <c r="N1028" s="2"/>
+      <c r="O1028" s="2"/>
+      <c r="P1028" s="2"/>
+      <c r="Q1028" s="2"/>
+      <c r="R1028" s="2"/>
+      <c r="S1028" s="2"/>
+      <c r="T1028" s="2"/>
+      <c r="U1028" s="2"/>
+      <c r="V1028" s="2"/>
+      <c r="W1028" s="2"/>
+      <c r="X1028" s="2"/>
+      <c r="Y1028" s="2"/>
+      <c r="Z1028" s="2"/>
+    </row>
+    <row r="1029" ht="15.75" customHeight="1">
+      <c r="A1029" s="2"/>
+      <c r="B1029" s="2"/>
+      <c r="C1029" s="2"/>
+      <c r="D1029" s="2"/>
+      <c r="E1029" s="2"/>
+      <c r="F1029" s="2"/>
+      <c r="G1029" s="2"/>
+      <c r="H1029" s="2"/>
+      <c r="I1029" s="2"/>
+      <c r="J1029" s="2"/>
+      <c r="K1029" s="2"/>
+      <c r="L1029" s="2"/>
+      <c r="M1029" s="2"/>
+      <c r="N1029" s="2"/>
+      <c r="O1029" s="2"/>
+      <c r="P1029" s="2"/>
+      <c r="Q1029" s="2"/>
+      <c r="R1029" s="2"/>
+      <c r="S1029" s="2"/>
+      <c r="T1029" s="2"/>
+      <c r="U1029" s="2"/>
+      <c r="V1029" s="2"/>
+      <c r="W1029" s="2"/>
+      <c r="X1029" s="2"/>
+      <c r="Y1029" s="2"/>
+      <c r="Z1029" s="2"/>
+    </row>
+    <row r="1030" ht="15.75" customHeight="1">
+      <c r="A1030" s="2"/>
+      <c r="B1030" s="2"/>
+      <c r="C1030" s="2"/>
+      <c r="D1030" s="2"/>
+      <c r="E1030" s="2"/>
+      <c r="F1030" s="2"/>
+      <c r="G1030" s="2"/>
+      <c r="H1030" s="2"/>
+      <c r="I1030" s="2"/>
+      <c r="J1030" s="2"/>
+      <c r="K1030" s="2"/>
+      <c r="L1030" s="2"/>
+      <c r="M1030" s="2"/>
+      <c r="N1030" s="2"/>
+      <c r="O1030" s="2"/>
+      <c r="P1030" s="2"/>
+      <c r="Q1030" s="2"/>
+      <c r="R1030" s="2"/>
+      <c r="S1030" s="2"/>
+      <c r="T1030" s="2"/>
+      <c r="U1030" s="2"/>
+      <c r="V1030" s="2"/>
+      <c r="W1030" s="2"/>
+      <c r="X1030" s="2"/>
+      <c r="Y1030" s="2"/>
+      <c r="Z1030" s="2"/>
+    </row>
+    <row r="1031" ht="15.75" customHeight="1">
+      <c r="A1031" s="2"/>
+      <c r="B1031" s="2"/>
+      <c r="C1031" s="2"/>
+      <c r="D1031" s="2"/>
+      <c r="E1031" s="2"/>
+      <c r="F1031" s="2"/>
+      <c r="G1031" s="2"/>
+      <c r="H1031" s="2"/>
+      <c r="I1031" s="2"/>
+      <c r="J1031" s="2"/>
+      <c r="K1031" s="2"/>
+      <c r="L1031" s="2"/>
+      <c r="M1031" s="2"/>
+      <c r="N1031" s="2"/>
+      <c r="O1031" s="2"/>
+      <c r="P1031" s="2"/>
+      <c r="Q1031" s="2"/>
+      <c r="R1031" s="2"/>
+      <c r="S1031" s="2"/>
+      <c r="T1031" s="2"/>
+      <c r="U1031" s="2"/>
+      <c r="V1031" s="2"/>
+      <c r="W1031" s="2"/>
+      <c r="X1031" s="2"/>
+      <c r="Y1031" s="2"/>
+      <c r="Z1031" s="2"/>
+    </row>
+    <row r="1032" ht="15.75" customHeight="1">
+      <c r="A1032" s="2"/>
+      <c r="B1032" s="2"/>
+      <c r="C1032" s="2"/>
+      <c r="D1032" s="2"/>
+      <c r="E1032" s="2"/>
+      <c r="F1032" s="2"/>
+      <c r="G1032" s="2"/>
+      <c r="H1032" s="2"/>
+      <c r="I1032" s="2"/>
+      <c r="J1032" s="2"/>
+      <c r="K1032" s="2"/>
+      <c r="L1032" s="2"/>
+      <c r="M1032" s="2"/>
+      <c r="N1032" s="2"/>
+      <c r="O1032" s="2"/>
+      <c r="P1032" s="2"/>
+      <c r="Q1032" s="2"/>
+      <c r="R1032" s="2"/>
+      <c r="S1032" s="2"/>
+      <c r="T1032" s="2"/>
+      <c r="U1032" s="2"/>
+      <c r="V1032" s="2"/>
+      <c r="W1032" s="2"/>
+      <c r="X1032" s="2"/>
+      <c r="Y1032" s="2"/>
+      <c r="Z1032" s="2"/>
+    </row>
+    <row r="1033" ht="15.75" customHeight="1">
+      <c r="A1033" s="2"/>
+      <c r="B1033" s="2"/>
+      <c r="C1033" s="2"/>
+      <c r="D1033" s="2"/>
+      <c r="E1033" s="2"/>
+      <c r="F1033" s="2"/>
+      <c r="G1033" s="2"/>
+      <c r="H1033" s="2"/>
+      <c r="I1033" s="2"/>
+      <c r="J1033" s="2"/>
+      <c r="K1033" s="2"/>
+      <c r="L1033" s="2"/>
+      <c r="M1033" s="2"/>
+      <c r="N1033" s="2"/>
+      <c r="O1033" s="2"/>
+      <c r="P1033" s="2"/>
+      <c r="Q1033" s="2"/>
+      <c r="R1033" s="2"/>
+      <c r="S1033" s="2"/>
+      <c r="T1033" s="2"/>
+      <c r="U1033" s="2"/>
+      <c r="V1033" s="2"/>
+      <c r="W1033" s="2"/>
+      <c r="X1033" s="2"/>
+      <c r="Y1033" s="2"/>
+      <c r="Z1033" s="2"/>
+    </row>
+    <row r="1034" ht="15.75" customHeight="1">
+      <c r="A1034" s="2"/>
+      <c r="B1034" s="2"/>
+      <c r="C1034" s="2"/>
+      <c r="D1034" s="2"/>
+      <c r="E1034" s="2"/>
+      <c r="F1034" s="2"/>
+      <c r="G1034" s="2"/>
+      <c r="H1034" s="2"/>
+      <c r="I1034" s="2"/>
+      <c r="J1034" s="2"/>
+      <c r="K1034" s="2"/>
+      <c r="L1034" s="2"/>
+      <c r="M1034" s="2"/>
+      <c r="N1034" s="2"/>
+      <c r="O1034" s="2"/>
+      <c r="P1034" s="2"/>
+      <c r="Q1034" s="2"/>
+      <c r="R1034" s="2"/>
+      <c r="S1034" s="2"/>
+      <c r="T1034" s="2"/>
+      <c r="U1034" s="2"/>
+      <c r="V1034" s="2"/>
+      <c r="W1034" s="2"/>
+      <c r="X1034" s="2"/>
+      <c r="Y1034" s="2"/>
+      <c r="Z1034" s="2"/>
+    </row>
+    <row r="1035" ht="15.75" customHeight="1">
+      <c r="A1035" s="2"/>
+      <c r="B1035" s="2"/>
+      <c r="C1035" s="2"/>
+      <c r="D1035" s="2"/>
+      <c r="E1035" s="2"/>
+      <c r="F1035" s="2"/>
+      <c r="G1035" s="2"/>
+      <c r="H1035" s="2"/>
+      <c r="I1035" s="2"/>
+      <c r="J1035" s="2"/>
+      <c r="K1035" s="2"/>
+      <c r="L1035" s="2"/>
+      <c r="M1035" s="2"/>
+      <c r="N1035" s="2"/>
+      <c r="O1035" s="2"/>
+      <c r="P1035" s="2"/>
+      <c r="Q1035" s="2"/>
+      <c r="R1035" s="2"/>
+      <c r="S1035" s="2"/>
+      <c r="T1035" s="2"/>
+      <c r="U1035" s="2"/>
+      <c r="V1035" s="2"/>
+      <c r="W1035" s="2"/>
+      <c r="X1035" s="2"/>
+      <c r="Y1035" s="2"/>
+      <c r="Z1035" s="2"/>
+    </row>
+    <row r="1036" ht="15.75" customHeight="1">
+      <c r="A1036" s="2"/>
+      <c r="B1036" s="2"/>
+      <c r="C1036" s="2"/>
+      <c r="D1036" s="2"/>
+      <c r="E1036" s="2"/>
+      <c r="F1036" s="2"/>
+      <c r="G1036" s="2"/>
+      <c r="H1036" s="2"/>
+      <c r="I1036" s="2"/>
+      <c r="J1036" s="2"/>
+      <c r="K1036" s="2"/>
+      <c r="L1036" s="2"/>
+      <c r="M1036" s="2"/>
+      <c r="N1036" s="2"/>
+      <c r="O1036" s="2"/>
+      <c r="P1036" s="2"/>
+      <c r="Q1036" s="2"/>
+      <c r="R1036" s="2"/>
+      <c r="S1036" s="2"/>
+      <c r="T1036" s="2"/>
+      <c r="U1036" s="2"/>
+      <c r="V1036" s="2"/>
+      <c r="W1036" s="2"/>
+      <c r="X1036" s="2"/>
+      <c r="Y1036" s="2"/>
+      <c r="Z1036" s="2"/>
+    </row>
+    <row r="1037" ht="15.75" customHeight="1">
+      <c r="A1037" s="2"/>
+      <c r="B1037" s="2"/>
+      <c r="C1037" s="2"/>
+      <c r="D1037" s="2"/>
+      <c r="E1037" s="2"/>
+      <c r="F1037" s="2"/>
+      <c r="G1037" s="2"/>
+      <c r="H1037" s="2"/>
+      <c r="I1037" s="2"/>
+      <c r="J1037" s="2"/>
+      <c r="K1037" s="2"/>
+      <c r="L1037" s="2"/>
+      <c r="M1037" s="2"/>
+      <c r="N1037" s="2"/>
+      <c r="O1037" s="2"/>
+      <c r="P1037" s="2"/>
+      <c r="Q1037" s="2"/>
+      <c r="R1037" s="2"/>
+      <c r="S1037" s="2"/>
+      <c r="T1037" s="2"/>
+      <c r="U1037" s="2"/>
+      <c r="V1037" s="2"/>
+      <c r="W1037" s="2"/>
+      <c r="X1037" s="2"/>
+      <c r="Y1037" s="2"/>
+      <c r="Z1037" s="2"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Templates/Tables/StringInfo/StrTable.xlsx
+++ b/Templates/Tables/StringInfo/StrTable.xlsx
@@ -202,7 +202,7 @@
     <t>추적 설명 팝업 메세지</t>
   </si>
   <si>
-    <t>앱 추적을 승인\n해주세요</t>
+    <t>앱 추적을 승인해\n주세요</t>
   </si>
   <si>
     <t>Allow tracking on the\nnext screen for</t>

--- a/Templates/Tables/StringInfo/StrTable.xlsx
+++ b/Templates/Tables/StringInfo/StrTable.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="311">
   <si>
     <t>ID</t>
   </si>
@@ -40,6 +40,18 @@
     <t>Do you want to quit the editor?</t>
   </si>
   <si>
+    <t>EDITOR_RESET_P_MSG</t>
+  </si>
+  <si>
+    <t>에디터 리셋 팝업 메세지</t>
+  </si>
+  <si>
+    <t>에디터를 리셋하시겠습니까?</t>
+  </si>
+  <si>
+    <t>Do you want to reset the editor?</t>
+  </si>
+  <si>
     <t>EDITOR_REMOVE_LP_MSG</t>
   </si>
   <si>
@@ -86,6 +98,18 @@
   </si>
   <si>
     <t>Do you want to quit the game?</t>
+  </si>
+  <si>
+    <t>LEAVE_P_MSG</t>
+  </si>
+  <si>
+    <t>그만두기 팝업 메세지</t>
+  </si>
+  <si>
+    <t>게임을 그만두시겠습니까?</t>
+  </si>
+  <si>
+    <t>Do you want to leave the game?</t>
   </si>
   <si>
     <t>UPDATE_P_MSG</t>
@@ -926,7 +950,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -934,6 +958,10 @@
     </font>
     <font>
       <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -1006,7 +1034,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="32">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1021,13 +1049,25 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="3" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="3" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -1396,177 +1436,177 @@
       <c r="E3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
-      <c r="U3" s="7"/>
-      <c r="V3" s="7"/>
-      <c r="W3" s="7"/>
-      <c r="X3" s="7"/>
-      <c r="Y3" s="7"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
+      <c r="Q3" s="8"/>
+      <c r="R3" s="8"/>
+      <c r="S3" s="8"/>
+      <c r="T3" s="8"/>
+      <c r="U3" s="8"/>
+      <c r="V3" s="8"/>
+      <c r="W3" s="8"/>
+      <c r="X3" s="8"/>
+      <c r="Y3" s="8"/>
     </row>
     <row r="4" ht="15.0" customHeight="1">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="10">
         <v>0.0</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="7"/>
-      <c r="T4" s="7"/>
-      <c r="U4" s="7"/>
-      <c r="V4" s="7"/>
-      <c r="W4" s="7"/>
-      <c r="X4" s="7"/>
-      <c r="Y4" s="7"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
+      <c r="Q4" s="8"/>
+      <c r="R4" s="8"/>
+      <c r="S4" s="8"/>
+      <c r="T4" s="8"/>
+      <c r="U4" s="8"/>
+      <c r="V4" s="8"/>
+      <c r="W4" s="8"/>
+      <c r="X4" s="8"/>
+      <c r="Y4" s="8"/>
     </row>
     <row r="5" ht="15.0" customHeight="1">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="10">
         <v>0.0</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="7"/>
-      <c r="S5" s="7"/>
-      <c r="T5" s="7"/>
-      <c r="U5" s="7"/>
-      <c r="V5" s="7"/>
-      <c r="W5" s="7"/>
-      <c r="X5" s="7"/>
-      <c r="Y5" s="7"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
+      <c r="Q5" s="8"/>
+      <c r="R5" s="8"/>
+      <c r="S5" s="8"/>
+      <c r="T5" s="8"/>
+      <c r="U5" s="8"/>
+      <c r="V5" s="8"/>
+      <c r="W5" s="8"/>
+      <c r="X5" s="8"/>
+      <c r="Y5" s="8"/>
     </row>
     <row r="6" ht="15.0" customHeight="1">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="10">
         <v>0.0</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="7"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="7"/>
-      <c r="T6" s="7"/>
-      <c r="U6" s="7"/>
-      <c r="V6" s="7"/>
-      <c r="W6" s="7"/>
-      <c r="X6" s="7"/>
-      <c r="Y6" s="7"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="8"/>
+      <c r="Q6" s="8"/>
+      <c r="R6" s="8"/>
+      <c r="S6" s="8"/>
+      <c r="T6" s="8"/>
+      <c r="U6" s="8"/>
+      <c r="V6" s="8"/>
+      <c r="W6" s="8"/>
+      <c r="X6" s="8"/>
+      <c r="Y6" s="8"/>
     </row>
     <row r="7" ht="15.0" customHeight="1">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="10">
         <v>0.0</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="7"/>
-      <c r="R7" s="7"/>
-      <c r="S7" s="7"/>
-      <c r="T7" s="7"/>
-      <c r="U7" s="7"/>
-      <c r="V7" s="7"/>
-      <c r="W7" s="7"/>
-      <c r="X7" s="7"/>
-      <c r="Y7" s="7"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+      <c r="S7" s="8"/>
+      <c r="T7" s="8"/>
+      <c r="U7" s="8"/>
+      <c r="V7" s="8"/>
+      <c r="W7" s="8"/>
+      <c r="X7" s="8"/>
+      <c r="Y7" s="8"/>
     </row>
     <row r="8" ht="15.0" customHeight="1">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="5" t="s">
         <v>29</v>
       </c>
       <c r="B8" s="6">
@@ -1578,2747 +1618,2767 @@
       <c r="D8" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
-      <c r="P8" s="7"/>
-      <c r="Q8" s="7"/>
-      <c r="R8" s="7"/>
-      <c r="S8" s="7"/>
-      <c r="T8" s="7"/>
-      <c r="U8" s="7"/>
-      <c r="V8" s="7"/>
-      <c r="W8" s="7"/>
-      <c r="X8" s="7"/>
-      <c r="Y8" s="7"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+      <c r="S8" s="8"/>
+      <c r="T8" s="8"/>
+      <c r="U8" s="8"/>
+      <c r="V8" s="8"/>
+      <c r="W8" s="8"/>
+      <c r="X8" s="8"/>
+      <c r="Y8" s="8"/>
     </row>
     <row r="9" ht="15.0" customHeight="1">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="10">
         <v>0.0</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7"/>
-      <c r="P9" s="7"/>
-      <c r="Q9" s="7"/>
-      <c r="R9" s="7"/>
-      <c r="S9" s="7"/>
-      <c r="T9" s="7"/>
-      <c r="U9" s="7"/>
-      <c r="V9" s="7"/>
-      <c r="W9" s="7"/>
-      <c r="X9" s="7"/>
-      <c r="Y9" s="7"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="8"/>
+      <c r="S9" s="8"/>
+      <c r="T9" s="8"/>
+      <c r="U9" s="8"/>
+      <c r="V9" s="8"/>
+      <c r="W9" s="8"/>
+      <c r="X9" s="8"/>
+      <c r="Y9" s="8"/>
     </row>
     <row r="10" ht="15.0" customHeight="1">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="10">
         <v>0.0</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
-      <c r="O10" s="7"/>
-      <c r="P10" s="7"/>
-      <c r="Q10" s="7"/>
-      <c r="R10" s="7"/>
-      <c r="S10" s="7"/>
-      <c r="T10" s="7"/>
-      <c r="U10" s="7"/>
-      <c r="V10" s="7"/>
-      <c r="W10" s="7"/>
-      <c r="X10" s="7"/>
-      <c r="Y10" s="7"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="8"/>
+      <c r="S10" s="8"/>
+      <c r="T10" s="8"/>
+      <c r="U10" s="8"/>
+      <c r="V10" s="8"/>
+      <c r="W10" s="8"/>
+      <c r="X10" s="8"/>
+      <c r="Y10" s="8"/>
     </row>
     <row r="11" ht="15.0" customHeight="1">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="10">
         <v>0.0</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="7"/>
-      <c r="O11" s="7"/>
-      <c r="P11" s="7"/>
-      <c r="Q11" s="7"/>
-      <c r="R11" s="7"/>
-      <c r="S11" s="7"/>
-      <c r="T11" s="7"/>
-      <c r="U11" s="7"/>
-      <c r="V11" s="7"/>
-      <c r="W11" s="7"/>
-      <c r="X11" s="7"/>
-      <c r="Y11" s="7"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
+      <c r="Q11" s="8"/>
+      <c r="R11" s="8"/>
+      <c r="S11" s="8"/>
+      <c r="T11" s="8"/>
+      <c r="U11" s="8"/>
+      <c r="V11" s="8"/>
+      <c r="W11" s="8"/>
+      <c r="X11" s="8"/>
+      <c r="Y11" s="8"/>
     </row>
     <row r="12" ht="15.0" customHeight="1">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="10">
         <v>0.0</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
-      <c r="P12" s="7"/>
-      <c r="Q12" s="7"/>
-      <c r="R12" s="7"/>
-      <c r="S12" s="7"/>
-      <c r="T12" s="7"/>
-      <c r="U12" s="7"/>
-      <c r="V12" s="7"/>
-      <c r="W12" s="7"/>
-      <c r="X12" s="7"/>
-      <c r="Y12" s="7"/>
+      <c r="E12" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
+      <c r="Q12" s="8"/>
+      <c r="R12" s="8"/>
+      <c r="S12" s="8"/>
+      <c r="T12" s="8"/>
+      <c r="U12" s="8"/>
+      <c r="V12" s="8"/>
+      <c r="W12" s="8"/>
+      <c r="X12" s="8"/>
+      <c r="Y12" s="8"/>
     </row>
     <row r="13" ht="15.0" customHeight="1">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
+      <c r="Q13" s="8"/>
+      <c r="R13" s="8"/>
+      <c r="S13" s="8"/>
+      <c r="T13" s="8"/>
+      <c r="U13" s="8"/>
+      <c r="V13" s="8"/>
+      <c r="W13" s="8"/>
+      <c r="X13" s="8"/>
+      <c r="Y13" s="8"/>
+    </row>
+    <row r="14" ht="15.0" customHeight="1">
+      <c r="A14" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8"/>
+      <c r="Q14" s="8"/>
+      <c r="R14" s="8"/>
+      <c r="S14" s="8"/>
+      <c r="T14" s="8"/>
+      <c r="U14" s="8"/>
+      <c r="V14" s="8"/>
+      <c r="W14" s="8"/>
+      <c r="X14" s="8"/>
+      <c r="Y14" s="8"/>
+    </row>
+    <row r="15" ht="15.0" customHeight="1">
+      <c r="A15" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8"/>
+      <c r="O15" s="8"/>
+      <c r="P15" s="8"/>
+      <c r="Q15" s="8"/>
+      <c r="R15" s="8"/>
+      <c r="S15" s="8"/>
+      <c r="T15" s="8"/>
+      <c r="U15" s="8"/>
+      <c r="V15" s="8"/>
+      <c r="W15" s="8"/>
+      <c r="X15" s="8"/>
+      <c r="Y15" s="8"/>
+    </row>
+    <row r="16" ht="15.0" customHeight="1">
+      <c r="A16" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8"/>
+      <c r="Q16" s="8"/>
+      <c r="R16" s="8"/>
+      <c r="S16" s="8"/>
+      <c r="T16" s="8"/>
+      <c r="U16" s="8"/>
+      <c r="V16" s="8"/>
+      <c r="W16" s="8"/>
+      <c r="X16" s="8"/>
+      <c r="Y16" s="8"/>
+    </row>
+    <row r="17" ht="15.0" customHeight="1">
+      <c r="A17" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D17" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="6">
+      <c r="E17" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8"/>
+      <c r="P17" s="8"/>
+      <c r="Q17" s="8"/>
+      <c r="R17" s="8"/>
+      <c r="S17" s="8"/>
+      <c r="T17" s="8"/>
+      <c r="U17" s="8"/>
+      <c r="V17" s="8"/>
+      <c r="W17" s="8"/>
+      <c r="X17" s="8"/>
+      <c r="Y17" s="8"/>
+    </row>
+    <row r="18" ht="15.0" customHeight="1">
+      <c r="A18" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" s="10">
         <v>0.0</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="7"/>
-      <c r="R13" s="7"/>
-      <c r="S13" s="7"/>
-      <c r="T13" s="7"/>
-      <c r="U13" s="7"/>
-      <c r="V13" s="7"/>
-      <c r="W13" s="7"/>
-      <c r="X13" s="7"/>
-      <c r="Y13" s="7"/>
-    </row>
-    <row r="14" ht="15.0" customHeight="1">
-      <c r="A14" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" s="6">
+      <c r="C18" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
+      <c r="O18" s="8"/>
+      <c r="P18" s="8"/>
+      <c r="Q18" s="8"/>
+      <c r="R18" s="8"/>
+      <c r="S18" s="8"/>
+      <c r="T18" s="8"/>
+      <c r="U18" s="8"/>
+      <c r="V18" s="8"/>
+      <c r="W18" s="8"/>
+      <c r="X18" s="8"/>
+      <c r="Y18" s="8"/>
+    </row>
+    <row r="19" ht="15.0" customHeight="1">
+      <c r="A19" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B19" s="10">
         <v>0.0</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
-      <c r="O14" s="7"/>
-      <c r="P14" s="7"/>
-      <c r="Q14" s="7"/>
-      <c r="R14" s="7"/>
-      <c r="S14" s="7"/>
-      <c r="T14" s="7"/>
-      <c r="U14" s="7"/>
-      <c r="V14" s="7"/>
-      <c r="W14" s="7"/>
-      <c r="X14" s="7"/>
-      <c r="Y14" s="7"/>
-    </row>
-    <row r="15" ht="15.0" customHeight="1">
-      <c r="A15" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B15" s="6">
+      <c r="C19" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="8"/>
+      <c r="P19" s="8"/>
+      <c r="Q19" s="8"/>
+      <c r="R19" s="8"/>
+      <c r="S19" s="8"/>
+      <c r="T19" s="8"/>
+      <c r="U19" s="8"/>
+      <c r="V19" s="8"/>
+      <c r="W19" s="8"/>
+      <c r="X19" s="8"/>
+      <c r="Y19" s="8"/>
+    </row>
+    <row r="20" ht="15.0" customHeight="1">
+      <c r="A20" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="10">
         <v>0.0</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C20" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="8"/>
+      <c r="P20" s="8"/>
+      <c r="Q20" s="8"/>
+      <c r="R20" s="8"/>
+      <c r="S20" s="8"/>
+      <c r="T20" s="8"/>
+      <c r="U20" s="8"/>
+      <c r="V20" s="8"/>
+      <c r="W20" s="8"/>
+      <c r="X20" s="8"/>
+      <c r="Y20" s="8"/>
+    </row>
+    <row r="21" ht="15.0" customHeight="1">
+      <c r="A21" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="8"/>
+      <c r="Q21" s="8"/>
+      <c r="R21" s="8"/>
+      <c r="S21" s="8"/>
+      <c r="T21" s="8"/>
+      <c r="U21" s="8"/>
+      <c r="V21" s="8"/>
+      <c r="W21" s="8"/>
+      <c r="X21" s="8"/>
+      <c r="Y21" s="8"/>
+    </row>
+    <row r="22" ht="15.0" customHeight="1">
+      <c r="A22" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B22" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
+      <c r="P22" s="8"/>
+      <c r="Q22" s="8"/>
+      <c r="R22" s="8"/>
+      <c r="S22" s="8"/>
+      <c r="T22" s="8"/>
+      <c r="U22" s="8"/>
+      <c r="V22" s="8"/>
+      <c r="W22" s="8"/>
+      <c r="X22" s="8"/>
+      <c r="Y22" s="8"/>
+    </row>
+    <row r="23" ht="15.0" customHeight="1">
+      <c r="A23" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B23" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="8"/>
+      <c r="P23" s="8"/>
+      <c r="Q23" s="8"/>
+      <c r="R23" s="8"/>
+      <c r="S23" s="8"/>
+      <c r="T23" s="8"/>
+      <c r="U23" s="8"/>
+      <c r="V23" s="8"/>
+      <c r="W23" s="8"/>
+      <c r="X23" s="8"/>
+      <c r="Y23" s="8"/>
+    </row>
+    <row r="24" ht="15.0" customHeight="1">
+      <c r="A24" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B24" s="13">
+        <v>0.0</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14"/>
+      <c r="P24" s="14"/>
+      <c r="Q24" s="14"/>
+      <c r="R24" s="14"/>
+      <c r="S24" s="14"/>
+      <c r="T24" s="14"/>
+      <c r="U24" s="14"/>
+      <c r="V24" s="14"/>
+      <c r="W24" s="14"/>
+      <c r="X24" s="14"/>
+      <c r="Y24" s="14"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="B25" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="17"/>
+      <c r="L25" s="17"/>
+      <c r="M25" s="17"/>
+      <c r="N25" s="17"/>
+      <c r="O25" s="17"/>
+      <c r="P25" s="17"/>
+      <c r="Q25" s="17"/>
+      <c r="R25" s="17"/>
+      <c r="S25" s="17"/>
+      <c r="T25" s="17"/>
+      <c r="U25" s="17"/>
+      <c r="V25" s="17"/>
+      <c r="W25" s="17"/>
+      <c r="X25" s="17"/>
+      <c r="Y25" s="17"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="B26" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="20"/>
+      <c r="K26" s="20"/>
+      <c r="L26" s="20"/>
+      <c r="M26" s="20"/>
+      <c r="N26" s="20"/>
+      <c r="O26" s="20"/>
+      <c r="P26" s="20"/>
+      <c r="Q26" s="20"/>
+      <c r="R26" s="20"/>
+      <c r="S26" s="20"/>
+      <c r="T26" s="20"/>
+      <c r="U26" s="20"/>
+      <c r="V26" s="20"/>
+      <c r="W26" s="20"/>
+      <c r="X26" s="20"/>
+      <c r="Y26" s="20"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="B27" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="20"/>
+      <c r="K27" s="20"/>
+      <c r="L27" s="20"/>
+      <c r="M27" s="20"/>
+      <c r="N27" s="20"/>
+      <c r="O27" s="20"/>
+      <c r="P27" s="20"/>
+      <c r="Q27" s="20"/>
+      <c r="R27" s="20"/>
+      <c r="S27" s="20"/>
+      <c r="T27" s="20"/>
+      <c r="U27" s="20"/>
+      <c r="V27" s="20"/>
+      <c r="W27" s="20"/>
+      <c r="X27" s="20"/>
+      <c r="Y27" s="20"/>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="B28" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="C28" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="20"/>
+      <c r="K28" s="20"/>
+      <c r="L28" s="20"/>
+      <c r="M28" s="20"/>
+      <c r="N28" s="20"/>
+      <c r="O28" s="20"/>
+      <c r="P28" s="20"/>
+      <c r="Q28" s="20"/>
+      <c r="R28" s="20"/>
+      <c r="S28" s="20"/>
+      <c r="T28" s="20"/>
+      <c r="U28" s="20"/>
+      <c r="V28" s="20"/>
+      <c r="W28" s="20"/>
+      <c r="X28" s="20"/>
+      <c r="Y28" s="20"/>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="B29" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="C29" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="D29" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="E29" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="20"/>
+      <c r="K29" s="20"/>
+      <c r="L29" s="20"/>
+      <c r="M29" s="20"/>
+      <c r="N29" s="20"/>
+      <c r="O29" s="20"/>
+      <c r="P29" s="20"/>
+      <c r="Q29" s="20"/>
+      <c r="R29" s="20"/>
+      <c r="S29" s="20"/>
+      <c r="T29" s="20"/>
+      <c r="U29" s="20"/>
+      <c r="V29" s="20"/>
+      <c r="W29" s="20"/>
+      <c r="X29" s="20"/>
+      <c r="Y29" s="20"/>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="B30" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="C30" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="D30" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="E30" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="20"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="20"/>
+      <c r="K30" s="20"/>
+      <c r="L30" s="20"/>
+      <c r="M30" s="20"/>
+      <c r="N30" s="20"/>
+      <c r="O30" s="20"/>
+      <c r="P30" s="20"/>
+      <c r="Q30" s="20"/>
+      <c r="R30" s="20"/>
+      <c r="S30" s="20"/>
+      <c r="T30" s="20"/>
+      <c r="U30" s="20"/>
+      <c r="V30" s="20"/>
+      <c r="W30" s="20"/>
+      <c r="X30" s="20"/>
+      <c r="Y30" s="20"/>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="B31" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="C31" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="D31" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="E31" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="20"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="20"/>
+      <c r="K31" s="20"/>
+      <c r="L31" s="20"/>
+      <c r="M31" s="20"/>
+      <c r="N31" s="20"/>
+      <c r="O31" s="20"/>
+      <c r="P31" s="20"/>
+      <c r="Q31" s="20"/>
+      <c r="R31" s="20"/>
+      <c r="S31" s="20"/>
+      <c r="T31" s="20"/>
+      <c r="U31" s="20"/>
+      <c r="V31" s="20"/>
+      <c r="W31" s="20"/>
+      <c r="X31" s="20"/>
+      <c r="Y31" s="20"/>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="B32" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="C32" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="D32" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="E32" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="20"/>
+      <c r="K32" s="20"/>
+      <c r="L32" s="20"/>
+      <c r="M32" s="20"/>
+      <c r="N32" s="20"/>
+      <c r="O32" s="20"/>
+      <c r="P32" s="20"/>
+      <c r="Q32" s="20"/>
+      <c r="R32" s="20"/>
+      <c r="S32" s="20"/>
+      <c r="T32" s="20"/>
+      <c r="U32" s="20"/>
+      <c r="V32" s="20"/>
+      <c r="W32" s="20"/>
+      <c r="X32" s="20"/>
+      <c r="Y32" s="20"/>
+    </row>
+    <row r="33" ht="15.0" customHeight="1">
+      <c r="A33" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B33" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="C33" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="D33" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="E33" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+      <c r="H33" s="20"/>
+      <c r="I33" s="20"/>
+      <c r="J33" s="20"/>
+      <c r="K33" s="20"/>
+      <c r="L33" s="20"/>
+      <c r="M33" s="20"/>
+      <c r="N33" s="20"/>
+      <c r="O33" s="20"/>
+      <c r="P33" s="20"/>
+      <c r="Q33" s="20"/>
+      <c r="R33" s="20"/>
+      <c r="S33" s="20"/>
+      <c r="T33" s="20"/>
+      <c r="U33" s="20"/>
+      <c r="V33" s="20"/>
+      <c r="W33" s="20"/>
+      <c r="X33" s="20"/>
+      <c r="Y33" s="20"/>
+    </row>
+    <row r="34" ht="15.0" customHeight="1">
+      <c r="A34" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="B34" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="C34" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="D34" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="E34" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="20"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="20"/>
+      <c r="K34" s="20"/>
+      <c r="L34" s="20"/>
+      <c r="M34" s="20"/>
+      <c r="N34" s="20"/>
+      <c r="O34" s="20"/>
+      <c r="P34" s="20"/>
+      <c r="Q34" s="20"/>
+      <c r="R34" s="20"/>
+      <c r="S34" s="20"/>
+      <c r="T34" s="20"/>
+      <c r="U34" s="20"/>
+      <c r="V34" s="20"/>
+      <c r="W34" s="20"/>
+      <c r="X34" s="20"/>
+      <c r="Y34" s="20"/>
+    </row>
+    <row r="35" ht="15.0" customHeight="1">
+      <c r="A35" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="B35" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="C35" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="D35" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="E35" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
+      <c r="H35" s="20"/>
+      <c r="I35" s="20"/>
+      <c r="J35" s="20"/>
+      <c r="K35" s="20"/>
+      <c r="L35" s="20"/>
+      <c r="M35" s="20"/>
+      <c r="N35" s="20"/>
+      <c r="O35" s="20"/>
+      <c r="P35" s="20"/>
+      <c r="Q35" s="20"/>
+      <c r="R35" s="20"/>
+      <c r="S35" s="20"/>
+      <c r="T35" s="20"/>
+      <c r="U35" s="20"/>
+      <c r="V35" s="20"/>
+      <c r="W35" s="20"/>
+      <c r="X35" s="20"/>
+      <c r="Y35" s="20"/>
+    </row>
+    <row r="36" ht="15.0" customHeight="1">
+      <c r="A36" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="B36" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="C36" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="D36" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="E36" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
+      <c r="H36" s="20"/>
+      <c r="I36" s="20"/>
+      <c r="J36" s="20"/>
+      <c r="K36" s="20"/>
+      <c r="L36" s="20"/>
+      <c r="M36" s="20"/>
+      <c r="N36" s="20"/>
+      <c r="O36" s="20"/>
+      <c r="P36" s="20"/>
+      <c r="Q36" s="20"/>
+      <c r="R36" s="20"/>
+      <c r="S36" s="20"/>
+      <c r="T36" s="20"/>
+      <c r="U36" s="20"/>
+      <c r="V36" s="20"/>
+      <c r="W36" s="20"/>
+      <c r="X36" s="20"/>
+      <c r="Y36" s="20"/>
+    </row>
+    <row r="37" ht="15.0" customHeight="1">
+      <c r="A37" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="B37" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="C37" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="D37" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="E37" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="F37" s="20"/>
+      <c r="G37" s="20"/>
+      <c r="H37" s="20"/>
+      <c r="I37" s="20"/>
+      <c r="J37" s="20"/>
+      <c r="K37" s="20"/>
+      <c r="L37" s="20"/>
+      <c r="M37" s="20"/>
+      <c r="N37" s="20"/>
+      <c r="O37" s="20"/>
+      <c r="P37" s="20"/>
+      <c r="Q37" s="20"/>
+      <c r="R37" s="20"/>
+      <c r="S37" s="20"/>
+      <c r="T37" s="20"/>
+      <c r="U37" s="20"/>
+      <c r="V37" s="20"/>
+      <c r="W37" s="20"/>
+      <c r="X37" s="20"/>
+      <c r="Y37" s="20"/>
+    </row>
+    <row r="38" ht="15.0" customHeight="1">
+      <c r="A38" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="B38" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="C38" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="D38" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="E38" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="F38" s="20"/>
+      <c r="G38" s="20"/>
+      <c r="H38" s="20"/>
+      <c r="I38" s="20"/>
+      <c r="J38" s="20"/>
+      <c r="K38" s="20"/>
+      <c r="L38" s="20"/>
+      <c r="M38" s="20"/>
+      <c r="N38" s="20"/>
+      <c r="O38" s="20"/>
+      <c r="P38" s="20"/>
+      <c r="Q38" s="20"/>
+      <c r="R38" s="20"/>
+      <c r="S38" s="20"/>
+      <c r="T38" s="20"/>
+      <c r="U38" s="20"/>
+      <c r="V38" s="20"/>
+      <c r="W38" s="20"/>
+      <c r="X38" s="20"/>
+      <c r="Y38" s="20"/>
+    </row>
+    <row r="39" ht="15.0" customHeight="1">
+      <c r="A39" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="B39" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="C39" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="D39" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="E39" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="F39" s="20"/>
+      <c r="G39" s="20"/>
+      <c r="H39" s="20"/>
+      <c r="I39" s="20"/>
+      <c r="J39" s="20"/>
+      <c r="K39" s="20"/>
+      <c r="L39" s="20"/>
+      <c r="M39" s="20"/>
+      <c r="N39" s="20"/>
+      <c r="O39" s="20"/>
+      <c r="P39" s="20"/>
+      <c r="Q39" s="20"/>
+      <c r="R39" s="20"/>
+      <c r="S39" s="20"/>
+      <c r="T39" s="20"/>
+      <c r="U39" s="20"/>
+      <c r="V39" s="20"/>
+      <c r="W39" s="20"/>
+      <c r="X39" s="20"/>
+      <c r="Y39" s="20"/>
+    </row>
+    <row r="40" ht="15.0" customHeight="1">
+      <c r="A40" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="B40" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="C40" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="D40" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="E40" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="F40" s="20"/>
+      <c r="G40" s="20"/>
+      <c r="H40" s="20"/>
+      <c r="I40" s="20"/>
+      <c r="J40" s="20"/>
+      <c r="K40" s="20"/>
+      <c r="L40" s="20"/>
+      <c r="M40" s="20"/>
+      <c r="N40" s="20"/>
+      <c r="O40" s="20"/>
+      <c r="P40" s="20"/>
+      <c r="Q40" s="20"/>
+      <c r="R40" s="20"/>
+      <c r="S40" s="20"/>
+      <c r="T40" s="20"/>
+      <c r="U40" s="20"/>
+      <c r="V40" s="20"/>
+      <c r="W40" s="20"/>
+      <c r="X40" s="20"/>
+      <c r="Y40" s="20"/>
+    </row>
+    <row r="41" ht="15.0" customHeight="1">
+      <c r="A41" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="B41" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="C41" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="D41" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="E41" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="F41" s="20"/>
+      <c r="G41" s="20"/>
+      <c r="H41" s="20"/>
+      <c r="I41" s="20"/>
+      <c r="J41" s="20"/>
+      <c r="K41" s="20"/>
+      <c r="L41" s="20"/>
+      <c r="M41" s="20"/>
+      <c r="N41" s="20"/>
+      <c r="O41" s="20"/>
+      <c r="P41" s="20"/>
+      <c r="Q41" s="20"/>
+      <c r="R41" s="20"/>
+      <c r="S41" s="20"/>
+      <c r="T41" s="20"/>
+      <c r="U41" s="20"/>
+      <c r="V41" s="20"/>
+      <c r="W41" s="20"/>
+      <c r="X41" s="20"/>
+      <c r="Y41" s="20"/>
+    </row>
+    <row r="42" ht="15.0" customHeight="1">
+      <c r="A42" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="B42" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="C42" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="D42" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="E42" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="F42" s="20"/>
+      <c r="G42" s="20"/>
+      <c r="H42" s="20"/>
+      <c r="I42" s="20"/>
+      <c r="J42" s="20"/>
+      <c r="K42" s="20"/>
+      <c r="L42" s="20"/>
+      <c r="M42" s="20"/>
+      <c r="N42" s="20"/>
+      <c r="O42" s="20"/>
+      <c r="P42" s="20"/>
+      <c r="Q42" s="20"/>
+      <c r="R42" s="20"/>
+      <c r="S42" s="20"/>
+      <c r="T42" s="20"/>
+      <c r="U42" s="20"/>
+      <c r="V42" s="20"/>
+      <c r="W42" s="20"/>
+      <c r="X42" s="20"/>
+      <c r="Y42" s="20"/>
+    </row>
+    <row r="43" ht="15.0" customHeight="1">
+      <c r="A43" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="B43" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="C43" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="D43" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="E43" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="F43" s="20"/>
+      <c r="G43" s="20"/>
+      <c r="H43" s="20"/>
+      <c r="I43" s="20"/>
+      <c r="J43" s="20"/>
+      <c r="K43" s="20"/>
+      <c r="L43" s="20"/>
+      <c r="M43" s="20"/>
+      <c r="N43" s="20"/>
+      <c r="O43" s="20"/>
+      <c r="P43" s="20"/>
+      <c r="Q43" s="20"/>
+      <c r="R43" s="20"/>
+      <c r="S43" s="20"/>
+      <c r="T43" s="20"/>
+      <c r="U43" s="20"/>
+      <c r="V43" s="20"/>
+      <c r="W43" s="20"/>
+      <c r="X43" s="20"/>
+      <c r="Y43" s="20"/>
+    </row>
+    <row r="44" ht="15.0" customHeight="1">
+      <c r="A44" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="B44" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="C44" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="D44" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="E44" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="F44" s="20"/>
+      <c r="G44" s="20"/>
+      <c r="H44" s="20"/>
+      <c r="I44" s="20"/>
+      <c r="J44" s="20"/>
+      <c r="K44" s="20"/>
+      <c r="L44" s="20"/>
+      <c r="M44" s="20"/>
+      <c r="N44" s="20"/>
+      <c r="O44" s="20"/>
+      <c r="P44" s="20"/>
+      <c r="Q44" s="20"/>
+      <c r="R44" s="20"/>
+      <c r="S44" s="20"/>
+      <c r="T44" s="20"/>
+      <c r="U44" s="20"/>
+      <c r="V44" s="20"/>
+      <c r="W44" s="20"/>
+      <c r="X44" s="20"/>
+      <c r="Y44" s="20"/>
+    </row>
+    <row r="45" ht="15.0" customHeight="1">
+      <c r="A45" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="B45" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="C45" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="D45" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="E45" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="F45" s="20"/>
+      <c r="G45" s="20"/>
+      <c r="H45" s="20"/>
+      <c r="I45" s="20"/>
+      <c r="J45" s="20"/>
+      <c r="K45" s="20"/>
+      <c r="L45" s="20"/>
+      <c r="M45" s="20"/>
+      <c r="N45" s="20"/>
+      <c r="O45" s="20"/>
+      <c r="P45" s="20"/>
+      <c r="Q45" s="20"/>
+      <c r="R45" s="20"/>
+      <c r="S45" s="20"/>
+      <c r="T45" s="20"/>
+      <c r="U45" s="20"/>
+      <c r="V45" s="20"/>
+      <c r="W45" s="20"/>
+      <c r="X45" s="20"/>
+      <c r="Y45" s="20"/>
+    </row>
+    <row r="46" ht="15.0" customHeight="1">
+      <c r="A46" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="B46" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="C46" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="D46" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="E46" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="F46" s="20"/>
+      <c r="G46" s="20"/>
+      <c r="H46" s="20"/>
+      <c r="I46" s="20"/>
+      <c r="J46" s="20"/>
+      <c r="K46" s="20"/>
+      <c r="L46" s="20"/>
+      <c r="M46" s="20"/>
+      <c r="N46" s="20"/>
+      <c r="O46" s="20"/>
+      <c r="P46" s="20"/>
+      <c r="Q46" s="20"/>
+      <c r="R46" s="20"/>
+      <c r="S46" s="20"/>
+      <c r="T46" s="20"/>
+      <c r="U46" s="20"/>
+      <c r="V46" s="20"/>
+      <c r="W46" s="20"/>
+      <c r="X46" s="20"/>
+      <c r="Y46" s="20"/>
+    </row>
+    <row r="47" ht="15.0" customHeight="1">
+      <c r="A47" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="B47" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="C47" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="D47" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="E47" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="F47" s="20"/>
+      <c r="G47" s="20"/>
+      <c r="H47" s="20"/>
+      <c r="I47" s="20"/>
+      <c r="J47" s="20"/>
+      <c r="K47" s="20"/>
+      <c r="L47" s="20"/>
+      <c r="M47" s="20"/>
+      <c r="N47" s="20"/>
+      <c r="O47" s="20"/>
+      <c r="P47" s="20"/>
+      <c r="Q47" s="20"/>
+      <c r="R47" s="20"/>
+      <c r="S47" s="20"/>
+      <c r="T47" s="20"/>
+      <c r="U47" s="20"/>
+      <c r="V47" s="20"/>
+      <c r="W47" s="20"/>
+      <c r="X47" s="20"/>
+      <c r="Y47" s="20"/>
+    </row>
+    <row r="48" ht="15.0" customHeight="1">
+      <c r="A48" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="B48" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="C48" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="D48" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="E48" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="F48" s="20"/>
+      <c r="G48" s="20"/>
+      <c r="H48" s="20"/>
+      <c r="I48" s="20"/>
+      <c r="J48" s="20"/>
+      <c r="K48" s="20"/>
+      <c r="L48" s="20"/>
+      <c r="M48" s="20"/>
+      <c r="N48" s="20"/>
+      <c r="O48" s="20"/>
+      <c r="P48" s="20"/>
+      <c r="Q48" s="20"/>
+      <c r="R48" s="20"/>
+      <c r="S48" s="20"/>
+      <c r="T48" s="20"/>
+      <c r="U48" s="20"/>
+      <c r="V48" s="20"/>
+      <c r="W48" s="20"/>
+      <c r="X48" s="20"/>
+      <c r="Y48" s="20"/>
+    </row>
+    <row r="49" ht="15.0" customHeight="1">
+      <c r="A49" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="B49" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="C49" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="D49" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="E49" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="F49" s="20"/>
+      <c r="G49" s="20"/>
+      <c r="H49" s="20"/>
+      <c r="I49" s="20"/>
+      <c r="J49" s="20"/>
+      <c r="K49" s="20"/>
+      <c r="L49" s="20"/>
+      <c r="M49" s="20"/>
+      <c r="N49" s="20"/>
+      <c r="O49" s="20"/>
+      <c r="P49" s="20"/>
+      <c r="Q49" s="20"/>
+      <c r="R49" s="20"/>
+      <c r="S49" s="20"/>
+      <c r="T49" s="20"/>
+      <c r="U49" s="20"/>
+      <c r="V49" s="20"/>
+      <c r="W49" s="20"/>
+      <c r="X49" s="20"/>
+      <c r="Y49" s="20"/>
+    </row>
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="A50" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="B50" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="C50" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="D50" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="E50" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="F50" s="20"/>
+      <c r="G50" s="20"/>
+      <c r="H50" s="20"/>
+      <c r="I50" s="20"/>
+      <c r="J50" s="20"/>
+      <c r="K50" s="20"/>
+      <c r="L50" s="20"/>
+      <c r="M50" s="20"/>
+      <c r="N50" s="20"/>
+      <c r="O50" s="20"/>
+      <c r="P50" s="20"/>
+      <c r="Q50" s="20"/>
+      <c r="R50" s="20"/>
+      <c r="S50" s="20"/>
+      <c r="T50" s="20"/>
+      <c r="U50" s="20"/>
+      <c r="V50" s="20"/>
+      <c r="W50" s="20"/>
+      <c r="X50" s="20"/>
+      <c r="Y50" s="20"/>
+    </row>
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="A51" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="B51" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="C51" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="D51" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="E51" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="F51" s="20"/>
+      <c r="G51" s="20"/>
+      <c r="H51" s="20"/>
+      <c r="I51" s="20"/>
+      <c r="J51" s="20"/>
+      <c r="K51" s="20"/>
+      <c r="L51" s="20"/>
+      <c r="M51" s="20"/>
+      <c r="N51" s="20"/>
+      <c r="O51" s="20"/>
+      <c r="P51" s="20"/>
+      <c r="Q51" s="20"/>
+      <c r="R51" s="20"/>
+      <c r="S51" s="20"/>
+      <c r="T51" s="20"/>
+      <c r="U51" s="20"/>
+      <c r="V51" s="20"/>
+      <c r="W51" s="20"/>
+      <c r="X51" s="20"/>
+      <c r="Y51" s="20"/>
+    </row>
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="A52" s="18" t="s">
+        <v>197</v>
+      </c>
+      <c r="B52" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="C52" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="D52" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="E52" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="F52" s="20"/>
+      <c r="G52" s="20"/>
+      <c r="H52" s="20"/>
+      <c r="I52" s="20"/>
+      <c r="J52" s="20"/>
+      <c r="K52" s="20"/>
+      <c r="L52" s="20"/>
+      <c r="M52" s="20"/>
+      <c r="N52" s="20"/>
+      <c r="O52" s="20"/>
+      <c r="P52" s="20"/>
+      <c r="Q52" s="20"/>
+      <c r="R52" s="20"/>
+      <c r="S52" s="20"/>
+      <c r="T52" s="20"/>
+      <c r="U52" s="20"/>
+      <c r="V52" s="20"/>
+      <c r="W52" s="20"/>
+      <c r="X52" s="20"/>
+      <c r="Y52" s="20"/>
+    </row>
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="A53" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="B53" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="C53" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="D53" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="E53" s="20" t="s">
+        <v>204</v>
+      </c>
+      <c r="F53" s="20"/>
+      <c r="G53" s="20"/>
+      <c r="H53" s="20"/>
+      <c r="I53" s="20"/>
+      <c r="J53" s="20"/>
+      <c r="K53" s="20"/>
+      <c r="L53" s="20"/>
+      <c r="M53" s="20"/>
+      <c r="N53" s="20"/>
+      <c r="O53" s="20"/>
+      <c r="P53" s="20"/>
+      <c r="Q53" s="20"/>
+      <c r="R53" s="20"/>
+      <c r="S53" s="20"/>
+      <c r="T53" s="20"/>
+      <c r="U53" s="20"/>
+      <c r="V53" s="20"/>
+      <c r="W53" s="20"/>
+      <c r="X53" s="20"/>
+      <c r="Y53" s="20"/>
+    </row>
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="A54" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="B54" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="C54" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="D54" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E54" s="20" t="s">
+        <v>208</v>
+      </c>
+      <c r="F54" s="20"/>
+      <c r="G54" s="20"/>
+      <c r="H54" s="20"/>
+      <c r="I54" s="20"/>
+      <c r="J54" s="20"/>
+      <c r="K54" s="20"/>
+      <c r="L54" s="20"/>
+      <c r="M54" s="20"/>
+      <c r="N54" s="20"/>
+      <c r="O54" s="20"/>
+      <c r="P54" s="20"/>
+      <c r="Q54" s="20"/>
+      <c r="R54" s="20"/>
+      <c r="S54" s="20"/>
+      <c r="T54" s="20"/>
+      <c r="U54" s="20"/>
+      <c r="V54" s="20"/>
+      <c r="W54" s="20"/>
+      <c r="X54" s="20"/>
+      <c r="Y54" s="20"/>
+    </row>
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="A55" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="B55" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="C55" s="20" t="s">
+        <v>210</v>
+      </c>
+      <c r="D55" s="20" t="s">
+        <v>211</v>
+      </c>
+      <c r="E55" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="F55" s="20"/>
+      <c r="G55" s="20"/>
+      <c r="H55" s="20"/>
+      <c r="I55" s="20"/>
+      <c r="J55" s="20"/>
+      <c r="K55" s="20"/>
+      <c r="L55" s="20"/>
+      <c r="M55" s="20"/>
+      <c r="N55" s="20"/>
+      <c r="O55" s="20"/>
+      <c r="P55" s="20"/>
+      <c r="Q55" s="20"/>
+      <c r="R55" s="20"/>
+      <c r="S55" s="20"/>
+      <c r="T55" s="20"/>
+      <c r="U55" s="20"/>
+      <c r="V55" s="20"/>
+      <c r="W55" s="20"/>
+      <c r="X55" s="20"/>
+      <c r="Y55" s="20"/>
+    </row>
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="A56" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="B56" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="C56" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="D56" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="E56" s="20" t="s">
+        <v>216</v>
+      </c>
+      <c r="F56" s="20"/>
+      <c r="G56" s="20"/>
+      <c r="H56" s="20"/>
+      <c r="I56" s="20"/>
+      <c r="J56" s="20"/>
+      <c r="K56" s="20"/>
+      <c r="L56" s="20"/>
+      <c r="M56" s="20"/>
+      <c r="N56" s="20"/>
+      <c r="O56" s="20"/>
+      <c r="P56" s="20"/>
+      <c r="Q56" s="20"/>
+      <c r="R56" s="20"/>
+      <c r="S56" s="20"/>
+      <c r="T56" s="20"/>
+      <c r="U56" s="20"/>
+      <c r="V56" s="20"/>
+      <c r="W56" s="20"/>
+      <c r="X56" s="20"/>
+      <c r="Y56" s="20"/>
+    </row>
+    <row r="57" ht="15.0" customHeight="1">
+      <c r="A57" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="B57" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="C57" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="D57" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="E57" s="20" t="s">
+        <v>220</v>
+      </c>
+      <c r="F57" s="20"/>
+      <c r="G57" s="20"/>
+      <c r="H57" s="20"/>
+      <c r="I57" s="20"/>
+      <c r="J57" s="20"/>
+      <c r="K57" s="20"/>
+      <c r="L57" s="20"/>
+      <c r="M57" s="20"/>
+      <c r="N57" s="20"/>
+      <c r="O57" s="20"/>
+      <c r="P57" s="20"/>
+      <c r="Q57" s="20"/>
+      <c r="R57" s="20"/>
+      <c r="S57" s="20"/>
+      <c r="T57" s="20"/>
+      <c r="U57" s="20"/>
+      <c r="V57" s="20"/>
+      <c r="W57" s="20"/>
+      <c r="X57" s="20"/>
+      <c r="Y57" s="20"/>
+    </row>
+    <row r="58" ht="15.0" customHeight="1">
+      <c r="A58" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="B58" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="C58" s="20" t="s">
+        <v>222</v>
+      </c>
+      <c r="D58" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E58" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="D15" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
-      <c r="P15" s="7"/>
-      <c r="Q15" s="7"/>
-      <c r="R15" s="7"/>
-      <c r="S15" s="7"/>
-      <c r="T15" s="7"/>
-      <c r="U15" s="7"/>
-      <c r="V15" s="7"/>
-      <c r="W15" s="7"/>
-      <c r="X15" s="7"/>
-      <c r="Y15" s="7"/>
-    </row>
-    <row r="16" ht="15.0" customHeight="1">
-      <c r="A16" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B16" s="6">
+      <c r="F58" s="20"/>
+      <c r="G58" s="20"/>
+      <c r="H58" s="20"/>
+      <c r="I58" s="20"/>
+      <c r="J58" s="20"/>
+      <c r="K58" s="20"/>
+      <c r="L58" s="20"/>
+      <c r="M58" s="20"/>
+      <c r="N58" s="20"/>
+      <c r="O58" s="20"/>
+      <c r="P58" s="20"/>
+      <c r="Q58" s="20"/>
+      <c r="R58" s="20"/>
+      <c r="S58" s="20"/>
+      <c r="T58" s="20"/>
+      <c r="U58" s="20"/>
+      <c r="V58" s="20"/>
+      <c r="W58" s="20"/>
+      <c r="X58" s="20"/>
+      <c r="Y58" s="20"/>
+    </row>
+    <row r="59" ht="15.0" customHeight="1">
+      <c r="A59" s="18" t="s">
+        <v>223</v>
+      </c>
+      <c r="B59" s="19">
         <v>0.0</v>
       </c>
-      <c r="C16" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="7"/>
-      <c r="Q16" s="7"/>
-      <c r="R16" s="7"/>
-      <c r="S16" s="7"/>
-      <c r="T16" s="7"/>
-      <c r="U16" s="7"/>
-      <c r="V16" s="7"/>
-      <c r="W16" s="7"/>
-      <c r="X16" s="7"/>
-      <c r="Y16" s="7"/>
-    </row>
-    <row r="17" ht="15.0" customHeight="1">
-      <c r="A17" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="B17" s="6">
+      <c r="C59" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="D59" s="20" t="s">
+        <v>225</v>
+      </c>
+      <c r="E59" s="20" t="s">
+        <v>226</v>
+      </c>
+      <c r="F59" s="20"/>
+      <c r="G59" s="20"/>
+      <c r="H59" s="20"/>
+      <c r="I59" s="20"/>
+      <c r="J59" s="20"/>
+      <c r="K59" s="20"/>
+      <c r="L59" s="20"/>
+      <c r="M59" s="20"/>
+      <c r="N59" s="20"/>
+      <c r="O59" s="20"/>
+      <c r="P59" s="20"/>
+      <c r="Q59" s="20"/>
+      <c r="R59" s="20"/>
+      <c r="S59" s="20"/>
+      <c r="T59" s="20"/>
+      <c r="U59" s="20"/>
+      <c r="V59" s="20"/>
+      <c r="W59" s="20"/>
+      <c r="X59" s="20"/>
+      <c r="Y59" s="20"/>
+    </row>
+    <row r="60" ht="15.0" customHeight="1">
+      <c r="A60" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="B60" s="19">
         <v>0.0</v>
       </c>
-      <c r="C17" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="7"/>
-      <c r="O17" s="7"/>
-      <c r="P17" s="7"/>
-      <c r="Q17" s="7"/>
-      <c r="R17" s="7"/>
-      <c r="S17" s="7"/>
-      <c r="T17" s="7"/>
-      <c r="U17" s="7"/>
-      <c r="V17" s="7"/>
-      <c r="W17" s="7"/>
-      <c r="X17" s="7"/>
-      <c r="Y17" s="7"/>
-    </row>
-    <row r="18" ht="15.0" customHeight="1">
-      <c r="A18" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B18" s="6">
+      <c r="C60" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="D60" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="E60" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="F60" s="20"/>
+      <c r="G60" s="20"/>
+      <c r="H60" s="20"/>
+      <c r="I60" s="20"/>
+      <c r="J60" s="20"/>
+      <c r="K60" s="20"/>
+      <c r="L60" s="20"/>
+      <c r="M60" s="20"/>
+      <c r="N60" s="20"/>
+      <c r="O60" s="20"/>
+      <c r="P60" s="20"/>
+      <c r="Q60" s="20"/>
+      <c r="R60" s="20"/>
+      <c r="S60" s="20"/>
+      <c r="T60" s="20"/>
+      <c r="U60" s="20"/>
+      <c r="V60" s="20"/>
+      <c r="W60" s="20"/>
+      <c r="X60" s="20"/>
+      <c r="Y60" s="20"/>
+    </row>
+    <row r="61" ht="15.0" customHeight="1">
+      <c r="A61" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="B61" s="19">
         <v>0.0</v>
       </c>
-      <c r="C18" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="7"/>
-      <c r="O18" s="7"/>
-      <c r="P18" s="7"/>
-      <c r="Q18" s="7"/>
-      <c r="R18" s="7"/>
-      <c r="S18" s="7"/>
-      <c r="T18" s="7"/>
-      <c r="U18" s="7"/>
-      <c r="V18" s="7"/>
-      <c r="W18" s="7"/>
-      <c r="X18" s="7"/>
-      <c r="Y18" s="7"/>
-    </row>
-    <row r="19" ht="15.0" customHeight="1">
-      <c r="A19" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B19" s="6">
+      <c r="C61" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="D61" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="E61" s="20" t="s">
+        <v>234</v>
+      </c>
+      <c r="F61" s="20"/>
+      <c r="G61" s="20"/>
+      <c r="H61" s="20"/>
+      <c r="I61" s="20"/>
+      <c r="J61" s="20"/>
+      <c r="K61" s="20"/>
+      <c r="L61" s="20"/>
+      <c r="M61" s="20"/>
+      <c r="N61" s="20"/>
+      <c r="O61" s="20"/>
+      <c r="P61" s="20"/>
+      <c r="Q61" s="20"/>
+      <c r="R61" s="20"/>
+      <c r="S61" s="20"/>
+      <c r="T61" s="20"/>
+      <c r="U61" s="20"/>
+      <c r="V61" s="20"/>
+      <c r="W61" s="20"/>
+      <c r="X61" s="20"/>
+      <c r="Y61" s="20"/>
+    </row>
+    <row r="62" ht="15.0" customHeight="1">
+      <c r="A62" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="B62" s="19">
         <v>0.0</v>
       </c>
-      <c r="C19" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="7"/>
-      <c r="N19" s="7"/>
-      <c r="O19" s="7"/>
-      <c r="P19" s="7"/>
-      <c r="Q19" s="7"/>
-      <c r="R19" s="7"/>
-      <c r="S19" s="7"/>
-      <c r="T19" s="7"/>
-      <c r="U19" s="7"/>
-      <c r="V19" s="7"/>
-      <c r="W19" s="7"/>
-      <c r="X19" s="7"/>
-      <c r="Y19" s="7"/>
-    </row>
-    <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B20" s="6">
+      <c r="C62" s="20" t="s">
+        <v>236</v>
+      </c>
+      <c r="D62" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="E62" s="20" t="s">
+        <v>238</v>
+      </c>
+      <c r="F62" s="20"/>
+      <c r="G62" s="20"/>
+      <c r="H62" s="20"/>
+      <c r="I62" s="20"/>
+      <c r="J62" s="20"/>
+      <c r="K62" s="20"/>
+      <c r="L62" s="20"/>
+      <c r="M62" s="20"/>
+      <c r="N62" s="20"/>
+      <c r="O62" s="20"/>
+      <c r="P62" s="20"/>
+      <c r="Q62" s="20"/>
+      <c r="R62" s="20"/>
+      <c r="S62" s="20"/>
+      <c r="T62" s="20"/>
+      <c r="U62" s="20"/>
+      <c r="V62" s="20"/>
+      <c r="W62" s="20"/>
+      <c r="X62" s="20"/>
+      <c r="Y62" s="20"/>
+    </row>
+    <row r="63" ht="15.0" customHeight="1">
+      <c r="A63" s="18" t="s">
+        <v>239</v>
+      </c>
+      <c r="B63" s="19">
         <v>0.0</v>
       </c>
-      <c r="C20" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7"/>
-      <c r="N20" s="7"/>
-      <c r="O20" s="7"/>
-      <c r="P20" s="7"/>
-      <c r="Q20" s="7"/>
-      <c r="R20" s="7"/>
-      <c r="S20" s="7"/>
-      <c r="T20" s="7"/>
-      <c r="U20" s="7"/>
-      <c r="V20" s="7"/>
-      <c r="W20" s="7"/>
-      <c r="X20" s="7"/>
-      <c r="Y20" s="7"/>
-    </row>
-    <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B21" s="6">
+      <c r="C63" s="20" t="s">
+        <v>240</v>
+      </c>
+      <c r="D63" s="20" t="s">
+        <v>241</v>
+      </c>
+      <c r="E63" s="20" t="s">
+        <v>242</v>
+      </c>
+      <c r="F63" s="20"/>
+      <c r="G63" s="20"/>
+      <c r="H63" s="20"/>
+      <c r="I63" s="20"/>
+      <c r="J63" s="20"/>
+      <c r="K63" s="20"/>
+      <c r="L63" s="20"/>
+      <c r="M63" s="20"/>
+      <c r="N63" s="20"/>
+      <c r="O63" s="20"/>
+      <c r="P63" s="20"/>
+      <c r="Q63" s="20"/>
+      <c r="R63" s="20"/>
+      <c r="S63" s="20"/>
+      <c r="T63" s="20"/>
+      <c r="U63" s="20"/>
+      <c r="V63" s="20"/>
+      <c r="W63" s="20"/>
+      <c r="X63" s="20"/>
+      <c r="Y63" s="20"/>
+    </row>
+    <row r="64" ht="15.0" customHeight="1">
+      <c r="A64" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="B64" s="19">
         <v>0.0</v>
       </c>
-      <c r="C21" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="7"/>
-      <c r="N21" s="7"/>
-      <c r="O21" s="7"/>
-      <c r="P21" s="7"/>
-      <c r="Q21" s="7"/>
-      <c r="R21" s="7"/>
-      <c r="S21" s="7"/>
-      <c r="T21" s="7"/>
-      <c r="U21" s="7"/>
-      <c r="V21" s="7"/>
-      <c r="W21" s="7"/>
-      <c r="X21" s="7"/>
-      <c r="Y21" s="7"/>
-    </row>
-    <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="B22" s="9">
+      <c r="C64" s="20" t="s">
+        <v>244</v>
+      </c>
+      <c r="D64" s="20" t="s">
+        <v>245</v>
+      </c>
+      <c r="E64" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="F64" s="20"/>
+      <c r="G64" s="20"/>
+      <c r="H64" s="20"/>
+      <c r="I64" s="20"/>
+      <c r="J64" s="20"/>
+      <c r="K64" s="20"/>
+      <c r="L64" s="20"/>
+      <c r="M64" s="20"/>
+      <c r="N64" s="20"/>
+      <c r="O64" s="20"/>
+      <c r="P64" s="20"/>
+      <c r="Q64" s="20"/>
+      <c r="R64" s="20"/>
+      <c r="S64" s="20"/>
+      <c r="T64" s="20"/>
+      <c r="U64" s="20"/>
+      <c r="V64" s="20"/>
+      <c r="W64" s="20"/>
+      <c r="X64" s="20"/>
+      <c r="Y64" s="20"/>
+    </row>
+    <row r="65" ht="15.0" customHeight="1">
+      <c r="A65" s="18" t="s">
+        <v>247</v>
+      </c>
+      <c r="B65" s="19">
         <v>0.0</v>
       </c>
-      <c r="C22" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
-      <c r="M22" s="10"/>
-      <c r="N22" s="10"/>
-      <c r="O22" s="10"/>
-      <c r="P22" s="10"/>
-      <c r="Q22" s="10"/>
-      <c r="R22" s="10"/>
-      <c r="S22" s="10"/>
-      <c r="T22" s="10"/>
-      <c r="U22" s="10"/>
-      <c r="V22" s="10"/>
-      <c r="W22" s="10"/>
-      <c r="X22" s="10"/>
-      <c r="Y22" s="10"/>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="B23" s="12">
+      <c r="C65" s="20" t="s">
+        <v>248</v>
+      </c>
+      <c r="D65" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="E65" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="F65" s="20"/>
+      <c r="G65" s="20"/>
+      <c r="H65" s="20"/>
+      <c r="I65" s="20"/>
+      <c r="J65" s="20"/>
+      <c r="K65" s="20"/>
+      <c r="L65" s="20"/>
+      <c r="M65" s="20"/>
+      <c r="N65" s="20"/>
+      <c r="O65" s="20"/>
+      <c r="P65" s="20"/>
+      <c r="Q65" s="20"/>
+      <c r="R65" s="20"/>
+      <c r="S65" s="20"/>
+      <c r="T65" s="20"/>
+      <c r="U65" s="20"/>
+      <c r="V65" s="20"/>
+      <c r="W65" s="20"/>
+      <c r="X65" s="20"/>
+      <c r="Y65" s="20"/>
+    </row>
+    <row r="66" ht="15.0" customHeight="1">
+      <c r="A66" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="B66" s="19">
         <v>0.0</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="13"/>
-      <c r="L23" s="13"/>
-      <c r="M23" s="13"/>
-      <c r="N23" s="13"/>
-      <c r="O23" s="13"/>
-      <c r="P23" s="13"/>
-      <c r="Q23" s="13"/>
-      <c r="R23" s="13"/>
-      <c r="S23" s="13"/>
-      <c r="T23" s="13"/>
-      <c r="U23" s="13"/>
-      <c r="V23" s="13"/>
-      <c r="W23" s="13"/>
-      <c r="X23" s="13"/>
-      <c r="Y23" s="13"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="B24" s="15">
+      <c r="C66" s="20" t="s">
+        <v>252</v>
+      </c>
+      <c r="D66" s="20" t="s">
+        <v>253</v>
+      </c>
+      <c r="E66" s="20" t="s">
+        <v>254</v>
+      </c>
+      <c r="F66" s="20"/>
+      <c r="G66" s="20"/>
+      <c r="H66" s="20"/>
+      <c r="I66" s="20"/>
+      <c r="J66" s="20"/>
+      <c r="K66" s="20"/>
+      <c r="L66" s="20"/>
+      <c r="M66" s="20"/>
+      <c r="N66" s="20"/>
+      <c r="O66" s="20"/>
+      <c r="P66" s="20"/>
+      <c r="Q66" s="20"/>
+      <c r="R66" s="20"/>
+      <c r="S66" s="20"/>
+      <c r="T66" s="20"/>
+      <c r="U66" s="20"/>
+      <c r="V66" s="20"/>
+      <c r="W66" s="20"/>
+      <c r="X66" s="20"/>
+      <c r="Y66" s="20"/>
+    </row>
+    <row r="67" ht="15.0" customHeight="1">
+      <c r="A67" s="18" t="s">
+        <v>255</v>
+      </c>
+      <c r="B67" s="19">
         <v>0.0</v>
       </c>
-      <c r="C24" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="D24" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="E24" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="16"/>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="16"/>
-      <c r="O24" s="16"/>
-      <c r="P24" s="16"/>
-      <c r="Q24" s="16"/>
-      <c r="R24" s="16"/>
-      <c r="S24" s="16"/>
-      <c r="T24" s="16"/>
-      <c r="U24" s="16"/>
-      <c r="V24" s="16"/>
-      <c r="W24" s="16"/>
-      <c r="X24" s="16"/>
-      <c r="Y24" s="16"/>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="B25" s="15">
+      <c r="C67" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="D67" s="20" t="s">
+        <v>257</v>
+      </c>
+      <c r="E67" s="20" t="s">
+        <v>258</v>
+      </c>
+      <c r="F67" s="20"/>
+      <c r="G67" s="20"/>
+      <c r="H67" s="20"/>
+      <c r="I67" s="20"/>
+      <c r="J67" s="20"/>
+      <c r="K67" s="20"/>
+      <c r="L67" s="20"/>
+      <c r="M67" s="20"/>
+      <c r="N67" s="20"/>
+      <c r="O67" s="20"/>
+      <c r="P67" s="20"/>
+      <c r="Q67" s="20"/>
+      <c r="R67" s="20"/>
+      <c r="S67" s="20"/>
+      <c r="T67" s="20"/>
+      <c r="U67" s="20"/>
+      <c r="V67" s="20"/>
+      <c r="W67" s="20"/>
+      <c r="X67" s="20"/>
+      <c r="Y67" s="20"/>
+    </row>
+    <row r="68" ht="15.0" customHeight="1">
+      <c r="A68" s="18" t="s">
+        <v>259</v>
+      </c>
+      <c r="B68" s="19">
         <v>0.0</v>
       </c>
-      <c r="C25" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="D25" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="E25" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
-      <c r="J25" s="16"/>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="16"/>
-      <c r="O25" s="16"/>
-      <c r="P25" s="16"/>
-      <c r="Q25" s="16"/>
-      <c r="R25" s="16"/>
-      <c r="S25" s="16"/>
-      <c r="T25" s="16"/>
-      <c r="U25" s="16"/>
-      <c r="V25" s="16"/>
-      <c r="W25" s="16"/>
-      <c r="X25" s="16"/>
-      <c r="Y25" s="16"/>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="B26" s="15">
+      <c r="C68" s="20" t="s">
+        <v>260</v>
+      </c>
+      <c r="D68" s="20" t="s">
+        <v>261</v>
+      </c>
+      <c r="E68" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="F68" s="20"/>
+      <c r="G68" s="20"/>
+      <c r="H68" s="20"/>
+      <c r="I68" s="20"/>
+      <c r="J68" s="20"/>
+      <c r="K68" s="20"/>
+      <c r="L68" s="20"/>
+      <c r="M68" s="20"/>
+      <c r="N68" s="20"/>
+      <c r="O68" s="20"/>
+      <c r="P68" s="20"/>
+      <c r="Q68" s="20"/>
+      <c r="R68" s="20"/>
+      <c r="S68" s="20"/>
+      <c r="T68" s="20"/>
+      <c r="U68" s="20"/>
+      <c r="V68" s="20"/>
+      <c r="W68" s="20"/>
+      <c r="X68" s="20"/>
+      <c r="Y68" s="20"/>
+    </row>
+    <row r="69" ht="15.0" customHeight="1">
+      <c r="A69" s="18" t="s">
+        <v>263</v>
+      </c>
+      <c r="B69" s="19">
         <v>0.0</v>
       </c>
-      <c r="C26" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="D26" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="E26" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="16"/>
-      <c r="J26" s="16"/>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="16"/>
-      <c r="O26" s="16"/>
-      <c r="P26" s="16"/>
-      <c r="Q26" s="16"/>
-      <c r="R26" s="16"/>
-      <c r="S26" s="16"/>
-      <c r="T26" s="16"/>
-      <c r="U26" s="16"/>
-      <c r="V26" s="16"/>
-      <c r="W26" s="16"/>
-      <c r="X26" s="16"/>
-      <c r="Y26" s="16"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="B27" s="15">
+      <c r="C69" s="20" t="s">
+        <v>264</v>
+      </c>
+      <c r="D69" s="20" t="s">
+        <v>265</v>
+      </c>
+      <c r="E69" s="20" t="s">
+        <v>266</v>
+      </c>
+      <c r="F69" s="20"/>
+      <c r="G69" s="20"/>
+      <c r="H69" s="20"/>
+      <c r="I69" s="20"/>
+      <c r="J69" s="20"/>
+      <c r="K69" s="20"/>
+      <c r="L69" s="20"/>
+      <c r="M69" s="20"/>
+      <c r="N69" s="20"/>
+      <c r="O69" s="20"/>
+      <c r="P69" s="20"/>
+      <c r="Q69" s="20"/>
+      <c r="R69" s="20"/>
+      <c r="S69" s="20"/>
+      <c r="T69" s="20"/>
+      <c r="U69" s="20"/>
+      <c r="V69" s="20"/>
+      <c r="W69" s="20"/>
+      <c r="X69" s="20"/>
+      <c r="Y69" s="20"/>
+    </row>
+    <row r="70" ht="15.0" customHeight="1">
+      <c r="A70" s="18" t="s">
+        <v>267</v>
+      </c>
+      <c r="B70" s="19">
         <v>0.0</v>
       </c>
-      <c r="C27" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="D27" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="E27" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="16"/>
-      <c r="J27" s="16"/>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="16"/>
-      <c r="O27" s="16"/>
-      <c r="P27" s="16"/>
-      <c r="Q27" s="16"/>
-      <c r="R27" s="16"/>
-      <c r="S27" s="16"/>
-      <c r="T27" s="16"/>
-      <c r="U27" s="16"/>
-      <c r="V27" s="16"/>
-      <c r="W27" s="16"/>
-      <c r="X27" s="16"/>
-      <c r="Y27" s="16"/>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="B28" s="15">
+      <c r="C70" s="20" t="s">
+        <v>268</v>
+      </c>
+      <c r="D70" s="20" t="s">
+        <v>269</v>
+      </c>
+      <c r="E70" s="20" t="s">
+        <v>270</v>
+      </c>
+      <c r="F70" s="20"/>
+      <c r="G70" s="20"/>
+      <c r="H70" s="20"/>
+      <c r="I70" s="20"/>
+      <c r="J70" s="20"/>
+      <c r="K70" s="20"/>
+      <c r="L70" s="20"/>
+      <c r="M70" s="20"/>
+      <c r="N70" s="20"/>
+      <c r="O70" s="20"/>
+      <c r="P70" s="20"/>
+      <c r="Q70" s="20"/>
+      <c r="R70" s="20"/>
+      <c r="S70" s="20"/>
+      <c r="T70" s="20"/>
+      <c r="U70" s="20"/>
+      <c r="V70" s="20"/>
+      <c r="W70" s="20"/>
+      <c r="X70" s="20"/>
+      <c r="Y70" s="20"/>
+    </row>
+    <row r="71" ht="15.0" customHeight="1">
+      <c r="A71" s="18" t="s">
+        <v>271</v>
+      </c>
+      <c r="B71" s="19">
         <v>0.0</v>
       </c>
-      <c r="C28" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="D28" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="E28" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="16"/>
-      <c r="J28" s="16"/>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="16"/>
-      <c r="O28" s="16"/>
-      <c r="P28" s="16"/>
-      <c r="Q28" s="16"/>
-      <c r="R28" s="16"/>
-      <c r="S28" s="16"/>
-      <c r="T28" s="16"/>
-      <c r="U28" s="16"/>
-      <c r="V28" s="16"/>
-      <c r="W28" s="16"/>
-      <c r="X28" s="16"/>
-      <c r="Y28" s="16"/>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="B29" s="15">
+      <c r="C71" s="20" t="s">
+        <v>272</v>
+      </c>
+      <c r="D71" s="20" t="s">
+        <v>273</v>
+      </c>
+      <c r="E71" s="20" t="s">
+        <v>274</v>
+      </c>
+      <c r="F71" s="20"/>
+      <c r="G71" s="20"/>
+      <c r="H71" s="20"/>
+      <c r="I71" s="20"/>
+      <c r="J71" s="20"/>
+      <c r="K71" s="20"/>
+      <c r="L71" s="20"/>
+      <c r="M71" s="20"/>
+      <c r="N71" s="20"/>
+      <c r="O71" s="20"/>
+      <c r="P71" s="20"/>
+      <c r="Q71" s="20"/>
+      <c r="R71" s="20"/>
+      <c r="S71" s="20"/>
+      <c r="T71" s="20"/>
+      <c r="U71" s="20"/>
+      <c r="V71" s="20"/>
+      <c r="W71" s="20"/>
+      <c r="X71" s="20"/>
+      <c r="Y71" s="20"/>
+    </row>
+    <row r="72" ht="15.0" customHeight="1">
+      <c r="A72" s="18" t="s">
+        <v>275</v>
+      </c>
+      <c r="B72" s="19">
         <v>0.0</v>
       </c>
-      <c r="C29" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="D29" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="E29" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="F29" s="16"/>
-      <c r="G29" s="16"/>
-      <c r="H29" s="16"/>
-      <c r="I29" s="16"/>
-      <c r="J29" s="16"/>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="16"/>
-      <c r="O29" s="16"/>
-      <c r="P29" s="16"/>
-      <c r="Q29" s="16"/>
-      <c r="R29" s="16"/>
-      <c r="S29" s="16"/>
-      <c r="T29" s="16"/>
-      <c r="U29" s="16"/>
-      <c r="V29" s="16"/>
-      <c r="W29" s="16"/>
-      <c r="X29" s="16"/>
-      <c r="Y29" s="16"/>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="B30" s="15">
+      <c r="C72" s="20" t="s">
+        <v>276</v>
+      </c>
+      <c r="D72" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="E72" s="20" t="s">
+        <v>278</v>
+      </c>
+      <c r="F72" s="20"/>
+      <c r="G72" s="20"/>
+      <c r="H72" s="20"/>
+      <c r="I72" s="20"/>
+      <c r="J72" s="20"/>
+      <c r="K72" s="20"/>
+      <c r="L72" s="20"/>
+      <c r="M72" s="20"/>
+      <c r="N72" s="20"/>
+      <c r="O72" s="20"/>
+      <c r="P72" s="20"/>
+      <c r="Q72" s="20"/>
+      <c r="R72" s="20"/>
+      <c r="S72" s="20"/>
+      <c r="T72" s="20"/>
+      <c r="U72" s="20"/>
+      <c r="V72" s="20"/>
+      <c r="W72" s="20"/>
+      <c r="X72" s="20"/>
+      <c r="Y72" s="20"/>
+    </row>
+    <row r="73" ht="15.0" customHeight="1">
+      <c r="A73" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="B73" s="22">
         <v>0.0</v>
       </c>
-      <c r="C30" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="D30" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="E30" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="F30" s="16"/>
-      <c r="G30" s="16"/>
-      <c r="H30" s="16"/>
-      <c r="I30" s="16"/>
-      <c r="J30" s="16"/>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="16"/>
-      <c r="O30" s="16"/>
-      <c r="P30" s="16"/>
-      <c r="Q30" s="16"/>
-      <c r="R30" s="16"/>
-      <c r="S30" s="16"/>
-      <c r="T30" s="16"/>
-      <c r="U30" s="16"/>
-      <c r="V30" s="16"/>
-      <c r="W30" s="16"/>
-      <c r="X30" s="16"/>
-      <c r="Y30" s="16"/>
-    </row>
-    <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="B31" s="15">
+      <c r="C73" s="23" t="s">
+        <v>280</v>
+      </c>
+      <c r="D73" s="23" t="s">
+        <v>281</v>
+      </c>
+      <c r="E73" s="23" t="s">
+        <v>282</v>
+      </c>
+      <c r="F73" s="23"/>
+      <c r="G73" s="23"/>
+      <c r="H73" s="23"/>
+      <c r="I73" s="23"/>
+      <c r="J73" s="23"/>
+      <c r="K73" s="23"/>
+      <c r="L73" s="23"/>
+      <c r="M73" s="23"/>
+      <c r="N73" s="23"/>
+      <c r="O73" s="23"/>
+      <c r="P73" s="23"/>
+      <c r="Q73" s="23"/>
+      <c r="R73" s="23"/>
+      <c r="S73" s="23"/>
+      <c r="T73" s="23"/>
+      <c r="U73" s="23"/>
+      <c r="V73" s="23"/>
+      <c r="W73" s="23"/>
+      <c r="X73" s="23"/>
+      <c r="Y73" s="23"/>
+    </row>
+    <row r="74" ht="15.0" customHeight="1">
+      <c r="A74" s="24" t="s">
+        <v>283</v>
+      </c>
+      <c r="B74" s="25">
         <v>0.0</v>
       </c>
-      <c r="C31" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="D31" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="E31" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
-      <c r="H31" s="16"/>
-      <c r="I31" s="16"/>
-      <c r="J31" s="16"/>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="16"/>
-      <c r="O31" s="16"/>
-      <c r="P31" s="16"/>
-      <c r="Q31" s="16"/>
-      <c r="R31" s="16"/>
-      <c r="S31" s="16"/>
-      <c r="T31" s="16"/>
-      <c r="U31" s="16"/>
-      <c r="V31" s="16"/>
-      <c r="W31" s="16"/>
-      <c r="X31" s="16"/>
-      <c r="Y31" s="16"/>
-    </row>
-    <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="B32" s="15">
+      <c r="C74" s="25" t="s">
+        <v>284</v>
+      </c>
+      <c r="D74" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="E74" s="25" t="s">
+        <v>160</v>
+      </c>
+      <c r="F74" s="25"/>
+      <c r="G74" s="25"/>
+      <c r="H74" s="25"/>
+      <c r="I74" s="25"/>
+      <c r="J74" s="25"/>
+      <c r="K74" s="25"/>
+      <c r="L74" s="25"/>
+      <c r="M74" s="25"/>
+      <c r="N74" s="25"/>
+      <c r="O74" s="25"/>
+      <c r="P74" s="25"/>
+      <c r="Q74" s="25"/>
+      <c r="R74" s="25"/>
+      <c r="S74" s="25"/>
+      <c r="T74" s="25"/>
+      <c r="U74" s="25"/>
+      <c r="V74" s="25"/>
+      <c r="W74" s="25"/>
+      <c r="X74" s="25"/>
+      <c r="Y74" s="25"/>
+    </row>
+    <row r="75" ht="15.0" customHeight="1">
+      <c r="A75" s="24" t="s">
+        <v>285</v>
+      </c>
+      <c r="B75" s="25">
         <v>0.0</v>
       </c>
-      <c r="C32" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="D32" s="16" t="s">
-        <v>119</v>
-      </c>
-      <c r="E32" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="16"/>
-      <c r="I32" s="16"/>
-      <c r="J32" s="16"/>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="16"/>
-      <c r="O32" s="16"/>
-      <c r="P32" s="16"/>
-      <c r="Q32" s="16"/>
-      <c r="R32" s="16"/>
-      <c r="S32" s="16"/>
-      <c r="T32" s="16"/>
-      <c r="U32" s="16"/>
-      <c r="V32" s="16"/>
-      <c r="W32" s="16"/>
-      <c r="X32" s="16"/>
-      <c r="Y32" s="16"/>
-    </row>
-    <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="B33" s="15">
+      <c r="C75" s="25" t="s">
+        <v>286</v>
+      </c>
+      <c r="D75" s="25" t="s">
+        <v>287</v>
+      </c>
+      <c r="E75" s="25" t="s">
+        <v>288</v>
+      </c>
+      <c r="F75" s="25"/>
+      <c r="G75" s="25"/>
+      <c r="H75" s="25"/>
+      <c r="I75" s="25"/>
+      <c r="J75" s="25"/>
+      <c r="K75" s="25"/>
+      <c r="L75" s="25"/>
+      <c r="M75" s="25"/>
+      <c r="N75" s="25"/>
+      <c r="O75" s="25"/>
+      <c r="P75" s="25"/>
+      <c r="Q75" s="25"/>
+      <c r="R75" s="25"/>
+      <c r="S75" s="25"/>
+      <c r="T75" s="25"/>
+      <c r="U75" s="25"/>
+      <c r="V75" s="25"/>
+      <c r="W75" s="25"/>
+      <c r="X75" s="25"/>
+      <c r="Y75" s="25"/>
+    </row>
+    <row r="76" ht="15.75" customHeight="1">
+      <c r="A76" s="24" t="s">
+        <v>289</v>
+      </c>
+      <c r="B76" s="25">
         <v>0.0</v>
       </c>
-      <c r="C33" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="D33" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="E33" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="F33" s="16"/>
-      <c r="G33" s="16"/>
-      <c r="H33" s="16"/>
-      <c r="I33" s="16"/>
-      <c r="J33" s="16"/>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="16"/>
-      <c r="O33" s="16"/>
-      <c r="P33" s="16"/>
-      <c r="Q33" s="16"/>
-      <c r="R33" s="16"/>
-      <c r="S33" s="16"/>
-      <c r="T33" s="16"/>
-      <c r="U33" s="16"/>
-      <c r="V33" s="16"/>
-      <c r="W33" s="16"/>
-      <c r="X33" s="16"/>
-      <c r="Y33" s="16"/>
-    </row>
-    <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="B34" s="15">
+      <c r="C76" s="25" t="s">
+        <v>290</v>
+      </c>
+      <c r="D76" s="25" t="s">
+        <v>187</v>
+      </c>
+      <c r="E76" s="25" t="s">
+        <v>188</v>
+      </c>
+      <c r="F76" s="25"/>
+      <c r="G76" s="25"/>
+      <c r="H76" s="25"/>
+      <c r="I76" s="25"/>
+      <c r="J76" s="25"/>
+      <c r="K76" s="25"/>
+      <c r="L76" s="25"/>
+      <c r="M76" s="25"/>
+      <c r="N76" s="25"/>
+      <c r="O76" s="25"/>
+      <c r="P76" s="25"/>
+      <c r="Q76" s="25"/>
+      <c r="R76" s="25"/>
+      <c r="S76" s="25"/>
+      <c r="T76" s="25"/>
+      <c r="U76" s="25"/>
+      <c r="V76" s="25"/>
+      <c r="W76" s="25"/>
+      <c r="X76" s="25"/>
+      <c r="Y76" s="25"/>
+    </row>
+    <row r="77" ht="15.75" customHeight="1">
+      <c r="A77" s="24" t="s">
+        <v>291</v>
+      </c>
+      <c r="B77" s="25">
         <v>0.0</v>
       </c>
-      <c r="C34" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="D34" s="16" t="s">
-        <v>127</v>
-      </c>
-      <c r="E34" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="F34" s="16"/>
-      <c r="G34" s="16"/>
-      <c r="H34" s="16"/>
-      <c r="I34" s="16"/>
-      <c r="J34" s="16"/>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="16"/>
-      <c r="O34" s="16"/>
-      <c r="P34" s="16"/>
-      <c r="Q34" s="16"/>
-      <c r="R34" s="16"/>
-      <c r="S34" s="16"/>
-      <c r="T34" s="16"/>
-      <c r="U34" s="16"/>
-      <c r="V34" s="16"/>
-      <c r="W34" s="16"/>
-      <c r="X34" s="16"/>
-      <c r="Y34" s="16"/>
-    </row>
-    <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="B35" s="15">
+      <c r="C77" s="25" t="s">
+        <v>292</v>
+      </c>
+      <c r="D77" s="25" t="s">
+        <v>293</v>
+      </c>
+      <c r="E77" s="25" t="s">
+        <v>294</v>
+      </c>
+      <c r="F77" s="25"/>
+      <c r="G77" s="25"/>
+      <c r="H77" s="25"/>
+      <c r="I77" s="25"/>
+      <c r="J77" s="25"/>
+      <c r="K77" s="25"/>
+      <c r="L77" s="25"/>
+      <c r="M77" s="25"/>
+      <c r="N77" s="25"/>
+      <c r="O77" s="25"/>
+      <c r="P77" s="25"/>
+      <c r="Q77" s="25"/>
+      <c r="R77" s="25"/>
+      <c r="S77" s="25"/>
+      <c r="T77" s="25"/>
+      <c r="U77" s="25"/>
+      <c r="V77" s="25"/>
+      <c r="W77" s="25"/>
+      <c r="X77" s="25"/>
+      <c r="Y77" s="25"/>
+    </row>
+    <row r="78" ht="15.0" customHeight="1">
+      <c r="A78" s="24" t="s">
+        <v>295</v>
+      </c>
+      <c r="B78" s="25">
         <v>0.0</v>
       </c>
-      <c r="C35" s="16" t="s">
-        <v>130</v>
-      </c>
-      <c r="D35" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="E35" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="F35" s="16"/>
-      <c r="G35" s="16"/>
-      <c r="H35" s="16"/>
-      <c r="I35" s="16"/>
-      <c r="J35" s="16"/>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="16"/>
-      <c r="O35" s="16"/>
-      <c r="P35" s="16"/>
-      <c r="Q35" s="16"/>
-      <c r="R35" s="16"/>
-      <c r="S35" s="16"/>
-      <c r="T35" s="16"/>
-      <c r="U35" s="16"/>
-      <c r="V35" s="16"/>
-      <c r="W35" s="16"/>
-      <c r="X35" s="16"/>
-      <c r="Y35" s="16"/>
-    </row>
-    <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="B36" s="15">
+      <c r="C78" s="25" t="s">
+        <v>296</v>
+      </c>
+      <c r="D78" s="25" t="s">
+        <v>297</v>
+      </c>
+      <c r="E78" s="25" t="s">
+        <v>298</v>
+      </c>
+      <c r="F78" s="25"/>
+      <c r="G78" s="25"/>
+      <c r="H78" s="25"/>
+      <c r="I78" s="25"/>
+      <c r="J78" s="25"/>
+      <c r="K78" s="25"/>
+      <c r="L78" s="25"/>
+      <c r="M78" s="25"/>
+      <c r="N78" s="25"/>
+      <c r="O78" s="25"/>
+      <c r="P78" s="25"/>
+      <c r="Q78" s="25"/>
+      <c r="R78" s="25"/>
+      <c r="S78" s="25"/>
+      <c r="T78" s="25"/>
+      <c r="U78" s="25"/>
+      <c r="V78" s="25"/>
+      <c r="W78" s="25"/>
+      <c r="X78" s="25"/>
+      <c r="Y78" s="25"/>
+    </row>
+    <row r="79" ht="15.0" customHeight="1">
+      <c r="A79" s="24" t="s">
+        <v>299</v>
+      </c>
+      <c r="B79" s="25">
         <v>0.0</v>
       </c>
-      <c r="C36" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="D36" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="E36" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="F36" s="16"/>
-      <c r="G36" s="16"/>
-      <c r="H36" s="16"/>
-      <c r="I36" s="16"/>
-      <c r="J36" s="16"/>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="16"/>
-      <c r="O36" s="16"/>
-      <c r="P36" s="16"/>
-      <c r="Q36" s="16"/>
-      <c r="R36" s="16"/>
-      <c r="S36" s="16"/>
-      <c r="T36" s="16"/>
-      <c r="U36" s="16"/>
-      <c r="V36" s="16"/>
-      <c r="W36" s="16"/>
-      <c r="X36" s="16"/>
-      <c r="Y36" s="16"/>
-    </row>
-    <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="B37" s="15">
+      <c r="C79" s="25" t="s">
+        <v>300</v>
+      </c>
+      <c r="D79" s="25" t="s">
+        <v>301</v>
+      </c>
+      <c r="E79" s="25" t="s">
+        <v>302</v>
+      </c>
+      <c r="F79" s="25"/>
+      <c r="G79" s="25"/>
+      <c r="H79" s="25"/>
+      <c r="I79" s="25"/>
+      <c r="J79" s="25"/>
+      <c r="K79" s="25"/>
+      <c r="L79" s="25"/>
+      <c r="M79" s="25"/>
+      <c r="N79" s="25"/>
+      <c r="O79" s="25"/>
+      <c r="P79" s="25"/>
+      <c r="Q79" s="25"/>
+      <c r="R79" s="25"/>
+      <c r="S79" s="25"/>
+      <c r="T79" s="25"/>
+      <c r="U79" s="25"/>
+      <c r="V79" s="25"/>
+      <c r="W79" s="25"/>
+      <c r="X79" s="25"/>
+      <c r="Y79" s="25"/>
+    </row>
+    <row r="80" ht="15.0" customHeight="1">
+      <c r="A80" s="24" t="s">
+        <v>303</v>
+      </c>
+      <c r="B80" s="25">
         <v>0.0</v>
       </c>
-      <c r="C37" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="D37" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="E37" s="16" t="s">
-        <v>140</v>
-      </c>
-      <c r="F37" s="16"/>
-      <c r="G37" s="16"/>
-      <c r="H37" s="16"/>
-      <c r="I37" s="16"/>
-      <c r="J37" s="16"/>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="16"/>
-      <c r="O37" s="16"/>
-      <c r="P37" s="16"/>
-      <c r="Q37" s="16"/>
-      <c r="R37" s="16"/>
-      <c r="S37" s="16"/>
-      <c r="T37" s="16"/>
-      <c r="U37" s="16"/>
-      <c r="V37" s="16"/>
-      <c r="W37" s="16"/>
-      <c r="X37" s="16"/>
-      <c r="Y37" s="16"/>
-    </row>
-    <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="B38" s="15">
+      <c r="C80" s="25" t="s">
+        <v>304</v>
+      </c>
+      <c r="D80" s="25" t="s">
+        <v>305</v>
+      </c>
+      <c r="E80" s="25" t="s">
+        <v>306</v>
+      </c>
+      <c r="F80" s="25"/>
+      <c r="G80" s="25"/>
+      <c r="H80" s="25"/>
+      <c r="I80" s="25"/>
+      <c r="J80" s="25"/>
+      <c r="K80" s="25"/>
+      <c r="L80" s="25"/>
+      <c r="M80" s="25"/>
+      <c r="N80" s="25"/>
+      <c r="O80" s="25"/>
+      <c r="P80" s="25"/>
+      <c r="Q80" s="25"/>
+      <c r="R80" s="25"/>
+      <c r="S80" s="25"/>
+      <c r="T80" s="25"/>
+      <c r="U80" s="25"/>
+      <c r="V80" s="25"/>
+      <c r="W80" s="25"/>
+      <c r="X80" s="25"/>
+      <c r="Y80" s="25"/>
+    </row>
+    <row r="81" ht="15.0" customHeight="1">
+      <c r="A81" s="26" t="s">
+        <v>307</v>
+      </c>
+      <c r="B81" s="27">
         <v>0.0</v>
       </c>
-      <c r="C38" s="16" t="s">
-        <v>142</v>
-      </c>
-      <c r="D38" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="E38" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="F38" s="16"/>
-      <c r="G38" s="16"/>
-      <c r="H38" s="16"/>
-      <c r="I38" s="16"/>
-      <c r="J38" s="16"/>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="16"/>
-      <c r="O38" s="16"/>
-      <c r="P38" s="16"/>
-      <c r="Q38" s="16"/>
-      <c r="R38" s="16"/>
-      <c r="S38" s="16"/>
-      <c r="T38" s="16"/>
-      <c r="U38" s="16"/>
-      <c r="V38" s="16"/>
-      <c r="W38" s="16"/>
-      <c r="X38" s="16"/>
-      <c r="Y38" s="16"/>
-    </row>
-    <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="B39" s="15">
+      <c r="C81" s="28" t="s">
+        <v>308</v>
+      </c>
+      <c r="D81" s="28" t="s">
+        <v>219</v>
+      </c>
+      <c r="E81" s="28" t="s">
+        <v>220</v>
+      </c>
+      <c r="F81" s="28"/>
+      <c r="G81" s="28"/>
+      <c r="H81" s="28"/>
+      <c r="I81" s="28"/>
+      <c r="J81" s="28"/>
+      <c r="K81" s="28"/>
+      <c r="L81" s="28"/>
+      <c r="M81" s="28"/>
+      <c r="N81" s="28"/>
+      <c r="O81" s="28"/>
+      <c r="P81" s="28"/>
+      <c r="Q81" s="28"/>
+      <c r="R81" s="28"/>
+      <c r="S81" s="28"/>
+      <c r="T81" s="28"/>
+      <c r="U81" s="28"/>
+      <c r="V81" s="28"/>
+      <c r="W81" s="28"/>
+      <c r="X81" s="28"/>
+      <c r="Y81" s="28"/>
+    </row>
+    <row r="82" ht="15.0" customHeight="1">
+      <c r="A82" s="29" t="s">
+        <v>309</v>
+      </c>
+      <c r="B82" s="30">
         <v>0.0</v>
       </c>
-      <c r="C39" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="D39" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="E39" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="F39" s="16"/>
-      <c r="G39" s="16"/>
-      <c r="H39" s="16"/>
-      <c r="I39" s="16"/>
-      <c r="J39" s="16"/>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="16"/>
-      <c r="O39" s="16"/>
-      <c r="P39" s="16"/>
-      <c r="Q39" s="16"/>
-      <c r="R39" s="16"/>
-      <c r="S39" s="16"/>
-      <c r="T39" s="16"/>
-      <c r="U39" s="16"/>
-      <c r="V39" s="16"/>
-      <c r="W39" s="16"/>
-      <c r="X39" s="16"/>
-      <c r="Y39" s="16"/>
-    </row>
-    <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="B40" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C40" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="D40" s="16" t="s">
+      <c r="C82" s="31" t="s">
+        <v>310</v>
+      </c>
+      <c r="D82" s="31" t="s">
         <v>151</v>
       </c>
-      <c r="E40" s="16" t="s">
+      <c r="E82" s="31" t="s">
         <v>152</v>
       </c>
-      <c r="F40" s="16"/>
-      <c r="G40" s="16"/>
-      <c r="H40" s="16"/>
-      <c r="I40" s="16"/>
-      <c r="J40" s="16"/>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="16"/>
-      <c r="O40" s="16"/>
-      <c r="P40" s="16"/>
-      <c r="Q40" s="16"/>
-      <c r="R40" s="16"/>
-      <c r="S40" s="16"/>
-      <c r="T40" s="16"/>
-      <c r="U40" s="16"/>
-      <c r="V40" s="16"/>
-      <c r="W40" s="16"/>
-      <c r="X40" s="16"/>
-      <c r="Y40" s="16"/>
-    </row>
-    <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="14" t="s">
-        <v>153</v>
-      </c>
-      <c r="B41" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C41" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="D41" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="E41" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="F41" s="16"/>
-      <c r="G41" s="16"/>
-      <c r="H41" s="16"/>
-      <c r="I41" s="16"/>
-      <c r="J41" s="16"/>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="16"/>
-      <c r="O41" s="16"/>
-      <c r="P41" s="16"/>
-      <c r="Q41" s="16"/>
-      <c r="R41" s="16"/>
-      <c r="S41" s="16"/>
-      <c r="T41" s="16"/>
-      <c r="U41" s="16"/>
-      <c r="V41" s="16"/>
-      <c r="W41" s="16"/>
-      <c r="X41" s="16"/>
-      <c r="Y41" s="16"/>
-    </row>
-    <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="14" t="s">
-        <v>157</v>
-      </c>
-      <c r="B42" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C42" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="D42" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="E42" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="F42" s="16"/>
-      <c r="G42" s="16"/>
-      <c r="H42" s="16"/>
-      <c r="I42" s="16"/>
-      <c r="J42" s="16"/>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="16"/>
-      <c r="O42" s="16"/>
-      <c r="P42" s="16"/>
-      <c r="Q42" s="16"/>
-      <c r="R42" s="16"/>
-      <c r="S42" s="16"/>
-      <c r="T42" s="16"/>
-      <c r="U42" s="16"/>
-      <c r="V42" s="16"/>
-      <c r="W42" s="16"/>
-      <c r="X42" s="16"/>
-      <c r="Y42" s="16"/>
-    </row>
-    <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="B43" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C43" s="16" t="s">
-        <v>162</v>
-      </c>
-      <c r="D43" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="E43" s="16" t="s">
-        <v>164</v>
-      </c>
-      <c r="F43" s="16"/>
-      <c r="G43" s="16"/>
-      <c r="H43" s="16"/>
-      <c r="I43" s="16"/>
-      <c r="J43" s="16"/>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="16"/>
-      <c r="O43" s="16"/>
-      <c r="P43" s="16"/>
-      <c r="Q43" s="16"/>
-      <c r="R43" s="16"/>
-      <c r="S43" s="16"/>
-      <c r="T43" s="16"/>
-      <c r="U43" s="16"/>
-      <c r="V43" s="16"/>
-      <c r="W43" s="16"/>
-      <c r="X43" s="16"/>
-      <c r="Y43" s="16"/>
-    </row>
-    <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="B44" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C44" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="D44" s="16" t="s">
-        <v>167</v>
-      </c>
-      <c r="E44" s="16" t="s">
-        <v>168</v>
-      </c>
-      <c r="F44" s="16"/>
-      <c r="G44" s="16"/>
-      <c r="H44" s="16"/>
-      <c r="I44" s="16"/>
-      <c r="J44" s="16"/>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="16"/>
-      <c r="O44" s="16"/>
-      <c r="P44" s="16"/>
-      <c r="Q44" s="16"/>
-      <c r="R44" s="16"/>
-      <c r="S44" s="16"/>
-      <c r="T44" s="16"/>
-      <c r="U44" s="16"/>
-      <c r="V44" s="16"/>
-      <c r="W44" s="16"/>
-      <c r="X44" s="16"/>
-      <c r="Y44" s="16"/>
-    </row>
-    <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="B45" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C45" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="D45" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="E45" s="16" t="s">
-        <v>172</v>
-      </c>
-      <c r="F45" s="16"/>
-      <c r="G45" s="16"/>
-      <c r="H45" s="16"/>
-      <c r="I45" s="16"/>
-      <c r="J45" s="16"/>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="16"/>
-      <c r="O45" s="16"/>
-      <c r="P45" s="16"/>
-      <c r="Q45" s="16"/>
-      <c r="R45" s="16"/>
-      <c r="S45" s="16"/>
-      <c r="T45" s="16"/>
-      <c r="U45" s="16"/>
-      <c r="V45" s="16"/>
-      <c r="W45" s="16"/>
-      <c r="X45" s="16"/>
-      <c r="Y45" s="16"/>
-    </row>
-    <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="B46" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C46" s="16" t="s">
-        <v>174</v>
-      </c>
-      <c r="D46" s="16" t="s">
-        <v>175</v>
-      </c>
-      <c r="E46" s="16" t="s">
-        <v>176</v>
-      </c>
-      <c r="F46" s="16"/>
-      <c r="G46" s="16"/>
-      <c r="H46" s="16"/>
-      <c r="I46" s="16"/>
-      <c r="J46" s="16"/>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="16"/>
-      <c r="O46" s="16"/>
-      <c r="P46" s="16"/>
-      <c r="Q46" s="16"/>
-      <c r="R46" s="16"/>
-      <c r="S46" s="16"/>
-      <c r="T46" s="16"/>
-      <c r="U46" s="16"/>
-      <c r="V46" s="16"/>
-      <c r="W46" s="16"/>
-      <c r="X46" s="16"/>
-      <c r="Y46" s="16"/>
-    </row>
-    <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="B47" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C47" s="16" t="s">
-        <v>178</v>
-      </c>
-      <c r="D47" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="E47" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="F47" s="16"/>
-      <c r="G47" s="16"/>
-      <c r="H47" s="16"/>
-      <c r="I47" s="16"/>
-      <c r="J47" s="16"/>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="16"/>
-      <c r="O47" s="16"/>
-      <c r="P47" s="16"/>
-      <c r="Q47" s="16"/>
-      <c r="R47" s="16"/>
-      <c r="S47" s="16"/>
-      <c r="T47" s="16"/>
-      <c r="U47" s="16"/>
-      <c r="V47" s="16"/>
-      <c r="W47" s="16"/>
-      <c r="X47" s="16"/>
-      <c r="Y47" s="16"/>
-    </row>
-    <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="14" t="s">
-        <v>181</v>
-      </c>
-      <c r="B48" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C48" s="16" t="s">
-        <v>182</v>
-      </c>
-      <c r="D48" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="E48" s="16" t="s">
-        <v>184</v>
-      </c>
-      <c r="F48" s="16"/>
-      <c r="G48" s="16"/>
-      <c r="H48" s="16"/>
-      <c r="I48" s="16"/>
-      <c r="J48" s="16"/>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="16"/>
-      <c r="O48" s="16"/>
-      <c r="P48" s="16"/>
-      <c r="Q48" s="16"/>
-      <c r="R48" s="16"/>
-      <c r="S48" s="16"/>
-      <c r="T48" s="16"/>
-      <c r="U48" s="16"/>
-      <c r="V48" s="16"/>
-      <c r="W48" s="16"/>
-      <c r="X48" s="16"/>
-      <c r="Y48" s="16"/>
-    </row>
-    <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="B49" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C49" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="D49" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="E49" s="16" t="s">
-        <v>188</v>
-      </c>
-      <c r="F49" s="16"/>
-      <c r="G49" s="16"/>
-      <c r="H49" s="16"/>
-      <c r="I49" s="16"/>
-      <c r="J49" s="16"/>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="16"/>
-      <c r="O49" s="16"/>
-      <c r="P49" s="16"/>
-      <c r="Q49" s="16"/>
-      <c r="R49" s="16"/>
-      <c r="S49" s="16"/>
-      <c r="T49" s="16"/>
-      <c r="U49" s="16"/>
-      <c r="V49" s="16"/>
-      <c r="W49" s="16"/>
-      <c r="X49" s="16"/>
-      <c r="Y49" s="16"/>
-    </row>
-    <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="B50" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C50" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="D50" s="16" t="s">
-        <v>191</v>
-      </c>
-      <c r="E50" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="F50" s="16"/>
-      <c r="G50" s="16"/>
-      <c r="H50" s="16"/>
-      <c r="I50" s="16"/>
-      <c r="J50" s="16"/>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="16"/>
-      <c r="O50" s="16"/>
-      <c r="P50" s="16"/>
-      <c r="Q50" s="16"/>
-      <c r="R50" s="16"/>
-      <c r="S50" s="16"/>
-      <c r="T50" s="16"/>
-      <c r="U50" s="16"/>
-      <c r="V50" s="16"/>
-      <c r="W50" s="16"/>
-      <c r="X50" s="16"/>
-      <c r="Y50" s="16"/>
-    </row>
-    <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="B51" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C51" s="16" t="s">
-        <v>194</v>
-      </c>
-      <c r="D51" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="E51" s="16" t="s">
-        <v>196</v>
-      </c>
-      <c r="F51" s="16"/>
-      <c r="G51" s="16"/>
-      <c r="H51" s="16"/>
-      <c r="I51" s="16"/>
-      <c r="J51" s="16"/>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="16"/>
-      <c r="O51" s="16"/>
-      <c r="P51" s="16"/>
-      <c r="Q51" s="16"/>
-      <c r="R51" s="16"/>
-      <c r="S51" s="16"/>
-      <c r="T51" s="16"/>
-      <c r="U51" s="16"/>
-      <c r="V51" s="16"/>
-      <c r="W51" s="16"/>
-      <c r="X51" s="16"/>
-      <c r="Y51" s="16"/>
-    </row>
-    <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="B52" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C52" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="D52" s="16" t="s">
-        <v>199</v>
-      </c>
-      <c r="E52" s="16" t="s">
-        <v>200</v>
-      </c>
-      <c r="F52" s="16"/>
-      <c r="G52" s="16"/>
-      <c r="H52" s="16"/>
-      <c r="I52" s="16"/>
-      <c r="J52" s="16"/>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="16"/>
-      <c r="O52" s="16"/>
-      <c r="P52" s="16"/>
-      <c r="Q52" s="16"/>
-      <c r="R52" s="16"/>
-      <c r="S52" s="16"/>
-      <c r="T52" s="16"/>
-      <c r="U52" s="16"/>
-      <c r="V52" s="16"/>
-      <c r="W52" s="16"/>
-      <c r="X52" s="16"/>
-      <c r="Y52" s="16"/>
-    </row>
-    <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="B53" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C53" s="16" t="s">
-        <v>202</v>
-      </c>
-      <c r="D53" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="E53" s="16" t="s">
-        <v>204</v>
-      </c>
-      <c r="F53" s="16"/>
-      <c r="G53" s="16"/>
-      <c r="H53" s="16"/>
-      <c r="I53" s="16"/>
-      <c r="J53" s="16"/>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
-      <c r="N53" s="16"/>
-      <c r="O53" s="16"/>
-      <c r="P53" s="16"/>
-      <c r="Q53" s="16"/>
-      <c r="R53" s="16"/>
-      <c r="S53" s="16"/>
-      <c r="T53" s="16"/>
-      <c r="U53" s="16"/>
-      <c r="V53" s="16"/>
-      <c r="W53" s="16"/>
-      <c r="X53" s="16"/>
-      <c r="Y53" s="16"/>
-    </row>
-    <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="B54" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C54" s="16" t="s">
-        <v>206</v>
-      </c>
-      <c r="D54" s="16" t="s">
-        <v>207</v>
-      </c>
-      <c r="E54" s="16" t="s">
-        <v>208</v>
-      </c>
-      <c r="F54" s="16"/>
-      <c r="G54" s="16"/>
-      <c r="H54" s="16"/>
-      <c r="I54" s="16"/>
-      <c r="J54" s="16"/>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
-      <c r="N54" s="16"/>
-      <c r="O54" s="16"/>
-      <c r="P54" s="16"/>
-      <c r="Q54" s="16"/>
-      <c r="R54" s="16"/>
-      <c r="S54" s="16"/>
-      <c r="T54" s="16"/>
-      <c r="U54" s="16"/>
-      <c r="V54" s="16"/>
-      <c r="W54" s="16"/>
-      <c r="X54" s="16"/>
-      <c r="Y54" s="16"/>
-    </row>
-    <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="14" t="s">
-        <v>209</v>
-      </c>
-      <c r="B55" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C55" s="16" t="s">
-        <v>210</v>
-      </c>
-      <c r="D55" s="16" t="s">
-        <v>211</v>
-      </c>
-      <c r="E55" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="F55" s="16"/>
-      <c r="G55" s="16"/>
-      <c r="H55" s="16"/>
-      <c r="I55" s="16"/>
-      <c r="J55" s="16"/>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
-      <c r="N55" s="16"/>
-      <c r="O55" s="16"/>
-      <c r="P55" s="16"/>
-      <c r="Q55" s="16"/>
-      <c r="R55" s="16"/>
-      <c r="S55" s="16"/>
-      <c r="T55" s="16"/>
-      <c r="U55" s="16"/>
-      <c r="V55" s="16"/>
-      <c r="W55" s="16"/>
-      <c r="X55" s="16"/>
-      <c r="Y55" s="16"/>
-    </row>
-    <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="B56" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C56" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="D56" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="E56" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="F56" s="16"/>
-      <c r="G56" s="16"/>
-      <c r="H56" s="16"/>
-      <c r="I56" s="16"/>
-      <c r="J56" s="16"/>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
-      <c r="N56" s="16"/>
-      <c r="O56" s="16"/>
-      <c r="P56" s="16"/>
-      <c r="Q56" s="16"/>
-      <c r="R56" s="16"/>
-      <c r="S56" s="16"/>
-      <c r="T56" s="16"/>
-      <c r="U56" s="16"/>
-      <c r="V56" s="16"/>
-      <c r="W56" s="16"/>
-      <c r="X56" s="16"/>
-      <c r="Y56" s="16"/>
-    </row>
-    <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="14" t="s">
-        <v>215</v>
-      </c>
-      <c r="B57" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C57" s="16" t="s">
-        <v>216</v>
-      </c>
-      <c r="D57" s="16" t="s">
-        <v>217</v>
-      </c>
-      <c r="E57" s="16" t="s">
-        <v>218</v>
-      </c>
-      <c r="F57" s="16"/>
-      <c r="G57" s="16"/>
-      <c r="H57" s="16"/>
-      <c r="I57" s="16"/>
-      <c r="J57" s="16"/>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
-      <c r="N57" s="16"/>
-      <c r="O57" s="16"/>
-      <c r="P57" s="16"/>
-      <c r="Q57" s="16"/>
-      <c r="R57" s="16"/>
-      <c r="S57" s="16"/>
-      <c r="T57" s="16"/>
-      <c r="U57" s="16"/>
-      <c r="V57" s="16"/>
-      <c r="W57" s="16"/>
-      <c r="X57" s="16"/>
-      <c r="Y57" s="16"/>
-    </row>
-    <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="14" t="s">
-        <v>219</v>
-      </c>
-      <c r="B58" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C58" s="16" t="s">
-        <v>220</v>
-      </c>
-      <c r="D58" s="16" t="s">
-        <v>221</v>
-      </c>
-      <c r="E58" s="16" t="s">
-        <v>222</v>
-      </c>
-      <c r="F58" s="16"/>
-      <c r="G58" s="16"/>
-      <c r="H58" s="16"/>
-      <c r="I58" s="16"/>
-      <c r="J58" s="16"/>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
-      <c r="N58" s="16"/>
-      <c r="O58" s="16"/>
-      <c r="P58" s="16"/>
-      <c r="Q58" s="16"/>
-      <c r="R58" s="16"/>
-      <c r="S58" s="16"/>
-      <c r="T58" s="16"/>
-      <c r="U58" s="16"/>
-      <c r="V58" s="16"/>
-      <c r="W58" s="16"/>
-      <c r="X58" s="16"/>
-      <c r="Y58" s="16"/>
-    </row>
-    <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="14" t="s">
-        <v>223</v>
-      </c>
-      <c r="B59" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C59" s="16" t="s">
-        <v>224</v>
-      </c>
-      <c r="D59" s="16" t="s">
-        <v>225</v>
-      </c>
-      <c r="E59" s="16" t="s">
-        <v>226</v>
-      </c>
-      <c r="F59" s="16"/>
-      <c r="G59" s="16"/>
-      <c r="H59" s="16"/>
-      <c r="I59" s="16"/>
-      <c r="J59" s="16"/>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
-      <c r="N59" s="16"/>
-      <c r="O59" s="16"/>
-      <c r="P59" s="16"/>
-      <c r="Q59" s="16"/>
-      <c r="R59" s="16"/>
-      <c r="S59" s="16"/>
-      <c r="T59" s="16"/>
-      <c r="U59" s="16"/>
-      <c r="V59" s="16"/>
-      <c r="W59" s="16"/>
-      <c r="X59" s="16"/>
-      <c r="Y59" s="16"/>
-    </row>
-    <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="14" t="s">
-        <v>227</v>
-      </c>
-      <c r="B60" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C60" s="16" t="s">
-        <v>228</v>
-      </c>
-      <c r="D60" s="16" t="s">
-        <v>229</v>
-      </c>
-      <c r="E60" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="F60" s="16"/>
-      <c r="G60" s="16"/>
-      <c r="H60" s="16"/>
-      <c r="I60" s="16"/>
-      <c r="J60" s="16"/>
-      <c r="K60" s="16"/>
-      <c r="L60" s="16"/>
-      <c r="M60" s="16"/>
-      <c r="N60" s="16"/>
-      <c r="O60" s="16"/>
-      <c r="P60" s="16"/>
-      <c r="Q60" s="16"/>
-      <c r="R60" s="16"/>
-      <c r="S60" s="16"/>
-      <c r="T60" s="16"/>
-      <c r="U60" s="16"/>
-      <c r="V60" s="16"/>
-      <c r="W60" s="16"/>
-      <c r="X60" s="16"/>
-      <c r="Y60" s="16"/>
-    </row>
-    <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="14" t="s">
-        <v>231</v>
-      </c>
-      <c r="B61" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C61" s="16" t="s">
-        <v>232</v>
-      </c>
-      <c r="D61" s="16" t="s">
-        <v>233</v>
-      </c>
-      <c r="E61" s="16" t="s">
-        <v>234</v>
-      </c>
-      <c r="F61" s="16"/>
-      <c r="G61" s="16"/>
-      <c r="H61" s="16"/>
-      <c r="I61" s="16"/>
-      <c r="J61" s="16"/>
-      <c r="K61" s="16"/>
-      <c r="L61" s="16"/>
-      <c r="M61" s="16"/>
-      <c r="N61" s="16"/>
-      <c r="O61" s="16"/>
-      <c r="P61" s="16"/>
-      <c r="Q61" s="16"/>
-      <c r="R61" s="16"/>
-      <c r="S61" s="16"/>
-      <c r="T61" s="16"/>
-      <c r="U61" s="16"/>
-      <c r="V61" s="16"/>
-      <c r="W61" s="16"/>
-      <c r="X61" s="16"/>
-      <c r="Y61" s="16"/>
-    </row>
-    <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="14" t="s">
-        <v>235</v>
-      </c>
-      <c r="B62" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C62" s="16" t="s">
-        <v>236</v>
-      </c>
-      <c r="D62" s="16" t="s">
-        <v>237</v>
-      </c>
-      <c r="E62" s="16" t="s">
-        <v>238</v>
-      </c>
-      <c r="F62" s="16"/>
-      <c r="G62" s="16"/>
-      <c r="H62" s="16"/>
-      <c r="I62" s="16"/>
-      <c r="J62" s="16"/>
-      <c r="K62" s="16"/>
-      <c r="L62" s="16"/>
-      <c r="M62" s="16"/>
-      <c r="N62" s="16"/>
-      <c r="O62" s="16"/>
-      <c r="P62" s="16"/>
-      <c r="Q62" s="16"/>
-      <c r="R62" s="16"/>
-      <c r="S62" s="16"/>
-      <c r="T62" s="16"/>
-      <c r="U62" s="16"/>
-      <c r="V62" s="16"/>
-      <c r="W62" s="16"/>
-      <c r="X62" s="16"/>
-      <c r="Y62" s="16"/>
-    </row>
-    <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="B63" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C63" s="16" t="s">
-        <v>240</v>
-      </c>
-      <c r="D63" s="16" t="s">
-        <v>241</v>
-      </c>
-      <c r="E63" s="16" t="s">
-        <v>242</v>
-      </c>
-      <c r="F63" s="16"/>
-      <c r="G63" s="16"/>
-      <c r="H63" s="16"/>
-      <c r="I63" s="16"/>
-      <c r="J63" s="16"/>
-      <c r="K63" s="16"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="16"/>
-      <c r="N63" s="16"/>
-      <c r="O63" s="16"/>
-      <c r="P63" s="16"/>
-      <c r="Q63" s="16"/>
-      <c r="R63" s="16"/>
-      <c r="S63" s="16"/>
-      <c r="T63" s="16"/>
-      <c r="U63" s="16"/>
-      <c r="V63" s="16"/>
-      <c r="W63" s="16"/>
-      <c r="X63" s="16"/>
-      <c r="Y63" s="16"/>
-    </row>
-    <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="14" t="s">
-        <v>243</v>
-      </c>
-      <c r="B64" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C64" s="16" t="s">
-        <v>244</v>
-      </c>
-      <c r="D64" s="16" t="s">
-        <v>245</v>
-      </c>
-      <c r="E64" s="16" t="s">
-        <v>246</v>
-      </c>
-      <c r="F64" s="16"/>
-      <c r="G64" s="16"/>
-      <c r="H64" s="16"/>
-      <c r="I64" s="16"/>
-      <c r="J64" s="16"/>
-      <c r="K64" s="16"/>
-      <c r="L64" s="16"/>
-      <c r="M64" s="16"/>
-      <c r="N64" s="16"/>
-      <c r="O64" s="16"/>
-      <c r="P64" s="16"/>
-      <c r="Q64" s="16"/>
-      <c r="R64" s="16"/>
-      <c r="S64" s="16"/>
-      <c r="T64" s="16"/>
-      <c r="U64" s="16"/>
-      <c r="V64" s="16"/>
-      <c r="W64" s="16"/>
-      <c r="X64" s="16"/>
-      <c r="Y64" s="16"/>
-    </row>
-    <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="14" t="s">
-        <v>247</v>
-      </c>
-      <c r="B65" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C65" s="16" t="s">
-        <v>248</v>
-      </c>
-      <c r="D65" s="16" t="s">
-        <v>249</v>
-      </c>
-      <c r="E65" s="16" t="s">
-        <v>250</v>
-      </c>
-      <c r="F65" s="16"/>
-      <c r="G65" s="16"/>
-      <c r="H65" s="16"/>
-      <c r="I65" s="16"/>
-      <c r="J65" s="16"/>
-      <c r="K65" s="16"/>
-      <c r="L65" s="16"/>
-      <c r="M65" s="16"/>
-      <c r="N65" s="16"/>
-      <c r="O65" s="16"/>
-      <c r="P65" s="16"/>
-      <c r="Q65" s="16"/>
-      <c r="R65" s="16"/>
-      <c r="S65" s="16"/>
-      <c r="T65" s="16"/>
-      <c r="U65" s="16"/>
-      <c r="V65" s="16"/>
-      <c r="W65" s="16"/>
-      <c r="X65" s="16"/>
-      <c r="Y65" s="16"/>
-    </row>
-    <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="14" t="s">
-        <v>251</v>
-      </c>
-      <c r="B66" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C66" s="16" t="s">
-        <v>252</v>
-      </c>
-      <c r="D66" s="16" t="s">
-        <v>253</v>
-      </c>
-      <c r="E66" s="16" t="s">
-        <v>254</v>
-      </c>
-      <c r="F66" s="16"/>
-      <c r="G66" s="16"/>
-      <c r="H66" s="16"/>
-      <c r="I66" s="16"/>
-      <c r="J66" s="16"/>
-      <c r="K66" s="16"/>
-      <c r="L66" s="16"/>
-      <c r="M66" s="16"/>
-      <c r="N66" s="16"/>
-      <c r="O66" s="16"/>
-      <c r="P66" s="16"/>
-      <c r="Q66" s="16"/>
-      <c r="R66" s="16"/>
-      <c r="S66" s="16"/>
-      <c r="T66" s="16"/>
-      <c r="U66" s="16"/>
-      <c r="V66" s="16"/>
-      <c r="W66" s="16"/>
-      <c r="X66" s="16"/>
-      <c r="Y66" s="16"/>
-    </row>
-    <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="14" t="s">
-        <v>255</v>
-      </c>
-      <c r="B67" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C67" s="16" t="s">
-        <v>256</v>
-      </c>
-      <c r="D67" s="16" t="s">
-        <v>257</v>
-      </c>
-      <c r="E67" s="16" t="s">
-        <v>258</v>
-      </c>
-      <c r="F67" s="16"/>
-      <c r="G67" s="16"/>
-      <c r="H67" s="16"/>
-      <c r="I67" s="16"/>
-      <c r="J67" s="16"/>
-      <c r="K67" s="16"/>
-      <c r="L67" s="16"/>
-      <c r="M67" s="16"/>
-      <c r="N67" s="16"/>
-      <c r="O67" s="16"/>
-      <c r="P67" s="16"/>
-      <c r="Q67" s="16"/>
-      <c r="R67" s="16"/>
-      <c r="S67" s="16"/>
-      <c r="T67" s="16"/>
-      <c r="U67" s="16"/>
-      <c r="V67" s="16"/>
-      <c r="W67" s="16"/>
-      <c r="X67" s="16"/>
-      <c r="Y67" s="16"/>
-    </row>
-    <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="14" t="s">
-        <v>259</v>
-      </c>
-      <c r="B68" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C68" s="16" t="s">
-        <v>260</v>
-      </c>
-      <c r="D68" s="16" t="s">
-        <v>261</v>
-      </c>
-      <c r="E68" s="16" t="s">
-        <v>262</v>
-      </c>
-      <c r="F68" s="16"/>
-      <c r="G68" s="16"/>
-      <c r="H68" s="16"/>
-      <c r="I68" s="16"/>
-      <c r="J68" s="16"/>
-      <c r="K68" s="16"/>
-      <c r="L68" s="16"/>
-      <c r="M68" s="16"/>
-      <c r="N68" s="16"/>
-      <c r="O68" s="16"/>
-      <c r="P68" s="16"/>
-      <c r="Q68" s="16"/>
-      <c r="R68" s="16"/>
-      <c r="S68" s="16"/>
-      <c r="T68" s="16"/>
-      <c r="U68" s="16"/>
-      <c r="V68" s="16"/>
-      <c r="W68" s="16"/>
-      <c r="X68" s="16"/>
-      <c r="Y68" s="16"/>
-    </row>
-    <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="14" t="s">
-        <v>263</v>
-      </c>
-      <c r="B69" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C69" s="16" t="s">
-        <v>264</v>
-      </c>
-      <c r="D69" s="16" t="s">
-        <v>265</v>
-      </c>
-      <c r="E69" s="16" t="s">
-        <v>266</v>
-      </c>
-      <c r="F69" s="16"/>
-      <c r="G69" s="16"/>
-      <c r="H69" s="16"/>
-      <c r="I69" s="16"/>
-      <c r="J69" s="16"/>
-      <c r="K69" s="16"/>
-      <c r="L69" s="16"/>
-      <c r="M69" s="16"/>
-      <c r="N69" s="16"/>
-      <c r="O69" s="16"/>
-      <c r="P69" s="16"/>
-      <c r="Q69" s="16"/>
-      <c r="R69" s="16"/>
-      <c r="S69" s="16"/>
-      <c r="T69" s="16"/>
-      <c r="U69" s="16"/>
-      <c r="V69" s="16"/>
-      <c r="W69" s="16"/>
-      <c r="X69" s="16"/>
-      <c r="Y69" s="16"/>
-    </row>
-    <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="14" t="s">
-        <v>267</v>
-      </c>
-      <c r="B70" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="C70" s="16" t="s">
-        <v>268</v>
-      </c>
-      <c r="D70" s="16" t="s">
-        <v>269</v>
-      </c>
-      <c r="E70" s="16" t="s">
-        <v>270</v>
-      </c>
-      <c r="F70" s="16"/>
-      <c r="G70" s="16"/>
-      <c r="H70" s="16"/>
-      <c r="I70" s="16"/>
-      <c r="J70" s="16"/>
-      <c r="K70" s="16"/>
-      <c r="L70" s="16"/>
-      <c r="M70" s="16"/>
-      <c r="N70" s="16"/>
-      <c r="O70" s="16"/>
-      <c r="P70" s="16"/>
-      <c r="Q70" s="16"/>
-      <c r="R70" s="16"/>
-      <c r="S70" s="16"/>
-      <c r="T70" s="16"/>
-      <c r="U70" s="16"/>
-      <c r="V70" s="16"/>
-      <c r="W70" s="16"/>
-      <c r="X70" s="16"/>
-      <c r="Y70" s="16"/>
-    </row>
-    <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="17" t="s">
-        <v>271</v>
-      </c>
-      <c r="B71" s="18">
-        <v>0.0</v>
-      </c>
-      <c r="C71" s="19" t="s">
-        <v>272</v>
-      </c>
-      <c r="D71" s="19" t="s">
-        <v>273</v>
-      </c>
-      <c r="E71" s="19" t="s">
-        <v>274</v>
-      </c>
-      <c r="F71" s="19"/>
-      <c r="G71" s="19"/>
-      <c r="H71" s="19"/>
-      <c r="I71" s="19"/>
-      <c r="J71" s="19"/>
-      <c r="K71" s="19"/>
-      <c r="L71" s="19"/>
-      <c r="M71" s="19"/>
-      <c r="N71" s="19"/>
-      <c r="O71" s="19"/>
-      <c r="P71" s="19"/>
-      <c r="Q71" s="19"/>
-      <c r="R71" s="19"/>
-      <c r="S71" s="19"/>
-      <c r="T71" s="19"/>
-      <c r="U71" s="19"/>
-      <c r="V71" s="19"/>
-      <c r="W71" s="19"/>
-      <c r="X71" s="19"/>
-      <c r="Y71" s="19"/>
-    </row>
-    <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="20" t="s">
-        <v>275</v>
-      </c>
-      <c r="B72" s="21">
-        <v>0.0</v>
-      </c>
-      <c r="C72" s="21" t="s">
-        <v>276</v>
-      </c>
-      <c r="D72" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="E72" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="F72" s="21"/>
-      <c r="G72" s="21"/>
-      <c r="H72" s="21"/>
-      <c r="I72" s="21"/>
-      <c r="J72" s="21"/>
-      <c r="K72" s="21"/>
-      <c r="L72" s="21"/>
-      <c r="M72" s="21"/>
-      <c r="N72" s="21"/>
-      <c r="O72" s="21"/>
-      <c r="P72" s="21"/>
-      <c r="Q72" s="21"/>
-      <c r="R72" s="21"/>
-      <c r="S72" s="21"/>
-      <c r="T72" s="21"/>
-      <c r="U72" s="21"/>
-      <c r="V72" s="21"/>
-      <c r="W72" s="21"/>
-      <c r="X72" s="21"/>
-      <c r="Y72" s="21"/>
-    </row>
-    <row r="73" ht="15.0" customHeight="1">
-      <c r="A73" s="20" t="s">
-        <v>277</v>
-      </c>
-      <c r="B73" s="21">
-        <v>0.0</v>
-      </c>
-      <c r="C73" s="21" t="s">
-        <v>278</v>
-      </c>
-      <c r="D73" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="E73" s="21" t="s">
-        <v>280</v>
-      </c>
-      <c r="F73" s="21"/>
-      <c r="G73" s="21"/>
-      <c r="H73" s="21"/>
-      <c r="I73" s="21"/>
-      <c r="J73" s="21"/>
-      <c r="K73" s="21"/>
-      <c r="L73" s="21"/>
-      <c r="M73" s="21"/>
-      <c r="N73" s="21"/>
-      <c r="O73" s="21"/>
-      <c r="P73" s="21"/>
-      <c r="Q73" s="21"/>
-      <c r="R73" s="21"/>
-      <c r="S73" s="21"/>
-      <c r="T73" s="21"/>
-      <c r="U73" s="21"/>
-      <c r="V73" s="21"/>
-      <c r="W73" s="21"/>
-      <c r="X73" s="21"/>
-      <c r="Y73" s="21"/>
-    </row>
-    <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="20" t="s">
-        <v>281</v>
-      </c>
-      <c r="B74" s="21">
-        <v>0.0</v>
-      </c>
-      <c r="C74" s="21" t="s">
-        <v>282</v>
-      </c>
-      <c r="D74" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="E74" s="21" t="s">
-        <v>180</v>
-      </c>
-      <c r="F74" s="21"/>
-      <c r="G74" s="21"/>
-      <c r="H74" s="21"/>
-      <c r="I74" s="21"/>
-      <c r="J74" s="21"/>
-      <c r="K74" s="21"/>
-      <c r="L74" s="21"/>
-      <c r="M74" s="21"/>
-      <c r="N74" s="21"/>
-      <c r="O74" s="21"/>
-      <c r="P74" s="21"/>
-      <c r="Q74" s="21"/>
-      <c r="R74" s="21"/>
-      <c r="S74" s="21"/>
-      <c r="T74" s="21"/>
-      <c r="U74" s="21"/>
-      <c r="V74" s="21"/>
-      <c r="W74" s="21"/>
-      <c r="X74" s="21"/>
-      <c r="Y74" s="21"/>
-    </row>
-    <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="20" t="s">
-        <v>283</v>
-      </c>
-      <c r="B75" s="21">
-        <v>0.0</v>
-      </c>
-      <c r="C75" s="21" t="s">
-        <v>284</v>
-      </c>
-      <c r="D75" s="21" t="s">
-        <v>285</v>
-      </c>
-      <c r="E75" s="21" t="s">
-        <v>286</v>
-      </c>
-      <c r="F75" s="21"/>
-      <c r="G75" s="21"/>
-      <c r="H75" s="21"/>
-      <c r="I75" s="21"/>
-      <c r="J75" s="21"/>
-      <c r="K75" s="21"/>
-      <c r="L75" s="21"/>
-      <c r="M75" s="21"/>
-      <c r="N75" s="21"/>
-      <c r="O75" s="21"/>
-      <c r="P75" s="21"/>
-      <c r="Q75" s="21"/>
-      <c r="R75" s="21"/>
-      <c r="S75" s="21"/>
-      <c r="T75" s="21"/>
-      <c r="U75" s="21"/>
-      <c r="V75" s="21"/>
-      <c r="W75" s="21"/>
-      <c r="X75" s="21"/>
-      <c r="Y75" s="21"/>
-    </row>
-    <row r="76" ht="15.0" customHeight="1">
-      <c r="A76" s="20" t="s">
-        <v>287</v>
-      </c>
-      <c r="B76" s="21">
-        <v>0.0</v>
-      </c>
-      <c r="C76" s="21" t="s">
-        <v>288</v>
-      </c>
-      <c r="D76" s="21" t="s">
-        <v>289</v>
-      </c>
-      <c r="E76" s="21" t="s">
-        <v>290</v>
-      </c>
-      <c r="F76" s="21"/>
-      <c r="G76" s="21"/>
-      <c r="H76" s="21"/>
-      <c r="I76" s="21"/>
-      <c r="J76" s="21"/>
-      <c r="K76" s="21"/>
-      <c r="L76" s="21"/>
-      <c r="M76" s="21"/>
-      <c r="N76" s="21"/>
-      <c r="O76" s="21"/>
-      <c r="P76" s="21"/>
-      <c r="Q76" s="21"/>
-      <c r="R76" s="21"/>
-      <c r="S76" s="21"/>
-      <c r="T76" s="21"/>
-      <c r="U76" s="21"/>
-      <c r="V76" s="21"/>
-      <c r="W76" s="21"/>
-      <c r="X76" s="21"/>
-      <c r="Y76" s="21"/>
-    </row>
-    <row r="77" ht="15.0" customHeight="1">
-      <c r="A77" s="20" t="s">
-        <v>291</v>
-      </c>
-      <c r="B77" s="21">
-        <v>0.0</v>
-      </c>
-      <c r="C77" s="21" t="s">
-        <v>292</v>
-      </c>
-      <c r="D77" s="21" t="s">
-        <v>293</v>
-      </c>
-      <c r="E77" s="21" t="s">
-        <v>294</v>
-      </c>
-      <c r="F77" s="21"/>
-      <c r="G77" s="21"/>
-      <c r="H77" s="21"/>
-      <c r="I77" s="21"/>
-      <c r="J77" s="21"/>
-      <c r="K77" s="21"/>
-      <c r="L77" s="21"/>
-      <c r="M77" s="21"/>
-      <c r="N77" s="21"/>
-      <c r="O77" s="21"/>
-      <c r="P77" s="21"/>
-      <c r="Q77" s="21"/>
-      <c r="R77" s="21"/>
-      <c r="S77" s="21"/>
-      <c r="T77" s="21"/>
-      <c r="U77" s="21"/>
-      <c r="V77" s="21"/>
-      <c r="W77" s="21"/>
-      <c r="X77" s="21"/>
-      <c r="Y77" s="21"/>
-    </row>
-    <row r="78" ht="15.0" customHeight="1">
-      <c r="A78" s="20" t="s">
-        <v>295</v>
-      </c>
-      <c r="B78" s="21">
-        <v>0.0</v>
-      </c>
-      <c r="C78" s="21" t="s">
-        <v>296</v>
-      </c>
-      <c r="D78" s="21" t="s">
-        <v>297</v>
-      </c>
-      <c r="E78" s="21" t="s">
-        <v>298</v>
-      </c>
-      <c r="F78" s="21"/>
-      <c r="G78" s="21"/>
-      <c r="H78" s="21"/>
-      <c r="I78" s="21"/>
-      <c r="J78" s="21"/>
-      <c r="K78" s="21"/>
-      <c r="L78" s="21"/>
-      <c r="M78" s="21"/>
-      <c r="N78" s="21"/>
-      <c r="O78" s="21"/>
-      <c r="P78" s="21"/>
-      <c r="Q78" s="21"/>
-      <c r="R78" s="21"/>
-      <c r="S78" s="21"/>
-      <c r="T78" s="21"/>
-      <c r="U78" s="21"/>
-      <c r="V78" s="21"/>
-      <c r="W78" s="21"/>
-      <c r="X78" s="21"/>
-      <c r="Y78" s="21"/>
-    </row>
-    <row r="79" ht="15.0" customHeight="1">
-      <c r="A79" s="22" t="s">
-        <v>299</v>
-      </c>
-      <c r="B79" s="23">
-        <v>0.0</v>
-      </c>
-      <c r="C79" s="24" t="s">
-        <v>300</v>
-      </c>
-      <c r="D79" s="24" t="s">
-        <v>211</v>
-      </c>
-      <c r="E79" s="24" t="s">
-        <v>212</v>
-      </c>
-      <c r="F79" s="24"/>
-      <c r="G79" s="24"/>
-      <c r="H79" s="24"/>
-      <c r="I79" s="24"/>
-      <c r="J79" s="24"/>
-      <c r="K79" s="24"/>
-      <c r="L79" s="24"/>
-      <c r="M79" s="24"/>
-      <c r="N79" s="24"/>
-      <c r="O79" s="24"/>
-      <c r="P79" s="24"/>
-      <c r="Q79" s="24"/>
-      <c r="R79" s="24"/>
-      <c r="S79" s="24"/>
-      <c r="T79" s="24"/>
-      <c r="U79" s="24"/>
-      <c r="V79" s="24"/>
-      <c r="W79" s="24"/>
-      <c r="X79" s="24"/>
-      <c r="Y79" s="24"/>
-    </row>
-    <row r="80" ht="15.0" customHeight="1">
-      <c r="A80" s="25" t="s">
-        <v>301</v>
-      </c>
-      <c r="B80" s="26">
-        <v>0.0</v>
-      </c>
-      <c r="C80" s="27" t="s">
-        <v>302</v>
-      </c>
-      <c r="D80" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="E80" s="27" t="s">
-        <v>144</v>
-      </c>
-      <c r="F80" s="27"/>
-      <c r="G80" s="27"/>
-      <c r="H80" s="27"/>
-      <c r="I80" s="27"/>
-      <c r="J80" s="27"/>
-      <c r="K80" s="27"/>
-      <c r="L80" s="27"/>
-      <c r="M80" s="27"/>
-      <c r="N80" s="27"/>
-      <c r="O80" s="27"/>
-      <c r="P80" s="27"/>
-      <c r="Q80" s="27"/>
-      <c r="R80" s="27"/>
-      <c r="S80" s="27"/>
-      <c r="T80" s="27"/>
-      <c r="U80" s="27"/>
-      <c r="V80" s="27"/>
-      <c r="W80" s="27"/>
-      <c r="X80" s="27"/>
-      <c r="Y80" s="27"/>
-    </row>
-    <row r="81" ht="15.0" customHeight="1">
-      <c r="A81" s="1"/>
-      <c r="B81" s="1"/>
-      <c r="C81" s="1"/>
-      <c r="D81" s="1"/>
-      <c r="E81" s="1"/>
-      <c r="F81" s="1"/>
-      <c r="G81" s="1"/>
-      <c r="H81" s="1"/>
-      <c r="I81" s="1"/>
-      <c r="J81" s="1"/>
-      <c r="K81" s="1"/>
-      <c r="L81" s="1"/>
-      <c r="M81" s="1"/>
-      <c r="N81" s="1"/>
-      <c r="O81" s="1"/>
-      <c r="P81" s="1"/>
-      <c r="Q81" s="1"/>
-      <c r="R81" s="1"/>
-      <c r="S81" s="1"/>
-      <c r="T81" s="1"/>
-      <c r="U81" s="1"/>
-      <c r="V81" s="1"/>
-      <c r="W81" s="1"/>
-      <c r="X81" s="1"/>
-      <c r="Y81" s="1"/>
-    </row>
-    <row r="82" ht="15.0" customHeight="1">
-      <c r="A82" s="1"/>
-      <c r="B82" s="1"/>
-      <c r="C82" s="1"/>
-      <c r="D82" s="1"/>
-      <c r="E82" s="1"/>
-      <c r="F82" s="1"/>
-      <c r="G82" s="1"/>
-      <c r="H82" s="1"/>
-      <c r="I82" s="1"/>
-      <c r="J82" s="1"/>
-      <c r="K82" s="1"/>
-      <c r="L82" s="1"/>
-      <c r="M82" s="1"/>
-      <c r="N82" s="1"/>
-      <c r="O82" s="1"/>
-      <c r="P82" s="1"/>
-      <c r="Q82" s="1"/>
-      <c r="R82" s="1"/>
-      <c r="S82" s="1"/>
-      <c r="T82" s="1"/>
-      <c r="U82" s="1"/>
-      <c r="V82" s="1"/>
-      <c r="W82" s="1"/>
-      <c r="X82" s="1"/>
-      <c r="Y82" s="1"/>
+      <c r="F82" s="31"/>
+      <c r="G82" s="31"/>
+      <c r="H82" s="31"/>
+      <c r="I82" s="31"/>
+      <c r="J82" s="31"/>
+      <c r="K82" s="31"/>
+      <c r="L82" s="31"/>
+      <c r="M82" s="31"/>
+      <c r="N82" s="31"/>
+      <c r="O82" s="31"/>
+      <c r="P82" s="31"/>
+      <c r="Q82" s="31"/>
+      <c r="R82" s="31"/>
+      <c r="S82" s="31"/>
+      <c r="T82" s="31"/>
+      <c r="U82" s="31"/>
+      <c r="V82" s="31"/>
+      <c r="W82" s="31"/>
+      <c r="X82" s="31"/>
+      <c r="Y82" s="31"/>
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="1"/>
@@ -9234,7 +9294,7 @@
       <c r="X264" s="1"/>
       <c r="Y264" s="1"/>
     </row>
-    <row r="265" ht="15.75" customHeight="1">
+    <row r="265" ht="15.0" customHeight="1">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -9261,7 +9321,7 @@
       <c r="X265" s="1"/>
       <c r="Y265" s="1"/>
     </row>
-    <row r="266" ht="15.75" customHeight="1">
+    <row r="266" ht="15.0" customHeight="1">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -9666,8 +9726,60 @@
       <c r="X280" s="1"/>
       <c r="Y280" s="1"/>
     </row>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1">
+      <c r="A281" s="1"/>
+      <c r="B281" s="1"/>
+      <c r="C281" s="1"/>
+      <c r="D281" s="1"/>
+      <c r="E281" s="1"/>
+      <c r="F281" s="1"/>
+      <c r="G281" s="1"/>
+      <c r="H281" s="1"/>
+      <c r="I281" s="1"/>
+      <c r="J281" s="1"/>
+      <c r="K281" s="1"/>
+      <c r="L281" s="1"/>
+      <c r="M281" s="1"/>
+      <c r="N281" s="1"/>
+      <c r="O281" s="1"/>
+      <c r="P281" s="1"/>
+      <c r="Q281" s="1"/>
+      <c r="R281" s="1"/>
+      <c r="S281" s="1"/>
+      <c r="T281" s="1"/>
+      <c r="U281" s="1"/>
+      <c r="V281" s="1"/>
+      <c r="W281" s="1"/>
+      <c r="X281" s="1"/>
+      <c r="Y281" s="1"/>
+    </row>
+    <row r="282" ht="15.75" customHeight="1">
+      <c r="A282" s="1"/>
+      <c r="B282" s="1"/>
+      <c r="C282" s="1"/>
+      <c r="D282" s="1"/>
+      <c r="E282" s="1"/>
+      <c r="F282" s="1"/>
+      <c r="G282" s="1"/>
+      <c r="H282" s="1"/>
+      <c r="I282" s="1"/>
+      <c r="J282" s="1"/>
+      <c r="K282" s="1"/>
+      <c r="L282" s="1"/>
+      <c r="M282" s="1"/>
+      <c r="N282" s="1"/>
+      <c r="O282" s="1"/>
+      <c r="P282" s="1"/>
+      <c r="Q282" s="1"/>
+      <c r="R282" s="1"/>
+      <c r="S282" s="1"/>
+      <c r="T282" s="1"/>
+      <c r="U282" s="1"/>
+      <c r="V282" s="1"/>
+      <c r="W282" s="1"/>
+      <c r="X282" s="1"/>
+      <c r="Y282" s="1"/>
+    </row>
     <row r="283" ht="15.75" customHeight="1"/>
     <row r="284" ht="15.75" customHeight="1"/>
     <row r="285" ht="15.75" customHeight="1"/>
@@ -10386,6 +10498,8 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
+    <row r="1002" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Templates/Tables/StringInfo/StrTable.xlsx
+++ b/Templates/Tables/StringInfo/StrTable.xlsx
@@ -148,6 +148,27 @@
     <t>Do you want to save progress?\n&lt;color=#ff0000ff&gt;&lt;size=24&gt;(When saving, previous progress cannot be recovered)&lt;/size&gt;&lt;/color&gt;</t>
   </si>
   <si>
+    <t>AGREE_P_EU_TITLE</t>
+  </si>
+  <si>
+    <t>약관 동의 팝업 EU 제목</t>
+  </si>
+  <si>
+    <t>Notice</t>
+  </si>
+  <si>
+    <t>AGREE_P_PRIVACY_TITLE</t>
+  </si>
+  <si>
+    <t>약관 동의 팝업 개인 정보 제목</t>
+  </si>
+  <si>
+    <t>개인정보 보호정책</t>
+  </si>
+  <si>
+    <t>Privacy Policy</t>
+  </si>
+  <si>
     <t>AGREE_P_SERVICES_TITLE</t>
   </si>
   <si>
@@ -160,25 +181,16 @@
     <t>Terms of Service</t>
   </si>
   <si>
-    <t>AGREE_P_PRIVACY_TITLE</t>
-  </si>
-  <si>
-    <t>약관 동의 팝업 개인 정보 제목</t>
-  </si>
-  <si>
-    <t>개인정보 보호정책</t>
-  </si>
-  <si>
-    <t>Privacy Policy</t>
-  </si>
-  <si>
-    <t>AGREE_P_EU_TITLE</t>
-  </si>
-  <si>
-    <t>약관 동의 팝업 EU 제목</t>
-  </si>
-  <si>
-    <t>Notice</t>
+    <t>AGREE_P_PRIVACY_BTN_TEXT</t>
+  </si>
+  <si>
+    <t>약관 동의 팝업 개인 정보 버튼 텍스트</t>
+  </si>
+  <si>
+    <t>AGREE_P_SERVICES_BTN_TEXT</t>
+  </si>
+  <si>
+    <t>약관 동의 팝업 서비스 버튼 텍스트</t>
   </si>
   <si>
     <t>AGREE_P_DESC_TEXT_01</t>
@@ -197,18 +209,6 @@
   </si>
   <si>
     <t>and</t>
-  </si>
-  <si>
-    <t>AGREE_P_SERVICES_BTN_TEXT</t>
-  </si>
-  <si>
-    <t>약관 동의 팝업 서비스 버튼 텍스트</t>
-  </si>
-  <si>
-    <t>AGREE_P_PRIVACY_BTN_TEXT</t>
-  </si>
-  <si>
-    <t>약관 동의 팝업 개인 정보 버튼 텍스트</t>
   </si>
   <si>
     <t>TRACKING_DP_TITLE</t>
@@ -1034,7 +1034,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="29">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1049,25 +1049,16 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="3" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="3" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -1436,174 +1427,174 @@
       <c r="E3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8"/>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="8"/>
-      <c r="S3" s="8"/>
-      <c r="T3" s="8"/>
-      <c r="U3" s="8"/>
-      <c r="V3" s="8"/>
-      <c r="W3" s="8"/>
-      <c r="X3" s="8"/>
-      <c r="Y3" s="8"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7"/>
+      <c r="S3" s="7"/>
+      <c r="T3" s="7"/>
+      <c r="U3" s="7"/>
+      <c r="V3" s="7"/>
+      <c r="W3" s="7"/>
+      <c r="X3" s="7"/>
+      <c r="Y3" s="7"/>
     </row>
     <row r="4" ht="15.0" customHeight="1">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="6">
         <v>0.0</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="8"/>
-      <c r="Q4" s="8"/>
-      <c r="R4" s="8"/>
-      <c r="S4" s="8"/>
-      <c r="T4" s="8"/>
-      <c r="U4" s="8"/>
-      <c r="V4" s="8"/>
-      <c r="W4" s="8"/>
-      <c r="X4" s="8"/>
-      <c r="Y4" s="8"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="7"/>
+      <c r="S4" s="7"/>
+      <c r="T4" s="7"/>
+      <c r="U4" s="7"/>
+      <c r="V4" s="7"/>
+      <c r="W4" s="7"/>
+      <c r="X4" s="7"/>
+      <c r="Y4" s="7"/>
     </row>
     <row r="5" ht="15.0" customHeight="1">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="6">
         <v>0.0</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8"/>
-      <c r="N5" s="8"/>
-      <c r="O5" s="8"/>
-      <c r="P5" s="8"/>
-      <c r="Q5" s="8"/>
-      <c r="R5" s="8"/>
-      <c r="S5" s="8"/>
-      <c r="T5" s="8"/>
-      <c r="U5" s="8"/>
-      <c r="V5" s="8"/>
-      <c r="W5" s="8"/>
-      <c r="X5" s="8"/>
-      <c r="Y5" s="8"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7"/>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7"/>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7"/>
     </row>
     <row r="6" ht="15.0" customHeight="1">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="6">
         <v>0.0</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="8"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="8"/>
-      <c r="U6" s="8"/>
-      <c r="V6" s="8"/>
-      <c r="W6" s="8"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="8"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7"/>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7"/>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7"/>
     </row>
     <row r="7" ht="15.0" customHeight="1">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="6">
         <v>0.0</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="8"/>
-      <c r="S7" s="8"/>
-      <c r="T7" s="8"/>
-      <c r="U7" s="8"/>
-      <c r="V7" s="8"/>
-      <c r="W7" s="8"/>
-      <c r="X7" s="8"/>
-      <c r="Y7" s="8"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="7"/>
+      <c r="U7" s="7"/>
+      <c r="V7" s="7"/>
+      <c r="W7" s="7"/>
+      <c r="X7" s="7"/>
+      <c r="Y7" s="7"/>
     </row>
     <row r="8" ht="15.0" customHeight="1">
       <c r="A8" s="5" t="s">
@@ -1618,2767 +1609,2767 @@
       <c r="D8" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="8"/>
-      <c r="R8" s="8"/>
-      <c r="S8" s="8"/>
-      <c r="T8" s="8"/>
-      <c r="U8" s="8"/>
-      <c r="V8" s="8"/>
-      <c r="W8" s="8"/>
-      <c r="X8" s="8"/>
-      <c r="Y8" s="8"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="7"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="7"/>
+      <c r="U8" s="7"/>
+      <c r="V8" s="7"/>
+      <c r="W8" s="7"/>
+      <c r="X8" s="7"/>
+      <c r="Y8" s="7"/>
     </row>
     <row r="9" ht="15.0" customHeight="1">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="6">
         <v>0.0</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="8"/>
-      <c r="S9" s="8"/>
-      <c r="T9" s="8"/>
-      <c r="U9" s="8"/>
-      <c r="V9" s="8"/>
-      <c r="W9" s="8"/>
-      <c r="X9" s="8"/>
-      <c r="Y9" s="8"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="7"/>
+      <c r="S9" s="7"/>
+      <c r="T9" s="7"/>
+      <c r="U9" s="7"/>
+      <c r="V9" s="7"/>
+      <c r="W9" s="7"/>
+      <c r="X9" s="7"/>
+      <c r="Y9" s="7"/>
     </row>
     <row r="10" ht="15.0" customHeight="1">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="6">
         <v>0.0</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="8"/>
-      <c r="P10" s="8"/>
-      <c r="Q10" s="8"/>
-      <c r="R10" s="8"/>
-      <c r="S10" s="8"/>
-      <c r="T10" s="8"/>
-      <c r="U10" s="8"/>
-      <c r="V10" s="8"/>
-      <c r="W10" s="8"/>
-      <c r="X10" s="8"/>
-      <c r="Y10" s="8"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="7"/>
+      <c r="P10" s="7"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="7"/>
+      <c r="S10" s="7"/>
+      <c r="T10" s="7"/>
+      <c r="U10" s="7"/>
+      <c r="V10" s="7"/>
+      <c r="W10" s="7"/>
+      <c r="X10" s="7"/>
+      <c r="Y10" s="7"/>
     </row>
     <row r="11" ht="15.0" customHeight="1">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="6">
         <v>0.0</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
-      <c r="N11" s="8"/>
-      <c r="O11" s="8"/>
-      <c r="P11" s="8"/>
-      <c r="Q11" s="8"/>
-      <c r="R11" s="8"/>
-      <c r="S11" s="8"/>
-      <c r="T11" s="8"/>
-      <c r="U11" s="8"/>
-      <c r="V11" s="8"/>
-      <c r="W11" s="8"/>
-      <c r="X11" s="8"/>
-      <c r="Y11" s="8"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="7"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="7"/>
+      <c r="U11" s="7"/>
+      <c r="V11" s="7"/>
+      <c r="W11" s="7"/>
+      <c r="X11" s="7"/>
+      <c r="Y11" s="7"/>
     </row>
     <row r="12" ht="15.0" customHeight="1">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="6">
         <v>0.0</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="7"/>
+      <c r="P12" s="7"/>
+      <c r="Q12" s="7"/>
+      <c r="R12" s="7"/>
+      <c r="S12" s="7"/>
+      <c r="T12" s="7"/>
+      <c r="U12" s="7"/>
+      <c r="V12" s="7"/>
+      <c r="W12" s="7"/>
+      <c r="X12" s="7"/>
+      <c r="Y12" s="7"/>
+    </row>
+    <row r="13" ht="15.0" customHeight="1">
+      <c r="A13" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="8"/>
-      <c r="Q12" s="8"/>
-      <c r="R12" s="8"/>
-      <c r="S12" s="8"/>
-      <c r="T12" s="8"/>
-      <c r="U12" s="8"/>
-      <c r="V12" s="8"/>
-      <c r="W12" s="8"/>
-      <c r="X12" s="8"/>
-      <c r="Y12" s="8"/>
-    </row>
-    <row r="13" ht="15.0" customHeight="1">
-      <c r="A13" s="9" t="s">
+      <c r="B13" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="10">
+      <c r="D13" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
+      <c r="P13" s="7"/>
+      <c r="Q13" s="7"/>
+      <c r="R13" s="7"/>
+      <c r="S13" s="7"/>
+      <c r="T13" s="7"/>
+      <c r="U13" s="7"/>
+      <c r="V13" s="7"/>
+      <c r="W13" s="7"/>
+      <c r="X13" s="7"/>
+      <c r="Y13" s="7"/>
+    </row>
+    <row r="14" ht="15.0" customHeight="1">
+      <c r="A14" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="6">
         <v>0.0</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="D13" s="8" t="s">
+      <c r="C14" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="7"/>
+      <c r="R14" s="7"/>
+      <c r="S14" s="7"/>
+      <c r="T14" s="7"/>
+      <c r="U14" s="7"/>
+      <c r="V14" s="7"/>
+      <c r="W14" s="7"/>
+      <c r="X14" s="7"/>
+      <c r="Y14" s="7"/>
+    </row>
+    <row r="15" ht="15.0" customHeight="1">
+      <c r="A15" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="8"/>
-      <c r="N13" s="8"/>
-      <c r="O13" s="8"/>
-      <c r="P13" s="8"/>
-      <c r="Q13" s="8"/>
-      <c r="R13" s="8"/>
-      <c r="S13" s="8"/>
-      <c r="T13" s="8"/>
-      <c r="U13" s="8"/>
-      <c r="V13" s="8"/>
-      <c r="W13" s="8"/>
-      <c r="X13" s="8"/>
-      <c r="Y13" s="8"/>
-    </row>
-    <row r="14" ht="15.0" customHeight="1">
-      <c r="A14" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="B14" s="10">
+      <c r="E15" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7"/>
+      <c r="R15" s="7"/>
+      <c r="S15" s="7"/>
+      <c r="T15" s="7"/>
+      <c r="U15" s="7"/>
+      <c r="V15" s="7"/>
+      <c r="W15" s="7"/>
+      <c r="X15" s="7"/>
+      <c r="Y15" s="7"/>
+    </row>
+    <row r="16" ht="15.0" customHeight="1">
+      <c r="A16" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B16" s="6">
         <v>0.0</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="D14" s="8" t="s">
+      <c r="C16" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E16" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8"/>
-      <c r="O14" s="8"/>
-      <c r="P14" s="8"/>
-      <c r="Q14" s="8"/>
-      <c r="R14" s="8"/>
-      <c r="S14" s="8"/>
-      <c r="T14" s="8"/>
-      <c r="U14" s="8"/>
-      <c r="V14" s="8"/>
-      <c r="W14" s="8"/>
-      <c r="X14" s="8"/>
-      <c r="Y14" s="8"/>
-    </row>
-    <row r="15" ht="15.0" customHeight="1">
-      <c r="A15" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="B15" s="10">
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
+      <c r="O16" s="7"/>
+      <c r="P16" s="7"/>
+      <c r="Q16" s="7"/>
+      <c r="R16" s="7"/>
+      <c r="S16" s="7"/>
+      <c r="T16" s="7"/>
+      <c r="U16" s="7"/>
+      <c r="V16" s="7"/>
+      <c r="W16" s="7"/>
+      <c r="X16" s="7"/>
+      <c r="Y16" s="7"/>
+    </row>
+    <row r="17" ht="15.0" customHeight="1">
+      <c r="A17" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" s="6">
         <v>0.0</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
-      <c r="N15" s="8"/>
-      <c r="O15" s="8"/>
-      <c r="P15" s="8"/>
-      <c r="Q15" s="8"/>
-      <c r="R15" s="8"/>
-      <c r="S15" s="8"/>
-      <c r="T15" s="8"/>
-      <c r="U15" s="8"/>
-      <c r="V15" s="8"/>
-      <c r="W15" s="8"/>
-      <c r="X15" s="8"/>
-      <c r="Y15" s="8"/>
-    </row>
-    <row r="16" ht="15.0" customHeight="1">
-      <c r="A16" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="B16" s="10">
+      <c r="C17" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="7"/>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="7"/>
+      <c r="R17" s="7"/>
+      <c r="S17" s="7"/>
+      <c r="T17" s="7"/>
+      <c r="U17" s="7"/>
+      <c r="V17" s="7"/>
+      <c r="W17" s="7"/>
+      <c r="X17" s="7"/>
+      <c r="Y17" s="7"/>
+    </row>
+    <row r="18" ht="15.0" customHeight="1">
+      <c r="A18" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" s="6">
         <v>0.0</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
-      <c r="N16" s="8"/>
-      <c r="O16" s="8"/>
-      <c r="P16" s="8"/>
-      <c r="Q16" s="8"/>
-      <c r="R16" s="8"/>
-      <c r="S16" s="8"/>
-      <c r="T16" s="8"/>
-      <c r="U16" s="8"/>
-      <c r="V16" s="8"/>
-      <c r="W16" s="8"/>
-      <c r="X16" s="8"/>
-      <c r="Y16" s="8"/>
-    </row>
-    <row r="17" ht="15.0" customHeight="1">
-      <c r="A17" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="B17" s="10">
+      <c r="C18" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="7"/>
+      <c r="O18" s="7"/>
+      <c r="P18" s="7"/>
+      <c r="Q18" s="7"/>
+      <c r="R18" s="7"/>
+      <c r="S18" s="7"/>
+      <c r="T18" s="7"/>
+      <c r="U18" s="7"/>
+      <c r="V18" s="7"/>
+      <c r="W18" s="7"/>
+      <c r="X18" s="7"/>
+      <c r="Y18" s="7"/>
+    </row>
+    <row r="19" ht="15.0" customHeight="1">
+      <c r="A19" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B19" s="6">
         <v>0.0</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
-      <c r="N17" s="8"/>
-      <c r="O17" s="8"/>
-      <c r="P17" s="8"/>
-      <c r="Q17" s="8"/>
-      <c r="R17" s="8"/>
-      <c r="S17" s="8"/>
-      <c r="T17" s="8"/>
-      <c r="U17" s="8"/>
-      <c r="V17" s="8"/>
-      <c r="W17" s="8"/>
-      <c r="X17" s="8"/>
-      <c r="Y17" s="8"/>
-    </row>
-    <row r="18" ht="15.0" customHeight="1">
-      <c r="A18" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="B18" s="10">
+      <c r="C19" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="7"/>
+      <c r="O19" s="7"/>
+      <c r="P19" s="7"/>
+      <c r="Q19" s="7"/>
+      <c r="R19" s="7"/>
+      <c r="S19" s="7"/>
+      <c r="T19" s="7"/>
+      <c r="U19" s="7"/>
+      <c r="V19" s="7"/>
+      <c r="W19" s="7"/>
+      <c r="X19" s="7"/>
+      <c r="Y19" s="7"/>
+    </row>
+    <row r="20" ht="15.0" customHeight="1">
+      <c r="A20" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="6">
         <v>0.0</v>
       </c>
-      <c r="C18" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
-      <c r="N18" s="8"/>
-      <c r="O18" s="8"/>
-      <c r="P18" s="8"/>
-      <c r="Q18" s="8"/>
-      <c r="R18" s="8"/>
-      <c r="S18" s="8"/>
-      <c r="T18" s="8"/>
-      <c r="U18" s="8"/>
-      <c r="V18" s="8"/>
-      <c r="W18" s="8"/>
-      <c r="X18" s="8"/>
-      <c r="Y18" s="8"/>
-    </row>
-    <row r="19" ht="15.0" customHeight="1">
-      <c r="A19" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="B19" s="10">
+      <c r="C20" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="7"/>
+      <c r="O20" s="7"/>
+      <c r="P20" s="7"/>
+      <c r="Q20" s="7"/>
+      <c r="R20" s="7"/>
+      <c r="S20" s="7"/>
+      <c r="T20" s="7"/>
+      <c r="U20" s="7"/>
+      <c r="V20" s="7"/>
+      <c r="W20" s="7"/>
+      <c r="X20" s="7"/>
+      <c r="Y20" s="7"/>
+    </row>
+    <row r="21" ht="15.0" customHeight="1">
+      <c r="A21" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" s="6">
         <v>0.0</v>
       </c>
-      <c r="C19" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D19" s="8" t="s">
+      <c r="C21" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="7"/>
+      <c r="O21" s="7"/>
+      <c r="P21" s="7"/>
+      <c r="Q21" s="7"/>
+      <c r="R21" s="7"/>
+      <c r="S21" s="7"/>
+      <c r="T21" s="7"/>
+      <c r="U21" s="7"/>
+      <c r="V21" s="7"/>
+      <c r="W21" s="7"/>
+      <c r="X21" s="7"/>
+      <c r="Y21" s="7"/>
+    </row>
+    <row r="22" ht="15.0" customHeight="1">
+      <c r="A22" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B22" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
+      <c r="M22" s="7"/>
+      <c r="N22" s="7"/>
+      <c r="O22" s="7"/>
+      <c r="P22" s="7"/>
+      <c r="Q22" s="7"/>
+      <c r="R22" s="7"/>
+      <c r="S22" s="7"/>
+      <c r="T22" s="7"/>
+      <c r="U22" s="7"/>
+      <c r="V22" s="7"/>
+      <c r="W22" s="7"/>
+      <c r="X22" s="7"/>
+      <c r="Y22" s="7"/>
+    </row>
+    <row r="23" ht="15.0" customHeight="1">
+      <c r="A23" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B23" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="7"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="7"/>
+      <c r="O23" s="7"/>
+      <c r="P23" s="7"/>
+      <c r="Q23" s="7"/>
+      <c r="R23" s="7"/>
+      <c r="S23" s="7"/>
+      <c r="T23" s="7"/>
+      <c r="U23" s="7"/>
+      <c r="V23" s="7"/>
+      <c r="W23" s="7"/>
+      <c r="X23" s="7"/>
+      <c r="Y23" s="7"/>
+    </row>
+    <row r="24" ht="15.0" customHeight="1">
+      <c r="A24" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B24" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
+      <c r="N24" s="11"/>
+      <c r="O24" s="11"/>
+      <c r="P24" s="11"/>
+      <c r="Q24" s="11"/>
+      <c r="R24" s="11"/>
+      <c r="S24" s="11"/>
+      <c r="T24" s="11"/>
+      <c r="U24" s="11"/>
+      <c r="V24" s="11"/>
+      <c r="W24" s="11"/>
+      <c r="X24" s="11"/>
+      <c r="Y24" s="11"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="B25" s="13">
+        <v>0.0</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+      <c r="K25" s="14"/>
+      <c r="L25" s="14"/>
+      <c r="M25" s="14"/>
+      <c r="N25" s="14"/>
+      <c r="O25" s="14"/>
+      <c r="P25" s="14"/>
+      <c r="Q25" s="14"/>
+      <c r="R25" s="14"/>
+      <c r="S25" s="14"/>
+      <c r="T25" s="14"/>
+      <c r="U25" s="14"/>
+      <c r="V25" s="14"/>
+      <c r="W25" s="14"/>
+      <c r="X25" s="14"/>
+      <c r="Y25" s="14"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="B26" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="17"/>
+      <c r="L26" s="17"/>
+      <c r="M26" s="17"/>
+      <c r="N26" s="17"/>
+      <c r="O26" s="17"/>
+      <c r="P26" s="17"/>
+      <c r="Q26" s="17"/>
+      <c r="R26" s="17"/>
+      <c r="S26" s="17"/>
+      <c r="T26" s="17"/>
+      <c r="U26" s="17"/>
+      <c r="V26" s="17"/>
+      <c r="W26" s="17"/>
+      <c r="X26" s="17"/>
+      <c r="Y26" s="17"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="B27" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="E27" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="17"/>
+      <c r="L27" s="17"/>
+      <c r="M27" s="17"/>
+      <c r="N27" s="17"/>
+      <c r="O27" s="17"/>
+      <c r="P27" s="17"/>
+      <c r="Q27" s="17"/>
+      <c r="R27" s="17"/>
+      <c r="S27" s="17"/>
+      <c r="T27" s="17"/>
+      <c r="U27" s="17"/>
+      <c r="V27" s="17"/>
+      <c r="W27" s="17"/>
+      <c r="X27" s="17"/>
+      <c r="Y27" s="17"/>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="B28" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="D28" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="17"/>
+      <c r="M28" s="17"/>
+      <c r="N28" s="17"/>
+      <c r="O28" s="17"/>
+      <c r="P28" s="17"/>
+      <c r="Q28" s="17"/>
+      <c r="R28" s="17"/>
+      <c r="S28" s="17"/>
+      <c r="T28" s="17"/>
+      <c r="U28" s="17"/>
+      <c r="V28" s="17"/>
+      <c r="W28" s="17"/>
+      <c r="X28" s="17"/>
+      <c r="Y28" s="17"/>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="B29" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="D29" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="17"/>
+      <c r="J29" s="17"/>
+      <c r="K29" s="17"/>
+      <c r="L29" s="17"/>
+      <c r="M29" s="17"/>
+      <c r="N29" s="17"/>
+      <c r="O29" s="17"/>
+      <c r="P29" s="17"/>
+      <c r="Q29" s="17"/>
+      <c r="R29" s="17"/>
+      <c r="S29" s="17"/>
+      <c r="T29" s="17"/>
+      <c r="U29" s="17"/>
+      <c r="V29" s="17"/>
+      <c r="W29" s="17"/>
+      <c r="X29" s="17"/>
+      <c r="Y29" s="17"/>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="B30" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="F30" s="17"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="17"/>
+      <c r="I30" s="17"/>
+      <c r="J30" s="17"/>
+      <c r="K30" s="17"/>
+      <c r="L30" s="17"/>
+      <c r="M30" s="17"/>
+      <c r="N30" s="17"/>
+      <c r="O30" s="17"/>
+      <c r="P30" s="17"/>
+      <c r="Q30" s="17"/>
+      <c r="R30" s="17"/>
+      <c r="S30" s="17"/>
+      <c r="T30" s="17"/>
+      <c r="U30" s="17"/>
+      <c r="V30" s="17"/>
+      <c r="W30" s="17"/>
+      <c r="X30" s="17"/>
+      <c r="Y30" s="17"/>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="B31" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="F31" s="17"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17"/>
+      <c r="J31" s="17"/>
+      <c r="K31" s="17"/>
+      <c r="L31" s="17"/>
+      <c r="M31" s="17"/>
+      <c r="N31" s="17"/>
+      <c r="O31" s="17"/>
+      <c r="P31" s="17"/>
+      <c r="Q31" s="17"/>
+      <c r="R31" s="17"/>
+      <c r="S31" s="17"/>
+      <c r="T31" s="17"/>
+      <c r="U31" s="17"/>
+      <c r="V31" s="17"/>
+      <c r="W31" s="17"/>
+      <c r="X31" s="17"/>
+      <c r="Y31" s="17"/>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="B32" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="D32" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="17"/>
+      <c r="J32" s="17"/>
+      <c r="K32" s="17"/>
+      <c r="L32" s="17"/>
+      <c r="M32" s="17"/>
+      <c r="N32" s="17"/>
+      <c r="O32" s="17"/>
+      <c r="P32" s="17"/>
+      <c r="Q32" s="17"/>
+      <c r="R32" s="17"/>
+      <c r="S32" s="17"/>
+      <c r="T32" s="17"/>
+      <c r="U32" s="17"/>
+      <c r="V32" s="17"/>
+      <c r="W32" s="17"/>
+      <c r="X32" s="17"/>
+      <c r="Y32" s="17"/>
+    </row>
+    <row r="33" ht="15.0" customHeight="1">
+      <c r="A33" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="B33" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="D33" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="17"/>
+      <c r="I33" s="17"/>
+      <c r="J33" s="17"/>
+      <c r="K33" s="17"/>
+      <c r="L33" s="17"/>
+      <c r="M33" s="17"/>
+      <c r="N33" s="17"/>
+      <c r="O33" s="17"/>
+      <c r="P33" s="17"/>
+      <c r="Q33" s="17"/>
+      <c r="R33" s="17"/>
+      <c r="S33" s="17"/>
+      <c r="T33" s="17"/>
+      <c r="U33" s="17"/>
+      <c r="V33" s="17"/>
+      <c r="W33" s="17"/>
+      <c r="X33" s="17"/>
+      <c r="Y33" s="17"/>
+    </row>
+    <row r="34" ht="15.0" customHeight="1">
+      <c r="A34" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="B34" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="D34" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="E34" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="17"/>
+      <c r="I34" s="17"/>
+      <c r="J34" s="17"/>
+      <c r="K34" s="17"/>
+      <c r="L34" s="17"/>
+      <c r="M34" s="17"/>
+      <c r="N34" s="17"/>
+      <c r="O34" s="17"/>
+      <c r="P34" s="17"/>
+      <c r="Q34" s="17"/>
+      <c r="R34" s="17"/>
+      <c r="S34" s="17"/>
+      <c r="T34" s="17"/>
+      <c r="U34" s="17"/>
+      <c r="V34" s="17"/>
+      <c r="W34" s="17"/>
+      <c r="X34" s="17"/>
+      <c r="Y34" s="17"/>
+    </row>
+    <row r="35" ht="15.0" customHeight="1">
+      <c r="A35" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="B35" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="D35" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="F35" s="17"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="17"/>
+      <c r="I35" s="17"/>
+      <c r="J35" s="17"/>
+      <c r="K35" s="17"/>
+      <c r="L35" s="17"/>
+      <c r="M35" s="17"/>
+      <c r="N35" s="17"/>
+      <c r="O35" s="17"/>
+      <c r="P35" s="17"/>
+      <c r="Q35" s="17"/>
+      <c r="R35" s="17"/>
+      <c r="S35" s="17"/>
+      <c r="T35" s="17"/>
+      <c r="U35" s="17"/>
+      <c r="V35" s="17"/>
+      <c r="W35" s="17"/>
+      <c r="X35" s="17"/>
+      <c r="Y35" s="17"/>
+    </row>
+    <row r="36" ht="15.0" customHeight="1">
+      <c r="A36" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="B36" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="D36" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="F36" s="17"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="17"/>
+      <c r="I36" s="17"/>
+      <c r="J36" s="17"/>
+      <c r="K36" s="17"/>
+      <c r="L36" s="17"/>
+      <c r="M36" s="17"/>
+      <c r="N36" s="17"/>
+      <c r="O36" s="17"/>
+      <c r="P36" s="17"/>
+      <c r="Q36" s="17"/>
+      <c r="R36" s="17"/>
+      <c r="S36" s="17"/>
+      <c r="T36" s="17"/>
+      <c r="U36" s="17"/>
+      <c r="V36" s="17"/>
+      <c r="W36" s="17"/>
+      <c r="X36" s="17"/>
+      <c r="Y36" s="17"/>
+    </row>
+    <row r="37" ht="15.0" customHeight="1">
+      <c r="A37" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="B37" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="D37" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="F37" s="17"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="17"/>
+      <c r="I37" s="17"/>
+      <c r="J37" s="17"/>
+      <c r="K37" s="17"/>
+      <c r="L37" s="17"/>
+      <c r="M37" s="17"/>
+      <c r="N37" s="17"/>
+      <c r="O37" s="17"/>
+      <c r="P37" s="17"/>
+      <c r="Q37" s="17"/>
+      <c r="R37" s="17"/>
+      <c r="S37" s="17"/>
+      <c r="T37" s="17"/>
+      <c r="U37" s="17"/>
+      <c r="V37" s="17"/>
+      <c r="W37" s="17"/>
+      <c r="X37" s="17"/>
+      <c r="Y37" s="17"/>
+    </row>
+    <row r="38" ht="15.0" customHeight="1">
+      <c r="A38" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="B38" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="D38" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="E38" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="F38" s="17"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="17"/>
+      <c r="I38" s="17"/>
+      <c r="J38" s="17"/>
+      <c r="K38" s="17"/>
+      <c r="L38" s="17"/>
+      <c r="M38" s="17"/>
+      <c r="N38" s="17"/>
+      <c r="O38" s="17"/>
+      <c r="P38" s="17"/>
+      <c r="Q38" s="17"/>
+      <c r="R38" s="17"/>
+      <c r="S38" s="17"/>
+      <c r="T38" s="17"/>
+      <c r="U38" s="17"/>
+      <c r="V38" s="17"/>
+      <c r="W38" s="17"/>
+      <c r="X38" s="17"/>
+      <c r="Y38" s="17"/>
+    </row>
+    <row r="39" ht="15.0" customHeight="1">
+      <c r="A39" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="B39" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="C39" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="D39" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="F39" s="17"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="17"/>
+      <c r="I39" s="17"/>
+      <c r="J39" s="17"/>
+      <c r="K39" s="17"/>
+      <c r="L39" s="17"/>
+      <c r="M39" s="17"/>
+      <c r="N39" s="17"/>
+      <c r="O39" s="17"/>
+      <c r="P39" s="17"/>
+      <c r="Q39" s="17"/>
+      <c r="R39" s="17"/>
+      <c r="S39" s="17"/>
+      <c r="T39" s="17"/>
+      <c r="U39" s="17"/>
+      <c r="V39" s="17"/>
+      <c r="W39" s="17"/>
+      <c r="X39" s="17"/>
+      <c r="Y39" s="17"/>
+    </row>
+    <row r="40" ht="15.0" customHeight="1">
+      <c r="A40" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="B40" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="C40" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="D40" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="E40" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="F40" s="17"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="17"/>
+      <c r="I40" s="17"/>
+      <c r="J40" s="17"/>
+      <c r="K40" s="17"/>
+      <c r="L40" s="17"/>
+      <c r="M40" s="17"/>
+      <c r="N40" s="17"/>
+      <c r="O40" s="17"/>
+      <c r="P40" s="17"/>
+      <c r="Q40" s="17"/>
+      <c r="R40" s="17"/>
+      <c r="S40" s="17"/>
+      <c r="T40" s="17"/>
+      <c r="U40" s="17"/>
+      <c r="V40" s="17"/>
+      <c r="W40" s="17"/>
+      <c r="X40" s="17"/>
+      <c r="Y40" s="17"/>
+    </row>
+    <row r="41" ht="15.0" customHeight="1">
+      <c r="A41" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="B41" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="C41" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="D41" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E41" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="F41" s="17"/>
+      <c r="G41" s="17"/>
+      <c r="H41" s="17"/>
+      <c r="I41" s="17"/>
+      <c r="J41" s="17"/>
+      <c r="K41" s="17"/>
+      <c r="L41" s="17"/>
+      <c r="M41" s="17"/>
+      <c r="N41" s="17"/>
+      <c r="O41" s="17"/>
+      <c r="P41" s="17"/>
+      <c r="Q41" s="17"/>
+      <c r="R41" s="17"/>
+      <c r="S41" s="17"/>
+      <c r="T41" s="17"/>
+      <c r="U41" s="17"/>
+      <c r="V41" s="17"/>
+      <c r="W41" s="17"/>
+      <c r="X41" s="17"/>
+      <c r="Y41" s="17"/>
+    </row>
+    <row r="42" ht="15.0" customHeight="1">
+      <c r="A42" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="B42" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="C42" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="D42" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="E42" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="F42" s="17"/>
+      <c r="G42" s="17"/>
+      <c r="H42" s="17"/>
+      <c r="I42" s="17"/>
+      <c r="J42" s="17"/>
+      <c r="K42" s="17"/>
+      <c r="L42" s="17"/>
+      <c r="M42" s="17"/>
+      <c r="N42" s="17"/>
+      <c r="O42" s="17"/>
+      <c r="P42" s="17"/>
+      <c r="Q42" s="17"/>
+      <c r="R42" s="17"/>
+      <c r="S42" s="17"/>
+      <c r="T42" s="17"/>
+      <c r="U42" s="17"/>
+      <c r="V42" s="17"/>
+      <c r="W42" s="17"/>
+      <c r="X42" s="17"/>
+      <c r="Y42" s="17"/>
+    </row>
+    <row r="43" ht="15.0" customHeight="1">
+      <c r="A43" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="B43" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="C43" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="D43" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="E43" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="F43" s="17"/>
+      <c r="G43" s="17"/>
+      <c r="H43" s="17"/>
+      <c r="I43" s="17"/>
+      <c r="J43" s="17"/>
+      <c r="K43" s="17"/>
+      <c r="L43" s="17"/>
+      <c r="M43" s="17"/>
+      <c r="N43" s="17"/>
+      <c r="O43" s="17"/>
+      <c r="P43" s="17"/>
+      <c r="Q43" s="17"/>
+      <c r="R43" s="17"/>
+      <c r="S43" s="17"/>
+      <c r="T43" s="17"/>
+      <c r="U43" s="17"/>
+      <c r="V43" s="17"/>
+      <c r="W43" s="17"/>
+      <c r="X43" s="17"/>
+      <c r="Y43" s="17"/>
+    </row>
+    <row r="44" ht="15.0" customHeight="1">
+      <c r="A44" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="B44" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="C44" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="D44" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="E44" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="F44" s="17"/>
+      <c r="G44" s="17"/>
+      <c r="H44" s="17"/>
+      <c r="I44" s="17"/>
+      <c r="J44" s="17"/>
+      <c r="K44" s="17"/>
+      <c r="L44" s="17"/>
+      <c r="M44" s="17"/>
+      <c r="N44" s="17"/>
+      <c r="O44" s="17"/>
+      <c r="P44" s="17"/>
+      <c r="Q44" s="17"/>
+      <c r="R44" s="17"/>
+      <c r="S44" s="17"/>
+      <c r="T44" s="17"/>
+      <c r="U44" s="17"/>
+      <c r="V44" s="17"/>
+      <c r="W44" s="17"/>
+      <c r="X44" s="17"/>
+      <c r="Y44" s="17"/>
+    </row>
+    <row r="45" ht="15.0" customHeight="1">
+      <c r="A45" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="B45" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="C45" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="D45" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="E45" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="F45" s="17"/>
+      <c r="G45" s="17"/>
+      <c r="H45" s="17"/>
+      <c r="I45" s="17"/>
+      <c r="J45" s="17"/>
+      <c r="K45" s="17"/>
+      <c r="L45" s="17"/>
+      <c r="M45" s="17"/>
+      <c r="N45" s="17"/>
+      <c r="O45" s="17"/>
+      <c r="P45" s="17"/>
+      <c r="Q45" s="17"/>
+      <c r="R45" s="17"/>
+      <c r="S45" s="17"/>
+      <c r="T45" s="17"/>
+      <c r="U45" s="17"/>
+      <c r="V45" s="17"/>
+      <c r="W45" s="17"/>
+      <c r="X45" s="17"/>
+      <c r="Y45" s="17"/>
+    </row>
+    <row r="46" ht="15.0" customHeight="1">
+      <c r="A46" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="B46" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="C46" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="D46" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="E46" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="F46" s="17"/>
+      <c r="G46" s="17"/>
+      <c r="H46" s="17"/>
+      <c r="I46" s="17"/>
+      <c r="J46" s="17"/>
+      <c r="K46" s="17"/>
+      <c r="L46" s="17"/>
+      <c r="M46" s="17"/>
+      <c r="N46" s="17"/>
+      <c r="O46" s="17"/>
+      <c r="P46" s="17"/>
+      <c r="Q46" s="17"/>
+      <c r="R46" s="17"/>
+      <c r="S46" s="17"/>
+      <c r="T46" s="17"/>
+      <c r="U46" s="17"/>
+      <c r="V46" s="17"/>
+      <c r="W46" s="17"/>
+      <c r="X46" s="17"/>
+      <c r="Y46" s="17"/>
+    </row>
+    <row r="47" ht="15.0" customHeight="1">
+      <c r="A47" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="B47" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="C47" s="17" t="s">
+        <v>178</v>
+      </c>
+      <c r="D47" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="E47" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="F47" s="17"/>
+      <c r="G47" s="17"/>
+      <c r="H47" s="17"/>
+      <c r="I47" s="17"/>
+      <c r="J47" s="17"/>
+      <c r="K47" s="17"/>
+      <c r="L47" s="17"/>
+      <c r="M47" s="17"/>
+      <c r="N47" s="17"/>
+      <c r="O47" s="17"/>
+      <c r="P47" s="17"/>
+      <c r="Q47" s="17"/>
+      <c r="R47" s="17"/>
+      <c r="S47" s="17"/>
+      <c r="T47" s="17"/>
+      <c r="U47" s="17"/>
+      <c r="V47" s="17"/>
+      <c r="W47" s="17"/>
+      <c r="X47" s="17"/>
+      <c r="Y47" s="17"/>
+    </row>
+    <row r="48" ht="15.0" customHeight="1">
+      <c r="A48" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="B48" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="C48" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="D48" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="E48" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="F48" s="17"/>
+      <c r="G48" s="17"/>
+      <c r="H48" s="17"/>
+      <c r="I48" s="17"/>
+      <c r="J48" s="17"/>
+      <c r="K48" s="17"/>
+      <c r="L48" s="17"/>
+      <c r="M48" s="17"/>
+      <c r="N48" s="17"/>
+      <c r="O48" s="17"/>
+      <c r="P48" s="17"/>
+      <c r="Q48" s="17"/>
+      <c r="R48" s="17"/>
+      <c r="S48" s="17"/>
+      <c r="T48" s="17"/>
+      <c r="U48" s="17"/>
+      <c r="V48" s="17"/>
+      <c r="W48" s="17"/>
+      <c r="X48" s="17"/>
+      <c r="Y48" s="17"/>
+    </row>
+    <row r="49" ht="15.0" customHeight="1">
+      <c r="A49" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="B49" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="C49" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="D49" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="E49" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="F49" s="17"/>
+      <c r="G49" s="17"/>
+      <c r="H49" s="17"/>
+      <c r="I49" s="17"/>
+      <c r="J49" s="17"/>
+      <c r="K49" s="17"/>
+      <c r="L49" s="17"/>
+      <c r="M49" s="17"/>
+      <c r="N49" s="17"/>
+      <c r="O49" s="17"/>
+      <c r="P49" s="17"/>
+      <c r="Q49" s="17"/>
+      <c r="R49" s="17"/>
+      <c r="S49" s="17"/>
+      <c r="T49" s="17"/>
+      <c r="U49" s="17"/>
+      <c r="V49" s="17"/>
+      <c r="W49" s="17"/>
+      <c r="X49" s="17"/>
+      <c r="Y49" s="17"/>
+    </row>
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="A50" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="B50" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="C50" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="D50" s="17" t="s">
+        <v>191</v>
+      </c>
+      <c r="E50" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="F50" s="17"/>
+      <c r="G50" s="17"/>
+      <c r="H50" s="17"/>
+      <c r="I50" s="17"/>
+      <c r="J50" s="17"/>
+      <c r="K50" s="17"/>
+      <c r="L50" s="17"/>
+      <c r="M50" s="17"/>
+      <c r="N50" s="17"/>
+      <c r="O50" s="17"/>
+      <c r="P50" s="17"/>
+      <c r="Q50" s="17"/>
+      <c r="R50" s="17"/>
+      <c r="S50" s="17"/>
+      <c r="T50" s="17"/>
+      <c r="U50" s="17"/>
+      <c r="V50" s="17"/>
+      <c r="W50" s="17"/>
+      <c r="X50" s="17"/>
+      <c r="Y50" s="17"/>
+    </row>
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="A51" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="B51" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="C51" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="D51" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="E51" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="F51" s="17"/>
+      <c r="G51" s="17"/>
+      <c r="H51" s="17"/>
+      <c r="I51" s="17"/>
+      <c r="J51" s="17"/>
+      <c r="K51" s="17"/>
+      <c r="L51" s="17"/>
+      <c r="M51" s="17"/>
+      <c r="N51" s="17"/>
+      <c r="O51" s="17"/>
+      <c r="P51" s="17"/>
+      <c r="Q51" s="17"/>
+      <c r="R51" s="17"/>
+      <c r="S51" s="17"/>
+      <c r="T51" s="17"/>
+      <c r="U51" s="17"/>
+      <c r="V51" s="17"/>
+      <c r="W51" s="17"/>
+      <c r="X51" s="17"/>
+      <c r="Y51" s="17"/>
+    </row>
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="A52" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="B52" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="C52" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="D52" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="E52" s="17" t="s">
+        <v>200</v>
+      </c>
+      <c r="F52" s="17"/>
+      <c r="G52" s="17"/>
+      <c r="H52" s="17"/>
+      <c r="I52" s="17"/>
+      <c r="J52" s="17"/>
+      <c r="K52" s="17"/>
+      <c r="L52" s="17"/>
+      <c r="M52" s="17"/>
+      <c r="N52" s="17"/>
+      <c r="O52" s="17"/>
+      <c r="P52" s="17"/>
+      <c r="Q52" s="17"/>
+      <c r="R52" s="17"/>
+      <c r="S52" s="17"/>
+      <c r="T52" s="17"/>
+      <c r="U52" s="17"/>
+      <c r="V52" s="17"/>
+      <c r="W52" s="17"/>
+      <c r="X52" s="17"/>
+      <c r="Y52" s="17"/>
+    </row>
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="A53" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="B53" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="C53" s="17" t="s">
+        <v>202</v>
+      </c>
+      <c r="D53" s="17" t="s">
+        <v>203</v>
+      </c>
+      <c r="E53" s="17" t="s">
+        <v>204</v>
+      </c>
+      <c r="F53" s="17"/>
+      <c r="G53" s="17"/>
+      <c r="H53" s="17"/>
+      <c r="I53" s="17"/>
+      <c r="J53" s="17"/>
+      <c r="K53" s="17"/>
+      <c r="L53" s="17"/>
+      <c r="M53" s="17"/>
+      <c r="N53" s="17"/>
+      <c r="O53" s="17"/>
+      <c r="P53" s="17"/>
+      <c r="Q53" s="17"/>
+      <c r="R53" s="17"/>
+      <c r="S53" s="17"/>
+      <c r="T53" s="17"/>
+      <c r="U53" s="17"/>
+      <c r="V53" s="17"/>
+      <c r="W53" s="17"/>
+      <c r="X53" s="17"/>
+      <c r="Y53" s="17"/>
+    </row>
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="A54" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="B54" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="C54" s="17" t="s">
+        <v>206</v>
+      </c>
+      <c r="D54" s="17" t="s">
+        <v>207</v>
+      </c>
+      <c r="E54" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="F54" s="17"/>
+      <c r="G54" s="17"/>
+      <c r="H54" s="17"/>
+      <c r="I54" s="17"/>
+      <c r="J54" s="17"/>
+      <c r="K54" s="17"/>
+      <c r="L54" s="17"/>
+      <c r="M54" s="17"/>
+      <c r="N54" s="17"/>
+      <c r="O54" s="17"/>
+      <c r="P54" s="17"/>
+      <c r="Q54" s="17"/>
+      <c r="R54" s="17"/>
+      <c r="S54" s="17"/>
+      <c r="T54" s="17"/>
+      <c r="U54" s="17"/>
+      <c r="V54" s="17"/>
+      <c r="W54" s="17"/>
+      <c r="X54" s="17"/>
+      <c r="Y54" s="17"/>
+    </row>
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="A55" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="B55" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="C55" s="17" t="s">
+        <v>210</v>
+      </c>
+      <c r="D55" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="E55" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="F55" s="17"/>
+      <c r="G55" s="17"/>
+      <c r="H55" s="17"/>
+      <c r="I55" s="17"/>
+      <c r="J55" s="17"/>
+      <c r="K55" s="17"/>
+      <c r="L55" s="17"/>
+      <c r="M55" s="17"/>
+      <c r="N55" s="17"/>
+      <c r="O55" s="17"/>
+      <c r="P55" s="17"/>
+      <c r="Q55" s="17"/>
+      <c r="R55" s="17"/>
+      <c r="S55" s="17"/>
+      <c r="T55" s="17"/>
+      <c r="U55" s="17"/>
+      <c r="V55" s="17"/>
+      <c r="W55" s="17"/>
+      <c r="X55" s="17"/>
+      <c r="Y55" s="17"/>
+    </row>
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="A56" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="B56" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="C56" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="D56" s="17" t="s">
+        <v>215</v>
+      </c>
+      <c r="E56" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="F56" s="17"/>
+      <c r="G56" s="17"/>
+      <c r="H56" s="17"/>
+      <c r="I56" s="17"/>
+      <c r="J56" s="17"/>
+      <c r="K56" s="17"/>
+      <c r="L56" s="17"/>
+      <c r="M56" s="17"/>
+      <c r="N56" s="17"/>
+      <c r="O56" s="17"/>
+      <c r="P56" s="17"/>
+      <c r="Q56" s="17"/>
+      <c r="R56" s="17"/>
+      <c r="S56" s="17"/>
+      <c r="T56" s="17"/>
+      <c r="U56" s="17"/>
+      <c r="V56" s="17"/>
+      <c r="W56" s="17"/>
+      <c r="X56" s="17"/>
+      <c r="Y56" s="17"/>
+    </row>
+    <row r="57" ht="15.0" customHeight="1">
+      <c r="A57" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="B57" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="C57" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="D57" s="17" t="s">
+        <v>219</v>
+      </c>
+      <c r="E57" s="17" t="s">
+        <v>220</v>
+      </c>
+      <c r="F57" s="17"/>
+      <c r="G57" s="17"/>
+      <c r="H57" s="17"/>
+      <c r="I57" s="17"/>
+      <c r="J57" s="17"/>
+      <c r="K57" s="17"/>
+      <c r="L57" s="17"/>
+      <c r="M57" s="17"/>
+      <c r="N57" s="17"/>
+      <c r="O57" s="17"/>
+      <c r="P57" s="17"/>
+      <c r="Q57" s="17"/>
+      <c r="R57" s="17"/>
+      <c r="S57" s="17"/>
+      <c r="T57" s="17"/>
+      <c r="U57" s="17"/>
+      <c r="V57" s="17"/>
+      <c r="W57" s="17"/>
+      <c r="X57" s="17"/>
+      <c r="Y57" s="17"/>
+    </row>
+    <row r="58" ht="15.0" customHeight="1">
+      <c r="A58" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="B58" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="C58" s="17" t="s">
+        <v>222</v>
+      </c>
+      <c r="D58" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="E19" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="8"/>
-      <c r="N19" s="8"/>
-      <c r="O19" s="8"/>
-      <c r="P19" s="8"/>
-      <c r="Q19" s="8"/>
-      <c r="R19" s="8"/>
-      <c r="S19" s="8"/>
-      <c r="T19" s="8"/>
-      <c r="U19" s="8"/>
-      <c r="V19" s="8"/>
-      <c r="W19" s="8"/>
-      <c r="X19" s="8"/>
-      <c r="Y19" s="8"/>
-    </row>
-    <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="B20" s="10">
+      <c r="E58" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="F58" s="17"/>
+      <c r="G58" s="17"/>
+      <c r="H58" s="17"/>
+      <c r="I58" s="17"/>
+      <c r="J58" s="17"/>
+      <c r="K58" s="17"/>
+      <c r="L58" s="17"/>
+      <c r="M58" s="17"/>
+      <c r="N58" s="17"/>
+      <c r="O58" s="17"/>
+      <c r="P58" s="17"/>
+      <c r="Q58" s="17"/>
+      <c r="R58" s="17"/>
+      <c r="S58" s="17"/>
+      <c r="T58" s="17"/>
+      <c r="U58" s="17"/>
+      <c r="V58" s="17"/>
+      <c r="W58" s="17"/>
+      <c r="X58" s="17"/>
+      <c r="Y58" s="17"/>
+    </row>
+    <row r="59" ht="15.0" customHeight="1">
+      <c r="A59" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="B59" s="16">
         <v>0.0</v>
       </c>
-      <c r="C20" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8"/>
-      <c r="K20" s="8"/>
-      <c r="L20" s="8"/>
-      <c r="M20" s="8"/>
-      <c r="N20" s="8"/>
-      <c r="O20" s="8"/>
-      <c r="P20" s="8"/>
-      <c r="Q20" s="8"/>
-      <c r="R20" s="8"/>
-      <c r="S20" s="8"/>
-      <c r="T20" s="8"/>
-      <c r="U20" s="8"/>
-      <c r="V20" s="8"/>
-      <c r="W20" s="8"/>
-      <c r="X20" s="8"/>
-      <c r="Y20" s="8"/>
-    </row>
-    <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="B21" s="10">
+      <c r="C59" s="17" t="s">
+        <v>224</v>
+      </c>
+      <c r="D59" s="17" t="s">
+        <v>225</v>
+      </c>
+      <c r="E59" s="17" t="s">
+        <v>226</v>
+      </c>
+      <c r="F59" s="17"/>
+      <c r="G59" s="17"/>
+      <c r="H59" s="17"/>
+      <c r="I59" s="17"/>
+      <c r="J59" s="17"/>
+      <c r="K59" s="17"/>
+      <c r="L59" s="17"/>
+      <c r="M59" s="17"/>
+      <c r="N59" s="17"/>
+      <c r="O59" s="17"/>
+      <c r="P59" s="17"/>
+      <c r="Q59" s="17"/>
+      <c r="R59" s="17"/>
+      <c r="S59" s="17"/>
+      <c r="T59" s="17"/>
+      <c r="U59" s="17"/>
+      <c r="V59" s="17"/>
+      <c r="W59" s="17"/>
+      <c r="X59" s="17"/>
+      <c r="Y59" s="17"/>
+    </row>
+    <row r="60" ht="15.0" customHeight="1">
+      <c r="A60" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="B60" s="16">
         <v>0.0</v>
       </c>
-      <c r="C21" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8"/>
-      <c r="K21" s="8"/>
-      <c r="L21" s="8"/>
-      <c r="M21" s="8"/>
-      <c r="N21" s="8"/>
-      <c r="O21" s="8"/>
-      <c r="P21" s="8"/>
-      <c r="Q21" s="8"/>
-      <c r="R21" s="8"/>
-      <c r="S21" s="8"/>
-      <c r="T21" s="8"/>
-      <c r="U21" s="8"/>
-      <c r="V21" s="8"/>
-      <c r="W21" s="8"/>
-      <c r="X21" s="8"/>
-      <c r="Y21" s="8"/>
-    </row>
-    <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="B22" s="10">
+      <c r="C60" s="17" t="s">
+        <v>228</v>
+      </c>
+      <c r="D60" s="17" t="s">
+        <v>229</v>
+      </c>
+      <c r="E60" s="17" t="s">
+        <v>230</v>
+      </c>
+      <c r="F60" s="17"/>
+      <c r="G60" s="17"/>
+      <c r="H60" s="17"/>
+      <c r="I60" s="17"/>
+      <c r="J60" s="17"/>
+      <c r="K60" s="17"/>
+      <c r="L60" s="17"/>
+      <c r="M60" s="17"/>
+      <c r="N60" s="17"/>
+      <c r="O60" s="17"/>
+      <c r="P60" s="17"/>
+      <c r="Q60" s="17"/>
+      <c r="R60" s="17"/>
+      <c r="S60" s="17"/>
+      <c r="T60" s="17"/>
+      <c r="U60" s="17"/>
+      <c r="V60" s="17"/>
+      <c r="W60" s="17"/>
+      <c r="X60" s="17"/>
+      <c r="Y60" s="17"/>
+    </row>
+    <row r="61" ht="15.0" customHeight="1">
+      <c r="A61" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="B61" s="16">
         <v>0.0</v>
       </c>
-      <c r="C22" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8"/>
-      <c r="K22" s="8"/>
-      <c r="L22" s="8"/>
-      <c r="M22" s="8"/>
-      <c r="N22" s="8"/>
-      <c r="O22" s="8"/>
-      <c r="P22" s="8"/>
-      <c r="Q22" s="8"/>
-      <c r="R22" s="8"/>
-      <c r="S22" s="8"/>
-      <c r="T22" s="8"/>
-      <c r="U22" s="8"/>
-      <c r="V22" s="8"/>
-      <c r="W22" s="8"/>
-      <c r="X22" s="8"/>
-      <c r="Y22" s="8"/>
-    </row>
-    <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="B23" s="10">
+      <c r="C61" s="17" t="s">
+        <v>232</v>
+      </c>
+      <c r="D61" s="17" t="s">
+        <v>233</v>
+      </c>
+      <c r="E61" s="17" t="s">
+        <v>234</v>
+      </c>
+      <c r="F61" s="17"/>
+      <c r="G61" s="17"/>
+      <c r="H61" s="17"/>
+      <c r="I61" s="17"/>
+      <c r="J61" s="17"/>
+      <c r="K61" s="17"/>
+      <c r="L61" s="17"/>
+      <c r="M61" s="17"/>
+      <c r="N61" s="17"/>
+      <c r="O61" s="17"/>
+      <c r="P61" s="17"/>
+      <c r="Q61" s="17"/>
+      <c r="R61" s="17"/>
+      <c r="S61" s="17"/>
+      <c r="T61" s="17"/>
+      <c r="U61" s="17"/>
+      <c r="V61" s="17"/>
+      <c r="W61" s="17"/>
+      <c r="X61" s="17"/>
+      <c r="Y61" s="17"/>
+    </row>
+    <row r="62" ht="15.0" customHeight="1">
+      <c r="A62" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="B62" s="16">
         <v>0.0</v>
       </c>
-      <c r="C23" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
-      <c r="K23" s="8"/>
-      <c r="L23" s="8"/>
-      <c r="M23" s="8"/>
-      <c r="N23" s="8"/>
-      <c r="O23" s="8"/>
-      <c r="P23" s="8"/>
-      <c r="Q23" s="8"/>
-      <c r="R23" s="8"/>
-      <c r="S23" s="8"/>
-      <c r="T23" s="8"/>
-      <c r="U23" s="8"/>
-      <c r="V23" s="8"/>
-      <c r="W23" s="8"/>
-      <c r="X23" s="8"/>
-      <c r="Y23" s="8"/>
-    </row>
-    <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="B24" s="13">
+      <c r="C62" s="17" t="s">
+        <v>236</v>
+      </c>
+      <c r="D62" s="17" t="s">
+        <v>237</v>
+      </c>
+      <c r="E62" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="F62" s="17"/>
+      <c r="G62" s="17"/>
+      <c r="H62" s="17"/>
+      <c r="I62" s="17"/>
+      <c r="J62" s="17"/>
+      <c r="K62" s="17"/>
+      <c r="L62" s="17"/>
+      <c r="M62" s="17"/>
+      <c r="N62" s="17"/>
+      <c r="O62" s="17"/>
+      <c r="P62" s="17"/>
+      <c r="Q62" s="17"/>
+      <c r="R62" s="17"/>
+      <c r="S62" s="17"/>
+      <c r="T62" s="17"/>
+      <c r="U62" s="17"/>
+      <c r="V62" s="17"/>
+      <c r="W62" s="17"/>
+      <c r="X62" s="17"/>
+      <c r="Y62" s="17"/>
+    </row>
+    <row r="63" ht="15.0" customHeight="1">
+      <c r="A63" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="B63" s="16">
         <v>0.0</v>
       </c>
-      <c r="C24" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="E24" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="14"/>
-      <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
-      <c r="Q24" s="14"/>
-      <c r="R24" s="14"/>
-      <c r="S24" s="14"/>
-      <c r="T24" s="14"/>
-      <c r="U24" s="14"/>
-      <c r="V24" s="14"/>
-      <c r="W24" s="14"/>
-      <c r="X24" s="14"/>
-      <c r="Y24" s="14"/>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="B25" s="16">
+      <c r="C63" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="D63" s="17" t="s">
+        <v>241</v>
+      </c>
+      <c r="E63" s="17" t="s">
+        <v>242</v>
+      </c>
+      <c r="F63" s="17"/>
+      <c r="G63" s="17"/>
+      <c r="H63" s="17"/>
+      <c r="I63" s="17"/>
+      <c r="J63" s="17"/>
+      <c r="K63" s="17"/>
+      <c r="L63" s="17"/>
+      <c r="M63" s="17"/>
+      <c r="N63" s="17"/>
+      <c r="O63" s="17"/>
+      <c r="P63" s="17"/>
+      <c r="Q63" s="17"/>
+      <c r="R63" s="17"/>
+      <c r="S63" s="17"/>
+      <c r="T63" s="17"/>
+      <c r="U63" s="17"/>
+      <c r="V63" s="17"/>
+      <c r="W63" s="17"/>
+      <c r="X63" s="17"/>
+      <c r="Y63" s="17"/>
+    </row>
+    <row r="64" ht="15.0" customHeight="1">
+      <c r="A64" s="15" t="s">
+        <v>243</v>
+      </c>
+      <c r="B64" s="16">
         <v>0.0</v>
       </c>
-      <c r="C25" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="D25" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="E25" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="17"/>
-      <c r="L25" s="17"/>
-      <c r="M25" s="17"/>
-      <c r="N25" s="17"/>
-      <c r="O25" s="17"/>
-      <c r="P25" s="17"/>
-      <c r="Q25" s="17"/>
-      <c r="R25" s="17"/>
-      <c r="S25" s="17"/>
-      <c r="T25" s="17"/>
-      <c r="U25" s="17"/>
-      <c r="V25" s="17"/>
-      <c r="W25" s="17"/>
-      <c r="X25" s="17"/>
-      <c r="Y25" s="17"/>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="B26" s="19">
+      <c r="C64" s="17" t="s">
+        <v>244</v>
+      </c>
+      <c r="D64" s="17" t="s">
+        <v>245</v>
+      </c>
+      <c r="E64" s="17" t="s">
+        <v>246</v>
+      </c>
+      <c r="F64" s="17"/>
+      <c r="G64" s="17"/>
+      <c r="H64" s="17"/>
+      <c r="I64" s="17"/>
+      <c r="J64" s="17"/>
+      <c r="K64" s="17"/>
+      <c r="L64" s="17"/>
+      <c r="M64" s="17"/>
+      <c r="N64" s="17"/>
+      <c r="O64" s="17"/>
+      <c r="P64" s="17"/>
+      <c r="Q64" s="17"/>
+      <c r="R64" s="17"/>
+      <c r="S64" s="17"/>
+      <c r="T64" s="17"/>
+      <c r="U64" s="17"/>
+      <c r="V64" s="17"/>
+      <c r="W64" s="17"/>
+      <c r="X64" s="17"/>
+      <c r="Y64" s="17"/>
+    </row>
+    <row r="65" ht="15.0" customHeight="1">
+      <c r="A65" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="B65" s="16">
         <v>0.0</v>
       </c>
-      <c r="C26" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="D26" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="E26" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
-      <c r="K26" s="20"/>
-      <c r="L26" s="20"/>
-      <c r="M26" s="20"/>
-      <c r="N26" s="20"/>
-      <c r="O26" s="20"/>
-      <c r="P26" s="20"/>
-      <c r="Q26" s="20"/>
-      <c r="R26" s="20"/>
-      <c r="S26" s="20"/>
-      <c r="T26" s="20"/>
-      <c r="U26" s="20"/>
-      <c r="V26" s="20"/>
-      <c r="W26" s="20"/>
-      <c r="X26" s="20"/>
-      <c r="Y26" s="20"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="B27" s="19">
+      <c r="C65" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="D65" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="E65" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="F65" s="17"/>
+      <c r="G65" s="17"/>
+      <c r="H65" s="17"/>
+      <c r="I65" s="17"/>
+      <c r="J65" s="17"/>
+      <c r="K65" s="17"/>
+      <c r="L65" s="17"/>
+      <c r="M65" s="17"/>
+      <c r="N65" s="17"/>
+      <c r="O65" s="17"/>
+      <c r="P65" s="17"/>
+      <c r="Q65" s="17"/>
+      <c r="R65" s="17"/>
+      <c r="S65" s="17"/>
+      <c r="T65" s="17"/>
+      <c r="U65" s="17"/>
+      <c r="V65" s="17"/>
+      <c r="W65" s="17"/>
+      <c r="X65" s="17"/>
+      <c r="Y65" s="17"/>
+    </row>
+    <row r="66" ht="15.0" customHeight="1">
+      <c r="A66" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="B66" s="16">
         <v>0.0</v>
       </c>
-      <c r="C27" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="D27" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="E27" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="20"/>
-      <c r="J27" s="20"/>
-      <c r="K27" s="20"/>
-      <c r="L27" s="20"/>
-      <c r="M27" s="20"/>
-      <c r="N27" s="20"/>
-      <c r="O27" s="20"/>
-      <c r="P27" s="20"/>
-      <c r="Q27" s="20"/>
-      <c r="R27" s="20"/>
-      <c r="S27" s="20"/>
-      <c r="T27" s="20"/>
-      <c r="U27" s="20"/>
-      <c r="V27" s="20"/>
-      <c r="W27" s="20"/>
-      <c r="X27" s="20"/>
-      <c r="Y27" s="20"/>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="B28" s="19">
+      <c r="C66" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="D66" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="E66" s="17" t="s">
+        <v>254</v>
+      </c>
+      <c r="F66" s="17"/>
+      <c r="G66" s="17"/>
+      <c r="H66" s="17"/>
+      <c r="I66" s="17"/>
+      <c r="J66" s="17"/>
+      <c r="K66" s="17"/>
+      <c r="L66" s="17"/>
+      <c r="M66" s="17"/>
+      <c r="N66" s="17"/>
+      <c r="O66" s="17"/>
+      <c r="P66" s="17"/>
+      <c r="Q66" s="17"/>
+      <c r="R66" s="17"/>
+      <c r="S66" s="17"/>
+      <c r="T66" s="17"/>
+      <c r="U66" s="17"/>
+      <c r="V66" s="17"/>
+      <c r="W66" s="17"/>
+      <c r="X66" s="17"/>
+      <c r="Y66" s="17"/>
+    </row>
+    <row r="67" ht="15.0" customHeight="1">
+      <c r="A67" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="B67" s="16">
         <v>0.0</v>
       </c>
-      <c r="C28" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="D28" s="20" t="s">
-        <v>103</v>
-      </c>
-      <c r="E28" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="20"/>
-      <c r="K28" s="20"/>
-      <c r="L28" s="20"/>
-      <c r="M28" s="20"/>
-      <c r="N28" s="20"/>
-      <c r="O28" s="20"/>
-      <c r="P28" s="20"/>
-      <c r="Q28" s="20"/>
-      <c r="R28" s="20"/>
-      <c r="S28" s="20"/>
-      <c r="T28" s="20"/>
-      <c r="U28" s="20"/>
-      <c r="V28" s="20"/>
-      <c r="W28" s="20"/>
-      <c r="X28" s="20"/>
-      <c r="Y28" s="20"/>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="B29" s="19">
+      <c r="C67" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="D67" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="E67" s="17" t="s">
+        <v>258</v>
+      </c>
+      <c r="F67" s="17"/>
+      <c r="G67" s="17"/>
+      <c r="H67" s="17"/>
+      <c r="I67" s="17"/>
+      <c r="J67" s="17"/>
+      <c r="K67" s="17"/>
+      <c r="L67" s="17"/>
+      <c r="M67" s="17"/>
+      <c r="N67" s="17"/>
+      <c r="O67" s="17"/>
+      <c r="P67" s="17"/>
+      <c r="Q67" s="17"/>
+      <c r="R67" s="17"/>
+      <c r="S67" s="17"/>
+      <c r="T67" s="17"/>
+      <c r="U67" s="17"/>
+      <c r="V67" s="17"/>
+      <c r="W67" s="17"/>
+      <c r="X67" s="17"/>
+      <c r="Y67" s="17"/>
+    </row>
+    <row r="68" ht="15.0" customHeight="1">
+      <c r="A68" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="B68" s="16">
         <v>0.0</v>
       </c>
-      <c r="C29" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="D29" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="E29" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="20"/>
-      <c r="K29" s="20"/>
-      <c r="L29" s="20"/>
-      <c r="M29" s="20"/>
-      <c r="N29" s="20"/>
-      <c r="O29" s="20"/>
-      <c r="P29" s="20"/>
-      <c r="Q29" s="20"/>
-      <c r="R29" s="20"/>
-      <c r="S29" s="20"/>
-      <c r="T29" s="20"/>
-      <c r="U29" s="20"/>
-      <c r="V29" s="20"/>
-      <c r="W29" s="20"/>
-      <c r="X29" s="20"/>
-      <c r="Y29" s="20"/>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="B30" s="19">
+      <c r="C68" s="17" t="s">
+        <v>260</v>
+      </c>
+      <c r="D68" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="E68" s="17" t="s">
+        <v>262</v>
+      </c>
+      <c r="F68" s="17"/>
+      <c r="G68" s="17"/>
+      <c r="H68" s="17"/>
+      <c r="I68" s="17"/>
+      <c r="J68" s="17"/>
+      <c r="K68" s="17"/>
+      <c r="L68" s="17"/>
+      <c r="M68" s="17"/>
+      <c r="N68" s="17"/>
+      <c r="O68" s="17"/>
+      <c r="P68" s="17"/>
+      <c r="Q68" s="17"/>
+      <c r="R68" s="17"/>
+      <c r="S68" s="17"/>
+      <c r="T68" s="17"/>
+      <c r="U68" s="17"/>
+      <c r="V68" s="17"/>
+      <c r="W68" s="17"/>
+      <c r="X68" s="17"/>
+      <c r="Y68" s="17"/>
+    </row>
+    <row r="69" ht="15.0" customHeight="1">
+      <c r="A69" s="15" t="s">
+        <v>263</v>
+      </c>
+      <c r="B69" s="16">
         <v>0.0</v>
       </c>
-      <c r="C30" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="D30" s="20" t="s">
-        <v>111</v>
-      </c>
-      <c r="E30" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
-      <c r="J30" s="20"/>
-      <c r="K30" s="20"/>
-      <c r="L30" s="20"/>
-      <c r="M30" s="20"/>
-      <c r="N30" s="20"/>
-      <c r="O30" s="20"/>
-      <c r="P30" s="20"/>
-      <c r="Q30" s="20"/>
-      <c r="R30" s="20"/>
-      <c r="S30" s="20"/>
-      <c r="T30" s="20"/>
-      <c r="U30" s="20"/>
-      <c r="V30" s="20"/>
-      <c r="W30" s="20"/>
-      <c r="X30" s="20"/>
-      <c r="Y30" s="20"/>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="B31" s="19">
+      <c r="C69" s="17" t="s">
+        <v>264</v>
+      </c>
+      <c r="D69" s="17" t="s">
+        <v>265</v>
+      </c>
+      <c r="E69" s="17" t="s">
+        <v>266</v>
+      </c>
+      <c r="F69" s="17"/>
+      <c r="G69" s="17"/>
+      <c r="H69" s="17"/>
+      <c r="I69" s="17"/>
+      <c r="J69" s="17"/>
+      <c r="K69" s="17"/>
+      <c r="L69" s="17"/>
+      <c r="M69" s="17"/>
+      <c r="N69" s="17"/>
+      <c r="O69" s="17"/>
+      <c r="P69" s="17"/>
+      <c r="Q69" s="17"/>
+      <c r="R69" s="17"/>
+      <c r="S69" s="17"/>
+      <c r="T69" s="17"/>
+      <c r="U69" s="17"/>
+      <c r="V69" s="17"/>
+      <c r="W69" s="17"/>
+      <c r="X69" s="17"/>
+      <c r="Y69" s="17"/>
+    </row>
+    <row r="70" ht="15.0" customHeight="1">
+      <c r="A70" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="B70" s="16">
         <v>0.0</v>
       </c>
-      <c r="C31" s="20" t="s">
-        <v>114</v>
-      </c>
-      <c r="D31" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="E31" s="20" t="s">
-        <v>116</v>
-      </c>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
-      <c r="J31" s="20"/>
-      <c r="K31" s="20"/>
-      <c r="L31" s="20"/>
-      <c r="M31" s="20"/>
-      <c r="N31" s="20"/>
-      <c r="O31" s="20"/>
-      <c r="P31" s="20"/>
-      <c r="Q31" s="20"/>
-      <c r="R31" s="20"/>
-      <c r="S31" s="20"/>
-      <c r="T31" s="20"/>
-      <c r="U31" s="20"/>
-      <c r="V31" s="20"/>
-      <c r="W31" s="20"/>
-      <c r="X31" s="20"/>
-      <c r="Y31" s="20"/>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="18" t="s">
-        <v>117</v>
-      </c>
-      <c r="B32" s="19">
+      <c r="C70" s="17" t="s">
+        <v>268</v>
+      </c>
+      <c r="D70" s="17" t="s">
+        <v>269</v>
+      </c>
+      <c r="E70" s="17" t="s">
+        <v>270</v>
+      </c>
+      <c r="F70" s="17"/>
+      <c r="G70" s="17"/>
+      <c r="H70" s="17"/>
+      <c r="I70" s="17"/>
+      <c r="J70" s="17"/>
+      <c r="K70" s="17"/>
+      <c r="L70" s="17"/>
+      <c r="M70" s="17"/>
+      <c r="N70" s="17"/>
+      <c r="O70" s="17"/>
+      <c r="P70" s="17"/>
+      <c r="Q70" s="17"/>
+      <c r="R70" s="17"/>
+      <c r="S70" s="17"/>
+      <c r="T70" s="17"/>
+      <c r="U70" s="17"/>
+      <c r="V70" s="17"/>
+      <c r="W70" s="17"/>
+      <c r="X70" s="17"/>
+      <c r="Y70" s="17"/>
+    </row>
+    <row r="71" ht="15.0" customHeight="1">
+      <c r="A71" s="15" t="s">
+        <v>271</v>
+      </c>
+      <c r="B71" s="16">
         <v>0.0</v>
       </c>
-      <c r="C32" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="D32" s="20" t="s">
-        <v>119</v>
-      </c>
-      <c r="E32" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20"/>
-      <c r="J32" s="20"/>
-      <c r="K32" s="20"/>
-      <c r="L32" s="20"/>
-      <c r="M32" s="20"/>
-      <c r="N32" s="20"/>
-      <c r="O32" s="20"/>
-      <c r="P32" s="20"/>
-      <c r="Q32" s="20"/>
-      <c r="R32" s="20"/>
-      <c r="S32" s="20"/>
-      <c r="T32" s="20"/>
-      <c r="U32" s="20"/>
-      <c r="V32" s="20"/>
-      <c r="W32" s="20"/>
-      <c r="X32" s="20"/>
-      <c r="Y32" s="20"/>
-    </row>
-    <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="18" t="s">
-        <v>121</v>
-      </c>
-      <c r="B33" s="19">
+      <c r="C71" s="17" t="s">
+        <v>272</v>
+      </c>
+      <c r="D71" s="17" t="s">
+        <v>273</v>
+      </c>
+      <c r="E71" s="17" t="s">
+        <v>274</v>
+      </c>
+      <c r="F71" s="17"/>
+      <c r="G71" s="17"/>
+      <c r="H71" s="17"/>
+      <c r="I71" s="17"/>
+      <c r="J71" s="17"/>
+      <c r="K71" s="17"/>
+      <c r="L71" s="17"/>
+      <c r="M71" s="17"/>
+      <c r="N71" s="17"/>
+      <c r="O71" s="17"/>
+      <c r="P71" s="17"/>
+      <c r="Q71" s="17"/>
+      <c r="R71" s="17"/>
+      <c r="S71" s="17"/>
+      <c r="T71" s="17"/>
+      <c r="U71" s="17"/>
+      <c r="V71" s="17"/>
+      <c r="W71" s="17"/>
+      <c r="X71" s="17"/>
+      <c r="Y71" s="17"/>
+    </row>
+    <row r="72" ht="15.0" customHeight="1">
+      <c r="A72" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="B72" s="16">
         <v>0.0</v>
       </c>
-      <c r="C33" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="D33" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="E33" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="F33" s="20"/>
-      <c r="G33" s="20"/>
-      <c r="H33" s="20"/>
-      <c r="I33" s="20"/>
-      <c r="J33" s="20"/>
-      <c r="K33" s="20"/>
-      <c r="L33" s="20"/>
-      <c r="M33" s="20"/>
-      <c r="N33" s="20"/>
-      <c r="O33" s="20"/>
-      <c r="P33" s="20"/>
-      <c r="Q33" s="20"/>
-      <c r="R33" s="20"/>
-      <c r="S33" s="20"/>
-      <c r="T33" s="20"/>
-      <c r="U33" s="20"/>
-      <c r="V33" s="20"/>
-      <c r="W33" s="20"/>
-      <c r="X33" s="20"/>
-      <c r="Y33" s="20"/>
-    </row>
-    <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="B34" s="19">
+      <c r="C72" s="17" t="s">
+        <v>276</v>
+      </c>
+      <c r="D72" s="17" t="s">
+        <v>277</v>
+      </c>
+      <c r="E72" s="17" t="s">
+        <v>278</v>
+      </c>
+      <c r="F72" s="17"/>
+      <c r="G72" s="17"/>
+      <c r="H72" s="17"/>
+      <c r="I72" s="17"/>
+      <c r="J72" s="17"/>
+      <c r="K72" s="17"/>
+      <c r="L72" s="17"/>
+      <c r="M72" s="17"/>
+      <c r="N72" s="17"/>
+      <c r="O72" s="17"/>
+      <c r="P72" s="17"/>
+      <c r="Q72" s="17"/>
+      <c r="R72" s="17"/>
+      <c r="S72" s="17"/>
+      <c r="T72" s="17"/>
+      <c r="U72" s="17"/>
+      <c r="V72" s="17"/>
+      <c r="W72" s="17"/>
+      <c r="X72" s="17"/>
+      <c r="Y72" s="17"/>
+    </row>
+    <row r="73" ht="15.0" customHeight="1">
+      <c r="A73" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="B73" s="19">
         <v>0.0</v>
       </c>
-      <c r="C34" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="D34" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="E34" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="20"/>
-      <c r="I34" s="20"/>
-      <c r="J34" s="20"/>
-      <c r="K34" s="20"/>
-      <c r="L34" s="20"/>
-      <c r="M34" s="20"/>
-      <c r="N34" s="20"/>
-      <c r="O34" s="20"/>
-      <c r="P34" s="20"/>
-      <c r="Q34" s="20"/>
-      <c r="R34" s="20"/>
-      <c r="S34" s="20"/>
-      <c r="T34" s="20"/>
-      <c r="U34" s="20"/>
-      <c r="V34" s="20"/>
-      <c r="W34" s="20"/>
-      <c r="X34" s="20"/>
-      <c r="Y34" s="20"/>
-    </row>
-    <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="B35" s="19">
+      <c r="C73" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="D73" s="20" t="s">
+        <v>281</v>
+      </c>
+      <c r="E73" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="F73" s="20"/>
+      <c r="G73" s="20"/>
+      <c r="H73" s="20"/>
+      <c r="I73" s="20"/>
+      <c r="J73" s="20"/>
+      <c r="K73" s="20"/>
+      <c r="L73" s="20"/>
+      <c r="M73" s="20"/>
+      <c r="N73" s="20"/>
+      <c r="O73" s="20"/>
+      <c r="P73" s="20"/>
+      <c r="Q73" s="20"/>
+      <c r="R73" s="20"/>
+      <c r="S73" s="20"/>
+      <c r="T73" s="20"/>
+      <c r="U73" s="20"/>
+      <c r="V73" s="20"/>
+      <c r="W73" s="20"/>
+      <c r="X73" s="20"/>
+      <c r="Y73" s="20"/>
+    </row>
+    <row r="74" ht="15.0" customHeight="1">
+      <c r="A74" s="21" t="s">
+        <v>283</v>
+      </c>
+      <c r="B74" s="22">
         <v>0.0</v>
       </c>
-      <c r="C35" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="D35" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="E35" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
-      <c r="J35" s="20"/>
-      <c r="K35" s="20"/>
-      <c r="L35" s="20"/>
-      <c r="M35" s="20"/>
-      <c r="N35" s="20"/>
-      <c r="O35" s="20"/>
-      <c r="P35" s="20"/>
-      <c r="Q35" s="20"/>
-      <c r="R35" s="20"/>
-      <c r="S35" s="20"/>
-      <c r="T35" s="20"/>
-      <c r="U35" s="20"/>
-      <c r="V35" s="20"/>
-      <c r="W35" s="20"/>
-      <c r="X35" s="20"/>
-      <c r="Y35" s="20"/>
-    </row>
-    <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="B36" s="19">
+      <c r="C74" s="22" t="s">
+        <v>284</v>
+      </c>
+      <c r="D74" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="E74" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="F74" s="22"/>
+      <c r="G74" s="22"/>
+      <c r="H74" s="22"/>
+      <c r="I74" s="22"/>
+      <c r="J74" s="22"/>
+      <c r="K74" s="22"/>
+      <c r="L74" s="22"/>
+      <c r="M74" s="22"/>
+      <c r="N74" s="22"/>
+      <c r="O74" s="22"/>
+      <c r="P74" s="22"/>
+      <c r="Q74" s="22"/>
+      <c r="R74" s="22"/>
+      <c r="S74" s="22"/>
+      <c r="T74" s="22"/>
+      <c r="U74" s="22"/>
+      <c r="V74" s="22"/>
+      <c r="W74" s="22"/>
+      <c r="X74" s="22"/>
+      <c r="Y74" s="22"/>
+    </row>
+    <row r="75" ht="15.0" customHeight="1">
+      <c r="A75" s="21" t="s">
+        <v>285</v>
+      </c>
+      <c r="B75" s="22">
         <v>0.0</v>
       </c>
-      <c r="C36" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="D36" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="E36" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="F36" s="20"/>
-      <c r="G36" s="20"/>
-      <c r="H36" s="20"/>
-      <c r="I36" s="20"/>
-      <c r="J36" s="20"/>
-      <c r="K36" s="20"/>
-      <c r="L36" s="20"/>
-      <c r="M36" s="20"/>
-      <c r="N36" s="20"/>
-      <c r="O36" s="20"/>
-      <c r="P36" s="20"/>
-      <c r="Q36" s="20"/>
-      <c r="R36" s="20"/>
-      <c r="S36" s="20"/>
-      <c r="T36" s="20"/>
-      <c r="U36" s="20"/>
-      <c r="V36" s="20"/>
-      <c r="W36" s="20"/>
-      <c r="X36" s="20"/>
-      <c r="Y36" s="20"/>
-    </row>
-    <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="B37" s="19">
+      <c r="C75" s="22" t="s">
+        <v>286</v>
+      </c>
+      <c r="D75" s="22" t="s">
+        <v>287</v>
+      </c>
+      <c r="E75" s="22" t="s">
+        <v>288</v>
+      </c>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="22"/>
+      <c r="K75" s="22"/>
+      <c r="L75" s="22"/>
+      <c r="M75" s="22"/>
+      <c r="N75" s="22"/>
+      <c r="O75" s="22"/>
+      <c r="P75" s="22"/>
+      <c r="Q75" s="22"/>
+      <c r="R75" s="22"/>
+      <c r="S75" s="22"/>
+      <c r="T75" s="22"/>
+      <c r="U75" s="22"/>
+      <c r="V75" s="22"/>
+      <c r="W75" s="22"/>
+      <c r="X75" s="22"/>
+      <c r="Y75" s="22"/>
+    </row>
+    <row r="76" ht="15.75" customHeight="1">
+      <c r="A76" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="B76" s="22">
         <v>0.0</v>
       </c>
-      <c r="C37" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="D37" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="E37" s="20" t="s">
-        <v>140</v>
-      </c>
-      <c r="F37" s="20"/>
-      <c r="G37" s="20"/>
-      <c r="H37" s="20"/>
-      <c r="I37" s="20"/>
-      <c r="J37" s="20"/>
-      <c r="K37" s="20"/>
-      <c r="L37" s="20"/>
-      <c r="M37" s="20"/>
-      <c r="N37" s="20"/>
-      <c r="O37" s="20"/>
-      <c r="P37" s="20"/>
-      <c r="Q37" s="20"/>
-      <c r="R37" s="20"/>
-      <c r="S37" s="20"/>
-      <c r="T37" s="20"/>
-      <c r="U37" s="20"/>
-      <c r="V37" s="20"/>
-      <c r="W37" s="20"/>
-      <c r="X37" s="20"/>
-      <c r="Y37" s="20"/>
-    </row>
-    <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="B38" s="19">
+      <c r="C76" s="22" t="s">
+        <v>290</v>
+      </c>
+      <c r="D76" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="E76" s="22" t="s">
+        <v>188</v>
+      </c>
+      <c r="F76" s="22"/>
+      <c r="G76" s="22"/>
+      <c r="H76" s="22"/>
+      <c r="I76" s="22"/>
+      <c r="J76" s="22"/>
+      <c r="K76" s="22"/>
+      <c r="L76" s="22"/>
+      <c r="M76" s="22"/>
+      <c r="N76" s="22"/>
+      <c r="O76" s="22"/>
+      <c r="P76" s="22"/>
+      <c r="Q76" s="22"/>
+      <c r="R76" s="22"/>
+      <c r="S76" s="22"/>
+      <c r="T76" s="22"/>
+      <c r="U76" s="22"/>
+      <c r="V76" s="22"/>
+      <c r="W76" s="22"/>
+      <c r="X76" s="22"/>
+      <c r="Y76" s="22"/>
+    </row>
+    <row r="77" ht="15.75" customHeight="1">
+      <c r="A77" s="21" t="s">
+        <v>291</v>
+      </c>
+      <c r="B77" s="22">
         <v>0.0</v>
       </c>
-      <c r="C38" s="20" t="s">
-        <v>142</v>
-      </c>
-      <c r="D38" s="20" t="s">
-        <v>143</v>
-      </c>
-      <c r="E38" s="20" t="s">
-        <v>144</v>
-      </c>
-      <c r="F38" s="20"/>
-      <c r="G38" s="20"/>
-      <c r="H38" s="20"/>
-      <c r="I38" s="20"/>
-      <c r="J38" s="20"/>
-      <c r="K38" s="20"/>
-      <c r="L38" s="20"/>
-      <c r="M38" s="20"/>
-      <c r="N38" s="20"/>
-      <c r="O38" s="20"/>
-      <c r="P38" s="20"/>
-      <c r="Q38" s="20"/>
-      <c r="R38" s="20"/>
-      <c r="S38" s="20"/>
-      <c r="T38" s="20"/>
-      <c r="U38" s="20"/>
-      <c r="V38" s="20"/>
-      <c r="W38" s="20"/>
-      <c r="X38" s="20"/>
-      <c r="Y38" s="20"/>
-    </row>
-    <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="B39" s="19">
+      <c r="C77" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="D77" s="22" t="s">
+        <v>293</v>
+      </c>
+      <c r="E77" s="22" t="s">
+        <v>294</v>
+      </c>
+      <c r="F77" s="22"/>
+      <c r="G77" s="22"/>
+      <c r="H77" s="22"/>
+      <c r="I77" s="22"/>
+      <c r="J77" s="22"/>
+      <c r="K77" s="22"/>
+      <c r="L77" s="22"/>
+      <c r="M77" s="22"/>
+      <c r="N77" s="22"/>
+      <c r="O77" s="22"/>
+      <c r="P77" s="22"/>
+      <c r="Q77" s="22"/>
+      <c r="R77" s="22"/>
+      <c r="S77" s="22"/>
+      <c r="T77" s="22"/>
+      <c r="U77" s="22"/>
+      <c r="V77" s="22"/>
+      <c r="W77" s="22"/>
+      <c r="X77" s="22"/>
+      <c r="Y77" s="22"/>
+    </row>
+    <row r="78" ht="15.0" customHeight="1">
+      <c r="A78" s="21" t="s">
+        <v>295</v>
+      </c>
+      <c r="B78" s="22">
         <v>0.0</v>
       </c>
-      <c r="C39" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="D39" s="20" t="s">
-        <v>147</v>
-      </c>
-      <c r="E39" s="20" t="s">
-        <v>148</v>
-      </c>
-      <c r="F39" s="20"/>
-      <c r="G39" s="20"/>
-      <c r="H39" s="20"/>
-      <c r="I39" s="20"/>
-      <c r="J39" s="20"/>
-      <c r="K39" s="20"/>
-      <c r="L39" s="20"/>
-      <c r="M39" s="20"/>
-      <c r="N39" s="20"/>
-      <c r="O39" s="20"/>
-      <c r="P39" s="20"/>
-      <c r="Q39" s="20"/>
-      <c r="R39" s="20"/>
-      <c r="S39" s="20"/>
-      <c r="T39" s="20"/>
-      <c r="U39" s="20"/>
-      <c r="V39" s="20"/>
-      <c r="W39" s="20"/>
-      <c r="X39" s="20"/>
-      <c r="Y39" s="20"/>
-    </row>
-    <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="B40" s="19">
+      <c r="C78" s="22" t="s">
+        <v>296</v>
+      </c>
+      <c r="D78" s="22" t="s">
+        <v>297</v>
+      </c>
+      <c r="E78" s="22" t="s">
+        <v>298</v>
+      </c>
+      <c r="F78" s="22"/>
+      <c r="G78" s="22"/>
+      <c r="H78" s="22"/>
+      <c r="I78" s="22"/>
+      <c r="J78" s="22"/>
+      <c r="K78" s="22"/>
+      <c r="L78" s="22"/>
+      <c r="M78" s="22"/>
+      <c r="N78" s="22"/>
+      <c r="O78" s="22"/>
+      <c r="P78" s="22"/>
+      <c r="Q78" s="22"/>
+      <c r="R78" s="22"/>
+      <c r="S78" s="22"/>
+      <c r="T78" s="22"/>
+      <c r="U78" s="22"/>
+      <c r="V78" s="22"/>
+      <c r="W78" s="22"/>
+      <c r="X78" s="22"/>
+      <c r="Y78" s="22"/>
+    </row>
+    <row r="79" ht="15.0" customHeight="1">
+      <c r="A79" s="21" t="s">
+        <v>299</v>
+      </c>
+      <c r="B79" s="22">
         <v>0.0</v>
       </c>
-      <c r="C40" s="20" t="s">
-        <v>150</v>
-      </c>
-      <c r="D40" s="20" t="s">
+      <c r="C79" s="22" t="s">
+        <v>300</v>
+      </c>
+      <c r="D79" s="22" t="s">
+        <v>301</v>
+      </c>
+      <c r="E79" s="22" t="s">
+        <v>302</v>
+      </c>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="22"/>
+      <c r="K79" s="22"/>
+      <c r="L79" s="22"/>
+      <c r="M79" s="22"/>
+      <c r="N79" s="22"/>
+      <c r="O79" s="22"/>
+      <c r="P79" s="22"/>
+      <c r="Q79" s="22"/>
+      <c r="R79" s="22"/>
+      <c r="S79" s="22"/>
+      <c r="T79" s="22"/>
+      <c r="U79" s="22"/>
+      <c r="V79" s="22"/>
+      <c r="W79" s="22"/>
+      <c r="X79" s="22"/>
+      <c r="Y79" s="22"/>
+    </row>
+    <row r="80" ht="15.0" customHeight="1">
+      <c r="A80" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="B80" s="22">
+        <v>0.0</v>
+      </c>
+      <c r="C80" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="D80" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="E80" s="22" t="s">
+        <v>306</v>
+      </c>
+      <c r="F80" s="22"/>
+      <c r="G80" s="22"/>
+      <c r="H80" s="22"/>
+      <c r="I80" s="22"/>
+      <c r="J80" s="22"/>
+      <c r="K80" s="22"/>
+      <c r="L80" s="22"/>
+      <c r="M80" s="22"/>
+      <c r="N80" s="22"/>
+      <c r="O80" s="22"/>
+      <c r="P80" s="22"/>
+      <c r="Q80" s="22"/>
+      <c r="R80" s="22"/>
+      <c r="S80" s="22"/>
+      <c r="T80" s="22"/>
+      <c r="U80" s="22"/>
+      <c r="V80" s="22"/>
+      <c r="W80" s="22"/>
+      <c r="X80" s="22"/>
+      <c r="Y80" s="22"/>
+    </row>
+    <row r="81" ht="15.0" customHeight="1">
+      <c r="A81" s="23" t="s">
+        <v>307</v>
+      </c>
+      <c r="B81" s="24">
+        <v>0.0</v>
+      </c>
+      <c r="C81" s="25" t="s">
+        <v>308</v>
+      </c>
+      <c r="D81" s="25" t="s">
+        <v>219</v>
+      </c>
+      <c r="E81" s="25" t="s">
+        <v>220</v>
+      </c>
+      <c r="F81" s="25"/>
+      <c r="G81" s="25"/>
+      <c r="H81" s="25"/>
+      <c r="I81" s="25"/>
+      <c r="J81" s="25"/>
+      <c r="K81" s="25"/>
+      <c r="L81" s="25"/>
+      <c r="M81" s="25"/>
+      <c r="N81" s="25"/>
+      <c r="O81" s="25"/>
+      <c r="P81" s="25"/>
+      <c r="Q81" s="25"/>
+      <c r="R81" s="25"/>
+      <c r="S81" s="25"/>
+      <c r="T81" s="25"/>
+      <c r="U81" s="25"/>
+      <c r="V81" s="25"/>
+      <c r="W81" s="25"/>
+      <c r="X81" s="25"/>
+      <c r="Y81" s="25"/>
+    </row>
+    <row r="82" ht="15.0" customHeight="1">
+      <c r="A82" s="26" t="s">
+        <v>309</v>
+      </c>
+      <c r="B82" s="27">
+        <v>0.0</v>
+      </c>
+      <c r="C82" s="28" t="s">
+        <v>310</v>
+      </c>
+      <c r="D82" s="28" t="s">
         <v>151</v>
       </c>
-      <c r="E40" s="20" t="s">
+      <c r="E82" s="28" t="s">
         <v>152</v>
       </c>
-      <c r="F40" s="20"/>
-      <c r="G40" s="20"/>
-      <c r="H40" s="20"/>
-      <c r="I40" s="20"/>
-      <c r="J40" s="20"/>
-      <c r="K40" s="20"/>
-      <c r="L40" s="20"/>
-      <c r="M40" s="20"/>
-      <c r="N40" s="20"/>
-      <c r="O40" s="20"/>
-      <c r="P40" s="20"/>
-      <c r="Q40" s="20"/>
-      <c r="R40" s="20"/>
-      <c r="S40" s="20"/>
-      <c r="T40" s="20"/>
-      <c r="U40" s="20"/>
-      <c r="V40" s="20"/>
-      <c r="W40" s="20"/>
-      <c r="X40" s="20"/>
-      <c r="Y40" s="20"/>
-    </row>
-    <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="B41" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="C41" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="D41" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="E41" s="20" t="s">
-        <v>156</v>
-      </c>
-      <c r="F41" s="20"/>
-      <c r="G41" s="20"/>
-      <c r="H41" s="20"/>
-      <c r="I41" s="20"/>
-      <c r="J41" s="20"/>
-      <c r="K41" s="20"/>
-      <c r="L41" s="20"/>
-      <c r="M41" s="20"/>
-      <c r="N41" s="20"/>
-      <c r="O41" s="20"/>
-      <c r="P41" s="20"/>
-      <c r="Q41" s="20"/>
-      <c r="R41" s="20"/>
-      <c r="S41" s="20"/>
-      <c r="T41" s="20"/>
-      <c r="U41" s="20"/>
-      <c r="V41" s="20"/>
-      <c r="W41" s="20"/>
-      <c r="X41" s="20"/>
-      <c r="Y41" s="20"/>
-    </row>
-    <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="B42" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="C42" s="20" t="s">
-        <v>158</v>
-      </c>
-      <c r="D42" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="E42" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="F42" s="20"/>
-      <c r="G42" s="20"/>
-      <c r="H42" s="20"/>
-      <c r="I42" s="20"/>
-      <c r="J42" s="20"/>
-      <c r="K42" s="20"/>
-      <c r="L42" s="20"/>
-      <c r="M42" s="20"/>
-      <c r="N42" s="20"/>
-      <c r="O42" s="20"/>
-      <c r="P42" s="20"/>
-      <c r="Q42" s="20"/>
-      <c r="R42" s="20"/>
-      <c r="S42" s="20"/>
-      <c r="T42" s="20"/>
-      <c r="U42" s="20"/>
-      <c r="V42" s="20"/>
-      <c r="W42" s="20"/>
-      <c r="X42" s="20"/>
-      <c r="Y42" s="20"/>
-    </row>
-    <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="B43" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="C43" s="20" t="s">
-        <v>162</v>
-      </c>
-      <c r="D43" s="20" t="s">
-        <v>163</v>
-      </c>
-      <c r="E43" s="20" t="s">
-        <v>164</v>
-      </c>
-      <c r="F43" s="20"/>
-      <c r="G43" s="20"/>
-      <c r="H43" s="20"/>
-      <c r="I43" s="20"/>
-      <c r="J43" s="20"/>
-      <c r="K43" s="20"/>
-      <c r="L43" s="20"/>
-      <c r="M43" s="20"/>
-      <c r="N43" s="20"/>
-      <c r="O43" s="20"/>
-      <c r="P43" s="20"/>
-      <c r="Q43" s="20"/>
-      <c r="R43" s="20"/>
-      <c r="S43" s="20"/>
-      <c r="T43" s="20"/>
-      <c r="U43" s="20"/>
-      <c r="V43" s="20"/>
-      <c r="W43" s="20"/>
-      <c r="X43" s="20"/>
-      <c r="Y43" s="20"/>
-    </row>
-    <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="B44" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="C44" s="20" t="s">
-        <v>166</v>
-      </c>
-      <c r="D44" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="E44" s="20" t="s">
-        <v>168</v>
-      </c>
-      <c r="F44" s="20"/>
-      <c r="G44" s="20"/>
-      <c r="H44" s="20"/>
-      <c r="I44" s="20"/>
-      <c r="J44" s="20"/>
-      <c r="K44" s="20"/>
-      <c r="L44" s="20"/>
-      <c r="M44" s="20"/>
-      <c r="N44" s="20"/>
-      <c r="O44" s="20"/>
-      <c r="P44" s="20"/>
-      <c r="Q44" s="20"/>
-      <c r="R44" s="20"/>
-      <c r="S44" s="20"/>
-      <c r="T44" s="20"/>
-      <c r="U44" s="20"/>
-      <c r="V44" s="20"/>
-      <c r="W44" s="20"/>
-      <c r="X44" s="20"/>
-      <c r="Y44" s="20"/>
-    </row>
-    <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="B45" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="C45" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="D45" s="20" t="s">
-        <v>171</v>
-      </c>
-      <c r="E45" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="F45" s="20"/>
-      <c r="G45" s="20"/>
-      <c r="H45" s="20"/>
-      <c r="I45" s="20"/>
-      <c r="J45" s="20"/>
-      <c r="K45" s="20"/>
-      <c r="L45" s="20"/>
-      <c r="M45" s="20"/>
-      <c r="N45" s="20"/>
-      <c r="O45" s="20"/>
-      <c r="P45" s="20"/>
-      <c r="Q45" s="20"/>
-      <c r="R45" s="20"/>
-      <c r="S45" s="20"/>
-      <c r="T45" s="20"/>
-      <c r="U45" s="20"/>
-      <c r="V45" s="20"/>
-      <c r="W45" s="20"/>
-      <c r="X45" s="20"/>
-      <c r="Y45" s="20"/>
-    </row>
-    <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="18" t="s">
-        <v>173</v>
-      </c>
-      <c r="B46" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="C46" s="20" t="s">
-        <v>174</v>
-      </c>
-      <c r="D46" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="E46" s="20" t="s">
-        <v>176</v>
-      </c>
-      <c r="F46" s="20"/>
-      <c r="G46" s="20"/>
-      <c r="H46" s="20"/>
-      <c r="I46" s="20"/>
-      <c r="J46" s="20"/>
-      <c r="K46" s="20"/>
-      <c r="L46" s="20"/>
-      <c r="M46" s="20"/>
-      <c r="N46" s="20"/>
-      <c r="O46" s="20"/>
-      <c r="P46" s="20"/>
-      <c r="Q46" s="20"/>
-      <c r="R46" s="20"/>
-      <c r="S46" s="20"/>
-      <c r="T46" s="20"/>
-      <c r="U46" s="20"/>
-      <c r="V46" s="20"/>
-      <c r="W46" s="20"/>
-      <c r="X46" s="20"/>
-      <c r="Y46" s="20"/>
-    </row>
-    <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="B47" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="C47" s="20" t="s">
-        <v>178</v>
-      </c>
-      <c r="D47" s="20" t="s">
-        <v>179</v>
-      </c>
-      <c r="E47" s="20" t="s">
-        <v>180</v>
-      </c>
-      <c r="F47" s="20"/>
-      <c r="G47" s="20"/>
-      <c r="H47" s="20"/>
-      <c r="I47" s="20"/>
-      <c r="J47" s="20"/>
-      <c r="K47" s="20"/>
-      <c r="L47" s="20"/>
-      <c r="M47" s="20"/>
-      <c r="N47" s="20"/>
-      <c r="O47" s="20"/>
-      <c r="P47" s="20"/>
-      <c r="Q47" s="20"/>
-      <c r="R47" s="20"/>
-      <c r="S47" s="20"/>
-      <c r="T47" s="20"/>
-      <c r="U47" s="20"/>
-      <c r="V47" s="20"/>
-      <c r="W47" s="20"/>
-      <c r="X47" s="20"/>
-      <c r="Y47" s="20"/>
-    </row>
-    <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="18" t="s">
-        <v>181</v>
-      </c>
-      <c r="B48" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="C48" s="20" t="s">
-        <v>182</v>
-      </c>
-      <c r="D48" s="20" t="s">
-        <v>183</v>
-      </c>
-      <c r="E48" s="20" t="s">
-        <v>184</v>
-      </c>
-      <c r="F48" s="20"/>
-      <c r="G48" s="20"/>
-      <c r="H48" s="20"/>
-      <c r="I48" s="20"/>
-      <c r="J48" s="20"/>
-      <c r="K48" s="20"/>
-      <c r="L48" s="20"/>
-      <c r="M48" s="20"/>
-      <c r="N48" s="20"/>
-      <c r="O48" s="20"/>
-      <c r="P48" s="20"/>
-      <c r="Q48" s="20"/>
-      <c r="R48" s="20"/>
-      <c r="S48" s="20"/>
-      <c r="T48" s="20"/>
-      <c r="U48" s="20"/>
-      <c r="V48" s="20"/>
-      <c r="W48" s="20"/>
-      <c r="X48" s="20"/>
-      <c r="Y48" s="20"/>
-    </row>
-    <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="18" t="s">
-        <v>185</v>
-      </c>
-      <c r="B49" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="C49" s="20" t="s">
-        <v>186</v>
-      </c>
-      <c r="D49" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="E49" s="20" t="s">
-        <v>188</v>
-      </c>
-      <c r="F49" s="20"/>
-      <c r="G49" s="20"/>
-      <c r="H49" s="20"/>
-      <c r="I49" s="20"/>
-      <c r="J49" s="20"/>
-      <c r="K49" s="20"/>
-      <c r="L49" s="20"/>
-      <c r="M49" s="20"/>
-      <c r="N49" s="20"/>
-      <c r="O49" s="20"/>
-      <c r="P49" s="20"/>
-      <c r="Q49" s="20"/>
-      <c r="R49" s="20"/>
-      <c r="S49" s="20"/>
-      <c r="T49" s="20"/>
-      <c r="U49" s="20"/>
-      <c r="V49" s="20"/>
-      <c r="W49" s="20"/>
-      <c r="X49" s="20"/>
-      <c r="Y49" s="20"/>
-    </row>
-    <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="18" t="s">
-        <v>189</v>
-      </c>
-      <c r="B50" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="C50" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="D50" s="20" t="s">
-        <v>191</v>
-      </c>
-      <c r="E50" s="20" t="s">
-        <v>192</v>
-      </c>
-      <c r="F50" s="20"/>
-      <c r="G50" s="20"/>
-      <c r="H50" s="20"/>
-      <c r="I50" s="20"/>
-      <c r="J50" s="20"/>
-      <c r="K50" s="20"/>
-      <c r="L50" s="20"/>
-      <c r="M50" s="20"/>
-      <c r="N50" s="20"/>
-      <c r="O50" s="20"/>
-      <c r="P50" s="20"/>
-      <c r="Q50" s="20"/>
-      <c r="R50" s="20"/>
-      <c r="S50" s="20"/>
-      <c r="T50" s="20"/>
-      <c r="U50" s="20"/>
-      <c r="V50" s="20"/>
-      <c r="W50" s="20"/>
-      <c r="X50" s="20"/>
-      <c r="Y50" s="20"/>
-    </row>
-    <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="B51" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="C51" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="D51" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="E51" s="20" t="s">
-        <v>196</v>
-      </c>
-      <c r="F51" s="20"/>
-      <c r="G51" s="20"/>
-      <c r="H51" s="20"/>
-      <c r="I51" s="20"/>
-      <c r="J51" s="20"/>
-      <c r="K51" s="20"/>
-      <c r="L51" s="20"/>
-      <c r="M51" s="20"/>
-      <c r="N51" s="20"/>
-      <c r="O51" s="20"/>
-      <c r="P51" s="20"/>
-      <c r="Q51" s="20"/>
-      <c r="R51" s="20"/>
-      <c r="S51" s="20"/>
-      <c r="T51" s="20"/>
-      <c r="U51" s="20"/>
-      <c r="V51" s="20"/>
-      <c r="W51" s="20"/>
-      <c r="X51" s="20"/>
-      <c r="Y51" s="20"/>
-    </row>
-    <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="B52" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="C52" s="20" t="s">
-        <v>198</v>
-      </c>
-      <c r="D52" s="20" t="s">
-        <v>199</v>
-      </c>
-      <c r="E52" s="20" t="s">
-        <v>200</v>
-      </c>
-      <c r="F52" s="20"/>
-      <c r="G52" s="20"/>
-      <c r="H52" s="20"/>
-      <c r="I52" s="20"/>
-      <c r="J52" s="20"/>
-      <c r="K52" s="20"/>
-      <c r="L52" s="20"/>
-      <c r="M52" s="20"/>
-      <c r="N52" s="20"/>
-      <c r="O52" s="20"/>
-      <c r="P52" s="20"/>
-      <c r="Q52" s="20"/>
-      <c r="R52" s="20"/>
-      <c r="S52" s="20"/>
-      <c r="T52" s="20"/>
-      <c r="U52" s="20"/>
-      <c r="V52" s="20"/>
-      <c r="W52" s="20"/>
-      <c r="X52" s="20"/>
-      <c r="Y52" s="20"/>
-    </row>
-    <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="B53" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="C53" s="20" t="s">
-        <v>202</v>
-      </c>
-      <c r="D53" s="20" t="s">
-        <v>203</v>
-      </c>
-      <c r="E53" s="20" t="s">
-        <v>204</v>
-      </c>
-      <c r="F53" s="20"/>
-      <c r="G53" s="20"/>
-      <c r="H53" s="20"/>
-      <c r="I53" s="20"/>
-      <c r="J53" s="20"/>
-      <c r="K53" s="20"/>
-      <c r="L53" s="20"/>
-      <c r="M53" s="20"/>
-      <c r="N53" s="20"/>
-      <c r="O53" s="20"/>
-      <c r="P53" s="20"/>
-      <c r="Q53" s="20"/>
-      <c r="R53" s="20"/>
-      <c r="S53" s="20"/>
-      <c r="T53" s="20"/>
-      <c r="U53" s="20"/>
-      <c r="V53" s="20"/>
-      <c r="W53" s="20"/>
-      <c r="X53" s="20"/>
-      <c r="Y53" s="20"/>
-    </row>
-    <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="18" t="s">
-        <v>205</v>
-      </c>
-      <c r="B54" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="C54" s="20" t="s">
-        <v>206</v>
-      </c>
-      <c r="D54" s="20" t="s">
-        <v>207</v>
-      </c>
-      <c r="E54" s="20" t="s">
-        <v>208</v>
-      </c>
-      <c r="F54" s="20"/>
-      <c r="G54" s="20"/>
-      <c r="H54" s="20"/>
-      <c r="I54" s="20"/>
-      <c r="J54" s="20"/>
-      <c r="K54" s="20"/>
-      <c r="L54" s="20"/>
-      <c r="M54" s="20"/>
-      <c r="N54" s="20"/>
-      <c r="O54" s="20"/>
-      <c r="P54" s="20"/>
-      <c r="Q54" s="20"/>
-      <c r="R54" s="20"/>
-      <c r="S54" s="20"/>
-      <c r="T54" s="20"/>
-      <c r="U54" s="20"/>
-      <c r="V54" s="20"/>
-      <c r="W54" s="20"/>
-      <c r="X54" s="20"/>
-      <c r="Y54" s="20"/>
-    </row>
-    <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="B55" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="C55" s="20" t="s">
-        <v>210</v>
-      </c>
-      <c r="D55" s="20" t="s">
-        <v>211</v>
-      </c>
-      <c r="E55" s="20" t="s">
-        <v>212</v>
-      </c>
-      <c r="F55" s="20"/>
-      <c r="G55" s="20"/>
-      <c r="H55" s="20"/>
-      <c r="I55" s="20"/>
-      <c r="J55" s="20"/>
-      <c r="K55" s="20"/>
-      <c r="L55" s="20"/>
-      <c r="M55" s="20"/>
-      <c r="N55" s="20"/>
-      <c r="O55" s="20"/>
-      <c r="P55" s="20"/>
-      <c r="Q55" s="20"/>
-      <c r="R55" s="20"/>
-      <c r="S55" s="20"/>
-      <c r="T55" s="20"/>
-      <c r="U55" s="20"/>
-      <c r="V55" s="20"/>
-      <c r="W55" s="20"/>
-      <c r="X55" s="20"/>
-      <c r="Y55" s="20"/>
-    </row>
-    <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="18" t="s">
-        <v>213</v>
-      </c>
-      <c r="B56" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="C56" s="20" t="s">
-        <v>214</v>
-      </c>
-      <c r="D56" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="E56" s="20" t="s">
-        <v>216</v>
-      </c>
-      <c r="F56" s="20"/>
-      <c r="G56" s="20"/>
-      <c r="H56" s="20"/>
-      <c r="I56" s="20"/>
-      <c r="J56" s="20"/>
-      <c r="K56" s="20"/>
-      <c r="L56" s="20"/>
-      <c r="M56" s="20"/>
-      <c r="N56" s="20"/>
-      <c r="O56" s="20"/>
-      <c r="P56" s="20"/>
-      <c r="Q56" s="20"/>
-      <c r="R56" s="20"/>
-      <c r="S56" s="20"/>
-      <c r="T56" s="20"/>
-      <c r="U56" s="20"/>
-      <c r="V56" s="20"/>
-      <c r="W56" s="20"/>
-      <c r="X56" s="20"/>
-      <c r="Y56" s="20"/>
-    </row>
-    <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="18" t="s">
-        <v>217</v>
-      </c>
-      <c r="B57" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="C57" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="D57" s="20" t="s">
-        <v>219</v>
-      </c>
-      <c r="E57" s="20" t="s">
-        <v>220</v>
-      </c>
-      <c r="F57" s="20"/>
-      <c r="G57" s="20"/>
-      <c r="H57" s="20"/>
-      <c r="I57" s="20"/>
-      <c r="J57" s="20"/>
-      <c r="K57" s="20"/>
-      <c r="L57" s="20"/>
-      <c r="M57" s="20"/>
-      <c r="N57" s="20"/>
-      <c r="O57" s="20"/>
-      <c r="P57" s="20"/>
-      <c r="Q57" s="20"/>
-      <c r="R57" s="20"/>
-      <c r="S57" s="20"/>
-      <c r="T57" s="20"/>
-      <c r="U57" s="20"/>
-      <c r="V57" s="20"/>
-      <c r="W57" s="20"/>
-      <c r="X57" s="20"/>
-      <c r="Y57" s="20"/>
-    </row>
-    <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="18" t="s">
-        <v>221</v>
-      </c>
-      <c r="B58" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="C58" s="20" t="s">
-        <v>222</v>
-      </c>
-      <c r="D58" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="E58" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="F58" s="20"/>
-      <c r="G58" s="20"/>
-      <c r="H58" s="20"/>
-      <c r="I58" s="20"/>
-      <c r="J58" s="20"/>
-      <c r="K58" s="20"/>
-      <c r="L58" s="20"/>
-      <c r="M58" s="20"/>
-      <c r="N58" s="20"/>
-      <c r="O58" s="20"/>
-      <c r="P58" s="20"/>
-      <c r="Q58" s="20"/>
-      <c r="R58" s="20"/>
-      <c r="S58" s="20"/>
-      <c r="T58" s="20"/>
-      <c r="U58" s="20"/>
-      <c r="V58" s="20"/>
-      <c r="W58" s="20"/>
-      <c r="X58" s="20"/>
-      <c r="Y58" s="20"/>
-    </row>
-    <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="18" t="s">
-        <v>223</v>
-      </c>
-      <c r="B59" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="C59" s="20" t="s">
-        <v>224</v>
-      </c>
-      <c r="D59" s="20" t="s">
-        <v>225</v>
-      </c>
-      <c r="E59" s="20" t="s">
-        <v>226</v>
-      </c>
-      <c r="F59" s="20"/>
-      <c r="G59" s="20"/>
-      <c r="H59" s="20"/>
-      <c r="I59" s="20"/>
-      <c r="J59" s="20"/>
-      <c r="K59" s="20"/>
-      <c r="L59" s="20"/>
-      <c r="M59" s="20"/>
-      <c r="N59" s="20"/>
-      <c r="O59" s="20"/>
-      <c r="P59" s="20"/>
-      <c r="Q59" s="20"/>
-      <c r="R59" s="20"/>
-      <c r="S59" s="20"/>
-      <c r="T59" s="20"/>
-      <c r="U59" s="20"/>
-      <c r="V59" s="20"/>
-      <c r="W59" s="20"/>
-      <c r="X59" s="20"/>
-      <c r="Y59" s="20"/>
-    </row>
-    <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="18" t="s">
-        <v>227</v>
-      </c>
-      <c r="B60" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="C60" s="20" t="s">
-        <v>228</v>
-      </c>
-      <c r="D60" s="20" t="s">
-        <v>229</v>
-      </c>
-      <c r="E60" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="F60" s="20"/>
-      <c r="G60" s="20"/>
-      <c r="H60" s="20"/>
-      <c r="I60" s="20"/>
-      <c r="J60" s="20"/>
-      <c r="K60" s="20"/>
-      <c r="L60" s="20"/>
-      <c r="M60" s="20"/>
-      <c r="N60" s="20"/>
-      <c r="O60" s="20"/>
-      <c r="P60" s="20"/>
-      <c r="Q60" s="20"/>
-      <c r="R60" s="20"/>
-      <c r="S60" s="20"/>
-      <c r="T60" s="20"/>
-      <c r="U60" s="20"/>
-      <c r="V60" s="20"/>
-      <c r="W60" s="20"/>
-      <c r="X60" s="20"/>
-      <c r="Y60" s="20"/>
-    </row>
-    <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="18" t="s">
-        <v>231</v>
-      </c>
-      <c r="B61" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="C61" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="D61" s="20" t="s">
-        <v>233</v>
-      </c>
-      <c r="E61" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="F61" s="20"/>
-      <c r="G61" s="20"/>
-      <c r="H61" s="20"/>
-      <c r="I61" s="20"/>
-      <c r="J61" s="20"/>
-      <c r="K61" s="20"/>
-      <c r="L61" s="20"/>
-      <c r="M61" s="20"/>
-      <c r="N61" s="20"/>
-      <c r="O61" s="20"/>
-      <c r="P61" s="20"/>
-      <c r="Q61" s="20"/>
-      <c r="R61" s="20"/>
-      <c r="S61" s="20"/>
-      <c r="T61" s="20"/>
-      <c r="U61" s="20"/>
-      <c r="V61" s="20"/>
-      <c r="W61" s="20"/>
-      <c r="X61" s="20"/>
-      <c r="Y61" s="20"/>
-    </row>
-    <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="B62" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="C62" s="20" t="s">
-        <v>236</v>
-      </c>
-      <c r="D62" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="E62" s="20" t="s">
-        <v>238</v>
-      </c>
-      <c r="F62" s="20"/>
-      <c r="G62" s="20"/>
-      <c r="H62" s="20"/>
-      <c r="I62" s="20"/>
-      <c r="J62" s="20"/>
-      <c r="K62" s="20"/>
-      <c r="L62" s="20"/>
-      <c r="M62" s="20"/>
-      <c r="N62" s="20"/>
-      <c r="O62" s="20"/>
-      <c r="P62" s="20"/>
-      <c r="Q62" s="20"/>
-      <c r="R62" s="20"/>
-      <c r="S62" s="20"/>
-      <c r="T62" s="20"/>
-      <c r="U62" s="20"/>
-      <c r="V62" s="20"/>
-      <c r="W62" s="20"/>
-      <c r="X62" s="20"/>
-      <c r="Y62" s="20"/>
-    </row>
-    <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="18" t="s">
-        <v>239</v>
-      </c>
-      <c r="B63" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="C63" s="20" t="s">
-        <v>240</v>
-      </c>
-      <c r="D63" s="20" t="s">
-        <v>241</v>
-      </c>
-      <c r="E63" s="20" t="s">
-        <v>242</v>
-      </c>
-      <c r="F63" s="20"/>
-      <c r="G63" s="20"/>
-      <c r="H63" s="20"/>
-      <c r="I63" s="20"/>
-      <c r="J63" s="20"/>
-      <c r="K63" s="20"/>
-      <c r="L63" s="20"/>
-      <c r="M63" s="20"/>
-      <c r="N63" s="20"/>
-      <c r="O63" s="20"/>
-      <c r="P63" s="20"/>
-      <c r="Q63" s="20"/>
-      <c r="R63" s="20"/>
-      <c r="S63" s="20"/>
-      <c r="T63" s="20"/>
-      <c r="U63" s="20"/>
-      <c r="V63" s="20"/>
-      <c r="W63" s="20"/>
-      <c r="X63" s="20"/>
-      <c r="Y63" s="20"/>
-    </row>
-    <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="18" t="s">
-        <v>243</v>
-      </c>
-      <c r="B64" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="C64" s="20" t="s">
-        <v>244</v>
-      </c>
-      <c r="D64" s="20" t="s">
-        <v>245</v>
-      </c>
-      <c r="E64" s="20" t="s">
-        <v>246</v>
-      </c>
-      <c r="F64" s="20"/>
-      <c r="G64" s="20"/>
-      <c r="H64" s="20"/>
-      <c r="I64" s="20"/>
-      <c r="J64" s="20"/>
-      <c r="K64" s="20"/>
-      <c r="L64" s="20"/>
-      <c r="M64" s="20"/>
-      <c r="N64" s="20"/>
-      <c r="O64" s="20"/>
-      <c r="P64" s="20"/>
-      <c r="Q64" s="20"/>
-      <c r="R64" s="20"/>
-      <c r="S64" s="20"/>
-      <c r="T64" s="20"/>
-      <c r="U64" s="20"/>
-      <c r="V64" s="20"/>
-      <c r="W64" s="20"/>
-      <c r="X64" s="20"/>
-      <c r="Y64" s="20"/>
-    </row>
-    <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="18" t="s">
-        <v>247</v>
-      </c>
-      <c r="B65" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="C65" s="20" t="s">
-        <v>248</v>
-      </c>
-      <c r="D65" s="20" t="s">
-        <v>249</v>
-      </c>
-      <c r="E65" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="F65" s="20"/>
-      <c r="G65" s="20"/>
-      <c r="H65" s="20"/>
-      <c r="I65" s="20"/>
-      <c r="J65" s="20"/>
-      <c r="K65" s="20"/>
-      <c r="L65" s="20"/>
-      <c r="M65" s="20"/>
-      <c r="N65" s="20"/>
-      <c r="O65" s="20"/>
-      <c r="P65" s="20"/>
-      <c r="Q65" s="20"/>
-      <c r="R65" s="20"/>
-      <c r="S65" s="20"/>
-      <c r="T65" s="20"/>
-      <c r="U65" s="20"/>
-      <c r="V65" s="20"/>
-      <c r="W65" s="20"/>
-      <c r="X65" s="20"/>
-      <c r="Y65" s="20"/>
-    </row>
-    <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="18" t="s">
-        <v>251</v>
-      </c>
-      <c r="B66" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="C66" s="20" t="s">
-        <v>252</v>
-      </c>
-      <c r="D66" s="20" t="s">
-        <v>253</v>
-      </c>
-      <c r="E66" s="20" t="s">
-        <v>254</v>
-      </c>
-      <c r="F66" s="20"/>
-      <c r="G66" s="20"/>
-      <c r="H66" s="20"/>
-      <c r="I66" s="20"/>
-      <c r="J66" s="20"/>
-      <c r="K66" s="20"/>
-      <c r="L66" s="20"/>
-      <c r="M66" s="20"/>
-      <c r="N66" s="20"/>
-      <c r="O66" s="20"/>
-      <c r="P66" s="20"/>
-      <c r="Q66" s="20"/>
-      <c r="R66" s="20"/>
-      <c r="S66" s="20"/>
-      <c r="T66" s="20"/>
-      <c r="U66" s="20"/>
-      <c r="V66" s="20"/>
-      <c r="W66" s="20"/>
-      <c r="X66" s="20"/>
-      <c r="Y66" s="20"/>
-    </row>
-    <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="18" t="s">
-        <v>255</v>
-      </c>
-      <c r="B67" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="C67" s="20" t="s">
-        <v>256</v>
-      </c>
-      <c r="D67" s="20" t="s">
-        <v>257</v>
-      </c>
-      <c r="E67" s="20" t="s">
-        <v>258</v>
-      </c>
-      <c r="F67" s="20"/>
-      <c r="G67" s="20"/>
-      <c r="H67" s="20"/>
-      <c r="I67" s="20"/>
-      <c r="J67" s="20"/>
-      <c r="K67" s="20"/>
-      <c r="L67" s="20"/>
-      <c r="M67" s="20"/>
-      <c r="N67" s="20"/>
-      <c r="O67" s="20"/>
-      <c r="P67" s="20"/>
-      <c r="Q67" s="20"/>
-      <c r="R67" s="20"/>
-      <c r="S67" s="20"/>
-      <c r="T67" s="20"/>
-      <c r="U67" s="20"/>
-      <c r="V67" s="20"/>
-      <c r="W67" s="20"/>
-      <c r="X67" s="20"/>
-      <c r="Y67" s="20"/>
-    </row>
-    <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="18" t="s">
-        <v>259</v>
-      </c>
-      <c r="B68" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="C68" s="20" t="s">
-        <v>260</v>
-      </c>
-      <c r="D68" s="20" t="s">
-        <v>261</v>
-      </c>
-      <c r="E68" s="20" t="s">
-        <v>262</v>
-      </c>
-      <c r="F68" s="20"/>
-      <c r="G68" s="20"/>
-      <c r="H68" s="20"/>
-      <c r="I68" s="20"/>
-      <c r="J68" s="20"/>
-      <c r="K68" s="20"/>
-      <c r="L68" s="20"/>
-      <c r="M68" s="20"/>
-      <c r="N68" s="20"/>
-      <c r="O68" s="20"/>
-      <c r="P68" s="20"/>
-      <c r="Q68" s="20"/>
-      <c r="R68" s="20"/>
-      <c r="S68" s="20"/>
-      <c r="T68" s="20"/>
-      <c r="U68" s="20"/>
-      <c r="V68" s="20"/>
-      <c r="W68" s="20"/>
-      <c r="X68" s="20"/>
-      <c r="Y68" s="20"/>
-    </row>
-    <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="18" t="s">
-        <v>263</v>
-      </c>
-      <c r="B69" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="C69" s="20" t="s">
-        <v>264</v>
-      </c>
-      <c r="D69" s="20" t="s">
-        <v>265</v>
-      </c>
-      <c r="E69" s="20" t="s">
-        <v>266</v>
-      </c>
-      <c r="F69" s="20"/>
-      <c r="G69" s="20"/>
-      <c r="H69" s="20"/>
-      <c r="I69" s="20"/>
-      <c r="J69" s="20"/>
-      <c r="K69" s="20"/>
-      <c r="L69" s="20"/>
-      <c r="M69" s="20"/>
-      <c r="N69" s="20"/>
-      <c r="O69" s="20"/>
-      <c r="P69" s="20"/>
-      <c r="Q69" s="20"/>
-      <c r="R69" s="20"/>
-      <c r="S69" s="20"/>
-      <c r="T69" s="20"/>
-      <c r="U69" s="20"/>
-      <c r="V69" s="20"/>
-      <c r="W69" s="20"/>
-      <c r="X69" s="20"/>
-      <c r="Y69" s="20"/>
-    </row>
-    <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="18" t="s">
-        <v>267</v>
-      </c>
-      <c r="B70" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="C70" s="20" t="s">
-        <v>268</v>
-      </c>
-      <c r="D70" s="20" t="s">
-        <v>269</v>
-      </c>
-      <c r="E70" s="20" t="s">
-        <v>270</v>
-      </c>
-      <c r="F70" s="20"/>
-      <c r="G70" s="20"/>
-      <c r="H70" s="20"/>
-      <c r="I70" s="20"/>
-      <c r="J70" s="20"/>
-      <c r="K70" s="20"/>
-      <c r="L70" s="20"/>
-      <c r="M70" s="20"/>
-      <c r="N70" s="20"/>
-      <c r="O70" s="20"/>
-      <c r="P70" s="20"/>
-      <c r="Q70" s="20"/>
-      <c r="R70" s="20"/>
-      <c r="S70" s="20"/>
-      <c r="T70" s="20"/>
-      <c r="U70" s="20"/>
-      <c r="V70" s="20"/>
-      <c r="W70" s="20"/>
-      <c r="X70" s="20"/>
-      <c r="Y70" s="20"/>
-    </row>
-    <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="18" t="s">
-        <v>271</v>
-      </c>
-      <c r="B71" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="C71" s="20" t="s">
-        <v>272</v>
-      </c>
-      <c r="D71" s="20" t="s">
-        <v>273</v>
-      </c>
-      <c r="E71" s="20" t="s">
-        <v>274</v>
-      </c>
-      <c r="F71" s="20"/>
-      <c r="G71" s="20"/>
-      <c r="H71" s="20"/>
-      <c r="I71" s="20"/>
-      <c r="J71" s="20"/>
-      <c r="K71" s="20"/>
-      <c r="L71" s="20"/>
-      <c r="M71" s="20"/>
-      <c r="N71" s="20"/>
-      <c r="O71" s="20"/>
-      <c r="P71" s="20"/>
-      <c r="Q71" s="20"/>
-      <c r="R71" s="20"/>
-      <c r="S71" s="20"/>
-      <c r="T71" s="20"/>
-      <c r="U71" s="20"/>
-      <c r="V71" s="20"/>
-      <c r="W71" s="20"/>
-      <c r="X71" s="20"/>
-      <c r="Y71" s="20"/>
-    </row>
-    <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="18" t="s">
-        <v>275</v>
-      </c>
-      <c r="B72" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="C72" s="20" t="s">
-        <v>276</v>
-      </c>
-      <c r="D72" s="20" t="s">
-        <v>277</v>
-      </c>
-      <c r="E72" s="20" t="s">
-        <v>278</v>
-      </c>
-      <c r="F72" s="20"/>
-      <c r="G72" s="20"/>
-      <c r="H72" s="20"/>
-      <c r="I72" s="20"/>
-      <c r="J72" s="20"/>
-      <c r="K72" s="20"/>
-      <c r="L72" s="20"/>
-      <c r="M72" s="20"/>
-      <c r="N72" s="20"/>
-      <c r="O72" s="20"/>
-      <c r="P72" s="20"/>
-      <c r="Q72" s="20"/>
-      <c r="R72" s="20"/>
-      <c r="S72" s="20"/>
-      <c r="T72" s="20"/>
-      <c r="U72" s="20"/>
-      <c r="V72" s="20"/>
-      <c r="W72" s="20"/>
-      <c r="X72" s="20"/>
-      <c r="Y72" s="20"/>
-    </row>
-    <row r="73" ht="15.0" customHeight="1">
-      <c r="A73" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="B73" s="22">
-        <v>0.0</v>
-      </c>
-      <c r="C73" s="23" t="s">
-        <v>280</v>
-      </c>
-      <c r="D73" s="23" t="s">
-        <v>281</v>
-      </c>
-      <c r="E73" s="23" t="s">
-        <v>282</v>
-      </c>
-      <c r="F73" s="23"/>
-      <c r="G73" s="23"/>
-      <c r="H73" s="23"/>
-      <c r="I73" s="23"/>
-      <c r="J73" s="23"/>
-      <c r="K73" s="23"/>
-      <c r="L73" s="23"/>
-      <c r="M73" s="23"/>
-      <c r="N73" s="23"/>
-      <c r="O73" s="23"/>
-      <c r="P73" s="23"/>
-      <c r="Q73" s="23"/>
-      <c r="R73" s="23"/>
-      <c r="S73" s="23"/>
-      <c r="T73" s="23"/>
-      <c r="U73" s="23"/>
-      <c r="V73" s="23"/>
-      <c r="W73" s="23"/>
-      <c r="X73" s="23"/>
-      <c r="Y73" s="23"/>
-    </row>
-    <row r="74" ht="15.0" customHeight="1">
-      <c r="A74" s="24" t="s">
-        <v>283</v>
-      </c>
-      <c r="B74" s="25">
-        <v>0.0</v>
-      </c>
-      <c r="C74" s="25" t="s">
-        <v>284</v>
-      </c>
-      <c r="D74" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="E74" s="25" t="s">
-        <v>160</v>
-      </c>
-      <c r="F74" s="25"/>
-      <c r="G74" s="25"/>
-      <c r="H74" s="25"/>
-      <c r="I74" s="25"/>
-      <c r="J74" s="25"/>
-      <c r="K74" s="25"/>
-      <c r="L74" s="25"/>
-      <c r="M74" s="25"/>
-      <c r="N74" s="25"/>
-      <c r="O74" s="25"/>
-      <c r="P74" s="25"/>
-      <c r="Q74" s="25"/>
-      <c r="R74" s="25"/>
-      <c r="S74" s="25"/>
-      <c r="T74" s="25"/>
-      <c r="U74" s="25"/>
-      <c r="V74" s="25"/>
-      <c r="W74" s="25"/>
-      <c r="X74" s="25"/>
-      <c r="Y74" s="25"/>
-    </row>
-    <row r="75" ht="15.0" customHeight="1">
-      <c r="A75" s="24" t="s">
-        <v>285</v>
-      </c>
-      <c r="B75" s="25">
-        <v>0.0</v>
-      </c>
-      <c r="C75" s="25" t="s">
-        <v>286</v>
-      </c>
-      <c r="D75" s="25" t="s">
-        <v>287</v>
-      </c>
-      <c r="E75" s="25" t="s">
-        <v>288</v>
-      </c>
-      <c r="F75" s="25"/>
-      <c r="G75" s="25"/>
-      <c r="H75" s="25"/>
-      <c r="I75" s="25"/>
-      <c r="J75" s="25"/>
-      <c r="K75" s="25"/>
-      <c r="L75" s="25"/>
-      <c r="M75" s="25"/>
-      <c r="N75" s="25"/>
-      <c r="O75" s="25"/>
-      <c r="P75" s="25"/>
-      <c r="Q75" s="25"/>
-      <c r="R75" s="25"/>
-      <c r="S75" s="25"/>
-      <c r="T75" s="25"/>
-      <c r="U75" s="25"/>
-      <c r="V75" s="25"/>
-      <c r="W75" s="25"/>
-      <c r="X75" s="25"/>
-      <c r="Y75" s="25"/>
-    </row>
-    <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="24" t="s">
-        <v>289</v>
-      </c>
-      <c r="B76" s="25">
-        <v>0.0</v>
-      </c>
-      <c r="C76" s="25" t="s">
-        <v>290</v>
-      </c>
-      <c r="D76" s="25" t="s">
-        <v>187</v>
-      </c>
-      <c r="E76" s="25" t="s">
-        <v>188</v>
-      </c>
-      <c r="F76" s="25"/>
-      <c r="G76" s="25"/>
-      <c r="H76" s="25"/>
-      <c r="I76" s="25"/>
-      <c r="J76" s="25"/>
-      <c r="K76" s="25"/>
-      <c r="L76" s="25"/>
-      <c r="M76" s="25"/>
-      <c r="N76" s="25"/>
-      <c r="O76" s="25"/>
-      <c r="P76" s="25"/>
-      <c r="Q76" s="25"/>
-      <c r="R76" s="25"/>
-      <c r="S76" s="25"/>
-      <c r="T76" s="25"/>
-      <c r="U76" s="25"/>
-      <c r="V76" s="25"/>
-      <c r="W76" s="25"/>
-      <c r="X76" s="25"/>
-      <c r="Y76" s="25"/>
-    </row>
-    <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="24" t="s">
-        <v>291</v>
-      </c>
-      <c r="B77" s="25">
-        <v>0.0</v>
-      </c>
-      <c r="C77" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="D77" s="25" t="s">
-        <v>293</v>
-      </c>
-      <c r="E77" s="25" t="s">
-        <v>294</v>
-      </c>
-      <c r="F77" s="25"/>
-      <c r="G77" s="25"/>
-      <c r="H77" s="25"/>
-      <c r="I77" s="25"/>
-      <c r="J77" s="25"/>
-      <c r="K77" s="25"/>
-      <c r="L77" s="25"/>
-      <c r="M77" s="25"/>
-      <c r="N77" s="25"/>
-      <c r="O77" s="25"/>
-      <c r="P77" s="25"/>
-      <c r="Q77" s="25"/>
-      <c r="R77" s="25"/>
-      <c r="S77" s="25"/>
-      <c r="T77" s="25"/>
-      <c r="U77" s="25"/>
-      <c r="V77" s="25"/>
-      <c r="W77" s="25"/>
-      <c r="X77" s="25"/>
-      <c r="Y77" s="25"/>
-    </row>
-    <row r="78" ht="15.0" customHeight="1">
-      <c r="A78" s="24" t="s">
-        <v>295</v>
-      </c>
-      <c r="B78" s="25">
-        <v>0.0</v>
-      </c>
-      <c r="C78" s="25" t="s">
-        <v>296</v>
-      </c>
-      <c r="D78" s="25" t="s">
-        <v>297</v>
-      </c>
-      <c r="E78" s="25" t="s">
-        <v>298</v>
-      </c>
-      <c r="F78" s="25"/>
-      <c r="G78" s="25"/>
-      <c r="H78" s="25"/>
-      <c r="I78" s="25"/>
-      <c r="J78" s="25"/>
-      <c r="K78" s="25"/>
-      <c r="L78" s="25"/>
-      <c r="M78" s="25"/>
-      <c r="N78" s="25"/>
-      <c r="O78" s="25"/>
-      <c r="P78" s="25"/>
-      <c r="Q78" s="25"/>
-      <c r="R78" s="25"/>
-      <c r="S78" s="25"/>
-      <c r="T78" s="25"/>
-      <c r="U78" s="25"/>
-      <c r="V78" s="25"/>
-      <c r="W78" s="25"/>
-      <c r="X78" s="25"/>
-      <c r="Y78" s="25"/>
-    </row>
-    <row r="79" ht="15.0" customHeight="1">
-      <c r="A79" s="24" t="s">
-        <v>299</v>
-      </c>
-      <c r="B79" s="25">
-        <v>0.0</v>
-      </c>
-      <c r="C79" s="25" t="s">
-        <v>300</v>
-      </c>
-      <c r="D79" s="25" t="s">
-        <v>301</v>
-      </c>
-      <c r="E79" s="25" t="s">
-        <v>302</v>
-      </c>
-      <c r="F79" s="25"/>
-      <c r="G79" s="25"/>
-      <c r="H79" s="25"/>
-      <c r="I79" s="25"/>
-      <c r="J79" s="25"/>
-      <c r="K79" s="25"/>
-      <c r="L79" s="25"/>
-      <c r="M79" s="25"/>
-      <c r="N79" s="25"/>
-      <c r="O79" s="25"/>
-      <c r="P79" s="25"/>
-      <c r="Q79" s="25"/>
-      <c r="R79" s="25"/>
-      <c r="S79" s="25"/>
-      <c r="T79" s="25"/>
-      <c r="U79" s="25"/>
-      <c r="V79" s="25"/>
-      <c r="W79" s="25"/>
-      <c r="X79" s="25"/>
-      <c r="Y79" s="25"/>
-    </row>
-    <row r="80" ht="15.0" customHeight="1">
-      <c r="A80" s="24" t="s">
-        <v>303</v>
-      </c>
-      <c r="B80" s="25">
-        <v>0.0</v>
-      </c>
-      <c r="C80" s="25" t="s">
-        <v>304</v>
-      </c>
-      <c r="D80" s="25" t="s">
-        <v>305</v>
-      </c>
-      <c r="E80" s="25" t="s">
-        <v>306</v>
-      </c>
-      <c r="F80" s="25"/>
-      <c r="G80" s="25"/>
-      <c r="H80" s="25"/>
-      <c r="I80" s="25"/>
-      <c r="J80" s="25"/>
-      <c r="K80" s="25"/>
-      <c r="L80" s="25"/>
-      <c r="M80" s="25"/>
-      <c r="N80" s="25"/>
-      <c r="O80" s="25"/>
-      <c r="P80" s="25"/>
-      <c r="Q80" s="25"/>
-      <c r="R80" s="25"/>
-      <c r="S80" s="25"/>
-      <c r="T80" s="25"/>
-      <c r="U80" s="25"/>
-      <c r="V80" s="25"/>
-      <c r="W80" s="25"/>
-      <c r="X80" s="25"/>
-      <c r="Y80" s="25"/>
-    </row>
-    <row r="81" ht="15.0" customHeight="1">
-      <c r="A81" s="26" t="s">
-        <v>307</v>
-      </c>
-      <c r="B81" s="27">
-        <v>0.0</v>
-      </c>
-      <c r="C81" s="28" t="s">
-        <v>308</v>
-      </c>
-      <c r="D81" s="28" t="s">
-        <v>219</v>
-      </c>
-      <c r="E81" s="28" t="s">
-        <v>220</v>
-      </c>
-      <c r="F81" s="28"/>
-      <c r="G81" s="28"/>
-      <c r="H81" s="28"/>
-      <c r="I81" s="28"/>
-      <c r="J81" s="28"/>
-      <c r="K81" s="28"/>
-      <c r="L81" s="28"/>
-      <c r="M81" s="28"/>
-      <c r="N81" s="28"/>
-      <c r="O81" s="28"/>
-      <c r="P81" s="28"/>
-      <c r="Q81" s="28"/>
-      <c r="R81" s="28"/>
-      <c r="S81" s="28"/>
-      <c r="T81" s="28"/>
-      <c r="U81" s="28"/>
-      <c r="V81" s="28"/>
-      <c r="W81" s="28"/>
-      <c r="X81" s="28"/>
-      <c r="Y81" s="28"/>
-    </row>
-    <row r="82" ht="15.0" customHeight="1">
-      <c r="A82" s="29" t="s">
-        <v>309</v>
-      </c>
-      <c r="B82" s="30">
-        <v>0.0</v>
-      </c>
-      <c r="C82" s="31" t="s">
-        <v>310</v>
-      </c>
-      <c r="D82" s="31" t="s">
-        <v>151</v>
-      </c>
-      <c r="E82" s="31" t="s">
-        <v>152</v>
-      </c>
-      <c r="F82" s="31"/>
-      <c r="G82" s="31"/>
-      <c r="H82" s="31"/>
-      <c r="I82" s="31"/>
-      <c r="J82" s="31"/>
-      <c r="K82" s="31"/>
-      <c r="L82" s="31"/>
-      <c r="M82" s="31"/>
-      <c r="N82" s="31"/>
-      <c r="O82" s="31"/>
-      <c r="P82" s="31"/>
-      <c r="Q82" s="31"/>
-      <c r="R82" s="31"/>
-      <c r="S82" s="31"/>
-      <c r="T82" s="31"/>
-      <c r="U82" s="31"/>
-      <c r="V82" s="31"/>
-      <c r="W82" s="31"/>
-      <c r="X82" s="31"/>
-      <c r="Y82" s="31"/>
+      <c r="F82" s="28"/>
+      <c r="G82" s="28"/>
+      <c r="H82" s="28"/>
+      <c r="I82" s="28"/>
+      <c r="J82" s="28"/>
+      <c r="K82" s="28"/>
+      <c r="L82" s="28"/>
+      <c r="M82" s="28"/>
+      <c r="N82" s="28"/>
+      <c r="O82" s="28"/>
+      <c r="P82" s="28"/>
+      <c r="Q82" s="28"/>
+      <c r="R82" s="28"/>
+      <c r="S82" s="28"/>
+      <c r="T82" s="28"/>
+      <c r="U82" s="28"/>
+      <c r="V82" s="28"/>
+      <c r="W82" s="28"/>
+      <c r="X82" s="28"/>
+      <c r="Y82" s="28"/>
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="1"/>
@@ -10498,8 +10489,6 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
-    <row r="1001" ht="15.75" customHeight="1"/>
-    <row r="1002" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Templates/Tables/StringInfo/StrTable.xlsx
+++ b/Templates/Tables/StringInfo/StrTable.xlsx
@@ -238,10 +238,10 @@
     <t>추적 설명 팝업 설명 메세지 1</t>
   </si>
   <si>
-    <t>∙ 특별한 프로모션을 제공해\n드립니다</t>
-  </si>
-  <si>
-    <t>∙ Special offers and promotions\njust for you</t>
+    <t>특별한 프로모션을 제공해\n드립니다</t>
+  </si>
+  <si>
+    <t>Special offers and promotions\njust for you</t>
   </si>
   <si>
     <t>TRACKING_DP_DESC_MSG_02</t>
@@ -250,10 +250,10 @@
     <t>추적 설명 팝업 설명 메세지 2</t>
   </si>
   <si>
-    <t>∙ 관심사에 맞는 광고를 보여\n드립니다</t>
-  </si>
-  <si>
-    <t>∙ Advertisements that match\nyour interests</t>
+    <t>관심사에 맞는 광고를 보여\n드립니다</t>
+  </si>
+  <si>
+    <t>Advertisements that match\nyour interests</t>
   </si>
   <si>
     <t>TRACKING_DP_DESC_MSG_03</t>
@@ -262,10 +262,10 @@
     <t>추적 설명 팝업 설명 메세지 3</t>
   </si>
   <si>
-    <t>∙ 개인화 된 경험을 향상 시켜\n드립니다</t>
-  </si>
-  <si>
-    <t>∙ An improved personalized\nexperience over time</t>
+    <t>개인화 된 경험을 향상 시켜\n드립니다</t>
+  </si>
+  <si>
+    <t>An improved personalized\nexperience over time</t>
   </si>
   <si>
     <t>START_SM_LOADING_TEXT</t>
@@ -1034,7 +1034,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1059,6 +1059,9 @@
     </xf>
     <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -2087,10 +2090,10 @@
       <c r="C21" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="9" t="s">
         <v>76</v>
       </c>
       <c r="F21" s="7"/>
@@ -2124,10 +2127,10 @@
       <c r="C22" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="9" t="s">
         <v>80</v>
       </c>
       <c r="F22" s="7"/>
@@ -2161,10 +2164,10 @@
       <c r="C23" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" s="9" t="s">
         <v>84</v>
       </c>
       <c r="F23" s="7"/>
@@ -2189,2187 +2192,2187 @@
       <c r="Y23" s="7"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="9" t="s">
+      <c r="A24" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="B24" s="10">
+      <c r="B24" s="11">
         <v>0.0</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D24" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="E24" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="11"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
-      <c r="N24" s="11"/>
-      <c r="O24" s="11"/>
-      <c r="P24" s="11"/>
-      <c r="Q24" s="11"/>
-      <c r="R24" s="11"/>
-      <c r="S24" s="11"/>
-      <c r="T24" s="11"/>
-      <c r="U24" s="11"/>
-      <c r="V24" s="11"/>
-      <c r="W24" s="11"/>
-      <c r="X24" s="11"/>
-      <c r="Y24" s="11"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="12"/>
+      <c r="M24" s="12"/>
+      <c r="N24" s="12"/>
+      <c r="O24" s="12"/>
+      <c r="P24" s="12"/>
+      <c r="Q24" s="12"/>
+      <c r="R24" s="12"/>
+      <c r="S24" s="12"/>
+      <c r="T24" s="12"/>
+      <c r="U24" s="12"/>
+      <c r="V24" s="12"/>
+      <c r="W24" s="12"/>
+      <c r="X24" s="12"/>
+      <c r="Y24" s="12"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="12" t="s">
+      <c r="A25" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="B25" s="13">
+      <c r="B25" s="14">
         <v>0.0</v>
       </c>
-      <c r="C25" s="14" t="s">
+      <c r="C25" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="D25" s="14" t="s">
+      <c r="D25" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="E25" s="14" t="s">
+      <c r="E25" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="14"/>
-      <c r="J25" s="14"/>
-      <c r="K25" s="14"/>
-      <c r="L25" s="14"/>
-      <c r="M25" s="14"/>
-      <c r="N25" s="14"/>
-      <c r="O25" s="14"/>
-      <c r="P25" s="14"/>
-      <c r="Q25" s="14"/>
-      <c r="R25" s="14"/>
-      <c r="S25" s="14"/>
-      <c r="T25" s="14"/>
-      <c r="U25" s="14"/>
-      <c r="V25" s="14"/>
-      <c r="W25" s="14"/>
-      <c r="X25" s="14"/>
-      <c r="Y25" s="14"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="15"/>
+      <c r="J25" s="15"/>
+      <c r="K25" s="15"/>
+      <c r="L25" s="15"/>
+      <c r="M25" s="15"/>
+      <c r="N25" s="15"/>
+      <c r="O25" s="15"/>
+      <c r="P25" s="15"/>
+      <c r="Q25" s="15"/>
+      <c r="R25" s="15"/>
+      <c r="S25" s="15"/>
+      <c r="T25" s="15"/>
+      <c r="U25" s="15"/>
+      <c r="V25" s="15"/>
+      <c r="W25" s="15"/>
+      <c r="X25" s="15"/>
+      <c r="Y25" s="15"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="15" t="s">
+      <c r="A26" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="B26" s="16">
+      <c r="B26" s="17">
         <v>0.0</v>
       </c>
-      <c r="C26" s="17" t="s">
+      <c r="C26" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="D26" s="17" t="s">
+      <c r="D26" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="E26" s="17" t="s">
+      <c r="E26" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="17"/>
-      <c r="I26" s="17"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="17"/>
-      <c r="L26" s="17"/>
-      <c r="M26" s="17"/>
-      <c r="N26" s="17"/>
-      <c r="O26" s="17"/>
-      <c r="P26" s="17"/>
-      <c r="Q26" s="17"/>
-      <c r="R26" s="17"/>
-      <c r="S26" s="17"/>
-      <c r="T26" s="17"/>
-      <c r="U26" s="17"/>
-      <c r="V26" s="17"/>
-      <c r="W26" s="17"/>
-      <c r="X26" s="17"/>
-      <c r="Y26" s="17"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="18"/>
+      <c r="J26" s="18"/>
+      <c r="K26" s="18"/>
+      <c r="L26" s="18"/>
+      <c r="M26" s="18"/>
+      <c r="N26" s="18"/>
+      <c r="O26" s="18"/>
+      <c r="P26" s="18"/>
+      <c r="Q26" s="18"/>
+      <c r="R26" s="18"/>
+      <c r="S26" s="18"/>
+      <c r="T26" s="18"/>
+      <c r="U26" s="18"/>
+      <c r="V26" s="18"/>
+      <c r="W26" s="18"/>
+      <c r="X26" s="18"/>
+      <c r="Y26" s="18"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="15" t="s">
+      <c r="A27" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="B27" s="16">
+      <c r="B27" s="17">
         <v>0.0</v>
       </c>
-      <c r="C27" s="17" t="s">
+      <c r="C27" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="D27" s="17" t="s">
+      <c r="D27" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="E27" s="17" t="s">
+      <c r="E27" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="17"/>
-      <c r="I27" s="17"/>
-      <c r="J27" s="17"/>
-      <c r="K27" s="17"/>
-      <c r="L27" s="17"/>
-      <c r="M27" s="17"/>
-      <c r="N27" s="17"/>
-      <c r="O27" s="17"/>
-      <c r="P27" s="17"/>
-      <c r="Q27" s="17"/>
-      <c r="R27" s="17"/>
-      <c r="S27" s="17"/>
-      <c r="T27" s="17"/>
-      <c r="U27" s="17"/>
-      <c r="V27" s="17"/>
-      <c r="W27" s="17"/>
-      <c r="X27" s="17"/>
-      <c r="Y27" s="17"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="18"/>
+      <c r="K27" s="18"/>
+      <c r="L27" s="18"/>
+      <c r="M27" s="18"/>
+      <c r="N27" s="18"/>
+      <c r="O27" s="18"/>
+      <c r="P27" s="18"/>
+      <c r="Q27" s="18"/>
+      <c r="R27" s="18"/>
+      <c r="S27" s="18"/>
+      <c r="T27" s="18"/>
+      <c r="U27" s="18"/>
+      <c r="V27" s="18"/>
+      <c r="W27" s="18"/>
+      <c r="X27" s="18"/>
+      <c r="Y27" s="18"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="15" t="s">
+      <c r="A28" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="B28" s="16">
+      <c r="B28" s="17">
         <v>0.0</v>
       </c>
-      <c r="C28" s="17" t="s">
+      <c r="C28" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="D28" s="17" t="s">
+      <c r="D28" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="E28" s="17" t="s">
+      <c r="E28" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="17"/>
-      <c r="I28" s="17"/>
-      <c r="J28" s="17"/>
-      <c r="K28" s="17"/>
-      <c r="L28" s="17"/>
-      <c r="M28" s="17"/>
-      <c r="N28" s="17"/>
-      <c r="O28" s="17"/>
-      <c r="P28" s="17"/>
-      <c r="Q28" s="17"/>
-      <c r="R28" s="17"/>
-      <c r="S28" s="17"/>
-      <c r="T28" s="17"/>
-      <c r="U28" s="17"/>
-      <c r="V28" s="17"/>
-      <c r="W28" s="17"/>
-      <c r="X28" s="17"/>
-      <c r="Y28" s="17"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18"/>
+      <c r="J28" s="18"/>
+      <c r="K28" s="18"/>
+      <c r="L28" s="18"/>
+      <c r="M28" s="18"/>
+      <c r="N28" s="18"/>
+      <c r="O28" s="18"/>
+      <c r="P28" s="18"/>
+      <c r="Q28" s="18"/>
+      <c r="R28" s="18"/>
+      <c r="S28" s="18"/>
+      <c r="T28" s="18"/>
+      <c r="U28" s="18"/>
+      <c r="V28" s="18"/>
+      <c r="W28" s="18"/>
+      <c r="X28" s="18"/>
+      <c r="Y28" s="18"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="15" t="s">
+      <c r="A29" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="B29" s="16">
+      <c r="B29" s="17">
         <v>0.0</v>
       </c>
-      <c r="C29" s="17" t="s">
+      <c r="C29" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="D29" s="17" t="s">
+      <c r="D29" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="E29" s="17" t="s">
+      <c r="E29" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17"/>
-      <c r="H29" s="17"/>
-      <c r="I29" s="17"/>
-      <c r="J29" s="17"/>
-      <c r="K29" s="17"/>
-      <c r="L29" s="17"/>
-      <c r="M29" s="17"/>
-      <c r="N29" s="17"/>
-      <c r="O29" s="17"/>
-      <c r="P29" s="17"/>
-      <c r="Q29" s="17"/>
-      <c r="R29" s="17"/>
-      <c r="S29" s="17"/>
-      <c r="T29" s="17"/>
-      <c r="U29" s="17"/>
-      <c r="V29" s="17"/>
-      <c r="W29" s="17"/>
-      <c r="X29" s="17"/>
-      <c r="Y29" s="17"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="18"/>
+      <c r="J29" s="18"/>
+      <c r="K29" s="18"/>
+      <c r="L29" s="18"/>
+      <c r="M29" s="18"/>
+      <c r="N29" s="18"/>
+      <c r="O29" s="18"/>
+      <c r="P29" s="18"/>
+      <c r="Q29" s="18"/>
+      <c r="R29" s="18"/>
+      <c r="S29" s="18"/>
+      <c r="T29" s="18"/>
+      <c r="U29" s="18"/>
+      <c r="V29" s="18"/>
+      <c r="W29" s="18"/>
+      <c r="X29" s="18"/>
+      <c r="Y29" s="18"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="15" t="s">
+      <c r="A30" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="B30" s="16">
+      <c r="B30" s="17">
         <v>0.0</v>
       </c>
-      <c r="C30" s="17" t="s">
+      <c r="C30" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="D30" s="17" t="s">
+      <c r="D30" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="E30" s="17" t="s">
+      <c r="E30" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="17"/>
-      <c r="I30" s="17"/>
-      <c r="J30" s="17"/>
-      <c r="K30" s="17"/>
-      <c r="L30" s="17"/>
-      <c r="M30" s="17"/>
-      <c r="N30" s="17"/>
-      <c r="O30" s="17"/>
-      <c r="P30" s="17"/>
-      <c r="Q30" s="17"/>
-      <c r="R30" s="17"/>
-      <c r="S30" s="17"/>
-      <c r="T30" s="17"/>
-      <c r="U30" s="17"/>
-      <c r="V30" s="17"/>
-      <c r="W30" s="17"/>
-      <c r="X30" s="17"/>
-      <c r="Y30" s="17"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="18"/>
+      <c r="J30" s="18"/>
+      <c r="K30" s="18"/>
+      <c r="L30" s="18"/>
+      <c r="M30" s="18"/>
+      <c r="N30" s="18"/>
+      <c r="O30" s="18"/>
+      <c r="P30" s="18"/>
+      <c r="Q30" s="18"/>
+      <c r="R30" s="18"/>
+      <c r="S30" s="18"/>
+      <c r="T30" s="18"/>
+      <c r="U30" s="18"/>
+      <c r="V30" s="18"/>
+      <c r="W30" s="18"/>
+      <c r="X30" s="18"/>
+      <c r="Y30" s="18"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="15" t="s">
+      <c r="A31" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="B31" s="16">
+      <c r="B31" s="17">
         <v>0.0</v>
       </c>
-      <c r="C31" s="17" t="s">
+      <c r="C31" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="D31" s="17" t="s">
+      <c r="D31" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="E31" s="17" t="s">
+      <c r="E31" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="17"/>
-      <c r="I31" s="17"/>
-      <c r="J31" s="17"/>
-      <c r="K31" s="17"/>
-      <c r="L31" s="17"/>
-      <c r="M31" s="17"/>
-      <c r="N31" s="17"/>
-      <c r="O31" s="17"/>
-      <c r="P31" s="17"/>
-      <c r="Q31" s="17"/>
-      <c r="R31" s="17"/>
-      <c r="S31" s="17"/>
-      <c r="T31" s="17"/>
-      <c r="U31" s="17"/>
-      <c r="V31" s="17"/>
-      <c r="W31" s="17"/>
-      <c r="X31" s="17"/>
-      <c r="Y31" s="17"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="18"/>
+      <c r="J31" s="18"/>
+      <c r="K31" s="18"/>
+      <c r="L31" s="18"/>
+      <c r="M31" s="18"/>
+      <c r="N31" s="18"/>
+      <c r="O31" s="18"/>
+      <c r="P31" s="18"/>
+      <c r="Q31" s="18"/>
+      <c r="R31" s="18"/>
+      <c r="S31" s="18"/>
+      <c r="T31" s="18"/>
+      <c r="U31" s="18"/>
+      <c r="V31" s="18"/>
+      <c r="W31" s="18"/>
+      <c r="X31" s="18"/>
+      <c r="Y31" s="18"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="15" t="s">
+      <c r="A32" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="B32" s="16">
+      <c r="B32" s="17">
         <v>0.0</v>
       </c>
-      <c r="C32" s="17" t="s">
+      <c r="C32" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="D32" s="17" t="s">
+      <c r="D32" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="E32" s="17" t="s">
+      <c r="E32" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="F32" s="17"/>
-      <c r="G32" s="17"/>
-      <c r="H32" s="17"/>
-      <c r="I32" s="17"/>
-      <c r="J32" s="17"/>
-      <c r="K32" s="17"/>
-      <c r="L32" s="17"/>
-      <c r="M32" s="17"/>
-      <c r="N32" s="17"/>
-      <c r="O32" s="17"/>
-      <c r="P32" s="17"/>
-      <c r="Q32" s="17"/>
-      <c r="R32" s="17"/>
-      <c r="S32" s="17"/>
-      <c r="T32" s="17"/>
-      <c r="U32" s="17"/>
-      <c r="V32" s="17"/>
-      <c r="W32" s="17"/>
-      <c r="X32" s="17"/>
-      <c r="Y32" s="17"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="18"/>
+      <c r="K32" s="18"/>
+      <c r="L32" s="18"/>
+      <c r="M32" s="18"/>
+      <c r="N32" s="18"/>
+      <c r="O32" s="18"/>
+      <c r="P32" s="18"/>
+      <c r="Q32" s="18"/>
+      <c r="R32" s="18"/>
+      <c r="S32" s="18"/>
+      <c r="T32" s="18"/>
+      <c r="U32" s="18"/>
+      <c r="V32" s="18"/>
+      <c r="W32" s="18"/>
+      <c r="X32" s="18"/>
+      <c r="Y32" s="18"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="15" t="s">
+      <c r="A33" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="B33" s="16">
+      <c r="B33" s="17">
         <v>0.0</v>
       </c>
-      <c r="C33" s="17" t="s">
+      <c r="C33" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="D33" s="17" t="s">
+      <c r="D33" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="E33" s="17" t="s">
+      <c r="E33" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="17"/>
-      <c r="I33" s="17"/>
-      <c r="J33" s="17"/>
-      <c r="K33" s="17"/>
-      <c r="L33" s="17"/>
-      <c r="M33" s="17"/>
-      <c r="N33" s="17"/>
-      <c r="O33" s="17"/>
-      <c r="P33" s="17"/>
-      <c r="Q33" s="17"/>
-      <c r="R33" s="17"/>
-      <c r="S33" s="17"/>
-      <c r="T33" s="17"/>
-      <c r="U33" s="17"/>
-      <c r="V33" s="17"/>
-      <c r="W33" s="17"/>
-      <c r="X33" s="17"/>
-      <c r="Y33" s="17"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="18"/>
+      <c r="I33" s="18"/>
+      <c r="J33" s="18"/>
+      <c r="K33" s="18"/>
+      <c r="L33" s="18"/>
+      <c r="M33" s="18"/>
+      <c r="N33" s="18"/>
+      <c r="O33" s="18"/>
+      <c r="P33" s="18"/>
+      <c r="Q33" s="18"/>
+      <c r="R33" s="18"/>
+      <c r="S33" s="18"/>
+      <c r="T33" s="18"/>
+      <c r="U33" s="18"/>
+      <c r="V33" s="18"/>
+      <c r="W33" s="18"/>
+      <c r="X33" s="18"/>
+      <c r="Y33" s="18"/>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="15" t="s">
+      <c r="A34" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="B34" s="16">
+      <c r="B34" s="17">
         <v>0.0</v>
       </c>
-      <c r="C34" s="17" t="s">
+      <c r="C34" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="D34" s="17" t="s">
+      <c r="D34" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="E34" s="17" t="s">
+      <c r="E34" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="F34" s="17"/>
-      <c r="G34" s="17"/>
-      <c r="H34" s="17"/>
-      <c r="I34" s="17"/>
-      <c r="J34" s="17"/>
-      <c r="K34" s="17"/>
-      <c r="L34" s="17"/>
-      <c r="M34" s="17"/>
-      <c r="N34" s="17"/>
-      <c r="O34" s="17"/>
-      <c r="P34" s="17"/>
-      <c r="Q34" s="17"/>
-      <c r="R34" s="17"/>
-      <c r="S34" s="17"/>
-      <c r="T34" s="17"/>
-      <c r="U34" s="17"/>
-      <c r="V34" s="17"/>
-      <c r="W34" s="17"/>
-      <c r="X34" s="17"/>
-      <c r="Y34" s="17"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18"/>
+      <c r="I34" s="18"/>
+      <c r="J34" s="18"/>
+      <c r="K34" s="18"/>
+      <c r="L34" s="18"/>
+      <c r="M34" s="18"/>
+      <c r="N34" s="18"/>
+      <c r="O34" s="18"/>
+      <c r="P34" s="18"/>
+      <c r="Q34" s="18"/>
+      <c r="R34" s="18"/>
+      <c r="S34" s="18"/>
+      <c r="T34" s="18"/>
+      <c r="U34" s="18"/>
+      <c r="V34" s="18"/>
+      <c r="W34" s="18"/>
+      <c r="X34" s="18"/>
+      <c r="Y34" s="18"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="15" t="s">
+      <c r="A35" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="B35" s="16">
+      <c r="B35" s="17">
         <v>0.0</v>
       </c>
-      <c r="C35" s="17" t="s">
+      <c r="C35" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="D35" s="17" t="s">
+      <c r="D35" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="E35" s="17" t="s">
+      <c r="E35" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="F35" s="17"/>
-      <c r="G35" s="17"/>
-      <c r="H35" s="17"/>
-      <c r="I35" s="17"/>
-      <c r="J35" s="17"/>
-      <c r="K35" s="17"/>
-      <c r="L35" s="17"/>
-      <c r="M35" s="17"/>
-      <c r="N35" s="17"/>
-      <c r="O35" s="17"/>
-      <c r="P35" s="17"/>
-      <c r="Q35" s="17"/>
-      <c r="R35" s="17"/>
-      <c r="S35" s="17"/>
-      <c r="T35" s="17"/>
-      <c r="U35" s="17"/>
-      <c r="V35" s="17"/>
-      <c r="W35" s="17"/>
-      <c r="X35" s="17"/>
-      <c r="Y35" s="17"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="18"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="18"/>
+      <c r="J35" s="18"/>
+      <c r="K35" s="18"/>
+      <c r="L35" s="18"/>
+      <c r="M35" s="18"/>
+      <c r="N35" s="18"/>
+      <c r="O35" s="18"/>
+      <c r="P35" s="18"/>
+      <c r="Q35" s="18"/>
+      <c r="R35" s="18"/>
+      <c r="S35" s="18"/>
+      <c r="T35" s="18"/>
+      <c r="U35" s="18"/>
+      <c r="V35" s="18"/>
+      <c r="W35" s="18"/>
+      <c r="X35" s="18"/>
+      <c r="Y35" s="18"/>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="15" t="s">
+      <c r="A36" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="B36" s="16">
+      <c r="B36" s="17">
         <v>0.0</v>
       </c>
-      <c r="C36" s="17" t="s">
+      <c r="C36" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="D36" s="17" t="s">
+      <c r="D36" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="E36" s="17" t="s">
+      <c r="E36" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="F36" s="17"/>
-      <c r="G36" s="17"/>
-      <c r="H36" s="17"/>
-      <c r="I36" s="17"/>
-      <c r="J36" s="17"/>
-      <c r="K36" s="17"/>
-      <c r="L36" s="17"/>
-      <c r="M36" s="17"/>
-      <c r="N36" s="17"/>
-      <c r="O36" s="17"/>
-      <c r="P36" s="17"/>
-      <c r="Q36" s="17"/>
-      <c r="R36" s="17"/>
-      <c r="S36" s="17"/>
-      <c r="T36" s="17"/>
-      <c r="U36" s="17"/>
-      <c r="V36" s="17"/>
-      <c r="W36" s="17"/>
-      <c r="X36" s="17"/>
-      <c r="Y36" s="17"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
+      <c r="H36" s="18"/>
+      <c r="I36" s="18"/>
+      <c r="J36" s="18"/>
+      <c r="K36" s="18"/>
+      <c r="L36" s="18"/>
+      <c r="M36" s="18"/>
+      <c r="N36" s="18"/>
+      <c r="O36" s="18"/>
+      <c r="P36" s="18"/>
+      <c r="Q36" s="18"/>
+      <c r="R36" s="18"/>
+      <c r="S36" s="18"/>
+      <c r="T36" s="18"/>
+      <c r="U36" s="18"/>
+      <c r="V36" s="18"/>
+      <c r="W36" s="18"/>
+      <c r="X36" s="18"/>
+      <c r="Y36" s="18"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="15" t="s">
+      <c r="A37" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="B37" s="16">
+      <c r="B37" s="17">
         <v>0.0</v>
       </c>
-      <c r="C37" s="17" t="s">
+      <c r="C37" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="D37" s="17" t="s">
+      <c r="D37" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="E37" s="17" t="s">
+      <c r="E37" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="F37" s="17"/>
-      <c r="G37" s="17"/>
-      <c r="H37" s="17"/>
-      <c r="I37" s="17"/>
-      <c r="J37" s="17"/>
-      <c r="K37" s="17"/>
-      <c r="L37" s="17"/>
-      <c r="M37" s="17"/>
-      <c r="N37" s="17"/>
-      <c r="O37" s="17"/>
-      <c r="P37" s="17"/>
-      <c r="Q37" s="17"/>
-      <c r="R37" s="17"/>
-      <c r="S37" s="17"/>
-      <c r="T37" s="17"/>
-      <c r="U37" s="17"/>
-      <c r="V37" s="17"/>
-      <c r="W37" s="17"/>
-      <c r="X37" s="17"/>
-      <c r="Y37" s="17"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="18"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="18"/>
+      <c r="J37" s="18"/>
+      <c r="K37" s="18"/>
+      <c r="L37" s="18"/>
+      <c r="M37" s="18"/>
+      <c r="N37" s="18"/>
+      <c r="O37" s="18"/>
+      <c r="P37" s="18"/>
+      <c r="Q37" s="18"/>
+      <c r="R37" s="18"/>
+      <c r="S37" s="18"/>
+      <c r="T37" s="18"/>
+      <c r="U37" s="18"/>
+      <c r="V37" s="18"/>
+      <c r="W37" s="18"/>
+      <c r="X37" s="18"/>
+      <c r="Y37" s="18"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="15" t="s">
+      <c r="A38" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="B38" s="16">
+      <c r="B38" s="17">
         <v>0.0</v>
       </c>
-      <c r="C38" s="17" t="s">
+      <c r="C38" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="D38" s="17" t="s">
+      <c r="D38" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="E38" s="17" t="s">
+      <c r="E38" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="F38" s="17"/>
-      <c r="G38" s="17"/>
-      <c r="H38" s="17"/>
-      <c r="I38" s="17"/>
-      <c r="J38" s="17"/>
-      <c r="K38" s="17"/>
-      <c r="L38" s="17"/>
-      <c r="M38" s="17"/>
-      <c r="N38" s="17"/>
-      <c r="O38" s="17"/>
-      <c r="P38" s="17"/>
-      <c r="Q38" s="17"/>
-      <c r="R38" s="17"/>
-      <c r="S38" s="17"/>
-      <c r="T38" s="17"/>
-      <c r="U38" s="17"/>
-      <c r="V38" s="17"/>
-      <c r="W38" s="17"/>
-      <c r="X38" s="17"/>
-      <c r="Y38" s="17"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="18"/>
+      <c r="J38" s="18"/>
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
+      <c r="M38" s="18"/>
+      <c r="N38" s="18"/>
+      <c r="O38" s="18"/>
+      <c r="P38" s="18"/>
+      <c r="Q38" s="18"/>
+      <c r="R38" s="18"/>
+      <c r="S38" s="18"/>
+      <c r="T38" s="18"/>
+      <c r="U38" s="18"/>
+      <c r="V38" s="18"/>
+      <c r="W38" s="18"/>
+      <c r="X38" s="18"/>
+      <c r="Y38" s="18"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="15" t="s">
+      <c r="A39" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="B39" s="16">
+      <c r="B39" s="17">
         <v>0.0</v>
       </c>
-      <c r="C39" s="17" t="s">
+      <c r="C39" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="D39" s="17" t="s">
+      <c r="D39" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="E39" s="17" t="s">
+      <c r="E39" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="F39" s="17"/>
-      <c r="G39" s="17"/>
-      <c r="H39" s="17"/>
-      <c r="I39" s="17"/>
-      <c r="J39" s="17"/>
-      <c r="K39" s="17"/>
-      <c r="L39" s="17"/>
-      <c r="M39" s="17"/>
-      <c r="N39" s="17"/>
-      <c r="O39" s="17"/>
-      <c r="P39" s="17"/>
-      <c r="Q39" s="17"/>
-      <c r="R39" s="17"/>
-      <c r="S39" s="17"/>
-      <c r="T39" s="17"/>
-      <c r="U39" s="17"/>
-      <c r="V39" s="17"/>
-      <c r="W39" s="17"/>
-      <c r="X39" s="17"/>
-      <c r="Y39" s="17"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="18"/>
+      <c r="H39" s="18"/>
+      <c r="I39" s="18"/>
+      <c r="J39" s="18"/>
+      <c r="K39" s="18"/>
+      <c r="L39" s="18"/>
+      <c r="M39" s="18"/>
+      <c r="N39" s="18"/>
+      <c r="O39" s="18"/>
+      <c r="P39" s="18"/>
+      <c r="Q39" s="18"/>
+      <c r="R39" s="18"/>
+      <c r="S39" s="18"/>
+      <c r="T39" s="18"/>
+      <c r="U39" s="18"/>
+      <c r="V39" s="18"/>
+      <c r="W39" s="18"/>
+      <c r="X39" s="18"/>
+      <c r="Y39" s="18"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="15" t="s">
+      <c r="A40" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B40" s="16">
+      <c r="B40" s="17">
         <v>0.0</v>
       </c>
-      <c r="C40" s="17" t="s">
+      <c r="C40" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="D40" s="17" t="s">
+      <c r="D40" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="E40" s="17" t="s">
+      <c r="E40" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="F40" s="17"/>
-      <c r="G40" s="17"/>
-      <c r="H40" s="17"/>
-      <c r="I40" s="17"/>
-      <c r="J40" s="17"/>
-      <c r="K40" s="17"/>
-      <c r="L40" s="17"/>
-      <c r="M40" s="17"/>
-      <c r="N40" s="17"/>
-      <c r="O40" s="17"/>
-      <c r="P40" s="17"/>
-      <c r="Q40" s="17"/>
-      <c r="R40" s="17"/>
-      <c r="S40" s="17"/>
-      <c r="T40" s="17"/>
-      <c r="U40" s="17"/>
-      <c r="V40" s="17"/>
-      <c r="W40" s="17"/>
-      <c r="X40" s="17"/>
-      <c r="Y40" s="17"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
+      <c r="I40" s="18"/>
+      <c r="J40" s="18"/>
+      <c r="K40" s="18"/>
+      <c r="L40" s="18"/>
+      <c r="M40" s="18"/>
+      <c r="N40" s="18"/>
+      <c r="O40" s="18"/>
+      <c r="P40" s="18"/>
+      <c r="Q40" s="18"/>
+      <c r="R40" s="18"/>
+      <c r="S40" s="18"/>
+      <c r="T40" s="18"/>
+      <c r="U40" s="18"/>
+      <c r="V40" s="18"/>
+      <c r="W40" s="18"/>
+      <c r="X40" s="18"/>
+      <c r="Y40" s="18"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="15" t="s">
+      <c r="A41" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="B41" s="16">
+      <c r="B41" s="17">
         <v>0.0</v>
       </c>
-      <c r="C41" s="17" t="s">
+      <c r="C41" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="D41" s="17" t="s">
+      <c r="D41" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="E41" s="17" t="s">
+      <c r="E41" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="F41" s="17"/>
-      <c r="G41" s="17"/>
-      <c r="H41" s="17"/>
-      <c r="I41" s="17"/>
-      <c r="J41" s="17"/>
-      <c r="K41" s="17"/>
-      <c r="L41" s="17"/>
-      <c r="M41" s="17"/>
-      <c r="N41" s="17"/>
-      <c r="O41" s="17"/>
-      <c r="P41" s="17"/>
-      <c r="Q41" s="17"/>
-      <c r="R41" s="17"/>
-      <c r="S41" s="17"/>
-      <c r="T41" s="17"/>
-      <c r="U41" s="17"/>
-      <c r="V41" s="17"/>
-      <c r="W41" s="17"/>
-      <c r="X41" s="17"/>
-      <c r="Y41" s="17"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
+      <c r="I41" s="18"/>
+      <c r="J41" s="18"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="18"/>
+      <c r="M41" s="18"/>
+      <c r="N41" s="18"/>
+      <c r="O41" s="18"/>
+      <c r="P41" s="18"/>
+      <c r="Q41" s="18"/>
+      <c r="R41" s="18"/>
+      <c r="S41" s="18"/>
+      <c r="T41" s="18"/>
+      <c r="U41" s="18"/>
+      <c r="V41" s="18"/>
+      <c r="W41" s="18"/>
+      <c r="X41" s="18"/>
+      <c r="Y41" s="18"/>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="15" t="s">
+      <c r="A42" s="16" t="s">
         <v>157</v>
       </c>
-      <c r="B42" s="16">
+      <c r="B42" s="17">
         <v>0.0</v>
       </c>
-      <c r="C42" s="17" t="s">
+      <c r="C42" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="D42" s="17" t="s">
+      <c r="D42" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="E42" s="17" t="s">
+      <c r="E42" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="F42" s="17"/>
-      <c r="G42" s="17"/>
-      <c r="H42" s="17"/>
-      <c r="I42" s="17"/>
-      <c r="J42" s="17"/>
-      <c r="K42" s="17"/>
-      <c r="L42" s="17"/>
-      <c r="M42" s="17"/>
-      <c r="N42" s="17"/>
-      <c r="O42" s="17"/>
-      <c r="P42" s="17"/>
-      <c r="Q42" s="17"/>
-      <c r="R42" s="17"/>
-      <c r="S42" s="17"/>
-      <c r="T42" s="17"/>
-      <c r="U42" s="17"/>
-      <c r="V42" s="17"/>
-      <c r="W42" s="17"/>
-      <c r="X42" s="17"/>
-      <c r="Y42" s="17"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="18"/>
+      <c r="H42" s="18"/>
+      <c r="I42" s="18"/>
+      <c r="J42" s="18"/>
+      <c r="K42" s="18"/>
+      <c r="L42" s="18"/>
+      <c r="M42" s="18"/>
+      <c r="N42" s="18"/>
+      <c r="O42" s="18"/>
+      <c r="P42" s="18"/>
+      <c r="Q42" s="18"/>
+      <c r="R42" s="18"/>
+      <c r="S42" s="18"/>
+      <c r="T42" s="18"/>
+      <c r="U42" s="18"/>
+      <c r="V42" s="18"/>
+      <c r="W42" s="18"/>
+      <c r="X42" s="18"/>
+      <c r="Y42" s="18"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="15" t="s">
+      <c r="A43" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="B43" s="16">
+      <c r="B43" s="17">
         <v>0.0</v>
       </c>
-      <c r="C43" s="17" t="s">
+      <c r="C43" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="D43" s="17" t="s">
+      <c r="D43" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="E43" s="17" t="s">
+      <c r="E43" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="F43" s="17"/>
-      <c r="G43" s="17"/>
-      <c r="H43" s="17"/>
-      <c r="I43" s="17"/>
-      <c r="J43" s="17"/>
-      <c r="K43" s="17"/>
-      <c r="L43" s="17"/>
-      <c r="M43" s="17"/>
-      <c r="N43" s="17"/>
-      <c r="O43" s="17"/>
-      <c r="P43" s="17"/>
-      <c r="Q43" s="17"/>
-      <c r="R43" s="17"/>
-      <c r="S43" s="17"/>
-      <c r="T43" s="17"/>
-      <c r="U43" s="17"/>
-      <c r="V43" s="17"/>
-      <c r="W43" s="17"/>
-      <c r="X43" s="17"/>
-      <c r="Y43" s="17"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="18"/>
+      <c r="H43" s="18"/>
+      <c r="I43" s="18"/>
+      <c r="J43" s="18"/>
+      <c r="K43" s="18"/>
+      <c r="L43" s="18"/>
+      <c r="M43" s="18"/>
+      <c r="N43" s="18"/>
+      <c r="O43" s="18"/>
+      <c r="P43" s="18"/>
+      <c r="Q43" s="18"/>
+      <c r="R43" s="18"/>
+      <c r="S43" s="18"/>
+      <c r="T43" s="18"/>
+      <c r="U43" s="18"/>
+      <c r="V43" s="18"/>
+      <c r="W43" s="18"/>
+      <c r="X43" s="18"/>
+      <c r="Y43" s="18"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="15" t="s">
+      <c r="A44" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="B44" s="16">
+      <c r="B44" s="17">
         <v>0.0</v>
       </c>
-      <c r="C44" s="17" t="s">
+      <c r="C44" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="D44" s="17" t="s">
+      <c r="D44" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="E44" s="17" t="s">
+      <c r="E44" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="F44" s="17"/>
-      <c r="G44" s="17"/>
-      <c r="H44" s="17"/>
-      <c r="I44" s="17"/>
-      <c r="J44" s="17"/>
-      <c r="K44" s="17"/>
-      <c r="L44" s="17"/>
-      <c r="M44" s="17"/>
-      <c r="N44" s="17"/>
-      <c r="O44" s="17"/>
-      <c r="P44" s="17"/>
-      <c r="Q44" s="17"/>
-      <c r="R44" s="17"/>
-      <c r="S44" s="17"/>
-      <c r="T44" s="17"/>
-      <c r="U44" s="17"/>
-      <c r="V44" s="17"/>
-      <c r="W44" s="17"/>
-      <c r="X44" s="17"/>
-      <c r="Y44" s="17"/>
+      <c r="F44" s="18"/>
+      <c r="G44" s="18"/>
+      <c r="H44" s="18"/>
+      <c r="I44" s="18"/>
+      <c r="J44" s="18"/>
+      <c r="K44" s="18"/>
+      <c r="L44" s="18"/>
+      <c r="M44" s="18"/>
+      <c r="N44" s="18"/>
+      <c r="O44" s="18"/>
+      <c r="P44" s="18"/>
+      <c r="Q44" s="18"/>
+      <c r="R44" s="18"/>
+      <c r="S44" s="18"/>
+      <c r="T44" s="18"/>
+      <c r="U44" s="18"/>
+      <c r="V44" s="18"/>
+      <c r="W44" s="18"/>
+      <c r="X44" s="18"/>
+      <c r="Y44" s="18"/>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="15" t="s">
+      <c r="A45" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="B45" s="16">
+      <c r="B45" s="17">
         <v>0.0</v>
       </c>
-      <c r="C45" s="17" t="s">
+      <c r="C45" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="D45" s="17" t="s">
+      <c r="D45" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="E45" s="17" t="s">
+      <c r="E45" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="F45" s="17"/>
-      <c r="G45" s="17"/>
-      <c r="H45" s="17"/>
-      <c r="I45" s="17"/>
-      <c r="J45" s="17"/>
-      <c r="K45" s="17"/>
-      <c r="L45" s="17"/>
-      <c r="M45" s="17"/>
-      <c r="N45" s="17"/>
-      <c r="O45" s="17"/>
-      <c r="P45" s="17"/>
-      <c r="Q45" s="17"/>
-      <c r="R45" s="17"/>
-      <c r="S45" s="17"/>
-      <c r="T45" s="17"/>
-      <c r="U45" s="17"/>
-      <c r="V45" s="17"/>
-      <c r="W45" s="17"/>
-      <c r="X45" s="17"/>
-      <c r="Y45" s="17"/>
+      <c r="F45" s="18"/>
+      <c r="G45" s="18"/>
+      <c r="H45" s="18"/>
+      <c r="I45" s="18"/>
+      <c r="J45" s="18"/>
+      <c r="K45" s="18"/>
+      <c r="L45" s="18"/>
+      <c r="M45" s="18"/>
+      <c r="N45" s="18"/>
+      <c r="O45" s="18"/>
+      <c r="P45" s="18"/>
+      <c r="Q45" s="18"/>
+      <c r="R45" s="18"/>
+      <c r="S45" s="18"/>
+      <c r="T45" s="18"/>
+      <c r="U45" s="18"/>
+      <c r="V45" s="18"/>
+      <c r="W45" s="18"/>
+      <c r="X45" s="18"/>
+      <c r="Y45" s="18"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="15" t="s">
+      <c r="A46" s="16" t="s">
         <v>173</v>
       </c>
-      <c r="B46" s="16">
+      <c r="B46" s="17">
         <v>0.0</v>
       </c>
-      <c r="C46" s="17" t="s">
+      <c r="C46" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="D46" s="17" t="s">
+      <c r="D46" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="E46" s="17" t="s">
+      <c r="E46" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="F46" s="17"/>
-      <c r="G46" s="17"/>
-      <c r="H46" s="17"/>
-      <c r="I46" s="17"/>
-      <c r="J46" s="17"/>
-      <c r="K46" s="17"/>
-      <c r="L46" s="17"/>
-      <c r="M46" s="17"/>
-      <c r="N46" s="17"/>
-      <c r="O46" s="17"/>
-      <c r="P46" s="17"/>
-      <c r="Q46" s="17"/>
-      <c r="R46" s="17"/>
-      <c r="S46" s="17"/>
-      <c r="T46" s="17"/>
-      <c r="U46" s="17"/>
-      <c r="V46" s="17"/>
-      <c r="W46" s="17"/>
-      <c r="X46" s="17"/>
-      <c r="Y46" s="17"/>
+      <c r="F46" s="18"/>
+      <c r="G46" s="18"/>
+      <c r="H46" s="18"/>
+      <c r="I46" s="18"/>
+      <c r="J46" s="18"/>
+      <c r="K46" s="18"/>
+      <c r="L46" s="18"/>
+      <c r="M46" s="18"/>
+      <c r="N46" s="18"/>
+      <c r="O46" s="18"/>
+      <c r="P46" s="18"/>
+      <c r="Q46" s="18"/>
+      <c r="R46" s="18"/>
+      <c r="S46" s="18"/>
+      <c r="T46" s="18"/>
+      <c r="U46" s="18"/>
+      <c r="V46" s="18"/>
+      <c r="W46" s="18"/>
+      <c r="X46" s="18"/>
+      <c r="Y46" s="18"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="15" t="s">
+      <c r="A47" s="16" t="s">
         <v>177</v>
       </c>
-      <c r="B47" s="16">
+      <c r="B47" s="17">
         <v>0.0</v>
       </c>
-      <c r="C47" s="17" t="s">
+      <c r="C47" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="D47" s="17" t="s">
+      <c r="D47" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="E47" s="17" t="s">
+      <c r="E47" s="18" t="s">
         <v>180</v>
       </c>
-      <c r="F47" s="17"/>
-      <c r="G47" s="17"/>
-      <c r="H47" s="17"/>
-      <c r="I47" s="17"/>
-      <c r="J47" s="17"/>
-      <c r="K47" s="17"/>
-      <c r="L47" s="17"/>
-      <c r="M47" s="17"/>
-      <c r="N47" s="17"/>
-      <c r="O47" s="17"/>
-      <c r="P47" s="17"/>
-      <c r="Q47" s="17"/>
-      <c r="R47" s="17"/>
-      <c r="S47" s="17"/>
-      <c r="T47" s="17"/>
-      <c r="U47" s="17"/>
-      <c r="V47" s="17"/>
-      <c r="W47" s="17"/>
-      <c r="X47" s="17"/>
-      <c r="Y47" s="17"/>
+      <c r="F47" s="18"/>
+      <c r="G47" s="18"/>
+      <c r="H47" s="18"/>
+      <c r="I47" s="18"/>
+      <c r="J47" s="18"/>
+      <c r="K47" s="18"/>
+      <c r="L47" s="18"/>
+      <c r="M47" s="18"/>
+      <c r="N47" s="18"/>
+      <c r="O47" s="18"/>
+      <c r="P47" s="18"/>
+      <c r="Q47" s="18"/>
+      <c r="R47" s="18"/>
+      <c r="S47" s="18"/>
+      <c r="T47" s="18"/>
+      <c r="U47" s="18"/>
+      <c r="V47" s="18"/>
+      <c r="W47" s="18"/>
+      <c r="X47" s="18"/>
+      <c r="Y47" s="18"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="15" t="s">
+      <c r="A48" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="B48" s="16">
+      <c r="B48" s="17">
         <v>0.0</v>
       </c>
-      <c r="C48" s="17" t="s">
+      <c r="C48" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="D48" s="17" t="s">
+      <c r="D48" s="18" t="s">
         <v>183</v>
       </c>
-      <c r="E48" s="17" t="s">
+      <c r="E48" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="F48" s="17"/>
-      <c r="G48" s="17"/>
-      <c r="H48" s="17"/>
-      <c r="I48" s="17"/>
-      <c r="J48" s="17"/>
-      <c r="K48" s="17"/>
-      <c r="L48" s="17"/>
-      <c r="M48" s="17"/>
-      <c r="N48" s="17"/>
-      <c r="O48" s="17"/>
-      <c r="P48" s="17"/>
-      <c r="Q48" s="17"/>
-      <c r="R48" s="17"/>
-      <c r="S48" s="17"/>
-      <c r="T48" s="17"/>
-      <c r="U48" s="17"/>
-      <c r="V48" s="17"/>
-      <c r="W48" s="17"/>
-      <c r="X48" s="17"/>
-      <c r="Y48" s="17"/>
+      <c r="F48" s="18"/>
+      <c r="G48" s="18"/>
+      <c r="H48" s="18"/>
+      <c r="I48" s="18"/>
+      <c r="J48" s="18"/>
+      <c r="K48" s="18"/>
+      <c r="L48" s="18"/>
+      <c r="M48" s="18"/>
+      <c r="N48" s="18"/>
+      <c r="O48" s="18"/>
+      <c r="P48" s="18"/>
+      <c r="Q48" s="18"/>
+      <c r="R48" s="18"/>
+      <c r="S48" s="18"/>
+      <c r="T48" s="18"/>
+      <c r="U48" s="18"/>
+      <c r="V48" s="18"/>
+      <c r="W48" s="18"/>
+      <c r="X48" s="18"/>
+      <c r="Y48" s="18"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="15" t="s">
+      <c r="A49" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="B49" s="16">
+      <c r="B49" s="17">
         <v>0.0</v>
       </c>
-      <c r="C49" s="17" t="s">
+      <c r="C49" s="18" t="s">
         <v>186</v>
       </c>
-      <c r="D49" s="17" t="s">
+      <c r="D49" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="E49" s="17" t="s">
+      <c r="E49" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="F49" s="17"/>
-      <c r="G49" s="17"/>
-      <c r="H49" s="17"/>
-      <c r="I49" s="17"/>
-      <c r="J49" s="17"/>
-      <c r="K49" s="17"/>
-      <c r="L49" s="17"/>
-      <c r="M49" s="17"/>
-      <c r="N49" s="17"/>
-      <c r="O49" s="17"/>
-      <c r="P49" s="17"/>
-      <c r="Q49" s="17"/>
-      <c r="R49" s="17"/>
-      <c r="S49" s="17"/>
-      <c r="T49" s="17"/>
-      <c r="U49" s="17"/>
-      <c r="V49" s="17"/>
-      <c r="W49" s="17"/>
-      <c r="X49" s="17"/>
-      <c r="Y49" s="17"/>
+      <c r="F49" s="18"/>
+      <c r="G49" s="18"/>
+      <c r="H49" s="18"/>
+      <c r="I49" s="18"/>
+      <c r="J49" s="18"/>
+      <c r="K49" s="18"/>
+      <c r="L49" s="18"/>
+      <c r="M49" s="18"/>
+      <c r="N49" s="18"/>
+      <c r="O49" s="18"/>
+      <c r="P49" s="18"/>
+      <c r="Q49" s="18"/>
+      <c r="R49" s="18"/>
+      <c r="S49" s="18"/>
+      <c r="T49" s="18"/>
+      <c r="U49" s="18"/>
+      <c r="V49" s="18"/>
+      <c r="W49" s="18"/>
+      <c r="X49" s="18"/>
+      <c r="Y49" s="18"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="15" t="s">
+      <c r="A50" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="B50" s="16">
+      <c r="B50" s="17">
         <v>0.0</v>
       </c>
-      <c r="C50" s="17" t="s">
+      <c r="C50" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="D50" s="17" t="s">
+      <c r="D50" s="18" t="s">
         <v>191</v>
       </c>
-      <c r="E50" s="17" t="s">
+      <c r="E50" s="18" t="s">
         <v>192</v>
       </c>
-      <c r="F50" s="17"/>
-      <c r="G50" s="17"/>
-      <c r="H50" s="17"/>
-      <c r="I50" s="17"/>
-      <c r="J50" s="17"/>
-      <c r="K50" s="17"/>
-      <c r="L50" s="17"/>
-      <c r="M50" s="17"/>
-      <c r="N50" s="17"/>
-      <c r="O50" s="17"/>
-      <c r="P50" s="17"/>
-      <c r="Q50" s="17"/>
-      <c r="R50" s="17"/>
-      <c r="S50" s="17"/>
-      <c r="T50" s="17"/>
-      <c r="U50" s="17"/>
-      <c r="V50" s="17"/>
-      <c r="W50" s="17"/>
-      <c r="X50" s="17"/>
-      <c r="Y50" s="17"/>
+      <c r="F50" s="18"/>
+      <c r="G50" s="18"/>
+      <c r="H50" s="18"/>
+      <c r="I50" s="18"/>
+      <c r="J50" s="18"/>
+      <c r="K50" s="18"/>
+      <c r="L50" s="18"/>
+      <c r="M50" s="18"/>
+      <c r="N50" s="18"/>
+      <c r="O50" s="18"/>
+      <c r="P50" s="18"/>
+      <c r="Q50" s="18"/>
+      <c r="R50" s="18"/>
+      <c r="S50" s="18"/>
+      <c r="T50" s="18"/>
+      <c r="U50" s="18"/>
+      <c r="V50" s="18"/>
+      <c r="W50" s="18"/>
+      <c r="X50" s="18"/>
+      <c r="Y50" s="18"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="15" t="s">
+      <c r="A51" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="B51" s="16">
+      <c r="B51" s="17">
         <v>0.0</v>
       </c>
-      <c r="C51" s="17" t="s">
+      <c r="C51" s="18" t="s">
         <v>194</v>
       </c>
-      <c r="D51" s="17" t="s">
+      <c r="D51" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="E51" s="17" t="s">
+      <c r="E51" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="F51" s="17"/>
-      <c r="G51" s="17"/>
-      <c r="H51" s="17"/>
-      <c r="I51" s="17"/>
-      <c r="J51" s="17"/>
-      <c r="K51" s="17"/>
-      <c r="L51" s="17"/>
-      <c r="M51" s="17"/>
-      <c r="N51" s="17"/>
-      <c r="O51" s="17"/>
-      <c r="P51" s="17"/>
-      <c r="Q51" s="17"/>
-      <c r="R51" s="17"/>
-      <c r="S51" s="17"/>
-      <c r="T51" s="17"/>
-      <c r="U51" s="17"/>
-      <c r="V51" s="17"/>
-      <c r="W51" s="17"/>
-      <c r="X51" s="17"/>
-      <c r="Y51" s="17"/>
+      <c r="F51" s="18"/>
+      <c r="G51" s="18"/>
+      <c r="H51" s="18"/>
+      <c r="I51" s="18"/>
+      <c r="J51" s="18"/>
+      <c r="K51" s="18"/>
+      <c r="L51" s="18"/>
+      <c r="M51" s="18"/>
+      <c r="N51" s="18"/>
+      <c r="O51" s="18"/>
+      <c r="P51" s="18"/>
+      <c r="Q51" s="18"/>
+      <c r="R51" s="18"/>
+      <c r="S51" s="18"/>
+      <c r="T51" s="18"/>
+      <c r="U51" s="18"/>
+      <c r="V51" s="18"/>
+      <c r="W51" s="18"/>
+      <c r="X51" s="18"/>
+      <c r="Y51" s="18"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="15" t="s">
+      <c r="A52" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="B52" s="16">
+      <c r="B52" s="17">
         <v>0.0</v>
       </c>
-      <c r="C52" s="17" t="s">
+      <c r="C52" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="D52" s="17" t="s">
+      <c r="D52" s="18" t="s">
         <v>199</v>
       </c>
-      <c r="E52" s="17" t="s">
+      <c r="E52" s="18" t="s">
         <v>200</v>
       </c>
-      <c r="F52" s="17"/>
-      <c r="G52" s="17"/>
-      <c r="H52" s="17"/>
-      <c r="I52" s="17"/>
-      <c r="J52" s="17"/>
-      <c r="K52" s="17"/>
-      <c r="L52" s="17"/>
-      <c r="M52" s="17"/>
-      <c r="N52" s="17"/>
-      <c r="O52" s="17"/>
-      <c r="P52" s="17"/>
-      <c r="Q52" s="17"/>
-      <c r="R52" s="17"/>
-      <c r="S52" s="17"/>
-      <c r="T52" s="17"/>
-      <c r="U52" s="17"/>
-      <c r="V52" s="17"/>
-      <c r="W52" s="17"/>
-      <c r="X52" s="17"/>
-      <c r="Y52" s="17"/>
+      <c r="F52" s="18"/>
+      <c r="G52" s="18"/>
+      <c r="H52" s="18"/>
+      <c r="I52" s="18"/>
+      <c r="J52" s="18"/>
+      <c r="K52" s="18"/>
+      <c r="L52" s="18"/>
+      <c r="M52" s="18"/>
+      <c r="N52" s="18"/>
+      <c r="O52" s="18"/>
+      <c r="P52" s="18"/>
+      <c r="Q52" s="18"/>
+      <c r="R52" s="18"/>
+      <c r="S52" s="18"/>
+      <c r="T52" s="18"/>
+      <c r="U52" s="18"/>
+      <c r="V52" s="18"/>
+      <c r="W52" s="18"/>
+      <c r="X52" s="18"/>
+      <c r="Y52" s="18"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="15" t="s">
+      <c r="A53" s="16" t="s">
         <v>201</v>
       </c>
-      <c r="B53" s="16">
+      <c r="B53" s="17">
         <v>0.0</v>
       </c>
-      <c r="C53" s="17" t="s">
+      <c r="C53" s="18" t="s">
         <v>202</v>
       </c>
-      <c r="D53" s="17" t="s">
+      <c r="D53" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="E53" s="17" t="s">
+      <c r="E53" s="18" t="s">
         <v>204</v>
       </c>
-      <c r="F53" s="17"/>
-      <c r="G53" s="17"/>
-      <c r="H53" s="17"/>
-      <c r="I53" s="17"/>
-      <c r="J53" s="17"/>
-      <c r="K53" s="17"/>
-      <c r="L53" s="17"/>
-      <c r="M53" s="17"/>
-      <c r="N53" s="17"/>
-      <c r="O53" s="17"/>
-      <c r="P53" s="17"/>
-      <c r="Q53" s="17"/>
-      <c r="R53" s="17"/>
-      <c r="S53" s="17"/>
-      <c r="T53" s="17"/>
-      <c r="U53" s="17"/>
-      <c r="V53" s="17"/>
-      <c r="W53" s="17"/>
-      <c r="X53" s="17"/>
-      <c r="Y53" s="17"/>
+      <c r="F53" s="18"/>
+      <c r="G53" s="18"/>
+      <c r="H53" s="18"/>
+      <c r="I53" s="18"/>
+      <c r="J53" s="18"/>
+      <c r="K53" s="18"/>
+      <c r="L53" s="18"/>
+      <c r="M53" s="18"/>
+      <c r="N53" s="18"/>
+      <c r="O53" s="18"/>
+      <c r="P53" s="18"/>
+      <c r="Q53" s="18"/>
+      <c r="R53" s="18"/>
+      <c r="S53" s="18"/>
+      <c r="T53" s="18"/>
+      <c r="U53" s="18"/>
+      <c r="V53" s="18"/>
+      <c r="W53" s="18"/>
+      <c r="X53" s="18"/>
+      <c r="Y53" s="18"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="15" t="s">
+      <c r="A54" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="B54" s="16">
+      <c r="B54" s="17">
         <v>0.0</v>
       </c>
-      <c r="C54" s="17" t="s">
+      <c r="C54" s="18" t="s">
         <v>206</v>
       </c>
-      <c r="D54" s="17" t="s">
+      <c r="D54" s="18" t="s">
         <v>207</v>
       </c>
-      <c r="E54" s="17" t="s">
+      <c r="E54" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="F54" s="17"/>
-      <c r="G54" s="17"/>
-      <c r="H54" s="17"/>
-      <c r="I54" s="17"/>
-      <c r="J54" s="17"/>
-      <c r="K54" s="17"/>
-      <c r="L54" s="17"/>
-      <c r="M54" s="17"/>
-      <c r="N54" s="17"/>
-      <c r="O54" s="17"/>
-      <c r="P54" s="17"/>
-      <c r="Q54" s="17"/>
-      <c r="R54" s="17"/>
-      <c r="S54" s="17"/>
-      <c r="T54" s="17"/>
-      <c r="U54" s="17"/>
-      <c r="V54" s="17"/>
-      <c r="W54" s="17"/>
-      <c r="X54" s="17"/>
-      <c r="Y54" s="17"/>
+      <c r="F54" s="18"/>
+      <c r="G54" s="18"/>
+      <c r="H54" s="18"/>
+      <c r="I54" s="18"/>
+      <c r="J54" s="18"/>
+      <c r="K54" s="18"/>
+      <c r="L54" s="18"/>
+      <c r="M54" s="18"/>
+      <c r="N54" s="18"/>
+      <c r="O54" s="18"/>
+      <c r="P54" s="18"/>
+      <c r="Q54" s="18"/>
+      <c r="R54" s="18"/>
+      <c r="S54" s="18"/>
+      <c r="T54" s="18"/>
+      <c r="U54" s="18"/>
+      <c r="V54" s="18"/>
+      <c r="W54" s="18"/>
+      <c r="X54" s="18"/>
+      <c r="Y54" s="18"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="15" t="s">
+      <c r="A55" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="B55" s="16">
+      <c r="B55" s="17">
         <v>0.0</v>
       </c>
-      <c r="C55" s="17" t="s">
+      <c r="C55" s="18" t="s">
         <v>210</v>
       </c>
-      <c r="D55" s="17" t="s">
+      <c r="D55" s="18" t="s">
         <v>211</v>
       </c>
-      <c r="E55" s="17" t="s">
+      <c r="E55" s="18" t="s">
         <v>212</v>
       </c>
-      <c r="F55" s="17"/>
-      <c r="G55" s="17"/>
-      <c r="H55" s="17"/>
-      <c r="I55" s="17"/>
-      <c r="J55" s="17"/>
-      <c r="K55" s="17"/>
-      <c r="L55" s="17"/>
-      <c r="M55" s="17"/>
-      <c r="N55" s="17"/>
-      <c r="O55" s="17"/>
-      <c r="P55" s="17"/>
-      <c r="Q55" s="17"/>
-      <c r="R55" s="17"/>
-      <c r="S55" s="17"/>
-      <c r="T55" s="17"/>
-      <c r="U55" s="17"/>
-      <c r="V55" s="17"/>
-      <c r="W55" s="17"/>
-      <c r="X55" s="17"/>
-      <c r="Y55" s="17"/>
+      <c r="F55" s="18"/>
+      <c r="G55" s="18"/>
+      <c r="H55" s="18"/>
+      <c r="I55" s="18"/>
+      <c r="J55" s="18"/>
+      <c r="K55" s="18"/>
+      <c r="L55" s="18"/>
+      <c r="M55" s="18"/>
+      <c r="N55" s="18"/>
+      <c r="O55" s="18"/>
+      <c r="P55" s="18"/>
+      <c r="Q55" s="18"/>
+      <c r="R55" s="18"/>
+      <c r="S55" s="18"/>
+      <c r="T55" s="18"/>
+      <c r="U55" s="18"/>
+      <c r="V55" s="18"/>
+      <c r="W55" s="18"/>
+      <c r="X55" s="18"/>
+      <c r="Y55" s="18"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="15" t="s">
+      <c r="A56" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="B56" s="16">
+      <c r="B56" s="17">
         <v>0.0</v>
       </c>
-      <c r="C56" s="17" t="s">
+      <c r="C56" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="D56" s="17" t="s">
+      <c r="D56" s="18" t="s">
         <v>215</v>
       </c>
-      <c r="E56" s="17" t="s">
+      <c r="E56" s="18" t="s">
         <v>216</v>
       </c>
-      <c r="F56" s="17"/>
-      <c r="G56" s="17"/>
-      <c r="H56" s="17"/>
-      <c r="I56" s="17"/>
-      <c r="J56" s="17"/>
-      <c r="K56" s="17"/>
-      <c r="L56" s="17"/>
-      <c r="M56" s="17"/>
-      <c r="N56" s="17"/>
-      <c r="O56" s="17"/>
-      <c r="P56" s="17"/>
-      <c r="Q56" s="17"/>
-      <c r="R56" s="17"/>
-      <c r="S56" s="17"/>
-      <c r="T56" s="17"/>
-      <c r="U56" s="17"/>
-      <c r="V56" s="17"/>
-      <c r="W56" s="17"/>
-      <c r="X56" s="17"/>
-      <c r="Y56" s="17"/>
+      <c r="F56" s="18"/>
+      <c r="G56" s="18"/>
+      <c r="H56" s="18"/>
+      <c r="I56" s="18"/>
+      <c r="J56" s="18"/>
+      <c r="K56" s="18"/>
+      <c r="L56" s="18"/>
+      <c r="M56" s="18"/>
+      <c r="N56" s="18"/>
+      <c r="O56" s="18"/>
+      <c r="P56" s="18"/>
+      <c r="Q56" s="18"/>
+      <c r="R56" s="18"/>
+      <c r="S56" s="18"/>
+      <c r="T56" s="18"/>
+      <c r="U56" s="18"/>
+      <c r="V56" s="18"/>
+      <c r="W56" s="18"/>
+      <c r="X56" s="18"/>
+      <c r="Y56" s="18"/>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="15" t="s">
+      <c r="A57" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="B57" s="16">
+      <c r="B57" s="17">
         <v>0.0</v>
       </c>
-      <c r="C57" s="17" t="s">
+      <c r="C57" s="18" t="s">
         <v>218</v>
       </c>
-      <c r="D57" s="17" t="s">
+      <c r="D57" s="18" t="s">
         <v>219</v>
       </c>
-      <c r="E57" s="17" t="s">
+      <c r="E57" s="18" t="s">
         <v>220</v>
       </c>
-      <c r="F57" s="17"/>
-      <c r="G57" s="17"/>
-      <c r="H57" s="17"/>
-      <c r="I57" s="17"/>
-      <c r="J57" s="17"/>
-      <c r="K57" s="17"/>
-      <c r="L57" s="17"/>
-      <c r="M57" s="17"/>
-      <c r="N57" s="17"/>
-      <c r="O57" s="17"/>
-      <c r="P57" s="17"/>
-      <c r="Q57" s="17"/>
-      <c r="R57" s="17"/>
-      <c r="S57" s="17"/>
-      <c r="T57" s="17"/>
-      <c r="U57" s="17"/>
-      <c r="V57" s="17"/>
-      <c r="W57" s="17"/>
-      <c r="X57" s="17"/>
-      <c r="Y57" s="17"/>
+      <c r="F57" s="18"/>
+      <c r="G57" s="18"/>
+      <c r="H57" s="18"/>
+      <c r="I57" s="18"/>
+      <c r="J57" s="18"/>
+      <c r="K57" s="18"/>
+      <c r="L57" s="18"/>
+      <c r="M57" s="18"/>
+      <c r="N57" s="18"/>
+      <c r="O57" s="18"/>
+      <c r="P57" s="18"/>
+      <c r="Q57" s="18"/>
+      <c r="R57" s="18"/>
+      <c r="S57" s="18"/>
+      <c r="T57" s="18"/>
+      <c r="U57" s="18"/>
+      <c r="V57" s="18"/>
+      <c r="W57" s="18"/>
+      <c r="X57" s="18"/>
+      <c r="Y57" s="18"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="15" t="s">
+      <c r="A58" s="16" t="s">
         <v>221</v>
       </c>
-      <c r="B58" s="16">
+      <c r="B58" s="17">
         <v>0.0</v>
       </c>
-      <c r="C58" s="17" t="s">
+      <c r="C58" s="18" t="s">
         <v>222</v>
       </c>
-      <c r="D58" s="17" t="s">
+      <c r="D58" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="E58" s="17" t="s">
+      <c r="E58" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="F58" s="17"/>
-      <c r="G58" s="17"/>
-      <c r="H58" s="17"/>
-      <c r="I58" s="17"/>
-      <c r="J58" s="17"/>
-      <c r="K58" s="17"/>
-      <c r="L58" s="17"/>
-      <c r="M58" s="17"/>
-      <c r="N58" s="17"/>
-      <c r="O58" s="17"/>
-      <c r="P58" s="17"/>
-      <c r="Q58" s="17"/>
-      <c r="R58" s="17"/>
-      <c r="S58" s="17"/>
-      <c r="T58" s="17"/>
-      <c r="U58" s="17"/>
-      <c r="V58" s="17"/>
-      <c r="W58" s="17"/>
-      <c r="X58" s="17"/>
-      <c r="Y58" s="17"/>
+      <c r="F58" s="18"/>
+      <c r="G58" s="18"/>
+      <c r="H58" s="18"/>
+      <c r="I58" s="18"/>
+      <c r="J58" s="18"/>
+      <c r="K58" s="18"/>
+      <c r="L58" s="18"/>
+      <c r="M58" s="18"/>
+      <c r="N58" s="18"/>
+      <c r="O58" s="18"/>
+      <c r="P58" s="18"/>
+      <c r="Q58" s="18"/>
+      <c r="R58" s="18"/>
+      <c r="S58" s="18"/>
+      <c r="T58" s="18"/>
+      <c r="U58" s="18"/>
+      <c r="V58" s="18"/>
+      <c r="W58" s="18"/>
+      <c r="X58" s="18"/>
+      <c r="Y58" s="18"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="15" t="s">
+      <c r="A59" s="16" t="s">
         <v>223</v>
       </c>
-      <c r="B59" s="16">
+      <c r="B59" s="17">
         <v>0.0</v>
       </c>
-      <c r="C59" s="17" t="s">
+      <c r="C59" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="D59" s="17" t="s">
+      <c r="D59" s="18" t="s">
         <v>225</v>
       </c>
-      <c r="E59" s="17" t="s">
+      <c r="E59" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="F59" s="17"/>
-      <c r="G59" s="17"/>
-      <c r="H59" s="17"/>
-      <c r="I59" s="17"/>
-      <c r="J59" s="17"/>
-      <c r="K59" s="17"/>
-      <c r="L59" s="17"/>
-      <c r="M59" s="17"/>
-      <c r="N59" s="17"/>
-      <c r="O59" s="17"/>
-      <c r="P59" s="17"/>
-      <c r="Q59" s="17"/>
-      <c r="R59" s="17"/>
-      <c r="S59" s="17"/>
-      <c r="T59" s="17"/>
-      <c r="U59" s="17"/>
-      <c r="V59" s="17"/>
-      <c r="W59" s="17"/>
-      <c r="X59" s="17"/>
-      <c r="Y59" s="17"/>
+      <c r="F59" s="18"/>
+      <c r="G59" s="18"/>
+      <c r="H59" s="18"/>
+      <c r="I59" s="18"/>
+      <c r="J59" s="18"/>
+      <c r="K59" s="18"/>
+      <c r="L59" s="18"/>
+      <c r="M59" s="18"/>
+      <c r="N59" s="18"/>
+      <c r="O59" s="18"/>
+      <c r="P59" s="18"/>
+      <c r="Q59" s="18"/>
+      <c r="R59" s="18"/>
+      <c r="S59" s="18"/>
+      <c r="T59" s="18"/>
+      <c r="U59" s="18"/>
+      <c r="V59" s="18"/>
+      <c r="W59" s="18"/>
+      <c r="X59" s="18"/>
+      <c r="Y59" s="18"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="15" t="s">
+      <c r="A60" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="B60" s="16">
+      <c r="B60" s="17">
         <v>0.0</v>
       </c>
-      <c r="C60" s="17" t="s">
+      <c r="C60" s="18" t="s">
         <v>228</v>
       </c>
-      <c r="D60" s="17" t="s">
+      <c r="D60" s="18" t="s">
         <v>229</v>
       </c>
-      <c r="E60" s="17" t="s">
+      <c r="E60" s="18" t="s">
         <v>230</v>
       </c>
-      <c r="F60" s="17"/>
-      <c r="G60" s="17"/>
-      <c r="H60" s="17"/>
-      <c r="I60" s="17"/>
-      <c r="J60" s="17"/>
-      <c r="K60" s="17"/>
-      <c r="L60" s="17"/>
-      <c r="M60" s="17"/>
-      <c r="N60" s="17"/>
-      <c r="O60" s="17"/>
-      <c r="P60" s="17"/>
-      <c r="Q60" s="17"/>
-      <c r="R60" s="17"/>
-      <c r="S60" s="17"/>
-      <c r="T60" s="17"/>
-      <c r="U60" s="17"/>
-      <c r="V60" s="17"/>
-      <c r="W60" s="17"/>
-      <c r="X60" s="17"/>
-      <c r="Y60" s="17"/>
+      <c r="F60" s="18"/>
+      <c r="G60" s="18"/>
+      <c r="H60" s="18"/>
+      <c r="I60" s="18"/>
+      <c r="J60" s="18"/>
+      <c r="K60" s="18"/>
+      <c r="L60" s="18"/>
+      <c r="M60" s="18"/>
+      <c r="N60" s="18"/>
+      <c r="O60" s="18"/>
+      <c r="P60" s="18"/>
+      <c r="Q60" s="18"/>
+      <c r="R60" s="18"/>
+      <c r="S60" s="18"/>
+      <c r="T60" s="18"/>
+      <c r="U60" s="18"/>
+      <c r="V60" s="18"/>
+      <c r="W60" s="18"/>
+      <c r="X60" s="18"/>
+      <c r="Y60" s="18"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="15" t="s">
+      <c r="A61" s="16" t="s">
         <v>231</v>
       </c>
-      <c r="B61" s="16">
+      <c r="B61" s="17">
         <v>0.0</v>
       </c>
-      <c r="C61" s="17" t="s">
+      <c r="C61" s="18" t="s">
         <v>232</v>
       </c>
-      <c r="D61" s="17" t="s">
+      <c r="D61" s="18" t="s">
         <v>233</v>
       </c>
-      <c r="E61" s="17" t="s">
+      <c r="E61" s="18" t="s">
         <v>234</v>
       </c>
-      <c r="F61" s="17"/>
-      <c r="G61" s="17"/>
-      <c r="H61" s="17"/>
-      <c r="I61" s="17"/>
-      <c r="J61" s="17"/>
-      <c r="K61" s="17"/>
-      <c r="L61" s="17"/>
-      <c r="M61" s="17"/>
-      <c r="N61" s="17"/>
-      <c r="O61" s="17"/>
-      <c r="P61" s="17"/>
-      <c r="Q61" s="17"/>
-      <c r="R61" s="17"/>
-      <c r="S61" s="17"/>
-      <c r="T61" s="17"/>
-      <c r="U61" s="17"/>
-      <c r="V61" s="17"/>
-      <c r="W61" s="17"/>
-      <c r="X61" s="17"/>
-      <c r="Y61" s="17"/>
+      <c r="F61" s="18"/>
+      <c r="G61" s="18"/>
+      <c r="H61" s="18"/>
+      <c r="I61" s="18"/>
+      <c r="J61" s="18"/>
+      <c r="K61" s="18"/>
+      <c r="L61" s="18"/>
+      <c r="M61" s="18"/>
+      <c r="N61" s="18"/>
+      <c r="O61" s="18"/>
+      <c r="P61" s="18"/>
+      <c r="Q61" s="18"/>
+      <c r="R61" s="18"/>
+      <c r="S61" s="18"/>
+      <c r="T61" s="18"/>
+      <c r="U61" s="18"/>
+      <c r="V61" s="18"/>
+      <c r="W61" s="18"/>
+      <c r="X61" s="18"/>
+      <c r="Y61" s="18"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="15" t="s">
+      <c r="A62" s="16" t="s">
         <v>235</v>
       </c>
-      <c r="B62" s="16">
+      <c r="B62" s="17">
         <v>0.0</v>
       </c>
-      <c r="C62" s="17" t="s">
+      <c r="C62" s="18" t="s">
         <v>236</v>
       </c>
-      <c r="D62" s="17" t="s">
+      <c r="D62" s="18" t="s">
         <v>237</v>
       </c>
-      <c r="E62" s="17" t="s">
+      <c r="E62" s="18" t="s">
         <v>238</v>
       </c>
-      <c r="F62" s="17"/>
-      <c r="G62" s="17"/>
-      <c r="H62" s="17"/>
-      <c r="I62" s="17"/>
-      <c r="J62" s="17"/>
-      <c r="K62" s="17"/>
-      <c r="L62" s="17"/>
-      <c r="M62" s="17"/>
-      <c r="N62" s="17"/>
-      <c r="O62" s="17"/>
-      <c r="P62" s="17"/>
-      <c r="Q62" s="17"/>
-      <c r="R62" s="17"/>
-      <c r="S62" s="17"/>
-      <c r="T62" s="17"/>
-      <c r="U62" s="17"/>
-      <c r="V62" s="17"/>
-      <c r="W62" s="17"/>
-      <c r="X62" s="17"/>
-      <c r="Y62" s="17"/>
+      <c r="F62" s="18"/>
+      <c r="G62" s="18"/>
+      <c r="H62" s="18"/>
+      <c r="I62" s="18"/>
+      <c r="J62" s="18"/>
+      <c r="K62" s="18"/>
+      <c r="L62" s="18"/>
+      <c r="M62" s="18"/>
+      <c r="N62" s="18"/>
+      <c r="O62" s="18"/>
+      <c r="P62" s="18"/>
+      <c r="Q62" s="18"/>
+      <c r="R62" s="18"/>
+      <c r="S62" s="18"/>
+      <c r="T62" s="18"/>
+      <c r="U62" s="18"/>
+      <c r="V62" s="18"/>
+      <c r="W62" s="18"/>
+      <c r="X62" s="18"/>
+      <c r="Y62" s="18"/>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="15" t="s">
+      <c r="A63" s="16" t="s">
         <v>239</v>
       </c>
-      <c r="B63" s="16">
+      <c r="B63" s="17">
         <v>0.0</v>
       </c>
-      <c r="C63" s="17" t="s">
+      <c r="C63" s="18" t="s">
         <v>240</v>
       </c>
-      <c r="D63" s="17" t="s">
+      <c r="D63" s="18" t="s">
         <v>241</v>
       </c>
-      <c r="E63" s="17" t="s">
+      <c r="E63" s="18" t="s">
         <v>242</v>
       </c>
-      <c r="F63" s="17"/>
-      <c r="G63" s="17"/>
-      <c r="H63" s="17"/>
-      <c r="I63" s="17"/>
-      <c r="J63" s="17"/>
-      <c r="K63" s="17"/>
-      <c r="L63" s="17"/>
-      <c r="M63" s="17"/>
-      <c r="N63" s="17"/>
-      <c r="O63" s="17"/>
-      <c r="P63" s="17"/>
-      <c r="Q63" s="17"/>
-      <c r="R63" s="17"/>
-      <c r="S63" s="17"/>
-      <c r="T63" s="17"/>
-      <c r="U63" s="17"/>
-      <c r="V63" s="17"/>
-      <c r="W63" s="17"/>
-      <c r="X63" s="17"/>
-      <c r="Y63" s="17"/>
+      <c r="F63" s="18"/>
+      <c r="G63" s="18"/>
+      <c r="H63" s="18"/>
+      <c r="I63" s="18"/>
+      <c r="J63" s="18"/>
+      <c r="K63" s="18"/>
+      <c r="L63" s="18"/>
+      <c r="M63" s="18"/>
+      <c r="N63" s="18"/>
+      <c r="O63" s="18"/>
+      <c r="P63" s="18"/>
+      <c r="Q63" s="18"/>
+      <c r="R63" s="18"/>
+      <c r="S63" s="18"/>
+      <c r="T63" s="18"/>
+      <c r="U63" s="18"/>
+      <c r="V63" s="18"/>
+      <c r="W63" s="18"/>
+      <c r="X63" s="18"/>
+      <c r="Y63" s="18"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="15" t="s">
+      <c r="A64" s="16" t="s">
         <v>243</v>
       </c>
-      <c r="B64" s="16">
+      <c r="B64" s="17">
         <v>0.0</v>
       </c>
-      <c r="C64" s="17" t="s">
+      <c r="C64" s="18" t="s">
         <v>244</v>
       </c>
-      <c r="D64" s="17" t="s">
+      <c r="D64" s="18" t="s">
         <v>245</v>
       </c>
-      <c r="E64" s="17" t="s">
+      <c r="E64" s="18" t="s">
         <v>246</v>
       </c>
-      <c r="F64" s="17"/>
-      <c r="G64" s="17"/>
-      <c r="H64" s="17"/>
-      <c r="I64" s="17"/>
-      <c r="J64" s="17"/>
-      <c r="K64" s="17"/>
-      <c r="L64" s="17"/>
-      <c r="M64" s="17"/>
-      <c r="N64" s="17"/>
-      <c r="O64" s="17"/>
-      <c r="P64" s="17"/>
-      <c r="Q64" s="17"/>
-      <c r="R64" s="17"/>
-      <c r="S64" s="17"/>
-      <c r="T64" s="17"/>
-      <c r="U64" s="17"/>
-      <c r="V64" s="17"/>
-      <c r="W64" s="17"/>
-      <c r="X64" s="17"/>
-      <c r="Y64" s="17"/>
+      <c r="F64" s="18"/>
+      <c r="G64" s="18"/>
+      <c r="H64" s="18"/>
+      <c r="I64" s="18"/>
+      <c r="J64" s="18"/>
+      <c r="K64" s="18"/>
+      <c r="L64" s="18"/>
+      <c r="M64" s="18"/>
+      <c r="N64" s="18"/>
+      <c r="O64" s="18"/>
+      <c r="P64" s="18"/>
+      <c r="Q64" s="18"/>
+      <c r="R64" s="18"/>
+      <c r="S64" s="18"/>
+      <c r="T64" s="18"/>
+      <c r="U64" s="18"/>
+      <c r="V64" s="18"/>
+      <c r="W64" s="18"/>
+      <c r="X64" s="18"/>
+      <c r="Y64" s="18"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="15" t="s">
+      <c r="A65" s="16" t="s">
         <v>247</v>
       </c>
-      <c r="B65" s="16">
+      <c r="B65" s="17">
         <v>0.0</v>
       </c>
-      <c r="C65" s="17" t="s">
+      <c r="C65" s="18" t="s">
         <v>248</v>
       </c>
-      <c r="D65" s="17" t="s">
+      <c r="D65" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="E65" s="17" t="s">
+      <c r="E65" s="18" t="s">
         <v>250</v>
       </c>
-      <c r="F65" s="17"/>
-      <c r="G65" s="17"/>
-      <c r="H65" s="17"/>
-      <c r="I65" s="17"/>
-      <c r="J65" s="17"/>
-      <c r="K65" s="17"/>
-      <c r="L65" s="17"/>
-      <c r="M65" s="17"/>
-      <c r="N65" s="17"/>
-      <c r="O65" s="17"/>
-      <c r="P65" s="17"/>
-      <c r="Q65" s="17"/>
-      <c r="R65" s="17"/>
-      <c r="S65" s="17"/>
-      <c r="T65" s="17"/>
-      <c r="U65" s="17"/>
-      <c r="V65" s="17"/>
-      <c r="W65" s="17"/>
-      <c r="X65" s="17"/>
-      <c r="Y65" s="17"/>
+      <c r="F65" s="18"/>
+      <c r="G65" s="18"/>
+      <c r="H65" s="18"/>
+      <c r="I65" s="18"/>
+      <c r="J65" s="18"/>
+      <c r="K65" s="18"/>
+      <c r="L65" s="18"/>
+      <c r="M65" s="18"/>
+      <c r="N65" s="18"/>
+      <c r="O65" s="18"/>
+      <c r="P65" s="18"/>
+      <c r="Q65" s="18"/>
+      <c r="R65" s="18"/>
+      <c r="S65" s="18"/>
+      <c r="T65" s="18"/>
+      <c r="U65" s="18"/>
+      <c r="V65" s="18"/>
+      <c r="W65" s="18"/>
+      <c r="X65" s="18"/>
+      <c r="Y65" s="18"/>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="15" t="s">
+      <c r="A66" s="16" t="s">
         <v>251</v>
       </c>
-      <c r="B66" s="16">
+      <c r="B66" s="17">
         <v>0.0</v>
       </c>
-      <c r="C66" s="17" t="s">
+      <c r="C66" s="18" t="s">
         <v>252</v>
       </c>
-      <c r="D66" s="17" t="s">
+      <c r="D66" s="18" t="s">
         <v>253</v>
       </c>
-      <c r="E66" s="17" t="s">
+      <c r="E66" s="18" t="s">
         <v>254</v>
       </c>
-      <c r="F66" s="17"/>
-      <c r="G66" s="17"/>
-      <c r="H66" s="17"/>
-      <c r="I66" s="17"/>
-      <c r="J66" s="17"/>
-      <c r="K66" s="17"/>
-      <c r="L66" s="17"/>
-      <c r="M66" s="17"/>
-      <c r="N66" s="17"/>
-      <c r="O66" s="17"/>
-      <c r="P66" s="17"/>
-      <c r="Q66" s="17"/>
-      <c r="R66" s="17"/>
-      <c r="S66" s="17"/>
-      <c r="T66" s="17"/>
-      <c r="U66" s="17"/>
-      <c r="V66" s="17"/>
-      <c r="W66" s="17"/>
-      <c r="X66" s="17"/>
-      <c r="Y66" s="17"/>
+      <c r="F66" s="18"/>
+      <c r="G66" s="18"/>
+      <c r="H66" s="18"/>
+      <c r="I66" s="18"/>
+      <c r="J66" s="18"/>
+      <c r="K66" s="18"/>
+      <c r="L66" s="18"/>
+      <c r="M66" s="18"/>
+      <c r="N66" s="18"/>
+      <c r="O66" s="18"/>
+      <c r="P66" s="18"/>
+      <c r="Q66" s="18"/>
+      <c r="R66" s="18"/>
+      <c r="S66" s="18"/>
+      <c r="T66" s="18"/>
+      <c r="U66" s="18"/>
+      <c r="V66" s="18"/>
+      <c r="W66" s="18"/>
+      <c r="X66" s="18"/>
+      <c r="Y66" s="18"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="15" t="s">
+      <c r="A67" s="16" t="s">
         <v>255</v>
       </c>
-      <c r="B67" s="16">
+      <c r="B67" s="17">
         <v>0.0</v>
       </c>
-      <c r="C67" s="17" t="s">
+      <c r="C67" s="18" t="s">
         <v>256</v>
       </c>
-      <c r="D67" s="17" t="s">
+      <c r="D67" s="18" t="s">
         <v>257</v>
       </c>
-      <c r="E67" s="17" t="s">
+      <c r="E67" s="18" t="s">
         <v>258</v>
       </c>
-      <c r="F67" s="17"/>
-      <c r="G67" s="17"/>
-      <c r="H67" s="17"/>
-      <c r="I67" s="17"/>
-      <c r="J67" s="17"/>
-      <c r="K67" s="17"/>
-      <c r="L67" s="17"/>
-      <c r="M67" s="17"/>
-      <c r="N67" s="17"/>
-      <c r="O67" s="17"/>
-      <c r="P67" s="17"/>
-      <c r="Q67" s="17"/>
-      <c r="R67" s="17"/>
-      <c r="S67" s="17"/>
-      <c r="T67" s="17"/>
-      <c r="U67" s="17"/>
-      <c r="V67" s="17"/>
-      <c r="W67" s="17"/>
-      <c r="X67" s="17"/>
-      <c r="Y67" s="17"/>
+      <c r="F67" s="18"/>
+      <c r="G67" s="18"/>
+      <c r="H67" s="18"/>
+      <c r="I67" s="18"/>
+      <c r="J67" s="18"/>
+      <c r="K67" s="18"/>
+      <c r="L67" s="18"/>
+      <c r="M67" s="18"/>
+      <c r="N67" s="18"/>
+      <c r="O67" s="18"/>
+      <c r="P67" s="18"/>
+      <c r="Q67" s="18"/>
+      <c r="R67" s="18"/>
+      <c r="S67" s="18"/>
+      <c r="T67" s="18"/>
+      <c r="U67" s="18"/>
+      <c r="V67" s="18"/>
+      <c r="W67" s="18"/>
+      <c r="X67" s="18"/>
+      <c r="Y67" s="18"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="15" t="s">
+      <c r="A68" s="16" t="s">
         <v>259</v>
       </c>
-      <c r="B68" s="16">
+      <c r="B68" s="17">
         <v>0.0</v>
       </c>
-      <c r="C68" s="17" t="s">
+      <c r="C68" s="18" t="s">
         <v>260</v>
       </c>
-      <c r="D68" s="17" t="s">
+      <c r="D68" s="18" t="s">
         <v>261</v>
       </c>
-      <c r="E68" s="17" t="s">
+      <c r="E68" s="18" t="s">
         <v>262</v>
       </c>
-      <c r="F68" s="17"/>
-      <c r="G68" s="17"/>
-      <c r="H68" s="17"/>
-      <c r="I68" s="17"/>
-      <c r="J68" s="17"/>
-      <c r="K68" s="17"/>
-      <c r="L68" s="17"/>
-      <c r="M68" s="17"/>
-      <c r="N68" s="17"/>
-      <c r="O68" s="17"/>
-      <c r="P68" s="17"/>
-      <c r="Q68" s="17"/>
-      <c r="R68" s="17"/>
-      <c r="S68" s="17"/>
-      <c r="T68" s="17"/>
-      <c r="U68" s="17"/>
-      <c r="V68" s="17"/>
-      <c r="W68" s="17"/>
-      <c r="X68" s="17"/>
-      <c r="Y68" s="17"/>
+      <c r="F68" s="18"/>
+      <c r="G68" s="18"/>
+      <c r="H68" s="18"/>
+      <c r="I68" s="18"/>
+      <c r="J68" s="18"/>
+      <c r="K68" s="18"/>
+      <c r="L68" s="18"/>
+      <c r="M68" s="18"/>
+      <c r="N68" s="18"/>
+      <c r="O68" s="18"/>
+      <c r="P68" s="18"/>
+      <c r="Q68" s="18"/>
+      <c r="R68" s="18"/>
+      <c r="S68" s="18"/>
+      <c r="T68" s="18"/>
+      <c r="U68" s="18"/>
+      <c r="V68" s="18"/>
+      <c r="W68" s="18"/>
+      <c r="X68" s="18"/>
+      <c r="Y68" s="18"/>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="15" t="s">
+      <c r="A69" s="16" t="s">
         <v>263</v>
       </c>
-      <c r="B69" s="16">
+      <c r="B69" s="17">
         <v>0.0</v>
       </c>
-      <c r="C69" s="17" t="s">
+      <c r="C69" s="18" t="s">
         <v>264</v>
       </c>
-      <c r="D69" s="17" t="s">
+      <c r="D69" s="18" t="s">
         <v>265</v>
       </c>
-      <c r="E69" s="17" t="s">
+      <c r="E69" s="18" t="s">
         <v>266</v>
       </c>
-      <c r="F69" s="17"/>
-      <c r="G69" s="17"/>
-      <c r="H69" s="17"/>
-      <c r="I69" s="17"/>
-      <c r="J69" s="17"/>
-      <c r="K69" s="17"/>
-      <c r="L69" s="17"/>
-      <c r="M69" s="17"/>
-      <c r="N69" s="17"/>
-      <c r="O69" s="17"/>
-      <c r="P69" s="17"/>
-      <c r="Q69" s="17"/>
-      <c r="R69" s="17"/>
-      <c r="S69" s="17"/>
-      <c r="T69" s="17"/>
-      <c r="U69" s="17"/>
-      <c r="V69" s="17"/>
-      <c r="W69" s="17"/>
-      <c r="X69" s="17"/>
-      <c r="Y69" s="17"/>
+      <c r="F69" s="18"/>
+      <c r="G69" s="18"/>
+      <c r="H69" s="18"/>
+      <c r="I69" s="18"/>
+      <c r="J69" s="18"/>
+      <c r="K69" s="18"/>
+      <c r="L69" s="18"/>
+      <c r="M69" s="18"/>
+      <c r="N69" s="18"/>
+      <c r="O69" s="18"/>
+      <c r="P69" s="18"/>
+      <c r="Q69" s="18"/>
+      <c r="R69" s="18"/>
+      <c r="S69" s="18"/>
+      <c r="T69" s="18"/>
+      <c r="U69" s="18"/>
+      <c r="V69" s="18"/>
+      <c r="W69" s="18"/>
+      <c r="X69" s="18"/>
+      <c r="Y69" s="18"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="15" t="s">
+      <c r="A70" s="16" t="s">
         <v>267</v>
       </c>
-      <c r="B70" s="16">
+      <c r="B70" s="17">
         <v>0.0</v>
       </c>
-      <c r="C70" s="17" t="s">
+      <c r="C70" s="18" t="s">
         <v>268</v>
       </c>
-      <c r="D70" s="17" t="s">
+      <c r="D70" s="18" t="s">
         <v>269</v>
       </c>
-      <c r="E70" s="17" t="s">
+      <c r="E70" s="18" t="s">
         <v>270</v>
       </c>
-      <c r="F70" s="17"/>
-      <c r="G70" s="17"/>
-      <c r="H70" s="17"/>
-      <c r="I70" s="17"/>
-      <c r="J70" s="17"/>
-      <c r="K70" s="17"/>
-      <c r="L70" s="17"/>
-      <c r="M70" s="17"/>
-      <c r="N70" s="17"/>
-      <c r="O70" s="17"/>
-      <c r="P70" s="17"/>
-      <c r="Q70" s="17"/>
-      <c r="R70" s="17"/>
-      <c r="S70" s="17"/>
-      <c r="T70" s="17"/>
-      <c r="U70" s="17"/>
-      <c r="V70" s="17"/>
-      <c r="W70" s="17"/>
-      <c r="X70" s="17"/>
-      <c r="Y70" s="17"/>
+      <c r="F70" s="18"/>
+      <c r="G70" s="18"/>
+      <c r="H70" s="18"/>
+      <c r="I70" s="18"/>
+      <c r="J70" s="18"/>
+      <c r="K70" s="18"/>
+      <c r="L70" s="18"/>
+      <c r="M70" s="18"/>
+      <c r="N70" s="18"/>
+      <c r="O70" s="18"/>
+      <c r="P70" s="18"/>
+      <c r="Q70" s="18"/>
+      <c r="R70" s="18"/>
+      <c r="S70" s="18"/>
+      <c r="T70" s="18"/>
+      <c r="U70" s="18"/>
+      <c r="V70" s="18"/>
+      <c r="W70" s="18"/>
+      <c r="X70" s="18"/>
+      <c r="Y70" s="18"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="15" t="s">
+      <c r="A71" s="16" t="s">
         <v>271</v>
       </c>
-      <c r="B71" s="16">
+      <c r="B71" s="17">
         <v>0.0</v>
       </c>
-      <c r="C71" s="17" t="s">
+      <c r="C71" s="18" t="s">
         <v>272</v>
       </c>
-      <c r="D71" s="17" t="s">
+      <c r="D71" s="18" t="s">
         <v>273</v>
       </c>
-      <c r="E71" s="17" t="s">
+      <c r="E71" s="18" t="s">
         <v>274</v>
       </c>
-      <c r="F71" s="17"/>
-      <c r="G71" s="17"/>
-      <c r="H71" s="17"/>
-      <c r="I71" s="17"/>
-      <c r="J71" s="17"/>
-      <c r="K71" s="17"/>
-      <c r="L71" s="17"/>
-      <c r="M71" s="17"/>
-      <c r="N71" s="17"/>
-      <c r="O71" s="17"/>
-      <c r="P71" s="17"/>
-      <c r="Q71" s="17"/>
-      <c r="R71" s="17"/>
-      <c r="S71" s="17"/>
-      <c r="T71" s="17"/>
-      <c r="U71" s="17"/>
-      <c r="V71" s="17"/>
-      <c r="W71" s="17"/>
-      <c r="X71" s="17"/>
-      <c r="Y71" s="17"/>
+      <c r="F71" s="18"/>
+      <c r="G71" s="18"/>
+      <c r="H71" s="18"/>
+      <c r="I71" s="18"/>
+      <c r="J71" s="18"/>
+      <c r="K71" s="18"/>
+      <c r="L71" s="18"/>
+      <c r="M71" s="18"/>
+      <c r="N71" s="18"/>
+      <c r="O71" s="18"/>
+      <c r="P71" s="18"/>
+      <c r="Q71" s="18"/>
+      <c r="R71" s="18"/>
+      <c r="S71" s="18"/>
+      <c r="T71" s="18"/>
+      <c r="U71" s="18"/>
+      <c r="V71" s="18"/>
+      <c r="W71" s="18"/>
+      <c r="X71" s="18"/>
+      <c r="Y71" s="18"/>
     </row>
     <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="15" t="s">
+      <c r="A72" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="B72" s="16">
+      <c r="B72" s="17">
         <v>0.0</v>
       </c>
-      <c r="C72" s="17" t="s">
+      <c r="C72" s="18" t="s">
         <v>276</v>
       </c>
-      <c r="D72" s="17" t="s">
+      <c r="D72" s="18" t="s">
         <v>277</v>
       </c>
-      <c r="E72" s="17" t="s">
+      <c r="E72" s="18" t="s">
         <v>278</v>
       </c>
-      <c r="F72" s="17"/>
-      <c r="G72" s="17"/>
-      <c r="H72" s="17"/>
-      <c r="I72" s="17"/>
-      <c r="J72" s="17"/>
-      <c r="K72" s="17"/>
-      <c r="L72" s="17"/>
-      <c r="M72" s="17"/>
-      <c r="N72" s="17"/>
-      <c r="O72" s="17"/>
-      <c r="P72" s="17"/>
-      <c r="Q72" s="17"/>
-      <c r="R72" s="17"/>
-      <c r="S72" s="17"/>
-      <c r="T72" s="17"/>
-      <c r="U72" s="17"/>
-      <c r="V72" s="17"/>
-      <c r="W72" s="17"/>
-      <c r="X72" s="17"/>
-      <c r="Y72" s="17"/>
+      <c r="F72" s="18"/>
+      <c r="G72" s="18"/>
+      <c r="H72" s="18"/>
+      <c r="I72" s="18"/>
+      <c r="J72" s="18"/>
+      <c r="K72" s="18"/>
+      <c r="L72" s="18"/>
+      <c r="M72" s="18"/>
+      <c r="N72" s="18"/>
+      <c r="O72" s="18"/>
+      <c r="P72" s="18"/>
+      <c r="Q72" s="18"/>
+      <c r="R72" s="18"/>
+      <c r="S72" s="18"/>
+      <c r="T72" s="18"/>
+      <c r="U72" s="18"/>
+      <c r="V72" s="18"/>
+      <c r="W72" s="18"/>
+      <c r="X72" s="18"/>
+      <c r="Y72" s="18"/>
     </row>
     <row r="73" ht="15.0" customHeight="1">
-      <c r="A73" s="18" t="s">
+      <c r="A73" s="19" t="s">
         <v>279</v>
       </c>
-      <c r="B73" s="19">
+      <c r="B73" s="20">
         <v>0.0</v>
       </c>
-      <c r="C73" s="20" t="s">
+      <c r="C73" s="21" t="s">
         <v>280</v>
       </c>
-      <c r="D73" s="20" t="s">
+      <c r="D73" s="21" t="s">
         <v>281</v>
       </c>
-      <c r="E73" s="20" t="s">
+      <c r="E73" s="21" t="s">
         <v>282</v>
       </c>
-      <c r="F73" s="20"/>
-      <c r="G73" s="20"/>
-      <c r="H73" s="20"/>
-      <c r="I73" s="20"/>
-      <c r="J73" s="20"/>
-      <c r="K73" s="20"/>
-      <c r="L73" s="20"/>
-      <c r="M73" s="20"/>
-      <c r="N73" s="20"/>
-      <c r="O73" s="20"/>
-      <c r="P73" s="20"/>
-      <c r="Q73" s="20"/>
-      <c r="R73" s="20"/>
-      <c r="S73" s="20"/>
-      <c r="T73" s="20"/>
-      <c r="U73" s="20"/>
-      <c r="V73" s="20"/>
-      <c r="W73" s="20"/>
-      <c r="X73" s="20"/>
-      <c r="Y73" s="20"/>
+      <c r="F73" s="21"/>
+      <c r="G73" s="21"/>
+      <c r="H73" s="21"/>
+      <c r="I73" s="21"/>
+      <c r="J73" s="21"/>
+      <c r="K73" s="21"/>
+      <c r="L73" s="21"/>
+      <c r="M73" s="21"/>
+      <c r="N73" s="21"/>
+      <c r="O73" s="21"/>
+      <c r="P73" s="21"/>
+      <c r="Q73" s="21"/>
+      <c r="R73" s="21"/>
+      <c r="S73" s="21"/>
+      <c r="T73" s="21"/>
+      <c r="U73" s="21"/>
+      <c r="V73" s="21"/>
+      <c r="W73" s="21"/>
+      <c r="X73" s="21"/>
+      <c r="Y73" s="21"/>
     </row>
     <row r="74" ht="15.0" customHeight="1">
-      <c r="A74" s="21" t="s">
+      <c r="A74" s="22" t="s">
         <v>283</v>
       </c>
-      <c r="B74" s="22">
+      <c r="B74" s="23">
         <v>0.0</v>
       </c>
-      <c r="C74" s="22" t="s">
+      <c r="C74" s="23" t="s">
         <v>284</v>
       </c>
-      <c r="D74" s="22" t="s">
+      <c r="D74" s="23" t="s">
         <v>159</v>
       </c>
-      <c r="E74" s="22" t="s">
+      <c r="E74" s="23" t="s">
         <v>160</v>
       </c>
-      <c r="F74" s="22"/>
-      <c r="G74" s="22"/>
-      <c r="H74" s="22"/>
-      <c r="I74" s="22"/>
-      <c r="J74" s="22"/>
-      <c r="K74" s="22"/>
-      <c r="L74" s="22"/>
-      <c r="M74" s="22"/>
-      <c r="N74" s="22"/>
-      <c r="O74" s="22"/>
-      <c r="P74" s="22"/>
-      <c r="Q74" s="22"/>
-      <c r="R74" s="22"/>
-      <c r="S74" s="22"/>
-      <c r="T74" s="22"/>
-      <c r="U74" s="22"/>
-      <c r="V74" s="22"/>
-      <c r="W74" s="22"/>
-      <c r="X74" s="22"/>
-      <c r="Y74" s="22"/>
+      <c r="F74" s="23"/>
+      <c r="G74" s="23"/>
+      <c r="H74" s="23"/>
+      <c r="I74" s="23"/>
+      <c r="J74" s="23"/>
+      <c r="K74" s="23"/>
+      <c r="L74" s="23"/>
+      <c r="M74" s="23"/>
+      <c r="N74" s="23"/>
+      <c r="O74" s="23"/>
+      <c r="P74" s="23"/>
+      <c r="Q74" s="23"/>
+      <c r="R74" s="23"/>
+      <c r="S74" s="23"/>
+      <c r="T74" s="23"/>
+      <c r="U74" s="23"/>
+      <c r="V74" s="23"/>
+      <c r="W74" s="23"/>
+      <c r="X74" s="23"/>
+      <c r="Y74" s="23"/>
     </row>
     <row r="75" ht="15.0" customHeight="1">
-      <c r="A75" s="21" t="s">
+      <c r="A75" s="22" t="s">
         <v>285</v>
       </c>
-      <c r="B75" s="22">
+      <c r="B75" s="23">
         <v>0.0</v>
       </c>
-      <c r="C75" s="22" t="s">
+      <c r="C75" s="23" t="s">
         <v>286</v>
       </c>
-      <c r="D75" s="22" t="s">
+      <c r="D75" s="23" t="s">
         <v>287</v>
       </c>
-      <c r="E75" s="22" t="s">
+      <c r="E75" s="23" t="s">
         <v>288</v>
       </c>
-      <c r="F75" s="22"/>
-      <c r="G75" s="22"/>
-      <c r="H75" s="22"/>
-      <c r="I75" s="22"/>
-      <c r="J75" s="22"/>
-      <c r="K75" s="22"/>
-      <c r="L75" s="22"/>
-      <c r="M75" s="22"/>
-      <c r="N75" s="22"/>
-      <c r="O75" s="22"/>
-      <c r="P75" s="22"/>
-      <c r="Q75" s="22"/>
-      <c r="R75" s="22"/>
-      <c r="S75" s="22"/>
-      <c r="T75" s="22"/>
-      <c r="U75" s="22"/>
-      <c r="V75" s="22"/>
-      <c r="W75" s="22"/>
-      <c r="X75" s="22"/>
-      <c r="Y75" s="22"/>
+      <c r="F75" s="23"/>
+      <c r="G75" s="23"/>
+      <c r="H75" s="23"/>
+      <c r="I75" s="23"/>
+      <c r="J75" s="23"/>
+      <c r="K75" s="23"/>
+      <c r="L75" s="23"/>
+      <c r="M75" s="23"/>
+      <c r="N75" s="23"/>
+      <c r="O75" s="23"/>
+      <c r="P75" s="23"/>
+      <c r="Q75" s="23"/>
+      <c r="R75" s="23"/>
+      <c r="S75" s="23"/>
+      <c r="T75" s="23"/>
+      <c r="U75" s="23"/>
+      <c r="V75" s="23"/>
+      <c r="W75" s="23"/>
+      <c r="X75" s="23"/>
+      <c r="Y75" s="23"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="21" t="s">
+      <c r="A76" s="22" t="s">
         <v>289</v>
       </c>
-      <c r="B76" s="22">
+      <c r="B76" s="23">
         <v>0.0</v>
       </c>
-      <c r="C76" s="22" t="s">
+      <c r="C76" s="23" t="s">
         <v>290</v>
       </c>
-      <c r="D76" s="22" t="s">
+      <c r="D76" s="23" t="s">
         <v>187</v>
       </c>
-      <c r="E76" s="22" t="s">
+      <c r="E76" s="23" t="s">
         <v>188</v>
       </c>
-      <c r="F76" s="22"/>
-      <c r="G76" s="22"/>
-      <c r="H76" s="22"/>
-      <c r="I76" s="22"/>
-      <c r="J76" s="22"/>
-      <c r="K76" s="22"/>
-      <c r="L76" s="22"/>
-      <c r="M76" s="22"/>
-      <c r="N76" s="22"/>
-      <c r="O76" s="22"/>
-      <c r="P76" s="22"/>
-      <c r="Q76" s="22"/>
-      <c r="R76" s="22"/>
-      <c r="S76" s="22"/>
-      <c r="T76" s="22"/>
-      <c r="U76" s="22"/>
-      <c r="V76" s="22"/>
-      <c r="W76" s="22"/>
-      <c r="X76" s="22"/>
-      <c r="Y76" s="22"/>
+      <c r="F76" s="23"/>
+      <c r="G76" s="23"/>
+      <c r="H76" s="23"/>
+      <c r="I76" s="23"/>
+      <c r="J76" s="23"/>
+      <c r="K76" s="23"/>
+      <c r="L76" s="23"/>
+      <c r="M76" s="23"/>
+      <c r="N76" s="23"/>
+      <c r="O76" s="23"/>
+      <c r="P76" s="23"/>
+      <c r="Q76" s="23"/>
+      <c r="R76" s="23"/>
+      <c r="S76" s="23"/>
+      <c r="T76" s="23"/>
+      <c r="U76" s="23"/>
+      <c r="V76" s="23"/>
+      <c r="W76" s="23"/>
+      <c r="X76" s="23"/>
+      <c r="Y76" s="23"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="21" t="s">
+      <c r="A77" s="22" t="s">
         <v>291</v>
       </c>
-      <c r="B77" s="22">
+      <c r="B77" s="23">
         <v>0.0</v>
       </c>
-      <c r="C77" s="22" t="s">
+      <c r="C77" s="23" t="s">
         <v>292</v>
       </c>
-      <c r="D77" s="22" t="s">
+      <c r="D77" s="23" t="s">
         <v>293</v>
       </c>
-      <c r="E77" s="22" t="s">
+      <c r="E77" s="23" t="s">
         <v>294</v>
       </c>
-      <c r="F77" s="22"/>
-      <c r="G77" s="22"/>
-      <c r="H77" s="22"/>
-      <c r="I77" s="22"/>
-      <c r="J77" s="22"/>
-      <c r="K77" s="22"/>
-      <c r="L77" s="22"/>
-      <c r="M77" s="22"/>
-      <c r="N77" s="22"/>
-      <c r="O77" s="22"/>
-      <c r="P77" s="22"/>
-      <c r="Q77" s="22"/>
-      <c r="R77" s="22"/>
-      <c r="S77" s="22"/>
-      <c r="T77" s="22"/>
-      <c r="U77" s="22"/>
-      <c r="V77" s="22"/>
-      <c r="W77" s="22"/>
-      <c r="X77" s="22"/>
-      <c r="Y77" s="22"/>
+      <c r="F77" s="23"/>
+      <c r="G77" s="23"/>
+      <c r="H77" s="23"/>
+      <c r="I77" s="23"/>
+      <c r="J77" s="23"/>
+      <c r="K77" s="23"/>
+      <c r="L77" s="23"/>
+      <c r="M77" s="23"/>
+      <c r="N77" s="23"/>
+      <c r="O77" s="23"/>
+      <c r="P77" s="23"/>
+      <c r="Q77" s="23"/>
+      <c r="R77" s="23"/>
+      <c r="S77" s="23"/>
+      <c r="T77" s="23"/>
+      <c r="U77" s="23"/>
+      <c r="V77" s="23"/>
+      <c r="W77" s="23"/>
+      <c r="X77" s="23"/>
+      <c r="Y77" s="23"/>
     </row>
     <row r="78" ht="15.0" customHeight="1">
-      <c r="A78" s="21" t="s">
+      <c r="A78" s="22" t="s">
         <v>295</v>
       </c>
-      <c r="B78" s="22">
+      <c r="B78" s="23">
         <v>0.0</v>
       </c>
-      <c r="C78" s="22" t="s">
+      <c r="C78" s="23" t="s">
         <v>296</v>
       </c>
-      <c r="D78" s="22" t="s">
+      <c r="D78" s="23" t="s">
         <v>297</v>
       </c>
-      <c r="E78" s="22" t="s">
+      <c r="E78" s="23" t="s">
         <v>298</v>
       </c>
-      <c r="F78" s="22"/>
-      <c r="G78" s="22"/>
-      <c r="H78" s="22"/>
-      <c r="I78" s="22"/>
-      <c r="J78" s="22"/>
-      <c r="K78" s="22"/>
-      <c r="L78" s="22"/>
-      <c r="M78" s="22"/>
-      <c r="N78" s="22"/>
-      <c r="O78" s="22"/>
-      <c r="P78" s="22"/>
-      <c r="Q78" s="22"/>
-      <c r="R78" s="22"/>
-      <c r="S78" s="22"/>
-      <c r="T78" s="22"/>
-      <c r="U78" s="22"/>
-      <c r="V78" s="22"/>
-      <c r="W78" s="22"/>
-      <c r="X78" s="22"/>
-      <c r="Y78" s="22"/>
+      <c r="F78" s="23"/>
+      <c r="G78" s="23"/>
+      <c r="H78" s="23"/>
+      <c r="I78" s="23"/>
+      <c r="J78" s="23"/>
+      <c r="K78" s="23"/>
+      <c r="L78" s="23"/>
+      <c r="M78" s="23"/>
+      <c r="N78" s="23"/>
+      <c r="O78" s="23"/>
+      <c r="P78" s="23"/>
+      <c r="Q78" s="23"/>
+      <c r="R78" s="23"/>
+      <c r="S78" s="23"/>
+      <c r="T78" s="23"/>
+      <c r="U78" s="23"/>
+      <c r="V78" s="23"/>
+      <c r="W78" s="23"/>
+      <c r="X78" s="23"/>
+      <c r="Y78" s="23"/>
     </row>
     <row r="79" ht="15.0" customHeight="1">
-      <c r="A79" s="21" t="s">
+      <c r="A79" s="22" t="s">
         <v>299</v>
       </c>
-      <c r="B79" s="22">
+      <c r="B79" s="23">
         <v>0.0</v>
       </c>
-      <c r="C79" s="22" t="s">
+      <c r="C79" s="23" t="s">
         <v>300</v>
       </c>
-      <c r="D79" s="22" t="s">
+      <c r="D79" s="23" t="s">
         <v>301</v>
       </c>
-      <c r="E79" s="22" t="s">
+      <c r="E79" s="23" t="s">
         <v>302</v>
       </c>
-      <c r="F79" s="22"/>
-      <c r="G79" s="22"/>
-      <c r="H79" s="22"/>
-      <c r="I79" s="22"/>
-      <c r="J79" s="22"/>
-      <c r="K79" s="22"/>
-      <c r="L79" s="22"/>
-      <c r="M79" s="22"/>
-      <c r="N79" s="22"/>
-      <c r="O79" s="22"/>
-      <c r="P79" s="22"/>
-      <c r="Q79" s="22"/>
-      <c r="R79" s="22"/>
-      <c r="S79" s="22"/>
-      <c r="T79" s="22"/>
-      <c r="U79" s="22"/>
-      <c r="V79" s="22"/>
-      <c r="W79" s="22"/>
-      <c r="X79" s="22"/>
-      <c r="Y79" s="22"/>
+      <c r="F79" s="23"/>
+      <c r="G79" s="23"/>
+      <c r="H79" s="23"/>
+      <c r="I79" s="23"/>
+      <c r="J79" s="23"/>
+      <c r="K79" s="23"/>
+      <c r="L79" s="23"/>
+      <c r="M79" s="23"/>
+      <c r="N79" s="23"/>
+      <c r="O79" s="23"/>
+      <c r="P79" s="23"/>
+      <c r="Q79" s="23"/>
+      <c r="R79" s="23"/>
+      <c r="S79" s="23"/>
+      <c r="T79" s="23"/>
+      <c r="U79" s="23"/>
+      <c r="V79" s="23"/>
+      <c r="W79" s="23"/>
+      <c r="X79" s="23"/>
+      <c r="Y79" s="23"/>
     </row>
     <row r="80" ht="15.0" customHeight="1">
-      <c r="A80" s="21" t="s">
+      <c r="A80" s="22" t="s">
         <v>303</v>
       </c>
-      <c r="B80" s="22">
+      <c r="B80" s="23">
         <v>0.0</v>
       </c>
-      <c r="C80" s="22" t="s">
+      <c r="C80" s="23" t="s">
         <v>304</v>
       </c>
-      <c r="D80" s="22" t="s">
+      <c r="D80" s="23" t="s">
         <v>305</v>
       </c>
-      <c r="E80" s="22" t="s">
+      <c r="E80" s="23" t="s">
         <v>306</v>
       </c>
-      <c r="F80" s="22"/>
-      <c r="G80" s="22"/>
-      <c r="H80" s="22"/>
-      <c r="I80" s="22"/>
-      <c r="J80" s="22"/>
-      <c r="K80" s="22"/>
-      <c r="L80" s="22"/>
-      <c r="M80" s="22"/>
-      <c r="N80" s="22"/>
-      <c r="O80" s="22"/>
-      <c r="P80" s="22"/>
-      <c r="Q80" s="22"/>
-      <c r="R80" s="22"/>
-      <c r="S80" s="22"/>
-      <c r="T80" s="22"/>
-      <c r="U80" s="22"/>
-      <c r="V80" s="22"/>
-      <c r="W80" s="22"/>
-      <c r="X80" s="22"/>
-      <c r="Y80" s="22"/>
+      <c r="F80" s="23"/>
+      <c r="G80" s="23"/>
+      <c r="H80" s="23"/>
+      <c r="I80" s="23"/>
+      <c r="J80" s="23"/>
+      <c r="K80" s="23"/>
+      <c r="L80" s="23"/>
+      <c r="M80" s="23"/>
+      <c r="N80" s="23"/>
+      <c r="O80" s="23"/>
+      <c r="P80" s="23"/>
+      <c r="Q80" s="23"/>
+      <c r="R80" s="23"/>
+      <c r="S80" s="23"/>
+      <c r="T80" s="23"/>
+      <c r="U80" s="23"/>
+      <c r="V80" s="23"/>
+      <c r="W80" s="23"/>
+      <c r="X80" s="23"/>
+      <c r="Y80" s="23"/>
     </row>
     <row r="81" ht="15.0" customHeight="1">
-      <c r="A81" s="23" t="s">
+      <c r="A81" s="24" t="s">
         <v>307</v>
       </c>
-      <c r="B81" s="24">
+      <c r="B81" s="25">
         <v>0.0</v>
       </c>
-      <c r="C81" s="25" t="s">
+      <c r="C81" s="26" t="s">
         <v>308</v>
       </c>
-      <c r="D81" s="25" t="s">
+      <c r="D81" s="26" t="s">
         <v>219</v>
       </c>
-      <c r="E81" s="25" t="s">
+      <c r="E81" s="26" t="s">
         <v>220</v>
       </c>
-      <c r="F81" s="25"/>
-      <c r="G81" s="25"/>
-      <c r="H81" s="25"/>
-      <c r="I81" s="25"/>
-      <c r="J81" s="25"/>
-      <c r="K81" s="25"/>
-      <c r="L81" s="25"/>
-      <c r="M81" s="25"/>
-      <c r="N81" s="25"/>
-      <c r="O81" s="25"/>
-      <c r="P81" s="25"/>
-      <c r="Q81" s="25"/>
-      <c r="R81" s="25"/>
-      <c r="S81" s="25"/>
-      <c r="T81" s="25"/>
-      <c r="U81" s="25"/>
-      <c r="V81" s="25"/>
-      <c r="W81" s="25"/>
-      <c r="X81" s="25"/>
-      <c r="Y81" s="25"/>
+      <c r="F81" s="26"/>
+      <c r="G81" s="26"/>
+      <c r="H81" s="26"/>
+      <c r="I81" s="26"/>
+      <c r="J81" s="26"/>
+      <c r="K81" s="26"/>
+      <c r="L81" s="26"/>
+      <c r="M81" s="26"/>
+      <c r="N81" s="26"/>
+      <c r="O81" s="26"/>
+      <c r="P81" s="26"/>
+      <c r="Q81" s="26"/>
+      <c r="R81" s="26"/>
+      <c r="S81" s="26"/>
+      <c r="T81" s="26"/>
+      <c r="U81" s="26"/>
+      <c r="V81" s="26"/>
+      <c r="W81" s="26"/>
+      <c r="X81" s="26"/>
+      <c r="Y81" s="26"/>
     </row>
     <row r="82" ht="15.0" customHeight="1">
-      <c r="A82" s="26" t="s">
+      <c r="A82" s="27" t="s">
         <v>309</v>
       </c>
-      <c r="B82" s="27">
+      <c r="B82" s="28">
         <v>0.0</v>
       </c>
-      <c r="C82" s="28" t="s">
+      <c r="C82" s="29" t="s">
         <v>310</v>
       </c>
-      <c r="D82" s="28" t="s">
+      <c r="D82" s="29" t="s">
         <v>151</v>
       </c>
-      <c r="E82" s="28" t="s">
+      <c r="E82" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="F82" s="28"/>
-      <c r="G82" s="28"/>
-      <c r="H82" s="28"/>
-      <c r="I82" s="28"/>
-      <c r="J82" s="28"/>
-      <c r="K82" s="28"/>
-      <c r="L82" s="28"/>
-      <c r="M82" s="28"/>
-      <c r="N82" s="28"/>
-      <c r="O82" s="28"/>
-      <c r="P82" s="28"/>
-      <c r="Q82" s="28"/>
-      <c r="R82" s="28"/>
-      <c r="S82" s="28"/>
-      <c r="T82" s="28"/>
-      <c r="U82" s="28"/>
-      <c r="V82" s="28"/>
-      <c r="W82" s="28"/>
-      <c r="X82" s="28"/>
-      <c r="Y82" s="28"/>
+      <c r="F82" s="29"/>
+      <c r="G82" s="29"/>
+      <c r="H82" s="29"/>
+      <c r="I82" s="29"/>
+      <c r="J82" s="29"/>
+      <c r="K82" s="29"/>
+      <c r="L82" s="29"/>
+      <c r="M82" s="29"/>
+      <c r="N82" s="29"/>
+      <c r="O82" s="29"/>
+      <c r="P82" s="29"/>
+      <c r="Q82" s="29"/>
+      <c r="R82" s="29"/>
+      <c r="S82" s="29"/>
+      <c r="T82" s="29"/>
+      <c r="U82" s="29"/>
+      <c r="V82" s="29"/>
+      <c r="W82" s="29"/>
+      <c r="X82" s="29"/>
+      <c r="Y82" s="29"/>
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="1"/>

--- a/Templates/Tables/StringInfo/StrTable.xlsx
+++ b/Templates/Tables/StringInfo/StrTable.xlsx
@@ -226,7 +226,7 @@
     <t>추적 설명 팝업 메세지</t>
   </si>
   <si>
-    <t>앱 추적을 승인해\n주세요</t>
+    <t>앱 추적 승인</t>
   </si>
   <si>
     <t>Allow tracking on the\nnext screen for</t>
@@ -2053,7 +2053,7 @@
       <c r="C20" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="9" t="s">
         <v>71</v>
       </c>
       <c r="E20" s="7" t="s">
@@ -2090,10 +2090,10 @@
       <c r="C21" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="E21" s="7" t="s">
         <v>76</v>
       </c>
       <c r="F21" s="7"/>
@@ -2127,10 +2127,10 @@
       <c r="C22" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="D22" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="E22" s="7" t="s">
         <v>80</v>
       </c>
       <c r="F22" s="7"/>
@@ -2164,10 +2164,10 @@
       <c r="C23" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="D23" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="E23" s="7" t="s">
         <v>84</v>
       </c>
       <c r="F23" s="7"/>

--- a/Templates/Tables/StringInfo/StrTable.xlsx
+++ b/Templates/Tables/StringInfo/StrTable.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="287">
   <si>
     <t>ID</t>
   </si>
@@ -148,78 +148,18 @@
     <t>Do you want to save progress?\n&lt;color=#ff0000ff&gt;&lt;size=24&gt;(When saving, previous progress cannot be recovered)&lt;/size&gt;&lt;/color&gt;</t>
   </si>
   <si>
-    <t>AGREE_P_EU_TITLE</t>
-  </si>
-  <si>
-    <t>약관 동의 팝업 EU 제목</t>
+    <t>TRACKING_DP_TITLE</t>
+  </si>
+  <si>
+    <t>추적 설명 팝업 제목</t>
+  </si>
+  <si>
+    <t>알림</t>
   </si>
   <si>
     <t>Notice</t>
   </si>
   <si>
-    <t>AGREE_P_PRIVACY_TITLE</t>
-  </si>
-  <si>
-    <t>약관 동의 팝업 개인 정보 제목</t>
-  </si>
-  <si>
-    <t>개인정보 보호정책</t>
-  </si>
-  <si>
-    <t>Privacy Policy</t>
-  </si>
-  <si>
-    <t>AGREE_P_SERVICES_TITLE</t>
-  </si>
-  <si>
-    <t>약관 동의 팝업 서비스 제목</t>
-  </si>
-  <si>
-    <t>서비스 이용약관</t>
-  </si>
-  <si>
-    <t>Terms of Service</t>
-  </si>
-  <si>
-    <t>AGREE_P_PRIVACY_BTN_TEXT</t>
-  </si>
-  <si>
-    <t>약관 동의 팝업 개인 정보 버튼 텍스트</t>
-  </si>
-  <si>
-    <t>AGREE_P_SERVICES_BTN_TEXT</t>
-  </si>
-  <si>
-    <t>약관 동의 팝업 서비스 버튼 텍스트</t>
-  </si>
-  <si>
-    <t>AGREE_P_DESC_TEXT_01</t>
-  </si>
-  <si>
-    <t>약관 동의 팝업 설명 텍스트 1</t>
-  </si>
-  <si>
-    <t>Tap OK to accept our</t>
-  </si>
-  <si>
-    <t>AGREE_P_DESC_TEXT_02</t>
-  </si>
-  <si>
-    <t>약관 동의 팝업 설명 텍스트 2</t>
-  </si>
-  <si>
-    <t>and</t>
-  </si>
-  <si>
-    <t>TRACKING_DP_TITLE</t>
-  </si>
-  <si>
-    <t>추적 설명 팝업 제목</t>
-  </si>
-  <si>
-    <t>알림</t>
-  </si>
-  <si>
     <t>TRACKING_DP_MSG</t>
   </si>
   <si>
@@ -266,18 +206,6 @@
   </si>
   <si>
     <t>An improved personalized\nexperience over time</t>
-  </si>
-  <si>
-    <t>START_SM_LOADING_TEXT</t>
-  </si>
-  <si>
-    <t>시작 씬 관리자 로딩 텍스트</t>
-  </si>
-  <si>
-    <t>로딩 중</t>
-  </si>
-  <si>
-    <t>Loading</t>
   </si>
   <si>
     <t>COMMON_LOGIN_SUCCESS_MSG</t>
@@ -1034,7 +962,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="26">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1059,18 +987,6 @@
     </xf>
     <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="5" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="5" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -1761,7 +1677,7 @@
         <v>47</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
@@ -1786,19 +1702,19 @@
     </row>
     <row r="13" ht="15.0" customHeight="1">
       <c r="A13" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B13" s="6">
         <v>0.0</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
@@ -1823,19 +1739,19 @@
     </row>
     <row r="14" ht="15.0" customHeight="1">
       <c r="A14" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B14" s="6">
         <v>0.0</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
@@ -1860,19 +1776,19 @@
     </row>
     <row r="15" ht="15.0" customHeight="1">
       <c r="A15" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B15" s="6">
         <v>0.0</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
@@ -1897,19 +1813,19 @@
     </row>
     <row r="16" ht="15.0" customHeight="1">
       <c r="A16" s="5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B16" s="6">
         <v>0.0</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
@@ -1932,2447 +1848,2367 @@
       <c r="X16" s="7"/>
       <c r="Y16" s="7"/>
     </row>
-    <row r="17" ht="15.0" customHeight="1">
-      <c r="A17" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B17" s="6">
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" s="10">
         <v>0.0</v>
       </c>
-      <c r="C17" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="7"/>
-      <c r="O17" s="7"/>
-      <c r="P17" s="7"/>
-      <c r="Q17" s="7"/>
-      <c r="R17" s="7"/>
-      <c r="S17" s="7"/>
-      <c r="T17" s="7"/>
-      <c r="U17" s="7"/>
-      <c r="V17" s="7"/>
-      <c r="W17" s="7"/>
-      <c r="X17" s="7"/>
-      <c r="Y17" s="7"/>
-    </row>
-    <row r="18" ht="15.0" customHeight="1">
-      <c r="A18" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B18" s="6">
+      <c r="C17" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11"/>
+      <c r="O17" s="11"/>
+      <c r="P17" s="11"/>
+      <c r="Q17" s="11"/>
+      <c r="R17" s="11"/>
+      <c r="S17" s="11"/>
+      <c r="T17" s="11"/>
+      <c r="U17" s="11"/>
+      <c r="V17" s="11"/>
+      <c r="W17" s="11"/>
+      <c r="X17" s="11"/>
+      <c r="Y17" s="11"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B18" s="13">
         <v>0.0</v>
       </c>
-      <c r="C18" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="7"/>
-      <c r="O18" s="7"/>
-      <c r="P18" s="7"/>
-      <c r="Q18" s="7"/>
-      <c r="R18" s="7"/>
-      <c r="S18" s="7"/>
-      <c r="T18" s="7"/>
-      <c r="U18" s="7"/>
-      <c r="V18" s="7"/>
-      <c r="W18" s="7"/>
-      <c r="X18" s="7"/>
-      <c r="Y18" s="7"/>
-    </row>
-    <row r="19" ht="15.0" customHeight="1">
-      <c r="A19" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B19" s="6">
+      <c r="C18" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="14"/>
+      <c r="N18" s="14"/>
+      <c r="O18" s="14"/>
+      <c r="P18" s="14"/>
+      <c r="Q18" s="14"/>
+      <c r="R18" s="14"/>
+      <c r="S18" s="14"/>
+      <c r="T18" s="14"/>
+      <c r="U18" s="14"/>
+      <c r="V18" s="14"/>
+      <c r="W18" s="14"/>
+      <c r="X18" s="14"/>
+      <c r="Y18" s="14"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="13">
         <v>0.0</v>
       </c>
-      <c r="C19" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E19" s="7" t="s">
+      <c r="C19" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="14"/>
+      <c r="N19" s="14"/>
+      <c r="O19" s="14"/>
+      <c r="P19" s="14"/>
+      <c r="Q19" s="14"/>
+      <c r="R19" s="14"/>
+      <c r="S19" s="14"/>
+      <c r="T19" s="14"/>
+      <c r="U19" s="14"/>
+      <c r="V19" s="14"/>
+      <c r="W19" s="14"/>
+      <c r="X19" s="14"/>
+      <c r="Y19" s="14"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B20" s="13">
+        <v>0.0</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+      <c r="K20" s="14"/>
+      <c r="L20" s="14"/>
+      <c r="M20" s="14"/>
+      <c r="N20" s="14"/>
+      <c r="O20" s="14"/>
+      <c r="P20" s="14"/>
+      <c r="Q20" s="14"/>
+      <c r="R20" s="14"/>
+      <c r="S20" s="14"/>
+      <c r="T20" s="14"/>
+      <c r="U20" s="14"/>
+      <c r="V20" s="14"/>
+      <c r="W20" s="14"/>
+      <c r="X20" s="14"/>
+      <c r="Y20" s="14"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="B21" s="13">
+        <v>0.0</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="14"/>
+      <c r="L21" s="14"/>
+      <c r="M21" s="14"/>
+      <c r="N21" s="14"/>
+      <c r="O21" s="14"/>
+      <c r="P21" s="14"/>
+      <c r="Q21" s="14"/>
+      <c r="R21" s="14"/>
+      <c r="S21" s="14"/>
+      <c r="T21" s="14"/>
+      <c r="U21" s="14"/>
+      <c r="V21" s="14"/>
+      <c r="W21" s="14"/>
+      <c r="X21" s="14"/>
+      <c r="Y21" s="14"/>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B22" s="13">
+        <v>0.0</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+      <c r="K22" s="14"/>
+      <c r="L22" s="14"/>
+      <c r="M22" s="14"/>
+      <c r="N22" s="14"/>
+      <c r="O22" s="14"/>
+      <c r="P22" s="14"/>
+      <c r="Q22" s="14"/>
+      <c r="R22" s="14"/>
+      <c r="S22" s="14"/>
+      <c r="T22" s="14"/>
+      <c r="U22" s="14"/>
+      <c r="V22" s="14"/>
+      <c r="W22" s="14"/>
+      <c r="X22" s="14"/>
+      <c r="Y22" s="14"/>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="B23" s="13">
+        <v>0.0</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="14"/>
+      <c r="L23" s="14"/>
+      <c r="M23" s="14"/>
+      <c r="N23" s="14"/>
+      <c r="O23" s="14"/>
+      <c r="P23" s="14"/>
+      <c r="Q23" s="14"/>
+      <c r="R23" s="14"/>
+      <c r="S23" s="14"/>
+      <c r="T23" s="14"/>
+      <c r="U23" s="14"/>
+      <c r="V23" s="14"/>
+      <c r="W23" s="14"/>
+      <c r="X23" s="14"/>
+      <c r="Y23" s="14"/>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="B24" s="13">
+        <v>0.0</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14"/>
+      <c r="P24" s="14"/>
+      <c r="Q24" s="14"/>
+      <c r="R24" s="14"/>
+      <c r="S24" s="14"/>
+      <c r="T24" s="14"/>
+      <c r="U24" s="14"/>
+      <c r="V24" s="14"/>
+      <c r="W24" s="14"/>
+      <c r="X24" s="14"/>
+      <c r="Y24" s="14"/>
+    </row>
+    <row r="25" ht="15.0" customHeight="1">
+      <c r="A25" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="B25" s="13">
+        <v>0.0</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+      <c r="K25" s="14"/>
+      <c r="L25" s="14"/>
+      <c r="M25" s="14"/>
+      <c r="N25" s="14"/>
+      <c r="O25" s="14"/>
+      <c r="P25" s="14"/>
+      <c r="Q25" s="14"/>
+      <c r="R25" s="14"/>
+      <c r="S25" s="14"/>
+      <c r="T25" s="14"/>
+      <c r="U25" s="14"/>
+      <c r="V25" s="14"/>
+      <c r="W25" s="14"/>
+      <c r="X25" s="14"/>
+      <c r="Y25" s="14"/>
+    </row>
+    <row r="26" ht="15.0" customHeight="1">
+      <c r="A26" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="B26" s="13">
+        <v>0.0</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="14"/>
+      <c r="L26" s="14"/>
+      <c r="M26" s="14"/>
+      <c r="N26" s="14"/>
+      <c r="O26" s="14"/>
+      <c r="P26" s="14"/>
+      <c r="Q26" s="14"/>
+      <c r="R26" s="14"/>
+      <c r="S26" s="14"/>
+      <c r="T26" s="14"/>
+      <c r="U26" s="14"/>
+      <c r="V26" s="14"/>
+      <c r="W26" s="14"/>
+      <c r="X26" s="14"/>
+      <c r="Y26" s="14"/>
+    </row>
+    <row r="27" ht="15.0" customHeight="1">
+      <c r="A27" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="B27" s="13">
+        <v>0.0</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="14"/>
+      <c r="L27" s="14"/>
+      <c r="M27" s="14"/>
+      <c r="N27" s="14"/>
+      <c r="O27" s="14"/>
+      <c r="P27" s="14"/>
+      <c r="Q27" s="14"/>
+      <c r="R27" s="14"/>
+      <c r="S27" s="14"/>
+      <c r="T27" s="14"/>
+      <c r="U27" s="14"/>
+      <c r="V27" s="14"/>
+      <c r="W27" s="14"/>
+      <c r="X27" s="14"/>
+      <c r="Y27" s="14"/>
+    </row>
+    <row r="28" ht="15.0" customHeight="1">
+      <c r="A28" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="B28" s="13">
+        <v>0.0</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
+      <c r="K28" s="14"/>
+      <c r="L28" s="14"/>
+      <c r="M28" s="14"/>
+      <c r="N28" s="14"/>
+      <c r="O28" s="14"/>
+      <c r="P28" s="14"/>
+      <c r="Q28" s="14"/>
+      <c r="R28" s="14"/>
+      <c r="S28" s="14"/>
+      <c r="T28" s="14"/>
+      <c r="U28" s="14"/>
+      <c r="V28" s="14"/>
+      <c r="W28" s="14"/>
+      <c r="X28" s="14"/>
+      <c r="Y28" s="14"/>
+    </row>
+    <row r="29" ht="15.0" customHeight="1">
+      <c r="A29" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="B29" s="13">
+        <v>0.0</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="14"/>
+      <c r="L29" s="14"/>
+      <c r="M29" s="14"/>
+      <c r="N29" s="14"/>
+      <c r="O29" s="14"/>
+      <c r="P29" s="14"/>
+      <c r="Q29" s="14"/>
+      <c r="R29" s="14"/>
+      <c r="S29" s="14"/>
+      <c r="T29" s="14"/>
+      <c r="U29" s="14"/>
+      <c r="V29" s="14"/>
+      <c r="W29" s="14"/>
+      <c r="X29" s="14"/>
+      <c r="Y29" s="14"/>
+    </row>
+    <row r="30" ht="15.0" customHeight="1">
+      <c r="A30" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="B30" s="13">
+        <v>0.0</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="14"/>
+      <c r="L30" s="14"/>
+      <c r="M30" s="14"/>
+      <c r="N30" s="14"/>
+      <c r="O30" s="14"/>
+      <c r="P30" s="14"/>
+      <c r="Q30" s="14"/>
+      <c r="R30" s="14"/>
+      <c r="S30" s="14"/>
+      <c r="T30" s="14"/>
+      <c r="U30" s="14"/>
+      <c r="V30" s="14"/>
+      <c r="W30" s="14"/>
+      <c r="X30" s="14"/>
+      <c r="Y30" s="14"/>
+    </row>
+    <row r="31" ht="15.0" customHeight="1">
+      <c r="A31" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B31" s="13">
+        <v>0.0</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
+      <c r="M31" s="14"/>
+      <c r="N31" s="14"/>
+      <c r="O31" s="14"/>
+      <c r="P31" s="14"/>
+      <c r="Q31" s="14"/>
+      <c r="R31" s="14"/>
+      <c r="S31" s="14"/>
+      <c r="T31" s="14"/>
+      <c r="U31" s="14"/>
+      <c r="V31" s="14"/>
+      <c r="W31" s="14"/>
+      <c r="X31" s="14"/>
+      <c r="Y31" s="14"/>
+    </row>
+    <row r="32" ht="15.0" customHeight="1">
+      <c r="A32" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="B32" s="13">
+        <v>0.0</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="E32" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
+      <c r="K32" s="14"/>
+      <c r="L32" s="14"/>
+      <c r="M32" s="14"/>
+      <c r="N32" s="14"/>
+      <c r="O32" s="14"/>
+      <c r="P32" s="14"/>
+      <c r="Q32" s="14"/>
+      <c r="R32" s="14"/>
+      <c r="S32" s="14"/>
+      <c r="T32" s="14"/>
+      <c r="U32" s="14"/>
+      <c r="V32" s="14"/>
+      <c r="W32" s="14"/>
+      <c r="X32" s="14"/>
+      <c r="Y32" s="14"/>
+    </row>
+    <row r="33" ht="15.0" customHeight="1">
+      <c r="A33" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="B33" s="13">
+        <v>0.0</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14"/>
+      <c r="K33" s="14"/>
+      <c r="L33" s="14"/>
+      <c r="M33" s="14"/>
+      <c r="N33" s="14"/>
+      <c r="O33" s="14"/>
+      <c r="P33" s="14"/>
+      <c r="Q33" s="14"/>
+      <c r="R33" s="14"/>
+      <c r="S33" s="14"/>
+      <c r="T33" s="14"/>
+      <c r="U33" s="14"/>
+      <c r="V33" s="14"/>
+      <c r="W33" s="14"/>
+      <c r="X33" s="14"/>
+      <c r="Y33" s="14"/>
+    </row>
+    <row r="34" ht="15.0" customHeight="1">
+      <c r="A34" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="B34" s="13">
+        <v>0.0</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="E34" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="14"/>
+      <c r="K34" s="14"/>
+      <c r="L34" s="14"/>
+      <c r="M34" s="14"/>
+      <c r="N34" s="14"/>
+      <c r="O34" s="14"/>
+      <c r="P34" s="14"/>
+      <c r="Q34" s="14"/>
+      <c r="R34" s="14"/>
+      <c r="S34" s="14"/>
+      <c r="T34" s="14"/>
+      <c r="U34" s="14"/>
+      <c r="V34" s="14"/>
+      <c r="W34" s="14"/>
+      <c r="X34" s="14"/>
+      <c r="Y34" s="14"/>
+    </row>
+    <row r="35" ht="15.0" customHeight="1">
+      <c r="A35" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="B35" s="13">
+        <v>0.0</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="14"/>
+      <c r="K35" s="14"/>
+      <c r="L35" s="14"/>
+      <c r="M35" s="14"/>
+      <c r="N35" s="14"/>
+      <c r="O35" s="14"/>
+      <c r="P35" s="14"/>
+      <c r="Q35" s="14"/>
+      <c r="R35" s="14"/>
+      <c r="S35" s="14"/>
+      <c r="T35" s="14"/>
+      <c r="U35" s="14"/>
+      <c r="V35" s="14"/>
+      <c r="W35" s="14"/>
+      <c r="X35" s="14"/>
+      <c r="Y35" s="14"/>
+    </row>
+    <row r="36" ht="15.0" customHeight="1">
+      <c r="A36" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="B36" s="13">
+        <v>0.0</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="D36" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="E36" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="14"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="14"/>
+      <c r="M36" s="14"/>
+      <c r="N36" s="14"/>
+      <c r="O36" s="14"/>
+      <c r="P36" s="14"/>
+      <c r="Q36" s="14"/>
+      <c r="R36" s="14"/>
+      <c r="S36" s="14"/>
+      <c r="T36" s="14"/>
+      <c r="U36" s="14"/>
+      <c r="V36" s="14"/>
+      <c r="W36" s="14"/>
+      <c r="X36" s="14"/>
+      <c r="Y36" s="14"/>
+    </row>
+    <row r="37" ht="15.0" customHeight="1">
+      <c r="A37" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="B37" s="13">
+        <v>0.0</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
+      <c r="K37" s="14"/>
+      <c r="L37" s="14"/>
+      <c r="M37" s="14"/>
+      <c r="N37" s="14"/>
+      <c r="O37" s="14"/>
+      <c r="P37" s="14"/>
+      <c r="Q37" s="14"/>
+      <c r="R37" s="14"/>
+      <c r="S37" s="14"/>
+      <c r="T37" s="14"/>
+      <c r="U37" s="14"/>
+      <c r="V37" s="14"/>
+      <c r="W37" s="14"/>
+      <c r="X37" s="14"/>
+      <c r="Y37" s="14"/>
+    </row>
+    <row r="38" ht="15.0" customHeight="1">
+      <c r="A38" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="B38" s="13">
+        <v>0.0</v>
+      </c>
+      <c r="C38" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="D38" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="E38" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="14"/>
+      <c r="J38" s="14"/>
+      <c r="K38" s="14"/>
+      <c r="L38" s="14"/>
+      <c r="M38" s="14"/>
+      <c r="N38" s="14"/>
+      <c r="O38" s="14"/>
+      <c r="P38" s="14"/>
+      <c r="Q38" s="14"/>
+      <c r="R38" s="14"/>
+      <c r="S38" s="14"/>
+      <c r="T38" s="14"/>
+      <c r="U38" s="14"/>
+      <c r="V38" s="14"/>
+      <c r="W38" s="14"/>
+      <c r="X38" s="14"/>
+      <c r="Y38" s="14"/>
+    </row>
+    <row r="39" ht="15.0" customHeight="1">
+      <c r="A39" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="B39" s="13">
+        <v>0.0</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="D39" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="F39" s="14"/>
+      <c r="G39" s="14"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="14"/>
+      <c r="J39" s="14"/>
+      <c r="K39" s="14"/>
+      <c r="L39" s="14"/>
+      <c r="M39" s="14"/>
+      <c r="N39" s="14"/>
+      <c r="O39" s="14"/>
+      <c r="P39" s="14"/>
+      <c r="Q39" s="14"/>
+      <c r="R39" s="14"/>
+      <c r="S39" s="14"/>
+      <c r="T39" s="14"/>
+      <c r="U39" s="14"/>
+      <c r="V39" s="14"/>
+      <c r="W39" s="14"/>
+      <c r="X39" s="14"/>
+      <c r="Y39" s="14"/>
+    </row>
+    <row r="40" ht="15.0" customHeight="1">
+      <c r="A40" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="B40" s="13">
+        <v>0.0</v>
+      </c>
+      <c r="C40" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="D40" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="E40" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="F40" s="14"/>
+      <c r="G40" s="14"/>
+      <c r="H40" s="14"/>
+      <c r="I40" s="14"/>
+      <c r="J40" s="14"/>
+      <c r="K40" s="14"/>
+      <c r="L40" s="14"/>
+      <c r="M40" s="14"/>
+      <c r="N40" s="14"/>
+      <c r="O40" s="14"/>
+      <c r="P40" s="14"/>
+      <c r="Q40" s="14"/>
+      <c r="R40" s="14"/>
+      <c r="S40" s="14"/>
+      <c r="T40" s="14"/>
+      <c r="U40" s="14"/>
+      <c r="V40" s="14"/>
+      <c r="W40" s="14"/>
+      <c r="X40" s="14"/>
+      <c r="Y40" s="14"/>
+    </row>
+    <row r="41" ht="15.0" customHeight="1">
+      <c r="A41" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="B41" s="13">
+        <v>0.0</v>
+      </c>
+      <c r="C41" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="D41" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="E41" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="F41" s="14"/>
+      <c r="G41" s="14"/>
+      <c r="H41" s="14"/>
+      <c r="I41" s="14"/>
+      <c r="J41" s="14"/>
+      <c r="K41" s="14"/>
+      <c r="L41" s="14"/>
+      <c r="M41" s="14"/>
+      <c r="N41" s="14"/>
+      <c r="O41" s="14"/>
+      <c r="P41" s="14"/>
+      <c r="Q41" s="14"/>
+      <c r="R41" s="14"/>
+      <c r="S41" s="14"/>
+      <c r="T41" s="14"/>
+      <c r="U41" s="14"/>
+      <c r="V41" s="14"/>
+      <c r="W41" s="14"/>
+      <c r="X41" s="14"/>
+      <c r="Y41" s="14"/>
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="A42" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="B42" s="13">
+        <v>0.0</v>
+      </c>
+      <c r="C42" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="D42" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="E42" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="F42" s="14"/>
+      <c r="G42" s="14"/>
+      <c r="H42" s="14"/>
+      <c r="I42" s="14"/>
+      <c r="J42" s="14"/>
+      <c r="K42" s="14"/>
+      <c r="L42" s="14"/>
+      <c r="M42" s="14"/>
+      <c r="N42" s="14"/>
+      <c r="O42" s="14"/>
+      <c r="P42" s="14"/>
+      <c r="Q42" s="14"/>
+      <c r="R42" s="14"/>
+      <c r="S42" s="14"/>
+      <c r="T42" s="14"/>
+      <c r="U42" s="14"/>
+      <c r="V42" s="14"/>
+      <c r="W42" s="14"/>
+      <c r="X42" s="14"/>
+      <c r="Y42" s="14"/>
+    </row>
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="A43" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="B43" s="13">
+        <v>0.0</v>
+      </c>
+      <c r="C43" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="D43" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="E43" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
+      <c r="H43" s="14"/>
+      <c r="I43" s="14"/>
+      <c r="J43" s="14"/>
+      <c r="K43" s="14"/>
+      <c r="L43" s="14"/>
+      <c r="M43" s="14"/>
+      <c r="N43" s="14"/>
+      <c r="O43" s="14"/>
+      <c r="P43" s="14"/>
+      <c r="Q43" s="14"/>
+      <c r="R43" s="14"/>
+      <c r="S43" s="14"/>
+      <c r="T43" s="14"/>
+      <c r="U43" s="14"/>
+      <c r="V43" s="14"/>
+      <c r="W43" s="14"/>
+      <c r="X43" s="14"/>
+      <c r="Y43" s="14"/>
+    </row>
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="A44" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="B44" s="13">
+        <v>0.0</v>
+      </c>
+      <c r="C44" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="D44" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="E44" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="F44" s="14"/>
+      <c r="G44" s="14"/>
+      <c r="H44" s="14"/>
+      <c r="I44" s="14"/>
+      <c r="J44" s="14"/>
+      <c r="K44" s="14"/>
+      <c r="L44" s="14"/>
+      <c r="M44" s="14"/>
+      <c r="N44" s="14"/>
+      <c r="O44" s="14"/>
+      <c r="P44" s="14"/>
+      <c r="Q44" s="14"/>
+      <c r="R44" s="14"/>
+      <c r="S44" s="14"/>
+      <c r="T44" s="14"/>
+      <c r="U44" s="14"/>
+      <c r="V44" s="14"/>
+      <c r="W44" s="14"/>
+      <c r="X44" s="14"/>
+      <c r="Y44" s="14"/>
+    </row>
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="A45" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="B45" s="13">
+        <v>0.0</v>
+      </c>
+      <c r="C45" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="D45" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="E45" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="F45" s="14"/>
+      <c r="G45" s="14"/>
+      <c r="H45" s="14"/>
+      <c r="I45" s="14"/>
+      <c r="J45" s="14"/>
+      <c r="K45" s="14"/>
+      <c r="L45" s="14"/>
+      <c r="M45" s="14"/>
+      <c r="N45" s="14"/>
+      <c r="O45" s="14"/>
+      <c r="P45" s="14"/>
+      <c r="Q45" s="14"/>
+      <c r="R45" s="14"/>
+      <c r="S45" s="14"/>
+      <c r="T45" s="14"/>
+      <c r="U45" s="14"/>
+      <c r="V45" s="14"/>
+      <c r="W45" s="14"/>
+      <c r="X45" s="14"/>
+      <c r="Y45" s="14"/>
+    </row>
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="B46" s="13">
+        <v>0.0</v>
+      </c>
+      <c r="C46" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="D46" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="E46" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="F46" s="14"/>
+      <c r="G46" s="14"/>
+      <c r="H46" s="14"/>
+      <c r="I46" s="14"/>
+      <c r="J46" s="14"/>
+      <c r="K46" s="14"/>
+      <c r="L46" s="14"/>
+      <c r="M46" s="14"/>
+      <c r="N46" s="14"/>
+      <c r="O46" s="14"/>
+      <c r="P46" s="14"/>
+      <c r="Q46" s="14"/>
+      <c r="R46" s="14"/>
+      <c r="S46" s="14"/>
+      <c r="T46" s="14"/>
+      <c r="U46" s="14"/>
+      <c r="V46" s="14"/>
+      <c r="W46" s="14"/>
+      <c r="X46" s="14"/>
+      <c r="Y46" s="14"/>
+    </row>
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="A47" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="B47" s="13">
+        <v>0.0</v>
+      </c>
+      <c r="C47" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="D47" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="E47" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="F47" s="14"/>
+      <c r="G47" s="14"/>
+      <c r="H47" s="14"/>
+      <c r="I47" s="14"/>
+      <c r="J47" s="14"/>
+      <c r="K47" s="14"/>
+      <c r="L47" s="14"/>
+      <c r="M47" s="14"/>
+      <c r="N47" s="14"/>
+      <c r="O47" s="14"/>
+      <c r="P47" s="14"/>
+      <c r="Q47" s="14"/>
+      <c r="R47" s="14"/>
+      <c r="S47" s="14"/>
+      <c r="T47" s="14"/>
+      <c r="U47" s="14"/>
+      <c r="V47" s="14"/>
+      <c r="W47" s="14"/>
+      <c r="X47" s="14"/>
+      <c r="Y47" s="14"/>
+    </row>
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="A48" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="B48" s="13">
+        <v>0.0</v>
+      </c>
+      <c r="C48" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="D48" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="E48" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="F48" s="14"/>
+      <c r="G48" s="14"/>
+      <c r="H48" s="14"/>
+      <c r="I48" s="14"/>
+      <c r="J48" s="14"/>
+      <c r="K48" s="14"/>
+      <c r="L48" s="14"/>
+      <c r="M48" s="14"/>
+      <c r="N48" s="14"/>
+      <c r="O48" s="14"/>
+      <c r="P48" s="14"/>
+      <c r="Q48" s="14"/>
+      <c r="R48" s="14"/>
+      <c r="S48" s="14"/>
+      <c r="T48" s="14"/>
+      <c r="U48" s="14"/>
+      <c r="V48" s="14"/>
+      <c r="W48" s="14"/>
+      <c r="X48" s="14"/>
+      <c r="Y48" s="14"/>
+    </row>
+    <row r="49" ht="15.0" customHeight="1">
+      <c r="A49" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="B49" s="13">
+        <v>0.0</v>
+      </c>
+      <c r="C49" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="D49" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="E49" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="F49" s="14"/>
+      <c r="G49" s="14"/>
+      <c r="H49" s="14"/>
+      <c r="I49" s="14"/>
+      <c r="J49" s="14"/>
+      <c r="K49" s="14"/>
+      <c r="L49" s="14"/>
+      <c r="M49" s="14"/>
+      <c r="N49" s="14"/>
+      <c r="O49" s="14"/>
+      <c r="P49" s="14"/>
+      <c r="Q49" s="14"/>
+      <c r="R49" s="14"/>
+      <c r="S49" s="14"/>
+      <c r="T49" s="14"/>
+      <c r="U49" s="14"/>
+      <c r="V49" s="14"/>
+      <c r="W49" s="14"/>
+      <c r="X49" s="14"/>
+      <c r="Y49" s="14"/>
+    </row>
+    <row r="50" ht="15.0" customHeight="1">
+      <c r="A50" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="B50" s="13">
+        <v>0.0</v>
+      </c>
+      <c r="C50" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="D50" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="7"/>
-      <c r="N19" s="7"/>
-      <c r="O19" s="7"/>
-      <c r="P19" s="7"/>
-      <c r="Q19" s="7"/>
-      <c r="R19" s="7"/>
-      <c r="S19" s="7"/>
-      <c r="T19" s="7"/>
-      <c r="U19" s="7"/>
-      <c r="V19" s="7"/>
-      <c r="W19" s="7"/>
-      <c r="X19" s="7"/>
-      <c r="Y19" s="7"/>
-    </row>
-    <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B20" s="6">
+      <c r="E50" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="F50" s="14"/>
+      <c r="G50" s="14"/>
+      <c r="H50" s="14"/>
+      <c r="I50" s="14"/>
+      <c r="J50" s="14"/>
+      <c r="K50" s="14"/>
+      <c r="L50" s="14"/>
+      <c r="M50" s="14"/>
+      <c r="N50" s="14"/>
+      <c r="O50" s="14"/>
+      <c r="P50" s="14"/>
+      <c r="Q50" s="14"/>
+      <c r="R50" s="14"/>
+      <c r="S50" s="14"/>
+      <c r="T50" s="14"/>
+      <c r="U50" s="14"/>
+      <c r="V50" s="14"/>
+      <c r="W50" s="14"/>
+      <c r="X50" s="14"/>
+      <c r="Y50" s="14"/>
+    </row>
+    <row r="51" ht="15.0" customHeight="1">
+      <c r="A51" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="B51" s="13">
         <v>0.0</v>
       </c>
-      <c r="C20" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7"/>
-      <c r="N20" s="7"/>
-      <c r="O20" s="7"/>
-      <c r="P20" s="7"/>
-      <c r="Q20" s="7"/>
-      <c r="R20" s="7"/>
-      <c r="S20" s="7"/>
-      <c r="T20" s="7"/>
-      <c r="U20" s="7"/>
-      <c r="V20" s="7"/>
-      <c r="W20" s="7"/>
-      <c r="X20" s="7"/>
-      <c r="Y20" s="7"/>
-    </row>
-    <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B21" s="6">
+      <c r="C51" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="D51" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="E51" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="F51" s="14"/>
+      <c r="G51" s="14"/>
+      <c r="H51" s="14"/>
+      <c r="I51" s="14"/>
+      <c r="J51" s="14"/>
+      <c r="K51" s="14"/>
+      <c r="L51" s="14"/>
+      <c r="M51" s="14"/>
+      <c r="N51" s="14"/>
+      <c r="O51" s="14"/>
+      <c r="P51" s="14"/>
+      <c r="Q51" s="14"/>
+      <c r="R51" s="14"/>
+      <c r="S51" s="14"/>
+      <c r="T51" s="14"/>
+      <c r="U51" s="14"/>
+      <c r="V51" s="14"/>
+      <c r="W51" s="14"/>
+      <c r="X51" s="14"/>
+      <c r="Y51" s="14"/>
+    </row>
+    <row r="52" ht="15.0" customHeight="1">
+      <c r="A52" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="B52" s="13">
         <v>0.0</v>
       </c>
-      <c r="C21" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="7"/>
-      <c r="N21" s="7"/>
-      <c r="O21" s="7"/>
-      <c r="P21" s="7"/>
-      <c r="Q21" s="7"/>
-      <c r="R21" s="7"/>
-      <c r="S21" s="7"/>
-      <c r="T21" s="7"/>
-      <c r="U21" s="7"/>
-      <c r="V21" s="7"/>
-      <c r="W21" s="7"/>
-      <c r="X21" s="7"/>
-      <c r="Y21" s="7"/>
-    </row>
-    <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B22" s="6">
+      <c r="C52" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="D52" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="E52" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="F52" s="14"/>
+      <c r="G52" s="14"/>
+      <c r="H52" s="14"/>
+      <c r="I52" s="14"/>
+      <c r="J52" s="14"/>
+      <c r="K52" s="14"/>
+      <c r="L52" s="14"/>
+      <c r="M52" s="14"/>
+      <c r="N52" s="14"/>
+      <c r="O52" s="14"/>
+      <c r="P52" s="14"/>
+      <c r="Q52" s="14"/>
+      <c r="R52" s="14"/>
+      <c r="S52" s="14"/>
+      <c r="T52" s="14"/>
+      <c r="U52" s="14"/>
+      <c r="V52" s="14"/>
+      <c r="W52" s="14"/>
+      <c r="X52" s="14"/>
+      <c r="Y52" s="14"/>
+    </row>
+    <row r="53" ht="15.0" customHeight="1">
+      <c r="A53" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="B53" s="13">
         <v>0.0</v>
       </c>
-      <c r="C22" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7"/>
-      <c r="N22" s="7"/>
-      <c r="O22" s="7"/>
-      <c r="P22" s="7"/>
-      <c r="Q22" s="7"/>
-      <c r="R22" s="7"/>
-      <c r="S22" s="7"/>
-      <c r="T22" s="7"/>
-      <c r="U22" s="7"/>
-      <c r="V22" s="7"/>
-      <c r="W22" s="7"/>
-      <c r="X22" s="7"/>
-      <c r="Y22" s="7"/>
-    </row>
-    <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B23" s="6">
+      <c r="C53" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="D53" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="E53" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="F53" s="14"/>
+      <c r="G53" s="14"/>
+      <c r="H53" s="14"/>
+      <c r="I53" s="14"/>
+      <c r="J53" s="14"/>
+      <c r="K53" s="14"/>
+      <c r="L53" s="14"/>
+      <c r="M53" s="14"/>
+      <c r="N53" s="14"/>
+      <c r="O53" s="14"/>
+      <c r="P53" s="14"/>
+      <c r="Q53" s="14"/>
+      <c r="R53" s="14"/>
+      <c r="S53" s="14"/>
+      <c r="T53" s="14"/>
+      <c r="U53" s="14"/>
+      <c r="V53" s="14"/>
+      <c r="W53" s="14"/>
+      <c r="X53" s="14"/>
+      <c r="Y53" s="14"/>
+    </row>
+    <row r="54" ht="15.0" customHeight="1">
+      <c r="A54" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="B54" s="13">
         <v>0.0</v>
       </c>
-      <c r="C23" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="7"/>
-      <c r="M23" s="7"/>
-      <c r="N23" s="7"/>
-      <c r="O23" s="7"/>
-      <c r="P23" s="7"/>
-      <c r="Q23" s="7"/>
-      <c r="R23" s="7"/>
-      <c r="S23" s="7"/>
-      <c r="T23" s="7"/>
-      <c r="U23" s="7"/>
-      <c r="V23" s="7"/>
-      <c r="W23" s="7"/>
-      <c r="X23" s="7"/>
-      <c r="Y23" s="7"/>
-    </row>
-    <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="B24" s="11">
+      <c r="C54" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="D54" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="E54" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="F54" s="14"/>
+      <c r="G54" s="14"/>
+      <c r="H54" s="14"/>
+      <c r="I54" s="14"/>
+      <c r="J54" s="14"/>
+      <c r="K54" s="14"/>
+      <c r="L54" s="14"/>
+      <c r="M54" s="14"/>
+      <c r="N54" s="14"/>
+      <c r="O54" s="14"/>
+      <c r="P54" s="14"/>
+      <c r="Q54" s="14"/>
+      <c r="R54" s="14"/>
+      <c r="S54" s="14"/>
+      <c r="T54" s="14"/>
+      <c r="U54" s="14"/>
+      <c r="V54" s="14"/>
+      <c r="W54" s="14"/>
+      <c r="X54" s="14"/>
+      <c r="Y54" s="14"/>
+    </row>
+    <row r="55" ht="15.0" customHeight="1">
+      <c r="A55" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="B55" s="13">
         <v>0.0</v>
       </c>
-      <c r="C24" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="E24" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12"/>
-      <c r="J24" s="12"/>
-      <c r="K24" s="12"/>
-      <c r="L24" s="12"/>
-      <c r="M24" s="12"/>
-      <c r="N24" s="12"/>
-      <c r="O24" s="12"/>
-      <c r="P24" s="12"/>
-      <c r="Q24" s="12"/>
-      <c r="R24" s="12"/>
-      <c r="S24" s="12"/>
-      <c r="T24" s="12"/>
-      <c r="U24" s="12"/>
-      <c r="V24" s="12"/>
-      <c r="W24" s="12"/>
-      <c r="X24" s="12"/>
-      <c r="Y24" s="12"/>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="B25" s="14">
+      <c r="C55" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="D55" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="E55" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="F55" s="14"/>
+      <c r="G55" s="14"/>
+      <c r="H55" s="14"/>
+      <c r="I55" s="14"/>
+      <c r="J55" s="14"/>
+      <c r="K55" s="14"/>
+      <c r="L55" s="14"/>
+      <c r="M55" s="14"/>
+      <c r="N55" s="14"/>
+      <c r="O55" s="14"/>
+      <c r="P55" s="14"/>
+      <c r="Q55" s="14"/>
+      <c r="R55" s="14"/>
+      <c r="S55" s="14"/>
+      <c r="T55" s="14"/>
+      <c r="U55" s="14"/>
+      <c r="V55" s="14"/>
+      <c r="W55" s="14"/>
+      <c r="X55" s="14"/>
+      <c r="Y55" s="14"/>
+    </row>
+    <row r="56" ht="15.0" customHeight="1">
+      <c r="A56" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="B56" s="13">
         <v>0.0</v>
       </c>
-      <c r="C25" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="D25" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="E25" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
-      <c r="J25" s="15"/>
-      <c r="K25" s="15"/>
-      <c r="L25" s="15"/>
-      <c r="M25" s="15"/>
-      <c r="N25" s="15"/>
-      <c r="O25" s="15"/>
-      <c r="P25" s="15"/>
-      <c r="Q25" s="15"/>
-      <c r="R25" s="15"/>
-      <c r="S25" s="15"/>
-      <c r="T25" s="15"/>
-      <c r="U25" s="15"/>
-      <c r="V25" s="15"/>
-      <c r="W25" s="15"/>
-      <c r="X25" s="15"/>
-      <c r="Y25" s="15"/>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="B26" s="17">
+      <c r="C56" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="D56" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="E56" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="F56" s="14"/>
+      <c r="G56" s="14"/>
+      <c r="H56" s="14"/>
+      <c r="I56" s="14"/>
+      <c r="J56" s="14"/>
+      <c r="K56" s="14"/>
+      <c r="L56" s="14"/>
+      <c r="M56" s="14"/>
+      <c r="N56" s="14"/>
+      <c r="O56" s="14"/>
+      <c r="P56" s="14"/>
+      <c r="Q56" s="14"/>
+      <c r="R56" s="14"/>
+      <c r="S56" s="14"/>
+      <c r="T56" s="14"/>
+      <c r="U56" s="14"/>
+      <c r="V56" s="14"/>
+      <c r="W56" s="14"/>
+      <c r="X56" s="14"/>
+      <c r="Y56" s="14"/>
+    </row>
+    <row r="57" ht="15.0" customHeight="1">
+      <c r="A57" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="B57" s="13">
         <v>0.0</v>
       </c>
-      <c r="C26" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="D26" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="E26" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="18"/>
-      <c r="I26" s="18"/>
-      <c r="J26" s="18"/>
-      <c r="K26" s="18"/>
-      <c r="L26" s="18"/>
-      <c r="M26" s="18"/>
-      <c r="N26" s="18"/>
-      <c r="O26" s="18"/>
-      <c r="P26" s="18"/>
-      <c r="Q26" s="18"/>
-      <c r="R26" s="18"/>
-      <c r="S26" s="18"/>
-      <c r="T26" s="18"/>
-      <c r="U26" s="18"/>
-      <c r="V26" s="18"/>
-      <c r="W26" s="18"/>
-      <c r="X26" s="18"/>
-      <c r="Y26" s="18"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="B27" s="17">
+      <c r="C57" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="D57" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="E57" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="F57" s="14"/>
+      <c r="G57" s="14"/>
+      <c r="H57" s="14"/>
+      <c r="I57" s="14"/>
+      <c r="J57" s="14"/>
+      <c r="K57" s="14"/>
+      <c r="L57" s="14"/>
+      <c r="M57" s="14"/>
+      <c r="N57" s="14"/>
+      <c r="O57" s="14"/>
+      <c r="P57" s="14"/>
+      <c r="Q57" s="14"/>
+      <c r="R57" s="14"/>
+      <c r="S57" s="14"/>
+      <c r="T57" s="14"/>
+      <c r="U57" s="14"/>
+      <c r="V57" s="14"/>
+      <c r="W57" s="14"/>
+      <c r="X57" s="14"/>
+      <c r="Y57" s="14"/>
+    </row>
+    <row r="58" ht="15.0" customHeight="1">
+      <c r="A58" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="B58" s="13">
         <v>0.0</v>
       </c>
-      <c r="C27" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="D27" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="E27" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="18"/>
-      <c r="I27" s="18"/>
-      <c r="J27" s="18"/>
-      <c r="K27" s="18"/>
-      <c r="L27" s="18"/>
-      <c r="M27" s="18"/>
-      <c r="N27" s="18"/>
-      <c r="O27" s="18"/>
-      <c r="P27" s="18"/>
-      <c r="Q27" s="18"/>
-      <c r="R27" s="18"/>
-      <c r="S27" s="18"/>
-      <c r="T27" s="18"/>
-      <c r="U27" s="18"/>
-      <c r="V27" s="18"/>
-      <c r="W27" s="18"/>
-      <c r="X27" s="18"/>
-      <c r="Y27" s="18"/>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="B28" s="17">
+      <c r="C58" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="D58" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="E58" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="F58" s="14"/>
+      <c r="G58" s="14"/>
+      <c r="H58" s="14"/>
+      <c r="I58" s="14"/>
+      <c r="J58" s="14"/>
+      <c r="K58" s="14"/>
+      <c r="L58" s="14"/>
+      <c r="M58" s="14"/>
+      <c r="N58" s="14"/>
+      <c r="O58" s="14"/>
+      <c r="P58" s="14"/>
+      <c r="Q58" s="14"/>
+      <c r="R58" s="14"/>
+      <c r="S58" s="14"/>
+      <c r="T58" s="14"/>
+      <c r="U58" s="14"/>
+      <c r="V58" s="14"/>
+      <c r="W58" s="14"/>
+      <c r="X58" s="14"/>
+      <c r="Y58" s="14"/>
+    </row>
+    <row r="59" ht="15.0" customHeight="1">
+      <c r="A59" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="B59" s="13">
         <v>0.0</v>
       </c>
-      <c r="C28" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="D28" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="E28" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="18"/>
-      <c r="I28" s="18"/>
-      <c r="J28" s="18"/>
-      <c r="K28" s="18"/>
-      <c r="L28" s="18"/>
-      <c r="M28" s="18"/>
-      <c r="N28" s="18"/>
-      <c r="O28" s="18"/>
-      <c r="P28" s="18"/>
-      <c r="Q28" s="18"/>
-      <c r="R28" s="18"/>
-      <c r="S28" s="18"/>
-      <c r="T28" s="18"/>
-      <c r="U28" s="18"/>
-      <c r="V28" s="18"/>
-      <c r="W28" s="18"/>
-      <c r="X28" s="18"/>
-      <c r="Y28" s="18"/>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="B29" s="17">
+      <c r="C59" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="D59" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="E59" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="F59" s="14"/>
+      <c r="G59" s="14"/>
+      <c r="H59" s="14"/>
+      <c r="I59" s="14"/>
+      <c r="J59" s="14"/>
+      <c r="K59" s="14"/>
+      <c r="L59" s="14"/>
+      <c r="M59" s="14"/>
+      <c r="N59" s="14"/>
+      <c r="O59" s="14"/>
+      <c r="P59" s="14"/>
+      <c r="Q59" s="14"/>
+      <c r="R59" s="14"/>
+      <c r="S59" s="14"/>
+      <c r="T59" s="14"/>
+      <c r="U59" s="14"/>
+      <c r="V59" s="14"/>
+      <c r="W59" s="14"/>
+      <c r="X59" s="14"/>
+      <c r="Y59" s="14"/>
+    </row>
+    <row r="60" ht="15.0" customHeight="1">
+      <c r="A60" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="B60" s="13">
         <v>0.0</v>
       </c>
-      <c r="C29" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="D29" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="E29" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="18"/>
-      <c r="I29" s="18"/>
-      <c r="J29" s="18"/>
-      <c r="K29" s="18"/>
-      <c r="L29" s="18"/>
-      <c r="M29" s="18"/>
-      <c r="N29" s="18"/>
-      <c r="O29" s="18"/>
-      <c r="P29" s="18"/>
-      <c r="Q29" s="18"/>
-      <c r="R29" s="18"/>
-      <c r="S29" s="18"/>
-      <c r="T29" s="18"/>
-      <c r="U29" s="18"/>
-      <c r="V29" s="18"/>
-      <c r="W29" s="18"/>
-      <c r="X29" s="18"/>
-      <c r="Y29" s="18"/>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="B30" s="17">
+      <c r="C60" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="D60" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="E60" s="14" t="s">
+        <v>238</v>
+      </c>
+      <c r="F60" s="14"/>
+      <c r="G60" s="14"/>
+      <c r="H60" s="14"/>
+      <c r="I60" s="14"/>
+      <c r="J60" s="14"/>
+      <c r="K60" s="14"/>
+      <c r="L60" s="14"/>
+      <c r="M60" s="14"/>
+      <c r="N60" s="14"/>
+      <c r="O60" s="14"/>
+      <c r="P60" s="14"/>
+      <c r="Q60" s="14"/>
+      <c r="R60" s="14"/>
+      <c r="S60" s="14"/>
+      <c r="T60" s="14"/>
+      <c r="U60" s="14"/>
+      <c r="V60" s="14"/>
+      <c r="W60" s="14"/>
+      <c r="X60" s="14"/>
+      <c r="Y60" s="14"/>
+    </row>
+    <row r="61" ht="15.0" customHeight="1">
+      <c r="A61" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="B61" s="13">
         <v>0.0</v>
       </c>
-      <c r="C30" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="D30" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="E30" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="18"/>
-      <c r="I30" s="18"/>
-      <c r="J30" s="18"/>
-      <c r="K30" s="18"/>
-      <c r="L30" s="18"/>
-      <c r="M30" s="18"/>
-      <c r="N30" s="18"/>
-      <c r="O30" s="18"/>
-      <c r="P30" s="18"/>
-      <c r="Q30" s="18"/>
-      <c r="R30" s="18"/>
-      <c r="S30" s="18"/>
-      <c r="T30" s="18"/>
-      <c r="U30" s="18"/>
-      <c r="V30" s="18"/>
-      <c r="W30" s="18"/>
-      <c r="X30" s="18"/>
-      <c r="Y30" s="18"/>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="B31" s="17">
+      <c r="C61" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="D61" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="E61" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="F61" s="14"/>
+      <c r="G61" s="14"/>
+      <c r="H61" s="14"/>
+      <c r="I61" s="14"/>
+      <c r="J61" s="14"/>
+      <c r="K61" s="14"/>
+      <c r="L61" s="14"/>
+      <c r="M61" s="14"/>
+      <c r="N61" s="14"/>
+      <c r="O61" s="14"/>
+      <c r="P61" s="14"/>
+      <c r="Q61" s="14"/>
+      <c r="R61" s="14"/>
+      <c r="S61" s="14"/>
+      <c r="T61" s="14"/>
+      <c r="U61" s="14"/>
+      <c r="V61" s="14"/>
+      <c r="W61" s="14"/>
+      <c r="X61" s="14"/>
+      <c r="Y61" s="14"/>
+    </row>
+    <row r="62" ht="15.0" customHeight="1">
+      <c r="A62" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="B62" s="13">
         <v>0.0</v>
       </c>
-      <c r="C31" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="D31" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="E31" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="18"/>
-      <c r="I31" s="18"/>
-      <c r="J31" s="18"/>
-      <c r="K31" s="18"/>
-      <c r="L31" s="18"/>
-      <c r="M31" s="18"/>
-      <c r="N31" s="18"/>
-      <c r="O31" s="18"/>
-      <c r="P31" s="18"/>
-      <c r="Q31" s="18"/>
-      <c r="R31" s="18"/>
-      <c r="S31" s="18"/>
-      <c r="T31" s="18"/>
-      <c r="U31" s="18"/>
-      <c r="V31" s="18"/>
-      <c r="W31" s="18"/>
-      <c r="X31" s="18"/>
-      <c r="Y31" s="18"/>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="B32" s="17">
+      <c r="C62" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="D62" s="14" t="s">
+        <v>245</v>
+      </c>
+      <c r="E62" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="F62" s="14"/>
+      <c r="G62" s="14"/>
+      <c r="H62" s="14"/>
+      <c r="I62" s="14"/>
+      <c r="J62" s="14"/>
+      <c r="K62" s="14"/>
+      <c r="L62" s="14"/>
+      <c r="M62" s="14"/>
+      <c r="N62" s="14"/>
+      <c r="O62" s="14"/>
+      <c r="P62" s="14"/>
+      <c r="Q62" s="14"/>
+      <c r="R62" s="14"/>
+      <c r="S62" s="14"/>
+      <c r="T62" s="14"/>
+      <c r="U62" s="14"/>
+      <c r="V62" s="14"/>
+      <c r="W62" s="14"/>
+      <c r="X62" s="14"/>
+      <c r="Y62" s="14"/>
+    </row>
+    <row r="63" ht="15.0" customHeight="1">
+      <c r="A63" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="B63" s="13">
         <v>0.0</v>
       </c>
-      <c r="C32" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="D32" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="E32" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="18"/>
-      <c r="J32" s="18"/>
-      <c r="K32" s="18"/>
-      <c r="L32" s="18"/>
-      <c r="M32" s="18"/>
-      <c r="N32" s="18"/>
-      <c r="O32" s="18"/>
-      <c r="P32" s="18"/>
-      <c r="Q32" s="18"/>
-      <c r="R32" s="18"/>
-      <c r="S32" s="18"/>
-      <c r="T32" s="18"/>
-      <c r="U32" s="18"/>
-      <c r="V32" s="18"/>
-      <c r="W32" s="18"/>
-      <c r="X32" s="18"/>
-      <c r="Y32" s="18"/>
-    </row>
-    <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="B33" s="17">
+      <c r="C63" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="D63" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="E63" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="F63" s="14"/>
+      <c r="G63" s="14"/>
+      <c r="H63" s="14"/>
+      <c r="I63" s="14"/>
+      <c r="J63" s="14"/>
+      <c r="K63" s="14"/>
+      <c r="L63" s="14"/>
+      <c r="M63" s="14"/>
+      <c r="N63" s="14"/>
+      <c r="O63" s="14"/>
+      <c r="P63" s="14"/>
+      <c r="Q63" s="14"/>
+      <c r="R63" s="14"/>
+      <c r="S63" s="14"/>
+      <c r="T63" s="14"/>
+      <c r="U63" s="14"/>
+      <c r="V63" s="14"/>
+      <c r="W63" s="14"/>
+      <c r="X63" s="14"/>
+      <c r="Y63" s="14"/>
+    </row>
+    <row r="64" ht="15.0" customHeight="1">
+      <c r="A64" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="B64" s="13">
         <v>0.0</v>
       </c>
-      <c r="C33" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="D33" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="E33" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="18"/>
-      <c r="I33" s="18"/>
-      <c r="J33" s="18"/>
-      <c r="K33" s="18"/>
-      <c r="L33" s="18"/>
-      <c r="M33" s="18"/>
-      <c r="N33" s="18"/>
-      <c r="O33" s="18"/>
-      <c r="P33" s="18"/>
-      <c r="Q33" s="18"/>
-      <c r="R33" s="18"/>
-      <c r="S33" s="18"/>
-      <c r="T33" s="18"/>
-      <c r="U33" s="18"/>
-      <c r="V33" s="18"/>
-      <c r="W33" s="18"/>
-      <c r="X33" s="18"/>
-      <c r="Y33" s="18"/>
-    </row>
-    <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="B34" s="17">
+      <c r="C64" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="D64" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="E64" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="F64" s="14"/>
+      <c r="G64" s="14"/>
+      <c r="H64" s="14"/>
+      <c r="I64" s="14"/>
+      <c r="J64" s="14"/>
+      <c r="K64" s="14"/>
+      <c r="L64" s="14"/>
+      <c r="M64" s="14"/>
+      <c r="N64" s="14"/>
+      <c r="O64" s="14"/>
+      <c r="P64" s="14"/>
+      <c r="Q64" s="14"/>
+      <c r="R64" s="14"/>
+      <c r="S64" s="14"/>
+      <c r="T64" s="14"/>
+      <c r="U64" s="14"/>
+      <c r="V64" s="14"/>
+      <c r="W64" s="14"/>
+      <c r="X64" s="14"/>
+      <c r="Y64" s="14"/>
+    </row>
+    <row r="65" ht="15.0" customHeight="1">
+      <c r="A65" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="B65" s="16">
         <v>0.0</v>
       </c>
-      <c r="C34" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="D34" s="18" t="s">
+      <c r="C65" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="D65" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="E65" s="17" t="s">
+        <v>258</v>
+      </c>
+      <c r="F65" s="17"/>
+      <c r="G65" s="17"/>
+      <c r="H65" s="17"/>
+      <c r="I65" s="17"/>
+      <c r="J65" s="17"/>
+      <c r="K65" s="17"/>
+      <c r="L65" s="17"/>
+      <c r="M65" s="17"/>
+      <c r="N65" s="17"/>
+      <c r="O65" s="17"/>
+      <c r="P65" s="17"/>
+      <c r="Q65" s="17"/>
+      <c r="R65" s="17"/>
+      <c r="S65" s="17"/>
+      <c r="T65" s="17"/>
+      <c r="U65" s="17"/>
+      <c r="V65" s="17"/>
+      <c r="W65" s="17"/>
+      <c r="X65" s="17"/>
+      <c r="Y65" s="17"/>
+    </row>
+    <row r="66" ht="15.0" customHeight="1">
+      <c r="A66" s="18" t="s">
+        <v>259</v>
+      </c>
+      <c r="B66" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="C66" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="D66" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="E66" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="F66" s="19"/>
+      <c r="G66" s="19"/>
+      <c r="H66" s="19"/>
+      <c r="I66" s="19"/>
+      <c r="J66" s="19"/>
+      <c r="K66" s="19"/>
+      <c r="L66" s="19"/>
+      <c r="M66" s="19"/>
+      <c r="N66" s="19"/>
+      <c r="O66" s="19"/>
+      <c r="P66" s="19"/>
+      <c r="Q66" s="19"/>
+      <c r="R66" s="19"/>
+      <c r="S66" s="19"/>
+      <c r="T66" s="19"/>
+      <c r="U66" s="19"/>
+      <c r="V66" s="19"/>
+      <c r="W66" s="19"/>
+      <c r="X66" s="19"/>
+      <c r="Y66" s="19"/>
+    </row>
+    <row r="67" ht="15.0" customHeight="1">
+      <c r="A67" s="18" t="s">
+        <v>261</v>
+      </c>
+      <c r="B67" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="C67" s="19" t="s">
+        <v>262</v>
+      </c>
+      <c r="D67" s="19" t="s">
+        <v>263</v>
+      </c>
+      <c r="E67" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="F67" s="19"/>
+      <c r="G67" s="19"/>
+      <c r="H67" s="19"/>
+      <c r="I67" s="19"/>
+      <c r="J67" s="19"/>
+      <c r="K67" s="19"/>
+      <c r="L67" s="19"/>
+      <c r="M67" s="19"/>
+      <c r="N67" s="19"/>
+      <c r="O67" s="19"/>
+      <c r="P67" s="19"/>
+      <c r="Q67" s="19"/>
+      <c r="R67" s="19"/>
+      <c r="S67" s="19"/>
+      <c r="T67" s="19"/>
+      <c r="U67" s="19"/>
+      <c r="V67" s="19"/>
+      <c r="W67" s="19"/>
+      <c r="X67" s="19"/>
+      <c r="Y67" s="19"/>
+    </row>
+    <row r="68" ht="15.75" customHeight="1">
+      <c r="A68" s="18" t="s">
+        <v>265</v>
+      </c>
+      <c r="B68" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="C68" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="D68" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="E68" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="F68" s="19"/>
+      <c r="G68" s="19"/>
+      <c r="H68" s="19"/>
+      <c r="I68" s="19"/>
+      <c r="J68" s="19"/>
+      <c r="K68" s="19"/>
+      <c r="L68" s="19"/>
+      <c r="M68" s="19"/>
+      <c r="N68" s="19"/>
+      <c r="O68" s="19"/>
+      <c r="P68" s="19"/>
+      <c r="Q68" s="19"/>
+      <c r="R68" s="19"/>
+      <c r="S68" s="19"/>
+      <c r="T68" s="19"/>
+      <c r="U68" s="19"/>
+      <c r="V68" s="19"/>
+      <c r="W68" s="19"/>
+      <c r="X68" s="19"/>
+      <c r="Y68" s="19"/>
+    </row>
+    <row r="69" ht="15.75" customHeight="1">
+      <c r="A69" s="18" t="s">
+        <v>267</v>
+      </c>
+      <c r="B69" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="C69" s="19" t="s">
+        <v>268</v>
+      </c>
+      <c r="D69" s="19" t="s">
+        <v>269</v>
+      </c>
+      <c r="E69" s="19" t="s">
+        <v>270</v>
+      </c>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="19"/>
+      <c r="K69" s="19"/>
+      <c r="L69" s="19"/>
+      <c r="M69" s="19"/>
+      <c r="N69" s="19"/>
+      <c r="O69" s="19"/>
+      <c r="P69" s="19"/>
+      <c r="Q69" s="19"/>
+      <c r="R69" s="19"/>
+      <c r="S69" s="19"/>
+      <c r="T69" s="19"/>
+      <c r="U69" s="19"/>
+      <c r="V69" s="19"/>
+      <c r="W69" s="19"/>
+      <c r="X69" s="19"/>
+      <c r="Y69" s="19"/>
+    </row>
+    <row r="70" ht="15.0" customHeight="1">
+      <c r="A70" s="18" t="s">
+        <v>271</v>
+      </c>
+      <c r="B70" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="C70" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="D70" s="19" t="s">
+        <v>273</v>
+      </c>
+      <c r="E70" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="F70" s="19"/>
+      <c r="G70" s="19"/>
+      <c r="H70" s="19"/>
+      <c r="I70" s="19"/>
+      <c r="J70" s="19"/>
+      <c r="K70" s="19"/>
+      <c r="L70" s="19"/>
+      <c r="M70" s="19"/>
+      <c r="N70" s="19"/>
+      <c r="O70" s="19"/>
+      <c r="P70" s="19"/>
+      <c r="Q70" s="19"/>
+      <c r="R70" s="19"/>
+      <c r="S70" s="19"/>
+      <c r="T70" s="19"/>
+      <c r="U70" s="19"/>
+      <c r="V70" s="19"/>
+      <c r="W70" s="19"/>
+      <c r="X70" s="19"/>
+      <c r="Y70" s="19"/>
+    </row>
+    <row r="71" ht="15.0" customHeight="1">
+      <c r="A71" s="18" t="s">
+        <v>275</v>
+      </c>
+      <c r="B71" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="C71" s="19" t="s">
+        <v>276</v>
+      </c>
+      <c r="D71" s="19" t="s">
+        <v>277</v>
+      </c>
+      <c r="E71" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="F71" s="19"/>
+      <c r="G71" s="19"/>
+      <c r="H71" s="19"/>
+      <c r="I71" s="19"/>
+      <c r="J71" s="19"/>
+      <c r="K71" s="19"/>
+      <c r="L71" s="19"/>
+      <c r="M71" s="19"/>
+      <c r="N71" s="19"/>
+      <c r="O71" s="19"/>
+      <c r="P71" s="19"/>
+      <c r="Q71" s="19"/>
+      <c r="R71" s="19"/>
+      <c r="S71" s="19"/>
+      <c r="T71" s="19"/>
+      <c r="U71" s="19"/>
+      <c r="V71" s="19"/>
+      <c r="W71" s="19"/>
+      <c r="X71" s="19"/>
+      <c r="Y71" s="19"/>
+    </row>
+    <row r="72" ht="15.0" customHeight="1">
+      <c r="A72" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="B72" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="C72" s="19" t="s">
+        <v>280</v>
+      </c>
+      <c r="D72" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E72" s="19" t="s">
+        <v>282</v>
+      </c>
+      <c r="F72" s="19"/>
+      <c r="G72" s="19"/>
+      <c r="H72" s="19"/>
+      <c r="I72" s="19"/>
+      <c r="J72" s="19"/>
+      <c r="K72" s="19"/>
+      <c r="L72" s="19"/>
+      <c r="M72" s="19"/>
+      <c r="N72" s="19"/>
+      <c r="O72" s="19"/>
+      <c r="P72" s="19"/>
+      <c r="Q72" s="19"/>
+      <c r="R72" s="19"/>
+      <c r="S72" s="19"/>
+      <c r="T72" s="19"/>
+      <c r="U72" s="19"/>
+      <c r="V72" s="19"/>
+      <c r="W72" s="19"/>
+      <c r="X72" s="19"/>
+      <c r="Y72" s="19"/>
+    </row>
+    <row r="73" ht="15.0" customHeight="1">
+      <c r="A73" s="20" t="s">
+        <v>283</v>
+      </c>
+      <c r="B73" s="21">
+        <v>0.0</v>
+      </c>
+      <c r="C73" s="22" t="s">
+        <v>284</v>
+      </c>
+      <c r="D73" s="22" t="s">
+        <v>195</v>
+      </c>
+      <c r="E73" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="F73" s="22"/>
+      <c r="G73" s="22"/>
+      <c r="H73" s="22"/>
+      <c r="I73" s="22"/>
+      <c r="J73" s="22"/>
+      <c r="K73" s="22"/>
+      <c r="L73" s="22"/>
+      <c r="M73" s="22"/>
+      <c r="N73" s="22"/>
+      <c r="O73" s="22"/>
+      <c r="P73" s="22"/>
+      <c r="Q73" s="22"/>
+      <c r="R73" s="22"/>
+      <c r="S73" s="22"/>
+      <c r="T73" s="22"/>
+      <c r="U73" s="22"/>
+      <c r="V73" s="22"/>
+      <c r="W73" s="22"/>
+      <c r="X73" s="22"/>
+      <c r="Y73" s="22"/>
+    </row>
+    <row r="74" ht="15.0" customHeight="1">
+      <c r="A74" s="23" t="s">
+        <v>285</v>
+      </c>
+      <c r="B74" s="24">
+        <v>0.0</v>
+      </c>
+      <c r="C74" s="25" t="s">
+        <v>286</v>
+      </c>
+      <c r="D74" s="25" t="s">
         <v>127</v>
       </c>
-      <c r="E34" s="18" t="s">
+      <c r="E74" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="18"/>
-      <c r="I34" s="18"/>
-      <c r="J34" s="18"/>
-      <c r="K34" s="18"/>
-      <c r="L34" s="18"/>
-      <c r="M34" s="18"/>
-      <c r="N34" s="18"/>
-      <c r="O34" s="18"/>
-      <c r="P34" s="18"/>
-      <c r="Q34" s="18"/>
-      <c r="R34" s="18"/>
-      <c r="S34" s="18"/>
-      <c r="T34" s="18"/>
-      <c r="U34" s="18"/>
-      <c r="V34" s="18"/>
-      <c r="W34" s="18"/>
-      <c r="X34" s="18"/>
-      <c r="Y34" s="18"/>
-    </row>
-    <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="B35" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="C35" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="D35" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="E35" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="F35" s="18"/>
-      <c r="G35" s="18"/>
-      <c r="H35" s="18"/>
-      <c r="I35" s="18"/>
-      <c r="J35" s="18"/>
-      <c r="K35" s="18"/>
-      <c r="L35" s="18"/>
-      <c r="M35" s="18"/>
-      <c r="N35" s="18"/>
-      <c r="O35" s="18"/>
-      <c r="P35" s="18"/>
-      <c r="Q35" s="18"/>
-      <c r="R35" s="18"/>
-      <c r="S35" s="18"/>
-      <c r="T35" s="18"/>
-      <c r="U35" s="18"/>
-      <c r="V35" s="18"/>
-      <c r="W35" s="18"/>
-      <c r="X35" s="18"/>
-      <c r="Y35" s="18"/>
-    </row>
-    <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="B36" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="C36" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="D36" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="E36" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="F36" s="18"/>
-      <c r="G36" s="18"/>
-      <c r="H36" s="18"/>
-      <c r="I36" s="18"/>
-      <c r="J36" s="18"/>
-      <c r="K36" s="18"/>
-      <c r="L36" s="18"/>
-      <c r="M36" s="18"/>
-      <c r="N36" s="18"/>
-      <c r="O36" s="18"/>
-      <c r="P36" s="18"/>
-      <c r="Q36" s="18"/>
-      <c r="R36" s="18"/>
-      <c r="S36" s="18"/>
-      <c r="T36" s="18"/>
-      <c r="U36" s="18"/>
-      <c r="V36" s="18"/>
-      <c r="W36" s="18"/>
-      <c r="X36" s="18"/>
-      <c r="Y36" s="18"/>
-    </row>
-    <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="B37" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="C37" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="D37" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="E37" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="F37" s="18"/>
-      <c r="G37" s="18"/>
-      <c r="H37" s="18"/>
-      <c r="I37" s="18"/>
-      <c r="J37" s="18"/>
-      <c r="K37" s="18"/>
-      <c r="L37" s="18"/>
-      <c r="M37" s="18"/>
-      <c r="N37" s="18"/>
-      <c r="O37" s="18"/>
-      <c r="P37" s="18"/>
-      <c r="Q37" s="18"/>
-      <c r="R37" s="18"/>
-      <c r="S37" s="18"/>
-      <c r="T37" s="18"/>
-      <c r="U37" s="18"/>
-      <c r="V37" s="18"/>
-      <c r="W37" s="18"/>
-      <c r="X37" s="18"/>
-      <c r="Y37" s="18"/>
-    </row>
-    <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="16" t="s">
-        <v>141</v>
-      </c>
-      <c r="B38" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="C38" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="D38" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="E38" s="18" t="s">
-        <v>144</v>
-      </c>
-      <c r="F38" s="18"/>
-      <c r="G38" s="18"/>
-      <c r="H38" s="18"/>
-      <c r="I38" s="18"/>
-      <c r="J38" s="18"/>
-      <c r="K38" s="18"/>
-      <c r="L38" s="18"/>
-      <c r="M38" s="18"/>
-      <c r="N38" s="18"/>
-      <c r="O38" s="18"/>
-      <c r="P38" s="18"/>
-      <c r="Q38" s="18"/>
-      <c r="R38" s="18"/>
-      <c r="S38" s="18"/>
-      <c r="T38" s="18"/>
-      <c r="U38" s="18"/>
-      <c r="V38" s="18"/>
-      <c r="W38" s="18"/>
-      <c r="X38" s="18"/>
-      <c r="Y38" s="18"/>
-    </row>
-    <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="B39" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="C39" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="D39" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="E39" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="F39" s="18"/>
-      <c r="G39" s="18"/>
-      <c r="H39" s="18"/>
-      <c r="I39" s="18"/>
-      <c r="J39" s="18"/>
-      <c r="K39" s="18"/>
-      <c r="L39" s="18"/>
-      <c r="M39" s="18"/>
-      <c r="N39" s="18"/>
-      <c r="O39" s="18"/>
-      <c r="P39" s="18"/>
-      <c r="Q39" s="18"/>
-      <c r="R39" s="18"/>
-      <c r="S39" s="18"/>
-      <c r="T39" s="18"/>
-      <c r="U39" s="18"/>
-      <c r="V39" s="18"/>
-      <c r="W39" s="18"/>
-      <c r="X39" s="18"/>
-      <c r="Y39" s="18"/>
-    </row>
-    <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="B40" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="C40" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="D40" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="E40" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="F40" s="18"/>
-      <c r="G40" s="18"/>
-      <c r="H40" s="18"/>
-      <c r="I40" s="18"/>
-      <c r="J40" s="18"/>
-      <c r="K40" s="18"/>
-      <c r="L40" s="18"/>
-      <c r="M40" s="18"/>
-      <c r="N40" s="18"/>
-      <c r="O40" s="18"/>
-      <c r="P40" s="18"/>
-      <c r="Q40" s="18"/>
-      <c r="R40" s="18"/>
-      <c r="S40" s="18"/>
-      <c r="T40" s="18"/>
-      <c r="U40" s="18"/>
-      <c r="V40" s="18"/>
-      <c r="W40" s="18"/>
-      <c r="X40" s="18"/>
-      <c r="Y40" s="18"/>
-    </row>
-    <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="B41" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="C41" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="D41" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="E41" s="18" t="s">
-        <v>156</v>
-      </c>
-      <c r="F41" s="18"/>
-      <c r="G41" s="18"/>
-      <c r="H41" s="18"/>
-      <c r="I41" s="18"/>
-      <c r="J41" s="18"/>
-      <c r="K41" s="18"/>
-      <c r="L41" s="18"/>
-      <c r="M41" s="18"/>
-      <c r="N41" s="18"/>
-      <c r="O41" s="18"/>
-      <c r="P41" s="18"/>
-      <c r="Q41" s="18"/>
-      <c r="R41" s="18"/>
-      <c r="S41" s="18"/>
-      <c r="T41" s="18"/>
-      <c r="U41" s="18"/>
-      <c r="V41" s="18"/>
-      <c r="W41" s="18"/>
-      <c r="X41" s="18"/>
-      <c r="Y41" s="18"/>
-    </row>
-    <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="16" t="s">
-        <v>157</v>
-      </c>
-      <c r="B42" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="C42" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="D42" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="E42" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="F42" s="18"/>
-      <c r="G42" s="18"/>
-      <c r="H42" s="18"/>
-      <c r="I42" s="18"/>
-      <c r="J42" s="18"/>
-      <c r="K42" s="18"/>
-      <c r="L42" s="18"/>
-      <c r="M42" s="18"/>
-      <c r="N42" s="18"/>
-      <c r="O42" s="18"/>
-      <c r="P42" s="18"/>
-      <c r="Q42" s="18"/>
-      <c r="R42" s="18"/>
-      <c r="S42" s="18"/>
-      <c r="T42" s="18"/>
-      <c r="U42" s="18"/>
-      <c r="V42" s="18"/>
-      <c r="W42" s="18"/>
-      <c r="X42" s="18"/>
-      <c r="Y42" s="18"/>
-    </row>
-    <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="16" t="s">
-        <v>161</v>
-      </c>
-      <c r="B43" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="C43" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="D43" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="E43" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="F43" s="18"/>
-      <c r="G43" s="18"/>
-      <c r="H43" s="18"/>
-      <c r="I43" s="18"/>
-      <c r="J43" s="18"/>
-      <c r="K43" s="18"/>
-      <c r="L43" s="18"/>
-      <c r="M43" s="18"/>
-      <c r="N43" s="18"/>
-      <c r="O43" s="18"/>
-      <c r="P43" s="18"/>
-      <c r="Q43" s="18"/>
-      <c r="R43" s="18"/>
-      <c r="S43" s="18"/>
-      <c r="T43" s="18"/>
-      <c r="U43" s="18"/>
-      <c r="V43" s="18"/>
-      <c r="W43" s="18"/>
-      <c r="X43" s="18"/>
-      <c r="Y43" s="18"/>
-    </row>
-    <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="16" t="s">
-        <v>165</v>
-      </c>
-      <c r="B44" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="C44" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="D44" s="18" t="s">
-        <v>167</v>
-      </c>
-      <c r="E44" s="18" t="s">
-        <v>168</v>
-      </c>
-      <c r="F44" s="18"/>
-      <c r="G44" s="18"/>
-      <c r="H44" s="18"/>
-      <c r="I44" s="18"/>
-      <c r="J44" s="18"/>
-      <c r="K44" s="18"/>
-      <c r="L44" s="18"/>
-      <c r="M44" s="18"/>
-      <c r="N44" s="18"/>
-      <c r="O44" s="18"/>
-      <c r="P44" s="18"/>
-      <c r="Q44" s="18"/>
-      <c r="R44" s="18"/>
-      <c r="S44" s="18"/>
-      <c r="T44" s="18"/>
-      <c r="U44" s="18"/>
-      <c r="V44" s="18"/>
-      <c r="W44" s="18"/>
-      <c r="X44" s="18"/>
-      <c r="Y44" s="18"/>
-    </row>
-    <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="16" t="s">
-        <v>169</v>
-      </c>
-      <c r="B45" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="C45" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="D45" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="E45" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="F45" s="18"/>
-      <c r="G45" s="18"/>
-      <c r="H45" s="18"/>
-      <c r="I45" s="18"/>
-      <c r="J45" s="18"/>
-      <c r="K45" s="18"/>
-      <c r="L45" s="18"/>
-      <c r="M45" s="18"/>
-      <c r="N45" s="18"/>
-      <c r="O45" s="18"/>
-      <c r="P45" s="18"/>
-      <c r="Q45" s="18"/>
-      <c r="R45" s="18"/>
-      <c r="S45" s="18"/>
-      <c r="T45" s="18"/>
-      <c r="U45" s="18"/>
-      <c r="V45" s="18"/>
-      <c r="W45" s="18"/>
-      <c r="X45" s="18"/>
-      <c r="Y45" s="18"/>
-    </row>
-    <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="B46" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="C46" s="18" t="s">
-        <v>174</v>
-      </c>
-      <c r="D46" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="E46" s="18" t="s">
-        <v>176</v>
-      </c>
-      <c r="F46" s="18"/>
-      <c r="G46" s="18"/>
-      <c r="H46" s="18"/>
-      <c r="I46" s="18"/>
-      <c r="J46" s="18"/>
-      <c r="K46" s="18"/>
-      <c r="L46" s="18"/>
-      <c r="M46" s="18"/>
-      <c r="N46" s="18"/>
-      <c r="O46" s="18"/>
-      <c r="P46" s="18"/>
-      <c r="Q46" s="18"/>
-      <c r="R46" s="18"/>
-      <c r="S46" s="18"/>
-      <c r="T46" s="18"/>
-      <c r="U46" s="18"/>
-      <c r="V46" s="18"/>
-      <c r="W46" s="18"/>
-      <c r="X46" s="18"/>
-      <c r="Y46" s="18"/>
-    </row>
-    <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="16" t="s">
-        <v>177</v>
-      </c>
-      <c r="B47" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="C47" s="18" t="s">
-        <v>178</v>
-      </c>
-      <c r="D47" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="E47" s="18" t="s">
-        <v>180</v>
-      </c>
-      <c r="F47" s="18"/>
-      <c r="G47" s="18"/>
-      <c r="H47" s="18"/>
-      <c r="I47" s="18"/>
-      <c r="J47" s="18"/>
-      <c r="K47" s="18"/>
-      <c r="L47" s="18"/>
-      <c r="M47" s="18"/>
-      <c r="N47" s="18"/>
-      <c r="O47" s="18"/>
-      <c r="P47" s="18"/>
-      <c r="Q47" s="18"/>
-      <c r="R47" s="18"/>
-      <c r="S47" s="18"/>
-      <c r="T47" s="18"/>
-      <c r="U47" s="18"/>
-      <c r="V47" s="18"/>
-      <c r="W47" s="18"/>
-      <c r="X47" s="18"/>
-      <c r="Y47" s="18"/>
-    </row>
-    <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="16" t="s">
-        <v>181</v>
-      </c>
-      <c r="B48" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="C48" s="18" t="s">
-        <v>182</v>
-      </c>
-      <c r="D48" s="18" t="s">
-        <v>183</v>
-      </c>
-      <c r="E48" s="18" t="s">
-        <v>184</v>
-      </c>
-      <c r="F48" s="18"/>
-      <c r="G48" s="18"/>
-      <c r="H48" s="18"/>
-      <c r="I48" s="18"/>
-      <c r="J48" s="18"/>
-      <c r="K48" s="18"/>
-      <c r="L48" s="18"/>
-      <c r="M48" s="18"/>
-      <c r="N48" s="18"/>
-      <c r="O48" s="18"/>
-      <c r="P48" s="18"/>
-      <c r="Q48" s="18"/>
-      <c r="R48" s="18"/>
-      <c r="S48" s="18"/>
-      <c r="T48" s="18"/>
-      <c r="U48" s="18"/>
-      <c r="V48" s="18"/>
-      <c r="W48" s="18"/>
-      <c r="X48" s="18"/>
-      <c r="Y48" s="18"/>
-    </row>
-    <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="B49" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="C49" s="18" t="s">
-        <v>186</v>
-      </c>
-      <c r="D49" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="E49" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="F49" s="18"/>
-      <c r="G49" s="18"/>
-      <c r="H49" s="18"/>
-      <c r="I49" s="18"/>
-      <c r="J49" s="18"/>
-      <c r="K49" s="18"/>
-      <c r="L49" s="18"/>
-      <c r="M49" s="18"/>
-      <c r="N49" s="18"/>
-      <c r="O49" s="18"/>
-      <c r="P49" s="18"/>
-      <c r="Q49" s="18"/>
-      <c r="R49" s="18"/>
-      <c r="S49" s="18"/>
-      <c r="T49" s="18"/>
-      <c r="U49" s="18"/>
-      <c r="V49" s="18"/>
-      <c r="W49" s="18"/>
-      <c r="X49" s="18"/>
-      <c r="Y49" s="18"/>
-    </row>
-    <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B50" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="C50" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="D50" s="18" t="s">
-        <v>191</v>
-      </c>
-      <c r="E50" s="18" t="s">
-        <v>192</v>
-      </c>
-      <c r="F50" s="18"/>
-      <c r="G50" s="18"/>
-      <c r="H50" s="18"/>
-      <c r="I50" s="18"/>
-      <c r="J50" s="18"/>
-      <c r="K50" s="18"/>
-      <c r="L50" s="18"/>
-      <c r="M50" s="18"/>
-      <c r="N50" s="18"/>
-      <c r="O50" s="18"/>
-      <c r="P50" s="18"/>
-      <c r="Q50" s="18"/>
-      <c r="R50" s="18"/>
-      <c r="S50" s="18"/>
-      <c r="T50" s="18"/>
-      <c r="U50" s="18"/>
-      <c r="V50" s="18"/>
-      <c r="W50" s="18"/>
-      <c r="X50" s="18"/>
-      <c r="Y50" s="18"/>
-    </row>
-    <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="16" t="s">
-        <v>193</v>
-      </c>
-      <c r="B51" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="C51" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="D51" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="E51" s="18" t="s">
-        <v>196</v>
-      </c>
-      <c r="F51" s="18"/>
-      <c r="G51" s="18"/>
-      <c r="H51" s="18"/>
-      <c r="I51" s="18"/>
-      <c r="J51" s="18"/>
-      <c r="K51" s="18"/>
-      <c r="L51" s="18"/>
-      <c r="M51" s="18"/>
-      <c r="N51" s="18"/>
-      <c r="O51" s="18"/>
-      <c r="P51" s="18"/>
-      <c r="Q51" s="18"/>
-      <c r="R51" s="18"/>
-      <c r="S51" s="18"/>
-      <c r="T51" s="18"/>
-      <c r="U51" s="18"/>
-      <c r="V51" s="18"/>
-      <c r="W51" s="18"/>
-      <c r="X51" s="18"/>
-      <c r="Y51" s="18"/>
-    </row>
-    <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="16" t="s">
-        <v>197</v>
-      </c>
-      <c r="B52" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="C52" s="18" t="s">
-        <v>198</v>
-      </c>
-      <c r="D52" s="18" t="s">
-        <v>199</v>
-      </c>
-      <c r="E52" s="18" t="s">
-        <v>200</v>
-      </c>
-      <c r="F52" s="18"/>
-      <c r="G52" s="18"/>
-      <c r="H52" s="18"/>
-      <c r="I52" s="18"/>
-      <c r="J52" s="18"/>
-      <c r="K52" s="18"/>
-      <c r="L52" s="18"/>
-      <c r="M52" s="18"/>
-      <c r="N52" s="18"/>
-      <c r="O52" s="18"/>
-      <c r="P52" s="18"/>
-      <c r="Q52" s="18"/>
-      <c r="R52" s="18"/>
-      <c r="S52" s="18"/>
-      <c r="T52" s="18"/>
-      <c r="U52" s="18"/>
-      <c r="V52" s="18"/>
-      <c r="W52" s="18"/>
-      <c r="X52" s="18"/>
-      <c r="Y52" s="18"/>
-    </row>
-    <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="16" t="s">
-        <v>201</v>
-      </c>
-      <c r="B53" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="C53" s="18" t="s">
-        <v>202</v>
-      </c>
-      <c r="D53" s="18" t="s">
-        <v>203</v>
-      </c>
-      <c r="E53" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="F53" s="18"/>
-      <c r="G53" s="18"/>
-      <c r="H53" s="18"/>
-      <c r="I53" s="18"/>
-      <c r="J53" s="18"/>
-      <c r="K53" s="18"/>
-      <c r="L53" s="18"/>
-      <c r="M53" s="18"/>
-      <c r="N53" s="18"/>
-      <c r="O53" s="18"/>
-      <c r="P53" s="18"/>
-      <c r="Q53" s="18"/>
-      <c r="R53" s="18"/>
-      <c r="S53" s="18"/>
-      <c r="T53" s="18"/>
-      <c r="U53" s="18"/>
-      <c r="V53" s="18"/>
-      <c r="W53" s="18"/>
-      <c r="X53" s="18"/>
-      <c r="Y53" s="18"/>
-    </row>
-    <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="16" t="s">
-        <v>205</v>
-      </c>
-      <c r="B54" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="C54" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="D54" s="18" t="s">
-        <v>207</v>
-      </c>
-      <c r="E54" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="F54" s="18"/>
-      <c r="G54" s="18"/>
-      <c r="H54" s="18"/>
-      <c r="I54" s="18"/>
-      <c r="J54" s="18"/>
-      <c r="K54" s="18"/>
-      <c r="L54" s="18"/>
-      <c r="M54" s="18"/>
-      <c r="N54" s="18"/>
-      <c r="O54" s="18"/>
-      <c r="P54" s="18"/>
-      <c r="Q54" s="18"/>
-      <c r="R54" s="18"/>
-      <c r="S54" s="18"/>
-      <c r="T54" s="18"/>
-      <c r="U54" s="18"/>
-      <c r="V54" s="18"/>
-      <c r="W54" s="18"/>
-      <c r="X54" s="18"/>
-      <c r="Y54" s="18"/>
-    </row>
-    <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="B55" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="C55" s="18" t="s">
-        <v>210</v>
-      </c>
-      <c r="D55" s="18" t="s">
-        <v>211</v>
-      </c>
-      <c r="E55" s="18" t="s">
-        <v>212</v>
-      </c>
-      <c r="F55" s="18"/>
-      <c r="G55" s="18"/>
-      <c r="H55" s="18"/>
-      <c r="I55" s="18"/>
-      <c r="J55" s="18"/>
-      <c r="K55" s="18"/>
-      <c r="L55" s="18"/>
-      <c r="M55" s="18"/>
-      <c r="N55" s="18"/>
-      <c r="O55" s="18"/>
-      <c r="P55" s="18"/>
-      <c r="Q55" s="18"/>
-      <c r="R55" s="18"/>
-      <c r="S55" s="18"/>
-      <c r="T55" s="18"/>
-      <c r="U55" s="18"/>
-      <c r="V55" s="18"/>
-      <c r="W55" s="18"/>
-      <c r="X55" s="18"/>
-      <c r="Y55" s="18"/>
-    </row>
-    <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="B56" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="C56" s="18" t="s">
-        <v>214</v>
-      </c>
-      <c r="D56" s="18" t="s">
-        <v>215</v>
-      </c>
-      <c r="E56" s="18" t="s">
-        <v>216</v>
-      </c>
-      <c r="F56" s="18"/>
-      <c r="G56" s="18"/>
-      <c r="H56" s="18"/>
-      <c r="I56" s="18"/>
-      <c r="J56" s="18"/>
-      <c r="K56" s="18"/>
-      <c r="L56" s="18"/>
-      <c r="M56" s="18"/>
-      <c r="N56" s="18"/>
-      <c r="O56" s="18"/>
-      <c r="P56" s="18"/>
-      <c r="Q56" s="18"/>
-      <c r="R56" s="18"/>
-      <c r="S56" s="18"/>
-      <c r="T56" s="18"/>
-      <c r="U56" s="18"/>
-      <c r="V56" s="18"/>
-      <c r="W56" s="18"/>
-      <c r="X56" s="18"/>
-      <c r="Y56" s="18"/>
-    </row>
-    <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="16" t="s">
-        <v>217</v>
-      </c>
-      <c r="B57" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="C57" s="18" t="s">
-        <v>218</v>
-      </c>
-      <c r="D57" s="18" t="s">
-        <v>219</v>
-      </c>
-      <c r="E57" s="18" t="s">
-        <v>220</v>
-      </c>
-      <c r="F57" s="18"/>
-      <c r="G57" s="18"/>
-      <c r="H57" s="18"/>
-      <c r="I57" s="18"/>
-      <c r="J57" s="18"/>
-      <c r="K57" s="18"/>
-      <c r="L57" s="18"/>
-      <c r="M57" s="18"/>
-      <c r="N57" s="18"/>
-      <c r="O57" s="18"/>
-      <c r="P57" s="18"/>
-      <c r="Q57" s="18"/>
-      <c r="R57" s="18"/>
-      <c r="S57" s="18"/>
-      <c r="T57" s="18"/>
-      <c r="U57" s="18"/>
-      <c r="V57" s="18"/>
-      <c r="W57" s="18"/>
-      <c r="X57" s="18"/>
-      <c r="Y57" s="18"/>
-    </row>
-    <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="16" t="s">
-        <v>221</v>
-      </c>
-      <c r="B58" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="C58" s="18" t="s">
-        <v>222</v>
-      </c>
-      <c r="D58" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="E58" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="F58" s="18"/>
-      <c r="G58" s="18"/>
-      <c r="H58" s="18"/>
-      <c r="I58" s="18"/>
-      <c r="J58" s="18"/>
-      <c r="K58" s="18"/>
-      <c r="L58" s="18"/>
-      <c r="M58" s="18"/>
-      <c r="N58" s="18"/>
-      <c r="O58" s="18"/>
-      <c r="P58" s="18"/>
-      <c r="Q58" s="18"/>
-      <c r="R58" s="18"/>
-      <c r="S58" s="18"/>
-      <c r="T58" s="18"/>
-      <c r="U58" s="18"/>
-      <c r="V58" s="18"/>
-      <c r="W58" s="18"/>
-      <c r="X58" s="18"/>
-      <c r="Y58" s="18"/>
-    </row>
-    <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="16" t="s">
-        <v>223</v>
-      </c>
-      <c r="B59" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="C59" s="18" t="s">
-        <v>224</v>
-      </c>
-      <c r="D59" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="E59" s="18" t="s">
-        <v>226</v>
-      </c>
-      <c r="F59" s="18"/>
-      <c r="G59" s="18"/>
-      <c r="H59" s="18"/>
-      <c r="I59" s="18"/>
-      <c r="J59" s="18"/>
-      <c r="K59" s="18"/>
-      <c r="L59" s="18"/>
-      <c r="M59" s="18"/>
-      <c r="N59" s="18"/>
-      <c r="O59" s="18"/>
-      <c r="P59" s="18"/>
-      <c r="Q59" s="18"/>
-      <c r="R59" s="18"/>
-      <c r="S59" s="18"/>
-      <c r="T59" s="18"/>
-      <c r="U59" s="18"/>
-      <c r="V59" s="18"/>
-      <c r="W59" s="18"/>
-      <c r="X59" s="18"/>
-      <c r="Y59" s="18"/>
-    </row>
-    <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="16" t="s">
-        <v>227</v>
-      </c>
-      <c r="B60" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="C60" s="18" t="s">
-        <v>228</v>
-      </c>
-      <c r="D60" s="18" t="s">
-        <v>229</v>
-      </c>
-      <c r="E60" s="18" t="s">
-        <v>230</v>
-      </c>
-      <c r="F60" s="18"/>
-      <c r="G60" s="18"/>
-      <c r="H60" s="18"/>
-      <c r="I60" s="18"/>
-      <c r="J60" s="18"/>
-      <c r="K60" s="18"/>
-      <c r="L60" s="18"/>
-      <c r="M60" s="18"/>
-      <c r="N60" s="18"/>
-      <c r="O60" s="18"/>
-      <c r="P60" s="18"/>
-      <c r="Q60" s="18"/>
-      <c r="R60" s="18"/>
-      <c r="S60" s="18"/>
-      <c r="T60" s="18"/>
-      <c r="U60" s="18"/>
-      <c r="V60" s="18"/>
-      <c r="W60" s="18"/>
-      <c r="X60" s="18"/>
-      <c r="Y60" s="18"/>
-    </row>
-    <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="B61" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="C61" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="D61" s="18" t="s">
-        <v>233</v>
-      </c>
-      <c r="E61" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="F61" s="18"/>
-      <c r="G61" s="18"/>
-      <c r="H61" s="18"/>
-      <c r="I61" s="18"/>
-      <c r="J61" s="18"/>
-      <c r="K61" s="18"/>
-      <c r="L61" s="18"/>
-      <c r="M61" s="18"/>
-      <c r="N61" s="18"/>
-      <c r="O61" s="18"/>
-      <c r="P61" s="18"/>
-      <c r="Q61" s="18"/>
-      <c r="R61" s="18"/>
-      <c r="S61" s="18"/>
-      <c r="T61" s="18"/>
-      <c r="U61" s="18"/>
-      <c r="V61" s="18"/>
-      <c r="W61" s="18"/>
-      <c r="X61" s="18"/>
-      <c r="Y61" s="18"/>
-    </row>
-    <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="16" t="s">
-        <v>235</v>
-      </c>
-      <c r="B62" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="C62" s="18" t="s">
-        <v>236</v>
-      </c>
-      <c r="D62" s="18" t="s">
-        <v>237</v>
-      </c>
-      <c r="E62" s="18" t="s">
-        <v>238</v>
-      </c>
-      <c r="F62" s="18"/>
-      <c r="G62" s="18"/>
-      <c r="H62" s="18"/>
-      <c r="I62" s="18"/>
-      <c r="J62" s="18"/>
-      <c r="K62" s="18"/>
-      <c r="L62" s="18"/>
-      <c r="M62" s="18"/>
-      <c r="N62" s="18"/>
-      <c r="O62" s="18"/>
-      <c r="P62" s="18"/>
-      <c r="Q62" s="18"/>
-      <c r="R62" s="18"/>
-      <c r="S62" s="18"/>
-      <c r="T62" s="18"/>
-      <c r="U62" s="18"/>
-      <c r="V62" s="18"/>
-      <c r="W62" s="18"/>
-      <c r="X62" s="18"/>
-      <c r="Y62" s="18"/>
-    </row>
-    <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="16" t="s">
-        <v>239</v>
-      </c>
-      <c r="B63" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="C63" s="18" t="s">
-        <v>240</v>
-      </c>
-      <c r="D63" s="18" t="s">
-        <v>241</v>
-      </c>
-      <c r="E63" s="18" t="s">
-        <v>242</v>
-      </c>
-      <c r="F63" s="18"/>
-      <c r="G63" s="18"/>
-      <c r="H63" s="18"/>
-      <c r="I63" s="18"/>
-      <c r="J63" s="18"/>
-      <c r="K63" s="18"/>
-      <c r="L63" s="18"/>
-      <c r="M63" s="18"/>
-      <c r="N63" s="18"/>
-      <c r="O63" s="18"/>
-      <c r="P63" s="18"/>
-      <c r="Q63" s="18"/>
-      <c r="R63" s="18"/>
-      <c r="S63" s="18"/>
-      <c r="T63" s="18"/>
-      <c r="U63" s="18"/>
-      <c r="V63" s="18"/>
-      <c r="W63" s="18"/>
-      <c r="X63" s="18"/>
-      <c r="Y63" s="18"/>
-    </row>
-    <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="16" t="s">
-        <v>243</v>
-      </c>
-      <c r="B64" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="C64" s="18" t="s">
-        <v>244</v>
-      </c>
-      <c r="D64" s="18" t="s">
-        <v>245</v>
-      </c>
-      <c r="E64" s="18" t="s">
-        <v>246</v>
-      </c>
-      <c r="F64" s="18"/>
-      <c r="G64" s="18"/>
-      <c r="H64" s="18"/>
-      <c r="I64" s="18"/>
-      <c r="J64" s="18"/>
-      <c r="K64" s="18"/>
-      <c r="L64" s="18"/>
-      <c r="M64" s="18"/>
-      <c r="N64" s="18"/>
-      <c r="O64" s="18"/>
-      <c r="P64" s="18"/>
-      <c r="Q64" s="18"/>
-      <c r="R64" s="18"/>
-      <c r="S64" s="18"/>
-      <c r="T64" s="18"/>
-      <c r="U64" s="18"/>
-      <c r="V64" s="18"/>
-      <c r="W64" s="18"/>
-      <c r="X64" s="18"/>
-      <c r="Y64" s="18"/>
-    </row>
-    <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="16" t="s">
-        <v>247</v>
-      </c>
-      <c r="B65" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="C65" s="18" t="s">
-        <v>248</v>
-      </c>
-      <c r="D65" s="18" t="s">
-        <v>249</v>
-      </c>
-      <c r="E65" s="18" t="s">
-        <v>250</v>
-      </c>
-      <c r="F65" s="18"/>
-      <c r="G65" s="18"/>
-      <c r="H65" s="18"/>
-      <c r="I65" s="18"/>
-      <c r="J65" s="18"/>
-      <c r="K65" s="18"/>
-      <c r="L65" s="18"/>
-      <c r="M65" s="18"/>
-      <c r="N65" s="18"/>
-      <c r="O65" s="18"/>
-      <c r="P65" s="18"/>
-      <c r="Q65" s="18"/>
-      <c r="R65" s="18"/>
-      <c r="S65" s="18"/>
-      <c r="T65" s="18"/>
-      <c r="U65" s="18"/>
-      <c r="V65" s="18"/>
-      <c r="W65" s="18"/>
-      <c r="X65" s="18"/>
-      <c r="Y65" s="18"/>
-    </row>
-    <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="16" t="s">
-        <v>251</v>
-      </c>
-      <c r="B66" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="C66" s="18" t="s">
-        <v>252</v>
-      </c>
-      <c r="D66" s="18" t="s">
-        <v>253</v>
-      </c>
-      <c r="E66" s="18" t="s">
-        <v>254</v>
-      </c>
-      <c r="F66" s="18"/>
-      <c r="G66" s="18"/>
-      <c r="H66" s="18"/>
-      <c r="I66" s="18"/>
-      <c r="J66" s="18"/>
-      <c r="K66" s="18"/>
-      <c r="L66" s="18"/>
-      <c r="M66" s="18"/>
-      <c r="N66" s="18"/>
-      <c r="O66" s="18"/>
-      <c r="P66" s="18"/>
-      <c r="Q66" s="18"/>
-      <c r="R66" s="18"/>
-      <c r="S66" s="18"/>
-      <c r="T66" s="18"/>
-      <c r="U66" s="18"/>
-      <c r="V66" s="18"/>
-      <c r="W66" s="18"/>
-      <c r="X66" s="18"/>
-      <c r="Y66" s="18"/>
-    </row>
-    <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="16" t="s">
-        <v>255</v>
-      </c>
-      <c r="B67" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="C67" s="18" t="s">
-        <v>256</v>
-      </c>
-      <c r="D67" s="18" t="s">
-        <v>257</v>
-      </c>
-      <c r="E67" s="18" t="s">
-        <v>258</v>
-      </c>
-      <c r="F67" s="18"/>
-      <c r="G67" s="18"/>
-      <c r="H67" s="18"/>
-      <c r="I67" s="18"/>
-      <c r="J67" s="18"/>
-      <c r="K67" s="18"/>
-      <c r="L67" s="18"/>
-      <c r="M67" s="18"/>
-      <c r="N67" s="18"/>
-      <c r="O67" s="18"/>
-      <c r="P67" s="18"/>
-      <c r="Q67" s="18"/>
-      <c r="R67" s="18"/>
-      <c r="S67" s="18"/>
-      <c r="T67" s="18"/>
-      <c r="U67" s="18"/>
-      <c r="V67" s="18"/>
-      <c r="W67" s="18"/>
-      <c r="X67" s="18"/>
-      <c r="Y67" s="18"/>
-    </row>
-    <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="16" t="s">
-        <v>259</v>
-      </c>
-      <c r="B68" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="C68" s="18" t="s">
-        <v>260</v>
-      </c>
-      <c r="D68" s="18" t="s">
-        <v>261</v>
-      </c>
-      <c r="E68" s="18" t="s">
-        <v>262</v>
-      </c>
-      <c r="F68" s="18"/>
-      <c r="G68" s="18"/>
-      <c r="H68" s="18"/>
-      <c r="I68" s="18"/>
-      <c r="J68" s="18"/>
-      <c r="K68" s="18"/>
-      <c r="L68" s="18"/>
-      <c r="M68" s="18"/>
-      <c r="N68" s="18"/>
-      <c r="O68" s="18"/>
-      <c r="P68" s="18"/>
-      <c r="Q68" s="18"/>
-      <c r="R68" s="18"/>
-      <c r="S68" s="18"/>
-      <c r="T68" s="18"/>
-      <c r="U68" s="18"/>
-      <c r="V68" s="18"/>
-      <c r="W68" s="18"/>
-      <c r="X68" s="18"/>
-      <c r="Y68" s="18"/>
-    </row>
-    <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="16" t="s">
-        <v>263</v>
-      </c>
-      <c r="B69" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="C69" s="18" t="s">
-        <v>264</v>
-      </c>
-      <c r="D69" s="18" t="s">
-        <v>265</v>
-      </c>
-      <c r="E69" s="18" t="s">
-        <v>266</v>
-      </c>
-      <c r="F69" s="18"/>
-      <c r="G69" s="18"/>
-      <c r="H69" s="18"/>
-      <c r="I69" s="18"/>
-      <c r="J69" s="18"/>
-      <c r="K69" s="18"/>
-      <c r="L69" s="18"/>
-      <c r="M69" s="18"/>
-      <c r="N69" s="18"/>
-      <c r="O69" s="18"/>
-      <c r="P69" s="18"/>
-      <c r="Q69" s="18"/>
-      <c r="R69" s="18"/>
-      <c r="S69" s="18"/>
-      <c r="T69" s="18"/>
-      <c r="U69" s="18"/>
-      <c r="V69" s="18"/>
-      <c r="W69" s="18"/>
-      <c r="X69" s="18"/>
-      <c r="Y69" s="18"/>
-    </row>
-    <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="16" t="s">
-        <v>267</v>
-      </c>
-      <c r="B70" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="C70" s="18" t="s">
-        <v>268</v>
-      </c>
-      <c r="D70" s="18" t="s">
-        <v>269</v>
-      </c>
-      <c r="E70" s="18" t="s">
-        <v>270</v>
-      </c>
-      <c r="F70" s="18"/>
-      <c r="G70" s="18"/>
-      <c r="H70" s="18"/>
-      <c r="I70" s="18"/>
-      <c r="J70" s="18"/>
-      <c r="K70" s="18"/>
-      <c r="L70" s="18"/>
-      <c r="M70" s="18"/>
-      <c r="N70" s="18"/>
-      <c r="O70" s="18"/>
-      <c r="P70" s="18"/>
-      <c r="Q70" s="18"/>
-      <c r="R70" s="18"/>
-      <c r="S70" s="18"/>
-      <c r="T70" s="18"/>
-      <c r="U70" s="18"/>
-      <c r="V70" s="18"/>
-      <c r="W70" s="18"/>
-      <c r="X70" s="18"/>
-      <c r="Y70" s="18"/>
-    </row>
-    <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="16" t="s">
-        <v>271</v>
-      </c>
-      <c r="B71" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="C71" s="18" t="s">
-        <v>272</v>
-      </c>
-      <c r="D71" s="18" t="s">
-        <v>273</v>
-      </c>
-      <c r="E71" s="18" t="s">
-        <v>274</v>
-      </c>
-      <c r="F71" s="18"/>
-      <c r="G71" s="18"/>
-      <c r="H71" s="18"/>
-      <c r="I71" s="18"/>
-      <c r="J71" s="18"/>
-      <c r="K71" s="18"/>
-      <c r="L71" s="18"/>
-      <c r="M71" s="18"/>
-      <c r="N71" s="18"/>
-      <c r="O71" s="18"/>
-      <c r="P71" s="18"/>
-      <c r="Q71" s="18"/>
-      <c r="R71" s="18"/>
-      <c r="S71" s="18"/>
-      <c r="T71" s="18"/>
-      <c r="U71" s="18"/>
-      <c r="V71" s="18"/>
-      <c r="W71" s="18"/>
-      <c r="X71" s="18"/>
-      <c r="Y71" s="18"/>
-    </row>
-    <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="16" t="s">
-        <v>275</v>
-      </c>
-      <c r="B72" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="C72" s="18" t="s">
-        <v>276</v>
-      </c>
-      <c r="D72" s="18" t="s">
-        <v>277</v>
-      </c>
-      <c r="E72" s="18" t="s">
-        <v>278</v>
-      </c>
-      <c r="F72" s="18"/>
-      <c r="G72" s="18"/>
-      <c r="H72" s="18"/>
-      <c r="I72" s="18"/>
-      <c r="J72" s="18"/>
-      <c r="K72" s="18"/>
-      <c r="L72" s="18"/>
-      <c r="M72" s="18"/>
-      <c r="N72" s="18"/>
-      <c r="O72" s="18"/>
-      <c r="P72" s="18"/>
-      <c r="Q72" s="18"/>
-      <c r="R72" s="18"/>
-      <c r="S72" s="18"/>
-      <c r="T72" s="18"/>
-      <c r="U72" s="18"/>
-      <c r="V72" s="18"/>
-      <c r="W72" s="18"/>
-      <c r="X72" s="18"/>
-      <c r="Y72" s="18"/>
-    </row>
-    <row r="73" ht="15.0" customHeight="1">
-      <c r="A73" s="19" t="s">
-        <v>279</v>
-      </c>
-      <c r="B73" s="20">
-        <v>0.0</v>
-      </c>
-      <c r="C73" s="21" t="s">
-        <v>280</v>
-      </c>
-      <c r="D73" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="E73" s="21" t="s">
-        <v>282</v>
-      </c>
-      <c r="F73" s="21"/>
-      <c r="G73" s="21"/>
-      <c r="H73" s="21"/>
-      <c r="I73" s="21"/>
-      <c r="J73" s="21"/>
-      <c r="K73" s="21"/>
-      <c r="L73" s="21"/>
-      <c r="M73" s="21"/>
-      <c r="N73" s="21"/>
-      <c r="O73" s="21"/>
-      <c r="P73" s="21"/>
-      <c r="Q73" s="21"/>
-      <c r="R73" s="21"/>
-      <c r="S73" s="21"/>
-      <c r="T73" s="21"/>
-      <c r="U73" s="21"/>
-      <c r="V73" s="21"/>
-      <c r="W73" s="21"/>
-      <c r="X73" s="21"/>
-      <c r="Y73" s="21"/>
-    </row>
-    <row r="74" ht="15.0" customHeight="1">
-      <c r="A74" s="22" t="s">
-        <v>283</v>
-      </c>
-      <c r="B74" s="23">
-        <v>0.0</v>
-      </c>
-      <c r="C74" s="23" t="s">
-        <v>284</v>
-      </c>
-      <c r="D74" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="E74" s="23" t="s">
-        <v>160</v>
-      </c>
-      <c r="F74" s="23"/>
-      <c r="G74" s="23"/>
-      <c r="H74" s="23"/>
-      <c r="I74" s="23"/>
-      <c r="J74" s="23"/>
-      <c r="K74" s="23"/>
-      <c r="L74" s="23"/>
-      <c r="M74" s="23"/>
-      <c r="N74" s="23"/>
-      <c r="O74" s="23"/>
-      <c r="P74" s="23"/>
-      <c r="Q74" s="23"/>
-      <c r="R74" s="23"/>
-      <c r="S74" s="23"/>
-      <c r="T74" s="23"/>
-      <c r="U74" s="23"/>
-      <c r="V74" s="23"/>
-      <c r="W74" s="23"/>
-      <c r="X74" s="23"/>
-      <c r="Y74" s="23"/>
+      <c r="F74" s="25"/>
+      <c r="G74" s="25"/>
+      <c r="H74" s="25"/>
+      <c r="I74" s="25"/>
+      <c r="J74" s="25"/>
+      <c r="K74" s="25"/>
+      <c r="L74" s="25"/>
+      <c r="M74" s="25"/>
+      <c r="N74" s="25"/>
+      <c r="O74" s="25"/>
+      <c r="P74" s="25"/>
+      <c r="Q74" s="25"/>
+      <c r="R74" s="25"/>
+      <c r="S74" s="25"/>
+      <c r="T74" s="25"/>
+      <c r="U74" s="25"/>
+      <c r="V74" s="25"/>
+      <c r="W74" s="25"/>
+      <c r="X74" s="25"/>
+      <c r="Y74" s="25"/>
     </row>
     <row r="75" ht="15.0" customHeight="1">
-      <c r="A75" s="22" t="s">
-        <v>285</v>
-      </c>
-      <c r="B75" s="23">
-        <v>0.0</v>
-      </c>
-      <c r="C75" s="23" t="s">
-        <v>286</v>
-      </c>
-      <c r="D75" s="23" t="s">
-        <v>287</v>
-      </c>
-      <c r="E75" s="23" t="s">
-        <v>288</v>
-      </c>
-      <c r="F75" s="23"/>
-      <c r="G75" s="23"/>
-      <c r="H75" s="23"/>
-      <c r="I75" s="23"/>
-      <c r="J75" s="23"/>
-      <c r="K75" s="23"/>
-      <c r="L75" s="23"/>
-      <c r="M75" s="23"/>
-      <c r="N75" s="23"/>
-      <c r="O75" s="23"/>
-      <c r="P75" s="23"/>
-      <c r="Q75" s="23"/>
-      <c r="R75" s="23"/>
-      <c r="S75" s="23"/>
-      <c r="T75" s="23"/>
-      <c r="U75" s="23"/>
-      <c r="V75" s="23"/>
-      <c r="W75" s="23"/>
-      <c r="X75" s="23"/>
-      <c r="Y75" s="23"/>
-    </row>
-    <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="22" t="s">
-        <v>289</v>
-      </c>
-      <c r="B76" s="23">
-        <v>0.0</v>
-      </c>
-      <c r="C76" s="23" t="s">
-        <v>290</v>
-      </c>
-      <c r="D76" s="23" t="s">
-        <v>187</v>
-      </c>
-      <c r="E76" s="23" t="s">
-        <v>188</v>
-      </c>
-      <c r="F76" s="23"/>
-      <c r="G76" s="23"/>
-      <c r="H76" s="23"/>
-      <c r="I76" s="23"/>
-      <c r="J76" s="23"/>
-      <c r="K76" s="23"/>
-      <c r="L76" s="23"/>
-      <c r="M76" s="23"/>
-      <c r="N76" s="23"/>
-      <c r="O76" s="23"/>
-      <c r="P76" s="23"/>
-      <c r="Q76" s="23"/>
-      <c r="R76" s="23"/>
-      <c r="S76" s="23"/>
-      <c r="T76" s="23"/>
-      <c r="U76" s="23"/>
-      <c r="V76" s="23"/>
-      <c r="W76" s="23"/>
-      <c r="X76" s="23"/>
-      <c r="Y76" s="23"/>
-    </row>
-    <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="22" t="s">
-        <v>291</v>
-      </c>
-      <c r="B77" s="23">
-        <v>0.0</v>
-      </c>
-      <c r="C77" s="23" t="s">
-        <v>292</v>
-      </c>
-      <c r="D77" s="23" t="s">
-        <v>293</v>
-      </c>
-      <c r="E77" s="23" t="s">
-        <v>294</v>
-      </c>
-      <c r="F77" s="23"/>
-      <c r="G77" s="23"/>
-      <c r="H77" s="23"/>
-      <c r="I77" s="23"/>
-      <c r="J77" s="23"/>
-      <c r="K77" s="23"/>
-      <c r="L77" s="23"/>
-      <c r="M77" s="23"/>
-      <c r="N77" s="23"/>
-      <c r="O77" s="23"/>
-      <c r="P77" s="23"/>
-      <c r="Q77" s="23"/>
-      <c r="R77" s="23"/>
-      <c r="S77" s="23"/>
-      <c r="T77" s="23"/>
-      <c r="U77" s="23"/>
-      <c r="V77" s="23"/>
-      <c r="W77" s="23"/>
-      <c r="X77" s="23"/>
-      <c r="Y77" s="23"/>
+      <c r="A75" s="1"/>
+      <c r="B75" s="1"/>
+      <c r="C75" s="1"/>
+      <c r="D75" s="1"/>
+      <c r="E75" s="1"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1"/>
+      <c r="K75" s="1"/>
+      <c r="L75" s="1"/>
+      <c r="M75" s="1"/>
+      <c r="N75" s="1"/>
+      <c r="O75" s="1"/>
+      <c r="P75" s="1"/>
+      <c r="Q75" s="1"/>
+      <c r="R75" s="1"/>
+      <c r="S75" s="1"/>
+      <c r="T75" s="1"/>
+      <c r="U75" s="1"/>
+      <c r="V75" s="1"/>
+      <c r="W75" s="1"/>
+      <c r="X75" s="1"/>
+      <c r="Y75" s="1"/>
+    </row>
+    <row r="76" ht="15.0" customHeight="1">
+      <c r="A76" s="1"/>
+      <c r="B76" s="1"/>
+      <c r="C76" s="1"/>
+      <c r="D76" s="1"/>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
+      <c r="J76" s="1"/>
+      <c r="K76" s="1"/>
+      <c r="L76" s="1"/>
+      <c r="M76" s="1"/>
+      <c r="N76" s="1"/>
+      <c r="O76" s="1"/>
+      <c r="P76" s="1"/>
+      <c r="Q76" s="1"/>
+      <c r="R76" s="1"/>
+      <c r="S76" s="1"/>
+      <c r="T76" s="1"/>
+      <c r="U76" s="1"/>
+      <c r="V76" s="1"/>
+      <c r="W76" s="1"/>
+      <c r="X76" s="1"/>
+      <c r="Y76" s="1"/>
+    </row>
+    <row r="77" ht="15.0" customHeight="1">
+      <c r="A77" s="1"/>
+      <c r="B77" s="1"/>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1"/>
+      <c r="E77" s="1"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+      <c r="J77" s="1"/>
+      <c r="K77" s="1"/>
+      <c r="L77" s="1"/>
+      <c r="M77" s="1"/>
+      <c r="N77" s="1"/>
+      <c r="O77" s="1"/>
+      <c r="P77" s="1"/>
+      <c r="Q77" s="1"/>
+      <c r="R77" s="1"/>
+      <c r="S77" s="1"/>
+      <c r="T77" s="1"/>
+      <c r="U77" s="1"/>
+      <c r="V77" s="1"/>
+      <c r="W77" s="1"/>
+      <c r="X77" s="1"/>
+      <c r="Y77" s="1"/>
     </row>
     <row r="78" ht="15.0" customHeight="1">
-      <c r="A78" s="22" t="s">
-        <v>295</v>
-      </c>
-      <c r="B78" s="23">
-        <v>0.0</v>
-      </c>
-      <c r="C78" s="23" t="s">
-        <v>296</v>
-      </c>
-      <c r="D78" s="23" t="s">
-        <v>297</v>
-      </c>
-      <c r="E78" s="23" t="s">
-        <v>298</v>
-      </c>
-      <c r="F78" s="23"/>
-      <c r="G78" s="23"/>
-      <c r="H78" s="23"/>
-      <c r="I78" s="23"/>
-      <c r="J78" s="23"/>
-      <c r="K78" s="23"/>
-      <c r="L78" s="23"/>
-      <c r="M78" s="23"/>
-      <c r="N78" s="23"/>
-      <c r="O78" s="23"/>
-      <c r="P78" s="23"/>
-      <c r="Q78" s="23"/>
-      <c r="R78" s="23"/>
-      <c r="S78" s="23"/>
-      <c r="T78" s="23"/>
-      <c r="U78" s="23"/>
-      <c r="V78" s="23"/>
-      <c r="W78" s="23"/>
-      <c r="X78" s="23"/>
-      <c r="Y78" s="23"/>
+      <c r="A78" s="1"/>
+      <c r="B78" s="1"/>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="1"/>
+      <c r="K78" s="1"/>
+      <c r="L78" s="1"/>
+      <c r="M78" s="1"/>
+      <c r="N78" s="1"/>
+      <c r="O78" s="1"/>
+      <c r="P78" s="1"/>
+      <c r="Q78" s="1"/>
+      <c r="R78" s="1"/>
+      <c r="S78" s="1"/>
+      <c r="T78" s="1"/>
+      <c r="U78" s="1"/>
+      <c r="V78" s="1"/>
+      <c r="W78" s="1"/>
+      <c r="X78" s="1"/>
+      <c r="Y78" s="1"/>
     </row>
     <row r="79" ht="15.0" customHeight="1">
-      <c r="A79" s="22" t="s">
-        <v>299</v>
-      </c>
-      <c r="B79" s="23">
-        <v>0.0</v>
-      </c>
-      <c r="C79" s="23" t="s">
-        <v>300</v>
-      </c>
-      <c r="D79" s="23" t="s">
-        <v>301</v>
-      </c>
-      <c r="E79" s="23" t="s">
-        <v>302</v>
-      </c>
-      <c r="F79" s="23"/>
-      <c r="G79" s="23"/>
-      <c r="H79" s="23"/>
-      <c r="I79" s="23"/>
-      <c r="J79" s="23"/>
-      <c r="K79" s="23"/>
-      <c r="L79" s="23"/>
-      <c r="M79" s="23"/>
-      <c r="N79" s="23"/>
-      <c r="O79" s="23"/>
-      <c r="P79" s="23"/>
-      <c r="Q79" s="23"/>
-      <c r="R79" s="23"/>
-      <c r="S79" s="23"/>
-      <c r="T79" s="23"/>
-      <c r="U79" s="23"/>
-      <c r="V79" s="23"/>
-      <c r="W79" s="23"/>
-      <c r="X79" s="23"/>
-      <c r="Y79" s="23"/>
+      <c r="A79" s="1"/>
+      <c r="B79" s="1"/>
+      <c r="C79" s="1"/>
+      <c r="D79" s="1"/>
+      <c r="E79" s="1"/>
+      <c r="F79" s="1"/>
+      <c r="G79" s="1"/>
+      <c r="H79" s="1"/>
+      <c r="I79" s="1"/>
+      <c r="J79" s="1"/>
+      <c r="K79" s="1"/>
+      <c r="L79" s="1"/>
+      <c r="M79" s="1"/>
+      <c r="N79" s="1"/>
+      <c r="O79" s="1"/>
+      <c r="P79" s="1"/>
+      <c r="Q79" s="1"/>
+      <c r="R79" s="1"/>
+      <c r="S79" s="1"/>
+      <c r="T79" s="1"/>
+      <c r="U79" s="1"/>
+      <c r="V79" s="1"/>
+      <c r="W79" s="1"/>
+      <c r="X79" s="1"/>
+      <c r="Y79" s="1"/>
     </row>
     <row r="80" ht="15.0" customHeight="1">
-      <c r="A80" s="22" t="s">
-        <v>303</v>
-      </c>
-      <c r="B80" s="23">
-        <v>0.0</v>
-      </c>
-      <c r="C80" s="23" t="s">
-        <v>304</v>
-      </c>
-      <c r="D80" s="23" t="s">
-        <v>305</v>
-      </c>
-      <c r="E80" s="23" t="s">
-        <v>306</v>
-      </c>
-      <c r="F80" s="23"/>
-      <c r="G80" s="23"/>
-      <c r="H80" s="23"/>
-      <c r="I80" s="23"/>
-      <c r="J80" s="23"/>
-      <c r="K80" s="23"/>
-      <c r="L80" s="23"/>
-      <c r="M80" s="23"/>
-      <c r="N80" s="23"/>
-      <c r="O80" s="23"/>
-      <c r="P80" s="23"/>
-      <c r="Q80" s="23"/>
-      <c r="R80" s="23"/>
-      <c r="S80" s="23"/>
-      <c r="T80" s="23"/>
-      <c r="U80" s="23"/>
-      <c r="V80" s="23"/>
-      <c r="W80" s="23"/>
-      <c r="X80" s="23"/>
-      <c r="Y80" s="23"/>
+      <c r="A80" s="1"/>
+      <c r="B80" s="1"/>
+      <c r="C80" s="1"/>
+      <c r="D80" s="1"/>
+      <c r="E80" s="1"/>
+      <c r="F80" s="1"/>
+      <c r="G80" s="1"/>
+      <c r="H80" s="1"/>
+      <c r="I80" s="1"/>
+      <c r="J80" s="1"/>
+      <c r="K80" s="1"/>
+      <c r="L80" s="1"/>
+      <c r="M80" s="1"/>
+      <c r="N80" s="1"/>
+      <c r="O80" s="1"/>
+      <c r="P80" s="1"/>
+      <c r="Q80" s="1"/>
+      <c r="R80" s="1"/>
+      <c r="S80" s="1"/>
+      <c r="T80" s="1"/>
+      <c r="U80" s="1"/>
+      <c r="V80" s="1"/>
+      <c r="W80" s="1"/>
+      <c r="X80" s="1"/>
+      <c r="Y80" s="1"/>
     </row>
     <row r="81" ht="15.0" customHeight="1">
-      <c r="A81" s="24" t="s">
-        <v>307</v>
-      </c>
-      <c r="B81" s="25">
-        <v>0.0</v>
-      </c>
-      <c r="C81" s="26" t="s">
-        <v>308</v>
-      </c>
-      <c r="D81" s="26" t="s">
-        <v>219</v>
-      </c>
-      <c r="E81" s="26" t="s">
-        <v>220</v>
-      </c>
-      <c r="F81" s="26"/>
-      <c r="G81" s="26"/>
-      <c r="H81" s="26"/>
-      <c r="I81" s="26"/>
-      <c r="J81" s="26"/>
-      <c r="K81" s="26"/>
-      <c r="L81" s="26"/>
-      <c r="M81" s="26"/>
-      <c r="N81" s="26"/>
-      <c r="O81" s="26"/>
-      <c r="P81" s="26"/>
-      <c r="Q81" s="26"/>
-      <c r="R81" s="26"/>
-      <c r="S81" s="26"/>
-      <c r="T81" s="26"/>
-      <c r="U81" s="26"/>
-      <c r="V81" s="26"/>
-      <c r="W81" s="26"/>
-      <c r="X81" s="26"/>
-      <c r="Y81" s="26"/>
+      <c r="A81" s="1"/>
+      <c r="B81" s="1"/>
+      <c r="C81" s="1"/>
+      <c r="D81" s="1"/>
+      <c r="E81" s="1"/>
+      <c r="F81" s="1"/>
+      <c r="G81" s="1"/>
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
+      <c r="J81" s="1"/>
+      <c r="K81" s="1"/>
+      <c r="L81" s="1"/>
+      <c r="M81" s="1"/>
+      <c r="N81" s="1"/>
+      <c r="O81" s="1"/>
+      <c r="P81" s="1"/>
+      <c r="Q81" s="1"/>
+      <c r="R81" s="1"/>
+      <c r="S81" s="1"/>
+      <c r="T81" s="1"/>
+      <c r="U81" s="1"/>
+      <c r="V81" s="1"/>
+      <c r="W81" s="1"/>
+      <c r="X81" s="1"/>
+      <c r="Y81" s="1"/>
     </row>
     <row r="82" ht="15.0" customHeight="1">
-      <c r="A82" s="27" t="s">
-        <v>309</v>
-      </c>
-      <c r="B82" s="28">
-        <v>0.0</v>
-      </c>
-      <c r="C82" s="29" t="s">
-        <v>310</v>
-      </c>
-      <c r="D82" s="29" t="s">
-        <v>151</v>
-      </c>
-      <c r="E82" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="F82" s="29"/>
-      <c r="G82" s="29"/>
-      <c r="H82" s="29"/>
-      <c r="I82" s="29"/>
-      <c r="J82" s="29"/>
-      <c r="K82" s="29"/>
-      <c r="L82" s="29"/>
-      <c r="M82" s="29"/>
-      <c r="N82" s="29"/>
-      <c r="O82" s="29"/>
-      <c r="P82" s="29"/>
-      <c r="Q82" s="29"/>
-      <c r="R82" s="29"/>
-      <c r="S82" s="29"/>
-      <c r="T82" s="29"/>
-      <c r="U82" s="29"/>
-      <c r="V82" s="29"/>
-      <c r="W82" s="29"/>
-      <c r="X82" s="29"/>
-      <c r="Y82" s="29"/>
+      <c r="A82" s="1"/>
+      <c r="B82" s="1"/>
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="1"/>
+      <c r="H82" s="1"/>
+      <c r="I82" s="1"/>
+      <c r="J82" s="1"/>
+      <c r="K82" s="1"/>
+      <c r="L82" s="1"/>
+      <c r="M82" s="1"/>
+      <c r="N82" s="1"/>
+      <c r="O82" s="1"/>
+      <c r="P82" s="1"/>
+      <c r="Q82" s="1"/>
+      <c r="R82" s="1"/>
+      <c r="S82" s="1"/>
+      <c r="T82" s="1"/>
+      <c r="U82" s="1"/>
+      <c r="V82" s="1"/>
+      <c r="W82" s="1"/>
+      <c r="X82" s="1"/>
+      <c r="Y82" s="1"/>
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="1"/>
@@ -9126,7 +8962,7 @@
       <c r="X258" s="1"/>
       <c r="Y258" s="1"/>
     </row>
-    <row r="259" ht="15.0" customHeight="1">
+    <row r="259" ht="15.75" customHeight="1">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -9153,7 +8989,7 @@
       <c r="X259" s="1"/>
       <c r="Y259" s="1"/>
     </row>
-    <row r="260" ht="15.0" customHeight="1">
+    <row r="260" ht="15.75" customHeight="1">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -9180,7 +9016,7 @@
       <c r="X260" s="1"/>
       <c r="Y260" s="1"/>
     </row>
-    <row r="261" ht="15.0" customHeight="1">
+    <row r="261" ht="15.75" customHeight="1">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -9207,7 +9043,7 @@
       <c r="X261" s="1"/>
       <c r="Y261" s="1"/>
     </row>
-    <row r="262" ht="15.0" customHeight="1">
+    <row r="262" ht="15.75" customHeight="1">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -9234,7 +9070,7 @@
       <c r="X262" s="1"/>
       <c r="Y262" s="1"/>
     </row>
-    <row r="263" ht="15.0" customHeight="1">
+    <row r="263" ht="15.75" customHeight="1">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -9261,7 +9097,7 @@
       <c r="X263" s="1"/>
       <c r="Y263" s="1"/>
     </row>
-    <row r="264" ht="15.0" customHeight="1">
+    <row r="264" ht="15.75" customHeight="1">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -9288,7 +9124,7 @@
       <c r="X264" s="1"/>
       <c r="Y264" s="1"/>
     </row>
-    <row r="265" ht="15.0" customHeight="1">
+    <row r="265" ht="15.75" customHeight="1">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -9315,7 +9151,7 @@
       <c r="X265" s="1"/>
       <c r="Y265" s="1"/>
     </row>
-    <row r="266" ht="15.0" customHeight="1">
+    <row r="266" ht="15.75" customHeight="1">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -9558,222 +9394,14 @@
       <c r="X274" s="1"/>
       <c r="Y274" s="1"/>
     </row>
-    <row r="275" ht="15.75" customHeight="1">
-      <c r="A275" s="1"/>
-      <c r="B275" s="1"/>
-      <c r="C275" s="1"/>
-      <c r="D275" s="1"/>
-      <c r="E275" s="1"/>
-      <c r="F275" s="1"/>
-      <c r="G275" s="1"/>
-      <c r="H275" s="1"/>
-      <c r="I275" s="1"/>
-      <c r="J275" s="1"/>
-      <c r="K275" s="1"/>
-      <c r="L275" s="1"/>
-      <c r="M275" s="1"/>
-      <c r="N275" s="1"/>
-      <c r="O275" s="1"/>
-      <c r="P275" s="1"/>
-      <c r="Q275" s="1"/>
-      <c r="R275" s="1"/>
-      <c r="S275" s="1"/>
-      <c r="T275" s="1"/>
-      <c r="U275" s="1"/>
-      <c r="V275" s="1"/>
-      <c r="W275" s="1"/>
-      <c r="X275" s="1"/>
-      <c r="Y275" s="1"/>
-    </row>
-    <row r="276" ht="15.75" customHeight="1">
-      <c r="A276" s="1"/>
-      <c r="B276" s="1"/>
-      <c r="C276" s="1"/>
-      <c r="D276" s="1"/>
-      <c r="E276" s="1"/>
-      <c r="F276" s="1"/>
-      <c r="G276" s="1"/>
-      <c r="H276" s="1"/>
-      <c r="I276" s="1"/>
-      <c r="J276" s="1"/>
-      <c r="K276" s="1"/>
-      <c r="L276" s="1"/>
-      <c r="M276" s="1"/>
-      <c r="N276" s="1"/>
-      <c r="O276" s="1"/>
-      <c r="P276" s="1"/>
-      <c r="Q276" s="1"/>
-      <c r="R276" s="1"/>
-      <c r="S276" s="1"/>
-      <c r="T276" s="1"/>
-      <c r="U276" s="1"/>
-      <c r="V276" s="1"/>
-      <c r="W276" s="1"/>
-      <c r="X276" s="1"/>
-      <c r="Y276" s="1"/>
-    </row>
-    <row r="277" ht="15.75" customHeight="1">
-      <c r="A277" s="1"/>
-      <c r="B277" s="1"/>
-      <c r="C277" s="1"/>
-      <c r="D277" s="1"/>
-      <c r="E277" s="1"/>
-      <c r="F277" s="1"/>
-      <c r="G277" s="1"/>
-      <c r="H277" s="1"/>
-      <c r="I277" s="1"/>
-      <c r="J277" s="1"/>
-      <c r="K277" s="1"/>
-      <c r="L277" s="1"/>
-      <c r="M277" s="1"/>
-      <c r="N277" s="1"/>
-      <c r="O277" s="1"/>
-      <c r="P277" s="1"/>
-      <c r="Q277" s="1"/>
-      <c r="R277" s="1"/>
-      <c r="S277" s="1"/>
-      <c r="T277" s="1"/>
-      <c r="U277" s="1"/>
-      <c r="V277" s="1"/>
-      <c r="W277" s="1"/>
-      <c r="X277" s="1"/>
-      <c r="Y277" s="1"/>
-    </row>
-    <row r="278" ht="15.75" customHeight="1">
-      <c r="A278" s="1"/>
-      <c r="B278" s="1"/>
-      <c r="C278" s="1"/>
-      <c r="D278" s="1"/>
-      <c r="E278" s="1"/>
-      <c r="F278" s="1"/>
-      <c r="G278" s="1"/>
-      <c r="H278" s="1"/>
-      <c r="I278" s="1"/>
-      <c r="J278" s="1"/>
-      <c r="K278" s="1"/>
-      <c r="L278" s="1"/>
-      <c r="M278" s="1"/>
-      <c r="N278" s="1"/>
-      <c r="O278" s="1"/>
-      <c r="P278" s="1"/>
-      <c r="Q278" s="1"/>
-      <c r="R278" s="1"/>
-      <c r="S278" s="1"/>
-      <c r="T278" s="1"/>
-      <c r="U278" s="1"/>
-      <c r="V278" s="1"/>
-      <c r="W278" s="1"/>
-      <c r="X278" s="1"/>
-      <c r="Y278" s="1"/>
-    </row>
-    <row r="279" ht="15.75" customHeight="1">
-      <c r="A279" s="1"/>
-      <c r="B279" s="1"/>
-      <c r="C279" s="1"/>
-      <c r="D279" s="1"/>
-      <c r="E279" s="1"/>
-      <c r="F279" s="1"/>
-      <c r="G279" s="1"/>
-      <c r="H279" s="1"/>
-      <c r="I279" s="1"/>
-      <c r="J279" s="1"/>
-      <c r="K279" s="1"/>
-      <c r="L279" s="1"/>
-      <c r="M279" s="1"/>
-      <c r="N279" s="1"/>
-      <c r="O279" s="1"/>
-      <c r="P279" s="1"/>
-      <c r="Q279" s="1"/>
-      <c r="R279" s="1"/>
-      <c r="S279" s="1"/>
-      <c r="T279" s="1"/>
-      <c r="U279" s="1"/>
-      <c r="V279" s="1"/>
-      <c r="W279" s="1"/>
-      <c r="X279" s="1"/>
-      <c r="Y279" s="1"/>
-    </row>
-    <row r="280" ht="15.75" customHeight="1">
-      <c r="A280" s="1"/>
-      <c r="B280" s="1"/>
-      <c r="C280" s="1"/>
-      <c r="D280" s="1"/>
-      <c r="E280" s="1"/>
-      <c r="F280" s="1"/>
-      <c r="G280" s="1"/>
-      <c r="H280" s="1"/>
-      <c r="I280" s="1"/>
-      <c r="J280" s="1"/>
-      <c r="K280" s="1"/>
-      <c r="L280" s="1"/>
-      <c r="M280" s="1"/>
-      <c r="N280" s="1"/>
-      <c r="O280" s="1"/>
-      <c r="P280" s="1"/>
-      <c r="Q280" s="1"/>
-      <c r="R280" s="1"/>
-      <c r="S280" s="1"/>
-      <c r="T280" s="1"/>
-      <c r="U280" s="1"/>
-      <c r="V280" s="1"/>
-      <c r="W280" s="1"/>
-      <c r="X280" s="1"/>
-      <c r="Y280" s="1"/>
-    </row>
-    <row r="281" ht="15.75" customHeight="1">
-      <c r="A281" s="1"/>
-      <c r="B281" s="1"/>
-      <c r="C281" s="1"/>
-      <c r="D281" s="1"/>
-      <c r="E281" s="1"/>
-      <c r="F281" s="1"/>
-      <c r="G281" s="1"/>
-      <c r="H281" s="1"/>
-      <c r="I281" s="1"/>
-      <c r="J281" s="1"/>
-      <c r="K281" s="1"/>
-      <c r="L281" s="1"/>
-      <c r="M281" s="1"/>
-      <c r="N281" s="1"/>
-      <c r="O281" s="1"/>
-      <c r="P281" s="1"/>
-      <c r="Q281" s="1"/>
-      <c r="R281" s="1"/>
-      <c r="S281" s="1"/>
-      <c r="T281" s="1"/>
-      <c r="U281" s="1"/>
-      <c r="V281" s="1"/>
-      <c r="W281" s="1"/>
-      <c r="X281" s="1"/>
-      <c r="Y281" s="1"/>
-    </row>
-    <row r="282" ht="15.75" customHeight="1">
-      <c r="A282" s="1"/>
-      <c r="B282" s="1"/>
-      <c r="C282" s="1"/>
-      <c r="D282" s="1"/>
-      <c r="E282" s="1"/>
-      <c r="F282" s="1"/>
-      <c r="G282" s="1"/>
-      <c r="H282" s="1"/>
-      <c r="I282" s="1"/>
-      <c r="J282" s="1"/>
-      <c r="K282" s="1"/>
-      <c r="L282" s="1"/>
-      <c r="M282" s="1"/>
-      <c r="N282" s="1"/>
-      <c r="O282" s="1"/>
-      <c r="P282" s="1"/>
-      <c r="Q282" s="1"/>
-      <c r="R282" s="1"/>
-      <c r="S282" s="1"/>
-      <c r="T282" s="1"/>
-      <c r="U282" s="1"/>
-      <c r="V282" s="1"/>
-      <c r="W282" s="1"/>
-      <c r="X282" s="1"/>
-      <c r="Y282" s="1"/>
-    </row>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
     <row r="283" ht="15.75" customHeight="1"/>
     <row r="284" ht="15.75" customHeight="1"/>
     <row r="285" ht="15.75" customHeight="1"/>
@@ -10484,14 +10112,6 @@
     <row r="990" ht="15.75" customHeight="1"/>
     <row r="991" ht="15.75" customHeight="1"/>
     <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Templates/Tables/StringInfo/StrTable.xlsx
+++ b/Templates/Tables/StringInfo/StrTable.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="299">
   <si>
     <t>ID</t>
   </si>
@@ -50,6 +50,42 @@
   </si>
   <si>
     <t>Do you want to reset the editor?</t>
+  </si>
+  <si>
+    <t>EDITOR_A_SET_P_MSG</t>
+  </si>
+  <si>
+    <t>에디터 세트 A 팝업 메세지</t>
+  </si>
+  <si>
+    <t>A 세트 를 설정하시겠습니까?</t>
+  </si>
+  <si>
+    <t>Do you want to set up the A set?</t>
+  </si>
+  <si>
+    <t>EDITOR_B_SET_P_MSG</t>
+  </si>
+  <si>
+    <t>에디터 세트 B 팝업 메세지</t>
+  </si>
+  <si>
+    <t>B 세트 를 설정하시겠습니까?</t>
+  </si>
+  <si>
+    <t>Do you want to set up the B set?</t>
+  </si>
+  <si>
+    <t>EDITOR_TABLE_RL_MSG</t>
+  </si>
+  <si>
+    <t>에디터 테이블 다시 로드 메세지</t>
+  </si>
+  <si>
+    <t>테이블을 다시 로드하시겠습니까?</t>
+  </si>
+  <si>
+    <t>Do you want to reload the table?</t>
   </si>
   <si>
     <t>EDITOR_REMOVE_LP_MSG</t>
@@ -962,7 +998,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -984,6 +1020,15 @@
     </xf>
     <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="3" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
@@ -1368,19 +1413,19 @@
       <c r="Y3" s="7"/>
     </row>
     <row r="4" ht="15.0" customHeight="1">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="9">
         <v>0.0</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="10" t="s">
         <v>16</v>
       </c>
       <c r="F4" s="7"/>
@@ -1405,19 +1450,19 @@
       <c r="Y4" s="7"/>
     </row>
     <row r="5" ht="15.0" customHeight="1">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="9">
         <v>0.0</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="10" t="s">
         <v>20</v>
       </c>
       <c r="F5" s="7"/>
@@ -1442,19 +1487,19 @@
       <c r="Y5" s="7"/>
     </row>
     <row r="6" ht="15.0" customHeight="1">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="9">
         <v>0.0</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="10" t="s">
         <v>24</v>
       </c>
       <c r="F6" s="7"/>
@@ -1528,7 +1573,7 @@
       <c r="D8" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F8" s="7"/>
@@ -1590,7 +1635,7 @@
       <c r="Y9" s="7"/>
     </row>
     <row r="10" ht="15.0" customHeight="1">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="5" t="s">
         <v>37</v>
       </c>
       <c r="B10" s="6">
@@ -1627,7 +1672,7 @@
       <c r="Y10" s="7"/>
     </row>
     <row r="11" ht="15.0" customHeight="1">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="5" t="s">
         <v>41</v>
       </c>
       <c r="B11" s="6">
@@ -1639,7 +1684,7 @@
       <c r="D11" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="11" t="s">
         <v>44</v>
       </c>
       <c r="F11" s="7"/>
@@ -1701,7 +1746,7 @@
       <c r="Y12" s="7"/>
     </row>
     <row r="13" ht="15.0" customHeight="1">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="7" t="s">
         <v>49</v>
       </c>
       <c r="B13" s="6">
@@ -1738,7 +1783,7 @@
       <c r="Y13" s="7"/>
     </row>
     <row r="14" ht="15.0" customHeight="1">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="7" t="s">
         <v>53</v>
       </c>
       <c r="B14" s="6">
@@ -1848,116 +1893,116 @@
       <c r="X16" s="7"/>
       <c r="Y16" s="7"/>
     </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="9" t="s">
+    <row r="17" ht="15.0" customHeight="1">
+      <c r="A17" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="6">
         <v>0.0</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="11"/>
-      <c r="O17" s="11"/>
-      <c r="P17" s="11"/>
-      <c r="Q17" s="11"/>
-      <c r="R17" s="11"/>
-      <c r="S17" s="11"/>
-      <c r="T17" s="11"/>
-      <c r="U17" s="11"/>
-      <c r="V17" s="11"/>
-      <c r="W17" s="11"/>
-      <c r="X17" s="11"/>
-      <c r="Y17" s="11"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="12" t="s">
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="7"/>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="7"/>
+      <c r="R17" s="7"/>
+      <c r="S17" s="7"/>
+      <c r="T17" s="7"/>
+      <c r="U17" s="7"/>
+      <c r="V17" s="7"/>
+      <c r="W17" s="7"/>
+      <c r="X17" s="7"/>
+      <c r="Y17" s="7"/>
+    </row>
+    <row r="18" ht="15.0" customHeight="1">
+      <c r="A18" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="6">
         <v>0.0</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C18" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="E18" s="14" t="s">
+      <c r="E18" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="14"/>
-      <c r="K18" s="14"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="14"/>
-      <c r="N18" s="14"/>
-      <c r="O18" s="14"/>
-      <c r="P18" s="14"/>
-      <c r="Q18" s="14"/>
-      <c r="R18" s="14"/>
-      <c r="S18" s="14"/>
-      <c r="T18" s="14"/>
-      <c r="U18" s="14"/>
-      <c r="V18" s="14"/>
-      <c r="W18" s="14"/>
-      <c r="X18" s="14"/>
-      <c r="Y18" s="14"/>
-    </row>
-    <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="12" t="s">
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="7"/>
+      <c r="O18" s="7"/>
+      <c r="P18" s="7"/>
+      <c r="Q18" s="7"/>
+      <c r="R18" s="7"/>
+      <c r="S18" s="7"/>
+      <c r="T18" s="7"/>
+      <c r="U18" s="7"/>
+      <c r="V18" s="7"/>
+      <c r="W18" s="7"/>
+      <c r="X18" s="7"/>
+      <c r="Y18" s="7"/>
+    </row>
+    <row r="19" ht="15.0" customHeight="1">
+      <c r="A19" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B19" s="13">
+      <c r="B19" s="6">
         <v>0.0</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C19" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D19" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E19" s="14" t="s">
+      <c r="E19" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="14"/>
-      <c r="K19" s="14"/>
-      <c r="L19" s="14"/>
-      <c r="M19" s="14"/>
-      <c r="N19" s="14"/>
-      <c r="O19" s="14"/>
-      <c r="P19" s="14"/>
-      <c r="Q19" s="14"/>
-      <c r="R19" s="14"/>
-      <c r="S19" s="14"/>
-      <c r="T19" s="14"/>
-      <c r="U19" s="14"/>
-      <c r="V19" s="14"/>
-      <c r="W19" s="14"/>
-      <c r="X19" s="14"/>
-      <c r="Y19" s="14"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="7"/>
+      <c r="O19" s="7"/>
+      <c r="P19" s="7"/>
+      <c r="Q19" s="7"/>
+      <c r="R19" s="7"/>
+      <c r="S19" s="7"/>
+      <c r="T19" s="7"/>
+      <c r="U19" s="7"/>
+      <c r="V19" s="7"/>
+      <c r="W19" s="7"/>
+      <c r="X19" s="7"/>
+      <c r="Y19" s="7"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="12" t="s">
@@ -1997,1632 +2042,1632 @@
       <c r="Y20" s="14"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="B21" s="13">
+      <c r="B21" s="16">
         <v>0.0</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="C21" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="D21" s="14" t="s">
+      <c r="D21" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="E21" s="14" t="s">
+      <c r="E21" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="14"/>
-      <c r="J21" s="14"/>
-      <c r="K21" s="14"/>
-      <c r="L21" s="14"/>
-      <c r="M21" s="14"/>
-      <c r="N21" s="14"/>
-      <c r="O21" s="14"/>
-      <c r="P21" s="14"/>
-      <c r="Q21" s="14"/>
-      <c r="R21" s="14"/>
-      <c r="S21" s="14"/>
-      <c r="T21" s="14"/>
-      <c r="U21" s="14"/>
-      <c r="V21" s="14"/>
-      <c r="W21" s="14"/>
-      <c r="X21" s="14"/>
-      <c r="Y21" s="14"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="17"/>
+      <c r="M21" s="17"/>
+      <c r="N21" s="17"/>
+      <c r="O21" s="17"/>
+      <c r="P21" s="17"/>
+      <c r="Q21" s="17"/>
+      <c r="R21" s="17"/>
+      <c r="S21" s="17"/>
+      <c r="T21" s="17"/>
+      <c r="U21" s="17"/>
+      <c r="V21" s="17"/>
+      <c r="W21" s="17"/>
+      <c r="X21" s="17"/>
+      <c r="Y21" s="17"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="B22" s="13">
+      <c r="B22" s="16">
         <v>0.0</v>
       </c>
-      <c r="C22" s="14" t="s">
+      <c r="C22" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="D22" s="14" t="s">
+      <c r="D22" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="E22" s="14" t="s">
+      <c r="E22" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="14"/>
-      <c r="J22" s="14"/>
-      <c r="K22" s="14"/>
-      <c r="L22" s="14"/>
-      <c r="M22" s="14"/>
-      <c r="N22" s="14"/>
-      <c r="O22" s="14"/>
-      <c r="P22" s="14"/>
-      <c r="Q22" s="14"/>
-      <c r="R22" s="14"/>
-      <c r="S22" s="14"/>
-      <c r="T22" s="14"/>
-      <c r="U22" s="14"/>
-      <c r="V22" s="14"/>
-      <c r="W22" s="14"/>
-      <c r="X22" s="14"/>
-      <c r="Y22" s="14"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="17"/>
+      <c r="L22" s="17"/>
+      <c r="M22" s="17"/>
+      <c r="N22" s="17"/>
+      <c r="O22" s="17"/>
+      <c r="P22" s="17"/>
+      <c r="Q22" s="17"/>
+      <c r="R22" s="17"/>
+      <c r="S22" s="17"/>
+      <c r="T22" s="17"/>
+      <c r="U22" s="17"/>
+      <c r="V22" s="17"/>
+      <c r="W22" s="17"/>
+      <c r="X22" s="17"/>
+      <c r="Y22" s="17"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="B23" s="13">
+      <c r="B23" s="16">
         <v>0.0</v>
       </c>
-      <c r="C23" s="14" t="s">
+      <c r="C23" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="D23" s="14" t="s">
+      <c r="D23" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="E23" s="14" t="s">
+      <c r="E23" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="14"/>
-      <c r="K23" s="14"/>
-      <c r="L23" s="14"/>
-      <c r="M23" s="14"/>
-      <c r="N23" s="14"/>
-      <c r="O23" s="14"/>
-      <c r="P23" s="14"/>
-      <c r="Q23" s="14"/>
-      <c r="R23" s="14"/>
-      <c r="S23" s="14"/>
-      <c r="T23" s="14"/>
-      <c r="U23" s="14"/>
-      <c r="V23" s="14"/>
-      <c r="W23" s="14"/>
-      <c r="X23" s="14"/>
-      <c r="Y23" s="14"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="17"/>
+      <c r="M23" s="17"/>
+      <c r="N23" s="17"/>
+      <c r="O23" s="17"/>
+      <c r="P23" s="17"/>
+      <c r="Q23" s="17"/>
+      <c r="R23" s="17"/>
+      <c r="S23" s="17"/>
+      <c r="T23" s="17"/>
+      <c r="U23" s="17"/>
+      <c r="V23" s="17"/>
+      <c r="W23" s="17"/>
+      <c r="X23" s="17"/>
+      <c r="Y23" s="17"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="12" t="s">
+      <c r="A24" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="B24" s="13">
+      <c r="B24" s="16">
         <v>0.0</v>
       </c>
-      <c r="C24" s="14" t="s">
+      <c r="C24" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="D24" s="14" t="s">
+      <c r="D24" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="E24" s="14" t="s">
+      <c r="E24" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="14"/>
-      <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
-      <c r="Q24" s="14"/>
-      <c r="R24" s="14"/>
-      <c r="S24" s="14"/>
-      <c r="T24" s="14"/>
-      <c r="U24" s="14"/>
-      <c r="V24" s="14"/>
-      <c r="W24" s="14"/>
-      <c r="X24" s="14"/>
-      <c r="Y24" s="14"/>
-    </row>
-    <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="12" t="s">
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="17"/>
+      <c r="L24" s="17"/>
+      <c r="M24" s="17"/>
+      <c r="N24" s="17"/>
+      <c r="O24" s="17"/>
+      <c r="P24" s="17"/>
+      <c r="Q24" s="17"/>
+      <c r="R24" s="17"/>
+      <c r="S24" s="17"/>
+      <c r="T24" s="17"/>
+      <c r="U24" s="17"/>
+      <c r="V24" s="17"/>
+      <c r="W24" s="17"/>
+      <c r="X24" s="17"/>
+      <c r="Y24" s="17"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="B25" s="13">
+      <c r="B25" s="16">
         <v>0.0</v>
       </c>
-      <c r="C25" s="14" t="s">
+      <c r="C25" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="D25" s="14" t="s">
+      <c r="D25" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="E25" s="14" t="s">
+      <c r="E25" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="14"/>
-      <c r="J25" s="14"/>
-      <c r="K25" s="14"/>
-      <c r="L25" s="14"/>
-      <c r="M25" s="14"/>
-      <c r="N25" s="14"/>
-      <c r="O25" s="14"/>
-      <c r="P25" s="14"/>
-      <c r="Q25" s="14"/>
-      <c r="R25" s="14"/>
-      <c r="S25" s="14"/>
-      <c r="T25" s="14"/>
-      <c r="U25" s="14"/>
-      <c r="V25" s="14"/>
-      <c r="W25" s="14"/>
-      <c r="X25" s="14"/>
-      <c r="Y25" s="14"/>
-    </row>
-    <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="12" t="s">
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="17"/>
+      <c r="L25" s="17"/>
+      <c r="M25" s="17"/>
+      <c r="N25" s="17"/>
+      <c r="O25" s="17"/>
+      <c r="P25" s="17"/>
+      <c r="Q25" s="17"/>
+      <c r="R25" s="17"/>
+      <c r="S25" s="17"/>
+      <c r="T25" s="17"/>
+      <c r="U25" s="17"/>
+      <c r="V25" s="17"/>
+      <c r="W25" s="17"/>
+      <c r="X25" s="17"/>
+      <c r="Y25" s="17"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="B26" s="13">
+      <c r="B26" s="16">
         <v>0.0</v>
       </c>
-      <c r="C26" s="14" t="s">
+      <c r="C26" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="D26" s="14" t="s">
+      <c r="D26" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="E26" s="14" t="s">
+      <c r="E26" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="14"/>
-      <c r="J26" s="14"/>
-      <c r="K26" s="14"/>
-      <c r="L26" s="14"/>
-      <c r="M26" s="14"/>
-      <c r="N26" s="14"/>
-      <c r="O26" s="14"/>
-      <c r="P26" s="14"/>
-      <c r="Q26" s="14"/>
-      <c r="R26" s="14"/>
-      <c r="S26" s="14"/>
-      <c r="T26" s="14"/>
-      <c r="U26" s="14"/>
-      <c r="V26" s="14"/>
-      <c r="W26" s="14"/>
-      <c r="X26" s="14"/>
-      <c r="Y26" s="14"/>
-    </row>
-    <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="12" t="s">
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="17"/>
+      <c r="L26" s="17"/>
+      <c r="M26" s="17"/>
+      <c r="N26" s="17"/>
+      <c r="O26" s="17"/>
+      <c r="P26" s="17"/>
+      <c r="Q26" s="17"/>
+      <c r="R26" s="17"/>
+      <c r="S26" s="17"/>
+      <c r="T26" s="17"/>
+      <c r="U26" s="17"/>
+      <c r="V26" s="17"/>
+      <c r="W26" s="17"/>
+      <c r="X26" s="17"/>
+      <c r="Y26" s="17"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="B27" s="13">
+      <c r="B27" s="16">
         <v>0.0</v>
       </c>
-      <c r="C27" s="14" t="s">
+      <c r="C27" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="D27" s="14" t="s">
+      <c r="D27" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="E27" s="14" t="s">
+      <c r="E27" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="14"/>
-      <c r="J27" s="14"/>
-      <c r="K27" s="14"/>
-      <c r="L27" s="14"/>
-      <c r="M27" s="14"/>
-      <c r="N27" s="14"/>
-      <c r="O27" s="14"/>
-      <c r="P27" s="14"/>
-      <c r="Q27" s="14"/>
-      <c r="R27" s="14"/>
-      <c r="S27" s="14"/>
-      <c r="T27" s="14"/>
-      <c r="U27" s="14"/>
-      <c r="V27" s="14"/>
-      <c r="W27" s="14"/>
-      <c r="X27" s="14"/>
-      <c r="Y27" s="14"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="17"/>
+      <c r="L27" s="17"/>
+      <c r="M27" s="17"/>
+      <c r="N27" s="17"/>
+      <c r="O27" s="17"/>
+      <c r="P27" s="17"/>
+      <c r="Q27" s="17"/>
+      <c r="R27" s="17"/>
+      <c r="S27" s="17"/>
+      <c r="T27" s="17"/>
+      <c r="U27" s="17"/>
+      <c r="V27" s="17"/>
+      <c r="W27" s="17"/>
+      <c r="X27" s="17"/>
+      <c r="Y27" s="17"/>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="12" t="s">
+      <c r="A28" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="B28" s="13">
+      <c r="B28" s="16">
         <v>0.0</v>
       </c>
-      <c r="C28" s="14" t="s">
+      <c r="C28" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="D28" s="14" t="s">
+      <c r="D28" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="E28" s="14" t="s">
+      <c r="E28" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="14"/>
-      <c r="J28" s="14"/>
-      <c r="K28" s="14"/>
-      <c r="L28" s="14"/>
-      <c r="M28" s="14"/>
-      <c r="N28" s="14"/>
-      <c r="O28" s="14"/>
-      <c r="P28" s="14"/>
-      <c r="Q28" s="14"/>
-      <c r="R28" s="14"/>
-      <c r="S28" s="14"/>
-      <c r="T28" s="14"/>
-      <c r="U28" s="14"/>
-      <c r="V28" s="14"/>
-      <c r="W28" s="14"/>
-      <c r="X28" s="14"/>
-      <c r="Y28" s="14"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="17"/>
+      <c r="M28" s="17"/>
+      <c r="N28" s="17"/>
+      <c r="O28" s="17"/>
+      <c r="P28" s="17"/>
+      <c r="Q28" s="17"/>
+      <c r="R28" s="17"/>
+      <c r="S28" s="17"/>
+      <c r="T28" s="17"/>
+      <c r="U28" s="17"/>
+      <c r="V28" s="17"/>
+      <c r="W28" s="17"/>
+      <c r="X28" s="17"/>
+      <c r="Y28" s="17"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="12" t="s">
+      <c r="A29" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="B29" s="13">
+      <c r="B29" s="16">
         <v>0.0</v>
       </c>
-      <c r="C29" s="14" t="s">
+      <c r="C29" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="D29" s="14" t="s">
+      <c r="D29" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="E29" s="14" t="s">
+      <c r="E29" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="14"/>
-      <c r="J29" s="14"/>
-      <c r="K29" s="14"/>
-      <c r="L29" s="14"/>
-      <c r="M29" s="14"/>
-      <c r="N29" s="14"/>
-      <c r="O29" s="14"/>
-      <c r="P29" s="14"/>
-      <c r="Q29" s="14"/>
-      <c r="R29" s="14"/>
-      <c r="S29" s="14"/>
-      <c r="T29" s="14"/>
-      <c r="U29" s="14"/>
-      <c r="V29" s="14"/>
-      <c r="W29" s="14"/>
-      <c r="X29" s="14"/>
-      <c r="Y29" s="14"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="17"/>
+      <c r="J29" s="17"/>
+      <c r="K29" s="17"/>
+      <c r="L29" s="17"/>
+      <c r="M29" s="17"/>
+      <c r="N29" s="17"/>
+      <c r="O29" s="17"/>
+      <c r="P29" s="17"/>
+      <c r="Q29" s="17"/>
+      <c r="R29" s="17"/>
+      <c r="S29" s="17"/>
+      <c r="T29" s="17"/>
+      <c r="U29" s="17"/>
+      <c r="V29" s="17"/>
+      <c r="W29" s="17"/>
+      <c r="X29" s="17"/>
+      <c r="Y29" s="17"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="12" t="s">
+      <c r="A30" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="B30" s="13">
+      <c r="B30" s="16">
         <v>0.0</v>
       </c>
-      <c r="C30" s="14" t="s">
+      <c r="C30" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="D30" s="14" t="s">
+      <c r="D30" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="E30" s="14" t="s">
+      <c r="E30" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="14"/>
-      <c r="J30" s="14"/>
-      <c r="K30" s="14"/>
-      <c r="L30" s="14"/>
-      <c r="M30" s="14"/>
-      <c r="N30" s="14"/>
-      <c r="O30" s="14"/>
-      <c r="P30" s="14"/>
-      <c r="Q30" s="14"/>
-      <c r="R30" s="14"/>
-      <c r="S30" s="14"/>
-      <c r="T30" s="14"/>
-      <c r="U30" s="14"/>
-      <c r="V30" s="14"/>
-      <c r="W30" s="14"/>
-      <c r="X30" s="14"/>
-      <c r="Y30" s="14"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="17"/>
+      <c r="I30" s="17"/>
+      <c r="J30" s="17"/>
+      <c r="K30" s="17"/>
+      <c r="L30" s="17"/>
+      <c r="M30" s="17"/>
+      <c r="N30" s="17"/>
+      <c r="O30" s="17"/>
+      <c r="P30" s="17"/>
+      <c r="Q30" s="17"/>
+      <c r="R30" s="17"/>
+      <c r="S30" s="17"/>
+      <c r="T30" s="17"/>
+      <c r="U30" s="17"/>
+      <c r="V30" s="17"/>
+      <c r="W30" s="17"/>
+      <c r="X30" s="17"/>
+      <c r="Y30" s="17"/>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="12" t="s">
+      <c r="A31" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="B31" s="13">
+      <c r="B31" s="16">
         <v>0.0</v>
       </c>
-      <c r="C31" s="14" t="s">
+      <c r="C31" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="D31" s="14" t="s">
+      <c r="D31" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="E31" s="14" t="s">
+      <c r="E31" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="14"/>
-      <c r="J31" s="14"/>
-      <c r="K31" s="14"/>
-      <c r="L31" s="14"/>
-      <c r="M31" s="14"/>
-      <c r="N31" s="14"/>
-      <c r="O31" s="14"/>
-      <c r="P31" s="14"/>
-      <c r="Q31" s="14"/>
-      <c r="R31" s="14"/>
-      <c r="S31" s="14"/>
-      <c r="T31" s="14"/>
-      <c r="U31" s="14"/>
-      <c r="V31" s="14"/>
-      <c r="W31" s="14"/>
-      <c r="X31" s="14"/>
-      <c r="Y31" s="14"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17"/>
+      <c r="J31" s="17"/>
+      <c r="K31" s="17"/>
+      <c r="L31" s="17"/>
+      <c r="M31" s="17"/>
+      <c r="N31" s="17"/>
+      <c r="O31" s="17"/>
+      <c r="P31" s="17"/>
+      <c r="Q31" s="17"/>
+      <c r="R31" s="17"/>
+      <c r="S31" s="17"/>
+      <c r="T31" s="17"/>
+      <c r="U31" s="17"/>
+      <c r="V31" s="17"/>
+      <c r="W31" s="17"/>
+      <c r="X31" s="17"/>
+      <c r="Y31" s="17"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="12" t="s">
+      <c r="A32" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="B32" s="13">
+      <c r="B32" s="16">
         <v>0.0</v>
       </c>
-      <c r="C32" s="14" t="s">
+      <c r="C32" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="D32" s="14" t="s">
+      <c r="D32" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="E32" s="14" t="s">
+      <c r="E32" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="14"/>
-      <c r="J32" s="14"/>
-      <c r="K32" s="14"/>
-      <c r="L32" s="14"/>
-      <c r="M32" s="14"/>
-      <c r="N32" s="14"/>
-      <c r="O32" s="14"/>
-      <c r="P32" s="14"/>
-      <c r="Q32" s="14"/>
-      <c r="R32" s="14"/>
-      <c r="S32" s="14"/>
-      <c r="T32" s="14"/>
-      <c r="U32" s="14"/>
-      <c r="V32" s="14"/>
-      <c r="W32" s="14"/>
-      <c r="X32" s="14"/>
-      <c r="Y32" s="14"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="17"/>
+      <c r="J32" s="17"/>
+      <c r="K32" s="17"/>
+      <c r="L32" s="17"/>
+      <c r="M32" s="17"/>
+      <c r="N32" s="17"/>
+      <c r="O32" s="17"/>
+      <c r="P32" s="17"/>
+      <c r="Q32" s="17"/>
+      <c r="R32" s="17"/>
+      <c r="S32" s="17"/>
+      <c r="T32" s="17"/>
+      <c r="U32" s="17"/>
+      <c r="V32" s="17"/>
+      <c r="W32" s="17"/>
+      <c r="X32" s="17"/>
+      <c r="Y32" s="17"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="12" t="s">
+      <c r="A33" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="B33" s="13">
+      <c r="B33" s="16">
         <v>0.0</v>
       </c>
-      <c r="C33" s="14" t="s">
+      <c r="C33" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="D33" s="14" t="s">
+      <c r="D33" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="14" t="s">
+      <c r="E33" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="14"/>
-      <c r="J33" s="14"/>
-      <c r="K33" s="14"/>
-      <c r="L33" s="14"/>
-      <c r="M33" s="14"/>
-      <c r="N33" s="14"/>
-      <c r="O33" s="14"/>
-      <c r="P33" s="14"/>
-      <c r="Q33" s="14"/>
-      <c r="R33" s="14"/>
-      <c r="S33" s="14"/>
-      <c r="T33" s="14"/>
-      <c r="U33" s="14"/>
-      <c r="V33" s="14"/>
-      <c r="W33" s="14"/>
-      <c r="X33" s="14"/>
-      <c r="Y33" s="14"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="17"/>
+      <c r="I33" s="17"/>
+      <c r="J33" s="17"/>
+      <c r="K33" s="17"/>
+      <c r="L33" s="17"/>
+      <c r="M33" s="17"/>
+      <c r="N33" s="17"/>
+      <c r="O33" s="17"/>
+      <c r="P33" s="17"/>
+      <c r="Q33" s="17"/>
+      <c r="R33" s="17"/>
+      <c r="S33" s="17"/>
+      <c r="T33" s="17"/>
+      <c r="U33" s="17"/>
+      <c r="V33" s="17"/>
+      <c r="W33" s="17"/>
+      <c r="X33" s="17"/>
+      <c r="Y33" s="17"/>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="12" t="s">
+      <c r="A34" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="B34" s="13">
+      <c r="B34" s="16">
         <v>0.0</v>
       </c>
-      <c r="C34" s="14" t="s">
+      <c r="C34" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="D34" s="14" t="s">
+      <c r="D34" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="E34" s="14" t="s">
+      <c r="E34" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="14"/>
-      <c r="J34" s="14"/>
-      <c r="K34" s="14"/>
-      <c r="L34" s="14"/>
-      <c r="M34" s="14"/>
-      <c r="N34" s="14"/>
-      <c r="O34" s="14"/>
-      <c r="P34" s="14"/>
-      <c r="Q34" s="14"/>
-      <c r="R34" s="14"/>
-      <c r="S34" s="14"/>
-      <c r="T34" s="14"/>
-      <c r="U34" s="14"/>
-      <c r="V34" s="14"/>
-      <c r="W34" s="14"/>
-      <c r="X34" s="14"/>
-      <c r="Y34" s="14"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="17"/>
+      <c r="I34" s="17"/>
+      <c r="J34" s="17"/>
+      <c r="K34" s="17"/>
+      <c r="L34" s="17"/>
+      <c r="M34" s="17"/>
+      <c r="N34" s="17"/>
+      <c r="O34" s="17"/>
+      <c r="P34" s="17"/>
+      <c r="Q34" s="17"/>
+      <c r="R34" s="17"/>
+      <c r="S34" s="17"/>
+      <c r="T34" s="17"/>
+      <c r="U34" s="17"/>
+      <c r="V34" s="17"/>
+      <c r="W34" s="17"/>
+      <c r="X34" s="17"/>
+      <c r="Y34" s="17"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="12" t="s">
+      <c r="A35" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="B35" s="13">
+      <c r="B35" s="16">
         <v>0.0</v>
       </c>
-      <c r="C35" s="14" t="s">
+      <c r="C35" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D35" s="14" t="s">
+      <c r="D35" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="E35" s="14" t="s">
+      <c r="E35" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="14"/>
-      <c r="J35" s="14"/>
-      <c r="K35" s="14"/>
-      <c r="L35" s="14"/>
-      <c r="M35" s="14"/>
-      <c r="N35" s="14"/>
-      <c r="O35" s="14"/>
-      <c r="P35" s="14"/>
-      <c r="Q35" s="14"/>
-      <c r="R35" s="14"/>
-      <c r="S35" s="14"/>
-      <c r="T35" s="14"/>
-      <c r="U35" s="14"/>
-      <c r="V35" s="14"/>
-      <c r="W35" s="14"/>
-      <c r="X35" s="14"/>
-      <c r="Y35" s="14"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="17"/>
+      <c r="I35" s="17"/>
+      <c r="J35" s="17"/>
+      <c r="K35" s="17"/>
+      <c r="L35" s="17"/>
+      <c r="M35" s="17"/>
+      <c r="N35" s="17"/>
+      <c r="O35" s="17"/>
+      <c r="P35" s="17"/>
+      <c r="Q35" s="17"/>
+      <c r="R35" s="17"/>
+      <c r="S35" s="17"/>
+      <c r="T35" s="17"/>
+      <c r="U35" s="17"/>
+      <c r="V35" s="17"/>
+      <c r="W35" s="17"/>
+      <c r="X35" s="17"/>
+      <c r="Y35" s="17"/>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="12" t="s">
+      <c r="A36" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="B36" s="13">
+      <c r="B36" s="16">
         <v>0.0</v>
       </c>
-      <c r="C36" s="14" t="s">
+      <c r="C36" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="D36" s="14" t="s">
+      <c r="D36" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="E36" s="14" t="s">
+      <c r="E36" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="14"/>
-      <c r="J36" s="14"/>
-      <c r="K36" s="14"/>
-      <c r="L36" s="14"/>
-      <c r="M36" s="14"/>
-      <c r="N36" s="14"/>
-      <c r="O36" s="14"/>
-      <c r="P36" s="14"/>
-      <c r="Q36" s="14"/>
-      <c r="R36" s="14"/>
-      <c r="S36" s="14"/>
-      <c r="T36" s="14"/>
-      <c r="U36" s="14"/>
-      <c r="V36" s="14"/>
-      <c r="W36" s="14"/>
-      <c r="X36" s="14"/>
-      <c r="Y36" s="14"/>
+      <c r="F36" s="17"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="17"/>
+      <c r="I36" s="17"/>
+      <c r="J36" s="17"/>
+      <c r="K36" s="17"/>
+      <c r="L36" s="17"/>
+      <c r="M36" s="17"/>
+      <c r="N36" s="17"/>
+      <c r="O36" s="17"/>
+      <c r="P36" s="17"/>
+      <c r="Q36" s="17"/>
+      <c r="R36" s="17"/>
+      <c r="S36" s="17"/>
+      <c r="T36" s="17"/>
+      <c r="U36" s="17"/>
+      <c r="V36" s="17"/>
+      <c r="W36" s="17"/>
+      <c r="X36" s="17"/>
+      <c r="Y36" s="17"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="12" t="s">
+      <c r="A37" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="B37" s="13">
+      <c r="B37" s="16">
         <v>0.0</v>
       </c>
-      <c r="C37" s="14" t="s">
+      <c r="C37" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="D37" s="14" t="s">
+      <c r="D37" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="E37" s="14" t="s">
+      <c r="E37" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="14"/>
-      <c r="J37" s="14"/>
-      <c r="K37" s="14"/>
-      <c r="L37" s="14"/>
-      <c r="M37" s="14"/>
-      <c r="N37" s="14"/>
-      <c r="O37" s="14"/>
-      <c r="P37" s="14"/>
-      <c r="Q37" s="14"/>
-      <c r="R37" s="14"/>
-      <c r="S37" s="14"/>
-      <c r="T37" s="14"/>
-      <c r="U37" s="14"/>
-      <c r="V37" s="14"/>
-      <c r="W37" s="14"/>
-      <c r="X37" s="14"/>
-      <c r="Y37" s="14"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="17"/>
+      <c r="I37" s="17"/>
+      <c r="J37" s="17"/>
+      <c r="K37" s="17"/>
+      <c r="L37" s="17"/>
+      <c r="M37" s="17"/>
+      <c r="N37" s="17"/>
+      <c r="O37" s="17"/>
+      <c r="P37" s="17"/>
+      <c r="Q37" s="17"/>
+      <c r="R37" s="17"/>
+      <c r="S37" s="17"/>
+      <c r="T37" s="17"/>
+      <c r="U37" s="17"/>
+      <c r="V37" s="17"/>
+      <c r="W37" s="17"/>
+      <c r="X37" s="17"/>
+      <c r="Y37" s="17"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="12" t="s">
+      <c r="A38" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="B38" s="13">
+      <c r="B38" s="16">
         <v>0.0</v>
       </c>
-      <c r="C38" s="14" t="s">
+      <c r="C38" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="D38" s="14" t="s">
+      <c r="D38" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="E38" s="14" t="s">
+      <c r="E38" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="14"/>
-      <c r="J38" s="14"/>
-      <c r="K38" s="14"/>
-      <c r="L38" s="14"/>
-      <c r="M38" s="14"/>
-      <c r="N38" s="14"/>
-      <c r="O38" s="14"/>
-      <c r="P38" s="14"/>
-      <c r="Q38" s="14"/>
-      <c r="R38" s="14"/>
-      <c r="S38" s="14"/>
-      <c r="T38" s="14"/>
-      <c r="U38" s="14"/>
-      <c r="V38" s="14"/>
-      <c r="W38" s="14"/>
-      <c r="X38" s="14"/>
-      <c r="Y38" s="14"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="17"/>
+      <c r="I38" s="17"/>
+      <c r="J38" s="17"/>
+      <c r="K38" s="17"/>
+      <c r="L38" s="17"/>
+      <c r="M38" s="17"/>
+      <c r="N38" s="17"/>
+      <c r="O38" s="17"/>
+      <c r="P38" s="17"/>
+      <c r="Q38" s="17"/>
+      <c r="R38" s="17"/>
+      <c r="S38" s="17"/>
+      <c r="T38" s="17"/>
+      <c r="U38" s="17"/>
+      <c r="V38" s="17"/>
+      <c r="W38" s="17"/>
+      <c r="X38" s="17"/>
+      <c r="Y38" s="17"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="12" t="s">
+      <c r="A39" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="B39" s="13">
+      <c r="B39" s="16">
         <v>0.0</v>
       </c>
-      <c r="C39" s="14" t="s">
+      <c r="C39" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="D39" s="14" t="s">
+      <c r="D39" s="17" t="s">
         <v>155</v>
       </c>
-      <c r="E39" s="14" t="s">
+      <c r="E39" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="14"/>
-      <c r="J39" s="14"/>
-      <c r="K39" s="14"/>
-      <c r="L39" s="14"/>
-      <c r="M39" s="14"/>
-      <c r="N39" s="14"/>
-      <c r="O39" s="14"/>
-      <c r="P39" s="14"/>
-      <c r="Q39" s="14"/>
-      <c r="R39" s="14"/>
-      <c r="S39" s="14"/>
-      <c r="T39" s="14"/>
-      <c r="U39" s="14"/>
-      <c r="V39" s="14"/>
-      <c r="W39" s="14"/>
-      <c r="X39" s="14"/>
-      <c r="Y39" s="14"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="17"/>
+      <c r="I39" s="17"/>
+      <c r="J39" s="17"/>
+      <c r="K39" s="17"/>
+      <c r="L39" s="17"/>
+      <c r="M39" s="17"/>
+      <c r="N39" s="17"/>
+      <c r="O39" s="17"/>
+      <c r="P39" s="17"/>
+      <c r="Q39" s="17"/>
+      <c r="R39" s="17"/>
+      <c r="S39" s="17"/>
+      <c r="T39" s="17"/>
+      <c r="U39" s="17"/>
+      <c r="V39" s="17"/>
+      <c r="W39" s="17"/>
+      <c r="X39" s="17"/>
+      <c r="Y39" s="17"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="12" t="s">
+      <c r="A40" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="B40" s="13">
+      <c r="B40" s="16">
         <v>0.0</v>
       </c>
-      <c r="C40" s="14" t="s">
+      <c r="C40" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="D40" s="14" t="s">
+      <c r="D40" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="E40" s="14" t="s">
+      <c r="E40" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="14"/>
-      <c r="J40" s="14"/>
-      <c r="K40" s="14"/>
-      <c r="L40" s="14"/>
-      <c r="M40" s="14"/>
-      <c r="N40" s="14"/>
-      <c r="O40" s="14"/>
-      <c r="P40" s="14"/>
-      <c r="Q40" s="14"/>
-      <c r="R40" s="14"/>
-      <c r="S40" s="14"/>
-      <c r="T40" s="14"/>
-      <c r="U40" s="14"/>
-      <c r="V40" s="14"/>
-      <c r="W40" s="14"/>
-      <c r="X40" s="14"/>
-      <c r="Y40" s="14"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="17"/>
+      <c r="I40" s="17"/>
+      <c r="J40" s="17"/>
+      <c r="K40" s="17"/>
+      <c r="L40" s="17"/>
+      <c r="M40" s="17"/>
+      <c r="N40" s="17"/>
+      <c r="O40" s="17"/>
+      <c r="P40" s="17"/>
+      <c r="Q40" s="17"/>
+      <c r="R40" s="17"/>
+      <c r="S40" s="17"/>
+      <c r="T40" s="17"/>
+      <c r="U40" s="17"/>
+      <c r="V40" s="17"/>
+      <c r="W40" s="17"/>
+      <c r="X40" s="17"/>
+      <c r="Y40" s="17"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="12" t="s">
+      <c r="A41" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="B41" s="13">
+      <c r="B41" s="16">
         <v>0.0</v>
       </c>
-      <c r="C41" s="14" t="s">
+      <c r="C41" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="D41" s="14" t="s">
+      <c r="D41" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="E41" s="14" t="s">
+      <c r="E41" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="14"/>
-      <c r="J41" s="14"/>
-      <c r="K41" s="14"/>
-      <c r="L41" s="14"/>
-      <c r="M41" s="14"/>
-      <c r="N41" s="14"/>
-      <c r="O41" s="14"/>
-      <c r="P41" s="14"/>
-      <c r="Q41" s="14"/>
-      <c r="R41" s="14"/>
-      <c r="S41" s="14"/>
-      <c r="T41" s="14"/>
-      <c r="U41" s="14"/>
-      <c r="V41" s="14"/>
-      <c r="W41" s="14"/>
-      <c r="X41" s="14"/>
-      <c r="Y41" s="14"/>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="12" t="s">
+      <c r="F41" s="17"/>
+      <c r="G41" s="17"/>
+      <c r="H41" s="17"/>
+      <c r="I41" s="17"/>
+      <c r="J41" s="17"/>
+      <c r="K41" s="17"/>
+      <c r="L41" s="17"/>
+      <c r="M41" s="17"/>
+      <c r="N41" s="17"/>
+      <c r="O41" s="17"/>
+      <c r="P41" s="17"/>
+      <c r="Q41" s="17"/>
+      <c r="R41" s="17"/>
+      <c r="S41" s="17"/>
+      <c r="T41" s="17"/>
+      <c r="U41" s="17"/>
+      <c r="V41" s="17"/>
+      <c r="W41" s="17"/>
+      <c r="X41" s="17"/>
+      <c r="Y41" s="17"/>
+    </row>
+    <row r="42" ht="15.0" customHeight="1">
+      <c r="A42" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="B42" s="13">
+      <c r="B42" s="16">
         <v>0.0</v>
       </c>
-      <c r="C42" s="14" t="s">
+      <c r="C42" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="D42" s="14" t="s">
+      <c r="D42" s="17" t="s">
         <v>167</v>
       </c>
-      <c r="E42" s="14" t="s">
+      <c r="E42" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="14"/>
-      <c r="J42" s="14"/>
-      <c r="K42" s="14"/>
-      <c r="L42" s="14"/>
-      <c r="M42" s="14"/>
-      <c r="N42" s="14"/>
-      <c r="O42" s="14"/>
-      <c r="P42" s="14"/>
-      <c r="Q42" s="14"/>
-      <c r="R42" s="14"/>
-      <c r="S42" s="14"/>
-      <c r="T42" s="14"/>
-      <c r="U42" s="14"/>
-      <c r="V42" s="14"/>
-      <c r="W42" s="14"/>
-      <c r="X42" s="14"/>
-      <c r="Y42" s="14"/>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="12" t="s">
+      <c r="F42" s="17"/>
+      <c r="G42" s="17"/>
+      <c r="H42" s="17"/>
+      <c r="I42" s="17"/>
+      <c r="J42" s="17"/>
+      <c r="K42" s="17"/>
+      <c r="L42" s="17"/>
+      <c r="M42" s="17"/>
+      <c r="N42" s="17"/>
+      <c r="O42" s="17"/>
+      <c r="P42" s="17"/>
+      <c r="Q42" s="17"/>
+      <c r="R42" s="17"/>
+      <c r="S42" s="17"/>
+      <c r="T42" s="17"/>
+      <c r="U42" s="17"/>
+      <c r="V42" s="17"/>
+      <c r="W42" s="17"/>
+      <c r="X42" s="17"/>
+      <c r="Y42" s="17"/>
+    </row>
+    <row r="43" ht="15.0" customHeight="1">
+      <c r="A43" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="B43" s="13">
+      <c r="B43" s="16">
         <v>0.0</v>
       </c>
-      <c r="C43" s="14" t="s">
+      <c r="C43" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="D43" s="14" t="s">
+      <c r="D43" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="E43" s="14" t="s">
+      <c r="E43" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="14"/>
-      <c r="J43" s="14"/>
-      <c r="K43" s="14"/>
-      <c r="L43" s="14"/>
-      <c r="M43" s="14"/>
-      <c r="N43" s="14"/>
-      <c r="O43" s="14"/>
-      <c r="P43" s="14"/>
-      <c r="Q43" s="14"/>
-      <c r="R43" s="14"/>
-      <c r="S43" s="14"/>
-      <c r="T43" s="14"/>
-      <c r="U43" s="14"/>
-      <c r="V43" s="14"/>
-      <c r="W43" s="14"/>
-      <c r="X43" s="14"/>
-      <c r="Y43" s="14"/>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="12" t="s">
+      <c r="F43" s="17"/>
+      <c r="G43" s="17"/>
+      <c r="H43" s="17"/>
+      <c r="I43" s="17"/>
+      <c r="J43" s="17"/>
+      <c r="K43" s="17"/>
+      <c r="L43" s="17"/>
+      <c r="M43" s="17"/>
+      <c r="N43" s="17"/>
+      <c r="O43" s="17"/>
+      <c r="P43" s="17"/>
+      <c r="Q43" s="17"/>
+      <c r="R43" s="17"/>
+      <c r="S43" s="17"/>
+      <c r="T43" s="17"/>
+      <c r="U43" s="17"/>
+      <c r="V43" s="17"/>
+      <c r="W43" s="17"/>
+      <c r="X43" s="17"/>
+      <c r="Y43" s="17"/>
+    </row>
+    <row r="44" ht="15.0" customHeight="1">
+      <c r="A44" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="B44" s="13">
+      <c r="B44" s="16">
         <v>0.0</v>
       </c>
-      <c r="C44" s="14" t="s">
+      <c r="C44" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="D44" s="14" t="s">
+      <c r="D44" s="17" t="s">
         <v>175</v>
       </c>
-      <c r="E44" s="14" t="s">
+      <c r="E44" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="14"/>
-      <c r="J44" s="14"/>
-      <c r="K44" s="14"/>
-      <c r="L44" s="14"/>
-      <c r="M44" s="14"/>
-      <c r="N44" s="14"/>
-      <c r="O44" s="14"/>
-      <c r="P44" s="14"/>
-      <c r="Q44" s="14"/>
-      <c r="R44" s="14"/>
-      <c r="S44" s="14"/>
-      <c r="T44" s="14"/>
-      <c r="U44" s="14"/>
-      <c r="V44" s="14"/>
-      <c r="W44" s="14"/>
-      <c r="X44" s="14"/>
-      <c r="Y44" s="14"/>
+      <c r="F44" s="17"/>
+      <c r="G44" s="17"/>
+      <c r="H44" s="17"/>
+      <c r="I44" s="17"/>
+      <c r="J44" s="17"/>
+      <c r="K44" s="17"/>
+      <c r="L44" s="17"/>
+      <c r="M44" s="17"/>
+      <c r="N44" s="17"/>
+      <c r="O44" s="17"/>
+      <c r="P44" s="17"/>
+      <c r="Q44" s="17"/>
+      <c r="R44" s="17"/>
+      <c r="S44" s="17"/>
+      <c r="T44" s="17"/>
+      <c r="U44" s="17"/>
+      <c r="V44" s="17"/>
+      <c r="W44" s="17"/>
+      <c r="X44" s="17"/>
+      <c r="Y44" s="17"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="12" t="s">
+      <c r="A45" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="B45" s="13">
+      <c r="B45" s="16">
         <v>0.0</v>
       </c>
-      <c r="C45" s="14" t="s">
+      <c r="C45" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="D45" s="14" t="s">
+      <c r="D45" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="E45" s="14" t="s">
+      <c r="E45" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="14"/>
-      <c r="J45" s="14"/>
-      <c r="K45" s="14"/>
-      <c r="L45" s="14"/>
-      <c r="M45" s="14"/>
-      <c r="N45" s="14"/>
-      <c r="O45" s="14"/>
-      <c r="P45" s="14"/>
-      <c r="Q45" s="14"/>
-      <c r="R45" s="14"/>
-      <c r="S45" s="14"/>
-      <c r="T45" s="14"/>
-      <c r="U45" s="14"/>
-      <c r="V45" s="14"/>
-      <c r="W45" s="14"/>
-      <c r="X45" s="14"/>
-      <c r="Y45" s="14"/>
+      <c r="F45" s="17"/>
+      <c r="G45" s="17"/>
+      <c r="H45" s="17"/>
+      <c r="I45" s="17"/>
+      <c r="J45" s="17"/>
+      <c r="K45" s="17"/>
+      <c r="L45" s="17"/>
+      <c r="M45" s="17"/>
+      <c r="N45" s="17"/>
+      <c r="O45" s="17"/>
+      <c r="P45" s="17"/>
+      <c r="Q45" s="17"/>
+      <c r="R45" s="17"/>
+      <c r="S45" s="17"/>
+      <c r="T45" s="17"/>
+      <c r="U45" s="17"/>
+      <c r="V45" s="17"/>
+      <c r="W45" s="17"/>
+      <c r="X45" s="17"/>
+      <c r="Y45" s="17"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="12" t="s">
+      <c r="A46" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="B46" s="13">
+      <c r="B46" s="16">
         <v>0.0</v>
       </c>
-      <c r="C46" s="14" t="s">
+      <c r="C46" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="D46" s="14" t="s">
+      <c r="D46" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="E46" s="14" t="s">
+      <c r="E46" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="14"/>
-      <c r="J46" s="14"/>
-      <c r="K46" s="14"/>
-      <c r="L46" s="14"/>
-      <c r="M46" s="14"/>
-      <c r="N46" s="14"/>
-      <c r="O46" s="14"/>
-      <c r="P46" s="14"/>
-      <c r="Q46" s="14"/>
-      <c r="R46" s="14"/>
-      <c r="S46" s="14"/>
-      <c r="T46" s="14"/>
-      <c r="U46" s="14"/>
-      <c r="V46" s="14"/>
-      <c r="W46" s="14"/>
-      <c r="X46" s="14"/>
-      <c r="Y46" s="14"/>
+      <c r="F46" s="17"/>
+      <c r="G46" s="17"/>
+      <c r="H46" s="17"/>
+      <c r="I46" s="17"/>
+      <c r="J46" s="17"/>
+      <c r="K46" s="17"/>
+      <c r="L46" s="17"/>
+      <c r="M46" s="17"/>
+      <c r="N46" s="17"/>
+      <c r="O46" s="17"/>
+      <c r="P46" s="17"/>
+      <c r="Q46" s="17"/>
+      <c r="R46" s="17"/>
+      <c r="S46" s="17"/>
+      <c r="T46" s="17"/>
+      <c r="U46" s="17"/>
+      <c r="V46" s="17"/>
+      <c r="W46" s="17"/>
+      <c r="X46" s="17"/>
+      <c r="Y46" s="17"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="12" t="s">
+      <c r="A47" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="B47" s="13">
+      <c r="B47" s="16">
         <v>0.0</v>
       </c>
-      <c r="C47" s="14" t="s">
+      <c r="C47" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="D47" s="14" t="s">
+      <c r="D47" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="E47" s="14" t="s">
+      <c r="E47" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="14"/>
-      <c r="J47" s="14"/>
-      <c r="K47" s="14"/>
-      <c r="L47" s="14"/>
-      <c r="M47" s="14"/>
-      <c r="N47" s="14"/>
-      <c r="O47" s="14"/>
-      <c r="P47" s="14"/>
-      <c r="Q47" s="14"/>
-      <c r="R47" s="14"/>
-      <c r="S47" s="14"/>
-      <c r="T47" s="14"/>
-      <c r="U47" s="14"/>
-      <c r="V47" s="14"/>
-      <c r="W47" s="14"/>
-      <c r="X47" s="14"/>
-      <c r="Y47" s="14"/>
+      <c r="F47" s="17"/>
+      <c r="G47" s="17"/>
+      <c r="H47" s="17"/>
+      <c r="I47" s="17"/>
+      <c r="J47" s="17"/>
+      <c r="K47" s="17"/>
+      <c r="L47" s="17"/>
+      <c r="M47" s="17"/>
+      <c r="N47" s="17"/>
+      <c r="O47" s="17"/>
+      <c r="P47" s="17"/>
+      <c r="Q47" s="17"/>
+      <c r="R47" s="17"/>
+      <c r="S47" s="17"/>
+      <c r="T47" s="17"/>
+      <c r="U47" s="17"/>
+      <c r="V47" s="17"/>
+      <c r="W47" s="17"/>
+      <c r="X47" s="17"/>
+      <c r="Y47" s="17"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="12" t="s">
+      <c r="A48" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="B48" s="13">
+      <c r="B48" s="16">
         <v>0.0</v>
       </c>
-      <c r="C48" s="14" t="s">
+      <c r="C48" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="D48" s="14" t="s">
+      <c r="D48" s="17" t="s">
         <v>191</v>
       </c>
-      <c r="E48" s="14" t="s">
+      <c r="E48" s="17" t="s">
         <v>192</v>
       </c>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="14"/>
-      <c r="J48" s="14"/>
-      <c r="K48" s="14"/>
-      <c r="L48" s="14"/>
-      <c r="M48" s="14"/>
-      <c r="N48" s="14"/>
-      <c r="O48" s="14"/>
-      <c r="P48" s="14"/>
-      <c r="Q48" s="14"/>
-      <c r="R48" s="14"/>
-      <c r="S48" s="14"/>
-      <c r="T48" s="14"/>
-      <c r="U48" s="14"/>
-      <c r="V48" s="14"/>
-      <c r="W48" s="14"/>
-      <c r="X48" s="14"/>
-      <c r="Y48" s="14"/>
-    </row>
-    <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="12" t="s">
+      <c r="F48" s="17"/>
+      <c r="G48" s="17"/>
+      <c r="H48" s="17"/>
+      <c r="I48" s="17"/>
+      <c r="J48" s="17"/>
+      <c r="K48" s="17"/>
+      <c r="L48" s="17"/>
+      <c r="M48" s="17"/>
+      <c r="N48" s="17"/>
+      <c r="O48" s="17"/>
+      <c r="P48" s="17"/>
+      <c r="Q48" s="17"/>
+      <c r="R48" s="17"/>
+      <c r="S48" s="17"/>
+      <c r="T48" s="17"/>
+      <c r="U48" s="17"/>
+      <c r="V48" s="17"/>
+      <c r="W48" s="17"/>
+      <c r="X48" s="17"/>
+      <c r="Y48" s="17"/>
+    </row>
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="A49" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="B49" s="13">
+      <c r="B49" s="16">
         <v>0.0</v>
       </c>
-      <c r="C49" s="14" t="s">
+      <c r="C49" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="D49" s="14" t="s">
+      <c r="D49" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="E49" s="14" t="s">
+      <c r="E49" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="14"/>
-      <c r="J49" s="14"/>
-      <c r="K49" s="14"/>
-      <c r="L49" s="14"/>
-      <c r="M49" s="14"/>
-      <c r="N49" s="14"/>
-      <c r="O49" s="14"/>
-      <c r="P49" s="14"/>
-      <c r="Q49" s="14"/>
-      <c r="R49" s="14"/>
-      <c r="S49" s="14"/>
-      <c r="T49" s="14"/>
-      <c r="U49" s="14"/>
-      <c r="V49" s="14"/>
-      <c r="W49" s="14"/>
-      <c r="X49" s="14"/>
-      <c r="Y49" s="14"/>
-    </row>
-    <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="12" t="s">
+      <c r="F49" s="17"/>
+      <c r="G49" s="17"/>
+      <c r="H49" s="17"/>
+      <c r="I49" s="17"/>
+      <c r="J49" s="17"/>
+      <c r="K49" s="17"/>
+      <c r="L49" s="17"/>
+      <c r="M49" s="17"/>
+      <c r="N49" s="17"/>
+      <c r="O49" s="17"/>
+      <c r="P49" s="17"/>
+      <c r="Q49" s="17"/>
+      <c r="R49" s="17"/>
+      <c r="S49" s="17"/>
+      <c r="T49" s="17"/>
+      <c r="U49" s="17"/>
+      <c r="V49" s="17"/>
+      <c r="W49" s="17"/>
+      <c r="X49" s="17"/>
+      <c r="Y49" s="17"/>
+    </row>
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="A50" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="B50" s="13">
+      <c r="B50" s="16">
         <v>0.0</v>
       </c>
-      <c r="C50" s="14" t="s">
+      <c r="C50" s="17" t="s">
         <v>198</v>
       </c>
-      <c r="D50" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="E50" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="14"/>
-      <c r="J50" s="14"/>
-      <c r="K50" s="14"/>
-      <c r="L50" s="14"/>
-      <c r="M50" s="14"/>
-      <c r="N50" s="14"/>
-      <c r="O50" s="14"/>
-      <c r="P50" s="14"/>
-      <c r="Q50" s="14"/>
-      <c r="R50" s="14"/>
-      <c r="S50" s="14"/>
-      <c r="T50" s="14"/>
-      <c r="U50" s="14"/>
-      <c r="V50" s="14"/>
-      <c r="W50" s="14"/>
-      <c r="X50" s="14"/>
-      <c r="Y50" s="14"/>
-    </row>
-    <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="12" t="s">
+      <c r="D50" s="17" t="s">
         <v>199</v>
       </c>
-      <c r="B51" s="13">
+      <c r="E50" s="17" t="s">
+        <v>200</v>
+      </c>
+      <c r="F50" s="17"/>
+      <c r="G50" s="17"/>
+      <c r="H50" s="17"/>
+      <c r="I50" s="17"/>
+      <c r="J50" s="17"/>
+      <c r="K50" s="17"/>
+      <c r="L50" s="17"/>
+      <c r="M50" s="17"/>
+      <c r="N50" s="17"/>
+      <c r="O50" s="17"/>
+      <c r="P50" s="17"/>
+      <c r="Q50" s="17"/>
+      <c r="R50" s="17"/>
+      <c r="S50" s="17"/>
+      <c r="T50" s="17"/>
+      <c r="U50" s="17"/>
+      <c r="V50" s="17"/>
+      <c r="W50" s="17"/>
+      <c r="X50" s="17"/>
+      <c r="Y50" s="17"/>
+    </row>
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="A51" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="B51" s="16">
         <v>0.0</v>
       </c>
-      <c r="C51" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="D51" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="E51" s="14" t="s">
+      <c r="C51" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14"/>
-      <c r="K51" s="14"/>
-      <c r="L51" s="14"/>
-      <c r="M51" s="14"/>
-      <c r="N51" s="14"/>
-      <c r="O51" s="14"/>
-      <c r="P51" s="14"/>
-      <c r="Q51" s="14"/>
-      <c r="R51" s="14"/>
-      <c r="S51" s="14"/>
-      <c r="T51" s="14"/>
-      <c r="U51" s="14"/>
-      <c r="V51" s="14"/>
-      <c r="W51" s="14"/>
-      <c r="X51" s="14"/>
-      <c r="Y51" s="14"/>
+      <c r="D51" s="17" t="s">
+        <v>203</v>
+      </c>
+      <c r="E51" s="17" t="s">
+        <v>204</v>
+      </c>
+      <c r="F51" s="17"/>
+      <c r="G51" s="17"/>
+      <c r="H51" s="17"/>
+      <c r="I51" s="17"/>
+      <c r="J51" s="17"/>
+      <c r="K51" s="17"/>
+      <c r="L51" s="17"/>
+      <c r="M51" s="17"/>
+      <c r="N51" s="17"/>
+      <c r="O51" s="17"/>
+      <c r="P51" s="17"/>
+      <c r="Q51" s="17"/>
+      <c r="R51" s="17"/>
+      <c r="S51" s="17"/>
+      <c r="T51" s="17"/>
+      <c r="U51" s="17"/>
+      <c r="V51" s="17"/>
+      <c r="W51" s="17"/>
+      <c r="X51" s="17"/>
+      <c r="Y51" s="17"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="B52" s="13">
+      <c r="A52" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="B52" s="16">
         <v>0.0</v>
       </c>
-      <c r="C52" s="14" t="s">
-        <v>204</v>
-      </c>
-      <c r="D52" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="E52" s="14" t="s">
+      <c r="C52" s="17" t="s">
         <v>206</v>
       </c>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="14"/>
-      <c r="J52" s="14"/>
-      <c r="K52" s="14"/>
-      <c r="L52" s="14"/>
-      <c r="M52" s="14"/>
-      <c r="N52" s="14"/>
-      <c r="O52" s="14"/>
-      <c r="P52" s="14"/>
-      <c r="Q52" s="14"/>
-      <c r="R52" s="14"/>
-      <c r="S52" s="14"/>
-      <c r="T52" s="14"/>
-      <c r="U52" s="14"/>
-      <c r="V52" s="14"/>
-      <c r="W52" s="14"/>
-      <c r="X52" s="14"/>
-      <c r="Y52" s="14"/>
+      <c r="D52" s="17" t="s">
+        <v>207</v>
+      </c>
+      <c r="E52" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="F52" s="17"/>
+      <c r="G52" s="17"/>
+      <c r="H52" s="17"/>
+      <c r="I52" s="17"/>
+      <c r="J52" s="17"/>
+      <c r="K52" s="17"/>
+      <c r="L52" s="17"/>
+      <c r="M52" s="17"/>
+      <c r="N52" s="17"/>
+      <c r="O52" s="17"/>
+      <c r="P52" s="17"/>
+      <c r="Q52" s="17"/>
+      <c r="R52" s="17"/>
+      <c r="S52" s="17"/>
+      <c r="T52" s="17"/>
+      <c r="U52" s="17"/>
+      <c r="V52" s="17"/>
+      <c r="W52" s="17"/>
+      <c r="X52" s="17"/>
+      <c r="Y52" s="17"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="B53" s="13">
+      <c r="A53" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="B53" s="16">
         <v>0.0</v>
       </c>
-      <c r="C53" s="14" t="s">
-        <v>208</v>
-      </c>
-      <c r="D53" s="14" t="s">
-        <v>209</v>
-      </c>
-      <c r="E53" s="14" t="s">
+      <c r="C53" s="17" t="s">
         <v>210</v>
       </c>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="14"/>
-      <c r="J53" s="14"/>
-      <c r="K53" s="14"/>
-      <c r="L53" s="14"/>
-      <c r="M53" s="14"/>
-      <c r="N53" s="14"/>
-      <c r="O53" s="14"/>
-      <c r="P53" s="14"/>
-      <c r="Q53" s="14"/>
-      <c r="R53" s="14"/>
-      <c r="S53" s="14"/>
-      <c r="T53" s="14"/>
-      <c r="U53" s="14"/>
-      <c r="V53" s="14"/>
-      <c r="W53" s="14"/>
-      <c r="X53" s="14"/>
-      <c r="Y53" s="14"/>
+      <c r="D53" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="E53" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="F53" s="17"/>
+      <c r="G53" s="17"/>
+      <c r="H53" s="17"/>
+      <c r="I53" s="17"/>
+      <c r="J53" s="17"/>
+      <c r="K53" s="17"/>
+      <c r="L53" s="17"/>
+      <c r="M53" s="17"/>
+      <c r="N53" s="17"/>
+      <c r="O53" s="17"/>
+      <c r="P53" s="17"/>
+      <c r="Q53" s="17"/>
+      <c r="R53" s="17"/>
+      <c r="S53" s="17"/>
+      <c r="T53" s="17"/>
+      <c r="U53" s="17"/>
+      <c r="V53" s="17"/>
+      <c r="W53" s="17"/>
+      <c r="X53" s="17"/>
+      <c r="Y53" s="17"/>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="12" t="s">
+      <c r="A54" s="15" t="s">
         <v>211</v>
       </c>
-      <c r="B54" s="13">
+      <c r="B54" s="16">
         <v>0.0</v>
       </c>
-      <c r="C54" s="14" t="s">
+      <c r="C54" s="17" t="s">
         <v>212</v>
       </c>
-      <c r="D54" s="14" t="s">
+      <c r="D54" s="17" t="s">
         <v>213</v>
       </c>
-      <c r="E54" s="14" t="s">
+      <c r="E54" s="17" t="s">
         <v>214</v>
       </c>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="14"/>
-      <c r="J54" s="14"/>
-      <c r="K54" s="14"/>
-      <c r="L54" s="14"/>
-      <c r="M54" s="14"/>
-      <c r="N54" s="14"/>
-      <c r="O54" s="14"/>
-      <c r="P54" s="14"/>
-      <c r="Q54" s="14"/>
-      <c r="R54" s="14"/>
-      <c r="S54" s="14"/>
-      <c r="T54" s="14"/>
-      <c r="U54" s="14"/>
-      <c r="V54" s="14"/>
-      <c r="W54" s="14"/>
-      <c r="X54" s="14"/>
-      <c r="Y54" s="14"/>
+      <c r="F54" s="17"/>
+      <c r="G54" s="17"/>
+      <c r="H54" s="17"/>
+      <c r="I54" s="17"/>
+      <c r="J54" s="17"/>
+      <c r="K54" s="17"/>
+      <c r="L54" s="17"/>
+      <c r="M54" s="17"/>
+      <c r="N54" s="17"/>
+      <c r="O54" s="17"/>
+      <c r="P54" s="17"/>
+      <c r="Q54" s="17"/>
+      <c r="R54" s="17"/>
+      <c r="S54" s="17"/>
+      <c r="T54" s="17"/>
+      <c r="U54" s="17"/>
+      <c r="V54" s="17"/>
+      <c r="W54" s="17"/>
+      <c r="X54" s="17"/>
+      <c r="Y54" s="17"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="12" t="s">
+      <c r="A55" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="B55" s="13">
+      <c r="B55" s="16">
         <v>0.0</v>
       </c>
-      <c r="C55" s="14" t="s">
+      <c r="C55" s="17" t="s">
         <v>216</v>
       </c>
-      <c r="D55" s="14" t="s">
+      <c r="D55" s="17" t="s">
         <v>217</v>
       </c>
-      <c r="E55" s="14" t="s">
+      <c r="E55" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="14"/>
-      <c r="J55" s="14"/>
-      <c r="K55" s="14"/>
-      <c r="L55" s="14"/>
-      <c r="M55" s="14"/>
-      <c r="N55" s="14"/>
-      <c r="O55" s="14"/>
-      <c r="P55" s="14"/>
-      <c r="Q55" s="14"/>
-      <c r="R55" s="14"/>
-      <c r="S55" s="14"/>
-      <c r="T55" s="14"/>
-      <c r="U55" s="14"/>
-      <c r="V55" s="14"/>
-      <c r="W55" s="14"/>
-      <c r="X55" s="14"/>
-      <c r="Y55" s="14"/>
+      <c r="F55" s="17"/>
+      <c r="G55" s="17"/>
+      <c r="H55" s="17"/>
+      <c r="I55" s="17"/>
+      <c r="J55" s="17"/>
+      <c r="K55" s="17"/>
+      <c r="L55" s="17"/>
+      <c r="M55" s="17"/>
+      <c r="N55" s="17"/>
+      <c r="O55" s="17"/>
+      <c r="P55" s="17"/>
+      <c r="Q55" s="17"/>
+      <c r="R55" s="17"/>
+      <c r="S55" s="17"/>
+      <c r="T55" s="17"/>
+      <c r="U55" s="17"/>
+      <c r="V55" s="17"/>
+      <c r="W55" s="17"/>
+      <c r="X55" s="17"/>
+      <c r="Y55" s="17"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="12" t="s">
+      <c r="A56" s="15" t="s">
         <v>219</v>
       </c>
-      <c r="B56" s="13">
+      <c r="B56" s="16">
         <v>0.0</v>
       </c>
-      <c r="C56" s="14" t="s">
+      <c r="C56" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="D56" s="14" t="s">
+      <c r="D56" s="17" t="s">
         <v>221</v>
       </c>
-      <c r="E56" s="14" t="s">
+      <c r="E56" s="17" t="s">
         <v>222</v>
       </c>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="14"/>
-      <c r="J56" s="14"/>
-      <c r="K56" s="14"/>
-      <c r="L56" s="14"/>
-      <c r="M56" s="14"/>
-      <c r="N56" s="14"/>
-      <c r="O56" s="14"/>
-      <c r="P56" s="14"/>
-      <c r="Q56" s="14"/>
-      <c r="R56" s="14"/>
-      <c r="S56" s="14"/>
-      <c r="T56" s="14"/>
-      <c r="U56" s="14"/>
-      <c r="V56" s="14"/>
-      <c r="W56" s="14"/>
-      <c r="X56" s="14"/>
-      <c r="Y56" s="14"/>
+      <c r="F56" s="17"/>
+      <c r="G56" s="17"/>
+      <c r="H56" s="17"/>
+      <c r="I56" s="17"/>
+      <c r="J56" s="17"/>
+      <c r="K56" s="17"/>
+      <c r="L56" s="17"/>
+      <c r="M56" s="17"/>
+      <c r="N56" s="17"/>
+      <c r="O56" s="17"/>
+      <c r="P56" s="17"/>
+      <c r="Q56" s="17"/>
+      <c r="R56" s="17"/>
+      <c r="S56" s="17"/>
+      <c r="T56" s="17"/>
+      <c r="U56" s="17"/>
+      <c r="V56" s="17"/>
+      <c r="W56" s="17"/>
+      <c r="X56" s="17"/>
+      <c r="Y56" s="17"/>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="12" t="s">
+      <c r="A57" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="B57" s="13">
+      <c r="B57" s="16">
         <v>0.0</v>
       </c>
-      <c r="C57" s="14" t="s">
+      <c r="C57" s="17" t="s">
         <v>224</v>
       </c>
-      <c r="D57" s="14" t="s">
+      <c r="D57" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="E57" s="14" t="s">
+      <c r="E57" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="14"/>
-      <c r="J57" s="14"/>
-      <c r="K57" s="14"/>
-      <c r="L57" s="14"/>
-      <c r="M57" s="14"/>
-      <c r="N57" s="14"/>
-      <c r="O57" s="14"/>
-      <c r="P57" s="14"/>
-      <c r="Q57" s="14"/>
-      <c r="R57" s="14"/>
-      <c r="S57" s="14"/>
-      <c r="T57" s="14"/>
-      <c r="U57" s="14"/>
-      <c r="V57" s="14"/>
-      <c r="W57" s="14"/>
-      <c r="X57" s="14"/>
-      <c r="Y57" s="14"/>
+      <c r="F57" s="17"/>
+      <c r="G57" s="17"/>
+      <c r="H57" s="17"/>
+      <c r="I57" s="17"/>
+      <c r="J57" s="17"/>
+      <c r="K57" s="17"/>
+      <c r="L57" s="17"/>
+      <c r="M57" s="17"/>
+      <c r="N57" s="17"/>
+      <c r="O57" s="17"/>
+      <c r="P57" s="17"/>
+      <c r="Q57" s="17"/>
+      <c r="R57" s="17"/>
+      <c r="S57" s="17"/>
+      <c r="T57" s="17"/>
+      <c r="U57" s="17"/>
+      <c r="V57" s="17"/>
+      <c r="W57" s="17"/>
+      <c r="X57" s="17"/>
+      <c r="Y57" s="17"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="12" t="s">
+      <c r="A58" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="B58" s="13">
+      <c r="B58" s="16">
         <v>0.0</v>
       </c>
-      <c r="C58" s="14" t="s">
+      <c r="C58" s="17" t="s">
         <v>228</v>
       </c>
-      <c r="D58" s="14" t="s">
+      <c r="D58" s="17" t="s">
         <v>229</v>
       </c>
-      <c r="E58" s="14" t="s">
+      <c r="E58" s="17" t="s">
         <v>230</v>
       </c>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="14"/>
-      <c r="J58" s="14"/>
-      <c r="K58" s="14"/>
-      <c r="L58" s="14"/>
-      <c r="M58" s="14"/>
-      <c r="N58" s="14"/>
-      <c r="O58" s="14"/>
-      <c r="P58" s="14"/>
-      <c r="Q58" s="14"/>
-      <c r="R58" s="14"/>
-      <c r="S58" s="14"/>
-      <c r="T58" s="14"/>
-      <c r="U58" s="14"/>
-      <c r="V58" s="14"/>
-      <c r="W58" s="14"/>
-      <c r="X58" s="14"/>
-      <c r="Y58" s="14"/>
+      <c r="F58" s="17"/>
+      <c r="G58" s="17"/>
+      <c r="H58" s="17"/>
+      <c r="I58" s="17"/>
+      <c r="J58" s="17"/>
+      <c r="K58" s="17"/>
+      <c r="L58" s="17"/>
+      <c r="M58" s="17"/>
+      <c r="N58" s="17"/>
+      <c r="O58" s="17"/>
+      <c r="P58" s="17"/>
+      <c r="Q58" s="17"/>
+      <c r="R58" s="17"/>
+      <c r="S58" s="17"/>
+      <c r="T58" s="17"/>
+      <c r="U58" s="17"/>
+      <c r="V58" s="17"/>
+      <c r="W58" s="17"/>
+      <c r="X58" s="17"/>
+      <c r="Y58" s="17"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="12" t="s">
+      <c r="A59" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="B59" s="13">
+      <c r="B59" s="16">
         <v>0.0</v>
       </c>
-      <c r="C59" s="14" t="s">
+      <c r="C59" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="D59" s="14" t="s">
+      <c r="D59" s="17" t="s">
         <v>233</v>
       </c>
-      <c r="E59" s="14" t="s">
+      <c r="E59" s="17" t="s">
         <v>234</v>
       </c>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
-      <c r="I59" s="14"/>
-      <c r="J59" s="14"/>
-      <c r="K59" s="14"/>
-      <c r="L59" s="14"/>
-      <c r="M59" s="14"/>
-      <c r="N59" s="14"/>
-      <c r="O59" s="14"/>
-      <c r="P59" s="14"/>
-      <c r="Q59" s="14"/>
-      <c r="R59" s="14"/>
-      <c r="S59" s="14"/>
-      <c r="T59" s="14"/>
-      <c r="U59" s="14"/>
-      <c r="V59" s="14"/>
-      <c r="W59" s="14"/>
-      <c r="X59" s="14"/>
-      <c r="Y59" s="14"/>
+      <c r="F59" s="17"/>
+      <c r="G59" s="17"/>
+      <c r="H59" s="17"/>
+      <c r="I59" s="17"/>
+      <c r="J59" s="17"/>
+      <c r="K59" s="17"/>
+      <c r="L59" s="17"/>
+      <c r="M59" s="17"/>
+      <c r="N59" s="17"/>
+      <c r="O59" s="17"/>
+      <c r="P59" s="17"/>
+      <c r="Q59" s="17"/>
+      <c r="R59" s="17"/>
+      <c r="S59" s="17"/>
+      <c r="T59" s="17"/>
+      <c r="U59" s="17"/>
+      <c r="V59" s="17"/>
+      <c r="W59" s="17"/>
+      <c r="X59" s="17"/>
+      <c r="Y59" s="17"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="12" t="s">
+      <c r="A60" s="15" t="s">
         <v>235</v>
       </c>
-      <c r="B60" s="13">
+      <c r="B60" s="16">
         <v>0.0</v>
       </c>
-      <c r="C60" s="14" t="s">
+      <c r="C60" s="17" t="s">
         <v>236</v>
       </c>
-      <c r="D60" s="14" t="s">
+      <c r="D60" s="17" t="s">
         <v>237</v>
       </c>
-      <c r="E60" s="14" t="s">
+      <c r="E60" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="14"/>
-      <c r="J60" s="14"/>
-      <c r="K60" s="14"/>
-      <c r="L60" s="14"/>
-      <c r="M60" s="14"/>
-      <c r="N60" s="14"/>
-      <c r="O60" s="14"/>
-      <c r="P60" s="14"/>
-      <c r="Q60" s="14"/>
-      <c r="R60" s="14"/>
-      <c r="S60" s="14"/>
-      <c r="T60" s="14"/>
-      <c r="U60" s="14"/>
-      <c r="V60" s="14"/>
-      <c r="W60" s="14"/>
-      <c r="X60" s="14"/>
-      <c r="Y60" s="14"/>
+      <c r="F60" s="17"/>
+      <c r="G60" s="17"/>
+      <c r="H60" s="17"/>
+      <c r="I60" s="17"/>
+      <c r="J60" s="17"/>
+      <c r="K60" s="17"/>
+      <c r="L60" s="17"/>
+      <c r="M60" s="17"/>
+      <c r="N60" s="17"/>
+      <c r="O60" s="17"/>
+      <c r="P60" s="17"/>
+      <c r="Q60" s="17"/>
+      <c r="R60" s="17"/>
+      <c r="S60" s="17"/>
+      <c r="T60" s="17"/>
+      <c r="U60" s="17"/>
+      <c r="V60" s="17"/>
+      <c r="W60" s="17"/>
+      <c r="X60" s="17"/>
+      <c r="Y60" s="17"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="12" t="s">
+      <c r="A61" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="B61" s="13">
+      <c r="B61" s="16">
         <v>0.0</v>
       </c>
-      <c r="C61" s="14" t="s">
+      <c r="C61" s="17" t="s">
         <v>240</v>
       </c>
-      <c r="D61" s="14" t="s">
+      <c r="D61" s="17" t="s">
         <v>241</v>
       </c>
-      <c r="E61" s="14" t="s">
+      <c r="E61" s="17" t="s">
         <v>242</v>
       </c>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="14"/>
-      <c r="J61" s="14"/>
-      <c r="K61" s="14"/>
-      <c r="L61" s="14"/>
-      <c r="M61" s="14"/>
-      <c r="N61" s="14"/>
-      <c r="O61" s="14"/>
-      <c r="P61" s="14"/>
-      <c r="Q61" s="14"/>
-      <c r="R61" s="14"/>
-      <c r="S61" s="14"/>
-      <c r="T61" s="14"/>
-      <c r="U61" s="14"/>
-      <c r="V61" s="14"/>
-      <c r="W61" s="14"/>
-      <c r="X61" s="14"/>
-      <c r="Y61" s="14"/>
+      <c r="F61" s="17"/>
+      <c r="G61" s="17"/>
+      <c r="H61" s="17"/>
+      <c r="I61" s="17"/>
+      <c r="J61" s="17"/>
+      <c r="K61" s="17"/>
+      <c r="L61" s="17"/>
+      <c r="M61" s="17"/>
+      <c r="N61" s="17"/>
+      <c r="O61" s="17"/>
+      <c r="P61" s="17"/>
+      <c r="Q61" s="17"/>
+      <c r="R61" s="17"/>
+      <c r="S61" s="17"/>
+      <c r="T61" s="17"/>
+      <c r="U61" s="17"/>
+      <c r="V61" s="17"/>
+      <c r="W61" s="17"/>
+      <c r="X61" s="17"/>
+      <c r="Y61" s="17"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="12" t="s">
+      <c r="A62" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="B62" s="13">
+      <c r="B62" s="16">
         <v>0.0</v>
       </c>
-      <c r="C62" s="14" t="s">
+      <c r="C62" s="17" t="s">
         <v>244</v>
       </c>
-      <c r="D62" s="14" t="s">
+      <c r="D62" s="17" t="s">
         <v>245</v>
       </c>
-      <c r="E62" s="14" t="s">
+      <c r="E62" s="17" t="s">
         <v>246</v>
       </c>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="14"/>
-      <c r="J62" s="14"/>
-      <c r="K62" s="14"/>
-      <c r="L62" s="14"/>
-      <c r="M62" s="14"/>
-      <c r="N62" s="14"/>
-      <c r="O62" s="14"/>
-      <c r="P62" s="14"/>
-      <c r="Q62" s="14"/>
-      <c r="R62" s="14"/>
-      <c r="S62" s="14"/>
-      <c r="T62" s="14"/>
-      <c r="U62" s="14"/>
-      <c r="V62" s="14"/>
-      <c r="W62" s="14"/>
-      <c r="X62" s="14"/>
-      <c r="Y62" s="14"/>
+      <c r="F62" s="17"/>
+      <c r="G62" s="17"/>
+      <c r="H62" s="17"/>
+      <c r="I62" s="17"/>
+      <c r="J62" s="17"/>
+      <c r="K62" s="17"/>
+      <c r="L62" s="17"/>
+      <c r="M62" s="17"/>
+      <c r="N62" s="17"/>
+      <c r="O62" s="17"/>
+      <c r="P62" s="17"/>
+      <c r="Q62" s="17"/>
+      <c r="R62" s="17"/>
+      <c r="S62" s="17"/>
+      <c r="T62" s="17"/>
+      <c r="U62" s="17"/>
+      <c r="V62" s="17"/>
+      <c r="W62" s="17"/>
+      <c r="X62" s="17"/>
+      <c r="Y62" s="17"/>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="12" t="s">
+      <c r="A63" s="15" t="s">
         <v>247</v>
       </c>
-      <c r="B63" s="13">
+      <c r="B63" s="16">
         <v>0.0</v>
       </c>
-      <c r="C63" s="14" t="s">
+      <c r="C63" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="D63" s="14" t="s">
+      <c r="D63" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="E63" s="14" t="s">
+      <c r="E63" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="14"/>
-      <c r="J63" s="14"/>
-      <c r="K63" s="14"/>
-      <c r="L63" s="14"/>
-      <c r="M63" s="14"/>
-      <c r="N63" s="14"/>
-      <c r="O63" s="14"/>
-      <c r="P63" s="14"/>
-      <c r="Q63" s="14"/>
-      <c r="R63" s="14"/>
-      <c r="S63" s="14"/>
-      <c r="T63" s="14"/>
-      <c r="U63" s="14"/>
-      <c r="V63" s="14"/>
-      <c r="W63" s="14"/>
-      <c r="X63" s="14"/>
-      <c r="Y63" s="14"/>
+      <c r="F63" s="17"/>
+      <c r="G63" s="17"/>
+      <c r="H63" s="17"/>
+      <c r="I63" s="17"/>
+      <c r="J63" s="17"/>
+      <c r="K63" s="17"/>
+      <c r="L63" s="17"/>
+      <c r="M63" s="17"/>
+      <c r="N63" s="17"/>
+      <c r="O63" s="17"/>
+      <c r="P63" s="17"/>
+      <c r="Q63" s="17"/>
+      <c r="R63" s="17"/>
+      <c r="S63" s="17"/>
+      <c r="T63" s="17"/>
+      <c r="U63" s="17"/>
+      <c r="V63" s="17"/>
+      <c r="W63" s="17"/>
+      <c r="X63" s="17"/>
+      <c r="Y63" s="17"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="12" t="s">
+      <c r="A64" s="15" t="s">
         <v>251</v>
       </c>
-      <c r="B64" s="13">
+      <c r="B64" s="16">
         <v>0.0</v>
       </c>
-      <c r="C64" s="14" t="s">
+      <c r="C64" s="17" t="s">
         <v>252</v>
       </c>
-      <c r="D64" s="14" t="s">
+      <c r="D64" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="E64" s="14" t="s">
+      <c r="E64" s="17" t="s">
         <v>254</v>
       </c>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
-      <c r="I64" s="14"/>
-      <c r="J64" s="14"/>
-      <c r="K64" s="14"/>
-      <c r="L64" s="14"/>
-      <c r="M64" s="14"/>
-      <c r="N64" s="14"/>
-      <c r="O64" s="14"/>
-      <c r="P64" s="14"/>
-      <c r="Q64" s="14"/>
-      <c r="R64" s="14"/>
-      <c r="S64" s="14"/>
-      <c r="T64" s="14"/>
-      <c r="U64" s="14"/>
-      <c r="V64" s="14"/>
-      <c r="W64" s="14"/>
-      <c r="X64" s="14"/>
-      <c r="Y64" s="14"/>
+      <c r="F64" s="17"/>
+      <c r="G64" s="17"/>
+      <c r="H64" s="17"/>
+      <c r="I64" s="17"/>
+      <c r="J64" s="17"/>
+      <c r="K64" s="17"/>
+      <c r="L64" s="17"/>
+      <c r="M64" s="17"/>
+      <c r="N64" s="17"/>
+      <c r="O64" s="17"/>
+      <c r="P64" s="17"/>
+      <c r="Q64" s="17"/>
+      <c r="R64" s="17"/>
+      <c r="S64" s="17"/>
+      <c r="T64" s="17"/>
+      <c r="U64" s="17"/>
+      <c r="V64" s="17"/>
+      <c r="W64" s="17"/>
+      <c r="X64" s="17"/>
+      <c r="Y64" s="17"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="15" t="s">
@@ -3662,279 +3707,279 @@
       <c r="Y65" s="17"/>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="18" t="s">
+      <c r="A66" s="15" t="s">
         <v>259</v>
       </c>
-      <c r="B66" s="19">
+      <c r="B66" s="16">
         <v>0.0</v>
       </c>
-      <c r="C66" s="19" t="s">
+      <c r="C66" s="17" t="s">
         <v>260</v>
       </c>
-      <c r="D66" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="E66" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="F66" s="19"/>
-      <c r="G66" s="19"/>
-      <c r="H66" s="19"/>
-      <c r="I66" s="19"/>
-      <c r="J66" s="19"/>
-      <c r="K66" s="19"/>
-      <c r="L66" s="19"/>
-      <c r="M66" s="19"/>
-      <c r="N66" s="19"/>
-      <c r="O66" s="19"/>
-      <c r="P66" s="19"/>
-      <c r="Q66" s="19"/>
-      <c r="R66" s="19"/>
-      <c r="S66" s="19"/>
-      <c r="T66" s="19"/>
-      <c r="U66" s="19"/>
-      <c r="V66" s="19"/>
-      <c r="W66" s="19"/>
-      <c r="X66" s="19"/>
-      <c r="Y66" s="19"/>
+      <c r="D66" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="E66" s="17" t="s">
+        <v>262</v>
+      </c>
+      <c r="F66" s="17"/>
+      <c r="G66" s="17"/>
+      <c r="H66" s="17"/>
+      <c r="I66" s="17"/>
+      <c r="J66" s="17"/>
+      <c r="K66" s="17"/>
+      <c r="L66" s="17"/>
+      <c r="M66" s="17"/>
+      <c r="N66" s="17"/>
+      <c r="O66" s="17"/>
+      <c r="P66" s="17"/>
+      <c r="Q66" s="17"/>
+      <c r="R66" s="17"/>
+      <c r="S66" s="17"/>
+      <c r="T66" s="17"/>
+      <c r="U66" s="17"/>
+      <c r="V66" s="17"/>
+      <c r="W66" s="17"/>
+      <c r="X66" s="17"/>
+      <c r="Y66" s="17"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="18" t="s">
-        <v>261</v>
-      </c>
-      <c r="B67" s="19">
+      <c r="A67" s="15" t="s">
+        <v>263</v>
+      </c>
+      <c r="B67" s="16">
         <v>0.0</v>
       </c>
-      <c r="C67" s="19" t="s">
-        <v>262</v>
-      </c>
-      <c r="D67" s="19" t="s">
-        <v>263</v>
-      </c>
-      <c r="E67" s="19" t="s">
+      <c r="C67" s="17" t="s">
         <v>264</v>
       </c>
-      <c r="F67" s="19"/>
-      <c r="G67" s="19"/>
-      <c r="H67" s="19"/>
-      <c r="I67" s="19"/>
-      <c r="J67" s="19"/>
-      <c r="K67" s="19"/>
-      <c r="L67" s="19"/>
-      <c r="M67" s="19"/>
-      <c r="N67" s="19"/>
-      <c r="O67" s="19"/>
-      <c r="P67" s="19"/>
-      <c r="Q67" s="19"/>
-      <c r="R67" s="19"/>
-      <c r="S67" s="19"/>
-      <c r="T67" s="19"/>
-      <c r="U67" s="19"/>
-      <c r="V67" s="19"/>
-      <c r="W67" s="19"/>
-      <c r="X67" s="19"/>
-      <c r="Y67" s="19"/>
-    </row>
-    <row r="68" ht="15.75" customHeight="1">
+      <c r="D67" s="17" t="s">
+        <v>265</v>
+      </c>
+      <c r="E67" s="17" t="s">
+        <v>266</v>
+      </c>
+      <c r="F67" s="17"/>
+      <c r="G67" s="17"/>
+      <c r="H67" s="17"/>
+      <c r="I67" s="17"/>
+      <c r="J67" s="17"/>
+      <c r="K67" s="17"/>
+      <c r="L67" s="17"/>
+      <c r="M67" s="17"/>
+      <c r="N67" s="17"/>
+      <c r="O67" s="17"/>
+      <c r="P67" s="17"/>
+      <c r="Q67" s="17"/>
+      <c r="R67" s="17"/>
+      <c r="S67" s="17"/>
+      <c r="T67" s="17"/>
+      <c r="U67" s="17"/>
+      <c r="V67" s="17"/>
+      <c r="W67" s="17"/>
+      <c r="X67" s="17"/>
+      <c r="Y67" s="17"/>
+    </row>
+    <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="18" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B68" s="19">
         <v>0.0</v>
       </c>
-      <c r="C68" s="19" t="s">
-        <v>266</v>
-      </c>
-      <c r="D68" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="E68" s="19" t="s">
-        <v>164</v>
-      </c>
-      <c r="F68" s="19"/>
-      <c r="G68" s="19"/>
-      <c r="H68" s="19"/>
-      <c r="I68" s="19"/>
-      <c r="J68" s="19"/>
-      <c r="K68" s="19"/>
-      <c r="L68" s="19"/>
-      <c r="M68" s="19"/>
-      <c r="N68" s="19"/>
-      <c r="O68" s="19"/>
-      <c r="P68" s="19"/>
-      <c r="Q68" s="19"/>
-      <c r="R68" s="19"/>
-      <c r="S68" s="19"/>
-      <c r="T68" s="19"/>
-      <c r="U68" s="19"/>
-      <c r="V68" s="19"/>
-      <c r="W68" s="19"/>
-      <c r="X68" s="19"/>
-      <c r="Y68" s="19"/>
-    </row>
-    <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="18" t="s">
-        <v>267</v>
-      </c>
-      <c r="B69" s="19">
+      <c r="C68" s="20" t="s">
+        <v>268</v>
+      </c>
+      <c r="D68" s="20" t="s">
+        <v>269</v>
+      </c>
+      <c r="E68" s="20" t="s">
+        <v>270</v>
+      </c>
+      <c r="F68" s="20"/>
+      <c r="G68" s="20"/>
+      <c r="H68" s="20"/>
+      <c r="I68" s="20"/>
+      <c r="J68" s="20"/>
+      <c r="K68" s="20"/>
+      <c r="L68" s="20"/>
+      <c r="M68" s="20"/>
+      <c r="N68" s="20"/>
+      <c r="O68" s="20"/>
+      <c r="P68" s="20"/>
+      <c r="Q68" s="20"/>
+      <c r="R68" s="20"/>
+      <c r="S68" s="20"/>
+      <c r="T68" s="20"/>
+      <c r="U68" s="20"/>
+      <c r="V68" s="20"/>
+      <c r="W68" s="20"/>
+      <c r="X68" s="20"/>
+      <c r="Y68" s="20"/>
+    </row>
+    <row r="69" ht="15.0" customHeight="1">
+      <c r="A69" s="21" t="s">
+        <v>271</v>
+      </c>
+      <c r="B69" s="22">
         <v>0.0</v>
       </c>
-      <c r="C69" s="19" t="s">
-        <v>268</v>
-      </c>
-      <c r="D69" s="19" t="s">
-        <v>269</v>
-      </c>
-      <c r="E69" s="19" t="s">
-        <v>270</v>
-      </c>
-      <c r="F69" s="19"/>
-      <c r="G69" s="19"/>
-      <c r="H69" s="19"/>
-      <c r="I69" s="19"/>
-      <c r="J69" s="19"/>
-      <c r="K69" s="19"/>
-      <c r="L69" s="19"/>
-      <c r="M69" s="19"/>
-      <c r="N69" s="19"/>
-      <c r="O69" s="19"/>
-      <c r="P69" s="19"/>
-      <c r="Q69" s="19"/>
-      <c r="R69" s="19"/>
-      <c r="S69" s="19"/>
-      <c r="T69" s="19"/>
-      <c r="U69" s="19"/>
-      <c r="V69" s="19"/>
-      <c r="W69" s="19"/>
-      <c r="X69" s="19"/>
-      <c r="Y69" s="19"/>
+      <c r="C69" s="22" t="s">
+        <v>272</v>
+      </c>
+      <c r="D69" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="E69" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="F69" s="22"/>
+      <c r="G69" s="22"/>
+      <c r="H69" s="22"/>
+      <c r="I69" s="22"/>
+      <c r="J69" s="22"/>
+      <c r="K69" s="22"/>
+      <c r="L69" s="22"/>
+      <c r="M69" s="22"/>
+      <c r="N69" s="22"/>
+      <c r="O69" s="22"/>
+      <c r="P69" s="22"/>
+      <c r="Q69" s="22"/>
+      <c r="R69" s="22"/>
+      <c r="S69" s="22"/>
+      <c r="T69" s="22"/>
+      <c r="U69" s="22"/>
+      <c r="V69" s="22"/>
+      <c r="W69" s="22"/>
+      <c r="X69" s="22"/>
+      <c r="Y69" s="22"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="18" t="s">
-        <v>271</v>
-      </c>
-      <c r="B70" s="19">
+      <c r="A70" s="21" t="s">
+        <v>273</v>
+      </c>
+      <c r="B70" s="22">
         <v>0.0</v>
       </c>
-      <c r="C70" s="19" t="s">
-        <v>272</v>
-      </c>
-      <c r="D70" s="19" t="s">
-        <v>273</v>
-      </c>
-      <c r="E70" s="19" t="s">
+      <c r="C70" s="22" t="s">
         <v>274</v>
       </c>
-      <c r="F70" s="19"/>
-      <c r="G70" s="19"/>
-      <c r="H70" s="19"/>
-      <c r="I70" s="19"/>
-      <c r="J70" s="19"/>
-      <c r="K70" s="19"/>
-      <c r="L70" s="19"/>
-      <c r="M70" s="19"/>
-      <c r="N70" s="19"/>
-      <c r="O70" s="19"/>
-      <c r="P70" s="19"/>
-      <c r="Q70" s="19"/>
-      <c r="R70" s="19"/>
-      <c r="S70" s="19"/>
-      <c r="T70" s="19"/>
-      <c r="U70" s="19"/>
-      <c r="V70" s="19"/>
-      <c r="W70" s="19"/>
-      <c r="X70" s="19"/>
-      <c r="Y70" s="19"/>
-    </row>
-    <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="18" t="s">
+      <c r="D70" s="22" t="s">
         <v>275</v>
       </c>
-      <c r="B71" s="19">
+      <c r="E70" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="F70" s="22"/>
+      <c r="G70" s="22"/>
+      <c r="H70" s="22"/>
+      <c r="I70" s="22"/>
+      <c r="J70" s="22"/>
+      <c r="K70" s="22"/>
+      <c r="L70" s="22"/>
+      <c r="M70" s="22"/>
+      <c r="N70" s="22"/>
+      <c r="O70" s="22"/>
+      <c r="P70" s="22"/>
+      <c r="Q70" s="22"/>
+      <c r="R70" s="22"/>
+      <c r="S70" s="22"/>
+      <c r="T70" s="22"/>
+      <c r="U70" s="22"/>
+      <c r="V70" s="22"/>
+      <c r="W70" s="22"/>
+      <c r="X70" s="22"/>
+      <c r="Y70" s="22"/>
+    </row>
+    <row r="71" ht="15.75" customHeight="1">
+      <c r="A71" s="21" t="s">
+        <v>277</v>
+      </c>
+      <c r="B71" s="22">
         <v>0.0</v>
       </c>
-      <c r="C71" s="19" t="s">
-        <v>276</v>
-      </c>
-      <c r="D71" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="E71" s="19" t="s">
+      <c r="C71" s="22" t="s">
         <v>278</v>
       </c>
-      <c r="F71" s="19"/>
-      <c r="G71" s="19"/>
-      <c r="H71" s="19"/>
-      <c r="I71" s="19"/>
-      <c r="J71" s="19"/>
-      <c r="K71" s="19"/>
-      <c r="L71" s="19"/>
-      <c r="M71" s="19"/>
-      <c r="N71" s="19"/>
-      <c r="O71" s="19"/>
-      <c r="P71" s="19"/>
-      <c r="Q71" s="19"/>
-      <c r="R71" s="19"/>
-      <c r="S71" s="19"/>
-      <c r="T71" s="19"/>
-      <c r="U71" s="19"/>
-      <c r="V71" s="19"/>
-      <c r="W71" s="19"/>
-      <c r="X71" s="19"/>
-      <c r="Y71" s="19"/>
-    </row>
-    <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="18" t="s">
+      <c r="D71" s="22" t="s">
+        <v>175</v>
+      </c>
+      <c r="E71" s="22" t="s">
+        <v>176</v>
+      </c>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="22"/>
+      <c r="K71" s="22"/>
+      <c r="L71" s="22"/>
+      <c r="M71" s="22"/>
+      <c r="N71" s="22"/>
+      <c r="O71" s="22"/>
+      <c r="P71" s="22"/>
+      <c r="Q71" s="22"/>
+      <c r="R71" s="22"/>
+      <c r="S71" s="22"/>
+      <c r="T71" s="22"/>
+      <c r="U71" s="22"/>
+      <c r="V71" s="22"/>
+      <c r="W71" s="22"/>
+      <c r="X71" s="22"/>
+      <c r="Y71" s="22"/>
+    </row>
+    <row r="72" ht="15.75" customHeight="1">
+      <c r="A72" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="B72" s="19">
+      <c r="B72" s="22">
         <v>0.0</v>
       </c>
-      <c r="C72" s="19" t="s">
+      <c r="C72" s="22" t="s">
         <v>280</v>
       </c>
-      <c r="D72" s="19" t="s">
+      <c r="D72" s="22" t="s">
         <v>281</v>
       </c>
-      <c r="E72" s="19" t="s">
+      <c r="E72" s="22" t="s">
         <v>282</v>
       </c>
-      <c r="F72" s="19"/>
-      <c r="G72" s="19"/>
-      <c r="H72" s="19"/>
-      <c r="I72" s="19"/>
-      <c r="J72" s="19"/>
-      <c r="K72" s="19"/>
-      <c r="L72" s="19"/>
-      <c r="M72" s="19"/>
-      <c r="N72" s="19"/>
-      <c r="O72" s="19"/>
-      <c r="P72" s="19"/>
-      <c r="Q72" s="19"/>
-      <c r="R72" s="19"/>
-      <c r="S72" s="19"/>
-      <c r="T72" s="19"/>
-      <c r="U72" s="19"/>
-      <c r="V72" s="19"/>
-      <c r="W72" s="19"/>
-      <c r="X72" s="19"/>
-      <c r="Y72" s="19"/>
+      <c r="F72" s="22"/>
+      <c r="G72" s="22"/>
+      <c r="H72" s="22"/>
+      <c r="I72" s="22"/>
+      <c r="J72" s="22"/>
+      <c r="K72" s="22"/>
+      <c r="L72" s="22"/>
+      <c r="M72" s="22"/>
+      <c r="N72" s="22"/>
+      <c r="O72" s="22"/>
+      <c r="P72" s="22"/>
+      <c r="Q72" s="22"/>
+      <c r="R72" s="22"/>
+      <c r="S72" s="22"/>
+      <c r="T72" s="22"/>
+      <c r="U72" s="22"/>
+      <c r="V72" s="22"/>
+      <c r="W72" s="22"/>
+      <c r="X72" s="22"/>
+      <c r="Y72" s="22"/>
     </row>
     <row r="73" ht="15.0" customHeight="1">
-      <c r="A73" s="20" t="s">
+      <c r="A73" s="21" t="s">
         <v>283</v>
       </c>
-      <c r="B73" s="21">
+      <c r="B73" s="22">
         <v>0.0</v>
       </c>
       <c r="C73" s="22" t="s">
         <v>284</v>
       </c>
       <c r="D73" s="22" t="s">
-        <v>195</v>
+        <v>285</v>
       </c>
       <c r="E73" s="22" t="s">
-        <v>196</v>
+        <v>286</v>
       </c>
       <c r="F73" s="22"/>
       <c r="G73" s="22"/>
@@ -3958,122 +4003,152 @@
       <c r="Y73" s="22"/>
     </row>
     <row r="74" ht="15.0" customHeight="1">
-      <c r="A74" s="23" t="s">
-        <v>285</v>
-      </c>
-      <c r="B74" s="24">
+      <c r="A74" s="21" t="s">
+        <v>287</v>
+      </c>
+      <c r="B74" s="22">
         <v>0.0</v>
       </c>
-      <c r="C74" s="25" t="s">
-        <v>286</v>
-      </c>
-      <c r="D74" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="E74" s="25" t="s">
-        <v>128</v>
-      </c>
-      <c r="F74" s="25"/>
-      <c r="G74" s="25"/>
-      <c r="H74" s="25"/>
-      <c r="I74" s="25"/>
-      <c r="J74" s="25"/>
-      <c r="K74" s="25"/>
-      <c r="L74" s="25"/>
-      <c r="M74" s="25"/>
-      <c r="N74" s="25"/>
-      <c r="O74" s="25"/>
-      <c r="P74" s="25"/>
-      <c r="Q74" s="25"/>
-      <c r="R74" s="25"/>
-      <c r="S74" s="25"/>
-      <c r="T74" s="25"/>
-      <c r="U74" s="25"/>
-      <c r="V74" s="25"/>
-      <c r="W74" s="25"/>
-      <c r="X74" s="25"/>
-      <c r="Y74" s="25"/>
+      <c r="C74" s="22" t="s">
+        <v>288</v>
+      </c>
+      <c r="D74" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="E74" s="22" t="s">
+        <v>290</v>
+      </c>
+      <c r="F74" s="22"/>
+      <c r="G74" s="22"/>
+      <c r="H74" s="22"/>
+      <c r="I74" s="22"/>
+      <c r="J74" s="22"/>
+      <c r="K74" s="22"/>
+      <c r="L74" s="22"/>
+      <c r="M74" s="22"/>
+      <c r="N74" s="22"/>
+      <c r="O74" s="22"/>
+      <c r="P74" s="22"/>
+      <c r="Q74" s="22"/>
+      <c r="R74" s="22"/>
+      <c r="S74" s="22"/>
+      <c r="T74" s="22"/>
+      <c r="U74" s="22"/>
+      <c r="V74" s="22"/>
+      <c r="W74" s="22"/>
+      <c r="X74" s="22"/>
+      <c r="Y74" s="22"/>
     </row>
     <row r="75" ht="15.0" customHeight="1">
-      <c r="A75" s="1"/>
-      <c r="B75" s="1"/>
-      <c r="C75" s="1"/>
-      <c r="D75" s="1"/>
-      <c r="E75" s="1"/>
-      <c r="F75" s="1"/>
-      <c r="G75" s="1"/>
-      <c r="H75" s="1"/>
-      <c r="I75" s="1"/>
-      <c r="J75" s="1"/>
-      <c r="K75" s="1"/>
-      <c r="L75" s="1"/>
-      <c r="M75" s="1"/>
-      <c r="N75" s="1"/>
-      <c r="O75" s="1"/>
-      <c r="P75" s="1"/>
-      <c r="Q75" s="1"/>
-      <c r="R75" s="1"/>
-      <c r="S75" s="1"/>
-      <c r="T75" s="1"/>
-      <c r="U75" s="1"/>
-      <c r="V75" s="1"/>
-      <c r="W75" s="1"/>
-      <c r="X75" s="1"/>
-      <c r="Y75" s="1"/>
+      <c r="A75" s="21" t="s">
+        <v>291</v>
+      </c>
+      <c r="B75" s="22">
+        <v>0.0</v>
+      </c>
+      <c r="C75" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="D75" s="22" t="s">
+        <v>293</v>
+      </c>
+      <c r="E75" s="22" t="s">
+        <v>294</v>
+      </c>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="22"/>
+      <c r="K75" s="22"/>
+      <c r="L75" s="22"/>
+      <c r="M75" s="22"/>
+      <c r="N75" s="22"/>
+      <c r="O75" s="22"/>
+      <c r="P75" s="22"/>
+      <c r="Q75" s="22"/>
+      <c r="R75" s="22"/>
+      <c r="S75" s="22"/>
+      <c r="T75" s="22"/>
+      <c r="U75" s="22"/>
+      <c r="V75" s="22"/>
+      <c r="W75" s="22"/>
+      <c r="X75" s="22"/>
+      <c r="Y75" s="22"/>
     </row>
     <row r="76" ht="15.0" customHeight="1">
-      <c r="A76" s="1"/>
-      <c r="B76" s="1"/>
-      <c r="C76" s="1"/>
-      <c r="D76" s="1"/>
-      <c r="E76" s="1"/>
-      <c r="F76" s="1"/>
-      <c r="G76" s="1"/>
-      <c r="H76" s="1"/>
-      <c r="I76" s="1"/>
-      <c r="J76" s="1"/>
-      <c r="K76" s="1"/>
-      <c r="L76" s="1"/>
-      <c r="M76" s="1"/>
-      <c r="N76" s="1"/>
-      <c r="O76" s="1"/>
-      <c r="P76" s="1"/>
-      <c r="Q76" s="1"/>
-      <c r="R76" s="1"/>
-      <c r="S76" s="1"/>
-      <c r="T76" s="1"/>
-      <c r="U76" s="1"/>
-      <c r="V76" s="1"/>
-      <c r="W76" s="1"/>
-      <c r="X76" s="1"/>
-      <c r="Y76" s="1"/>
+      <c r="A76" s="23" t="s">
+        <v>295</v>
+      </c>
+      <c r="B76" s="24">
+        <v>0.0</v>
+      </c>
+      <c r="C76" s="25" t="s">
+        <v>296</v>
+      </c>
+      <c r="D76" s="25" t="s">
+        <v>207</v>
+      </c>
+      <c r="E76" s="25" t="s">
+        <v>208</v>
+      </c>
+      <c r="F76" s="25"/>
+      <c r="G76" s="25"/>
+      <c r="H76" s="25"/>
+      <c r="I76" s="25"/>
+      <c r="J76" s="25"/>
+      <c r="K76" s="25"/>
+      <c r="L76" s="25"/>
+      <c r="M76" s="25"/>
+      <c r="N76" s="25"/>
+      <c r="O76" s="25"/>
+      <c r="P76" s="25"/>
+      <c r="Q76" s="25"/>
+      <c r="R76" s="25"/>
+      <c r="S76" s="25"/>
+      <c r="T76" s="25"/>
+      <c r="U76" s="25"/>
+      <c r="V76" s="25"/>
+      <c r="W76" s="25"/>
+      <c r="X76" s="25"/>
+      <c r="Y76" s="25"/>
     </row>
     <row r="77" ht="15.0" customHeight="1">
-      <c r="A77" s="1"/>
-      <c r="B77" s="1"/>
-      <c r="C77" s="1"/>
-      <c r="D77" s="1"/>
-      <c r="E77" s="1"/>
-      <c r="F77" s="1"/>
-      <c r="G77" s="1"/>
-      <c r="H77" s="1"/>
-      <c r="I77" s="1"/>
-      <c r="J77" s="1"/>
-      <c r="K77" s="1"/>
-      <c r="L77" s="1"/>
-      <c r="M77" s="1"/>
-      <c r="N77" s="1"/>
-      <c r="O77" s="1"/>
-      <c r="P77" s="1"/>
-      <c r="Q77" s="1"/>
-      <c r="R77" s="1"/>
-      <c r="S77" s="1"/>
-      <c r="T77" s="1"/>
-      <c r="U77" s="1"/>
-      <c r="V77" s="1"/>
-      <c r="W77" s="1"/>
-      <c r="X77" s="1"/>
-      <c r="Y77" s="1"/>
+      <c r="A77" s="26" t="s">
+        <v>297</v>
+      </c>
+      <c r="B77" s="27">
+        <v>0.0</v>
+      </c>
+      <c r="C77" s="28" t="s">
+        <v>298</v>
+      </c>
+      <c r="D77" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="E77" s="28" t="s">
+        <v>140</v>
+      </c>
+      <c r="F77" s="28"/>
+      <c r="G77" s="28"/>
+      <c r="H77" s="28"/>
+      <c r="I77" s="28"/>
+      <c r="J77" s="28"/>
+      <c r="K77" s="28"/>
+      <c r="L77" s="28"/>
+      <c r="M77" s="28"/>
+      <c r="N77" s="28"/>
+      <c r="O77" s="28"/>
+      <c r="P77" s="28"/>
+      <c r="Q77" s="28"/>
+      <c r="R77" s="28"/>
+      <c r="S77" s="28"/>
+      <c r="T77" s="28"/>
+      <c r="U77" s="28"/>
+      <c r="V77" s="28"/>
+      <c r="W77" s="28"/>
+      <c r="X77" s="28"/>
+      <c r="Y77" s="28"/>
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="1"/>
@@ -8962,7 +9037,7 @@
       <c r="X258" s="1"/>
       <c r="Y258" s="1"/>
     </row>
-    <row r="259" ht="15.75" customHeight="1">
+    <row r="259" ht="15.0" customHeight="1">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -8989,7 +9064,7 @@
       <c r="X259" s="1"/>
       <c r="Y259" s="1"/>
     </row>
-    <row r="260" ht="15.75" customHeight="1">
+    <row r="260" ht="15.0" customHeight="1">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -9016,7 +9091,7 @@
       <c r="X260" s="1"/>
       <c r="Y260" s="1"/>
     </row>
-    <row r="261" ht="15.75" customHeight="1">
+    <row r="261" ht="15.0" customHeight="1">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -9394,9 +9469,87 @@
       <c r="X274" s="1"/>
       <c r="Y274" s="1"/>
     </row>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1">
+      <c r="A275" s="1"/>
+      <c r="B275" s="1"/>
+      <c r="C275" s="1"/>
+      <c r="D275" s="1"/>
+      <c r="E275" s="1"/>
+      <c r="F275" s="1"/>
+      <c r="G275" s="1"/>
+      <c r="H275" s="1"/>
+      <c r="I275" s="1"/>
+      <c r="J275" s="1"/>
+      <c r="K275" s="1"/>
+      <c r="L275" s="1"/>
+      <c r="M275" s="1"/>
+      <c r="N275" s="1"/>
+      <c r="O275" s="1"/>
+      <c r="P275" s="1"/>
+      <c r="Q275" s="1"/>
+      <c r="R275" s="1"/>
+      <c r="S275" s="1"/>
+      <c r="T275" s="1"/>
+      <c r="U275" s="1"/>
+      <c r="V275" s="1"/>
+      <c r="W275" s="1"/>
+      <c r="X275" s="1"/>
+      <c r="Y275" s="1"/>
+    </row>
+    <row r="276" ht="15.75" customHeight="1">
+      <c r="A276" s="1"/>
+      <c r="B276" s="1"/>
+      <c r="C276" s="1"/>
+      <c r="D276" s="1"/>
+      <c r="E276" s="1"/>
+      <c r="F276" s="1"/>
+      <c r="G276" s="1"/>
+      <c r="H276" s="1"/>
+      <c r="I276" s="1"/>
+      <c r="J276" s="1"/>
+      <c r="K276" s="1"/>
+      <c r="L276" s="1"/>
+      <c r="M276" s="1"/>
+      <c r="N276" s="1"/>
+      <c r="O276" s="1"/>
+      <c r="P276" s="1"/>
+      <c r="Q276" s="1"/>
+      <c r="R276" s="1"/>
+      <c r="S276" s="1"/>
+      <c r="T276" s="1"/>
+      <c r="U276" s="1"/>
+      <c r="V276" s="1"/>
+      <c r="W276" s="1"/>
+      <c r="X276" s="1"/>
+      <c r="Y276" s="1"/>
+    </row>
+    <row r="277" ht="15.75" customHeight="1">
+      <c r="A277" s="1"/>
+      <c r="B277" s="1"/>
+      <c r="C277" s="1"/>
+      <c r="D277" s="1"/>
+      <c r="E277" s="1"/>
+      <c r="F277" s="1"/>
+      <c r="G277" s="1"/>
+      <c r="H277" s="1"/>
+      <c r="I277" s="1"/>
+      <c r="J277" s="1"/>
+      <c r="K277" s="1"/>
+      <c r="L277" s="1"/>
+      <c r="M277" s="1"/>
+      <c r="N277" s="1"/>
+      <c r="O277" s="1"/>
+      <c r="P277" s="1"/>
+      <c r="Q277" s="1"/>
+      <c r="R277" s="1"/>
+      <c r="S277" s="1"/>
+      <c r="T277" s="1"/>
+      <c r="U277" s="1"/>
+      <c r="V277" s="1"/>
+      <c r="W277" s="1"/>
+      <c r="X277" s="1"/>
+      <c r="Y277" s="1"/>
+    </row>
     <row r="278" ht="15.75" customHeight="1"/>
     <row r="279" ht="15.75" customHeight="1"/>
     <row r="280" ht="15.75" customHeight="1"/>
@@ -10112,6 +10265,17 @@
     <row r="990" ht="15.75" customHeight="1"/>
     <row r="991" ht="15.75" customHeight="1"/>
     <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
+    <row r="1002" ht="15.75" customHeight="1"/>
+    <row r="1003" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Templates/Tables/StringInfo/StrTable.xlsx
+++ b/Templates/Tables/StringInfo/StrTable.xlsx
@@ -13,901 +13,901 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="299">
   <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Replace</t>
+  </si>
+  <si>
     <t>ID</t>
   </si>
   <si>
-    <t>Replace</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
     <t>Korean</t>
   </si>
   <si>
     <t>English</t>
   </si>
   <si>
+    <t>에디터 종료 팝업 메세지</t>
+  </si>
+  <si>
     <t>EDITOR_QUIT_P_MSG</t>
   </si>
   <si>
-    <t>에디터 종료 팝업 메세지</t>
-  </si>
-  <si>
     <t>에디터를 종료하시겠습니까?</t>
   </si>
   <si>
     <t>Do you want to quit the editor?</t>
   </si>
   <si>
+    <t>에디터 리셋 팝업 메세지</t>
+  </si>
+  <si>
     <t>EDITOR_RESET_P_MSG</t>
   </si>
   <si>
-    <t>에디터 리셋 팝업 메세지</t>
-  </si>
-  <si>
     <t>에디터를 리셋하시겠습니까?</t>
   </si>
   <si>
     <t>Do you want to reset the editor?</t>
   </si>
   <si>
+    <t>에디터 세트 A 팝업 메세지</t>
+  </si>
+  <si>
     <t>EDITOR_A_SET_P_MSG</t>
   </si>
   <si>
-    <t>에디터 세트 A 팝업 메세지</t>
-  </si>
-  <si>
     <t>A 세트 를 설정하시겠습니까?</t>
   </si>
   <si>
     <t>Do you want to set up the A set?</t>
   </si>
   <si>
+    <t>에디터 세트 B 팝업 메세지</t>
+  </si>
+  <si>
     <t>EDITOR_B_SET_P_MSG</t>
   </si>
   <si>
-    <t>에디터 세트 B 팝업 메세지</t>
-  </si>
-  <si>
     <t>B 세트 를 설정하시겠습니까?</t>
   </si>
   <si>
     <t>Do you want to set up the B set?</t>
   </si>
   <si>
+    <t>에디터 테이블 다시 로드 메세지</t>
+  </si>
+  <si>
     <t>EDITOR_TABLE_RL_MSG</t>
   </si>
   <si>
-    <t>에디터 테이블 다시 로드 메세지</t>
-  </si>
-  <si>
     <t>테이블을 다시 로드하시겠습니까?</t>
   </si>
   <si>
     <t>Do you want to reload the table?</t>
   </si>
   <si>
+    <t>에디터 레벨 제거 팝업 메세지</t>
+  </si>
+  <si>
     <t>EDITOR_REMOVE_LP_MSG</t>
   </si>
   <si>
-    <t>에디터 레벨 제거 팝업 메세지</t>
-  </si>
-  <si>
     <t>레벨을 제거하시겠습니까?</t>
   </si>
   <si>
     <t>Do you want to remove the level?</t>
   </si>
   <si>
+    <t>에디터 스테이지 제거 팝업 메세지</t>
+  </si>
+  <si>
     <t>EDITOR_REMOVE_SP_MSG</t>
   </si>
   <si>
-    <t>에디터 스테이지 제거 팝업 메세지</t>
-  </si>
-  <si>
     <t>스테이지를 제거하시겠습니까?</t>
   </si>
   <si>
     <t>Do you want to remove the stage?</t>
   </si>
   <si>
+    <t>에디터 챕터 제거 팝업 메세지</t>
+  </si>
+  <si>
     <t>EDITOR_REMOVE_CP_MSG</t>
   </si>
   <si>
-    <t>에디터 챕터 제거 팝업 메세지</t>
-  </si>
-  <si>
     <t>챕터를 제거하시겠습니까?</t>
   </si>
   <si>
     <t>Do you want to remove the chapter?</t>
   </si>
   <si>
+    <t>종료 팝업 메세지</t>
+  </si>
+  <si>
     <t>QUIT_P_MSG</t>
   </si>
   <si>
-    <t>종료 팝업 메세지</t>
-  </si>
-  <si>
     <t>게임을 종료하시겠습니까?</t>
   </si>
   <si>
     <t>Do you want to quit the game?</t>
   </si>
   <si>
+    <t>그만두기 팝업 메세지</t>
+  </si>
+  <si>
     <t>LEAVE_P_MSG</t>
   </si>
   <si>
-    <t>그만두기 팝업 메세지</t>
-  </si>
-  <si>
     <t>게임을 그만두시겠습니까?</t>
   </si>
   <si>
     <t>Do you want to leave the game?</t>
   </si>
   <si>
+    <t>업데이트 팝업 메세지</t>
+  </si>
+  <si>
     <t>UPDATE_P_MSG</t>
   </si>
   <si>
-    <t>업데이트 팝업 메세지</t>
-  </si>
-  <si>
     <t>새로운 버전이 출시되었습니다.\n업데이트 하시겠습니까?</t>
   </si>
   <si>
     <t>A new version has been released.\nWould you like to update it?</t>
   </si>
   <si>
+    <t>로드 팝업 메세지</t>
+  </si>
+  <si>
     <t>LOAD_P_MSG</t>
   </si>
   <si>
-    <t>로드 팝업 메세지</t>
-  </si>
-  <si>
     <t>진행 상황을 로드하시겠습니까?\n&lt;color=#ff0000ff&gt;&lt;size=24&gt;(로드 시 현재 진행 상황은 복구 할 수 없습니다)&lt;/size&gt;&lt;/color&gt;</t>
   </si>
   <si>
     <t>Do you want to load progress?\n&lt;color=#ff0000ff&gt;&lt;size=24&gt;(When loading, current progress cannot be recovered)&lt;/size&gt;&lt;/color&gt;</t>
   </si>
   <si>
+    <t>저장 팝업 메세지</t>
+  </si>
+  <si>
     <t>SAVE_P_MSG</t>
   </si>
   <si>
-    <t>저장 팝업 메세지</t>
-  </si>
-  <si>
     <t>진행 상황을 저장하시겠습니까?\n&lt;color=#ff0000ff&gt;&lt;size=24&gt;(저장 시 이전 진행 상황은 복구 할 수 없습니다)&lt;/size&gt;&lt;/color&gt;</t>
   </si>
   <si>
     <t>Do you want to save progress?\n&lt;color=#ff0000ff&gt;&lt;size=24&gt;(When saving, previous progress cannot be recovered)&lt;/size&gt;&lt;/color&gt;</t>
   </si>
   <si>
+    <t>추적 설명 팝업 제목</t>
+  </si>
+  <si>
     <t>TRACKING_DP_TITLE</t>
   </si>
   <si>
-    <t>추적 설명 팝업 제목</t>
-  </si>
-  <si>
     <t>알림</t>
   </si>
   <si>
     <t>Notice</t>
   </si>
   <si>
+    <t>추적 설명 팝업 메세지</t>
+  </si>
+  <si>
     <t>TRACKING_DP_MSG</t>
   </si>
   <si>
-    <t>추적 설명 팝업 메세지</t>
-  </si>
-  <si>
     <t>앱 추적 승인</t>
   </si>
   <si>
     <t>Allow tracking on the\nnext screen for</t>
   </si>
   <si>
+    <t>추적 설명 팝업 설명 메세지 1</t>
+  </si>
+  <si>
     <t>TRACKING_DP_DESC_MSG_01</t>
   </si>
   <si>
-    <t>추적 설명 팝업 설명 메세지 1</t>
-  </si>
-  <si>
     <t>특별한 프로모션을 제공해\n드립니다</t>
   </si>
   <si>
     <t>Special offers and promotions\njust for you</t>
   </si>
   <si>
+    <t>추적 설명 팝업 설명 메세지 2</t>
+  </si>
+  <si>
     <t>TRACKING_DP_DESC_MSG_02</t>
   </si>
   <si>
-    <t>추적 설명 팝업 설명 메세지 2</t>
-  </si>
-  <si>
     <t>관심사에 맞는 광고를 보여\n드립니다</t>
   </si>
   <si>
     <t>Advertisements that match\nyour interests</t>
   </si>
   <si>
+    <t>추적 설명 팝업 설명 메세지 3</t>
+  </si>
+  <si>
     <t>TRACKING_DP_DESC_MSG_03</t>
   </si>
   <si>
-    <t>추적 설명 팝업 설명 메세지 3</t>
-  </si>
-  <si>
     <t>개인화 된 경험을 향상 시켜\n드립니다</t>
   </si>
   <si>
     <t>An improved personalized\nexperience over time</t>
   </si>
   <si>
+    <t>공용 로그인 성공 메세지</t>
+  </si>
+  <si>
     <t>COMMON_LOGIN_SUCCESS_MSG</t>
   </si>
   <si>
-    <t>공용 로그인 성공 메세지</t>
-  </si>
-  <si>
     <t>로그인했습니다</t>
   </si>
   <si>
     <t>You have successfully login</t>
   </si>
   <si>
+    <t>공용 로그인 실패 메세지</t>
+  </si>
+  <si>
     <t>COMMON_LOGIN_FAIL_MSG</t>
   </si>
   <si>
-    <t>공용 로그인 실패 메세지</t>
-  </si>
-  <si>
     <t>로그인에 실패했습니다</t>
   </si>
   <si>
     <t>You have failed to login</t>
   </si>
   <si>
+    <t>공용 로그아웃 성공 메세지</t>
+  </si>
+  <si>
     <t>COMMON_LOGOUT_SUCCESS_MSG</t>
   </si>
   <si>
-    <t>공용 로그아웃 성공 메세지</t>
-  </si>
-  <si>
     <t>로그아웃했습니다</t>
   </si>
   <si>
     <t>You have successfully logout</t>
   </si>
   <si>
+    <t>공용 로그아웃 실패 메세지</t>
+  </si>
+  <si>
     <t>COMMON_LOGOUT_FAIL_MSG</t>
   </si>
   <si>
-    <t>공용 로그아웃 실패 메세지</t>
-  </si>
-  <si>
     <t>로그아웃에 실패했습니다</t>
   </si>
   <si>
     <t>You have failed to logout</t>
   </si>
   <si>
+    <t>공용 로드 성공 메세지</t>
+  </si>
+  <si>
     <t>COMMON_LOAD_SUCCESS_MSG</t>
   </si>
   <si>
-    <t>공용 로드 성공 메세지</t>
-  </si>
-  <si>
     <t>진행 상황을 로드했습니다</t>
   </si>
   <si>
     <t>You have successfully loaded progress</t>
   </si>
   <si>
+    <t>공용 로드 실패 메세지</t>
+  </si>
+  <si>
     <t>COMMON_LOAD_FAIL_MSG</t>
   </si>
   <si>
-    <t>공용 로드 실패 메세지</t>
-  </si>
-  <si>
     <t>진행 상황 로드에 실패했습니다</t>
   </si>
   <si>
     <t>You have failed to load progress</t>
   </si>
   <si>
+    <t>공용 저장 성공 메세지</t>
+  </si>
+  <si>
     <t>COMMON_SAVE_SUCCESS_MSG</t>
   </si>
   <si>
-    <t>공용 저장 성공 메세지</t>
-  </si>
-  <si>
     <t>진행 상황을 저장했습니다</t>
   </si>
   <si>
     <t>You have successfully saved progress</t>
   </si>
   <si>
+    <t>공용 저장 실패 메세지</t>
+  </si>
+  <si>
     <t>COMMON_SAVE_FAIL_MSG</t>
   </si>
   <si>
-    <t>공용 저장 실패 메세지</t>
-  </si>
-  <si>
     <t>진행 상황 저장에 실패했습니다</t>
   </si>
   <si>
     <t>You have failed to save progress</t>
   </si>
   <si>
+    <t>공용 결제 성공 메세지</t>
+  </si>
+  <si>
     <t>COMMON_PURCHASE_SUCCESS_MSG</t>
   </si>
   <si>
-    <t>공용 결제 성공 메세지</t>
-  </si>
-  <si>
     <t>해당 상품을 구입했습니다</t>
   </si>
   <si>
     <t>You have successfully purchased this product</t>
   </si>
   <si>
+    <t>공용 결제 실패 메세지</t>
+  </si>
+  <si>
     <t>COMMON_PURCHASE_FAIL_MSG</t>
   </si>
   <si>
-    <t>공용 결제 실패 메세지</t>
-  </si>
-  <si>
     <t>해당 상품 구입에 실패했습니다</t>
   </si>
   <si>
     <t>You have failed to purchase this product</t>
   </si>
   <si>
+    <t>공용 복원 성공 메세지</t>
+  </si>
+  <si>
     <t>COMMON_RESTORE_SUCCESS_MSG</t>
   </si>
   <si>
-    <t>공용 복원 성공 메세지</t>
-  </si>
-  <si>
     <t>상품을 복원했습니다</t>
   </si>
   <si>
     <t>The product has been restored</t>
   </si>
   <si>
+    <t>공용 복원 실패 메세지</t>
+  </si>
+  <si>
     <t>COMMON_RESTORE_FAIL_MSG</t>
   </si>
   <si>
-    <t>공용 복원 실패 메세지</t>
-  </si>
-  <si>
     <t>상품 복원에 실패했습니다</t>
   </si>
   <si>
     <t>Failed to restore the product</t>
   </si>
   <si>
+    <t>공용 확인 텍스트</t>
+  </si>
+  <si>
     <t>COMMON_OK_TEXT</t>
   </si>
   <si>
-    <t>공용 확인 텍스트</t>
-  </si>
-  <si>
     <t>확인</t>
   </si>
   <si>
     <t>OK</t>
   </si>
   <si>
+    <t>공용 취소 텍스트</t>
+  </si>
+  <si>
     <t>COMMON_CANCEL_TEXT</t>
   </si>
   <si>
-    <t>공용 취소 텍스트</t>
-  </si>
-  <si>
     <t>취소</t>
   </si>
   <si>
     <t>Cancel</t>
   </si>
   <si>
+    <t>공용 동의 텍스트</t>
+  </si>
+  <si>
     <t>COMMON_AGREE_TEXT</t>
   </si>
   <si>
-    <t>공용 동의 텍스트</t>
-  </si>
-  <si>
     <t>동의</t>
   </si>
   <si>
     <t>Agree</t>
   </si>
   <si>
+    <t>공용 결과 텍스트</t>
+  </si>
+  <si>
     <t>COMMON_RESULT_TEXT</t>
   </si>
   <si>
-    <t>공용 결과 텍스트</t>
-  </si>
-  <si>
     <t>결과</t>
   </si>
   <si>
     <t>Result</t>
   </si>
   <si>
+    <t>공용 획득 텍스트</t>
+  </si>
+  <si>
     <t>COMMON_GET_TEXT</t>
   </si>
   <si>
-    <t>공용 획득 텍스트</t>
-  </si>
-  <si>
     <t>획득</t>
   </si>
   <si>
     <t>Get</t>
   </si>
   <si>
+    <t>공용 상점 텍스트</t>
+  </si>
+  <si>
     <t>COMMON_STORE_TEXT</t>
   </si>
   <si>
-    <t>공용 상점 텍스트</t>
-  </si>
-  <si>
     <t>상점</t>
   </si>
   <si>
     <t>Store</t>
   </si>
   <si>
+    <t>공용 이벤트 텍스트</t>
+  </si>
+  <si>
     <t>COMMON_EVENT_TEXT</t>
   </si>
   <si>
-    <t>공용 이벤트 텍스트</t>
-  </si>
-  <si>
     <t>이벤트</t>
   </si>
   <si>
     <t>Event</t>
   </si>
   <si>
+    <t>공용 다음 텍스트</t>
+  </si>
+  <si>
     <t>COMMON_NEXT_TEXT</t>
   </si>
   <si>
-    <t>공용 다음 텍스트</t>
-  </si>
-  <si>
     <t>다음</t>
   </si>
   <si>
     <t>Next</t>
   </si>
   <si>
+    <t>공용 홈 텍스트</t>
+  </si>
+  <si>
     <t>COMMON_HOME_TEXT</t>
   </si>
   <si>
-    <t>공용 홈 텍스트</t>
-  </si>
-  <si>
     <t>홈</t>
   </si>
   <si>
     <t>Home</t>
   </si>
   <si>
+    <t>공용 플레이 텍스트</t>
+  </si>
+  <si>
     <t>COMMON_PLAY_TEXT</t>
   </si>
   <si>
-    <t>공용 플레이 텍스트</t>
-  </si>
-  <si>
     <t>플레이</t>
   </si>
   <si>
     <t>Play</t>
   </si>
   <si>
+    <t>공용 재시도 텍스트</t>
+  </si>
+  <si>
     <t>COMMON_RETRY_TEXT</t>
   </si>
   <si>
-    <t>공용 재시도 텍스트</t>
-  </si>
-  <si>
     <t>재시도</t>
   </si>
   <si>
     <t>Retry</t>
   </si>
   <si>
+    <t>공용 나가기 텍스트</t>
+  </si>
+  <si>
     <t>COMMON_LEAVE_TEXT</t>
   </si>
   <si>
-    <t>공용 나가기 텍스트</t>
-  </si>
-  <si>
     <t>나가기</t>
   </si>
   <si>
     <t>Leave</t>
   </si>
   <si>
+    <t>공용 동기화 텍스트</t>
+  </si>
+  <si>
     <t>COMMON_SYNC_TEXT</t>
   </si>
   <si>
-    <t>공용 동기화 텍스트</t>
-  </si>
-  <si>
     <t>동기화</t>
   </si>
   <si>
     <t>Sync</t>
   </si>
   <si>
+    <t>공용 로그인 텍스트</t>
+  </si>
+  <si>
     <t>COMMON_LOGIN_TEXT</t>
   </si>
   <si>
-    <t>공용 로그인 텍스트</t>
-  </si>
-  <si>
     <t>로그인</t>
   </si>
   <si>
     <t>Login</t>
   </si>
   <si>
+    <t>공용 애플 로그인 텍스트</t>
+  </si>
+  <si>
     <t>COMMON_APPLE_LOGIN_TEXT</t>
   </si>
   <si>
-    <t>공용 애플 로그인 텍스트</t>
-  </si>
-  <si>
     <t>애플 로그인</t>
   </si>
   <si>
     <t>Sign in with Apple</t>
   </si>
   <si>
+    <t>공용 페이스 북 로그인</t>
+  </si>
+  <si>
     <t>COMMON_FACEBOOK_LOGIN_TEXT</t>
   </si>
   <si>
-    <t>공용 페이스 북 로그인</t>
-  </si>
-  <si>
     <t>페이스 북 로그인</t>
   </si>
   <si>
     <t>Sign in with Facebook</t>
   </si>
   <si>
+    <t>공용 로그아웃 텍스트</t>
+  </si>
+  <si>
     <t>COMMON_LOGOUT_TEXT</t>
   </si>
   <si>
-    <t>공용 로그아웃 텍스트</t>
-  </si>
-  <si>
     <t>로그아웃</t>
   </si>
   <si>
     <t>Logout</t>
   </si>
   <si>
+    <t>공용 연결 해제 텍스트</t>
+  </si>
+  <si>
     <t>COMMON_DISCONNECT_TEXT</t>
   </si>
   <si>
-    <t>공용 연결 해제 텍스트</t>
-  </si>
-  <si>
     <t>연결 해제</t>
   </si>
   <si>
     <t>Disconnect</t>
   </si>
   <si>
+    <t>공용 로드 텍스트</t>
+  </si>
+  <si>
     <t>COMMON_LOAD_TEXT</t>
   </si>
   <si>
-    <t>공용 로드 텍스트</t>
-  </si>
-  <si>
     <t>불러오기</t>
   </si>
   <si>
     <t>Load</t>
   </si>
   <si>
+    <t>공용 저장 텍스트</t>
+  </si>
+  <si>
     <t>COMMON_SAVE_TEXT</t>
   </si>
   <si>
-    <t>공용 저장 텍스트</t>
-  </si>
-  <si>
     <t>저장하기</t>
   </si>
   <si>
     <t>Save</t>
   </si>
   <si>
+    <t>공용 이어하기 텍스트</t>
+  </si>
+  <si>
     <t>COMMON_CONTINUE_TEXT</t>
   </si>
   <si>
-    <t>공용 이어하기 텍스트</t>
-  </si>
-  <si>
     <t>이어하기</t>
   </si>
   <si>
     <t>Continue</t>
   </si>
   <si>
+    <t>공용 알림 텍스트</t>
+  </si>
+  <si>
     <t>COMMON_NOTI_TEXT</t>
   </si>
   <si>
-    <t>공용 알림 텍스트</t>
+    <t>공용 평가 텍스트</t>
   </si>
   <si>
     <t>COMMON_REVIEW_TEXT</t>
   </si>
   <si>
-    <t>공용 평가 텍스트</t>
-  </si>
-  <si>
     <t>평가</t>
   </si>
   <si>
     <t>Review</t>
   </si>
   <si>
+    <t>공용 지원 텍스트</t>
+  </si>
+  <si>
     <t>COMMON_SUPPORTS_TEXT</t>
   </si>
   <si>
-    <t>공용 지원 텍스트</t>
-  </si>
-  <si>
     <t>문의</t>
   </si>
   <si>
     <t>Supports</t>
   </si>
   <si>
+    <t>공용 배경음 텍스트</t>
+  </si>
+  <si>
     <t>COMMON_BG_SND_TEXT</t>
   </si>
   <si>
-    <t>공용 배경음 텍스트</t>
-  </si>
-  <si>
     <t>배경음</t>
   </si>
   <si>
     <t>BGM</t>
   </si>
   <si>
+    <t>공용 효과음 텍스트</t>
+  </si>
+  <si>
     <t>COMMON_FX_SNDS_TEXT</t>
   </si>
   <si>
-    <t>공용 효과음 텍스트</t>
-  </si>
-  <si>
     <t>효과음</t>
   </si>
   <si>
     <t>SFX</t>
   </si>
   <si>
+    <t>공용 광고 시청 텍스트</t>
+  </si>
+  <si>
     <t>COMMON_WATCH_ADS_TEXT</t>
   </si>
   <si>
-    <t>공용 광고 시청 텍스트</t>
-  </si>
-  <si>
     <t>광고 시청</t>
   </si>
   <si>
     <t>Watch Ads</t>
   </si>
   <si>
+    <t>공용 결제 복원 텍스트</t>
+  </si>
+  <si>
     <t>COMMON_RESTORE_PAYMENT_TEXT</t>
   </si>
   <si>
-    <t>공용 결제 복원 텍스트</t>
-  </si>
-  <si>
     <t>결제 복원</t>
   </si>
   <si>
     <t>Restore Payment</t>
   </si>
   <si>
+    <t>공용 레벨 텍스트</t>
+  </si>
+  <si>
     <t>COMMON_LEVEL_TEXT</t>
   </si>
   <si>
-    <t>공용 레벨 텍스트</t>
-  </si>
-  <si>
     <t>레벨</t>
   </si>
   <si>
     <t>Level</t>
   </si>
   <si>
+    <t>공용 스테이지 텍스트</t>
+  </si>
+  <si>
     <t>COMMON_STAGE_TEXT</t>
   </si>
   <si>
-    <t>공용 스테이지 텍스트</t>
-  </si>
-  <si>
     <t>스테이지</t>
   </si>
   <si>
     <t>Stage</t>
   </si>
   <si>
+    <t>공용 챕터 텍스트</t>
+  </si>
+  <si>
     <t>COMMON_CHAPTER_TEXT</t>
   </si>
   <si>
-    <t>공용 챕터 텍스트</t>
-  </si>
-  <si>
     <t>챕터</t>
   </si>
   <si>
     <t>Chapter</t>
   </si>
   <si>
+    <t>공용 레벨 번호 텍스트 형식</t>
+  </si>
+  <si>
     <t>COMMON_LEVEL_NUM_TEXT_FMT</t>
   </si>
   <si>
-    <t>공용 레벨 번호 텍스트 형식</t>
-  </si>
-  <si>
     <t>레벨 {0}</t>
   </si>
   <si>
     <t>Level {0}</t>
   </si>
   <si>
+    <t>공용 스테이지 번호 텍스트 형식</t>
+  </si>
+  <si>
     <t>COMMON_STAGE_NUM_TEXT_FMT</t>
   </si>
   <si>
-    <t>공용 스테이지 번호 텍스트 형식</t>
-  </si>
-  <si>
     <t>스테이지 {0}</t>
   </si>
   <si>
     <t>Stage {0}</t>
   </si>
   <si>
+    <t>공용 챕터 번호 텍스트 형식</t>
+  </si>
+  <si>
     <t>COMMON_CHAPTER_NUM_TEXT_FMT</t>
   </si>
   <si>
-    <t>공용 챕터 번호 텍스트 형식</t>
-  </si>
-  <si>
     <t>챕터 {0}</t>
   </si>
   <si>
     <t>Chapter {0}</t>
   </si>
   <si>
+    <t>공용 레벨 페이지 텍스트 형식</t>
+  </si>
+  <si>
     <t>COMMON_LEVEL_PAGE_TEXT_FMT</t>
   </si>
   <si>
-    <t>공용 레벨 페이지 텍스트 형식</t>
-  </si>
-  <si>
     <t>레벨 {0}/{1}</t>
   </si>
   <si>
     <t>Level {0}/{1}</t>
   </si>
   <si>
+    <t>공용 스테이지 페이지 텍스트 형식</t>
+  </si>
+  <si>
     <t>COMMON_STAGE_PAGE_TEXT_FMT</t>
   </si>
   <si>
-    <t>공용 스테이지 페이지 텍스트 형식</t>
-  </si>
-  <si>
     <t>스테이지 {0}/{1}</t>
   </si>
   <si>
     <t>Stage {0}/{1}</t>
   </si>
   <si>
+    <t>공용 챕터 페이지 텍스트 형식</t>
+  </si>
+  <si>
     <t>COMMON_CHAPTER_PAGE_TEXT_FMT</t>
   </si>
   <si>
-    <t>공용 챕터 페이지 텍스트 형식</t>
-  </si>
-  <si>
     <t>챕터 {0}/{1}</t>
   </si>
   <si>
     <t>Chapter {0}/{1}</t>
   </si>
   <si>
+    <t>상점 팝업 타이틀</t>
+  </si>
+  <si>
     <t>STORE_P_TITLE</t>
   </si>
   <si>
-    <t>상점 팝업 타이틀</t>
+    <t>설정 팝업 타이틀</t>
   </si>
   <si>
     <t>SETTINGS_P_TITLE</t>
   </si>
   <si>
-    <t>설정 팝업 타이틀</t>
-  </si>
-  <si>
     <t>설정</t>
   </si>
   <si>
     <t>Settings</t>
   </si>
   <si>
+    <t>동기화 팝업 타이틀</t>
+  </si>
+  <si>
     <t>SYNC_P_TITLE</t>
   </si>
   <si>
-    <t>동기화 팝업 타이틀</t>
+    <t>일일 미션 팝업 타이틀</t>
   </si>
   <si>
     <t>DAILY_MP_TITLE</t>
   </si>
   <si>
-    <t>일일 미션 팝업 타이틀</t>
-  </si>
-  <si>
     <t>일일 미션</t>
   </si>
   <si>
     <t>Daily Mission</t>
   </si>
   <si>
+    <t>무료 보상 팝업 타이틀</t>
+  </si>
+  <si>
     <t>FREE_RP_TITLE</t>
   </si>
   <si>
-    <t>무료 보상 팝업 타이틀</t>
-  </si>
-  <si>
     <t>무료 보상</t>
   </si>
   <si>
     <t>Free Reward</t>
   </si>
   <si>
+    <t>일일 보상 팝업 타이틀</t>
+  </si>
+  <si>
     <t>DAILY_RP_TITLE</t>
   </si>
   <si>
-    <t>일일 보상 팝업 타이틀</t>
-  </si>
-  <si>
     <t>일일 보상</t>
   </si>
   <si>
     <t>Daily Reward</t>
   </si>
   <si>
+    <t>판매 코인 팝업 타이틀</t>
+  </si>
+  <si>
     <t>SALE_CP_TITLE</t>
   </si>
   <si>
-    <t>판매 코인 팝업 타이틀</t>
-  </si>
-  <si>
     <t>판매 코인</t>
   </si>
   <si>
     <t>Sale Coins</t>
   </si>
   <si>
+    <t>이어하기 팝업 타이틀</t>
+  </si>
+  <si>
     <t>CONTINUE_P_TITLE</t>
   </si>
   <si>
-    <t>이어하기 팝업 타이틀</t>
+    <t>결과 팝업 제목</t>
   </si>
   <si>
     <t>RESULT_P_TITLE</t>
-  </si>
-  <si>
-    <t>결과 팝업 제목</t>
   </si>
 </sst>
 </file>
@@ -961,7 +961,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="9">
     <border/>
     <border>
       <left style="thin">
@@ -977,9 +977,22 @@
       </top>
     </border>
     <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
     </border>
     <border>
       <left style="thin">
@@ -994,11 +1007,19 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="34">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1012,7 +1033,8 @@
     <xf borderId="2" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="3" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1021,18 +1043,20 @@
     <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="3" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf borderId="6" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="7" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="7" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
@@ -1042,7 +1066,7 @@
     <xf borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="3" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1051,18 +1075,20 @@
     <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="6" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="3" fillId="5" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="2" fillId="5" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="5" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="3" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1071,13 +1097,13 @@
     <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="4" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="6" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="5" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="5" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -1293,9 +1319,9 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="37.71"/>
+    <col customWidth="1" min="1" max="1" width="26.29"/>
     <col customWidth="1" min="2" max="2" width="14.43"/>
-    <col customWidth="1" min="3" max="3" width="29.0"/>
+    <col customWidth="1" min="3" max="3" width="37.29"/>
     <col customWidth="1" min="4" max="4" width="98.14"/>
     <col customWidth="1" min="5" max="5" width="112.0"/>
     <col customWidth="1" min="6" max="6" width="14.43"/>
@@ -1374,2781 +1400,2857 @@
       <c r="W2" s="4"/>
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
+      <c r="Z2" s="5"/>
     </row>
     <row r="3" ht="15.0" customHeight="1">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="7">
         <v>0.0</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
-      <c r="U3" s="7"/>
-      <c r="V3" s="7"/>
-      <c r="W3" s="7"/>
-      <c r="X3" s="7"/>
-      <c r="Y3" s="7"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
+      <c r="Q3" s="8"/>
+      <c r="R3" s="8"/>
+      <c r="S3" s="8"/>
+      <c r="T3" s="8"/>
+      <c r="U3" s="8"/>
+      <c r="V3" s="8"/>
+      <c r="W3" s="8"/>
+      <c r="X3" s="8"/>
+      <c r="Y3" s="8"/>
+      <c r="Z3" s="9"/>
     </row>
     <row r="4" ht="15.0" customHeight="1">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="7">
         <v>0.0</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="7"/>
-      <c r="T4" s="7"/>
-      <c r="U4" s="7"/>
-      <c r="V4" s="7"/>
-      <c r="W4" s="7"/>
-      <c r="X4" s="7"/>
-      <c r="Y4" s="7"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
+      <c r="Q4" s="8"/>
+      <c r="R4" s="8"/>
+      <c r="S4" s="8"/>
+      <c r="T4" s="8"/>
+      <c r="U4" s="8"/>
+      <c r="V4" s="8"/>
+      <c r="W4" s="8"/>
+      <c r="X4" s="8"/>
+      <c r="Y4" s="8"/>
+      <c r="Z4" s="9"/>
     </row>
     <row r="5" ht="15.0" customHeight="1">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="7">
         <v>0.0</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="7"/>
-      <c r="S5" s="7"/>
-      <c r="T5" s="7"/>
-      <c r="U5" s="7"/>
-      <c r="V5" s="7"/>
-      <c r="W5" s="7"/>
-      <c r="X5" s="7"/>
-      <c r="Y5" s="7"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
+      <c r="Q5" s="8"/>
+      <c r="R5" s="8"/>
+      <c r="S5" s="8"/>
+      <c r="T5" s="8"/>
+      <c r="U5" s="8"/>
+      <c r="V5" s="8"/>
+      <c r="W5" s="8"/>
+      <c r="X5" s="8"/>
+      <c r="Y5" s="8"/>
+      <c r="Z5" s="9"/>
     </row>
     <row r="6" ht="15.0" customHeight="1">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="7">
         <v>0.0</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="7"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="7"/>
-      <c r="T6" s="7"/>
-      <c r="U6" s="7"/>
-      <c r="V6" s="7"/>
-      <c r="W6" s="7"/>
-      <c r="X6" s="7"/>
-      <c r="Y6" s="7"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="8"/>
+      <c r="Q6" s="8"/>
+      <c r="R6" s="8"/>
+      <c r="S6" s="8"/>
+      <c r="T6" s="8"/>
+      <c r="U6" s="8"/>
+      <c r="V6" s="8"/>
+      <c r="W6" s="8"/>
+      <c r="X6" s="8"/>
+      <c r="Y6" s="8"/>
+      <c r="Z6" s="9"/>
     </row>
     <row r="7" ht="15.0" customHeight="1">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="7">
         <v>0.0</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="7"/>
-      <c r="R7" s="7"/>
-      <c r="S7" s="7"/>
-      <c r="T7" s="7"/>
-      <c r="U7" s="7"/>
-      <c r="V7" s="7"/>
-      <c r="W7" s="7"/>
-      <c r="X7" s="7"/>
-      <c r="Y7" s="7"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+      <c r="S7" s="8"/>
+      <c r="T7" s="8"/>
+      <c r="U7" s="8"/>
+      <c r="V7" s="8"/>
+      <c r="W7" s="8"/>
+      <c r="X7" s="8"/>
+      <c r="Y7" s="8"/>
+      <c r="Z7" s="9"/>
     </row>
     <row r="8" ht="15.0" customHeight="1">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="7">
         <v>0.0</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
-      <c r="P8" s="7"/>
-      <c r="Q8" s="7"/>
-      <c r="R8" s="7"/>
-      <c r="S8" s="7"/>
-      <c r="T8" s="7"/>
-      <c r="U8" s="7"/>
-      <c r="V8" s="7"/>
-      <c r="W8" s="7"/>
-      <c r="X8" s="7"/>
-      <c r="Y8" s="7"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+      <c r="S8" s="8"/>
+      <c r="T8" s="8"/>
+      <c r="U8" s="8"/>
+      <c r="V8" s="8"/>
+      <c r="W8" s="8"/>
+      <c r="X8" s="8"/>
+      <c r="Y8" s="8"/>
+      <c r="Z8" s="9"/>
     </row>
     <row r="9" ht="15.0" customHeight="1">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="7">
         <v>0.0</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7"/>
-      <c r="P9" s="7"/>
-      <c r="Q9" s="7"/>
-      <c r="R9" s="7"/>
-      <c r="S9" s="7"/>
-      <c r="T9" s="7"/>
-      <c r="U9" s="7"/>
-      <c r="V9" s="7"/>
-      <c r="W9" s="7"/>
-      <c r="X9" s="7"/>
-      <c r="Y9" s="7"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="8"/>
+      <c r="S9" s="8"/>
+      <c r="T9" s="8"/>
+      <c r="U9" s="8"/>
+      <c r="V9" s="8"/>
+      <c r="W9" s="8"/>
+      <c r="X9" s="8"/>
+      <c r="Y9" s="8"/>
+      <c r="Z9" s="9"/>
     </row>
     <row r="10" ht="15.0" customHeight="1">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="7">
         <v>0.0</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
-      <c r="O10" s="7"/>
-      <c r="P10" s="7"/>
-      <c r="Q10" s="7"/>
-      <c r="R10" s="7"/>
-      <c r="S10" s="7"/>
-      <c r="T10" s="7"/>
-      <c r="U10" s="7"/>
-      <c r="V10" s="7"/>
-      <c r="W10" s="7"/>
-      <c r="X10" s="7"/>
-      <c r="Y10" s="7"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="8"/>
+      <c r="S10" s="8"/>
+      <c r="T10" s="8"/>
+      <c r="U10" s="8"/>
+      <c r="V10" s="8"/>
+      <c r="W10" s="8"/>
+      <c r="X10" s="8"/>
+      <c r="Y10" s="8"/>
+      <c r="Z10" s="9"/>
     </row>
     <row r="11" ht="15.0" customHeight="1">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="7">
         <v>0.0</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="7"/>
-      <c r="O11" s="7"/>
-      <c r="P11" s="7"/>
-      <c r="Q11" s="7"/>
-      <c r="R11" s="7"/>
-      <c r="S11" s="7"/>
-      <c r="T11" s="7"/>
-      <c r="U11" s="7"/>
-      <c r="V11" s="7"/>
-      <c r="W11" s="7"/>
-      <c r="X11" s="7"/>
-      <c r="Y11" s="7"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
+      <c r="Q11" s="8"/>
+      <c r="R11" s="8"/>
+      <c r="S11" s="8"/>
+      <c r="T11" s="8"/>
+      <c r="U11" s="8"/>
+      <c r="V11" s="8"/>
+      <c r="W11" s="8"/>
+      <c r="X11" s="8"/>
+      <c r="Y11" s="8"/>
+      <c r="Z11" s="9"/>
     </row>
     <row r="12" ht="15.0" customHeight="1">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="7">
         <v>0.0</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
-      <c r="P12" s="7"/>
-      <c r="Q12" s="7"/>
-      <c r="R12" s="7"/>
-      <c r="S12" s="7"/>
-      <c r="T12" s="7"/>
-      <c r="U12" s="7"/>
-      <c r="V12" s="7"/>
-      <c r="W12" s="7"/>
-      <c r="X12" s="7"/>
-      <c r="Y12" s="7"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
+      <c r="Q12" s="8"/>
+      <c r="R12" s="8"/>
+      <c r="S12" s="8"/>
+      <c r="T12" s="8"/>
+      <c r="U12" s="8"/>
+      <c r="V12" s="8"/>
+      <c r="W12" s="8"/>
+      <c r="X12" s="8"/>
+      <c r="Y12" s="8"/>
+      <c r="Z12" s="9"/>
     </row>
     <row r="13" ht="15.0" customHeight="1">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="7">
         <v>0.0</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="7"/>
-      <c r="R13" s="7"/>
-      <c r="S13" s="7"/>
-      <c r="T13" s="7"/>
-      <c r="U13" s="7"/>
-      <c r="V13" s="7"/>
-      <c r="W13" s="7"/>
-      <c r="X13" s="7"/>
-      <c r="Y13" s="7"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
+      <c r="Q13" s="8"/>
+      <c r="R13" s="8"/>
+      <c r="S13" s="8"/>
+      <c r="T13" s="8"/>
+      <c r="U13" s="8"/>
+      <c r="V13" s="8"/>
+      <c r="W13" s="8"/>
+      <c r="X13" s="8"/>
+      <c r="Y13" s="8"/>
+      <c r="Z13" s="9"/>
     </row>
     <row r="14" ht="15.0" customHeight="1">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="7">
         <v>0.0</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
-      <c r="O14" s="7"/>
-      <c r="P14" s="7"/>
-      <c r="Q14" s="7"/>
-      <c r="R14" s="7"/>
-      <c r="S14" s="7"/>
-      <c r="T14" s="7"/>
-      <c r="U14" s="7"/>
-      <c r="V14" s="7"/>
-      <c r="W14" s="7"/>
-      <c r="X14" s="7"/>
-      <c r="Y14" s="7"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8"/>
+      <c r="Q14" s="8"/>
+      <c r="R14" s="8"/>
+      <c r="S14" s="8"/>
+      <c r="T14" s="8"/>
+      <c r="U14" s="8"/>
+      <c r="V14" s="8"/>
+      <c r="W14" s="8"/>
+      <c r="X14" s="8"/>
+      <c r="Y14" s="8"/>
+      <c r="Z14" s="9"/>
     </row>
     <row r="15" ht="15.0" customHeight="1">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="7">
         <v>0.0</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
-      <c r="P15" s="7"/>
-      <c r="Q15" s="7"/>
-      <c r="R15" s="7"/>
-      <c r="S15" s="7"/>
-      <c r="T15" s="7"/>
-      <c r="U15" s="7"/>
-      <c r="V15" s="7"/>
-      <c r="W15" s="7"/>
-      <c r="X15" s="7"/>
-      <c r="Y15" s="7"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8"/>
+      <c r="O15" s="8"/>
+      <c r="P15" s="8"/>
+      <c r="Q15" s="8"/>
+      <c r="R15" s="8"/>
+      <c r="S15" s="8"/>
+      <c r="T15" s="8"/>
+      <c r="U15" s="8"/>
+      <c r="V15" s="8"/>
+      <c r="W15" s="8"/>
+      <c r="X15" s="8"/>
+      <c r="Y15" s="8"/>
+      <c r="Z15" s="9"/>
     </row>
     <row r="16" ht="15.0" customHeight="1">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="7">
         <v>0.0</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="7"/>
-      <c r="Q16" s="7"/>
-      <c r="R16" s="7"/>
-      <c r="S16" s="7"/>
-      <c r="T16" s="7"/>
-      <c r="U16" s="7"/>
-      <c r="V16" s="7"/>
-      <c r="W16" s="7"/>
-      <c r="X16" s="7"/>
-      <c r="Y16" s="7"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8"/>
+      <c r="Q16" s="8"/>
+      <c r="R16" s="8"/>
+      <c r="S16" s="8"/>
+      <c r="T16" s="8"/>
+      <c r="U16" s="8"/>
+      <c r="V16" s="8"/>
+      <c r="W16" s="8"/>
+      <c r="X16" s="8"/>
+      <c r="Y16" s="8"/>
+      <c r="Z16" s="9"/>
     </row>
     <row r="17" ht="15.0" customHeight="1">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="7">
         <v>0.0</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="7"/>
-      <c r="O17" s="7"/>
-      <c r="P17" s="7"/>
-      <c r="Q17" s="7"/>
-      <c r="R17" s="7"/>
-      <c r="S17" s="7"/>
-      <c r="T17" s="7"/>
-      <c r="U17" s="7"/>
-      <c r="V17" s="7"/>
-      <c r="W17" s="7"/>
-      <c r="X17" s="7"/>
-      <c r="Y17" s="7"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8"/>
+      <c r="P17" s="8"/>
+      <c r="Q17" s="8"/>
+      <c r="R17" s="8"/>
+      <c r="S17" s="8"/>
+      <c r="T17" s="8"/>
+      <c r="U17" s="8"/>
+      <c r="V17" s="8"/>
+      <c r="W17" s="8"/>
+      <c r="X17" s="8"/>
+      <c r="Y17" s="8"/>
+      <c r="Z17" s="9"/>
     </row>
     <row r="18" ht="15.0" customHeight="1">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B18" s="7">
         <v>0.0</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="7"/>
-      <c r="O18" s="7"/>
-      <c r="P18" s="7"/>
-      <c r="Q18" s="7"/>
-      <c r="R18" s="7"/>
-      <c r="S18" s="7"/>
-      <c r="T18" s="7"/>
-      <c r="U18" s="7"/>
-      <c r="V18" s="7"/>
-      <c r="W18" s="7"/>
-      <c r="X18" s="7"/>
-      <c r="Y18" s="7"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
+      <c r="O18" s="8"/>
+      <c r="P18" s="8"/>
+      <c r="Q18" s="8"/>
+      <c r="R18" s="8"/>
+      <c r="S18" s="8"/>
+      <c r="T18" s="8"/>
+      <c r="U18" s="8"/>
+      <c r="V18" s="8"/>
+      <c r="W18" s="8"/>
+      <c r="X18" s="8"/>
+      <c r="Y18" s="8"/>
+      <c r="Z18" s="9"/>
     </row>
     <row r="19" ht="15.0" customHeight="1">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19" s="12">
         <v>0.0</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="7"/>
-      <c r="N19" s="7"/>
-      <c r="O19" s="7"/>
-      <c r="P19" s="7"/>
-      <c r="Q19" s="7"/>
-      <c r="R19" s="7"/>
-      <c r="S19" s="7"/>
-      <c r="T19" s="7"/>
-      <c r="U19" s="7"/>
-      <c r="V19" s="7"/>
-      <c r="W19" s="7"/>
-      <c r="X19" s="7"/>
-      <c r="Y19" s="7"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13"/>
+      <c r="L19" s="13"/>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13"/>
+      <c r="P19" s="13"/>
+      <c r="Q19" s="13"/>
+      <c r="R19" s="13"/>
+      <c r="S19" s="13"/>
+      <c r="T19" s="13"/>
+      <c r="U19" s="13"/>
+      <c r="V19" s="13"/>
+      <c r="W19" s="13"/>
+      <c r="X19" s="13"/>
+      <c r="Y19" s="13"/>
+      <c r="Z19" s="14"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="B20" s="13">
+      <c r="B20" s="16">
         <v>0.0</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C20" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="D20" s="14" t="s">
+      <c r="D20" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="E20" s="14" t="s">
+      <c r="E20" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="14"/>
-      <c r="K20" s="14"/>
-      <c r="L20" s="14"/>
-      <c r="M20" s="14"/>
-      <c r="N20" s="14"/>
-      <c r="O20" s="14"/>
-      <c r="P20" s="14"/>
-      <c r="Q20" s="14"/>
-      <c r="R20" s="14"/>
-      <c r="S20" s="14"/>
-      <c r="T20" s="14"/>
-      <c r="U20" s="14"/>
-      <c r="V20" s="14"/>
-      <c r="W20" s="14"/>
-      <c r="X20" s="14"/>
-      <c r="Y20" s="14"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="17"/>
+      <c r="M20" s="17"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="17"/>
+      <c r="P20" s="17"/>
+      <c r="Q20" s="17"/>
+      <c r="R20" s="17"/>
+      <c r="S20" s="17"/>
+      <c r="T20" s="17"/>
+      <c r="U20" s="17"/>
+      <c r="V20" s="17"/>
+      <c r="W20" s="17"/>
+      <c r="X20" s="17"/>
+      <c r="Y20" s="17"/>
+      <c r="Z20" s="5"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="B21" s="16">
+      <c r="B21" s="19">
         <v>0.0</v>
       </c>
-      <c r="C21" s="17" t="s">
+      <c r="C21" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="D21" s="17" t="s">
+      <c r="D21" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="E21" s="17" t="s">
+      <c r="E21" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="17"/>
-      <c r="L21" s="17"/>
-      <c r="M21" s="17"/>
-      <c r="N21" s="17"/>
-      <c r="O21" s="17"/>
-      <c r="P21" s="17"/>
-      <c r="Q21" s="17"/>
-      <c r="R21" s="17"/>
-      <c r="S21" s="17"/>
-      <c r="T21" s="17"/>
-      <c r="U21" s="17"/>
-      <c r="V21" s="17"/>
-      <c r="W21" s="17"/>
-      <c r="X21" s="17"/>
-      <c r="Y21" s="17"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
+      <c r="O21" s="20"/>
+      <c r="P21" s="20"/>
+      <c r="Q21" s="20"/>
+      <c r="R21" s="20"/>
+      <c r="S21" s="20"/>
+      <c r="T21" s="20"/>
+      <c r="U21" s="20"/>
+      <c r="V21" s="20"/>
+      <c r="W21" s="20"/>
+      <c r="X21" s="20"/>
+      <c r="Y21" s="20"/>
+      <c r="Z21" s="9"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="B22" s="16">
+      <c r="B22" s="19">
         <v>0.0</v>
       </c>
-      <c r="C22" s="17" t="s">
+      <c r="C22" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="D22" s="17" t="s">
+      <c r="D22" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="E22" s="17" t="s">
+      <c r="E22" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="17"/>
-      <c r="L22" s="17"/>
-      <c r="M22" s="17"/>
-      <c r="N22" s="17"/>
-      <c r="O22" s="17"/>
-      <c r="P22" s="17"/>
-      <c r="Q22" s="17"/>
-      <c r="R22" s="17"/>
-      <c r="S22" s="17"/>
-      <c r="T22" s="17"/>
-      <c r="U22" s="17"/>
-      <c r="V22" s="17"/>
-      <c r="W22" s="17"/>
-      <c r="X22" s="17"/>
-      <c r="Y22" s="17"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="20"/>
+      <c r="R22" s="20"/>
+      <c r="S22" s="20"/>
+      <c r="T22" s="20"/>
+      <c r="U22" s="20"/>
+      <c r="V22" s="20"/>
+      <c r="W22" s="20"/>
+      <c r="X22" s="20"/>
+      <c r="Y22" s="20"/>
+      <c r="Z22" s="9"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="B23" s="16">
+      <c r="B23" s="19">
         <v>0.0</v>
       </c>
-      <c r="C23" s="17" t="s">
+      <c r="C23" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="D23" s="17" t="s">
+      <c r="D23" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="E23" s="17" t="s">
+      <c r="E23" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="17"/>
-      <c r="K23" s="17"/>
-      <c r="L23" s="17"/>
-      <c r="M23" s="17"/>
-      <c r="N23" s="17"/>
-      <c r="O23" s="17"/>
-      <c r="P23" s="17"/>
-      <c r="Q23" s="17"/>
-      <c r="R23" s="17"/>
-      <c r="S23" s="17"/>
-      <c r="T23" s="17"/>
-      <c r="U23" s="17"/>
-      <c r="V23" s="17"/>
-      <c r="W23" s="17"/>
-      <c r="X23" s="17"/>
-      <c r="Y23" s="17"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20"/>
+      <c r="R23" s="20"/>
+      <c r="S23" s="20"/>
+      <c r="T23" s="20"/>
+      <c r="U23" s="20"/>
+      <c r="V23" s="20"/>
+      <c r="W23" s="20"/>
+      <c r="X23" s="20"/>
+      <c r="Y23" s="20"/>
+      <c r="Z23" s="9"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="15" t="s">
+      <c r="A24" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="B24" s="16">
+      <c r="B24" s="19">
         <v>0.0</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="C24" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="D24" s="17" t="s">
+      <c r="D24" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="E24" s="17" t="s">
+      <c r="E24" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="17"/>
-      <c r="L24" s="17"/>
-      <c r="M24" s="17"/>
-      <c r="N24" s="17"/>
-      <c r="O24" s="17"/>
-      <c r="P24" s="17"/>
-      <c r="Q24" s="17"/>
-      <c r="R24" s="17"/>
-      <c r="S24" s="17"/>
-      <c r="T24" s="17"/>
-      <c r="U24" s="17"/>
-      <c r="V24" s="17"/>
-      <c r="W24" s="17"/>
-      <c r="X24" s="17"/>
-      <c r="Y24" s="17"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+      <c r="M24" s="20"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20"/>
+      <c r="R24" s="20"/>
+      <c r="S24" s="20"/>
+      <c r="T24" s="20"/>
+      <c r="U24" s="20"/>
+      <c r="V24" s="20"/>
+      <c r="W24" s="20"/>
+      <c r="X24" s="20"/>
+      <c r="Y24" s="20"/>
+      <c r="Z24" s="9"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="15" t="s">
+      <c r="A25" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="B25" s="16">
+      <c r="B25" s="19">
         <v>0.0</v>
       </c>
-      <c r="C25" s="17" t="s">
+      <c r="C25" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="D25" s="17" t="s">
+      <c r="D25" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="E25" s="17" t="s">
+      <c r="E25" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="17"/>
-      <c r="L25" s="17"/>
-      <c r="M25" s="17"/>
-      <c r="N25" s="17"/>
-      <c r="O25" s="17"/>
-      <c r="P25" s="17"/>
-      <c r="Q25" s="17"/>
-      <c r="R25" s="17"/>
-      <c r="S25" s="17"/>
-      <c r="T25" s="17"/>
-      <c r="U25" s="17"/>
-      <c r="V25" s="17"/>
-      <c r="W25" s="17"/>
-      <c r="X25" s="17"/>
-      <c r="Y25" s="17"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="20"/>
+      <c r="R25" s="20"/>
+      <c r="S25" s="20"/>
+      <c r="T25" s="20"/>
+      <c r="U25" s="20"/>
+      <c r="V25" s="20"/>
+      <c r="W25" s="20"/>
+      <c r="X25" s="20"/>
+      <c r="Y25" s="20"/>
+      <c r="Z25" s="9"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="15" t="s">
+      <c r="A26" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="B26" s="16">
+      <c r="B26" s="19">
         <v>0.0</v>
       </c>
-      <c r="C26" s="17" t="s">
+      <c r="C26" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D26" s="17" t="s">
+      <c r="D26" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E26" s="17" t="s">
+      <c r="E26" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="17"/>
-      <c r="I26" s="17"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="17"/>
-      <c r="L26" s="17"/>
-      <c r="M26" s="17"/>
-      <c r="N26" s="17"/>
-      <c r="O26" s="17"/>
-      <c r="P26" s="17"/>
-      <c r="Q26" s="17"/>
-      <c r="R26" s="17"/>
-      <c r="S26" s="17"/>
-      <c r="T26" s="17"/>
-      <c r="U26" s="17"/>
-      <c r="V26" s="17"/>
-      <c r="W26" s="17"/>
-      <c r="X26" s="17"/>
-      <c r="Y26" s="17"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="20"/>
+      <c r="K26" s="20"/>
+      <c r="L26" s="20"/>
+      <c r="M26" s="20"/>
+      <c r="N26" s="20"/>
+      <c r="O26" s="20"/>
+      <c r="P26" s="20"/>
+      <c r="Q26" s="20"/>
+      <c r="R26" s="20"/>
+      <c r="S26" s="20"/>
+      <c r="T26" s="20"/>
+      <c r="U26" s="20"/>
+      <c r="V26" s="20"/>
+      <c r="W26" s="20"/>
+      <c r="X26" s="20"/>
+      <c r="Y26" s="20"/>
+      <c r="Z26" s="9"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="15" t="s">
+      <c r="A27" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="B27" s="16">
+      <c r="B27" s="19">
         <v>0.0</v>
       </c>
-      <c r="C27" s="17" t="s">
+      <c r="C27" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="D27" s="17" t="s">
+      <c r="D27" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="E27" s="17" t="s">
+      <c r="E27" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="17"/>
-      <c r="I27" s="17"/>
-      <c r="J27" s="17"/>
-      <c r="K27" s="17"/>
-      <c r="L27" s="17"/>
-      <c r="M27" s="17"/>
-      <c r="N27" s="17"/>
-      <c r="O27" s="17"/>
-      <c r="P27" s="17"/>
-      <c r="Q27" s="17"/>
-      <c r="R27" s="17"/>
-      <c r="S27" s="17"/>
-      <c r="T27" s="17"/>
-      <c r="U27" s="17"/>
-      <c r="V27" s="17"/>
-      <c r="W27" s="17"/>
-      <c r="X27" s="17"/>
-      <c r="Y27" s="17"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="20"/>
+      <c r="K27" s="20"/>
+      <c r="L27" s="20"/>
+      <c r="M27" s="20"/>
+      <c r="N27" s="20"/>
+      <c r="O27" s="20"/>
+      <c r="P27" s="20"/>
+      <c r="Q27" s="20"/>
+      <c r="R27" s="20"/>
+      <c r="S27" s="20"/>
+      <c r="T27" s="20"/>
+      <c r="U27" s="20"/>
+      <c r="V27" s="20"/>
+      <c r="W27" s="20"/>
+      <c r="X27" s="20"/>
+      <c r="Y27" s="20"/>
+      <c r="Z27" s="9"/>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="15" t="s">
+      <c r="A28" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="B28" s="16">
+      <c r="B28" s="19">
         <v>0.0</v>
       </c>
-      <c r="C28" s="17" t="s">
+      <c r="C28" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="D28" s="17" t="s">
+      <c r="D28" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="E28" s="17" t="s">
+      <c r="E28" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="17"/>
-      <c r="I28" s="17"/>
-      <c r="J28" s="17"/>
-      <c r="K28" s="17"/>
-      <c r="L28" s="17"/>
-      <c r="M28" s="17"/>
-      <c r="N28" s="17"/>
-      <c r="O28" s="17"/>
-      <c r="P28" s="17"/>
-      <c r="Q28" s="17"/>
-      <c r="R28" s="17"/>
-      <c r="S28" s="17"/>
-      <c r="T28" s="17"/>
-      <c r="U28" s="17"/>
-      <c r="V28" s="17"/>
-      <c r="W28" s="17"/>
-      <c r="X28" s="17"/>
-      <c r="Y28" s="17"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="20"/>
+      <c r="K28" s="20"/>
+      <c r="L28" s="20"/>
+      <c r="M28" s="20"/>
+      <c r="N28" s="20"/>
+      <c r="O28" s="20"/>
+      <c r="P28" s="20"/>
+      <c r="Q28" s="20"/>
+      <c r="R28" s="20"/>
+      <c r="S28" s="20"/>
+      <c r="T28" s="20"/>
+      <c r="U28" s="20"/>
+      <c r="V28" s="20"/>
+      <c r="W28" s="20"/>
+      <c r="X28" s="20"/>
+      <c r="Y28" s="20"/>
+      <c r="Z28" s="9"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="15" t="s">
+      <c r="A29" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="B29" s="16">
+      <c r="B29" s="19">
         <v>0.0</v>
       </c>
-      <c r="C29" s="17" t="s">
+      <c r="C29" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="D29" s="17" t="s">
+      <c r="D29" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="E29" s="17" t="s">
+      <c r="E29" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17"/>
-      <c r="H29" s="17"/>
-      <c r="I29" s="17"/>
-      <c r="J29" s="17"/>
-      <c r="K29" s="17"/>
-      <c r="L29" s="17"/>
-      <c r="M29" s="17"/>
-      <c r="N29" s="17"/>
-      <c r="O29" s="17"/>
-      <c r="P29" s="17"/>
-      <c r="Q29" s="17"/>
-      <c r="R29" s="17"/>
-      <c r="S29" s="17"/>
-      <c r="T29" s="17"/>
-      <c r="U29" s="17"/>
-      <c r="V29" s="17"/>
-      <c r="W29" s="17"/>
-      <c r="X29" s="17"/>
-      <c r="Y29" s="17"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="20"/>
+      <c r="K29" s="20"/>
+      <c r="L29" s="20"/>
+      <c r="M29" s="20"/>
+      <c r="N29" s="20"/>
+      <c r="O29" s="20"/>
+      <c r="P29" s="20"/>
+      <c r="Q29" s="20"/>
+      <c r="R29" s="20"/>
+      <c r="S29" s="20"/>
+      <c r="T29" s="20"/>
+      <c r="U29" s="20"/>
+      <c r="V29" s="20"/>
+      <c r="W29" s="20"/>
+      <c r="X29" s="20"/>
+      <c r="Y29" s="20"/>
+      <c r="Z29" s="9"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="15" t="s">
+      <c r="A30" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="B30" s="16">
+      <c r="B30" s="19">
         <v>0.0</v>
       </c>
-      <c r="C30" s="17" t="s">
+      <c r="C30" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="D30" s="17" t="s">
+      <c r="D30" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="E30" s="17" t="s">
+      <c r="E30" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="17"/>
-      <c r="I30" s="17"/>
-      <c r="J30" s="17"/>
-      <c r="K30" s="17"/>
-      <c r="L30" s="17"/>
-      <c r="M30" s="17"/>
-      <c r="N30" s="17"/>
-      <c r="O30" s="17"/>
-      <c r="P30" s="17"/>
-      <c r="Q30" s="17"/>
-      <c r="R30" s="17"/>
-      <c r="S30" s="17"/>
-      <c r="T30" s="17"/>
-      <c r="U30" s="17"/>
-      <c r="V30" s="17"/>
-      <c r="W30" s="17"/>
-      <c r="X30" s="17"/>
-      <c r="Y30" s="17"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="20"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="20"/>
+      <c r="K30" s="20"/>
+      <c r="L30" s="20"/>
+      <c r="M30" s="20"/>
+      <c r="N30" s="20"/>
+      <c r="O30" s="20"/>
+      <c r="P30" s="20"/>
+      <c r="Q30" s="20"/>
+      <c r="R30" s="20"/>
+      <c r="S30" s="20"/>
+      <c r="T30" s="20"/>
+      <c r="U30" s="20"/>
+      <c r="V30" s="20"/>
+      <c r="W30" s="20"/>
+      <c r="X30" s="20"/>
+      <c r="Y30" s="20"/>
+      <c r="Z30" s="9"/>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="15" t="s">
+      <c r="A31" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="B31" s="16">
+      <c r="B31" s="19">
         <v>0.0</v>
       </c>
-      <c r="C31" s="17" t="s">
+      <c r="C31" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="D31" s="17" t="s">
+      <c r="D31" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="E31" s="17" t="s">
+      <c r="E31" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="17"/>
-      <c r="I31" s="17"/>
-      <c r="J31" s="17"/>
-      <c r="K31" s="17"/>
-      <c r="L31" s="17"/>
-      <c r="M31" s="17"/>
-      <c r="N31" s="17"/>
-      <c r="O31" s="17"/>
-      <c r="P31" s="17"/>
-      <c r="Q31" s="17"/>
-      <c r="R31" s="17"/>
-      <c r="S31" s="17"/>
-      <c r="T31" s="17"/>
-      <c r="U31" s="17"/>
-      <c r="V31" s="17"/>
-      <c r="W31" s="17"/>
-      <c r="X31" s="17"/>
-      <c r="Y31" s="17"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="20"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="20"/>
+      <c r="K31" s="20"/>
+      <c r="L31" s="20"/>
+      <c r="M31" s="20"/>
+      <c r="N31" s="20"/>
+      <c r="O31" s="20"/>
+      <c r="P31" s="20"/>
+      <c r="Q31" s="20"/>
+      <c r="R31" s="20"/>
+      <c r="S31" s="20"/>
+      <c r="T31" s="20"/>
+      <c r="U31" s="20"/>
+      <c r="V31" s="20"/>
+      <c r="W31" s="20"/>
+      <c r="X31" s="20"/>
+      <c r="Y31" s="20"/>
+      <c r="Z31" s="9"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="15" t="s">
+      <c r="A32" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="B32" s="16">
+      <c r="B32" s="19">
         <v>0.0</v>
       </c>
-      <c r="C32" s="17" t="s">
+      <c r="C32" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="D32" s="17" t="s">
+      <c r="D32" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="E32" s="17" t="s">
+      <c r="E32" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="F32" s="17"/>
-      <c r="G32" s="17"/>
-      <c r="H32" s="17"/>
-      <c r="I32" s="17"/>
-      <c r="J32" s="17"/>
-      <c r="K32" s="17"/>
-      <c r="L32" s="17"/>
-      <c r="M32" s="17"/>
-      <c r="N32" s="17"/>
-      <c r="O32" s="17"/>
-      <c r="P32" s="17"/>
-      <c r="Q32" s="17"/>
-      <c r="R32" s="17"/>
-      <c r="S32" s="17"/>
-      <c r="T32" s="17"/>
-      <c r="U32" s="17"/>
-      <c r="V32" s="17"/>
-      <c r="W32" s="17"/>
-      <c r="X32" s="17"/>
-      <c r="Y32" s="17"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="20"/>
+      <c r="K32" s="20"/>
+      <c r="L32" s="20"/>
+      <c r="M32" s="20"/>
+      <c r="N32" s="20"/>
+      <c r="O32" s="20"/>
+      <c r="P32" s="20"/>
+      <c r="Q32" s="20"/>
+      <c r="R32" s="20"/>
+      <c r="S32" s="20"/>
+      <c r="T32" s="20"/>
+      <c r="U32" s="20"/>
+      <c r="V32" s="20"/>
+      <c r="W32" s="20"/>
+      <c r="X32" s="20"/>
+      <c r="Y32" s="20"/>
+      <c r="Z32" s="9"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="15" t="s">
+      <c r="A33" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="B33" s="16">
+      <c r="B33" s="19">
         <v>0.0</v>
       </c>
-      <c r="C33" s="17" t="s">
+      <c r="C33" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="D33" s="17" t="s">
+      <c r="D33" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="17" t="s">
+      <c r="E33" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="17"/>
-      <c r="I33" s="17"/>
-      <c r="J33" s="17"/>
-      <c r="K33" s="17"/>
-      <c r="L33" s="17"/>
-      <c r="M33" s="17"/>
-      <c r="N33" s="17"/>
-      <c r="O33" s="17"/>
-      <c r="P33" s="17"/>
-      <c r="Q33" s="17"/>
-      <c r="R33" s="17"/>
-      <c r="S33" s="17"/>
-      <c r="T33" s="17"/>
-      <c r="U33" s="17"/>
-      <c r="V33" s="17"/>
-      <c r="W33" s="17"/>
-      <c r="X33" s="17"/>
-      <c r="Y33" s="17"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+      <c r="H33" s="20"/>
+      <c r="I33" s="20"/>
+      <c r="J33" s="20"/>
+      <c r="K33" s="20"/>
+      <c r="L33" s="20"/>
+      <c r="M33" s="20"/>
+      <c r="N33" s="20"/>
+      <c r="O33" s="20"/>
+      <c r="P33" s="20"/>
+      <c r="Q33" s="20"/>
+      <c r="R33" s="20"/>
+      <c r="S33" s="20"/>
+      <c r="T33" s="20"/>
+      <c r="U33" s="20"/>
+      <c r="V33" s="20"/>
+      <c r="W33" s="20"/>
+      <c r="X33" s="20"/>
+      <c r="Y33" s="20"/>
+      <c r="Z33" s="9"/>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="15" t="s">
+      <c r="A34" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="B34" s="16">
+      <c r="B34" s="19">
         <v>0.0</v>
       </c>
-      <c r="C34" s="17" t="s">
+      <c r="C34" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="D34" s="17" t="s">
+      <c r="D34" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="E34" s="17" t="s">
+      <c r="E34" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="F34" s="17"/>
-      <c r="G34" s="17"/>
-      <c r="H34" s="17"/>
-      <c r="I34" s="17"/>
-      <c r="J34" s="17"/>
-      <c r="K34" s="17"/>
-      <c r="L34" s="17"/>
-      <c r="M34" s="17"/>
-      <c r="N34" s="17"/>
-      <c r="O34" s="17"/>
-      <c r="P34" s="17"/>
-      <c r="Q34" s="17"/>
-      <c r="R34" s="17"/>
-      <c r="S34" s="17"/>
-      <c r="T34" s="17"/>
-      <c r="U34" s="17"/>
-      <c r="V34" s="17"/>
-      <c r="W34" s="17"/>
-      <c r="X34" s="17"/>
-      <c r="Y34" s="17"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="20"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="20"/>
+      <c r="K34" s="20"/>
+      <c r="L34" s="20"/>
+      <c r="M34" s="20"/>
+      <c r="N34" s="20"/>
+      <c r="O34" s="20"/>
+      <c r="P34" s="20"/>
+      <c r="Q34" s="20"/>
+      <c r="R34" s="20"/>
+      <c r="S34" s="20"/>
+      <c r="T34" s="20"/>
+      <c r="U34" s="20"/>
+      <c r="V34" s="20"/>
+      <c r="W34" s="20"/>
+      <c r="X34" s="20"/>
+      <c r="Y34" s="20"/>
+      <c r="Z34" s="9"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="15" t="s">
+      <c r="A35" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="B35" s="16">
+      <c r="B35" s="19">
         <v>0.0</v>
       </c>
-      <c r="C35" s="17" t="s">
+      <c r="C35" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="D35" s="17" t="s">
+      <c r="D35" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="E35" s="17" t="s">
+      <c r="E35" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="F35" s="17"/>
-      <c r="G35" s="17"/>
-      <c r="H35" s="17"/>
-      <c r="I35" s="17"/>
-      <c r="J35" s="17"/>
-      <c r="K35" s="17"/>
-      <c r="L35" s="17"/>
-      <c r="M35" s="17"/>
-      <c r="N35" s="17"/>
-      <c r="O35" s="17"/>
-      <c r="P35" s="17"/>
-      <c r="Q35" s="17"/>
-      <c r="R35" s="17"/>
-      <c r="S35" s="17"/>
-      <c r="T35" s="17"/>
-      <c r="U35" s="17"/>
-      <c r="V35" s="17"/>
-      <c r="W35" s="17"/>
-      <c r="X35" s="17"/>
-      <c r="Y35" s="17"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
+      <c r="H35" s="20"/>
+      <c r="I35" s="20"/>
+      <c r="J35" s="20"/>
+      <c r="K35" s="20"/>
+      <c r="L35" s="20"/>
+      <c r="M35" s="20"/>
+      <c r="N35" s="20"/>
+      <c r="O35" s="20"/>
+      <c r="P35" s="20"/>
+      <c r="Q35" s="20"/>
+      <c r="R35" s="20"/>
+      <c r="S35" s="20"/>
+      <c r="T35" s="20"/>
+      <c r="U35" s="20"/>
+      <c r="V35" s="20"/>
+      <c r="W35" s="20"/>
+      <c r="X35" s="20"/>
+      <c r="Y35" s="20"/>
+      <c r="Z35" s="9"/>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="15" t="s">
+      <c r="A36" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="B36" s="16">
+      <c r="B36" s="19">
         <v>0.0</v>
       </c>
-      <c r="C36" s="17" t="s">
+      <c r="C36" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="D36" s="17" t="s">
+      <c r="D36" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="E36" s="17" t="s">
+      <c r="E36" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="F36" s="17"/>
-      <c r="G36" s="17"/>
-      <c r="H36" s="17"/>
-      <c r="I36" s="17"/>
-      <c r="J36" s="17"/>
-      <c r="K36" s="17"/>
-      <c r="L36" s="17"/>
-      <c r="M36" s="17"/>
-      <c r="N36" s="17"/>
-      <c r="O36" s="17"/>
-      <c r="P36" s="17"/>
-      <c r="Q36" s="17"/>
-      <c r="R36" s="17"/>
-      <c r="S36" s="17"/>
-      <c r="T36" s="17"/>
-      <c r="U36" s="17"/>
-      <c r="V36" s="17"/>
-      <c r="W36" s="17"/>
-      <c r="X36" s="17"/>
-      <c r="Y36" s="17"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
+      <c r="H36" s="20"/>
+      <c r="I36" s="20"/>
+      <c r="J36" s="20"/>
+      <c r="K36" s="20"/>
+      <c r="L36" s="20"/>
+      <c r="M36" s="20"/>
+      <c r="N36" s="20"/>
+      <c r="O36" s="20"/>
+      <c r="P36" s="20"/>
+      <c r="Q36" s="20"/>
+      <c r="R36" s="20"/>
+      <c r="S36" s="20"/>
+      <c r="T36" s="20"/>
+      <c r="U36" s="20"/>
+      <c r="V36" s="20"/>
+      <c r="W36" s="20"/>
+      <c r="X36" s="20"/>
+      <c r="Y36" s="20"/>
+      <c r="Z36" s="9"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="15" t="s">
+      <c r="A37" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="B37" s="16">
+      <c r="B37" s="19">
         <v>0.0</v>
       </c>
-      <c r="C37" s="17" t="s">
+      <c r="C37" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="D37" s="17" t="s">
+      <c r="D37" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="E37" s="17" t="s">
+      <c r="E37" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="F37" s="17"/>
-      <c r="G37" s="17"/>
-      <c r="H37" s="17"/>
-      <c r="I37" s="17"/>
-      <c r="J37" s="17"/>
-      <c r="K37" s="17"/>
-      <c r="L37" s="17"/>
-      <c r="M37" s="17"/>
-      <c r="N37" s="17"/>
-      <c r="O37" s="17"/>
-      <c r="P37" s="17"/>
-      <c r="Q37" s="17"/>
-      <c r="R37" s="17"/>
-      <c r="S37" s="17"/>
-      <c r="T37" s="17"/>
-      <c r="U37" s="17"/>
-      <c r="V37" s="17"/>
-      <c r="W37" s="17"/>
-      <c r="X37" s="17"/>
-      <c r="Y37" s="17"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="20"/>
+      <c r="H37" s="20"/>
+      <c r="I37" s="20"/>
+      <c r="J37" s="20"/>
+      <c r="K37" s="20"/>
+      <c r="L37" s="20"/>
+      <c r="M37" s="20"/>
+      <c r="N37" s="20"/>
+      <c r="O37" s="20"/>
+      <c r="P37" s="20"/>
+      <c r="Q37" s="20"/>
+      <c r="R37" s="20"/>
+      <c r="S37" s="20"/>
+      <c r="T37" s="20"/>
+      <c r="U37" s="20"/>
+      <c r="V37" s="20"/>
+      <c r="W37" s="20"/>
+      <c r="X37" s="20"/>
+      <c r="Y37" s="20"/>
+      <c r="Z37" s="9"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="15" t="s">
+      <c r="A38" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="B38" s="16">
+      <c r="B38" s="19">
         <v>0.0</v>
       </c>
-      <c r="C38" s="17" t="s">
+      <c r="C38" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="D38" s="17" t="s">
+      <c r="D38" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="E38" s="17" t="s">
+      <c r="E38" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="F38" s="17"/>
-      <c r="G38" s="17"/>
-      <c r="H38" s="17"/>
-      <c r="I38" s="17"/>
-      <c r="J38" s="17"/>
-      <c r="K38" s="17"/>
-      <c r="L38" s="17"/>
-      <c r="M38" s="17"/>
-      <c r="N38" s="17"/>
-      <c r="O38" s="17"/>
-      <c r="P38" s="17"/>
-      <c r="Q38" s="17"/>
-      <c r="R38" s="17"/>
-      <c r="S38" s="17"/>
-      <c r="T38" s="17"/>
-      <c r="U38" s="17"/>
-      <c r="V38" s="17"/>
-      <c r="W38" s="17"/>
-      <c r="X38" s="17"/>
-      <c r="Y38" s="17"/>
+      <c r="F38" s="20"/>
+      <c r="G38" s="20"/>
+      <c r="H38" s="20"/>
+      <c r="I38" s="20"/>
+      <c r="J38" s="20"/>
+      <c r="K38" s="20"/>
+      <c r="L38" s="20"/>
+      <c r="M38" s="20"/>
+      <c r="N38" s="20"/>
+      <c r="O38" s="20"/>
+      <c r="P38" s="20"/>
+      <c r="Q38" s="20"/>
+      <c r="R38" s="20"/>
+      <c r="S38" s="20"/>
+      <c r="T38" s="20"/>
+      <c r="U38" s="20"/>
+      <c r="V38" s="20"/>
+      <c r="W38" s="20"/>
+      <c r="X38" s="20"/>
+      <c r="Y38" s="20"/>
+      <c r="Z38" s="9"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="15" t="s">
+      <c r="A39" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="B39" s="16">
+      <c r="B39" s="19">
         <v>0.0</v>
       </c>
-      <c r="C39" s="17" t="s">
+      <c r="C39" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="D39" s="17" t="s">
+      <c r="D39" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="E39" s="17" t="s">
+      <c r="E39" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="F39" s="17"/>
-      <c r="G39" s="17"/>
-      <c r="H39" s="17"/>
-      <c r="I39" s="17"/>
-      <c r="J39" s="17"/>
-      <c r="K39" s="17"/>
-      <c r="L39" s="17"/>
-      <c r="M39" s="17"/>
-      <c r="N39" s="17"/>
-      <c r="O39" s="17"/>
-      <c r="P39" s="17"/>
-      <c r="Q39" s="17"/>
-      <c r="R39" s="17"/>
-      <c r="S39" s="17"/>
-      <c r="T39" s="17"/>
-      <c r="U39" s="17"/>
-      <c r="V39" s="17"/>
-      <c r="W39" s="17"/>
-      <c r="X39" s="17"/>
-      <c r="Y39" s="17"/>
+      <c r="F39" s="20"/>
+      <c r="G39" s="20"/>
+      <c r="H39" s="20"/>
+      <c r="I39" s="20"/>
+      <c r="J39" s="20"/>
+      <c r="K39" s="20"/>
+      <c r="L39" s="20"/>
+      <c r="M39" s="20"/>
+      <c r="N39" s="20"/>
+      <c r="O39" s="20"/>
+      <c r="P39" s="20"/>
+      <c r="Q39" s="20"/>
+      <c r="R39" s="20"/>
+      <c r="S39" s="20"/>
+      <c r="T39" s="20"/>
+      <c r="U39" s="20"/>
+      <c r="V39" s="20"/>
+      <c r="W39" s="20"/>
+      <c r="X39" s="20"/>
+      <c r="Y39" s="20"/>
+      <c r="Z39" s="9"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="15" t="s">
+      <c r="A40" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="B40" s="16">
+      <c r="B40" s="19">
         <v>0.0</v>
       </c>
-      <c r="C40" s="17" t="s">
+      <c r="C40" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="D40" s="17" t="s">
+      <c r="D40" s="20" t="s">
         <v>159</v>
       </c>
-      <c r="E40" s="17" t="s">
+      <c r="E40" s="20" t="s">
         <v>160</v>
       </c>
-      <c r="F40" s="17"/>
-      <c r="G40" s="17"/>
-      <c r="H40" s="17"/>
-      <c r="I40" s="17"/>
-      <c r="J40" s="17"/>
-      <c r="K40" s="17"/>
-      <c r="L40" s="17"/>
-      <c r="M40" s="17"/>
-      <c r="N40" s="17"/>
-      <c r="O40" s="17"/>
-      <c r="P40" s="17"/>
-      <c r="Q40" s="17"/>
-      <c r="R40" s="17"/>
-      <c r="S40" s="17"/>
-      <c r="T40" s="17"/>
-      <c r="U40" s="17"/>
-      <c r="V40" s="17"/>
-      <c r="W40" s="17"/>
-      <c r="X40" s="17"/>
-      <c r="Y40" s="17"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="20"/>
+      <c r="H40" s="20"/>
+      <c r="I40" s="20"/>
+      <c r="J40" s="20"/>
+      <c r="K40" s="20"/>
+      <c r="L40" s="20"/>
+      <c r="M40" s="20"/>
+      <c r="N40" s="20"/>
+      <c r="O40" s="20"/>
+      <c r="P40" s="20"/>
+      <c r="Q40" s="20"/>
+      <c r="R40" s="20"/>
+      <c r="S40" s="20"/>
+      <c r="T40" s="20"/>
+      <c r="U40" s="20"/>
+      <c r="V40" s="20"/>
+      <c r="W40" s="20"/>
+      <c r="X40" s="20"/>
+      <c r="Y40" s="20"/>
+      <c r="Z40" s="9"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="15" t="s">
+      <c r="A41" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B41" s="16">
+      <c r="B41" s="19">
         <v>0.0</v>
       </c>
-      <c r="C41" s="17" t="s">
+      <c r="C41" s="20" t="s">
         <v>162</v>
       </c>
-      <c r="D41" s="17" t="s">
+      <c r="D41" s="20" t="s">
         <v>163</v>
       </c>
-      <c r="E41" s="17" t="s">
+      <c r="E41" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="F41" s="17"/>
-      <c r="G41" s="17"/>
-      <c r="H41" s="17"/>
-      <c r="I41" s="17"/>
-      <c r="J41" s="17"/>
-      <c r="K41" s="17"/>
-      <c r="L41" s="17"/>
-      <c r="M41" s="17"/>
-      <c r="N41" s="17"/>
-      <c r="O41" s="17"/>
-      <c r="P41" s="17"/>
-      <c r="Q41" s="17"/>
-      <c r="R41" s="17"/>
-      <c r="S41" s="17"/>
-      <c r="T41" s="17"/>
-      <c r="U41" s="17"/>
-      <c r="V41" s="17"/>
-      <c r="W41" s="17"/>
-      <c r="X41" s="17"/>
-      <c r="Y41" s="17"/>
+      <c r="F41" s="20"/>
+      <c r="G41" s="20"/>
+      <c r="H41" s="20"/>
+      <c r="I41" s="20"/>
+      <c r="J41" s="20"/>
+      <c r="K41" s="20"/>
+      <c r="L41" s="20"/>
+      <c r="M41" s="20"/>
+      <c r="N41" s="20"/>
+      <c r="O41" s="20"/>
+      <c r="P41" s="20"/>
+      <c r="Q41" s="20"/>
+      <c r="R41" s="20"/>
+      <c r="S41" s="20"/>
+      <c r="T41" s="20"/>
+      <c r="U41" s="20"/>
+      <c r="V41" s="20"/>
+      <c r="W41" s="20"/>
+      <c r="X41" s="20"/>
+      <c r="Y41" s="20"/>
+      <c r="Z41" s="9"/>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="15" t="s">
+      <c r="A42" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="B42" s="16">
+      <c r="B42" s="19">
         <v>0.0</v>
       </c>
-      <c r="C42" s="17" t="s">
+      <c r="C42" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="D42" s="17" t="s">
+      <c r="D42" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="E42" s="17" t="s">
+      <c r="E42" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="F42" s="17"/>
-      <c r="G42" s="17"/>
-      <c r="H42" s="17"/>
-      <c r="I42" s="17"/>
-      <c r="J42" s="17"/>
-      <c r="K42" s="17"/>
-      <c r="L42" s="17"/>
-      <c r="M42" s="17"/>
-      <c r="N42" s="17"/>
-      <c r="O42" s="17"/>
-      <c r="P42" s="17"/>
-      <c r="Q42" s="17"/>
-      <c r="R42" s="17"/>
-      <c r="S42" s="17"/>
-      <c r="T42" s="17"/>
-      <c r="U42" s="17"/>
-      <c r="V42" s="17"/>
-      <c r="W42" s="17"/>
-      <c r="X42" s="17"/>
-      <c r="Y42" s="17"/>
+      <c r="F42" s="20"/>
+      <c r="G42" s="20"/>
+      <c r="H42" s="20"/>
+      <c r="I42" s="20"/>
+      <c r="J42" s="20"/>
+      <c r="K42" s="20"/>
+      <c r="L42" s="20"/>
+      <c r="M42" s="20"/>
+      <c r="N42" s="20"/>
+      <c r="O42" s="20"/>
+      <c r="P42" s="20"/>
+      <c r="Q42" s="20"/>
+      <c r="R42" s="20"/>
+      <c r="S42" s="20"/>
+      <c r="T42" s="20"/>
+      <c r="U42" s="20"/>
+      <c r="V42" s="20"/>
+      <c r="W42" s="20"/>
+      <c r="X42" s="20"/>
+      <c r="Y42" s="20"/>
+      <c r="Z42" s="9"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="15" t="s">
+      <c r="A43" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="B43" s="16">
+      <c r="B43" s="19">
         <v>0.0</v>
       </c>
-      <c r="C43" s="17" t="s">
+      <c r="C43" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="D43" s="17" t="s">
+      <c r="D43" s="20" t="s">
         <v>171</v>
       </c>
-      <c r="E43" s="17" t="s">
+      <c r="E43" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="F43" s="17"/>
-      <c r="G43" s="17"/>
-      <c r="H43" s="17"/>
-      <c r="I43" s="17"/>
-      <c r="J43" s="17"/>
-      <c r="K43" s="17"/>
-      <c r="L43" s="17"/>
-      <c r="M43" s="17"/>
-      <c r="N43" s="17"/>
-      <c r="O43" s="17"/>
-      <c r="P43" s="17"/>
-      <c r="Q43" s="17"/>
-      <c r="R43" s="17"/>
-      <c r="S43" s="17"/>
-      <c r="T43" s="17"/>
-      <c r="U43" s="17"/>
-      <c r="V43" s="17"/>
-      <c r="W43" s="17"/>
-      <c r="X43" s="17"/>
-      <c r="Y43" s="17"/>
+      <c r="F43" s="20"/>
+      <c r="G43" s="20"/>
+      <c r="H43" s="20"/>
+      <c r="I43" s="20"/>
+      <c r="J43" s="20"/>
+      <c r="K43" s="20"/>
+      <c r="L43" s="20"/>
+      <c r="M43" s="20"/>
+      <c r="N43" s="20"/>
+      <c r="O43" s="20"/>
+      <c r="P43" s="20"/>
+      <c r="Q43" s="20"/>
+      <c r="R43" s="20"/>
+      <c r="S43" s="20"/>
+      <c r="T43" s="20"/>
+      <c r="U43" s="20"/>
+      <c r="V43" s="20"/>
+      <c r="W43" s="20"/>
+      <c r="X43" s="20"/>
+      <c r="Y43" s="20"/>
+      <c r="Z43" s="9"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="15" t="s">
+      <c r="A44" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="B44" s="16">
+      <c r="B44" s="19">
         <v>0.0</v>
       </c>
-      <c r="C44" s="17" t="s">
+      <c r="C44" s="20" t="s">
         <v>174</v>
       </c>
-      <c r="D44" s="17" t="s">
+      <c r="D44" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="E44" s="17" t="s">
+      <c r="E44" s="20" t="s">
         <v>176</v>
       </c>
-      <c r="F44" s="17"/>
-      <c r="G44" s="17"/>
-      <c r="H44" s="17"/>
-      <c r="I44" s="17"/>
-      <c r="J44" s="17"/>
-      <c r="K44" s="17"/>
-      <c r="L44" s="17"/>
-      <c r="M44" s="17"/>
-      <c r="N44" s="17"/>
-      <c r="O44" s="17"/>
-      <c r="P44" s="17"/>
-      <c r="Q44" s="17"/>
-      <c r="R44" s="17"/>
-      <c r="S44" s="17"/>
-      <c r="T44" s="17"/>
-      <c r="U44" s="17"/>
-      <c r="V44" s="17"/>
-      <c r="W44" s="17"/>
-      <c r="X44" s="17"/>
-      <c r="Y44" s="17"/>
+      <c r="F44" s="20"/>
+      <c r="G44" s="20"/>
+      <c r="H44" s="20"/>
+      <c r="I44" s="20"/>
+      <c r="J44" s="20"/>
+      <c r="K44" s="20"/>
+      <c r="L44" s="20"/>
+      <c r="M44" s="20"/>
+      <c r="N44" s="20"/>
+      <c r="O44" s="20"/>
+      <c r="P44" s="20"/>
+      <c r="Q44" s="20"/>
+      <c r="R44" s="20"/>
+      <c r="S44" s="20"/>
+      <c r="T44" s="20"/>
+      <c r="U44" s="20"/>
+      <c r="V44" s="20"/>
+      <c r="W44" s="20"/>
+      <c r="X44" s="20"/>
+      <c r="Y44" s="20"/>
+      <c r="Z44" s="9"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="15" t="s">
+      <c r="A45" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="B45" s="16">
+      <c r="B45" s="19">
         <v>0.0</v>
       </c>
-      <c r="C45" s="17" t="s">
+      <c r="C45" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="D45" s="17" t="s">
+      <c r="D45" s="20" t="s">
         <v>179</v>
       </c>
-      <c r="E45" s="17" t="s">
+      <c r="E45" s="20" t="s">
         <v>180</v>
       </c>
-      <c r="F45" s="17"/>
-      <c r="G45" s="17"/>
-      <c r="H45" s="17"/>
-      <c r="I45" s="17"/>
-      <c r="J45" s="17"/>
-      <c r="K45" s="17"/>
-      <c r="L45" s="17"/>
-      <c r="M45" s="17"/>
-      <c r="N45" s="17"/>
-      <c r="O45" s="17"/>
-      <c r="P45" s="17"/>
-      <c r="Q45" s="17"/>
-      <c r="R45" s="17"/>
-      <c r="S45" s="17"/>
-      <c r="T45" s="17"/>
-      <c r="U45" s="17"/>
-      <c r="V45" s="17"/>
-      <c r="W45" s="17"/>
-      <c r="X45" s="17"/>
-      <c r="Y45" s="17"/>
+      <c r="F45" s="20"/>
+      <c r="G45" s="20"/>
+      <c r="H45" s="20"/>
+      <c r="I45" s="20"/>
+      <c r="J45" s="20"/>
+      <c r="K45" s="20"/>
+      <c r="L45" s="20"/>
+      <c r="M45" s="20"/>
+      <c r="N45" s="20"/>
+      <c r="O45" s="20"/>
+      <c r="P45" s="20"/>
+      <c r="Q45" s="20"/>
+      <c r="R45" s="20"/>
+      <c r="S45" s="20"/>
+      <c r="T45" s="20"/>
+      <c r="U45" s="20"/>
+      <c r="V45" s="20"/>
+      <c r="W45" s="20"/>
+      <c r="X45" s="20"/>
+      <c r="Y45" s="20"/>
+      <c r="Z45" s="9"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="15" t="s">
+      <c r="A46" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="B46" s="16">
+      <c r="B46" s="19">
         <v>0.0</v>
       </c>
-      <c r="C46" s="17" t="s">
+      <c r="C46" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="D46" s="17" t="s">
+      <c r="D46" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="E46" s="17" t="s">
+      <c r="E46" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="F46" s="17"/>
-      <c r="G46" s="17"/>
-      <c r="H46" s="17"/>
-      <c r="I46" s="17"/>
-      <c r="J46" s="17"/>
-      <c r="K46" s="17"/>
-      <c r="L46" s="17"/>
-      <c r="M46" s="17"/>
-      <c r="N46" s="17"/>
-      <c r="O46" s="17"/>
-      <c r="P46" s="17"/>
-      <c r="Q46" s="17"/>
-      <c r="R46" s="17"/>
-      <c r="S46" s="17"/>
-      <c r="T46" s="17"/>
-      <c r="U46" s="17"/>
-      <c r="V46" s="17"/>
-      <c r="W46" s="17"/>
-      <c r="X46" s="17"/>
-      <c r="Y46" s="17"/>
+      <c r="F46" s="20"/>
+      <c r="G46" s="20"/>
+      <c r="H46" s="20"/>
+      <c r="I46" s="20"/>
+      <c r="J46" s="20"/>
+      <c r="K46" s="20"/>
+      <c r="L46" s="20"/>
+      <c r="M46" s="20"/>
+      <c r="N46" s="20"/>
+      <c r="O46" s="20"/>
+      <c r="P46" s="20"/>
+      <c r="Q46" s="20"/>
+      <c r="R46" s="20"/>
+      <c r="S46" s="20"/>
+      <c r="T46" s="20"/>
+      <c r="U46" s="20"/>
+      <c r="V46" s="20"/>
+      <c r="W46" s="20"/>
+      <c r="X46" s="20"/>
+      <c r="Y46" s="20"/>
+      <c r="Z46" s="9"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="15" t="s">
+      <c r="A47" s="18" t="s">
         <v>185</v>
       </c>
-      <c r="B47" s="16">
+      <c r="B47" s="19">
         <v>0.0</v>
       </c>
-      <c r="C47" s="17" t="s">
+      <c r="C47" s="20" t="s">
         <v>186</v>
       </c>
-      <c r="D47" s="17" t="s">
+      <c r="D47" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="E47" s="17" t="s">
+      <c r="E47" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="F47" s="17"/>
-      <c r="G47" s="17"/>
-      <c r="H47" s="17"/>
-      <c r="I47" s="17"/>
-      <c r="J47" s="17"/>
-      <c r="K47" s="17"/>
-      <c r="L47" s="17"/>
-      <c r="M47" s="17"/>
-      <c r="N47" s="17"/>
-      <c r="O47" s="17"/>
-      <c r="P47" s="17"/>
-      <c r="Q47" s="17"/>
-      <c r="R47" s="17"/>
-      <c r="S47" s="17"/>
-      <c r="T47" s="17"/>
-      <c r="U47" s="17"/>
-      <c r="V47" s="17"/>
-      <c r="W47" s="17"/>
-      <c r="X47" s="17"/>
-      <c r="Y47" s="17"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="20"/>
+      <c r="H47" s="20"/>
+      <c r="I47" s="20"/>
+      <c r="J47" s="20"/>
+      <c r="K47" s="20"/>
+      <c r="L47" s="20"/>
+      <c r="M47" s="20"/>
+      <c r="N47" s="20"/>
+      <c r="O47" s="20"/>
+      <c r="P47" s="20"/>
+      <c r="Q47" s="20"/>
+      <c r="R47" s="20"/>
+      <c r="S47" s="20"/>
+      <c r="T47" s="20"/>
+      <c r="U47" s="20"/>
+      <c r="V47" s="20"/>
+      <c r="W47" s="20"/>
+      <c r="X47" s="20"/>
+      <c r="Y47" s="20"/>
+      <c r="Z47" s="9"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="15" t="s">
+      <c r="A48" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="B48" s="16">
+      <c r="B48" s="19">
         <v>0.0</v>
       </c>
-      <c r="C48" s="17" t="s">
+      <c r="C48" s="20" t="s">
         <v>190</v>
       </c>
-      <c r="D48" s="17" t="s">
+      <c r="D48" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="E48" s="17" t="s">
+      <c r="E48" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="F48" s="17"/>
-      <c r="G48" s="17"/>
-      <c r="H48" s="17"/>
-      <c r="I48" s="17"/>
-      <c r="J48" s="17"/>
-      <c r="K48" s="17"/>
-      <c r="L48" s="17"/>
-      <c r="M48" s="17"/>
-      <c r="N48" s="17"/>
-      <c r="O48" s="17"/>
-      <c r="P48" s="17"/>
-      <c r="Q48" s="17"/>
-      <c r="R48" s="17"/>
-      <c r="S48" s="17"/>
-      <c r="T48" s="17"/>
-      <c r="U48" s="17"/>
-      <c r="V48" s="17"/>
-      <c r="W48" s="17"/>
-      <c r="X48" s="17"/>
-      <c r="Y48" s="17"/>
+      <c r="F48" s="20"/>
+      <c r="G48" s="20"/>
+      <c r="H48" s="20"/>
+      <c r="I48" s="20"/>
+      <c r="J48" s="20"/>
+      <c r="K48" s="20"/>
+      <c r="L48" s="20"/>
+      <c r="M48" s="20"/>
+      <c r="N48" s="20"/>
+      <c r="O48" s="20"/>
+      <c r="P48" s="20"/>
+      <c r="Q48" s="20"/>
+      <c r="R48" s="20"/>
+      <c r="S48" s="20"/>
+      <c r="T48" s="20"/>
+      <c r="U48" s="20"/>
+      <c r="V48" s="20"/>
+      <c r="W48" s="20"/>
+      <c r="X48" s="20"/>
+      <c r="Y48" s="20"/>
+      <c r="Z48" s="9"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="15" t="s">
+      <c r="A49" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="B49" s="16">
+      <c r="B49" s="19">
         <v>0.0</v>
       </c>
-      <c r="C49" s="17" t="s">
+      <c r="C49" s="20" t="s">
         <v>194</v>
       </c>
-      <c r="D49" s="17" t="s">
+      <c r="D49" s="20" t="s">
         <v>195</v>
       </c>
-      <c r="E49" s="17" t="s">
+      <c r="E49" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="F49" s="17"/>
-      <c r="G49" s="17"/>
-      <c r="H49" s="17"/>
-      <c r="I49" s="17"/>
-      <c r="J49" s="17"/>
-      <c r="K49" s="17"/>
-      <c r="L49" s="17"/>
-      <c r="M49" s="17"/>
-      <c r="N49" s="17"/>
-      <c r="O49" s="17"/>
-      <c r="P49" s="17"/>
-      <c r="Q49" s="17"/>
-      <c r="R49" s="17"/>
-      <c r="S49" s="17"/>
-      <c r="T49" s="17"/>
-      <c r="U49" s="17"/>
-      <c r="V49" s="17"/>
-      <c r="W49" s="17"/>
-      <c r="X49" s="17"/>
-      <c r="Y49" s="17"/>
+      <c r="F49" s="20"/>
+      <c r="G49" s="20"/>
+      <c r="H49" s="20"/>
+      <c r="I49" s="20"/>
+      <c r="J49" s="20"/>
+      <c r="K49" s="20"/>
+      <c r="L49" s="20"/>
+      <c r="M49" s="20"/>
+      <c r="N49" s="20"/>
+      <c r="O49" s="20"/>
+      <c r="P49" s="20"/>
+      <c r="Q49" s="20"/>
+      <c r="R49" s="20"/>
+      <c r="S49" s="20"/>
+      <c r="T49" s="20"/>
+      <c r="U49" s="20"/>
+      <c r="V49" s="20"/>
+      <c r="W49" s="20"/>
+      <c r="X49" s="20"/>
+      <c r="Y49" s="20"/>
+      <c r="Z49" s="9"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="15" t="s">
+      <c r="A50" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="B50" s="16">
+      <c r="B50" s="19">
         <v>0.0</v>
       </c>
-      <c r="C50" s="17" t="s">
+      <c r="C50" s="20" t="s">
         <v>198</v>
       </c>
-      <c r="D50" s="17" t="s">
+      <c r="D50" s="20" t="s">
         <v>199</v>
       </c>
-      <c r="E50" s="17" t="s">
+      <c r="E50" s="20" t="s">
         <v>200</v>
       </c>
-      <c r="F50" s="17"/>
-      <c r="G50" s="17"/>
-      <c r="H50" s="17"/>
-      <c r="I50" s="17"/>
-      <c r="J50" s="17"/>
-      <c r="K50" s="17"/>
-      <c r="L50" s="17"/>
-      <c r="M50" s="17"/>
-      <c r="N50" s="17"/>
-      <c r="O50" s="17"/>
-      <c r="P50" s="17"/>
-      <c r="Q50" s="17"/>
-      <c r="R50" s="17"/>
-      <c r="S50" s="17"/>
-      <c r="T50" s="17"/>
-      <c r="U50" s="17"/>
-      <c r="V50" s="17"/>
-      <c r="W50" s="17"/>
-      <c r="X50" s="17"/>
-      <c r="Y50" s="17"/>
+      <c r="F50" s="20"/>
+      <c r="G50" s="20"/>
+      <c r="H50" s="20"/>
+      <c r="I50" s="20"/>
+      <c r="J50" s="20"/>
+      <c r="K50" s="20"/>
+      <c r="L50" s="20"/>
+      <c r="M50" s="20"/>
+      <c r="N50" s="20"/>
+      <c r="O50" s="20"/>
+      <c r="P50" s="20"/>
+      <c r="Q50" s="20"/>
+      <c r="R50" s="20"/>
+      <c r="S50" s="20"/>
+      <c r="T50" s="20"/>
+      <c r="U50" s="20"/>
+      <c r="V50" s="20"/>
+      <c r="W50" s="20"/>
+      <c r="X50" s="20"/>
+      <c r="Y50" s="20"/>
+      <c r="Z50" s="9"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="15" t="s">
+      <c r="A51" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="B51" s="16">
+      <c r="B51" s="19">
         <v>0.0</v>
       </c>
-      <c r="C51" s="17" t="s">
+      <c r="C51" s="20" t="s">
         <v>202</v>
       </c>
-      <c r="D51" s="17" t="s">
+      <c r="D51" s="20" t="s">
         <v>203</v>
       </c>
-      <c r="E51" s="17" t="s">
+      <c r="E51" s="20" t="s">
         <v>204</v>
       </c>
-      <c r="F51" s="17"/>
-      <c r="G51" s="17"/>
-      <c r="H51" s="17"/>
-      <c r="I51" s="17"/>
-      <c r="J51" s="17"/>
-      <c r="K51" s="17"/>
-      <c r="L51" s="17"/>
-      <c r="M51" s="17"/>
-      <c r="N51" s="17"/>
-      <c r="O51" s="17"/>
-      <c r="P51" s="17"/>
-      <c r="Q51" s="17"/>
-      <c r="R51" s="17"/>
-      <c r="S51" s="17"/>
-      <c r="T51" s="17"/>
-      <c r="U51" s="17"/>
-      <c r="V51" s="17"/>
-      <c r="W51" s="17"/>
-      <c r="X51" s="17"/>
-      <c r="Y51" s="17"/>
+      <c r="F51" s="20"/>
+      <c r="G51" s="20"/>
+      <c r="H51" s="20"/>
+      <c r="I51" s="20"/>
+      <c r="J51" s="20"/>
+      <c r="K51" s="20"/>
+      <c r="L51" s="20"/>
+      <c r="M51" s="20"/>
+      <c r="N51" s="20"/>
+      <c r="O51" s="20"/>
+      <c r="P51" s="20"/>
+      <c r="Q51" s="20"/>
+      <c r="R51" s="20"/>
+      <c r="S51" s="20"/>
+      <c r="T51" s="20"/>
+      <c r="U51" s="20"/>
+      <c r="V51" s="20"/>
+      <c r="W51" s="20"/>
+      <c r="X51" s="20"/>
+      <c r="Y51" s="20"/>
+      <c r="Z51" s="9"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="15" t="s">
+      <c r="A52" s="18" t="s">
         <v>205</v>
       </c>
-      <c r="B52" s="16">
+      <c r="B52" s="19">
         <v>0.0</v>
       </c>
-      <c r="C52" s="17" t="s">
+      <c r="C52" s="20" t="s">
         <v>206</v>
       </c>
-      <c r="D52" s="17" t="s">
+      <c r="D52" s="20" t="s">
         <v>207</v>
       </c>
-      <c r="E52" s="17" t="s">
+      <c r="E52" s="20" t="s">
         <v>208</v>
       </c>
-      <c r="F52" s="17"/>
-      <c r="G52" s="17"/>
-      <c r="H52" s="17"/>
-      <c r="I52" s="17"/>
-      <c r="J52" s="17"/>
-      <c r="K52" s="17"/>
-      <c r="L52" s="17"/>
-      <c r="M52" s="17"/>
-      <c r="N52" s="17"/>
-      <c r="O52" s="17"/>
-      <c r="P52" s="17"/>
-      <c r="Q52" s="17"/>
-      <c r="R52" s="17"/>
-      <c r="S52" s="17"/>
-      <c r="T52" s="17"/>
-      <c r="U52" s="17"/>
-      <c r="V52" s="17"/>
-      <c r="W52" s="17"/>
-      <c r="X52" s="17"/>
-      <c r="Y52" s="17"/>
+      <c r="F52" s="20"/>
+      <c r="G52" s="20"/>
+      <c r="H52" s="20"/>
+      <c r="I52" s="20"/>
+      <c r="J52" s="20"/>
+      <c r="K52" s="20"/>
+      <c r="L52" s="20"/>
+      <c r="M52" s="20"/>
+      <c r="N52" s="20"/>
+      <c r="O52" s="20"/>
+      <c r="P52" s="20"/>
+      <c r="Q52" s="20"/>
+      <c r="R52" s="20"/>
+      <c r="S52" s="20"/>
+      <c r="T52" s="20"/>
+      <c r="U52" s="20"/>
+      <c r="V52" s="20"/>
+      <c r="W52" s="20"/>
+      <c r="X52" s="20"/>
+      <c r="Y52" s="20"/>
+      <c r="Z52" s="9"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="15" t="s">
+      <c r="A53" s="18" t="s">
         <v>209</v>
       </c>
-      <c r="B53" s="16">
+      <c r="B53" s="19">
         <v>0.0</v>
       </c>
-      <c r="C53" s="17" t="s">
+      <c r="C53" s="20" t="s">
         <v>210</v>
       </c>
-      <c r="D53" s="17" t="s">
+      <c r="D53" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="E53" s="17" t="s">
+      <c r="E53" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="F53" s="17"/>
-      <c r="G53" s="17"/>
-      <c r="H53" s="17"/>
-      <c r="I53" s="17"/>
-      <c r="J53" s="17"/>
-      <c r="K53" s="17"/>
-      <c r="L53" s="17"/>
-      <c r="M53" s="17"/>
-      <c r="N53" s="17"/>
-      <c r="O53" s="17"/>
-      <c r="P53" s="17"/>
-      <c r="Q53" s="17"/>
-      <c r="R53" s="17"/>
-      <c r="S53" s="17"/>
-      <c r="T53" s="17"/>
-      <c r="U53" s="17"/>
-      <c r="V53" s="17"/>
-      <c r="W53" s="17"/>
-      <c r="X53" s="17"/>
-      <c r="Y53" s="17"/>
+      <c r="F53" s="20"/>
+      <c r="G53" s="20"/>
+      <c r="H53" s="20"/>
+      <c r="I53" s="20"/>
+      <c r="J53" s="20"/>
+      <c r="K53" s="20"/>
+      <c r="L53" s="20"/>
+      <c r="M53" s="20"/>
+      <c r="N53" s="20"/>
+      <c r="O53" s="20"/>
+      <c r="P53" s="20"/>
+      <c r="Q53" s="20"/>
+      <c r="R53" s="20"/>
+      <c r="S53" s="20"/>
+      <c r="T53" s="20"/>
+      <c r="U53" s="20"/>
+      <c r="V53" s="20"/>
+      <c r="W53" s="20"/>
+      <c r="X53" s="20"/>
+      <c r="Y53" s="20"/>
+      <c r="Z53" s="9"/>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="15" t="s">
+      <c r="A54" s="18" t="s">
         <v>211</v>
       </c>
-      <c r="B54" s="16">
+      <c r="B54" s="19">
         <v>0.0</v>
       </c>
-      <c r="C54" s="17" t="s">
+      <c r="C54" s="20" t="s">
         <v>212</v>
       </c>
-      <c r="D54" s="17" t="s">
+      <c r="D54" s="20" t="s">
         <v>213</v>
       </c>
-      <c r="E54" s="17" t="s">
+      <c r="E54" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="F54" s="17"/>
-      <c r="G54" s="17"/>
-      <c r="H54" s="17"/>
-      <c r="I54" s="17"/>
-      <c r="J54" s="17"/>
-      <c r="K54" s="17"/>
-      <c r="L54" s="17"/>
-      <c r="M54" s="17"/>
-      <c r="N54" s="17"/>
-      <c r="O54" s="17"/>
-      <c r="P54" s="17"/>
-      <c r="Q54" s="17"/>
-      <c r="R54" s="17"/>
-      <c r="S54" s="17"/>
-      <c r="T54" s="17"/>
-      <c r="U54" s="17"/>
-      <c r="V54" s="17"/>
-      <c r="W54" s="17"/>
-      <c r="X54" s="17"/>
-      <c r="Y54" s="17"/>
+      <c r="F54" s="20"/>
+      <c r="G54" s="20"/>
+      <c r="H54" s="20"/>
+      <c r="I54" s="20"/>
+      <c r="J54" s="20"/>
+      <c r="K54" s="20"/>
+      <c r="L54" s="20"/>
+      <c r="M54" s="20"/>
+      <c r="N54" s="20"/>
+      <c r="O54" s="20"/>
+      <c r="P54" s="20"/>
+      <c r="Q54" s="20"/>
+      <c r="R54" s="20"/>
+      <c r="S54" s="20"/>
+      <c r="T54" s="20"/>
+      <c r="U54" s="20"/>
+      <c r="V54" s="20"/>
+      <c r="W54" s="20"/>
+      <c r="X54" s="20"/>
+      <c r="Y54" s="20"/>
+      <c r="Z54" s="9"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="15" t="s">
+      <c r="A55" s="18" t="s">
         <v>215</v>
       </c>
-      <c r="B55" s="16">
+      <c r="B55" s="19">
         <v>0.0</v>
       </c>
-      <c r="C55" s="17" t="s">
+      <c r="C55" s="20" t="s">
         <v>216</v>
       </c>
-      <c r="D55" s="17" t="s">
+      <c r="D55" s="20" t="s">
         <v>217</v>
       </c>
-      <c r="E55" s="17" t="s">
+      <c r="E55" s="20" t="s">
         <v>218</v>
       </c>
-      <c r="F55" s="17"/>
-      <c r="G55" s="17"/>
-      <c r="H55" s="17"/>
-      <c r="I55" s="17"/>
-      <c r="J55" s="17"/>
-      <c r="K55" s="17"/>
-      <c r="L55" s="17"/>
-      <c r="M55" s="17"/>
-      <c r="N55" s="17"/>
-      <c r="O55" s="17"/>
-      <c r="P55" s="17"/>
-      <c r="Q55" s="17"/>
-      <c r="R55" s="17"/>
-      <c r="S55" s="17"/>
-      <c r="T55" s="17"/>
-      <c r="U55" s="17"/>
-      <c r="V55" s="17"/>
-      <c r="W55" s="17"/>
-      <c r="X55" s="17"/>
-      <c r="Y55" s="17"/>
+      <c r="F55" s="20"/>
+      <c r="G55" s="20"/>
+      <c r="H55" s="20"/>
+      <c r="I55" s="20"/>
+      <c r="J55" s="20"/>
+      <c r="K55" s="20"/>
+      <c r="L55" s="20"/>
+      <c r="M55" s="20"/>
+      <c r="N55" s="20"/>
+      <c r="O55" s="20"/>
+      <c r="P55" s="20"/>
+      <c r="Q55" s="20"/>
+      <c r="R55" s="20"/>
+      <c r="S55" s="20"/>
+      <c r="T55" s="20"/>
+      <c r="U55" s="20"/>
+      <c r="V55" s="20"/>
+      <c r="W55" s="20"/>
+      <c r="X55" s="20"/>
+      <c r="Y55" s="20"/>
+      <c r="Z55" s="9"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="15" t="s">
+      <c r="A56" s="18" t="s">
         <v>219</v>
       </c>
-      <c r="B56" s="16">
+      <c r="B56" s="19">
         <v>0.0</v>
       </c>
-      <c r="C56" s="17" t="s">
+      <c r="C56" s="20" t="s">
         <v>220</v>
       </c>
-      <c r="D56" s="17" t="s">
+      <c r="D56" s="20" t="s">
         <v>221</v>
       </c>
-      <c r="E56" s="17" t="s">
+      <c r="E56" s="20" t="s">
         <v>222</v>
       </c>
-      <c r="F56" s="17"/>
-      <c r="G56" s="17"/>
-      <c r="H56" s="17"/>
-      <c r="I56" s="17"/>
-      <c r="J56" s="17"/>
-      <c r="K56" s="17"/>
-      <c r="L56" s="17"/>
-      <c r="M56" s="17"/>
-      <c r="N56" s="17"/>
-      <c r="O56" s="17"/>
-      <c r="P56" s="17"/>
-      <c r="Q56" s="17"/>
-      <c r="R56" s="17"/>
-      <c r="S56" s="17"/>
-      <c r="T56" s="17"/>
-      <c r="U56" s="17"/>
-      <c r="V56" s="17"/>
-      <c r="W56" s="17"/>
-      <c r="X56" s="17"/>
-      <c r="Y56" s="17"/>
+      <c r="F56" s="20"/>
+      <c r="G56" s="20"/>
+      <c r="H56" s="20"/>
+      <c r="I56" s="20"/>
+      <c r="J56" s="20"/>
+      <c r="K56" s="20"/>
+      <c r="L56" s="20"/>
+      <c r="M56" s="20"/>
+      <c r="N56" s="20"/>
+      <c r="O56" s="20"/>
+      <c r="P56" s="20"/>
+      <c r="Q56" s="20"/>
+      <c r="R56" s="20"/>
+      <c r="S56" s="20"/>
+      <c r="T56" s="20"/>
+      <c r="U56" s="20"/>
+      <c r="V56" s="20"/>
+      <c r="W56" s="20"/>
+      <c r="X56" s="20"/>
+      <c r="Y56" s="20"/>
+      <c r="Z56" s="9"/>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="15" t="s">
+      <c r="A57" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="B57" s="16">
+      <c r="B57" s="19">
         <v>0.0</v>
       </c>
-      <c r="C57" s="17" t="s">
+      <c r="C57" s="20" t="s">
         <v>224</v>
       </c>
-      <c r="D57" s="17" t="s">
+      <c r="D57" s="20" t="s">
         <v>225</v>
       </c>
-      <c r="E57" s="17" t="s">
+      <c r="E57" s="20" t="s">
         <v>226</v>
       </c>
-      <c r="F57" s="17"/>
-      <c r="G57" s="17"/>
-      <c r="H57" s="17"/>
-      <c r="I57" s="17"/>
-      <c r="J57" s="17"/>
-      <c r="K57" s="17"/>
-      <c r="L57" s="17"/>
-      <c r="M57" s="17"/>
-      <c r="N57" s="17"/>
-      <c r="O57" s="17"/>
-      <c r="P57" s="17"/>
-      <c r="Q57" s="17"/>
-      <c r="R57" s="17"/>
-      <c r="S57" s="17"/>
-      <c r="T57" s="17"/>
-      <c r="U57" s="17"/>
-      <c r="V57" s="17"/>
-      <c r="W57" s="17"/>
-      <c r="X57" s="17"/>
-      <c r="Y57" s="17"/>
+      <c r="F57" s="20"/>
+      <c r="G57" s="20"/>
+      <c r="H57" s="20"/>
+      <c r="I57" s="20"/>
+      <c r="J57" s="20"/>
+      <c r="K57" s="20"/>
+      <c r="L57" s="20"/>
+      <c r="M57" s="20"/>
+      <c r="N57" s="20"/>
+      <c r="O57" s="20"/>
+      <c r="P57" s="20"/>
+      <c r="Q57" s="20"/>
+      <c r="R57" s="20"/>
+      <c r="S57" s="20"/>
+      <c r="T57" s="20"/>
+      <c r="U57" s="20"/>
+      <c r="V57" s="20"/>
+      <c r="W57" s="20"/>
+      <c r="X57" s="20"/>
+      <c r="Y57" s="20"/>
+      <c r="Z57" s="9"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="15" t="s">
+      <c r="A58" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="B58" s="16">
+      <c r="B58" s="19">
         <v>0.0</v>
       </c>
-      <c r="C58" s="17" t="s">
+      <c r="C58" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="D58" s="17" t="s">
+      <c r="D58" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="E58" s="17" t="s">
+      <c r="E58" s="20" t="s">
         <v>230</v>
       </c>
-      <c r="F58" s="17"/>
-      <c r="G58" s="17"/>
-      <c r="H58" s="17"/>
-      <c r="I58" s="17"/>
-      <c r="J58" s="17"/>
-      <c r="K58" s="17"/>
-      <c r="L58" s="17"/>
-      <c r="M58" s="17"/>
-      <c r="N58" s="17"/>
-      <c r="O58" s="17"/>
-      <c r="P58" s="17"/>
-      <c r="Q58" s="17"/>
-      <c r="R58" s="17"/>
-      <c r="S58" s="17"/>
-      <c r="T58" s="17"/>
-      <c r="U58" s="17"/>
-      <c r="V58" s="17"/>
-      <c r="W58" s="17"/>
-      <c r="X58" s="17"/>
-      <c r="Y58" s="17"/>
+      <c r="F58" s="20"/>
+      <c r="G58" s="20"/>
+      <c r="H58" s="20"/>
+      <c r="I58" s="20"/>
+      <c r="J58" s="20"/>
+      <c r="K58" s="20"/>
+      <c r="L58" s="20"/>
+      <c r="M58" s="20"/>
+      <c r="N58" s="20"/>
+      <c r="O58" s="20"/>
+      <c r="P58" s="20"/>
+      <c r="Q58" s="20"/>
+      <c r="R58" s="20"/>
+      <c r="S58" s="20"/>
+      <c r="T58" s="20"/>
+      <c r="U58" s="20"/>
+      <c r="V58" s="20"/>
+      <c r="W58" s="20"/>
+      <c r="X58" s="20"/>
+      <c r="Y58" s="20"/>
+      <c r="Z58" s="9"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="15" t="s">
+      <c r="A59" s="18" t="s">
         <v>231</v>
       </c>
-      <c r="B59" s="16">
+      <c r="B59" s="19">
         <v>0.0</v>
       </c>
-      <c r="C59" s="17" t="s">
+      <c r="C59" s="20" t="s">
         <v>232</v>
       </c>
-      <c r="D59" s="17" t="s">
+      <c r="D59" s="20" t="s">
         <v>233</v>
       </c>
-      <c r="E59" s="17" t="s">
+      <c r="E59" s="20" t="s">
         <v>234</v>
       </c>
-      <c r="F59" s="17"/>
-      <c r="G59" s="17"/>
-      <c r="H59" s="17"/>
-      <c r="I59" s="17"/>
-      <c r="J59" s="17"/>
-      <c r="K59" s="17"/>
-      <c r="L59" s="17"/>
-      <c r="M59" s="17"/>
-      <c r="N59" s="17"/>
-      <c r="O59" s="17"/>
-      <c r="P59" s="17"/>
-      <c r="Q59" s="17"/>
-      <c r="R59" s="17"/>
-      <c r="S59" s="17"/>
-      <c r="T59" s="17"/>
-      <c r="U59" s="17"/>
-      <c r="V59" s="17"/>
-      <c r="W59" s="17"/>
-      <c r="X59" s="17"/>
-      <c r="Y59" s="17"/>
+      <c r="F59" s="20"/>
+      <c r="G59" s="20"/>
+      <c r="H59" s="20"/>
+      <c r="I59" s="20"/>
+      <c r="J59" s="20"/>
+      <c r="K59" s="20"/>
+      <c r="L59" s="20"/>
+      <c r="M59" s="20"/>
+      <c r="N59" s="20"/>
+      <c r="O59" s="20"/>
+      <c r="P59" s="20"/>
+      <c r="Q59" s="20"/>
+      <c r="R59" s="20"/>
+      <c r="S59" s="20"/>
+      <c r="T59" s="20"/>
+      <c r="U59" s="20"/>
+      <c r="V59" s="20"/>
+      <c r="W59" s="20"/>
+      <c r="X59" s="20"/>
+      <c r="Y59" s="20"/>
+      <c r="Z59" s="9"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="15" t="s">
+      <c r="A60" s="18" t="s">
         <v>235</v>
       </c>
-      <c r="B60" s="16">
+      <c r="B60" s="19">
         <v>0.0</v>
       </c>
-      <c r="C60" s="17" t="s">
+      <c r="C60" s="20" t="s">
         <v>236</v>
       </c>
-      <c r="D60" s="17" t="s">
+      <c r="D60" s="20" t="s">
         <v>237</v>
       </c>
-      <c r="E60" s="17" t="s">
+      <c r="E60" s="20" t="s">
         <v>238</v>
       </c>
-      <c r="F60" s="17"/>
-      <c r="G60" s="17"/>
-      <c r="H60" s="17"/>
-      <c r="I60" s="17"/>
-      <c r="J60" s="17"/>
-      <c r="K60" s="17"/>
-      <c r="L60" s="17"/>
-      <c r="M60" s="17"/>
-      <c r="N60" s="17"/>
-      <c r="O60" s="17"/>
-      <c r="P60" s="17"/>
-      <c r="Q60" s="17"/>
-      <c r="R60" s="17"/>
-      <c r="S60" s="17"/>
-      <c r="T60" s="17"/>
-      <c r="U60" s="17"/>
-      <c r="V60" s="17"/>
-      <c r="W60" s="17"/>
-      <c r="X60" s="17"/>
-      <c r="Y60" s="17"/>
+      <c r="F60" s="20"/>
+      <c r="G60" s="20"/>
+      <c r="H60" s="20"/>
+      <c r="I60" s="20"/>
+      <c r="J60" s="20"/>
+      <c r="K60" s="20"/>
+      <c r="L60" s="20"/>
+      <c r="M60" s="20"/>
+      <c r="N60" s="20"/>
+      <c r="O60" s="20"/>
+      <c r="P60" s="20"/>
+      <c r="Q60" s="20"/>
+      <c r="R60" s="20"/>
+      <c r="S60" s="20"/>
+      <c r="T60" s="20"/>
+      <c r="U60" s="20"/>
+      <c r="V60" s="20"/>
+      <c r="W60" s="20"/>
+      <c r="X60" s="20"/>
+      <c r="Y60" s="20"/>
+      <c r="Z60" s="9"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="15" t="s">
+      <c r="A61" s="18" t="s">
         <v>239</v>
       </c>
-      <c r="B61" s="16">
+      <c r="B61" s="19">
         <v>0.0</v>
       </c>
-      <c r="C61" s="17" t="s">
+      <c r="C61" s="20" t="s">
         <v>240</v>
       </c>
-      <c r="D61" s="17" t="s">
+      <c r="D61" s="20" t="s">
         <v>241</v>
       </c>
-      <c r="E61" s="17" t="s">
+      <c r="E61" s="20" t="s">
         <v>242</v>
       </c>
-      <c r="F61" s="17"/>
-      <c r="G61" s="17"/>
-      <c r="H61" s="17"/>
-      <c r="I61" s="17"/>
-      <c r="J61" s="17"/>
-      <c r="K61" s="17"/>
-      <c r="L61" s="17"/>
-      <c r="M61" s="17"/>
-      <c r="N61" s="17"/>
-      <c r="O61" s="17"/>
-      <c r="P61" s="17"/>
-      <c r="Q61" s="17"/>
-      <c r="R61" s="17"/>
-      <c r="S61" s="17"/>
-      <c r="T61" s="17"/>
-      <c r="U61" s="17"/>
-      <c r="V61" s="17"/>
-      <c r="W61" s="17"/>
-      <c r="X61" s="17"/>
-      <c r="Y61" s="17"/>
+      <c r="F61" s="20"/>
+      <c r="G61" s="20"/>
+      <c r="H61" s="20"/>
+      <c r="I61" s="20"/>
+      <c r="J61" s="20"/>
+      <c r="K61" s="20"/>
+      <c r="L61" s="20"/>
+      <c r="M61" s="20"/>
+      <c r="N61" s="20"/>
+      <c r="O61" s="20"/>
+      <c r="P61" s="20"/>
+      <c r="Q61" s="20"/>
+      <c r="R61" s="20"/>
+      <c r="S61" s="20"/>
+      <c r="T61" s="20"/>
+      <c r="U61" s="20"/>
+      <c r="V61" s="20"/>
+      <c r="W61" s="20"/>
+      <c r="X61" s="20"/>
+      <c r="Y61" s="20"/>
+      <c r="Z61" s="9"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="15" t="s">
+      <c r="A62" s="18" t="s">
         <v>243</v>
       </c>
-      <c r="B62" s="16">
+      <c r="B62" s="19">
         <v>0.0</v>
       </c>
-      <c r="C62" s="17" t="s">
+      <c r="C62" s="20" t="s">
         <v>244</v>
       </c>
-      <c r="D62" s="17" t="s">
+      <c r="D62" s="20" t="s">
         <v>245</v>
       </c>
-      <c r="E62" s="17" t="s">
+      <c r="E62" s="20" t="s">
         <v>246</v>
       </c>
-      <c r="F62" s="17"/>
-      <c r="G62" s="17"/>
-      <c r="H62" s="17"/>
-      <c r="I62" s="17"/>
-      <c r="J62" s="17"/>
-      <c r="K62" s="17"/>
-      <c r="L62" s="17"/>
-      <c r="M62" s="17"/>
-      <c r="N62" s="17"/>
-      <c r="O62" s="17"/>
-      <c r="P62" s="17"/>
-      <c r="Q62" s="17"/>
-      <c r="R62" s="17"/>
-      <c r="S62" s="17"/>
-      <c r="T62" s="17"/>
-      <c r="U62" s="17"/>
-      <c r="V62" s="17"/>
-      <c r="W62" s="17"/>
-      <c r="X62" s="17"/>
-      <c r="Y62" s="17"/>
+      <c r="F62" s="20"/>
+      <c r="G62" s="20"/>
+      <c r="H62" s="20"/>
+      <c r="I62" s="20"/>
+      <c r="J62" s="20"/>
+      <c r="K62" s="20"/>
+      <c r="L62" s="20"/>
+      <c r="M62" s="20"/>
+      <c r="N62" s="20"/>
+      <c r="O62" s="20"/>
+      <c r="P62" s="20"/>
+      <c r="Q62" s="20"/>
+      <c r="R62" s="20"/>
+      <c r="S62" s="20"/>
+      <c r="T62" s="20"/>
+      <c r="U62" s="20"/>
+      <c r="V62" s="20"/>
+      <c r="W62" s="20"/>
+      <c r="X62" s="20"/>
+      <c r="Y62" s="20"/>
+      <c r="Z62" s="9"/>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="15" t="s">
+      <c r="A63" s="18" t="s">
         <v>247</v>
       </c>
-      <c r="B63" s="16">
+      <c r="B63" s="19">
         <v>0.0</v>
       </c>
-      <c r="C63" s="17" t="s">
+      <c r="C63" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="D63" s="17" t="s">
+      <c r="D63" s="20" t="s">
         <v>249</v>
       </c>
-      <c r="E63" s="17" t="s">
+      <c r="E63" s="20" t="s">
         <v>250</v>
       </c>
-      <c r="F63" s="17"/>
-      <c r="G63" s="17"/>
-      <c r="H63" s="17"/>
-      <c r="I63" s="17"/>
-      <c r="J63" s="17"/>
-      <c r="K63" s="17"/>
-      <c r="L63" s="17"/>
-      <c r="M63" s="17"/>
-      <c r="N63" s="17"/>
-      <c r="O63" s="17"/>
-      <c r="P63" s="17"/>
-      <c r="Q63" s="17"/>
-      <c r="R63" s="17"/>
-      <c r="S63" s="17"/>
-      <c r="T63" s="17"/>
-      <c r="U63" s="17"/>
-      <c r="V63" s="17"/>
-      <c r="W63" s="17"/>
-      <c r="X63" s="17"/>
-      <c r="Y63" s="17"/>
+      <c r="F63" s="20"/>
+      <c r="G63" s="20"/>
+      <c r="H63" s="20"/>
+      <c r="I63" s="20"/>
+      <c r="J63" s="20"/>
+      <c r="K63" s="20"/>
+      <c r="L63" s="20"/>
+      <c r="M63" s="20"/>
+      <c r="N63" s="20"/>
+      <c r="O63" s="20"/>
+      <c r="P63" s="20"/>
+      <c r="Q63" s="20"/>
+      <c r="R63" s="20"/>
+      <c r="S63" s="20"/>
+      <c r="T63" s="20"/>
+      <c r="U63" s="20"/>
+      <c r="V63" s="20"/>
+      <c r="W63" s="20"/>
+      <c r="X63" s="20"/>
+      <c r="Y63" s="20"/>
+      <c r="Z63" s="9"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="15" t="s">
+      <c r="A64" s="18" t="s">
         <v>251</v>
       </c>
-      <c r="B64" s="16">
+      <c r="B64" s="19">
         <v>0.0</v>
       </c>
-      <c r="C64" s="17" t="s">
+      <c r="C64" s="20" t="s">
         <v>252</v>
       </c>
-      <c r="D64" s="17" t="s">
+      <c r="D64" s="20" t="s">
         <v>253</v>
       </c>
-      <c r="E64" s="17" t="s">
+      <c r="E64" s="20" t="s">
         <v>254</v>
       </c>
-      <c r="F64" s="17"/>
-      <c r="G64" s="17"/>
-      <c r="H64" s="17"/>
-      <c r="I64" s="17"/>
-      <c r="J64" s="17"/>
-      <c r="K64" s="17"/>
-      <c r="L64" s="17"/>
-      <c r="M64" s="17"/>
-      <c r="N64" s="17"/>
-      <c r="O64" s="17"/>
-      <c r="P64" s="17"/>
-      <c r="Q64" s="17"/>
-      <c r="R64" s="17"/>
-      <c r="S64" s="17"/>
-      <c r="T64" s="17"/>
-      <c r="U64" s="17"/>
-      <c r="V64" s="17"/>
-      <c r="W64" s="17"/>
-      <c r="X64" s="17"/>
-      <c r="Y64" s="17"/>
+      <c r="F64" s="20"/>
+      <c r="G64" s="20"/>
+      <c r="H64" s="20"/>
+      <c r="I64" s="20"/>
+      <c r="J64" s="20"/>
+      <c r="K64" s="20"/>
+      <c r="L64" s="20"/>
+      <c r="M64" s="20"/>
+      <c r="N64" s="20"/>
+      <c r="O64" s="20"/>
+      <c r="P64" s="20"/>
+      <c r="Q64" s="20"/>
+      <c r="R64" s="20"/>
+      <c r="S64" s="20"/>
+      <c r="T64" s="20"/>
+      <c r="U64" s="20"/>
+      <c r="V64" s="20"/>
+      <c r="W64" s="20"/>
+      <c r="X64" s="20"/>
+      <c r="Y64" s="20"/>
+      <c r="Z64" s="9"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="15" t="s">
+      <c r="A65" s="18" t="s">
         <v>255</v>
       </c>
-      <c r="B65" s="16">
+      <c r="B65" s="19">
         <v>0.0</v>
       </c>
-      <c r="C65" s="17" t="s">
+      <c r="C65" s="20" t="s">
         <v>256</v>
       </c>
-      <c r="D65" s="17" t="s">
+      <c r="D65" s="20" t="s">
         <v>257</v>
       </c>
-      <c r="E65" s="17" t="s">
+      <c r="E65" s="20" t="s">
         <v>258</v>
       </c>
-      <c r="F65" s="17"/>
-      <c r="G65" s="17"/>
-      <c r="H65" s="17"/>
-      <c r="I65" s="17"/>
-      <c r="J65" s="17"/>
-      <c r="K65" s="17"/>
-      <c r="L65" s="17"/>
-      <c r="M65" s="17"/>
-      <c r="N65" s="17"/>
-      <c r="O65" s="17"/>
-      <c r="P65" s="17"/>
-      <c r="Q65" s="17"/>
-      <c r="R65" s="17"/>
-      <c r="S65" s="17"/>
-      <c r="T65" s="17"/>
-      <c r="U65" s="17"/>
-      <c r="V65" s="17"/>
-      <c r="W65" s="17"/>
-      <c r="X65" s="17"/>
-      <c r="Y65" s="17"/>
+      <c r="F65" s="20"/>
+      <c r="G65" s="20"/>
+      <c r="H65" s="20"/>
+      <c r="I65" s="20"/>
+      <c r="J65" s="20"/>
+      <c r="K65" s="20"/>
+      <c r="L65" s="20"/>
+      <c r="M65" s="20"/>
+      <c r="N65" s="20"/>
+      <c r="O65" s="20"/>
+      <c r="P65" s="20"/>
+      <c r="Q65" s="20"/>
+      <c r="R65" s="20"/>
+      <c r="S65" s="20"/>
+      <c r="T65" s="20"/>
+      <c r="U65" s="20"/>
+      <c r="V65" s="20"/>
+      <c r="W65" s="20"/>
+      <c r="X65" s="20"/>
+      <c r="Y65" s="20"/>
+      <c r="Z65" s="9"/>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="15" t="s">
+      <c r="A66" s="18" t="s">
         <v>259</v>
       </c>
-      <c r="B66" s="16">
+      <c r="B66" s="19">
         <v>0.0</v>
       </c>
-      <c r="C66" s="17" t="s">
+      <c r="C66" s="20" t="s">
         <v>260</v>
       </c>
-      <c r="D66" s="17" t="s">
+      <c r="D66" s="20" t="s">
         <v>261</v>
       </c>
-      <c r="E66" s="17" t="s">
+      <c r="E66" s="20" t="s">
         <v>262</v>
       </c>
-      <c r="F66" s="17"/>
-      <c r="G66" s="17"/>
-      <c r="H66" s="17"/>
-      <c r="I66" s="17"/>
-      <c r="J66" s="17"/>
-      <c r="K66" s="17"/>
-      <c r="L66" s="17"/>
-      <c r="M66" s="17"/>
-      <c r="N66" s="17"/>
-      <c r="O66" s="17"/>
-      <c r="P66" s="17"/>
-      <c r="Q66" s="17"/>
-      <c r="R66" s="17"/>
-      <c r="S66" s="17"/>
-      <c r="T66" s="17"/>
-      <c r="U66" s="17"/>
-      <c r="V66" s="17"/>
-      <c r="W66" s="17"/>
-      <c r="X66" s="17"/>
-      <c r="Y66" s="17"/>
+      <c r="F66" s="20"/>
+      <c r="G66" s="20"/>
+      <c r="H66" s="20"/>
+      <c r="I66" s="20"/>
+      <c r="J66" s="20"/>
+      <c r="K66" s="20"/>
+      <c r="L66" s="20"/>
+      <c r="M66" s="20"/>
+      <c r="N66" s="20"/>
+      <c r="O66" s="20"/>
+      <c r="P66" s="20"/>
+      <c r="Q66" s="20"/>
+      <c r="R66" s="20"/>
+      <c r="S66" s="20"/>
+      <c r="T66" s="20"/>
+      <c r="U66" s="20"/>
+      <c r="V66" s="20"/>
+      <c r="W66" s="20"/>
+      <c r="X66" s="20"/>
+      <c r="Y66" s="20"/>
+      <c r="Z66" s="9"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="15" t="s">
+      <c r="A67" s="18" t="s">
         <v>263</v>
       </c>
-      <c r="B67" s="16">
+      <c r="B67" s="19">
         <v>0.0</v>
       </c>
-      <c r="C67" s="17" t="s">
+      <c r="C67" s="20" t="s">
         <v>264</v>
       </c>
-      <c r="D67" s="17" t="s">
+      <c r="D67" s="20" t="s">
         <v>265</v>
       </c>
-      <c r="E67" s="17" t="s">
+      <c r="E67" s="20" t="s">
         <v>266</v>
       </c>
-      <c r="F67" s="17"/>
-      <c r="G67" s="17"/>
-      <c r="H67" s="17"/>
-      <c r="I67" s="17"/>
-      <c r="J67" s="17"/>
-      <c r="K67" s="17"/>
-      <c r="L67" s="17"/>
-      <c r="M67" s="17"/>
-      <c r="N67" s="17"/>
-      <c r="O67" s="17"/>
-      <c r="P67" s="17"/>
-      <c r="Q67" s="17"/>
-      <c r="R67" s="17"/>
-      <c r="S67" s="17"/>
-      <c r="T67" s="17"/>
-      <c r="U67" s="17"/>
-      <c r="V67" s="17"/>
-      <c r="W67" s="17"/>
-      <c r="X67" s="17"/>
-      <c r="Y67" s="17"/>
+      <c r="F67" s="20"/>
+      <c r="G67" s="20"/>
+      <c r="H67" s="20"/>
+      <c r="I67" s="20"/>
+      <c r="J67" s="20"/>
+      <c r="K67" s="20"/>
+      <c r="L67" s="20"/>
+      <c r="M67" s="20"/>
+      <c r="N67" s="20"/>
+      <c r="O67" s="20"/>
+      <c r="P67" s="20"/>
+      <c r="Q67" s="20"/>
+      <c r="R67" s="20"/>
+      <c r="S67" s="20"/>
+      <c r="T67" s="20"/>
+      <c r="U67" s="20"/>
+      <c r="V67" s="20"/>
+      <c r="W67" s="20"/>
+      <c r="X67" s="20"/>
+      <c r="Y67" s="20"/>
+      <c r="Z67" s="9"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="18" t="s">
+      <c r="A68" s="21" t="s">
         <v>267</v>
       </c>
-      <c r="B68" s="19">
+      <c r="B68" s="22">
         <v>0.0</v>
       </c>
-      <c r="C68" s="20" t="s">
+      <c r="C68" s="23" t="s">
         <v>268</v>
       </c>
-      <c r="D68" s="20" t="s">
+      <c r="D68" s="23" t="s">
         <v>269</v>
       </c>
-      <c r="E68" s="20" t="s">
+      <c r="E68" s="23" t="s">
         <v>270</v>
       </c>
-      <c r="F68" s="20"/>
-      <c r="G68" s="20"/>
-      <c r="H68" s="20"/>
-      <c r="I68" s="20"/>
-      <c r="J68" s="20"/>
-      <c r="K68" s="20"/>
-      <c r="L68" s="20"/>
-      <c r="M68" s="20"/>
-      <c r="N68" s="20"/>
-      <c r="O68" s="20"/>
-      <c r="P68" s="20"/>
-      <c r="Q68" s="20"/>
-      <c r="R68" s="20"/>
-      <c r="S68" s="20"/>
-      <c r="T68" s="20"/>
-      <c r="U68" s="20"/>
-      <c r="V68" s="20"/>
-      <c r="W68" s="20"/>
-      <c r="X68" s="20"/>
-      <c r="Y68" s="20"/>
+      <c r="F68" s="23"/>
+      <c r="G68" s="23"/>
+      <c r="H68" s="23"/>
+      <c r="I68" s="23"/>
+      <c r="J68" s="23"/>
+      <c r="K68" s="23"/>
+      <c r="L68" s="23"/>
+      <c r="M68" s="23"/>
+      <c r="N68" s="23"/>
+      <c r="O68" s="23"/>
+      <c r="P68" s="23"/>
+      <c r="Q68" s="23"/>
+      <c r="R68" s="23"/>
+      <c r="S68" s="23"/>
+      <c r="T68" s="23"/>
+      <c r="U68" s="23"/>
+      <c r="V68" s="23"/>
+      <c r="W68" s="23"/>
+      <c r="X68" s="23"/>
+      <c r="Y68" s="23"/>
+      <c r="Z68" s="14"/>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="21" t="s">
+      <c r="A69" s="24" t="s">
         <v>271</v>
       </c>
-      <c r="B69" s="22">
+      <c r="B69" s="25">
         <v>0.0</v>
       </c>
-      <c r="C69" s="22" t="s">
+      <c r="C69" s="25" t="s">
         <v>272</v>
       </c>
-      <c r="D69" s="22" t="s">
+      <c r="D69" s="25" t="s">
         <v>147</v>
       </c>
-      <c r="E69" s="22" t="s">
+      <c r="E69" s="25" t="s">
         <v>148</v>
       </c>
-      <c r="F69" s="22"/>
-      <c r="G69" s="22"/>
-      <c r="H69" s="22"/>
-      <c r="I69" s="22"/>
-      <c r="J69" s="22"/>
-      <c r="K69" s="22"/>
-      <c r="L69" s="22"/>
-      <c r="M69" s="22"/>
-      <c r="N69" s="22"/>
-      <c r="O69" s="22"/>
-      <c r="P69" s="22"/>
-      <c r="Q69" s="22"/>
-      <c r="R69" s="22"/>
-      <c r="S69" s="22"/>
-      <c r="T69" s="22"/>
-      <c r="U69" s="22"/>
-      <c r="V69" s="22"/>
-      <c r="W69" s="22"/>
-      <c r="X69" s="22"/>
-      <c r="Y69" s="22"/>
+      <c r="F69" s="25"/>
+      <c r="G69" s="25"/>
+      <c r="H69" s="25"/>
+      <c r="I69" s="25"/>
+      <c r="J69" s="25"/>
+      <c r="K69" s="25"/>
+      <c r="L69" s="25"/>
+      <c r="M69" s="25"/>
+      <c r="N69" s="25"/>
+      <c r="O69" s="25"/>
+      <c r="P69" s="25"/>
+      <c r="Q69" s="25"/>
+      <c r="R69" s="25"/>
+      <c r="S69" s="25"/>
+      <c r="T69" s="25"/>
+      <c r="U69" s="25"/>
+      <c r="V69" s="25"/>
+      <c r="W69" s="25"/>
+      <c r="X69" s="25"/>
+      <c r="Y69" s="25"/>
+      <c r="Z69" s="5"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="21" t="s">
+      <c r="A70" s="26" t="s">
         <v>273</v>
       </c>
-      <c r="B70" s="22">
+      <c r="B70" s="27">
         <v>0.0</v>
       </c>
-      <c r="C70" s="22" t="s">
+      <c r="C70" s="27" t="s">
         <v>274</v>
       </c>
-      <c r="D70" s="22" t="s">
+      <c r="D70" s="27" t="s">
         <v>275</v>
       </c>
-      <c r="E70" s="22" t="s">
+      <c r="E70" s="27" t="s">
         <v>276</v>
       </c>
-      <c r="F70" s="22"/>
-      <c r="G70" s="22"/>
-      <c r="H70" s="22"/>
-      <c r="I70" s="22"/>
-      <c r="J70" s="22"/>
-      <c r="K70" s="22"/>
-      <c r="L70" s="22"/>
-      <c r="M70" s="22"/>
-      <c r="N70" s="22"/>
-      <c r="O70" s="22"/>
-      <c r="P70" s="22"/>
-      <c r="Q70" s="22"/>
-      <c r="R70" s="22"/>
-      <c r="S70" s="22"/>
-      <c r="T70" s="22"/>
-      <c r="U70" s="22"/>
-      <c r="V70" s="22"/>
-      <c r="W70" s="22"/>
-      <c r="X70" s="22"/>
-      <c r="Y70" s="22"/>
+      <c r="F70" s="27"/>
+      <c r="G70" s="27"/>
+      <c r="H70" s="27"/>
+      <c r="I70" s="27"/>
+      <c r="J70" s="27"/>
+      <c r="K70" s="27"/>
+      <c r="L70" s="27"/>
+      <c r="M70" s="27"/>
+      <c r="N70" s="27"/>
+      <c r="O70" s="27"/>
+      <c r="P70" s="27"/>
+      <c r="Q70" s="27"/>
+      <c r="R70" s="27"/>
+      <c r="S70" s="27"/>
+      <c r="T70" s="27"/>
+      <c r="U70" s="27"/>
+      <c r="V70" s="27"/>
+      <c r="W70" s="27"/>
+      <c r="X70" s="27"/>
+      <c r="Y70" s="27"/>
+      <c r="Z70" s="9"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="21" t="s">
+      <c r="A71" s="26" t="s">
         <v>277</v>
       </c>
-      <c r="B71" s="22">
+      <c r="B71" s="27">
         <v>0.0</v>
       </c>
-      <c r="C71" s="22" t="s">
+      <c r="C71" s="27" t="s">
         <v>278</v>
       </c>
-      <c r="D71" s="22" t="s">
+      <c r="D71" s="27" t="s">
         <v>175</v>
       </c>
-      <c r="E71" s="22" t="s">
+      <c r="E71" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="F71" s="22"/>
-      <c r="G71" s="22"/>
-      <c r="H71" s="22"/>
-      <c r="I71" s="22"/>
-      <c r="J71" s="22"/>
-      <c r="K71" s="22"/>
-      <c r="L71" s="22"/>
-      <c r="M71" s="22"/>
-      <c r="N71" s="22"/>
-      <c r="O71" s="22"/>
-      <c r="P71" s="22"/>
-      <c r="Q71" s="22"/>
-      <c r="R71" s="22"/>
-      <c r="S71" s="22"/>
-      <c r="T71" s="22"/>
-      <c r="U71" s="22"/>
-      <c r="V71" s="22"/>
-      <c r="W71" s="22"/>
-      <c r="X71" s="22"/>
-      <c r="Y71" s="22"/>
+      <c r="F71" s="27"/>
+      <c r="G71" s="27"/>
+      <c r="H71" s="27"/>
+      <c r="I71" s="27"/>
+      <c r="J71" s="27"/>
+      <c r="K71" s="27"/>
+      <c r="L71" s="27"/>
+      <c r="M71" s="27"/>
+      <c r="N71" s="27"/>
+      <c r="O71" s="27"/>
+      <c r="P71" s="27"/>
+      <c r="Q71" s="27"/>
+      <c r="R71" s="27"/>
+      <c r="S71" s="27"/>
+      <c r="T71" s="27"/>
+      <c r="U71" s="27"/>
+      <c r="V71" s="27"/>
+      <c r="W71" s="27"/>
+      <c r="X71" s="27"/>
+      <c r="Y71" s="27"/>
+      <c r="Z71" s="9"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="21" t="s">
+      <c r="A72" s="26" t="s">
         <v>279</v>
       </c>
-      <c r="B72" s="22">
+      <c r="B72" s="27">
         <v>0.0</v>
       </c>
-      <c r="C72" s="22" t="s">
+      <c r="C72" s="27" t="s">
         <v>280</v>
       </c>
-      <c r="D72" s="22" t="s">
+      <c r="D72" s="27" t="s">
         <v>281</v>
       </c>
-      <c r="E72" s="22" t="s">
+      <c r="E72" s="27" t="s">
         <v>282</v>
       </c>
-      <c r="F72" s="22"/>
-      <c r="G72" s="22"/>
-      <c r="H72" s="22"/>
-      <c r="I72" s="22"/>
-      <c r="J72" s="22"/>
-      <c r="K72" s="22"/>
-      <c r="L72" s="22"/>
-      <c r="M72" s="22"/>
-      <c r="N72" s="22"/>
-      <c r="O72" s="22"/>
-      <c r="P72" s="22"/>
-      <c r="Q72" s="22"/>
-      <c r="R72" s="22"/>
-      <c r="S72" s="22"/>
-      <c r="T72" s="22"/>
-      <c r="U72" s="22"/>
-      <c r="V72" s="22"/>
-      <c r="W72" s="22"/>
-      <c r="X72" s="22"/>
-      <c r="Y72" s="22"/>
+      <c r="F72" s="27"/>
+      <c r="G72" s="27"/>
+      <c r="H72" s="27"/>
+      <c r="I72" s="27"/>
+      <c r="J72" s="27"/>
+      <c r="K72" s="27"/>
+      <c r="L72" s="27"/>
+      <c r="M72" s="27"/>
+      <c r="N72" s="27"/>
+      <c r="O72" s="27"/>
+      <c r="P72" s="27"/>
+      <c r="Q72" s="27"/>
+      <c r="R72" s="27"/>
+      <c r="S72" s="27"/>
+      <c r="T72" s="27"/>
+      <c r="U72" s="27"/>
+      <c r="V72" s="27"/>
+      <c r="W72" s="27"/>
+      <c r="X72" s="27"/>
+      <c r="Y72" s="27"/>
+      <c r="Z72" s="9"/>
     </row>
     <row r="73" ht="15.0" customHeight="1">
-      <c r="A73" s="21" t="s">
+      <c r="A73" s="26" t="s">
         <v>283</v>
       </c>
-      <c r="B73" s="22">
+      <c r="B73" s="27">
         <v>0.0</v>
       </c>
-      <c r="C73" s="22" t="s">
+      <c r="C73" s="27" t="s">
         <v>284</v>
       </c>
-      <c r="D73" s="22" t="s">
+      <c r="D73" s="27" t="s">
         <v>285</v>
       </c>
-      <c r="E73" s="22" t="s">
+      <c r="E73" s="27" t="s">
         <v>286</v>
       </c>
-      <c r="F73" s="22"/>
-      <c r="G73" s="22"/>
-      <c r="H73" s="22"/>
-      <c r="I73" s="22"/>
-      <c r="J73" s="22"/>
-      <c r="K73" s="22"/>
-      <c r="L73" s="22"/>
-      <c r="M73" s="22"/>
-      <c r="N73" s="22"/>
-      <c r="O73" s="22"/>
-      <c r="P73" s="22"/>
-      <c r="Q73" s="22"/>
-      <c r="R73" s="22"/>
-      <c r="S73" s="22"/>
-      <c r="T73" s="22"/>
-      <c r="U73" s="22"/>
-      <c r="V73" s="22"/>
-      <c r="W73" s="22"/>
-      <c r="X73" s="22"/>
-      <c r="Y73" s="22"/>
+      <c r="F73" s="27"/>
+      <c r="G73" s="27"/>
+      <c r="H73" s="27"/>
+      <c r="I73" s="27"/>
+      <c r="J73" s="27"/>
+      <c r="K73" s="27"/>
+      <c r="L73" s="27"/>
+      <c r="M73" s="27"/>
+      <c r="N73" s="27"/>
+      <c r="O73" s="27"/>
+      <c r="P73" s="27"/>
+      <c r="Q73" s="27"/>
+      <c r="R73" s="27"/>
+      <c r="S73" s="27"/>
+      <c r="T73" s="27"/>
+      <c r="U73" s="27"/>
+      <c r="V73" s="27"/>
+      <c r="W73" s="27"/>
+      <c r="X73" s="27"/>
+      <c r="Y73" s="27"/>
+      <c r="Z73" s="9"/>
     </row>
     <row r="74" ht="15.0" customHeight="1">
-      <c r="A74" s="21" t="s">
+      <c r="A74" s="26" t="s">
         <v>287</v>
       </c>
-      <c r="B74" s="22">
+      <c r="B74" s="27">
         <v>0.0</v>
       </c>
-      <c r="C74" s="22" t="s">
+      <c r="C74" s="27" t="s">
         <v>288</v>
       </c>
-      <c r="D74" s="22" t="s">
+      <c r="D74" s="27" t="s">
         <v>289</v>
       </c>
-      <c r="E74" s="22" t="s">
+      <c r="E74" s="27" t="s">
         <v>290</v>
       </c>
-      <c r="F74" s="22"/>
-      <c r="G74" s="22"/>
-      <c r="H74" s="22"/>
-      <c r="I74" s="22"/>
-      <c r="J74" s="22"/>
-      <c r="K74" s="22"/>
-      <c r="L74" s="22"/>
-      <c r="M74" s="22"/>
-      <c r="N74" s="22"/>
-      <c r="O74" s="22"/>
-      <c r="P74" s="22"/>
-      <c r="Q74" s="22"/>
-      <c r="R74" s="22"/>
-      <c r="S74" s="22"/>
-      <c r="T74" s="22"/>
-      <c r="U74" s="22"/>
-      <c r="V74" s="22"/>
-      <c r="W74" s="22"/>
-      <c r="X74" s="22"/>
-      <c r="Y74" s="22"/>
+      <c r="F74" s="27"/>
+      <c r="G74" s="27"/>
+      <c r="H74" s="27"/>
+      <c r="I74" s="27"/>
+      <c r="J74" s="27"/>
+      <c r="K74" s="27"/>
+      <c r="L74" s="27"/>
+      <c r="M74" s="27"/>
+      <c r="N74" s="27"/>
+      <c r="O74" s="27"/>
+      <c r="P74" s="27"/>
+      <c r="Q74" s="27"/>
+      <c r="R74" s="27"/>
+      <c r="S74" s="27"/>
+      <c r="T74" s="27"/>
+      <c r="U74" s="27"/>
+      <c r="V74" s="27"/>
+      <c r="W74" s="27"/>
+      <c r="X74" s="27"/>
+      <c r="Y74" s="27"/>
+      <c r="Z74" s="9"/>
     </row>
     <row r="75" ht="15.0" customHeight="1">
-      <c r="A75" s="21" t="s">
+      <c r="A75" s="26" t="s">
         <v>291</v>
       </c>
-      <c r="B75" s="22">
+      <c r="B75" s="27">
         <v>0.0</v>
       </c>
-      <c r="C75" s="22" t="s">
+      <c r="C75" s="27" t="s">
         <v>292</v>
       </c>
-      <c r="D75" s="22" t="s">
+      <c r="D75" s="27" t="s">
         <v>293</v>
       </c>
-      <c r="E75" s="22" t="s">
+      <c r="E75" s="27" t="s">
         <v>294</v>
       </c>
-      <c r="F75" s="22"/>
-      <c r="G75" s="22"/>
-      <c r="H75" s="22"/>
-      <c r="I75" s="22"/>
-      <c r="J75" s="22"/>
-      <c r="K75" s="22"/>
-      <c r="L75" s="22"/>
-      <c r="M75" s="22"/>
-      <c r="N75" s="22"/>
-      <c r="O75" s="22"/>
-      <c r="P75" s="22"/>
-      <c r="Q75" s="22"/>
-      <c r="R75" s="22"/>
-      <c r="S75" s="22"/>
-      <c r="T75" s="22"/>
-      <c r="U75" s="22"/>
-      <c r="V75" s="22"/>
-      <c r="W75" s="22"/>
-      <c r="X75" s="22"/>
-      <c r="Y75" s="22"/>
+      <c r="F75" s="27"/>
+      <c r="G75" s="27"/>
+      <c r="H75" s="27"/>
+      <c r="I75" s="27"/>
+      <c r="J75" s="27"/>
+      <c r="K75" s="27"/>
+      <c r="L75" s="27"/>
+      <c r="M75" s="27"/>
+      <c r="N75" s="27"/>
+      <c r="O75" s="27"/>
+      <c r="P75" s="27"/>
+      <c r="Q75" s="27"/>
+      <c r="R75" s="27"/>
+      <c r="S75" s="27"/>
+      <c r="T75" s="27"/>
+      <c r="U75" s="27"/>
+      <c r="V75" s="27"/>
+      <c r="W75" s="27"/>
+      <c r="X75" s="27"/>
+      <c r="Y75" s="27"/>
+      <c r="Z75" s="9"/>
     </row>
     <row r="76" ht="15.0" customHeight="1">
-      <c r="A76" s="23" t="s">
+      <c r="A76" s="28" t="s">
         <v>295</v>
       </c>
-      <c r="B76" s="24">
+      <c r="B76" s="29">
         <v>0.0</v>
       </c>
-      <c r="C76" s="25" t="s">
+      <c r="C76" s="30" t="s">
         <v>296</v>
       </c>
-      <c r="D76" s="25" t="s">
+      <c r="D76" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="E76" s="25" t="s">
+      <c r="E76" s="30" t="s">
         <v>208</v>
       </c>
-      <c r="F76" s="25"/>
-      <c r="G76" s="25"/>
-      <c r="H76" s="25"/>
-      <c r="I76" s="25"/>
-      <c r="J76" s="25"/>
-      <c r="K76" s="25"/>
-      <c r="L76" s="25"/>
-      <c r="M76" s="25"/>
-      <c r="N76" s="25"/>
-      <c r="O76" s="25"/>
-      <c r="P76" s="25"/>
-      <c r="Q76" s="25"/>
-      <c r="R76" s="25"/>
-      <c r="S76" s="25"/>
-      <c r="T76" s="25"/>
-      <c r="U76" s="25"/>
-      <c r="V76" s="25"/>
-      <c r="W76" s="25"/>
-      <c r="X76" s="25"/>
-      <c r="Y76" s="25"/>
+      <c r="F76" s="30"/>
+      <c r="G76" s="30"/>
+      <c r="H76" s="30"/>
+      <c r="I76" s="30"/>
+      <c r="J76" s="30"/>
+      <c r="K76" s="30"/>
+      <c r="L76" s="30"/>
+      <c r="M76" s="30"/>
+      <c r="N76" s="30"/>
+      <c r="O76" s="30"/>
+      <c r="P76" s="30"/>
+      <c r="Q76" s="30"/>
+      <c r="R76" s="30"/>
+      <c r="S76" s="30"/>
+      <c r="T76" s="30"/>
+      <c r="U76" s="30"/>
+      <c r="V76" s="30"/>
+      <c r="W76" s="30"/>
+      <c r="X76" s="30"/>
+      <c r="Y76" s="30"/>
+      <c r="Z76" s="9"/>
     </row>
     <row r="77" ht="15.0" customHeight="1">
-      <c r="A77" s="26" t="s">
+      <c r="A77" s="31" t="s">
         <v>297</v>
       </c>
-      <c r="B77" s="27">
+      <c r="B77" s="32">
         <v>0.0</v>
       </c>
-      <c r="C77" s="28" t="s">
+      <c r="C77" s="33" t="s">
         <v>298</v>
       </c>
-      <c r="D77" s="28" t="s">
+      <c r="D77" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="E77" s="28" t="s">
+      <c r="E77" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="F77" s="28"/>
-      <c r="G77" s="28"/>
-      <c r="H77" s="28"/>
-      <c r="I77" s="28"/>
-      <c r="J77" s="28"/>
-      <c r="K77" s="28"/>
-      <c r="L77" s="28"/>
-      <c r="M77" s="28"/>
-      <c r="N77" s="28"/>
-      <c r="O77" s="28"/>
-      <c r="P77" s="28"/>
-      <c r="Q77" s="28"/>
-      <c r="R77" s="28"/>
-      <c r="S77" s="28"/>
-      <c r="T77" s="28"/>
-      <c r="U77" s="28"/>
-      <c r="V77" s="28"/>
-      <c r="W77" s="28"/>
-      <c r="X77" s="28"/>
-      <c r="Y77" s="28"/>
+      <c r="F77" s="33"/>
+      <c r="G77" s="33"/>
+      <c r="H77" s="33"/>
+      <c r="I77" s="33"/>
+      <c r="J77" s="33"/>
+      <c r="K77" s="33"/>
+      <c r="L77" s="33"/>
+      <c r="M77" s="33"/>
+      <c r="N77" s="33"/>
+      <c r="O77" s="33"/>
+      <c r="P77" s="33"/>
+      <c r="Q77" s="33"/>
+      <c r="R77" s="33"/>
+      <c r="S77" s="33"/>
+      <c r="T77" s="33"/>
+      <c r="U77" s="33"/>
+      <c r="V77" s="33"/>
+      <c r="W77" s="33"/>
+      <c r="X77" s="33"/>
+      <c r="Y77" s="33"/>
+      <c r="Z77" s="14"/>
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="1"/>
@@ -10273,9 +10375,6 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
-    <row r="1001" ht="15.75" customHeight="1"/>
-    <row r="1002" ht="15.75" customHeight="1"/>
-    <row r="1003" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Templates/Tables/StringInfo/StrTable.xlsx
+++ b/Templates/Tables/StringInfo/StrTable.xlsx
@@ -76,16 +76,16 @@
     <t>Do you want to set up the B set?</t>
   </si>
   <si>
-    <t>에디터 테이블 다시 로드 메세지</t>
-  </si>
-  <si>
-    <t>EDITOR_TABLE_RL_MSG</t>
-  </si>
-  <si>
-    <t>테이블을 다시 로드하시겠습니까?</t>
-  </si>
-  <si>
-    <t>Do you want to reload the table?</t>
+    <t>에디터 테이블 로드 메세지</t>
+  </si>
+  <si>
+    <t>EDITOR_TABLE_LP_MSG</t>
+  </si>
+  <si>
+    <t>테이블을 로드하시겠습니까?</t>
+  </si>
+  <si>
+    <t>Do you want to load the table?</t>
   </si>
   <si>
     <t>에디터 레벨 제거 팝업 메세지</t>
@@ -919,6 +919,7 @@
       <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <color theme="1"/>
@@ -961,7 +962,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="6">
     <border/>
     <border>
       <left style="thin">
@@ -977,22 +978,9 @@
       </top>
     </border>
     <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
     </border>
     <border>
       <left style="thin">
@@ -1007,19 +995,11 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
-    <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1033,8 +1013,7 @@
     <xf borderId="2" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1043,20 +1022,24 @@
     <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="6" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="7" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="7" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
@@ -1066,7 +1049,7 @@
     <xf borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1075,20 +1058,20 @@
     <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="6" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="7" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="7" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="2" fillId="5" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="5" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="5" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="4" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1097,13 +1080,13 @@
     <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="6" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="7" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="7" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -1317,14 +1300,14 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="26.29"/>
-    <col customWidth="1" min="2" max="2" width="14.43"/>
-    <col customWidth="1" min="3" max="3" width="37.29"/>
-    <col customWidth="1" min="4" max="4" width="98.14"/>
-    <col customWidth="1" min="5" max="5" width="112.0"/>
-    <col customWidth="1" min="6" max="6" width="14.43"/>
+    <col customWidth="1" min="1" max="1" width="23.0"/>
+    <col customWidth="1" min="2" max="2" width="14.38"/>
+    <col customWidth="1" min="3" max="3" width="32.63"/>
+    <col customWidth="1" min="4" max="4" width="85.88"/>
+    <col customWidth="1" min="5" max="5" width="98.0"/>
+    <col customWidth="1" min="6" max="26" width="14.38"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
@@ -1400,615 +1383,598 @@
       <c r="W2" s="4"/>
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
-      <c r="Z2" s="5"/>
     </row>
     <row r="3" ht="15.0" customHeight="1">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>0.0</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8"/>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="8"/>
-      <c r="S3" s="8"/>
-      <c r="T3" s="8"/>
-      <c r="U3" s="8"/>
-      <c r="V3" s="8"/>
-      <c r="W3" s="8"/>
-      <c r="X3" s="8"/>
-      <c r="Y3" s="8"/>
-      <c r="Z3" s="9"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7"/>
+      <c r="S3" s="7"/>
+      <c r="T3" s="7"/>
+      <c r="U3" s="7"/>
+      <c r="V3" s="7"/>
+      <c r="W3" s="7"/>
+      <c r="X3" s="7"/>
+      <c r="Y3" s="7"/>
     </row>
     <row r="4" ht="15.0" customHeight="1">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="6">
         <v>0.0</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="8"/>
-      <c r="Q4" s="8"/>
-      <c r="R4" s="8"/>
-      <c r="S4" s="8"/>
-      <c r="T4" s="8"/>
-      <c r="U4" s="8"/>
-      <c r="V4" s="8"/>
-      <c r="W4" s="8"/>
-      <c r="X4" s="8"/>
-      <c r="Y4" s="8"/>
-      <c r="Z4" s="9"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="7"/>
+      <c r="S4" s="7"/>
+      <c r="T4" s="7"/>
+      <c r="U4" s="7"/>
+      <c r="V4" s="7"/>
+      <c r="W4" s="7"/>
+      <c r="X4" s="7"/>
+      <c r="Y4" s="7"/>
     </row>
     <row r="5" ht="15.0" customHeight="1">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>0.0</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8"/>
-      <c r="N5" s="8"/>
-      <c r="O5" s="8"/>
-      <c r="P5" s="8"/>
-      <c r="Q5" s="8"/>
-      <c r="R5" s="8"/>
-      <c r="S5" s="8"/>
-      <c r="T5" s="8"/>
-      <c r="U5" s="8"/>
-      <c r="V5" s="8"/>
-      <c r="W5" s="8"/>
-      <c r="X5" s="8"/>
-      <c r="Y5" s="8"/>
-      <c r="Z5" s="9"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7"/>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7"/>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7"/>
     </row>
     <row r="6" ht="15.0" customHeight="1">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="6">
         <v>0.0</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="8"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="8"/>
-      <c r="U6" s="8"/>
-      <c r="V6" s="8"/>
-      <c r="W6" s="8"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="8"/>
-      <c r="Z6" s="9"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7"/>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7"/>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7"/>
     </row>
     <row r="7" ht="15.0" customHeight="1">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="6">
         <v>0.0</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="8"/>
-      <c r="S7" s="8"/>
-      <c r="T7" s="8"/>
-      <c r="U7" s="8"/>
-      <c r="V7" s="8"/>
-      <c r="W7" s="8"/>
-      <c r="X7" s="8"/>
-      <c r="Y7" s="8"/>
-      <c r="Z7" s="9"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="7"/>
+      <c r="U7" s="7"/>
+      <c r="V7" s="7"/>
+      <c r="W7" s="7"/>
+      <c r="X7" s="7"/>
+      <c r="Y7" s="7"/>
     </row>
     <row r="8" ht="15.0" customHeight="1">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="6">
         <v>0.0</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="8"/>
-      <c r="R8" s="8"/>
-      <c r="S8" s="8"/>
-      <c r="T8" s="8"/>
-      <c r="U8" s="8"/>
-      <c r="V8" s="8"/>
-      <c r="W8" s="8"/>
-      <c r="X8" s="8"/>
-      <c r="Y8" s="8"/>
-      <c r="Z8" s="9"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="7"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="7"/>
+      <c r="U8" s="7"/>
+      <c r="V8" s="7"/>
+      <c r="W8" s="7"/>
+      <c r="X8" s="7"/>
+      <c r="Y8" s="7"/>
     </row>
     <row r="9" ht="15.0" customHeight="1">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="6">
         <v>0.0</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="8"/>
-      <c r="S9" s="8"/>
-      <c r="T9" s="8"/>
-      <c r="U9" s="8"/>
-      <c r="V9" s="8"/>
-      <c r="W9" s="8"/>
-      <c r="X9" s="8"/>
-      <c r="Y9" s="8"/>
-      <c r="Z9" s="9"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="7"/>
+      <c r="S9" s="7"/>
+      <c r="T9" s="7"/>
+      <c r="U9" s="7"/>
+      <c r="V9" s="7"/>
+      <c r="W9" s="7"/>
+      <c r="X9" s="7"/>
+      <c r="Y9" s="7"/>
     </row>
     <row r="10" ht="15.0" customHeight="1">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="6">
         <v>0.0</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="8"/>
-      <c r="P10" s="8"/>
-      <c r="Q10" s="8"/>
-      <c r="R10" s="8"/>
-      <c r="S10" s="8"/>
-      <c r="T10" s="8"/>
-      <c r="U10" s="8"/>
-      <c r="V10" s="8"/>
-      <c r="W10" s="8"/>
-      <c r="X10" s="8"/>
-      <c r="Y10" s="8"/>
-      <c r="Z10" s="9"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="7"/>
+      <c r="P10" s="7"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="7"/>
+      <c r="S10" s="7"/>
+      <c r="T10" s="7"/>
+      <c r="U10" s="7"/>
+      <c r="V10" s="7"/>
+      <c r="W10" s="7"/>
+      <c r="X10" s="7"/>
+      <c r="Y10" s="7"/>
     </row>
     <row r="11" ht="15.0" customHeight="1">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="6">
         <v>0.0</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="7" t="s">
         <v>43</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
-      <c r="N11" s="8"/>
-      <c r="O11" s="8"/>
-      <c r="P11" s="8"/>
-      <c r="Q11" s="8"/>
-      <c r="R11" s="8"/>
-      <c r="S11" s="8"/>
-      <c r="T11" s="8"/>
-      <c r="U11" s="8"/>
-      <c r="V11" s="8"/>
-      <c r="W11" s="8"/>
-      <c r="X11" s="8"/>
-      <c r="Y11" s="8"/>
-      <c r="Z11" s="9"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="7"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="7"/>
+      <c r="U11" s="7"/>
+      <c r="V11" s="7"/>
+      <c r="W11" s="7"/>
+      <c r="X11" s="7"/>
+      <c r="Y11" s="7"/>
     </row>
     <row r="12" ht="15.0" customHeight="1">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="6">
         <v>0.0</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="8"/>
-      <c r="Q12" s="8"/>
-      <c r="R12" s="8"/>
-      <c r="S12" s="8"/>
-      <c r="T12" s="8"/>
-      <c r="U12" s="8"/>
-      <c r="V12" s="8"/>
-      <c r="W12" s="8"/>
-      <c r="X12" s="8"/>
-      <c r="Y12" s="8"/>
-      <c r="Z12" s="9"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="7"/>
+      <c r="P12" s="7"/>
+      <c r="Q12" s="7"/>
+      <c r="R12" s="7"/>
+      <c r="S12" s="7"/>
+      <c r="T12" s="7"/>
+      <c r="U12" s="7"/>
+      <c r="V12" s="7"/>
+      <c r="W12" s="7"/>
+      <c r="X12" s="7"/>
+      <c r="Y12" s="7"/>
     </row>
     <row r="13" ht="15.0" customHeight="1">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="6">
         <v>0.0</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="8"/>
-      <c r="N13" s="8"/>
-      <c r="O13" s="8"/>
-      <c r="P13" s="8"/>
-      <c r="Q13" s="8"/>
-      <c r="R13" s="8"/>
-      <c r="S13" s="8"/>
-      <c r="T13" s="8"/>
-      <c r="U13" s="8"/>
-      <c r="V13" s="8"/>
-      <c r="W13" s="8"/>
-      <c r="X13" s="8"/>
-      <c r="Y13" s="8"/>
-      <c r="Z13" s="9"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
+      <c r="P13" s="7"/>
+      <c r="Q13" s="7"/>
+      <c r="R13" s="7"/>
+      <c r="S13" s="7"/>
+      <c r="T13" s="7"/>
+      <c r="U13" s="7"/>
+      <c r="V13" s="7"/>
+      <c r="W13" s="7"/>
+      <c r="X13" s="7"/>
+      <c r="Y13" s="7"/>
     </row>
     <row r="14" ht="15.0" customHeight="1">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="6">
         <v>0.0</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8"/>
-      <c r="O14" s="8"/>
-      <c r="P14" s="8"/>
-      <c r="Q14" s="8"/>
-      <c r="R14" s="8"/>
-      <c r="S14" s="8"/>
-      <c r="T14" s="8"/>
-      <c r="U14" s="8"/>
-      <c r="V14" s="8"/>
-      <c r="W14" s="8"/>
-      <c r="X14" s="8"/>
-      <c r="Y14" s="8"/>
-      <c r="Z14" s="9"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="7"/>
+      <c r="R14" s="7"/>
+      <c r="S14" s="7"/>
+      <c r="T14" s="7"/>
+      <c r="U14" s="7"/>
+      <c r="V14" s="7"/>
+      <c r="W14" s="7"/>
+      <c r="X14" s="7"/>
+      <c r="Y14" s="7"/>
     </row>
     <row r="15" ht="15.0" customHeight="1">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="6">
         <v>0.0</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
-      <c r="N15" s="8"/>
-      <c r="O15" s="8"/>
-      <c r="P15" s="8"/>
-      <c r="Q15" s="8"/>
-      <c r="R15" s="8"/>
-      <c r="S15" s="8"/>
-      <c r="T15" s="8"/>
-      <c r="U15" s="8"/>
-      <c r="V15" s="8"/>
-      <c r="W15" s="8"/>
-      <c r="X15" s="8"/>
-      <c r="Y15" s="8"/>
-      <c r="Z15" s="9"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7"/>
+      <c r="R15" s="7"/>
+      <c r="S15" s="7"/>
+      <c r="T15" s="7"/>
+      <c r="U15" s="7"/>
+      <c r="V15" s="7"/>
+      <c r="W15" s="7"/>
+      <c r="X15" s="7"/>
+      <c r="Y15" s="7"/>
     </row>
     <row r="16" ht="15.0" customHeight="1">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="6">
         <v>0.0</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
-      <c r="N16" s="8"/>
-      <c r="O16" s="8"/>
-      <c r="P16" s="8"/>
-      <c r="Q16" s="8"/>
-      <c r="R16" s="8"/>
-      <c r="S16" s="8"/>
-      <c r="T16" s="8"/>
-      <c r="U16" s="8"/>
-      <c r="V16" s="8"/>
-      <c r="W16" s="8"/>
-      <c r="X16" s="8"/>
-      <c r="Y16" s="8"/>
-      <c r="Z16" s="9"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
+      <c r="O16" s="7"/>
+      <c r="P16" s="7"/>
+      <c r="Q16" s="7"/>
+      <c r="R16" s="7"/>
+      <c r="S16" s="7"/>
+      <c r="T16" s="7"/>
+      <c r="U16" s="7"/>
+      <c r="V16" s="7"/>
+      <c r="W16" s="7"/>
+      <c r="X16" s="7"/>
+      <c r="Y16" s="7"/>
     </row>
     <row r="17" ht="15.0" customHeight="1">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="6">
         <v>0.0</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
-      <c r="N17" s="8"/>
-      <c r="O17" s="8"/>
-      <c r="P17" s="8"/>
-      <c r="Q17" s="8"/>
-      <c r="R17" s="8"/>
-      <c r="S17" s="8"/>
-      <c r="T17" s="8"/>
-      <c r="U17" s="8"/>
-      <c r="V17" s="8"/>
-      <c r="W17" s="8"/>
-      <c r="X17" s="8"/>
-      <c r="Y17" s="8"/>
-      <c r="Z17" s="9"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="7"/>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="7"/>
+      <c r="R17" s="7"/>
+      <c r="S17" s="7"/>
+      <c r="T17" s="7"/>
+      <c r="U17" s="7"/>
+      <c r="V17" s="7"/>
+      <c r="W17" s="7"/>
+      <c r="X17" s="7"/>
+      <c r="Y17" s="7"/>
     </row>
     <row r="18" ht="15.0" customHeight="1">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="6">
         <v>0.0</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
-      <c r="N18" s="8"/>
-      <c r="O18" s="8"/>
-      <c r="P18" s="8"/>
-      <c r="Q18" s="8"/>
-      <c r="R18" s="8"/>
-      <c r="S18" s="8"/>
-      <c r="T18" s="8"/>
-      <c r="U18" s="8"/>
-      <c r="V18" s="8"/>
-      <c r="W18" s="8"/>
-      <c r="X18" s="8"/>
-      <c r="Y18" s="8"/>
-      <c r="Z18" s="9"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="7"/>
+      <c r="O18" s="7"/>
+      <c r="P18" s="7"/>
+      <c r="Q18" s="7"/>
+      <c r="R18" s="7"/>
+      <c r="S18" s="7"/>
+      <c r="T18" s="7"/>
+      <c r="U18" s="7"/>
+      <c r="V18" s="7"/>
+      <c r="W18" s="7"/>
+      <c r="X18" s="7"/>
+      <c r="Y18" s="7"/>
     </row>
     <row r="19" ht="15.0" customHeight="1">
       <c r="A19" s="11" t="s">
@@ -2046,2211 +2012,2152 @@
       <c r="W19" s="13"/>
       <c r="X19" s="13"/>
       <c r="Y19" s="13"/>
-      <c r="Z19" s="14"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="B20" s="16">
+      <c r="B20" s="15">
         <v>0.0</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="E20" s="17" t="s">
+      <c r="E20" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="17"/>
-      <c r="L20" s="17"/>
-      <c r="M20" s="17"/>
-      <c r="N20" s="17"/>
-      <c r="O20" s="17"/>
-      <c r="P20" s="17"/>
-      <c r="Q20" s="17"/>
-      <c r="R20" s="17"/>
-      <c r="S20" s="17"/>
-      <c r="T20" s="17"/>
-      <c r="U20" s="17"/>
-      <c r="V20" s="17"/>
-      <c r="W20" s="17"/>
-      <c r="X20" s="17"/>
-      <c r="Y20" s="17"/>
-      <c r="Z20" s="5"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="16"/>
+      <c r="J20" s="16"/>
+      <c r="K20" s="16"/>
+      <c r="L20" s="16"/>
+      <c r="M20" s="16"/>
+      <c r="N20" s="16"/>
+      <c r="O20" s="16"/>
+      <c r="P20" s="16"/>
+      <c r="Q20" s="16"/>
+      <c r="R20" s="16"/>
+      <c r="S20" s="16"/>
+      <c r="T20" s="16"/>
+      <c r="U20" s="16"/>
+      <c r="V20" s="16"/>
+      <c r="W20" s="16"/>
+      <c r="X20" s="16"/>
+      <c r="Y20" s="16"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="B21" s="19">
+      <c r="B21" s="18">
         <v>0.0</v>
       </c>
-      <c r="C21" s="20" t="s">
+      <c r="C21" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="D21" s="20" t="s">
+      <c r="D21" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="E21" s="20" t="s">
+      <c r="E21" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-      <c r="M21" s="20"/>
-      <c r="N21" s="20"/>
-      <c r="O21" s="20"/>
-      <c r="P21" s="20"/>
-      <c r="Q21" s="20"/>
-      <c r="R21" s="20"/>
-      <c r="S21" s="20"/>
-      <c r="T21" s="20"/>
-      <c r="U21" s="20"/>
-      <c r="V21" s="20"/>
-      <c r="W21" s="20"/>
-      <c r="X21" s="20"/>
-      <c r="Y21" s="20"/>
-      <c r="Z21" s="9"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="19"/>
+      <c r="L21" s="19"/>
+      <c r="M21" s="19"/>
+      <c r="N21" s="19"/>
+      <c r="O21" s="19"/>
+      <c r="P21" s="19"/>
+      <c r="Q21" s="19"/>
+      <c r="R21" s="19"/>
+      <c r="S21" s="19"/>
+      <c r="T21" s="19"/>
+      <c r="U21" s="19"/>
+      <c r="V21" s="19"/>
+      <c r="W21" s="19"/>
+      <c r="X21" s="19"/>
+      <c r="Y21" s="19"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="B22" s="19">
+      <c r="B22" s="18">
         <v>0.0</v>
       </c>
-      <c r="C22" s="20" t="s">
+      <c r="C22" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="D22" s="20" t="s">
+      <c r="D22" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="E22" s="20" t="s">
+      <c r="E22" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-      <c r="M22" s="20"/>
-      <c r="N22" s="20"/>
-      <c r="O22" s="20"/>
-      <c r="P22" s="20"/>
-      <c r="Q22" s="20"/>
-      <c r="R22" s="20"/>
-      <c r="S22" s="20"/>
-      <c r="T22" s="20"/>
-      <c r="U22" s="20"/>
-      <c r="V22" s="20"/>
-      <c r="W22" s="20"/>
-      <c r="X22" s="20"/>
-      <c r="Y22" s="20"/>
-      <c r="Z22" s="9"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="19"/>
+      <c r="L22" s="19"/>
+      <c r="M22" s="19"/>
+      <c r="N22" s="19"/>
+      <c r="O22" s="19"/>
+      <c r="P22" s="19"/>
+      <c r="Q22" s="19"/>
+      <c r="R22" s="19"/>
+      <c r="S22" s="19"/>
+      <c r="T22" s="19"/>
+      <c r="U22" s="19"/>
+      <c r="V22" s="19"/>
+      <c r="W22" s="19"/>
+      <c r="X22" s="19"/>
+      <c r="Y22" s="19"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="18" t="s">
+      <c r="A23" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="B23" s="19">
+      <c r="B23" s="18">
         <v>0.0</v>
       </c>
-      <c r="C23" s="20" t="s">
+      <c r="C23" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="D23" s="20" t="s">
+      <c r="D23" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="E23" s="20" t="s">
+      <c r="E23" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-      <c r="M23" s="20"/>
-      <c r="N23" s="20"/>
-      <c r="O23" s="20"/>
-      <c r="P23" s="20"/>
-      <c r="Q23" s="20"/>
-      <c r="R23" s="20"/>
-      <c r="S23" s="20"/>
-      <c r="T23" s="20"/>
-      <c r="U23" s="20"/>
-      <c r="V23" s="20"/>
-      <c r="W23" s="20"/>
-      <c r="X23" s="20"/>
-      <c r="Y23" s="20"/>
-      <c r="Z23" s="9"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="19"/>
+      <c r="M23" s="19"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="19"/>
+      <c r="P23" s="19"/>
+      <c r="Q23" s="19"/>
+      <c r="R23" s="19"/>
+      <c r="S23" s="19"/>
+      <c r="T23" s="19"/>
+      <c r="U23" s="19"/>
+      <c r="V23" s="19"/>
+      <c r="W23" s="19"/>
+      <c r="X23" s="19"/>
+      <c r="Y23" s="19"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="18" t="s">
+      <c r="A24" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="B24" s="19">
+      <c r="B24" s="18">
         <v>0.0</v>
       </c>
-      <c r="C24" s="20" t="s">
+      <c r="C24" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="D24" s="20" t="s">
+      <c r="D24" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="E24" s="20" t="s">
+      <c r="E24" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-      <c r="M24" s="20"/>
-      <c r="N24" s="20"/>
-      <c r="O24" s="20"/>
-      <c r="P24" s="20"/>
-      <c r="Q24" s="20"/>
-      <c r="R24" s="20"/>
-      <c r="S24" s="20"/>
-      <c r="T24" s="20"/>
-      <c r="U24" s="20"/>
-      <c r="V24" s="20"/>
-      <c r="W24" s="20"/>
-      <c r="X24" s="20"/>
-      <c r="Y24" s="20"/>
-      <c r="Z24" s="9"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="19"/>
+      <c r="K24" s="19"/>
+      <c r="L24" s="19"/>
+      <c r="M24" s="19"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="19"/>
+      <c r="P24" s="19"/>
+      <c r="Q24" s="19"/>
+      <c r="R24" s="19"/>
+      <c r="S24" s="19"/>
+      <c r="T24" s="19"/>
+      <c r="U24" s="19"/>
+      <c r="V24" s="19"/>
+      <c r="W24" s="19"/>
+      <c r="X24" s="19"/>
+      <c r="Y24" s="19"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="18" t="s">
+      <c r="A25" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="B25" s="19">
+      <c r="B25" s="18">
         <v>0.0</v>
       </c>
-      <c r="C25" s="20" t="s">
+      <c r="C25" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="D25" s="20" t="s">
+      <c r="D25" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="E25" s="20" t="s">
+      <c r="E25" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-      <c r="M25" s="20"/>
-      <c r="N25" s="20"/>
-      <c r="O25" s="20"/>
-      <c r="P25" s="20"/>
-      <c r="Q25" s="20"/>
-      <c r="R25" s="20"/>
-      <c r="S25" s="20"/>
-      <c r="T25" s="20"/>
-      <c r="U25" s="20"/>
-      <c r="V25" s="20"/>
-      <c r="W25" s="20"/>
-      <c r="X25" s="20"/>
-      <c r="Y25" s="20"/>
-      <c r="Z25" s="9"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
+      <c r="R25" s="19"/>
+      <c r="S25" s="19"/>
+      <c r="T25" s="19"/>
+      <c r="U25" s="19"/>
+      <c r="V25" s="19"/>
+      <c r="W25" s="19"/>
+      <c r="X25" s="19"/>
+      <c r="Y25" s="19"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="18" t="s">
+      <c r="A26" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="B26" s="19">
+      <c r="B26" s="18">
         <v>0.0</v>
       </c>
-      <c r="C26" s="20" t="s">
+      <c r="C26" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="D26" s="20" t="s">
+      <c r="D26" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="E26" s="20" t="s">
+      <c r="E26" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
-      <c r="K26" s="20"/>
-      <c r="L26" s="20"/>
-      <c r="M26" s="20"/>
-      <c r="N26" s="20"/>
-      <c r="O26" s="20"/>
-      <c r="P26" s="20"/>
-      <c r="Q26" s="20"/>
-      <c r="R26" s="20"/>
-      <c r="S26" s="20"/>
-      <c r="T26" s="20"/>
-      <c r="U26" s="20"/>
-      <c r="V26" s="20"/>
-      <c r="W26" s="20"/>
-      <c r="X26" s="20"/>
-      <c r="Y26" s="20"/>
-      <c r="Z26" s="9"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="19"/>
+      <c r="M26" s="19"/>
+      <c r="N26" s="19"/>
+      <c r="O26" s="19"/>
+      <c r="P26" s="19"/>
+      <c r="Q26" s="19"/>
+      <c r="R26" s="19"/>
+      <c r="S26" s="19"/>
+      <c r="T26" s="19"/>
+      <c r="U26" s="19"/>
+      <c r="V26" s="19"/>
+      <c r="W26" s="19"/>
+      <c r="X26" s="19"/>
+      <c r="Y26" s="19"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="18" t="s">
+      <c r="A27" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="B27" s="19">
+      <c r="B27" s="18">
         <v>0.0</v>
       </c>
-      <c r="C27" s="20" t="s">
+      <c r="C27" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="D27" s="20" t="s">
+      <c r="D27" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="E27" s="20" t="s">
+      <c r="E27" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="20"/>
-      <c r="J27" s="20"/>
-      <c r="K27" s="20"/>
-      <c r="L27" s="20"/>
-      <c r="M27" s="20"/>
-      <c r="N27" s="20"/>
-      <c r="O27" s="20"/>
-      <c r="P27" s="20"/>
-      <c r="Q27" s="20"/>
-      <c r="R27" s="20"/>
-      <c r="S27" s="20"/>
-      <c r="T27" s="20"/>
-      <c r="U27" s="20"/>
-      <c r="V27" s="20"/>
-      <c r="W27" s="20"/>
-      <c r="X27" s="20"/>
-      <c r="Y27" s="20"/>
-      <c r="Z27" s="9"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="19"/>
+      <c r="N27" s="19"/>
+      <c r="O27" s="19"/>
+      <c r="P27" s="19"/>
+      <c r="Q27" s="19"/>
+      <c r="R27" s="19"/>
+      <c r="S27" s="19"/>
+      <c r="T27" s="19"/>
+      <c r="U27" s="19"/>
+      <c r="V27" s="19"/>
+      <c r="W27" s="19"/>
+      <c r="X27" s="19"/>
+      <c r="Y27" s="19"/>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="18" t="s">
+      <c r="A28" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="B28" s="19">
+      <c r="B28" s="18">
         <v>0.0</v>
       </c>
-      <c r="C28" s="20" t="s">
+      <c r="C28" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="D28" s="20" t="s">
+      <c r="D28" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="E28" s="20" t="s">
+      <c r="E28" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="20"/>
-      <c r="K28" s="20"/>
-      <c r="L28" s="20"/>
-      <c r="M28" s="20"/>
-      <c r="N28" s="20"/>
-      <c r="O28" s="20"/>
-      <c r="P28" s="20"/>
-      <c r="Q28" s="20"/>
-      <c r="R28" s="20"/>
-      <c r="S28" s="20"/>
-      <c r="T28" s="20"/>
-      <c r="U28" s="20"/>
-      <c r="V28" s="20"/>
-      <c r="W28" s="20"/>
-      <c r="X28" s="20"/>
-      <c r="Y28" s="20"/>
-      <c r="Z28" s="9"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="19"/>
+      <c r="Q28" s="19"/>
+      <c r="R28" s="19"/>
+      <c r="S28" s="19"/>
+      <c r="T28" s="19"/>
+      <c r="U28" s="19"/>
+      <c r="V28" s="19"/>
+      <c r="W28" s="19"/>
+      <c r="X28" s="19"/>
+      <c r="Y28" s="19"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="18" t="s">
+      <c r="A29" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="B29" s="19">
+      <c r="B29" s="18">
         <v>0.0</v>
       </c>
-      <c r="C29" s="20" t="s">
+      <c r="C29" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="D29" s="20" t="s">
+      <c r="D29" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="E29" s="20" t="s">
+      <c r="E29" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="20"/>
-      <c r="K29" s="20"/>
-      <c r="L29" s="20"/>
-      <c r="M29" s="20"/>
-      <c r="N29" s="20"/>
-      <c r="O29" s="20"/>
-      <c r="P29" s="20"/>
-      <c r="Q29" s="20"/>
-      <c r="R29" s="20"/>
-      <c r="S29" s="20"/>
-      <c r="T29" s="20"/>
-      <c r="U29" s="20"/>
-      <c r="V29" s="20"/>
-      <c r="W29" s="20"/>
-      <c r="X29" s="20"/>
-      <c r="Y29" s="20"/>
-      <c r="Z29" s="9"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="19"/>
+      <c r="O29" s="19"/>
+      <c r="P29" s="19"/>
+      <c r="Q29" s="19"/>
+      <c r="R29" s="19"/>
+      <c r="S29" s="19"/>
+      <c r="T29" s="19"/>
+      <c r="U29" s="19"/>
+      <c r="V29" s="19"/>
+      <c r="W29" s="19"/>
+      <c r="X29" s="19"/>
+      <c r="Y29" s="19"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="18" t="s">
+      <c r="A30" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="B30" s="19">
+      <c r="B30" s="18">
         <v>0.0</v>
       </c>
-      <c r="C30" s="20" t="s">
+      <c r="C30" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="D30" s="20" t="s">
+      <c r="D30" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="E30" s="20" t="s">
+      <c r="E30" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
-      <c r="J30" s="20"/>
-      <c r="K30" s="20"/>
-      <c r="L30" s="20"/>
-      <c r="M30" s="20"/>
-      <c r="N30" s="20"/>
-      <c r="O30" s="20"/>
-      <c r="P30" s="20"/>
-      <c r="Q30" s="20"/>
-      <c r="R30" s="20"/>
-      <c r="S30" s="20"/>
-      <c r="T30" s="20"/>
-      <c r="U30" s="20"/>
-      <c r="V30" s="20"/>
-      <c r="W30" s="20"/>
-      <c r="X30" s="20"/>
-      <c r="Y30" s="20"/>
-      <c r="Z30" s="9"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="19"/>
+      <c r="M30" s="19"/>
+      <c r="N30" s="19"/>
+      <c r="O30" s="19"/>
+      <c r="P30" s="19"/>
+      <c r="Q30" s="19"/>
+      <c r="R30" s="19"/>
+      <c r="S30" s="19"/>
+      <c r="T30" s="19"/>
+      <c r="U30" s="19"/>
+      <c r="V30" s="19"/>
+      <c r="W30" s="19"/>
+      <c r="X30" s="19"/>
+      <c r="Y30" s="19"/>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="18" t="s">
+      <c r="A31" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="B31" s="19">
+      <c r="B31" s="18">
         <v>0.0</v>
       </c>
-      <c r="C31" s="20" t="s">
+      <c r="C31" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="D31" s="20" t="s">
+      <c r="D31" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="E31" s="20" t="s">
+      <c r="E31" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
-      <c r="J31" s="20"/>
-      <c r="K31" s="20"/>
-      <c r="L31" s="20"/>
-      <c r="M31" s="20"/>
-      <c r="N31" s="20"/>
-      <c r="O31" s="20"/>
-      <c r="P31" s="20"/>
-      <c r="Q31" s="20"/>
-      <c r="R31" s="20"/>
-      <c r="S31" s="20"/>
-      <c r="T31" s="20"/>
-      <c r="U31" s="20"/>
-      <c r="V31" s="20"/>
-      <c r="W31" s="20"/>
-      <c r="X31" s="20"/>
-      <c r="Y31" s="20"/>
-      <c r="Z31" s="9"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="19"/>
+      <c r="K31" s="19"/>
+      <c r="L31" s="19"/>
+      <c r="M31" s="19"/>
+      <c r="N31" s="19"/>
+      <c r="O31" s="19"/>
+      <c r="P31" s="19"/>
+      <c r="Q31" s="19"/>
+      <c r="R31" s="19"/>
+      <c r="S31" s="19"/>
+      <c r="T31" s="19"/>
+      <c r="U31" s="19"/>
+      <c r="V31" s="19"/>
+      <c r="W31" s="19"/>
+      <c r="X31" s="19"/>
+      <c r="Y31" s="19"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="18" t="s">
+      <c r="A32" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="B32" s="19">
+      <c r="B32" s="18">
         <v>0.0</v>
       </c>
-      <c r="C32" s="20" t="s">
+      <c r="C32" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="D32" s="20" t="s">
+      <c r="D32" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="E32" s="20" t="s">
+      <c r="E32" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20"/>
-      <c r="J32" s="20"/>
-      <c r="K32" s="20"/>
-      <c r="L32" s="20"/>
-      <c r="M32" s="20"/>
-      <c r="N32" s="20"/>
-      <c r="O32" s="20"/>
-      <c r="P32" s="20"/>
-      <c r="Q32" s="20"/>
-      <c r="R32" s="20"/>
-      <c r="S32" s="20"/>
-      <c r="T32" s="20"/>
-      <c r="U32" s="20"/>
-      <c r="V32" s="20"/>
-      <c r="W32" s="20"/>
-      <c r="X32" s="20"/>
-      <c r="Y32" s="20"/>
-      <c r="Z32" s="9"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="19"/>
+      <c r="K32" s="19"/>
+      <c r="L32" s="19"/>
+      <c r="M32" s="19"/>
+      <c r="N32" s="19"/>
+      <c r="O32" s="19"/>
+      <c r="P32" s="19"/>
+      <c r="Q32" s="19"/>
+      <c r="R32" s="19"/>
+      <c r="S32" s="19"/>
+      <c r="T32" s="19"/>
+      <c r="U32" s="19"/>
+      <c r="V32" s="19"/>
+      <c r="W32" s="19"/>
+      <c r="X32" s="19"/>
+      <c r="Y32" s="19"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="18" t="s">
+      <c r="A33" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="B33" s="19">
+      <c r="B33" s="18">
         <v>0.0</v>
       </c>
-      <c r="C33" s="20" t="s">
+      <c r="C33" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="D33" s="20" t="s">
+      <c r="D33" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="20" t="s">
+      <c r="E33" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="F33" s="20"/>
-      <c r="G33" s="20"/>
-      <c r="H33" s="20"/>
-      <c r="I33" s="20"/>
-      <c r="J33" s="20"/>
-      <c r="K33" s="20"/>
-      <c r="L33" s="20"/>
-      <c r="M33" s="20"/>
-      <c r="N33" s="20"/>
-      <c r="O33" s="20"/>
-      <c r="P33" s="20"/>
-      <c r="Q33" s="20"/>
-      <c r="R33" s="20"/>
-      <c r="S33" s="20"/>
-      <c r="T33" s="20"/>
-      <c r="U33" s="20"/>
-      <c r="V33" s="20"/>
-      <c r="W33" s="20"/>
-      <c r="X33" s="20"/>
-      <c r="Y33" s="20"/>
-      <c r="Z33" s="9"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="19"/>
+      <c r="J33" s="19"/>
+      <c r="K33" s="19"/>
+      <c r="L33" s="19"/>
+      <c r="M33" s="19"/>
+      <c r="N33" s="19"/>
+      <c r="O33" s="19"/>
+      <c r="P33" s="19"/>
+      <c r="Q33" s="19"/>
+      <c r="R33" s="19"/>
+      <c r="S33" s="19"/>
+      <c r="T33" s="19"/>
+      <c r="U33" s="19"/>
+      <c r="V33" s="19"/>
+      <c r="W33" s="19"/>
+      <c r="X33" s="19"/>
+      <c r="Y33" s="19"/>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="18" t="s">
+      <c r="A34" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="B34" s="19">
+      <c r="B34" s="18">
         <v>0.0</v>
       </c>
-      <c r="C34" s="20" t="s">
+      <c r="C34" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="D34" s="20" t="s">
+      <c r="D34" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="E34" s="20" t="s">
+      <c r="E34" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="20"/>
-      <c r="I34" s="20"/>
-      <c r="J34" s="20"/>
-      <c r="K34" s="20"/>
-      <c r="L34" s="20"/>
-      <c r="M34" s="20"/>
-      <c r="N34" s="20"/>
-      <c r="O34" s="20"/>
-      <c r="P34" s="20"/>
-      <c r="Q34" s="20"/>
-      <c r="R34" s="20"/>
-      <c r="S34" s="20"/>
-      <c r="T34" s="20"/>
-      <c r="U34" s="20"/>
-      <c r="V34" s="20"/>
-      <c r="W34" s="20"/>
-      <c r="X34" s="20"/>
-      <c r="Y34" s="20"/>
-      <c r="Z34" s="9"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
+      <c r="I34" s="19"/>
+      <c r="J34" s="19"/>
+      <c r="K34" s="19"/>
+      <c r="L34" s="19"/>
+      <c r="M34" s="19"/>
+      <c r="N34" s="19"/>
+      <c r="O34" s="19"/>
+      <c r="P34" s="19"/>
+      <c r="Q34" s="19"/>
+      <c r="R34" s="19"/>
+      <c r="S34" s="19"/>
+      <c r="T34" s="19"/>
+      <c r="U34" s="19"/>
+      <c r="V34" s="19"/>
+      <c r="W34" s="19"/>
+      <c r="X34" s="19"/>
+      <c r="Y34" s="19"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="18" t="s">
+      <c r="A35" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="B35" s="19">
+      <c r="B35" s="18">
         <v>0.0</v>
       </c>
-      <c r="C35" s="20" t="s">
+      <c r="C35" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D35" s="20" t="s">
+      <c r="D35" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="E35" s="20" t="s">
+      <c r="E35" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
-      <c r="J35" s="20"/>
-      <c r="K35" s="20"/>
-      <c r="L35" s="20"/>
-      <c r="M35" s="20"/>
-      <c r="N35" s="20"/>
-      <c r="O35" s="20"/>
-      <c r="P35" s="20"/>
-      <c r="Q35" s="20"/>
-      <c r="R35" s="20"/>
-      <c r="S35" s="20"/>
-      <c r="T35" s="20"/>
-      <c r="U35" s="20"/>
-      <c r="V35" s="20"/>
-      <c r="W35" s="20"/>
-      <c r="X35" s="20"/>
-      <c r="Y35" s="20"/>
-      <c r="Z35" s="9"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="19"/>
+      <c r="I35" s="19"/>
+      <c r="J35" s="19"/>
+      <c r="K35" s="19"/>
+      <c r="L35" s="19"/>
+      <c r="M35" s="19"/>
+      <c r="N35" s="19"/>
+      <c r="O35" s="19"/>
+      <c r="P35" s="19"/>
+      <c r="Q35" s="19"/>
+      <c r="R35" s="19"/>
+      <c r="S35" s="19"/>
+      <c r="T35" s="19"/>
+      <c r="U35" s="19"/>
+      <c r="V35" s="19"/>
+      <c r="W35" s="19"/>
+      <c r="X35" s="19"/>
+      <c r="Y35" s="19"/>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="18" t="s">
+      <c r="A36" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="B36" s="19">
+      <c r="B36" s="18">
         <v>0.0</v>
       </c>
-      <c r="C36" s="20" t="s">
+      <c r="C36" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="D36" s="20" t="s">
+      <c r="D36" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="E36" s="20" t="s">
+      <c r="E36" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="F36" s="20"/>
-      <c r="G36" s="20"/>
-      <c r="H36" s="20"/>
-      <c r="I36" s="20"/>
-      <c r="J36" s="20"/>
-      <c r="K36" s="20"/>
-      <c r="L36" s="20"/>
-      <c r="M36" s="20"/>
-      <c r="N36" s="20"/>
-      <c r="O36" s="20"/>
-      <c r="P36" s="20"/>
-      <c r="Q36" s="20"/>
-      <c r="R36" s="20"/>
-      <c r="S36" s="20"/>
-      <c r="T36" s="20"/>
-      <c r="U36" s="20"/>
-      <c r="V36" s="20"/>
-      <c r="W36" s="20"/>
-      <c r="X36" s="20"/>
-      <c r="Y36" s="20"/>
-      <c r="Z36" s="9"/>
+      <c r="F36" s="19"/>
+      <c r="G36" s="19"/>
+      <c r="H36" s="19"/>
+      <c r="I36" s="19"/>
+      <c r="J36" s="19"/>
+      <c r="K36" s="19"/>
+      <c r="L36" s="19"/>
+      <c r="M36" s="19"/>
+      <c r="N36" s="19"/>
+      <c r="O36" s="19"/>
+      <c r="P36" s="19"/>
+      <c r="Q36" s="19"/>
+      <c r="R36" s="19"/>
+      <c r="S36" s="19"/>
+      <c r="T36" s="19"/>
+      <c r="U36" s="19"/>
+      <c r="V36" s="19"/>
+      <c r="W36" s="19"/>
+      <c r="X36" s="19"/>
+      <c r="Y36" s="19"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="18" t="s">
+      <c r="A37" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="B37" s="19">
+      <c r="B37" s="18">
         <v>0.0</v>
       </c>
-      <c r="C37" s="20" t="s">
+      <c r="C37" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="D37" s="20" t="s">
+      <c r="D37" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="E37" s="20" t="s">
+      <c r="E37" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="F37" s="20"/>
-      <c r="G37" s="20"/>
-      <c r="H37" s="20"/>
-      <c r="I37" s="20"/>
-      <c r="J37" s="20"/>
-      <c r="K37" s="20"/>
-      <c r="L37" s="20"/>
-      <c r="M37" s="20"/>
-      <c r="N37" s="20"/>
-      <c r="O37" s="20"/>
-      <c r="P37" s="20"/>
-      <c r="Q37" s="20"/>
-      <c r="R37" s="20"/>
-      <c r="S37" s="20"/>
-      <c r="T37" s="20"/>
-      <c r="U37" s="20"/>
-      <c r="V37" s="20"/>
-      <c r="W37" s="20"/>
-      <c r="X37" s="20"/>
-      <c r="Y37" s="20"/>
-      <c r="Z37" s="9"/>
+      <c r="F37" s="19"/>
+      <c r="G37" s="19"/>
+      <c r="H37" s="19"/>
+      <c r="I37" s="19"/>
+      <c r="J37" s="19"/>
+      <c r="K37" s="19"/>
+      <c r="L37" s="19"/>
+      <c r="M37" s="19"/>
+      <c r="N37" s="19"/>
+      <c r="O37" s="19"/>
+      <c r="P37" s="19"/>
+      <c r="Q37" s="19"/>
+      <c r="R37" s="19"/>
+      <c r="S37" s="19"/>
+      <c r="T37" s="19"/>
+      <c r="U37" s="19"/>
+      <c r="V37" s="19"/>
+      <c r="W37" s="19"/>
+      <c r="X37" s="19"/>
+      <c r="Y37" s="19"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="18" t="s">
+      <c r="A38" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="B38" s="19">
+      <c r="B38" s="18">
         <v>0.0</v>
       </c>
-      <c r="C38" s="20" t="s">
+      <c r="C38" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="D38" s="20" t="s">
+      <c r="D38" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="E38" s="20" t="s">
+      <c r="E38" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="F38" s="20"/>
-      <c r="G38" s="20"/>
-      <c r="H38" s="20"/>
-      <c r="I38" s="20"/>
-      <c r="J38" s="20"/>
-      <c r="K38" s="20"/>
-      <c r="L38" s="20"/>
-      <c r="M38" s="20"/>
-      <c r="N38" s="20"/>
-      <c r="O38" s="20"/>
-      <c r="P38" s="20"/>
-      <c r="Q38" s="20"/>
-      <c r="R38" s="20"/>
-      <c r="S38" s="20"/>
-      <c r="T38" s="20"/>
-      <c r="U38" s="20"/>
-      <c r="V38" s="20"/>
-      <c r="W38" s="20"/>
-      <c r="X38" s="20"/>
-      <c r="Y38" s="20"/>
-      <c r="Z38" s="9"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="19"/>
+      <c r="K38" s="19"/>
+      <c r="L38" s="19"/>
+      <c r="M38" s="19"/>
+      <c r="N38" s="19"/>
+      <c r="O38" s="19"/>
+      <c r="P38" s="19"/>
+      <c r="Q38" s="19"/>
+      <c r="R38" s="19"/>
+      <c r="S38" s="19"/>
+      <c r="T38" s="19"/>
+      <c r="U38" s="19"/>
+      <c r="V38" s="19"/>
+      <c r="W38" s="19"/>
+      <c r="X38" s="19"/>
+      <c r="Y38" s="19"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="18" t="s">
+      <c r="A39" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="B39" s="19">
+      <c r="B39" s="18">
         <v>0.0</v>
       </c>
-      <c r="C39" s="20" t="s">
+      <c r="C39" s="19" t="s">
         <v>154</v>
       </c>
-      <c r="D39" s="20" t="s">
+      <c r="D39" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="E39" s="20" t="s">
+      <c r="E39" s="19" t="s">
         <v>156</v>
       </c>
-      <c r="F39" s="20"/>
-      <c r="G39" s="20"/>
-      <c r="H39" s="20"/>
-      <c r="I39" s="20"/>
-      <c r="J39" s="20"/>
-      <c r="K39" s="20"/>
-      <c r="L39" s="20"/>
-      <c r="M39" s="20"/>
-      <c r="N39" s="20"/>
-      <c r="O39" s="20"/>
-      <c r="P39" s="20"/>
-      <c r="Q39" s="20"/>
-      <c r="R39" s="20"/>
-      <c r="S39" s="20"/>
-      <c r="T39" s="20"/>
-      <c r="U39" s="20"/>
-      <c r="V39" s="20"/>
-      <c r="W39" s="20"/>
-      <c r="X39" s="20"/>
-      <c r="Y39" s="20"/>
-      <c r="Z39" s="9"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="19"/>
+      <c r="K39" s="19"/>
+      <c r="L39" s="19"/>
+      <c r="M39" s="19"/>
+      <c r="N39" s="19"/>
+      <c r="O39" s="19"/>
+      <c r="P39" s="19"/>
+      <c r="Q39" s="19"/>
+      <c r="R39" s="19"/>
+      <c r="S39" s="19"/>
+      <c r="T39" s="19"/>
+      <c r="U39" s="19"/>
+      <c r="V39" s="19"/>
+      <c r="W39" s="19"/>
+      <c r="X39" s="19"/>
+      <c r="Y39" s="19"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="18" t="s">
+      <c r="A40" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="B40" s="19">
+      <c r="B40" s="18">
         <v>0.0</v>
       </c>
-      <c r="C40" s="20" t="s">
+      <c r="C40" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="D40" s="20" t="s">
+      <c r="D40" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="E40" s="20" t="s">
+      <c r="E40" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="F40" s="20"/>
-      <c r="G40" s="20"/>
-      <c r="H40" s="20"/>
-      <c r="I40" s="20"/>
-      <c r="J40" s="20"/>
-      <c r="K40" s="20"/>
-      <c r="L40" s="20"/>
-      <c r="M40" s="20"/>
-      <c r="N40" s="20"/>
-      <c r="O40" s="20"/>
-      <c r="P40" s="20"/>
-      <c r="Q40" s="20"/>
-      <c r="R40" s="20"/>
-      <c r="S40" s="20"/>
-      <c r="T40" s="20"/>
-      <c r="U40" s="20"/>
-      <c r="V40" s="20"/>
-      <c r="W40" s="20"/>
-      <c r="X40" s="20"/>
-      <c r="Y40" s="20"/>
-      <c r="Z40" s="9"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
+      <c r="M40" s="19"/>
+      <c r="N40" s="19"/>
+      <c r="O40" s="19"/>
+      <c r="P40" s="19"/>
+      <c r="Q40" s="19"/>
+      <c r="R40" s="19"/>
+      <c r="S40" s="19"/>
+      <c r="T40" s="19"/>
+      <c r="U40" s="19"/>
+      <c r="V40" s="19"/>
+      <c r="W40" s="19"/>
+      <c r="X40" s="19"/>
+      <c r="Y40" s="19"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="18" t="s">
+      <c r="A41" s="17" t="s">
         <v>161</v>
       </c>
-      <c r="B41" s="19">
+      <c r="B41" s="18">
         <v>0.0</v>
       </c>
-      <c r="C41" s="20" t="s">
+      <c r="C41" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="D41" s="20" t="s">
+      <c r="D41" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="E41" s="20" t="s">
+      <c r="E41" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="F41" s="20"/>
-      <c r="G41" s="20"/>
-      <c r="H41" s="20"/>
-      <c r="I41" s="20"/>
-      <c r="J41" s="20"/>
-      <c r="K41" s="20"/>
-      <c r="L41" s="20"/>
-      <c r="M41" s="20"/>
-      <c r="N41" s="20"/>
-      <c r="O41" s="20"/>
-      <c r="P41" s="20"/>
-      <c r="Q41" s="20"/>
-      <c r="R41" s="20"/>
-      <c r="S41" s="20"/>
-      <c r="T41" s="20"/>
-      <c r="U41" s="20"/>
-      <c r="V41" s="20"/>
-      <c r="W41" s="20"/>
-      <c r="X41" s="20"/>
-      <c r="Y41" s="20"/>
-      <c r="Z41" s="9"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="19"/>
+      <c r="H41" s="19"/>
+      <c r="I41" s="19"/>
+      <c r="J41" s="19"/>
+      <c r="K41" s="19"/>
+      <c r="L41" s="19"/>
+      <c r="M41" s="19"/>
+      <c r="N41" s="19"/>
+      <c r="O41" s="19"/>
+      <c r="P41" s="19"/>
+      <c r="Q41" s="19"/>
+      <c r="R41" s="19"/>
+      <c r="S41" s="19"/>
+      <c r="T41" s="19"/>
+      <c r="U41" s="19"/>
+      <c r="V41" s="19"/>
+      <c r="W41" s="19"/>
+      <c r="X41" s="19"/>
+      <c r="Y41" s="19"/>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="18" t="s">
+      <c r="A42" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="B42" s="19">
+      <c r="B42" s="18">
         <v>0.0</v>
       </c>
-      <c r="C42" s="20" t="s">
+      <c r="C42" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="D42" s="20" t="s">
+      <c r="D42" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="E42" s="20" t="s">
+      <c r="E42" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="F42" s="20"/>
-      <c r="G42" s="20"/>
-      <c r="H42" s="20"/>
-      <c r="I42" s="20"/>
-      <c r="J42" s="20"/>
-      <c r="K42" s="20"/>
-      <c r="L42" s="20"/>
-      <c r="M42" s="20"/>
-      <c r="N42" s="20"/>
-      <c r="O42" s="20"/>
-      <c r="P42" s="20"/>
-      <c r="Q42" s="20"/>
-      <c r="R42" s="20"/>
-      <c r="S42" s="20"/>
-      <c r="T42" s="20"/>
-      <c r="U42" s="20"/>
-      <c r="V42" s="20"/>
-      <c r="W42" s="20"/>
-      <c r="X42" s="20"/>
-      <c r="Y42" s="20"/>
-      <c r="Z42" s="9"/>
+      <c r="F42" s="19"/>
+      <c r="G42" s="19"/>
+      <c r="H42" s="19"/>
+      <c r="I42" s="19"/>
+      <c r="J42" s="19"/>
+      <c r="K42" s="19"/>
+      <c r="L42" s="19"/>
+      <c r="M42" s="19"/>
+      <c r="N42" s="19"/>
+      <c r="O42" s="19"/>
+      <c r="P42" s="19"/>
+      <c r="Q42" s="19"/>
+      <c r="R42" s="19"/>
+      <c r="S42" s="19"/>
+      <c r="T42" s="19"/>
+      <c r="U42" s="19"/>
+      <c r="V42" s="19"/>
+      <c r="W42" s="19"/>
+      <c r="X42" s="19"/>
+      <c r="Y42" s="19"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="18" t="s">
+      <c r="A43" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="B43" s="19">
+      <c r="B43" s="18">
         <v>0.0</v>
       </c>
-      <c r="C43" s="20" t="s">
+      <c r="C43" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="D43" s="20" t="s">
+      <c r="D43" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="E43" s="20" t="s">
+      <c r="E43" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="F43" s="20"/>
-      <c r="G43" s="20"/>
-      <c r="H43" s="20"/>
-      <c r="I43" s="20"/>
-      <c r="J43" s="20"/>
-      <c r="K43" s="20"/>
-      <c r="L43" s="20"/>
-      <c r="M43" s="20"/>
-      <c r="N43" s="20"/>
-      <c r="O43" s="20"/>
-      <c r="P43" s="20"/>
-      <c r="Q43" s="20"/>
-      <c r="R43" s="20"/>
-      <c r="S43" s="20"/>
-      <c r="T43" s="20"/>
-      <c r="U43" s="20"/>
-      <c r="V43" s="20"/>
-      <c r="W43" s="20"/>
-      <c r="X43" s="20"/>
-      <c r="Y43" s="20"/>
-      <c r="Z43" s="9"/>
+      <c r="F43" s="19"/>
+      <c r="G43" s="19"/>
+      <c r="H43" s="19"/>
+      <c r="I43" s="19"/>
+      <c r="J43" s="19"/>
+      <c r="K43" s="19"/>
+      <c r="L43" s="19"/>
+      <c r="M43" s="19"/>
+      <c r="N43" s="19"/>
+      <c r="O43" s="19"/>
+      <c r="P43" s="19"/>
+      <c r="Q43" s="19"/>
+      <c r="R43" s="19"/>
+      <c r="S43" s="19"/>
+      <c r="T43" s="19"/>
+      <c r="U43" s="19"/>
+      <c r="V43" s="19"/>
+      <c r="W43" s="19"/>
+      <c r="X43" s="19"/>
+      <c r="Y43" s="19"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="18" t="s">
+      <c r="A44" s="17" t="s">
         <v>173</v>
       </c>
-      <c r="B44" s="19">
+      <c r="B44" s="18">
         <v>0.0</v>
       </c>
-      <c r="C44" s="20" t="s">
+      <c r="C44" s="19" t="s">
         <v>174</v>
       </c>
-      <c r="D44" s="20" t="s">
+      <c r="D44" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="E44" s="20" t="s">
+      <c r="E44" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="F44" s="20"/>
-      <c r="G44" s="20"/>
-      <c r="H44" s="20"/>
-      <c r="I44" s="20"/>
-      <c r="J44" s="20"/>
-      <c r="K44" s="20"/>
-      <c r="L44" s="20"/>
-      <c r="M44" s="20"/>
-      <c r="N44" s="20"/>
-      <c r="O44" s="20"/>
-      <c r="P44" s="20"/>
-      <c r="Q44" s="20"/>
-      <c r="R44" s="20"/>
-      <c r="S44" s="20"/>
-      <c r="T44" s="20"/>
-      <c r="U44" s="20"/>
-      <c r="V44" s="20"/>
-      <c r="W44" s="20"/>
-      <c r="X44" s="20"/>
-      <c r="Y44" s="20"/>
-      <c r="Z44" s="9"/>
+      <c r="F44" s="19"/>
+      <c r="G44" s="19"/>
+      <c r="H44" s="19"/>
+      <c r="I44" s="19"/>
+      <c r="J44" s="19"/>
+      <c r="K44" s="19"/>
+      <c r="L44" s="19"/>
+      <c r="M44" s="19"/>
+      <c r="N44" s="19"/>
+      <c r="O44" s="19"/>
+      <c r="P44" s="19"/>
+      <c r="Q44" s="19"/>
+      <c r="R44" s="19"/>
+      <c r="S44" s="19"/>
+      <c r="T44" s="19"/>
+      <c r="U44" s="19"/>
+      <c r="V44" s="19"/>
+      <c r="W44" s="19"/>
+      <c r="X44" s="19"/>
+      <c r="Y44" s="19"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="18" t="s">
+      <c r="A45" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="B45" s="19">
+      <c r="B45" s="18">
         <v>0.0</v>
       </c>
-      <c r="C45" s="20" t="s">
+      <c r="C45" s="19" t="s">
         <v>178</v>
       </c>
-      <c r="D45" s="20" t="s">
+      <c r="D45" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="E45" s="20" t="s">
+      <c r="E45" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="F45" s="20"/>
-      <c r="G45" s="20"/>
-      <c r="H45" s="20"/>
-      <c r="I45" s="20"/>
-      <c r="J45" s="20"/>
-      <c r="K45" s="20"/>
-      <c r="L45" s="20"/>
-      <c r="M45" s="20"/>
-      <c r="N45" s="20"/>
-      <c r="O45" s="20"/>
-      <c r="P45" s="20"/>
-      <c r="Q45" s="20"/>
-      <c r="R45" s="20"/>
-      <c r="S45" s="20"/>
-      <c r="T45" s="20"/>
-      <c r="U45" s="20"/>
-      <c r="V45" s="20"/>
-      <c r="W45" s="20"/>
-      <c r="X45" s="20"/>
-      <c r="Y45" s="20"/>
-      <c r="Z45" s="9"/>
+      <c r="F45" s="19"/>
+      <c r="G45" s="19"/>
+      <c r="H45" s="19"/>
+      <c r="I45" s="19"/>
+      <c r="J45" s="19"/>
+      <c r="K45" s="19"/>
+      <c r="L45" s="19"/>
+      <c r="M45" s="19"/>
+      <c r="N45" s="19"/>
+      <c r="O45" s="19"/>
+      <c r="P45" s="19"/>
+      <c r="Q45" s="19"/>
+      <c r="R45" s="19"/>
+      <c r="S45" s="19"/>
+      <c r="T45" s="19"/>
+      <c r="U45" s="19"/>
+      <c r="V45" s="19"/>
+      <c r="W45" s="19"/>
+      <c r="X45" s="19"/>
+      <c r="Y45" s="19"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="18" t="s">
+      <c r="A46" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="B46" s="19">
+      <c r="B46" s="18">
         <v>0.0</v>
       </c>
-      <c r="C46" s="20" t="s">
+      <c r="C46" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="D46" s="20" t="s">
+      <c r="D46" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="E46" s="20" t="s">
+      <c r="E46" s="19" t="s">
         <v>184</v>
       </c>
-      <c r="F46" s="20"/>
-      <c r="G46" s="20"/>
-      <c r="H46" s="20"/>
-      <c r="I46" s="20"/>
-      <c r="J46" s="20"/>
-      <c r="K46" s="20"/>
-      <c r="L46" s="20"/>
-      <c r="M46" s="20"/>
-      <c r="N46" s="20"/>
-      <c r="O46" s="20"/>
-      <c r="P46" s="20"/>
-      <c r="Q46" s="20"/>
-      <c r="R46" s="20"/>
-      <c r="S46" s="20"/>
-      <c r="T46" s="20"/>
-      <c r="U46" s="20"/>
-      <c r="V46" s="20"/>
-      <c r="W46" s="20"/>
-      <c r="X46" s="20"/>
-      <c r="Y46" s="20"/>
-      <c r="Z46" s="9"/>
+      <c r="F46" s="19"/>
+      <c r="G46" s="19"/>
+      <c r="H46" s="19"/>
+      <c r="I46" s="19"/>
+      <c r="J46" s="19"/>
+      <c r="K46" s="19"/>
+      <c r="L46" s="19"/>
+      <c r="M46" s="19"/>
+      <c r="N46" s="19"/>
+      <c r="O46" s="19"/>
+      <c r="P46" s="19"/>
+      <c r="Q46" s="19"/>
+      <c r="R46" s="19"/>
+      <c r="S46" s="19"/>
+      <c r="T46" s="19"/>
+      <c r="U46" s="19"/>
+      <c r="V46" s="19"/>
+      <c r="W46" s="19"/>
+      <c r="X46" s="19"/>
+      <c r="Y46" s="19"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="18" t="s">
+      <c r="A47" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="B47" s="19">
+      <c r="B47" s="18">
         <v>0.0</v>
       </c>
-      <c r="C47" s="20" t="s">
+      <c r="C47" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="D47" s="20" t="s">
+      <c r="D47" s="19" t="s">
         <v>187</v>
       </c>
-      <c r="E47" s="20" t="s">
+      <c r="E47" s="19" t="s">
         <v>188</v>
       </c>
-      <c r="F47" s="20"/>
-      <c r="G47" s="20"/>
-      <c r="H47" s="20"/>
-      <c r="I47" s="20"/>
-      <c r="J47" s="20"/>
-      <c r="K47" s="20"/>
-      <c r="L47" s="20"/>
-      <c r="M47" s="20"/>
-      <c r="N47" s="20"/>
-      <c r="O47" s="20"/>
-      <c r="P47" s="20"/>
-      <c r="Q47" s="20"/>
-      <c r="R47" s="20"/>
-      <c r="S47" s="20"/>
-      <c r="T47" s="20"/>
-      <c r="U47" s="20"/>
-      <c r="V47" s="20"/>
-      <c r="W47" s="20"/>
-      <c r="X47" s="20"/>
-      <c r="Y47" s="20"/>
-      <c r="Z47" s="9"/>
+      <c r="F47" s="19"/>
+      <c r="G47" s="19"/>
+      <c r="H47" s="19"/>
+      <c r="I47" s="19"/>
+      <c r="J47" s="19"/>
+      <c r="K47" s="19"/>
+      <c r="L47" s="19"/>
+      <c r="M47" s="19"/>
+      <c r="N47" s="19"/>
+      <c r="O47" s="19"/>
+      <c r="P47" s="19"/>
+      <c r="Q47" s="19"/>
+      <c r="R47" s="19"/>
+      <c r="S47" s="19"/>
+      <c r="T47" s="19"/>
+      <c r="U47" s="19"/>
+      <c r="V47" s="19"/>
+      <c r="W47" s="19"/>
+      <c r="X47" s="19"/>
+      <c r="Y47" s="19"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="18" t="s">
+      <c r="A48" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="B48" s="19">
+      <c r="B48" s="18">
         <v>0.0</v>
       </c>
-      <c r="C48" s="20" t="s">
+      <c r="C48" s="19" t="s">
         <v>190</v>
       </c>
-      <c r="D48" s="20" t="s">
+      <c r="D48" s="19" t="s">
         <v>191</v>
       </c>
-      <c r="E48" s="20" t="s">
+      <c r="E48" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="F48" s="20"/>
-      <c r="G48" s="20"/>
-      <c r="H48" s="20"/>
-      <c r="I48" s="20"/>
-      <c r="J48" s="20"/>
-      <c r="K48" s="20"/>
-      <c r="L48" s="20"/>
-      <c r="M48" s="20"/>
-      <c r="N48" s="20"/>
-      <c r="O48" s="20"/>
-      <c r="P48" s="20"/>
-      <c r="Q48" s="20"/>
-      <c r="R48" s="20"/>
-      <c r="S48" s="20"/>
-      <c r="T48" s="20"/>
-      <c r="U48" s="20"/>
-      <c r="V48" s="20"/>
-      <c r="W48" s="20"/>
-      <c r="X48" s="20"/>
-      <c r="Y48" s="20"/>
-      <c r="Z48" s="9"/>
+      <c r="F48" s="19"/>
+      <c r="G48" s="19"/>
+      <c r="H48" s="19"/>
+      <c r="I48" s="19"/>
+      <c r="J48" s="19"/>
+      <c r="K48" s="19"/>
+      <c r="L48" s="19"/>
+      <c r="M48" s="19"/>
+      <c r="N48" s="19"/>
+      <c r="O48" s="19"/>
+      <c r="P48" s="19"/>
+      <c r="Q48" s="19"/>
+      <c r="R48" s="19"/>
+      <c r="S48" s="19"/>
+      <c r="T48" s="19"/>
+      <c r="U48" s="19"/>
+      <c r="V48" s="19"/>
+      <c r="W48" s="19"/>
+      <c r="X48" s="19"/>
+      <c r="Y48" s="19"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="18" t="s">
+      <c r="A49" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="B49" s="19">
+      <c r="B49" s="18">
         <v>0.0</v>
       </c>
-      <c r="C49" s="20" t="s">
+      <c r="C49" s="19" t="s">
         <v>194</v>
       </c>
-      <c r="D49" s="20" t="s">
+      <c r="D49" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="E49" s="20" t="s">
+      <c r="E49" s="19" t="s">
         <v>196</v>
       </c>
-      <c r="F49" s="20"/>
-      <c r="G49" s="20"/>
-      <c r="H49" s="20"/>
-      <c r="I49" s="20"/>
-      <c r="J49" s="20"/>
-      <c r="K49" s="20"/>
-      <c r="L49" s="20"/>
-      <c r="M49" s="20"/>
-      <c r="N49" s="20"/>
-      <c r="O49" s="20"/>
-      <c r="P49" s="20"/>
-      <c r="Q49" s="20"/>
-      <c r="R49" s="20"/>
-      <c r="S49" s="20"/>
-      <c r="T49" s="20"/>
-      <c r="U49" s="20"/>
-      <c r="V49" s="20"/>
-      <c r="W49" s="20"/>
-      <c r="X49" s="20"/>
-      <c r="Y49" s="20"/>
-      <c r="Z49" s="9"/>
+      <c r="F49" s="19"/>
+      <c r="G49" s="19"/>
+      <c r="H49" s="19"/>
+      <c r="I49" s="19"/>
+      <c r="J49" s="19"/>
+      <c r="K49" s="19"/>
+      <c r="L49" s="19"/>
+      <c r="M49" s="19"/>
+      <c r="N49" s="19"/>
+      <c r="O49" s="19"/>
+      <c r="P49" s="19"/>
+      <c r="Q49" s="19"/>
+      <c r="R49" s="19"/>
+      <c r="S49" s="19"/>
+      <c r="T49" s="19"/>
+      <c r="U49" s="19"/>
+      <c r="V49" s="19"/>
+      <c r="W49" s="19"/>
+      <c r="X49" s="19"/>
+      <c r="Y49" s="19"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="18" t="s">
+      <c r="A50" s="17" t="s">
         <v>197</v>
       </c>
-      <c r="B50" s="19">
+      <c r="B50" s="18">
         <v>0.0</v>
       </c>
-      <c r="C50" s="20" t="s">
+      <c r="C50" s="19" t="s">
         <v>198</v>
       </c>
-      <c r="D50" s="20" t="s">
+      <c r="D50" s="19" t="s">
         <v>199</v>
       </c>
-      <c r="E50" s="20" t="s">
+      <c r="E50" s="19" t="s">
         <v>200</v>
       </c>
-      <c r="F50" s="20"/>
-      <c r="G50" s="20"/>
-      <c r="H50" s="20"/>
-      <c r="I50" s="20"/>
-      <c r="J50" s="20"/>
-      <c r="K50" s="20"/>
-      <c r="L50" s="20"/>
-      <c r="M50" s="20"/>
-      <c r="N50" s="20"/>
-      <c r="O50" s="20"/>
-      <c r="P50" s="20"/>
-      <c r="Q50" s="20"/>
-      <c r="R50" s="20"/>
-      <c r="S50" s="20"/>
-      <c r="T50" s="20"/>
-      <c r="U50" s="20"/>
-      <c r="V50" s="20"/>
-      <c r="W50" s="20"/>
-      <c r="X50" s="20"/>
-      <c r="Y50" s="20"/>
-      <c r="Z50" s="9"/>
+      <c r="F50" s="19"/>
+      <c r="G50" s="19"/>
+      <c r="H50" s="19"/>
+      <c r="I50" s="19"/>
+      <c r="J50" s="19"/>
+      <c r="K50" s="19"/>
+      <c r="L50" s="19"/>
+      <c r="M50" s="19"/>
+      <c r="N50" s="19"/>
+      <c r="O50" s="19"/>
+      <c r="P50" s="19"/>
+      <c r="Q50" s="19"/>
+      <c r="R50" s="19"/>
+      <c r="S50" s="19"/>
+      <c r="T50" s="19"/>
+      <c r="U50" s="19"/>
+      <c r="V50" s="19"/>
+      <c r="W50" s="19"/>
+      <c r="X50" s="19"/>
+      <c r="Y50" s="19"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="18" t="s">
+      <c r="A51" s="17" t="s">
         <v>201</v>
       </c>
-      <c r="B51" s="19">
+      <c r="B51" s="18">
         <v>0.0</v>
       </c>
-      <c r="C51" s="20" t="s">
+      <c r="C51" s="19" t="s">
         <v>202</v>
       </c>
-      <c r="D51" s="20" t="s">
+      <c r="D51" s="19" t="s">
         <v>203</v>
       </c>
-      <c r="E51" s="20" t="s">
+      <c r="E51" s="19" t="s">
         <v>204</v>
       </c>
-      <c r="F51" s="20"/>
-      <c r="G51" s="20"/>
-      <c r="H51" s="20"/>
-      <c r="I51" s="20"/>
-      <c r="J51" s="20"/>
-      <c r="K51" s="20"/>
-      <c r="L51" s="20"/>
-      <c r="M51" s="20"/>
-      <c r="N51" s="20"/>
-      <c r="O51" s="20"/>
-      <c r="P51" s="20"/>
-      <c r="Q51" s="20"/>
-      <c r="R51" s="20"/>
-      <c r="S51" s="20"/>
-      <c r="T51" s="20"/>
-      <c r="U51" s="20"/>
-      <c r="V51" s="20"/>
-      <c r="W51" s="20"/>
-      <c r="X51" s="20"/>
-      <c r="Y51" s="20"/>
-      <c r="Z51" s="9"/>
+      <c r="F51" s="19"/>
+      <c r="G51" s="19"/>
+      <c r="H51" s="19"/>
+      <c r="I51" s="19"/>
+      <c r="J51" s="19"/>
+      <c r="K51" s="19"/>
+      <c r="L51" s="19"/>
+      <c r="M51" s="19"/>
+      <c r="N51" s="19"/>
+      <c r="O51" s="19"/>
+      <c r="P51" s="19"/>
+      <c r="Q51" s="19"/>
+      <c r="R51" s="19"/>
+      <c r="S51" s="19"/>
+      <c r="T51" s="19"/>
+      <c r="U51" s="19"/>
+      <c r="V51" s="19"/>
+      <c r="W51" s="19"/>
+      <c r="X51" s="19"/>
+      <c r="Y51" s="19"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="18" t="s">
+      <c r="A52" s="17" t="s">
         <v>205</v>
       </c>
-      <c r="B52" s="19">
+      <c r="B52" s="18">
         <v>0.0</v>
       </c>
-      <c r="C52" s="20" t="s">
+      <c r="C52" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="D52" s="20" t="s">
+      <c r="D52" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="E52" s="20" t="s">
+      <c r="E52" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="F52" s="20"/>
-      <c r="G52" s="20"/>
-      <c r="H52" s="20"/>
-      <c r="I52" s="20"/>
-      <c r="J52" s="20"/>
-      <c r="K52" s="20"/>
-      <c r="L52" s="20"/>
-      <c r="M52" s="20"/>
-      <c r="N52" s="20"/>
-      <c r="O52" s="20"/>
-      <c r="P52" s="20"/>
-      <c r="Q52" s="20"/>
-      <c r="R52" s="20"/>
-      <c r="S52" s="20"/>
-      <c r="T52" s="20"/>
-      <c r="U52" s="20"/>
-      <c r="V52" s="20"/>
-      <c r="W52" s="20"/>
-      <c r="X52" s="20"/>
-      <c r="Y52" s="20"/>
-      <c r="Z52" s="9"/>
+      <c r="F52" s="19"/>
+      <c r="G52" s="19"/>
+      <c r="H52" s="19"/>
+      <c r="I52" s="19"/>
+      <c r="J52" s="19"/>
+      <c r="K52" s="19"/>
+      <c r="L52" s="19"/>
+      <c r="M52" s="19"/>
+      <c r="N52" s="19"/>
+      <c r="O52" s="19"/>
+      <c r="P52" s="19"/>
+      <c r="Q52" s="19"/>
+      <c r="R52" s="19"/>
+      <c r="S52" s="19"/>
+      <c r="T52" s="19"/>
+      <c r="U52" s="19"/>
+      <c r="V52" s="19"/>
+      <c r="W52" s="19"/>
+      <c r="X52" s="19"/>
+      <c r="Y52" s="19"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="18" t="s">
+      <c r="A53" s="17" t="s">
         <v>209</v>
       </c>
-      <c r="B53" s="19">
+      <c r="B53" s="18">
         <v>0.0</v>
       </c>
-      <c r="C53" s="20" t="s">
+      <c r="C53" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="D53" s="20" t="s">
+      <c r="D53" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="E53" s="20" t="s">
+      <c r="E53" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="F53" s="20"/>
-      <c r="G53" s="20"/>
-      <c r="H53" s="20"/>
-      <c r="I53" s="20"/>
-      <c r="J53" s="20"/>
-      <c r="K53" s="20"/>
-      <c r="L53" s="20"/>
-      <c r="M53" s="20"/>
-      <c r="N53" s="20"/>
-      <c r="O53" s="20"/>
-      <c r="P53" s="20"/>
-      <c r="Q53" s="20"/>
-      <c r="R53" s="20"/>
-      <c r="S53" s="20"/>
-      <c r="T53" s="20"/>
-      <c r="U53" s="20"/>
-      <c r="V53" s="20"/>
-      <c r="W53" s="20"/>
-      <c r="X53" s="20"/>
-      <c r="Y53" s="20"/>
-      <c r="Z53" s="9"/>
+      <c r="F53" s="19"/>
+      <c r="G53" s="19"/>
+      <c r="H53" s="19"/>
+      <c r="I53" s="19"/>
+      <c r="J53" s="19"/>
+      <c r="K53" s="19"/>
+      <c r="L53" s="19"/>
+      <c r="M53" s="19"/>
+      <c r="N53" s="19"/>
+      <c r="O53" s="19"/>
+      <c r="P53" s="19"/>
+      <c r="Q53" s="19"/>
+      <c r="R53" s="19"/>
+      <c r="S53" s="19"/>
+      <c r="T53" s="19"/>
+      <c r="U53" s="19"/>
+      <c r="V53" s="19"/>
+      <c r="W53" s="19"/>
+      <c r="X53" s="19"/>
+      <c r="Y53" s="19"/>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="18" t="s">
+      <c r="A54" s="17" t="s">
         <v>211</v>
       </c>
-      <c r="B54" s="19">
+      <c r="B54" s="18">
         <v>0.0</v>
       </c>
-      <c r="C54" s="20" t="s">
+      <c r="C54" s="19" t="s">
         <v>212</v>
       </c>
-      <c r="D54" s="20" t="s">
+      <c r="D54" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="E54" s="20" t="s">
+      <c r="E54" s="19" t="s">
         <v>214</v>
       </c>
-      <c r="F54" s="20"/>
-      <c r="G54" s="20"/>
-      <c r="H54" s="20"/>
-      <c r="I54" s="20"/>
-      <c r="J54" s="20"/>
-      <c r="K54" s="20"/>
-      <c r="L54" s="20"/>
-      <c r="M54" s="20"/>
-      <c r="N54" s="20"/>
-      <c r="O54" s="20"/>
-      <c r="P54" s="20"/>
-      <c r="Q54" s="20"/>
-      <c r="R54" s="20"/>
-      <c r="S54" s="20"/>
-      <c r="T54" s="20"/>
-      <c r="U54" s="20"/>
-      <c r="V54" s="20"/>
-      <c r="W54" s="20"/>
-      <c r="X54" s="20"/>
-      <c r="Y54" s="20"/>
-      <c r="Z54" s="9"/>
+      <c r="F54" s="19"/>
+      <c r="G54" s="19"/>
+      <c r="H54" s="19"/>
+      <c r="I54" s="19"/>
+      <c r="J54" s="19"/>
+      <c r="K54" s="19"/>
+      <c r="L54" s="19"/>
+      <c r="M54" s="19"/>
+      <c r="N54" s="19"/>
+      <c r="O54" s="19"/>
+      <c r="P54" s="19"/>
+      <c r="Q54" s="19"/>
+      <c r="R54" s="19"/>
+      <c r="S54" s="19"/>
+      <c r="T54" s="19"/>
+      <c r="U54" s="19"/>
+      <c r="V54" s="19"/>
+      <c r="W54" s="19"/>
+      <c r="X54" s="19"/>
+      <c r="Y54" s="19"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="18" t="s">
+      <c r="A55" s="17" t="s">
         <v>215</v>
       </c>
-      <c r="B55" s="19">
+      <c r="B55" s="18">
         <v>0.0</v>
       </c>
-      <c r="C55" s="20" t="s">
+      <c r="C55" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="D55" s="20" t="s">
+      <c r="D55" s="19" t="s">
         <v>217</v>
       </c>
-      <c r="E55" s="20" t="s">
+      <c r="E55" s="19" t="s">
         <v>218</v>
       </c>
-      <c r="F55" s="20"/>
-      <c r="G55" s="20"/>
-      <c r="H55" s="20"/>
-      <c r="I55" s="20"/>
-      <c r="J55" s="20"/>
-      <c r="K55" s="20"/>
-      <c r="L55" s="20"/>
-      <c r="M55" s="20"/>
-      <c r="N55" s="20"/>
-      <c r="O55" s="20"/>
-      <c r="P55" s="20"/>
-      <c r="Q55" s="20"/>
-      <c r="R55" s="20"/>
-      <c r="S55" s="20"/>
-      <c r="T55" s="20"/>
-      <c r="U55" s="20"/>
-      <c r="V55" s="20"/>
-      <c r="W55" s="20"/>
-      <c r="X55" s="20"/>
-      <c r="Y55" s="20"/>
-      <c r="Z55" s="9"/>
+      <c r="F55" s="19"/>
+      <c r="G55" s="19"/>
+      <c r="H55" s="19"/>
+      <c r="I55" s="19"/>
+      <c r="J55" s="19"/>
+      <c r="K55" s="19"/>
+      <c r="L55" s="19"/>
+      <c r="M55" s="19"/>
+      <c r="N55" s="19"/>
+      <c r="O55" s="19"/>
+      <c r="P55" s="19"/>
+      <c r="Q55" s="19"/>
+      <c r="R55" s="19"/>
+      <c r="S55" s="19"/>
+      <c r="T55" s="19"/>
+      <c r="U55" s="19"/>
+      <c r="V55" s="19"/>
+      <c r="W55" s="19"/>
+      <c r="X55" s="19"/>
+      <c r="Y55" s="19"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="18" t="s">
+      <c r="A56" s="17" t="s">
         <v>219</v>
       </c>
-      <c r="B56" s="19">
+      <c r="B56" s="18">
         <v>0.0</v>
       </c>
-      <c r="C56" s="20" t="s">
+      <c r="C56" s="19" t="s">
         <v>220</v>
       </c>
-      <c r="D56" s="20" t="s">
+      <c r="D56" s="19" t="s">
         <v>221</v>
       </c>
-      <c r="E56" s="20" t="s">
+      <c r="E56" s="19" t="s">
         <v>222</v>
       </c>
-      <c r="F56" s="20"/>
-      <c r="G56" s="20"/>
-      <c r="H56" s="20"/>
-      <c r="I56" s="20"/>
-      <c r="J56" s="20"/>
-      <c r="K56" s="20"/>
-      <c r="L56" s="20"/>
-      <c r="M56" s="20"/>
-      <c r="N56" s="20"/>
-      <c r="O56" s="20"/>
-      <c r="P56" s="20"/>
-      <c r="Q56" s="20"/>
-      <c r="R56" s="20"/>
-      <c r="S56" s="20"/>
-      <c r="T56" s="20"/>
-      <c r="U56" s="20"/>
-      <c r="V56" s="20"/>
-      <c r="W56" s="20"/>
-      <c r="X56" s="20"/>
-      <c r="Y56" s="20"/>
-      <c r="Z56" s="9"/>
+      <c r="F56" s="19"/>
+      <c r="G56" s="19"/>
+      <c r="H56" s="19"/>
+      <c r="I56" s="19"/>
+      <c r="J56" s="19"/>
+      <c r="K56" s="19"/>
+      <c r="L56" s="19"/>
+      <c r="M56" s="19"/>
+      <c r="N56" s="19"/>
+      <c r="O56" s="19"/>
+      <c r="P56" s="19"/>
+      <c r="Q56" s="19"/>
+      <c r="R56" s="19"/>
+      <c r="S56" s="19"/>
+      <c r="T56" s="19"/>
+      <c r="U56" s="19"/>
+      <c r="V56" s="19"/>
+      <c r="W56" s="19"/>
+      <c r="X56" s="19"/>
+      <c r="Y56" s="19"/>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="18" t="s">
+      <c r="A57" s="17" t="s">
         <v>223</v>
       </c>
-      <c r="B57" s="19">
+      <c r="B57" s="18">
         <v>0.0</v>
       </c>
-      <c r="C57" s="20" t="s">
+      <c r="C57" s="19" t="s">
         <v>224</v>
       </c>
-      <c r="D57" s="20" t="s">
+      <c r="D57" s="19" t="s">
         <v>225</v>
       </c>
-      <c r="E57" s="20" t="s">
+      <c r="E57" s="19" t="s">
         <v>226</v>
       </c>
-      <c r="F57" s="20"/>
-      <c r="G57" s="20"/>
-      <c r="H57" s="20"/>
-      <c r="I57" s="20"/>
-      <c r="J57" s="20"/>
-      <c r="K57" s="20"/>
-      <c r="L57" s="20"/>
-      <c r="M57" s="20"/>
-      <c r="N57" s="20"/>
-      <c r="O57" s="20"/>
-      <c r="P57" s="20"/>
-      <c r="Q57" s="20"/>
-      <c r="R57" s="20"/>
-      <c r="S57" s="20"/>
-      <c r="T57" s="20"/>
-      <c r="U57" s="20"/>
-      <c r="V57" s="20"/>
-      <c r="W57" s="20"/>
-      <c r="X57" s="20"/>
-      <c r="Y57" s="20"/>
-      <c r="Z57" s="9"/>
+      <c r="F57" s="19"/>
+      <c r="G57" s="19"/>
+      <c r="H57" s="19"/>
+      <c r="I57" s="19"/>
+      <c r="J57" s="19"/>
+      <c r="K57" s="19"/>
+      <c r="L57" s="19"/>
+      <c r="M57" s="19"/>
+      <c r="N57" s="19"/>
+      <c r="O57" s="19"/>
+      <c r="P57" s="19"/>
+      <c r="Q57" s="19"/>
+      <c r="R57" s="19"/>
+      <c r="S57" s="19"/>
+      <c r="T57" s="19"/>
+      <c r="U57" s="19"/>
+      <c r="V57" s="19"/>
+      <c r="W57" s="19"/>
+      <c r="X57" s="19"/>
+      <c r="Y57" s="19"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="18" t="s">
+      <c r="A58" s="17" t="s">
         <v>227</v>
       </c>
-      <c r="B58" s="19">
+      <c r="B58" s="18">
         <v>0.0</v>
       </c>
-      <c r="C58" s="20" t="s">
+      <c r="C58" s="19" t="s">
         <v>228</v>
       </c>
-      <c r="D58" s="20" t="s">
+      <c r="D58" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="E58" s="20" t="s">
+      <c r="E58" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="F58" s="20"/>
-      <c r="G58" s="20"/>
-      <c r="H58" s="20"/>
-      <c r="I58" s="20"/>
-      <c r="J58" s="20"/>
-      <c r="K58" s="20"/>
-      <c r="L58" s="20"/>
-      <c r="M58" s="20"/>
-      <c r="N58" s="20"/>
-      <c r="O58" s="20"/>
-      <c r="P58" s="20"/>
-      <c r="Q58" s="20"/>
-      <c r="R58" s="20"/>
-      <c r="S58" s="20"/>
-      <c r="T58" s="20"/>
-      <c r="U58" s="20"/>
-      <c r="V58" s="20"/>
-      <c r="W58" s="20"/>
-      <c r="X58" s="20"/>
-      <c r="Y58" s="20"/>
-      <c r="Z58" s="9"/>
+      <c r="F58" s="19"/>
+      <c r="G58" s="19"/>
+      <c r="H58" s="19"/>
+      <c r="I58" s="19"/>
+      <c r="J58" s="19"/>
+      <c r="K58" s="19"/>
+      <c r="L58" s="19"/>
+      <c r="M58" s="19"/>
+      <c r="N58" s="19"/>
+      <c r="O58" s="19"/>
+      <c r="P58" s="19"/>
+      <c r="Q58" s="19"/>
+      <c r="R58" s="19"/>
+      <c r="S58" s="19"/>
+      <c r="T58" s="19"/>
+      <c r="U58" s="19"/>
+      <c r="V58" s="19"/>
+      <c r="W58" s="19"/>
+      <c r="X58" s="19"/>
+      <c r="Y58" s="19"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="18" t="s">
+      <c r="A59" s="17" t="s">
         <v>231</v>
       </c>
-      <c r="B59" s="19">
+      <c r="B59" s="18">
         <v>0.0</v>
       </c>
-      <c r="C59" s="20" t="s">
+      <c r="C59" s="19" t="s">
         <v>232</v>
       </c>
-      <c r="D59" s="20" t="s">
+      <c r="D59" s="19" t="s">
         <v>233</v>
       </c>
-      <c r="E59" s="20" t="s">
+      <c r="E59" s="19" t="s">
         <v>234</v>
       </c>
-      <c r="F59" s="20"/>
-      <c r="G59" s="20"/>
-      <c r="H59" s="20"/>
-      <c r="I59" s="20"/>
-      <c r="J59" s="20"/>
-      <c r="K59" s="20"/>
-      <c r="L59" s="20"/>
-      <c r="M59" s="20"/>
-      <c r="N59" s="20"/>
-      <c r="O59" s="20"/>
-      <c r="P59" s="20"/>
-      <c r="Q59" s="20"/>
-      <c r="R59" s="20"/>
-      <c r="S59" s="20"/>
-      <c r="T59" s="20"/>
-      <c r="U59" s="20"/>
-      <c r="V59" s="20"/>
-      <c r="W59" s="20"/>
-      <c r="X59" s="20"/>
-      <c r="Y59" s="20"/>
-      <c r="Z59" s="9"/>
+      <c r="F59" s="19"/>
+      <c r="G59" s="19"/>
+      <c r="H59" s="19"/>
+      <c r="I59" s="19"/>
+      <c r="J59" s="19"/>
+      <c r="K59" s="19"/>
+      <c r="L59" s="19"/>
+      <c r="M59" s="19"/>
+      <c r="N59" s="19"/>
+      <c r="O59" s="19"/>
+      <c r="P59" s="19"/>
+      <c r="Q59" s="19"/>
+      <c r="R59" s="19"/>
+      <c r="S59" s="19"/>
+      <c r="T59" s="19"/>
+      <c r="U59" s="19"/>
+      <c r="V59" s="19"/>
+      <c r="W59" s="19"/>
+      <c r="X59" s="19"/>
+      <c r="Y59" s="19"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="18" t="s">
+      <c r="A60" s="17" t="s">
         <v>235</v>
       </c>
-      <c r="B60" s="19">
+      <c r="B60" s="18">
         <v>0.0</v>
       </c>
-      <c r="C60" s="20" t="s">
+      <c r="C60" s="19" t="s">
         <v>236</v>
       </c>
-      <c r="D60" s="20" t="s">
+      <c r="D60" s="19" t="s">
         <v>237</v>
       </c>
-      <c r="E60" s="20" t="s">
+      <c r="E60" s="19" t="s">
         <v>238</v>
       </c>
-      <c r="F60" s="20"/>
-      <c r="G60" s="20"/>
-      <c r="H60" s="20"/>
-      <c r="I60" s="20"/>
-      <c r="J60" s="20"/>
-      <c r="K60" s="20"/>
-      <c r="L60" s="20"/>
-      <c r="M60" s="20"/>
-      <c r="N60" s="20"/>
-      <c r="O60" s="20"/>
-      <c r="P60" s="20"/>
-      <c r="Q60" s="20"/>
-      <c r="R60" s="20"/>
-      <c r="S60" s="20"/>
-      <c r="T60" s="20"/>
-      <c r="U60" s="20"/>
-      <c r="V60" s="20"/>
-      <c r="W60" s="20"/>
-      <c r="X60" s="20"/>
-      <c r="Y60" s="20"/>
-      <c r="Z60" s="9"/>
+      <c r="F60" s="19"/>
+      <c r="G60" s="19"/>
+      <c r="H60" s="19"/>
+      <c r="I60" s="19"/>
+      <c r="J60" s="19"/>
+      <c r="K60" s="19"/>
+      <c r="L60" s="19"/>
+      <c r="M60" s="19"/>
+      <c r="N60" s="19"/>
+      <c r="O60" s="19"/>
+      <c r="P60" s="19"/>
+      <c r="Q60" s="19"/>
+      <c r="R60" s="19"/>
+      <c r="S60" s="19"/>
+      <c r="T60" s="19"/>
+      <c r="U60" s="19"/>
+      <c r="V60" s="19"/>
+      <c r="W60" s="19"/>
+      <c r="X60" s="19"/>
+      <c r="Y60" s="19"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="18" t="s">
+      <c r="A61" s="17" t="s">
         <v>239</v>
       </c>
-      <c r="B61" s="19">
+      <c r="B61" s="18">
         <v>0.0</v>
       </c>
-      <c r="C61" s="20" t="s">
+      <c r="C61" s="19" t="s">
         <v>240</v>
       </c>
-      <c r="D61" s="20" t="s">
+      <c r="D61" s="19" t="s">
         <v>241</v>
       </c>
-      <c r="E61" s="20" t="s">
+      <c r="E61" s="19" t="s">
         <v>242</v>
       </c>
-      <c r="F61" s="20"/>
-      <c r="G61" s="20"/>
-      <c r="H61" s="20"/>
-      <c r="I61" s="20"/>
-      <c r="J61" s="20"/>
-      <c r="K61" s="20"/>
-      <c r="L61" s="20"/>
-      <c r="M61" s="20"/>
-      <c r="N61" s="20"/>
-      <c r="O61" s="20"/>
-      <c r="P61" s="20"/>
-      <c r="Q61" s="20"/>
-      <c r="R61" s="20"/>
-      <c r="S61" s="20"/>
-      <c r="T61" s="20"/>
-      <c r="U61" s="20"/>
-      <c r="V61" s="20"/>
-      <c r="W61" s="20"/>
-      <c r="X61" s="20"/>
-      <c r="Y61" s="20"/>
-      <c r="Z61" s="9"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="19"/>
+      <c r="K61" s="19"/>
+      <c r="L61" s="19"/>
+      <c r="M61" s="19"/>
+      <c r="N61" s="19"/>
+      <c r="O61" s="19"/>
+      <c r="P61" s="19"/>
+      <c r="Q61" s="19"/>
+      <c r="R61" s="19"/>
+      <c r="S61" s="19"/>
+      <c r="T61" s="19"/>
+      <c r="U61" s="19"/>
+      <c r="V61" s="19"/>
+      <c r="W61" s="19"/>
+      <c r="X61" s="19"/>
+      <c r="Y61" s="19"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="18" t="s">
+      <c r="A62" s="17" t="s">
         <v>243</v>
       </c>
-      <c r="B62" s="19">
+      <c r="B62" s="18">
         <v>0.0</v>
       </c>
-      <c r="C62" s="20" t="s">
+      <c r="C62" s="19" t="s">
         <v>244</v>
       </c>
-      <c r="D62" s="20" t="s">
+      <c r="D62" s="19" t="s">
         <v>245</v>
       </c>
-      <c r="E62" s="20" t="s">
+      <c r="E62" s="19" t="s">
         <v>246</v>
       </c>
-      <c r="F62" s="20"/>
-      <c r="G62" s="20"/>
-      <c r="H62" s="20"/>
-      <c r="I62" s="20"/>
-      <c r="J62" s="20"/>
-      <c r="K62" s="20"/>
-      <c r="L62" s="20"/>
-      <c r="M62" s="20"/>
-      <c r="N62" s="20"/>
-      <c r="O62" s="20"/>
-      <c r="P62" s="20"/>
-      <c r="Q62" s="20"/>
-      <c r="R62" s="20"/>
-      <c r="S62" s="20"/>
-      <c r="T62" s="20"/>
-      <c r="U62" s="20"/>
-      <c r="V62" s="20"/>
-      <c r="W62" s="20"/>
-      <c r="X62" s="20"/>
-      <c r="Y62" s="20"/>
-      <c r="Z62" s="9"/>
+      <c r="F62" s="19"/>
+      <c r="G62" s="19"/>
+      <c r="H62" s="19"/>
+      <c r="I62" s="19"/>
+      <c r="J62" s="19"/>
+      <c r="K62" s="19"/>
+      <c r="L62" s="19"/>
+      <c r="M62" s="19"/>
+      <c r="N62" s="19"/>
+      <c r="O62" s="19"/>
+      <c r="P62" s="19"/>
+      <c r="Q62" s="19"/>
+      <c r="R62" s="19"/>
+      <c r="S62" s="19"/>
+      <c r="T62" s="19"/>
+      <c r="U62" s="19"/>
+      <c r="V62" s="19"/>
+      <c r="W62" s="19"/>
+      <c r="X62" s="19"/>
+      <c r="Y62" s="19"/>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="18" t="s">
+      <c r="A63" s="17" t="s">
         <v>247</v>
       </c>
-      <c r="B63" s="19">
+      <c r="B63" s="18">
         <v>0.0</v>
       </c>
-      <c r="C63" s="20" t="s">
+      <c r="C63" s="19" t="s">
         <v>248</v>
       </c>
-      <c r="D63" s="20" t="s">
+      <c r="D63" s="19" t="s">
         <v>249</v>
       </c>
-      <c r="E63" s="20" t="s">
+      <c r="E63" s="19" t="s">
         <v>250</v>
       </c>
-      <c r="F63" s="20"/>
-      <c r="G63" s="20"/>
-      <c r="H63" s="20"/>
-      <c r="I63" s="20"/>
-      <c r="J63" s="20"/>
-      <c r="K63" s="20"/>
-      <c r="L63" s="20"/>
-      <c r="M63" s="20"/>
-      <c r="N63" s="20"/>
-      <c r="O63" s="20"/>
-      <c r="P63" s="20"/>
-      <c r="Q63" s="20"/>
-      <c r="R63" s="20"/>
-      <c r="S63" s="20"/>
-      <c r="T63" s="20"/>
-      <c r="U63" s="20"/>
-      <c r="V63" s="20"/>
-      <c r="W63" s="20"/>
-      <c r="X63" s="20"/>
-      <c r="Y63" s="20"/>
-      <c r="Z63" s="9"/>
+      <c r="F63" s="19"/>
+      <c r="G63" s="19"/>
+      <c r="H63" s="19"/>
+      <c r="I63" s="19"/>
+      <c r="J63" s="19"/>
+      <c r="K63" s="19"/>
+      <c r="L63" s="19"/>
+      <c r="M63" s="19"/>
+      <c r="N63" s="19"/>
+      <c r="O63" s="19"/>
+      <c r="P63" s="19"/>
+      <c r="Q63" s="19"/>
+      <c r="R63" s="19"/>
+      <c r="S63" s="19"/>
+      <c r="T63" s="19"/>
+      <c r="U63" s="19"/>
+      <c r="V63" s="19"/>
+      <c r="W63" s="19"/>
+      <c r="X63" s="19"/>
+      <c r="Y63" s="19"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="18" t="s">
+      <c r="A64" s="17" t="s">
         <v>251</v>
       </c>
-      <c r="B64" s="19">
+      <c r="B64" s="18">
         <v>0.0</v>
       </c>
-      <c r="C64" s="20" t="s">
+      <c r="C64" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D64" s="20" t="s">
+      <c r="D64" s="19" t="s">
         <v>253</v>
       </c>
-      <c r="E64" s="20" t="s">
+      <c r="E64" s="19" t="s">
         <v>254</v>
       </c>
-      <c r="F64" s="20"/>
-      <c r="G64" s="20"/>
-      <c r="H64" s="20"/>
-      <c r="I64" s="20"/>
-      <c r="J64" s="20"/>
-      <c r="K64" s="20"/>
-      <c r="L64" s="20"/>
-      <c r="M64" s="20"/>
-      <c r="N64" s="20"/>
-      <c r="O64" s="20"/>
-      <c r="P64" s="20"/>
-      <c r="Q64" s="20"/>
-      <c r="R64" s="20"/>
-      <c r="S64" s="20"/>
-      <c r="T64" s="20"/>
-      <c r="U64" s="20"/>
-      <c r="V64" s="20"/>
-      <c r="W64" s="20"/>
-      <c r="X64" s="20"/>
-      <c r="Y64" s="20"/>
-      <c r="Z64" s="9"/>
+      <c r="F64" s="19"/>
+      <c r="G64" s="19"/>
+      <c r="H64" s="19"/>
+      <c r="I64" s="19"/>
+      <c r="J64" s="19"/>
+      <c r="K64" s="19"/>
+      <c r="L64" s="19"/>
+      <c r="M64" s="19"/>
+      <c r="N64" s="19"/>
+      <c r="O64" s="19"/>
+      <c r="P64" s="19"/>
+      <c r="Q64" s="19"/>
+      <c r="R64" s="19"/>
+      <c r="S64" s="19"/>
+      <c r="T64" s="19"/>
+      <c r="U64" s="19"/>
+      <c r="V64" s="19"/>
+      <c r="W64" s="19"/>
+      <c r="X64" s="19"/>
+      <c r="Y64" s="19"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="18" t="s">
+      <c r="A65" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="B65" s="19">
+      <c r="B65" s="18">
         <v>0.0</v>
       </c>
-      <c r="C65" s="20" t="s">
+      <c r="C65" s="19" t="s">
         <v>256</v>
       </c>
-      <c r="D65" s="20" t="s">
+      <c r="D65" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="E65" s="20" t="s">
+      <c r="E65" s="19" t="s">
         <v>258</v>
       </c>
-      <c r="F65" s="20"/>
-      <c r="G65" s="20"/>
-      <c r="H65" s="20"/>
-      <c r="I65" s="20"/>
-      <c r="J65" s="20"/>
-      <c r="K65" s="20"/>
-      <c r="L65" s="20"/>
-      <c r="M65" s="20"/>
-      <c r="N65" s="20"/>
-      <c r="O65" s="20"/>
-      <c r="P65" s="20"/>
-      <c r="Q65" s="20"/>
-      <c r="R65" s="20"/>
-      <c r="S65" s="20"/>
-      <c r="T65" s="20"/>
-      <c r="U65" s="20"/>
-      <c r="V65" s="20"/>
-      <c r="W65" s="20"/>
-      <c r="X65" s="20"/>
-      <c r="Y65" s="20"/>
-      <c r="Z65" s="9"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="19"/>
+      <c r="K65" s="19"/>
+      <c r="L65" s="19"/>
+      <c r="M65" s="19"/>
+      <c r="N65" s="19"/>
+      <c r="O65" s="19"/>
+      <c r="P65" s="19"/>
+      <c r="Q65" s="19"/>
+      <c r="R65" s="19"/>
+      <c r="S65" s="19"/>
+      <c r="T65" s="19"/>
+      <c r="U65" s="19"/>
+      <c r="V65" s="19"/>
+      <c r="W65" s="19"/>
+      <c r="X65" s="19"/>
+      <c r="Y65" s="19"/>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="18" t="s">
+      <c r="A66" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="B66" s="19">
+      <c r="B66" s="18">
         <v>0.0</v>
       </c>
-      <c r="C66" s="20" t="s">
+      <c r="C66" s="19" t="s">
         <v>260</v>
       </c>
-      <c r="D66" s="20" t="s">
+      <c r="D66" s="19" t="s">
         <v>261</v>
       </c>
-      <c r="E66" s="20" t="s">
+      <c r="E66" s="19" t="s">
         <v>262</v>
       </c>
-      <c r="F66" s="20"/>
-      <c r="G66" s="20"/>
-      <c r="H66" s="20"/>
-      <c r="I66" s="20"/>
-      <c r="J66" s="20"/>
-      <c r="K66" s="20"/>
-      <c r="L66" s="20"/>
-      <c r="M66" s="20"/>
-      <c r="N66" s="20"/>
-      <c r="O66" s="20"/>
-      <c r="P66" s="20"/>
-      <c r="Q66" s="20"/>
-      <c r="R66" s="20"/>
-      <c r="S66" s="20"/>
-      <c r="T66" s="20"/>
-      <c r="U66" s="20"/>
-      <c r="V66" s="20"/>
-      <c r="W66" s="20"/>
-      <c r="X66" s="20"/>
-      <c r="Y66" s="20"/>
-      <c r="Z66" s="9"/>
+      <c r="F66" s="19"/>
+      <c r="G66" s="19"/>
+      <c r="H66" s="19"/>
+      <c r="I66" s="19"/>
+      <c r="J66" s="19"/>
+      <c r="K66" s="19"/>
+      <c r="L66" s="19"/>
+      <c r="M66" s="19"/>
+      <c r="N66" s="19"/>
+      <c r="O66" s="19"/>
+      <c r="P66" s="19"/>
+      <c r="Q66" s="19"/>
+      <c r="R66" s="19"/>
+      <c r="S66" s="19"/>
+      <c r="T66" s="19"/>
+      <c r="U66" s="19"/>
+      <c r="V66" s="19"/>
+      <c r="W66" s="19"/>
+      <c r="X66" s="19"/>
+      <c r="Y66" s="19"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="18" t="s">
+      <c r="A67" s="17" t="s">
         <v>263</v>
       </c>
-      <c r="B67" s="19">
+      <c r="B67" s="18">
         <v>0.0</v>
       </c>
-      <c r="C67" s="20" t="s">
+      <c r="C67" s="19" t="s">
         <v>264</v>
       </c>
-      <c r="D67" s="20" t="s">
+      <c r="D67" s="19" t="s">
         <v>265</v>
       </c>
-      <c r="E67" s="20" t="s">
+      <c r="E67" s="19" t="s">
         <v>266</v>
       </c>
-      <c r="F67" s="20"/>
-      <c r="G67" s="20"/>
-      <c r="H67" s="20"/>
-      <c r="I67" s="20"/>
-      <c r="J67" s="20"/>
-      <c r="K67" s="20"/>
-      <c r="L67" s="20"/>
-      <c r="M67" s="20"/>
-      <c r="N67" s="20"/>
-      <c r="O67" s="20"/>
-      <c r="P67" s="20"/>
-      <c r="Q67" s="20"/>
-      <c r="R67" s="20"/>
-      <c r="S67" s="20"/>
-      <c r="T67" s="20"/>
-      <c r="U67" s="20"/>
-      <c r="V67" s="20"/>
-      <c r="W67" s="20"/>
-      <c r="X67" s="20"/>
-      <c r="Y67" s="20"/>
-      <c r="Z67" s="9"/>
+      <c r="F67" s="19"/>
+      <c r="G67" s="19"/>
+      <c r="H67" s="19"/>
+      <c r="I67" s="19"/>
+      <c r="J67" s="19"/>
+      <c r="K67" s="19"/>
+      <c r="L67" s="19"/>
+      <c r="M67" s="19"/>
+      <c r="N67" s="19"/>
+      <c r="O67" s="19"/>
+      <c r="P67" s="19"/>
+      <c r="Q67" s="19"/>
+      <c r="R67" s="19"/>
+      <c r="S67" s="19"/>
+      <c r="T67" s="19"/>
+      <c r="U67" s="19"/>
+      <c r="V67" s="19"/>
+      <c r="W67" s="19"/>
+      <c r="X67" s="19"/>
+      <c r="Y67" s="19"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="21" t="s">
+      <c r="A68" s="20" t="s">
         <v>267</v>
       </c>
-      <c r="B68" s="22">
+      <c r="B68" s="21">
         <v>0.0</v>
       </c>
-      <c r="C68" s="23" t="s">
+      <c r="C68" s="22" t="s">
         <v>268</v>
       </c>
-      <c r="D68" s="23" t="s">
+      <c r="D68" s="22" t="s">
         <v>269</v>
       </c>
-      <c r="E68" s="23" t="s">
+      <c r="E68" s="22" t="s">
         <v>270</v>
       </c>
-      <c r="F68" s="23"/>
-      <c r="G68" s="23"/>
-      <c r="H68" s="23"/>
-      <c r="I68" s="23"/>
-      <c r="J68" s="23"/>
-      <c r="K68" s="23"/>
-      <c r="L68" s="23"/>
-      <c r="M68" s="23"/>
-      <c r="N68" s="23"/>
-      <c r="O68" s="23"/>
-      <c r="P68" s="23"/>
-      <c r="Q68" s="23"/>
-      <c r="R68" s="23"/>
-      <c r="S68" s="23"/>
-      <c r="T68" s="23"/>
-      <c r="U68" s="23"/>
-      <c r="V68" s="23"/>
-      <c r="W68" s="23"/>
-      <c r="X68" s="23"/>
-      <c r="Y68" s="23"/>
-      <c r="Z68" s="14"/>
+      <c r="F68" s="22"/>
+      <c r="G68" s="22"/>
+      <c r="H68" s="22"/>
+      <c r="I68" s="22"/>
+      <c r="J68" s="22"/>
+      <c r="K68" s="22"/>
+      <c r="L68" s="22"/>
+      <c r="M68" s="22"/>
+      <c r="N68" s="22"/>
+      <c r="O68" s="22"/>
+      <c r="P68" s="22"/>
+      <c r="Q68" s="22"/>
+      <c r="R68" s="22"/>
+      <c r="S68" s="22"/>
+      <c r="T68" s="22"/>
+      <c r="U68" s="22"/>
+      <c r="V68" s="22"/>
+      <c r="W68" s="22"/>
+      <c r="X68" s="22"/>
+      <c r="Y68" s="22"/>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="24" t="s">
+      <c r="A69" s="23" t="s">
         <v>271</v>
       </c>
-      <c r="B69" s="25">
+      <c r="B69" s="24">
         <v>0.0</v>
       </c>
-      <c r="C69" s="25" t="s">
+      <c r="C69" s="24" t="s">
         <v>272</v>
       </c>
-      <c r="D69" s="25" t="s">
+      <c r="D69" s="24" t="s">
         <v>147</v>
       </c>
-      <c r="E69" s="25" t="s">
+      <c r="E69" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="F69" s="25"/>
-      <c r="G69" s="25"/>
-      <c r="H69" s="25"/>
-      <c r="I69" s="25"/>
-      <c r="J69" s="25"/>
-      <c r="K69" s="25"/>
-      <c r="L69" s="25"/>
-      <c r="M69" s="25"/>
-      <c r="N69" s="25"/>
-      <c r="O69" s="25"/>
-      <c r="P69" s="25"/>
-      <c r="Q69" s="25"/>
-      <c r="R69" s="25"/>
-      <c r="S69" s="25"/>
-      <c r="T69" s="25"/>
-      <c r="U69" s="25"/>
-      <c r="V69" s="25"/>
-      <c r="W69" s="25"/>
-      <c r="X69" s="25"/>
-      <c r="Y69" s="25"/>
-      <c r="Z69" s="5"/>
+      <c r="F69" s="24"/>
+      <c r="G69" s="24"/>
+      <c r="H69" s="24"/>
+      <c r="I69" s="24"/>
+      <c r="J69" s="24"/>
+      <c r="K69" s="24"/>
+      <c r="L69" s="24"/>
+      <c r="M69" s="24"/>
+      <c r="N69" s="24"/>
+      <c r="O69" s="24"/>
+      <c r="P69" s="24"/>
+      <c r="Q69" s="24"/>
+      <c r="R69" s="24"/>
+      <c r="S69" s="24"/>
+      <c r="T69" s="24"/>
+      <c r="U69" s="24"/>
+      <c r="V69" s="24"/>
+      <c r="W69" s="24"/>
+      <c r="X69" s="24"/>
+      <c r="Y69" s="24"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="26" t="s">
+      <c r="A70" s="25" t="s">
         <v>273</v>
       </c>
-      <c r="B70" s="27">
+      <c r="B70" s="26">
         <v>0.0</v>
       </c>
-      <c r="C70" s="27" t="s">
+      <c r="C70" s="26" t="s">
         <v>274</v>
       </c>
-      <c r="D70" s="27" t="s">
+      <c r="D70" s="26" t="s">
         <v>275</v>
       </c>
-      <c r="E70" s="27" t="s">
+      <c r="E70" s="26" t="s">
         <v>276</v>
       </c>
-      <c r="F70" s="27"/>
-      <c r="G70" s="27"/>
-      <c r="H70" s="27"/>
-      <c r="I70" s="27"/>
-      <c r="J70" s="27"/>
-      <c r="K70" s="27"/>
-      <c r="L70" s="27"/>
-      <c r="M70" s="27"/>
-      <c r="N70" s="27"/>
-      <c r="O70" s="27"/>
-      <c r="P70" s="27"/>
-      <c r="Q70" s="27"/>
-      <c r="R70" s="27"/>
-      <c r="S70" s="27"/>
-      <c r="T70" s="27"/>
-      <c r="U70" s="27"/>
-      <c r="V70" s="27"/>
-      <c r="W70" s="27"/>
-      <c r="X70" s="27"/>
-      <c r="Y70" s="27"/>
-      <c r="Z70" s="9"/>
+      <c r="F70" s="26"/>
+      <c r="G70" s="26"/>
+      <c r="H70" s="26"/>
+      <c r="I70" s="26"/>
+      <c r="J70" s="26"/>
+      <c r="K70" s="26"/>
+      <c r="L70" s="26"/>
+      <c r="M70" s="26"/>
+      <c r="N70" s="26"/>
+      <c r="O70" s="26"/>
+      <c r="P70" s="26"/>
+      <c r="Q70" s="26"/>
+      <c r="R70" s="26"/>
+      <c r="S70" s="26"/>
+      <c r="T70" s="26"/>
+      <c r="U70" s="26"/>
+      <c r="V70" s="26"/>
+      <c r="W70" s="26"/>
+      <c r="X70" s="26"/>
+      <c r="Y70" s="26"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="26" t="s">
+      <c r="A71" s="25" t="s">
         <v>277</v>
       </c>
-      <c r="B71" s="27">
+      <c r="B71" s="26">
         <v>0.0</v>
       </c>
-      <c r="C71" s="27" t="s">
+      <c r="C71" s="26" t="s">
         <v>278</v>
       </c>
-      <c r="D71" s="27" t="s">
+      <c r="D71" s="26" t="s">
         <v>175</v>
       </c>
-      <c r="E71" s="27" t="s">
+      <c r="E71" s="26" t="s">
         <v>176</v>
       </c>
-      <c r="F71" s="27"/>
-      <c r="G71" s="27"/>
-      <c r="H71" s="27"/>
-      <c r="I71" s="27"/>
-      <c r="J71" s="27"/>
-      <c r="K71" s="27"/>
-      <c r="L71" s="27"/>
-      <c r="M71" s="27"/>
-      <c r="N71" s="27"/>
-      <c r="O71" s="27"/>
-      <c r="P71" s="27"/>
-      <c r="Q71" s="27"/>
-      <c r="R71" s="27"/>
-      <c r="S71" s="27"/>
-      <c r="T71" s="27"/>
-      <c r="U71" s="27"/>
-      <c r="V71" s="27"/>
-      <c r="W71" s="27"/>
-      <c r="X71" s="27"/>
-      <c r="Y71" s="27"/>
-      <c r="Z71" s="9"/>
+      <c r="F71" s="26"/>
+      <c r="G71" s="26"/>
+      <c r="H71" s="26"/>
+      <c r="I71" s="26"/>
+      <c r="J71" s="26"/>
+      <c r="K71" s="26"/>
+      <c r="L71" s="26"/>
+      <c r="M71" s="26"/>
+      <c r="N71" s="26"/>
+      <c r="O71" s="26"/>
+      <c r="P71" s="26"/>
+      <c r="Q71" s="26"/>
+      <c r="R71" s="26"/>
+      <c r="S71" s="26"/>
+      <c r="T71" s="26"/>
+      <c r="U71" s="26"/>
+      <c r="V71" s="26"/>
+      <c r="W71" s="26"/>
+      <c r="X71" s="26"/>
+      <c r="Y71" s="26"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="26" t="s">
+      <c r="A72" s="25" t="s">
         <v>279</v>
       </c>
-      <c r="B72" s="27">
+      <c r="B72" s="26">
         <v>0.0</v>
       </c>
-      <c r="C72" s="27" t="s">
+      <c r="C72" s="26" t="s">
         <v>280</v>
       </c>
-      <c r="D72" s="27" t="s">
+      <c r="D72" s="26" t="s">
         <v>281</v>
       </c>
-      <c r="E72" s="27" t="s">
+      <c r="E72" s="26" t="s">
         <v>282</v>
       </c>
-      <c r="F72" s="27"/>
-      <c r="G72" s="27"/>
-      <c r="H72" s="27"/>
-      <c r="I72" s="27"/>
-      <c r="J72" s="27"/>
-      <c r="K72" s="27"/>
-      <c r="L72" s="27"/>
-      <c r="M72" s="27"/>
-      <c r="N72" s="27"/>
-      <c r="O72" s="27"/>
-      <c r="P72" s="27"/>
-      <c r="Q72" s="27"/>
-      <c r="R72" s="27"/>
-      <c r="S72" s="27"/>
-      <c r="T72" s="27"/>
-      <c r="U72" s="27"/>
-      <c r="V72" s="27"/>
-      <c r="W72" s="27"/>
-      <c r="X72" s="27"/>
-      <c r="Y72" s="27"/>
-      <c r="Z72" s="9"/>
+      <c r="F72" s="26"/>
+      <c r="G72" s="26"/>
+      <c r="H72" s="26"/>
+      <c r="I72" s="26"/>
+      <c r="J72" s="26"/>
+      <c r="K72" s="26"/>
+      <c r="L72" s="26"/>
+      <c r="M72" s="26"/>
+      <c r="N72" s="26"/>
+      <c r="O72" s="26"/>
+      <c r="P72" s="26"/>
+      <c r="Q72" s="26"/>
+      <c r="R72" s="26"/>
+      <c r="S72" s="26"/>
+      <c r="T72" s="26"/>
+      <c r="U72" s="26"/>
+      <c r="V72" s="26"/>
+      <c r="W72" s="26"/>
+      <c r="X72" s="26"/>
+      <c r="Y72" s="26"/>
     </row>
     <row r="73" ht="15.0" customHeight="1">
-      <c r="A73" s="26" t="s">
+      <c r="A73" s="25" t="s">
         <v>283</v>
       </c>
-      <c r="B73" s="27">
+      <c r="B73" s="26">
         <v>0.0</v>
       </c>
-      <c r="C73" s="27" t="s">
+      <c r="C73" s="26" t="s">
         <v>284</v>
       </c>
-      <c r="D73" s="27" t="s">
+      <c r="D73" s="26" t="s">
         <v>285</v>
       </c>
-      <c r="E73" s="27" t="s">
+      <c r="E73" s="26" t="s">
         <v>286</v>
       </c>
-      <c r="F73" s="27"/>
-      <c r="G73" s="27"/>
-      <c r="H73" s="27"/>
-      <c r="I73" s="27"/>
-      <c r="J73" s="27"/>
-      <c r="K73" s="27"/>
-      <c r="L73" s="27"/>
-      <c r="M73" s="27"/>
-      <c r="N73" s="27"/>
-      <c r="O73" s="27"/>
-      <c r="P73" s="27"/>
-      <c r="Q73" s="27"/>
-      <c r="R73" s="27"/>
-      <c r="S73" s="27"/>
-      <c r="T73" s="27"/>
-      <c r="U73" s="27"/>
-      <c r="V73" s="27"/>
-      <c r="W73" s="27"/>
-      <c r="X73" s="27"/>
-      <c r="Y73" s="27"/>
-      <c r="Z73" s="9"/>
+      <c r="F73" s="26"/>
+      <c r="G73" s="26"/>
+      <c r="H73" s="26"/>
+      <c r="I73" s="26"/>
+      <c r="J73" s="26"/>
+      <c r="K73" s="26"/>
+      <c r="L73" s="26"/>
+      <c r="M73" s="26"/>
+      <c r="N73" s="26"/>
+      <c r="O73" s="26"/>
+      <c r="P73" s="26"/>
+      <c r="Q73" s="26"/>
+      <c r="R73" s="26"/>
+      <c r="S73" s="26"/>
+      <c r="T73" s="26"/>
+      <c r="U73" s="26"/>
+      <c r="V73" s="26"/>
+      <c r="W73" s="26"/>
+      <c r="X73" s="26"/>
+      <c r="Y73" s="26"/>
     </row>
     <row r="74" ht="15.0" customHeight="1">
-      <c r="A74" s="26" t="s">
+      <c r="A74" s="25" t="s">
         <v>287</v>
       </c>
-      <c r="B74" s="27">
+      <c r="B74" s="26">
         <v>0.0</v>
       </c>
-      <c r="C74" s="27" t="s">
+      <c r="C74" s="26" t="s">
         <v>288</v>
       </c>
-      <c r="D74" s="27" t="s">
+      <c r="D74" s="26" t="s">
         <v>289</v>
       </c>
-      <c r="E74" s="27" t="s">
+      <c r="E74" s="26" t="s">
         <v>290</v>
       </c>
-      <c r="F74" s="27"/>
-      <c r="G74" s="27"/>
-      <c r="H74" s="27"/>
-      <c r="I74" s="27"/>
-      <c r="J74" s="27"/>
-      <c r="K74" s="27"/>
-      <c r="L74" s="27"/>
-      <c r="M74" s="27"/>
-      <c r="N74" s="27"/>
-      <c r="O74" s="27"/>
-      <c r="P74" s="27"/>
-      <c r="Q74" s="27"/>
-      <c r="R74" s="27"/>
-      <c r="S74" s="27"/>
-      <c r="T74" s="27"/>
-      <c r="U74" s="27"/>
-      <c r="V74" s="27"/>
-      <c r="W74" s="27"/>
-      <c r="X74" s="27"/>
-      <c r="Y74" s="27"/>
-      <c r="Z74" s="9"/>
+      <c r="F74" s="26"/>
+      <c r="G74" s="26"/>
+      <c r="H74" s="26"/>
+      <c r="I74" s="26"/>
+      <c r="J74" s="26"/>
+      <c r="K74" s="26"/>
+      <c r="L74" s="26"/>
+      <c r="M74" s="26"/>
+      <c r="N74" s="26"/>
+      <c r="O74" s="26"/>
+      <c r="P74" s="26"/>
+      <c r="Q74" s="26"/>
+      <c r="R74" s="26"/>
+      <c r="S74" s="26"/>
+      <c r="T74" s="26"/>
+      <c r="U74" s="26"/>
+      <c r="V74" s="26"/>
+      <c r="W74" s="26"/>
+      <c r="X74" s="26"/>
+      <c r="Y74" s="26"/>
     </row>
     <row r="75" ht="15.0" customHeight="1">
-      <c r="A75" s="26" t="s">
+      <c r="A75" s="25" t="s">
         <v>291</v>
       </c>
-      <c r="B75" s="27">
+      <c r="B75" s="26">
         <v>0.0</v>
       </c>
-      <c r="C75" s="27" t="s">
+      <c r="C75" s="26" t="s">
         <v>292</v>
       </c>
-      <c r="D75" s="27" t="s">
+      <c r="D75" s="26" t="s">
         <v>293</v>
       </c>
-      <c r="E75" s="27" t="s">
+      <c r="E75" s="26" t="s">
         <v>294</v>
       </c>
-      <c r="F75" s="27"/>
-      <c r="G75" s="27"/>
-      <c r="H75" s="27"/>
-      <c r="I75" s="27"/>
-      <c r="J75" s="27"/>
-      <c r="K75" s="27"/>
-      <c r="L75" s="27"/>
-      <c r="M75" s="27"/>
-      <c r="N75" s="27"/>
-      <c r="O75" s="27"/>
-      <c r="P75" s="27"/>
-      <c r="Q75" s="27"/>
-      <c r="R75" s="27"/>
-      <c r="S75" s="27"/>
-      <c r="T75" s="27"/>
-      <c r="U75" s="27"/>
-      <c r="V75" s="27"/>
-      <c r="W75" s="27"/>
-      <c r="X75" s="27"/>
-      <c r="Y75" s="27"/>
-      <c r="Z75" s="9"/>
+      <c r="F75" s="26"/>
+      <c r="G75" s="26"/>
+      <c r="H75" s="26"/>
+      <c r="I75" s="26"/>
+      <c r="J75" s="26"/>
+      <c r="K75" s="26"/>
+      <c r="L75" s="26"/>
+      <c r="M75" s="26"/>
+      <c r="N75" s="26"/>
+      <c r="O75" s="26"/>
+      <c r="P75" s="26"/>
+      <c r="Q75" s="26"/>
+      <c r="R75" s="26"/>
+      <c r="S75" s="26"/>
+      <c r="T75" s="26"/>
+      <c r="U75" s="26"/>
+      <c r="V75" s="26"/>
+      <c r="W75" s="26"/>
+      <c r="X75" s="26"/>
+      <c r="Y75" s="26"/>
     </row>
     <row r="76" ht="15.0" customHeight="1">
-      <c r="A76" s="28" t="s">
+      <c r="A76" s="27" t="s">
         <v>295</v>
       </c>
-      <c r="B76" s="29">
+      <c r="B76" s="28">
         <v>0.0</v>
       </c>
-      <c r="C76" s="30" t="s">
+      <c r="C76" s="29" t="s">
         <v>296</v>
       </c>
-      <c r="D76" s="30" t="s">
+      <c r="D76" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="E76" s="30" t="s">
+      <c r="E76" s="29" t="s">
         <v>208</v>
       </c>
-      <c r="F76" s="30"/>
-      <c r="G76" s="30"/>
-      <c r="H76" s="30"/>
-      <c r="I76" s="30"/>
-      <c r="J76" s="30"/>
-      <c r="K76" s="30"/>
-      <c r="L76" s="30"/>
-      <c r="M76" s="30"/>
-      <c r="N76" s="30"/>
-      <c r="O76" s="30"/>
-      <c r="P76" s="30"/>
-      <c r="Q76" s="30"/>
-      <c r="R76" s="30"/>
-      <c r="S76" s="30"/>
-      <c r="T76" s="30"/>
-      <c r="U76" s="30"/>
-      <c r="V76" s="30"/>
-      <c r="W76" s="30"/>
-      <c r="X76" s="30"/>
-      <c r="Y76" s="30"/>
-      <c r="Z76" s="9"/>
+      <c r="F76" s="29"/>
+      <c r="G76" s="29"/>
+      <c r="H76" s="29"/>
+      <c r="I76" s="29"/>
+      <c r="J76" s="29"/>
+      <c r="K76" s="29"/>
+      <c r="L76" s="29"/>
+      <c r="M76" s="29"/>
+      <c r="N76" s="29"/>
+      <c r="O76" s="29"/>
+      <c r="P76" s="29"/>
+      <c r="Q76" s="29"/>
+      <c r="R76" s="29"/>
+      <c r="S76" s="29"/>
+      <c r="T76" s="29"/>
+      <c r="U76" s="29"/>
+      <c r="V76" s="29"/>
+      <c r="W76" s="29"/>
+      <c r="X76" s="29"/>
+      <c r="Y76" s="29"/>
     </row>
     <row r="77" ht="15.0" customHeight="1">
-      <c r="A77" s="31" t="s">
+      <c r="A77" s="30" t="s">
         <v>297</v>
       </c>
-      <c r="B77" s="32">
+      <c r="B77" s="31">
         <v>0.0</v>
       </c>
-      <c r="C77" s="33" t="s">
+      <c r="C77" s="32" t="s">
         <v>298</v>
       </c>
-      <c r="D77" s="33" t="s">
+      <c r="D77" s="32" t="s">
         <v>139</v>
       </c>
-      <c r="E77" s="33" t="s">
+      <c r="E77" s="32" t="s">
         <v>140</v>
       </c>
-      <c r="F77" s="33"/>
-      <c r="G77" s="33"/>
-      <c r="H77" s="33"/>
-      <c r="I77" s="33"/>
-      <c r="J77" s="33"/>
-      <c r="K77" s="33"/>
-      <c r="L77" s="33"/>
-      <c r="M77" s="33"/>
-      <c r="N77" s="33"/>
-      <c r="O77" s="33"/>
-      <c r="P77" s="33"/>
-      <c r="Q77" s="33"/>
-      <c r="R77" s="33"/>
-      <c r="S77" s="33"/>
-      <c r="T77" s="33"/>
-      <c r="U77" s="33"/>
-      <c r="V77" s="33"/>
-      <c r="W77" s="33"/>
-      <c r="X77" s="33"/>
-      <c r="Y77" s="33"/>
-      <c r="Z77" s="14"/>
+      <c r="F77" s="32"/>
+      <c r="G77" s="32"/>
+      <c r="H77" s="32"/>
+      <c r="I77" s="32"/>
+      <c r="J77" s="32"/>
+      <c r="K77" s="32"/>
+      <c r="L77" s="32"/>
+      <c r="M77" s="32"/>
+      <c r="N77" s="32"/>
+      <c r="O77" s="32"/>
+      <c r="P77" s="32"/>
+      <c r="Q77" s="32"/>
+      <c r="R77" s="32"/>
+      <c r="S77" s="32"/>
+      <c r="T77" s="32"/>
+      <c r="U77" s="32"/>
+      <c r="V77" s="32"/>
+      <c r="W77" s="32"/>
+      <c r="X77" s="32"/>
+      <c r="Y77" s="32"/>
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="1"/>

--- a/Templates/Tables/StringInfo/StrTable.xlsx
+++ b/Templates/Tables/StringInfo/StrTable.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="307">
   <si>
     <t>Description</t>
   </si>
@@ -826,13 +826,13 @@
     <t>Chapter {0}/{1}</t>
   </si>
   <si>
-    <t>상점 팝업 타이틀</t>
+    <t>상점 팝업 제목</t>
   </si>
   <si>
     <t>STORE_P_TITLE</t>
   </si>
   <si>
-    <t>설정 팝업 타이틀</t>
+    <t>설정 팝업 제목</t>
   </si>
   <si>
     <t>SETTINGS_P_TITLE</t>
@@ -844,13 +844,13 @@
     <t>Settings</t>
   </si>
   <si>
-    <t>동기화 팝업 타이틀</t>
+    <t>동기화 팝업 제목</t>
   </si>
   <si>
     <t>SYNC_P_TITLE</t>
   </si>
   <si>
-    <t>일일 미션 팝업 타이틀</t>
+    <t>일일 미션 팝업 제목</t>
   </si>
   <si>
     <t>DAILY_MP_TITLE</t>
@@ -862,7 +862,7 @@
     <t>Daily Mission</t>
   </si>
   <si>
-    <t>무료 보상 팝업 타이틀</t>
+    <t>무료 보상 팝업 제목</t>
   </si>
   <si>
     <t>FREE_RP_TITLE</t>
@@ -874,7 +874,7 @@
     <t>Free Reward</t>
   </si>
   <si>
-    <t>일일 보상 팝업 타이틀</t>
+    <t>일일 보상 팝업 제목</t>
   </si>
   <si>
     <t>DAILY_RP_TITLE</t>
@@ -886,7 +886,7 @@
     <t>Daily Reward</t>
   </si>
   <si>
-    <t>판매 코인 팝업 타이틀</t>
+    <t>판매 코인 팝업 제목</t>
   </si>
   <si>
     <t>SALE_CP_TITLE</t>
@@ -898,7 +898,7 @@
     <t>Sale Coins</t>
   </si>
   <si>
-    <t>이어하기 팝업 타이틀</t>
+    <t>이어하기 팝업 제목</t>
   </si>
   <si>
     <t>CONTINUE_P_TITLE</t>
@@ -908,13 +908,37 @@
   </si>
   <si>
     <t>RESULT_P_TITLE</t>
+  </si>
+  <si>
+    <t>재개 팝업 제목</t>
+  </si>
+  <si>
+    <t>RESUME_P_TITLE</t>
+  </si>
+  <si>
+    <t>다시하기</t>
+  </si>
+  <si>
+    <t>Resume</t>
+  </si>
+  <si>
+    <t>정지 팝업 제목</t>
+  </si>
+  <si>
+    <t>PAUSE_P_TITLE</t>
+  </si>
+  <si>
+    <t>일시정지</t>
+  </si>
+  <si>
+    <t>Pause</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -928,6 +952,11 @@
     <font>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -962,7 +991,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="9">
     <border/>
     <border>
       <left style="thin">
@@ -995,11 +1024,32 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1021,12 +1071,6 @@
     </xf>
     <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="3" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
@@ -1058,21 +1102,18 @@
     <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
+    <xf borderId="2" fillId="5" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="2" fillId="5" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="5" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="7" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="3" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
@@ -1080,15 +1121,28 @@
     <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="4" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="4" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
     <xf borderId="5" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="5" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="8" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1307,7 +1361,7 @@
     <col customWidth="1" min="3" max="3" width="32.63"/>
     <col customWidth="1" min="4" max="4" width="85.88"/>
     <col customWidth="1" min="5" max="5" width="98.0"/>
-    <col customWidth="1" min="6" max="26" width="14.38"/>
+    <col customWidth="1" min="6" max="25" width="14.38"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
@@ -1496,19 +1550,19 @@
       <c r="Y5" s="7"/>
     </row>
     <row r="6" ht="15.0" customHeight="1">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="5" t="s">
         <v>21</v>
       </c>
       <c r="B6" s="6">
         <v>0.0</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="7" t="s">
         <v>24</v>
       </c>
       <c r="F6" s="7"/>
@@ -1693,7 +1747,7 @@
       <c r="D11" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="8" t="s">
         <v>44</v>
       </c>
       <c r="F11" s="7"/>
@@ -1977,2241 +2031,2272 @@
       <c r="Y18" s="7"/>
     </row>
     <row r="19" ht="15.0" customHeight="1">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="10">
         <v>0.0</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="E19" s="13" t="s">
+      <c r="E19" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="13"/>
-      <c r="L19" s="13"/>
-      <c r="M19" s="13"/>
-      <c r="N19" s="13"/>
-      <c r="O19" s="13"/>
-      <c r="P19" s="13"/>
-      <c r="Q19" s="13"/>
-      <c r="R19" s="13"/>
-      <c r="S19" s="13"/>
-      <c r="T19" s="13"/>
-      <c r="U19" s="13"/>
-      <c r="V19" s="13"/>
-      <c r="W19" s="13"/>
-      <c r="X19" s="13"/>
-      <c r="Y19" s="13"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="11"/>
+      <c r="P19" s="11"/>
+      <c r="Q19" s="11"/>
+      <c r="R19" s="11"/>
+      <c r="S19" s="11"/>
+      <c r="T19" s="11"/>
+      <c r="U19" s="11"/>
+      <c r="V19" s="11"/>
+      <c r="W19" s="11"/>
+      <c r="X19" s="11"/>
+      <c r="Y19" s="11"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="B20" s="15">
+      <c r="B20" s="13">
         <v>0.0</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="C20" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="E20" s="16" t="s">
+      <c r="E20" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="16"/>
-      <c r="J20" s="16"/>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="16"/>
-      <c r="O20" s="16"/>
-      <c r="P20" s="16"/>
-      <c r="Q20" s="16"/>
-      <c r="R20" s="16"/>
-      <c r="S20" s="16"/>
-      <c r="T20" s="16"/>
-      <c r="U20" s="16"/>
-      <c r="V20" s="16"/>
-      <c r="W20" s="16"/>
-      <c r="X20" s="16"/>
-      <c r="Y20" s="16"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+      <c r="K20" s="14"/>
+      <c r="L20" s="14"/>
+      <c r="M20" s="14"/>
+      <c r="N20" s="14"/>
+      <c r="O20" s="14"/>
+      <c r="P20" s="14"/>
+      <c r="Q20" s="14"/>
+      <c r="R20" s="14"/>
+      <c r="S20" s="14"/>
+      <c r="T20" s="14"/>
+      <c r="U20" s="14"/>
+      <c r="V20" s="14"/>
+      <c r="W20" s="14"/>
+      <c r="X20" s="14"/>
+      <c r="Y20" s="14"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="B21" s="18">
+      <c r="B21" s="16">
         <v>0.0</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="D21" s="19" t="s">
+      <c r="D21" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="E21" s="19" t="s">
+      <c r="E21" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="19"/>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19"/>
-      <c r="M21" s="19"/>
-      <c r="N21" s="19"/>
-      <c r="O21" s="19"/>
-      <c r="P21" s="19"/>
-      <c r="Q21" s="19"/>
-      <c r="R21" s="19"/>
-      <c r="S21" s="19"/>
-      <c r="T21" s="19"/>
-      <c r="U21" s="19"/>
-      <c r="V21" s="19"/>
-      <c r="W21" s="19"/>
-      <c r="X21" s="19"/>
-      <c r="Y21" s="19"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="17"/>
+      <c r="M21" s="17"/>
+      <c r="N21" s="17"/>
+      <c r="O21" s="17"/>
+      <c r="P21" s="17"/>
+      <c r="Q21" s="17"/>
+      <c r="R21" s="17"/>
+      <c r="S21" s="17"/>
+      <c r="T21" s="17"/>
+      <c r="U21" s="17"/>
+      <c r="V21" s="17"/>
+      <c r="W21" s="17"/>
+      <c r="X21" s="17"/>
+      <c r="Y21" s="17"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="B22" s="18">
+      <c r="B22" s="16">
         <v>0.0</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="C22" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="D22" s="19" t="s">
+      <c r="D22" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="E22" s="19" t="s">
+      <c r="E22" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="19"/>
-      <c r="J22" s="19"/>
-      <c r="K22" s="19"/>
-      <c r="L22" s="19"/>
-      <c r="M22" s="19"/>
-      <c r="N22" s="19"/>
-      <c r="O22" s="19"/>
-      <c r="P22" s="19"/>
-      <c r="Q22" s="19"/>
-      <c r="R22" s="19"/>
-      <c r="S22" s="19"/>
-      <c r="T22" s="19"/>
-      <c r="U22" s="19"/>
-      <c r="V22" s="19"/>
-      <c r="W22" s="19"/>
-      <c r="X22" s="19"/>
-      <c r="Y22" s="19"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="17"/>
+      <c r="L22" s="17"/>
+      <c r="M22" s="17"/>
+      <c r="N22" s="17"/>
+      <c r="O22" s="17"/>
+      <c r="P22" s="17"/>
+      <c r="Q22" s="17"/>
+      <c r="R22" s="17"/>
+      <c r="S22" s="17"/>
+      <c r="T22" s="17"/>
+      <c r="U22" s="17"/>
+      <c r="V22" s="17"/>
+      <c r="W22" s="17"/>
+      <c r="X22" s="17"/>
+      <c r="Y22" s="17"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="B23" s="18">
+      <c r="B23" s="16">
         <v>0.0</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="C23" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="D23" s="19" t="s">
+      <c r="D23" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="E23" s="19" t="s">
+      <c r="E23" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="19"/>
-      <c r="J23" s="19"/>
-      <c r="K23" s="19"/>
-      <c r="L23" s="19"/>
-      <c r="M23" s="19"/>
-      <c r="N23" s="19"/>
-      <c r="O23" s="19"/>
-      <c r="P23" s="19"/>
-      <c r="Q23" s="19"/>
-      <c r="R23" s="19"/>
-      <c r="S23" s="19"/>
-      <c r="T23" s="19"/>
-      <c r="U23" s="19"/>
-      <c r="V23" s="19"/>
-      <c r="W23" s="19"/>
-      <c r="X23" s="19"/>
-      <c r="Y23" s="19"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="17"/>
+      <c r="M23" s="17"/>
+      <c r="N23" s="17"/>
+      <c r="O23" s="17"/>
+      <c r="P23" s="17"/>
+      <c r="Q23" s="17"/>
+      <c r="R23" s="17"/>
+      <c r="S23" s="17"/>
+      <c r="T23" s="17"/>
+      <c r="U23" s="17"/>
+      <c r="V23" s="17"/>
+      <c r="W23" s="17"/>
+      <c r="X23" s="17"/>
+      <c r="Y23" s="17"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="B24" s="18">
+      <c r="B24" s="16">
         <v>0.0</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="C24" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="D24" s="19" t="s">
+      <c r="D24" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="E24" s="19" t="s">
+      <c r="E24" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="19"/>
-      <c r="J24" s="19"/>
-      <c r="K24" s="19"/>
-      <c r="L24" s="19"/>
-      <c r="M24" s="19"/>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19"/>
-      <c r="P24" s="19"/>
-      <c r="Q24" s="19"/>
-      <c r="R24" s="19"/>
-      <c r="S24" s="19"/>
-      <c r="T24" s="19"/>
-      <c r="U24" s="19"/>
-      <c r="V24" s="19"/>
-      <c r="W24" s="19"/>
-      <c r="X24" s="19"/>
-      <c r="Y24" s="19"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="17"/>
+      <c r="L24" s="17"/>
+      <c r="M24" s="17"/>
+      <c r="N24" s="17"/>
+      <c r="O24" s="17"/>
+      <c r="P24" s="17"/>
+      <c r="Q24" s="17"/>
+      <c r="R24" s="17"/>
+      <c r="S24" s="17"/>
+      <c r="T24" s="17"/>
+      <c r="U24" s="17"/>
+      <c r="V24" s="17"/>
+      <c r="W24" s="17"/>
+      <c r="X24" s="17"/>
+      <c r="Y24" s="17"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="B25" s="18">
+      <c r="B25" s="16">
         <v>0.0</v>
       </c>
-      <c r="C25" s="19" t="s">
+      <c r="C25" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="D25" s="19" t="s">
+      <c r="D25" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="E25" s="19" t="s">
+      <c r="E25" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="19"/>
-      <c r="J25" s="19"/>
-      <c r="K25" s="19"/>
-      <c r="L25" s="19"/>
-      <c r="M25" s="19"/>
-      <c r="N25" s="19"/>
-      <c r="O25" s="19"/>
-      <c r="P25" s="19"/>
-      <c r="Q25" s="19"/>
-      <c r="R25" s="19"/>
-      <c r="S25" s="19"/>
-      <c r="T25" s="19"/>
-      <c r="U25" s="19"/>
-      <c r="V25" s="19"/>
-      <c r="W25" s="19"/>
-      <c r="X25" s="19"/>
-      <c r="Y25" s="19"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="17"/>
+      <c r="L25" s="17"/>
+      <c r="M25" s="17"/>
+      <c r="N25" s="17"/>
+      <c r="O25" s="17"/>
+      <c r="P25" s="17"/>
+      <c r="Q25" s="17"/>
+      <c r="R25" s="17"/>
+      <c r="S25" s="17"/>
+      <c r="T25" s="17"/>
+      <c r="U25" s="17"/>
+      <c r="V25" s="17"/>
+      <c r="W25" s="17"/>
+      <c r="X25" s="17"/>
+      <c r="Y25" s="17"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="17" t="s">
+      <c r="A26" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="B26" s="18">
+      <c r="B26" s="16">
         <v>0.0</v>
       </c>
-      <c r="C26" s="19" t="s">
+      <c r="C26" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="D26" s="19" t="s">
+      <c r="D26" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="E26" s="19" t="s">
+      <c r="E26" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="19"/>
-      <c r="I26" s="19"/>
-      <c r="J26" s="19"/>
-      <c r="K26" s="19"/>
-      <c r="L26" s="19"/>
-      <c r="M26" s="19"/>
-      <c r="N26" s="19"/>
-      <c r="O26" s="19"/>
-      <c r="P26" s="19"/>
-      <c r="Q26" s="19"/>
-      <c r="R26" s="19"/>
-      <c r="S26" s="19"/>
-      <c r="T26" s="19"/>
-      <c r="U26" s="19"/>
-      <c r="V26" s="19"/>
-      <c r="W26" s="19"/>
-      <c r="X26" s="19"/>
-      <c r="Y26" s="19"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="17"/>
+      <c r="L26" s="17"/>
+      <c r="M26" s="17"/>
+      <c r="N26" s="17"/>
+      <c r="O26" s="17"/>
+      <c r="P26" s="17"/>
+      <c r="Q26" s="17"/>
+      <c r="R26" s="17"/>
+      <c r="S26" s="17"/>
+      <c r="T26" s="17"/>
+      <c r="U26" s="17"/>
+      <c r="V26" s="17"/>
+      <c r="W26" s="17"/>
+      <c r="X26" s="17"/>
+      <c r="Y26" s="17"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="B27" s="18">
+      <c r="B27" s="16">
         <v>0.0</v>
       </c>
-      <c r="C27" s="19" t="s">
+      <c r="C27" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="D27" s="19" t="s">
+      <c r="D27" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="E27" s="19" t="s">
+      <c r="E27" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="19"/>
-      <c r="J27" s="19"/>
-      <c r="K27" s="19"/>
-      <c r="L27" s="19"/>
-      <c r="M27" s="19"/>
-      <c r="N27" s="19"/>
-      <c r="O27" s="19"/>
-      <c r="P27" s="19"/>
-      <c r="Q27" s="19"/>
-      <c r="R27" s="19"/>
-      <c r="S27" s="19"/>
-      <c r="T27" s="19"/>
-      <c r="U27" s="19"/>
-      <c r="V27" s="19"/>
-      <c r="W27" s="19"/>
-      <c r="X27" s="19"/>
-      <c r="Y27" s="19"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="17"/>
+      <c r="L27" s="17"/>
+      <c r="M27" s="17"/>
+      <c r="N27" s="17"/>
+      <c r="O27" s="17"/>
+      <c r="P27" s="17"/>
+      <c r="Q27" s="17"/>
+      <c r="R27" s="17"/>
+      <c r="S27" s="17"/>
+      <c r="T27" s="17"/>
+      <c r="U27" s="17"/>
+      <c r="V27" s="17"/>
+      <c r="W27" s="17"/>
+      <c r="X27" s="17"/>
+      <c r="Y27" s="17"/>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="17" t="s">
+      <c r="A28" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="B28" s="18">
+      <c r="B28" s="16">
         <v>0.0</v>
       </c>
-      <c r="C28" s="19" t="s">
+      <c r="C28" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="D28" s="19" t="s">
+      <c r="D28" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="E28" s="19" t="s">
+      <c r="E28" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="19"/>
-      <c r="J28" s="19"/>
-      <c r="K28" s="19"/>
-      <c r="L28" s="19"/>
-      <c r="M28" s="19"/>
-      <c r="N28" s="19"/>
-      <c r="O28" s="19"/>
-      <c r="P28" s="19"/>
-      <c r="Q28" s="19"/>
-      <c r="R28" s="19"/>
-      <c r="S28" s="19"/>
-      <c r="T28" s="19"/>
-      <c r="U28" s="19"/>
-      <c r="V28" s="19"/>
-      <c r="W28" s="19"/>
-      <c r="X28" s="19"/>
-      <c r="Y28" s="19"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="17"/>
+      <c r="M28" s="17"/>
+      <c r="N28" s="17"/>
+      <c r="O28" s="17"/>
+      <c r="P28" s="17"/>
+      <c r="Q28" s="17"/>
+      <c r="R28" s="17"/>
+      <c r="S28" s="17"/>
+      <c r="T28" s="17"/>
+      <c r="U28" s="17"/>
+      <c r="V28" s="17"/>
+      <c r="W28" s="17"/>
+      <c r="X28" s="17"/>
+      <c r="Y28" s="17"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="17" t="s">
+      <c r="A29" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="B29" s="18">
+      <c r="B29" s="16">
         <v>0.0</v>
       </c>
-      <c r="C29" s="19" t="s">
+      <c r="C29" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="D29" s="19" t="s">
+      <c r="D29" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="E29" s="19" t="s">
+      <c r="E29" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="19"/>
-      <c r="J29" s="19"/>
-      <c r="K29" s="19"/>
-      <c r="L29" s="19"/>
-      <c r="M29" s="19"/>
-      <c r="N29" s="19"/>
-      <c r="O29" s="19"/>
-      <c r="P29" s="19"/>
-      <c r="Q29" s="19"/>
-      <c r="R29" s="19"/>
-      <c r="S29" s="19"/>
-      <c r="T29" s="19"/>
-      <c r="U29" s="19"/>
-      <c r="V29" s="19"/>
-      <c r="W29" s="19"/>
-      <c r="X29" s="19"/>
-      <c r="Y29" s="19"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="17"/>
+      <c r="J29" s="17"/>
+      <c r="K29" s="17"/>
+      <c r="L29" s="17"/>
+      <c r="M29" s="17"/>
+      <c r="N29" s="17"/>
+      <c r="O29" s="17"/>
+      <c r="P29" s="17"/>
+      <c r="Q29" s="17"/>
+      <c r="R29" s="17"/>
+      <c r="S29" s="17"/>
+      <c r="T29" s="17"/>
+      <c r="U29" s="17"/>
+      <c r="V29" s="17"/>
+      <c r="W29" s="17"/>
+      <c r="X29" s="17"/>
+      <c r="Y29" s="17"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="17" t="s">
+      <c r="A30" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="B30" s="18">
+      <c r="B30" s="16">
         <v>0.0</v>
       </c>
-      <c r="C30" s="19" t="s">
+      <c r="C30" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="D30" s="19" t="s">
+      <c r="D30" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="E30" s="19" t="s">
+      <c r="E30" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="19"/>
-      <c r="J30" s="19"/>
-      <c r="K30" s="19"/>
-      <c r="L30" s="19"/>
-      <c r="M30" s="19"/>
-      <c r="N30" s="19"/>
-      <c r="O30" s="19"/>
-      <c r="P30" s="19"/>
-      <c r="Q30" s="19"/>
-      <c r="R30" s="19"/>
-      <c r="S30" s="19"/>
-      <c r="T30" s="19"/>
-      <c r="U30" s="19"/>
-      <c r="V30" s="19"/>
-      <c r="W30" s="19"/>
-      <c r="X30" s="19"/>
-      <c r="Y30" s="19"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="17"/>
+      <c r="I30" s="17"/>
+      <c r="J30" s="17"/>
+      <c r="K30" s="17"/>
+      <c r="L30" s="17"/>
+      <c r="M30" s="17"/>
+      <c r="N30" s="17"/>
+      <c r="O30" s="17"/>
+      <c r="P30" s="17"/>
+      <c r="Q30" s="17"/>
+      <c r="R30" s="17"/>
+      <c r="S30" s="17"/>
+      <c r="T30" s="17"/>
+      <c r="U30" s="17"/>
+      <c r="V30" s="17"/>
+      <c r="W30" s="17"/>
+      <c r="X30" s="17"/>
+      <c r="Y30" s="17"/>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="17" t="s">
+      <c r="A31" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="B31" s="18">
+      <c r="B31" s="16">
         <v>0.0</v>
       </c>
-      <c r="C31" s="19" t="s">
+      <c r="C31" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="D31" s="19" t="s">
+      <c r="D31" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="E31" s="19" t="s">
+      <c r="E31" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="19"/>
-      <c r="J31" s="19"/>
-      <c r="K31" s="19"/>
-      <c r="L31" s="19"/>
-      <c r="M31" s="19"/>
-      <c r="N31" s="19"/>
-      <c r="O31" s="19"/>
-      <c r="P31" s="19"/>
-      <c r="Q31" s="19"/>
-      <c r="R31" s="19"/>
-      <c r="S31" s="19"/>
-      <c r="T31" s="19"/>
-      <c r="U31" s="19"/>
-      <c r="V31" s="19"/>
-      <c r="W31" s="19"/>
-      <c r="X31" s="19"/>
-      <c r="Y31" s="19"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17"/>
+      <c r="J31" s="17"/>
+      <c r="K31" s="17"/>
+      <c r="L31" s="17"/>
+      <c r="M31" s="17"/>
+      <c r="N31" s="17"/>
+      <c r="O31" s="17"/>
+      <c r="P31" s="17"/>
+      <c r="Q31" s="17"/>
+      <c r="R31" s="17"/>
+      <c r="S31" s="17"/>
+      <c r="T31" s="17"/>
+      <c r="U31" s="17"/>
+      <c r="V31" s="17"/>
+      <c r="W31" s="17"/>
+      <c r="X31" s="17"/>
+      <c r="Y31" s="17"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="17" t="s">
+      <c r="A32" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="B32" s="18">
+      <c r="B32" s="16">
         <v>0.0</v>
       </c>
-      <c r="C32" s="19" t="s">
+      <c r="C32" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="D32" s="19" t="s">
+      <c r="D32" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="E32" s="19" t="s">
+      <c r="E32" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="19"/>
-      <c r="J32" s="19"/>
-      <c r="K32" s="19"/>
-      <c r="L32" s="19"/>
-      <c r="M32" s="19"/>
-      <c r="N32" s="19"/>
-      <c r="O32" s="19"/>
-      <c r="P32" s="19"/>
-      <c r="Q32" s="19"/>
-      <c r="R32" s="19"/>
-      <c r="S32" s="19"/>
-      <c r="T32" s="19"/>
-      <c r="U32" s="19"/>
-      <c r="V32" s="19"/>
-      <c r="W32" s="19"/>
-      <c r="X32" s="19"/>
-      <c r="Y32" s="19"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="17"/>
+      <c r="J32" s="17"/>
+      <c r="K32" s="17"/>
+      <c r="L32" s="17"/>
+      <c r="M32" s="17"/>
+      <c r="N32" s="17"/>
+      <c r="O32" s="17"/>
+      <c r="P32" s="17"/>
+      <c r="Q32" s="17"/>
+      <c r="R32" s="17"/>
+      <c r="S32" s="17"/>
+      <c r="T32" s="17"/>
+      <c r="U32" s="17"/>
+      <c r="V32" s="17"/>
+      <c r="W32" s="17"/>
+      <c r="X32" s="17"/>
+      <c r="Y32" s="17"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="17" t="s">
+      <c r="A33" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="B33" s="18">
+      <c r="B33" s="16">
         <v>0.0</v>
       </c>
-      <c r="C33" s="19" t="s">
+      <c r="C33" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="D33" s="19" t="s">
+      <c r="D33" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="19" t="s">
+      <c r="E33" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19"/>
-      <c r="I33" s="19"/>
-      <c r="J33" s="19"/>
-      <c r="K33" s="19"/>
-      <c r="L33" s="19"/>
-      <c r="M33" s="19"/>
-      <c r="N33" s="19"/>
-      <c r="O33" s="19"/>
-      <c r="P33" s="19"/>
-      <c r="Q33" s="19"/>
-      <c r="R33" s="19"/>
-      <c r="S33" s="19"/>
-      <c r="T33" s="19"/>
-      <c r="U33" s="19"/>
-      <c r="V33" s="19"/>
-      <c r="W33" s="19"/>
-      <c r="X33" s="19"/>
-      <c r="Y33" s="19"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="17"/>
+      <c r="I33" s="17"/>
+      <c r="J33" s="17"/>
+      <c r="K33" s="17"/>
+      <c r="L33" s="17"/>
+      <c r="M33" s="17"/>
+      <c r="N33" s="17"/>
+      <c r="O33" s="17"/>
+      <c r="P33" s="17"/>
+      <c r="Q33" s="17"/>
+      <c r="R33" s="17"/>
+      <c r="S33" s="17"/>
+      <c r="T33" s="17"/>
+      <c r="U33" s="17"/>
+      <c r="V33" s="17"/>
+      <c r="W33" s="17"/>
+      <c r="X33" s="17"/>
+      <c r="Y33" s="17"/>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="17" t="s">
+      <c r="A34" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="B34" s="18">
+      <c r="B34" s="16">
         <v>0.0</v>
       </c>
-      <c r="C34" s="19" t="s">
+      <c r="C34" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="D34" s="19" t="s">
+      <c r="D34" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="E34" s="19" t="s">
+      <c r="E34" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
-      <c r="I34" s="19"/>
-      <c r="J34" s="19"/>
-      <c r="K34" s="19"/>
-      <c r="L34" s="19"/>
-      <c r="M34" s="19"/>
-      <c r="N34" s="19"/>
-      <c r="O34" s="19"/>
-      <c r="P34" s="19"/>
-      <c r="Q34" s="19"/>
-      <c r="R34" s="19"/>
-      <c r="S34" s="19"/>
-      <c r="T34" s="19"/>
-      <c r="U34" s="19"/>
-      <c r="V34" s="19"/>
-      <c r="W34" s="19"/>
-      <c r="X34" s="19"/>
-      <c r="Y34" s="19"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="17"/>
+      <c r="I34" s="17"/>
+      <c r="J34" s="17"/>
+      <c r="K34" s="17"/>
+      <c r="L34" s="17"/>
+      <c r="M34" s="17"/>
+      <c r="N34" s="17"/>
+      <c r="O34" s="17"/>
+      <c r="P34" s="17"/>
+      <c r="Q34" s="17"/>
+      <c r="R34" s="17"/>
+      <c r="S34" s="17"/>
+      <c r="T34" s="17"/>
+      <c r="U34" s="17"/>
+      <c r="V34" s="17"/>
+      <c r="W34" s="17"/>
+      <c r="X34" s="17"/>
+      <c r="Y34" s="17"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="17" t="s">
+      <c r="A35" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="B35" s="18">
+      <c r="B35" s="16">
         <v>0.0</v>
       </c>
-      <c r="C35" s="19" t="s">
+      <c r="C35" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D35" s="19" t="s">
+      <c r="D35" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="E35" s="19" t="s">
+      <c r="E35" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="F35" s="19"/>
-      <c r="G35" s="19"/>
-      <c r="H35" s="19"/>
-      <c r="I35" s="19"/>
-      <c r="J35" s="19"/>
-      <c r="K35" s="19"/>
-      <c r="L35" s="19"/>
-      <c r="M35" s="19"/>
-      <c r="N35" s="19"/>
-      <c r="O35" s="19"/>
-      <c r="P35" s="19"/>
-      <c r="Q35" s="19"/>
-      <c r="R35" s="19"/>
-      <c r="S35" s="19"/>
-      <c r="T35" s="19"/>
-      <c r="U35" s="19"/>
-      <c r="V35" s="19"/>
-      <c r="W35" s="19"/>
-      <c r="X35" s="19"/>
-      <c r="Y35" s="19"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="17"/>
+      <c r="I35" s="17"/>
+      <c r="J35" s="17"/>
+      <c r="K35" s="17"/>
+      <c r="L35" s="17"/>
+      <c r="M35" s="17"/>
+      <c r="N35" s="17"/>
+      <c r="O35" s="17"/>
+      <c r="P35" s="17"/>
+      <c r="Q35" s="17"/>
+      <c r="R35" s="17"/>
+      <c r="S35" s="17"/>
+      <c r="T35" s="17"/>
+      <c r="U35" s="17"/>
+      <c r="V35" s="17"/>
+      <c r="W35" s="17"/>
+      <c r="X35" s="17"/>
+      <c r="Y35" s="17"/>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="17" t="s">
+      <c r="A36" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="B36" s="18">
+      <c r="B36" s="16">
         <v>0.0</v>
       </c>
-      <c r="C36" s="19" t="s">
+      <c r="C36" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="D36" s="19" t="s">
+      <c r="D36" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="E36" s="19" t="s">
+      <c r="E36" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="F36" s="19"/>
-      <c r="G36" s="19"/>
-      <c r="H36" s="19"/>
-      <c r="I36" s="19"/>
-      <c r="J36" s="19"/>
-      <c r="K36" s="19"/>
-      <c r="L36" s="19"/>
-      <c r="M36" s="19"/>
-      <c r="N36" s="19"/>
-      <c r="O36" s="19"/>
-      <c r="P36" s="19"/>
-      <c r="Q36" s="19"/>
-      <c r="R36" s="19"/>
-      <c r="S36" s="19"/>
-      <c r="T36" s="19"/>
-      <c r="U36" s="19"/>
-      <c r="V36" s="19"/>
-      <c r="W36" s="19"/>
-      <c r="X36" s="19"/>
-      <c r="Y36" s="19"/>
+      <c r="F36" s="17"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="17"/>
+      <c r="I36" s="17"/>
+      <c r="J36" s="17"/>
+      <c r="K36" s="17"/>
+      <c r="L36" s="17"/>
+      <c r="M36" s="17"/>
+      <c r="N36" s="17"/>
+      <c r="O36" s="17"/>
+      <c r="P36" s="17"/>
+      <c r="Q36" s="17"/>
+      <c r="R36" s="17"/>
+      <c r="S36" s="17"/>
+      <c r="T36" s="17"/>
+      <c r="U36" s="17"/>
+      <c r="V36" s="17"/>
+      <c r="W36" s="17"/>
+      <c r="X36" s="17"/>
+      <c r="Y36" s="17"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="17" t="s">
+      <c r="A37" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="B37" s="18">
+      <c r="B37" s="16">
         <v>0.0</v>
       </c>
-      <c r="C37" s="19" t="s">
+      <c r="C37" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="D37" s="19" t="s">
+      <c r="D37" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="E37" s="19" t="s">
+      <c r="E37" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="F37" s="19"/>
-      <c r="G37" s="19"/>
-      <c r="H37" s="19"/>
-      <c r="I37" s="19"/>
-      <c r="J37" s="19"/>
-      <c r="K37" s="19"/>
-      <c r="L37" s="19"/>
-      <c r="M37" s="19"/>
-      <c r="N37" s="19"/>
-      <c r="O37" s="19"/>
-      <c r="P37" s="19"/>
-      <c r="Q37" s="19"/>
-      <c r="R37" s="19"/>
-      <c r="S37" s="19"/>
-      <c r="T37" s="19"/>
-      <c r="U37" s="19"/>
-      <c r="V37" s="19"/>
-      <c r="W37" s="19"/>
-      <c r="X37" s="19"/>
-      <c r="Y37" s="19"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="17"/>
+      <c r="I37" s="17"/>
+      <c r="J37" s="17"/>
+      <c r="K37" s="17"/>
+      <c r="L37" s="17"/>
+      <c r="M37" s="17"/>
+      <c r="N37" s="17"/>
+      <c r="O37" s="17"/>
+      <c r="P37" s="17"/>
+      <c r="Q37" s="17"/>
+      <c r="R37" s="17"/>
+      <c r="S37" s="17"/>
+      <c r="T37" s="17"/>
+      <c r="U37" s="17"/>
+      <c r="V37" s="17"/>
+      <c r="W37" s="17"/>
+      <c r="X37" s="17"/>
+      <c r="Y37" s="17"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="17" t="s">
+      <c r="A38" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="B38" s="18">
+      <c r="B38" s="16">
         <v>0.0</v>
       </c>
-      <c r="C38" s="19" t="s">
+      <c r="C38" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="D38" s="19" t="s">
+      <c r="D38" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="E38" s="19" t="s">
+      <c r="E38" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="F38" s="19"/>
-      <c r="G38" s="19"/>
-      <c r="H38" s="19"/>
-      <c r="I38" s="19"/>
-      <c r="J38" s="19"/>
-      <c r="K38" s="19"/>
-      <c r="L38" s="19"/>
-      <c r="M38" s="19"/>
-      <c r="N38" s="19"/>
-      <c r="O38" s="19"/>
-      <c r="P38" s="19"/>
-      <c r="Q38" s="19"/>
-      <c r="R38" s="19"/>
-      <c r="S38" s="19"/>
-      <c r="T38" s="19"/>
-      <c r="U38" s="19"/>
-      <c r="V38" s="19"/>
-      <c r="W38" s="19"/>
-      <c r="X38" s="19"/>
-      <c r="Y38" s="19"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="17"/>
+      <c r="I38" s="17"/>
+      <c r="J38" s="17"/>
+      <c r="K38" s="17"/>
+      <c r="L38" s="17"/>
+      <c r="M38" s="17"/>
+      <c r="N38" s="17"/>
+      <c r="O38" s="17"/>
+      <c r="P38" s="17"/>
+      <c r="Q38" s="17"/>
+      <c r="R38" s="17"/>
+      <c r="S38" s="17"/>
+      <c r="T38" s="17"/>
+      <c r="U38" s="17"/>
+      <c r="V38" s="17"/>
+      <c r="W38" s="17"/>
+      <c r="X38" s="17"/>
+      <c r="Y38" s="17"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="17" t="s">
+      <c r="A39" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="B39" s="18">
+      <c r="B39" s="16">
         <v>0.0</v>
       </c>
-      <c r="C39" s="19" t="s">
+      <c r="C39" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="D39" s="19" t="s">
+      <c r="D39" s="17" t="s">
         <v>155</v>
       </c>
-      <c r="E39" s="19" t="s">
+      <c r="E39" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="F39" s="19"/>
-      <c r="G39" s="19"/>
-      <c r="H39" s="19"/>
-      <c r="I39" s="19"/>
-      <c r="J39" s="19"/>
-      <c r="K39" s="19"/>
-      <c r="L39" s="19"/>
-      <c r="M39" s="19"/>
-      <c r="N39" s="19"/>
-      <c r="O39" s="19"/>
-      <c r="P39" s="19"/>
-      <c r="Q39" s="19"/>
-      <c r="R39" s="19"/>
-      <c r="S39" s="19"/>
-      <c r="T39" s="19"/>
-      <c r="U39" s="19"/>
-      <c r="V39" s="19"/>
-      <c r="W39" s="19"/>
-      <c r="X39" s="19"/>
-      <c r="Y39" s="19"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="17"/>
+      <c r="I39" s="17"/>
+      <c r="J39" s="17"/>
+      <c r="K39" s="17"/>
+      <c r="L39" s="17"/>
+      <c r="M39" s="17"/>
+      <c r="N39" s="17"/>
+      <c r="O39" s="17"/>
+      <c r="P39" s="17"/>
+      <c r="Q39" s="17"/>
+      <c r="R39" s="17"/>
+      <c r="S39" s="17"/>
+      <c r="T39" s="17"/>
+      <c r="U39" s="17"/>
+      <c r="V39" s="17"/>
+      <c r="W39" s="17"/>
+      <c r="X39" s="17"/>
+      <c r="Y39" s="17"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="17" t="s">
+      <c r="A40" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="B40" s="18">
+      <c r="B40" s="16">
         <v>0.0</v>
       </c>
-      <c r="C40" s="19" t="s">
+      <c r="C40" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="D40" s="19" t="s">
+      <c r="D40" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="E40" s="19" t="s">
+      <c r="E40" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="F40" s="19"/>
-      <c r="G40" s="19"/>
-      <c r="H40" s="19"/>
-      <c r="I40" s="19"/>
-      <c r="J40" s="19"/>
-      <c r="K40" s="19"/>
-      <c r="L40" s="19"/>
-      <c r="M40" s="19"/>
-      <c r="N40" s="19"/>
-      <c r="O40" s="19"/>
-      <c r="P40" s="19"/>
-      <c r="Q40" s="19"/>
-      <c r="R40" s="19"/>
-      <c r="S40" s="19"/>
-      <c r="T40" s="19"/>
-      <c r="U40" s="19"/>
-      <c r="V40" s="19"/>
-      <c r="W40" s="19"/>
-      <c r="X40" s="19"/>
-      <c r="Y40" s="19"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="17"/>
+      <c r="I40" s="17"/>
+      <c r="J40" s="17"/>
+      <c r="K40" s="17"/>
+      <c r="L40" s="17"/>
+      <c r="M40" s="17"/>
+      <c r="N40" s="17"/>
+      <c r="O40" s="17"/>
+      <c r="P40" s="17"/>
+      <c r="Q40" s="17"/>
+      <c r="R40" s="17"/>
+      <c r="S40" s="17"/>
+      <c r="T40" s="17"/>
+      <c r="U40" s="17"/>
+      <c r="V40" s="17"/>
+      <c r="W40" s="17"/>
+      <c r="X40" s="17"/>
+      <c r="Y40" s="17"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="17" t="s">
+      <c r="A41" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="B41" s="18">
+      <c r="B41" s="16">
         <v>0.0</v>
       </c>
-      <c r="C41" s="19" t="s">
+      <c r="C41" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="D41" s="19" t="s">
+      <c r="D41" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="E41" s="19" t="s">
+      <c r="E41" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="F41" s="19"/>
-      <c r="G41" s="19"/>
-      <c r="H41" s="19"/>
-      <c r="I41" s="19"/>
-      <c r="J41" s="19"/>
-      <c r="K41" s="19"/>
-      <c r="L41" s="19"/>
-      <c r="M41" s="19"/>
-      <c r="N41" s="19"/>
-      <c r="O41" s="19"/>
-      <c r="P41" s="19"/>
-      <c r="Q41" s="19"/>
-      <c r="R41" s="19"/>
-      <c r="S41" s="19"/>
-      <c r="T41" s="19"/>
-      <c r="U41" s="19"/>
-      <c r="V41" s="19"/>
-      <c r="W41" s="19"/>
-      <c r="X41" s="19"/>
-      <c r="Y41" s="19"/>
+      <c r="F41" s="17"/>
+      <c r="G41" s="17"/>
+      <c r="H41" s="17"/>
+      <c r="I41" s="17"/>
+      <c r="J41" s="17"/>
+      <c r="K41" s="17"/>
+      <c r="L41" s="17"/>
+      <c r="M41" s="17"/>
+      <c r="N41" s="17"/>
+      <c r="O41" s="17"/>
+      <c r="P41" s="17"/>
+      <c r="Q41" s="17"/>
+      <c r="R41" s="17"/>
+      <c r="S41" s="17"/>
+      <c r="T41" s="17"/>
+      <c r="U41" s="17"/>
+      <c r="V41" s="17"/>
+      <c r="W41" s="17"/>
+      <c r="X41" s="17"/>
+      <c r="Y41" s="17"/>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="17" t="s">
+      <c r="A42" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="B42" s="18">
+      <c r="B42" s="16">
         <v>0.0</v>
       </c>
-      <c r="C42" s="19" t="s">
+      <c r="C42" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="D42" s="19" t="s">
+      <c r="D42" s="17" t="s">
         <v>167</v>
       </c>
-      <c r="E42" s="19" t="s">
+      <c r="E42" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="F42" s="19"/>
-      <c r="G42" s="19"/>
-      <c r="H42" s="19"/>
-      <c r="I42" s="19"/>
-      <c r="J42" s="19"/>
-      <c r="K42" s="19"/>
-      <c r="L42" s="19"/>
-      <c r="M42" s="19"/>
-      <c r="N42" s="19"/>
-      <c r="O42" s="19"/>
-      <c r="P42" s="19"/>
-      <c r="Q42" s="19"/>
-      <c r="R42" s="19"/>
-      <c r="S42" s="19"/>
-      <c r="T42" s="19"/>
-      <c r="U42" s="19"/>
-      <c r="V42" s="19"/>
-      <c r="W42" s="19"/>
-      <c r="X42" s="19"/>
-      <c r="Y42" s="19"/>
+      <c r="F42" s="17"/>
+      <c r="G42" s="17"/>
+      <c r="H42" s="17"/>
+      <c r="I42" s="17"/>
+      <c r="J42" s="17"/>
+      <c r="K42" s="17"/>
+      <c r="L42" s="17"/>
+      <c r="M42" s="17"/>
+      <c r="N42" s="17"/>
+      <c r="O42" s="17"/>
+      <c r="P42" s="17"/>
+      <c r="Q42" s="17"/>
+      <c r="R42" s="17"/>
+      <c r="S42" s="17"/>
+      <c r="T42" s="17"/>
+      <c r="U42" s="17"/>
+      <c r="V42" s="17"/>
+      <c r="W42" s="17"/>
+      <c r="X42" s="17"/>
+      <c r="Y42" s="17"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="17" t="s">
+      <c r="A43" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="B43" s="18">
+      <c r="B43" s="16">
         <v>0.0</v>
       </c>
-      <c r="C43" s="19" t="s">
+      <c r="C43" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="D43" s="19" t="s">
+      <c r="D43" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="E43" s="19" t="s">
+      <c r="E43" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="F43" s="19"/>
-      <c r="G43" s="19"/>
-      <c r="H43" s="19"/>
-      <c r="I43" s="19"/>
-      <c r="J43" s="19"/>
-      <c r="K43" s="19"/>
-      <c r="L43" s="19"/>
-      <c r="M43" s="19"/>
-      <c r="N43" s="19"/>
-      <c r="O43" s="19"/>
-      <c r="P43" s="19"/>
-      <c r="Q43" s="19"/>
-      <c r="R43" s="19"/>
-      <c r="S43" s="19"/>
-      <c r="T43" s="19"/>
-      <c r="U43" s="19"/>
-      <c r="V43" s="19"/>
-      <c r="W43" s="19"/>
-      <c r="X43" s="19"/>
-      <c r="Y43" s="19"/>
+      <c r="F43" s="17"/>
+      <c r="G43" s="17"/>
+      <c r="H43" s="17"/>
+      <c r="I43" s="17"/>
+      <c r="J43" s="17"/>
+      <c r="K43" s="17"/>
+      <c r="L43" s="17"/>
+      <c r="M43" s="17"/>
+      <c r="N43" s="17"/>
+      <c r="O43" s="17"/>
+      <c r="P43" s="17"/>
+      <c r="Q43" s="17"/>
+      <c r="R43" s="17"/>
+      <c r="S43" s="17"/>
+      <c r="T43" s="17"/>
+      <c r="U43" s="17"/>
+      <c r="V43" s="17"/>
+      <c r="W43" s="17"/>
+      <c r="X43" s="17"/>
+      <c r="Y43" s="17"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="17" t="s">
+      <c r="A44" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="B44" s="18">
+      <c r="B44" s="16">
         <v>0.0</v>
       </c>
-      <c r="C44" s="19" t="s">
+      <c r="C44" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="D44" s="19" t="s">
+      <c r="D44" s="17" t="s">
         <v>175</v>
       </c>
-      <c r="E44" s="19" t="s">
+      <c r="E44" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="F44" s="19"/>
-      <c r="G44" s="19"/>
-      <c r="H44" s="19"/>
-      <c r="I44" s="19"/>
-      <c r="J44" s="19"/>
-      <c r="K44" s="19"/>
-      <c r="L44" s="19"/>
-      <c r="M44" s="19"/>
-      <c r="N44" s="19"/>
-      <c r="O44" s="19"/>
-      <c r="P44" s="19"/>
-      <c r="Q44" s="19"/>
-      <c r="R44" s="19"/>
-      <c r="S44" s="19"/>
-      <c r="T44" s="19"/>
-      <c r="U44" s="19"/>
-      <c r="V44" s="19"/>
-      <c r="W44" s="19"/>
-      <c r="X44" s="19"/>
-      <c r="Y44" s="19"/>
+      <c r="F44" s="17"/>
+      <c r="G44" s="17"/>
+      <c r="H44" s="17"/>
+      <c r="I44" s="17"/>
+      <c r="J44" s="17"/>
+      <c r="K44" s="17"/>
+      <c r="L44" s="17"/>
+      <c r="M44" s="17"/>
+      <c r="N44" s="17"/>
+      <c r="O44" s="17"/>
+      <c r="P44" s="17"/>
+      <c r="Q44" s="17"/>
+      <c r="R44" s="17"/>
+      <c r="S44" s="17"/>
+      <c r="T44" s="17"/>
+      <c r="U44" s="17"/>
+      <c r="V44" s="17"/>
+      <c r="W44" s="17"/>
+      <c r="X44" s="17"/>
+      <c r="Y44" s="17"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="17" t="s">
+      <c r="A45" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="B45" s="18">
+      <c r="B45" s="16">
         <v>0.0</v>
       </c>
-      <c r="C45" s="19" t="s">
+      <c r="C45" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="D45" s="19" t="s">
+      <c r="D45" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="E45" s="19" t="s">
+      <c r="E45" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="F45" s="19"/>
-      <c r="G45" s="19"/>
-      <c r="H45" s="19"/>
-      <c r="I45" s="19"/>
-      <c r="J45" s="19"/>
-      <c r="K45" s="19"/>
-      <c r="L45" s="19"/>
-      <c r="M45" s="19"/>
-      <c r="N45" s="19"/>
-      <c r="O45" s="19"/>
-      <c r="P45" s="19"/>
-      <c r="Q45" s="19"/>
-      <c r="R45" s="19"/>
-      <c r="S45" s="19"/>
-      <c r="T45" s="19"/>
-      <c r="U45" s="19"/>
-      <c r="V45" s="19"/>
-      <c r="W45" s="19"/>
-      <c r="X45" s="19"/>
-      <c r="Y45" s="19"/>
+      <c r="F45" s="17"/>
+      <c r="G45" s="17"/>
+      <c r="H45" s="17"/>
+      <c r="I45" s="17"/>
+      <c r="J45" s="17"/>
+      <c r="K45" s="17"/>
+      <c r="L45" s="17"/>
+      <c r="M45" s="17"/>
+      <c r="N45" s="17"/>
+      <c r="O45" s="17"/>
+      <c r="P45" s="17"/>
+      <c r="Q45" s="17"/>
+      <c r="R45" s="17"/>
+      <c r="S45" s="17"/>
+      <c r="T45" s="17"/>
+      <c r="U45" s="17"/>
+      <c r="V45" s="17"/>
+      <c r="W45" s="17"/>
+      <c r="X45" s="17"/>
+      <c r="Y45" s="17"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="17" t="s">
+      <c r="A46" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="B46" s="18">
+      <c r="B46" s="16">
         <v>0.0</v>
       </c>
-      <c r="C46" s="19" t="s">
+      <c r="C46" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="D46" s="19" t="s">
+      <c r="D46" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="E46" s="19" t="s">
+      <c r="E46" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="F46" s="19"/>
-      <c r="G46" s="19"/>
-      <c r="H46" s="19"/>
-      <c r="I46" s="19"/>
-      <c r="J46" s="19"/>
-      <c r="K46" s="19"/>
-      <c r="L46" s="19"/>
-      <c r="M46" s="19"/>
-      <c r="N46" s="19"/>
-      <c r="O46" s="19"/>
-      <c r="P46" s="19"/>
-      <c r="Q46" s="19"/>
-      <c r="R46" s="19"/>
-      <c r="S46" s="19"/>
-      <c r="T46" s="19"/>
-      <c r="U46" s="19"/>
-      <c r="V46" s="19"/>
-      <c r="W46" s="19"/>
-      <c r="X46" s="19"/>
-      <c r="Y46" s="19"/>
+      <c r="F46" s="17"/>
+      <c r="G46" s="17"/>
+      <c r="H46" s="17"/>
+      <c r="I46" s="17"/>
+      <c r="J46" s="17"/>
+      <c r="K46" s="17"/>
+      <c r="L46" s="17"/>
+      <c r="M46" s="17"/>
+      <c r="N46" s="17"/>
+      <c r="O46" s="17"/>
+      <c r="P46" s="17"/>
+      <c r="Q46" s="17"/>
+      <c r="R46" s="17"/>
+      <c r="S46" s="17"/>
+      <c r="T46" s="17"/>
+      <c r="U46" s="17"/>
+      <c r="V46" s="17"/>
+      <c r="W46" s="17"/>
+      <c r="X46" s="17"/>
+      <c r="Y46" s="17"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="17" t="s">
+      <c r="A47" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="B47" s="18">
+      <c r="B47" s="16">
         <v>0.0</v>
       </c>
-      <c r="C47" s="19" t="s">
+      <c r="C47" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="D47" s="19" t="s">
+      <c r="D47" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="E47" s="19" t="s">
+      <c r="E47" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="F47" s="19"/>
-      <c r="G47" s="19"/>
-      <c r="H47" s="19"/>
-      <c r="I47" s="19"/>
-      <c r="J47" s="19"/>
-      <c r="K47" s="19"/>
-      <c r="L47" s="19"/>
-      <c r="M47" s="19"/>
-      <c r="N47" s="19"/>
-      <c r="O47" s="19"/>
-      <c r="P47" s="19"/>
-      <c r="Q47" s="19"/>
-      <c r="R47" s="19"/>
-      <c r="S47" s="19"/>
-      <c r="T47" s="19"/>
-      <c r="U47" s="19"/>
-      <c r="V47" s="19"/>
-      <c r="W47" s="19"/>
-      <c r="X47" s="19"/>
-      <c r="Y47" s="19"/>
+      <c r="F47" s="17"/>
+      <c r="G47" s="17"/>
+      <c r="H47" s="17"/>
+      <c r="I47" s="17"/>
+      <c r="J47" s="17"/>
+      <c r="K47" s="17"/>
+      <c r="L47" s="17"/>
+      <c r="M47" s="17"/>
+      <c r="N47" s="17"/>
+      <c r="O47" s="17"/>
+      <c r="P47" s="17"/>
+      <c r="Q47" s="17"/>
+      <c r="R47" s="17"/>
+      <c r="S47" s="17"/>
+      <c r="T47" s="17"/>
+      <c r="U47" s="17"/>
+      <c r="V47" s="17"/>
+      <c r="W47" s="17"/>
+      <c r="X47" s="17"/>
+      <c r="Y47" s="17"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="17" t="s">
+      <c r="A48" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="B48" s="18">
+      <c r="B48" s="16">
         <v>0.0</v>
       </c>
-      <c r="C48" s="19" t="s">
+      <c r="C48" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="D48" s="19" t="s">
+      <c r="D48" s="17" t="s">
         <v>191</v>
       </c>
-      <c r="E48" s="19" t="s">
+      <c r="E48" s="17" t="s">
         <v>192</v>
       </c>
-      <c r="F48" s="19"/>
-      <c r="G48" s="19"/>
-      <c r="H48" s="19"/>
-      <c r="I48" s="19"/>
-      <c r="J48" s="19"/>
-      <c r="K48" s="19"/>
-      <c r="L48" s="19"/>
-      <c r="M48" s="19"/>
-      <c r="N48" s="19"/>
-      <c r="O48" s="19"/>
-      <c r="P48" s="19"/>
-      <c r="Q48" s="19"/>
-      <c r="R48" s="19"/>
-      <c r="S48" s="19"/>
-      <c r="T48" s="19"/>
-      <c r="U48" s="19"/>
-      <c r="V48" s="19"/>
-      <c r="W48" s="19"/>
-      <c r="X48" s="19"/>
-      <c r="Y48" s="19"/>
+      <c r="F48" s="17"/>
+      <c r="G48" s="17"/>
+      <c r="H48" s="17"/>
+      <c r="I48" s="17"/>
+      <c r="J48" s="17"/>
+      <c r="K48" s="17"/>
+      <c r="L48" s="17"/>
+      <c r="M48" s="17"/>
+      <c r="N48" s="17"/>
+      <c r="O48" s="17"/>
+      <c r="P48" s="17"/>
+      <c r="Q48" s="17"/>
+      <c r="R48" s="17"/>
+      <c r="S48" s="17"/>
+      <c r="T48" s="17"/>
+      <c r="U48" s="17"/>
+      <c r="V48" s="17"/>
+      <c r="W48" s="17"/>
+      <c r="X48" s="17"/>
+      <c r="Y48" s="17"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="17" t="s">
+      <c r="A49" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="B49" s="18">
+      <c r="B49" s="16">
         <v>0.0</v>
       </c>
-      <c r="C49" s="19" t="s">
+      <c r="C49" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="D49" s="19" t="s">
+      <c r="D49" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="E49" s="19" t="s">
+      <c r="E49" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="F49" s="19"/>
-      <c r="G49" s="19"/>
-      <c r="H49" s="19"/>
-      <c r="I49" s="19"/>
-      <c r="J49" s="19"/>
-      <c r="K49" s="19"/>
-      <c r="L49" s="19"/>
-      <c r="M49" s="19"/>
-      <c r="N49" s="19"/>
-      <c r="O49" s="19"/>
-      <c r="P49" s="19"/>
-      <c r="Q49" s="19"/>
-      <c r="R49" s="19"/>
-      <c r="S49" s="19"/>
-      <c r="T49" s="19"/>
-      <c r="U49" s="19"/>
-      <c r="V49" s="19"/>
-      <c r="W49" s="19"/>
-      <c r="X49" s="19"/>
-      <c r="Y49" s="19"/>
+      <c r="F49" s="17"/>
+      <c r="G49" s="17"/>
+      <c r="H49" s="17"/>
+      <c r="I49" s="17"/>
+      <c r="J49" s="17"/>
+      <c r="K49" s="17"/>
+      <c r="L49" s="17"/>
+      <c r="M49" s="17"/>
+      <c r="N49" s="17"/>
+      <c r="O49" s="17"/>
+      <c r="P49" s="17"/>
+      <c r="Q49" s="17"/>
+      <c r="R49" s="17"/>
+      <c r="S49" s="17"/>
+      <c r="T49" s="17"/>
+      <c r="U49" s="17"/>
+      <c r="V49" s="17"/>
+      <c r="W49" s="17"/>
+      <c r="X49" s="17"/>
+      <c r="Y49" s="17"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="17" t="s">
+      <c r="A50" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="B50" s="18">
+      <c r="B50" s="16">
         <v>0.0</v>
       </c>
-      <c r="C50" s="19" t="s">
+      <c r="C50" s="17" t="s">
         <v>198</v>
       </c>
-      <c r="D50" s="19" t="s">
+      <c r="D50" s="17" t="s">
         <v>199</v>
       </c>
-      <c r="E50" s="19" t="s">
+      <c r="E50" s="17" t="s">
         <v>200</v>
       </c>
-      <c r="F50" s="19"/>
-      <c r="G50" s="19"/>
-      <c r="H50" s="19"/>
-      <c r="I50" s="19"/>
-      <c r="J50" s="19"/>
-      <c r="K50" s="19"/>
-      <c r="L50" s="19"/>
-      <c r="M50" s="19"/>
-      <c r="N50" s="19"/>
-      <c r="O50" s="19"/>
-      <c r="P50" s="19"/>
-      <c r="Q50" s="19"/>
-      <c r="R50" s="19"/>
-      <c r="S50" s="19"/>
-      <c r="T50" s="19"/>
-      <c r="U50" s="19"/>
-      <c r="V50" s="19"/>
-      <c r="W50" s="19"/>
-      <c r="X50" s="19"/>
-      <c r="Y50" s="19"/>
+      <c r="F50" s="17"/>
+      <c r="G50" s="17"/>
+      <c r="H50" s="17"/>
+      <c r="I50" s="17"/>
+      <c r="J50" s="17"/>
+      <c r="K50" s="17"/>
+      <c r="L50" s="17"/>
+      <c r="M50" s="17"/>
+      <c r="N50" s="17"/>
+      <c r="O50" s="17"/>
+      <c r="P50" s="17"/>
+      <c r="Q50" s="17"/>
+      <c r="R50" s="17"/>
+      <c r="S50" s="17"/>
+      <c r="T50" s="17"/>
+      <c r="U50" s="17"/>
+      <c r="V50" s="17"/>
+      <c r="W50" s="17"/>
+      <c r="X50" s="17"/>
+      <c r="Y50" s="17"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="17" t="s">
+      <c r="A51" s="15" t="s">
         <v>201</v>
       </c>
-      <c r="B51" s="18">
+      <c r="B51" s="16">
         <v>0.0</v>
       </c>
-      <c r="C51" s="19" t="s">
+      <c r="C51" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="D51" s="19" t="s">
+      <c r="D51" s="17" t="s">
         <v>203</v>
       </c>
-      <c r="E51" s="19" t="s">
+      <c r="E51" s="17" t="s">
         <v>204</v>
       </c>
-      <c r="F51" s="19"/>
-      <c r="G51" s="19"/>
-      <c r="H51" s="19"/>
-      <c r="I51" s="19"/>
-      <c r="J51" s="19"/>
-      <c r="K51" s="19"/>
-      <c r="L51" s="19"/>
-      <c r="M51" s="19"/>
-      <c r="N51" s="19"/>
-      <c r="O51" s="19"/>
-      <c r="P51" s="19"/>
-      <c r="Q51" s="19"/>
-      <c r="R51" s="19"/>
-      <c r="S51" s="19"/>
-      <c r="T51" s="19"/>
-      <c r="U51" s="19"/>
-      <c r="V51" s="19"/>
-      <c r="W51" s="19"/>
-      <c r="X51" s="19"/>
-      <c r="Y51" s="19"/>
+      <c r="F51" s="17"/>
+      <c r="G51" s="17"/>
+      <c r="H51" s="17"/>
+      <c r="I51" s="17"/>
+      <c r="J51" s="17"/>
+      <c r="K51" s="17"/>
+      <c r="L51" s="17"/>
+      <c r="M51" s="17"/>
+      <c r="N51" s="17"/>
+      <c r="O51" s="17"/>
+      <c r="P51" s="17"/>
+      <c r="Q51" s="17"/>
+      <c r="R51" s="17"/>
+      <c r="S51" s="17"/>
+      <c r="T51" s="17"/>
+      <c r="U51" s="17"/>
+      <c r="V51" s="17"/>
+      <c r="W51" s="17"/>
+      <c r="X51" s="17"/>
+      <c r="Y51" s="17"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="17" t="s">
+      <c r="A52" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="B52" s="18">
+      <c r="B52" s="16">
         <v>0.0</v>
       </c>
-      <c r="C52" s="19" t="s">
+      <c r="C52" s="17" t="s">
         <v>206</v>
       </c>
-      <c r="D52" s="19" t="s">
+      <c r="D52" s="17" t="s">
         <v>207</v>
       </c>
-      <c r="E52" s="19" t="s">
+      <c r="E52" s="17" t="s">
         <v>208</v>
       </c>
-      <c r="F52" s="19"/>
-      <c r="G52" s="19"/>
-      <c r="H52" s="19"/>
-      <c r="I52" s="19"/>
-      <c r="J52" s="19"/>
-      <c r="K52" s="19"/>
-      <c r="L52" s="19"/>
-      <c r="M52" s="19"/>
-      <c r="N52" s="19"/>
-      <c r="O52" s="19"/>
-      <c r="P52" s="19"/>
-      <c r="Q52" s="19"/>
-      <c r="R52" s="19"/>
-      <c r="S52" s="19"/>
-      <c r="T52" s="19"/>
-      <c r="U52" s="19"/>
-      <c r="V52" s="19"/>
-      <c r="W52" s="19"/>
-      <c r="X52" s="19"/>
-      <c r="Y52" s="19"/>
+      <c r="F52" s="17"/>
+      <c r="G52" s="17"/>
+      <c r="H52" s="17"/>
+      <c r="I52" s="17"/>
+      <c r="J52" s="17"/>
+      <c r="K52" s="17"/>
+      <c r="L52" s="17"/>
+      <c r="M52" s="17"/>
+      <c r="N52" s="17"/>
+      <c r="O52" s="17"/>
+      <c r="P52" s="17"/>
+      <c r="Q52" s="17"/>
+      <c r="R52" s="17"/>
+      <c r="S52" s="17"/>
+      <c r="T52" s="17"/>
+      <c r="U52" s="17"/>
+      <c r="V52" s="17"/>
+      <c r="W52" s="17"/>
+      <c r="X52" s="17"/>
+      <c r="Y52" s="17"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="17" t="s">
+      <c r="A53" s="15" t="s">
         <v>209</v>
       </c>
-      <c r="B53" s="18">
+      <c r="B53" s="16">
         <v>0.0</v>
       </c>
-      <c r="C53" s="19" t="s">
+      <c r="C53" s="17" t="s">
         <v>210</v>
       </c>
-      <c r="D53" s="19" t="s">
+      <c r="D53" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="E53" s="19" t="s">
+      <c r="E53" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="F53" s="19"/>
-      <c r="G53" s="19"/>
-      <c r="H53" s="19"/>
-      <c r="I53" s="19"/>
-      <c r="J53" s="19"/>
-      <c r="K53" s="19"/>
-      <c r="L53" s="19"/>
-      <c r="M53" s="19"/>
-      <c r="N53" s="19"/>
-      <c r="O53" s="19"/>
-      <c r="P53" s="19"/>
-      <c r="Q53" s="19"/>
-      <c r="R53" s="19"/>
-      <c r="S53" s="19"/>
-      <c r="T53" s="19"/>
-      <c r="U53" s="19"/>
-      <c r="V53" s="19"/>
-      <c r="W53" s="19"/>
-      <c r="X53" s="19"/>
-      <c r="Y53" s="19"/>
+      <c r="F53" s="17"/>
+      <c r="G53" s="17"/>
+      <c r="H53" s="17"/>
+      <c r="I53" s="17"/>
+      <c r="J53" s="17"/>
+      <c r="K53" s="17"/>
+      <c r="L53" s="17"/>
+      <c r="M53" s="17"/>
+      <c r="N53" s="17"/>
+      <c r="O53" s="17"/>
+      <c r="P53" s="17"/>
+      <c r="Q53" s="17"/>
+      <c r="R53" s="17"/>
+      <c r="S53" s="17"/>
+      <c r="T53" s="17"/>
+      <c r="U53" s="17"/>
+      <c r="V53" s="17"/>
+      <c r="W53" s="17"/>
+      <c r="X53" s="17"/>
+      <c r="Y53" s="17"/>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="17" t="s">
+      <c r="A54" s="15" t="s">
         <v>211</v>
       </c>
-      <c r="B54" s="18">
+      <c r="B54" s="16">
         <v>0.0</v>
       </c>
-      <c r="C54" s="19" t="s">
+      <c r="C54" s="17" t="s">
         <v>212</v>
       </c>
-      <c r="D54" s="19" t="s">
+      <c r="D54" s="17" t="s">
         <v>213</v>
       </c>
-      <c r="E54" s="19" t="s">
+      <c r="E54" s="17" t="s">
         <v>214</v>
       </c>
-      <c r="F54" s="19"/>
-      <c r="G54" s="19"/>
-      <c r="H54" s="19"/>
-      <c r="I54" s="19"/>
-      <c r="J54" s="19"/>
-      <c r="K54" s="19"/>
-      <c r="L54" s="19"/>
-      <c r="M54" s="19"/>
-      <c r="N54" s="19"/>
-      <c r="O54" s="19"/>
-      <c r="P54" s="19"/>
-      <c r="Q54" s="19"/>
-      <c r="R54" s="19"/>
-      <c r="S54" s="19"/>
-      <c r="T54" s="19"/>
-      <c r="U54" s="19"/>
-      <c r="V54" s="19"/>
-      <c r="W54" s="19"/>
-      <c r="X54" s="19"/>
-      <c r="Y54" s="19"/>
+      <c r="F54" s="17"/>
+      <c r="G54" s="17"/>
+      <c r="H54" s="17"/>
+      <c r="I54" s="17"/>
+      <c r="J54" s="17"/>
+      <c r="K54" s="17"/>
+      <c r="L54" s="17"/>
+      <c r="M54" s="17"/>
+      <c r="N54" s="17"/>
+      <c r="O54" s="17"/>
+      <c r="P54" s="17"/>
+      <c r="Q54" s="17"/>
+      <c r="R54" s="17"/>
+      <c r="S54" s="17"/>
+      <c r="T54" s="17"/>
+      <c r="U54" s="17"/>
+      <c r="V54" s="17"/>
+      <c r="W54" s="17"/>
+      <c r="X54" s="17"/>
+      <c r="Y54" s="17"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="17" t="s">
+      <c r="A55" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="B55" s="18">
+      <c r="B55" s="16">
         <v>0.0</v>
       </c>
-      <c r="C55" s="19" t="s">
+      <c r="C55" s="17" t="s">
         <v>216</v>
       </c>
-      <c r="D55" s="19" t="s">
+      <c r="D55" s="17" t="s">
         <v>217</v>
       </c>
-      <c r="E55" s="19" t="s">
+      <c r="E55" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="F55" s="19"/>
-      <c r="G55" s="19"/>
-      <c r="H55" s="19"/>
-      <c r="I55" s="19"/>
-      <c r="J55" s="19"/>
-      <c r="K55" s="19"/>
-      <c r="L55" s="19"/>
-      <c r="M55" s="19"/>
-      <c r="N55" s="19"/>
-      <c r="O55" s="19"/>
-      <c r="P55" s="19"/>
-      <c r="Q55" s="19"/>
-      <c r="R55" s="19"/>
-      <c r="S55" s="19"/>
-      <c r="T55" s="19"/>
-      <c r="U55" s="19"/>
-      <c r="V55" s="19"/>
-      <c r="W55" s="19"/>
-      <c r="X55" s="19"/>
-      <c r="Y55" s="19"/>
+      <c r="F55" s="17"/>
+      <c r="G55" s="17"/>
+      <c r="H55" s="17"/>
+      <c r="I55" s="17"/>
+      <c r="J55" s="17"/>
+      <c r="K55" s="17"/>
+      <c r="L55" s="17"/>
+      <c r="M55" s="17"/>
+      <c r="N55" s="17"/>
+      <c r="O55" s="17"/>
+      <c r="P55" s="17"/>
+      <c r="Q55" s="17"/>
+      <c r="R55" s="17"/>
+      <c r="S55" s="17"/>
+      <c r="T55" s="17"/>
+      <c r="U55" s="17"/>
+      <c r="V55" s="17"/>
+      <c r="W55" s="17"/>
+      <c r="X55" s="17"/>
+      <c r="Y55" s="17"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="17" t="s">
+      <c r="A56" s="15" t="s">
         <v>219</v>
       </c>
-      <c r="B56" s="18">
+      <c r="B56" s="16">
         <v>0.0</v>
       </c>
-      <c r="C56" s="19" t="s">
+      <c r="C56" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="D56" s="19" t="s">
+      <c r="D56" s="17" t="s">
         <v>221</v>
       </c>
-      <c r="E56" s="19" t="s">
+      <c r="E56" s="17" t="s">
         <v>222</v>
       </c>
-      <c r="F56" s="19"/>
-      <c r="G56" s="19"/>
-      <c r="H56" s="19"/>
-      <c r="I56" s="19"/>
-      <c r="J56" s="19"/>
-      <c r="K56" s="19"/>
-      <c r="L56" s="19"/>
-      <c r="M56" s="19"/>
-      <c r="N56" s="19"/>
-      <c r="O56" s="19"/>
-      <c r="P56" s="19"/>
-      <c r="Q56" s="19"/>
-      <c r="R56" s="19"/>
-      <c r="S56" s="19"/>
-      <c r="T56" s="19"/>
-      <c r="U56" s="19"/>
-      <c r="V56" s="19"/>
-      <c r="W56" s="19"/>
-      <c r="X56" s="19"/>
-      <c r="Y56" s="19"/>
+      <c r="F56" s="17"/>
+      <c r="G56" s="17"/>
+      <c r="H56" s="17"/>
+      <c r="I56" s="17"/>
+      <c r="J56" s="17"/>
+      <c r="K56" s="17"/>
+      <c r="L56" s="17"/>
+      <c r="M56" s="17"/>
+      <c r="N56" s="17"/>
+      <c r="O56" s="17"/>
+      <c r="P56" s="17"/>
+      <c r="Q56" s="17"/>
+      <c r="R56" s="17"/>
+      <c r="S56" s="17"/>
+      <c r="T56" s="17"/>
+      <c r="U56" s="17"/>
+      <c r="V56" s="17"/>
+      <c r="W56" s="17"/>
+      <c r="X56" s="17"/>
+      <c r="Y56" s="17"/>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="17" t="s">
+      <c r="A57" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="B57" s="18">
+      <c r="B57" s="16">
         <v>0.0</v>
       </c>
-      <c r="C57" s="19" t="s">
+      <c r="C57" s="17" t="s">
         <v>224</v>
       </c>
-      <c r="D57" s="19" t="s">
+      <c r="D57" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="E57" s="19" t="s">
+      <c r="E57" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="F57" s="19"/>
-      <c r="G57" s="19"/>
-      <c r="H57" s="19"/>
-      <c r="I57" s="19"/>
-      <c r="J57" s="19"/>
-      <c r="K57" s="19"/>
-      <c r="L57" s="19"/>
-      <c r="M57" s="19"/>
-      <c r="N57" s="19"/>
-      <c r="O57" s="19"/>
-      <c r="P57" s="19"/>
-      <c r="Q57" s="19"/>
-      <c r="R57" s="19"/>
-      <c r="S57" s="19"/>
-      <c r="T57" s="19"/>
-      <c r="U57" s="19"/>
-      <c r="V57" s="19"/>
-      <c r="W57" s="19"/>
-      <c r="X57" s="19"/>
-      <c r="Y57" s="19"/>
+      <c r="F57" s="17"/>
+      <c r="G57" s="17"/>
+      <c r="H57" s="17"/>
+      <c r="I57" s="17"/>
+      <c r="J57" s="17"/>
+      <c r="K57" s="17"/>
+      <c r="L57" s="17"/>
+      <c r="M57" s="17"/>
+      <c r="N57" s="17"/>
+      <c r="O57" s="17"/>
+      <c r="P57" s="17"/>
+      <c r="Q57" s="17"/>
+      <c r="R57" s="17"/>
+      <c r="S57" s="17"/>
+      <c r="T57" s="17"/>
+      <c r="U57" s="17"/>
+      <c r="V57" s="17"/>
+      <c r="W57" s="17"/>
+      <c r="X57" s="17"/>
+      <c r="Y57" s="17"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="17" t="s">
+      <c r="A58" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="B58" s="18">
+      <c r="B58" s="16">
         <v>0.0</v>
       </c>
-      <c r="C58" s="19" t="s">
+      <c r="C58" s="17" t="s">
         <v>228</v>
       </c>
-      <c r="D58" s="19" t="s">
+      <c r="D58" s="17" t="s">
         <v>229</v>
       </c>
-      <c r="E58" s="19" t="s">
+      <c r="E58" s="17" t="s">
         <v>230</v>
       </c>
-      <c r="F58" s="19"/>
-      <c r="G58" s="19"/>
-      <c r="H58" s="19"/>
-      <c r="I58" s="19"/>
-      <c r="J58" s="19"/>
-      <c r="K58" s="19"/>
-      <c r="L58" s="19"/>
-      <c r="M58" s="19"/>
-      <c r="N58" s="19"/>
-      <c r="O58" s="19"/>
-      <c r="P58" s="19"/>
-      <c r="Q58" s="19"/>
-      <c r="R58" s="19"/>
-      <c r="S58" s="19"/>
-      <c r="T58" s="19"/>
-      <c r="U58" s="19"/>
-      <c r="V58" s="19"/>
-      <c r="W58" s="19"/>
-      <c r="X58" s="19"/>
-      <c r="Y58" s="19"/>
+      <c r="F58" s="17"/>
+      <c r="G58" s="17"/>
+      <c r="H58" s="17"/>
+      <c r="I58" s="17"/>
+      <c r="J58" s="17"/>
+      <c r="K58" s="17"/>
+      <c r="L58" s="17"/>
+      <c r="M58" s="17"/>
+      <c r="N58" s="17"/>
+      <c r="O58" s="17"/>
+      <c r="P58" s="17"/>
+      <c r="Q58" s="17"/>
+      <c r="R58" s="17"/>
+      <c r="S58" s="17"/>
+      <c r="T58" s="17"/>
+      <c r="U58" s="17"/>
+      <c r="V58" s="17"/>
+      <c r="W58" s="17"/>
+      <c r="X58" s="17"/>
+      <c r="Y58" s="17"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="17" t="s">
+      <c r="A59" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="B59" s="18">
+      <c r="B59" s="16">
         <v>0.0</v>
       </c>
-      <c r="C59" s="19" t="s">
+      <c r="C59" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="D59" s="19" t="s">
+      <c r="D59" s="17" t="s">
         <v>233</v>
       </c>
-      <c r="E59" s="19" t="s">
+      <c r="E59" s="17" t="s">
         <v>234</v>
       </c>
-      <c r="F59" s="19"/>
-      <c r="G59" s="19"/>
-      <c r="H59" s="19"/>
-      <c r="I59" s="19"/>
-      <c r="J59" s="19"/>
-      <c r="K59" s="19"/>
-      <c r="L59" s="19"/>
-      <c r="M59" s="19"/>
-      <c r="N59" s="19"/>
-      <c r="O59" s="19"/>
-      <c r="P59" s="19"/>
-      <c r="Q59" s="19"/>
-      <c r="R59" s="19"/>
-      <c r="S59" s="19"/>
-      <c r="T59" s="19"/>
-      <c r="U59" s="19"/>
-      <c r="V59" s="19"/>
-      <c r="W59" s="19"/>
-      <c r="X59" s="19"/>
-      <c r="Y59" s="19"/>
+      <c r="F59" s="17"/>
+      <c r="G59" s="17"/>
+      <c r="H59" s="17"/>
+      <c r="I59" s="17"/>
+      <c r="J59" s="17"/>
+      <c r="K59" s="17"/>
+      <c r="L59" s="17"/>
+      <c r="M59" s="17"/>
+      <c r="N59" s="17"/>
+      <c r="O59" s="17"/>
+      <c r="P59" s="17"/>
+      <c r="Q59" s="17"/>
+      <c r="R59" s="17"/>
+      <c r="S59" s="17"/>
+      <c r="T59" s="17"/>
+      <c r="U59" s="17"/>
+      <c r="V59" s="17"/>
+      <c r="W59" s="17"/>
+      <c r="X59" s="17"/>
+      <c r="Y59" s="17"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="17" t="s">
+      <c r="A60" s="15" t="s">
         <v>235</v>
       </c>
-      <c r="B60" s="18">
+      <c r="B60" s="16">
         <v>0.0</v>
       </c>
-      <c r="C60" s="19" t="s">
+      <c r="C60" s="17" t="s">
         <v>236</v>
       </c>
-      <c r="D60" s="19" t="s">
+      <c r="D60" s="17" t="s">
         <v>237</v>
       </c>
-      <c r="E60" s="19" t="s">
+      <c r="E60" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="F60" s="19"/>
-      <c r="G60" s="19"/>
-      <c r="H60" s="19"/>
-      <c r="I60" s="19"/>
-      <c r="J60" s="19"/>
-      <c r="K60" s="19"/>
-      <c r="L60" s="19"/>
-      <c r="M60" s="19"/>
-      <c r="N60" s="19"/>
-      <c r="O60" s="19"/>
-      <c r="P60" s="19"/>
-      <c r="Q60" s="19"/>
-      <c r="R60" s="19"/>
-      <c r="S60" s="19"/>
-      <c r="T60" s="19"/>
-      <c r="U60" s="19"/>
-      <c r="V60" s="19"/>
-      <c r="W60" s="19"/>
-      <c r="X60" s="19"/>
-      <c r="Y60" s="19"/>
+      <c r="F60" s="17"/>
+      <c r="G60" s="17"/>
+      <c r="H60" s="17"/>
+      <c r="I60" s="17"/>
+      <c r="J60" s="17"/>
+      <c r="K60" s="17"/>
+      <c r="L60" s="17"/>
+      <c r="M60" s="17"/>
+      <c r="N60" s="17"/>
+      <c r="O60" s="17"/>
+      <c r="P60" s="17"/>
+      <c r="Q60" s="17"/>
+      <c r="R60" s="17"/>
+      <c r="S60" s="17"/>
+      <c r="T60" s="17"/>
+      <c r="U60" s="17"/>
+      <c r="V60" s="17"/>
+      <c r="W60" s="17"/>
+      <c r="X60" s="17"/>
+      <c r="Y60" s="17"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="17" t="s">
+      <c r="A61" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="B61" s="18">
+      <c r="B61" s="16">
         <v>0.0</v>
       </c>
-      <c r="C61" s="19" t="s">
+      <c r="C61" s="17" t="s">
         <v>240</v>
       </c>
-      <c r="D61" s="19" t="s">
+      <c r="D61" s="17" t="s">
         <v>241</v>
       </c>
-      <c r="E61" s="19" t="s">
+      <c r="E61" s="17" t="s">
         <v>242</v>
       </c>
-      <c r="F61" s="19"/>
-      <c r="G61" s="19"/>
-      <c r="H61" s="19"/>
-      <c r="I61" s="19"/>
-      <c r="J61" s="19"/>
-      <c r="K61" s="19"/>
-      <c r="L61" s="19"/>
-      <c r="M61" s="19"/>
-      <c r="N61" s="19"/>
-      <c r="O61" s="19"/>
-      <c r="P61" s="19"/>
-      <c r="Q61" s="19"/>
-      <c r="R61" s="19"/>
-      <c r="S61" s="19"/>
-      <c r="T61" s="19"/>
-      <c r="U61" s="19"/>
-      <c r="V61" s="19"/>
-      <c r="W61" s="19"/>
-      <c r="X61" s="19"/>
-      <c r="Y61" s="19"/>
+      <c r="F61" s="17"/>
+      <c r="G61" s="17"/>
+      <c r="H61" s="17"/>
+      <c r="I61" s="17"/>
+      <c r="J61" s="17"/>
+      <c r="K61" s="17"/>
+      <c r="L61" s="17"/>
+      <c r="M61" s="17"/>
+      <c r="N61" s="17"/>
+      <c r="O61" s="17"/>
+      <c r="P61" s="17"/>
+      <c r="Q61" s="17"/>
+      <c r="R61" s="17"/>
+      <c r="S61" s="17"/>
+      <c r="T61" s="17"/>
+      <c r="U61" s="17"/>
+      <c r="V61" s="17"/>
+      <c r="W61" s="17"/>
+      <c r="X61" s="17"/>
+      <c r="Y61" s="17"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="17" t="s">
+      <c r="A62" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="B62" s="18">
+      <c r="B62" s="16">
         <v>0.0</v>
       </c>
-      <c r="C62" s="19" t="s">
+      <c r="C62" s="17" t="s">
         <v>244</v>
       </c>
-      <c r="D62" s="19" t="s">
+      <c r="D62" s="17" t="s">
         <v>245</v>
       </c>
-      <c r="E62" s="19" t="s">
+      <c r="E62" s="17" t="s">
         <v>246</v>
       </c>
-      <c r="F62" s="19"/>
-      <c r="G62" s="19"/>
-      <c r="H62" s="19"/>
-      <c r="I62" s="19"/>
-      <c r="J62" s="19"/>
-      <c r="K62" s="19"/>
-      <c r="L62" s="19"/>
-      <c r="M62" s="19"/>
-      <c r="N62" s="19"/>
-      <c r="O62" s="19"/>
-      <c r="P62" s="19"/>
-      <c r="Q62" s="19"/>
-      <c r="R62" s="19"/>
-      <c r="S62" s="19"/>
-      <c r="T62" s="19"/>
-      <c r="U62" s="19"/>
-      <c r="V62" s="19"/>
-      <c r="W62" s="19"/>
-      <c r="X62" s="19"/>
-      <c r="Y62" s="19"/>
+      <c r="F62" s="17"/>
+      <c r="G62" s="17"/>
+      <c r="H62" s="17"/>
+      <c r="I62" s="17"/>
+      <c r="J62" s="17"/>
+      <c r="K62" s="17"/>
+      <c r="L62" s="17"/>
+      <c r="M62" s="17"/>
+      <c r="N62" s="17"/>
+      <c r="O62" s="17"/>
+      <c r="P62" s="17"/>
+      <c r="Q62" s="17"/>
+      <c r="R62" s="17"/>
+      <c r="S62" s="17"/>
+      <c r="T62" s="17"/>
+      <c r="U62" s="17"/>
+      <c r="V62" s="17"/>
+      <c r="W62" s="17"/>
+      <c r="X62" s="17"/>
+      <c r="Y62" s="17"/>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="17" t="s">
+      <c r="A63" s="15" t="s">
         <v>247</v>
       </c>
-      <c r="B63" s="18">
+      <c r="B63" s="16">
         <v>0.0</v>
       </c>
-      <c r="C63" s="19" t="s">
+      <c r="C63" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="D63" s="19" t="s">
+      <c r="D63" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="E63" s="19" t="s">
+      <c r="E63" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="F63" s="19"/>
-      <c r="G63" s="19"/>
-      <c r="H63" s="19"/>
-      <c r="I63" s="19"/>
-      <c r="J63" s="19"/>
-      <c r="K63" s="19"/>
-      <c r="L63" s="19"/>
-      <c r="M63" s="19"/>
-      <c r="N63" s="19"/>
-      <c r="O63" s="19"/>
-      <c r="P63" s="19"/>
-      <c r="Q63" s="19"/>
-      <c r="R63" s="19"/>
-      <c r="S63" s="19"/>
-      <c r="T63" s="19"/>
-      <c r="U63" s="19"/>
-      <c r="V63" s="19"/>
-      <c r="W63" s="19"/>
-      <c r="X63" s="19"/>
-      <c r="Y63" s="19"/>
+      <c r="F63" s="17"/>
+      <c r="G63" s="17"/>
+      <c r="H63" s="17"/>
+      <c r="I63" s="17"/>
+      <c r="J63" s="17"/>
+      <c r="K63" s="17"/>
+      <c r="L63" s="17"/>
+      <c r="M63" s="17"/>
+      <c r="N63" s="17"/>
+      <c r="O63" s="17"/>
+      <c r="P63" s="17"/>
+      <c r="Q63" s="17"/>
+      <c r="R63" s="17"/>
+      <c r="S63" s="17"/>
+      <c r="T63" s="17"/>
+      <c r="U63" s="17"/>
+      <c r="V63" s="17"/>
+      <c r="W63" s="17"/>
+      <c r="X63" s="17"/>
+      <c r="Y63" s="17"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="17" t="s">
+      <c r="A64" s="15" t="s">
         <v>251</v>
       </c>
-      <c r="B64" s="18">
+      <c r="B64" s="16">
         <v>0.0</v>
       </c>
-      <c r="C64" s="19" t="s">
+      <c r="C64" s="17" t="s">
         <v>252</v>
       </c>
-      <c r="D64" s="19" t="s">
+      <c r="D64" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="E64" s="19" t="s">
+      <c r="E64" s="17" t="s">
         <v>254</v>
       </c>
-      <c r="F64" s="19"/>
-      <c r="G64" s="19"/>
-      <c r="H64" s="19"/>
-      <c r="I64" s="19"/>
-      <c r="J64" s="19"/>
-      <c r="K64" s="19"/>
-      <c r="L64" s="19"/>
-      <c r="M64" s="19"/>
-      <c r="N64" s="19"/>
-      <c r="O64" s="19"/>
-      <c r="P64" s="19"/>
-      <c r="Q64" s="19"/>
-      <c r="R64" s="19"/>
-      <c r="S64" s="19"/>
-      <c r="T64" s="19"/>
-      <c r="U64" s="19"/>
-      <c r="V64" s="19"/>
-      <c r="W64" s="19"/>
-      <c r="X64" s="19"/>
-      <c r="Y64" s="19"/>
+      <c r="F64" s="17"/>
+      <c r="G64" s="17"/>
+      <c r="H64" s="17"/>
+      <c r="I64" s="17"/>
+      <c r="J64" s="17"/>
+      <c r="K64" s="17"/>
+      <c r="L64" s="17"/>
+      <c r="M64" s="17"/>
+      <c r="N64" s="17"/>
+      <c r="O64" s="17"/>
+      <c r="P64" s="17"/>
+      <c r="Q64" s="17"/>
+      <c r="R64" s="17"/>
+      <c r="S64" s="17"/>
+      <c r="T64" s="17"/>
+      <c r="U64" s="17"/>
+      <c r="V64" s="17"/>
+      <c r="W64" s="17"/>
+      <c r="X64" s="17"/>
+      <c r="Y64" s="17"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="17" t="s">
+      <c r="A65" s="15" t="s">
         <v>255</v>
       </c>
-      <c r="B65" s="18">
+      <c r="B65" s="16">
         <v>0.0</v>
       </c>
-      <c r="C65" s="19" t="s">
+      <c r="C65" s="17" t="s">
         <v>256</v>
       </c>
-      <c r="D65" s="19" t="s">
+      <c r="D65" s="17" t="s">
         <v>257</v>
       </c>
-      <c r="E65" s="19" t="s">
+      <c r="E65" s="17" t="s">
         <v>258</v>
       </c>
-      <c r="F65" s="19"/>
-      <c r="G65" s="19"/>
-      <c r="H65" s="19"/>
-      <c r="I65" s="19"/>
-      <c r="J65" s="19"/>
-      <c r="K65" s="19"/>
-      <c r="L65" s="19"/>
-      <c r="M65" s="19"/>
-      <c r="N65" s="19"/>
-      <c r="O65" s="19"/>
-      <c r="P65" s="19"/>
-      <c r="Q65" s="19"/>
-      <c r="R65" s="19"/>
-      <c r="S65" s="19"/>
-      <c r="T65" s="19"/>
-      <c r="U65" s="19"/>
-      <c r="V65" s="19"/>
-      <c r="W65" s="19"/>
-      <c r="X65" s="19"/>
-      <c r="Y65" s="19"/>
+      <c r="F65" s="17"/>
+      <c r="G65" s="17"/>
+      <c r="H65" s="17"/>
+      <c r="I65" s="17"/>
+      <c r="J65" s="17"/>
+      <c r="K65" s="17"/>
+      <c r="L65" s="17"/>
+      <c r="M65" s="17"/>
+      <c r="N65" s="17"/>
+      <c r="O65" s="17"/>
+      <c r="P65" s="17"/>
+      <c r="Q65" s="17"/>
+      <c r="R65" s="17"/>
+      <c r="S65" s="17"/>
+      <c r="T65" s="17"/>
+      <c r="U65" s="17"/>
+      <c r="V65" s="17"/>
+      <c r="W65" s="17"/>
+      <c r="X65" s="17"/>
+      <c r="Y65" s="17"/>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="17" t="s">
+      <c r="A66" s="15" t="s">
         <v>259</v>
       </c>
-      <c r="B66" s="18">
+      <c r="B66" s="16">
         <v>0.0</v>
       </c>
-      <c r="C66" s="19" t="s">
+      <c r="C66" s="17" t="s">
         <v>260</v>
       </c>
-      <c r="D66" s="19" t="s">
+      <c r="D66" s="17" t="s">
         <v>261</v>
       </c>
-      <c r="E66" s="19" t="s">
+      <c r="E66" s="17" t="s">
         <v>262</v>
       </c>
-      <c r="F66" s="19"/>
-      <c r="G66" s="19"/>
-      <c r="H66" s="19"/>
-      <c r="I66" s="19"/>
-      <c r="J66" s="19"/>
-      <c r="K66" s="19"/>
-      <c r="L66" s="19"/>
-      <c r="M66" s="19"/>
-      <c r="N66" s="19"/>
-      <c r="O66" s="19"/>
-      <c r="P66" s="19"/>
-      <c r="Q66" s="19"/>
-      <c r="R66" s="19"/>
-      <c r="S66" s="19"/>
-      <c r="T66" s="19"/>
-      <c r="U66" s="19"/>
-      <c r="V66" s="19"/>
-      <c r="W66" s="19"/>
-      <c r="X66" s="19"/>
-      <c r="Y66" s="19"/>
+      <c r="F66" s="17"/>
+      <c r="G66" s="17"/>
+      <c r="H66" s="17"/>
+      <c r="I66" s="17"/>
+      <c r="J66" s="17"/>
+      <c r="K66" s="17"/>
+      <c r="L66" s="17"/>
+      <c r="M66" s="17"/>
+      <c r="N66" s="17"/>
+      <c r="O66" s="17"/>
+      <c r="P66" s="17"/>
+      <c r="Q66" s="17"/>
+      <c r="R66" s="17"/>
+      <c r="S66" s="17"/>
+      <c r="T66" s="17"/>
+      <c r="U66" s="17"/>
+      <c r="V66" s="17"/>
+      <c r="W66" s="17"/>
+      <c r="X66" s="17"/>
+      <c r="Y66" s="17"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="17" t="s">
+      <c r="A67" s="15" t="s">
         <v>263</v>
       </c>
-      <c r="B67" s="18">
+      <c r="B67" s="16">
         <v>0.0</v>
       </c>
-      <c r="C67" s="19" t="s">
+      <c r="C67" s="17" t="s">
         <v>264</v>
       </c>
-      <c r="D67" s="19" t="s">
+      <c r="D67" s="17" t="s">
         <v>265</v>
       </c>
-      <c r="E67" s="19" t="s">
+      <c r="E67" s="17" t="s">
         <v>266</v>
       </c>
-      <c r="F67" s="19"/>
-      <c r="G67" s="19"/>
-      <c r="H67" s="19"/>
-      <c r="I67" s="19"/>
-      <c r="J67" s="19"/>
-      <c r="K67" s="19"/>
-      <c r="L67" s="19"/>
-      <c r="M67" s="19"/>
-      <c r="N67" s="19"/>
-      <c r="O67" s="19"/>
-      <c r="P67" s="19"/>
-      <c r="Q67" s="19"/>
-      <c r="R67" s="19"/>
-      <c r="S67" s="19"/>
-      <c r="T67" s="19"/>
-      <c r="U67" s="19"/>
-      <c r="V67" s="19"/>
-      <c r="W67" s="19"/>
-      <c r="X67" s="19"/>
-      <c r="Y67" s="19"/>
+      <c r="F67" s="17"/>
+      <c r="G67" s="17"/>
+      <c r="H67" s="17"/>
+      <c r="I67" s="17"/>
+      <c r="J67" s="17"/>
+      <c r="K67" s="17"/>
+      <c r="L67" s="17"/>
+      <c r="M67" s="17"/>
+      <c r="N67" s="17"/>
+      <c r="O67" s="17"/>
+      <c r="P67" s="17"/>
+      <c r="Q67" s="17"/>
+      <c r="R67" s="17"/>
+      <c r="S67" s="17"/>
+      <c r="T67" s="17"/>
+      <c r="U67" s="17"/>
+      <c r="V67" s="17"/>
+      <c r="W67" s="17"/>
+      <c r="X67" s="17"/>
+      <c r="Y67" s="17"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="20" t="s">
+      <c r="A68" s="15" t="s">
         <v>267</v>
       </c>
-      <c r="B68" s="21">
+      <c r="B68" s="16">
         <v>0.0</v>
       </c>
-      <c r="C68" s="22" t="s">
+      <c r="C68" s="17" t="s">
         <v>268</v>
       </c>
-      <c r="D68" s="22" t="s">
+      <c r="D68" s="17" t="s">
         <v>269</v>
       </c>
-      <c r="E68" s="22" t="s">
+      <c r="E68" s="17" t="s">
         <v>270</v>
       </c>
-      <c r="F68" s="22"/>
-      <c r="G68" s="22"/>
-      <c r="H68" s="22"/>
-      <c r="I68" s="22"/>
-      <c r="J68" s="22"/>
-      <c r="K68" s="22"/>
-      <c r="L68" s="22"/>
-      <c r="M68" s="22"/>
-      <c r="N68" s="22"/>
-      <c r="O68" s="22"/>
-      <c r="P68" s="22"/>
-      <c r="Q68" s="22"/>
-      <c r="R68" s="22"/>
-      <c r="S68" s="22"/>
-      <c r="T68" s="22"/>
-      <c r="U68" s="22"/>
-      <c r="V68" s="22"/>
-      <c r="W68" s="22"/>
-      <c r="X68" s="22"/>
-      <c r="Y68" s="22"/>
+      <c r="F68" s="17"/>
+      <c r="G68" s="17"/>
+      <c r="H68" s="17"/>
+      <c r="I68" s="17"/>
+      <c r="J68" s="17"/>
+      <c r="K68" s="17"/>
+      <c r="L68" s="17"/>
+      <c r="M68" s="17"/>
+      <c r="N68" s="17"/>
+      <c r="O68" s="17"/>
+      <c r="P68" s="17"/>
+      <c r="Q68" s="17"/>
+      <c r="R68" s="17"/>
+      <c r="S68" s="17"/>
+      <c r="T68" s="17"/>
+      <c r="U68" s="17"/>
+      <c r="V68" s="17"/>
+      <c r="W68" s="17"/>
+      <c r="X68" s="17"/>
+      <c r="Y68" s="17"/>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="23" t="s">
+      <c r="A69" s="18" t="s">
         <v>271</v>
       </c>
-      <c r="B69" s="24">
+      <c r="B69" s="19">
         <v>0.0</v>
       </c>
-      <c r="C69" s="24" t="s">
+      <c r="C69" s="19" t="s">
         <v>272</v>
       </c>
-      <c r="D69" s="24" t="s">
+      <c r="D69" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="E69" s="24" t="s">
+      <c r="E69" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="F69" s="24"/>
-      <c r="G69" s="24"/>
-      <c r="H69" s="24"/>
-      <c r="I69" s="24"/>
-      <c r="J69" s="24"/>
-      <c r="K69" s="24"/>
-      <c r="L69" s="24"/>
-      <c r="M69" s="24"/>
-      <c r="N69" s="24"/>
-      <c r="O69" s="24"/>
-      <c r="P69" s="24"/>
-      <c r="Q69" s="24"/>
-      <c r="R69" s="24"/>
-      <c r="S69" s="24"/>
-      <c r="T69" s="24"/>
-      <c r="U69" s="24"/>
-      <c r="V69" s="24"/>
-      <c r="W69" s="24"/>
-      <c r="X69" s="24"/>
-      <c r="Y69" s="24"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="19"/>
+      <c r="K69" s="19"/>
+      <c r="L69" s="19"/>
+      <c r="M69" s="19"/>
+      <c r="N69" s="19"/>
+      <c r="O69" s="19"/>
+      <c r="P69" s="19"/>
+      <c r="Q69" s="19"/>
+      <c r="R69" s="19"/>
+      <c r="S69" s="19"/>
+      <c r="T69" s="19"/>
+      <c r="U69" s="19"/>
+      <c r="V69" s="19"/>
+      <c r="W69" s="19"/>
+      <c r="X69" s="19"/>
+      <c r="Y69" s="19"/>
+      <c r="Z69" s="20"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="25" t="s">
+      <c r="A70" s="21" t="s">
         <v>273</v>
       </c>
-      <c r="B70" s="26">
+      <c r="B70" s="22">
         <v>0.0</v>
       </c>
-      <c r="C70" s="26" t="s">
+      <c r="C70" s="22" t="s">
         <v>274</v>
       </c>
-      <c r="D70" s="26" t="s">
+      <c r="D70" s="22" t="s">
         <v>275</v>
       </c>
-      <c r="E70" s="26" t="s">
+      <c r="E70" s="22" t="s">
         <v>276</v>
       </c>
-      <c r="F70" s="26"/>
-      <c r="G70" s="26"/>
-      <c r="H70" s="26"/>
-      <c r="I70" s="26"/>
-      <c r="J70" s="26"/>
-      <c r="K70" s="26"/>
-      <c r="L70" s="26"/>
-      <c r="M70" s="26"/>
-      <c r="N70" s="26"/>
-      <c r="O70" s="26"/>
-      <c r="P70" s="26"/>
-      <c r="Q70" s="26"/>
-      <c r="R70" s="26"/>
-      <c r="S70" s="26"/>
-      <c r="T70" s="26"/>
-      <c r="U70" s="26"/>
-      <c r="V70" s="26"/>
-      <c r="W70" s="26"/>
-      <c r="X70" s="26"/>
-      <c r="Y70" s="26"/>
+      <c r="F70" s="22"/>
+      <c r="G70" s="22"/>
+      <c r="H70" s="22"/>
+      <c r="I70" s="22"/>
+      <c r="J70" s="22"/>
+      <c r="K70" s="22"/>
+      <c r="L70" s="22"/>
+      <c r="M70" s="22"/>
+      <c r="N70" s="22"/>
+      <c r="O70" s="22"/>
+      <c r="P70" s="22"/>
+      <c r="Q70" s="22"/>
+      <c r="R70" s="22"/>
+      <c r="S70" s="22"/>
+      <c r="T70" s="22"/>
+      <c r="U70" s="22"/>
+      <c r="V70" s="22"/>
+      <c r="W70" s="22"/>
+      <c r="X70" s="22"/>
+      <c r="Y70" s="22"/>
+      <c r="Z70" s="23"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="25" t="s">
+      <c r="A71" s="21" t="s">
         <v>277</v>
       </c>
-      <c r="B71" s="26">
+      <c r="B71" s="22">
         <v>0.0</v>
       </c>
-      <c r="C71" s="26" t="s">
+      <c r="C71" s="22" t="s">
         <v>278</v>
       </c>
-      <c r="D71" s="26" t="s">
+      <c r="D71" s="22" t="s">
         <v>175</v>
       </c>
-      <c r="E71" s="26" t="s">
+      <c r="E71" s="22" t="s">
         <v>176</v>
       </c>
-      <c r="F71" s="26"/>
-      <c r="G71" s="26"/>
-      <c r="H71" s="26"/>
-      <c r="I71" s="26"/>
-      <c r="J71" s="26"/>
-      <c r="K71" s="26"/>
-      <c r="L71" s="26"/>
-      <c r="M71" s="26"/>
-      <c r="N71" s="26"/>
-      <c r="O71" s="26"/>
-      <c r="P71" s="26"/>
-      <c r="Q71" s="26"/>
-      <c r="R71" s="26"/>
-      <c r="S71" s="26"/>
-      <c r="T71" s="26"/>
-      <c r="U71" s="26"/>
-      <c r="V71" s="26"/>
-      <c r="W71" s="26"/>
-      <c r="X71" s="26"/>
-      <c r="Y71" s="26"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="22"/>
+      <c r="K71" s="22"/>
+      <c r="L71" s="22"/>
+      <c r="M71" s="22"/>
+      <c r="N71" s="22"/>
+      <c r="O71" s="22"/>
+      <c r="P71" s="22"/>
+      <c r="Q71" s="22"/>
+      <c r="R71" s="22"/>
+      <c r="S71" s="22"/>
+      <c r="T71" s="22"/>
+      <c r="U71" s="22"/>
+      <c r="V71" s="22"/>
+      <c r="W71" s="22"/>
+      <c r="X71" s="22"/>
+      <c r="Y71" s="22"/>
+      <c r="Z71" s="23"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="25" t="s">
+      <c r="A72" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="B72" s="26">
+      <c r="B72" s="22">
         <v>0.0</v>
       </c>
-      <c r="C72" s="26" t="s">
+      <c r="C72" s="22" t="s">
         <v>280</v>
       </c>
-      <c r="D72" s="26" t="s">
+      <c r="D72" s="22" t="s">
         <v>281</v>
       </c>
-      <c r="E72" s="26" t="s">
+      <c r="E72" s="22" t="s">
         <v>282</v>
       </c>
-      <c r="F72" s="26"/>
-      <c r="G72" s="26"/>
-      <c r="H72" s="26"/>
-      <c r="I72" s="26"/>
-      <c r="J72" s="26"/>
-      <c r="K72" s="26"/>
-      <c r="L72" s="26"/>
-      <c r="M72" s="26"/>
-      <c r="N72" s="26"/>
-      <c r="O72" s="26"/>
-      <c r="P72" s="26"/>
-      <c r="Q72" s="26"/>
-      <c r="R72" s="26"/>
-      <c r="S72" s="26"/>
-      <c r="T72" s="26"/>
-      <c r="U72" s="26"/>
-      <c r="V72" s="26"/>
-      <c r="W72" s="26"/>
-      <c r="X72" s="26"/>
-      <c r="Y72" s="26"/>
+      <c r="F72" s="22"/>
+      <c r="G72" s="22"/>
+      <c r="H72" s="22"/>
+      <c r="I72" s="22"/>
+      <c r="J72" s="22"/>
+      <c r="K72" s="22"/>
+      <c r="L72" s="22"/>
+      <c r="M72" s="22"/>
+      <c r="N72" s="22"/>
+      <c r="O72" s="22"/>
+      <c r="P72" s="22"/>
+      <c r="Q72" s="22"/>
+      <c r="R72" s="22"/>
+      <c r="S72" s="22"/>
+      <c r="T72" s="22"/>
+      <c r="U72" s="22"/>
+      <c r="V72" s="22"/>
+      <c r="W72" s="22"/>
+      <c r="X72" s="22"/>
+      <c r="Y72" s="22"/>
+      <c r="Z72" s="23"/>
     </row>
     <row r="73" ht="15.0" customHeight="1">
-      <c r="A73" s="25" t="s">
+      <c r="A73" s="21" t="s">
         <v>283</v>
       </c>
-      <c r="B73" s="26">
+      <c r="B73" s="22">
         <v>0.0</v>
       </c>
-      <c r="C73" s="26" t="s">
+      <c r="C73" s="22" t="s">
         <v>284</v>
       </c>
-      <c r="D73" s="26" t="s">
+      <c r="D73" s="22" t="s">
         <v>285</v>
       </c>
-      <c r="E73" s="26" t="s">
+      <c r="E73" s="22" t="s">
         <v>286</v>
       </c>
-      <c r="F73" s="26"/>
-      <c r="G73" s="26"/>
-      <c r="H73" s="26"/>
-      <c r="I73" s="26"/>
-      <c r="J73" s="26"/>
-      <c r="K73" s="26"/>
-      <c r="L73" s="26"/>
-      <c r="M73" s="26"/>
-      <c r="N73" s="26"/>
-      <c r="O73" s="26"/>
-      <c r="P73" s="26"/>
-      <c r="Q73" s="26"/>
-      <c r="R73" s="26"/>
-      <c r="S73" s="26"/>
-      <c r="T73" s="26"/>
-      <c r="U73" s="26"/>
-      <c r="V73" s="26"/>
-      <c r="W73" s="26"/>
-      <c r="X73" s="26"/>
-      <c r="Y73" s="26"/>
+      <c r="F73" s="22"/>
+      <c r="G73" s="22"/>
+      <c r="H73" s="22"/>
+      <c r="I73" s="22"/>
+      <c r="J73" s="22"/>
+      <c r="K73" s="22"/>
+      <c r="L73" s="22"/>
+      <c r="M73" s="22"/>
+      <c r="N73" s="22"/>
+      <c r="O73" s="22"/>
+      <c r="P73" s="22"/>
+      <c r="Q73" s="22"/>
+      <c r="R73" s="22"/>
+      <c r="S73" s="22"/>
+      <c r="T73" s="22"/>
+      <c r="U73" s="22"/>
+      <c r="V73" s="22"/>
+      <c r="W73" s="22"/>
+      <c r="X73" s="22"/>
+      <c r="Y73" s="22"/>
+      <c r="Z73" s="23"/>
     </row>
     <row r="74" ht="15.0" customHeight="1">
-      <c r="A74" s="25" t="s">
+      <c r="A74" s="21" t="s">
         <v>287</v>
       </c>
-      <c r="B74" s="26">
+      <c r="B74" s="22">
         <v>0.0</v>
       </c>
-      <c r="C74" s="26" t="s">
+      <c r="C74" s="22" t="s">
         <v>288</v>
       </c>
-      <c r="D74" s="26" t="s">
+      <c r="D74" s="22" t="s">
         <v>289</v>
       </c>
-      <c r="E74" s="26" t="s">
+      <c r="E74" s="22" t="s">
         <v>290</v>
       </c>
-      <c r="F74" s="26"/>
-      <c r="G74" s="26"/>
-      <c r="H74" s="26"/>
-      <c r="I74" s="26"/>
-      <c r="J74" s="26"/>
-      <c r="K74" s="26"/>
-      <c r="L74" s="26"/>
-      <c r="M74" s="26"/>
-      <c r="N74" s="26"/>
-      <c r="O74" s="26"/>
-      <c r="P74" s="26"/>
-      <c r="Q74" s="26"/>
-      <c r="R74" s="26"/>
-      <c r="S74" s="26"/>
-      <c r="T74" s="26"/>
-      <c r="U74" s="26"/>
-      <c r="V74" s="26"/>
-      <c r="W74" s="26"/>
-      <c r="X74" s="26"/>
-      <c r="Y74" s="26"/>
+      <c r="F74" s="22"/>
+      <c r="G74" s="22"/>
+      <c r="H74" s="22"/>
+      <c r="I74" s="22"/>
+      <c r="J74" s="22"/>
+      <c r="K74" s="22"/>
+      <c r="L74" s="22"/>
+      <c r="M74" s="22"/>
+      <c r="N74" s="22"/>
+      <c r="O74" s="22"/>
+      <c r="P74" s="22"/>
+      <c r="Q74" s="22"/>
+      <c r="R74" s="22"/>
+      <c r="S74" s="22"/>
+      <c r="T74" s="22"/>
+      <c r="U74" s="22"/>
+      <c r="V74" s="22"/>
+      <c r="W74" s="22"/>
+      <c r="X74" s="22"/>
+      <c r="Y74" s="22"/>
+      <c r="Z74" s="23"/>
     </row>
     <row r="75" ht="15.0" customHeight="1">
-      <c r="A75" s="25" t="s">
+      <c r="A75" s="21" t="s">
         <v>291</v>
       </c>
-      <c r="B75" s="26">
+      <c r="B75" s="22">
         <v>0.0</v>
       </c>
-      <c r="C75" s="26" t="s">
+      <c r="C75" s="22" t="s">
         <v>292</v>
       </c>
-      <c r="D75" s="26" t="s">
+      <c r="D75" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="E75" s="26" t="s">
+      <c r="E75" s="22" t="s">
         <v>294</v>
       </c>
-      <c r="F75" s="26"/>
-      <c r="G75" s="26"/>
-      <c r="H75" s="26"/>
-      <c r="I75" s="26"/>
-      <c r="J75" s="26"/>
-      <c r="K75" s="26"/>
-      <c r="L75" s="26"/>
-      <c r="M75" s="26"/>
-      <c r="N75" s="26"/>
-      <c r="O75" s="26"/>
-      <c r="P75" s="26"/>
-      <c r="Q75" s="26"/>
-      <c r="R75" s="26"/>
-      <c r="S75" s="26"/>
-      <c r="T75" s="26"/>
-      <c r="U75" s="26"/>
-      <c r="V75" s="26"/>
-      <c r="W75" s="26"/>
-      <c r="X75" s="26"/>
-      <c r="Y75" s="26"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="22"/>
+      <c r="K75" s="22"/>
+      <c r="L75" s="22"/>
+      <c r="M75" s="22"/>
+      <c r="N75" s="22"/>
+      <c r="O75" s="22"/>
+      <c r="P75" s="22"/>
+      <c r="Q75" s="22"/>
+      <c r="R75" s="22"/>
+      <c r="S75" s="22"/>
+      <c r="T75" s="22"/>
+      <c r="U75" s="22"/>
+      <c r="V75" s="22"/>
+      <c r="W75" s="22"/>
+      <c r="X75" s="22"/>
+      <c r="Y75" s="22"/>
+      <c r="Z75" s="23"/>
     </row>
     <row r="76" ht="15.0" customHeight="1">
-      <c r="A76" s="27" t="s">
+      <c r="A76" s="24" t="s">
         <v>295</v>
       </c>
-      <c r="B76" s="28">
+      <c r="B76" s="25">
         <v>0.0</v>
       </c>
-      <c r="C76" s="29" t="s">
+      <c r="C76" s="26" t="s">
         <v>296</v>
       </c>
-      <c r="D76" s="29" t="s">
+      <c r="D76" s="26" t="s">
         <v>207</v>
       </c>
-      <c r="E76" s="29" t="s">
+      <c r="E76" s="26" t="s">
         <v>208</v>
       </c>
-      <c r="F76" s="29"/>
-      <c r="G76" s="29"/>
-      <c r="H76" s="29"/>
-      <c r="I76" s="29"/>
-      <c r="J76" s="29"/>
-      <c r="K76" s="29"/>
-      <c r="L76" s="29"/>
-      <c r="M76" s="29"/>
-      <c r="N76" s="29"/>
-      <c r="O76" s="29"/>
-      <c r="P76" s="29"/>
-      <c r="Q76" s="29"/>
-      <c r="R76" s="29"/>
-      <c r="S76" s="29"/>
-      <c r="T76" s="29"/>
-      <c r="U76" s="29"/>
-      <c r="V76" s="29"/>
-      <c r="W76" s="29"/>
-      <c r="X76" s="29"/>
-      <c r="Y76" s="29"/>
+      <c r="F76" s="26"/>
+      <c r="G76" s="26"/>
+      <c r="H76" s="26"/>
+      <c r="I76" s="26"/>
+      <c r="J76" s="26"/>
+      <c r="K76" s="26"/>
+      <c r="L76" s="26"/>
+      <c r="M76" s="26"/>
+      <c r="N76" s="26"/>
+      <c r="O76" s="26"/>
+      <c r="P76" s="26"/>
+      <c r="Q76" s="26"/>
+      <c r="R76" s="26"/>
+      <c r="S76" s="26"/>
+      <c r="T76" s="26"/>
+      <c r="U76" s="26"/>
+      <c r="V76" s="26"/>
+      <c r="W76" s="26"/>
+      <c r="X76" s="26"/>
+      <c r="Y76" s="26"/>
+      <c r="Z76" s="23"/>
     </row>
     <row r="77" ht="15.0" customHeight="1">
-      <c r="A77" s="30" t="s">
+      <c r="A77" s="27" t="s">
         <v>297</v>
       </c>
-      <c r="B77" s="31">
+      <c r="B77" s="25">
         <v>0.0</v>
       </c>
-      <c r="C77" s="32" t="s">
+      <c r="C77" s="26" t="s">
         <v>298</v>
       </c>
-      <c r="D77" s="32" t="s">
+      <c r="D77" s="26" t="s">
         <v>139</v>
       </c>
-      <c r="E77" s="32" t="s">
+      <c r="E77" s="26" t="s">
         <v>140</v>
       </c>
-      <c r="F77" s="32"/>
-      <c r="G77" s="32"/>
-      <c r="H77" s="32"/>
-      <c r="I77" s="32"/>
-      <c r="J77" s="32"/>
-      <c r="K77" s="32"/>
-      <c r="L77" s="32"/>
-      <c r="M77" s="32"/>
-      <c r="N77" s="32"/>
-      <c r="O77" s="32"/>
-      <c r="P77" s="32"/>
-      <c r="Q77" s="32"/>
-      <c r="R77" s="32"/>
-      <c r="S77" s="32"/>
-      <c r="T77" s="32"/>
-      <c r="U77" s="32"/>
-      <c r="V77" s="32"/>
-      <c r="W77" s="32"/>
-      <c r="X77" s="32"/>
-      <c r="Y77" s="32"/>
+      <c r="F77" s="26"/>
+      <c r="G77" s="26"/>
+      <c r="H77" s="26"/>
+      <c r="I77" s="26"/>
+      <c r="J77" s="26"/>
+      <c r="K77" s="26"/>
+      <c r="L77" s="26"/>
+      <c r="M77" s="26"/>
+      <c r="N77" s="26"/>
+      <c r="O77" s="26"/>
+      <c r="P77" s="26"/>
+      <c r="Q77" s="26"/>
+      <c r="R77" s="26"/>
+      <c r="S77" s="26"/>
+      <c r="T77" s="26"/>
+      <c r="U77" s="26"/>
+      <c r="V77" s="26"/>
+      <c r="W77" s="26"/>
+      <c r="X77" s="26"/>
+      <c r="Y77" s="26"/>
+      <c r="Z77" s="23"/>
     </row>
     <row r="78" ht="15.0" customHeight="1">
-      <c r="A78" s="1"/>
-      <c r="B78" s="1"/>
-      <c r="C78" s="1"/>
-      <c r="D78" s="1"/>
-      <c r="E78" s="1"/>
-      <c r="F78" s="1"/>
-      <c r="G78" s="1"/>
-      <c r="H78" s="1"/>
-      <c r="I78" s="1"/>
-      <c r="J78" s="1"/>
-      <c r="K78" s="1"/>
-      <c r="L78" s="1"/>
-      <c r="M78" s="1"/>
-      <c r="N78" s="1"/>
-      <c r="O78" s="1"/>
-      <c r="P78" s="1"/>
-      <c r="Q78" s="1"/>
-      <c r="R78" s="1"/>
-      <c r="S78" s="1"/>
-      <c r="T78" s="1"/>
-      <c r="U78" s="1"/>
-      <c r="V78" s="1"/>
-      <c r="W78" s="1"/>
-      <c r="X78" s="1"/>
-      <c r="Y78" s="1"/>
+      <c r="A78" s="24" t="s">
+        <v>299</v>
+      </c>
+      <c r="B78" s="28">
+        <v>0.0</v>
+      </c>
+      <c r="C78" s="29" t="s">
+        <v>300</v>
+      </c>
+      <c r="D78" s="29" t="s">
+        <v>301</v>
+      </c>
+      <c r="E78" s="29" t="s">
+        <v>302</v>
+      </c>
+      <c r="F78" s="26"/>
+      <c r="G78" s="26"/>
+      <c r="H78" s="26"/>
+      <c r="I78" s="26"/>
+      <c r="J78" s="26"/>
+      <c r="K78" s="26"/>
+      <c r="L78" s="26"/>
+      <c r="M78" s="26"/>
+      <c r="N78" s="26"/>
+      <c r="O78" s="26"/>
+      <c r="P78" s="26"/>
+      <c r="Q78" s="26"/>
+      <c r="R78" s="26"/>
+      <c r="S78" s="26"/>
+      <c r="T78" s="26"/>
+      <c r="U78" s="26"/>
+      <c r="V78" s="26"/>
+      <c r="W78" s="26"/>
+      <c r="X78" s="26"/>
+      <c r="Y78" s="26"/>
+      <c r="Z78" s="23"/>
     </row>
     <row r="79" ht="15.0" customHeight="1">
-      <c r="A79" s="1"/>
-      <c r="B79" s="1"/>
-      <c r="C79" s="1"/>
-      <c r="D79" s="1"/>
-      <c r="E79" s="1"/>
-      <c r="F79" s="1"/>
-      <c r="G79" s="1"/>
-      <c r="H79" s="1"/>
-      <c r="I79" s="1"/>
-      <c r="J79" s="1"/>
-      <c r="K79" s="1"/>
-      <c r="L79" s="1"/>
-      <c r="M79" s="1"/>
-      <c r="N79" s="1"/>
-      <c r="O79" s="1"/>
-      <c r="P79" s="1"/>
-      <c r="Q79" s="1"/>
-      <c r="R79" s="1"/>
-      <c r="S79" s="1"/>
-      <c r="T79" s="1"/>
-      <c r="U79" s="1"/>
-      <c r="V79" s="1"/>
-      <c r="W79" s="1"/>
-      <c r="X79" s="1"/>
-      <c r="Y79" s="1"/>
+      <c r="A79" s="30" t="s">
+        <v>303</v>
+      </c>
+      <c r="B79" s="31">
+        <v>0.0</v>
+      </c>
+      <c r="C79" s="32" t="s">
+        <v>304</v>
+      </c>
+      <c r="D79" s="32" t="s">
+        <v>305</v>
+      </c>
+      <c r="E79" s="32" t="s">
+        <v>306</v>
+      </c>
+      <c r="F79" s="33"/>
+      <c r="G79" s="33"/>
+      <c r="H79" s="33"/>
+      <c r="I79" s="33"/>
+      <c r="J79" s="33"/>
+      <c r="K79" s="33"/>
+      <c r="L79" s="33"/>
+      <c r="M79" s="33"/>
+      <c r="N79" s="33"/>
+      <c r="O79" s="33"/>
+      <c r="P79" s="33"/>
+      <c r="Q79" s="33"/>
+      <c r="R79" s="33"/>
+      <c r="S79" s="33"/>
+      <c r="T79" s="33"/>
+      <c r="U79" s="33"/>
+      <c r="V79" s="33"/>
+      <c r="W79" s="33"/>
+      <c r="X79" s="33"/>
+      <c r="Y79" s="33"/>
+      <c r="Z79" s="34"/>
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="1"/>
@@ -9127,7 +9212,7 @@
       <c r="X261" s="1"/>
       <c r="Y261" s="1"/>
     </row>
-    <row r="262" ht="15.75" customHeight="1">
+    <row r="262" ht="15.0" customHeight="1">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -9154,7 +9239,7 @@
       <c r="X262" s="1"/>
       <c r="Y262" s="1"/>
     </row>
-    <row r="263" ht="15.75" customHeight="1">
+    <row r="263" ht="15.0" customHeight="1">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -9559,8 +9644,60 @@
       <c r="X277" s="1"/>
       <c r="Y277" s="1"/>
     </row>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1">
+      <c r="A278" s="1"/>
+      <c r="B278" s="1"/>
+      <c r="C278" s="1"/>
+      <c r="D278" s="1"/>
+      <c r="E278" s="1"/>
+      <c r="F278" s="1"/>
+      <c r="G278" s="1"/>
+      <c r="H278" s="1"/>
+      <c r="I278" s="1"/>
+      <c r="J278" s="1"/>
+      <c r="K278" s="1"/>
+      <c r="L278" s="1"/>
+      <c r="M278" s="1"/>
+      <c r="N278" s="1"/>
+      <c r="O278" s="1"/>
+      <c r="P278" s="1"/>
+      <c r="Q278" s="1"/>
+      <c r="R278" s="1"/>
+      <c r="S278" s="1"/>
+      <c r="T278" s="1"/>
+      <c r="U278" s="1"/>
+      <c r="V278" s="1"/>
+      <c r="W278" s="1"/>
+      <c r="X278" s="1"/>
+      <c r="Y278" s="1"/>
+    </row>
+    <row r="279" ht="15.75" customHeight="1">
+      <c r="A279" s="1"/>
+      <c r="B279" s="1"/>
+      <c r="C279" s="1"/>
+      <c r="D279" s="1"/>
+      <c r="E279" s="1"/>
+      <c r="F279" s="1"/>
+      <c r="G279" s="1"/>
+      <c r="H279" s="1"/>
+      <c r="I279" s="1"/>
+      <c r="J279" s="1"/>
+      <c r="K279" s="1"/>
+      <c r="L279" s="1"/>
+      <c r="M279" s="1"/>
+      <c r="N279" s="1"/>
+      <c r="O279" s="1"/>
+      <c r="P279" s="1"/>
+      <c r="Q279" s="1"/>
+      <c r="R279" s="1"/>
+      <c r="S279" s="1"/>
+      <c r="T279" s="1"/>
+      <c r="U279" s="1"/>
+      <c r="V279" s="1"/>
+      <c r="W279" s="1"/>
+      <c r="X279" s="1"/>
+      <c r="Y279" s="1"/>
+    </row>
     <row r="280" ht="15.75" customHeight="1"/>
     <row r="281" ht="15.75" customHeight="1"/>
     <row r="282" ht="15.75" customHeight="1"/>
@@ -10282,6 +10419,8 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
+    <row r="1002" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Templates/Tables/StringInfo/StrTable.xlsx
+++ b/Templates/Tables/StringInfo/StrTable.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="319">
   <si>
     <t>Description</t>
   </si>
@@ -754,6 +754,42 @@
     <t>Chapter</t>
   </si>
   <si>
+    <t>공용 초보자 패키지 텍스트</t>
+  </si>
+  <si>
+    <t>COMMON_BEGINNER_PKGS_TEXT</t>
+  </si>
+  <si>
+    <t>초보자 패키지</t>
+  </si>
+  <si>
+    <t>Beginner Pack</t>
+  </si>
+  <si>
+    <t>공용 전문가 패키지 텍스트</t>
+  </si>
+  <si>
+    <t>COMMON_EXPERT_PKGS_TEXT</t>
+  </si>
+  <si>
+    <t>전문가 패키지</t>
+  </si>
+  <si>
+    <t>Expert Pack</t>
+  </si>
+  <si>
+    <t>공용 프로 패키지 텍스트</t>
+  </si>
+  <si>
+    <t>COMMON_PRO_PKGS_TEXT</t>
+  </si>
+  <si>
+    <t>프로 패키지</t>
+  </si>
+  <si>
+    <t>Pro Pack</t>
+  </si>
+  <si>
     <t>공용 레벨 번호 텍스트 형식</t>
   </si>
   <si>
@@ -892,10 +928,10 @@
     <t>SALE_CP_TITLE</t>
   </si>
   <si>
-    <t>판매 코인</t>
-  </si>
-  <si>
-    <t>Sale Coins</t>
+    <t>코인 상자</t>
+  </si>
+  <si>
+    <t>Coins Box</t>
   </si>
   <si>
     <t>이어하기 팝업 제목</t>
@@ -991,7 +1027,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="6">
     <border/>
     <border>
       <left style="thin">
@@ -1024,32 +1060,11 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
-    <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="30">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1093,6 +1108,7 @@
     <xf borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="3" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
@@ -1102,18 +1118,13 @@
     <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="2" fillId="5" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="5" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="3" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+      <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
@@ -1121,28 +1132,15 @@
     <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="3" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="4" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
     <xf borderId="5" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="5" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="5" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -2103,2281 +2101,2352 @@
       <c r="W20" s="14"/>
       <c r="X20" s="14"/>
       <c r="Y20" s="14"/>
+      <c r="Z20" s="15"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="B21" s="16">
+      <c r="B21" s="17">
         <v>0.0</v>
       </c>
-      <c r="C21" s="17" t="s">
+      <c r="C21" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="D21" s="17" t="s">
+      <c r="D21" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="E21" s="17" t="s">
+      <c r="E21" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="17"/>
-      <c r="L21" s="17"/>
-      <c r="M21" s="17"/>
-      <c r="N21" s="17"/>
-      <c r="O21" s="17"/>
-      <c r="P21" s="17"/>
-      <c r="Q21" s="17"/>
-      <c r="R21" s="17"/>
-      <c r="S21" s="17"/>
-      <c r="T21" s="17"/>
-      <c r="U21" s="17"/>
-      <c r="V21" s="17"/>
-      <c r="W21" s="17"/>
-      <c r="X21" s="17"/>
-      <c r="Y21" s="17"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="18"/>
+      <c r="K21" s="18"/>
+      <c r="L21" s="18"/>
+      <c r="M21" s="18"/>
+      <c r="N21" s="18"/>
+      <c r="O21" s="18"/>
+      <c r="P21" s="18"/>
+      <c r="Q21" s="18"/>
+      <c r="R21" s="18"/>
+      <c r="S21" s="18"/>
+      <c r="T21" s="18"/>
+      <c r="U21" s="18"/>
+      <c r="V21" s="18"/>
+      <c r="W21" s="18"/>
+      <c r="X21" s="18"/>
+      <c r="Y21" s="18"/>
+      <c r="Z21" s="15"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="B22" s="16">
+      <c r="B22" s="17">
         <v>0.0</v>
       </c>
-      <c r="C22" s="17" t="s">
+      <c r="C22" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="D22" s="17" t="s">
+      <c r="D22" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="E22" s="17" t="s">
+      <c r="E22" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="17"/>
-      <c r="L22" s="17"/>
-      <c r="M22" s="17"/>
-      <c r="N22" s="17"/>
-      <c r="O22" s="17"/>
-      <c r="P22" s="17"/>
-      <c r="Q22" s="17"/>
-      <c r="R22" s="17"/>
-      <c r="S22" s="17"/>
-      <c r="T22" s="17"/>
-      <c r="U22" s="17"/>
-      <c r="V22" s="17"/>
-      <c r="W22" s="17"/>
-      <c r="X22" s="17"/>
-      <c r="Y22" s="17"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="18"/>
+      <c r="K22" s="18"/>
+      <c r="L22" s="18"/>
+      <c r="M22" s="18"/>
+      <c r="N22" s="18"/>
+      <c r="O22" s="18"/>
+      <c r="P22" s="18"/>
+      <c r="Q22" s="18"/>
+      <c r="R22" s="18"/>
+      <c r="S22" s="18"/>
+      <c r="T22" s="18"/>
+      <c r="U22" s="18"/>
+      <c r="V22" s="18"/>
+      <c r="W22" s="18"/>
+      <c r="X22" s="18"/>
+      <c r="Y22" s="18"/>
+      <c r="Z22" s="15"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="B23" s="16">
+      <c r="B23" s="17">
         <v>0.0</v>
       </c>
-      <c r="C23" s="17" t="s">
+      <c r="C23" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="D23" s="17" t="s">
+      <c r="D23" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="E23" s="17" t="s">
+      <c r="E23" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="17"/>
-      <c r="K23" s="17"/>
-      <c r="L23" s="17"/>
-      <c r="M23" s="17"/>
-      <c r="N23" s="17"/>
-      <c r="O23" s="17"/>
-      <c r="P23" s="17"/>
-      <c r="Q23" s="17"/>
-      <c r="R23" s="17"/>
-      <c r="S23" s="17"/>
-      <c r="T23" s="17"/>
-      <c r="U23" s="17"/>
-      <c r="V23" s="17"/>
-      <c r="W23" s="17"/>
-      <c r="X23" s="17"/>
-      <c r="Y23" s="17"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="18"/>
+      <c r="K23" s="18"/>
+      <c r="L23" s="18"/>
+      <c r="M23" s="18"/>
+      <c r="N23" s="18"/>
+      <c r="O23" s="18"/>
+      <c r="P23" s="18"/>
+      <c r="Q23" s="18"/>
+      <c r="R23" s="18"/>
+      <c r="S23" s="18"/>
+      <c r="T23" s="18"/>
+      <c r="U23" s="18"/>
+      <c r="V23" s="18"/>
+      <c r="W23" s="18"/>
+      <c r="X23" s="18"/>
+      <c r="Y23" s="18"/>
+      <c r="Z23" s="15"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="15" t="s">
+      <c r="A24" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="B24" s="16">
+      <c r="B24" s="17">
         <v>0.0</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="C24" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="D24" s="17" t="s">
+      <c r="D24" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="E24" s="17" t="s">
+      <c r="E24" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="17"/>
-      <c r="L24" s="17"/>
-      <c r="M24" s="17"/>
-      <c r="N24" s="17"/>
-      <c r="O24" s="17"/>
-      <c r="P24" s="17"/>
-      <c r="Q24" s="17"/>
-      <c r="R24" s="17"/>
-      <c r="S24" s="17"/>
-      <c r="T24" s="17"/>
-      <c r="U24" s="17"/>
-      <c r="V24" s="17"/>
-      <c r="W24" s="17"/>
-      <c r="X24" s="17"/>
-      <c r="Y24" s="17"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="18"/>
+      <c r="K24" s="18"/>
+      <c r="L24" s="18"/>
+      <c r="M24" s="18"/>
+      <c r="N24" s="18"/>
+      <c r="O24" s="18"/>
+      <c r="P24" s="18"/>
+      <c r="Q24" s="18"/>
+      <c r="R24" s="18"/>
+      <c r="S24" s="18"/>
+      <c r="T24" s="18"/>
+      <c r="U24" s="18"/>
+      <c r="V24" s="18"/>
+      <c r="W24" s="18"/>
+      <c r="X24" s="18"/>
+      <c r="Y24" s="18"/>
+      <c r="Z24" s="15"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="15" t="s">
+      <c r="A25" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="B25" s="16">
+      <c r="B25" s="17">
         <v>0.0</v>
       </c>
-      <c r="C25" s="17" t="s">
+      <c r="C25" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="D25" s="17" t="s">
+      <c r="D25" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="E25" s="17" t="s">
+      <c r="E25" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="17"/>
-      <c r="L25" s="17"/>
-      <c r="M25" s="17"/>
-      <c r="N25" s="17"/>
-      <c r="O25" s="17"/>
-      <c r="P25" s="17"/>
-      <c r="Q25" s="17"/>
-      <c r="R25" s="17"/>
-      <c r="S25" s="17"/>
-      <c r="T25" s="17"/>
-      <c r="U25" s="17"/>
-      <c r="V25" s="17"/>
-      <c r="W25" s="17"/>
-      <c r="X25" s="17"/>
-      <c r="Y25" s="17"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="18"/>
+      <c r="K25" s="18"/>
+      <c r="L25" s="18"/>
+      <c r="M25" s="18"/>
+      <c r="N25" s="18"/>
+      <c r="O25" s="18"/>
+      <c r="P25" s="18"/>
+      <c r="Q25" s="18"/>
+      <c r="R25" s="18"/>
+      <c r="S25" s="18"/>
+      <c r="T25" s="18"/>
+      <c r="U25" s="18"/>
+      <c r="V25" s="18"/>
+      <c r="W25" s="18"/>
+      <c r="X25" s="18"/>
+      <c r="Y25" s="18"/>
+      <c r="Z25" s="15"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="15" t="s">
+      <c r="A26" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="B26" s="16">
+      <c r="B26" s="17">
         <v>0.0</v>
       </c>
-      <c r="C26" s="17" t="s">
+      <c r="C26" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="D26" s="17" t="s">
+      <c r="D26" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="E26" s="17" t="s">
+      <c r="E26" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="17"/>
-      <c r="I26" s="17"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="17"/>
-      <c r="L26" s="17"/>
-      <c r="M26" s="17"/>
-      <c r="N26" s="17"/>
-      <c r="O26" s="17"/>
-      <c r="P26" s="17"/>
-      <c r="Q26" s="17"/>
-      <c r="R26" s="17"/>
-      <c r="S26" s="17"/>
-      <c r="T26" s="17"/>
-      <c r="U26" s="17"/>
-      <c r="V26" s="17"/>
-      <c r="W26" s="17"/>
-      <c r="X26" s="17"/>
-      <c r="Y26" s="17"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="18"/>
+      <c r="J26" s="18"/>
+      <c r="K26" s="18"/>
+      <c r="L26" s="18"/>
+      <c r="M26" s="18"/>
+      <c r="N26" s="18"/>
+      <c r="O26" s="18"/>
+      <c r="P26" s="18"/>
+      <c r="Q26" s="18"/>
+      <c r="R26" s="18"/>
+      <c r="S26" s="18"/>
+      <c r="T26" s="18"/>
+      <c r="U26" s="18"/>
+      <c r="V26" s="18"/>
+      <c r="W26" s="18"/>
+      <c r="X26" s="18"/>
+      <c r="Y26" s="18"/>
+      <c r="Z26" s="15"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="15" t="s">
+      <c r="A27" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="B27" s="16">
+      <c r="B27" s="17">
         <v>0.0</v>
       </c>
-      <c r="C27" s="17" t="s">
+      <c r="C27" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="D27" s="17" t="s">
+      <c r="D27" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="E27" s="17" t="s">
+      <c r="E27" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="17"/>
-      <c r="I27" s="17"/>
-      <c r="J27" s="17"/>
-      <c r="K27" s="17"/>
-      <c r="L27" s="17"/>
-      <c r="M27" s="17"/>
-      <c r="N27" s="17"/>
-      <c r="O27" s="17"/>
-      <c r="P27" s="17"/>
-      <c r="Q27" s="17"/>
-      <c r="R27" s="17"/>
-      <c r="S27" s="17"/>
-      <c r="T27" s="17"/>
-      <c r="U27" s="17"/>
-      <c r="V27" s="17"/>
-      <c r="W27" s="17"/>
-      <c r="X27" s="17"/>
-      <c r="Y27" s="17"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="18"/>
+      <c r="K27" s="18"/>
+      <c r="L27" s="18"/>
+      <c r="M27" s="18"/>
+      <c r="N27" s="18"/>
+      <c r="O27" s="18"/>
+      <c r="P27" s="18"/>
+      <c r="Q27" s="18"/>
+      <c r="R27" s="18"/>
+      <c r="S27" s="18"/>
+      <c r="T27" s="18"/>
+      <c r="U27" s="18"/>
+      <c r="V27" s="18"/>
+      <c r="W27" s="18"/>
+      <c r="X27" s="18"/>
+      <c r="Y27" s="18"/>
+      <c r="Z27" s="15"/>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="15" t="s">
+      <c r="A28" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="B28" s="16">
+      <c r="B28" s="17">
         <v>0.0</v>
       </c>
-      <c r="C28" s="17" t="s">
+      <c r="C28" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="D28" s="17" t="s">
+      <c r="D28" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="E28" s="17" t="s">
+      <c r="E28" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="17"/>
-      <c r="I28" s="17"/>
-      <c r="J28" s="17"/>
-      <c r="K28" s="17"/>
-      <c r="L28" s="17"/>
-      <c r="M28" s="17"/>
-      <c r="N28" s="17"/>
-      <c r="O28" s="17"/>
-      <c r="P28" s="17"/>
-      <c r="Q28" s="17"/>
-      <c r="R28" s="17"/>
-      <c r="S28" s="17"/>
-      <c r="T28" s="17"/>
-      <c r="U28" s="17"/>
-      <c r="V28" s="17"/>
-      <c r="W28" s="17"/>
-      <c r="X28" s="17"/>
-      <c r="Y28" s="17"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18"/>
+      <c r="J28" s="18"/>
+      <c r="K28" s="18"/>
+      <c r="L28" s="18"/>
+      <c r="M28" s="18"/>
+      <c r="N28" s="18"/>
+      <c r="O28" s="18"/>
+      <c r="P28" s="18"/>
+      <c r="Q28" s="18"/>
+      <c r="R28" s="18"/>
+      <c r="S28" s="18"/>
+      <c r="T28" s="18"/>
+      <c r="U28" s="18"/>
+      <c r="V28" s="18"/>
+      <c r="W28" s="18"/>
+      <c r="X28" s="18"/>
+      <c r="Y28" s="18"/>
+      <c r="Z28" s="15"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="15" t="s">
+      <c r="A29" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="B29" s="16">
+      <c r="B29" s="17">
         <v>0.0</v>
       </c>
-      <c r="C29" s="17" t="s">
+      <c r="C29" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="D29" s="17" t="s">
+      <c r="D29" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="E29" s="17" t="s">
+      <c r="E29" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17"/>
-      <c r="H29" s="17"/>
-      <c r="I29" s="17"/>
-      <c r="J29" s="17"/>
-      <c r="K29" s="17"/>
-      <c r="L29" s="17"/>
-      <c r="M29" s="17"/>
-      <c r="N29" s="17"/>
-      <c r="O29" s="17"/>
-      <c r="P29" s="17"/>
-      <c r="Q29" s="17"/>
-      <c r="R29" s="17"/>
-      <c r="S29" s="17"/>
-      <c r="T29" s="17"/>
-      <c r="U29" s="17"/>
-      <c r="V29" s="17"/>
-      <c r="W29" s="17"/>
-      <c r="X29" s="17"/>
-      <c r="Y29" s="17"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="18"/>
+      <c r="J29" s="18"/>
+      <c r="K29" s="18"/>
+      <c r="L29" s="18"/>
+      <c r="M29" s="18"/>
+      <c r="N29" s="18"/>
+      <c r="O29" s="18"/>
+      <c r="P29" s="18"/>
+      <c r="Q29" s="18"/>
+      <c r="R29" s="18"/>
+      <c r="S29" s="18"/>
+      <c r="T29" s="18"/>
+      <c r="U29" s="18"/>
+      <c r="V29" s="18"/>
+      <c r="W29" s="18"/>
+      <c r="X29" s="18"/>
+      <c r="Y29" s="18"/>
+      <c r="Z29" s="15"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="15" t="s">
+      <c r="A30" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="B30" s="16">
+      <c r="B30" s="17">
         <v>0.0</v>
       </c>
-      <c r="C30" s="17" t="s">
+      <c r="C30" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="D30" s="17" t="s">
+      <c r="D30" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="E30" s="17" t="s">
+      <c r="E30" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="17"/>
-      <c r="I30" s="17"/>
-      <c r="J30" s="17"/>
-      <c r="K30" s="17"/>
-      <c r="L30" s="17"/>
-      <c r="M30" s="17"/>
-      <c r="N30" s="17"/>
-      <c r="O30" s="17"/>
-      <c r="P30" s="17"/>
-      <c r="Q30" s="17"/>
-      <c r="R30" s="17"/>
-      <c r="S30" s="17"/>
-      <c r="T30" s="17"/>
-      <c r="U30" s="17"/>
-      <c r="V30" s="17"/>
-      <c r="W30" s="17"/>
-      <c r="X30" s="17"/>
-      <c r="Y30" s="17"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="18"/>
+      <c r="J30" s="18"/>
+      <c r="K30" s="18"/>
+      <c r="L30" s="18"/>
+      <c r="M30" s="18"/>
+      <c r="N30" s="18"/>
+      <c r="O30" s="18"/>
+      <c r="P30" s="18"/>
+      <c r="Q30" s="18"/>
+      <c r="R30" s="18"/>
+      <c r="S30" s="18"/>
+      <c r="T30" s="18"/>
+      <c r="U30" s="18"/>
+      <c r="V30" s="18"/>
+      <c r="W30" s="18"/>
+      <c r="X30" s="18"/>
+      <c r="Y30" s="18"/>
+      <c r="Z30" s="15"/>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="15" t="s">
+      <c r="A31" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="B31" s="16">
+      <c r="B31" s="17">
         <v>0.0</v>
       </c>
-      <c r="C31" s="17" t="s">
+      <c r="C31" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="D31" s="17" t="s">
+      <c r="D31" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="E31" s="17" t="s">
+      <c r="E31" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="17"/>
-      <c r="I31" s="17"/>
-      <c r="J31" s="17"/>
-      <c r="K31" s="17"/>
-      <c r="L31" s="17"/>
-      <c r="M31" s="17"/>
-      <c r="N31" s="17"/>
-      <c r="O31" s="17"/>
-      <c r="P31" s="17"/>
-      <c r="Q31" s="17"/>
-      <c r="R31" s="17"/>
-      <c r="S31" s="17"/>
-      <c r="T31" s="17"/>
-      <c r="U31" s="17"/>
-      <c r="V31" s="17"/>
-      <c r="W31" s="17"/>
-      <c r="X31" s="17"/>
-      <c r="Y31" s="17"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="18"/>
+      <c r="J31" s="18"/>
+      <c r="K31" s="18"/>
+      <c r="L31" s="18"/>
+      <c r="M31" s="18"/>
+      <c r="N31" s="18"/>
+      <c r="O31" s="18"/>
+      <c r="P31" s="18"/>
+      <c r="Q31" s="18"/>
+      <c r="R31" s="18"/>
+      <c r="S31" s="18"/>
+      <c r="T31" s="18"/>
+      <c r="U31" s="18"/>
+      <c r="V31" s="18"/>
+      <c r="W31" s="18"/>
+      <c r="X31" s="18"/>
+      <c r="Y31" s="18"/>
+      <c r="Z31" s="15"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="15" t="s">
+      <c r="A32" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="B32" s="16">
+      <c r="B32" s="17">
         <v>0.0</v>
       </c>
-      <c r="C32" s="17" t="s">
+      <c r="C32" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="D32" s="17" t="s">
+      <c r="D32" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="E32" s="17" t="s">
+      <c r="E32" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="F32" s="17"/>
-      <c r="G32" s="17"/>
-      <c r="H32" s="17"/>
-      <c r="I32" s="17"/>
-      <c r="J32" s="17"/>
-      <c r="K32" s="17"/>
-      <c r="L32" s="17"/>
-      <c r="M32" s="17"/>
-      <c r="N32" s="17"/>
-      <c r="O32" s="17"/>
-      <c r="P32" s="17"/>
-      <c r="Q32" s="17"/>
-      <c r="R32" s="17"/>
-      <c r="S32" s="17"/>
-      <c r="T32" s="17"/>
-      <c r="U32" s="17"/>
-      <c r="V32" s="17"/>
-      <c r="W32" s="17"/>
-      <c r="X32" s="17"/>
-      <c r="Y32" s="17"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="18"/>
+      <c r="K32" s="18"/>
+      <c r="L32" s="18"/>
+      <c r="M32" s="18"/>
+      <c r="N32" s="18"/>
+      <c r="O32" s="18"/>
+      <c r="P32" s="18"/>
+      <c r="Q32" s="18"/>
+      <c r="R32" s="18"/>
+      <c r="S32" s="18"/>
+      <c r="T32" s="18"/>
+      <c r="U32" s="18"/>
+      <c r="V32" s="18"/>
+      <c r="W32" s="18"/>
+      <c r="X32" s="18"/>
+      <c r="Y32" s="18"/>
+      <c r="Z32" s="15"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="15" t="s">
+      <c r="A33" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="B33" s="16">
+      <c r="B33" s="17">
         <v>0.0</v>
       </c>
-      <c r="C33" s="17" t="s">
+      <c r="C33" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="D33" s="17" t="s">
+      <c r="D33" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="17" t="s">
+      <c r="E33" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="17"/>
-      <c r="I33" s="17"/>
-      <c r="J33" s="17"/>
-      <c r="K33" s="17"/>
-      <c r="L33" s="17"/>
-      <c r="M33" s="17"/>
-      <c r="N33" s="17"/>
-      <c r="O33" s="17"/>
-      <c r="P33" s="17"/>
-      <c r="Q33" s="17"/>
-      <c r="R33" s="17"/>
-      <c r="S33" s="17"/>
-      <c r="T33" s="17"/>
-      <c r="U33" s="17"/>
-      <c r="V33" s="17"/>
-      <c r="W33" s="17"/>
-      <c r="X33" s="17"/>
-      <c r="Y33" s="17"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="18"/>
+      <c r="I33" s="18"/>
+      <c r="J33" s="18"/>
+      <c r="K33" s="18"/>
+      <c r="L33" s="18"/>
+      <c r="M33" s="18"/>
+      <c r="N33" s="18"/>
+      <c r="O33" s="18"/>
+      <c r="P33" s="18"/>
+      <c r="Q33" s="18"/>
+      <c r="R33" s="18"/>
+      <c r="S33" s="18"/>
+      <c r="T33" s="18"/>
+      <c r="U33" s="18"/>
+      <c r="V33" s="18"/>
+      <c r="W33" s="18"/>
+      <c r="X33" s="18"/>
+      <c r="Y33" s="18"/>
+      <c r="Z33" s="15"/>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="15" t="s">
+      <c r="A34" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="B34" s="16">
+      <c r="B34" s="17">
         <v>0.0</v>
       </c>
-      <c r="C34" s="17" t="s">
+      <c r="C34" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="D34" s="17" t="s">
+      <c r="D34" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="E34" s="17" t="s">
+      <c r="E34" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="F34" s="17"/>
-      <c r="G34" s="17"/>
-      <c r="H34" s="17"/>
-      <c r="I34" s="17"/>
-      <c r="J34" s="17"/>
-      <c r="K34" s="17"/>
-      <c r="L34" s="17"/>
-      <c r="M34" s="17"/>
-      <c r="N34" s="17"/>
-      <c r="O34" s="17"/>
-      <c r="P34" s="17"/>
-      <c r="Q34" s="17"/>
-      <c r="R34" s="17"/>
-      <c r="S34" s="17"/>
-      <c r="T34" s="17"/>
-      <c r="U34" s="17"/>
-      <c r="V34" s="17"/>
-      <c r="W34" s="17"/>
-      <c r="X34" s="17"/>
-      <c r="Y34" s="17"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18"/>
+      <c r="I34" s="18"/>
+      <c r="J34" s="18"/>
+      <c r="K34" s="18"/>
+      <c r="L34" s="18"/>
+      <c r="M34" s="18"/>
+      <c r="N34" s="18"/>
+      <c r="O34" s="18"/>
+      <c r="P34" s="18"/>
+      <c r="Q34" s="18"/>
+      <c r="R34" s="18"/>
+      <c r="S34" s="18"/>
+      <c r="T34" s="18"/>
+      <c r="U34" s="18"/>
+      <c r="V34" s="18"/>
+      <c r="W34" s="18"/>
+      <c r="X34" s="18"/>
+      <c r="Y34" s="18"/>
+      <c r="Z34" s="15"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="15" t="s">
+      <c r="A35" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="B35" s="16">
+      <c r="B35" s="17">
         <v>0.0</v>
       </c>
-      <c r="C35" s="17" t="s">
+      <c r="C35" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="D35" s="17" t="s">
+      <c r="D35" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="E35" s="17" t="s">
+      <c r="E35" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="F35" s="17"/>
-      <c r="G35" s="17"/>
-      <c r="H35" s="17"/>
-      <c r="I35" s="17"/>
-      <c r="J35" s="17"/>
-      <c r="K35" s="17"/>
-      <c r="L35" s="17"/>
-      <c r="M35" s="17"/>
-      <c r="N35" s="17"/>
-      <c r="O35" s="17"/>
-      <c r="P35" s="17"/>
-      <c r="Q35" s="17"/>
-      <c r="R35" s="17"/>
-      <c r="S35" s="17"/>
-      <c r="T35" s="17"/>
-      <c r="U35" s="17"/>
-      <c r="V35" s="17"/>
-      <c r="W35" s="17"/>
-      <c r="X35" s="17"/>
-      <c r="Y35" s="17"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="18"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="18"/>
+      <c r="J35" s="18"/>
+      <c r="K35" s="18"/>
+      <c r="L35" s="18"/>
+      <c r="M35" s="18"/>
+      <c r="N35" s="18"/>
+      <c r="O35" s="18"/>
+      <c r="P35" s="18"/>
+      <c r="Q35" s="18"/>
+      <c r="R35" s="18"/>
+      <c r="S35" s="18"/>
+      <c r="T35" s="18"/>
+      <c r="U35" s="18"/>
+      <c r="V35" s="18"/>
+      <c r="W35" s="18"/>
+      <c r="X35" s="18"/>
+      <c r="Y35" s="18"/>
+      <c r="Z35" s="15"/>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="15" t="s">
+      <c r="A36" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="B36" s="16">
+      <c r="B36" s="17">
         <v>0.0</v>
       </c>
-      <c r="C36" s="17" t="s">
+      <c r="C36" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="D36" s="17" t="s">
+      <c r="D36" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="E36" s="17" t="s">
+      <c r="E36" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="F36" s="17"/>
-      <c r="G36" s="17"/>
-      <c r="H36" s="17"/>
-      <c r="I36" s="17"/>
-      <c r="J36" s="17"/>
-      <c r="K36" s="17"/>
-      <c r="L36" s="17"/>
-      <c r="M36" s="17"/>
-      <c r="N36" s="17"/>
-      <c r="O36" s="17"/>
-      <c r="P36" s="17"/>
-      <c r="Q36" s="17"/>
-      <c r="R36" s="17"/>
-      <c r="S36" s="17"/>
-      <c r="T36" s="17"/>
-      <c r="U36" s="17"/>
-      <c r="V36" s="17"/>
-      <c r="W36" s="17"/>
-      <c r="X36" s="17"/>
-      <c r="Y36" s="17"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
+      <c r="H36" s="18"/>
+      <c r="I36" s="18"/>
+      <c r="J36" s="18"/>
+      <c r="K36" s="18"/>
+      <c r="L36" s="18"/>
+      <c r="M36" s="18"/>
+      <c r="N36" s="18"/>
+      <c r="O36" s="18"/>
+      <c r="P36" s="18"/>
+      <c r="Q36" s="18"/>
+      <c r="R36" s="18"/>
+      <c r="S36" s="18"/>
+      <c r="T36" s="18"/>
+      <c r="U36" s="18"/>
+      <c r="V36" s="18"/>
+      <c r="W36" s="18"/>
+      <c r="X36" s="18"/>
+      <c r="Y36" s="18"/>
+      <c r="Z36" s="15"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="15" t="s">
+      <c r="A37" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="B37" s="16">
+      <c r="B37" s="17">
         <v>0.0</v>
       </c>
-      <c r="C37" s="17" t="s">
+      <c r="C37" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="D37" s="17" t="s">
+      <c r="D37" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="E37" s="17" t="s">
+      <c r="E37" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="F37" s="17"/>
-      <c r="G37" s="17"/>
-      <c r="H37" s="17"/>
-      <c r="I37" s="17"/>
-      <c r="J37" s="17"/>
-      <c r="K37" s="17"/>
-      <c r="L37" s="17"/>
-      <c r="M37" s="17"/>
-      <c r="N37" s="17"/>
-      <c r="O37" s="17"/>
-      <c r="P37" s="17"/>
-      <c r="Q37" s="17"/>
-      <c r="R37" s="17"/>
-      <c r="S37" s="17"/>
-      <c r="T37" s="17"/>
-      <c r="U37" s="17"/>
-      <c r="V37" s="17"/>
-      <c r="W37" s="17"/>
-      <c r="X37" s="17"/>
-      <c r="Y37" s="17"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="18"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="18"/>
+      <c r="J37" s="18"/>
+      <c r="K37" s="18"/>
+      <c r="L37" s="18"/>
+      <c r="M37" s="18"/>
+      <c r="N37" s="18"/>
+      <c r="O37" s="18"/>
+      <c r="P37" s="18"/>
+      <c r="Q37" s="18"/>
+      <c r="R37" s="18"/>
+      <c r="S37" s="18"/>
+      <c r="T37" s="18"/>
+      <c r="U37" s="18"/>
+      <c r="V37" s="18"/>
+      <c r="W37" s="18"/>
+      <c r="X37" s="18"/>
+      <c r="Y37" s="18"/>
+      <c r="Z37" s="15"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="15" t="s">
+      <c r="A38" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B38" s="16">
+      <c r="B38" s="17">
         <v>0.0</v>
       </c>
-      <c r="C38" s="17" t="s">
+      <c r="C38" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="D38" s="17" t="s">
+      <c r="D38" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="E38" s="17" t="s">
+      <c r="E38" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="F38" s="17"/>
-      <c r="G38" s="17"/>
-      <c r="H38" s="17"/>
-      <c r="I38" s="17"/>
-      <c r="J38" s="17"/>
-      <c r="K38" s="17"/>
-      <c r="L38" s="17"/>
-      <c r="M38" s="17"/>
-      <c r="N38" s="17"/>
-      <c r="O38" s="17"/>
-      <c r="P38" s="17"/>
-      <c r="Q38" s="17"/>
-      <c r="R38" s="17"/>
-      <c r="S38" s="17"/>
-      <c r="T38" s="17"/>
-      <c r="U38" s="17"/>
-      <c r="V38" s="17"/>
-      <c r="W38" s="17"/>
-      <c r="X38" s="17"/>
-      <c r="Y38" s="17"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="18"/>
+      <c r="J38" s="18"/>
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
+      <c r="M38" s="18"/>
+      <c r="N38" s="18"/>
+      <c r="O38" s="18"/>
+      <c r="P38" s="18"/>
+      <c r="Q38" s="18"/>
+      <c r="R38" s="18"/>
+      <c r="S38" s="18"/>
+      <c r="T38" s="18"/>
+      <c r="U38" s="18"/>
+      <c r="V38" s="18"/>
+      <c r="W38" s="18"/>
+      <c r="X38" s="18"/>
+      <c r="Y38" s="18"/>
+      <c r="Z38" s="15"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="15" t="s">
+      <c r="A39" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="B39" s="16">
+      <c r="B39" s="17">
         <v>0.0</v>
       </c>
-      <c r="C39" s="17" t="s">
+      <c r="C39" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="D39" s="17" t="s">
+      <c r="D39" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="E39" s="17" t="s">
+      <c r="E39" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="F39" s="17"/>
-      <c r="G39" s="17"/>
-      <c r="H39" s="17"/>
-      <c r="I39" s="17"/>
-      <c r="J39" s="17"/>
-      <c r="K39" s="17"/>
-      <c r="L39" s="17"/>
-      <c r="M39" s="17"/>
-      <c r="N39" s="17"/>
-      <c r="O39" s="17"/>
-      <c r="P39" s="17"/>
-      <c r="Q39" s="17"/>
-      <c r="R39" s="17"/>
-      <c r="S39" s="17"/>
-      <c r="T39" s="17"/>
-      <c r="U39" s="17"/>
-      <c r="V39" s="17"/>
-      <c r="W39" s="17"/>
-      <c r="X39" s="17"/>
-      <c r="Y39" s="17"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="18"/>
+      <c r="H39" s="18"/>
+      <c r="I39" s="18"/>
+      <c r="J39" s="18"/>
+      <c r="K39" s="18"/>
+      <c r="L39" s="18"/>
+      <c r="M39" s="18"/>
+      <c r="N39" s="18"/>
+      <c r="O39" s="18"/>
+      <c r="P39" s="18"/>
+      <c r="Q39" s="18"/>
+      <c r="R39" s="18"/>
+      <c r="S39" s="18"/>
+      <c r="T39" s="18"/>
+      <c r="U39" s="18"/>
+      <c r="V39" s="18"/>
+      <c r="W39" s="18"/>
+      <c r="X39" s="18"/>
+      <c r="Y39" s="18"/>
+      <c r="Z39" s="15"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="15" t="s">
+      <c r="A40" s="16" t="s">
         <v>157</v>
       </c>
-      <c r="B40" s="16">
+      <c r="B40" s="17">
         <v>0.0</v>
       </c>
-      <c r="C40" s="17" t="s">
+      <c r="C40" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="D40" s="17" t="s">
+      <c r="D40" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="E40" s="17" t="s">
+      <c r="E40" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="F40" s="17"/>
-      <c r="G40" s="17"/>
-      <c r="H40" s="17"/>
-      <c r="I40" s="17"/>
-      <c r="J40" s="17"/>
-      <c r="K40" s="17"/>
-      <c r="L40" s="17"/>
-      <c r="M40" s="17"/>
-      <c r="N40" s="17"/>
-      <c r="O40" s="17"/>
-      <c r="P40" s="17"/>
-      <c r="Q40" s="17"/>
-      <c r="R40" s="17"/>
-      <c r="S40" s="17"/>
-      <c r="T40" s="17"/>
-      <c r="U40" s="17"/>
-      <c r="V40" s="17"/>
-      <c r="W40" s="17"/>
-      <c r="X40" s="17"/>
-      <c r="Y40" s="17"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
+      <c r="I40" s="18"/>
+      <c r="J40" s="18"/>
+      <c r="K40" s="18"/>
+      <c r="L40" s="18"/>
+      <c r="M40" s="18"/>
+      <c r="N40" s="18"/>
+      <c r="O40" s="18"/>
+      <c r="P40" s="18"/>
+      <c r="Q40" s="18"/>
+      <c r="R40" s="18"/>
+      <c r="S40" s="18"/>
+      <c r="T40" s="18"/>
+      <c r="U40" s="18"/>
+      <c r="V40" s="18"/>
+      <c r="W40" s="18"/>
+      <c r="X40" s="18"/>
+      <c r="Y40" s="18"/>
+      <c r="Z40" s="15"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="15" t="s">
+      <c r="A41" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="B41" s="16">
+      <c r="B41" s="17">
         <v>0.0</v>
       </c>
-      <c r="C41" s="17" t="s">
+      <c r="C41" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="D41" s="17" t="s">
+      <c r="D41" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="E41" s="17" t="s">
+      <c r="E41" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="F41" s="17"/>
-      <c r="G41" s="17"/>
-      <c r="H41" s="17"/>
-      <c r="I41" s="17"/>
-      <c r="J41" s="17"/>
-      <c r="K41" s="17"/>
-      <c r="L41" s="17"/>
-      <c r="M41" s="17"/>
-      <c r="N41" s="17"/>
-      <c r="O41" s="17"/>
-      <c r="P41" s="17"/>
-      <c r="Q41" s="17"/>
-      <c r="R41" s="17"/>
-      <c r="S41" s="17"/>
-      <c r="T41" s="17"/>
-      <c r="U41" s="17"/>
-      <c r="V41" s="17"/>
-      <c r="W41" s="17"/>
-      <c r="X41" s="17"/>
-      <c r="Y41" s="17"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
+      <c r="I41" s="18"/>
+      <c r="J41" s="18"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="18"/>
+      <c r="M41" s="18"/>
+      <c r="N41" s="18"/>
+      <c r="O41" s="18"/>
+      <c r="P41" s="18"/>
+      <c r="Q41" s="18"/>
+      <c r="R41" s="18"/>
+      <c r="S41" s="18"/>
+      <c r="T41" s="18"/>
+      <c r="U41" s="18"/>
+      <c r="V41" s="18"/>
+      <c r="W41" s="18"/>
+      <c r="X41" s="18"/>
+      <c r="Y41" s="18"/>
+      <c r="Z41" s="15"/>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="15" t="s">
+      <c r="A42" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="B42" s="16">
+      <c r="B42" s="17">
         <v>0.0</v>
       </c>
-      <c r="C42" s="17" t="s">
+      <c r="C42" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="D42" s="17" t="s">
+      <c r="D42" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="E42" s="17" t="s">
+      <c r="E42" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="F42" s="17"/>
-      <c r="G42" s="17"/>
-      <c r="H42" s="17"/>
-      <c r="I42" s="17"/>
-      <c r="J42" s="17"/>
-      <c r="K42" s="17"/>
-      <c r="L42" s="17"/>
-      <c r="M42" s="17"/>
-      <c r="N42" s="17"/>
-      <c r="O42" s="17"/>
-      <c r="P42" s="17"/>
-      <c r="Q42" s="17"/>
-      <c r="R42" s="17"/>
-      <c r="S42" s="17"/>
-      <c r="T42" s="17"/>
-      <c r="U42" s="17"/>
-      <c r="V42" s="17"/>
-      <c r="W42" s="17"/>
-      <c r="X42" s="17"/>
-      <c r="Y42" s="17"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="18"/>
+      <c r="H42" s="18"/>
+      <c r="I42" s="18"/>
+      <c r="J42" s="18"/>
+      <c r="K42" s="18"/>
+      <c r="L42" s="18"/>
+      <c r="M42" s="18"/>
+      <c r="N42" s="18"/>
+      <c r="O42" s="18"/>
+      <c r="P42" s="18"/>
+      <c r="Q42" s="18"/>
+      <c r="R42" s="18"/>
+      <c r="S42" s="18"/>
+      <c r="T42" s="18"/>
+      <c r="U42" s="18"/>
+      <c r="V42" s="18"/>
+      <c r="W42" s="18"/>
+      <c r="X42" s="18"/>
+      <c r="Y42" s="18"/>
+      <c r="Z42" s="15"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="15" t="s">
+      <c r="A43" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="B43" s="16">
+      <c r="B43" s="17">
         <v>0.0</v>
       </c>
-      <c r="C43" s="17" t="s">
+      <c r="C43" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="D43" s="17" t="s">
+      <c r="D43" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="E43" s="17" t="s">
+      <c r="E43" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="F43" s="17"/>
-      <c r="G43" s="17"/>
-      <c r="H43" s="17"/>
-      <c r="I43" s="17"/>
-      <c r="J43" s="17"/>
-      <c r="K43" s="17"/>
-      <c r="L43" s="17"/>
-      <c r="M43" s="17"/>
-      <c r="N43" s="17"/>
-      <c r="O43" s="17"/>
-      <c r="P43" s="17"/>
-      <c r="Q43" s="17"/>
-      <c r="R43" s="17"/>
-      <c r="S43" s="17"/>
-      <c r="T43" s="17"/>
-      <c r="U43" s="17"/>
-      <c r="V43" s="17"/>
-      <c r="W43" s="17"/>
-      <c r="X43" s="17"/>
-      <c r="Y43" s="17"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="18"/>
+      <c r="H43" s="18"/>
+      <c r="I43" s="18"/>
+      <c r="J43" s="18"/>
+      <c r="K43" s="18"/>
+      <c r="L43" s="18"/>
+      <c r="M43" s="18"/>
+      <c r="N43" s="18"/>
+      <c r="O43" s="18"/>
+      <c r="P43" s="18"/>
+      <c r="Q43" s="18"/>
+      <c r="R43" s="18"/>
+      <c r="S43" s="18"/>
+      <c r="T43" s="18"/>
+      <c r="U43" s="18"/>
+      <c r="V43" s="18"/>
+      <c r="W43" s="18"/>
+      <c r="X43" s="18"/>
+      <c r="Y43" s="18"/>
+      <c r="Z43" s="15"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="15" t="s">
+      <c r="A44" s="16" t="s">
         <v>173</v>
       </c>
-      <c r="B44" s="16">
+      <c r="B44" s="17">
         <v>0.0</v>
       </c>
-      <c r="C44" s="17" t="s">
+      <c r="C44" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="D44" s="17" t="s">
+      <c r="D44" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="E44" s="17" t="s">
+      <c r="E44" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="F44" s="17"/>
-      <c r="G44" s="17"/>
-      <c r="H44" s="17"/>
-      <c r="I44" s="17"/>
-      <c r="J44" s="17"/>
-      <c r="K44" s="17"/>
-      <c r="L44" s="17"/>
-      <c r="M44" s="17"/>
-      <c r="N44" s="17"/>
-      <c r="O44" s="17"/>
-      <c r="P44" s="17"/>
-      <c r="Q44" s="17"/>
-      <c r="R44" s="17"/>
-      <c r="S44" s="17"/>
-      <c r="T44" s="17"/>
-      <c r="U44" s="17"/>
-      <c r="V44" s="17"/>
-      <c r="W44" s="17"/>
-      <c r="X44" s="17"/>
-      <c r="Y44" s="17"/>
+      <c r="F44" s="18"/>
+      <c r="G44" s="18"/>
+      <c r="H44" s="18"/>
+      <c r="I44" s="18"/>
+      <c r="J44" s="18"/>
+      <c r="K44" s="18"/>
+      <c r="L44" s="18"/>
+      <c r="M44" s="18"/>
+      <c r="N44" s="18"/>
+      <c r="O44" s="18"/>
+      <c r="P44" s="18"/>
+      <c r="Q44" s="18"/>
+      <c r="R44" s="18"/>
+      <c r="S44" s="18"/>
+      <c r="T44" s="18"/>
+      <c r="U44" s="18"/>
+      <c r="V44" s="18"/>
+      <c r="W44" s="18"/>
+      <c r="X44" s="18"/>
+      <c r="Y44" s="18"/>
+      <c r="Z44" s="15"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="15" t="s">
+      <c r="A45" s="16" t="s">
         <v>177</v>
       </c>
-      <c r="B45" s="16">
+      <c r="B45" s="17">
         <v>0.0</v>
       </c>
-      <c r="C45" s="17" t="s">
+      <c r="C45" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="D45" s="17" t="s">
+      <c r="D45" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="E45" s="17" t="s">
+      <c r="E45" s="18" t="s">
         <v>180</v>
       </c>
-      <c r="F45" s="17"/>
-      <c r="G45" s="17"/>
-      <c r="H45" s="17"/>
-      <c r="I45" s="17"/>
-      <c r="J45" s="17"/>
-      <c r="K45" s="17"/>
-      <c r="L45" s="17"/>
-      <c r="M45" s="17"/>
-      <c r="N45" s="17"/>
-      <c r="O45" s="17"/>
-      <c r="P45" s="17"/>
-      <c r="Q45" s="17"/>
-      <c r="R45" s="17"/>
-      <c r="S45" s="17"/>
-      <c r="T45" s="17"/>
-      <c r="U45" s="17"/>
-      <c r="V45" s="17"/>
-      <c r="W45" s="17"/>
-      <c r="X45" s="17"/>
-      <c r="Y45" s="17"/>
+      <c r="F45" s="18"/>
+      <c r="G45" s="18"/>
+      <c r="H45" s="18"/>
+      <c r="I45" s="18"/>
+      <c r="J45" s="18"/>
+      <c r="K45" s="18"/>
+      <c r="L45" s="18"/>
+      <c r="M45" s="18"/>
+      <c r="N45" s="18"/>
+      <c r="O45" s="18"/>
+      <c r="P45" s="18"/>
+      <c r="Q45" s="18"/>
+      <c r="R45" s="18"/>
+      <c r="S45" s="18"/>
+      <c r="T45" s="18"/>
+      <c r="U45" s="18"/>
+      <c r="V45" s="18"/>
+      <c r="W45" s="18"/>
+      <c r="X45" s="18"/>
+      <c r="Y45" s="18"/>
+      <c r="Z45" s="15"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="15" t="s">
+      <c r="A46" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="B46" s="16">
+      <c r="B46" s="17">
         <v>0.0</v>
       </c>
-      <c r="C46" s="17" t="s">
+      <c r="C46" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="D46" s="17" t="s">
+      <c r="D46" s="18" t="s">
         <v>183</v>
       </c>
-      <c r="E46" s="17" t="s">
+      <c r="E46" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="F46" s="17"/>
-      <c r="G46" s="17"/>
-      <c r="H46" s="17"/>
-      <c r="I46" s="17"/>
-      <c r="J46" s="17"/>
-      <c r="K46" s="17"/>
-      <c r="L46" s="17"/>
-      <c r="M46" s="17"/>
-      <c r="N46" s="17"/>
-      <c r="O46" s="17"/>
-      <c r="P46" s="17"/>
-      <c r="Q46" s="17"/>
-      <c r="R46" s="17"/>
-      <c r="S46" s="17"/>
-      <c r="T46" s="17"/>
-      <c r="U46" s="17"/>
-      <c r="V46" s="17"/>
-      <c r="W46" s="17"/>
-      <c r="X46" s="17"/>
-      <c r="Y46" s="17"/>
+      <c r="F46" s="18"/>
+      <c r="G46" s="18"/>
+      <c r="H46" s="18"/>
+      <c r="I46" s="18"/>
+      <c r="J46" s="18"/>
+      <c r="K46" s="18"/>
+      <c r="L46" s="18"/>
+      <c r="M46" s="18"/>
+      <c r="N46" s="18"/>
+      <c r="O46" s="18"/>
+      <c r="P46" s="18"/>
+      <c r="Q46" s="18"/>
+      <c r="R46" s="18"/>
+      <c r="S46" s="18"/>
+      <c r="T46" s="18"/>
+      <c r="U46" s="18"/>
+      <c r="V46" s="18"/>
+      <c r="W46" s="18"/>
+      <c r="X46" s="18"/>
+      <c r="Y46" s="18"/>
+      <c r="Z46" s="15"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="15" t="s">
+      <c r="A47" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="B47" s="16">
+      <c r="B47" s="17">
         <v>0.0</v>
       </c>
-      <c r="C47" s="17" t="s">
+      <c r="C47" s="18" t="s">
         <v>186</v>
       </c>
-      <c r="D47" s="17" t="s">
+      <c r="D47" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="E47" s="17" t="s">
+      <c r="E47" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="F47" s="17"/>
-      <c r="G47" s="17"/>
-      <c r="H47" s="17"/>
-      <c r="I47" s="17"/>
-      <c r="J47" s="17"/>
-      <c r="K47" s="17"/>
-      <c r="L47" s="17"/>
-      <c r="M47" s="17"/>
-      <c r="N47" s="17"/>
-      <c r="O47" s="17"/>
-      <c r="P47" s="17"/>
-      <c r="Q47" s="17"/>
-      <c r="R47" s="17"/>
-      <c r="S47" s="17"/>
-      <c r="T47" s="17"/>
-      <c r="U47" s="17"/>
-      <c r="V47" s="17"/>
-      <c r="W47" s="17"/>
-      <c r="X47" s="17"/>
-      <c r="Y47" s="17"/>
+      <c r="F47" s="18"/>
+      <c r="G47" s="18"/>
+      <c r="H47" s="18"/>
+      <c r="I47" s="18"/>
+      <c r="J47" s="18"/>
+      <c r="K47" s="18"/>
+      <c r="L47" s="18"/>
+      <c r="M47" s="18"/>
+      <c r="N47" s="18"/>
+      <c r="O47" s="18"/>
+      <c r="P47" s="18"/>
+      <c r="Q47" s="18"/>
+      <c r="R47" s="18"/>
+      <c r="S47" s="18"/>
+      <c r="T47" s="18"/>
+      <c r="U47" s="18"/>
+      <c r="V47" s="18"/>
+      <c r="W47" s="18"/>
+      <c r="X47" s="18"/>
+      <c r="Y47" s="18"/>
+      <c r="Z47" s="15"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="15" t="s">
+      <c r="A48" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="B48" s="16">
+      <c r="B48" s="17">
         <v>0.0</v>
       </c>
-      <c r="C48" s="17" t="s">
+      <c r="C48" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="D48" s="17" t="s">
+      <c r="D48" s="18" t="s">
         <v>191</v>
       </c>
-      <c r="E48" s="17" t="s">
+      <c r="E48" s="18" t="s">
         <v>192</v>
       </c>
-      <c r="F48" s="17"/>
-      <c r="G48" s="17"/>
-      <c r="H48" s="17"/>
-      <c r="I48" s="17"/>
-      <c r="J48" s="17"/>
-      <c r="K48" s="17"/>
-      <c r="L48" s="17"/>
-      <c r="M48" s="17"/>
-      <c r="N48" s="17"/>
-      <c r="O48" s="17"/>
-      <c r="P48" s="17"/>
-      <c r="Q48" s="17"/>
-      <c r="R48" s="17"/>
-      <c r="S48" s="17"/>
-      <c r="T48" s="17"/>
-      <c r="U48" s="17"/>
-      <c r="V48" s="17"/>
-      <c r="W48" s="17"/>
-      <c r="X48" s="17"/>
-      <c r="Y48" s="17"/>
+      <c r="F48" s="18"/>
+      <c r="G48" s="18"/>
+      <c r="H48" s="18"/>
+      <c r="I48" s="18"/>
+      <c r="J48" s="18"/>
+      <c r="K48" s="18"/>
+      <c r="L48" s="18"/>
+      <c r="M48" s="18"/>
+      <c r="N48" s="18"/>
+      <c r="O48" s="18"/>
+      <c r="P48" s="18"/>
+      <c r="Q48" s="18"/>
+      <c r="R48" s="18"/>
+      <c r="S48" s="18"/>
+      <c r="T48" s="18"/>
+      <c r="U48" s="18"/>
+      <c r="V48" s="18"/>
+      <c r="W48" s="18"/>
+      <c r="X48" s="18"/>
+      <c r="Y48" s="18"/>
+      <c r="Z48" s="15"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="15" t="s">
+      <c r="A49" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="B49" s="16">
+      <c r="B49" s="17">
         <v>0.0</v>
       </c>
-      <c r="C49" s="17" t="s">
+      <c r="C49" s="18" t="s">
         <v>194</v>
       </c>
-      <c r="D49" s="17" t="s">
+      <c r="D49" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="E49" s="17" t="s">
+      <c r="E49" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="F49" s="17"/>
-      <c r="G49" s="17"/>
-      <c r="H49" s="17"/>
-      <c r="I49" s="17"/>
-      <c r="J49" s="17"/>
-      <c r="K49" s="17"/>
-      <c r="L49" s="17"/>
-      <c r="M49" s="17"/>
-      <c r="N49" s="17"/>
-      <c r="O49" s="17"/>
-      <c r="P49" s="17"/>
-      <c r="Q49" s="17"/>
-      <c r="R49" s="17"/>
-      <c r="S49" s="17"/>
-      <c r="T49" s="17"/>
-      <c r="U49" s="17"/>
-      <c r="V49" s="17"/>
-      <c r="W49" s="17"/>
-      <c r="X49" s="17"/>
-      <c r="Y49" s="17"/>
+      <c r="F49" s="18"/>
+      <c r="G49" s="18"/>
+      <c r="H49" s="18"/>
+      <c r="I49" s="18"/>
+      <c r="J49" s="18"/>
+      <c r="K49" s="18"/>
+      <c r="L49" s="18"/>
+      <c r="M49" s="18"/>
+      <c r="N49" s="18"/>
+      <c r="O49" s="18"/>
+      <c r="P49" s="18"/>
+      <c r="Q49" s="18"/>
+      <c r="R49" s="18"/>
+      <c r="S49" s="18"/>
+      <c r="T49" s="18"/>
+      <c r="U49" s="18"/>
+      <c r="V49" s="18"/>
+      <c r="W49" s="18"/>
+      <c r="X49" s="18"/>
+      <c r="Y49" s="18"/>
+      <c r="Z49" s="15"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="15" t="s">
+      <c r="A50" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="B50" s="16">
+      <c r="B50" s="17">
         <v>0.0</v>
       </c>
-      <c r="C50" s="17" t="s">
+      <c r="C50" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="D50" s="17" t="s">
+      <c r="D50" s="18" t="s">
         <v>199</v>
       </c>
-      <c r="E50" s="17" t="s">
+      <c r="E50" s="18" t="s">
         <v>200</v>
       </c>
-      <c r="F50" s="17"/>
-      <c r="G50" s="17"/>
-      <c r="H50" s="17"/>
-      <c r="I50" s="17"/>
-      <c r="J50" s="17"/>
-      <c r="K50" s="17"/>
-      <c r="L50" s="17"/>
-      <c r="M50" s="17"/>
-      <c r="N50" s="17"/>
-      <c r="O50" s="17"/>
-      <c r="P50" s="17"/>
-      <c r="Q50" s="17"/>
-      <c r="R50" s="17"/>
-      <c r="S50" s="17"/>
-      <c r="T50" s="17"/>
-      <c r="U50" s="17"/>
-      <c r="V50" s="17"/>
-      <c r="W50" s="17"/>
-      <c r="X50" s="17"/>
-      <c r="Y50" s="17"/>
+      <c r="F50" s="18"/>
+      <c r="G50" s="18"/>
+      <c r="H50" s="18"/>
+      <c r="I50" s="18"/>
+      <c r="J50" s="18"/>
+      <c r="K50" s="18"/>
+      <c r="L50" s="18"/>
+      <c r="M50" s="18"/>
+      <c r="N50" s="18"/>
+      <c r="O50" s="18"/>
+      <c r="P50" s="18"/>
+      <c r="Q50" s="18"/>
+      <c r="R50" s="18"/>
+      <c r="S50" s="18"/>
+      <c r="T50" s="18"/>
+      <c r="U50" s="18"/>
+      <c r="V50" s="18"/>
+      <c r="W50" s="18"/>
+      <c r="X50" s="18"/>
+      <c r="Y50" s="18"/>
+      <c r="Z50" s="15"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="15" t="s">
+      <c r="A51" s="16" t="s">
         <v>201</v>
       </c>
-      <c r="B51" s="16">
+      <c r="B51" s="17">
         <v>0.0</v>
       </c>
-      <c r="C51" s="17" t="s">
+      <c r="C51" s="18" t="s">
         <v>202</v>
       </c>
-      <c r="D51" s="17" t="s">
+      <c r="D51" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="E51" s="17" t="s">
+      <c r="E51" s="18" t="s">
         <v>204</v>
       </c>
-      <c r="F51" s="17"/>
-      <c r="G51" s="17"/>
-      <c r="H51" s="17"/>
-      <c r="I51" s="17"/>
-      <c r="J51" s="17"/>
-      <c r="K51" s="17"/>
-      <c r="L51" s="17"/>
-      <c r="M51" s="17"/>
-      <c r="N51" s="17"/>
-      <c r="O51" s="17"/>
-      <c r="P51" s="17"/>
-      <c r="Q51" s="17"/>
-      <c r="R51" s="17"/>
-      <c r="S51" s="17"/>
-      <c r="T51" s="17"/>
-      <c r="U51" s="17"/>
-      <c r="V51" s="17"/>
-      <c r="W51" s="17"/>
-      <c r="X51" s="17"/>
-      <c r="Y51" s="17"/>
+      <c r="F51" s="18"/>
+      <c r="G51" s="18"/>
+      <c r="H51" s="18"/>
+      <c r="I51" s="18"/>
+      <c r="J51" s="18"/>
+      <c r="K51" s="18"/>
+      <c r="L51" s="18"/>
+      <c r="M51" s="18"/>
+      <c r="N51" s="18"/>
+      <c r="O51" s="18"/>
+      <c r="P51" s="18"/>
+      <c r="Q51" s="18"/>
+      <c r="R51" s="18"/>
+      <c r="S51" s="18"/>
+      <c r="T51" s="18"/>
+      <c r="U51" s="18"/>
+      <c r="V51" s="18"/>
+      <c r="W51" s="18"/>
+      <c r="X51" s="18"/>
+      <c r="Y51" s="18"/>
+      <c r="Z51" s="15"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="15" t="s">
+      <c r="A52" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="B52" s="16">
+      <c r="B52" s="17">
         <v>0.0</v>
       </c>
-      <c r="C52" s="17" t="s">
+      <c r="C52" s="18" t="s">
         <v>206</v>
       </c>
-      <c r="D52" s="17" t="s">
+      <c r="D52" s="18" t="s">
         <v>207</v>
       </c>
-      <c r="E52" s="17" t="s">
+      <c r="E52" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="F52" s="17"/>
-      <c r="G52" s="17"/>
-      <c r="H52" s="17"/>
-      <c r="I52" s="17"/>
-      <c r="J52" s="17"/>
-      <c r="K52" s="17"/>
-      <c r="L52" s="17"/>
-      <c r="M52" s="17"/>
-      <c r="N52" s="17"/>
-      <c r="O52" s="17"/>
-      <c r="P52" s="17"/>
-      <c r="Q52" s="17"/>
-      <c r="R52" s="17"/>
-      <c r="S52" s="17"/>
-      <c r="T52" s="17"/>
-      <c r="U52" s="17"/>
-      <c r="V52" s="17"/>
-      <c r="W52" s="17"/>
-      <c r="X52" s="17"/>
-      <c r="Y52" s="17"/>
+      <c r="F52" s="18"/>
+      <c r="G52" s="18"/>
+      <c r="H52" s="18"/>
+      <c r="I52" s="18"/>
+      <c r="J52" s="18"/>
+      <c r="K52" s="18"/>
+      <c r="L52" s="18"/>
+      <c r="M52" s="18"/>
+      <c r="N52" s="18"/>
+      <c r="O52" s="18"/>
+      <c r="P52" s="18"/>
+      <c r="Q52" s="18"/>
+      <c r="R52" s="18"/>
+      <c r="S52" s="18"/>
+      <c r="T52" s="18"/>
+      <c r="U52" s="18"/>
+      <c r="V52" s="18"/>
+      <c r="W52" s="18"/>
+      <c r="X52" s="18"/>
+      <c r="Y52" s="18"/>
+      <c r="Z52" s="15"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="15" t="s">
+      <c r="A53" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="B53" s="16">
+      <c r="B53" s="17">
         <v>0.0</v>
       </c>
-      <c r="C53" s="17" t="s">
+      <c r="C53" s="18" t="s">
         <v>210</v>
       </c>
-      <c r="D53" s="17" t="s">
+      <c r="D53" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="E53" s="17" t="s">
+      <c r="E53" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="F53" s="17"/>
-      <c r="G53" s="17"/>
-      <c r="H53" s="17"/>
-      <c r="I53" s="17"/>
-      <c r="J53" s="17"/>
-      <c r="K53" s="17"/>
-      <c r="L53" s="17"/>
-      <c r="M53" s="17"/>
-      <c r="N53" s="17"/>
-      <c r="O53" s="17"/>
-      <c r="P53" s="17"/>
-      <c r="Q53" s="17"/>
-      <c r="R53" s="17"/>
-      <c r="S53" s="17"/>
-      <c r="T53" s="17"/>
-      <c r="U53" s="17"/>
-      <c r="V53" s="17"/>
-      <c r="W53" s="17"/>
-      <c r="X53" s="17"/>
-      <c r="Y53" s="17"/>
+      <c r="F53" s="18"/>
+      <c r="G53" s="18"/>
+      <c r="H53" s="18"/>
+      <c r="I53" s="18"/>
+      <c r="J53" s="18"/>
+      <c r="K53" s="18"/>
+      <c r="L53" s="18"/>
+      <c r="M53" s="18"/>
+      <c r="N53" s="18"/>
+      <c r="O53" s="18"/>
+      <c r="P53" s="18"/>
+      <c r="Q53" s="18"/>
+      <c r="R53" s="18"/>
+      <c r="S53" s="18"/>
+      <c r="T53" s="18"/>
+      <c r="U53" s="18"/>
+      <c r="V53" s="18"/>
+      <c r="W53" s="18"/>
+      <c r="X53" s="18"/>
+      <c r="Y53" s="18"/>
+      <c r="Z53" s="15"/>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="15" t="s">
+      <c r="A54" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="B54" s="16">
+      <c r="B54" s="17">
         <v>0.0</v>
       </c>
-      <c r="C54" s="17" t="s">
+      <c r="C54" s="18" t="s">
         <v>212</v>
       </c>
-      <c r="D54" s="17" t="s">
+      <c r="D54" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="E54" s="17" t="s">
+      <c r="E54" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="F54" s="17"/>
-      <c r="G54" s="17"/>
-      <c r="H54" s="17"/>
-      <c r="I54" s="17"/>
-      <c r="J54" s="17"/>
-      <c r="K54" s="17"/>
-      <c r="L54" s="17"/>
-      <c r="M54" s="17"/>
-      <c r="N54" s="17"/>
-      <c r="O54" s="17"/>
-      <c r="P54" s="17"/>
-      <c r="Q54" s="17"/>
-      <c r="R54" s="17"/>
-      <c r="S54" s="17"/>
-      <c r="T54" s="17"/>
-      <c r="U54" s="17"/>
-      <c r="V54" s="17"/>
-      <c r="W54" s="17"/>
-      <c r="X54" s="17"/>
-      <c r="Y54" s="17"/>
+      <c r="F54" s="18"/>
+      <c r="G54" s="18"/>
+      <c r="H54" s="18"/>
+      <c r="I54" s="18"/>
+      <c r="J54" s="18"/>
+      <c r="K54" s="18"/>
+      <c r="L54" s="18"/>
+      <c r="M54" s="18"/>
+      <c r="N54" s="18"/>
+      <c r="O54" s="18"/>
+      <c r="P54" s="18"/>
+      <c r="Q54" s="18"/>
+      <c r="R54" s="18"/>
+      <c r="S54" s="18"/>
+      <c r="T54" s="18"/>
+      <c r="U54" s="18"/>
+      <c r="V54" s="18"/>
+      <c r="W54" s="18"/>
+      <c r="X54" s="18"/>
+      <c r="Y54" s="18"/>
+      <c r="Z54" s="15"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="15" t="s">
+      <c r="A55" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="B55" s="16">
+      <c r="B55" s="17">
         <v>0.0</v>
       </c>
-      <c r="C55" s="17" t="s">
+      <c r="C55" s="18" t="s">
         <v>216</v>
       </c>
-      <c r="D55" s="17" t="s">
+      <c r="D55" s="18" t="s">
         <v>217</v>
       </c>
-      <c r="E55" s="17" t="s">
+      <c r="E55" s="18" t="s">
         <v>218</v>
       </c>
-      <c r="F55" s="17"/>
-      <c r="G55" s="17"/>
-      <c r="H55" s="17"/>
-      <c r="I55" s="17"/>
-      <c r="J55" s="17"/>
-      <c r="K55" s="17"/>
-      <c r="L55" s="17"/>
-      <c r="M55" s="17"/>
-      <c r="N55" s="17"/>
-      <c r="O55" s="17"/>
-      <c r="P55" s="17"/>
-      <c r="Q55" s="17"/>
-      <c r="R55" s="17"/>
-      <c r="S55" s="17"/>
-      <c r="T55" s="17"/>
-      <c r="U55" s="17"/>
-      <c r="V55" s="17"/>
-      <c r="W55" s="17"/>
-      <c r="X55" s="17"/>
-      <c r="Y55" s="17"/>
+      <c r="F55" s="18"/>
+      <c r="G55" s="18"/>
+      <c r="H55" s="18"/>
+      <c r="I55" s="18"/>
+      <c r="J55" s="18"/>
+      <c r="K55" s="18"/>
+      <c r="L55" s="18"/>
+      <c r="M55" s="18"/>
+      <c r="N55" s="18"/>
+      <c r="O55" s="18"/>
+      <c r="P55" s="18"/>
+      <c r="Q55" s="18"/>
+      <c r="R55" s="18"/>
+      <c r="S55" s="18"/>
+      <c r="T55" s="18"/>
+      <c r="U55" s="18"/>
+      <c r="V55" s="18"/>
+      <c r="W55" s="18"/>
+      <c r="X55" s="18"/>
+      <c r="Y55" s="18"/>
+      <c r="Z55" s="15"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="15" t="s">
+      <c r="A56" s="16" t="s">
         <v>219</v>
       </c>
-      <c r="B56" s="16">
+      <c r="B56" s="17">
         <v>0.0</v>
       </c>
-      <c r="C56" s="17" t="s">
+      <c r="C56" s="18" t="s">
         <v>220</v>
       </c>
-      <c r="D56" s="17" t="s">
+      <c r="D56" s="18" t="s">
         <v>221</v>
       </c>
-      <c r="E56" s="17" t="s">
+      <c r="E56" s="18" t="s">
         <v>222</v>
       </c>
-      <c r="F56" s="17"/>
-      <c r="G56" s="17"/>
-      <c r="H56" s="17"/>
-      <c r="I56" s="17"/>
-      <c r="J56" s="17"/>
-      <c r="K56" s="17"/>
-      <c r="L56" s="17"/>
-      <c r="M56" s="17"/>
-      <c r="N56" s="17"/>
-      <c r="O56" s="17"/>
-      <c r="P56" s="17"/>
-      <c r="Q56" s="17"/>
-      <c r="R56" s="17"/>
-      <c r="S56" s="17"/>
-      <c r="T56" s="17"/>
-      <c r="U56" s="17"/>
-      <c r="V56" s="17"/>
-      <c r="W56" s="17"/>
-      <c r="X56" s="17"/>
-      <c r="Y56" s="17"/>
+      <c r="F56" s="18"/>
+      <c r="G56" s="18"/>
+      <c r="H56" s="18"/>
+      <c r="I56" s="18"/>
+      <c r="J56" s="18"/>
+      <c r="K56" s="18"/>
+      <c r="L56" s="18"/>
+      <c r="M56" s="18"/>
+      <c r="N56" s="18"/>
+      <c r="O56" s="18"/>
+      <c r="P56" s="18"/>
+      <c r="Q56" s="18"/>
+      <c r="R56" s="18"/>
+      <c r="S56" s="18"/>
+      <c r="T56" s="18"/>
+      <c r="U56" s="18"/>
+      <c r="V56" s="18"/>
+      <c r="W56" s="18"/>
+      <c r="X56" s="18"/>
+      <c r="Y56" s="18"/>
+      <c r="Z56" s="15"/>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="15" t="s">
+      <c r="A57" s="16" t="s">
         <v>223</v>
       </c>
-      <c r="B57" s="16">
+      <c r="B57" s="17">
         <v>0.0</v>
       </c>
-      <c r="C57" s="17" t="s">
+      <c r="C57" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="D57" s="17" t="s">
+      <c r="D57" s="18" t="s">
         <v>225</v>
       </c>
-      <c r="E57" s="17" t="s">
+      <c r="E57" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="F57" s="17"/>
-      <c r="G57" s="17"/>
-      <c r="H57" s="17"/>
-      <c r="I57" s="17"/>
-      <c r="J57" s="17"/>
-      <c r="K57" s="17"/>
-      <c r="L57" s="17"/>
-      <c r="M57" s="17"/>
-      <c r="N57" s="17"/>
-      <c r="O57" s="17"/>
-      <c r="P57" s="17"/>
-      <c r="Q57" s="17"/>
-      <c r="R57" s="17"/>
-      <c r="S57" s="17"/>
-      <c r="T57" s="17"/>
-      <c r="U57" s="17"/>
-      <c r="V57" s="17"/>
-      <c r="W57" s="17"/>
-      <c r="X57" s="17"/>
-      <c r="Y57" s="17"/>
+      <c r="F57" s="18"/>
+      <c r="G57" s="18"/>
+      <c r="H57" s="18"/>
+      <c r="I57" s="18"/>
+      <c r="J57" s="18"/>
+      <c r="K57" s="18"/>
+      <c r="L57" s="18"/>
+      <c r="M57" s="18"/>
+      <c r="N57" s="18"/>
+      <c r="O57" s="18"/>
+      <c r="P57" s="18"/>
+      <c r="Q57" s="18"/>
+      <c r="R57" s="18"/>
+      <c r="S57" s="18"/>
+      <c r="T57" s="18"/>
+      <c r="U57" s="18"/>
+      <c r="V57" s="18"/>
+      <c r="W57" s="18"/>
+      <c r="X57" s="18"/>
+      <c r="Y57" s="18"/>
+      <c r="Z57" s="15"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="15" t="s">
+      <c r="A58" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="B58" s="16">
+      <c r="B58" s="17">
         <v>0.0</v>
       </c>
-      <c r="C58" s="17" t="s">
+      <c r="C58" s="18" t="s">
         <v>228</v>
       </c>
-      <c r="D58" s="17" t="s">
+      <c r="D58" s="18" t="s">
         <v>229</v>
       </c>
-      <c r="E58" s="17" t="s">
+      <c r="E58" s="18" t="s">
         <v>230</v>
       </c>
-      <c r="F58" s="17"/>
-      <c r="G58" s="17"/>
-      <c r="H58" s="17"/>
-      <c r="I58" s="17"/>
-      <c r="J58" s="17"/>
-      <c r="K58" s="17"/>
-      <c r="L58" s="17"/>
-      <c r="M58" s="17"/>
-      <c r="N58" s="17"/>
-      <c r="O58" s="17"/>
-      <c r="P58" s="17"/>
-      <c r="Q58" s="17"/>
-      <c r="R58" s="17"/>
-      <c r="S58" s="17"/>
-      <c r="T58" s="17"/>
-      <c r="U58" s="17"/>
-      <c r="V58" s="17"/>
-      <c r="W58" s="17"/>
-      <c r="X58" s="17"/>
-      <c r="Y58" s="17"/>
+      <c r="F58" s="18"/>
+      <c r="G58" s="18"/>
+      <c r="H58" s="18"/>
+      <c r="I58" s="18"/>
+      <c r="J58" s="18"/>
+      <c r="K58" s="18"/>
+      <c r="L58" s="18"/>
+      <c r="M58" s="18"/>
+      <c r="N58" s="18"/>
+      <c r="O58" s="18"/>
+      <c r="P58" s="18"/>
+      <c r="Q58" s="18"/>
+      <c r="R58" s="18"/>
+      <c r="S58" s="18"/>
+      <c r="T58" s="18"/>
+      <c r="U58" s="18"/>
+      <c r="V58" s="18"/>
+      <c r="W58" s="18"/>
+      <c r="X58" s="18"/>
+      <c r="Y58" s="18"/>
+      <c r="Z58" s="15"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="15" t="s">
+      <c r="A59" s="16" t="s">
         <v>231</v>
       </c>
-      <c r="B59" s="16">
+      <c r="B59" s="17">
         <v>0.0</v>
       </c>
-      <c r="C59" s="17" t="s">
+      <c r="C59" s="18" t="s">
         <v>232</v>
       </c>
-      <c r="D59" s="17" t="s">
+      <c r="D59" s="18" t="s">
         <v>233</v>
       </c>
-      <c r="E59" s="17" t="s">
+      <c r="E59" s="18" t="s">
         <v>234</v>
       </c>
-      <c r="F59" s="17"/>
-      <c r="G59" s="17"/>
-      <c r="H59" s="17"/>
-      <c r="I59" s="17"/>
-      <c r="J59" s="17"/>
-      <c r="K59" s="17"/>
-      <c r="L59" s="17"/>
-      <c r="M59" s="17"/>
-      <c r="N59" s="17"/>
-      <c r="O59" s="17"/>
-      <c r="P59" s="17"/>
-      <c r="Q59" s="17"/>
-      <c r="R59" s="17"/>
-      <c r="S59" s="17"/>
-      <c r="T59" s="17"/>
-      <c r="U59" s="17"/>
-      <c r="V59" s="17"/>
-      <c r="W59" s="17"/>
-      <c r="X59" s="17"/>
-      <c r="Y59" s="17"/>
+      <c r="F59" s="18"/>
+      <c r="G59" s="18"/>
+      <c r="H59" s="18"/>
+      <c r="I59" s="18"/>
+      <c r="J59" s="18"/>
+      <c r="K59" s="18"/>
+      <c r="L59" s="18"/>
+      <c r="M59" s="18"/>
+      <c r="N59" s="18"/>
+      <c r="O59" s="18"/>
+      <c r="P59" s="18"/>
+      <c r="Q59" s="18"/>
+      <c r="R59" s="18"/>
+      <c r="S59" s="18"/>
+      <c r="T59" s="18"/>
+      <c r="U59" s="18"/>
+      <c r="V59" s="18"/>
+      <c r="W59" s="18"/>
+      <c r="X59" s="18"/>
+      <c r="Y59" s="18"/>
+      <c r="Z59" s="15"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="15" t="s">
+      <c r="A60" s="16" t="s">
         <v>235</v>
       </c>
-      <c r="B60" s="16">
+      <c r="B60" s="17">
         <v>0.0</v>
       </c>
-      <c r="C60" s="17" t="s">
+      <c r="C60" s="18" t="s">
         <v>236</v>
       </c>
-      <c r="D60" s="17" t="s">
+      <c r="D60" s="18" t="s">
         <v>237</v>
       </c>
-      <c r="E60" s="17" t="s">
+      <c r="E60" s="18" t="s">
         <v>238</v>
       </c>
-      <c r="F60" s="17"/>
-      <c r="G60" s="17"/>
-      <c r="H60" s="17"/>
-      <c r="I60" s="17"/>
-      <c r="J60" s="17"/>
-      <c r="K60" s="17"/>
-      <c r="L60" s="17"/>
-      <c r="M60" s="17"/>
-      <c r="N60" s="17"/>
-      <c r="O60" s="17"/>
-      <c r="P60" s="17"/>
-      <c r="Q60" s="17"/>
-      <c r="R60" s="17"/>
-      <c r="S60" s="17"/>
-      <c r="T60" s="17"/>
-      <c r="U60" s="17"/>
-      <c r="V60" s="17"/>
-      <c r="W60" s="17"/>
-      <c r="X60" s="17"/>
-      <c r="Y60" s="17"/>
+      <c r="F60" s="18"/>
+      <c r="G60" s="18"/>
+      <c r="H60" s="18"/>
+      <c r="I60" s="18"/>
+      <c r="J60" s="18"/>
+      <c r="K60" s="18"/>
+      <c r="L60" s="18"/>
+      <c r="M60" s="18"/>
+      <c r="N60" s="18"/>
+      <c r="O60" s="18"/>
+      <c r="P60" s="18"/>
+      <c r="Q60" s="18"/>
+      <c r="R60" s="18"/>
+      <c r="S60" s="18"/>
+      <c r="T60" s="18"/>
+      <c r="U60" s="18"/>
+      <c r="V60" s="18"/>
+      <c r="W60" s="18"/>
+      <c r="X60" s="18"/>
+      <c r="Y60" s="18"/>
+      <c r="Z60" s="15"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="15" t="s">
+      <c r="A61" s="16" t="s">
         <v>239</v>
       </c>
-      <c r="B61" s="16">
+      <c r="B61" s="17">
         <v>0.0</v>
       </c>
-      <c r="C61" s="17" t="s">
+      <c r="C61" s="18" t="s">
         <v>240</v>
       </c>
-      <c r="D61" s="17" t="s">
+      <c r="D61" s="18" t="s">
         <v>241</v>
       </c>
-      <c r="E61" s="17" t="s">
+      <c r="E61" s="18" t="s">
         <v>242</v>
       </c>
-      <c r="F61" s="17"/>
-      <c r="G61" s="17"/>
-      <c r="H61" s="17"/>
-      <c r="I61" s="17"/>
-      <c r="J61" s="17"/>
-      <c r="K61" s="17"/>
-      <c r="L61" s="17"/>
-      <c r="M61" s="17"/>
-      <c r="N61" s="17"/>
-      <c r="O61" s="17"/>
-      <c r="P61" s="17"/>
-      <c r="Q61" s="17"/>
-      <c r="R61" s="17"/>
-      <c r="S61" s="17"/>
-      <c r="T61" s="17"/>
-      <c r="U61" s="17"/>
-      <c r="V61" s="17"/>
-      <c r="W61" s="17"/>
-      <c r="X61" s="17"/>
-      <c r="Y61" s="17"/>
+      <c r="F61" s="18"/>
+      <c r="G61" s="18"/>
+      <c r="H61" s="18"/>
+      <c r="I61" s="18"/>
+      <c r="J61" s="18"/>
+      <c r="K61" s="18"/>
+      <c r="L61" s="18"/>
+      <c r="M61" s="18"/>
+      <c r="N61" s="18"/>
+      <c r="O61" s="18"/>
+      <c r="P61" s="18"/>
+      <c r="Q61" s="18"/>
+      <c r="R61" s="18"/>
+      <c r="S61" s="18"/>
+      <c r="T61" s="18"/>
+      <c r="U61" s="18"/>
+      <c r="V61" s="18"/>
+      <c r="W61" s="18"/>
+      <c r="X61" s="18"/>
+      <c r="Y61" s="18"/>
+      <c r="Z61" s="15"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="15" t="s">
+      <c r="A62" s="16" t="s">
         <v>243</v>
       </c>
-      <c r="B62" s="16">
+      <c r="B62" s="17">
         <v>0.0</v>
       </c>
-      <c r="C62" s="17" t="s">
+      <c r="C62" s="18" t="s">
         <v>244</v>
       </c>
-      <c r="D62" s="17" t="s">
+      <c r="D62" s="18" t="s">
         <v>245</v>
       </c>
-      <c r="E62" s="17" t="s">
+      <c r="E62" s="18" t="s">
         <v>246</v>
       </c>
-      <c r="F62" s="17"/>
-      <c r="G62" s="17"/>
-      <c r="H62" s="17"/>
-      <c r="I62" s="17"/>
-      <c r="J62" s="17"/>
-      <c r="K62" s="17"/>
-      <c r="L62" s="17"/>
-      <c r="M62" s="17"/>
-      <c r="N62" s="17"/>
-      <c r="O62" s="17"/>
-      <c r="P62" s="17"/>
-      <c r="Q62" s="17"/>
-      <c r="R62" s="17"/>
-      <c r="S62" s="17"/>
-      <c r="T62" s="17"/>
-      <c r="U62" s="17"/>
-      <c r="V62" s="17"/>
-      <c r="W62" s="17"/>
-      <c r="X62" s="17"/>
-      <c r="Y62" s="17"/>
+      <c r="F62" s="18"/>
+      <c r="G62" s="18"/>
+      <c r="H62" s="18"/>
+      <c r="I62" s="18"/>
+      <c r="J62" s="18"/>
+      <c r="K62" s="18"/>
+      <c r="L62" s="18"/>
+      <c r="M62" s="18"/>
+      <c r="N62" s="18"/>
+      <c r="O62" s="18"/>
+      <c r="P62" s="18"/>
+      <c r="Q62" s="18"/>
+      <c r="R62" s="18"/>
+      <c r="S62" s="18"/>
+      <c r="T62" s="18"/>
+      <c r="U62" s="18"/>
+      <c r="V62" s="18"/>
+      <c r="W62" s="18"/>
+      <c r="X62" s="18"/>
+      <c r="Y62" s="18"/>
+      <c r="Z62" s="15"/>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="15" t="s">
+      <c r="A63" s="19" t="s">
         <v>247</v>
       </c>
-      <c r="B63" s="16">
+      <c r="B63" s="19">
         <v>0.0</v>
       </c>
-      <c r="C63" s="17" t="s">
+      <c r="C63" s="19" t="s">
         <v>248</v>
       </c>
-      <c r="D63" s="17" t="s">
+      <c r="D63" s="19" t="s">
         <v>249</v>
       </c>
-      <c r="E63" s="17" t="s">
+      <c r="E63" s="19" t="s">
         <v>250</v>
       </c>
-      <c r="F63" s="17"/>
-      <c r="G63" s="17"/>
-      <c r="H63" s="17"/>
-      <c r="I63" s="17"/>
-      <c r="J63" s="17"/>
-      <c r="K63" s="17"/>
-      <c r="L63" s="17"/>
-      <c r="M63" s="17"/>
-      <c r="N63" s="17"/>
-      <c r="O63" s="17"/>
-      <c r="P63" s="17"/>
-      <c r="Q63" s="17"/>
-      <c r="R63" s="17"/>
-      <c r="S63" s="17"/>
-      <c r="T63" s="17"/>
-      <c r="U63" s="17"/>
-      <c r="V63" s="17"/>
-      <c r="W63" s="17"/>
-      <c r="X63" s="17"/>
-      <c r="Y63" s="17"/>
+      <c r="F63" s="19"/>
+      <c r="G63" s="19"/>
+      <c r="H63" s="19"/>
+      <c r="I63" s="19"/>
+      <c r="J63" s="19"/>
+      <c r="K63" s="19"/>
+      <c r="L63" s="19"/>
+      <c r="M63" s="19"/>
+      <c r="N63" s="19"/>
+      <c r="O63" s="19"/>
+      <c r="P63" s="19"/>
+      <c r="Q63" s="19"/>
+      <c r="R63" s="19"/>
+      <c r="S63" s="19"/>
+      <c r="T63" s="19"/>
+      <c r="U63" s="19"/>
+      <c r="V63" s="19"/>
+      <c r="W63" s="19"/>
+      <c r="X63" s="19"/>
+      <c r="Y63" s="19"/>
+      <c r="Z63" s="15"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="15" t="s">
+      <c r="A64" s="19" t="s">
         <v>251</v>
       </c>
-      <c r="B64" s="16">
+      <c r="B64" s="19">
         <v>0.0</v>
       </c>
-      <c r="C64" s="17" t="s">
+      <c r="C64" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D64" s="17" t="s">
+      <c r="D64" s="19" t="s">
         <v>253</v>
       </c>
-      <c r="E64" s="17" t="s">
+      <c r="E64" s="19" t="s">
         <v>254</v>
       </c>
-      <c r="F64" s="17"/>
-      <c r="G64" s="17"/>
-      <c r="H64" s="17"/>
-      <c r="I64" s="17"/>
-      <c r="J64" s="17"/>
-      <c r="K64" s="17"/>
-      <c r="L64" s="17"/>
-      <c r="M64" s="17"/>
-      <c r="N64" s="17"/>
-      <c r="O64" s="17"/>
-      <c r="P64" s="17"/>
-      <c r="Q64" s="17"/>
-      <c r="R64" s="17"/>
-      <c r="S64" s="17"/>
-      <c r="T64" s="17"/>
-      <c r="U64" s="17"/>
-      <c r="V64" s="17"/>
-      <c r="W64" s="17"/>
-      <c r="X64" s="17"/>
-      <c r="Y64" s="17"/>
+      <c r="F64" s="19"/>
+      <c r="G64" s="19"/>
+      <c r="H64" s="19"/>
+      <c r="I64" s="19"/>
+      <c r="J64" s="19"/>
+      <c r="K64" s="19"/>
+      <c r="L64" s="19"/>
+      <c r="M64" s="19"/>
+      <c r="N64" s="19"/>
+      <c r="O64" s="19"/>
+      <c r="P64" s="19"/>
+      <c r="Q64" s="19"/>
+      <c r="R64" s="19"/>
+      <c r="S64" s="19"/>
+      <c r="T64" s="19"/>
+      <c r="U64" s="19"/>
+      <c r="V64" s="19"/>
+      <c r="W64" s="19"/>
+      <c r="X64" s="19"/>
+      <c r="Y64" s="19"/>
+      <c r="Z64" s="15"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="15" t="s">
+      <c r="A65" s="19" t="s">
         <v>255</v>
       </c>
-      <c r="B65" s="16">
+      <c r="B65" s="19">
         <v>0.0</v>
       </c>
-      <c r="C65" s="17" t="s">
+      <c r="C65" s="19" t="s">
         <v>256</v>
       </c>
-      <c r="D65" s="17" t="s">
+      <c r="D65" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="E65" s="17" t="s">
+      <c r="E65" s="19" t="s">
         <v>258</v>
       </c>
-      <c r="F65" s="17"/>
-      <c r="G65" s="17"/>
-      <c r="H65" s="17"/>
-      <c r="I65" s="17"/>
-      <c r="J65" s="17"/>
-      <c r="K65" s="17"/>
-      <c r="L65" s="17"/>
-      <c r="M65" s="17"/>
-      <c r="N65" s="17"/>
-      <c r="O65" s="17"/>
-      <c r="P65" s="17"/>
-      <c r="Q65" s="17"/>
-      <c r="R65" s="17"/>
-      <c r="S65" s="17"/>
-      <c r="T65" s="17"/>
-      <c r="U65" s="17"/>
-      <c r="V65" s="17"/>
-      <c r="W65" s="17"/>
-      <c r="X65" s="17"/>
-      <c r="Y65" s="17"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="19"/>
+      <c r="K65" s="19"/>
+      <c r="L65" s="19"/>
+      <c r="M65" s="19"/>
+      <c r="N65" s="19"/>
+      <c r="O65" s="19"/>
+      <c r="P65" s="19"/>
+      <c r="Q65" s="19"/>
+      <c r="R65" s="19"/>
+      <c r="S65" s="19"/>
+      <c r="T65" s="19"/>
+      <c r="U65" s="19"/>
+      <c r="V65" s="19"/>
+      <c r="W65" s="19"/>
+      <c r="X65" s="19"/>
+      <c r="Y65" s="19"/>
+      <c r="Z65" s="15"/>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="15" t="s">
+      <c r="A66" s="16" t="s">
         <v>259</v>
       </c>
-      <c r="B66" s="16">
+      <c r="B66" s="17">
         <v>0.0</v>
       </c>
-      <c r="C66" s="17" t="s">
+      <c r="C66" s="18" t="s">
         <v>260</v>
       </c>
-      <c r="D66" s="17" t="s">
+      <c r="D66" s="18" t="s">
         <v>261</v>
       </c>
-      <c r="E66" s="17" t="s">
+      <c r="E66" s="18" t="s">
         <v>262</v>
       </c>
-      <c r="F66" s="17"/>
-      <c r="G66" s="17"/>
-      <c r="H66" s="17"/>
-      <c r="I66" s="17"/>
-      <c r="J66" s="17"/>
-      <c r="K66" s="17"/>
-      <c r="L66" s="17"/>
-      <c r="M66" s="17"/>
-      <c r="N66" s="17"/>
-      <c r="O66" s="17"/>
-      <c r="P66" s="17"/>
-      <c r="Q66" s="17"/>
-      <c r="R66" s="17"/>
-      <c r="S66" s="17"/>
-      <c r="T66" s="17"/>
-      <c r="U66" s="17"/>
-      <c r="V66" s="17"/>
-      <c r="W66" s="17"/>
-      <c r="X66" s="17"/>
-      <c r="Y66" s="17"/>
+      <c r="F66" s="18"/>
+      <c r="G66" s="18"/>
+      <c r="H66" s="18"/>
+      <c r="I66" s="18"/>
+      <c r="J66" s="18"/>
+      <c r="K66" s="18"/>
+      <c r="L66" s="18"/>
+      <c r="M66" s="18"/>
+      <c r="N66" s="18"/>
+      <c r="O66" s="18"/>
+      <c r="P66" s="18"/>
+      <c r="Q66" s="18"/>
+      <c r="R66" s="18"/>
+      <c r="S66" s="18"/>
+      <c r="T66" s="18"/>
+      <c r="U66" s="18"/>
+      <c r="V66" s="18"/>
+      <c r="W66" s="18"/>
+      <c r="X66" s="18"/>
+      <c r="Y66" s="18"/>
+      <c r="Z66" s="15"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="15" t="s">
+      <c r="A67" s="16" t="s">
         <v>263</v>
       </c>
-      <c r="B67" s="16">
+      <c r="B67" s="17">
         <v>0.0</v>
       </c>
-      <c r="C67" s="17" t="s">
+      <c r="C67" s="18" t="s">
         <v>264</v>
       </c>
-      <c r="D67" s="17" t="s">
+      <c r="D67" s="18" t="s">
         <v>265</v>
       </c>
-      <c r="E67" s="17" t="s">
+      <c r="E67" s="18" t="s">
         <v>266</v>
       </c>
-      <c r="F67" s="17"/>
-      <c r="G67" s="17"/>
-      <c r="H67" s="17"/>
-      <c r="I67" s="17"/>
-      <c r="J67" s="17"/>
-      <c r="K67" s="17"/>
-      <c r="L67" s="17"/>
-      <c r="M67" s="17"/>
-      <c r="N67" s="17"/>
-      <c r="O67" s="17"/>
-      <c r="P67" s="17"/>
-      <c r="Q67" s="17"/>
-      <c r="R67" s="17"/>
-      <c r="S67" s="17"/>
-      <c r="T67" s="17"/>
-      <c r="U67" s="17"/>
-      <c r="V67" s="17"/>
-      <c r="W67" s="17"/>
-      <c r="X67" s="17"/>
-      <c r="Y67" s="17"/>
+      <c r="F67" s="18"/>
+      <c r="G67" s="18"/>
+      <c r="H67" s="18"/>
+      <c r="I67" s="18"/>
+      <c r="J67" s="18"/>
+      <c r="K67" s="18"/>
+      <c r="L67" s="18"/>
+      <c r="M67" s="18"/>
+      <c r="N67" s="18"/>
+      <c r="O67" s="18"/>
+      <c r="P67" s="18"/>
+      <c r="Q67" s="18"/>
+      <c r="R67" s="18"/>
+      <c r="S67" s="18"/>
+      <c r="T67" s="18"/>
+      <c r="U67" s="18"/>
+      <c r="V67" s="18"/>
+      <c r="W67" s="18"/>
+      <c r="X67" s="18"/>
+      <c r="Y67" s="18"/>
+      <c r="Z67" s="15"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="15" t="s">
+      <c r="A68" s="16" t="s">
         <v>267</v>
       </c>
-      <c r="B68" s="16">
+      <c r="B68" s="17">
         <v>0.0</v>
       </c>
-      <c r="C68" s="17" t="s">
+      <c r="C68" s="18" t="s">
         <v>268</v>
       </c>
-      <c r="D68" s="17" t="s">
+      <c r="D68" s="18" t="s">
         <v>269</v>
       </c>
-      <c r="E68" s="17" t="s">
+      <c r="E68" s="18" t="s">
         <v>270</v>
       </c>
-      <c r="F68" s="17"/>
-      <c r="G68" s="17"/>
-      <c r="H68" s="17"/>
-      <c r="I68" s="17"/>
-      <c r="J68" s="17"/>
-      <c r="K68" s="17"/>
-      <c r="L68" s="17"/>
-      <c r="M68" s="17"/>
-      <c r="N68" s="17"/>
-      <c r="O68" s="17"/>
-      <c r="P68" s="17"/>
-      <c r="Q68" s="17"/>
-      <c r="R68" s="17"/>
-      <c r="S68" s="17"/>
-      <c r="T68" s="17"/>
-      <c r="U68" s="17"/>
-      <c r="V68" s="17"/>
-      <c r="W68" s="17"/>
-      <c r="X68" s="17"/>
-      <c r="Y68" s="17"/>
+      <c r="F68" s="18"/>
+      <c r="G68" s="18"/>
+      <c r="H68" s="18"/>
+      <c r="I68" s="18"/>
+      <c r="J68" s="18"/>
+      <c r="K68" s="18"/>
+      <c r="L68" s="18"/>
+      <c r="M68" s="18"/>
+      <c r="N68" s="18"/>
+      <c r="O68" s="18"/>
+      <c r="P68" s="18"/>
+      <c r="Q68" s="18"/>
+      <c r="R68" s="18"/>
+      <c r="S68" s="18"/>
+      <c r="T68" s="18"/>
+      <c r="U68" s="18"/>
+      <c r="V68" s="18"/>
+      <c r="W68" s="18"/>
+      <c r="X68" s="18"/>
+      <c r="Y68" s="18"/>
+      <c r="Z68" s="15"/>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="18" t="s">
+      <c r="A69" s="16" t="s">
         <v>271</v>
       </c>
-      <c r="B69" s="19">
+      <c r="B69" s="17">
         <v>0.0</v>
       </c>
-      <c r="C69" s="19" t="s">
+      <c r="C69" s="18" t="s">
         <v>272</v>
       </c>
-      <c r="D69" s="19" t="s">
+      <c r="D69" s="18" t="s">
+        <v>273</v>
+      </c>
+      <c r="E69" s="18" t="s">
+        <v>274</v>
+      </c>
+      <c r="F69" s="18"/>
+      <c r="G69" s="18"/>
+      <c r="H69" s="18"/>
+      <c r="I69" s="18"/>
+      <c r="J69" s="18"/>
+      <c r="K69" s="18"/>
+      <c r="L69" s="18"/>
+      <c r="M69" s="18"/>
+      <c r="N69" s="18"/>
+      <c r="O69" s="18"/>
+      <c r="P69" s="18"/>
+      <c r="Q69" s="18"/>
+      <c r="R69" s="18"/>
+      <c r="S69" s="18"/>
+      <c r="T69" s="18"/>
+      <c r="U69" s="18"/>
+      <c r="V69" s="18"/>
+      <c r="W69" s="18"/>
+      <c r="X69" s="18"/>
+      <c r="Y69" s="18"/>
+      <c r="Z69" s="15"/>
+    </row>
+    <row r="70" ht="15.0" customHeight="1">
+      <c r="A70" s="16" t="s">
+        <v>275</v>
+      </c>
+      <c r="B70" s="17">
+        <v>0.0</v>
+      </c>
+      <c r="C70" s="18" t="s">
+        <v>276</v>
+      </c>
+      <c r="D70" s="18" t="s">
+        <v>277</v>
+      </c>
+      <c r="E70" s="18" t="s">
+        <v>278</v>
+      </c>
+      <c r="F70" s="18"/>
+      <c r="G70" s="18"/>
+      <c r="H70" s="18"/>
+      <c r="I70" s="18"/>
+      <c r="J70" s="18"/>
+      <c r="K70" s="18"/>
+      <c r="L70" s="18"/>
+      <c r="M70" s="18"/>
+      <c r="N70" s="18"/>
+      <c r="O70" s="18"/>
+      <c r="P70" s="18"/>
+      <c r="Q70" s="18"/>
+      <c r="R70" s="18"/>
+      <c r="S70" s="18"/>
+      <c r="T70" s="18"/>
+      <c r="U70" s="18"/>
+      <c r="V70" s="18"/>
+      <c r="W70" s="18"/>
+      <c r="X70" s="18"/>
+      <c r="Y70" s="18"/>
+      <c r="Z70" s="15"/>
+    </row>
+    <row r="71" ht="15.0" customHeight="1">
+      <c r="A71" s="16" t="s">
+        <v>279</v>
+      </c>
+      <c r="B71" s="17">
+        <v>0.0</v>
+      </c>
+      <c r="C71" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="D71" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="E71" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="F71" s="18"/>
+      <c r="G71" s="18"/>
+      <c r="H71" s="18"/>
+      <c r="I71" s="18"/>
+      <c r="J71" s="18"/>
+      <c r="K71" s="18"/>
+      <c r="L71" s="18"/>
+      <c r="M71" s="18"/>
+      <c r="N71" s="18"/>
+      <c r="O71" s="18"/>
+      <c r="P71" s="18"/>
+      <c r="Q71" s="18"/>
+      <c r="R71" s="18"/>
+      <c r="S71" s="18"/>
+      <c r="T71" s="18"/>
+      <c r="U71" s="18"/>
+      <c r="V71" s="18"/>
+      <c r="W71" s="18"/>
+      <c r="X71" s="18"/>
+      <c r="Y71" s="18"/>
+      <c r="Z71" s="15"/>
+    </row>
+    <row r="72" ht="15.0" customHeight="1">
+      <c r="A72" s="20" t="s">
+        <v>283</v>
+      </c>
+      <c r="B72" s="21">
+        <v>0.0</v>
+      </c>
+      <c r="C72" s="21" t="s">
+        <v>284</v>
+      </c>
+      <c r="D72" s="21" t="s">
         <v>147</v>
       </c>
-      <c r="E69" s="19" t="s">
+      <c r="E72" s="21" t="s">
         <v>148</v>
       </c>
-      <c r="F69" s="19"/>
-      <c r="G69" s="19"/>
-      <c r="H69" s="19"/>
-      <c r="I69" s="19"/>
-      <c r="J69" s="19"/>
-      <c r="K69" s="19"/>
-      <c r="L69" s="19"/>
-      <c r="M69" s="19"/>
-      <c r="N69" s="19"/>
-      <c r="O69" s="19"/>
-      <c r="P69" s="19"/>
-      <c r="Q69" s="19"/>
-      <c r="R69" s="19"/>
-      <c r="S69" s="19"/>
-      <c r="T69" s="19"/>
-      <c r="U69" s="19"/>
-      <c r="V69" s="19"/>
-      <c r="W69" s="19"/>
-      <c r="X69" s="19"/>
-      <c r="Y69" s="19"/>
-      <c r="Z69" s="20"/>
-    </row>
-    <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="21" t="s">
-        <v>273</v>
-      </c>
-      <c r="B70" s="22">
+      <c r="F72" s="21"/>
+      <c r="G72" s="21"/>
+      <c r="H72" s="21"/>
+      <c r="I72" s="21"/>
+      <c r="J72" s="21"/>
+      <c r="K72" s="21"/>
+      <c r="L72" s="21"/>
+      <c r="M72" s="21"/>
+      <c r="N72" s="21"/>
+      <c r="O72" s="21"/>
+      <c r="P72" s="21"/>
+      <c r="Q72" s="21"/>
+      <c r="R72" s="21"/>
+      <c r="S72" s="21"/>
+      <c r="T72" s="21"/>
+      <c r="U72" s="21"/>
+      <c r="V72" s="21"/>
+      <c r="W72" s="21"/>
+      <c r="X72" s="21"/>
+      <c r="Y72" s="21"/>
+    </row>
+    <row r="73" ht="15.0" customHeight="1">
+      <c r="A73" s="22" t="s">
+        <v>285</v>
+      </c>
+      <c r="B73" s="23">
         <v>0.0</v>
       </c>
-      <c r="C70" s="22" t="s">
-        <v>274</v>
-      </c>
-      <c r="D70" s="22" t="s">
-        <v>275</v>
-      </c>
-      <c r="E70" s="22" t="s">
-        <v>276</v>
-      </c>
-      <c r="F70" s="22"/>
-      <c r="G70" s="22"/>
-      <c r="H70" s="22"/>
-      <c r="I70" s="22"/>
-      <c r="J70" s="22"/>
-      <c r="K70" s="22"/>
-      <c r="L70" s="22"/>
-      <c r="M70" s="22"/>
-      <c r="N70" s="22"/>
-      <c r="O70" s="22"/>
-      <c r="P70" s="22"/>
-      <c r="Q70" s="22"/>
-      <c r="R70" s="22"/>
-      <c r="S70" s="22"/>
-      <c r="T70" s="22"/>
-      <c r="U70" s="22"/>
-      <c r="V70" s="22"/>
-      <c r="W70" s="22"/>
-      <c r="X70" s="22"/>
-      <c r="Y70" s="22"/>
-      <c r="Z70" s="23"/>
-    </row>
-    <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="21" t="s">
-        <v>277</v>
-      </c>
-      <c r="B71" s="22">
+      <c r="C73" s="23" t="s">
+        <v>286</v>
+      </c>
+      <c r="D73" s="23" t="s">
+        <v>287</v>
+      </c>
+      <c r="E73" s="23" t="s">
+        <v>288</v>
+      </c>
+      <c r="F73" s="23"/>
+      <c r="G73" s="23"/>
+      <c r="H73" s="23"/>
+      <c r="I73" s="23"/>
+      <c r="J73" s="23"/>
+      <c r="K73" s="23"/>
+      <c r="L73" s="23"/>
+      <c r="M73" s="23"/>
+      <c r="N73" s="23"/>
+      <c r="O73" s="23"/>
+      <c r="P73" s="23"/>
+      <c r="Q73" s="23"/>
+      <c r="R73" s="23"/>
+      <c r="S73" s="23"/>
+      <c r="T73" s="23"/>
+      <c r="U73" s="23"/>
+      <c r="V73" s="23"/>
+      <c r="W73" s="23"/>
+      <c r="X73" s="23"/>
+      <c r="Y73" s="23"/>
+    </row>
+    <row r="74" ht="15.75" customHeight="1">
+      <c r="A74" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="B74" s="23">
         <v>0.0</v>
       </c>
-      <c r="C71" s="22" t="s">
-        <v>278</v>
-      </c>
-      <c r="D71" s="22" t="s">
+      <c r="C74" s="23" t="s">
+        <v>290</v>
+      </c>
+      <c r="D74" s="23" t="s">
         <v>175</v>
       </c>
-      <c r="E71" s="22" t="s">
+      <c r="E74" s="23" t="s">
         <v>176</v>
       </c>
-      <c r="F71" s="22"/>
-      <c r="G71" s="22"/>
-      <c r="H71" s="22"/>
-      <c r="I71" s="22"/>
-      <c r="J71" s="22"/>
-      <c r="K71" s="22"/>
-      <c r="L71" s="22"/>
-      <c r="M71" s="22"/>
-      <c r="N71" s="22"/>
-      <c r="O71" s="22"/>
-      <c r="P71" s="22"/>
-      <c r="Q71" s="22"/>
-      <c r="R71" s="22"/>
-      <c r="S71" s="22"/>
-      <c r="T71" s="22"/>
-      <c r="U71" s="22"/>
-      <c r="V71" s="22"/>
-      <c r="W71" s="22"/>
-      <c r="X71" s="22"/>
-      <c r="Y71" s="22"/>
-      <c r="Z71" s="23"/>
-    </row>
-    <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="B72" s="22">
+      <c r="F74" s="23"/>
+      <c r="G74" s="23"/>
+      <c r="H74" s="23"/>
+      <c r="I74" s="23"/>
+      <c r="J74" s="23"/>
+      <c r="K74" s="23"/>
+      <c r="L74" s="23"/>
+      <c r="M74" s="23"/>
+      <c r="N74" s="23"/>
+      <c r="O74" s="23"/>
+      <c r="P74" s="23"/>
+      <c r="Q74" s="23"/>
+      <c r="R74" s="23"/>
+      <c r="S74" s="23"/>
+      <c r="T74" s="23"/>
+      <c r="U74" s="23"/>
+      <c r="V74" s="23"/>
+      <c r="W74" s="23"/>
+      <c r="X74" s="23"/>
+      <c r="Y74" s="23"/>
+    </row>
+    <row r="75" ht="15.75" customHeight="1">
+      <c r="A75" s="22" t="s">
+        <v>291</v>
+      </c>
+      <c r="B75" s="23">
         <v>0.0</v>
       </c>
-      <c r="C72" s="22" t="s">
-        <v>280</v>
-      </c>
-      <c r="D72" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="E72" s="22" t="s">
-        <v>282</v>
-      </c>
-      <c r="F72" s="22"/>
-      <c r="G72" s="22"/>
-      <c r="H72" s="22"/>
-      <c r="I72" s="22"/>
-      <c r="J72" s="22"/>
-      <c r="K72" s="22"/>
-      <c r="L72" s="22"/>
-      <c r="M72" s="22"/>
-      <c r="N72" s="22"/>
-      <c r="O72" s="22"/>
-      <c r="P72" s="22"/>
-      <c r="Q72" s="22"/>
-      <c r="R72" s="22"/>
-      <c r="S72" s="22"/>
-      <c r="T72" s="22"/>
-      <c r="U72" s="22"/>
-      <c r="V72" s="22"/>
-      <c r="W72" s="22"/>
-      <c r="X72" s="22"/>
-      <c r="Y72" s="22"/>
-      <c r="Z72" s="23"/>
-    </row>
-    <row r="73" ht="15.0" customHeight="1">
-      <c r="A73" s="21" t="s">
-        <v>283</v>
-      </c>
-      <c r="B73" s="22">
+      <c r="C75" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="D75" s="23" t="s">
+        <v>293</v>
+      </c>
+      <c r="E75" s="23" t="s">
+        <v>294</v>
+      </c>
+      <c r="F75" s="23"/>
+      <c r="G75" s="23"/>
+      <c r="H75" s="23"/>
+      <c r="I75" s="23"/>
+      <c r="J75" s="23"/>
+      <c r="K75" s="23"/>
+      <c r="L75" s="23"/>
+      <c r="M75" s="23"/>
+      <c r="N75" s="23"/>
+      <c r="O75" s="23"/>
+      <c r="P75" s="23"/>
+      <c r="Q75" s="23"/>
+      <c r="R75" s="23"/>
+      <c r="S75" s="23"/>
+      <c r="T75" s="23"/>
+      <c r="U75" s="23"/>
+      <c r="V75" s="23"/>
+      <c r="W75" s="23"/>
+      <c r="X75" s="23"/>
+      <c r="Y75" s="23"/>
+    </row>
+    <row r="76" ht="15.0" customHeight="1">
+      <c r="A76" s="22" t="s">
+        <v>295</v>
+      </c>
+      <c r="B76" s="23">
         <v>0.0</v>
       </c>
-      <c r="C73" s="22" t="s">
-        <v>284</v>
-      </c>
-      <c r="D73" s="22" t="s">
-        <v>285</v>
-      </c>
-      <c r="E73" s="22" t="s">
-        <v>286</v>
-      </c>
-      <c r="F73" s="22"/>
-      <c r="G73" s="22"/>
-      <c r="H73" s="22"/>
-      <c r="I73" s="22"/>
-      <c r="J73" s="22"/>
-      <c r="K73" s="22"/>
-      <c r="L73" s="22"/>
-      <c r="M73" s="22"/>
-      <c r="N73" s="22"/>
-      <c r="O73" s="22"/>
-      <c r="P73" s="22"/>
-      <c r="Q73" s="22"/>
-      <c r="R73" s="22"/>
-      <c r="S73" s="22"/>
-      <c r="T73" s="22"/>
-      <c r="U73" s="22"/>
-      <c r="V73" s="22"/>
-      <c r="W73" s="22"/>
-      <c r="X73" s="22"/>
-      <c r="Y73" s="22"/>
-      <c r="Z73" s="23"/>
-    </row>
-    <row r="74" ht="15.0" customHeight="1">
-      <c r="A74" s="21" t="s">
-        <v>287</v>
-      </c>
-      <c r="B74" s="22">
+      <c r="C76" s="23" t="s">
+        <v>296</v>
+      </c>
+      <c r="D76" s="23" t="s">
+        <v>297</v>
+      </c>
+      <c r="E76" s="23" t="s">
+        <v>298</v>
+      </c>
+      <c r="F76" s="23"/>
+      <c r="G76" s="23"/>
+      <c r="H76" s="23"/>
+      <c r="I76" s="23"/>
+      <c r="J76" s="23"/>
+      <c r="K76" s="23"/>
+      <c r="L76" s="23"/>
+      <c r="M76" s="23"/>
+      <c r="N76" s="23"/>
+      <c r="O76" s="23"/>
+      <c r="P76" s="23"/>
+      <c r="Q76" s="23"/>
+      <c r="R76" s="23"/>
+      <c r="S76" s="23"/>
+      <c r="T76" s="23"/>
+      <c r="U76" s="23"/>
+      <c r="V76" s="23"/>
+      <c r="W76" s="23"/>
+      <c r="X76" s="23"/>
+      <c r="Y76" s="23"/>
+    </row>
+    <row r="77" ht="15.0" customHeight="1">
+      <c r="A77" s="22" t="s">
+        <v>299</v>
+      </c>
+      <c r="B77" s="23">
         <v>0.0</v>
       </c>
-      <c r="C74" s="22" t="s">
-        <v>288</v>
-      </c>
-      <c r="D74" s="22" t="s">
-        <v>289</v>
-      </c>
-      <c r="E74" s="22" t="s">
-        <v>290</v>
-      </c>
-      <c r="F74" s="22"/>
-      <c r="G74" s="22"/>
-      <c r="H74" s="22"/>
-      <c r="I74" s="22"/>
-      <c r="J74" s="22"/>
-      <c r="K74" s="22"/>
-      <c r="L74" s="22"/>
-      <c r="M74" s="22"/>
-      <c r="N74" s="22"/>
-      <c r="O74" s="22"/>
-      <c r="P74" s="22"/>
-      <c r="Q74" s="22"/>
-      <c r="R74" s="22"/>
-      <c r="S74" s="22"/>
-      <c r="T74" s="22"/>
-      <c r="U74" s="22"/>
-      <c r="V74" s="22"/>
-      <c r="W74" s="22"/>
-      <c r="X74" s="22"/>
-      <c r="Y74" s="22"/>
-      <c r="Z74" s="23"/>
-    </row>
-    <row r="75" ht="15.0" customHeight="1">
-      <c r="A75" s="21" t="s">
-        <v>291</v>
-      </c>
-      <c r="B75" s="22">
+      <c r="C77" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="D77" s="23" t="s">
+        <v>301</v>
+      </c>
+      <c r="E77" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="F77" s="23"/>
+      <c r="G77" s="23"/>
+      <c r="H77" s="23"/>
+      <c r="I77" s="23"/>
+      <c r="J77" s="23"/>
+      <c r="K77" s="23"/>
+      <c r="L77" s="23"/>
+      <c r="M77" s="23"/>
+      <c r="N77" s="23"/>
+      <c r="O77" s="23"/>
+      <c r="P77" s="23"/>
+      <c r="Q77" s="23"/>
+      <c r="R77" s="23"/>
+      <c r="S77" s="23"/>
+      <c r="T77" s="23"/>
+      <c r="U77" s="23"/>
+      <c r="V77" s="23"/>
+      <c r="W77" s="23"/>
+      <c r="X77" s="23"/>
+      <c r="Y77" s="23"/>
+    </row>
+    <row r="78" ht="15.0" customHeight="1">
+      <c r="A78" s="22" t="s">
+        <v>303</v>
+      </c>
+      <c r="B78" s="23">
         <v>0.0</v>
       </c>
-      <c r="C75" s="22" t="s">
-        <v>292</v>
-      </c>
-      <c r="D75" s="22" t="s">
-        <v>293</v>
-      </c>
-      <c r="E75" s="22" t="s">
-        <v>294</v>
-      </c>
-      <c r="F75" s="22"/>
-      <c r="G75" s="22"/>
-      <c r="H75" s="22"/>
-      <c r="I75" s="22"/>
-      <c r="J75" s="22"/>
-      <c r="K75" s="22"/>
-      <c r="L75" s="22"/>
-      <c r="M75" s="22"/>
-      <c r="N75" s="22"/>
-      <c r="O75" s="22"/>
-      <c r="P75" s="22"/>
-      <c r="Q75" s="22"/>
-      <c r="R75" s="22"/>
-      <c r="S75" s="22"/>
-      <c r="T75" s="22"/>
-      <c r="U75" s="22"/>
-      <c r="V75" s="22"/>
-      <c r="W75" s="22"/>
-      <c r="X75" s="22"/>
-      <c r="Y75" s="22"/>
-      <c r="Z75" s="23"/>
-    </row>
-    <row r="76" ht="15.0" customHeight="1">
-      <c r="A76" s="24" t="s">
-        <v>295</v>
-      </c>
-      <c r="B76" s="25">
+      <c r="C78" s="23" t="s">
+        <v>304</v>
+      </c>
+      <c r="D78" s="23" t="s">
+        <v>305</v>
+      </c>
+      <c r="E78" s="23" t="s">
+        <v>306</v>
+      </c>
+      <c r="F78" s="23"/>
+      <c r="G78" s="23"/>
+      <c r="H78" s="23"/>
+      <c r="I78" s="23"/>
+      <c r="J78" s="23"/>
+      <c r="K78" s="23"/>
+      <c r="L78" s="23"/>
+      <c r="M78" s="23"/>
+      <c r="N78" s="23"/>
+      <c r="O78" s="23"/>
+      <c r="P78" s="23"/>
+      <c r="Q78" s="23"/>
+      <c r="R78" s="23"/>
+      <c r="S78" s="23"/>
+      <c r="T78" s="23"/>
+      <c r="U78" s="23"/>
+      <c r="V78" s="23"/>
+      <c r="W78" s="23"/>
+      <c r="X78" s="23"/>
+      <c r="Y78" s="23"/>
+    </row>
+    <row r="79" ht="15.0" customHeight="1">
+      <c r="A79" s="24" t="s">
+        <v>307</v>
+      </c>
+      <c r="B79" s="25">
         <v>0.0</v>
       </c>
-      <c r="C76" s="26" t="s">
-        <v>296</v>
-      </c>
-      <c r="D76" s="26" t="s">
+      <c r="C79" s="26" t="s">
+        <v>308</v>
+      </c>
+      <c r="D79" s="26" t="s">
         <v>207</v>
       </c>
-      <c r="E76" s="26" t="s">
+      <c r="E79" s="26" t="s">
         <v>208</v>
       </c>
-      <c r="F76" s="26"/>
-      <c r="G76" s="26"/>
-      <c r="H76" s="26"/>
-      <c r="I76" s="26"/>
-      <c r="J76" s="26"/>
-      <c r="K76" s="26"/>
-      <c r="L76" s="26"/>
-      <c r="M76" s="26"/>
-      <c r="N76" s="26"/>
-      <c r="O76" s="26"/>
-      <c r="P76" s="26"/>
-      <c r="Q76" s="26"/>
-      <c r="R76" s="26"/>
-      <c r="S76" s="26"/>
-      <c r="T76" s="26"/>
-      <c r="U76" s="26"/>
-      <c r="V76" s="26"/>
-      <c r="W76" s="26"/>
-      <c r="X76" s="26"/>
-      <c r="Y76" s="26"/>
-      <c r="Z76" s="23"/>
-    </row>
-    <row r="77" ht="15.0" customHeight="1">
-      <c r="A77" s="27" t="s">
-        <v>297</v>
-      </c>
-      <c r="B77" s="25">
+      <c r="F79" s="26"/>
+      <c r="G79" s="26"/>
+      <c r="H79" s="26"/>
+      <c r="I79" s="26"/>
+      <c r="J79" s="26"/>
+      <c r="K79" s="26"/>
+      <c r="L79" s="26"/>
+      <c r="M79" s="26"/>
+      <c r="N79" s="26"/>
+      <c r="O79" s="26"/>
+      <c r="P79" s="26"/>
+      <c r="Q79" s="26"/>
+      <c r="R79" s="26"/>
+      <c r="S79" s="26"/>
+      <c r="T79" s="26"/>
+      <c r="U79" s="26"/>
+      <c r="V79" s="26"/>
+      <c r="W79" s="26"/>
+      <c r="X79" s="26"/>
+      <c r="Y79" s="26"/>
+    </row>
+    <row r="80" ht="15.0" customHeight="1">
+      <c r="A80" s="24" t="s">
+        <v>309</v>
+      </c>
+      <c r="B80" s="25">
         <v>0.0</v>
       </c>
-      <c r="C77" s="26" t="s">
-        <v>298</v>
-      </c>
-      <c r="D77" s="26" t="s">
+      <c r="C80" s="26" t="s">
+        <v>310</v>
+      </c>
+      <c r="D80" s="26" t="s">
         <v>139</v>
       </c>
-      <c r="E77" s="26" t="s">
+      <c r="E80" s="26" t="s">
         <v>140</v>
       </c>
-      <c r="F77" s="26"/>
-      <c r="G77" s="26"/>
-      <c r="H77" s="26"/>
-      <c r="I77" s="26"/>
-      <c r="J77" s="26"/>
-      <c r="K77" s="26"/>
-      <c r="L77" s="26"/>
-      <c r="M77" s="26"/>
-      <c r="N77" s="26"/>
-      <c r="O77" s="26"/>
-      <c r="P77" s="26"/>
-      <c r="Q77" s="26"/>
-      <c r="R77" s="26"/>
-      <c r="S77" s="26"/>
-      <c r="T77" s="26"/>
-      <c r="U77" s="26"/>
-      <c r="V77" s="26"/>
-      <c r="W77" s="26"/>
-      <c r="X77" s="26"/>
-      <c r="Y77" s="26"/>
-      <c r="Z77" s="23"/>
-    </row>
-    <row r="78" ht="15.0" customHeight="1">
-      <c r="A78" s="24" t="s">
-        <v>299</v>
-      </c>
-      <c r="B78" s="28">
+      <c r="F80" s="26"/>
+      <c r="G80" s="26"/>
+      <c r="H80" s="26"/>
+      <c r="I80" s="26"/>
+      <c r="J80" s="26"/>
+      <c r="K80" s="26"/>
+      <c r="L80" s="26"/>
+      <c r="M80" s="26"/>
+      <c r="N80" s="26"/>
+      <c r="O80" s="26"/>
+      <c r="P80" s="26"/>
+      <c r="Q80" s="26"/>
+      <c r="R80" s="26"/>
+      <c r="S80" s="26"/>
+      <c r="T80" s="26"/>
+      <c r="U80" s="26"/>
+      <c r="V80" s="26"/>
+      <c r="W80" s="26"/>
+      <c r="X80" s="26"/>
+      <c r="Y80" s="26"/>
+    </row>
+    <row r="81" ht="15.0" customHeight="1">
+      <c r="A81" s="24" t="s">
+        <v>311</v>
+      </c>
+      <c r="B81" s="25">
         <v>0.0</v>
       </c>
-      <c r="C78" s="29" t="s">
-        <v>300</v>
-      </c>
-      <c r="D78" s="29" t="s">
-        <v>301</v>
-      </c>
-      <c r="E78" s="29" t="s">
-        <v>302</v>
-      </c>
-      <c r="F78" s="26"/>
-      <c r="G78" s="26"/>
-      <c r="H78" s="26"/>
-      <c r="I78" s="26"/>
-      <c r="J78" s="26"/>
-      <c r="K78" s="26"/>
-      <c r="L78" s="26"/>
-      <c r="M78" s="26"/>
-      <c r="N78" s="26"/>
-      <c r="O78" s="26"/>
-      <c r="P78" s="26"/>
-      <c r="Q78" s="26"/>
-      <c r="R78" s="26"/>
-      <c r="S78" s="26"/>
-      <c r="T78" s="26"/>
-      <c r="U78" s="26"/>
-      <c r="V78" s="26"/>
-      <c r="W78" s="26"/>
-      <c r="X78" s="26"/>
-      <c r="Y78" s="26"/>
-      <c r="Z78" s="23"/>
-    </row>
-    <row r="79" ht="15.0" customHeight="1">
-      <c r="A79" s="30" t="s">
-        <v>303</v>
-      </c>
-      <c r="B79" s="31">
+      <c r="C81" s="26" t="s">
+        <v>312</v>
+      </c>
+      <c r="D81" s="26" t="s">
+        <v>313</v>
+      </c>
+      <c r="E81" s="26" t="s">
+        <v>314</v>
+      </c>
+      <c r="F81" s="26"/>
+      <c r="G81" s="26"/>
+      <c r="H81" s="26"/>
+      <c r="I81" s="26"/>
+      <c r="J81" s="26"/>
+      <c r="K81" s="26"/>
+      <c r="L81" s="26"/>
+      <c r="M81" s="26"/>
+      <c r="N81" s="26"/>
+      <c r="O81" s="26"/>
+      <c r="P81" s="26"/>
+      <c r="Q81" s="26"/>
+      <c r="R81" s="26"/>
+      <c r="S81" s="26"/>
+      <c r="T81" s="26"/>
+      <c r="U81" s="26"/>
+      <c r="V81" s="26"/>
+      <c r="W81" s="26"/>
+      <c r="X81" s="26"/>
+      <c r="Y81" s="26"/>
+    </row>
+    <row r="82" ht="15.0" customHeight="1">
+      <c r="A82" s="27" t="s">
+        <v>315</v>
+      </c>
+      <c r="B82" s="28">
         <v>0.0</v>
       </c>
-      <c r="C79" s="32" t="s">
-        <v>304</v>
-      </c>
-      <c r="D79" s="32" t="s">
-        <v>305</v>
-      </c>
-      <c r="E79" s="32" t="s">
-        <v>306</v>
-      </c>
-      <c r="F79" s="33"/>
-      <c r="G79" s="33"/>
-      <c r="H79" s="33"/>
-      <c r="I79" s="33"/>
-      <c r="J79" s="33"/>
-      <c r="K79" s="33"/>
-      <c r="L79" s="33"/>
-      <c r="M79" s="33"/>
-      <c r="N79" s="33"/>
-      <c r="O79" s="33"/>
-      <c r="P79" s="33"/>
-      <c r="Q79" s="33"/>
-      <c r="R79" s="33"/>
-      <c r="S79" s="33"/>
-      <c r="T79" s="33"/>
-      <c r="U79" s="33"/>
-      <c r="V79" s="33"/>
-      <c r="W79" s="33"/>
-      <c r="X79" s="33"/>
-      <c r="Y79" s="33"/>
-      <c r="Z79" s="34"/>
-    </row>
-    <row r="80" ht="15.0" customHeight="1">
-      <c r="A80" s="1"/>
-      <c r="B80" s="1"/>
-      <c r="C80" s="1"/>
-      <c r="D80" s="1"/>
-      <c r="E80" s="1"/>
-      <c r="F80" s="1"/>
-      <c r="G80" s="1"/>
-      <c r="H80" s="1"/>
-      <c r="I80" s="1"/>
-      <c r="J80" s="1"/>
-      <c r="K80" s="1"/>
-      <c r="L80" s="1"/>
-      <c r="M80" s="1"/>
-      <c r="N80" s="1"/>
-      <c r="O80" s="1"/>
-      <c r="P80" s="1"/>
-      <c r="Q80" s="1"/>
-      <c r="R80" s="1"/>
-      <c r="S80" s="1"/>
-      <c r="T80" s="1"/>
-      <c r="U80" s="1"/>
-      <c r="V80" s="1"/>
-      <c r="W80" s="1"/>
-      <c r="X80" s="1"/>
-      <c r="Y80" s="1"/>
-    </row>
-    <row r="81" ht="15.0" customHeight="1">
-      <c r="A81" s="1"/>
-      <c r="B81" s="1"/>
-      <c r="C81" s="1"/>
-      <c r="D81" s="1"/>
-      <c r="E81" s="1"/>
-      <c r="F81" s="1"/>
-      <c r="G81" s="1"/>
-      <c r="H81" s="1"/>
-      <c r="I81" s="1"/>
-      <c r="J81" s="1"/>
-      <c r="K81" s="1"/>
-      <c r="L81" s="1"/>
-      <c r="M81" s="1"/>
-      <c r="N81" s="1"/>
-      <c r="O81" s="1"/>
-      <c r="P81" s="1"/>
-      <c r="Q81" s="1"/>
-      <c r="R81" s="1"/>
-      <c r="S81" s="1"/>
-      <c r="T81" s="1"/>
-      <c r="U81" s="1"/>
-      <c r="V81" s="1"/>
-      <c r="W81" s="1"/>
-      <c r="X81" s="1"/>
-      <c r="Y81" s="1"/>
-    </row>
-    <row r="82" ht="15.0" customHeight="1">
-      <c r="A82" s="1"/>
-      <c r="B82" s="1"/>
-      <c r="C82" s="1"/>
-      <c r="D82" s="1"/>
-      <c r="E82" s="1"/>
-      <c r="F82" s="1"/>
-      <c r="G82" s="1"/>
-      <c r="H82" s="1"/>
-      <c r="I82" s="1"/>
-      <c r="J82" s="1"/>
-      <c r="K82" s="1"/>
-      <c r="L82" s="1"/>
-      <c r="M82" s="1"/>
-      <c r="N82" s="1"/>
-      <c r="O82" s="1"/>
-      <c r="P82" s="1"/>
-      <c r="Q82" s="1"/>
-      <c r="R82" s="1"/>
-      <c r="S82" s="1"/>
-      <c r="T82" s="1"/>
-      <c r="U82" s="1"/>
-      <c r="V82" s="1"/>
-      <c r="W82" s="1"/>
-      <c r="X82" s="1"/>
-      <c r="Y82" s="1"/>
+      <c r="C82" s="29" t="s">
+        <v>316</v>
+      </c>
+      <c r="D82" s="29" t="s">
+        <v>317</v>
+      </c>
+      <c r="E82" s="29" t="s">
+        <v>318</v>
+      </c>
+      <c r="F82" s="29"/>
+      <c r="G82" s="29"/>
+      <c r="H82" s="29"/>
+      <c r="I82" s="29"/>
+      <c r="J82" s="29"/>
+      <c r="K82" s="29"/>
+      <c r="L82" s="29"/>
+      <c r="M82" s="29"/>
+      <c r="N82" s="29"/>
+      <c r="O82" s="29"/>
+      <c r="P82" s="29"/>
+      <c r="Q82" s="29"/>
+      <c r="R82" s="29"/>
+      <c r="S82" s="29"/>
+      <c r="T82" s="29"/>
+      <c r="U82" s="29"/>
+      <c r="V82" s="29"/>
+      <c r="W82" s="29"/>
+      <c r="X82" s="29"/>
+      <c r="Y82" s="29"/>
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="1"/>
@@ -9023,7 +9092,7 @@
       <c r="X254" s="1"/>
       <c r="Y254" s="1"/>
     </row>
-    <row r="255" ht="15.0" customHeight="1">
+    <row r="255" ht="15.75" customHeight="1">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -9050,7 +9119,7 @@
       <c r="X255" s="1"/>
       <c r="Y255" s="1"/>
     </row>
-    <row r="256" ht="15.0" customHeight="1">
+    <row r="256" ht="15.75" customHeight="1">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -9077,7 +9146,7 @@
       <c r="X256" s="1"/>
       <c r="Y256" s="1"/>
     </row>
-    <row r="257" ht="15.0" customHeight="1">
+    <row r="257" ht="15.75" customHeight="1">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -9104,7 +9173,7 @@
       <c r="X257" s="1"/>
       <c r="Y257" s="1"/>
     </row>
-    <row r="258" ht="15.0" customHeight="1">
+    <row r="258" ht="15.75" customHeight="1">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -9131,7 +9200,7 @@
       <c r="X258" s="1"/>
       <c r="Y258" s="1"/>
     </row>
-    <row r="259" ht="15.0" customHeight="1">
+    <row r="259" ht="15.75" customHeight="1">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -9158,7 +9227,7 @@
       <c r="X259" s="1"/>
       <c r="Y259" s="1"/>
     </row>
-    <row r="260" ht="15.0" customHeight="1">
+    <row r="260" ht="15.75" customHeight="1">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -9185,7 +9254,7 @@
       <c r="X260" s="1"/>
       <c r="Y260" s="1"/>
     </row>
-    <row r="261" ht="15.0" customHeight="1">
+    <row r="261" ht="15.75" customHeight="1">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -9212,7 +9281,7 @@
       <c r="X261" s="1"/>
       <c r="Y261" s="1"/>
     </row>
-    <row r="262" ht="15.0" customHeight="1">
+    <row r="262" ht="15.75" customHeight="1">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -9239,7 +9308,7 @@
       <c r="X262" s="1"/>
       <c r="Y262" s="1"/>
     </row>
-    <row r="263" ht="15.0" customHeight="1">
+    <row r="263" ht="15.75" customHeight="1">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -9455,249 +9524,15 @@
       <c r="X270" s="1"/>
       <c r="Y270" s="1"/>
     </row>
-    <row r="271" ht="15.75" customHeight="1">
-      <c r="A271" s="1"/>
-      <c r="B271" s="1"/>
-      <c r="C271" s="1"/>
-      <c r="D271" s="1"/>
-      <c r="E271" s="1"/>
-      <c r="F271" s="1"/>
-      <c r="G271" s="1"/>
-      <c r="H271" s="1"/>
-      <c r="I271" s="1"/>
-      <c r="J271" s="1"/>
-      <c r="K271" s="1"/>
-      <c r="L271" s="1"/>
-      <c r="M271" s="1"/>
-      <c r="N271" s="1"/>
-      <c r="O271" s="1"/>
-      <c r="P271" s="1"/>
-      <c r="Q271" s="1"/>
-      <c r="R271" s="1"/>
-      <c r="S271" s="1"/>
-      <c r="T271" s="1"/>
-      <c r="U271" s="1"/>
-      <c r="V271" s="1"/>
-      <c r="W271" s="1"/>
-      <c r="X271" s="1"/>
-      <c r="Y271" s="1"/>
-    </row>
-    <row r="272" ht="15.75" customHeight="1">
-      <c r="A272" s="1"/>
-      <c r="B272" s="1"/>
-      <c r="C272" s="1"/>
-      <c r="D272" s="1"/>
-      <c r="E272" s="1"/>
-      <c r="F272" s="1"/>
-      <c r="G272" s="1"/>
-      <c r="H272" s="1"/>
-      <c r="I272" s="1"/>
-      <c r="J272" s="1"/>
-      <c r="K272" s="1"/>
-      <c r="L272" s="1"/>
-      <c r="M272" s="1"/>
-      <c r="N272" s="1"/>
-      <c r="O272" s="1"/>
-      <c r="P272" s="1"/>
-      <c r="Q272" s="1"/>
-      <c r="R272" s="1"/>
-      <c r="S272" s="1"/>
-      <c r="T272" s="1"/>
-      <c r="U272" s="1"/>
-      <c r="V272" s="1"/>
-      <c r="W272" s="1"/>
-      <c r="X272" s="1"/>
-      <c r="Y272" s="1"/>
-    </row>
-    <row r="273" ht="15.75" customHeight="1">
-      <c r="A273" s="1"/>
-      <c r="B273" s="1"/>
-      <c r="C273" s="1"/>
-      <c r="D273" s="1"/>
-      <c r="E273" s="1"/>
-      <c r="F273" s="1"/>
-      <c r="G273" s="1"/>
-      <c r="H273" s="1"/>
-      <c r="I273" s="1"/>
-      <c r="J273" s="1"/>
-      <c r="K273" s="1"/>
-      <c r="L273" s="1"/>
-      <c r="M273" s="1"/>
-      <c r="N273" s="1"/>
-      <c r="O273" s="1"/>
-      <c r="P273" s="1"/>
-      <c r="Q273" s="1"/>
-      <c r="R273" s="1"/>
-      <c r="S273" s="1"/>
-      <c r="T273" s="1"/>
-      <c r="U273" s="1"/>
-      <c r="V273" s="1"/>
-      <c r="W273" s="1"/>
-      <c r="X273" s="1"/>
-      <c r="Y273" s="1"/>
-    </row>
-    <row r="274" ht="15.75" customHeight="1">
-      <c r="A274" s="1"/>
-      <c r="B274" s="1"/>
-      <c r="C274" s="1"/>
-      <c r="D274" s="1"/>
-      <c r="E274" s="1"/>
-      <c r="F274" s="1"/>
-      <c r="G274" s="1"/>
-      <c r="H274" s="1"/>
-      <c r="I274" s="1"/>
-      <c r="J274" s="1"/>
-      <c r="K274" s="1"/>
-      <c r="L274" s="1"/>
-      <c r="M274" s="1"/>
-      <c r="N274" s="1"/>
-      <c r="O274" s="1"/>
-      <c r="P274" s="1"/>
-      <c r="Q274" s="1"/>
-      <c r="R274" s="1"/>
-      <c r="S274" s="1"/>
-      <c r="T274" s="1"/>
-      <c r="U274" s="1"/>
-      <c r="V274" s="1"/>
-      <c r="W274" s="1"/>
-      <c r="X274" s="1"/>
-      <c r="Y274" s="1"/>
-    </row>
-    <row r="275" ht="15.75" customHeight="1">
-      <c r="A275" s="1"/>
-      <c r="B275" s="1"/>
-      <c r="C275" s="1"/>
-      <c r="D275" s="1"/>
-      <c r="E275" s="1"/>
-      <c r="F275" s="1"/>
-      <c r="G275" s="1"/>
-      <c r="H275" s="1"/>
-      <c r="I275" s="1"/>
-      <c r="J275" s="1"/>
-      <c r="K275" s="1"/>
-      <c r="L275" s="1"/>
-      <c r="M275" s="1"/>
-      <c r="N275" s="1"/>
-      <c r="O275" s="1"/>
-      <c r="P275" s="1"/>
-      <c r="Q275" s="1"/>
-      <c r="R275" s="1"/>
-      <c r="S275" s="1"/>
-      <c r="T275" s="1"/>
-      <c r="U275" s="1"/>
-      <c r="V275" s="1"/>
-      <c r="W275" s="1"/>
-      <c r="X275" s="1"/>
-      <c r="Y275" s="1"/>
-    </row>
-    <row r="276" ht="15.75" customHeight="1">
-      <c r="A276" s="1"/>
-      <c r="B276" s="1"/>
-      <c r="C276" s="1"/>
-      <c r="D276" s="1"/>
-      <c r="E276" s="1"/>
-      <c r="F276" s="1"/>
-      <c r="G276" s="1"/>
-      <c r="H276" s="1"/>
-      <c r="I276" s="1"/>
-      <c r="J276" s="1"/>
-      <c r="K276" s="1"/>
-      <c r="L276" s="1"/>
-      <c r="M276" s="1"/>
-      <c r="N276" s="1"/>
-      <c r="O276" s="1"/>
-      <c r="P276" s="1"/>
-      <c r="Q276" s="1"/>
-      <c r="R276" s="1"/>
-      <c r="S276" s="1"/>
-      <c r="T276" s="1"/>
-      <c r="U276" s="1"/>
-      <c r="V276" s="1"/>
-      <c r="W276" s="1"/>
-      <c r="X276" s="1"/>
-      <c r="Y276" s="1"/>
-    </row>
-    <row r="277" ht="15.75" customHeight="1">
-      <c r="A277" s="1"/>
-      <c r="B277" s="1"/>
-      <c r="C277" s="1"/>
-      <c r="D277" s="1"/>
-      <c r="E277" s="1"/>
-      <c r="F277" s="1"/>
-      <c r="G277" s="1"/>
-      <c r="H277" s="1"/>
-      <c r="I277" s="1"/>
-      <c r="J277" s="1"/>
-      <c r="K277" s="1"/>
-      <c r="L277" s="1"/>
-      <c r="M277" s="1"/>
-      <c r="N277" s="1"/>
-      <c r="O277" s="1"/>
-      <c r="P277" s="1"/>
-      <c r="Q277" s="1"/>
-      <c r="R277" s="1"/>
-      <c r="S277" s="1"/>
-      <c r="T277" s="1"/>
-      <c r="U277" s="1"/>
-      <c r="V277" s="1"/>
-      <c r="W277" s="1"/>
-      <c r="X277" s="1"/>
-      <c r="Y277" s="1"/>
-    </row>
-    <row r="278" ht="15.75" customHeight="1">
-      <c r="A278" s="1"/>
-      <c r="B278" s="1"/>
-      <c r="C278" s="1"/>
-      <c r="D278" s="1"/>
-      <c r="E278" s="1"/>
-      <c r="F278" s="1"/>
-      <c r="G278" s="1"/>
-      <c r="H278" s="1"/>
-      <c r="I278" s="1"/>
-      <c r="J278" s="1"/>
-      <c r="K278" s="1"/>
-      <c r="L278" s="1"/>
-      <c r="M278" s="1"/>
-      <c r="N278" s="1"/>
-      <c r="O278" s="1"/>
-      <c r="P278" s="1"/>
-      <c r="Q278" s="1"/>
-      <c r="R278" s="1"/>
-      <c r="S278" s="1"/>
-      <c r="T278" s="1"/>
-      <c r="U278" s="1"/>
-      <c r="V278" s="1"/>
-      <c r="W278" s="1"/>
-      <c r="X278" s="1"/>
-      <c r="Y278" s="1"/>
-    </row>
-    <row r="279" ht="15.75" customHeight="1">
-      <c r="A279" s="1"/>
-      <c r="B279" s="1"/>
-      <c r="C279" s="1"/>
-      <c r="D279" s="1"/>
-      <c r="E279" s="1"/>
-      <c r="F279" s="1"/>
-      <c r="G279" s="1"/>
-      <c r="H279" s="1"/>
-      <c r="I279" s="1"/>
-      <c r="J279" s="1"/>
-      <c r="K279" s="1"/>
-      <c r="L279" s="1"/>
-      <c r="M279" s="1"/>
-      <c r="N279" s="1"/>
-      <c r="O279" s="1"/>
-      <c r="P279" s="1"/>
-      <c r="Q279" s="1"/>
-      <c r="R279" s="1"/>
-      <c r="S279" s="1"/>
-      <c r="T279" s="1"/>
-      <c r="U279" s="1"/>
-      <c r="V279" s="1"/>
-      <c r="W279" s="1"/>
-      <c r="X279" s="1"/>
-      <c r="Y279" s="1"/>
-    </row>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
     <row r="280" ht="15.75" customHeight="1"/>
     <row r="281" ht="15.75" customHeight="1"/>
     <row r="282" ht="15.75" customHeight="1"/>
@@ -10411,16 +10246,6 @@
     <row r="990" ht="15.75" customHeight="1"/>
     <row r="991" ht="15.75" customHeight="1"/>
     <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
-    <row r="1001" ht="15.75" customHeight="1"/>
-    <row r="1002" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Templates/Tables/StringInfo/StrTable.xlsx
+++ b/Templates/Tables/StringInfo/StrTable.xlsx
@@ -2065,7 +2065,7 @@
       <c r="X19" s="11"/>
       <c r="Y19" s="11"/>
     </row>
-    <row r="20" ht="15.75" customHeight="1">
+    <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="12" t="s">
         <v>77</v>
       </c>
@@ -2103,7 +2103,7 @@
       <c r="Y20" s="14"/>
       <c r="Z20" s="15"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
+    <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="16" t="s">
         <v>81</v>
       </c>
@@ -2141,7 +2141,7 @@
       <c r="Y21" s="18"/>
       <c r="Z21" s="15"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
+    <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="16" t="s">
         <v>85</v>
       </c>
@@ -2179,7 +2179,7 @@
       <c r="Y22" s="18"/>
       <c r="Z22" s="15"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
+    <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="16" t="s">
         <v>89</v>
       </c>
@@ -2217,7 +2217,7 @@
       <c r="Y23" s="18"/>
       <c r="Z23" s="15"/>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
+    <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="16" t="s">
         <v>93</v>
       </c>
@@ -2255,7 +2255,7 @@
       <c r="Y24" s="18"/>
       <c r="Z24" s="15"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
+    <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="16" t="s">
         <v>97</v>
       </c>
@@ -2293,7 +2293,7 @@
       <c r="Y25" s="18"/>
       <c r="Z25" s="15"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
+    <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="16" t="s">
         <v>101</v>
       </c>
@@ -2331,7 +2331,7 @@
       <c r="Y26" s="18"/>
       <c r="Z26" s="15"/>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
+    <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="16" t="s">
         <v>105</v>
       </c>
@@ -3015,7 +3015,7 @@
       <c r="Y44" s="18"/>
       <c r="Z44" s="15"/>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
+    <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="16" t="s">
         <v>177</v>
       </c>
@@ -3053,7 +3053,7 @@
       <c r="Y45" s="18"/>
       <c r="Z45" s="15"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1">
+    <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="16" t="s">
         <v>181</v>
       </c>
@@ -3091,7 +3091,7 @@
       <c r="Y46" s="18"/>
       <c r="Z46" s="15"/>
     </row>
-    <row r="47" ht="15.75" customHeight="1">
+    <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="16" t="s">
         <v>185</v>
       </c>
@@ -3129,7 +3129,7 @@
       <c r="Y47" s="18"/>
       <c r="Z47" s="15"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1">
+    <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="16" t="s">
         <v>189</v>
       </c>
@@ -3167,7 +3167,7 @@
       <c r="Y48" s="18"/>
       <c r="Z48" s="15"/>
     </row>
-    <row r="49" ht="15.75" customHeight="1">
+    <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="16" t="s">
         <v>193</v>
       </c>
@@ -3205,7 +3205,7 @@
       <c r="Y49" s="18"/>
       <c r="Z49" s="15"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1">
+    <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="16" t="s">
         <v>197</v>
       </c>
@@ -3243,7 +3243,7 @@
       <c r="Y50" s="18"/>
       <c r="Z50" s="15"/>
     </row>
-    <row r="51" ht="15.75" customHeight="1">
+    <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="16" t="s">
         <v>201</v>
       </c>
@@ -4115,7 +4115,7 @@
       <c r="X73" s="23"/>
       <c r="Y73" s="23"/>
     </row>
-    <row r="74" ht="15.75" customHeight="1">
+    <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="22" t="s">
         <v>289</v>
       </c>
@@ -4152,7 +4152,7 @@
       <c r="X74" s="23"/>
       <c r="Y74" s="23"/>
     </row>
-    <row r="75" ht="15.75" customHeight="1">
+    <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="22" t="s">
         <v>291</v>
       </c>
@@ -9092,7 +9092,7 @@
       <c r="X254" s="1"/>
       <c r="Y254" s="1"/>
     </row>
-    <row r="255" ht="15.75" customHeight="1">
+    <row r="255" ht="15.0" customHeight="1">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -9119,7 +9119,7 @@
       <c r="X255" s="1"/>
       <c r="Y255" s="1"/>
     </row>
-    <row r="256" ht="15.75" customHeight="1">
+    <row r="256" ht="15.0" customHeight="1">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -9146,7 +9146,7 @@
       <c r="X256" s="1"/>
       <c r="Y256" s="1"/>
     </row>
-    <row r="257" ht="15.75" customHeight="1">
+    <row r="257" ht="15.0" customHeight="1">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -9173,7 +9173,7 @@
       <c r="X257" s="1"/>
       <c r="Y257" s="1"/>
     </row>
-    <row r="258" ht="15.75" customHeight="1">
+    <row r="258" ht="15.0" customHeight="1">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -9200,7 +9200,7 @@
       <c r="X258" s="1"/>
       <c r="Y258" s="1"/>
     </row>
-    <row r="259" ht="15.75" customHeight="1">
+    <row r="259" ht="15.0" customHeight="1">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -9227,7 +9227,7 @@
       <c r="X259" s="1"/>
       <c r="Y259" s="1"/>
     </row>
-    <row r="260" ht="15.75" customHeight="1">
+    <row r="260" ht="15.0" customHeight="1">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -9254,7 +9254,7 @@
       <c r="X260" s="1"/>
       <c r="Y260" s="1"/>
     </row>
-    <row r="261" ht="15.75" customHeight="1">
+    <row r="261" ht="15.0" customHeight="1">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -9281,7 +9281,7 @@
       <c r="X261" s="1"/>
       <c r="Y261" s="1"/>
     </row>
-    <row r="262" ht="15.75" customHeight="1">
+    <row r="262" ht="15.0" customHeight="1">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -9308,7 +9308,7 @@
       <c r="X262" s="1"/>
       <c r="Y262" s="1"/>
     </row>
-    <row r="263" ht="15.75" customHeight="1">
+    <row r="263" ht="15.0" customHeight="1">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -9335,7 +9335,7 @@
       <c r="X263" s="1"/>
       <c r="Y263" s="1"/>
     </row>
-    <row r="264" ht="15.75" customHeight="1">
+    <row r="264" ht="15.0" customHeight="1">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -9362,7 +9362,7 @@
       <c r="X264" s="1"/>
       <c r="Y264" s="1"/>
     </row>
-    <row r="265" ht="15.75" customHeight="1">
+    <row r="265" ht="15.0" customHeight="1">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -9389,7 +9389,7 @@
       <c r="X265" s="1"/>
       <c r="Y265" s="1"/>
     </row>
-    <row r="266" ht="15.75" customHeight="1">
+    <row r="266" ht="15.0" customHeight="1">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -9416,7 +9416,7 @@
       <c r="X266" s="1"/>
       <c r="Y266" s="1"/>
     </row>
-    <row r="267" ht="15.75" customHeight="1">
+    <row r="267" ht="15.0" customHeight="1">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -9443,7 +9443,7 @@
       <c r="X267" s="1"/>
       <c r="Y267" s="1"/>
     </row>
-    <row r="268" ht="15.75" customHeight="1">
+    <row r="268" ht="15.0" customHeight="1">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -9470,7 +9470,7 @@
       <c r="X268" s="1"/>
       <c r="Y268" s="1"/>
     </row>
-    <row r="269" ht="15.75" customHeight="1">
+    <row r="269" ht="15.0" customHeight="1">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -9497,7 +9497,7 @@
       <c r="X269" s="1"/>
       <c r="Y269" s="1"/>
     </row>
-    <row r="270" ht="15.75" customHeight="1">
+    <row r="270" ht="15.0" customHeight="1">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -9524,728 +9524,736 @@
       <c r="X270" s="1"/>
       <c r="Y270" s="1"/>
     </row>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
-    <row r="810" ht="15.75" customHeight="1"/>
-    <row r="811" ht="15.75" customHeight="1"/>
-    <row r="812" ht="15.75" customHeight="1"/>
-    <row r="813" ht="15.75" customHeight="1"/>
-    <row r="814" ht="15.75" customHeight="1"/>
-    <row r="815" ht="15.75" customHeight="1"/>
-    <row r="816" ht="15.75" customHeight="1"/>
-    <row r="817" ht="15.75" customHeight="1"/>
-    <row r="818" ht="15.75" customHeight="1"/>
-    <row r="819" ht="15.75" customHeight="1"/>
-    <row r="820" ht="15.75" customHeight="1"/>
-    <row r="821" ht="15.75" customHeight="1"/>
-    <row r="822" ht="15.75" customHeight="1"/>
-    <row r="823" ht="15.75" customHeight="1"/>
-    <row r="824" ht="15.75" customHeight="1"/>
-    <row r="825" ht="15.75" customHeight="1"/>
-    <row r="826" ht="15.75" customHeight="1"/>
-    <row r="827" ht="15.75" customHeight="1"/>
-    <row r="828" ht="15.75" customHeight="1"/>
-    <row r="829" ht="15.75" customHeight="1"/>
-    <row r="830" ht="15.75" customHeight="1"/>
-    <row r="831" ht="15.75" customHeight="1"/>
-    <row r="832" ht="15.75" customHeight="1"/>
-    <row r="833" ht="15.75" customHeight="1"/>
-    <row r="834" ht="15.75" customHeight="1"/>
-    <row r="835" ht="15.75" customHeight="1"/>
-    <row r="836" ht="15.75" customHeight="1"/>
-    <row r="837" ht="15.75" customHeight="1"/>
-    <row r="838" ht="15.75" customHeight="1"/>
-    <row r="839" ht="15.75" customHeight="1"/>
-    <row r="840" ht="15.75" customHeight="1"/>
-    <row r="841" ht="15.75" customHeight="1"/>
-    <row r="842" ht="15.75" customHeight="1"/>
-    <row r="843" ht="15.75" customHeight="1"/>
-    <row r="844" ht="15.75" customHeight="1"/>
-    <row r="845" ht="15.75" customHeight="1"/>
-    <row r="846" ht="15.75" customHeight="1"/>
-    <row r="847" ht="15.75" customHeight="1"/>
-    <row r="848" ht="15.75" customHeight="1"/>
-    <row r="849" ht="15.75" customHeight="1"/>
-    <row r="850" ht="15.75" customHeight="1"/>
-    <row r="851" ht="15.75" customHeight="1"/>
-    <row r="852" ht="15.75" customHeight="1"/>
-    <row r="853" ht="15.75" customHeight="1"/>
-    <row r="854" ht="15.75" customHeight="1"/>
-    <row r="855" ht="15.75" customHeight="1"/>
-    <row r="856" ht="15.75" customHeight="1"/>
-    <row r="857" ht="15.75" customHeight="1"/>
-    <row r="858" ht="15.75" customHeight="1"/>
-    <row r="859" ht="15.75" customHeight="1"/>
-    <row r="860" ht="15.75" customHeight="1"/>
-    <row r="861" ht="15.75" customHeight="1"/>
-    <row r="862" ht="15.75" customHeight="1"/>
-    <row r="863" ht="15.75" customHeight="1"/>
-    <row r="864" ht="15.75" customHeight="1"/>
-    <row r="865" ht="15.75" customHeight="1"/>
-    <row r="866" ht="15.75" customHeight="1"/>
-    <row r="867" ht="15.75" customHeight="1"/>
-    <row r="868" ht="15.75" customHeight="1"/>
-    <row r="869" ht="15.75" customHeight="1"/>
-    <row r="870" ht="15.75" customHeight="1"/>
-    <row r="871" ht="15.75" customHeight="1"/>
-    <row r="872" ht="15.75" customHeight="1"/>
-    <row r="873" ht="15.75" customHeight="1"/>
-    <row r="874" ht="15.75" customHeight="1"/>
-    <row r="875" ht="15.75" customHeight="1"/>
-    <row r="876" ht="15.75" customHeight="1"/>
-    <row r="877" ht="15.75" customHeight="1"/>
-    <row r="878" ht="15.75" customHeight="1"/>
-    <row r="879" ht="15.75" customHeight="1"/>
-    <row r="880" ht="15.75" customHeight="1"/>
-    <row r="881" ht="15.75" customHeight="1"/>
-    <row r="882" ht="15.75" customHeight="1"/>
-    <row r="883" ht="15.75" customHeight="1"/>
-    <row r="884" ht="15.75" customHeight="1"/>
-    <row r="885" ht="15.75" customHeight="1"/>
-    <row r="886" ht="15.75" customHeight="1"/>
-    <row r="887" ht="15.75" customHeight="1"/>
-    <row r="888" ht="15.75" customHeight="1"/>
-    <row r="889" ht="15.75" customHeight="1"/>
-    <row r="890" ht="15.75" customHeight="1"/>
-    <row r="891" ht="15.75" customHeight="1"/>
-    <row r="892" ht="15.75" customHeight="1"/>
-    <row r="893" ht="15.75" customHeight="1"/>
-    <row r="894" ht="15.75" customHeight="1"/>
-    <row r="895" ht="15.75" customHeight="1"/>
-    <row r="896" ht="15.75" customHeight="1"/>
-    <row r="897" ht="15.75" customHeight="1"/>
-    <row r="898" ht="15.75" customHeight="1"/>
-    <row r="899" ht="15.75" customHeight="1"/>
-    <row r="900" ht="15.75" customHeight="1"/>
-    <row r="901" ht="15.75" customHeight="1"/>
-    <row r="902" ht="15.75" customHeight="1"/>
-    <row r="903" ht="15.75" customHeight="1"/>
-    <row r="904" ht="15.75" customHeight="1"/>
-    <row r="905" ht="15.75" customHeight="1"/>
-    <row r="906" ht="15.75" customHeight="1"/>
-    <row r="907" ht="15.75" customHeight="1"/>
-    <row r="908" ht="15.75" customHeight="1"/>
-    <row r="909" ht="15.75" customHeight="1"/>
-    <row r="910" ht="15.75" customHeight="1"/>
-    <row r="911" ht="15.75" customHeight="1"/>
-    <row r="912" ht="15.75" customHeight="1"/>
-    <row r="913" ht="15.75" customHeight="1"/>
-    <row r="914" ht="15.75" customHeight="1"/>
-    <row r="915" ht="15.75" customHeight="1"/>
-    <row r="916" ht="15.75" customHeight="1"/>
-    <row r="917" ht="15.75" customHeight="1"/>
-    <row r="918" ht="15.75" customHeight="1"/>
-    <row r="919" ht="15.75" customHeight="1"/>
-    <row r="920" ht="15.75" customHeight="1"/>
-    <row r="921" ht="15.75" customHeight="1"/>
-    <row r="922" ht="15.75" customHeight="1"/>
-    <row r="923" ht="15.75" customHeight="1"/>
-    <row r="924" ht="15.75" customHeight="1"/>
-    <row r="925" ht="15.75" customHeight="1"/>
-    <row r="926" ht="15.75" customHeight="1"/>
-    <row r="927" ht="15.75" customHeight="1"/>
-    <row r="928" ht="15.75" customHeight="1"/>
-    <row r="929" ht="15.75" customHeight="1"/>
-    <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
-    <row r="935" ht="15.75" customHeight="1"/>
-    <row r="936" ht="15.75" customHeight="1"/>
-    <row r="937" ht="15.75" customHeight="1"/>
-    <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
-    <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
-    <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.0" customHeight="1"/>
+    <row r="272" ht="15.0" customHeight="1"/>
+    <row r="273" ht="15.0" customHeight="1"/>
+    <row r="274" ht="15.0" customHeight="1"/>
+    <row r="275" ht="15.0" customHeight="1"/>
+    <row r="276" ht="15.0" customHeight="1"/>
+    <row r="277" ht="15.0" customHeight="1"/>
+    <row r="278" ht="15.0" customHeight="1"/>
+    <row r="279" ht="15.0" customHeight="1"/>
+    <row r="280" ht="15.0" customHeight="1"/>
+    <row r="281" ht="15.0" customHeight="1"/>
+    <row r="282" ht="15.0" customHeight="1"/>
+    <row r="283" ht="15.0" customHeight="1"/>
+    <row r="284" ht="15.0" customHeight="1"/>
+    <row r="285" ht="15.0" customHeight="1"/>
+    <row r="286" ht="15.0" customHeight="1"/>
+    <row r="287" ht="15.0" customHeight="1"/>
+    <row r="288" ht="15.0" customHeight="1"/>
+    <row r="289" ht="15.0" customHeight="1"/>
+    <row r="290" ht="15.0" customHeight="1"/>
+    <row r="291" ht="15.0" customHeight="1"/>
+    <row r="292" ht="15.0" customHeight="1"/>
+    <row r="293" ht="15.0" customHeight="1"/>
+    <row r="294" ht="15.0" customHeight="1"/>
+    <row r="295" ht="15.0" customHeight="1"/>
+    <row r="296" ht="15.0" customHeight="1"/>
+    <row r="297" ht="15.0" customHeight="1"/>
+    <row r="298" ht="15.0" customHeight="1"/>
+    <row r="299" ht="15.0" customHeight="1"/>
+    <row r="300" ht="15.0" customHeight="1"/>
+    <row r="301" ht="15.0" customHeight="1"/>
+    <row r="302" ht="15.0" customHeight="1"/>
+    <row r="303" ht="15.0" customHeight="1"/>
+    <row r="304" ht="15.0" customHeight="1"/>
+    <row r="305" ht="15.0" customHeight="1"/>
+    <row r="306" ht="15.0" customHeight="1"/>
+    <row r="307" ht="15.0" customHeight="1"/>
+    <row r="308" ht="15.0" customHeight="1"/>
+    <row r="309" ht="15.0" customHeight="1"/>
+    <row r="310" ht="15.0" customHeight="1"/>
+    <row r="311" ht="15.0" customHeight="1"/>
+    <row r="312" ht="15.0" customHeight="1"/>
+    <row r="313" ht="15.0" customHeight="1"/>
+    <row r="314" ht="15.0" customHeight="1"/>
+    <row r="315" ht="15.0" customHeight="1"/>
+    <row r="316" ht="15.0" customHeight="1"/>
+    <row r="317" ht="15.0" customHeight="1"/>
+    <row r="318" ht="15.0" customHeight="1"/>
+    <row r="319" ht="15.0" customHeight="1"/>
+    <row r="320" ht="15.0" customHeight="1"/>
+    <row r="321" ht="15.0" customHeight="1"/>
+    <row r="322" ht="15.0" customHeight="1"/>
+    <row r="323" ht="15.0" customHeight="1"/>
+    <row r="324" ht="15.0" customHeight="1"/>
+    <row r="325" ht="15.0" customHeight="1"/>
+    <row r="326" ht="15.0" customHeight="1"/>
+    <row r="327" ht="15.0" customHeight="1"/>
+    <row r="328" ht="15.0" customHeight="1"/>
+    <row r="329" ht="15.0" customHeight="1"/>
+    <row r="330" ht="15.0" customHeight="1"/>
+    <row r="331" ht="15.0" customHeight="1"/>
+    <row r="332" ht="15.0" customHeight="1"/>
+    <row r="333" ht="15.0" customHeight="1"/>
+    <row r="334" ht="15.0" customHeight="1"/>
+    <row r="335" ht="15.0" customHeight="1"/>
+    <row r="336" ht="15.0" customHeight="1"/>
+    <row r="337" ht="15.0" customHeight="1"/>
+    <row r="338" ht="15.0" customHeight="1"/>
+    <row r="339" ht="15.0" customHeight="1"/>
+    <row r="340" ht="15.0" customHeight="1"/>
+    <row r="341" ht="15.0" customHeight="1"/>
+    <row r="342" ht="15.0" customHeight="1"/>
+    <row r="343" ht="15.0" customHeight="1"/>
+    <row r="344" ht="15.0" customHeight="1"/>
+    <row r="345" ht="15.0" customHeight="1"/>
+    <row r="346" ht="15.0" customHeight="1"/>
+    <row r="347" ht="15.0" customHeight="1"/>
+    <row r="348" ht="15.0" customHeight="1"/>
+    <row r="349" ht="15.0" customHeight="1"/>
+    <row r="350" ht="15.0" customHeight="1"/>
+    <row r="351" ht="15.0" customHeight="1"/>
+    <row r="352" ht="15.0" customHeight="1"/>
+    <row r="353" ht="15.0" customHeight="1"/>
+    <row r="354" ht="15.0" customHeight="1"/>
+    <row r="355" ht="15.0" customHeight="1"/>
+    <row r="356" ht="15.0" customHeight="1"/>
+    <row r="357" ht="15.0" customHeight="1"/>
+    <row r="358" ht="15.0" customHeight="1"/>
+    <row r="359" ht="15.0" customHeight="1"/>
+    <row r="360" ht="15.0" customHeight="1"/>
+    <row r="361" ht="15.0" customHeight="1"/>
+    <row r="362" ht="15.0" customHeight="1"/>
+    <row r="363" ht="15.0" customHeight="1"/>
+    <row r="364" ht="15.0" customHeight="1"/>
+    <row r="365" ht="15.0" customHeight="1"/>
+    <row r="366" ht="15.0" customHeight="1"/>
+    <row r="367" ht="15.0" customHeight="1"/>
+    <row r="368" ht="15.0" customHeight="1"/>
+    <row r="369" ht="15.0" customHeight="1"/>
+    <row r="370" ht="15.0" customHeight="1"/>
+    <row r="371" ht="15.0" customHeight="1"/>
+    <row r="372" ht="15.0" customHeight="1"/>
+    <row r="373" ht="15.0" customHeight="1"/>
+    <row r="374" ht="15.0" customHeight="1"/>
+    <row r="375" ht="15.0" customHeight="1"/>
+    <row r="376" ht="15.0" customHeight="1"/>
+    <row r="377" ht="15.0" customHeight="1"/>
+    <row r="378" ht="15.0" customHeight="1"/>
+    <row r="379" ht="15.0" customHeight="1"/>
+    <row r="380" ht="15.0" customHeight="1"/>
+    <row r="381" ht="15.0" customHeight="1"/>
+    <row r="382" ht="15.0" customHeight="1"/>
+    <row r="383" ht="15.0" customHeight="1"/>
+    <row r="384" ht="15.0" customHeight="1"/>
+    <row r="385" ht="15.0" customHeight="1"/>
+    <row r="386" ht="15.0" customHeight="1"/>
+    <row r="387" ht="15.0" customHeight="1"/>
+    <row r="388" ht="15.0" customHeight="1"/>
+    <row r="389" ht="15.0" customHeight="1"/>
+    <row r="390" ht="15.0" customHeight="1"/>
+    <row r="391" ht="15.0" customHeight="1"/>
+    <row r="392" ht="15.0" customHeight="1"/>
+    <row r="393" ht="15.0" customHeight="1"/>
+    <row r="394" ht="15.0" customHeight="1"/>
+    <row r="395" ht="15.0" customHeight="1"/>
+    <row r="396" ht="15.0" customHeight="1"/>
+    <row r="397" ht="15.0" customHeight="1"/>
+    <row r="398" ht="15.0" customHeight="1"/>
+    <row r="399" ht="15.0" customHeight="1"/>
+    <row r="400" ht="15.0" customHeight="1"/>
+    <row r="401" ht="15.0" customHeight="1"/>
+    <row r="402" ht="15.0" customHeight="1"/>
+    <row r="403" ht="15.0" customHeight="1"/>
+    <row r="404" ht="15.0" customHeight="1"/>
+    <row r="405" ht="15.0" customHeight="1"/>
+    <row r="406" ht="15.0" customHeight="1"/>
+    <row r="407" ht="15.0" customHeight="1"/>
+    <row r="408" ht="15.0" customHeight="1"/>
+    <row r="409" ht="15.0" customHeight="1"/>
+    <row r="410" ht="15.0" customHeight="1"/>
+    <row r="411" ht="15.0" customHeight="1"/>
+    <row r="412" ht="15.0" customHeight="1"/>
+    <row r="413" ht="15.0" customHeight="1"/>
+    <row r="414" ht="15.0" customHeight="1"/>
+    <row r="415" ht="15.0" customHeight="1"/>
+    <row r="416" ht="15.0" customHeight="1"/>
+    <row r="417" ht="15.0" customHeight="1"/>
+    <row r="418" ht="15.0" customHeight="1"/>
+    <row r="419" ht="15.0" customHeight="1"/>
+    <row r="420" ht="15.0" customHeight="1"/>
+    <row r="421" ht="15.0" customHeight="1"/>
+    <row r="422" ht="15.0" customHeight="1"/>
+    <row r="423" ht="15.0" customHeight="1"/>
+    <row r="424" ht="15.0" customHeight="1"/>
+    <row r="425" ht="15.0" customHeight="1"/>
+    <row r="426" ht="15.0" customHeight="1"/>
+    <row r="427" ht="15.0" customHeight="1"/>
+    <row r="428" ht="15.0" customHeight="1"/>
+    <row r="429" ht="15.0" customHeight="1"/>
+    <row r="430" ht="15.0" customHeight="1"/>
+    <row r="431" ht="15.0" customHeight="1"/>
+    <row r="432" ht="15.0" customHeight="1"/>
+    <row r="433" ht="15.0" customHeight="1"/>
+    <row r="434" ht="15.0" customHeight="1"/>
+    <row r="435" ht="15.0" customHeight="1"/>
+    <row r="436" ht="15.0" customHeight="1"/>
+    <row r="437" ht="15.0" customHeight="1"/>
+    <row r="438" ht="15.0" customHeight="1"/>
+    <row r="439" ht="15.0" customHeight="1"/>
+    <row r="440" ht="15.0" customHeight="1"/>
+    <row r="441" ht="15.0" customHeight="1"/>
+    <row r="442" ht="15.0" customHeight="1"/>
+    <row r="443" ht="15.0" customHeight="1"/>
+    <row r="444" ht="15.0" customHeight="1"/>
+    <row r="445" ht="15.0" customHeight="1"/>
+    <row r="446" ht="15.0" customHeight="1"/>
+    <row r="447" ht="15.0" customHeight="1"/>
+    <row r="448" ht="15.0" customHeight="1"/>
+    <row r="449" ht="15.0" customHeight="1"/>
+    <row r="450" ht="15.0" customHeight="1"/>
+    <row r="451" ht="15.0" customHeight="1"/>
+    <row r="452" ht="15.0" customHeight="1"/>
+    <row r="453" ht="15.0" customHeight="1"/>
+    <row r="454" ht="15.0" customHeight="1"/>
+    <row r="455" ht="15.0" customHeight="1"/>
+    <row r="456" ht="15.0" customHeight="1"/>
+    <row r="457" ht="15.0" customHeight="1"/>
+    <row r="458" ht="15.0" customHeight="1"/>
+    <row r="459" ht="15.0" customHeight="1"/>
+    <row r="460" ht="15.0" customHeight="1"/>
+    <row r="461" ht="15.0" customHeight="1"/>
+    <row r="462" ht="15.0" customHeight="1"/>
+    <row r="463" ht="15.0" customHeight="1"/>
+    <row r="464" ht="15.0" customHeight="1"/>
+    <row r="465" ht="15.0" customHeight="1"/>
+    <row r="466" ht="15.0" customHeight="1"/>
+    <row r="467" ht="15.0" customHeight="1"/>
+    <row r="468" ht="15.0" customHeight="1"/>
+    <row r="469" ht="15.0" customHeight="1"/>
+    <row r="470" ht="15.0" customHeight="1"/>
+    <row r="471" ht="15.0" customHeight="1"/>
+    <row r="472" ht="15.0" customHeight="1"/>
+    <row r="473" ht="15.0" customHeight="1"/>
+    <row r="474" ht="15.0" customHeight="1"/>
+    <row r="475" ht="15.0" customHeight="1"/>
+    <row r="476" ht="15.0" customHeight="1"/>
+    <row r="477" ht="15.0" customHeight="1"/>
+    <row r="478" ht="15.0" customHeight="1"/>
+    <row r="479" ht="15.0" customHeight="1"/>
+    <row r="480" ht="15.0" customHeight="1"/>
+    <row r="481" ht="15.0" customHeight="1"/>
+    <row r="482" ht="15.0" customHeight="1"/>
+    <row r="483" ht="15.0" customHeight="1"/>
+    <row r="484" ht="15.0" customHeight="1"/>
+    <row r="485" ht="15.0" customHeight="1"/>
+    <row r="486" ht="15.0" customHeight="1"/>
+    <row r="487" ht="15.0" customHeight="1"/>
+    <row r="488" ht="15.0" customHeight="1"/>
+    <row r="489" ht="15.0" customHeight="1"/>
+    <row r="490" ht="15.0" customHeight="1"/>
+    <row r="491" ht="15.0" customHeight="1"/>
+    <row r="492" ht="15.0" customHeight="1"/>
+    <row r="493" ht="15.0" customHeight="1"/>
+    <row r="494" ht="15.0" customHeight="1"/>
+    <row r="495" ht="15.0" customHeight="1"/>
+    <row r="496" ht="15.0" customHeight="1"/>
+    <row r="497" ht="15.0" customHeight="1"/>
+    <row r="498" ht="15.0" customHeight="1"/>
+    <row r="499" ht="15.0" customHeight="1"/>
+    <row r="500" ht="15.0" customHeight="1"/>
+    <row r="501" ht="15.0" customHeight="1"/>
+    <row r="502" ht="15.0" customHeight="1"/>
+    <row r="503" ht="15.0" customHeight="1"/>
+    <row r="504" ht="15.0" customHeight="1"/>
+    <row r="505" ht="15.0" customHeight="1"/>
+    <row r="506" ht="15.0" customHeight="1"/>
+    <row r="507" ht="15.0" customHeight="1"/>
+    <row r="508" ht="15.0" customHeight="1"/>
+    <row r="509" ht="15.0" customHeight="1"/>
+    <row r="510" ht="15.0" customHeight="1"/>
+    <row r="511" ht="15.0" customHeight="1"/>
+    <row r="512" ht="15.0" customHeight="1"/>
+    <row r="513" ht="15.0" customHeight="1"/>
+    <row r="514" ht="15.0" customHeight="1"/>
+    <row r="515" ht="15.0" customHeight="1"/>
+    <row r="516" ht="15.0" customHeight="1"/>
+    <row r="517" ht="15.0" customHeight="1"/>
+    <row r="518" ht="15.0" customHeight="1"/>
+    <row r="519" ht="15.0" customHeight="1"/>
+    <row r="520" ht="15.0" customHeight="1"/>
+    <row r="521" ht="15.0" customHeight="1"/>
+    <row r="522" ht="15.0" customHeight="1"/>
+    <row r="523" ht="15.0" customHeight="1"/>
+    <row r="524" ht="15.0" customHeight="1"/>
+    <row r="525" ht="15.0" customHeight="1"/>
+    <row r="526" ht="15.0" customHeight="1"/>
+    <row r="527" ht="15.0" customHeight="1"/>
+    <row r="528" ht="15.0" customHeight="1"/>
+    <row r="529" ht="15.0" customHeight="1"/>
+    <row r="530" ht="15.0" customHeight="1"/>
+    <row r="531" ht="15.0" customHeight="1"/>
+    <row r="532" ht="15.0" customHeight="1"/>
+    <row r="533" ht="15.0" customHeight="1"/>
+    <row r="534" ht="15.0" customHeight="1"/>
+    <row r="535" ht="15.0" customHeight="1"/>
+    <row r="536" ht="15.0" customHeight="1"/>
+    <row r="537" ht="15.0" customHeight="1"/>
+    <row r="538" ht="15.0" customHeight="1"/>
+    <row r="539" ht="15.0" customHeight="1"/>
+    <row r="540" ht="15.0" customHeight="1"/>
+    <row r="541" ht="15.0" customHeight="1"/>
+    <row r="542" ht="15.0" customHeight="1"/>
+    <row r="543" ht="15.0" customHeight="1"/>
+    <row r="544" ht="15.0" customHeight="1"/>
+    <row r="545" ht="15.0" customHeight="1"/>
+    <row r="546" ht="15.0" customHeight="1"/>
+    <row r="547" ht="15.0" customHeight="1"/>
+    <row r="548" ht="15.0" customHeight="1"/>
+    <row r="549" ht="15.0" customHeight="1"/>
+    <row r="550" ht="15.0" customHeight="1"/>
+    <row r="551" ht="15.0" customHeight="1"/>
+    <row r="552" ht="15.0" customHeight="1"/>
+    <row r="553" ht="15.0" customHeight="1"/>
+    <row r="554" ht="15.0" customHeight="1"/>
+    <row r="555" ht="15.0" customHeight="1"/>
+    <row r="556" ht="15.0" customHeight="1"/>
+    <row r="557" ht="15.0" customHeight="1"/>
+    <row r="558" ht="15.0" customHeight="1"/>
+    <row r="559" ht="15.0" customHeight="1"/>
+    <row r="560" ht="15.0" customHeight="1"/>
+    <row r="561" ht="15.0" customHeight="1"/>
+    <row r="562" ht="15.0" customHeight="1"/>
+    <row r="563" ht="15.0" customHeight="1"/>
+    <row r="564" ht="15.0" customHeight="1"/>
+    <row r="565" ht="15.0" customHeight="1"/>
+    <row r="566" ht="15.0" customHeight="1"/>
+    <row r="567" ht="15.0" customHeight="1"/>
+    <row r="568" ht="15.0" customHeight="1"/>
+    <row r="569" ht="15.0" customHeight="1"/>
+    <row r="570" ht="15.0" customHeight="1"/>
+    <row r="571" ht="15.0" customHeight="1"/>
+    <row r="572" ht="15.0" customHeight="1"/>
+    <row r="573" ht="15.0" customHeight="1"/>
+    <row r="574" ht="15.0" customHeight="1"/>
+    <row r="575" ht="15.0" customHeight="1"/>
+    <row r="576" ht="15.0" customHeight="1"/>
+    <row r="577" ht="15.0" customHeight="1"/>
+    <row r="578" ht="15.0" customHeight="1"/>
+    <row r="579" ht="15.0" customHeight="1"/>
+    <row r="580" ht="15.0" customHeight="1"/>
+    <row r="581" ht="15.0" customHeight="1"/>
+    <row r="582" ht="15.0" customHeight="1"/>
+    <row r="583" ht="15.0" customHeight="1"/>
+    <row r="584" ht="15.0" customHeight="1"/>
+    <row r="585" ht="15.0" customHeight="1"/>
+    <row r="586" ht="15.0" customHeight="1"/>
+    <row r="587" ht="15.0" customHeight="1"/>
+    <row r="588" ht="15.0" customHeight="1"/>
+    <row r="589" ht="15.0" customHeight="1"/>
+    <row r="590" ht="15.0" customHeight="1"/>
+    <row r="591" ht="15.0" customHeight="1"/>
+    <row r="592" ht="15.0" customHeight="1"/>
+    <row r="593" ht="15.0" customHeight="1"/>
+    <row r="594" ht="15.0" customHeight="1"/>
+    <row r="595" ht="15.0" customHeight="1"/>
+    <row r="596" ht="15.0" customHeight="1"/>
+    <row r="597" ht="15.0" customHeight="1"/>
+    <row r="598" ht="15.0" customHeight="1"/>
+    <row r="599" ht="15.0" customHeight="1"/>
+    <row r="600" ht="15.0" customHeight="1"/>
+    <row r="601" ht="15.0" customHeight="1"/>
+    <row r="602" ht="15.0" customHeight="1"/>
+    <row r="603" ht="15.0" customHeight="1"/>
+    <row r="604" ht="15.0" customHeight="1"/>
+    <row r="605" ht="15.0" customHeight="1"/>
+    <row r="606" ht="15.0" customHeight="1"/>
+    <row r="607" ht="15.0" customHeight="1"/>
+    <row r="608" ht="15.0" customHeight="1"/>
+    <row r="609" ht="15.0" customHeight="1"/>
+    <row r="610" ht="15.0" customHeight="1"/>
+    <row r="611" ht="15.0" customHeight="1"/>
+    <row r="612" ht="15.0" customHeight="1"/>
+    <row r="613" ht="15.0" customHeight="1"/>
+    <row r="614" ht="15.0" customHeight="1"/>
+    <row r="615" ht="15.0" customHeight="1"/>
+    <row r="616" ht="15.0" customHeight="1"/>
+    <row r="617" ht="15.0" customHeight="1"/>
+    <row r="618" ht="15.0" customHeight="1"/>
+    <row r="619" ht="15.0" customHeight="1"/>
+    <row r="620" ht="15.0" customHeight="1"/>
+    <row r="621" ht="15.0" customHeight="1"/>
+    <row r="622" ht="15.0" customHeight="1"/>
+    <row r="623" ht="15.0" customHeight="1"/>
+    <row r="624" ht="15.0" customHeight="1"/>
+    <row r="625" ht="15.0" customHeight="1"/>
+    <row r="626" ht="15.0" customHeight="1"/>
+    <row r="627" ht="15.0" customHeight="1"/>
+    <row r="628" ht="15.0" customHeight="1"/>
+    <row r="629" ht="15.0" customHeight="1"/>
+    <row r="630" ht="15.0" customHeight="1"/>
+    <row r="631" ht="15.0" customHeight="1"/>
+    <row r="632" ht="15.0" customHeight="1"/>
+    <row r="633" ht="15.0" customHeight="1"/>
+    <row r="634" ht="15.0" customHeight="1"/>
+    <row r="635" ht="15.0" customHeight="1"/>
+    <row r="636" ht="15.0" customHeight="1"/>
+    <row r="637" ht="15.0" customHeight="1"/>
+    <row r="638" ht="15.0" customHeight="1"/>
+    <row r="639" ht="15.0" customHeight="1"/>
+    <row r="640" ht="15.0" customHeight="1"/>
+    <row r="641" ht="15.0" customHeight="1"/>
+    <row r="642" ht="15.0" customHeight="1"/>
+    <row r="643" ht="15.0" customHeight="1"/>
+    <row r="644" ht="15.0" customHeight="1"/>
+    <row r="645" ht="15.0" customHeight="1"/>
+    <row r="646" ht="15.0" customHeight="1"/>
+    <row r="647" ht="15.0" customHeight="1"/>
+    <row r="648" ht="15.0" customHeight="1"/>
+    <row r="649" ht="15.0" customHeight="1"/>
+    <row r="650" ht="15.0" customHeight="1"/>
+    <row r="651" ht="15.0" customHeight="1"/>
+    <row r="652" ht="15.0" customHeight="1"/>
+    <row r="653" ht="15.0" customHeight="1"/>
+    <row r="654" ht="15.0" customHeight="1"/>
+    <row r="655" ht="15.0" customHeight="1"/>
+    <row r="656" ht="15.0" customHeight="1"/>
+    <row r="657" ht="15.0" customHeight="1"/>
+    <row r="658" ht="15.0" customHeight="1"/>
+    <row r="659" ht="15.0" customHeight="1"/>
+    <row r="660" ht="15.0" customHeight="1"/>
+    <row r="661" ht="15.0" customHeight="1"/>
+    <row r="662" ht="15.0" customHeight="1"/>
+    <row r="663" ht="15.0" customHeight="1"/>
+    <row r="664" ht="15.0" customHeight="1"/>
+    <row r="665" ht="15.0" customHeight="1"/>
+    <row r="666" ht="15.0" customHeight="1"/>
+    <row r="667" ht="15.0" customHeight="1"/>
+    <row r="668" ht="15.0" customHeight="1"/>
+    <row r="669" ht="15.0" customHeight="1"/>
+    <row r="670" ht="15.0" customHeight="1"/>
+    <row r="671" ht="15.0" customHeight="1"/>
+    <row r="672" ht="15.0" customHeight="1"/>
+    <row r="673" ht="15.0" customHeight="1"/>
+    <row r="674" ht="15.0" customHeight="1"/>
+    <row r="675" ht="15.0" customHeight="1"/>
+    <row r="676" ht="15.0" customHeight="1"/>
+    <row r="677" ht="15.0" customHeight="1"/>
+    <row r="678" ht="15.0" customHeight="1"/>
+    <row r="679" ht="15.0" customHeight="1"/>
+    <row r="680" ht="15.0" customHeight="1"/>
+    <row r="681" ht="15.0" customHeight="1"/>
+    <row r="682" ht="15.0" customHeight="1"/>
+    <row r="683" ht="15.0" customHeight="1"/>
+    <row r="684" ht="15.0" customHeight="1"/>
+    <row r="685" ht="15.0" customHeight="1"/>
+    <row r="686" ht="15.0" customHeight="1"/>
+    <row r="687" ht="15.0" customHeight="1"/>
+    <row r="688" ht="15.0" customHeight="1"/>
+    <row r="689" ht="15.0" customHeight="1"/>
+    <row r="690" ht="15.0" customHeight="1"/>
+    <row r="691" ht="15.0" customHeight="1"/>
+    <row r="692" ht="15.0" customHeight="1"/>
+    <row r="693" ht="15.0" customHeight="1"/>
+    <row r="694" ht="15.0" customHeight="1"/>
+    <row r="695" ht="15.0" customHeight="1"/>
+    <row r="696" ht="15.0" customHeight="1"/>
+    <row r="697" ht="15.0" customHeight="1"/>
+    <row r="698" ht="15.0" customHeight="1"/>
+    <row r="699" ht="15.0" customHeight="1"/>
+    <row r="700" ht="15.0" customHeight="1"/>
+    <row r="701" ht="15.0" customHeight="1"/>
+    <row r="702" ht="15.0" customHeight="1"/>
+    <row r="703" ht="15.0" customHeight="1"/>
+    <row r="704" ht="15.0" customHeight="1"/>
+    <row r="705" ht="15.0" customHeight="1"/>
+    <row r="706" ht="15.0" customHeight="1"/>
+    <row r="707" ht="15.0" customHeight="1"/>
+    <row r="708" ht="15.0" customHeight="1"/>
+    <row r="709" ht="15.0" customHeight="1"/>
+    <row r="710" ht="15.0" customHeight="1"/>
+    <row r="711" ht="15.0" customHeight="1"/>
+    <row r="712" ht="15.0" customHeight="1"/>
+    <row r="713" ht="15.0" customHeight="1"/>
+    <row r="714" ht="15.0" customHeight="1"/>
+    <row r="715" ht="15.0" customHeight="1"/>
+    <row r="716" ht="15.0" customHeight="1"/>
+    <row r="717" ht="15.0" customHeight="1"/>
+    <row r="718" ht="15.0" customHeight="1"/>
+    <row r="719" ht="15.0" customHeight="1"/>
+    <row r="720" ht="15.0" customHeight="1"/>
+    <row r="721" ht="15.0" customHeight="1"/>
+    <row r="722" ht="15.0" customHeight="1"/>
+    <row r="723" ht="15.0" customHeight="1"/>
+    <row r="724" ht="15.0" customHeight="1"/>
+    <row r="725" ht="15.0" customHeight="1"/>
+    <row r="726" ht="15.0" customHeight="1"/>
+    <row r="727" ht="15.0" customHeight="1"/>
+    <row r="728" ht="15.0" customHeight="1"/>
+    <row r="729" ht="15.0" customHeight="1"/>
+    <row r="730" ht="15.0" customHeight="1"/>
+    <row r="731" ht="15.0" customHeight="1"/>
+    <row r="732" ht="15.0" customHeight="1"/>
+    <row r="733" ht="15.0" customHeight="1"/>
+    <row r="734" ht="15.0" customHeight="1"/>
+    <row r="735" ht="15.0" customHeight="1"/>
+    <row r="736" ht="15.0" customHeight="1"/>
+    <row r="737" ht="15.0" customHeight="1"/>
+    <row r="738" ht="15.0" customHeight="1"/>
+    <row r="739" ht="15.0" customHeight="1"/>
+    <row r="740" ht="15.0" customHeight="1"/>
+    <row r="741" ht="15.0" customHeight="1"/>
+    <row r="742" ht="15.0" customHeight="1"/>
+    <row r="743" ht="15.0" customHeight="1"/>
+    <row r="744" ht="15.0" customHeight="1"/>
+    <row r="745" ht="15.0" customHeight="1"/>
+    <row r="746" ht="15.0" customHeight="1"/>
+    <row r="747" ht="15.0" customHeight="1"/>
+    <row r="748" ht="15.0" customHeight="1"/>
+    <row r="749" ht="15.0" customHeight="1"/>
+    <row r="750" ht="15.0" customHeight="1"/>
+    <row r="751" ht="15.0" customHeight="1"/>
+    <row r="752" ht="15.0" customHeight="1"/>
+    <row r="753" ht="15.0" customHeight="1"/>
+    <row r="754" ht="15.0" customHeight="1"/>
+    <row r="755" ht="15.0" customHeight="1"/>
+    <row r="756" ht="15.0" customHeight="1"/>
+    <row r="757" ht="15.0" customHeight="1"/>
+    <row r="758" ht="15.0" customHeight="1"/>
+    <row r="759" ht="15.0" customHeight="1"/>
+    <row r="760" ht="15.0" customHeight="1"/>
+    <row r="761" ht="15.0" customHeight="1"/>
+    <row r="762" ht="15.0" customHeight="1"/>
+    <row r="763" ht="15.0" customHeight="1"/>
+    <row r="764" ht="15.0" customHeight="1"/>
+    <row r="765" ht="15.0" customHeight="1"/>
+    <row r="766" ht="15.0" customHeight="1"/>
+    <row r="767" ht="15.0" customHeight="1"/>
+    <row r="768" ht="15.0" customHeight="1"/>
+    <row r="769" ht="15.0" customHeight="1"/>
+    <row r="770" ht="15.0" customHeight="1"/>
+    <row r="771" ht="15.0" customHeight="1"/>
+    <row r="772" ht="15.0" customHeight="1"/>
+    <row r="773" ht="15.0" customHeight="1"/>
+    <row r="774" ht="15.0" customHeight="1"/>
+    <row r="775" ht="15.0" customHeight="1"/>
+    <row r="776" ht="15.0" customHeight="1"/>
+    <row r="777" ht="15.0" customHeight="1"/>
+    <row r="778" ht="15.0" customHeight="1"/>
+    <row r="779" ht="15.0" customHeight="1"/>
+    <row r="780" ht="15.0" customHeight="1"/>
+    <row r="781" ht="15.0" customHeight="1"/>
+    <row r="782" ht="15.0" customHeight="1"/>
+    <row r="783" ht="15.0" customHeight="1"/>
+    <row r="784" ht="15.0" customHeight="1"/>
+    <row r="785" ht="15.0" customHeight="1"/>
+    <row r="786" ht="15.0" customHeight="1"/>
+    <row r="787" ht="15.0" customHeight="1"/>
+    <row r="788" ht="15.0" customHeight="1"/>
+    <row r="789" ht="15.0" customHeight="1"/>
+    <row r="790" ht="15.0" customHeight="1"/>
+    <row r="791" ht="15.0" customHeight="1"/>
+    <row r="792" ht="15.0" customHeight="1"/>
+    <row r="793" ht="15.0" customHeight="1"/>
+    <row r="794" ht="15.0" customHeight="1"/>
+    <row r="795" ht="15.0" customHeight="1"/>
+    <row r="796" ht="15.0" customHeight="1"/>
+    <row r="797" ht="15.0" customHeight="1"/>
+    <row r="798" ht="15.0" customHeight="1"/>
+    <row r="799" ht="15.0" customHeight="1"/>
+    <row r="800" ht="15.0" customHeight="1"/>
+    <row r="801" ht="15.0" customHeight="1"/>
+    <row r="802" ht="15.0" customHeight="1"/>
+    <row r="803" ht="15.0" customHeight="1"/>
+    <row r="804" ht="15.0" customHeight="1"/>
+    <row r="805" ht="15.0" customHeight="1"/>
+    <row r="806" ht="15.0" customHeight="1"/>
+    <row r="807" ht="15.0" customHeight="1"/>
+    <row r="808" ht="15.0" customHeight="1"/>
+    <row r="809" ht="15.0" customHeight="1"/>
+    <row r="810" ht="15.0" customHeight="1"/>
+    <row r="811" ht="15.0" customHeight="1"/>
+    <row r="812" ht="15.0" customHeight="1"/>
+    <row r="813" ht="15.0" customHeight="1"/>
+    <row r="814" ht="15.0" customHeight="1"/>
+    <row r="815" ht="15.0" customHeight="1"/>
+    <row r="816" ht="15.0" customHeight="1"/>
+    <row r="817" ht="15.0" customHeight="1"/>
+    <row r="818" ht="15.0" customHeight="1"/>
+    <row r="819" ht="15.0" customHeight="1"/>
+    <row r="820" ht="15.0" customHeight="1"/>
+    <row r="821" ht="15.0" customHeight="1"/>
+    <row r="822" ht="15.0" customHeight="1"/>
+    <row r="823" ht="15.0" customHeight="1"/>
+    <row r="824" ht="15.0" customHeight="1"/>
+    <row r="825" ht="15.0" customHeight="1"/>
+    <row r="826" ht="15.0" customHeight="1"/>
+    <row r="827" ht="15.0" customHeight="1"/>
+    <row r="828" ht="15.0" customHeight="1"/>
+    <row r="829" ht="15.0" customHeight="1"/>
+    <row r="830" ht="15.0" customHeight="1"/>
+    <row r="831" ht="15.0" customHeight="1"/>
+    <row r="832" ht="15.0" customHeight="1"/>
+    <row r="833" ht="15.0" customHeight="1"/>
+    <row r="834" ht="15.0" customHeight="1"/>
+    <row r="835" ht="15.0" customHeight="1"/>
+    <row r="836" ht="15.0" customHeight="1"/>
+    <row r="837" ht="15.0" customHeight="1"/>
+    <row r="838" ht="15.0" customHeight="1"/>
+    <row r="839" ht="15.0" customHeight="1"/>
+    <row r="840" ht="15.0" customHeight="1"/>
+    <row r="841" ht="15.0" customHeight="1"/>
+    <row r="842" ht="15.0" customHeight="1"/>
+    <row r="843" ht="15.0" customHeight="1"/>
+    <row r="844" ht="15.0" customHeight="1"/>
+    <row r="845" ht="15.0" customHeight="1"/>
+    <row r="846" ht="15.0" customHeight="1"/>
+    <row r="847" ht="15.0" customHeight="1"/>
+    <row r="848" ht="15.0" customHeight="1"/>
+    <row r="849" ht="15.0" customHeight="1"/>
+    <row r="850" ht="15.0" customHeight="1"/>
+    <row r="851" ht="15.0" customHeight="1"/>
+    <row r="852" ht="15.0" customHeight="1"/>
+    <row r="853" ht="15.0" customHeight="1"/>
+    <row r="854" ht="15.0" customHeight="1"/>
+    <row r="855" ht="15.0" customHeight="1"/>
+    <row r="856" ht="15.0" customHeight="1"/>
+    <row r="857" ht="15.0" customHeight="1"/>
+    <row r="858" ht="15.0" customHeight="1"/>
+    <row r="859" ht="15.0" customHeight="1"/>
+    <row r="860" ht="15.0" customHeight="1"/>
+    <row r="861" ht="15.0" customHeight="1"/>
+    <row r="862" ht="15.0" customHeight="1"/>
+    <row r="863" ht="15.0" customHeight="1"/>
+    <row r="864" ht="15.0" customHeight="1"/>
+    <row r="865" ht="15.0" customHeight="1"/>
+    <row r="866" ht="15.0" customHeight="1"/>
+    <row r="867" ht="15.0" customHeight="1"/>
+    <row r="868" ht="15.0" customHeight="1"/>
+    <row r="869" ht="15.0" customHeight="1"/>
+    <row r="870" ht="15.0" customHeight="1"/>
+    <row r="871" ht="15.0" customHeight="1"/>
+    <row r="872" ht="15.0" customHeight="1"/>
+    <row r="873" ht="15.0" customHeight="1"/>
+    <row r="874" ht="15.0" customHeight="1"/>
+    <row r="875" ht="15.0" customHeight="1"/>
+    <row r="876" ht="15.0" customHeight="1"/>
+    <row r="877" ht="15.0" customHeight="1"/>
+    <row r="878" ht="15.0" customHeight="1"/>
+    <row r="879" ht="15.0" customHeight="1"/>
+    <row r="880" ht="15.0" customHeight="1"/>
+    <row r="881" ht="15.0" customHeight="1"/>
+    <row r="882" ht="15.0" customHeight="1"/>
+    <row r="883" ht="15.0" customHeight="1"/>
+    <row r="884" ht="15.0" customHeight="1"/>
+    <row r="885" ht="15.0" customHeight="1"/>
+    <row r="886" ht="15.0" customHeight="1"/>
+    <row r="887" ht="15.0" customHeight="1"/>
+    <row r="888" ht="15.0" customHeight="1"/>
+    <row r="889" ht="15.0" customHeight="1"/>
+    <row r="890" ht="15.0" customHeight="1"/>
+    <row r="891" ht="15.0" customHeight="1"/>
+    <row r="892" ht="15.0" customHeight="1"/>
+    <row r="893" ht="15.0" customHeight="1"/>
+    <row r="894" ht="15.0" customHeight="1"/>
+    <row r="895" ht="15.0" customHeight="1"/>
+    <row r="896" ht="15.0" customHeight="1"/>
+    <row r="897" ht="15.0" customHeight="1"/>
+    <row r="898" ht="15.0" customHeight="1"/>
+    <row r="899" ht="15.0" customHeight="1"/>
+    <row r="900" ht="15.0" customHeight="1"/>
+    <row r="901" ht="15.0" customHeight="1"/>
+    <row r="902" ht="15.0" customHeight="1"/>
+    <row r="903" ht="15.0" customHeight="1"/>
+    <row r="904" ht="15.0" customHeight="1"/>
+    <row r="905" ht="15.0" customHeight="1"/>
+    <row r="906" ht="15.0" customHeight="1"/>
+    <row r="907" ht="15.0" customHeight="1"/>
+    <row r="908" ht="15.0" customHeight="1"/>
+    <row r="909" ht="15.0" customHeight="1"/>
+    <row r="910" ht="15.0" customHeight="1"/>
+    <row r="911" ht="15.0" customHeight="1"/>
+    <row r="912" ht="15.0" customHeight="1"/>
+    <row r="913" ht="15.0" customHeight="1"/>
+    <row r="914" ht="15.0" customHeight="1"/>
+    <row r="915" ht="15.0" customHeight="1"/>
+    <row r="916" ht="15.0" customHeight="1"/>
+    <row r="917" ht="15.0" customHeight="1"/>
+    <row r="918" ht="15.0" customHeight="1"/>
+    <row r="919" ht="15.0" customHeight="1"/>
+    <row r="920" ht="15.0" customHeight="1"/>
+    <row r="921" ht="15.0" customHeight="1"/>
+    <row r="922" ht="15.0" customHeight="1"/>
+    <row r="923" ht="15.0" customHeight="1"/>
+    <row r="924" ht="15.0" customHeight="1"/>
+    <row r="925" ht="15.0" customHeight="1"/>
+    <row r="926" ht="15.0" customHeight="1"/>
+    <row r="927" ht="15.0" customHeight="1"/>
+    <row r="928" ht="15.0" customHeight="1"/>
+    <row r="929" ht="15.0" customHeight="1"/>
+    <row r="930" ht="15.0" customHeight="1"/>
+    <row r="931" ht="15.0" customHeight="1"/>
+    <row r="932" ht="15.0" customHeight="1"/>
+    <row r="933" ht="15.0" customHeight="1"/>
+    <row r="934" ht="15.0" customHeight="1"/>
+    <row r="935" ht="15.0" customHeight="1"/>
+    <row r="936" ht="15.0" customHeight="1"/>
+    <row r="937" ht="15.0" customHeight="1"/>
+    <row r="938" ht="15.0" customHeight="1"/>
+    <row r="939" ht="15.0" customHeight="1"/>
+    <row r="940" ht="15.0" customHeight="1"/>
+    <row r="941" ht="15.0" customHeight="1"/>
+    <row r="942" ht="15.0" customHeight="1"/>
+    <row r="943" ht="15.0" customHeight="1"/>
+    <row r="944" ht="15.0" customHeight="1"/>
+    <row r="945" ht="15.0" customHeight="1"/>
+    <row r="946" ht="15.0" customHeight="1"/>
+    <row r="947" ht="15.0" customHeight="1"/>
+    <row r="948" ht="15.0" customHeight="1"/>
+    <row r="949" ht="15.0" customHeight="1"/>
+    <row r="950" ht="15.0" customHeight="1"/>
+    <row r="951" ht="15.0" customHeight="1"/>
+    <row r="952" ht="15.0" customHeight="1"/>
+    <row r="953" ht="15.0" customHeight="1"/>
+    <row r="954" ht="15.0" customHeight="1"/>
+    <row r="955" ht="15.0" customHeight="1"/>
+    <row r="956" ht="15.0" customHeight="1"/>
+    <row r="957" ht="15.0" customHeight="1"/>
+    <row r="958" ht="15.0" customHeight="1"/>
+    <row r="959" ht="15.0" customHeight="1"/>
+    <row r="960" ht="15.0" customHeight="1"/>
+    <row r="961" ht="15.0" customHeight="1"/>
+    <row r="962" ht="15.0" customHeight="1"/>
+    <row r="963" ht="15.0" customHeight="1"/>
+    <row r="964" ht="15.0" customHeight="1"/>
+    <row r="965" ht="15.0" customHeight="1"/>
+    <row r="966" ht="15.0" customHeight="1"/>
+    <row r="967" ht="15.0" customHeight="1"/>
+    <row r="968" ht="15.0" customHeight="1"/>
+    <row r="969" ht="15.0" customHeight="1"/>
+    <row r="970" ht="15.0" customHeight="1"/>
+    <row r="971" ht="15.0" customHeight="1"/>
+    <row r="972" ht="15.0" customHeight="1"/>
+    <row r="973" ht="15.0" customHeight="1"/>
+    <row r="974" ht="15.0" customHeight="1"/>
+    <row r="975" ht="15.0" customHeight="1"/>
+    <row r="976" ht="15.0" customHeight="1"/>
+    <row r="977" ht="15.0" customHeight="1"/>
+    <row r="978" ht="15.0" customHeight="1"/>
+    <row r="979" ht="15.0" customHeight="1"/>
+    <row r="980" ht="15.0" customHeight="1"/>
+    <row r="981" ht="15.0" customHeight="1"/>
+    <row r="982" ht="15.0" customHeight="1"/>
+    <row r="983" ht="15.0" customHeight="1"/>
+    <row r="984" ht="15.0" customHeight="1"/>
+    <row r="985" ht="15.0" customHeight="1"/>
+    <row r="986" ht="15.0" customHeight="1"/>
+    <row r="987" ht="15.0" customHeight="1"/>
+    <row r="988" ht="15.0" customHeight="1"/>
+    <row r="989" ht="15.0" customHeight="1"/>
+    <row r="990" ht="15.0" customHeight="1"/>
+    <row r="991" ht="15.0" customHeight="1"/>
+    <row r="992" ht="15.0" customHeight="1"/>
+    <row r="993" ht="15.0" customHeight="1"/>
+    <row r="994" ht="15.0" customHeight="1"/>
+    <row r="995" ht="15.0" customHeight="1"/>
+    <row r="996" ht="15.0" customHeight="1"/>
+    <row r="997" ht="15.0" customHeight="1"/>
+    <row r="998" ht="15.0" customHeight="1"/>
+    <row r="999" ht="15.0" customHeight="1"/>
+    <row r="1000" ht="15.0" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Templates/Tables/StringInfo/StrTable.xlsx
+++ b/Templates/Tables/StringInfo/StrTable.xlsx
@@ -986,13 +986,13 @@
       <name val="Arial"/>
     </font>
     <font>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1027,7 +1027,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="9">
     <border/>
     <border>
       <left style="thin">
@@ -1043,9 +1043,22 @@
       </top>
     </border>
     <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
     </border>
     <border>
       <left style="thin">
@@ -1060,11 +1073,19 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="35">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1078,7 +1099,8 @@
     <xf borderId="2" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="3" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="3" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1087,17 +1109,9 @@
     <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="5" fillId="3" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="5" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="5" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -1108,8 +1122,8 @@
     <xf borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="3" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="4" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1118,12 +1132,23 @@
     <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="5" fillId="4" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="2" fillId="5" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="5" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="6" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="7" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="7" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="8" fillId="4" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="5" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="3" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="5" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1132,15 +1157,16 @@
     <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="4" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="6" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="5" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="5" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="8" fillId="5" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1355,11 +1381,11 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="23.0"/>
-    <col customWidth="1" min="2" max="2" width="14.38"/>
+    <col customWidth="1" min="2" max="2" width="12.63"/>
     <col customWidth="1" min="3" max="3" width="32.63"/>
     <col customWidth="1" min="4" max="4" width="85.88"/>
     <col customWidth="1" min="5" max="5" width="98.0"/>
-    <col customWidth="1" min="6" max="25" width="14.38"/>
+    <col customWidth="1" min="6" max="26" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
@@ -1435,3018 +1461,3047 @@
       <c r="W2" s="4"/>
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
+      <c r="Z2" s="5"/>
     </row>
     <row r="3" ht="15.0" customHeight="1">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="7">
         <v>0.0</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
-      <c r="U3" s="7"/>
-      <c r="V3" s="7"/>
-      <c r="W3" s="7"/>
-      <c r="X3" s="7"/>
-      <c r="Y3" s="7"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
+      <c r="Q3" s="8"/>
+      <c r="R3" s="8"/>
+      <c r="S3" s="8"/>
+      <c r="T3" s="8"/>
+      <c r="U3" s="8"/>
+      <c r="V3" s="8"/>
+      <c r="W3" s="8"/>
+      <c r="X3" s="8"/>
+      <c r="Y3" s="8"/>
+      <c r="Z3" s="9"/>
     </row>
     <row r="4" ht="15.0" customHeight="1">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="7">
         <v>0.0</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="7"/>
-      <c r="T4" s="7"/>
-      <c r="U4" s="7"/>
-      <c r="V4" s="7"/>
-      <c r="W4" s="7"/>
-      <c r="X4" s="7"/>
-      <c r="Y4" s="7"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
+      <c r="Q4" s="8"/>
+      <c r="R4" s="8"/>
+      <c r="S4" s="8"/>
+      <c r="T4" s="8"/>
+      <c r="U4" s="8"/>
+      <c r="V4" s="8"/>
+      <c r="W4" s="8"/>
+      <c r="X4" s="8"/>
+      <c r="Y4" s="8"/>
+      <c r="Z4" s="9"/>
     </row>
     <row r="5" ht="15.0" customHeight="1">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="7">
         <v>0.0</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="7"/>
-      <c r="S5" s="7"/>
-      <c r="T5" s="7"/>
-      <c r="U5" s="7"/>
-      <c r="V5" s="7"/>
-      <c r="W5" s="7"/>
-      <c r="X5" s="7"/>
-      <c r="Y5" s="7"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
+      <c r="Q5" s="8"/>
+      <c r="R5" s="8"/>
+      <c r="S5" s="8"/>
+      <c r="T5" s="8"/>
+      <c r="U5" s="8"/>
+      <c r="V5" s="8"/>
+      <c r="W5" s="8"/>
+      <c r="X5" s="8"/>
+      <c r="Y5" s="8"/>
+      <c r="Z5" s="9"/>
     </row>
     <row r="6" ht="15.0" customHeight="1">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <v>0.0</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="7"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="7"/>
-      <c r="T6" s="7"/>
-      <c r="U6" s="7"/>
-      <c r="V6" s="7"/>
-      <c r="W6" s="7"/>
-      <c r="X6" s="7"/>
-      <c r="Y6" s="7"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="8"/>
+      <c r="Q6" s="8"/>
+      <c r="R6" s="8"/>
+      <c r="S6" s="8"/>
+      <c r="T6" s="8"/>
+      <c r="U6" s="8"/>
+      <c r="V6" s="8"/>
+      <c r="W6" s="8"/>
+      <c r="X6" s="8"/>
+      <c r="Y6" s="8"/>
+      <c r="Z6" s="9"/>
     </row>
     <row r="7" ht="15.0" customHeight="1">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="7">
         <v>0.0</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="7"/>
-      <c r="R7" s="7"/>
-      <c r="S7" s="7"/>
-      <c r="T7" s="7"/>
-      <c r="U7" s="7"/>
-      <c r="V7" s="7"/>
-      <c r="W7" s="7"/>
-      <c r="X7" s="7"/>
-      <c r="Y7" s="7"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+      <c r="S7" s="8"/>
+      <c r="T7" s="8"/>
+      <c r="U7" s="8"/>
+      <c r="V7" s="8"/>
+      <c r="W7" s="8"/>
+      <c r="X7" s="8"/>
+      <c r="Y7" s="8"/>
+      <c r="Z7" s="9"/>
     </row>
     <row r="8" ht="15.0" customHeight="1">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="7">
         <v>0.0</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
-      <c r="P8" s="7"/>
-      <c r="Q8" s="7"/>
-      <c r="R8" s="7"/>
-      <c r="S8" s="7"/>
-      <c r="T8" s="7"/>
-      <c r="U8" s="7"/>
-      <c r="V8" s="7"/>
-      <c r="W8" s="7"/>
-      <c r="X8" s="7"/>
-      <c r="Y8" s="7"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+      <c r="S8" s="8"/>
+      <c r="T8" s="8"/>
+      <c r="U8" s="8"/>
+      <c r="V8" s="8"/>
+      <c r="W8" s="8"/>
+      <c r="X8" s="8"/>
+      <c r="Y8" s="8"/>
+      <c r="Z8" s="9"/>
     </row>
     <row r="9" ht="15.0" customHeight="1">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="7">
         <v>0.0</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7"/>
-      <c r="P9" s="7"/>
-      <c r="Q9" s="7"/>
-      <c r="R9" s="7"/>
-      <c r="S9" s="7"/>
-      <c r="T9" s="7"/>
-      <c r="U9" s="7"/>
-      <c r="V9" s="7"/>
-      <c r="W9" s="7"/>
-      <c r="X9" s="7"/>
-      <c r="Y9" s="7"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="8"/>
+      <c r="S9" s="8"/>
+      <c r="T9" s="8"/>
+      <c r="U9" s="8"/>
+      <c r="V9" s="8"/>
+      <c r="W9" s="8"/>
+      <c r="X9" s="8"/>
+      <c r="Y9" s="8"/>
+      <c r="Z9" s="9"/>
     </row>
     <row r="10" ht="15.0" customHeight="1">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="7">
         <v>0.0</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
-      <c r="O10" s="7"/>
-      <c r="P10" s="7"/>
-      <c r="Q10" s="7"/>
-      <c r="R10" s="7"/>
-      <c r="S10" s="7"/>
-      <c r="T10" s="7"/>
-      <c r="U10" s="7"/>
-      <c r="V10" s="7"/>
-      <c r="W10" s="7"/>
-      <c r="X10" s="7"/>
-      <c r="Y10" s="7"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="8"/>
+      <c r="S10" s="8"/>
+      <c r="T10" s="8"/>
+      <c r="U10" s="8"/>
+      <c r="V10" s="8"/>
+      <c r="W10" s="8"/>
+      <c r="X10" s="8"/>
+      <c r="Y10" s="8"/>
+      <c r="Z10" s="9"/>
     </row>
     <row r="11" ht="15.0" customHeight="1">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="7">
         <v>0.0</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="7"/>
-      <c r="O11" s="7"/>
-      <c r="P11" s="7"/>
-      <c r="Q11" s="7"/>
-      <c r="R11" s="7"/>
-      <c r="S11" s="7"/>
-      <c r="T11" s="7"/>
-      <c r="U11" s="7"/>
-      <c r="V11" s="7"/>
-      <c r="W11" s="7"/>
-      <c r="X11" s="7"/>
-      <c r="Y11" s="7"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
+      <c r="Q11" s="8"/>
+      <c r="R11" s="8"/>
+      <c r="S11" s="8"/>
+      <c r="T11" s="8"/>
+      <c r="U11" s="8"/>
+      <c r="V11" s="8"/>
+      <c r="W11" s="8"/>
+      <c r="X11" s="8"/>
+      <c r="Y11" s="8"/>
+      <c r="Z11" s="9"/>
     </row>
     <row r="12" ht="15.0" customHeight="1">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="7">
         <v>0.0</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
-      <c r="P12" s="7"/>
-      <c r="Q12" s="7"/>
-      <c r="R12" s="7"/>
-      <c r="S12" s="7"/>
-      <c r="T12" s="7"/>
-      <c r="U12" s="7"/>
-      <c r="V12" s="7"/>
-      <c r="W12" s="7"/>
-      <c r="X12" s="7"/>
-      <c r="Y12" s="7"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
+      <c r="Q12" s="8"/>
+      <c r="R12" s="8"/>
+      <c r="S12" s="8"/>
+      <c r="T12" s="8"/>
+      <c r="U12" s="8"/>
+      <c r="V12" s="8"/>
+      <c r="W12" s="8"/>
+      <c r="X12" s="8"/>
+      <c r="Y12" s="8"/>
+      <c r="Z12" s="9"/>
     </row>
     <row r="13" ht="15.0" customHeight="1">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="7">
         <v>0.0</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="7"/>
-      <c r="R13" s="7"/>
-      <c r="S13" s="7"/>
-      <c r="T13" s="7"/>
-      <c r="U13" s="7"/>
-      <c r="V13" s="7"/>
-      <c r="W13" s="7"/>
-      <c r="X13" s="7"/>
-      <c r="Y13" s="7"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
+      <c r="Q13" s="8"/>
+      <c r="R13" s="8"/>
+      <c r="S13" s="8"/>
+      <c r="T13" s="8"/>
+      <c r="U13" s="8"/>
+      <c r="V13" s="8"/>
+      <c r="W13" s="8"/>
+      <c r="X13" s="8"/>
+      <c r="Y13" s="8"/>
+      <c r="Z13" s="9"/>
     </row>
     <row r="14" ht="15.0" customHeight="1">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="7">
         <v>0.0</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
-      <c r="O14" s="7"/>
-      <c r="P14" s="7"/>
-      <c r="Q14" s="7"/>
-      <c r="R14" s="7"/>
-      <c r="S14" s="7"/>
-      <c r="T14" s="7"/>
-      <c r="U14" s="7"/>
-      <c r="V14" s="7"/>
-      <c r="W14" s="7"/>
-      <c r="X14" s="7"/>
-      <c r="Y14" s="7"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8"/>
+      <c r="Q14" s="8"/>
+      <c r="R14" s="8"/>
+      <c r="S14" s="8"/>
+      <c r="T14" s="8"/>
+      <c r="U14" s="8"/>
+      <c r="V14" s="8"/>
+      <c r="W14" s="8"/>
+      <c r="X14" s="8"/>
+      <c r="Y14" s="8"/>
+      <c r="Z14" s="9"/>
     </row>
     <row r="15" ht="15.0" customHeight="1">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="7">
         <v>0.0</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
-      <c r="P15" s="7"/>
-      <c r="Q15" s="7"/>
-      <c r="R15" s="7"/>
-      <c r="S15" s="7"/>
-      <c r="T15" s="7"/>
-      <c r="U15" s="7"/>
-      <c r="V15" s="7"/>
-      <c r="W15" s="7"/>
-      <c r="X15" s="7"/>
-      <c r="Y15" s="7"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8"/>
+      <c r="O15" s="8"/>
+      <c r="P15" s="8"/>
+      <c r="Q15" s="8"/>
+      <c r="R15" s="8"/>
+      <c r="S15" s="8"/>
+      <c r="T15" s="8"/>
+      <c r="U15" s="8"/>
+      <c r="V15" s="8"/>
+      <c r="W15" s="8"/>
+      <c r="X15" s="8"/>
+      <c r="Y15" s="8"/>
+      <c r="Z15" s="9"/>
     </row>
     <row r="16" ht="15.0" customHeight="1">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="7">
         <v>0.0</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="7"/>
-      <c r="Q16" s="7"/>
-      <c r="R16" s="7"/>
-      <c r="S16" s="7"/>
-      <c r="T16" s="7"/>
-      <c r="U16" s="7"/>
-      <c r="V16" s="7"/>
-      <c r="W16" s="7"/>
-      <c r="X16" s="7"/>
-      <c r="Y16" s="7"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8"/>
+      <c r="Q16" s="8"/>
+      <c r="R16" s="8"/>
+      <c r="S16" s="8"/>
+      <c r="T16" s="8"/>
+      <c r="U16" s="8"/>
+      <c r="V16" s="8"/>
+      <c r="W16" s="8"/>
+      <c r="X16" s="8"/>
+      <c r="Y16" s="8"/>
+      <c r="Z16" s="9"/>
     </row>
     <row r="17" ht="15.0" customHeight="1">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="7">
         <v>0.0</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="7"/>
-      <c r="O17" s="7"/>
-      <c r="P17" s="7"/>
-      <c r="Q17" s="7"/>
-      <c r="R17" s="7"/>
-      <c r="S17" s="7"/>
-      <c r="T17" s="7"/>
-      <c r="U17" s="7"/>
-      <c r="V17" s="7"/>
-      <c r="W17" s="7"/>
-      <c r="X17" s="7"/>
-      <c r="Y17" s="7"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8"/>
+      <c r="P17" s="8"/>
+      <c r="Q17" s="8"/>
+      <c r="R17" s="8"/>
+      <c r="S17" s="8"/>
+      <c r="T17" s="8"/>
+      <c r="U17" s="8"/>
+      <c r="V17" s="8"/>
+      <c r="W17" s="8"/>
+      <c r="X17" s="8"/>
+      <c r="Y17" s="8"/>
+      <c r="Z17" s="9"/>
     </row>
     <row r="18" ht="15.0" customHeight="1">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B18" s="7">
         <v>0.0</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="7"/>
-      <c r="O18" s="7"/>
-      <c r="P18" s="7"/>
-      <c r="Q18" s="7"/>
-      <c r="R18" s="7"/>
-      <c r="S18" s="7"/>
-      <c r="T18" s="7"/>
-      <c r="U18" s="7"/>
-      <c r="V18" s="7"/>
-      <c r="W18" s="7"/>
-      <c r="X18" s="7"/>
-      <c r="Y18" s="7"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
+      <c r="O18" s="8"/>
+      <c r="P18" s="8"/>
+      <c r="Q18" s="8"/>
+      <c r="R18" s="8"/>
+      <c r="S18" s="8"/>
+      <c r="T18" s="8"/>
+      <c r="U18" s="8"/>
+      <c r="V18" s="8"/>
+      <c r="W18" s="8"/>
+      <c r="X18" s="8"/>
+      <c r="Y18" s="8"/>
+      <c r="Z18" s="9"/>
     </row>
     <row r="19" ht="15.0" customHeight="1">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="7">
         <v>0.0</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="E19" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="11"/>
-      <c r="O19" s="11"/>
-      <c r="P19" s="11"/>
-      <c r="Q19" s="11"/>
-      <c r="R19" s="11"/>
-      <c r="S19" s="11"/>
-      <c r="T19" s="11"/>
-      <c r="U19" s="11"/>
-      <c r="V19" s="11"/>
-      <c r="W19" s="11"/>
-      <c r="X19" s="11"/>
-      <c r="Y19" s="11"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="8"/>
+      <c r="P19" s="8"/>
+      <c r="Q19" s="8"/>
+      <c r="R19" s="8"/>
+      <c r="S19" s="8"/>
+      <c r="T19" s="8"/>
+      <c r="U19" s="8"/>
+      <c r="V19" s="8"/>
+      <c r="W19" s="8"/>
+      <c r="X19" s="8"/>
+      <c r="Y19" s="8"/>
+      <c r="Z19" s="9"/>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="B20" s="13">
+      <c r="B20" s="12">
         <v>0.0</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C20" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="D20" s="14" t="s">
+      <c r="D20" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="E20" s="14" t="s">
+      <c r="E20" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="14"/>
-      <c r="K20" s="14"/>
-      <c r="L20" s="14"/>
-      <c r="M20" s="14"/>
-      <c r="N20" s="14"/>
-      <c r="O20" s="14"/>
-      <c r="P20" s="14"/>
-      <c r="Q20" s="14"/>
-      <c r="R20" s="14"/>
-      <c r="S20" s="14"/>
-      <c r="T20" s="14"/>
-      <c r="U20" s="14"/>
-      <c r="V20" s="14"/>
-      <c r="W20" s="14"/>
-      <c r="X20" s="14"/>
-      <c r="Y20" s="14"/>
-      <c r="Z20" s="15"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="13"/>
+      <c r="L20" s="13"/>
+      <c r="M20" s="13"/>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13"/>
+      <c r="P20" s="13"/>
+      <c r="Q20" s="13"/>
+      <c r="R20" s="13"/>
+      <c r="S20" s="13"/>
+      <c r="T20" s="13"/>
+      <c r="U20" s="13"/>
+      <c r="V20" s="13"/>
+      <c r="W20" s="13"/>
+      <c r="X20" s="13"/>
+      <c r="Y20" s="13"/>
+      <c r="Z20" s="14"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="B21" s="17">
+      <c r="B21" s="16">
         <v>0.0</v>
       </c>
-      <c r="C21" s="18" t="s">
+      <c r="C21" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="D21" s="18" t="s">
+      <c r="D21" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="E21" s="18" t="s">
+      <c r="E21" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="18"/>
-      <c r="I21" s="18"/>
-      <c r="J21" s="18"/>
-      <c r="K21" s="18"/>
-      <c r="L21" s="18"/>
-      <c r="M21" s="18"/>
-      <c r="N21" s="18"/>
-      <c r="O21" s="18"/>
-      <c r="P21" s="18"/>
-      <c r="Q21" s="18"/>
-      <c r="R21" s="18"/>
-      <c r="S21" s="18"/>
-      <c r="T21" s="18"/>
-      <c r="U21" s="18"/>
-      <c r="V21" s="18"/>
-      <c r="W21" s="18"/>
-      <c r="X21" s="18"/>
-      <c r="Y21" s="18"/>
-      <c r="Z21" s="15"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="17"/>
+      <c r="M21" s="17"/>
+      <c r="N21" s="17"/>
+      <c r="O21" s="17"/>
+      <c r="P21" s="17"/>
+      <c r="Q21" s="17"/>
+      <c r="R21" s="17"/>
+      <c r="S21" s="17"/>
+      <c r="T21" s="17"/>
+      <c r="U21" s="17"/>
+      <c r="V21" s="17"/>
+      <c r="W21" s="17"/>
+      <c r="X21" s="17"/>
+      <c r="Y21" s="17"/>
+      <c r="Z21" s="18"/>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="16" t="s">
+      <c r="A22" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="B22" s="17">
+      <c r="B22" s="16">
         <v>0.0</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="D22" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="E22" s="18" t="s">
+      <c r="E22" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
-      <c r="I22" s="18"/>
-      <c r="J22" s="18"/>
-      <c r="K22" s="18"/>
-      <c r="L22" s="18"/>
-      <c r="M22" s="18"/>
-      <c r="N22" s="18"/>
-      <c r="O22" s="18"/>
-      <c r="P22" s="18"/>
-      <c r="Q22" s="18"/>
-      <c r="R22" s="18"/>
-      <c r="S22" s="18"/>
-      <c r="T22" s="18"/>
-      <c r="U22" s="18"/>
-      <c r="V22" s="18"/>
-      <c r="W22" s="18"/>
-      <c r="X22" s="18"/>
-      <c r="Y22" s="18"/>
-      <c r="Z22" s="15"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="17"/>
+      <c r="L22" s="17"/>
+      <c r="M22" s="17"/>
+      <c r="N22" s="17"/>
+      <c r="O22" s="17"/>
+      <c r="P22" s="17"/>
+      <c r="Q22" s="17"/>
+      <c r="R22" s="17"/>
+      <c r="S22" s="17"/>
+      <c r="T22" s="17"/>
+      <c r="U22" s="17"/>
+      <c r="V22" s="17"/>
+      <c r="W22" s="17"/>
+      <c r="X22" s="17"/>
+      <c r="Y22" s="17"/>
+      <c r="Z22" s="18"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="16" t="s">
+      <c r="A23" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="B23" s="17">
+      <c r="B23" s="16">
         <v>0.0</v>
       </c>
-      <c r="C23" s="18" t="s">
+      <c r="C23" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="D23" s="18" t="s">
+      <c r="D23" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="E23" s="18" t="s">
+      <c r="E23" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
-      <c r="I23" s="18"/>
-      <c r="J23" s="18"/>
-      <c r="K23" s="18"/>
-      <c r="L23" s="18"/>
-      <c r="M23" s="18"/>
-      <c r="N23" s="18"/>
-      <c r="O23" s="18"/>
-      <c r="P23" s="18"/>
-      <c r="Q23" s="18"/>
-      <c r="R23" s="18"/>
-      <c r="S23" s="18"/>
-      <c r="T23" s="18"/>
-      <c r="U23" s="18"/>
-      <c r="V23" s="18"/>
-      <c r="W23" s="18"/>
-      <c r="X23" s="18"/>
-      <c r="Y23" s="18"/>
-      <c r="Z23" s="15"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="17"/>
+      <c r="M23" s="17"/>
+      <c r="N23" s="17"/>
+      <c r="O23" s="17"/>
+      <c r="P23" s="17"/>
+      <c r="Q23" s="17"/>
+      <c r="R23" s="17"/>
+      <c r="S23" s="17"/>
+      <c r="T23" s="17"/>
+      <c r="U23" s="17"/>
+      <c r="V23" s="17"/>
+      <c r="W23" s="17"/>
+      <c r="X23" s="17"/>
+      <c r="Y23" s="17"/>
+      <c r="Z23" s="18"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="B24" s="17">
+      <c r="B24" s="16">
         <v>0.0</v>
       </c>
-      <c r="C24" s="18" t="s">
+      <c r="C24" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="D24" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="E24" s="18" t="s">
+      <c r="E24" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18"/>
-      <c r="I24" s="18"/>
-      <c r="J24" s="18"/>
-      <c r="K24" s="18"/>
-      <c r="L24" s="18"/>
-      <c r="M24" s="18"/>
-      <c r="N24" s="18"/>
-      <c r="O24" s="18"/>
-      <c r="P24" s="18"/>
-      <c r="Q24" s="18"/>
-      <c r="R24" s="18"/>
-      <c r="S24" s="18"/>
-      <c r="T24" s="18"/>
-      <c r="U24" s="18"/>
-      <c r="V24" s="18"/>
-      <c r="W24" s="18"/>
-      <c r="X24" s="18"/>
-      <c r="Y24" s="18"/>
-      <c r="Z24" s="15"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="17"/>
+      <c r="L24" s="17"/>
+      <c r="M24" s="17"/>
+      <c r="N24" s="17"/>
+      <c r="O24" s="17"/>
+      <c r="P24" s="17"/>
+      <c r="Q24" s="17"/>
+      <c r="R24" s="17"/>
+      <c r="S24" s="17"/>
+      <c r="T24" s="17"/>
+      <c r="U24" s="17"/>
+      <c r="V24" s="17"/>
+      <c r="W24" s="17"/>
+      <c r="X24" s="17"/>
+      <c r="Y24" s="17"/>
+      <c r="Z24" s="18"/>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="16" t="s">
+      <c r="A25" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="B25" s="17">
+      <c r="B25" s="16">
         <v>0.0</v>
       </c>
-      <c r="C25" s="18" t="s">
+      <c r="C25" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="D25" s="18" t="s">
+      <c r="D25" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="E25" s="18" t="s">
+      <c r="E25" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="18"/>
-      <c r="I25" s="18"/>
-      <c r="J25" s="18"/>
-      <c r="K25" s="18"/>
-      <c r="L25" s="18"/>
-      <c r="M25" s="18"/>
-      <c r="N25" s="18"/>
-      <c r="O25" s="18"/>
-      <c r="P25" s="18"/>
-      <c r="Q25" s="18"/>
-      <c r="R25" s="18"/>
-      <c r="S25" s="18"/>
-      <c r="T25" s="18"/>
-      <c r="U25" s="18"/>
-      <c r="V25" s="18"/>
-      <c r="W25" s="18"/>
-      <c r="X25" s="18"/>
-      <c r="Y25" s="18"/>
-      <c r="Z25" s="15"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="17"/>
+      <c r="L25" s="17"/>
+      <c r="M25" s="17"/>
+      <c r="N25" s="17"/>
+      <c r="O25" s="17"/>
+      <c r="P25" s="17"/>
+      <c r="Q25" s="17"/>
+      <c r="R25" s="17"/>
+      <c r="S25" s="17"/>
+      <c r="T25" s="17"/>
+      <c r="U25" s="17"/>
+      <c r="V25" s="17"/>
+      <c r="W25" s="17"/>
+      <c r="X25" s="17"/>
+      <c r="Y25" s="17"/>
+      <c r="Z25" s="18"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="16" t="s">
+      <c r="A26" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="B26" s="17">
+      <c r="B26" s="16">
         <v>0.0</v>
       </c>
-      <c r="C26" s="18" t="s">
+      <c r="C26" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="D26" s="18" t="s">
+      <c r="D26" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="E26" s="18" t="s">
+      <c r="E26" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="18"/>
-      <c r="I26" s="18"/>
-      <c r="J26" s="18"/>
-      <c r="K26" s="18"/>
-      <c r="L26" s="18"/>
-      <c r="M26" s="18"/>
-      <c r="N26" s="18"/>
-      <c r="O26" s="18"/>
-      <c r="P26" s="18"/>
-      <c r="Q26" s="18"/>
-      <c r="R26" s="18"/>
-      <c r="S26" s="18"/>
-      <c r="T26" s="18"/>
-      <c r="U26" s="18"/>
-      <c r="V26" s="18"/>
-      <c r="W26" s="18"/>
-      <c r="X26" s="18"/>
-      <c r="Y26" s="18"/>
-      <c r="Z26" s="15"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="17"/>
+      <c r="L26" s="17"/>
+      <c r="M26" s="17"/>
+      <c r="N26" s="17"/>
+      <c r="O26" s="17"/>
+      <c r="P26" s="17"/>
+      <c r="Q26" s="17"/>
+      <c r="R26" s="17"/>
+      <c r="S26" s="17"/>
+      <c r="T26" s="17"/>
+      <c r="U26" s="17"/>
+      <c r="V26" s="17"/>
+      <c r="W26" s="17"/>
+      <c r="X26" s="17"/>
+      <c r="Y26" s="17"/>
+      <c r="Z26" s="18"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="16" t="s">
+      <c r="A27" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="B27" s="17">
+      <c r="B27" s="16">
         <v>0.0</v>
       </c>
-      <c r="C27" s="18" t="s">
+      <c r="C27" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="D27" s="18" t="s">
+      <c r="D27" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="E27" s="18" t="s">
+      <c r="E27" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="18"/>
-      <c r="I27" s="18"/>
-      <c r="J27" s="18"/>
-      <c r="K27" s="18"/>
-      <c r="L27" s="18"/>
-      <c r="M27" s="18"/>
-      <c r="N27" s="18"/>
-      <c r="O27" s="18"/>
-      <c r="P27" s="18"/>
-      <c r="Q27" s="18"/>
-      <c r="R27" s="18"/>
-      <c r="S27" s="18"/>
-      <c r="T27" s="18"/>
-      <c r="U27" s="18"/>
-      <c r="V27" s="18"/>
-      <c r="W27" s="18"/>
-      <c r="X27" s="18"/>
-      <c r="Y27" s="18"/>
-      <c r="Z27" s="15"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="17"/>
+      <c r="L27" s="17"/>
+      <c r="M27" s="17"/>
+      <c r="N27" s="17"/>
+      <c r="O27" s="17"/>
+      <c r="P27" s="17"/>
+      <c r="Q27" s="17"/>
+      <c r="R27" s="17"/>
+      <c r="S27" s="17"/>
+      <c r="T27" s="17"/>
+      <c r="U27" s="17"/>
+      <c r="V27" s="17"/>
+      <c r="W27" s="17"/>
+      <c r="X27" s="17"/>
+      <c r="Y27" s="17"/>
+      <c r="Z27" s="18"/>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="16" t="s">
+      <c r="A28" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="B28" s="17">
+      <c r="B28" s="16">
         <v>0.0</v>
       </c>
-      <c r="C28" s="18" t="s">
+      <c r="C28" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="D28" s="18" t="s">
+      <c r="D28" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="E28" s="18" t="s">
+      <c r="E28" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="18"/>
-      <c r="I28" s="18"/>
-      <c r="J28" s="18"/>
-      <c r="K28" s="18"/>
-      <c r="L28" s="18"/>
-      <c r="M28" s="18"/>
-      <c r="N28" s="18"/>
-      <c r="O28" s="18"/>
-      <c r="P28" s="18"/>
-      <c r="Q28" s="18"/>
-      <c r="R28" s="18"/>
-      <c r="S28" s="18"/>
-      <c r="T28" s="18"/>
-      <c r="U28" s="18"/>
-      <c r="V28" s="18"/>
-      <c r="W28" s="18"/>
-      <c r="X28" s="18"/>
-      <c r="Y28" s="18"/>
-      <c r="Z28" s="15"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="17"/>
+      <c r="M28" s="17"/>
+      <c r="N28" s="17"/>
+      <c r="O28" s="17"/>
+      <c r="P28" s="17"/>
+      <c r="Q28" s="17"/>
+      <c r="R28" s="17"/>
+      <c r="S28" s="17"/>
+      <c r="T28" s="17"/>
+      <c r="U28" s="17"/>
+      <c r="V28" s="17"/>
+      <c r="W28" s="17"/>
+      <c r="X28" s="17"/>
+      <c r="Y28" s="17"/>
+      <c r="Z28" s="18"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="16" t="s">
+      <c r="A29" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="B29" s="17">
+      <c r="B29" s="16">
         <v>0.0</v>
       </c>
-      <c r="C29" s="18" t="s">
+      <c r="C29" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="D29" s="18" t="s">
+      <c r="D29" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="E29" s="18" t="s">
+      <c r="E29" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="18"/>
-      <c r="I29" s="18"/>
-      <c r="J29" s="18"/>
-      <c r="K29" s="18"/>
-      <c r="L29" s="18"/>
-      <c r="M29" s="18"/>
-      <c r="N29" s="18"/>
-      <c r="O29" s="18"/>
-      <c r="P29" s="18"/>
-      <c r="Q29" s="18"/>
-      <c r="R29" s="18"/>
-      <c r="S29" s="18"/>
-      <c r="T29" s="18"/>
-      <c r="U29" s="18"/>
-      <c r="V29" s="18"/>
-      <c r="W29" s="18"/>
-      <c r="X29" s="18"/>
-      <c r="Y29" s="18"/>
-      <c r="Z29" s="15"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="17"/>
+      <c r="J29" s="17"/>
+      <c r="K29" s="17"/>
+      <c r="L29" s="17"/>
+      <c r="M29" s="17"/>
+      <c r="N29" s="17"/>
+      <c r="O29" s="17"/>
+      <c r="P29" s="17"/>
+      <c r="Q29" s="17"/>
+      <c r="R29" s="17"/>
+      <c r="S29" s="17"/>
+      <c r="T29" s="17"/>
+      <c r="U29" s="17"/>
+      <c r="V29" s="17"/>
+      <c r="W29" s="17"/>
+      <c r="X29" s="17"/>
+      <c r="Y29" s="17"/>
+      <c r="Z29" s="18"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="16" t="s">
+      <c r="A30" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="B30" s="17">
+      <c r="B30" s="16">
         <v>0.0</v>
       </c>
-      <c r="C30" s="18" t="s">
+      <c r="C30" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="D30" s="18" t="s">
+      <c r="D30" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="E30" s="18" t="s">
+      <c r="E30" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="18"/>
-      <c r="I30" s="18"/>
-      <c r="J30" s="18"/>
-      <c r="K30" s="18"/>
-      <c r="L30" s="18"/>
-      <c r="M30" s="18"/>
-      <c r="N30" s="18"/>
-      <c r="O30" s="18"/>
-      <c r="P30" s="18"/>
-      <c r="Q30" s="18"/>
-      <c r="R30" s="18"/>
-      <c r="S30" s="18"/>
-      <c r="T30" s="18"/>
-      <c r="U30" s="18"/>
-      <c r="V30" s="18"/>
-      <c r="W30" s="18"/>
-      <c r="X30" s="18"/>
-      <c r="Y30" s="18"/>
-      <c r="Z30" s="15"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="17"/>
+      <c r="I30" s="17"/>
+      <c r="J30" s="17"/>
+      <c r="K30" s="17"/>
+      <c r="L30" s="17"/>
+      <c r="M30" s="17"/>
+      <c r="N30" s="17"/>
+      <c r="O30" s="17"/>
+      <c r="P30" s="17"/>
+      <c r="Q30" s="17"/>
+      <c r="R30" s="17"/>
+      <c r="S30" s="17"/>
+      <c r="T30" s="17"/>
+      <c r="U30" s="17"/>
+      <c r="V30" s="17"/>
+      <c r="W30" s="17"/>
+      <c r="X30" s="17"/>
+      <c r="Y30" s="17"/>
+      <c r="Z30" s="18"/>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="16" t="s">
+      <c r="A31" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="B31" s="17">
+      <c r="B31" s="16">
         <v>0.0</v>
       </c>
-      <c r="C31" s="18" t="s">
+      <c r="C31" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="D31" s="18" t="s">
+      <c r="D31" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="E31" s="18" t="s">
+      <c r="E31" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="18"/>
-      <c r="I31" s="18"/>
-      <c r="J31" s="18"/>
-      <c r="K31" s="18"/>
-      <c r="L31" s="18"/>
-      <c r="M31" s="18"/>
-      <c r="N31" s="18"/>
-      <c r="O31" s="18"/>
-      <c r="P31" s="18"/>
-      <c r="Q31" s="18"/>
-      <c r="R31" s="18"/>
-      <c r="S31" s="18"/>
-      <c r="T31" s="18"/>
-      <c r="U31" s="18"/>
-      <c r="V31" s="18"/>
-      <c r="W31" s="18"/>
-      <c r="X31" s="18"/>
-      <c r="Y31" s="18"/>
-      <c r="Z31" s="15"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17"/>
+      <c r="J31" s="17"/>
+      <c r="K31" s="17"/>
+      <c r="L31" s="17"/>
+      <c r="M31" s="17"/>
+      <c r="N31" s="17"/>
+      <c r="O31" s="17"/>
+      <c r="P31" s="17"/>
+      <c r="Q31" s="17"/>
+      <c r="R31" s="17"/>
+      <c r="S31" s="17"/>
+      <c r="T31" s="17"/>
+      <c r="U31" s="17"/>
+      <c r="V31" s="17"/>
+      <c r="W31" s="17"/>
+      <c r="X31" s="17"/>
+      <c r="Y31" s="17"/>
+      <c r="Z31" s="18"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="16" t="s">
+      <c r="A32" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="B32" s="17">
+      <c r="B32" s="16">
         <v>0.0</v>
       </c>
-      <c r="C32" s="18" t="s">
+      <c r="C32" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="D32" s="18" t="s">
+      <c r="D32" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="E32" s="18" t="s">
+      <c r="E32" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="18"/>
-      <c r="J32" s="18"/>
-      <c r="K32" s="18"/>
-      <c r="L32" s="18"/>
-      <c r="M32" s="18"/>
-      <c r="N32" s="18"/>
-      <c r="O32" s="18"/>
-      <c r="P32" s="18"/>
-      <c r="Q32" s="18"/>
-      <c r="R32" s="18"/>
-      <c r="S32" s="18"/>
-      <c r="T32" s="18"/>
-      <c r="U32" s="18"/>
-      <c r="V32" s="18"/>
-      <c r="W32" s="18"/>
-      <c r="X32" s="18"/>
-      <c r="Y32" s="18"/>
-      <c r="Z32" s="15"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="17"/>
+      <c r="J32" s="17"/>
+      <c r="K32" s="17"/>
+      <c r="L32" s="17"/>
+      <c r="M32" s="17"/>
+      <c r="N32" s="17"/>
+      <c r="O32" s="17"/>
+      <c r="P32" s="17"/>
+      <c r="Q32" s="17"/>
+      <c r="R32" s="17"/>
+      <c r="S32" s="17"/>
+      <c r="T32" s="17"/>
+      <c r="U32" s="17"/>
+      <c r="V32" s="17"/>
+      <c r="W32" s="17"/>
+      <c r="X32" s="17"/>
+      <c r="Y32" s="17"/>
+      <c r="Z32" s="18"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="16" t="s">
+      <c r="A33" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="B33" s="17">
+      <c r="B33" s="16">
         <v>0.0</v>
       </c>
-      <c r="C33" s="18" t="s">
+      <c r="C33" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="D33" s="18" t="s">
+      <c r="D33" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="18" t="s">
+      <c r="E33" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="18"/>
-      <c r="I33" s="18"/>
-      <c r="J33" s="18"/>
-      <c r="K33" s="18"/>
-      <c r="L33" s="18"/>
-      <c r="M33" s="18"/>
-      <c r="N33" s="18"/>
-      <c r="O33" s="18"/>
-      <c r="P33" s="18"/>
-      <c r="Q33" s="18"/>
-      <c r="R33" s="18"/>
-      <c r="S33" s="18"/>
-      <c r="T33" s="18"/>
-      <c r="U33" s="18"/>
-      <c r="V33" s="18"/>
-      <c r="W33" s="18"/>
-      <c r="X33" s="18"/>
-      <c r="Y33" s="18"/>
-      <c r="Z33" s="15"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="17"/>
+      <c r="I33" s="17"/>
+      <c r="J33" s="17"/>
+      <c r="K33" s="17"/>
+      <c r="L33" s="17"/>
+      <c r="M33" s="17"/>
+      <c r="N33" s="17"/>
+      <c r="O33" s="17"/>
+      <c r="P33" s="17"/>
+      <c r="Q33" s="17"/>
+      <c r="R33" s="17"/>
+      <c r="S33" s="17"/>
+      <c r="T33" s="17"/>
+      <c r="U33" s="17"/>
+      <c r="V33" s="17"/>
+      <c r="W33" s="17"/>
+      <c r="X33" s="17"/>
+      <c r="Y33" s="17"/>
+      <c r="Z33" s="18"/>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="16" t="s">
+      <c r="A34" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="B34" s="17">
+      <c r="B34" s="16">
         <v>0.0</v>
       </c>
-      <c r="C34" s="18" t="s">
+      <c r="C34" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="D34" s="18" t="s">
+      <c r="D34" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="E34" s="18" t="s">
+      <c r="E34" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="18"/>
-      <c r="I34" s="18"/>
-      <c r="J34" s="18"/>
-      <c r="K34" s="18"/>
-      <c r="L34" s="18"/>
-      <c r="M34" s="18"/>
-      <c r="N34" s="18"/>
-      <c r="O34" s="18"/>
-      <c r="P34" s="18"/>
-      <c r="Q34" s="18"/>
-      <c r="R34" s="18"/>
-      <c r="S34" s="18"/>
-      <c r="T34" s="18"/>
-      <c r="U34" s="18"/>
-      <c r="V34" s="18"/>
-      <c r="W34" s="18"/>
-      <c r="X34" s="18"/>
-      <c r="Y34" s="18"/>
-      <c r="Z34" s="15"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="17"/>
+      <c r="I34" s="17"/>
+      <c r="J34" s="17"/>
+      <c r="K34" s="17"/>
+      <c r="L34" s="17"/>
+      <c r="M34" s="17"/>
+      <c r="N34" s="17"/>
+      <c r="O34" s="17"/>
+      <c r="P34" s="17"/>
+      <c r="Q34" s="17"/>
+      <c r="R34" s="17"/>
+      <c r="S34" s="17"/>
+      <c r="T34" s="17"/>
+      <c r="U34" s="17"/>
+      <c r="V34" s="17"/>
+      <c r="W34" s="17"/>
+      <c r="X34" s="17"/>
+      <c r="Y34" s="17"/>
+      <c r="Z34" s="18"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="16" t="s">
+      <c r="A35" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="B35" s="17">
+      <c r="B35" s="16">
         <v>0.0</v>
       </c>
-      <c r="C35" s="18" t="s">
+      <c r="C35" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D35" s="18" t="s">
+      <c r="D35" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="E35" s="18" t="s">
+      <c r="E35" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="F35" s="18"/>
-      <c r="G35" s="18"/>
-      <c r="H35" s="18"/>
-      <c r="I35" s="18"/>
-      <c r="J35" s="18"/>
-      <c r="K35" s="18"/>
-      <c r="L35" s="18"/>
-      <c r="M35" s="18"/>
-      <c r="N35" s="18"/>
-      <c r="O35" s="18"/>
-      <c r="P35" s="18"/>
-      <c r="Q35" s="18"/>
-      <c r="R35" s="18"/>
-      <c r="S35" s="18"/>
-      <c r="T35" s="18"/>
-      <c r="U35" s="18"/>
-      <c r="V35" s="18"/>
-      <c r="W35" s="18"/>
-      <c r="X35" s="18"/>
-      <c r="Y35" s="18"/>
-      <c r="Z35" s="15"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="17"/>
+      <c r="I35" s="17"/>
+      <c r="J35" s="17"/>
+      <c r="K35" s="17"/>
+      <c r="L35" s="17"/>
+      <c r="M35" s="17"/>
+      <c r="N35" s="17"/>
+      <c r="O35" s="17"/>
+      <c r="P35" s="17"/>
+      <c r="Q35" s="17"/>
+      <c r="R35" s="17"/>
+      <c r="S35" s="17"/>
+      <c r="T35" s="17"/>
+      <c r="U35" s="17"/>
+      <c r="V35" s="17"/>
+      <c r="W35" s="17"/>
+      <c r="X35" s="17"/>
+      <c r="Y35" s="17"/>
+      <c r="Z35" s="18"/>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="16" t="s">
+      <c r="A36" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="B36" s="17">
+      <c r="B36" s="16">
         <v>0.0</v>
       </c>
-      <c r="C36" s="18" t="s">
+      <c r="C36" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="D36" s="18" t="s">
+      <c r="D36" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="E36" s="18" t="s">
+      <c r="E36" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="F36" s="18"/>
-      <c r="G36" s="18"/>
-      <c r="H36" s="18"/>
-      <c r="I36" s="18"/>
-      <c r="J36" s="18"/>
-      <c r="K36" s="18"/>
-      <c r="L36" s="18"/>
-      <c r="M36" s="18"/>
-      <c r="N36" s="18"/>
-      <c r="O36" s="18"/>
-      <c r="P36" s="18"/>
-      <c r="Q36" s="18"/>
-      <c r="R36" s="18"/>
-      <c r="S36" s="18"/>
-      <c r="T36" s="18"/>
-      <c r="U36" s="18"/>
-      <c r="V36" s="18"/>
-      <c r="W36" s="18"/>
-      <c r="X36" s="18"/>
-      <c r="Y36" s="18"/>
-      <c r="Z36" s="15"/>
+      <c r="F36" s="17"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="17"/>
+      <c r="I36" s="17"/>
+      <c r="J36" s="17"/>
+      <c r="K36" s="17"/>
+      <c r="L36" s="17"/>
+      <c r="M36" s="17"/>
+      <c r="N36" s="17"/>
+      <c r="O36" s="17"/>
+      <c r="P36" s="17"/>
+      <c r="Q36" s="17"/>
+      <c r="R36" s="17"/>
+      <c r="S36" s="17"/>
+      <c r="T36" s="17"/>
+      <c r="U36" s="17"/>
+      <c r="V36" s="17"/>
+      <c r="W36" s="17"/>
+      <c r="X36" s="17"/>
+      <c r="Y36" s="17"/>
+      <c r="Z36" s="18"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="16" t="s">
+      <c r="A37" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="B37" s="17">
+      <c r="B37" s="16">
         <v>0.0</v>
       </c>
-      <c r="C37" s="18" t="s">
+      <c r="C37" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="D37" s="18" t="s">
+      <c r="D37" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="E37" s="18" t="s">
+      <c r="E37" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="F37" s="18"/>
-      <c r="G37" s="18"/>
-      <c r="H37" s="18"/>
-      <c r="I37" s="18"/>
-      <c r="J37" s="18"/>
-      <c r="K37" s="18"/>
-      <c r="L37" s="18"/>
-      <c r="M37" s="18"/>
-      <c r="N37" s="18"/>
-      <c r="O37" s="18"/>
-      <c r="P37" s="18"/>
-      <c r="Q37" s="18"/>
-      <c r="R37" s="18"/>
-      <c r="S37" s="18"/>
-      <c r="T37" s="18"/>
-      <c r="U37" s="18"/>
-      <c r="V37" s="18"/>
-      <c r="W37" s="18"/>
-      <c r="X37" s="18"/>
-      <c r="Y37" s="18"/>
-      <c r="Z37" s="15"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="17"/>
+      <c r="I37" s="17"/>
+      <c r="J37" s="17"/>
+      <c r="K37" s="17"/>
+      <c r="L37" s="17"/>
+      <c r="M37" s="17"/>
+      <c r="N37" s="17"/>
+      <c r="O37" s="17"/>
+      <c r="P37" s="17"/>
+      <c r="Q37" s="17"/>
+      <c r="R37" s="17"/>
+      <c r="S37" s="17"/>
+      <c r="T37" s="17"/>
+      <c r="U37" s="17"/>
+      <c r="V37" s="17"/>
+      <c r="W37" s="17"/>
+      <c r="X37" s="17"/>
+      <c r="Y37" s="17"/>
+      <c r="Z37" s="18"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="16" t="s">
+      <c r="A38" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="B38" s="17">
+      <c r="B38" s="16">
         <v>0.0</v>
       </c>
-      <c r="C38" s="18" t="s">
+      <c r="C38" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="D38" s="18" t="s">
+      <c r="D38" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="E38" s="18" t="s">
+      <c r="E38" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="F38" s="18"/>
-      <c r="G38" s="18"/>
-      <c r="H38" s="18"/>
-      <c r="I38" s="18"/>
-      <c r="J38" s="18"/>
-      <c r="K38" s="18"/>
-      <c r="L38" s="18"/>
-      <c r="M38" s="18"/>
-      <c r="N38" s="18"/>
-      <c r="O38" s="18"/>
-      <c r="P38" s="18"/>
-      <c r="Q38" s="18"/>
-      <c r="R38" s="18"/>
-      <c r="S38" s="18"/>
-      <c r="T38" s="18"/>
-      <c r="U38" s="18"/>
-      <c r="V38" s="18"/>
-      <c r="W38" s="18"/>
-      <c r="X38" s="18"/>
-      <c r="Y38" s="18"/>
-      <c r="Z38" s="15"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="17"/>
+      <c r="I38" s="17"/>
+      <c r="J38" s="17"/>
+      <c r="K38" s="17"/>
+      <c r="L38" s="17"/>
+      <c r="M38" s="17"/>
+      <c r="N38" s="17"/>
+      <c r="O38" s="17"/>
+      <c r="P38" s="17"/>
+      <c r="Q38" s="17"/>
+      <c r="R38" s="17"/>
+      <c r="S38" s="17"/>
+      <c r="T38" s="17"/>
+      <c r="U38" s="17"/>
+      <c r="V38" s="17"/>
+      <c r="W38" s="17"/>
+      <c r="X38" s="17"/>
+      <c r="Y38" s="17"/>
+      <c r="Z38" s="18"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="16" t="s">
+      <c r="A39" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="B39" s="17">
+      <c r="B39" s="16">
         <v>0.0</v>
       </c>
-      <c r="C39" s="18" t="s">
+      <c r="C39" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="D39" s="18" t="s">
+      <c r="D39" s="17" t="s">
         <v>155</v>
       </c>
-      <c r="E39" s="18" t="s">
+      <c r="E39" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="F39" s="18"/>
-      <c r="G39" s="18"/>
-      <c r="H39" s="18"/>
-      <c r="I39" s="18"/>
-      <c r="J39" s="18"/>
-      <c r="K39" s="18"/>
-      <c r="L39" s="18"/>
-      <c r="M39" s="18"/>
-      <c r="N39" s="18"/>
-      <c r="O39" s="18"/>
-      <c r="P39" s="18"/>
-      <c r="Q39" s="18"/>
-      <c r="R39" s="18"/>
-      <c r="S39" s="18"/>
-      <c r="T39" s="18"/>
-      <c r="U39" s="18"/>
-      <c r="V39" s="18"/>
-      <c r="W39" s="18"/>
-      <c r="X39" s="18"/>
-      <c r="Y39" s="18"/>
-      <c r="Z39" s="15"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="17"/>
+      <c r="I39" s="17"/>
+      <c r="J39" s="17"/>
+      <c r="K39" s="17"/>
+      <c r="L39" s="17"/>
+      <c r="M39" s="17"/>
+      <c r="N39" s="17"/>
+      <c r="O39" s="17"/>
+      <c r="P39" s="17"/>
+      <c r="Q39" s="17"/>
+      <c r="R39" s="17"/>
+      <c r="S39" s="17"/>
+      <c r="T39" s="17"/>
+      <c r="U39" s="17"/>
+      <c r="V39" s="17"/>
+      <c r="W39" s="17"/>
+      <c r="X39" s="17"/>
+      <c r="Y39" s="17"/>
+      <c r="Z39" s="18"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="16" t="s">
+      <c r="A40" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="B40" s="17">
+      <c r="B40" s="16">
         <v>0.0</v>
       </c>
-      <c r="C40" s="18" t="s">
+      <c r="C40" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="D40" s="18" t="s">
+      <c r="D40" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="E40" s="18" t="s">
+      <c r="E40" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="F40" s="18"/>
-      <c r="G40" s="18"/>
-      <c r="H40" s="18"/>
-      <c r="I40" s="18"/>
-      <c r="J40" s="18"/>
-      <c r="K40" s="18"/>
-      <c r="L40" s="18"/>
-      <c r="M40" s="18"/>
-      <c r="N40" s="18"/>
-      <c r="O40" s="18"/>
-      <c r="P40" s="18"/>
-      <c r="Q40" s="18"/>
-      <c r="R40" s="18"/>
-      <c r="S40" s="18"/>
-      <c r="T40" s="18"/>
-      <c r="U40" s="18"/>
-      <c r="V40" s="18"/>
-      <c r="W40" s="18"/>
-      <c r="X40" s="18"/>
-      <c r="Y40" s="18"/>
-      <c r="Z40" s="15"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="17"/>
+      <c r="I40" s="17"/>
+      <c r="J40" s="17"/>
+      <c r="K40" s="17"/>
+      <c r="L40" s="17"/>
+      <c r="M40" s="17"/>
+      <c r="N40" s="17"/>
+      <c r="O40" s="17"/>
+      <c r="P40" s="17"/>
+      <c r="Q40" s="17"/>
+      <c r="R40" s="17"/>
+      <c r="S40" s="17"/>
+      <c r="T40" s="17"/>
+      <c r="U40" s="17"/>
+      <c r="V40" s="17"/>
+      <c r="W40" s="17"/>
+      <c r="X40" s="17"/>
+      <c r="Y40" s="17"/>
+      <c r="Z40" s="18"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="16" t="s">
+      <c r="A41" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="B41" s="17">
+      <c r="B41" s="16">
         <v>0.0</v>
       </c>
-      <c r="C41" s="18" t="s">
+      <c r="C41" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="D41" s="18" t="s">
+      <c r="D41" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="E41" s="18" t="s">
+      <c r="E41" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="F41" s="18"/>
-      <c r="G41" s="18"/>
-      <c r="H41" s="18"/>
-      <c r="I41" s="18"/>
-      <c r="J41" s="18"/>
-      <c r="K41" s="18"/>
-      <c r="L41" s="18"/>
-      <c r="M41" s="18"/>
-      <c r="N41" s="18"/>
-      <c r="O41" s="18"/>
-      <c r="P41" s="18"/>
-      <c r="Q41" s="18"/>
-      <c r="R41" s="18"/>
-      <c r="S41" s="18"/>
-      <c r="T41" s="18"/>
-      <c r="U41" s="18"/>
-      <c r="V41" s="18"/>
-      <c r="W41" s="18"/>
-      <c r="X41" s="18"/>
-      <c r="Y41" s="18"/>
-      <c r="Z41" s="15"/>
+      <c r="F41" s="17"/>
+      <c r="G41" s="17"/>
+      <c r="H41" s="17"/>
+      <c r="I41" s="17"/>
+      <c r="J41" s="17"/>
+      <c r="K41" s="17"/>
+      <c r="L41" s="17"/>
+      <c r="M41" s="17"/>
+      <c r="N41" s="17"/>
+      <c r="O41" s="17"/>
+      <c r="P41" s="17"/>
+      <c r="Q41" s="17"/>
+      <c r="R41" s="17"/>
+      <c r="S41" s="17"/>
+      <c r="T41" s="17"/>
+      <c r="U41" s="17"/>
+      <c r="V41" s="17"/>
+      <c r="W41" s="17"/>
+      <c r="X41" s="17"/>
+      <c r="Y41" s="17"/>
+      <c r="Z41" s="18"/>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="16" t="s">
+      <c r="A42" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="B42" s="17">
+      <c r="B42" s="16">
         <v>0.0</v>
       </c>
-      <c r="C42" s="18" t="s">
+      <c r="C42" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="D42" s="18" t="s">
+      <c r="D42" s="17" t="s">
         <v>167</v>
       </c>
-      <c r="E42" s="18" t="s">
+      <c r="E42" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="F42" s="18"/>
-      <c r="G42" s="18"/>
-      <c r="H42" s="18"/>
-      <c r="I42" s="18"/>
-      <c r="J42" s="18"/>
-      <c r="K42" s="18"/>
-      <c r="L42" s="18"/>
-      <c r="M42" s="18"/>
-      <c r="N42" s="18"/>
-      <c r="O42" s="18"/>
-      <c r="P42" s="18"/>
-      <c r="Q42" s="18"/>
-      <c r="R42" s="18"/>
-      <c r="S42" s="18"/>
-      <c r="T42" s="18"/>
-      <c r="U42" s="18"/>
-      <c r="V42" s="18"/>
-      <c r="W42" s="18"/>
-      <c r="X42" s="18"/>
-      <c r="Y42" s="18"/>
-      <c r="Z42" s="15"/>
+      <c r="F42" s="17"/>
+      <c r="G42" s="17"/>
+      <c r="H42" s="17"/>
+      <c r="I42" s="17"/>
+      <c r="J42" s="17"/>
+      <c r="K42" s="17"/>
+      <c r="L42" s="17"/>
+      <c r="M42" s="17"/>
+      <c r="N42" s="17"/>
+      <c r="O42" s="17"/>
+      <c r="P42" s="17"/>
+      <c r="Q42" s="17"/>
+      <c r="R42" s="17"/>
+      <c r="S42" s="17"/>
+      <c r="T42" s="17"/>
+      <c r="U42" s="17"/>
+      <c r="V42" s="17"/>
+      <c r="W42" s="17"/>
+      <c r="X42" s="17"/>
+      <c r="Y42" s="17"/>
+      <c r="Z42" s="18"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="16" t="s">
+      <c r="A43" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="B43" s="17">
+      <c r="B43" s="16">
         <v>0.0</v>
       </c>
-      <c r="C43" s="18" t="s">
+      <c r="C43" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="D43" s="18" t="s">
+      <c r="D43" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="E43" s="18" t="s">
+      <c r="E43" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="F43" s="18"/>
-      <c r="G43" s="18"/>
-      <c r="H43" s="18"/>
-      <c r="I43" s="18"/>
-      <c r="J43" s="18"/>
-      <c r="K43" s="18"/>
-      <c r="L43" s="18"/>
-      <c r="M43" s="18"/>
-      <c r="N43" s="18"/>
-      <c r="O43" s="18"/>
-      <c r="P43" s="18"/>
-      <c r="Q43" s="18"/>
-      <c r="R43" s="18"/>
-      <c r="S43" s="18"/>
-      <c r="T43" s="18"/>
-      <c r="U43" s="18"/>
-      <c r="V43" s="18"/>
-      <c r="W43" s="18"/>
-      <c r="X43" s="18"/>
-      <c r="Y43" s="18"/>
-      <c r="Z43" s="15"/>
+      <c r="F43" s="17"/>
+      <c r="G43" s="17"/>
+      <c r="H43" s="17"/>
+      <c r="I43" s="17"/>
+      <c r="J43" s="17"/>
+      <c r="K43" s="17"/>
+      <c r="L43" s="17"/>
+      <c r="M43" s="17"/>
+      <c r="N43" s="17"/>
+      <c r="O43" s="17"/>
+      <c r="P43" s="17"/>
+      <c r="Q43" s="17"/>
+      <c r="R43" s="17"/>
+      <c r="S43" s="17"/>
+      <c r="T43" s="17"/>
+      <c r="U43" s="17"/>
+      <c r="V43" s="17"/>
+      <c r="W43" s="17"/>
+      <c r="X43" s="17"/>
+      <c r="Y43" s="17"/>
+      <c r="Z43" s="18"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="16" t="s">
+      <c r="A44" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="B44" s="17">
+      <c r="B44" s="16">
         <v>0.0</v>
       </c>
-      <c r="C44" s="18" t="s">
+      <c r="C44" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="D44" s="18" t="s">
+      <c r="D44" s="17" t="s">
         <v>175</v>
       </c>
-      <c r="E44" s="18" t="s">
+      <c r="E44" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="F44" s="18"/>
-      <c r="G44" s="18"/>
-      <c r="H44" s="18"/>
-      <c r="I44" s="18"/>
-      <c r="J44" s="18"/>
-      <c r="K44" s="18"/>
-      <c r="L44" s="18"/>
-      <c r="M44" s="18"/>
-      <c r="N44" s="18"/>
-      <c r="O44" s="18"/>
-      <c r="P44" s="18"/>
-      <c r="Q44" s="18"/>
-      <c r="R44" s="18"/>
-      <c r="S44" s="18"/>
-      <c r="T44" s="18"/>
-      <c r="U44" s="18"/>
-      <c r="V44" s="18"/>
-      <c r="W44" s="18"/>
-      <c r="X44" s="18"/>
-      <c r="Y44" s="18"/>
-      <c r="Z44" s="15"/>
+      <c r="F44" s="17"/>
+      <c r="G44" s="17"/>
+      <c r="H44" s="17"/>
+      <c r="I44" s="17"/>
+      <c r="J44" s="17"/>
+      <c r="K44" s="17"/>
+      <c r="L44" s="17"/>
+      <c r="M44" s="17"/>
+      <c r="N44" s="17"/>
+      <c r="O44" s="17"/>
+      <c r="P44" s="17"/>
+      <c r="Q44" s="17"/>
+      <c r="R44" s="17"/>
+      <c r="S44" s="17"/>
+      <c r="T44" s="17"/>
+      <c r="U44" s="17"/>
+      <c r="V44" s="17"/>
+      <c r="W44" s="17"/>
+      <c r="X44" s="17"/>
+      <c r="Y44" s="17"/>
+      <c r="Z44" s="18"/>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="16" t="s">
+      <c r="A45" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="B45" s="17">
+      <c r="B45" s="16">
         <v>0.0</v>
       </c>
-      <c r="C45" s="18" t="s">
+      <c r="C45" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="D45" s="18" t="s">
+      <c r="D45" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="E45" s="18" t="s">
+      <c r="E45" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="F45" s="18"/>
-      <c r="G45" s="18"/>
-      <c r="H45" s="18"/>
-      <c r="I45" s="18"/>
-      <c r="J45" s="18"/>
-      <c r="K45" s="18"/>
-      <c r="L45" s="18"/>
-      <c r="M45" s="18"/>
-      <c r="N45" s="18"/>
-      <c r="O45" s="18"/>
-      <c r="P45" s="18"/>
-      <c r="Q45" s="18"/>
-      <c r="R45" s="18"/>
-      <c r="S45" s="18"/>
-      <c r="T45" s="18"/>
-      <c r="U45" s="18"/>
-      <c r="V45" s="18"/>
-      <c r="W45" s="18"/>
-      <c r="X45" s="18"/>
-      <c r="Y45" s="18"/>
-      <c r="Z45" s="15"/>
+      <c r="F45" s="17"/>
+      <c r="G45" s="17"/>
+      <c r="H45" s="17"/>
+      <c r="I45" s="17"/>
+      <c r="J45" s="17"/>
+      <c r="K45" s="17"/>
+      <c r="L45" s="17"/>
+      <c r="M45" s="17"/>
+      <c r="N45" s="17"/>
+      <c r="O45" s="17"/>
+      <c r="P45" s="17"/>
+      <c r="Q45" s="17"/>
+      <c r="R45" s="17"/>
+      <c r="S45" s="17"/>
+      <c r="T45" s="17"/>
+      <c r="U45" s="17"/>
+      <c r="V45" s="17"/>
+      <c r="W45" s="17"/>
+      <c r="X45" s="17"/>
+      <c r="Y45" s="17"/>
+      <c r="Z45" s="18"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="16" t="s">
+      <c r="A46" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="B46" s="17">
+      <c r="B46" s="16">
         <v>0.0</v>
       </c>
-      <c r="C46" s="18" t="s">
+      <c r="C46" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="D46" s="18" t="s">
+      <c r="D46" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="E46" s="18" t="s">
+      <c r="E46" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="F46" s="18"/>
-      <c r="G46" s="18"/>
-      <c r="H46" s="18"/>
-      <c r="I46" s="18"/>
-      <c r="J46" s="18"/>
-      <c r="K46" s="18"/>
-      <c r="L46" s="18"/>
-      <c r="M46" s="18"/>
-      <c r="N46" s="18"/>
-      <c r="O46" s="18"/>
-      <c r="P46" s="18"/>
-      <c r="Q46" s="18"/>
-      <c r="R46" s="18"/>
-      <c r="S46" s="18"/>
-      <c r="T46" s="18"/>
-      <c r="U46" s="18"/>
-      <c r="V46" s="18"/>
-      <c r="W46" s="18"/>
-      <c r="X46" s="18"/>
-      <c r="Y46" s="18"/>
-      <c r="Z46" s="15"/>
+      <c r="F46" s="17"/>
+      <c r="G46" s="17"/>
+      <c r="H46" s="17"/>
+      <c r="I46" s="17"/>
+      <c r="J46" s="17"/>
+      <c r="K46" s="17"/>
+      <c r="L46" s="17"/>
+      <c r="M46" s="17"/>
+      <c r="N46" s="17"/>
+      <c r="O46" s="17"/>
+      <c r="P46" s="17"/>
+      <c r="Q46" s="17"/>
+      <c r="R46" s="17"/>
+      <c r="S46" s="17"/>
+      <c r="T46" s="17"/>
+      <c r="U46" s="17"/>
+      <c r="V46" s="17"/>
+      <c r="W46" s="17"/>
+      <c r="X46" s="17"/>
+      <c r="Y46" s="17"/>
+      <c r="Z46" s="18"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="16" t="s">
+      <c r="A47" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="B47" s="17">
+      <c r="B47" s="16">
         <v>0.0</v>
       </c>
-      <c r="C47" s="18" t="s">
+      <c r="C47" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="D47" s="18" t="s">
+      <c r="D47" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="E47" s="18" t="s">
+      <c r="E47" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="F47" s="18"/>
-      <c r="G47" s="18"/>
-      <c r="H47" s="18"/>
-      <c r="I47" s="18"/>
-      <c r="J47" s="18"/>
-      <c r="K47" s="18"/>
-      <c r="L47" s="18"/>
-      <c r="M47" s="18"/>
-      <c r="N47" s="18"/>
-      <c r="O47" s="18"/>
-      <c r="P47" s="18"/>
-      <c r="Q47" s="18"/>
-      <c r="R47" s="18"/>
-      <c r="S47" s="18"/>
-      <c r="T47" s="18"/>
-      <c r="U47" s="18"/>
-      <c r="V47" s="18"/>
-      <c r="W47" s="18"/>
-      <c r="X47" s="18"/>
-      <c r="Y47" s="18"/>
-      <c r="Z47" s="15"/>
+      <c r="F47" s="17"/>
+      <c r="G47" s="17"/>
+      <c r="H47" s="17"/>
+      <c r="I47" s="17"/>
+      <c r="J47" s="17"/>
+      <c r="K47" s="17"/>
+      <c r="L47" s="17"/>
+      <c r="M47" s="17"/>
+      <c r="N47" s="17"/>
+      <c r="O47" s="17"/>
+      <c r="P47" s="17"/>
+      <c r="Q47" s="17"/>
+      <c r="R47" s="17"/>
+      <c r="S47" s="17"/>
+      <c r="T47" s="17"/>
+      <c r="U47" s="17"/>
+      <c r="V47" s="17"/>
+      <c r="W47" s="17"/>
+      <c r="X47" s="17"/>
+      <c r="Y47" s="17"/>
+      <c r="Z47" s="18"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="16" t="s">
+      <c r="A48" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="B48" s="17">
+      <c r="B48" s="16">
         <v>0.0</v>
       </c>
-      <c r="C48" s="18" t="s">
+      <c r="C48" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="D48" s="18" t="s">
+      <c r="D48" s="17" t="s">
         <v>191</v>
       </c>
-      <c r="E48" s="18" t="s">
+      <c r="E48" s="17" t="s">
         <v>192</v>
       </c>
-      <c r="F48" s="18"/>
-      <c r="G48" s="18"/>
-      <c r="H48" s="18"/>
-      <c r="I48" s="18"/>
-      <c r="J48" s="18"/>
-      <c r="K48" s="18"/>
-      <c r="L48" s="18"/>
-      <c r="M48" s="18"/>
-      <c r="N48" s="18"/>
-      <c r="O48" s="18"/>
-      <c r="P48" s="18"/>
-      <c r="Q48" s="18"/>
-      <c r="R48" s="18"/>
-      <c r="S48" s="18"/>
-      <c r="T48" s="18"/>
-      <c r="U48" s="18"/>
-      <c r="V48" s="18"/>
-      <c r="W48" s="18"/>
-      <c r="X48" s="18"/>
-      <c r="Y48" s="18"/>
-      <c r="Z48" s="15"/>
+      <c r="F48" s="17"/>
+      <c r="G48" s="17"/>
+      <c r="H48" s="17"/>
+      <c r="I48" s="17"/>
+      <c r="J48" s="17"/>
+      <c r="K48" s="17"/>
+      <c r="L48" s="17"/>
+      <c r="M48" s="17"/>
+      <c r="N48" s="17"/>
+      <c r="O48" s="17"/>
+      <c r="P48" s="17"/>
+      <c r="Q48" s="17"/>
+      <c r="R48" s="17"/>
+      <c r="S48" s="17"/>
+      <c r="T48" s="17"/>
+      <c r="U48" s="17"/>
+      <c r="V48" s="17"/>
+      <c r="W48" s="17"/>
+      <c r="X48" s="17"/>
+      <c r="Y48" s="17"/>
+      <c r="Z48" s="18"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="16" t="s">
+      <c r="A49" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="B49" s="17">
+      <c r="B49" s="16">
         <v>0.0</v>
       </c>
-      <c r="C49" s="18" t="s">
+      <c r="C49" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="D49" s="18" t="s">
+      <c r="D49" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="E49" s="18" t="s">
+      <c r="E49" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="F49" s="18"/>
-      <c r="G49" s="18"/>
-      <c r="H49" s="18"/>
-      <c r="I49" s="18"/>
-      <c r="J49" s="18"/>
-      <c r="K49" s="18"/>
-      <c r="L49" s="18"/>
-      <c r="M49" s="18"/>
-      <c r="N49" s="18"/>
-      <c r="O49" s="18"/>
-      <c r="P49" s="18"/>
-      <c r="Q49" s="18"/>
-      <c r="R49" s="18"/>
-      <c r="S49" s="18"/>
-      <c r="T49" s="18"/>
-      <c r="U49" s="18"/>
-      <c r="V49" s="18"/>
-      <c r="W49" s="18"/>
-      <c r="X49" s="18"/>
-      <c r="Y49" s="18"/>
-      <c r="Z49" s="15"/>
+      <c r="F49" s="17"/>
+      <c r="G49" s="17"/>
+      <c r="H49" s="17"/>
+      <c r="I49" s="17"/>
+      <c r="J49" s="17"/>
+      <c r="K49" s="17"/>
+      <c r="L49" s="17"/>
+      <c r="M49" s="17"/>
+      <c r="N49" s="17"/>
+      <c r="O49" s="17"/>
+      <c r="P49" s="17"/>
+      <c r="Q49" s="17"/>
+      <c r="R49" s="17"/>
+      <c r="S49" s="17"/>
+      <c r="T49" s="17"/>
+      <c r="U49" s="17"/>
+      <c r="V49" s="17"/>
+      <c r="W49" s="17"/>
+      <c r="X49" s="17"/>
+      <c r="Y49" s="17"/>
+      <c r="Z49" s="18"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="16" t="s">
+      <c r="A50" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="B50" s="17">
+      <c r="B50" s="16">
         <v>0.0</v>
       </c>
-      <c r="C50" s="18" t="s">
+      <c r="C50" s="17" t="s">
         <v>198</v>
       </c>
-      <c r="D50" s="18" t="s">
+      <c r="D50" s="17" t="s">
         <v>199</v>
       </c>
-      <c r="E50" s="18" t="s">
+      <c r="E50" s="17" t="s">
         <v>200</v>
       </c>
-      <c r="F50" s="18"/>
-      <c r="G50" s="18"/>
-      <c r="H50" s="18"/>
-      <c r="I50" s="18"/>
-      <c r="J50" s="18"/>
-      <c r="K50" s="18"/>
-      <c r="L50" s="18"/>
-      <c r="M50" s="18"/>
-      <c r="N50" s="18"/>
-      <c r="O50" s="18"/>
-      <c r="P50" s="18"/>
-      <c r="Q50" s="18"/>
-      <c r="R50" s="18"/>
-      <c r="S50" s="18"/>
-      <c r="T50" s="18"/>
-      <c r="U50" s="18"/>
-      <c r="V50" s="18"/>
-      <c r="W50" s="18"/>
-      <c r="X50" s="18"/>
-      <c r="Y50" s="18"/>
-      <c r="Z50" s="15"/>
+      <c r="F50" s="17"/>
+      <c r="G50" s="17"/>
+      <c r="H50" s="17"/>
+      <c r="I50" s="17"/>
+      <c r="J50" s="17"/>
+      <c r="K50" s="17"/>
+      <c r="L50" s="17"/>
+      <c r="M50" s="17"/>
+      <c r="N50" s="17"/>
+      <c r="O50" s="17"/>
+      <c r="P50" s="17"/>
+      <c r="Q50" s="17"/>
+      <c r="R50" s="17"/>
+      <c r="S50" s="17"/>
+      <c r="T50" s="17"/>
+      <c r="U50" s="17"/>
+      <c r="V50" s="17"/>
+      <c r="W50" s="17"/>
+      <c r="X50" s="17"/>
+      <c r="Y50" s="17"/>
+      <c r="Z50" s="18"/>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="16" t="s">
+      <c r="A51" s="15" t="s">
         <v>201</v>
       </c>
-      <c r="B51" s="17">
+      <c r="B51" s="16">
         <v>0.0</v>
       </c>
-      <c r="C51" s="18" t="s">
+      <c r="C51" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="D51" s="18" t="s">
+      <c r="D51" s="17" t="s">
         <v>203</v>
       </c>
-      <c r="E51" s="18" t="s">
+      <c r="E51" s="17" t="s">
         <v>204</v>
       </c>
-      <c r="F51" s="18"/>
-      <c r="G51" s="18"/>
-      <c r="H51" s="18"/>
-      <c r="I51" s="18"/>
-      <c r="J51" s="18"/>
-      <c r="K51" s="18"/>
-      <c r="L51" s="18"/>
-      <c r="M51" s="18"/>
-      <c r="N51" s="18"/>
-      <c r="O51" s="18"/>
-      <c r="P51" s="18"/>
-      <c r="Q51" s="18"/>
-      <c r="R51" s="18"/>
-      <c r="S51" s="18"/>
-      <c r="T51" s="18"/>
-      <c r="U51" s="18"/>
-      <c r="V51" s="18"/>
-      <c r="W51" s="18"/>
-      <c r="X51" s="18"/>
-      <c r="Y51" s="18"/>
-      <c r="Z51" s="15"/>
+      <c r="F51" s="17"/>
+      <c r="G51" s="17"/>
+      <c r="H51" s="17"/>
+      <c r="I51" s="17"/>
+      <c r="J51" s="17"/>
+      <c r="K51" s="17"/>
+      <c r="L51" s="17"/>
+      <c r="M51" s="17"/>
+      <c r="N51" s="17"/>
+      <c r="O51" s="17"/>
+      <c r="P51" s="17"/>
+      <c r="Q51" s="17"/>
+      <c r="R51" s="17"/>
+      <c r="S51" s="17"/>
+      <c r="T51" s="17"/>
+      <c r="U51" s="17"/>
+      <c r="V51" s="17"/>
+      <c r="W51" s="17"/>
+      <c r="X51" s="17"/>
+      <c r="Y51" s="17"/>
+      <c r="Z51" s="18"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="16" t="s">
+      <c r="A52" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="B52" s="17">
+      <c r="B52" s="16">
         <v>0.0</v>
       </c>
-      <c r="C52" s="18" t="s">
+      <c r="C52" s="17" t="s">
         <v>206</v>
       </c>
-      <c r="D52" s="18" t="s">
+      <c r="D52" s="17" t="s">
         <v>207</v>
       </c>
-      <c r="E52" s="18" t="s">
+      <c r="E52" s="17" t="s">
         <v>208</v>
       </c>
-      <c r="F52" s="18"/>
-      <c r="G52" s="18"/>
-      <c r="H52" s="18"/>
-      <c r="I52" s="18"/>
-      <c r="J52" s="18"/>
-      <c r="K52" s="18"/>
-      <c r="L52" s="18"/>
-      <c r="M52" s="18"/>
-      <c r="N52" s="18"/>
-      <c r="O52" s="18"/>
-      <c r="P52" s="18"/>
-      <c r="Q52" s="18"/>
-      <c r="R52" s="18"/>
-      <c r="S52" s="18"/>
-      <c r="T52" s="18"/>
-      <c r="U52" s="18"/>
-      <c r="V52" s="18"/>
-      <c r="W52" s="18"/>
-      <c r="X52" s="18"/>
-      <c r="Y52" s="18"/>
-      <c r="Z52" s="15"/>
+      <c r="F52" s="17"/>
+      <c r="G52" s="17"/>
+      <c r="H52" s="17"/>
+      <c r="I52" s="17"/>
+      <c r="J52" s="17"/>
+      <c r="K52" s="17"/>
+      <c r="L52" s="17"/>
+      <c r="M52" s="17"/>
+      <c r="N52" s="17"/>
+      <c r="O52" s="17"/>
+      <c r="P52" s="17"/>
+      <c r="Q52" s="17"/>
+      <c r="R52" s="17"/>
+      <c r="S52" s="17"/>
+      <c r="T52" s="17"/>
+      <c r="U52" s="17"/>
+      <c r="V52" s="17"/>
+      <c r="W52" s="17"/>
+      <c r="X52" s="17"/>
+      <c r="Y52" s="17"/>
+      <c r="Z52" s="18"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="16" t="s">
+      <c r="A53" s="15" t="s">
         <v>209</v>
       </c>
-      <c r="B53" s="17">
+      <c r="B53" s="16">
         <v>0.0</v>
       </c>
-      <c r="C53" s="18" t="s">
+      <c r="C53" s="17" t="s">
         <v>210</v>
       </c>
-      <c r="D53" s="18" t="s">
+      <c r="D53" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="E53" s="18" t="s">
+      <c r="E53" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="F53" s="18"/>
-      <c r="G53" s="18"/>
-      <c r="H53" s="18"/>
-      <c r="I53" s="18"/>
-      <c r="J53" s="18"/>
-      <c r="K53" s="18"/>
-      <c r="L53" s="18"/>
-      <c r="M53" s="18"/>
-      <c r="N53" s="18"/>
-      <c r="O53" s="18"/>
-      <c r="P53" s="18"/>
-      <c r="Q53" s="18"/>
-      <c r="R53" s="18"/>
-      <c r="S53" s="18"/>
-      <c r="T53" s="18"/>
-      <c r="U53" s="18"/>
-      <c r="V53" s="18"/>
-      <c r="W53" s="18"/>
-      <c r="X53" s="18"/>
-      <c r="Y53" s="18"/>
-      <c r="Z53" s="15"/>
+      <c r="F53" s="17"/>
+      <c r="G53" s="17"/>
+      <c r="H53" s="17"/>
+      <c r="I53" s="17"/>
+      <c r="J53" s="17"/>
+      <c r="K53" s="17"/>
+      <c r="L53" s="17"/>
+      <c r="M53" s="17"/>
+      <c r="N53" s="17"/>
+      <c r="O53" s="17"/>
+      <c r="P53" s="17"/>
+      <c r="Q53" s="17"/>
+      <c r="R53" s="17"/>
+      <c r="S53" s="17"/>
+      <c r="T53" s="17"/>
+      <c r="U53" s="17"/>
+      <c r="V53" s="17"/>
+      <c r="W53" s="17"/>
+      <c r="X53" s="17"/>
+      <c r="Y53" s="17"/>
+      <c r="Z53" s="18"/>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="16" t="s">
+      <c r="A54" s="15" t="s">
         <v>211</v>
       </c>
-      <c r="B54" s="17">
+      <c r="B54" s="16">
         <v>0.0</v>
       </c>
-      <c r="C54" s="18" t="s">
+      <c r="C54" s="17" t="s">
         <v>212</v>
       </c>
-      <c r="D54" s="18" t="s">
+      <c r="D54" s="17" t="s">
         <v>213</v>
       </c>
-      <c r="E54" s="18" t="s">
+      <c r="E54" s="17" t="s">
         <v>214</v>
       </c>
-      <c r="F54" s="18"/>
-      <c r="G54" s="18"/>
-      <c r="H54" s="18"/>
-      <c r="I54" s="18"/>
-      <c r="J54" s="18"/>
-      <c r="K54" s="18"/>
-      <c r="L54" s="18"/>
-      <c r="M54" s="18"/>
-      <c r="N54" s="18"/>
-      <c r="O54" s="18"/>
-      <c r="P54" s="18"/>
-      <c r="Q54" s="18"/>
-      <c r="R54" s="18"/>
-      <c r="S54" s="18"/>
-      <c r="T54" s="18"/>
-      <c r="U54" s="18"/>
-      <c r="V54" s="18"/>
-      <c r="W54" s="18"/>
-      <c r="X54" s="18"/>
-      <c r="Y54" s="18"/>
-      <c r="Z54" s="15"/>
+      <c r="F54" s="17"/>
+      <c r="G54" s="17"/>
+      <c r="H54" s="17"/>
+      <c r="I54" s="17"/>
+      <c r="J54" s="17"/>
+      <c r="K54" s="17"/>
+      <c r="L54" s="17"/>
+      <c r="M54" s="17"/>
+      <c r="N54" s="17"/>
+      <c r="O54" s="17"/>
+      <c r="P54" s="17"/>
+      <c r="Q54" s="17"/>
+      <c r="R54" s="17"/>
+      <c r="S54" s="17"/>
+      <c r="T54" s="17"/>
+      <c r="U54" s="17"/>
+      <c r="V54" s="17"/>
+      <c r="W54" s="17"/>
+      <c r="X54" s="17"/>
+      <c r="Y54" s="17"/>
+      <c r="Z54" s="18"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="16" t="s">
+      <c r="A55" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="B55" s="17">
+      <c r="B55" s="16">
         <v>0.0</v>
       </c>
-      <c r="C55" s="18" t="s">
+      <c r="C55" s="17" t="s">
         <v>216</v>
       </c>
-      <c r="D55" s="18" t="s">
+      <c r="D55" s="17" t="s">
         <v>217</v>
       </c>
-      <c r="E55" s="18" t="s">
+      <c r="E55" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="F55" s="18"/>
-      <c r="G55" s="18"/>
-      <c r="H55" s="18"/>
-      <c r="I55" s="18"/>
-      <c r="J55" s="18"/>
-      <c r="K55" s="18"/>
-      <c r="L55" s="18"/>
-      <c r="M55" s="18"/>
-      <c r="N55" s="18"/>
-      <c r="O55" s="18"/>
-      <c r="P55" s="18"/>
-      <c r="Q55" s="18"/>
-      <c r="R55" s="18"/>
-      <c r="S55" s="18"/>
-      <c r="T55" s="18"/>
-      <c r="U55" s="18"/>
-      <c r="V55" s="18"/>
-      <c r="W55" s="18"/>
-      <c r="X55" s="18"/>
-      <c r="Y55" s="18"/>
-      <c r="Z55" s="15"/>
+      <c r="F55" s="17"/>
+      <c r="G55" s="17"/>
+      <c r="H55" s="17"/>
+      <c r="I55" s="17"/>
+      <c r="J55" s="17"/>
+      <c r="K55" s="17"/>
+      <c r="L55" s="17"/>
+      <c r="M55" s="17"/>
+      <c r="N55" s="17"/>
+      <c r="O55" s="17"/>
+      <c r="P55" s="17"/>
+      <c r="Q55" s="17"/>
+      <c r="R55" s="17"/>
+      <c r="S55" s="17"/>
+      <c r="T55" s="17"/>
+      <c r="U55" s="17"/>
+      <c r="V55" s="17"/>
+      <c r="W55" s="17"/>
+      <c r="X55" s="17"/>
+      <c r="Y55" s="17"/>
+      <c r="Z55" s="18"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="16" t="s">
+      <c r="A56" s="15" t="s">
         <v>219</v>
       </c>
-      <c r="B56" s="17">
+      <c r="B56" s="16">
         <v>0.0</v>
       </c>
-      <c r="C56" s="18" t="s">
+      <c r="C56" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="D56" s="18" t="s">
+      <c r="D56" s="17" t="s">
         <v>221</v>
       </c>
-      <c r="E56" s="18" t="s">
+      <c r="E56" s="17" t="s">
         <v>222</v>
       </c>
-      <c r="F56" s="18"/>
-      <c r="G56" s="18"/>
-      <c r="H56" s="18"/>
-      <c r="I56" s="18"/>
-      <c r="J56" s="18"/>
-      <c r="K56" s="18"/>
-      <c r="L56" s="18"/>
-      <c r="M56" s="18"/>
-      <c r="N56" s="18"/>
-      <c r="O56" s="18"/>
-      <c r="P56" s="18"/>
-      <c r="Q56" s="18"/>
-      <c r="R56" s="18"/>
-      <c r="S56" s="18"/>
-      <c r="T56" s="18"/>
-      <c r="U56" s="18"/>
-      <c r="V56" s="18"/>
-      <c r="W56" s="18"/>
-      <c r="X56" s="18"/>
-      <c r="Y56" s="18"/>
-      <c r="Z56" s="15"/>
+      <c r="F56" s="17"/>
+      <c r="G56" s="17"/>
+      <c r="H56" s="17"/>
+      <c r="I56" s="17"/>
+      <c r="J56" s="17"/>
+      <c r="K56" s="17"/>
+      <c r="L56" s="17"/>
+      <c r="M56" s="17"/>
+      <c r="N56" s="17"/>
+      <c r="O56" s="17"/>
+      <c r="P56" s="17"/>
+      <c r="Q56" s="17"/>
+      <c r="R56" s="17"/>
+      <c r="S56" s="17"/>
+      <c r="T56" s="17"/>
+      <c r="U56" s="17"/>
+      <c r="V56" s="17"/>
+      <c r="W56" s="17"/>
+      <c r="X56" s="17"/>
+      <c r="Y56" s="17"/>
+      <c r="Z56" s="18"/>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="16" t="s">
+      <c r="A57" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="B57" s="17">
+      <c r="B57" s="16">
         <v>0.0</v>
       </c>
-      <c r="C57" s="18" t="s">
+      <c r="C57" s="17" t="s">
         <v>224</v>
       </c>
-      <c r="D57" s="18" t="s">
+      <c r="D57" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="E57" s="18" t="s">
+      <c r="E57" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="F57" s="18"/>
-      <c r="G57" s="18"/>
-      <c r="H57" s="18"/>
-      <c r="I57" s="18"/>
-      <c r="J57" s="18"/>
-      <c r="K57" s="18"/>
-      <c r="L57" s="18"/>
-      <c r="M57" s="18"/>
-      <c r="N57" s="18"/>
-      <c r="O57" s="18"/>
-      <c r="P57" s="18"/>
-      <c r="Q57" s="18"/>
-      <c r="R57" s="18"/>
-      <c r="S57" s="18"/>
-      <c r="T57" s="18"/>
-      <c r="U57" s="18"/>
-      <c r="V57" s="18"/>
-      <c r="W57" s="18"/>
-      <c r="X57" s="18"/>
-      <c r="Y57" s="18"/>
-      <c r="Z57" s="15"/>
+      <c r="F57" s="17"/>
+      <c r="G57" s="17"/>
+      <c r="H57" s="17"/>
+      <c r="I57" s="17"/>
+      <c r="J57" s="17"/>
+      <c r="K57" s="17"/>
+      <c r="L57" s="17"/>
+      <c r="M57" s="17"/>
+      <c r="N57" s="17"/>
+      <c r="O57" s="17"/>
+      <c r="P57" s="17"/>
+      <c r="Q57" s="17"/>
+      <c r="R57" s="17"/>
+      <c r="S57" s="17"/>
+      <c r="T57" s="17"/>
+      <c r="U57" s="17"/>
+      <c r="V57" s="17"/>
+      <c r="W57" s="17"/>
+      <c r="X57" s="17"/>
+      <c r="Y57" s="17"/>
+      <c r="Z57" s="18"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="16" t="s">
+      <c r="A58" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="B58" s="17">
+      <c r="B58" s="16">
         <v>0.0</v>
       </c>
-      <c r="C58" s="18" t="s">
+      <c r="C58" s="17" t="s">
         <v>228</v>
       </c>
-      <c r="D58" s="18" t="s">
+      <c r="D58" s="17" t="s">
         <v>229</v>
       </c>
-      <c r="E58" s="18" t="s">
+      <c r="E58" s="17" t="s">
         <v>230</v>
       </c>
-      <c r="F58" s="18"/>
-      <c r="G58" s="18"/>
-      <c r="H58" s="18"/>
-      <c r="I58" s="18"/>
-      <c r="J58" s="18"/>
-      <c r="K58" s="18"/>
-      <c r="L58" s="18"/>
-      <c r="M58" s="18"/>
-      <c r="N58" s="18"/>
-      <c r="O58" s="18"/>
-      <c r="P58" s="18"/>
-      <c r="Q58" s="18"/>
-      <c r="R58" s="18"/>
-      <c r="S58" s="18"/>
-      <c r="T58" s="18"/>
-      <c r="U58" s="18"/>
-      <c r="V58" s="18"/>
-      <c r="W58" s="18"/>
-      <c r="X58" s="18"/>
-      <c r="Y58" s="18"/>
-      <c r="Z58" s="15"/>
+      <c r="F58" s="17"/>
+      <c r="G58" s="17"/>
+      <c r="H58" s="17"/>
+      <c r="I58" s="17"/>
+      <c r="J58" s="17"/>
+      <c r="K58" s="17"/>
+      <c r="L58" s="17"/>
+      <c r="M58" s="17"/>
+      <c r="N58" s="17"/>
+      <c r="O58" s="17"/>
+      <c r="P58" s="17"/>
+      <c r="Q58" s="17"/>
+      <c r="R58" s="17"/>
+      <c r="S58" s="17"/>
+      <c r="T58" s="17"/>
+      <c r="U58" s="17"/>
+      <c r="V58" s="17"/>
+      <c r="W58" s="17"/>
+      <c r="X58" s="17"/>
+      <c r="Y58" s="17"/>
+      <c r="Z58" s="18"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="16" t="s">
+      <c r="A59" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="B59" s="17">
+      <c r="B59" s="16">
         <v>0.0</v>
       </c>
-      <c r="C59" s="18" t="s">
+      <c r="C59" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="D59" s="18" t="s">
+      <c r="D59" s="17" t="s">
         <v>233</v>
       </c>
-      <c r="E59" s="18" t="s">
+      <c r="E59" s="17" t="s">
         <v>234</v>
       </c>
-      <c r="F59" s="18"/>
-      <c r="G59" s="18"/>
-      <c r="H59" s="18"/>
-      <c r="I59" s="18"/>
-      <c r="J59" s="18"/>
-      <c r="K59" s="18"/>
-      <c r="L59" s="18"/>
-      <c r="M59" s="18"/>
-      <c r="N59" s="18"/>
-      <c r="O59" s="18"/>
-      <c r="P59" s="18"/>
-      <c r="Q59" s="18"/>
-      <c r="R59" s="18"/>
-      <c r="S59" s="18"/>
-      <c r="T59" s="18"/>
-      <c r="U59" s="18"/>
-      <c r="V59" s="18"/>
-      <c r="W59" s="18"/>
-      <c r="X59" s="18"/>
-      <c r="Y59" s="18"/>
-      <c r="Z59" s="15"/>
+      <c r="F59" s="17"/>
+      <c r="G59" s="17"/>
+      <c r="H59" s="17"/>
+      <c r="I59" s="17"/>
+      <c r="J59" s="17"/>
+      <c r="K59" s="17"/>
+      <c r="L59" s="17"/>
+      <c r="M59" s="17"/>
+      <c r="N59" s="17"/>
+      <c r="O59" s="17"/>
+      <c r="P59" s="17"/>
+      <c r="Q59" s="17"/>
+      <c r="R59" s="17"/>
+      <c r="S59" s="17"/>
+      <c r="T59" s="17"/>
+      <c r="U59" s="17"/>
+      <c r="V59" s="17"/>
+      <c r="W59" s="17"/>
+      <c r="X59" s="17"/>
+      <c r="Y59" s="17"/>
+      <c r="Z59" s="18"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="16" t="s">
+      <c r="A60" s="15" t="s">
         <v>235</v>
       </c>
-      <c r="B60" s="17">
+      <c r="B60" s="16">
         <v>0.0</v>
       </c>
-      <c r="C60" s="18" t="s">
+      <c r="C60" s="17" t="s">
         <v>236</v>
       </c>
-      <c r="D60" s="18" t="s">
+      <c r="D60" s="17" t="s">
         <v>237</v>
       </c>
-      <c r="E60" s="18" t="s">
+      <c r="E60" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="F60" s="18"/>
-      <c r="G60" s="18"/>
-      <c r="H60" s="18"/>
-      <c r="I60" s="18"/>
-      <c r="J60" s="18"/>
-      <c r="K60" s="18"/>
-      <c r="L60" s="18"/>
-      <c r="M60" s="18"/>
-      <c r="N60" s="18"/>
-      <c r="O60" s="18"/>
-      <c r="P60" s="18"/>
-      <c r="Q60" s="18"/>
-      <c r="R60" s="18"/>
-      <c r="S60" s="18"/>
-      <c r="T60" s="18"/>
-      <c r="U60" s="18"/>
-      <c r="V60" s="18"/>
-      <c r="W60" s="18"/>
-      <c r="X60" s="18"/>
-      <c r="Y60" s="18"/>
-      <c r="Z60" s="15"/>
+      <c r="F60" s="17"/>
+      <c r="G60" s="17"/>
+      <c r="H60" s="17"/>
+      <c r="I60" s="17"/>
+      <c r="J60" s="17"/>
+      <c r="K60" s="17"/>
+      <c r="L60" s="17"/>
+      <c r="M60" s="17"/>
+      <c r="N60" s="17"/>
+      <c r="O60" s="17"/>
+      <c r="P60" s="17"/>
+      <c r="Q60" s="17"/>
+      <c r="R60" s="17"/>
+      <c r="S60" s="17"/>
+      <c r="T60" s="17"/>
+      <c r="U60" s="17"/>
+      <c r="V60" s="17"/>
+      <c r="W60" s="17"/>
+      <c r="X60" s="17"/>
+      <c r="Y60" s="17"/>
+      <c r="Z60" s="18"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="16" t="s">
+      <c r="A61" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="B61" s="17">
+      <c r="B61" s="16">
         <v>0.0</v>
       </c>
-      <c r="C61" s="18" t="s">
+      <c r="C61" s="17" t="s">
         <v>240</v>
       </c>
-      <c r="D61" s="18" t="s">
+      <c r="D61" s="17" t="s">
         <v>241</v>
       </c>
-      <c r="E61" s="18" t="s">
+      <c r="E61" s="17" t="s">
         <v>242</v>
       </c>
-      <c r="F61" s="18"/>
-      <c r="G61" s="18"/>
-      <c r="H61" s="18"/>
-      <c r="I61" s="18"/>
-      <c r="J61" s="18"/>
-      <c r="K61" s="18"/>
-      <c r="L61" s="18"/>
-      <c r="M61" s="18"/>
-      <c r="N61" s="18"/>
-      <c r="O61" s="18"/>
-      <c r="P61" s="18"/>
-      <c r="Q61" s="18"/>
-      <c r="R61" s="18"/>
-      <c r="S61" s="18"/>
-      <c r="T61" s="18"/>
-      <c r="U61" s="18"/>
-      <c r="V61" s="18"/>
-      <c r="W61" s="18"/>
-      <c r="X61" s="18"/>
-      <c r="Y61" s="18"/>
-      <c r="Z61" s="15"/>
+      <c r="F61" s="17"/>
+      <c r="G61" s="17"/>
+      <c r="H61" s="17"/>
+      <c r="I61" s="17"/>
+      <c r="J61" s="17"/>
+      <c r="K61" s="17"/>
+      <c r="L61" s="17"/>
+      <c r="M61" s="17"/>
+      <c r="N61" s="17"/>
+      <c r="O61" s="17"/>
+      <c r="P61" s="17"/>
+      <c r="Q61" s="17"/>
+      <c r="R61" s="17"/>
+      <c r="S61" s="17"/>
+      <c r="T61" s="17"/>
+      <c r="U61" s="17"/>
+      <c r="V61" s="17"/>
+      <c r="W61" s="17"/>
+      <c r="X61" s="17"/>
+      <c r="Y61" s="17"/>
+      <c r="Z61" s="18"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="16" t="s">
+      <c r="A62" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="B62" s="17">
+      <c r="B62" s="16">
         <v>0.0</v>
       </c>
-      <c r="C62" s="18" t="s">
+      <c r="C62" s="17" t="s">
         <v>244</v>
       </c>
-      <c r="D62" s="18" t="s">
+      <c r="D62" s="17" t="s">
         <v>245</v>
       </c>
-      <c r="E62" s="18" t="s">
+      <c r="E62" s="17" t="s">
         <v>246</v>
       </c>
-      <c r="F62" s="18"/>
-      <c r="G62" s="18"/>
-      <c r="H62" s="18"/>
-      <c r="I62" s="18"/>
-      <c r="J62" s="18"/>
-      <c r="K62" s="18"/>
-      <c r="L62" s="18"/>
-      <c r="M62" s="18"/>
-      <c r="N62" s="18"/>
-      <c r="O62" s="18"/>
-      <c r="P62" s="18"/>
-      <c r="Q62" s="18"/>
-      <c r="R62" s="18"/>
-      <c r="S62" s="18"/>
-      <c r="T62" s="18"/>
-      <c r="U62" s="18"/>
-      <c r="V62" s="18"/>
-      <c r="W62" s="18"/>
-      <c r="X62" s="18"/>
-      <c r="Y62" s="18"/>
-      <c r="Z62" s="15"/>
+      <c r="F62" s="17"/>
+      <c r="G62" s="17"/>
+      <c r="H62" s="17"/>
+      <c r="I62" s="17"/>
+      <c r="J62" s="17"/>
+      <c r="K62" s="17"/>
+      <c r="L62" s="17"/>
+      <c r="M62" s="17"/>
+      <c r="N62" s="17"/>
+      <c r="O62" s="17"/>
+      <c r="P62" s="17"/>
+      <c r="Q62" s="17"/>
+      <c r="R62" s="17"/>
+      <c r="S62" s="17"/>
+      <c r="T62" s="17"/>
+      <c r="U62" s="17"/>
+      <c r="V62" s="17"/>
+      <c r="W62" s="17"/>
+      <c r="X62" s="17"/>
+      <c r="Y62" s="17"/>
+      <c r="Z62" s="18"/>
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="19" t="s">
         <v>247</v>
       </c>
-      <c r="B63" s="19">
+      <c r="B63" s="20">
         <v>0.0</v>
       </c>
-      <c r="C63" s="19" t="s">
+      <c r="C63" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="D63" s="19" t="s">
+      <c r="D63" s="20" t="s">
         <v>249</v>
       </c>
-      <c r="E63" s="19" t="s">
+      <c r="E63" s="20" t="s">
         <v>250</v>
       </c>
-      <c r="F63" s="19"/>
-      <c r="G63" s="19"/>
-      <c r="H63" s="19"/>
-      <c r="I63" s="19"/>
-      <c r="J63" s="19"/>
-      <c r="K63" s="19"/>
-      <c r="L63" s="19"/>
-      <c r="M63" s="19"/>
-      <c r="N63" s="19"/>
-      <c r="O63" s="19"/>
-      <c r="P63" s="19"/>
-      <c r="Q63" s="19"/>
-      <c r="R63" s="19"/>
-      <c r="S63" s="19"/>
-      <c r="T63" s="19"/>
-      <c r="U63" s="19"/>
-      <c r="V63" s="19"/>
-      <c r="W63" s="19"/>
-      <c r="X63" s="19"/>
-      <c r="Y63" s="19"/>
-      <c r="Z63" s="15"/>
+      <c r="F63" s="20"/>
+      <c r="G63" s="20"/>
+      <c r="H63" s="20"/>
+      <c r="I63" s="20"/>
+      <c r="J63" s="20"/>
+      <c r="K63" s="20"/>
+      <c r="L63" s="20"/>
+      <c r="M63" s="20"/>
+      <c r="N63" s="20"/>
+      <c r="O63" s="20"/>
+      <c r="P63" s="20"/>
+      <c r="Q63" s="20"/>
+      <c r="R63" s="20"/>
+      <c r="S63" s="20"/>
+      <c r="T63" s="20"/>
+      <c r="U63" s="20"/>
+      <c r="V63" s="20"/>
+      <c r="W63" s="20"/>
+      <c r="X63" s="20"/>
+      <c r="Y63" s="20"/>
+      <c r="Z63" s="18"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="19" t="s">
         <v>251</v>
       </c>
-      <c r="B64" s="19">
+      <c r="B64" s="20">
         <v>0.0</v>
       </c>
-      <c r="C64" s="19" t="s">
+      <c r="C64" s="20" t="s">
         <v>252</v>
       </c>
-      <c r="D64" s="19" t="s">
+      <c r="D64" s="20" t="s">
         <v>253</v>
       </c>
-      <c r="E64" s="19" t="s">
+      <c r="E64" s="20" t="s">
         <v>254</v>
       </c>
-      <c r="F64" s="19"/>
-      <c r="G64" s="19"/>
-      <c r="H64" s="19"/>
-      <c r="I64" s="19"/>
-      <c r="J64" s="19"/>
-      <c r="K64" s="19"/>
-      <c r="L64" s="19"/>
-      <c r="M64" s="19"/>
-      <c r="N64" s="19"/>
-      <c r="O64" s="19"/>
-      <c r="P64" s="19"/>
-      <c r="Q64" s="19"/>
-      <c r="R64" s="19"/>
-      <c r="S64" s="19"/>
-      <c r="T64" s="19"/>
-      <c r="U64" s="19"/>
-      <c r="V64" s="19"/>
-      <c r="W64" s="19"/>
-      <c r="X64" s="19"/>
-      <c r="Y64" s="19"/>
-      <c r="Z64" s="15"/>
+      <c r="F64" s="20"/>
+      <c r="G64" s="20"/>
+      <c r="H64" s="20"/>
+      <c r="I64" s="20"/>
+      <c r="J64" s="20"/>
+      <c r="K64" s="20"/>
+      <c r="L64" s="20"/>
+      <c r="M64" s="20"/>
+      <c r="N64" s="20"/>
+      <c r="O64" s="20"/>
+      <c r="P64" s="20"/>
+      <c r="Q64" s="20"/>
+      <c r="R64" s="20"/>
+      <c r="S64" s="20"/>
+      <c r="T64" s="20"/>
+      <c r="U64" s="20"/>
+      <c r="V64" s="20"/>
+      <c r="W64" s="20"/>
+      <c r="X64" s="20"/>
+      <c r="Y64" s="20"/>
+      <c r="Z64" s="18"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="19" t="s">
         <v>255</v>
       </c>
-      <c r="B65" s="19">
+      <c r="B65" s="20">
         <v>0.0</v>
       </c>
-      <c r="C65" s="19" t="s">
+      <c r="C65" s="20" t="s">
         <v>256</v>
       </c>
-      <c r="D65" s="19" t="s">
+      <c r="D65" s="20" t="s">
         <v>257</v>
       </c>
-      <c r="E65" s="19" t="s">
+      <c r="E65" s="20" t="s">
         <v>258</v>
       </c>
-      <c r="F65" s="19"/>
-      <c r="G65" s="19"/>
-      <c r="H65" s="19"/>
-      <c r="I65" s="19"/>
-      <c r="J65" s="19"/>
-      <c r="K65" s="19"/>
-      <c r="L65" s="19"/>
-      <c r="M65" s="19"/>
-      <c r="N65" s="19"/>
-      <c r="O65" s="19"/>
-      <c r="P65" s="19"/>
-      <c r="Q65" s="19"/>
-      <c r="R65" s="19"/>
-      <c r="S65" s="19"/>
-      <c r="T65" s="19"/>
-      <c r="U65" s="19"/>
-      <c r="V65" s="19"/>
-      <c r="W65" s="19"/>
-      <c r="X65" s="19"/>
-      <c r="Y65" s="19"/>
-      <c r="Z65" s="15"/>
+      <c r="F65" s="20"/>
+      <c r="G65" s="20"/>
+      <c r="H65" s="20"/>
+      <c r="I65" s="20"/>
+      <c r="J65" s="20"/>
+      <c r="K65" s="20"/>
+      <c r="L65" s="20"/>
+      <c r="M65" s="20"/>
+      <c r="N65" s="20"/>
+      <c r="O65" s="20"/>
+      <c r="P65" s="20"/>
+      <c r="Q65" s="20"/>
+      <c r="R65" s="20"/>
+      <c r="S65" s="20"/>
+      <c r="T65" s="20"/>
+      <c r="U65" s="20"/>
+      <c r="V65" s="20"/>
+      <c r="W65" s="20"/>
+      <c r="X65" s="20"/>
+      <c r="Y65" s="20"/>
+      <c r="Z65" s="18"/>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="16" t="s">
+      <c r="A66" s="15" t="s">
         <v>259</v>
       </c>
-      <c r="B66" s="17">
+      <c r="B66" s="16">
         <v>0.0</v>
       </c>
-      <c r="C66" s="18" t="s">
+      <c r="C66" s="17" t="s">
         <v>260</v>
       </c>
-      <c r="D66" s="18" t="s">
+      <c r="D66" s="17" t="s">
         <v>261</v>
       </c>
-      <c r="E66" s="18" t="s">
+      <c r="E66" s="17" t="s">
         <v>262</v>
       </c>
-      <c r="F66" s="18"/>
-      <c r="G66" s="18"/>
-      <c r="H66" s="18"/>
-      <c r="I66" s="18"/>
-      <c r="J66" s="18"/>
-      <c r="K66" s="18"/>
-      <c r="L66" s="18"/>
-      <c r="M66" s="18"/>
-      <c r="N66" s="18"/>
-      <c r="O66" s="18"/>
-      <c r="P66" s="18"/>
-      <c r="Q66" s="18"/>
-      <c r="R66" s="18"/>
-      <c r="S66" s="18"/>
-      <c r="T66" s="18"/>
-      <c r="U66" s="18"/>
-      <c r="V66" s="18"/>
-      <c r="W66" s="18"/>
-      <c r="X66" s="18"/>
-      <c r="Y66" s="18"/>
-      <c r="Z66" s="15"/>
+      <c r="F66" s="17"/>
+      <c r="G66" s="17"/>
+      <c r="H66" s="17"/>
+      <c r="I66" s="17"/>
+      <c r="J66" s="17"/>
+      <c r="K66" s="17"/>
+      <c r="L66" s="17"/>
+      <c r="M66" s="17"/>
+      <c r="N66" s="17"/>
+      <c r="O66" s="17"/>
+      <c r="P66" s="17"/>
+      <c r="Q66" s="17"/>
+      <c r="R66" s="17"/>
+      <c r="S66" s="17"/>
+      <c r="T66" s="17"/>
+      <c r="U66" s="17"/>
+      <c r="V66" s="17"/>
+      <c r="W66" s="17"/>
+      <c r="X66" s="17"/>
+      <c r="Y66" s="17"/>
+      <c r="Z66" s="18"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="16" t="s">
+      <c r="A67" s="15" t="s">
         <v>263</v>
       </c>
-      <c r="B67" s="17">
+      <c r="B67" s="16">
         <v>0.0</v>
       </c>
-      <c r="C67" s="18" t="s">
+      <c r="C67" s="17" t="s">
         <v>264</v>
       </c>
-      <c r="D67" s="18" t="s">
+      <c r="D67" s="17" t="s">
         <v>265</v>
       </c>
-      <c r="E67" s="18" t="s">
+      <c r="E67" s="17" t="s">
         <v>266</v>
       </c>
-      <c r="F67" s="18"/>
-      <c r="G67" s="18"/>
-      <c r="H67" s="18"/>
-      <c r="I67" s="18"/>
-      <c r="J67" s="18"/>
-      <c r="K67" s="18"/>
-      <c r="L67" s="18"/>
-      <c r="M67" s="18"/>
-      <c r="N67" s="18"/>
-      <c r="O67" s="18"/>
-      <c r="P67" s="18"/>
-      <c r="Q67" s="18"/>
-      <c r="R67" s="18"/>
-      <c r="S67" s="18"/>
-      <c r="T67" s="18"/>
-      <c r="U67" s="18"/>
-      <c r="V67" s="18"/>
-      <c r="W67" s="18"/>
-      <c r="X67" s="18"/>
-      <c r="Y67" s="18"/>
-      <c r="Z67" s="15"/>
+      <c r="F67" s="17"/>
+      <c r="G67" s="17"/>
+      <c r="H67" s="17"/>
+      <c r="I67" s="17"/>
+      <c r="J67" s="17"/>
+      <c r="K67" s="17"/>
+      <c r="L67" s="17"/>
+      <c r="M67" s="17"/>
+      <c r="N67" s="17"/>
+      <c r="O67" s="17"/>
+      <c r="P67" s="17"/>
+      <c r="Q67" s="17"/>
+      <c r="R67" s="17"/>
+      <c r="S67" s="17"/>
+      <c r="T67" s="17"/>
+      <c r="U67" s="17"/>
+      <c r="V67" s="17"/>
+      <c r="W67" s="17"/>
+      <c r="X67" s="17"/>
+      <c r="Y67" s="17"/>
+      <c r="Z67" s="18"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="16" t="s">
+      <c r="A68" s="15" t="s">
         <v>267</v>
       </c>
-      <c r="B68" s="17">
+      <c r="B68" s="16">
         <v>0.0</v>
       </c>
-      <c r="C68" s="18" t="s">
+      <c r="C68" s="17" t="s">
         <v>268</v>
       </c>
-      <c r="D68" s="18" t="s">
+      <c r="D68" s="17" t="s">
         <v>269</v>
       </c>
-      <c r="E68" s="18" t="s">
+      <c r="E68" s="17" t="s">
         <v>270</v>
       </c>
-      <c r="F68" s="18"/>
-      <c r="G68" s="18"/>
-      <c r="H68" s="18"/>
-      <c r="I68" s="18"/>
-      <c r="J68" s="18"/>
-      <c r="K68" s="18"/>
-      <c r="L68" s="18"/>
-      <c r="M68" s="18"/>
-      <c r="N68" s="18"/>
-      <c r="O68" s="18"/>
-      <c r="P68" s="18"/>
-      <c r="Q68" s="18"/>
-      <c r="R68" s="18"/>
-      <c r="S68" s="18"/>
-      <c r="T68" s="18"/>
-      <c r="U68" s="18"/>
-      <c r="V68" s="18"/>
-      <c r="W68" s="18"/>
-      <c r="X68" s="18"/>
-      <c r="Y68" s="18"/>
-      <c r="Z68" s="15"/>
+      <c r="F68" s="17"/>
+      <c r="G68" s="17"/>
+      <c r="H68" s="17"/>
+      <c r="I68" s="17"/>
+      <c r="J68" s="17"/>
+      <c r="K68" s="17"/>
+      <c r="L68" s="17"/>
+      <c r="M68" s="17"/>
+      <c r="N68" s="17"/>
+      <c r="O68" s="17"/>
+      <c r="P68" s="17"/>
+      <c r="Q68" s="17"/>
+      <c r="R68" s="17"/>
+      <c r="S68" s="17"/>
+      <c r="T68" s="17"/>
+      <c r="U68" s="17"/>
+      <c r="V68" s="17"/>
+      <c r="W68" s="17"/>
+      <c r="X68" s="17"/>
+      <c r="Y68" s="17"/>
+      <c r="Z68" s="18"/>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="16" t="s">
+      <c r="A69" s="15" t="s">
         <v>271</v>
       </c>
-      <c r="B69" s="17">
+      <c r="B69" s="16">
         <v>0.0</v>
       </c>
-      <c r="C69" s="18" t="s">
+      <c r="C69" s="17" t="s">
         <v>272</v>
       </c>
-      <c r="D69" s="18" t="s">
+      <c r="D69" s="17" t="s">
         <v>273</v>
       </c>
-      <c r="E69" s="18" t="s">
+      <c r="E69" s="17" t="s">
         <v>274</v>
       </c>
-      <c r="F69" s="18"/>
-      <c r="G69" s="18"/>
-      <c r="H69" s="18"/>
-      <c r="I69" s="18"/>
-      <c r="J69" s="18"/>
-      <c r="K69" s="18"/>
-      <c r="L69" s="18"/>
-      <c r="M69" s="18"/>
-      <c r="N69" s="18"/>
-      <c r="O69" s="18"/>
-      <c r="P69" s="18"/>
-      <c r="Q69" s="18"/>
-      <c r="R69" s="18"/>
-      <c r="S69" s="18"/>
-      <c r="T69" s="18"/>
-      <c r="U69" s="18"/>
-      <c r="V69" s="18"/>
-      <c r="W69" s="18"/>
-      <c r="X69" s="18"/>
-      <c r="Y69" s="18"/>
-      <c r="Z69" s="15"/>
+      <c r="F69" s="17"/>
+      <c r="G69" s="17"/>
+      <c r="H69" s="17"/>
+      <c r="I69" s="17"/>
+      <c r="J69" s="17"/>
+      <c r="K69" s="17"/>
+      <c r="L69" s="17"/>
+      <c r="M69" s="17"/>
+      <c r="N69" s="17"/>
+      <c r="O69" s="17"/>
+      <c r="P69" s="17"/>
+      <c r="Q69" s="17"/>
+      <c r="R69" s="17"/>
+      <c r="S69" s="17"/>
+      <c r="T69" s="17"/>
+      <c r="U69" s="17"/>
+      <c r="V69" s="17"/>
+      <c r="W69" s="17"/>
+      <c r="X69" s="17"/>
+      <c r="Y69" s="17"/>
+      <c r="Z69" s="18"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="16" t="s">
+      <c r="A70" s="15" t="s">
         <v>275</v>
       </c>
-      <c r="B70" s="17">
+      <c r="B70" s="16">
         <v>0.0</v>
       </c>
-      <c r="C70" s="18" t="s">
+      <c r="C70" s="17" t="s">
         <v>276</v>
       </c>
-      <c r="D70" s="18" t="s">
+      <c r="D70" s="17" t="s">
         <v>277</v>
       </c>
-      <c r="E70" s="18" t="s">
+      <c r="E70" s="17" t="s">
         <v>278</v>
       </c>
-      <c r="F70" s="18"/>
-      <c r="G70" s="18"/>
-      <c r="H70" s="18"/>
-      <c r="I70" s="18"/>
-      <c r="J70" s="18"/>
-      <c r="K70" s="18"/>
-      <c r="L70" s="18"/>
-      <c r="M70" s="18"/>
-      <c r="N70" s="18"/>
-      <c r="O70" s="18"/>
-      <c r="P70" s="18"/>
-      <c r="Q70" s="18"/>
-      <c r="R70" s="18"/>
-      <c r="S70" s="18"/>
-      <c r="T70" s="18"/>
-      <c r="U70" s="18"/>
-      <c r="V70" s="18"/>
-      <c r="W70" s="18"/>
-      <c r="X70" s="18"/>
-      <c r="Y70" s="18"/>
-      <c r="Z70" s="15"/>
+      <c r="F70" s="17"/>
+      <c r="G70" s="17"/>
+      <c r="H70" s="17"/>
+      <c r="I70" s="17"/>
+      <c r="J70" s="17"/>
+      <c r="K70" s="17"/>
+      <c r="L70" s="17"/>
+      <c r="M70" s="17"/>
+      <c r="N70" s="17"/>
+      <c r="O70" s="17"/>
+      <c r="P70" s="17"/>
+      <c r="Q70" s="17"/>
+      <c r="R70" s="17"/>
+      <c r="S70" s="17"/>
+      <c r="T70" s="17"/>
+      <c r="U70" s="17"/>
+      <c r="V70" s="17"/>
+      <c r="W70" s="17"/>
+      <c r="X70" s="17"/>
+      <c r="Y70" s="17"/>
+      <c r="Z70" s="18"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="16" t="s">
+      <c r="A71" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="B71" s="17">
+      <c r="B71" s="22">
         <v>0.0</v>
       </c>
-      <c r="C71" s="18" t="s">
+      <c r="C71" s="23" t="s">
         <v>280</v>
       </c>
-      <c r="D71" s="18" t="s">
+      <c r="D71" s="23" t="s">
         <v>281</v>
       </c>
-      <c r="E71" s="18" t="s">
+      <c r="E71" s="23" t="s">
         <v>282</v>
       </c>
-      <c r="F71" s="18"/>
-      <c r="G71" s="18"/>
-      <c r="H71" s="18"/>
-      <c r="I71" s="18"/>
-      <c r="J71" s="18"/>
-      <c r="K71" s="18"/>
-      <c r="L71" s="18"/>
-      <c r="M71" s="18"/>
-      <c r="N71" s="18"/>
-      <c r="O71" s="18"/>
-      <c r="P71" s="18"/>
-      <c r="Q71" s="18"/>
-      <c r="R71" s="18"/>
-      <c r="S71" s="18"/>
-      <c r="T71" s="18"/>
-      <c r="U71" s="18"/>
-      <c r="V71" s="18"/>
-      <c r="W71" s="18"/>
-      <c r="X71" s="18"/>
-      <c r="Y71" s="18"/>
-      <c r="Z71" s="15"/>
+      <c r="F71" s="23"/>
+      <c r="G71" s="23"/>
+      <c r="H71" s="23"/>
+      <c r="I71" s="23"/>
+      <c r="J71" s="23"/>
+      <c r="K71" s="23"/>
+      <c r="L71" s="23"/>
+      <c r="M71" s="23"/>
+      <c r="N71" s="23"/>
+      <c r="O71" s="23"/>
+      <c r="P71" s="23"/>
+      <c r="Q71" s="23"/>
+      <c r="R71" s="23"/>
+      <c r="S71" s="23"/>
+      <c r="T71" s="23"/>
+      <c r="U71" s="23"/>
+      <c r="V71" s="23"/>
+      <c r="W71" s="23"/>
+      <c r="X71" s="23"/>
+      <c r="Y71" s="23"/>
+      <c r="Z71" s="24"/>
     </row>
     <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="20" t="s">
+      <c r="A72" s="25" t="s">
         <v>283</v>
       </c>
-      <c r="B72" s="21">
+      <c r="B72" s="26">
         <v>0.0</v>
       </c>
-      <c r="C72" s="21" t="s">
+      <c r="C72" s="26" t="s">
         <v>284</v>
       </c>
-      <c r="D72" s="21" t="s">
+      <c r="D72" s="26" t="s">
         <v>147</v>
       </c>
-      <c r="E72" s="21" t="s">
+      <c r="E72" s="26" t="s">
         <v>148</v>
       </c>
-      <c r="F72" s="21"/>
-      <c r="G72" s="21"/>
-      <c r="H72" s="21"/>
-      <c r="I72" s="21"/>
-      <c r="J72" s="21"/>
-      <c r="K72" s="21"/>
-      <c r="L72" s="21"/>
-      <c r="M72" s="21"/>
-      <c r="N72" s="21"/>
-      <c r="O72" s="21"/>
-      <c r="P72" s="21"/>
-      <c r="Q72" s="21"/>
-      <c r="R72" s="21"/>
-      <c r="S72" s="21"/>
-      <c r="T72" s="21"/>
-      <c r="U72" s="21"/>
-      <c r="V72" s="21"/>
-      <c r="W72" s="21"/>
-      <c r="X72" s="21"/>
-      <c r="Y72" s="21"/>
+      <c r="F72" s="26"/>
+      <c r="G72" s="26"/>
+      <c r="H72" s="26"/>
+      <c r="I72" s="26"/>
+      <c r="J72" s="26"/>
+      <c r="K72" s="26"/>
+      <c r="L72" s="26"/>
+      <c r="M72" s="26"/>
+      <c r="N72" s="26"/>
+      <c r="O72" s="26"/>
+      <c r="P72" s="26"/>
+      <c r="Q72" s="26"/>
+      <c r="R72" s="26"/>
+      <c r="S72" s="26"/>
+      <c r="T72" s="26"/>
+      <c r="U72" s="26"/>
+      <c r="V72" s="26"/>
+      <c r="W72" s="26"/>
+      <c r="X72" s="26"/>
+      <c r="Y72" s="26"/>
+      <c r="Z72" s="27"/>
     </row>
     <row r="73" ht="15.0" customHeight="1">
-      <c r="A73" s="22" t="s">
+      <c r="A73" s="25" t="s">
         <v>285</v>
       </c>
-      <c r="B73" s="23">
+      <c r="B73" s="26">
         <v>0.0</v>
       </c>
-      <c r="C73" s="23" t="s">
+      <c r="C73" s="26" t="s">
         <v>286</v>
       </c>
-      <c r="D73" s="23" t="s">
+      <c r="D73" s="26" t="s">
         <v>287</v>
       </c>
-      <c r="E73" s="23" t="s">
+      <c r="E73" s="26" t="s">
         <v>288</v>
       </c>
-      <c r="F73" s="23"/>
-      <c r="G73" s="23"/>
-      <c r="H73" s="23"/>
-      <c r="I73" s="23"/>
-      <c r="J73" s="23"/>
-      <c r="K73" s="23"/>
-      <c r="L73" s="23"/>
-      <c r="M73" s="23"/>
-      <c r="N73" s="23"/>
-      <c r="O73" s="23"/>
-      <c r="P73" s="23"/>
-      <c r="Q73" s="23"/>
-      <c r="R73" s="23"/>
-      <c r="S73" s="23"/>
-      <c r="T73" s="23"/>
-      <c r="U73" s="23"/>
-      <c r="V73" s="23"/>
-      <c r="W73" s="23"/>
-      <c r="X73" s="23"/>
-      <c r="Y73" s="23"/>
+      <c r="F73" s="26"/>
+      <c r="G73" s="26"/>
+      <c r="H73" s="26"/>
+      <c r="I73" s="26"/>
+      <c r="J73" s="26"/>
+      <c r="K73" s="26"/>
+      <c r="L73" s="26"/>
+      <c r="M73" s="26"/>
+      <c r="N73" s="26"/>
+      <c r="O73" s="26"/>
+      <c r="P73" s="26"/>
+      <c r="Q73" s="26"/>
+      <c r="R73" s="26"/>
+      <c r="S73" s="26"/>
+      <c r="T73" s="26"/>
+      <c r="U73" s="26"/>
+      <c r="V73" s="26"/>
+      <c r="W73" s="26"/>
+      <c r="X73" s="26"/>
+      <c r="Y73" s="26"/>
+      <c r="Z73" s="27"/>
     </row>
     <row r="74" ht="15.0" customHeight="1">
-      <c r="A74" s="22" t="s">
+      <c r="A74" s="25" t="s">
         <v>289</v>
       </c>
-      <c r="B74" s="23">
+      <c r="B74" s="26">
         <v>0.0</v>
       </c>
-      <c r="C74" s="23" t="s">
+      <c r="C74" s="26" t="s">
         <v>290</v>
       </c>
-      <c r="D74" s="23" t="s">
+      <c r="D74" s="26" t="s">
         <v>175</v>
       </c>
-      <c r="E74" s="23" t="s">
+      <c r="E74" s="26" t="s">
         <v>176</v>
       </c>
-      <c r="F74" s="23"/>
-      <c r="G74" s="23"/>
-      <c r="H74" s="23"/>
-      <c r="I74" s="23"/>
-      <c r="J74" s="23"/>
-      <c r="K74" s="23"/>
-      <c r="L74" s="23"/>
-      <c r="M74" s="23"/>
-      <c r="N74" s="23"/>
-      <c r="O74" s="23"/>
-      <c r="P74" s="23"/>
-      <c r="Q74" s="23"/>
-      <c r="R74" s="23"/>
-      <c r="S74" s="23"/>
-      <c r="T74" s="23"/>
-      <c r="U74" s="23"/>
-      <c r="V74" s="23"/>
-      <c r="W74" s="23"/>
-      <c r="X74" s="23"/>
-      <c r="Y74" s="23"/>
+      <c r="F74" s="26"/>
+      <c r="G74" s="26"/>
+      <c r="H74" s="26"/>
+      <c r="I74" s="26"/>
+      <c r="J74" s="26"/>
+      <c r="K74" s="26"/>
+      <c r="L74" s="26"/>
+      <c r="M74" s="26"/>
+      <c r="N74" s="26"/>
+      <c r="O74" s="26"/>
+      <c r="P74" s="26"/>
+      <c r="Q74" s="26"/>
+      <c r="R74" s="26"/>
+      <c r="S74" s="26"/>
+      <c r="T74" s="26"/>
+      <c r="U74" s="26"/>
+      <c r="V74" s="26"/>
+      <c r="W74" s="26"/>
+      <c r="X74" s="26"/>
+      <c r="Y74" s="26"/>
+      <c r="Z74" s="27"/>
     </row>
     <row r="75" ht="15.0" customHeight="1">
-      <c r="A75" s="22" t="s">
+      <c r="A75" s="25" t="s">
         <v>291</v>
       </c>
-      <c r="B75" s="23">
+      <c r="B75" s="26">
         <v>0.0</v>
       </c>
-      <c r="C75" s="23" t="s">
+      <c r="C75" s="26" t="s">
         <v>292</v>
       </c>
-      <c r="D75" s="23" t="s">
+      <c r="D75" s="26" t="s">
         <v>293</v>
       </c>
-      <c r="E75" s="23" t="s">
+      <c r="E75" s="26" t="s">
         <v>294</v>
       </c>
-      <c r="F75" s="23"/>
-      <c r="G75" s="23"/>
-      <c r="H75" s="23"/>
-      <c r="I75" s="23"/>
-      <c r="J75" s="23"/>
-      <c r="K75" s="23"/>
-      <c r="L75" s="23"/>
-      <c r="M75" s="23"/>
-      <c r="N75" s="23"/>
-      <c r="O75" s="23"/>
-      <c r="P75" s="23"/>
-      <c r="Q75" s="23"/>
-      <c r="R75" s="23"/>
-      <c r="S75" s="23"/>
-      <c r="T75" s="23"/>
-      <c r="U75" s="23"/>
-      <c r="V75" s="23"/>
-      <c r="W75" s="23"/>
-      <c r="X75" s="23"/>
-      <c r="Y75" s="23"/>
+      <c r="F75" s="26"/>
+      <c r="G75" s="26"/>
+      <c r="H75" s="26"/>
+      <c r="I75" s="26"/>
+      <c r="J75" s="26"/>
+      <c r="K75" s="26"/>
+      <c r="L75" s="26"/>
+      <c r="M75" s="26"/>
+      <c r="N75" s="26"/>
+      <c r="O75" s="26"/>
+      <c r="P75" s="26"/>
+      <c r="Q75" s="26"/>
+      <c r="R75" s="26"/>
+      <c r="S75" s="26"/>
+      <c r="T75" s="26"/>
+      <c r="U75" s="26"/>
+      <c r="V75" s="26"/>
+      <c r="W75" s="26"/>
+      <c r="X75" s="26"/>
+      <c r="Y75" s="26"/>
+      <c r="Z75" s="27"/>
     </row>
     <row r="76" ht="15.0" customHeight="1">
-      <c r="A76" s="22" t="s">
+      <c r="A76" s="25" t="s">
         <v>295</v>
       </c>
-      <c r="B76" s="23">
+      <c r="B76" s="26">
         <v>0.0</v>
       </c>
-      <c r="C76" s="23" t="s">
+      <c r="C76" s="26" t="s">
         <v>296</v>
       </c>
-      <c r="D76" s="23" t="s">
+      <c r="D76" s="26" t="s">
         <v>297</v>
       </c>
-      <c r="E76" s="23" t="s">
+      <c r="E76" s="26" t="s">
         <v>298</v>
       </c>
-      <c r="F76" s="23"/>
-      <c r="G76" s="23"/>
-      <c r="H76" s="23"/>
-      <c r="I76" s="23"/>
-      <c r="J76" s="23"/>
-      <c r="K76" s="23"/>
-      <c r="L76" s="23"/>
-      <c r="M76" s="23"/>
-      <c r="N76" s="23"/>
-      <c r="O76" s="23"/>
-      <c r="P76" s="23"/>
-      <c r="Q76" s="23"/>
-      <c r="R76" s="23"/>
-      <c r="S76" s="23"/>
-      <c r="T76" s="23"/>
-      <c r="U76" s="23"/>
-      <c r="V76" s="23"/>
-      <c r="W76" s="23"/>
-      <c r="X76" s="23"/>
-      <c r="Y76" s="23"/>
+      <c r="F76" s="26"/>
+      <c r="G76" s="26"/>
+      <c r="H76" s="26"/>
+      <c r="I76" s="26"/>
+      <c r="J76" s="26"/>
+      <c r="K76" s="26"/>
+      <c r="L76" s="26"/>
+      <c r="M76" s="26"/>
+      <c r="N76" s="26"/>
+      <c r="O76" s="26"/>
+      <c r="P76" s="26"/>
+      <c r="Q76" s="26"/>
+      <c r="R76" s="26"/>
+      <c r="S76" s="26"/>
+      <c r="T76" s="26"/>
+      <c r="U76" s="26"/>
+      <c r="V76" s="26"/>
+      <c r="W76" s="26"/>
+      <c r="X76" s="26"/>
+      <c r="Y76" s="26"/>
+      <c r="Z76" s="27"/>
     </row>
     <row r="77" ht="15.0" customHeight="1">
-      <c r="A77" s="22" t="s">
+      <c r="A77" s="25" t="s">
         <v>299</v>
       </c>
-      <c r="B77" s="23">
+      <c r="B77" s="26">
         <v>0.0</v>
       </c>
-      <c r="C77" s="23" t="s">
+      <c r="C77" s="26" t="s">
         <v>300</v>
       </c>
-      <c r="D77" s="23" t="s">
+      <c r="D77" s="26" t="s">
         <v>301</v>
       </c>
-      <c r="E77" s="23" t="s">
+      <c r="E77" s="26" t="s">
         <v>302</v>
       </c>
-      <c r="F77" s="23"/>
-      <c r="G77" s="23"/>
-      <c r="H77" s="23"/>
-      <c r="I77" s="23"/>
-      <c r="J77" s="23"/>
-      <c r="K77" s="23"/>
-      <c r="L77" s="23"/>
-      <c r="M77" s="23"/>
-      <c r="N77" s="23"/>
-      <c r="O77" s="23"/>
-      <c r="P77" s="23"/>
-      <c r="Q77" s="23"/>
-      <c r="R77" s="23"/>
-      <c r="S77" s="23"/>
-      <c r="T77" s="23"/>
-      <c r="U77" s="23"/>
-      <c r="V77" s="23"/>
-      <c r="W77" s="23"/>
-      <c r="X77" s="23"/>
-      <c r="Y77" s="23"/>
+      <c r="F77" s="26"/>
+      <c r="G77" s="26"/>
+      <c r="H77" s="26"/>
+      <c r="I77" s="26"/>
+      <c r="J77" s="26"/>
+      <c r="K77" s="26"/>
+      <c r="L77" s="26"/>
+      <c r="M77" s="26"/>
+      <c r="N77" s="26"/>
+      <c r="O77" s="26"/>
+      <c r="P77" s="26"/>
+      <c r="Q77" s="26"/>
+      <c r="R77" s="26"/>
+      <c r="S77" s="26"/>
+      <c r="T77" s="26"/>
+      <c r="U77" s="26"/>
+      <c r="V77" s="26"/>
+      <c r="W77" s="26"/>
+      <c r="X77" s="26"/>
+      <c r="Y77" s="26"/>
+      <c r="Z77" s="27"/>
     </row>
     <row r="78" ht="15.0" customHeight="1">
-      <c r="A78" s="22" t="s">
+      <c r="A78" s="25" t="s">
         <v>303</v>
       </c>
-      <c r="B78" s="23">
+      <c r="B78" s="26">
         <v>0.0</v>
       </c>
-      <c r="C78" s="23" t="s">
+      <c r="C78" s="26" t="s">
         <v>304</v>
       </c>
-      <c r="D78" s="23" t="s">
+      <c r="D78" s="26" t="s">
         <v>305</v>
       </c>
-      <c r="E78" s="23" t="s">
+      <c r="E78" s="26" t="s">
         <v>306</v>
       </c>
-      <c r="F78" s="23"/>
-      <c r="G78" s="23"/>
-      <c r="H78" s="23"/>
-      <c r="I78" s="23"/>
-      <c r="J78" s="23"/>
-      <c r="K78" s="23"/>
-      <c r="L78" s="23"/>
-      <c r="M78" s="23"/>
-      <c r="N78" s="23"/>
-      <c r="O78" s="23"/>
-      <c r="P78" s="23"/>
-      <c r="Q78" s="23"/>
-      <c r="R78" s="23"/>
-      <c r="S78" s="23"/>
-      <c r="T78" s="23"/>
-      <c r="U78" s="23"/>
-      <c r="V78" s="23"/>
-      <c r="W78" s="23"/>
-      <c r="X78" s="23"/>
-      <c r="Y78" s="23"/>
+      <c r="F78" s="26"/>
+      <c r="G78" s="26"/>
+      <c r="H78" s="26"/>
+      <c r="I78" s="26"/>
+      <c r="J78" s="26"/>
+      <c r="K78" s="26"/>
+      <c r="L78" s="26"/>
+      <c r="M78" s="26"/>
+      <c r="N78" s="26"/>
+      <c r="O78" s="26"/>
+      <c r="P78" s="26"/>
+      <c r="Q78" s="26"/>
+      <c r="R78" s="26"/>
+      <c r="S78" s="26"/>
+      <c r="T78" s="26"/>
+      <c r="U78" s="26"/>
+      <c r="V78" s="26"/>
+      <c r="W78" s="26"/>
+      <c r="X78" s="26"/>
+      <c r="Y78" s="26"/>
+      <c r="Z78" s="27"/>
     </row>
     <row r="79" ht="15.0" customHeight="1">
-      <c r="A79" s="24" t="s">
+      <c r="A79" s="28" t="s">
         <v>307</v>
       </c>
-      <c r="B79" s="25">
+      <c r="B79" s="29">
         <v>0.0</v>
       </c>
-      <c r="C79" s="26" t="s">
+      <c r="C79" s="30" t="s">
         <v>308</v>
       </c>
-      <c r="D79" s="26" t="s">
+      <c r="D79" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="E79" s="26" t="s">
+      <c r="E79" s="30" t="s">
         <v>208</v>
       </c>
-      <c r="F79" s="26"/>
-      <c r="G79" s="26"/>
-      <c r="H79" s="26"/>
-      <c r="I79" s="26"/>
-      <c r="J79" s="26"/>
-      <c r="K79" s="26"/>
-      <c r="L79" s="26"/>
-      <c r="M79" s="26"/>
-      <c r="N79" s="26"/>
-      <c r="O79" s="26"/>
-      <c r="P79" s="26"/>
-      <c r="Q79" s="26"/>
-      <c r="R79" s="26"/>
-      <c r="S79" s="26"/>
-      <c r="T79" s="26"/>
-      <c r="U79" s="26"/>
-      <c r="V79" s="26"/>
-      <c r="W79" s="26"/>
-      <c r="X79" s="26"/>
-      <c r="Y79" s="26"/>
+      <c r="F79" s="30"/>
+      <c r="G79" s="30"/>
+      <c r="H79" s="30"/>
+      <c r="I79" s="30"/>
+      <c r="J79" s="30"/>
+      <c r="K79" s="30"/>
+      <c r="L79" s="30"/>
+      <c r="M79" s="30"/>
+      <c r="N79" s="30"/>
+      <c r="O79" s="30"/>
+      <c r="P79" s="30"/>
+      <c r="Q79" s="30"/>
+      <c r="R79" s="30"/>
+      <c r="S79" s="30"/>
+      <c r="T79" s="30"/>
+      <c r="U79" s="30"/>
+      <c r="V79" s="30"/>
+      <c r="W79" s="30"/>
+      <c r="X79" s="30"/>
+      <c r="Y79" s="30"/>
+      <c r="Z79" s="27"/>
     </row>
     <row r="80" ht="15.0" customHeight="1">
-      <c r="A80" s="24" t="s">
+      <c r="A80" s="28" t="s">
         <v>309</v>
       </c>
-      <c r="B80" s="25">
+      <c r="B80" s="29">
         <v>0.0</v>
       </c>
-      <c r="C80" s="26" t="s">
+      <c r="C80" s="30" t="s">
         <v>310</v>
       </c>
-      <c r="D80" s="26" t="s">
+      <c r="D80" s="30" t="s">
         <v>139</v>
       </c>
-      <c r="E80" s="26" t="s">
+      <c r="E80" s="30" t="s">
         <v>140</v>
       </c>
-      <c r="F80" s="26"/>
-      <c r="G80" s="26"/>
-      <c r="H80" s="26"/>
-      <c r="I80" s="26"/>
-      <c r="J80" s="26"/>
-      <c r="K80" s="26"/>
-      <c r="L80" s="26"/>
-      <c r="M80" s="26"/>
-      <c r="N80" s="26"/>
-      <c r="O80" s="26"/>
-      <c r="P80" s="26"/>
-      <c r="Q80" s="26"/>
-      <c r="R80" s="26"/>
-      <c r="S80" s="26"/>
-      <c r="T80" s="26"/>
-      <c r="U80" s="26"/>
-      <c r="V80" s="26"/>
-      <c r="W80" s="26"/>
-      <c r="X80" s="26"/>
-      <c r="Y80" s="26"/>
+      <c r="F80" s="30"/>
+      <c r="G80" s="30"/>
+      <c r="H80" s="30"/>
+      <c r="I80" s="30"/>
+      <c r="J80" s="30"/>
+      <c r="K80" s="30"/>
+      <c r="L80" s="30"/>
+      <c r="M80" s="30"/>
+      <c r="N80" s="30"/>
+      <c r="O80" s="30"/>
+      <c r="P80" s="30"/>
+      <c r="Q80" s="30"/>
+      <c r="R80" s="30"/>
+      <c r="S80" s="30"/>
+      <c r="T80" s="30"/>
+      <c r="U80" s="30"/>
+      <c r="V80" s="30"/>
+      <c r="W80" s="30"/>
+      <c r="X80" s="30"/>
+      <c r="Y80" s="30"/>
+      <c r="Z80" s="27"/>
     </row>
     <row r="81" ht="15.0" customHeight="1">
-      <c r="A81" s="24" t="s">
+      <c r="A81" s="28" t="s">
         <v>311</v>
       </c>
-      <c r="B81" s="25">
+      <c r="B81" s="29">
         <v>0.0</v>
       </c>
-      <c r="C81" s="26" t="s">
+      <c r="C81" s="30" t="s">
         <v>312</v>
       </c>
-      <c r="D81" s="26" t="s">
+      <c r="D81" s="30" t="s">
         <v>313</v>
       </c>
-      <c r="E81" s="26" t="s">
+      <c r="E81" s="30" t="s">
         <v>314</v>
       </c>
-      <c r="F81" s="26"/>
-      <c r="G81" s="26"/>
-      <c r="H81" s="26"/>
-      <c r="I81" s="26"/>
-      <c r="J81" s="26"/>
-      <c r="K81" s="26"/>
-      <c r="L81" s="26"/>
-      <c r="M81" s="26"/>
-      <c r="N81" s="26"/>
-      <c r="O81" s="26"/>
-      <c r="P81" s="26"/>
-      <c r="Q81" s="26"/>
-      <c r="R81" s="26"/>
-      <c r="S81" s="26"/>
-      <c r="T81" s="26"/>
-      <c r="U81" s="26"/>
-      <c r="V81" s="26"/>
-      <c r="W81" s="26"/>
-      <c r="X81" s="26"/>
-      <c r="Y81" s="26"/>
+      <c r="F81" s="30"/>
+      <c r="G81" s="30"/>
+      <c r="H81" s="30"/>
+      <c r="I81" s="30"/>
+      <c r="J81" s="30"/>
+      <c r="K81" s="30"/>
+      <c r="L81" s="30"/>
+      <c r="M81" s="30"/>
+      <c r="N81" s="30"/>
+      <c r="O81" s="30"/>
+      <c r="P81" s="30"/>
+      <c r="Q81" s="30"/>
+      <c r="R81" s="30"/>
+      <c r="S81" s="30"/>
+      <c r="T81" s="30"/>
+      <c r="U81" s="30"/>
+      <c r="V81" s="30"/>
+      <c r="W81" s="30"/>
+      <c r="X81" s="30"/>
+      <c r="Y81" s="30"/>
+      <c r="Z81" s="27"/>
     </row>
     <row r="82" ht="15.0" customHeight="1">
-      <c r="A82" s="27" t="s">
+      <c r="A82" s="31" t="s">
         <v>315</v>
       </c>
-      <c r="B82" s="28">
+      <c r="B82" s="32">
         <v>0.0</v>
       </c>
-      <c r="C82" s="29" t="s">
+      <c r="C82" s="33" t="s">
         <v>316</v>
       </c>
-      <c r="D82" s="29" t="s">
+      <c r="D82" s="33" t="s">
         <v>317</v>
       </c>
-      <c r="E82" s="29" t="s">
+      <c r="E82" s="33" t="s">
         <v>318</v>
       </c>
-      <c r="F82" s="29"/>
-      <c r="G82" s="29"/>
-      <c r="H82" s="29"/>
-      <c r="I82" s="29"/>
-      <c r="J82" s="29"/>
-      <c r="K82" s="29"/>
-      <c r="L82" s="29"/>
-      <c r="M82" s="29"/>
-      <c r="N82" s="29"/>
-      <c r="O82" s="29"/>
-      <c r="P82" s="29"/>
-      <c r="Q82" s="29"/>
-      <c r="R82" s="29"/>
-      <c r="S82" s="29"/>
-      <c r="T82" s="29"/>
-      <c r="U82" s="29"/>
-      <c r="V82" s="29"/>
-      <c r="W82" s="29"/>
-      <c r="X82" s="29"/>
-      <c r="Y82" s="29"/>
+      <c r="F82" s="33"/>
+      <c r="G82" s="33"/>
+      <c r="H82" s="33"/>
+      <c r="I82" s="33"/>
+      <c r="J82" s="33"/>
+      <c r="K82" s="33"/>
+      <c r="L82" s="33"/>
+      <c r="M82" s="33"/>
+      <c r="N82" s="33"/>
+      <c r="O82" s="33"/>
+      <c r="P82" s="33"/>
+      <c r="Q82" s="33"/>
+      <c r="R82" s="33"/>
+      <c r="S82" s="33"/>
+      <c r="T82" s="33"/>
+      <c r="U82" s="33"/>
+      <c r="V82" s="33"/>
+      <c r="W82" s="33"/>
+      <c r="X82" s="33"/>
+      <c r="Y82" s="33"/>
+      <c r="Z82" s="34"/>
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="1"/>

--- a/Templates/Tables/StringInfo/StrTable.xlsx
+++ b/Templates/Tables/StringInfo/StrTable.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="323">
   <si>
     <t>Description</t>
   </si>
@@ -122,6 +122,18 @@
   </si>
   <si>
     <t>Do you want to remove the chapter?</t>
+  </si>
+  <si>
+    <t>에디터 구글 시트 로드 팝업 메세지</t>
+  </si>
+  <si>
+    <t>EDITOR_GOOGLE_SLP_MSG</t>
+  </si>
+  <si>
+    <t>구글 시트 로드에 실패했습니다</t>
+  </si>
+  <si>
+    <t>You have failed to load google sheet</t>
   </si>
   <si>
     <t>종료 팝업 메세지</t>
@@ -974,7 +986,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -984,11 +996,6 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <color rgb="FF000000"/>
@@ -1027,7 +1034,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="6">
     <border/>
     <border>
       <left style="thin">
@@ -1043,22 +1050,9 @@
       </top>
     </border>
     <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
     </border>
     <border>
       <left style="thin">
@@ -1073,19 +1067,11 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
-    <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="31">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1099,8 +1085,7 @@
     <xf borderId="2" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="3" fillId="3" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1109,8 +1094,16 @@
     <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="5" fillId="3" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="3" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
     <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -1122,8 +1115,7 @@
     <xf borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="3" fillId="4" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1132,23 +1124,20 @@
     <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="4" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="6" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="7" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="7" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="8" fillId="4" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="5" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="3" fillId="5" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="5" fillId="5" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1157,16 +1146,15 @@
     <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="6" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="7" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="7" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="8" fillId="5" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1380,12 +1368,12 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="23.0"/>
+    <col customWidth="1" min="1" max="1" width="23.5"/>
     <col customWidth="1" min="2" max="2" width="12.63"/>
     <col customWidth="1" min="3" max="3" width="32.63"/>
     <col customWidth="1" min="4" max="4" width="85.88"/>
     <col customWidth="1" min="5" max="5" width="98.0"/>
-    <col customWidth="1" min="6" max="26" width="12.63"/>
+    <col customWidth="1" min="6" max="25" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
@@ -1461,729 +1449,709 @@
       <c r="W2" s="4"/>
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
-      <c r="Z2" s="5"/>
     </row>
     <row r="3" ht="15.0" customHeight="1">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>0.0</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8"/>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="8"/>
-      <c r="S3" s="8"/>
-      <c r="T3" s="8"/>
-      <c r="U3" s="8"/>
-      <c r="V3" s="8"/>
-      <c r="W3" s="8"/>
-      <c r="X3" s="8"/>
-      <c r="Y3" s="8"/>
-      <c r="Z3" s="9"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7"/>
+      <c r="S3" s="7"/>
+      <c r="T3" s="7"/>
+      <c r="U3" s="7"/>
+      <c r="V3" s="7"/>
+      <c r="W3" s="7"/>
+      <c r="X3" s="7"/>
+      <c r="Y3" s="7"/>
     </row>
     <row r="4" ht="15.0" customHeight="1">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="6">
         <v>0.0</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="8"/>
-      <c r="Q4" s="8"/>
-      <c r="R4" s="8"/>
-      <c r="S4" s="8"/>
-      <c r="T4" s="8"/>
-      <c r="U4" s="8"/>
-      <c r="V4" s="8"/>
-      <c r="W4" s="8"/>
-      <c r="X4" s="8"/>
-      <c r="Y4" s="8"/>
-      <c r="Z4" s="9"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="7"/>
+      <c r="S4" s="7"/>
+      <c r="T4" s="7"/>
+      <c r="U4" s="7"/>
+      <c r="V4" s="7"/>
+      <c r="W4" s="7"/>
+      <c r="X4" s="7"/>
+      <c r="Y4" s="7"/>
     </row>
     <row r="5" ht="15.0" customHeight="1">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>0.0</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8"/>
-      <c r="N5" s="8"/>
-      <c r="O5" s="8"/>
-      <c r="P5" s="8"/>
-      <c r="Q5" s="8"/>
-      <c r="R5" s="8"/>
-      <c r="S5" s="8"/>
-      <c r="T5" s="8"/>
-      <c r="U5" s="8"/>
-      <c r="V5" s="8"/>
-      <c r="W5" s="8"/>
-      <c r="X5" s="8"/>
-      <c r="Y5" s="8"/>
-      <c r="Z5" s="9"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7"/>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7"/>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7"/>
     </row>
     <row r="6" ht="15.0" customHeight="1">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="6">
         <v>0.0</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="8"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="8"/>
-      <c r="U6" s="8"/>
-      <c r="V6" s="8"/>
-      <c r="W6" s="8"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="8"/>
-      <c r="Z6" s="9"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7"/>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7"/>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7"/>
     </row>
     <row r="7" ht="15.0" customHeight="1">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="6">
         <v>0.0</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="8"/>
-      <c r="S7" s="8"/>
-      <c r="T7" s="8"/>
-      <c r="U7" s="8"/>
-      <c r="V7" s="8"/>
-      <c r="W7" s="8"/>
-      <c r="X7" s="8"/>
-      <c r="Y7" s="8"/>
-      <c r="Z7" s="9"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="7"/>
+      <c r="U7" s="7"/>
+      <c r="V7" s="7"/>
+      <c r="W7" s="7"/>
+      <c r="X7" s="7"/>
+      <c r="Y7" s="7"/>
     </row>
     <row r="8" ht="15.0" customHeight="1">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="6">
         <v>0.0</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="8"/>
-      <c r="R8" s="8"/>
-      <c r="S8" s="8"/>
-      <c r="T8" s="8"/>
-      <c r="U8" s="8"/>
-      <c r="V8" s="8"/>
-      <c r="W8" s="8"/>
-      <c r="X8" s="8"/>
-      <c r="Y8" s="8"/>
-      <c r="Z8" s="9"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="7"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="7"/>
+      <c r="U8" s="7"/>
+      <c r="V8" s="7"/>
+      <c r="W8" s="7"/>
+      <c r="X8" s="7"/>
+      <c r="Y8" s="7"/>
     </row>
     <row r="9" ht="15.0" customHeight="1">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="6">
         <v>0.0</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="8"/>
-      <c r="S9" s="8"/>
-      <c r="T9" s="8"/>
-      <c r="U9" s="8"/>
-      <c r="V9" s="8"/>
-      <c r="W9" s="8"/>
-      <c r="X9" s="8"/>
-      <c r="Y9" s="8"/>
-      <c r="Z9" s="9"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="7"/>
+      <c r="S9" s="7"/>
+      <c r="T9" s="7"/>
+      <c r="U9" s="7"/>
+      <c r="V9" s="7"/>
+      <c r="W9" s="7"/>
+      <c r="X9" s="7"/>
+      <c r="Y9" s="7"/>
     </row>
     <row r="10" ht="15.0" customHeight="1">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="9">
         <v>0.0</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="8"/>
-      <c r="P10" s="8"/>
-      <c r="Q10" s="8"/>
-      <c r="R10" s="8"/>
-      <c r="S10" s="8"/>
-      <c r="T10" s="8"/>
-      <c r="U10" s="8"/>
-      <c r="V10" s="8"/>
-      <c r="W10" s="8"/>
-      <c r="X10" s="8"/>
-      <c r="Y10" s="8"/>
-      <c r="Z10" s="9"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="7"/>
+      <c r="P10" s="7"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="7"/>
+      <c r="S10" s="7"/>
+      <c r="T10" s="7"/>
+      <c r="U10" s="7"/>
+      <c r="V10" s="7"/>
+      <c r="W10" s="7"/>
+      <c r="X10" s="7"/>
+      <c r="Y10" s="7"/>
     </row>
     <row r="11" ht="15.0" customHeight="1">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="6">
         <v>0.0</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
-      <c r="N11" s="8"/>
-      <c r="O11" s="8"/>
-      <c r="P11" s="8"/>
-      <c r="Q11" s="8"/>
-      <c r="R11" s="8"/>
-      <c r="S11" s="8"/>
-      <c r="T11" s="8"/>
-      <c r="U11" s="8"/>
-      <c r="V11" s="8"/>
-      <c r="W11" s="8"/>
-      <c r="X11" s="8"/>
-      <c r="Y11" s="8"/>
-      <c r="Z11" s="9"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="7"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="7"/>
+      <c r="U11" s="7"/>
+      <c r="V11" s="7"/>
+      <c r="W11" s="7"/>
+      <c r="X11" s="7"/>
+      <c r="Y11" s="7"/>
     </row>
     <row r="12" ht="15.0" customHeight="1">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="6">
         <v>0.0</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="8"/>
-      <c r="Q12" s="8"/>
-      <c r="R12" s="8"/>
-      <c r="S12" s="8"/>
-      <c r="T12" s="8"/>
-      <c r="U12" s="8"/>
-      <c r="V12" s="8"/>
-      <c r="W12" s="8"/>
-      <c r="X12" s="8"/>
-      <c r="Y12" s="8"/>
-      <c r="Z12" s="9"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="7"/>
+      <c r="P12" s="7"/>
+      <c r="Q12" s="7"/>
+      <c r="R12" s="7"/>
+      <c r="S12" s="7"/>
+      <c r="T12" s="7"/>
+      <c r="U12" s="7"/>
+      <c r="V12" s="7"/>
+      <c r="W12" s="7"/>
+      <c r="X12" s="7"/>
+      <c r="Y12" s="7"/>
     </row>
     <row r="13" ht="15.0" customHeight="1">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="6">
         <v>0.0</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="8"/>
-      <c r="N13" s="8"/>
-      <c r="O13" s="8"/>
-      <c r="P13" s="8"/>
-      <c r="Q13" s="8"/>
-      <c r="R13" s="8"/>
-      <c r="S13" s="8"/>
-      <c r="T13" s="8"/>
-      <c r="U13" s="8"/>
-      <c r="V13" s="8"/>
-      <c r="W13" s="8"/>
-      <c r="X13" s="8"/>
-      <c r="Y13" s="8"/>
-      <c r="Z13" s="9"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
+      <c r="P13" s="7"/>
+      <c r="Q13" s="7"/>
+      <c r="R13" s="7"/>
+      <c r="S13" s="7"/>
+      <c r="T13" s="7"/>
+      <c r="U13" s="7"/>
+      <c r="V13" s="7"/>
+      <c r="W13" s="7"/>
+      <c r="X13" s="7"/>
+      <c r="Y13" s="7"/>
     </row>
     <row r="14" ht="15.0" customHeight="1">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="6">
         <v>0.0</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8"/>
-      <c r="O14" s="8"/>
-      <c r="P14" s="8"/>
-      <c r="Q14" s="8"/>
-      <c r="R14" s="8"/>
-      <c r="S14" s="8"/>
-      <c r="T14" s="8"/>
-      <c r="U14" s="8"/>
-      <c r="V14" s="8"/>
-      <c r="W14" s="8"/>
-      <c r="X14" s="8"/>
-      <c r="Y14" s="8"/>
-      <c r="Z14" s="9"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="7"/>
+      <c r="R14" s="7"/>
+      <c r="S14" s="7"/>
+      <c r="T14" s="7"/>
+      <c r="U14" s="7"/>
+      <c r="V14" s="7"/>
+      <c r="W14" s="7"/>
+      <c r="X14" s="7"/>
+      <c r="Y14" s="7"/>
     </row>
     <row r="15" ht="15.0" customHeight="1">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="6">
         <v>0.0</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
-      <c r="N15" s="8"/>
-      <c r="O15" s="8"/>
-      <c r="P15" s="8"/>
-      <c r="Q15" s="8"/>
-      <c r="R15" s="8"/>
-      <c r="S15" s="8"/>
-      <c r="T15" s="8"/>
-      <c r="U15" s="8"/>
-      <c r="V15" s="8"/>
-      <c r="W15" s="8"/>
-      <c r="X15" s="8"/>
-      <c r="Y15" s="8"/>
-      <c r="Z15" s="9"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7"/>
+      <c r="R15" s="7"/>
+      <c r="S15" s="7"/>
+      <c r="T15" s="7"/>
+      <c r="U15" s="7"/>
+      <c r="V15" s="7"/>
+      <c r="W15" s="7"/>
+      <c r="X15" s="7"/>
+      <c r="Y15" s="7"/>
     </row>
     <row r="16" ht="15.0" customHeight="1">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="6">
         <v>0.0</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
-      <c r="N16" s="8"/>
-      <c r="O16" s="8"/>
-      <c r="P16" s="8"/>
-      <c r="Q16" s="8"/>
-      <c r="R16" s="8"/>
-      <c r="S16" s="8"/>
-      <c r="T16" s="8"/>
-      <c r="U16" s="8"/>
-      <c r="V16" s="8"/>
-      <c r="W16" s="8"/>
-      <c r="X16" s="8"/>
-      <c r="Y16" s="8"/>
-      <c r="Z16" s="9"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
+      <c r="O16" s="7"/>
+      <c r="P16" s="7"/>
+      <c r="Q16" s="7"/>
+      <c r="R16" s="7"/>
+      <c r="S16" s="7"/>
+      <c r="T16" s="7"/>
+      <c r="U16" s="7"/>
+      <c r="V16" s="7"/>
+      <c r="W16" s="7"/>
+      <c r="X16" s="7"/>
+      <c r="Y16" s="7"/>
     </row>
     <row r="17" ht="15.0" customHeight="1">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="6">
         <v>0.0</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
-      <c r="N17" s="8"/>
-      <c r="O17" s="8"/>
-      <c r="P17" s="8"/>
-      <c r="Q17" s="8"/>
-      <c r="R17" s="8"/>
-      <c r="S17" s="8"/>
-      <c r="T17" s="8"/>
-      <c r="U17" s="8"/>
-      <c r="V17" s="8"/>
-      <c r="W17" s="8"/>
-      <c r="X17" s="8"/>
-      <c r="Y17" s="8"/>
-      <c r="Z17" s="9"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="7"/>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="7"/>
+      <c r="R17" s="7"/>
+      <c r="S17" s="7"/>
+      <c r="T17" s="7"/>
+      <c r="U17" s="7"/>
+      <c r="V17" s="7"/>
+      <c r="W17" s="7"/>
+      <c r="X17" s="7"/>
+      <c r="Y17" s="7"/>
     </row>
     <row r="18" ht="15.0" customHeight="1">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="6">
         <v>0.0</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
-      <c r="N18" s="8"/>
-      <c r="O18" s="8"/>
-      <c r="P18" s="8"/>
-      <c r="Q18" s="8"/>
-      <c r="R18" s="8"/>
-      <c r="S18" s="8"/>
-      <c r="T18" s="8"/>
-      <c r="U18" s="8"/>
-      <c r="V18" s="8"/>
-      <c r="W18" s="8"/>
-      <c r="X18" s="8"/>
-      <c r="Y18" s="8"/>
-      <c r="Z18" s="9"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="7"/>
+      <c r="O18" s="7"/>
+      <c r="P18" s="7"/>
+      <c r="Q18" s="7"/>
+      <c r="R18" s="7"/>
+      <c r="S18" s="7"/>
+      <c r="T18" s="7"/>
+      <c r="U18" s="7"/>
+      <c r="V18" s="7"/>
+      <c r="W18" s="7"/>
+      <c r="X18" s="7"/>
+      <c r="Y18" s="7"/>
     </row>
     <row r="19" ht="15.0" customHeight="1">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="6">
         <v>0.0</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="8"/>
-      <c r="N19" s="8"/>
-      <c r="O19" s="8"/>
-      <c r="P19" s="8"/>
-      <c r="Q19" s="8"/>
-      <c r="R19" s="8"/>
-      <c r="S19" s="8"/>
-      <c r="T19" s="8"/>
-      <c r="U19" s="8"/>
-      <c r="V19" s="8"/>
-      <c r="W19" s="8"/>
-      <c r="X19" s="8"/>
-      <c r="Y19" s="8"/>
-      <c r="Z19" s="9"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="7"/>
+      <c r="O19" s="7"/>
+      <c r="P19" s="7"/>
+      <c r="Q19" s="7"/>
+      <c r="R19" s="7"/>
+      <c r="S19" s="7"/>
+      <c r="T19" s="7"/>
+      <c r="U19" s="7"/>
+      <c r="V19" s="7"/>
+      <c r="W19" s="7"/>
+      <c r="X19" s="7"/>
+      <c r="Y19" s="7"/>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B20" s="12">
+      <c r="B20" s="6">
         <v>0.0</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D20" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="E20" s="13" t="s">
+      <c r="E20" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
-      <c r="L20" s="13"/>
-      <c r="M20" s="13"/>
-      <c r="N20" s="13"/>
-      <c r="O20" s="13"/>
-      <c r="P20" s="13"/>
-      <c r="Q20" s="13"/>
-      <c r="R20" s="13"/>
-      <c r="S20" s="13"/>
-      <c r="T20" s="13"/>
-      <c r="U20" s="13"/>
-      <c r="V20" s="13"/>
-      <c r="W20" s="13"/>
-      <c r="X20" s="13"/>
-      <c r="Y20" s="13"/>
-      <c r="Z20" s="14"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="7"/>
+      <c r="O20" s="7"/>
+      <c r="P20" s="7"/>
+      <c r="Q20" s="7"/>
+      <c r="R20" s="7"/>
+      <c r="S20" s="7"/>
+      <c r="T20" s="7"/>
+      <c r="U20" s="7"/>
+      <c r="V20" s="7"/>
+      <c r="W20" s="7"/>
+      <c r="X20" s="7"/>
+      <c r="Y20" s="7"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="B21" s="16">
+      <c r="B21" s="13">
         <v>0.0</v>
       </c>
-      <c r="C21" s="17" t="s">
+      <c r="C21" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="D21" s="17" t="s">
+      <c r="D21" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="E21" s="17" t="s">
+      <c r="E21" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="17"/>
-      <c r="L21" s="17"/>
-      <c r="M21" s="17"/>
-      <c r="N21" s="17"/>
-      <c r="O21" s="17"/>
-      <c r="P21" s="17"/>
-      <c r="Q21" s="17"/>
-      <c r="R21" s="17"/>
-      <c r="S21" s="17"/>
-      <c r="T21" s="17"/>
-      <c r="U21" s="17"/>
-      <c r="V21" s="17"/>
-      <c r="W21" s="17"/>
-      <c r="X21" s="17"/>
-      <c r="Y21" s="17"/>
-      <c r="Z21" s="18"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="14"/>
+      <c r="L21" s="14"/>
+      <c r="M21" s="14"/>
+      <c r="N21" s="14"/>
+      <c r="O21" s="14"/>
+      <c r="P21" s="14"/>
+      <c r="Q21" s="14"/>
+      <c r="R21" s="14"/>
+      <c r="S21" s="14"/>
+      <c r="T21" s="14"/>
+      <c r="U21" s="14"/>
+      <c r="V21" s="14"/>
+      <c r="W21" s="14"/>
+      <c r="X21" s="14"/>
+      <c r="Y21" s="14"/>
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="15" t="s">
@@ -2221,7 +2189,6 @@
       <c r="W22" s="17"/>
       <c r="X22" s="17"/>
       <c r="Y22" s="17"/>
-      <c r="Z22" s="18"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="15" t="s">
@@ -2259,7 +2226,6 @@
       <c r="W23" s="17"/>
       <c r="X23" s="17"/>
       <c r="Y23" s="17"/>
-      <c r="Z23" s="18"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="15" t="s">
@@ -2297,7 +2263,6 @@
       <c r="W24" s="17"/>
       <c r="X24" s="17"/>
       <c r="Y24" s="17"/>
-      <c r="Z24" s="18"/>
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="15" t="s">
@@ -2335,7 +2300,6 @@
       <c r="W25" s="17"/>
       <c r="X25" s="17"/>
       <c r="Y25" s="17"/>
-      <c r="Z25" s="18"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="15" t="s">
@@ -2373,7 +2337,6 @@
       <c r="W26" s="17"/>
       <c r="X26" s="17"/>
       <c r="Y26" s="17"/>
-      <c r="Z26" s="18"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="15" t="s">
@@ -2411,7 +2374,6 @@
       <c r="W27" s="17"/>
       <c r="X27" s="17"/>
       <c r="Y27" s="17"/>
-      <c r="Z27" s="18"/>
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="15" t="s">
@@ -2449,7 +2411,6 @@
       <c r="W28" s="17"/>
       <c r="X28" s="17"/>
       <c r="Y28" s="17"/>
-      <c r="Z28" s="18"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="15" t="s">
@@ -2487,7 +2448,6 @@
       <c r="W29" s="17"/>
       <c r="X29" s="17"/>
       <c r="Y29" s="17"/>
-      <c r="Z29" s="18"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="15" t="s">
@@ -2525,7 +2485,6 @@
       <c r="W30" s="17"/>
       <c r="X30" s="17"/>
       <c r="Y30" s="17"/>
-      <c r="Z30" s="18"/>
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="15" t="s">
@@ -2563,7 +2522,6 @@
       <c r="W31" s="17"/>
       <c r="X31" s="17"/>
       <c r="Y31" s="17"/>
-      <c r="Z31" s="18"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="15" t="s">
@@ -2601,7 +2559,6 @@
       <c r="W32" s="17"/>
       <c r="X32" s="17"/>
       <c r="Y32" s="17"/>
-      <c r="Z32" s="18"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="15" t="s">
@@ -2639,7 +2596,6 @@
       <c r="W33" s="17"/>
       <c r="X33" s="17"/>
       <c r="Y33" s="17"/>
-      <c r="Z33" s="18"/>
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="15" t="s">
@@ -2677,7 +2633,6 @@
       <c r="W34" s="17"/>
       <c r="X34" s="17"/>
       <c r="Y34" s="17"/>
-      <c r="Z34" s="18"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="15" t="s">
@@ -2715,7 +2670,6 @@
       <c r="W35" s="17"/>
       <c r="X35" s="17"/>
       <c r="Y35" s="17"/>
-      <c r="Z35" s="18"/>
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="15" t="s">
@@ -2753,7 +2707,6 @@
       <c r="W36" s="17"/>
       <c r="X36" s="17"/>
       <c r="Y36" s="17"/>
-      <c r="Z36" s="18"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="15" t="s">
@@ -2791,7 +2744,6 @@
       <c r="W37" s="17"/>
       <c r="X37" s="17"/>
       <c r="Y37" s="17"/>
-      <c r="Z37" s="18"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="15" t="s">
@@ -2829,7 +2781,6 @@
       <c r="W38" s="17"/>
       <c r="X38" s="17"/>
       <c r="Y38" s="17"/>
-      <c r="Z38" s="18"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="15" t="s">
@@ -2867,7 +2818,6 @@
       <c r="W39" s="17"/>
       <c r="X39" s="17"/>
       <c r="Y39" s="17"/>
-      <c r="Z39" s="18"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="15" t="s">
@@ -2905,7 +2855,6 @@
       <c r="W40" s="17"/>
       <c r="X40" s="17"/>
       <c r="Y40" s="17"/>
-      <c r="Z40" s="18"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="15" t="s">
@@ -2943,7 +2892,6 @@
       <c r="W41" s="17"/>
       <c r="X41" s="17"/>
       <c r="Y41" s="17"/>
-      <c r="Z41" s="18"/>
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="15" t="s">
@@ -2981,7 +2929,6 @@
       <c r="W42" s="17"/>
       <c r="X42" s="17"/>
       <c r="Y42" s="17"/>
-      <c r="Z42" s="18"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="15" t="s">
@@ -3019,7 +2966,6 @@
       <c r="W43" s="17"/>
       <c r="X43" s="17"/>
       <c r="Y43" s="17"/>
-      <c r="Z43" s="18"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="15" t="s">
@@ -3057,7 +3003,6 @@
       <c r="W44" s="17"/>
       <c r="X44" s="17"/>
       <c r="Y44" s="17"/>
-      <c r="Z44" s="18"/>
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="15" t="s">
@@ -3095,7 +3040,6 @@
       <c r="W45" s="17"/>
       <c r="X45" s="17"/>
       <c r="Y45" s="17"/>
-      <c r="Z45" s="18"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="15" t="s">
@@ -3133,7 +3077,6 @@
       <c r="W46" s="17"/>
       <c r="X46" s="17"/>
       <c r="Y46" s="17"/>
-      <c r="Z46" s="18"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="15" t="s">
@@ -3171,7 +3114,6 @@
       <c r="W47" s="17"/>
       <c r="X47" s="17"/>
       <c r="Y47" s="17"/>
-      <c r="Z47" s="18"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="15" t="s">
@@ -3209,7 +3151,6 @@
       <c r="W48" s="17"/>
       <c r="X48" s="17"/>
       <c r="Y48" s="17"/>
-      <c r="Z48" s="18"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="15" t="s">
@@ -3247,7 +3188,6 @@
       <c r="W49" s="17"/>
       <c r="X49" s="17"/>
       <c r="Y49" s="17"/>
-      <c r="Z49" s="18"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="15" t="s">
@@ -3285,7 +3225,6 @@
       <c r="W50" s="17"/>
       <c r="X50" s="17"/>
       <c r="Y50" s="17"/>
-      <c r="Z50" s="18"/>
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="15" t="s">
@@ -3323,7 +3262,6 @@
       <c r="W51" s="17"/>
       <c r="X51" s="17"/>
       <c r="Y51" s="17"/>
-      <c r="Z51" s="18"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="15" t="s">
@@ -3361,7 +3299,6 @@
       <c r="W52" s="17"/>
       <c r="X52" s="17"/>
       <c r="Y52" s="17"/>
-      <c r="Z52" s="18"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="15" t="s">
@@ -3374,10 +3311,10 @@
         <v>210</v>
       </c>
       <c r="D53" s="17" t="s">
-        <v>59</v>
+        <v>211</v>
       </c>
       <c r="E53" s="17" t="s">
-        <v>60</v>
+        <v>212</v>
       </c>
       <c r="F53" s="17"/>
       <c r="G53" s="17"/>
@@ -3399,23 +3336,22 @@
       <c r="W53" s="17"/>
       <c r="X53" s="17"/>
       <c r="Y53" s="17"/>
-      <c r="Z53" s="18"/>
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="15" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B54" s="16">
         <v>0.0</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D54" s="17" t="s">
-        <v>213</v>
+        <v>63</v>
       </c>
       <c r="E54" s="17" t="s">
-        <v>214</v>
+        <v>64</v>
       </c>
       <c r="F54" s="17"/>
       <c r="G54" s="17"/>
@@ -3437,7 +3373,6 @@
       <c r="W54" s="17"/>
       <c r="X54" s="17"/>
       <c r="Y54" s="17"/>
-      <c r="Z54" s="18"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="15" t="s">
@@ -3475,7 +3410,6 @@
       <c r="W55" s="17"/>
       <c r="X55" s="17"/>
       <c r="Y55" s="17"/>
-      <c r="Z55" s="18"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="15" t="s">
@@ -3513,7 +3447,6 @@
       <c r="W56" s="17"/>
       <c r="X56" s="17"/>
       <c r="Y56" s="17"/>
-      <c r="Z56" s="18"/>
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="15" t="s">
@@ -3551,7 +3484,6 @@
       <c r="W57" s="17"/>
       <c r="X57" s="17"/>
       <c r="Y57" s="17"/>
-      <c r="Z57" s="18"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="15" t="s">
@@ -3589,7 +3521,6 @@
       <c r="W58" s="17"/>
       <c r="X58" s="17"/>
       <c r="Y58" s="17"/>
-      <c r="Z58" s="18"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="15" t="s">
@@ -3627,7 +3558,6 @@
       <c r="W59" s="17"/>
       <c r="X59" s="17"/>
       <c r="Y59" s="17"/>
-      <c r="Z59" s="18"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="15" t="s">
@@ -3665,7 +3595,6 @@
       <c r="W60" s="17"/>
       <c r="X60" s="17"/>
       <c r="Y60" s="17"/>
-      <c r="Z60" s="18"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="15" t="s">
@@ -3703,7 +3632,6 @@
       <c r="W61" s="17"/>
       <c r="X61" s="17"/>
       <c r="Y61" s="17"/>
-      <c r="Z61" s="18"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="15" t="s">
@@ -3741,159 +3669,154 @@
       <c r="W62" s="17"/>
       <c r="X62" s="17"/>
       <c r="Y62" s="17"/>
-      <c r="Z62" s="18"/>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="19" t="s">
+      <c r="A63" s="15" t="s">
         <v>247</v>
       </c>
-      <c r="B63" s="20">
+      <c r="B63" s="16">
         <v>0.0</v>
       </c>
-      <c r="C63" s="20" t="s">
+      <c r="C63" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="D63" s="20" t="s">
+      <c r="D63" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="E63" s="20" t="s">
+      <c r="E63" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="F63" s="20"/>
-      <c r="G63" s="20"/>
-      <c r="H63" s="20"/>
-      <c r="I63" s="20"/>
-      <c r="J63" s="20"/>
-      <c r="K63" s="20"/>
-      <c r="L63" s="20"/>
-      <c r="M63" s="20"/>
-      <c r="N63" s="20"/>
-      <c r="O63" s="20"/>
-      <c r="P63" s="20"/>
-      <c r="Q63" s="20"/>
-      <c r="R63" s="20"/>
-      <c r="S63" s="20"/>
-      <c r="T63" s="20"/>
-      <c r="U63" s="20"/>
-      <c r="V63" s="20"/>
-      <c r="W63" s="20"/>
-      <c r="X63" s="20"/>
-      <c r="Y63" s="20"/>
-      <c r="Z63" s="18"/>
+      <c r="F63" s="17"/>
+      <c r="G63" s="17"/>
+      <c r="H63" s="17"/>
+      <c r="I63" s="17"/>
+      <c r="J63" s="17"/>
+      <c r="K63" s="17"/>
+      <c r="L63" s="17"/>
+      <c r="M63" s="17"/>
+      <c r="N63" s="17"/>
+      <c r="O63" s="17"/>
+      <c r="P63" s="17"/>
+      <c r="Q63" s="17"/>
+      <c r="R63" s="17"/>
+      <c r="S63" s="17"/>
+      <c r="T63" s="17"/>
+      <c r="U63" s="17"/>
+      <c r="V63" s="17"/>
+      <c r="W63" s="17"/>
+      <c r="X63" s="17"/>
+      <c r="Y63" s="17"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="19" t="s">
+      <c r="A64" s="18" t="s">
         <v>251</v>
       </c>
-      <c r="B64" s="20">
+      <c r="B64" s="19">
         <v>0.0</v>
       </c>
-      <c r="C64" s="20" t="s">
+      <c r="C64" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="D64" s="20" t="s">
+      <c r="D64" s="19" t="s">
         <v>253</v>
       </c>
-      <c r="E64" s="20" t="s">
+      <c r="E64" s="19" t="s">
         <v>254</v>
       </c>
-      <c r="F64" s="20"/>
-      <c r="G64" s="20"/>
-      <c r="H64" s="20"/>
-      <c r="I64" s="20"/>
-      <c r="J64" s="20"/>
-      <c r="K64" s="20"/>
-      <c r="L64" s="20"/>
-      <c r="M64" s="20"/>
-      <c r="N64" s="20"/>
-      <c r="O64" s="20"/>
-      <c r="P64" s="20"/>
-      <c r="Q64" s="20"/>
-      <c r="R64" s="20"/>
-      <c r="S64" s="20"/>
-      <c r="T64" s="20"/>
-      <c r="U64" s="20"/>
-      <c r="V64" s="20"/>
-      <c r="W64" s="20"/>
-      <c r="X64" s="20"/>
-      <c r="Y64" s="20"/>
-      <c r="Z64" s="18"/>
+      <c r="F64" s="19"/>
+      <c r="G64" s="19"/>
+      <c r="H64" s="19"/>
+      <c r="I64" s="19"/>
+      <c r="J64" s="19"/>
+      <c r="K64" s="19"/>
+      <c r="L64" s="19"/>
+      <c r="M64" s="19"/>
+      <c r="N64" s="19"/>
+      <c r="O64" s="19"/>
+      <c r="P64" s="19"/>
+      <c r="Q64" s="19"/>
+      <c r="R64" s="19"/>
+      <c r="S64" s="19"/>
+      <c r="T64" s="19"/>
+      <c r="U64" s="19"/>
+      <c r="V64" s="19"/>
+      <c r="W64" s="19"/>
+      <c r="X64" s="19"/>
+      <c r="Y64" s="19"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="19" t="s">
+      <c r="A65" s="18" t="s">
         <v>255</v>
       </c>
-      <c r="B65" s="20">
+      <c r="B65" s="19">
         <v>0.0</v>
       </c>
-      <c r="C65" s="20" t="s">
+      <c r="C65" s="19" t="s">
         <v>256</v>
       </c>
-      <c r="D65" s="20" t="s">
+      <c r="D65" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="E65" s="20" t="s">
+      <c r="E65" s="19" t="s">
         <v>258</v>
       </c>
-      <c r="F65" s="20"/>
-      <c r="G65" s="20"/>
-      <c r="H65" s="20"/>
-      <c r="I65" s="20"/>
-      <c r="J65" s="20"/>
-      <c r="K65" s="20"/>
-      <c r="L65" s="20"/>
-      <c r="M65" s="20"/>
-      <c r="N65" s="20"/>
-      <c r="O65" s="20"/>
-      <c r="P65" s="20"/>
-      <c r="Q65" s="20"/>
-      <c r="R65" s="20"/>
-      <c r="S65" s="20"/>
-      <c r="T65" s="20"/>
-      <c r="U65" s="20"/>
-      <c r="V65" s="20"/>
-      <c r="W65" s="20"/>
-      <c r="X65" s="20"/>
-      <c r="Y65" s="20"/>
-      <c r="Z65" s="18"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="19"/>
+      <c r="K65" s="19"/>
+      <c r="L65" s="19"/>
+      <c r="M65" s="19"/>
+      <c r="N65" s="19"/>
+      <c r="O65" s="19"/>
+      <c r="P65" s="19"/>
+      <c r="Q65" s="19"/>
+      <c r="R65" s="19"/>
+      <c r="S65" s="19"/>
+      <c r="T65" s="19"/>
+      <c r="U65" s="19"/>
+      <c r="V65" s="19"/>
+      <c r="W65" s="19"/>
+      <c r="X65" s="19"/>
+      <c r="Y65" s="19"/>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="15" t="s">
+      <c r="A66" s="18" t="s">
         <v>259</v>
       </c>
-      <c r="B66" s="16">
+      <c r="B66" s="19">
         <v>0.0</v>
       </c>
-      <c r="C66" s="17" t="s">
+      <c r="C66" s="19" t="s">
         <v>260</v>
       </c>
-      <c r="D66" s="17" t="s">
+      <c r="D66" s="19" t="s">
         <v>261</v>
       </c>
-      <c r="E66" s="17" t="s">
+      <c r="E66" s="19" t="s">
         <v>262</v>
       </c>
-      <c r="F66" s="17"/>
-      <c r="G66" s="17"/>
-      <c r="H66" s="17"/>
-      <c r="I66" s="17"/>
-      <c r="J66" s="17"/>
-      <c r="K66" s="17"/>
-      <c r="L66" s="17"/>
-      <c r="M66" s="17"/>
-      <c r="N66" s="17"/>
-      <c r="O66" s="17"/>
-      <c r="P66" s="17"/>
-      <c r="Q66" s="17"/>
-      <c r="R66" s="17"/>
-      <c r="S66" s="17"/>
-      <c r="T66" s="17"/>
-      <c r="U66" s="17"/>
-      <c r="V66" s="17"/>
-      <c r="W66" s="17"/>
-      <c r="X66" s="17"/>
-      <c r="Y66" s="17"/>
-      <c r="Z66" s="18"/>
+      <c r="F66" s="19"/>
+      <c r="G66" s="19"/>
+      <c r="H66" s="19"/>
+      <c r="I66" s="19"/>
+      <c r="J66" s="19"/>
+      <c r="K66" s="19"/>
+      <c r="L66" s="19"/>
+      <c r="M66" s="19"/>
+      <c r="N66" s="19"/>
+      <c r="O66" s="19"/>
+      <c r="P66" s="19"/>
+      <c r="Q66" s="19"/>
+      <c r="R66" s="19"/>
+      <c r="S66" s="19"/>
+      <c r="T66" s="19"/>
+      <c r="U66" s="19"/>
+      <c r="V66" s="19"/>
+      <c r="W66" s="19"/>
+      <c r="X66" s="19"/>
+      <c r="Y66" s="19"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="15" t="s">
@@ -3931,7 +3854,6 @@
       <c r="W67" s="17"/>
       <c r="X67" s="17"/>
       <c r="Y67" s="17"/>
-      <c r="Z67" s="18"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="15" t="s">
@@ -3969,7 +3891,6 @@
       <c r="W68" s="17"/>
       <c r="X68" s="17"/>
       <c r="Y68" s="17"/>
-      <c r="Z68" s="18"/>
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="15" t="s">
@@ -4007,7 +3928,6 @@
       <c r="W69" s="17"/>
       <c r="X69" s="17"/>
       <c r="Y69" s="17"/>
-      <c r="Z69" s="18"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="15" t="s">
@@ -4045,490 +3965,487 @@
       <c r="W70" s="17"/>
       <c r="X70" s="17"/>
       <c r="Y70" s="17"/>
-      <c r="Z70" s="18"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="21" t="s">
+      <c r="A71" s="15" t="s">
         <v>279</v>
       </c>
-      <c r="B71" s="22">
+      <c r="B71" s="16">
         <v>0.0</v>
       </c>
-      <c r="C71" s="23" t="s">
+      <c r="C71" s="17" t="s">
         <v>280</v>
       </c>
-      <c r="D71" s="23" t="s">
+      <c r="D71" s="17" t="s">
         <v>281</v>
       </c>
-      <c r="E71" s="23" t="s">
+      <c r="E71" s="17" t="s">
         <v>282</v>
       </c>
-      <c r="F71" s="23"/>
-      <c r="G71" s="23"/>
-      <c r="H71" s="23"/>
-      <c r="I71" s="23"/>
-      <c r="J71" s="23"/>
-      <c r="K71" s="23"/>
-      <c r="L71" s="23"/>
-      <c r="M71" s="23"/>
-      <c r="N71" s="23"/>
-      <c r="O71" s="23"/>
-      <c r="P71" s="23"/>
-      <c r="Q71" s="23"/>
-      <c r="R71" s="23"/>
-      <c r="S71" s="23"/>
-      <c r="T71" s="23"/>
-      <c r="U71" s="23"/>
-      <c r="V71" s="23"/>
-      <c r="W71" s="23"/>
-      <c r="X71" s="23"/>
-      <c r="Y71" s="23"/>
-      <c r="Z71" s="24"/>
+      <c r="F71" s="17"/>
+      <c r="G71" s="17"/>
+      <c r="H71" s="17"/>
+      <c r="I71" s="17"/>
+      <c r="J71" s="17"/>
+      <c r="K71" s="17"/>
+      <c r="L71" s="17"/>
+      <c r="M71" s="17"/>
+      <c r="N71" s="17"/>
+      <c r="O71" s="17"/>
+      <c r="P71" s="17"/>
+      <c r="Q71" s="17"/>
+      <c r="R71" s="17"/>
+      <c r="S71" s="17"/>
+      <c r="T71" s="17"/>
+      <c r="U71" s="17"/>
+      <c r="V71" s="17"/>
+      <c r="W71" s="17"/>
+      <c r="X71" s="17"/>
+      <c r="Y71" s="17"/>
     </row>
     <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="25" t="s">
+      <c r="A72" s="20" t="s">
         <v>283</v>
       </c>
-      <c r="B72" s="26">
+      <c r="B72" s="21">
         <v>0.0</v>
       </c>
-      <c r="C72" s="26" t="s">
+      <c r="C72" s="22" t="s">
         <v>284</v>
       </c>
-      <c r="D72" s="26" t="s">
-        <v>147</v>
-      </c>
-      <c r="E72" s="26" t="s">
-        <v>148</v>
-      </c>
-      <c r="F72" s="26"/>
-      <c r="G72" s="26"/>
-      <c r="H72" s="26"/>
-      <c r="I72" s="26"/>
-      <c r="J72" s="26"/>
-      <c r="K72" s="26"/>
-      <c r="L72" s="26"/>
-      <c r="M72" s="26"/>
-      <c r="N72" s="26"/>
-      <c r="O72" s="26"/>
-      <c r="P72" s="26"/>
-      <c r="Q72" s="26"/>
-      <c r="R72" s="26"/>
-      <c r="S72" s="26"/>
-      <c r="T72" s="26"/>
-      <c r="U72" s="26"/>
-      <c r="V72" s="26"/>
-      <c r="W72" s="26"/>
-      <c r="X72" s="26"/>
-      <c r="Y72" s="26"/>
-      <c r="Z72" s="27"/>
+      <c r="D72" s="22" t="s">
+        <v>285</v>
+      </c>
+      <c r="E72" s="22" t="s">
+        <v>286</v>
+      </c>
+      <c r="F72" s="22"/>
+      <c r="G72" s="22"/>
+      <c r="H72" s="22"/>
+      <c r="I72" s="22"/>
+      <c r="J72" s="22"/>
+      <c r="K72" s="22"/>
+      <c r="L72" s="22"/>
+      <c r="M72" s="22"/>
+      <c r="N72" s="22"/>
+      <c r="O72" s="22"/>
+      <c r="P72" s="22"/>
+      <c r="Q72" s="22"/>
+      <c r="R72" s="22"/>
+      <c r="S72" s="22"/>
+      <c r="T72" s="22"/>
+      <c r="U72" s="22"/>
+      <c r="V72" s="22"/>
+      <c r="W72" s="22"/>
+      <c r="X72" s="22"/>
+      <c r="Y72" s="22"/>
     </row>
     <row r="73" ht="15.0" customHeight="1">
-      <c r="A73" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="B73" s="26">
+      <c r="A73" s="23" t="s">
+        <v>287</v>
+      </c>
+      <c r="B73" s="24">
         <v>0.0</v>
       </c>
-      <c r="C73" s="26" t="s">
-        <v>286</v>
-      </c>
-      <c r="D73" s="26" t="s">
-        <v>287</v>
-      </c>
-      <c r="E73" s="26" t="s">
+      <c r="C73" s="24" t="s">
         <v>288</v>
       </c>
-      <c r="F73" s="26"/>
-      <c r="G73" s="26"/>
-      <c r="H73" s="26"/>
-      <c r="I73" s="26"/>
-      <c r="J73" s="26"/>
-      <c r="K73" s="26"/>
-      <c r="L73" s="26"/>
-      <c r="M73" s="26"/>
-      <c r="N73" s="26"/>
-      <c r="O73" s="26"/>
-      <c r="P73" s="26"/>
-      <c r="Q73" s="26"/>
-      <c r="R73" s="26"/>
-      <c r="S73" s="26"/>
-      <c r="T73" s="26"/>
-      <c r="U73" s="26"/>
-      <c r="V73" s="26"/>
-      <c r="W73" s="26"/>
-      <c r="X73" s="26"/>
-      <c r="Y73" s="26"/>
-      <c r="Z73" s="27"/>
+      <c r="D73" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="E73" s="24" t="s">
+        <v>152</v>
+      </c>
+      <c r="F73" s="24"/>
+      <c r="G73" s="24"/>
+      <c r="H73" s="24"/>
+      <c r="I73" s="24"/>
+      <c r="J73" s="24"/>
+      <c r="K73" s="24"/>
+      <c r="L73" s="24"/>
+      <c r="M73" s="24"/>
+      <c r="N73" s="24"/>
+      <c r="O73" s="24"/>
+      <c r="P73" s="24"/>
+      <c r="Q73" s="24"/>
+      <c r="R73" s="24"/>
+      <c r="S73" s="24"/>
+      <c r="T73" s="24"/>
+      <c r="U73" s="24"/>
+      <c r="V73" s="24"/>
+      <c r="W73" s="24"/>
+      <c r="X73" s="24"/>
+      <c r="Y73" s="24"/>
     </row>
     <row r="74" ht="15.0" customHeight="1">
-      <c r="A74" s="25" t="s">
+      <c r="A74" s="23" t="s">
         <v>289</v>
       </c>
-      <c r="B74" s="26">
+      <c r="B74" s="24">
         <v>0.0</v>
       </c>
-      <c r="C74" s="26" t="s">
+      <c r="C74" s="24" t="s">
         <v>290</v>
       </c>
-      <c r="D74" s="26" t="s">
-        <v>175</v>
-      </c>
-      <c r="E74" s="26" t="s">
-        <v>176</v>
-      </c>
-      <c r="F74" s="26"/>
-      <c r="G74" s="26"/>
-      <c r="H74" s="26"/>
-      <c r="I74" s="26"/>
-      <c r="J74" s="26"/>
-      <c r="K74" s="26"/>
-      <c r="L74" s="26"/>
-      <c r="M74" s="26"/>
-      <c r="N74" s="26"/>
-      <c r="O74" s="26"/>
-      <c r="P74" s="26"/>
-      <c r="Q74" s="26"/>
-      <c r="R74" s="26"/>
-      <c r="S74" s="26"/>
-      <c r="T74" s="26"/>
-      <c r="U74" s="26"/>
-      <c r="V74" s="26"/>
-      <c r="W74" s="26"/>
-      <c r="X74" s="26"/>
-      <c r="Y74" s="26"/>
-      <c r="Z74" s="27"/>
+      <c r="D74" s="24" t="s">
+        <v>291</v>
+      </c>
+      <c r="E74" s="24" t="s">
+        <v>292</v>
+      </c>
+      <c r="F74" s="24"/>
+      <c r="G74" s="24"/>
+      <c r="H74" s="24"/>
+      <c r="I74" s="24"/>
+      <c r="J74" s="24"/>
+      <c r="K74" s="24"/>
+      <c r="L74" s="24"/>
+      <c r="M74" s="24"/>
+      <c r="N74" s="24"/>
+      <c r="O74" s="24"/>
+      <c r="P74" s="24"/>
+      <c r="Q74" s="24"/>
+      <c r="R74" s="24"/>
+      <c r="S74" s="24"/>
+      <c r="T74" s="24"/>
+      <c r="U74" s="24"/>
+      <c r="V74" s="24"/>
+      <c r="W74" s="24"/>
+      <c r="X74" s="24"/>
+      <c r="Y74" s="24"/>
     </row>
     <row r="75" ht="15.0" customHeight="1">
-      <c r="A75" s="25" t="s">
-        <v>291</v>
-      </c>
-      <c r="B75" s="26">
+      <c r="A75" s="23" t="s">
+        <v>293</v>
+      </c>
+      <c r="B75" s="24">
         <v>0.0</v>
       </c>
-      <c r="C75" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="D75" s="26" t="s">
-        <v>293</v>
-      </c>
-      <c r="E75" s="26" t="s">
+      <c r="C75" s="24" t="s">
         <v>294</v>
       </c>
-      <c r="F75" s="26"/>
-      <c r="G75" s="26"/>
-      <c r="H75" s="26"/>
-      <c r="I75" s="26"/>
-      <c r="J75" s="26"/>
-      <c r="K75" s="26"/>
-      <c r="L75" s="26"/>
-      <c r="M75" s="26"/>
-      <c r="N75" s="26"/>
-      <c r="O75" s="26"/>
-      <c r="P75" s="26"/>
-      <c r="Q75" s="26"/>
-      <c r="R75" s="26"/>
-      <c r="S75" s="26"/>
-      <c r="T75" s="26"/>
-      <c r="U75" s="26"/>
-      <c r="V75" s="26"/>
-      <c r="W75" s="26"/>
-      <c r="X75" s="26"/>
-      <c r="Y75" s="26"/>
-      <c r="Z75" s="27"/>
+      <c r="D75" s="24" t="s">
+        <v>179</v>
+      </c>
+      <c r="E75" s="24" t="s">
+        <v>180</v>
+      </c>
+      <c r="F75" s="24"/>
+      <c r="G75" s="24"/>
+      <c r="H75" s="24"/>
+      <c r="I75" s="24"/>
+      <c r="J75" s="24"/>
+      <c r="K75" s="24"/>
+      <c r="L75" s="24"/>
+      <c r="M75" s="24"/>
+      <c r="N75" s="24"/>
+      <c r="O75" s="24"/>
+      <c r="P75" s="24"/>
+      <c r="Q75" s="24"/>
+      <c r="R75" s="24"/>
+      <c r="S75" s="24"/>
+      <c r="T75" s="24"/>
+      <c r="U75" s="24"/>
+      <c r="V75" s="24"/>
+      <c r="W75" s="24"/>
+      <c r="X75" s="24"/>
+      <c r="Y75" s="24"/>
     </row>
     <row r="76" ht="15.0" customHeight="1">
-      <c r="A76" s="25" t="s">
+      <c r="A76" s="23" t="s">
         <v>295</v>
       </c>
-      <c r="B76" s="26">
+      <c r="B76" s="24">
         <v>0.0</v>
       </c>
-      <c r="C76" s="26" t="s">
+      <c r="C76" s="24" t="s">
         <v>296</v>
       </c>
-      <c r="D76" s="26" t="s">
+      <c r="D76" s="24" t="s">
         <v>297</v>
       </c>
-      <c r="E76" s="26" t="s">
+      <c r="E76" s="24" t="s">
         <v>298</v>
       </c>
-      <c r="F76" s="26"/>
-      <c r="G76" s="26"/>
-      <c r="H76" s="26"/>
-      <c r="I76" s="26"/>
-      <c r="J76" s="26"/>
-      <c r="K76" s="26"/>
-      <c r="L76" s="26"/>
-      <c r="M76" s="26"/>
-      <c r="N76" s="26"/>
-      <c r="O76" s="26"/>
-      <c r="P76" s="26"/>
-      <c r="Q76" s="26"/>
-      <c r="R76" s="26"/>
-      <c r="S76" s="26"/>
-      <c r="T76" s="26"/>
-      <c r="U76" s="26"/>
-      <c r="V76" s="26"/>
-      <c r="W76" s="26"/>
-      <c r="X76" s="26"/>
-      <c r="Y76" s="26"/>
-      <c r="Z76" s="27"/>
+      <c r="F76" s="24"/>
+      <c r="G76" s="24"/>
+      <c r="H76" s="24"/>
+      <c r="I76" s="24"/>
+      <c r="J76" s="24"/>
+      <c r="K76" s="24"/>
+      <c r="L76" s="24"/>
+      <c r="M76" s="24"/>
+      <c r="N76" s="24"/>
+      <c r="O76" s="24"/>
+      <c r="P76" s="24"/>
+      <c r="Q76" s="24"/>
+      <c r="R76" s="24"/>
+      <c r="S76" s="24"/>
+      <c r="T76" s="24"/>
+      <c r="U76" s="24"/>
+      <c r="V76" s="24"/>
+      <c r="W76" s="24"/>
+      <c r="X76" s="24"/>
+      <c r="Y76" s="24"/>
     </row>
     <row r="77" ht="15.0" customHeight="1">
-      <c r="A77" s="25" t="s">
+      <c r="A77" s="23" t="s">
         <v>299</v>
       </c>
-      <c r="B77" s="26">
+      <c r="B77" s="24">
         <v>0.0</v>
       </c>
-      <c r="C77" s="26" t="s">
+      <c r="C77" s="24" t="s">
         <v>300</v>
       </c>
-      <c r="D77" s="26" t="s">
+      <c r="D77" s="24" t="s">
         <v>301</v>
       </c>
-      <c r="E77" s="26" t="s">
+      <c r="E77" s="24" t="s">
         <v>302</v>
       </c>
-      <c r="F77" s="26"/>
-      <c r="G77" s="26"/>
-      <c r="H77" s="26"/>
-      <c r="I77" s="26"/>
-      <c r="J77" s="26"/>
-      <c r="K77" s="26"/>
-      <c r="L77" s="26"/>
-      <c r="M77" s="26"/>
-      <c r="N77" s="26"/>
-      <c r="O77" s="26"/>
-      <c r="P77" s="26"/>
-      <c r="Q77" s="26"/>
-      <c r="R77" s="26"/>
-      <c r="S77" s="26"/>
-      <c r="T77" s="26"/>
-      <c r="U77" s="26"/>
-      <c r="V77" s="26"/>
-      <c r="W77" s="26"/>
-      <c r="X77" s="26"/>
-      <c r="Y77" s="26"/>
-      <c r="Z77" s="27"/>
+      <c r="F77" s="24"/>
+      <c r="G77" s="24"/>
+      <c r="H77" s="24"/>
+      <c r="I77" s="24"/>
+      <c r="J77" s="24"/>
+      <c r="K77" s="24"/>
+      <c r="L77" s="24"/>
+      <c r="M77" s="24"/>
+      <c r="N77" s="24"/>
+      <c r="O77" s="24"/>
+      <c r="P77" s="24"/>
+      <c r="Q77" s="24"/>
+      <c r="R77" s="24"/>
+      <c r="S77" s="24"/>
+      <c r="T77" s="24"/>
+      <c r="U77" s="24"/>
+      <c r="V77" s="24"/>
+      <c r="W77" s="24"/>
+      <c r="X77" s="24"/>
+      <c r="Y77" s="24"/>
     </row>
     <row r="78" ht="15.0" customHeight="1">
-      <c r="A78" s="25" t="s">
+      <c r="A78" s="23" t="s">
         <v>303</v>
       </c>
-      <c r="B78" s="26">
+      <c r="B78" s="24">
         <v>0.0</v>
       </c>
-      <c r="C78" s="26" t="s">
+      <c r="C78" s="24" t="s">
         <v>304</v>
       </c>
-      <c r="D78" s="26" t="s">
+      <c r="D78" s="24" t="s">
         <v>305</v>
       </c>
-      <c r="E78" s="26" t="s">
+      <c r="E78" s="24" t="s">
         <v>306</v>
       </c>
-      <c r="F78" s="26"/>
-      <c r="G78" s="26"/>
-      <c r="H78" s="26"/>
-      <c r="I78" s="26"/>
-      <c r="J78" s="26"/>
-      <c r="K78" s="26"/>
-      <c r="L78" s="26"/>
-      <c r="M78" s="26"/>
-      <c r="N78" s="26"/>
-      <c r="O78" s="26"/>
-      <c r="P78" s="26"/>
-      <c r="Q78" s="26"/>
-      <c r="R78" s="26"/>
-      <c r="S78" s="26"/>
-      <c r="T78" s="26"/>
-      <c r="U78" s="26"/>
-      <c r="V78" s="26"/>
-      <c r="W78" s="26"/>
-      <c r="X78" s="26"/>
-      <c r="Y78" s="26"/>
-      <c r="Z78" s="27"/>
+      <c r="F78" s="24"/>
+      <c r="G78" s="24"/>
+      <c r="H78" s="24"/>
+      <c r="I78" s="24"/>
+      <c r="J78" s="24"/>
+      <c r="K78" s="24"/>
+      <c r="L78" s="24"/>
+      <c r="M78" s="24"/>
+      <c r="N78" s="24"/>
+      <c r="O78" s="24"/>
+      <c r="P78" s="24"/>
+      <c r="Q78" s="24"/>
+      <c r="R78" s="24"/>
+      <c r="S78" s="24"/>
+      <c r="T78" s="24"/>
+      <c r="U78" s="24"/>
+      <c r="V78" s="24"/>
+      <c r="W78" s="24"/>
+      <c r="X78" s="24"/>
+      <c r="Y78" s="24"/>
     </row>
     <row r="79" ht="15.0" customHeight="1">
-      <c r="A79" s="28" t="s">
+      <c r="A79" s="23" t="s">
         <v>307</v>
       </c>
-      <c r="B79" s="29">
+      <c r="B79" s="24">
         <v>0.0</v>
       </c>
-      <c r="C79" s="30" t="s">
+      <c r="C79" s="24" t="s">
         <v>308</v>
       </c>
-      <c r="D79" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E79" s="30" t="s">
-        <v>208</v>
-      </c>
-      <c r="F79" s="30"/>
-      <c r="G79" s="30"/>
-      <c r="H79" s="30"/>
-      <c r="I79" s="30"/>
-      <c r="J79" s="30"/>
-      <c r="K79" s="30"/>
-      <c r="L79" s="30"/>
-      <c r="M79" s="30"/>
-      <c r="N79" s="30"/>
-      <c r="O79" s="30"/>
-      <c r="P79" s="30"/>
-      <c r="Q79" s="30"/>
-      <c r="R79" s="30"/>
-      <c r="S79" s="30"/>
-      <c r="T79" s="30"/>
-      <c r="U79" s="30"/>
-      <c r="V79" s="30"/>
-      <c r="W79" s="30"/>
-      <c r="X79" s="30"/>
-      <c r="Y79" s="30"/>
-      <c r="Z79" s="27"/>
+      <c r="D79" s="24" t="s">
+        <v>309</v>
+      </c>
+      <c r="E79" s="24" t="s">
+        <v>310</v>
+      </c>
+      <c r="F79" s="24"/>
+      <c r="G79" s="24"/>
+      <c r="H79" s="24"/>
+      <c r="I79" s="24"/>
+      <c r="J79" s="24"/>
+      <c r="K79" s="24"/>
+      <c r="L79" s="24"/>
+      <c r="M79" s="24"/>
+      <c r="N79" s="24"/>
+      <c r="O79" s="24"/>
+      <c r="P79" s="24"/>
+      <c r="Q79" s="24"/>
+      <c r="R79" s="24"/>
+      <c r="S79" s="24"/>
+      <c r="T79" s="24"/>
+      <c r="U79" s="24"/>
+      <c r="V79" s="24"/>
+      <c r="W79" s="24"/>
+      <c r="X79" s="24"/>
+      <c r="Y79" s="24"/>
     </row>
     <row r="80" ht="15.0" customHeight="1">
-      <c r="A80" s="28" t="s">
-        <v>309</v>
-      </c>
-      <c r="B80" s="29">
+      <c r="A80" s="25" t="s">
+        <v>311</v>
+      </c>
+      <c r="B80" s="26">
         <v>0.0</v>
       </c>
-      <c r="C80" s="30" t="s">
-        <v>310</v>
-      </c>
-      <c r="D80" s="30" t="s">
-        <v>139</v>
-      </c>
-      <c r="E80" s="30" t="s">
-        <v>140</v>
-      </c>
-      <c r="F80" s="30"/>
-      <c r="G80" s="30"/>
-      <c r="H80" s="30"/>
-      <c r="I80" s="30"/>
-      <c r="J80" s="30"/>
-      <c r="K80" s="30"/>
-      <c r="L80" s="30"/>
-      <c r="M80" s="30"/>
-      <c r="N80" s="30"/>
-      <c r="O80" s="30"/>
-      <c r="P80" s="30"/>
-      <c r="Q80" s="30"/>
-      <c r="R80" s="30"/>
-      <c r="S80" s="30"/>
-      <c r="T80" s="30"/>
-      <c r="U80" s="30"/>
-      <c r="V80" s="30"/>
-      <c r="W80" s="30"/>
-      <c r="X80" s="30"/>
-      <c r="Y80" s="30"/>
-      <c r="Z80" s="27"/>
+      <c r="C80" s="27" t="s">
+        <v>312</v>
+      </c>
+      <c r="D80" s="27" t="s">
+        <v>211</v>
+      </c>
+      <c r="E80" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="F80" s="27"/>
+      <c r="G80" s="27"/>
+      <c r="H80" s="27"/>
+      <c r="I80" s="27"/>
+      <c r="J80" s="27"/>
+      <c r="K80" s="27"/>
+      <c r="L80" s="27"/>
+      <c r="M80" s="27"/>
+      <c r="N80" s="27"/>
+      <c r="O80" s="27"/>
+      <c r="P80" s="27"/>
+      <c r="Q80" s="27"/>
+      <c r="R80" s="27"/>
+      <c r="S80" s="27"/>
+      <c r="T80" s="27"/>
+      <c r="U80" s="27"/>
+      <c r="V80" s="27"/>
+      <c r="W80" s="27"/>
+      <c r="X80" s="27"/>
+      <c r="Y80" s="27"/>
     </row>
     <row r="81" ht="15.0" customHeight="1">
-      <c r="A81" s="28" t="s">
-        <v>311</v>
-      </c>
-      <c r="B81" s="29">
+      <c r="A81" s="25" t="s">
+        <v>313</v>
+      </c>
+      <c r="B81" s="26">
         <v>0.0</v>
       </c>
-      <c r="C81" s="30" t="s">
-        <v>312</v>
-      </c>
-      <c r="D81" s="30" t="s">
-        <v>313</v>
-      </c>
-      <c r="E81" s="30" t="s">
+      <c r="C81" s="27" t="s">
         <v>314</v>
       </c>
-      <c r="F81" s="30"/>
-      <c r="G81" s="30"/>
-      <c r="H81" s="30"/>
-      <c r="I81" s="30"/>
-      <c r="J81" s="30"/>
-      <c r="K81" s="30"/>
-      <c r="L81" s="30"/>
-      <c r="M81" s="30"/>
-      <c r="N81" s="30"/>
-      <c r="O81" s="30"/>
-      <c r="P81" s="30"/>
-      <c r="Q81" s="30"/>
-      <c r="R81" s="30"/>
-      <c r="S81" s="30"/>
-      <c r="T81" s="30"/>
-      <c r="U81" s="30"/>
-      <c r="V81" s="30"/>
-      <c r="W81" s="30"/>
-      <c r="X81" s="30"/>
-      <c r="Y81" s="30"/>
-      <c r="Z81" s="27"/>
+      <c r="D81" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="E81" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="F81" s="27"/>
+      <c r="G81" s="27"/>
+      <c r="H81" s="27"/>
+      <c r="I81" s="27"/>
+      <c r="J81" s="27"/>
+      <c r="K81" s="27"/>
+      <c r="L81" s="27"/>
+      <c r="M81" s="27"/>
+      <c r="N81" s="27"/>
+      <c r="O81" s="27"/>
+      <c r="P81" s="27"/>
+      <c r="Q81" s="27"/>
+      <c r="R81" s="27"/>
+      <c r="S81" s="27"/>
+      <c r="T81" s="27"/>
+      <c r="U81" s="27"/>
+      <c r="V81" s="27"/>
+      <c r="W81" s="27"/>
+      <c r="X81" s="27"/>
+      <c r="Y81" s="27"/>
     </row>
     <row r="82" ht="15.0" customHeight="1">
-      <c r="A82" s="31" t="s">
+      <c r="A82" s="25" t="s">
         <v>315</v>
       </c>
-      <c r="B82" s="32">
+      <c r="B82" s="26">
         <v>0.0</v>
       </c>
-      <c r="C82" s="33" t="s">
+      <c r="C82" s="27" t="s">
         <v>316</v>
       </c>
-      <c r="D82" s="33" t="s">
+      <c r="D82" s="27" t="s">
         <v>317</v>
       </c>
-      <c r="E82" s="33" t="s">
+      <c r="E82" s="27" t="s">
         <v>318</v>
       </c>
-      <c r="F82" s="33"/>
-      <c r="G82" s="33"/>
-      <c r="H82" s="33"/>
-      <c r="I82" s="33"/>
-      <c r="J82" s="33"/>
-      <c r="K82" s="33"/>
-      <c r="L82" s="33"/>
-      <c r="M82" s="33"/>
-      <c r="N82" s="33"/>
-      <c r="O82" s="33"/>
-      <c r="P82" s="33"/>
-      <c r="Q82" s="33"/>
-      <c r="R82" s="33"/>
-      <c r="S82" s="33"/>
-      <c r="T82" s="33"/>
-      <c r="U82" s="33"/>
-      <c r="V82" s="33"/>
-      <c r="W82" s="33"/>
-      <c r="X82" s="33"/>
-      <c r="Y82" s="33"/>
-      <c r="Z82" s="34"/>
+      <c r="F82" s="27"/>
+      <c r="G82" s="27"/>
+      <c r="H82" s="27"/>
+      <c r="I82" s="27"/>
+      <c r="J82" s="27"/>
+      <c r="K82" s="27"/>
+      <c r="L82" s="27"/>
+      <c r="M82" s="27"/>
+      <c r="N82" s="27"/>
+      <c r="O82" s="27"/>
+      <c r="P82" s="27"/>
+      <c r="Q82" s="27"/>
+      <c r="R82" s="27"/>
+      <c r="S82" s="27"/>
+      <c r="T82" s="27"/>
+      <c r="U82" s="27"/>
+      <c r="V82" s="27"/>
+      <c r="W82" s="27"/>
+      <c r="X82" s="27"/>
+      <c r="Y82" s="27"/>
     </row>
     <row r="83" ht="15.0" customHeight="1">
-      <c r="A83" s="1"/>
-      <c r="B83" s="1"/>
-      <c r="C83" s="1"/>
-      <c r="D83" s="1"/>
-      <c r="E83" s="1"/>
-      <c r="F83" s="1"/>
-      <c r="G83" s="1"/>
-      <c r="H83" s="1"/>
-      <c r="I83" s="1"/>
-      <c r="J83" s="1"/>
-      <c r="K83" s="1"/>
-      <c r="L83" s="1"/>
-      <c r="M83" s="1"/>
-      <c r="N83" s="1"/>
-      <c r="O83" s="1"/>
-      <c r="P83" s="1"/>
-      <c r="Q83" s="1"/>
-      <c r="R83" s="1"/>
-      <c r="S83" s="1"/>
-      <c r="T83" s="1"/>
-      <c r="U83" s="1"/>
-      <c r="V83" s="1"/>
-      <c r="W83" s="1"/>
-      <c r="X83" s="1"/>
-      <c r="Y83" s="1"/>
+      <c r="A83" s="28" t="s">
+        <v>319</v>
+      </c>
+      <c r="B83" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="C83" s="30" t="s">
+        <v>320</v>
+      </c>
+      <c r="D83" s="30" t="s">
+        <v>321</v>
+      </c>
+      <c r="E83" s="30" t="s">
+        <v>322</v>
+      </c>
+      <c r="F83" s="30"/>
+      <c r="G83" s="30"/>
+      <c r="H83" s="30"/>
+      <c r="I83" s="30"/>
+      <c r="J83" s="30"/>
+      <c r="K83" s="30"/>
+      <c r="L83" s="30"/>
+      <c r="M83" s="30"/>
+      <c r="N83" s="30"/>
+      <c r="O83" s="30"/>
+      <c r="P83" s="30"/>
+      <c r="Q83" s="30"/>
+      <c r="R83" s="30"/>
+      <c r="S83" s="30"/>
+      <c r="T83" s="30"/>
+      <c r="U83" s="30"/>
+      <c r="V83" s="30"/>
+      <c r="W83" s="30"/>
+      <c r="X83" s="30"/>
+      <c r="Y83" s="30"/>
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="1"/>
@@ -9579,7 +9496,33 @@
       <c r="X270" s="1"/>
       <c r="Y270" s="1"/>
     </row>
-    <row r="271" ht="15.0" customHeight="1"/>
+    <row r="271" ht="15.0" customHeight="1">
+      <c r="A271" s="1"/>
+      <c r="B271" s="1"/>
+      <c r="C271" s="1"/>
+      <c r="D271" s="1"/>
+      <c r="E271" s="1"/>
+      <c r="F271" s="1"/>
+      <c r="G271" s="1"/>
+      <c r="H271" s="1"/>
+      <c r="I271" s="1"/>
+      <c r="J271" s="1"/>
+      <c r="K271" s="1"/>
+      <c r="L271" s="1"/>
+      <c r="M271" s="1"/>
+      <c r="N271" s="1"/>
+      <c r="O271" s="1"/>
+      <c r="P271" s="1"/>
+      <c r="Q271" s="1"/>
+      <c r="R271" s="1"/>
+      <c r="S271" s="1"/>
+      <c r="T271" s="1"/>
+      <c r="U271" s="1"/>
+      <c r="V271" s="1"/>
+      <c r="W271" s="1"/>
+      <c r="X271" s="1"/>
+      <c r="Y271" s="1"/>
+    </row>
     <row r="272" ht="15.0" customHeight="1"/>
     <row r="273" ht="15.0" customHeight="1"/>
     <row r="274" ht="15.0" customHeight="1"/>
@@ -9592,723 +9535,724 @@
     <row r="281" ht="15.0" customHeight="1"/>
     <row r="282" ht="15.0" customHeight="1"/>
     <row r="283" ht="15.0" customHeight="1"/>
-    <row r="284" ht="15.0" customHeight="1"/>
-    <row r="285" ht="15.0" customHeight="1"/>
-    <row r="286" ht="15.0" customHeight="1"/>
-    <row r="287" ht="15.0" customHeight="1"/>
-    <row r="288" ht="15.0" customHeight="1"/>
-    <row r="289" ht="15.0" customHeight="1"/>
-    <row r="290" ht="15.0" customHeight="1"/>
-    <row r="291" ht="15.0" customHeight="1"/>
-    <row r="292" ht="15.0" customHeight="1"/>
-    <row r="293" ht="15.0" customHeight="1"/>
-    <row r="294" ht="15.0" customHeight="1"/>
-    <row r="295" ht="15.0" customHeight="1"/>
-    <row r="296" ht="15.0" customHeight="1"/>
-    <row r="297" ht="15.0" customHeight="1"/>
-    <row r="298" ht="15.0" customHeight="1"/>
-    <row r="299" ht="15.0" customHeight="1"/>
-    <row r="300" ht="15.0" customHeight="1"/>
-    <row r="301" ht="15.0" customHeight="1"/>
-    <row r="302" ht="15.0" customHeight="1"/>
-    <row r="303" ht="15.0" customHeight="1"/>
-    <row r="304" ht="15.0" customHeight="1"/>
-    <row r="305" ht="15.0" customHeight="1"/>
-    <row r="306" ht="15.0" customHeight="1"/>
-    <row r="307" ht="15.0" customHeight="1"/>
-    <row r="308" ht="15.0" customHeight="1"/>
-    <row r="309" ht="15.0" customHeight="1"/>
-    <row r="310" ht="15.0" customHeight="1"/>
-    <row r="311" ht="15.0" customHeight="1"/>
-    <row r="312" ht="15.0" customHeight="1"/>
-    <row r="313" ht="15.0" customHeight="1"/>
-    <row r="314" ht="15.0" customHeight="1"/>
-    <row r="315" ht="15.0" customHeight="1"/>
-    <row r="316" ht="15.0" customHeight="1"/>
-    <row r="317" ht="15.0" customHeight="1"/>
-    <row r="318" ht="15.0" customHeight="1"/>
-    <row r="319" ht="15.0" customHeight="1"/>
-    <row r="320" ht="15.0" customHeight="1"/>
-    <row r="321" ht="15.0" customHeight="1"/>
-    <row r="322" ht="15.0" customHeight="1"/>
-    <row r="323" ht="15.0" customHeight="1"/>
-    <row r="324" ht="15.0" customHeight="1"/>
-    <row r="325" ht="15.0" customHeight="1"/>
-    <row r="326" ht="15.0" customHeight="1"/>
-    <row r="327" ht="15.0" customHeight="1"/>
-    <row r="328" ht="15.0" customHeight="1"/>
-    <row r="329" ht="15.0" customHeight="1"/>
-    <row r="330" ht="15.0" customHeight="1"/>
-    <row r="331" ht="15.0" customHeight="1"/>
-    <row r="332" ht="15.0" customHeight="1"/>
-    <row r="333" ht="15.0" customHeight="1"/>
-    <row r="334" ht="15.0" customHeight="1"/>
-    <row r="335" ht="15.0" customHeight="1"/>
-    <row r="336" ht="15.0" customHeight="1"/>
-    <row r="337" ht="15.0" customHeight="1"/>
-    <row r="338" ht="15.0" customHeight="1"/>
-    <row r="339" ht="15.0" customHeight="1"/>
-    <row r="340" ht="15.0" customHeight="1"/>
-    <row r="341" ht="15.0" customHeight="1"/>
-    <row r="342" ht="15.0" customHeight="1"/>
-    <row r="343" ht="15.0" customHeight="1"/>
-    <row r="344" ht="15.0" customHeight="1"/>
-    <row r="345" ht="15.0" customHeight="1"/>
-    <row r="346" ht="15.0" customHeight="1"/>
-    <row r="347" ht="15.0" customHeight="1"/>
-    <row r="348" ht="15.0" customHeight="1"/>
-    <row r="349" ht="15.0" customHeight="1"/>
-    <row r="350" ht="15.0" customHeight="1"/>
-    <row r="351" ht="15.0" customHeight="1"/>
-    <row r="352" ht="15.0" customHeight="1"/>
-    <row r="353" ht="15.0" customHeight="1"/>
-    <row r="354" ht="15.0" customHeight="1"/>
-    <row r="355" ht="15.0" customHeight="1"/>
-    <row r="356" ht="15.0" customHeight="1"/>
-    <row r="357" ht="15.0" customHeight="1"/>
-    <row r="358" ht="15.0" customHeight="1"/>
-    <row r="359" ht="15.0" customHeight="1"/>
-    <row r="360" ht="15.0" customHeight="1"/>
-    <row r="361" ht="15.0" customHeight="1"/>
-    <row r="362" ht="15.0" customHeight="1"/>
-    <row r="363" ht="15.0" customHeight="1"/>
-    <row r="364" ht="15.0" customHeight="1"/>
-    <row r="365" ht="15.0" customHeight="1"/>
-    <row r="366" ht="15.0" customHeight="1"/>
-    <row r="367" ht="15.0" customHeight="1"/>
-    <row r="368" ht="15.0" customHeight="1"/>
-    <row r="369" ht="15.0" customHeight="1"/>
-    <row r="370" ht="15.0" customHeight="1"/>
-    <row r="371" ht="15.0" customHeight="1"/>
-    <row r="372" ht="15.0" customHeight="1"/>
-    <row r="373" ht="15.0" customHeight="1"/>
-    <row r="374" ht="15.0" customHeight="1"/>
-    <row r="375" ht="15.0" customHeight="1"/>
-    <row r="376" ht="15.0" customHeight="1"/>
-    <row r="377" ht="15.0" customHeight="1"/>
-    <row r="378" ht="15.0" customHeight="1"/>
-    <row r="379" ht="15.0" customHeight="1"/>
-    <row r="380" ht="15.0" customHeight="1"/>
-    <row r="381" ht="15.0" customHeight="1"/>
-    <row r="382" ht="15.0" customHeight="1"/>
-    <row r="383" ht="15.0" customHeight="1"/>
-    <row r="384" ht="15.0" customHeight="1"/>
-    <row r="385" ht="15.0" customHeight="1"/>
-    <row r="386" ht="15.0" customHeight="1"/>
-    <row r="387" ht="15.0" customHeight="1"/>
-    <row r="388" ht="15.0" customHeight="1"/>
-    <row r="389" ht="15.0" customHeight="1"/>
-    <row r="390" ht="15.0" customHeight="1"/>
-    <row r="391" ht="15.0" customHeight="1"/>
-    <row r="392" ht="15.0" customHeight="1"/>
-    <row r="393" ht="15.0" customHeight="1"/>
-    <row r="394" ht="15.0" customHeight="1"/>
-    <row r="395" ht="15.0" customHeight="1"/>
-    <row r="396" ht="15.0" customHeight="1"/>
-    <row r="397" ht="15.0" customHeight="1"/>
-    <row r="398" ht="15.0" customHeight="1"/>
-    <row r="399" ht="15.0" customHeight="1"/>
-    <row r="400" ht="15.0" customHeight="1"/>
-    <row r="401" ht="15.0" customHeight="1"/>
-    <row r="402" ht="15.0" customHeight="1"/>
-    <row r="403" ht="15.0" customHeight="1"/>
-    <row r="404" ht="15.0" customHeight="1"/>
-    <row r="405" ht="15.0" customHeight="1"/>
-    <row r="406" ht="15.0" customHeight="1"/>
-    <row r="407" ht="15.0" customHeight="1"/>
-    <row r="408" ht="15.0" customHeight="1"/>
-    <row r="409" ht="15.0" customHeight="1"/>
-    <row r="410" ht="15.0" customHeight="1"/>
-    <row r="411" ht="15.0" customHeight="1"/>
-    <row r="412" ht="15.0" customHeight="1"/>
-    <row r="413" ht="15.0" customHeight="1"/>
-    <row r="414" ht="15.0" customHeight="1"/>
-    <row r="415" ht="15.0" customHeight="1"/>
-    <row r="416" ht="15.0" customHeight="1"/>
-    <row r="417" ht="15.0" customHeight="1"/>
-    <row r="418" ht="15.0" customHeight="1"/>
-    <row r="419" ht="15.0" customHeight="1"/>
-    <row r="420" ht="15.0" customHeight="1"/>
-    <row r="421" ht="15.0" customHeight="1"/>
-    <row r="422" ht="15.0" customHeight="1"/>
-    <row r="423" ht="15.0" customHeight="1"/>
-    <row r="424" ht="15.0" customHeight="1"/>
-    <row r="425" ht="15.0" customHeight="1"/>
-    <row r="426" ht="15.0" customHeight="1"/>
-    <row r="427" ht="15.0" customHeight="1"/>
-    <row r="428" ht="15.0" customHeight="1"/>
-    <row r="429" ht="15.0" customHeight="1"/>
-    <row r="430" ht="15.0" customHeight="1"/>
-    <row r="431" ht="15.0" customHeight="1"/>
-    <row r="432" ht="15.0" customHeight="1"/>
-    <row r="433" ht="15.0" customHeight="1"/>
-    <row r="434" ht="15.0" customHeight="1"/>
-    <row r="435" ht="15.0" customHeight="1"/>
-    <row r="436" ht="15.0" customHeight="1"/>
-    <row r="437" ht="15.0" customHeight="1"/>
-    <row r="438" ht="15.0" customHeight="1"/>
-    <row r="439" ht="15.0" customHeight="1"/>
-    <row r="440" ht="15.0" customHeight="1"/>
-    <row r="441" ht="15.0" customHeight="1"/>
-    <row r="442" ht="15.0" customHeight="1"/>
-    <row r="443" ht="15.0" customHeight="1"/>
-    <row r="444" ht="15.0" customHeight="1"/>
-    <row r="445" ht="15.0" customHeight="1"/>
-    <row r="446" ht="15.0" customHeight="1"/>
-    <row r="447" ht="15.0" customHeight="1"/>
-    <row r="448" ht="15.0" customHeight="1"/>
-    <row r="449" ht="15.0" customHeight="1"/>
-    <row r="450" ht="15.0" customHeight="1"/>
-    <row r="451" ht="15.0" customHeight="1"/>
-    <row r="452" ht="15.0" customHeight="1"/>
-    <row r="453" ht="15.0" customHeight="1"/>
-    <row r="454" ht="15.0" customHeight="1"/>
-    <row r="455" ht="15.0" customHeight="1"/>
-    <row r="456" ht="15.0" customHeight="1"/>
-    <row r="457" ht="15.0" customHeight="1"/>
-    <row r="458" ht="15.0" customHeight="1"/>
-    <row r="459" ht="15.0" customHeight="1"/>
-    <row r="460" ht="15.0" customHeight="1"/>
-    <row r="461" ht="15.0" customHeight="1"/>
-    <row r="462" ht="15.0" customHeight="1"/>
-    <row r="463" ht="15.0" customHeight="1"/>
-    <row r="464" ht="15.0" customHeight="1"/>
-    <row r="465" ht="15.0" customHeight="1"/>
-    <row r="466" ht="15.0" customHeight="1"/>
-    <row r="467" ht="15.0" customHeight="1"/>
-    <row r="468" ht="15.0" customHeight="1"/>
-    <row r="469" ht="15.0" customHeight="1"/>
-    <row r="470" ht="15.0" customHeight="1"/>
-    <row r="471" ht="15.0" customHeight="1"/>
-    <row r="472" ht="15.0" customHeight="1"/>
-    <row r="473" ht="15.0" customHeight="1"/>
-    <row r="474" ht="15.0" customHeight="1"/>
-    <row r="475" ht="15.0" customHeight="1"/>
-    <row r="476" ht="15.0" customHeight="1"/>
-    <row r="477" ht="15.0" customHeight="1"/>
-    <row r="478" ht="15.0" customHeight="1"/>
-    <row r="479" ht="15.0" customHeight="1"/>
-    <row r="480" ht="15.0" customHeight="1"/>
-    <row r="481" ht="15.0" customHeight="1"/>
-    <row r="482" ht="15.0" customHeight="1"/>
-    <row r="483" ht="15.0" customHeight="1"/>
-    <row r="484" ht="15.0" customHeight="1"/>
-    <row r="485" ht="15.0" customHeight="1"/>
-    <row r="486" ht="15.0" customHeight="1"/>
-    <row r="487" ht="15.0" customHeight="1"/>
-    <row r="488" ht="15.0" customHeight="1"/>
-    <row r="489" ht="15.0" customHeight="1"/>
-    <row r="490" ht="15.0" customHeight="1"/>
-    <row r="491" ht="15.0" customHeight="1"/>
-    <row r="492" ht="15.0" customHeight="1"/>
-    <row r="493" ht="15.0" customHeight="1"/>
-    <row r="494" ht="15.0" customHeight="1"/>
-    <row r="495" ht="15.0" customHeight="1"/>
-    <row r="496" ht="15.0" customHeight="1"/>
-    <row r="497" ht="15.0" customHeight="1"/>
-    <row r="498" ht="15.0" customHeight="1"/>
-    <row r="499" ht="15.0" customHeight="1"/>
-    <row r="500" ht="15.0" customHeight="1"/>
-    <row r="501" ht="15.0" customHeight="1"/>
-    <row r="502" ht="15.0" customHeight="1"/>
-    <row r="503" ht="15.0" customHeight="1"/>
-    <row r="504" ht="15.0" customHeight="1"/>
-    <row r="505" ht="15.0" customHeight="1"/>
-    <row r="506" ht="15.0" customHeight="1"/>
-    <row r="507" ht="15.0" customHeight="1"/>
-    <row r="508" ht="15.0" customHeight="1"/>
-    <row r="509" ht="15.0" customHeight="1"/>
-    <row r="510" ht="15.0" customHeight="1"/>
-    <row r="511" ht="15.0" customHeight="1"/>
-    <row r="512" ht="15.0" customHeight="1"/>
-    <row r="513" ht="15.0" customHeight="1"/>
-    <row r="514" ht="15.0" customHeight="1"/>
-    <row r="515" ht="15.0" customHeight="1"/>
-    <row r="516" ht="15.0" customHeight="1"/>
-    <row r="517" ht="15.0" customHeight="1"/>
-    <row r="518" ht="15.0" customHeight="1"/>
-    <row r="519" ht="15.0" customHeight="1"/>
-    <row r="520" ht="15.0" customHeight="1"/>
-    <row r="521" ht="15.0" customHeight="1"/>
-    <row r="522" ht="15.0" customHeight="1"/>
-    <row r="523" ht="15.0" customHeight="1"/>
-    <row r="524" ht="15.0" customHeight="1"/>
-    <row r="525" ht="15.0" customHeight="1"/>
-    <row r="526" ht="15.0" customHeight="1"/>
-    <row r="527" ht="15.0" customHeight="1"/>
-    <row r="528" ht="15.0" customHeight="1"/>
-    <row r="529" ht="15.0" customHeight="1"/>
-    <row r="530" ht="15.0" customHeight="1"/>
-    <row r="531" ht="15.0" customHeight="1"/>
-    <row r="532" ht="15.0" customHeight="1"/>
-    <row r="533" ht="15.0" customHeight="1"/>
-    <row r="534" ht="15.0" customHeight="1"/>
-    <row r="535" ht="15.0" customHeight="1"/>
-    <row r="536" ht="15.0" customHeight="1"/>
-    <row r="537" ht="15.0" customHeight="1"/>
-    <row r="538" ht="15.0" customHeight="1"/>
-    <row r="539" ht="15.0" customHeight="1"/>
-    <row r="540" ht="15.0" customHeight="1"/>
-    <row r="541" ht="15.0" customHeight="1"/>
-    <row r="542" ht="15.0" customHeight="1"/>
-    <row r="543" ht="15.0" customHeight="1"/>
-    <row r="544" ht="15.0" customHeight="1"/>
-    <row r="545" ht="15.0" customHeight="1"/>
-    <row r="546" ht="15.0" customHeight="1"/>
-    <row r="547" ht="15.0" customHeight="1"/>
-    <row r="548" ht="15.0" customHeight="1"/>
-    <row r="549" ht="15.0" customHeight="1"/>
-    <row r="550" ht="15.0" customHeight="1"/>
-    <row r="551" ht="15.0" customHeight="1"/>
-    <row r="552" ht="15.0" customHeight="1"/>
-    <row r="553" ht="15.0" customHeight="1"/>
-    <row r="554" ht="15.0" customHeight="1"/>
-    <row r="555" ht="15.0" customHeight="1"/>
-    <row r="556" ht="15.0" customHeight="1"/>
-    <row r="557" ht="15.0" customHeight="1"/>
-    <row r="558" ht="15.0" customHeight="1"/>
-    <row r="559" ht="15.0" customHeight="1"/>
-    <row r="560" ht="15.0" customHeight="1"/>
-    <row r="561" ht="15.0" customHeight="1"/>
-    <row r="562" ht="15.0" customHeight="1"/>
-    <row r="563" ht="15.0" customHeight="1"/>
-    <row r="564" ht="15.0" customHeight="1"/>
-    <row r="565" ht="15.0" customHeight="1"/>
-    <row r="566" ht="15.0" customHeight="1"/>
-    <row r="567" ht="15.0" customHeight="1"/>
-    <row r="568" ht="15.0" customHeight="1"/>
-    <row r="569" ht="15.0" customHeight="1"/>
-    <row r="570" ht="15.0" customHeight="1"/>
-    <row r="571" ht="15.0" customHeight="1"/>
-    <row r="572" ht="15.0" customHeight="1"/>
-    <row r="573" ht="15.0" customHeight="1"/>
-    <row r="574" ht="15.0" customHeight="1"/>
-    <row r="575" ht="15.0" customHeight="1"/>
-    <row r="576" ht="15.0" customHeight="1"/>
-    <row r="577" ht="15.0" customHeight="1"/>
-    <row r="578" ht="15.0" customHeight="1"/>
-    <row r="579" ht="15.0" customHeight="1"/>
-    <row r="580" ht="15.0" customHeight="1"/>
-    <row r="581" ht="15.0" customHeight="1"/>
-    <row r="582" ht="15.0" customHeight="1"/>
-    <row r="583" ht="15.0" customHeight="1"/>
-    <row r="584" ht="15.0" customHeight="1"/>
-    <row r="585" ht="15.0" customHeight="1"/>
-    <row r="586" ht="15.0" customHeight="1"/>
-    <row r="587" ht="15.0" customHeight="1"/>
-    <row r="588" ht="15.0" customHeight="1"/>
-    <row r="589" ht="15.0" customHeight="1"/>
-    <row r="590" ht="15.0" customHeight="1"/>
-    <row r="591" ht="15.0" customHeight="1"/>
-    <row r="592" ht="15.0" customHeight="1"/>
-    <row r="593" ht="15.0" customHeight="1"/>
-    <row r="594" ht="15.0" customHeight="1"/>
-    <row r="595" ht="15.0" customHeight="1"/>
-    <row r="596" ht="15.0" customHeight="1"/>
-    <row r="597" ht="15.0" customHeight="1"/>
-    <row r="598" ht="15.0" customHeight="1"/>
-    <row r="599" ht="15.0" customHeight="1"/>
-    <row r="600" ht="15.0" customHeight="1"/>
-    <row r="601" ht="15.0" customHeight="1"/>
-    <row r="602" ht="15.0" customHeight="1"/>
-    <row r="603" ht="15.0" customHeight="1"/>
-    <row r="604" ht="15.0" customHeight="1"/>
-    <row r="605" ht="15.0" customHeight="1"/>
-    <row r="606" ht="15.0" customHeight="1"/>
-    <row r="607" ht="15.0" customHeight="1"/>
-    <row r="608" ht="15.0" customHeight="1"/>
-    <row r="609" ht="15.0" customHeight="1"/>
-    <row r="610" ht="15.0" customHeight="1"/>
-    <row r="611" ht="15.0" customHeight="1"/>
-    <row r="612" ht="15.0" customHeight="1"/>
-    <row r="613" ht="15.0" customHeight="1"/>
-    <row r="614" ht="15.0" customHeight="1"/>
-    <row r="615" ht="15.0" customHeight="1"/>
-    <row r="616" ht="15.0" customHeight="1"/>
-    <row r="617" ht="15.0" customHeight="1"/>
-    <row r="618" ht="15.0" customHeight="1"/>
-    <row r="619" ht="15.0" customHeight="1"/>
-    <row r="620" ht="15.0" customHeight="1"/>
-    <row r="621" ht="15.0" customHeight="1"/>
-    <row r="622" ht="15.0" customHeight="1"/>
-    <row r="623" ht="15.0" customHeight="1"/>
-    <row r="624" ht="15.0" customHeight="1"/>
-    <row r="625" ht="15.0" customHeight="1"/>
-    <row r="626" ht="15.0" customHeight="1"/>
-    <row r="627" ht="15.0" customHeight="1"/>
-    <row r="628" ht="15.0" customHeight="1"/>
-    <row r="629" ht="15.0" customHeight="1"/>
-    <row r="630" ht="15.0" customHeight="1"/>
-    <row r="631" ht="15.0" customHeight="1"/>
-    <row r="632" ht="15.0" customHeight="1"/>
-    <row r="633" ht="15.0" customHeight="1"/>
-    <row r="634" ht="15.0" customHeight="1"/>
-    <row r="635" ht="15.0" customHeight="1"/>
-    <row r="636" ht="15.0" customHeight="1"/>
-    <row r="637" ht="15.0" customHeight="1"/>
-    <row r="638" ht="15.0" customHeight="1"/>
-    <row r="639" ht="15.0" customHeight="1"/>
-    <row r="640" ht="15.0" customHeight="1"/>
-    <row r="641" ht="15.0" customHeight="1"/>
-    <row r="642" ht="15.0" customHeight="1"/>
-    <row r="643" ht="15.0" customHeight="1"/>
-    <row r="644" ht="15.0" customHeight="1"/>
-    <row r="645" ht="15.0" customHeight="1"/>
-    <row r="646" ht="15.0" customHeight="1"/>
-    <row r="647" ht="15.0" customHeight="1"/>
-    <row r="648" ht="15.0" customHeight="1"/>
-    <row r="649" ht="15.0" customHeight="1"/>
-    <row r="650" ht="15.0" customHeight="1"/>
-    <row r="651" ht="15.0" customHeight="1"/>
-    <row r="652" ht="15.0" customHeight="1"/>
-    <row r="653" ht="15.0" customHeight="1"/>
-    <row r="654" ht="15.0" customHeight="1"/>
-    <row r="655" ht="15.0" customHeight="1"/>
-    <row r="656" ht="15.0" customHeight="1"/>
-    <row r="657" ht="15.0" customHeight="1"/>
-    <row r="658" ht="15.0" customHeight="1"/>
-    <row r="659" ht="15.0" customHeight="1"/>
-    <row r="660" ht="15.0" customHeight="1"/>
-    <row r="661" ht="15.0" customHeight="1"/>
-    <row r="662" ht="15.0" customHeight="1"/>
-    <row r="663" ht="15.0" customHeight="1"/>
-    <row r="664" ht="15.0" customHeight="1"/>
-    <row r="665" ht="15.0" customHeight="1"/>
-    <row r="666" ht="15.0" customHeight="1"/>
-    <row r="667" ht="15.0" customHeight="1"/>
-    <row r="668" ht="15.0" customHeight="1"/>
-    <row r="669" ht="15.0" customHeight="1"/>
-    <row r="670" ht="15.0" customHeight="1"/>
-    <row r="671" ht="15.0" customHeight="1"/>
-    <row r="672" ht="15.0" customHeight="1"/>
-    <row r="673" ht="15.0" customHeight="1"/>
-    <row r="674" ht="15.0" customHeight="1"/>
-    <row r="675" ht="15.0" customHeight="1"/>
-    <row r="676" ht="15.0" customHeight="1"/>
-    <row r="677" ht="15.0" customHeight="1"/>
-    <row r="678" ht="15.0" customHeight="1"/>
-    <row r="679" ht="15.0" customHeight="1"/>
-    <row r="680" ht="15.0" customHeight="1"/>
-    <row r="681" ht="15.0" customHeight="1"/>
-    <row r="682" ht="15.0" customHeight="1"/>
-    <row r="683" ht="15.0" customHeight="1"/>
-    <row r="684" ht="15.0" customHeight="1"/>
-    <row r="685" ht="15.0" customHeight="1"/>
-    <row r="686" ht="15.0" customHeight="1"/>
-    <row r="687" ht="15.0" customHeight="1"/>
-    <row r="688" ht="15.0" customHeight="1"/>
-    <row r="689" ht="15.0" customHeight="1"/>
-    <row r="690" ht="15.0" customHeight="1"/>
-    <row r="691" ht="15.0" customHeight="1"/>
-    <row r="692" ht="15.0" customHeight="1"/>
-    <row r="693" ht="15.0" customHeight="1"/>
-    <row r="694" ht="15.0" customHeight="1"/>
-    <row r="695" ht="15.0" customHeight="1"/>
-    <row r="696" ht="15.0" customHeight="1"/>
-    <row r="697" ht="15.0" customHeight="1"/>
-    <row r="698" ht="15.0" customHeight="1"/>
-    <row r="699" ht="15.0" customHeight="1"/>
-    <row r="700" ht="15.0" customHeight="1"/>
-    <row r="701" ht="15.0" customHeight="1"/>
-    <row r="702" ht="15.0" customHeight="1"/>
-    <row r="703" ht="15.0" customHeight="1"/>
-    <row r="704" ht="15.0" customHeight="1"/>
-    <row r="705" ht="15.0" customHeight="1"/>
-    <row r="706" ht="15.0" customHeight="1"/>
-    <row r="707" ht="15.0" customHeight="1"/>
-    <row r="708" ht="15.0" customHeight="1"/>
-    <row r="709" ht="15.0" customHeight="1"/>
-    <row r="710" ht="15.0" customHeight="1"/>
-    <row r="711" ht="15.0" customHeight="1"/>
-    <row r="712" ht="15.0" customHeight="1"/>
-    <row r="713" ht="15.0" customHeight="1"/>
-    <row r="714" ht="15.0" customHeight="1"/>
-    <row r="715" ht="15.0" customHeight="1"/>
-    <row r="716" ht="15.0" customHeight="1"/>
-    <row r="717" ht="15.0" customHeight="1"/>
-    <row r="718" ht="15.0" customHeight="1"/>
-    <row r="719" ht="15.0" customHeight="1"/>
-    <row r="720" ht="15.0" customHeight="1"/>
-    <row r="721" ht="15.0" customHeight="1"/>
-    <row r="722" ht="15.0" customHeight="1"/>
-    <row r="723" ht="15.0" customHeight="1"/>
-    <row r="724" ht="15.0" customHeight="1"/>
-    <row r="725" ht="15.0" customHeight="1"/>
-    <row r="726" ht="15.0" customHeight="1"/>
-    <row r="727" ht="15.0" customHeight="1"/>
-    <row r="728" ht="15.0" customHeight="1"/>
-    <row r="729" ht="15.0" customHeight="1"/>
-    <row r="730" ht="15.0" customHeight="1"/>
-    <row r="731" ht="15.0" customHeight="1"/>
-    <row r="732" ht="15.0" customHeight="1"/>
-    <row r="733" ht="15.0" customHeight="1"/>
-    <row r="734" ht="15.0" customHeight="1"/>
-    <row r="735" ht="15.0" customHeight="1"/>
-    <row r="736" ht="15.0" customHeight="1"/>
-    <row r="737" ht="15.0" customHeight="1"/>
-    <row r="738" ht="15.0" customHeight="1"/>
-    <row r="739" ht="15.0" customHeight="1"/>
-    <row r="740" ht="15.0" customHeight="1"/>
-    <row r="741" ht="15.0" customHeight="1"/>
-    <row r="742" ht="15.0" customHeight="1"/>
-    <row r="743" ht="15.0" customHeight="1"/>
-    <row r="744" ht="15.0" customHeight="1"/>
-    <row r="745" ht="15.0" customHeight="1"/>
-    <row r="746" ht="15.0" customHeight="1"/>
-    <row r="747" ht="15.0" customHeight="1"/>
-    <row r="748" ht="15.0" customHeight="1"/>
-    <row r="749" ht="15.0" customHeight="1"/>
-    <row r="750" ht="15.0" customHeight="1"/>
-    <row r="751" ht="15.0" customHeight="1"/>
-    <row r="752" ht="15.0" customHeight="1"/>
-    <row r="753" ht="15.0" customHeight="1"/>
-    <row r="754" ht="15.0" customHeight="1"/>
-    <row r="755" ht="15.0" customHeight="1"/>
-    <row r="756" ht="15.0" customHeight="1"/>
-    <row r="757" ht="15.0" customHeight="1"/>
-    <row r="758" ht="15.0" customHeight="1"/>
-    <row r="759" ht="15.0" customHeight="1"/>
-    <row r="760" ht="15.0" customHeight="1"/>
-    <row r="761" ht="15.0" customHeight="1"/>
-    <row r="762" ht="15.0" customHeight="1"/>
-    <row r="763" ht="15.0" customHeight="1"/>
-    <row r="764" ht="15.0" customHeight="1"/>
-    <row r="765" ht="15.0" customHeight="1"/>
-    <row r="766" ht="15.0" customHeight="1"/>
-    <row r="767" ht="15.0" customHeight="1"/>
-    <row r="768" ht="15.0" customHeight="1"/>
-    <row r="769" ht="15.0" customHeight="1"/>
-    <row r="770" ht="15.0" customHeight="1"/>
-    <row r="771" ht="15.0" customHeight="1"/>
-    <row r="772" ht="15.0" customHeight="1"/>
-    <row r="773" ht="15.0" customHeight="1"/>
-    <row r="774" ht="15.0" customHeight="1"/>
-    <row r="775" ht="15.0" customHeight="1"/>
-    <row r="776" ht="15.0" customHeight="1"/>
-    <row r="777" ht="15.0" customHeight="1"/>
-    <row r="778" ht="15.0" customHeight="1"/>
-    <row r="779" ht="15.0" customHeight="1"/>
-    <row r="780" ht="15.0" customHeight="1"/>
-    <row r="781" ht="15.0" customHeight="1"/>
-    <row r="782" ht="15.0" customHeight="1"/>
-    <row r="783" ht="15.0" customHeight="1"/>
-    <row r="784" ht="15.0" customHeight="1"/>
-    <row r="785" ht="15.0" customHeight="1"/>
-    <row r="786" ht="15.0" customHeight="1"/>
-    <row r="787" ht="15.0" customHeight="1"/>
-    <row r="788" ht="15.0" customHeight="1"/>
-    <row r="789" ht="15.0" customHeight="1"/>
-    <row r="790" ht="15.0" customHeight="1"/>
-    <row r="791" ht="15.0" customHeight="1"/>
-    <row r="792" ht="15.0" customHeight="1"/>
-    <row r="793" ht="15.0" customHeight="1"/>
-    <row r="794" ht="15.0" customHeight="1"/>
-    <row r="795" ht="15.0" customHeight="1"/>
-    <row r="796" ht="15.0" customHeight="1"/>
-    <row r="797" ht="15.0" customHeight="1"/>
-    <row r="798" ht="15.0" customHeight="1"/>
-    <row r="799" ht="15.0" customHeight="1"/>
-    <row r="800" ht="15.0" customHeight="1"/>
-    <row r="801" ht="15.0" customHeight="1"/>
-    <row r="802" ht="15.0" customHeight="1"/>
-    <row r="803" ht="15.0" customHeight="1"/>
-    <row r="804" ht="15.0" customHeight="1"/>
-    <row r="805" ht="15.0" customHeight="1"/>
-    <row r="806" ht="15.0" customHeight="1"/>
-    <row r="807" ht="15.0" customHeight="1"/>
-    <row r="808" ht="15.0" customHeight="1"/>
-    <row r="809" ht="15.0" customHeight="1"/>
-    <row r="810" ht="15.0" customHeight="1"/>
-    <row r="811" ht="15.0" customHeight="1"/>
-    <row r="812" ht="15.0" customHeight="1"/>
-    <row r="813" ht="15.0" customHeight="1"/>
-    <row r="814" ht="15.0" customHeight="1"/>
-    <row r="815" ht="15.0" customHeight="1"/>
-    <row r="816" ht="15.0" customHeight="1"/>
-    <row r="817" ht="15.0" customHeight="1"/>
-    <row r="818" ht="15.0" customHeight="1"/>
-    <row r="819" ht="15.0" customHeight="1"/>
-    <row r="820" ht="15.0" customHeight="1"/>
-    <row r="821" ht="15.0" customHeight="1"/>
-    <row r="822" ht="15.0" customHeight="1"/>
-    <row r="823" ht="15.0" customHeight="1"/>
-    <row r="824" ht="15.0" customHeight="1"/>
-    <row r="825" ht="15.0" customHeight="1"/>
-    <row r="826" ht="15.0" customHeight="1"/>
-    <row r="827" ht="15.0" customHeight="1"/>
-    <row r="828" ht="15.0" customHeight="1"/>
-    <row r="829" ht="15.0" customHeight="1"/>
-    <row r="830" ht="15.0" customHeight="1"/>
-    <row r="831" ht="15.0" customHeight="1"/>
-    <row r="832" ht="15.0" customHeight="1"/>
-    <row r="833" ht="15.0" customHeight="1"/>
-    <row r="834" ht="15.0" customHeight="1"/>
-    <row r="835" ht="15.0" customHeight="1"/>
-    <row r="836" ht="15.0" customHeight="1"/>
-    <row r="837" ht="15.0" customHeight="1"/>
-    <row r="838" ht="15.0" customHeight="1"/>
-    <row r="839" ht="15.0" customHeight="1"/>
-    <row r="840" ht="15.0" customHeight="1"/>
-    <row r="841" ht="15.0" customHeight="1"/>
-    <row r="842" ht="15.0" customHeight="1"/>
-    <row r="843" ht="15.0" customHeight="1"/>
-    <row r="844" ht="15.0" customHeight="1"/>
-    <row r="845" ht="15.0" customHeight="1"/>
-    <row r="846" ht="15.0" customHeight="1"/>
-    <row r="847" ht="15.0" customHeight="1"/>
-    <row r="848" ht="15.0" customHeight="1"/>
-    <row r="849" ht="15.0" customHeight="1"/>
-    <row r="850" ht="15.0" customHeight="1"/>
-    <row r="851" ht="15.0" customHeight="1"/>
-    <row r="852" ht="15.0" customHeight="1"/>
-    <row r="853" ht="15.0" customHeight="1"/>
-    <row r="854" ht="15.0" customHeight="1"/>
-    <row r="855" ht="15.0" customHeight="1"/>
-    <row r="856" ht="15.0" customHeight="1"/>
-    <row r="857" ht="15.0" customHeight="1"/>
-    <row r="858" ht="15.0" customHeight="1"/>
-    <row r="859" ht="15.0" customHeight="1"/>
-    <row r="860" ht="15.0" customHeight="1"/>
-    <row r="861" ht="15.0" customHeight="1"/>
-    <row r="862" ht="15.0" customHeight="1"/>
-    <row r="863" ht="15.0" customHeight="1"/>
-    <row r="864" ht="15.0" customHeight="1"/>
-    <row r="865" ht="15.0" customHeight="1"/>
-    <row r="866" ht="15.0" customHeight="1"/>
-    <row r="867" ht="15.0" customHeight="1"/>
-    <row r="868" ht="15.0" customHeight="1"/>
-    <row r="869" ht="15.0" customHeight="1"/>
-    <row r="870" ht="15.0" customHeight="1"/>
-    <row r="871" ht="15.0" customHeight="1"/>
-    <row r="872" ht="15.0" customHeight="1"/>
-    <row r="873" ht="15.0" customHeight="1"/>
-    <row r="874" ht="15.0" customHeight="1"/>
-    <row r="875" ht="15.0" customHeight="1"/>
-    <row r="876" ht="15.0" customHeight="1"/>
-    <row r="877" ht="15.0" customHeight="1"/>
-    <row r="878" ht="15.0" customHeight="1"/>
-    <row r="879" ht="15.0" customHeight="1"/>
-    <row r="880" ht="15.0" customHeight="1"/>
-    <row r="881" ht="15.0" customHeight="1"/>
-    <row r="882" ht="15.0" customHeight="1"/>
-    <row r="883" ht="15.0" customHeight="1"/>
-    <row r="884" ht="15.0" customHeight="1"/>
-    <row r="885" ht="15.0" customHeight="1"/>
-    <row r="886" ht="15.0" customHeight="1"/>
-    <row r="887" ht="15.0" customHeight="1"/>
-    <row r="888" ht="15.0" customHeight="1"/>
-    <row r="889" ht="15.0" customHeight="1"/>
-    <row r="890" ht="15.0" customHeight="1"/>
-    <row r="891" ht="15.0" customHeight="1"/>
-    <row r="892" ht="15.0" customHeight="1"/>
-    <row r="893" ht="15.0" customHeight="1"/>
-    <row r="894" ht="15.0" customHeight="1"/>
-    <row r="895" ht="15.0" customHeight="1"/>
-    <row r="896" ht="15.0" customHeight="1"/>
-    <row r="897" ht="15.0" customHeight="1"/>
-    <row r="898" ht="15.0" customHeight="1"/>
-    <row r="899" ht="15.0" customHeight="1"/>
-    <row r="900" ht="15.0" customHeight="1"/>
-    <row r="901" ht="15.0" customHeight="1"/>
-    <row r="902" ht="15.0" customHeight="1"/>
-    <row r="903" ht="15.0" customHeight="1"/>
-    <row r="904" ht="15.0" customHeight="1"/>
-    <row r="905" ht="15.0" customHeight="1"/>
-    <row r="906" ht="15.0" customHeight="1"/>
-    <row r="907" ht="15.0" customHeight="1"/>
-    <row r="908" ht="15.0" customHeight="1"/>
-    <row r="909" ht="15.0" customHeight="1"/>
-    <row r="910" ht="15.0" customHeight="1"/>
-    <row r="911" ht="15.0" customHeight="1"/>
-    <row r="912" ht="15.0" customHeight="1"/>
-    <row r="913" ht="15.0" customHeight="1"/>
-    <row r="914" ht="15.0" customHeight="1"/>
-    <row r="915" ht="15.0" customHeight="1"/>
-    <row r="916" ht="15.0" customHeight="1"/>
-    <row r="917" ht="15.0" customHeight="1"/>
-    <row r="918" ht="15.0" customHeight="1"/>
-    <row r="919" ht="15.0" customHeight="1"/>
-    <row r="920" ht="15.0" customHeight="1"/>
-    <row r="921" ht="15.0" customHeight="1"/>
-    <row r="922" ht="15.0" customHeight="1"/>
-    <row r="923" ht="15.0" customHeight="1"/>
-    <row r="924" ht="15.0" customHeight="1"/>
-    <row r="925" ht="15.0" customHeight="1"/>
-    <row r="926" ht="15.0" customHeight="1"/>
-    <row r="927" ht="15.0" customHeight="1"/>
-    <row r="928" ht="15.0" customHeight="1"/>
-    <row r="929" ht="15.0" customHeight="1"/>
-    <row r="930" ht="15.0" customHeight="1"/>
-    <row r="931" ht="15.0" customHeight="1"/>
-    <row r="932" ht="15.0" customHeight="1"/>
-    <row r="933" ht="15.0" customHeight="1"/>
-    <row r="934" ht="15.0" customHeight="1"/>
-    <row r="935" ht="15.0" customHeight="1"/>
-    <row r="936" ht="15.0" customHeight="1"/>
-    <row r="937" ht="15.0" customHeight="1"/>
-    <row r="938" ht="15.0" customHeight="1"/>
-    <row r="939" ht="15.0" customHeight="1"/>
-    <row r="940" ht="15.0" customHeight="1"/>
-    <row r="941" ht="15.0" customHeight="1"/>
-    <row r="942" ht="15.0" customHeight="1"/>
-    <row r="943" ht="15.0" customHeight="1"/>
-    <row r="944" ht="15.0" customHeight="1"/>
-    <row r="945" ht="15.0" customHeight="1"/>
-    <row r="946" ht="15.0" customHeight="1"/>
-    <row r="947" ht="15.0" customHeight="1"/>
-    <row r="948" ht="15.0" customHeight="1"/>
-    <row r="949" ht="15.0" customHeight="1"/>
-    <row r="950" ht="15.0" customHeight="1"/>
-    <row r="951" ht="15.0" customHeight="1"/>
-    <row r="952" ht="15.0" customHeight="1"/>
-    <row r="953" ht="15.0" customHeight="1"/>
-    <row r="954" ht="15.0" customHeight="1"/>
-    <row r="955" ht="15.0" customHeight="1"/>
-    <row r="956" ht="15.0" customHeight="1"/>
-    <row r="957" ht="15.0" customHeight="1"/>
-    <row r="958" ht="15.0" customHeight="1"/>
-    <row r="959" ht="15.0" customHeight="1"/>
-    <row r="960" ht="15.0" customHeight="1"/>
-    <row r="961" ht="15.0" customHeight="1"/>
-    <row r="962" ht="15.0" customHeight="1"/>
-    <row r="963" ht="15.0" customHeight="1"/>
-    <row r="964" ht="15.0" customHeight="1"/>
-    <row r="965" ht="15.0" customHeight="1"/>
-    <row r="966" ht="15.0" customHeight="1"/>
-    <row r="967" ht="15.0" customHeight="1"/>
-    <row r="968" ht="15.0" customHeight="1"/>
-    <row r="969" ht="15.0" customHeight="1"/>
-    <row r="970" ht="15.0" customHeight="1"/>
-    <row r="971" ht="15.0" customHeight="1"/>
-    <row r="972" ht="15.0" customHeight="1"/>
-    <row r="973" ht="15.0" customHeight="1"/>
-    <row r="974" ht="15.0" customHeight="1"/>
-    <row r="975" ht="15.0" customHeight="1"/>
-    <row r="976" ht="15.0" customHeight="1"/>
-    <row r="977" ht="15.0" customHeight="1"/>
-    <row r="978" ht="15.0" customHeight="1"/>
-    <row r="979" ht="15.0" customHeight="1"/>
-    <row r="980" ht="15.0" customHeight="1"/>
-    <row r="981" ht="15.0" customHeight="1"/>
-    <row r="982" ht="15.0" customHeight="1"/>
-    <row r="983" ht="15.0" customHeight="1"/>
-    <row r="984" ht="15.0" customHeight="1"/>
-    <row r="985" ht="15.0" customHeight="1"/>
-    <row r="986" ht="15.0" customHeight="1"/>
-    <row r="987" ht="15.0" customHeight="1"/>
-    <row r="988" ht="15.0" customHeight="1"/>
-    <row r="989" ht="15.0" customHeight="1"/>
-    <row r="990" ht="15.0" customHeight="1"/>
-    <row r="991" ht="15.0" customHeight="1"/>
-    <row r="992" ht="15.0" customHeight="1"/>
-    <row r="993" ht="15.0" customHeight="1"/>
-    <row r="994" ht="15.0" customHeight="1"/>
-    <row r="995" ht="15.0" customHeight="1"/>
-    <row r="996" ht="15.0" customHeight="1"/>
-    <row r="997" ht="15.0" customHeight="1"/>
-    <row r="998" ht="15.0" customHeight="1"/>
-    <row r="999" ht="15.0" customHeight="1"/>
-    <row r="1000" ht="15.0" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Templates/Tables/StringInfo/StrTable.xlsx
+++ b/Templates/Tables/StringInfo/StrTable.xlsx
@@ -214,7 +214,7 @@
     <t>TRACKING_DP_MSG</t>
   </si>
   <si>
-    <t>앱 추적 승인</t>
+    <t>다음 화면에서\n추적 허용</t>
   </si>
   <si>
     <t>Allow tracking on the\nnext screen for</t>
@@ -226,10 +226,10 @@
     <t>TRACKING_DP_DESC_MSG_01</t>
   </si>
   <si>
-    <t>특별한 프로모션을 제공해\n드립니다</t>
-  </si>
-  <si>
-    <t>Special offers and promotions\njust for you</t>
+    <t>- 특별한 프로모션을 제공해\n드립니다</t>
+  </si>
+  <si>
+    <t>- Special offers and promotions\njust for you</t>
   </si>
   <si>
     <t>추적 설명 팝업 설명 메세지 2</t>
@@ -238,10 +238,10 @@
     <t>TRACKING_DP_DESC_MSG_02</t>
   </si>
   <si>
-    <t>관심사에 맞는 광고를 보여\n드립니다</t>
-  </si>
-  <si>
-    <t>Advertisements that match\nyour interests</t>
+    <t>- 관심사에 맞는 광고를 보여\n드립니다</t>
+  </si>
+  <si>
+    <t>- Advertisements that match\nyour interests</t>
   </si>
   <si>
     <t>추적 설명 팝업 설명 메세지 3</t>
@@ -250,10 +250,10 @@
     <t>TRACKING_DP_DESC_MSG_03</t>
   </si>
   <si>
-    <t>개인화 된 경험을 향상 시켜\n드립니다</t>
-  </si>
-  <si>
-    <t>An improved personalized\nexperience over time</t>
+    <t>- 개인화 된 경험을 향상 시켜\n드립니다</t>
+  </si>
+  <si>
+    <t>- An improved personalized\nexperience over time</t>
   </si>
   <si>
     <t>공용 로그인 성공 메세지</t>
@@ -1978,7 +1978,7 @@
       <c r="C17" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="10" t="s">
         <v>67</v>
       </c>
       <c r="E17" s="7" t="s">
@@ -2015,10 +2015,10 @@
       <c r="C18" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="10" t="s">
         <v>72</v>
       </c>
       <c r="F18" s="7"/>
@@ -2052,10 +2052,10 @@
       <c r="C19" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="10" t="s">
         <v>76</v>
       </c>
       <c r="F19" s="7"/>
@@ -2089,10 +2089,10 @@
       <c r="C20" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="10" t="s">
         <v>80</v>
       </c>
       <c r="F20" s="7"/>

--- a/Templates/Tables/StringInfo/StrTable.xlsx
+++ b/Templates/Tables/StringInfo/StrTable.xlsx
@@ -778,7 +778,7 @@
     <t>Beginner Pack</t>
   </si>
   <si>
-    <t>공용 전문가 패키지 텍스트</t>
+    <t>공용 숙련자 패키지 텍스트</t>
   </si>
   <si>
     <t>COMMON_EXPERT_PKGS_TEXT</t>
@@ -1071,7 +1071,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1126,6 +1126,9 @@
     </xf>
     <xf borderId="3" fillId="4" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="3" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
@@ -3745,7 +3748,7 @@
       <c r="Y64" s="19"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="18" t="s">
+      <c r="A65" s="20" t="s">
         <v>255</v>
       </c>
       <c r="B65" s="19">
@@ -4004,448 +4007,448 @@
       <c r="Y71" s="17"/>
     </row>
     <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="20" t="s">
+      <c r="A72" s="21" t="s">
         <v>283</v>
       </c>
-      <c r="B72" s="21">
+      <c r="B72" s="22">
         <v>0.0</v>
       </c>
-      <c r="C72" s="22" t="s">
+      <c r="C72" s="23" t="s">
         <v>284</v>
       </c>
-      <c r="D72" s="22" t="s">
+      <c r="D72" s="23" t="s">
         <v>285</v>
       </c>
-      <c r="E72" s="22" t="s">
+      <c r="E72" s="23" t="s">
         <v>286</v>
       </c>
-      <c r="F72" s="22"/>
-      <c r="G72" s="22"/>
-      <c r="H72" s="22"/>
-      <c r="I72" s="22"/>
-      <c r="J72" s="22"/>
-      <c r="K72" s="22"/>
-      <c r="L72" s="22"/>
-      <c r="M72" s="22"/>
-      <c r="N72" s="22"/>
-      <c r="O72" s="22"/>
-      <c r="P72" s="22"/>
-      <c r="Q72" s="22"/>
-      <c r="R72" s="22"/>
-      <c r="S72" s="22"/>
-      <c r="T72" s="22"/>
-      <c r="U72" s="22"/>
-      <c r="V72" s="22"/>
-      <c r="W72" s="22"/>
-      <c r="X72" s="22"/>
-      <c r="Y72" s="22"/>
+      <c r="F72" s="23"/>
+      <c r="G72" s="23"/>
+      <c r="H72" s="23"/>
+      <c r="I72" s="23"/>
+      <c r="J72" s="23"/>
+      <c r="K72" s="23"/>
+      <c r="L72" s="23"/>
+      <c r="M72" s="23"/>
+      <c r="N72" s="23"/>
+      <c r="O72" s="23"/>
+      <c r="P72" s="23"/>
+      <c r="Q72" s="23"/>
+      <c r="R72" s="23"/>
+      <c r="S72" s="23"/>
+      <c r="T72" s="23"/>
+      <c r="U72" s="23"/>
+      <c r="V72" s="23"/>
+      <c r="W72" s="23"/>
+      <c r="X72" s="23"/>
+      <c r="Y72" s="23"/>
     </row>
     <row r="73" ht="15.0" customHeight="1">
-      <c r="A73" s="23" t="s">
+      <c r="A73" s="24" t="s">
         <v>287</v>
       </c>
-      <c r="B73" s="24">
+      <c r="B73" s="25">
         <v>0.0</v>
       </c>
-      <c r="C73" s="24" t="s">
+      <c r="C73" s="25" t="s">
         <v>288</v>
       </c>
-      <c r="D73" s="24" t="s">
+      <c r="D73" s="25" t="s">
         <v>151</v>
       </c>
-      <c r="E73" s="24" t="s">
+      <c r="E73" s="25" t="s">
         <v>152</v>
       </c>
-      <c r="F73" s="24"/>
-      <c r="G73" s="24"/>
-      <c r="H73" s="24"/>
-      <c r="I73" s="24"/>
-      <c r="J73" s="24"/>
-      <c r="K73" s="24"/>
-      <c r="L73" s="24"/>
-      <c r="M73" s="24"/>
-      <c r="N73" s="24"/>
-      <c r="O73" s="24"/>
-      <c r="P73" s="24"/>
-      <c r="Q73" s="24"/>
-      <c r="R73" s="24"/>
-      <c r="S73" s="24"/>
-      <c r="T73" s="24"/>
-      <c r="U73" s="24"/>
-      <c r="V73" s="24"/>
-      <c r="W73" s="24"/>
-      <c r="X73" s="24"/>
-      <c r="Y73" s="24"/>
+      <c r="F73" s="25"/>
+      <c r="G73" s="25"/>
+      <c r="H73" s="25"/>
+      <c r="I73" s="25"/>
+      <c r="J73" s="25"/>
+      <c r="K73" s="25"/>
+      <c r="L73" s="25"/>
+      <c r="M73" s="25"/>
+      <c r="N73" s="25"/>
+      <c r="O73" s="25"/>
+      <c r="P73" s="25"/>
+      <c r="Q73" s="25"/>
+      <c r="R73" s="25"/>
+      <c r="S73" s="25"/>
+      <c r="T73" s="25"/>
+      <c r="U73" s="25"/>
+      <c r="V73" s="25"/>
+      <c r="W73" s="25"/>
+      <c r="X73" s="25"/>
+      <c r="Y73" s="25"/>
     </row>
     <row r="74" ht="15.0" customHeight="1">
-      <c r="A74" s="23" t="s">
+      <c r="A74" s="24" t="s">
         <v>289</v>
       </c>
-      <c r="B74" s="24">
+      <c r="B74" s="25">
         <v>0.0</v>
       </c>
-      <c r="C74" s="24" t="s">
+      <c r="C74" s="25" t="s">
         <v>290</v>
       </c>
-      <c r="D74" s="24" t="s">
+      <c r="D74" s="25" t="s">
         <v>291</v>
       </c>
-      <c r="E74" s="24" t="s">
+      <c r="E74" s="25" t="s">
         <v>292</v>
       </c>
-      <c r="F74" s="24"/>
-      <c r="G74" s="24"/>
-      <c r="H74" s="24"/>
-      <c r="I74" s="24"/>
-      <c r="J74" s="24"/>
-      <c r="K74" s="24"/>
-      <c r="L74" s="24"/>
-      <c r="M74" s="24"/>
-      <c r="N74" s="24"/>
-      <c r="O74" s="24"/>
-      <c r="P74" s="24"/>
-      <c r="Q74" s="24"/>
-      <c r="R74" s="24"/>
-      <c r="S74" s="24"/>
-      <c r="T74" s="24"/>
-      <c r="U74" s="24"/>
-      <c r="V74" s="24"/>
-      <c r="W74" s="24"/>
-      <c r="X74" s="24"/>
-      <c r="Y74" s="24"/>
+      <c r="F74" s="25"/>
+      <c r="G74" s="25"/>
+      <c r="H74" s="25"/>
+      <c r="I74" s="25"/>
+      <c r="J74" s="25"/>
+      <c r="K74" s="25"/>
+      <c r="L74" s="25"/>
+      <c r="M74" s="25"/>
+      <c r="N74" s="25"/>
+      <c r="O74" s="25"/>
+      <c r="P74" s="25"/>
+      <c r="Q74" s="25"/>
+      <c r="R74" s="25"/>
+      <c r="S74" s="25"/>
+      <c r="T74" s="25"/>
+      <c r="U74" s="25"/>
+      <c r="V74" s="25"/>
+      <c r="W74" s="25"/>
+      <c r="X74" s="25"/>
+      <c r="Y74" s="25"/>
     </row>
     <row r="75" ht="15.0" customHeight="1">
-      <c r="A75" s="23" t="s">
+      <c r="A75" s="24" t="s">
         <v>293</v>
       </c>
-      <c r="B75" s="24">
+      <c r="B75" s="25">
         <v>0.0</v>
       </c>
-      <c r="C75" s="24" t="s">
+      <c r="C75" s="25" t="s">
         <v>294</v>
       </c>
-      <c r="D75" s="24" t="s">
+      <c r="D75" s="25" t="s">
         <v>179</v>
       </c>
-      <c r="E75" s="24" t="s">
+      <c r="E75" s="25" t="s">
         <v>180</v>
       </c>
-      <c r="F75" s="24"/>
-      <c r="G75" s="24"/>
-      <c r="H75" s="24"/>
-      <c r="I75" s="24"/>
-      <c r="J75" s="24"/>
-      <c r="K75" s="24"/>
-      <c r="L75" s="24"/>
-      <c r="M75" s="24"/>
-      <c r="N75" s="24"/>
-      <c r="O75" s="24"/>
-      <c r="P75" s="24"/>
-      <c r="Q75" s="24"/>
-      <c r="R75" s="24"/>
-      <c r="S75" s="24"/>
-      <c r="T75" s="24"/>
-      <c r="U75" s="24"/>
-      <c r="V75" s="24"/>
-      <c r="W75" s="24"/>
-      <c r="X75" s="24"/>
-      <c r="Y75" s="24"/>
+      <c r="F75" s="25"/>
+      <c r="G75" s="25"/>
+      <c r="H75" s="25"/>
+      <c r="I75" s="25"/>
+      <c r="J75" s="25"/>
+      <c r="K75" s="25"/>
+      <c r="L75" s="25"/>
+      <c r="M75" s="25"/>
+      <c r="N75" s="25"/>
+      <c r="O75" s="25"/>
+      <c r="P75" s="25"/>
+      <c r="Q75" s="25"/>
+      <c r="R75" s="25"/>
+      <c r="S75" s="25"/>
+      <c r="T75" s="25"/>
+      <c r="U75" s="25"/>
+      <c r="V75" s="25"/>
+      <c r="W75" s="25"/>
+      <c r="X75" s="25"/>
+      <c r="Y75" s="25"/>
     </row>
     <row r="76" ht="15.0" customHeight="1">
-      <c r="A76" s="23" t="s">
+      <c r="A76" s="24" t="s">
         <v>295</v>
       </c>
-      <c r="B76" s="24">
+      <c r="B76" s="25">
         <v>0.0</v>
       </c>
-      <c r="C76" s="24" t="s">
+      <c r="C76" s="25" t="s">
         <v>296</v>
       </c>
-      <c r="D76" s="24" t="s">
+      <c r="D76" s="25" t="s">
         <v>297</v>
       </c>
-      <c r="E76" s="24" t="s">
+      <c r="E76" s="25" t="s">
         <v>298</v>
       </c>
-      <c r="F76" s="24"/>
-      <c r="G76" s="24"/>
-      <c r="H76" s="24"/>
-      <c r="I76" s="24"/>
-      <c r="J76" s="24"/>
-      <c r="K76" s="24"/>
-      <c r="L76" s="24"/>
-      <c r="M76" s="24"/>
-      <c r="N76" s="24"/>
-      <c r="O76" s="24"/>
-      <c r="P76" s="24"/>
-      <c r="Q76" s="24"/>
-      <c r="R76" s="24"/>
-      <c r="S76" s="24"/>
-      <c r="T76" s="24"/>
-      <c r="U76" s="24"/>
-      <c r="V76" s="24"/>
-      <c r="W76" s="24"/>
-      <c r="X76" s="24"/>
-      <c r="Y76" s="24"/>
+      <c r="F76" s="25"/>
+      <c r="G76" s="25"/>
+      <c r="H76" s="25"/>
+      <c r="I76" s="25"/>
+      <c r="J76" s="25"/>
+      <c r="K76" s="25"/>
+      <c r="L76" s="25"/>
+      <c r="M76" s="25"/>
+      <c r="N76" s="25"/>
+      <c r="O76" s="25"/>
+      <c r="P76" s="25"/>
+      <c r="Q76" s="25"/>
+      <c r="R76" s="25"/>
+      <c r="S76" s="25"/>
+      <c r="T76" s="25"/>
+      <c r="U76" s="25"/>
+      <c r="V76" s="25"/>
+      <c r="W76" s="25"/>
+      <c r="X76" s="25"/>
+      <c r="Y76" s="25"/>
     </row>
     <row r="77" ht="15.0" customHeight="1">
-      <c r="A77" s="23" t="s">
+      <c r="A77" s="24" t="s">
         <v>299</v>
       </c>
-      <c r="B77" s="24">
+      <c r="B77" s="25">
         <v>0.0</v>
       </c>
-      <c r="C77" s="24" t="s">
+      <c r="C77" s="25" t="s">
         <v>300</v>
       </c>
-      <c r="D77" s="24" t="s">
+      <c r="D77" s="25" t="s">
         <v>301</v>
       </c>
-      <c r="E77" s="24" t="s">
+      <c r="E77" s="25" t="s">
         <v>302</v>
       </c>
-      <c r="F77" s="24"/>
-      <c r="G77" s="24"/>
-      <c r="H77" s="24"/>
-      <c r="I77" s="24"/>
-      <c r="J77" s="24"/>
-      <c r="K77" s="24"/>
-      <c r="L77" s="24"/>
-      <c r="M77" s="24"/>
-      <c r="N77" s="24"/>
-      <c r="O77" s="24"/>
-      <c r="P77" s="24"/>
-      <c r="Q77" s="24"/>
-      <c r="R77" s="24"/>
-      <c r="S77" s="24"/>
-      <c r="T77" s="24"/>
-      <c r="U77" s="24"/>
-      <c r="V77" s="24"/>
-      <c r="W77" s="24"/>
-      <c r="X77" s="24"/>
-      <c r="Y77" s="24"/>
+      <c r="F77" s="25"/>
+      <c r="G77" s="25"/>
+      <c r="H77" s="25"/>
+      <c r="I77" s="25"/>
+      <c r="J77" s="25"/>
+      <c r="K77" s="25"/>
+      <c r="L77" s="25"/>
+      <c r="M77" s="25"/>
+      <c r="N77" s="25"/>
+      <c r="O77" s="25"/>
+      <c r="P77" s="25"/>
+      <c r="Q77" s="25"/>
+      <c r="R77" s="25"/>
+      <c r="S77" s="25"/>
+      <c r="T77" s="25"/>
+      <c r="U77" s="25"/>
+      <c r="V77" s="25"/>
+      <c r="W77" s="25"/>
+      <c r="X77" s="25"/>
+      <c r="Y77" s="25"/>
     </row>
     <row r="78" ht="15.0" customHeight="1">
-      <c r="A78" s="23" t="s">
+      <c r="A78" s="24" t="s">
         <v>303</v>
       </c>
-      <c r="B78" s="24">
+      <c r="B78" s="25">
         <v>0.0</v>
       </c>
-      <c r="C78" s="24" t="s">
+      <c r="C78" s="25" t="s">
         <v>304</v>
       </c>
-      <c r="D78" s="24" t="s">
+      <c r="D78" s="25" t="s">
         <v>305</v>
       </c>
-      <c r="E78" s="24" t="s">
+      <c r="E78" s="25" t="s">
         <v>306</v>
       </c>
-      <c r="F78" s="24"/>
-      <c r="G78" s="24"/>
-      <c r="H78" s="24"/>
-      <c r="I78" s="24"/>
-      <c r="J78" s="24"/>
-      <c r="K78" s="24"/>
-      <c r="L78" s="24"/>
-      <c r="M78" s="24"/>
-      <c r="N78" s="24"/>
-      <c r="O78" s="24"/>
-      <c r="P78" s="24"/>
-      <c r="Q78" s="24"/>
-      <c r="R78" s="24"/>
-      <c r="S78" s="24"/>
-      <c r="T78" s="24"/>
-      <c r="U78" s="24"/>
-      <c r="V78" s="24"/>
-      <c r="W78" s="24"/>
-      <c r="X78" s="24"/>
-      <c r="Y78" s="24"/>
+      <c r="F78" s="25"/>
+      <c r="G78" s="25"/>
+      <c r="H78" s="25"/>
+      <c r="I78" s="25"/>
+      <c r="J78" s="25"/>
+      <c r="K78" s="25"/>
+      <c r="L78" s="25"/>
+      <c r="M78" s="25"/>
+      <c r="N78" s="25"/>
+      <c r="O78" s="25"/>
+      <c r="P78" s="25"/>
+      <c r="Q78" s="25"/>
+      <c r="R78" s="25"/>
+      <c r="S78" s="25"/>
+      <c r="T78" s="25"/>
+      <c r="U78" s="25"/>
+      <c r="V78" s="25"/>
+      <c r="W78" s="25"/>
+      <c r="X78" s="25"/>
+      <c r="Y78" s="25"/>
     </row>
     <row r="79" ht="15.0" customHeight="1">
-      <c r="A79" s="23" t="s">
+      <c r="A79" s="24" t="s">
         <v>307</v>
       </c>
-      <c r="B79" s="24">
+      <c r="B79" s="25">
         <v>0.0</v>
       </c>
-      <c r="C79" s="24" t="s">
+      <c r="C79" s="25" t="s">
         <v>308</v>
       </c>
-      <c r="D79" s="24" t="s">
+      <c r="D79" s="25" t="s">
         <v>309</v>
       </c>
-      <c r="E79" s="24" t="s">
+      <c r="E79" s="25" t="s">
         <v>310</v>
       </c>
-      <c r="F79" s="24"/>
-      <c r="G79" s="24"/>
-      <c r="H79" s="24"/>
-      <c r="I79" s="24"/>
-      <c r="J79" s="24"/>
-      <c r="K79" s="24"/>
-      <c r="L79" s="24"/>
-      <c r="M79" s="24"/>
-      <c r="N79" s="24"/>
-      <c r="O79" s="24"/>
-      <c r="P79" s="24"/>
-      <c r="Q79" s="24"/>
-      <c r="R79" s="24"/>
-      <c r="S79" s="24"/>
-      <c r="T79" s="24"/>
-      <c r="U79" s="24"/>
-      <c r="V79" s="24"/>
-      <c r="W79" s="24"/>
-      <c r="X79" s="24"/>
-      <c r="Y79" s="24"/>
+      <c r="F79" s="25"/>
+      <c r="G79" s="25"/>
+      <c r="H79" s="25"/>
+      <c r="I79" s="25"/>
+      <c r="J79" s="25"/>
+      <c r="K79" s="25"/>
+      <c r="L79" s="25"/>
+      <c r="M79" s="25"/>
+      <c r="N79" s="25"/>
+      <c r="O79" s="25"/>
+      <c r="P79" s="25"/>
+      <c r="Q79" s="25"/>
+      <c r="R79" s="25"/>
+      <c r="S79" s="25"/>
+      <c r="T79" s="25"/>
+      <c r="U79" s="25"/>
+      <c r="V79" s="25"/>
+      <c r="W79" s="25"/>
+      <c r="X79" s="25"/>
+      <c r="Y79" s="25"/>
     </row>
     <row r="80" ht="15.0" customHeight="1">
-      <c r="A80" s="25" t="s">
+      <c r="A80" s="26" t="s">
         <v>311</v>
       </c>
-      <c r="B80" s="26">
+      <c r="B80" s="27">
         <v>0.0</v>
       </c>
-      <c r="C80" s="27" t="s">
+      <c r="C80" s="28" t="s">
         <v>312</v>
       </c>
-      <c r="D80" s="27" t="s">
+      <c r="D80" s="28" t="s">
         <v>211</v>
       </c>
-      <c r="E80" s="27" t="s">
+      <c r="E80" s="28" t="s">
         <v>212</v>
       </c>
-      <c r="F80" s="27"/>
-      <c r="G80" s="27"/>
-      <c r="H80" s="27"/>
-      <c r="I80" s="27"/>
-      <c r="J80" s="27"/>
-      <c r="K80" s="27"/>
-      <c r="L80" s="27"/>
-      <c r="M80" s="27"/>
-      <c r="N80" s="27"/>
-      <c r="O80" s="27"/>
-      <c r="P80" s="27"/>
-      <c r="Q80" s="27"/>
-      <c r="R80" s="27"/>
-      <c r="S80" s="27"/>
-      <c r="T80" s="27"/>
-      <c r="U80" s="27"/>
-      <c r="V80" s="27"/>
-      <c r="W80" s="27"/>
-      <c r="X80" s="27"/>
-      <c r="Y80" s="27"/>
+      <c r="F80" s="28"/>
+      <c r="G80" s="28"/>
+      <c r="H80" s="28"/>
+      <c r="I80" s="28"/>
+      <c r="J80" s="28"/>
+      <c r="K80" s="28"/>
+      <c r="L80" s="28"/>
+      <c r="M80" s="28"/>
+      <c r="N80" s="28"/>
+      <c r="O80" s="28"/>
+      <c r="P80" s="28"/>
+      <c r="Q80" s="28"/>
+      <c r="R80" s="28"/>
+      <c r="S80" s="28"/>
+      <c r="T80" s="28"/>
+      <c r="U80" s="28"/>
+      <c r="V80" s="28"/>
+      <c r="W80" s="28"/>
+      <c r="X80" s="28"/>
+      <c r="Y80" s="28"/>
     </row>
     <row r="81" ht="15.0" customHeight="1">
-      <c r="A81" s="25" t="s">
+      <c r="A81" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="B81" s="26">
+      <c r="B81" s="27">
         <v>0.0</v>
       </c>
-      <c r="C81" s="27" t="s">
+      <c r="C81" s="28" t="s">
         <v>314</v>
       </c>
-      <c r="D81" s="27" t="s">
+      <c r="D81" s="28" t="s">
         <v>143</v>
       </c>
-      <c r="E81" s="27" t="s">
+      <c r="E81" s="28" t="s">
         <v>144</v>
       </c>
-      <c r="F81" s="27"/>
-      <c r="G81" s="27"/>
-      <c r="H81" s="27"/>
-      <c r="I81" s="27"/>
-      <c r="J81" s="27"/>
-      <c r="K81" s="27"/>
-      <c r="L81" s="27"/>
-      <c r="M81" s="27"/>
-      <c r="N81" s="27"/>
-      <c r="O81" s="27"/>
-      <c r="P81" s="27"/>
-      <c r="Q81" s="27"/>
-      <c r="R81" s="27"/>
-      <c r="S81" s="27"/>
-      <c r="T81" s="27"/>
-      <c r="U81" s="27"/>
-      <c r="V81" s="27"/>
-      <c r="W81" s="27"/>
-      <c r="X81" s="27"/>
-      <c r="Y81" s="27"/>
+      <c r="F81" s="28"/>
+      <c r="G81" s="28"/>
+      <c r="H81" s="28"/>
+      <c r="I81" s="28"/>
+      <c r="J81" s="28"/>
+      <c r="K81" s="28"/>
+      <c r="L81" s="28"/>
+      <c r="M81" s="28"/>
+      <c r="N81" s="28"/>
+      <c r="O81" s="28"/>
+      <c r="P81" s="28"/>
+      <c r="Q81" s="28"/>
+      <c r="R81" s="28"/>
+      <c r="S81" s="28"/>
+      <c r="T81" s="28"/>
+      <c r="U81" s="28"/>
+      <c r="V81" s="28"/>
+      <c r="W81" s="28"/>
+      <c r="X81" s="28"/>
+      <c r="Y81" s="28"/>
     </row>
     <row r="82" ht="15.0" customHeight="1">
-      <c r="A82" s="25" t="s">
+      <c r="A82" s="26" t="s">
         <v>315</v>
       </c>
-      <c r="B82" s="26">
+      <c r="B82" s="27">
         <v>0.0</v>
       </c>
-      <c r="C82" s="27" t="s">
+      <c r="C82" s="28" t="s">
         <v>316</v>
       </c>
-      <c r="D82" s="27" t="s">
+      <c r="D82" s="28" t="s">
         <v>317</v>
       </c>
-      <c r="E82" s="27" t="s">
+      <c r="E82" s="28" t="s">
         <v>318</v>
       </c>
-      <c r="F82" s="27"/>
-      <c r="G82" s="27"/>
-      <c r="H82" s="27"/>
-      <c r="I82" s="27"/>
-      <c r="J82" s="27"/>
-      <c r="K82" s="27"/>
-      <c r="L82" s="27"/>
-      <c r="M82" s="27"/>
-      <c r="N82" s="27"/>
-      <c r="O82" s="27"/>
-      <c r="P82" s="27"/>
-      <c r="Q82" s="27"/>
-      <c r="R82" s="27"/>
-      <c r="S82" s="27"/>
-      <c r="T82" s="27"/>
-      <c r="U82" s="27"/>
-      <c r="V82" s="27"/>
-      <c r="W82" s="27"/>
-      <c r="X82" s="27"/>
-      <c r="Y82" s="27"/>
+      <c r="F82" s="28"/>
+      <c r="G82" s="28"/>
+      <c r="H82" s="28"/>
+      <c r="I82" s="28"/>
+      <c r="J82" s="28"/>
+      <c r="K82" s="28"/>
+      <c r="L82" s="28"/>
+      <c r="M82" s="28"/>
+      <c r="N82" s="28"/>
+      <c r="O82" s="28"/>
+      <c r="P82" s="28"/>
+      <c r="Q82" s="28"/>
+      <c r="R82" s="28"/>
+      <c r="S82" s="28"/>
+      <c r="T82" s="28"/>
+      <c r="U82" s="28"/>
+      <c r="V82" s="28"/>
+      <c r="W82" s="28"/>
+      <c r="X82" s="28"/>
+      <c r="Y82" s="28"/>
     </row>
     <row r="83" ht="15.0" customHeight="1">
-      <c r="A83" s="28" t="s">
+      <c r="A83" s="29" t="s">
         <v>319</v>
       </c>
-      <c r="B83" s="29">
+      <c r="B83" s="30">
         <v>0.0</v>
       </c>
-      <c r="C83" s="30" t="s">
+      <c r="C83" s="31" t="s">
         <v>320</v>
       </c>
-      <c r="D83" s="30" t="s">
+      <c r="D83" s="31" t="s">
         <v>321</v>
       </c>
-      <c r="E83" s="30" t="s">
+      <c r="E83" s="31" t="s">
         <v>322</v>
       </c>
-      <c r="F83" s="30"/>
-      <c r="G83" s="30"/>
-      <c r="H83" s="30"/>
-      <c r="I83" s="30"/>
-      <c r="J83" s="30"/>
-      <c r="K83" s="30"/>
-      <c r="L83" s="30"/>
-      <c r="M83" s="30"/>
-      <c r="N83" s="30"/>
-      <c r="O83" s="30"/>
-      <c r="P83" s="30"/>
-      <c r="Q83" s="30"/>
-      <c r="R83" s="30"/>
-      <c r="S83" s="30"/>
-      <c r="T83" s="30"/>
-      <c r="U83" s="30"/>
-      <c r="V83" s="30"/>
-      <c r="W83" s="30"/>
-      <c r="X83" s="30"/>
-      <c r="Y83" s="30"/>
+      <c r="F83" s="31"/>
+      <c r="G83" s="31"/>
+      <c r="H83" s="31"/>
+      <c r="I83" s="31"/>
+      <c r="J83" s="31"/>
+      <c r="K83" s="31"/>
+      <c r="L83" s="31"/>
+      <c r="M83" s="31"/>
+      <c r="N83" s="31"/>
+      <c r="O83" s="31"/>
+      <c r="P83" s="31"/>
+      <c r="Q83" s="31"/>
+      <c r="R83" s="31"/>
+      <c r="S83" s="31"/>
+      <c r="T83" s="31"/>
+      <c r="U83" s="31"/>
+      <c r="V83" s="31"/>
+      <c r="W83" s="31"/>
+      <c r="X83" s="31"/>
+      <c r="Y83" s="31"/>
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="1"/>

--- a/Templates/Tables/StringInfo/StrTable.xlsx
+++ b/Templates/Tables/StringInfo/StrTable.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="319">
   <si>
     <t>Description</t>
   </si>
@@ -259,7 +259,7 @@
     <t>공용 로그인 성공 메세지</t>
   </si>
   <si>
-    <t>COMMON_LOGIN_SUCCESS_MSG</t>
+    <t>C_LOGIN_SUCCESS_MSG</t>
   </si>
   <si>
     <t>로그인했습니다</t>
@@ -271,7 +271,7 @@
     <t>공용 로그인 실패 메세지</t>
   </si>
   <si>
-    <t>COMMON_LOGIN_FAIL_MSG</t>
+    <t>C_LOGIN_FAIL_MSG</t>
   </si>
   <si>
     <t>로그인에 실패했습니다</t>
@@ -283,7 +283,7 @@
     <t>공용 로그아웃 성공 메세지</t>
   </si>
   <si>
-    <t>COMMON_LOGOUT_SUCCESS_MSG</t>
+    <t>C_LOGOUT_SUCCESS_MSG</t>
   </si>
   <si>
     <t>로그아웃했습니다</t>
@@ -295,7 +295,7 @@
     <t>공용 로그아웃 실패 메세지</t>
   </si>
   <si>
-    <t>COMMON_LOGOUT_FAIL_MSG</t>
+    <t>C_LOGOUT_FAIL_MSG</t>
   </si>
   <si>
     <t>로그아웃에 실패했습니다</t>
@@ -307,7 +307,7 @@
     <t>공용 로드 성공 메세지</t>
   </si>
   <si>
-    <t>COMMON_LOAD_SUCCESS_MSG</t>
+    <t>C_LOAD_SUCCESS_MSG</t>
   </si>
   <si>
     <t>진행 상황을 로드했습니다</t>
@@ -319,7 +319,7 @@
     <t>공용 로드 실패 메세지</t>
   </si>
   <si>
-    <t>COMMON_LOAD_FAIL_MSG</t>
+    <t>C_LOAD_FAIL_MSG</t>
   </si>
   <si>
     <t>진행 상황 로드에 실패했습니다</t>
@@ -331,7 +331,7 @@
     <t>공용 저장 성공 메세지</t>
   </si>
   <si>
-    <t>COMMON_SAVE_SUCCESS_MSG</t>
+    <t>C_SAVE_SUCCESS_MSG</t>
   </si>
   <si>
     <t>진행 상황을 저장했습니다</t>
@@ -343,7 +343,7 @@
     <t>공용 저장 실패 메세지</t>
   </si>
   <si>
-    <t>COMMON_SAVE_FAIL_MSG</t>
+    <t>C_SAVE_FAIL_MSG</t>
   </si>
   <si>
     <t>진행 상황 저장에 실패했습니다</t>
@@ -355,7 +355,7 @@
     <t>공용 결제 성공 메세지</t>
   </si>
   <si>
-    <t>COMMON_PURCHASE_SUCCESS_MSG</t>
+    <t>C_PURCHASE_SUCCESS_MSG</t>
   </si>
   <si>
     <t>해당 상품을 구입했습니다</t>
@@ -367,7 +367,7 @@
     <t>공용 결제 실패 메세지</t>
   </si>
   <si>
-    <t>COMMON_PURCHASE_FAIL_MSG</t>
+    <t>C_PURCHASE_FAIL_MSG</t>
   </si>
   <si>
     <t>해당 상품 구입에 실패했습니다</t>
@@ -379,7 +379,7 @@
     <t>공용 복원 성공 메세지</t>
   </si>
   <si>
-    <t>COMMON_RESTORE_SUCCESS_MSG</t>
+    <t>C_RESTORE_SUCCESS_MSG</t>
   </si>
   <si>
     <t>상품을 복원했습니다</t>
@@ -391,7 +391,7 @@
     <t>공용 복원 실패 메세지</t>
   </si>
   <si>
-    <t>COMMON_RESTORE_FAIL_MSG</t>
+    <t>C_RESTORE_FAIL_MSG</t>
   </si>
   <si>
     <t>상품 복원에 실패했습니다</t>
@@ -403,7 +403,7 @@
     <t>공용 확인 텍스트</t>
   </si>
   <si>
-    <t>COMMON_OK_TEXT</t>
+    <t>C_OK_TEXT</t>
   </si>
   <si>
     <t>확인</t>
@@ -415,7 +415,7 @@
     <t>공용 취소 텍스트</t>
   </si>
   <si>
-    <t>COMMON_CANCEL_TEXT</t>
+    <t>C_CANCEL_TEXT</t>
   </si>
   <si>
     <t>취소</t>
@@ -427,7 +427,7 @@
     <t>공용 동의 텍스트</t>
   </si>
   <si>
-    <t>COMMON_AGREE_TEXT</t>
+    <t>C_AGREE_TEXT</t>
   </si>
   <si>
     <t>동의</t>
@@ -439,7 +439,7 @@
     <t>공용 결과 텍스트</t>
   </si>
   <si>
-    <t>COMMON_RESULT_TEXT</t>
+    <t>C_RESULT_TEXT</t>
   </si>
   <si>
     <t>결과</t>
@@ -451,7 +451,7 @@
     <t>공용 획득 텍스트</t>
   </si>
   <si>
-    <t>COMMON_GET_TEXT</t>
+    <t>C_GET_TEXT</t>
   </si>
   <si>
     <t>획득</t>
@@ -463,7 +463,7 @@
     <t>공용 상점 텍스트</t>
   </si>
   <si>
-    <t>COMMON_STORE_TEXT</t>
+    <t>C_STORE_TEXT</t>
   </si>
   <si>
     <t>상점</t>
@@ -475,7 +475,7 @@
     <t>공용 이벤트 텍스트</t>
   </si>
   <si>
-    <t>COMMON_EVENT_TEXT</t>
+    <t>C_EVENT_TEXT</t>
   </si>
   <si>
     <t>이벤트</t>
@@ -487,7 +487,7 @@
     <t>공용 다음 텍스트</t>
   </si>
   <si>
-    <t>COMMON_NEXT_TEXT</t>
+    <t>C_NEXT_TEXT</t>
   </si>
   <si>
     <t>다음</t>
@@ -499,7 +499,7 @@
     <t>공용 홈 텍스트</t>
   </si>
   <si>
-    <t>COMMON_HOME_TEXT</t>
+    <t>C_HOME_TEXT</t>
   </si>
   <si>
     <t>홈</t>
@@ -511,7 +511,7 @@
     <t>공용 플레이 텍스트</t>
   </si>
   <si>
-    <t>COMMON_PLAY_TEXT</t>
+    <t>C_PLAY_TEXT</t>
   </si>
   <si>
     <t>플레이</t>
@@ -523,7 +523,7 @@
     <t>공용 재시도 텍스트</t>
   </si>
   <si>
-    <t>COMMON_RETRY_TEXT</t>
+    <t>C_RETRY_TEXT</t>
   </si>
   <si>
     <t>재시도</t>
@@ -535,7 +535,7 @@
     <t>공용 나가기 텍스트</t>
   </si>
   <si>
-    <t>COMMON_LEAVE_TEXT</t>
+    <t>C_LEAVE_TEXT</t>
   </si>
   <si>
     <t>나가기</t>
@@ -547,7 +547,7 @@
     <t>공용 동기화 텍스트</t>
   </si>
   <si>
-    <t>COMMON_SYNC_TEXT</t>
+    <t>C_SYNC_TEXT</t>
   </si>
   <si>
     <t>동기화</t>
@@ -559,7 +559,7 @@
     <t>공용 로그인 텍스트</t>
   </si>
   <si>
-    <t>COMMON_LOGIN_TEXT</t>
+    <t>C_LOGIN_TEXT</t>
   </si>
   <si>
     <t>로그인</t>
@@ -571,7 +571,7 @@
     <t>공용 애플 로그인 텍스트</t>
   </si>
   <si>
-    <t>COMMON_APPLE_LOGIN_TEXT</t>
+    <t>C_APPLE_LOGIN_TEXT</t>
   </si>
   <si>
     <t>애플 로그인</t>
@@ -583,7 +583,7 @@
     <t>공용 페이스 북 로그인</t>
   </si>
   <si>
-    <t>COMMON_FACEBOOK_LOGIN_TEXT</t>
+    <t>C_FACEBOOK_LOGIN_TEXT</t>
   </si>
   <si>
     <t>페이스 북 로그인</t>
@@ -595,7 +595,7 @@
     <t>공용 로그아웃 텍스트</t>
   </si>
   <si>
-    <t>COMMON_LOGOUT_TEXT</t>
+    <t>C_LOGOUT_TEXT</t>
   </si>
   <si>
     <t>로그아웃</t>
@@ -607,7 +607,7 @@
     <t>공용 연결 해제 텍스트</t>
   </si>
   <si>
-    <t>COMMON_DISCONNECT_TEXT</t>
+    <t>C_DISCONNECT_TEXT</t>
   </si>
   <si>
     <t>연결 해제</t>
@@ -619,7 +619,7 @@
     <t>공용 로드 텍스트</t>
   </si>
   <si>
-    <t>COMMON_LOAD_TEXT</t>
+    <t>C_LOAD_TEXT</t>
   </si>
   <si>
     <t>불러오기</t>
@@ -631,7 +631,7 @@
     <t>공용 저장 텍스트</t>
   </si>
   <si>
-    <t>COMMON_SAVE_TEXT</t>
+    <t>C_SAVE_TEXT</t>
   </si>
   <si>
     <t>저장하기</t>
@@ -643,7 +643,7 @@
     <t>공용 이어하기 텍스트</t>
   </si>
   <si>
-    <t>COMMON_CONTINUE_TEXT</t>
+    <t>C_CONTINUE_TEXT</t>
   </si>
   <si>
     <t>이어하기</t>
@@ -655,13 +655,13 @@
     <t>공용 알림 텍스트</t>
   </si>
   <si>
-    <t>COMMON_NOTI_TEXT</t>
+    <t>C_NOTI_TEXT</t>
   </si>
   <si>
     <t>공용 평가 텍스트</t>
   </si>
   <si>
-    <t>COMMON_REVIEW_TEXT</t>
+    <t>C_REVIEW_TEXT</t>
   </si>
   <si>
     <t>평가</t>
@@ -673,7 +673,7 @@
     <t>공용 지원 텍스트</t>
   </si>
   <si>
-    <t>COMMON_SUPPORTS_TEXT</t>
+    <t>C_SUPPORTS_TEXT</t>
   </si>
   <si>
     <t>문의</t>
@@ -685,7 +685,7 @@
     <t>공용 배경음 텍스트</t>
   </si>
   <si>
-    <t>COMMON_BG_SND_TEXT</t>
+    <t>C_BG_SND_TEXT</t>
   </si>
   <si>
     <t>배경음</t>
@@ -697,7 +697,7 @@
     <t>공용 효과음 텍스트</t>
   </si>
   <si>
-    <t>COMMON_FX_SNDS_TEXT</t>
+    <t>C_FX_SNDS_TEXT</t>
   </si>
   <si>
     <t>효과음</t>
@@ -709,7 +709,7 @@
     <t>공용 광고 시청 텍스트</t>
   </si>
   <si>
-    <t>COMMON_WATCH_ADS_TEXT</t>
+    <t>C_WATCH_ADS_TEXT</t>
   </si>
   <si>
     <t>광고 시청</t>
@@ -718,10 +718,22 @@
     <t>Watch Ads</t>
   </si>
   <si>
+    <t>공용 광고 제거 텍스트</t>
+  </si>
+  <si>
+    <t>C_REMOVE_ADS_TEXT</t>
+  </si>
+  <si>
+    <t>광고 제거</t>
+  </si>
+  <si>
+    <t>Remove Ads</t>
+  </si>
+  <si>
     <t>공용 결제 복원 텍스트</t>
   </si>
   <si>
-    <t>COMMON_RESTORE_PAYMENT_TEXT</t>
+    <t>C_RESTORE_PAYMENT_TEXT</t>
   </si>
   <si>
     <t>결제 복원</t>
@@ -733,7 +745,7 @@
     <t>공용 레벨 텍스트</t>
   </si>
   <si>
-    <t>COMMON_LEVEL_TEXT</t>
+    <t>C_LEVEL_TEXT</t>
   </si>
   <si>
     <t>레벨</t>
@@ -745,7 +757,7 @@
     <t>공용 스테이지 텍스트</t>
   </si>
   <si>
-    <t>COMMON_STAGE_TEXT</t>
+    <t>C_STAGE_TEXT</t>
   </si>
   <si>
     <t>스테이지</t>
@@ -757,7 +769,7 @@
     <t>공용 챕터 텍스트</t>
   </si>
   <si>
-    <t>COMMON_CHAPTER_TEXT</t>
+    <t>C_CHAPTER_TEXT</t>
   </si>
   <si>
     <t>챕터</t>
@@ -766,10 +778,94 @@
     <t>Chapter</t>
   </si>
   <si>
+    <t>공용 설정 텍스트</t>
+  </si>
+  <si>
+    <t>C_SETTINGS_TEXT</t>
+  </si>
+  <si>
+    <t>설정</t>
+  </si>
+  <si>
+    <t>Settings</t>
+  </si>
+  <si>
+    <t>공용 일일 미션 텍스트</t>
+  </si>
+  <si>
+    <t>C_DAILY_MISSION_TEXT</t>
+  </si>
+  <si>
+    <t>일일 미션</t>
+  </si>
+  <si>
+    <t>Daily Mission</t>
+  </si>
+  <si>
+    <t>공용 무료 보상 텍스트</t>
+  </si>
+  <si>
+    <t>C_FREE_REWARD_TEXT</t>
+  </si>
+  <si>
+    <t>무료 보상</t>
+  </si>
+  <si>
+    <t>Free Reward</t>
+  </si>
+  <si>
+    <t>공용 일일 보상 텍스트</t>
+  </si>
+  <si>
+    <t>C_DAILY_REWARD_TEXT</t>
+  </si>
+  <si>
+    <t>일일 보상</t>
+  </si>
+  <si>
+    <t>Daily Reward</t>
+  </si>
+  <si>
+    <t>공용 코인 상자 텍스트</t>
+  </si>
+  <si>
+    <t>C_COINS_BOX_TEXT</t>
+  </si>
+  <si>
+    <t>코인 상자</t>
+  </si>
+  <si>
+    <t>Coins Box</t>
+  </si>
+  <si>
+    <t>공용 재개 텍스트</t>
+  </si>
+  <si>
+    <t>C_RESUME_TEXT</t>
+  </si>
+  <si>
+    <t>다시하기</t>
+  </si>
+  <si>
+    <t>Resume</t>
+  </si>
+  <si>
+    <t>공용 정지 텍스트</t>
+  </si>
+  <si>
+    <t>C_PAUSE_TEXT</t>
+  </si>
+  <si>
+    <t>일시정지</t>
+  </si>
+  <si>
+    <t>Pause</t>
+  </si>
+  <si>
     <t>공용 초보자 패키지 텍스트</t>
   </si>
   <si>
-    <t>COMMON_BEGINNER_PKGS_TEXT</t>
+    <t>C_BEGINNER_PKGS_TEXT</t>
   </si>
   <si>
     <t>초보자 패키지</t>
@@ -781,7 +877,7 @@
     <t>공용 숙련자 패키지 텍스트</t>
   </si>
   <si>
-    <t>COMMON_EXPERT_PKGS_TEXT</t>
+    <t>C_EXPERT_PKGS_TEXT</t>
   </si>
   <si>
     <t>전문가 패키지</t>
@@ -793,7 +889,7 @@
     <t>공용 프로 패키지 텍스트</t>
   </si>
   <si>
-    <t>COMMON_PRO_PKGS_TEXT</t>
+    <t>C_PRO_PKGS_TEXT</t>
   </si>
   <si>
     <t>프로 패키지</t>
@@ -805,7 +901,7 @@
     <t>공용 레벨 번호 텍스트 형식</t>
   </si>
   <si>
-    <t>COMMON_LEVEL_NUM_TEXT_FMT</t>
+    <t>C_LEVEL_NUM_TEXT_FMT</t>
   </si>
   <si>
     <t>레벨 {0}</t>
@@ -817,7 +913,7 @@
     <t>공용 스테이지 번호 텍스트 형식</t>
   </si>
   <si>
-    <t>COMMON_STAGE_NUM_TEXT_FMT</t>
+    <t>C_STAGE_NUM_TEXT_FMT</t>
   </si>
   <si>
     <t>스테이지 {0}</t>
@@ -829,7 +925,7 @@
     <t>공용 챕터 번호 텍스트 형식</t>
   </si>
   <si>
-    <t>COMMON_CHAPTER_NUM_TEXT_FMT</t>
+    <t>C_CHAPTER_NUM_TEXT_FMT</t>
   </si>
   <si>
     <t>챕터 {0}</t>
@@ -841,7 +937,7 @@
     <t>공용 레벨 페이지 텍스트 형식</t>
   </si>
   <si>
-    <t>COMMON_LEVEL_PAGE_TEXT_FMT</t>
+    <t>C_LEVEL_PAGE_TEXT_FMT</t>
   </si>
   <si>
     <t>레벨 {0}/{1}</t>
@@ -853,7 +949,7 @@
     <t>공용 스테이지 페이지 텍스트 형식</t>
   </si>
   <si>
-    <t>COMMON_STAGE_PAGE_TEXT_FMT</t>
+    <t>C_STAGE_PAGE_TEXT_FMT</t>
   </si>
   <si>
     <t>스테이지 {0}/{1}</t>
@@ -865,121 +961,13 @@
     <t>공용 챕터 페이지 텍스트 형식</t>
   </si>
   <si>
-    <t>COMMON_CHAPTER_PAGE_TEXT_FMT</t>
+    <t>C_CHAPTER_PAGE_TEXT_FMT</t>
   </si>
   <si>
     <t>챕터 {0}/{1}</t>
   </si>
   <si>
     <t>Chapter {0}/{1}</t>
-  </si>
-  <si>
-    <t>상점 팝업 제목</t>
-  </si>
-  <si>
-    <t>STORE_P_TITLE</t>
-  </si>
-  <si>
-    <t>설정 팝업 제목</t>
-  </si>
-  <si>
-    <t>SETTINGS_P_TITLE</t>
-  </si>
-  <si>
-    <t>설정</t>
-  </si>
-  <si>
-    <t>Settings</t>
-  </si>
-  <si>
-    <t>동기화 팝업 제목</t>
-  </si>
-  <si>
-    <t>SYNC_P_TITLE</t>
-  </si>
-  <si>
-    <t>일일 미션 팝업 제목</t>
-  </si>
-  <si>
-    <t>DAILY_MP_TITLE</t>
-  </si>
-  <si>
-    <t>일일 미션</t>
-  </si>
-  <si>
-    <t>Daily Mission</t>
-  </si>
-  <si>
-    <t>무료 보상 팝업 제목</t>
-  </si>
-  <si>
-    <t>FREE_RP_TITLE</t>
-  </si>
-  <si>
-    <t>무료 보상</t>
-  </si>
-  <si>
-    <t>Free Reward</t>
-  </si>
-  <si>
-    <t>일일 보상 팝업 제목</t>
-  </si>
-  <si>
-    <t>DAILY_RP_TITLE</t>
-  </si>
-  <si>
-    <t>일일 보상</t>
-  </si>
-  <si>
-    <t>Daily Reward</t>
-  </si>
-  <si>
-    <t>판매 코인 팝업 제목</t>
-  </si>
-  <si>
-    <t>SALE_CP_TITLE</t>
-  </si>
-  <si>
-    <t>코인 상자</t>
-  </si>
-  <si>
-    <t>Coins Box</t>
-  </si>
-  <si>
-    <t>이어하기 팝업 제목</t>
-  </si>
-  <si>
-    <t>CONTINUE_P_TITLE</t>
-  </si>
-  <si>
-    <t>결과 팝업 제목</t>
-  </si>
-  <si>
-    <t>RESULT_P_TITLE</t>
-  </si>
-  <si>
-    <t>재개 팝업 제목</t>
-  </si>
-  <si>
-    <t>RESUME_P_TITLE</t>
-  </si>
-  <si>
-    <t>다시하기</t>
-  </si>
-  <si>
-    <t>Resume</t>
-  </si>
-  <si>
-    <t>정지 팝업 제목</t>
-  </si>
-  <si>
-    <t>PAUSE_P_TITLE</t>
-  </si>
-  <si>
-    <t>일시정지</t>
-  </si>
-  <si>
-    <t>Pause</t>
   </si>
 </sst>
 </file>
@@ -1021,7 +1009,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="9">
     <border/>
     <border>
       <left style="thin">
@@ -1037,9 +1025,22 @@
       </top>
     </border>
     <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
     </border>
     <border>
       <left style="thin">
@@ -1054,11 +1055,19 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="24">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1073,7 +1082,8 @@
     <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="3" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1082,7 +1092,8 @@
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="3" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1094,19 +1105,29 @@
     <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="3" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="6" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="5" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="5" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="7" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="8" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1402,691 +1423,691 @@
       <c r="W2" s="5"/>
       <c r="X2" s="5"/>
       <c r="Y2" s="5"/>
-      <c r="Z2" s="2"/>
+      <c r="Z2" s="6"/>
     </row>
     <row r="3" ht="15.0" customHeight="1">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="8">
         <v>0.0</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8"/>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="8"/>
-      <c r="S3" s="8"/>
-      <c r="T3" s="8"/>
-      <c r="U3" s="8"/>
-      <c r="V3" s="8"/>
-      <c r="W3" s="8"/>
-      <c r="X3" s="8"/>
-      <c r="Y3" s="8"/>
-      <c r="Z3" s="2"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
+      <c r="V3" s="9"/>
+      <c r="W3" s="9"/>
+      <c r="X3" s="9"/>
+      <c r="Y3" s="9"/>
+      <c r="Z3" s="10"/>
     </row>
     <row r="4" ht="15.0" customHeight="1">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="8">
         <v>0.0</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="8"/>
-      <c r="Q4" s="8"/>
-      <c r="R4" s="8"/>
-      <c r="S4" s="8"/>
-      <c r="T4" s="8"/>
-      <c r="U4" s="8"/>
-      <c r="V4" s="8"/>
-      <c r="W4" s="8"/>
-      <c r="X4" s="8"/>
-      <c r="Y4" s="8"/>
-      <c r="Z4" s="2"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
+      <c r="V4" s="9"/>
+      <c r="W4" s="9"/>
+      <c r="X4" s="9"/>
+      <c r="Y4" s="9"/>
+      <c r="Z4" s="10"/>
     </row>
     <row r="5" ht="15.0" customHeight="1">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="8">
         <v>0.0</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8"/>
-      <c r="N5" s="8"/>
-      <c r="O5" s="8"/>
-      <c r="P5" s="8"/>
-      <c r="Q5" s="8"/>
-      <c r="R5" s="8"/>
-      <c r="S5" s="8"/>
-      <c r="T5" s="8"/>
-      <c r="U5" s="8"/>
-      <c r="V5" s="8"/>
-      <c r="W5" s="8"/>
-      <c r="X5" s="8"/>
-      <c r="Y5" s="8"/>
-      <c r="Z5" s="2"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="9"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="9"/>
+      <c r="W5" s="9"/>
+      <c r="X5" s="9"/>
+      <c r="Y5" s="9"/>
+      <c r="Z5" s="10"/>
     </row>
     <row r="6" ht="15.0" customHeight="1">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="8">
         <v>0.0</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="8"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="8"/>
-      <c r="U6" s="8"/>
-      <c r="V6" s="8"/>
-      <c r="W6" s="8"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="8"/>
-      <c r="Z6" s="2"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="9"/>
+      <c r="R6" s="9"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="9"/>
+      <c r="U6" s="9"/>
+      <c r="V6" s="9"/>
+      <c r="W6" s="9"/>
+      <c r="X6" s="9"/>
+      <c r="Y6" s="9"/>
+      <c r="Z6" s="10"/>
     </row>
     <row r="7" ht="15.0" customHeight="1">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="8">
         <v>0.0</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="8"/>
-      <c r="S7" s="8"/>
-      <c r="T7" s="8"/>
-      <c r="U7" s="8"/>
-      <c r="V7" s="8"/>
-      <c r="W7" s="8"/>
-      <c r="X7" s="8"/>
-      <c r="Y7" s="8"/>
-      <c r="Z7" s="2"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="9"/>
+      <c r="S7" s="9"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="9"/>
+      <c r="V7" s="9"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="9"/>
+      <c r="Y7" s="9"/>
+      <c r="Z7" s="10"/>
     </row>
     <row r="8" ht="15.0" customHeight="1">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="8">
         <v>0.0</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="8"/>
-      <c r="R8" s="8"/>
-      <c r="S8" s="8"/>
-      <c r="T8" s="8"/>
-      <c r="U8" s="8"/>
-      <c r="V8" s="8"/>
-      <c r="W8" s="8"/>
-      <c r="X8" s="8"/>
-      <c r="Y8" s="8"/>
-      <c r="Z8" s="2"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="9"/>
+      <c r="R8" s="9"/>
+      <c r="S8" s="9"/>
+      <c r="T8" s="9"/>
+      <c r="U8" s="9"/>
+      <c r="V8" s="9"/>
+      <c r="W8" s="9"/>
+      <c r="X8" s="9"/>
+      <c r="Y8" s="9"/>
+      <c r="Z8" s="10"/>
     </row>
     <row r="9" ht="15.0" customHeight="1">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="8">
         <v>0.0</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="8"/>
-      <c r="S9" s="8"/>
-      <c r="T9" s="8"/>
-      <c r="U9" s="8"/>
-      <c r="V9" s="8"/>
-      <c r="W9" s="8"/>
-      <c r="X9" s="8"/>
-      <c r="Y9" s="8"/>
-      <c r="Z9" s="2"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="9"/>
+      <c r="R9" s="9"/>
+      <c r="S9" s="9"/>
+      <c r="T9" s="9"/>
+      <c r="U9" s="9"/>
+      <c r="V9" s="9"/>
+      <c r="W9" s="9"/>
+      <c r="X9" s="9"/>
+      <c r="Y9" s="9"/>
+      <c r="Z9" s="10"/>
     </row>
     <row r="10" ht="15.0" customHeight="1">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="12">
         <v>0.0</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="8"/>
-      <c r="P10" s="8"/>
-      <c r="Q10" s="8"/>
-      <c r="R10" s="8"/>
-      <c r="S10" s="8"/>
-      <c r="T10" s="8"/>
-      <c r="U10" s="8"/>
-      <c r="V10" s="8"/>
-      <c r="W10" s="8"/>
-      <c r="X10" s="8"/>
-      <c r="Y10" s="8"/>
-      <c r="Z10" s="2"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="9"/>
+      <c r="O10" s="9"/>
+      <c r="P10" s="9"/>
+      <c r="Q10" s="9"/>
+      <c r="R10" s="9"/>
+      <c r="S10" s="9"/>
+      <c r="T10" s="9"/>
+      <c r="U10" s="9"/>
+      <c r="V10" s="9"/>
+      <c r="W10" s="9"/>
+      <c r="X10" s="9"/>
+      <c r="Y10" s="9"/>
+      <c r="Z10" s="10"/>
     </row>
     <row r="11" ht="15.0" customHeight="1">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="8">
         <v>0.0</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
-      <c r="N11" s="8"/>
-      <c r="O11" s="8"/>
-      <c r="P11" s="8"/>
-      <c r="Q11" s="8"/>
-      <c r="R11" s="8"/>
-      <c r="S11" s="8"/>
-      <c r="T11" s="8"/>
-      <c r="U11" s="8"/>
-      <c r="V11" s="8"/>
-      <c r="W11" s="8"/>
-      <c r="X11" s="8"/>
-      <c r="Y11" s="8"/>
-      <c r="Z11" s="2"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="9"/>
+      <c r="P11" s="9"/>
+      <c r="Q11" s="9"/>
+      <c r="R11" s="9"/>
+      <c r="S11" s="9"/>
+      <c r="T11" s="9"/>
+      <c r="U11" s="9"/>
+      <c r="V11" s="9"/>
+      <c r="W11" s="9"/>
+      <c r="X11" s="9"/>
+      <c r="Y11" s="9"/>
+      <c r="Z11" s="10"/>
     </row>
     <row r="12" ht="15.0" customHeight="1">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="8">
         <v>0.0</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="8"/>
-      <c r="Q12" s="8"/>
-      <c r="R12" s="8"/>
-      <c r="S12" s="8"/>
-      <c r="T12" s="8"/>
-      <c r="U12" s="8"/>
-      <c r="V12" s="8"/>
-      <c r="W12" s="8"/>
-      <c r="X12" s="8"/>
-      <c r="Y12" s="8"/>
-      <c r="Z12" s="2"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="9"/>
+      <c r="P12" s="9"/>
+      <c r="Q12" s="9"/>
+      <c r="R12" s="9"/>
+      <c r="S12" s="9"/>
+      <c r="T12" s="9"/>
+      <c r="U12" s="9"/>
+      <c r="V12" s="9"/>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="10"/>
     </row>
     <row r="13" ht="15.0" customHeight="1">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="8">
         <v>0.0</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="8"/>
-      <c r="N13" s="8"/>
-      <c r="O13" s="8"/>
-      <c r="P13" s="8"/>
-      <c r="Q13" s="8"/>
-      <c r="R13" s="8"/>
-      <c r="S13" s="8"/>
-      <c r="T13" s="8"/>
-      <c r="U13" s="8"/>
-      <c r="V13" s="8"/>
-      <c r="W13" s="8"/>
-      <c r="X13" s="8"/>
-      <c r="Y13" s="8"/>
-      <c r="Z13" s="2"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="9"/>
+      <c r="P13" s="9"/>
+      <c r="Q13" s="9"/>
+      <c r="R13" s="9"/>
+      <c r="S13" s="9"/>
+      <c r="T13" s="9"/>
+      <c r="U13" s="9"/>
+      <c r="V13" s="9"/>
+      <c r="W13" s="9"/>
+      <c r="X13" s="9"/>
+      <c r="Y13" s="9"/>
+      <c r="Z13" s="10"/>
     </row>
     <row r="14" ht="15.0" customHeight="1">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="8">
         <v>0.0</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8"/>
-      <c r="O14" s="8"/>
-      <c r="P14" s="8"/>
-      <c r="Q14" s="8"/>
-      <c r="R14" s="8"/>
-      <c r="S14" s="8"/>
-      <c r="T14" s="8"/>
-      <c r="U14" s="8"/>
-      <c r="V14" s="8"/>
-      <c r="W14" s="8"/>
-      <c r="X14" s="8"/>
-      <c r="Y14" s="8"/>
-      <c r="Z14" s="2"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
+      <c r="P14" s="9"/>
+      <c r="Q14" s="9"/>
+      <c r="R14" s="9"/>
+      <c r="S14" s="9"/>
+      <c r="T14" s="9"/>
+      <c r="U14" s="9"/>
+      <c r="V14" s="9"/>
+      <c r="W14" s="9"/>
+      <c r="X14" s="9"/>
+      <c r="Y14" s="9"/>
+      <c r="Z14" s="10"/>
     </row>
     <row r="15" ht="15.0" customHeight="1">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="8">
         <v>0.0</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
-      <c r="N15" s="8"/>
-      <c r="O15" s="8"/>
-      <c r="P15" s="8"/>
-      <c r="Q15" s="8"/>
-      <c r="R15" s="8"/>
-      <c r="S15" s="8"/>
-      <c r="T15" s="8"/>
-      <c r="U15" s="8"/>
-      <c r="V15" s="8"/>
-      <c r="W15" s="8"/>
-      <c r="X15" s="8"/>
-      <c r="Y15" s="8"/>
-      <c r="Z15" s="2"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="9"/>
+      <c r="P15" s="9"/>
+      <c r="Q15" s="9"/>
+      <c r="R15" s="9"/>
+      <c r="S15" s="9"/>
+      <c r="T15" s="9"/>
+      <c r="U15" s="9"/>
+      <c r="V15" s="9"/>
+      <c r="W15" s="9"/>
+      <c r="X15" s="9"/>
+      <c r="Y15" s="9"/>
+      <c r="Z15" s="10"/>
     </row>
     <row r="16" ht="15.0" customHeight="1">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="8">
         <v>0.0</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
-      <c r="N16" s="8"/>
-      <c r="O16" s="8"/>
-      <c r="P16" s="8"/>
-      <c r="Q16" s="8"/>
-      <c r="R16" s="8"/>
-      <c r="S16" s="8"/>
-      <c r="T16" s="8"/>
-      <c r="U16" s="8"/>
-      <c r="V16" s="8"/>
-      <c r="W16" s="8"/>
-      <c r="X16" s="8"/>
-      <c r="Y16" s="8"/>
-      <c r="Z16" s="2"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="9"/>
+      <c r="P16" s="9"/>
+      <c r="Q16" s="9"/>
+      <c r="R16" s="9"/>
+      <c r="S16" s="9"/>
+      <c r="T16" s="9"/>
+      <c r="U16" s="9"/>
+      <c r="V16" s="9"/>
+      <c r="W16" s="9"/>
+      <c r="X16" s="9"/>
+      <c r="Y16" s="9"/>
+      <c r="Z16" s="10"/>
     </row>
     <row r="17" ht="15.0" customHeight="1">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="8">
         <v>0.0</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
-      <c r="N17" s="8"/>
-      <c r="O17" s="8"/>
-      <c r="P17" s="8"/>
-      <c r="Q17" s="8"/>
-      <c r="R17" s="8"/>
-      <c r="S17" s="8"/>
-      <c r="T17" s="8"/>
-      <c r="U17" s="8"/>
-      <c r="V17" s="8"/>
-      <c r="W17" s="8"/>
-      <c r="X17" s="8"/>
-      <c r="Y17" s="8"/>
-      <c r="Z17" s="2"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="9"/>
+      <c r="P17" s="9"/>
+      <c r="Q17" s="9"/>
+      <c r="R17" s="9"/>
+      <c r="S17" s="9"/>
+      <c r="T17" s="9"/>
+      <c r="U17" s="9"/>
+      <c r="V17" s="9"/>
+      <c r="W17" s="9"/>
+      <c r="X17" s="9"/>
+      <c r="Y17" s="9"/>
+      <c r="Z17" s="10"/>
     </row>
     <row r="18" ht="15.0" customHeight="1">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="8">
         <v>0.0</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="E18" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
-      <c r="N18" s="8"/>
-      <c r="O18" s="8"/>
-      <c r="P18" s="8"/>
-      <c r="Q18" s="8"/>
-      <c r="R18" s="8"/>
-      <c r="S18" s="8"/>
-      <c r="T18" s="8"/>
-      <c r="U18" s="8"/>
-      <c r="V18" s="8"/>
-      <c r="W18" s="8"/>
-      <c r="X18" s="8"/>
-      <c r="Y18" s="8"/>
-      <c r="Z18" s="2"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="9"/>
+      <c r="P18" s="9"/>
+      <c r="Q18" s="9"/>
+      <c r="R18" s="9"/>
+      <c r="S18" s="9"/>
+      <c r="T18" s="9"/>
+      <c r="U18" s="9"/>
+      <c r="V18" s="9"/>
+      <c r="W18" s="9"/>
+      <c r="X18" s="9"/>
+      <c r="Y18" s="9"/>
+      <c r="Z18" s="10"/>
     </row>
     <row r="19" ht="15.0" customHeight="1">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="8">
         <v>0.0</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="E19" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="8"/>
-      <c r="N19" s="8"/>
-      <c r="O19" s="8"/>
-      <c r="P19" s="8"/>
-      <c r="Q19" s="8"/>
-      <c r="R19" s="8"/>
-      <c r="S19" s="8"/>
-      <c r="T19" s="8"/>
-      <c r="U19" s="8"/>
-      <c r="V19" s="8"/>
-      <c r="W19" s="8"/>
-      <c r="X19" s="8"/>
-      <c r="Y19" s="8"/>
-      <c r="Z19" s="2"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="9"/>
+      <c r="O19" s="9"/>
+      <c r="P19" s="9"/>
+      <c r="Q19" s="9"/>
+      <c r="R19" s="9"/>
+      <c r="S19" s="9"/>
+      <c r="T19" s="9"/>
+      <c r="U19" s="9"/>
+      <c r="V19" s="9"/>
+      <c r="W19" s="9"/>
+      <c r="X19" s="9"/>
+      <c r="Y19" s="9"/>
+      <c r="Z19" s="10"/>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="8">
         <v>0.0</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="E20" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8"/>
-      <c r="K20" s="8"/>
-      <c r="L20" s="8"/>
-      <c r="M20" s="8"/>
-      <c r="N20" s="8"/>
-      <c r="O20" s="8"/>
-      <c r="P20" s="8"/>
-      <c r="Q20" s="8"/>
-      <c r="R20" s="8"/>
-      <c r="S20" s="8"/>
-      <c r="T20" s="8"/>
-      <c r="U20" s="8"/>
-      <c r="V20" s="8"/>
-      <c r="W20" s="8"/>
-      <c r="X20" s="8"/>
-      <c r="Y20" s="8"/>
-      <c r="Z20" s="2"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
+      <c r="M20" s="9"/>
+      <c r="N20" s="9"/>
+      <c r="O20" s="9"/>
+      <c r="P20" s="9"/>
+      <c r="Q20" s="9"/>
+      <c r="R20" s="9"/>
+      <c r="S20" s="9"/>
+      <c r="T20" s="9"/>
+      <c r="U20" s="9"/>
+      <c r="V20" s="9"/>
+      <c r="W20" s="9"/>
+      <c r="X20" s="9"/>
+      <c r="Y20" s="9"/>
+      <c r="Z20" s="10"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="3" t="s">
@@ -2095,7 +2116,7 @@
       <c r="B21" s="4">
         <v>0.0</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="15" t="s">
         <v>82</v>
       </c>
       <c r="D21" s="5" t="s">
@@ -2124,1650 +2145,1650 @@
       <c r="W21" s="5"/>
       <c r="X21" s="5"/>
       <c r="Y21" s="5"/>
-      <c r="Z21" s="2"/>
+      <c r="Z21" s="6"/>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="8">
         <v>0.0</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="E22" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8"/>
-      <c r="K22" s="8"/>
-      <c r="L22" s="8"/>
-      <c r="M22" s="8"/>
-      <c r="N22" s="8"/>
-      <c r="O22" s="8"/>
-      <c r="P22" s="8"/>
-      <c r="Q22" s="8"/>
-      <c r="R22" s="8"/>
-      <c r="S22" s="8"/>
-      <c r="T22" s="8"/>
-      <c r="U22" s="8"/>
-      <c r="V22" s="8"/>
-      <c r="W22" s="8"/>
-      <c r="X22" s="8"/>
-      <c r="Y22" s="8"/>
-      <c r="Z22" s="2"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
+      <c r="M22" s="9"/>
+      <c r="N22" s="9"/>
+      <c r="O22" s="9"/>
+      <c r="P22" s="9"/>
+      <c r="Q22" s="9"/>
+      <c r="R22" s="9"/>
+      <c r="S22" s="9"/>
+      <c r="T22" s="9"/>
+      <c r="U22" s="9"/>
+      <c r="V22" s="9"/>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="10"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="8">
         <v>0.0</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="E23" s="8" t="s">
+      <c r="E23" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
-      <c r="K23" s="8"/>
-      <c r="L23" s="8"/>
-      <c r="M23" s="8"/>
-      <c r="N23" s="8"/>
-      <c r="O23" s="8"/>
-      <c r="P23" s="8"/>
-      <c r="Q23" s="8"/>
-      <c r="R23" s="8"/>
-      <c r="S23" s="8"/>
-      <c r="T23" s="8"/>
-      <c r="U23" s="8"/>
-      <c r="V23" s="8"/>
-      <c r="W23" s="8"/>
-      <c r="X23" s="8"/>
-      <c r="Y23" s="8"/>
-      <c r="Z23" s="2"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="9"/>
+      <c r="M23" s="9"/>
+      <c r="N23" s="9"/>
+      <c r="O23" s="9"/>
+      <c r="P23" s="9"/>
+      <c r="Q23" s="9"/>
+      <c r="R23" s="9"/>
+      <c r="S23" s="9"/>
+      <c r="T23" s="9"/>
+      <c r="U23" s="9"/>
+      <c r="V23" s="9"/>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="10"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="8">
         <v>0.0</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="E24" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="8"/>
-      <c r="N24" s="8"/>
-      <c r="O24" s="8"/>
-      <c r="P24" s="8"/>
-      <c r="Q24" s="8"/>
-      <c r="R24" s="8"/>
-      <c r="S24" s="8"/>
-      <c r="T24" s="8"/>
-      <c r="U24" s="8"/>
-      <c r="V24" s="8"/>
-      <c r="W24" s="8"/>
-      <c r="X24" s="8"/>
-      <c r="Y24" s="8"/>
-      <c r="Z24" s="2"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="9"/>
+      <c r="M24" s="9"/>
+      <c r="N24" s="9"/>
+      <c r="O24" s="9"/>
+      <c r="P24" s="9"/>
+      <c r="Q24" s="9"/>
+      <c r="R24" s="9"/>
+      <c r="S24" s="9"/>
+      <c r="T24" s="9"/>
+      <c r="U24" s="9"/>
+      <c r="V24" s="9"/>
+      <c r="W24" s="9"/>
+      <c r="X24" s="9"/>
+      <c r="Y24" s="9"/>
+      <c r="Z24" s="10"/>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="8">
         <v>0.0</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D25" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="E25" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="8"/>
-      <c r="K25" s="8"/>
-      <c r="L25" s="8"/>
-      <c r="M25" s="8"/>
-      <c r="N25" s="8"/>
-      <c r="O25" s="8"/>
-      <c r="P25" s="8"/>
-      <c r="Q25" s="8"/>
-      <c r="R25" s="8"/>
-      <c r="S25" s="8"/>
-      <c r="T25" s="8"/>
-      <c r="U25" s="8"/>
-      <c r="V25" s="8"/>
-      <c r="W25" s="8"/>
-      <c r="X25" s="8"/>
-      <c r="Y25" s="8"/>
-      <c r="Z25" s="2"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+      <c r="M25" s="9"/>
+      <c r="N25" s="9"/>
+      <c r="O25" s="9"/>
+      <c r="P25" s="9"/>
+      <c r="Q25" s="9"/>
+      <c r="R25" s="9"/>
+      <c r="S25" s="9"/>
+      <c r="T25" s="9"/>
+      <c r="U25" s="9"/>
+      <c r="V25" s="9"/>
+      <c r="W25" s="9"/>
+      <c r="X25" s="9"/>
+      <c r="Y25" s="9"/>
+      <c r="Z25" s="10"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="8">
         <v>0.0</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="D26" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="E26" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
-      <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="8"/>
-      <c r="M26" s="8"/>
-      <c r="N26" s="8"/>
-      <c r="O26" s="8"/>
-      <c r="P26" s="8"/>
-      <c r="Q26" s="8"/>
-      <c r="R26" s="8"/>
-      <c r="S26" s="8"/>
-      <c r="T26" s="8"/>
-      <c r="U26" s="8"/>
-      <c r="V26" s="8"/>
-      <c r="W26" s="8"/>
-      <c r="X26" s="8"/>
-      <c r="Y26" s="8"/>
-      <c r="Z26" s="2"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="9"/>
+      <c r="O26" s="9"/>
+      <c r="P26" s="9"/>
+      <c r="Q26" s="9"/>
+      <c r="R26" s="9"/>
+      <c r="S26" s="9"/>
+      <c r="T26" s="9"/>
+      <c r="U26" s="9"/>
+      <c r="V26" s="9"/>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="10"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="8">
         <v>0.0</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="D27" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="E27" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
-      <c r="J27" s="8"/>
-      <c r="K27" s="8"/>
-      <c r="L27" s="8"/>
-      <c r="M27" s="8"/>
-      <c r="N27" s="8"/>
-      <c r="O27" s="8"/>
-      <c r="P27" s="8"/>
-      <c r="Q27" s="8"/>
-      <c r="R27" s="8"/>
-      <c r="S27" s="8"/>
-      <c r="T27" s="8"/>
-      <c r="U27" s="8"/>
-      <c r="V27" s="8"/>
-      <c r="W27" s="8"/>
-      <c r="X27" s="8"/>
-      <c r="Y27" s="8"/>
-      <c r="Z27" s="2"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
+      <c r="M27" s="9"/>
+      <c r="N27" s="9"/>
+      <c r="O27" s="9"/>
+      <c r="P27" s="9"/>
+      <c r="Q27" s="9"/>
+      <c r="R27" s="9"/>
+      <c r="S27" s="9"/>
+      <c r="T27" s="9"/>
+      <c r="U27" s="9"/>
+      <c r="V27" s="9"/>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="10"/>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="8">
         <v>0.0</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="D28" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="E28" s="8" t="s">
+      <c r="E28" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8"/>
-      <c r="I28" s="8"/>
-      <c r="J28" s="8"/>
-      <c r="K28" s="8"/>
-      <c r="L28" s="8"/>
-      <c r="M28" s="8"/>
-      <c r="N28" s="8"/>
-      <c r="O28" s="8"/>
-      <c r="P28" s="8"/>
-      <c r="Q28" s="8"/>
-      <c r="R28" s="8"/>
-      <c r="S28" s="8"/>
-      <c r="T28" s="8"/>
-      <c r="U28" s="8"/>
-      <c r="V28" s="8"/>
-      <c r="W28" s="8"/>
-      <c r="X28" s="8"/>
-      <c r="Y28" s="8"/>
-      <c r="Z28" s="2"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9"/>
+      <c r="M28" s="9"/>
+      <c r="N28" s="9"/>
+      <c r="O28" s="9"/>
+      <c r="P28" s="9"/>
+      <c r="Q28" s="9"/>
+      <c r="R28" s="9"/>
+      <c r="S28" s="9"/>
+      <c r="T28" s="9"/>
+      <c r="U28" s="9"/>
+      <c r="V28" s="9"/>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="10"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29" s="8">
         <v>0.0</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="D29" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="E29" s="8" t="s">
+      <c r="E29" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="8"/>
-      <c r="K29" s="8"/>
-      <c r="L29" s="8"/>
-      <c r="M29" s="8"/>
-      <c r="N29" s="8"/>
-      <c r="O29" s="8"/>
-      <c r="P29" s="8"/>
-      <c r="Q29" s="8"/>
-      <c r="R29" s="8"/>
-      <c r="S29" s="8"/>
-      <c r="T29" s="8"/>
-      <c r="U29" s="8"/>
-      <c r="V29" s="8"/>
-      <c r="W29" s="8"/>
-      <c r="X29" s="8"/>
-      <c r="Y29" s="8"/>
-      <c r="Z29" s="2"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="9"/>
+      <c r="M29" s="9"/>
+      <c r="N29" s="9"/>
+      <c r="O29" s="9"/>
+      <c r="P29" s="9"/>
+      <c r="Q29" s="9"/>
+      <c r="R29" s="9"/>
+      <c r="S29" s="9"/>
+      <c r="T29" s="9"/>
+      <c r="U29" s="9"/>
+      <c r="V29" s="9"/>
+      <c r="W29" s="9"/>
+      <c r="X29" s="9"/>
+      <c r="Y29" s="9"/>
+      <c r="Z29" s="10"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30" s="8">
         <v>0.0</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="D30" s="8" t="s">
+      <c r="D30" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="E30" s="8" t="s">
+      <c r="E30" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
-      <c r="I30" s="8"/>
-      <c r="J30" s="8"/>
-      <c r="K30" s="8"/>
-      <c r="L30" s="8"/>
-      <c r="M30" s="8"/>
-      <c r="N30" s="8"/>
-      <c r="O30" s="8"/>
-      <c r="P30" s="8"/>
-      <c r="Q30" s="8"/>
-      <c r="R30" s="8"/>
-      <c r="S30" s="8"/>
-      <c r="T30" s="8"/>
-      <c r="U30" s="8"/>
-      <c r="V30" s="8"/>
-      <c r="W30" s="8"/>
-      <c r="X30" s="8"/>
-      <c r="Y30" s="8"/>
-      <c r="Z30" s="2"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
+      <c r="K30" s="9"/>
+      <c r="L30" s="9"/>
+      <c r="M30" s="9"/>
+      <c r="N30" s="9"/>
+      <c r="O30" s="9"/>
+      <c r="P30" s="9"/>
+      <c r="Q30" s="9"/>
+      <c r="R30" s="9"/>
+      <c r="S30" s="9"/>
+      <c r="T30" s="9"/>
+      <c r="U30" s="9"/>
+      <c r="V30" s="9"/>
+      <c r="W30" s="9"/>
+      <c r="X30" s="9"/>
+      <c r="Y30" s="9"/>
+      <c r="Z30" s="10"/>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="6" t="s">
+      <c r="A31" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="B31" s="7">
+      <c r="B31" s="8">
         <v>0.0</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="D31" s="8" t="s">
+      <c r="D31" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="E31" s="8" t="s">
+      <c r="E31" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
-      <c r="I31" s="8"/>
-      <c r="J31" s="8"/>
-      <c r="K31" s="8"/>
-      <c r="L31" s="8"/>
-      <c r="M31" s="8"/>
-      <c r="N31" s="8"/>
-      <c r="O31" s="8"/>
-      <c r="P31" s="8"/>
-      <c r="Q31" s="8"/>
-      <c r="R31" s="8"/>
-      <c r="S31" s="8"/>
-      <c r="T31" s="8"/>
-      <c r="U31" s="8"/>
-      <c r="V31" s="8"/>
-      <c r="W31" s="8"/>
-      <c r="X31" s="8"/>
-      <c r="Y31" s="8"/>
-      <c r="Z31" s="2"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
+      <c r="K31" s="9"/>
+      <c r="L31" s="9"/>
+      <c r="M31" s="9"/>
+      <c r="N31" s="9"/>
+      <c r="O31" s="9"/>
+      <c r="P31" s="9"/>
+      <c r="Q31" s="9"/>
+      <c r="R31" s="9"/>
+      <c r="S31" s="9"/>
+      <c r="T31" s="9"/>
+      <c r="U31" s="9"/>
+      <c r="V31" s="9"/>
+      <c r="W31" s="9"/>
+      <c r="X31" s="9"/>
+      <c r="Y31" s="9"/>
+      <c r="Z31" s="10"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="6" t="s">
+      <c r="A32" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="B32" s="7">
+      <c r="B32" s="8">
         <v>0.0</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="C32" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D32" s="8" t="s">
+      <c r="D32" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="E32" s="8" t="s">
+      <c r="E32" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="8"/>
-      <c r="I32" s="8"/>
-      <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
-      <c r="L32" s="8"/>
-      <c r="M32" s="8"/>
-      <c r="N32" s="8"/>
-      <c r="O32" s="8"/>
-      <c r="P32" s="8"/>
-      <c r="Q32" s="8"/>
-      <c r="R32" s="8"/>
-      <c r="S32" s="8"/>
-      <c r="T32" s="8"/>
-      <c r="U32" s="8"/>
-      <c r="V32" s="8"/>
-      <c r="W32" s="8"/>
-      <c r="X32" s="8"/>
-      <c r="Y32" s="8"/>
-      <c r="Z32" s="2"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="9"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="9"/>
+      <c r="M32" s="9"/>
+      <c r="N32" s="9"/>
+      <c r="O32" s="9"/>
+      <c r="P32" s="9"/>
+      <c r="Q32" s="9"/>
+      <c r="R32" s="9"/>
+      <c r="S32" s="9"/>
+      <c r="T32" s="9"/>
+      <c r="U32" s="9"/>
+      <c r="V32" s="9"/>
+      <c r="W32" s="9"/>
+      <c r="X32" s="9"/>
+      <c r="Y32" s="9"/>
+      <c r="Z32" s="10"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="B33" s="7">
+      <c r="B33" s="8">
         <v>0.0</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C33" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="D33" s="8" t="s">
+      <c r="D33" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="E33" s="8" t="s">
+      <c r="E33" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="8"/>
-      <c r="I33" s="8"/>
-      <c r="J33" s="8"/>
-      <c r="K33" s="8"/>
-      <c r="L33" s="8"/>
-      <c r="M33" s="8"/>
-      <c r="N33" s="8"/>
-      <c r="O33" s="8"/>
-      <c r="P33" s="8"/>
-      <c r="Q33" s="8"/>
-      <c r="R33" s="8"/>
-      <c r="S33" s="8"/>
-      <c r="T33" s="8"/>
-      <c r="U33" s="8"/>
-      <c r="V33" s="8"/>
-      <c r="W33" s="8"/>
-      <c r="X33" s="8"/>
-      <c r="Y33" s="8"/>
-      <c r="Z33" s="2"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="9"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="9"/>
+      <c r="M33" s="9"/>
+      <c r="N33" s="9"/>
+      <c r="O33" s="9"/>
+      <c r="P33" s="9"/>
+      <c r="Q33" s="9"/>
+      <c r="R33" s="9"/>
+      <c r="S33" s="9"/>
+      <c r="T33" s="9"/>
+      <c r="U33" s="9"/>
+      <c r="V33" s="9"/>
+      <c r="W33" s="9"/>
+      <c r="X33" s="9"/>
+      <c r="Y33" s="9"/>
+      <c r="Z33" s="10"/>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="B34" s="7">
+      <c r="B34" s="8">
         <v>0.0</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C34" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="D34" s="8" t="s">
+      <c r="D34" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="E34" s="8" t="s">
+      <c r="E34" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="8"/>
-      <c r="I34" s="8"/>
-      <c r="J34" s="8"/>
-      <c r="K34" s="8"/>
-      <c r="L34" s="8"/>
-      <c r="M34" s="8"/>
-      <c r="N34" s="8"/>
-      <c r="O34" s="8"/>
-      <c r="P34" s="8"/>
-      <c r="Q34" s="8"/>
-      <c r="R34" s="8"/>
-      <c r="S34" s="8"/>
-      <c r="T34" s="8"/>
-      <c r="U34" s="8"/>
-      <c r="V34" s="8"/>
-      <c r="W34" s="8"/>
-      <c r="X34" s="8"/>
-      <c r="Y34" s="8"/>
-      <c r="Z34" s="2"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="9"/>
+      <c r="K34" s="9"/>
+      <c r="L34" s="9"/>
+      <c r="M34" s="9"/>
+      <c r="N34" s="9"/>
+      <c r="O34" s="9"/>
+      <c r="P34" s="9"/>
+      <c r="Q34" s="9"/>
+      <c r="R34" s="9"/>
+      <c r="S34" s="9"/>
+      <c r="T34" s="9"/>
+      <c r="U34" s="9"/>
+      <c r="V34" s="9"/>
+      <c r="W34" s="9"/>
+      <c r="X34" s="9"/>
+      <c r="Y34" s="9"/>
+      <c r="Z34" s="10"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="B35" s="7">
+      <c r="B35" s="8">
         <v>0.0</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="D35" s="8" t="s">
+      <c r="D35" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="E35" s="8" t="s">
+      <c r="E35" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="8"/>
-      <c r="I35" s="8"/>
-      <c r="J35" s="8"/>
-      <c r="K35" s="8"/>
-      <c r="L35" s="8"/>
-      <c r="M35" s="8"/>
-      <c r="N35" s="8"/>
-      <c r="O35" s="8"/>
-      <c r="P35" s="8"/>
-      <c r="Q35" s="8"/>
-      <c r="R35" s="8"/>
-      <c r="S35" s="8"/>
-      <c r="T35" s="8"/>
-      <c r="U35" s="8"/>
-      <c r="V35" s="8"/>
-      <c r="W35" s="8"/>
-      <c r="X35" s="8"/>
-      <c r="Y35" s="8"/>
-      <c r="Z35" s="2"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
+      <c r="J35" s="9"/>
+      <c r="K35" s="9"/>
+      <c r="L35" s="9"/>
+      <c r="M35" s="9"/>
+      <c r="N35" s="9"/>
+      <c r="O35" s="9"/>
+      <c r="P35" s="9"/>
+      <c r="Q35" s="9"/>
+      <c r="R35" s="9"/>
+      <c r="S35" s="9"/>
+      <c r="T35" s="9"/>
+      <c r="U35" s="9"/>
+      <c r="V35" s="9"/>
+      <c r="W35" s="9"/>
+      <c r="X35" s="9"/>
+      <c r="Y35" s="9"/>
+      <c r="Z35" s="10"/>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B36" s="7">
+      <c r="B36" s="8">
         <v>0.0</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C36" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="D36" s="8" t="s">
+      <c r="D36" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="E36" s="8" t="s">
+      <c r="E36" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
-      <c r="H36" s="8"/>
-      <c r="I36" s="8"/>
-      <c r="J36" s="8"/>
-      <c r="K36" s="8"/>
-      <c r="L36" s="8"/>
-      <c r="M36" s="8"/>
-      <c r="N36" s="8"/>
-      <c r="O36" s="8"/>
-      <c r="P36" s="8"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="8"/>
-      <c r="S36" s="8"/>
-      <c r="T36" s="8"/>
-      <c r="U36" s="8"/>
-      <c r="V36" s="8"/>
-      <c r="W36" s="8"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="8"/>
-      <c r="Z36" s="2"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
+      <c r="I36" s="9"/>
+      <c r="J36" s="9"/>
+      <c r="K36" s="9"/>
+      <c r="L36" s="9"/>
+      <c r="M36" s="9"/>
+      <c r="N36" s="9"/>
+      <c r="O36" s="9"/>
+      <c r="P36" s="9"/>
+      <c r="Q36" s="9"/>
+      <c r="R36" s="9"/>
+      <c r="S36" s="9"/>
+      <c r="T36" s="9"/>
+      <c r="U36" s="9"/>
+      <c r="V36" s="9"/>
+      <c r="W36" s="9"/>
+      <c r="X36" s="9"/>
+      <c r="Y36" s="9"/>
+      <c r="Z36" s="10"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="6" t="s">
+      <c r="A37" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="B37" s="7">
+      <c r="B37" s="8">
         <v>0.0</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="C37" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="D37" s="8" t="s">
+      <c r="D37" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="E37" s="8" t="s">
+      <c r="E37" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
-      <c r="H37" s="8"/>
-      <c r="I37" s="8"/>
-      <c r="J37" s="8"/>
-      <c r="K37" s="8"/>
-      <c r="L37" s="8"/>
-      <c r="M37" s="8"/>
-      <c r="N37" s="8"/>
-      <c r="O37" s="8"/>
-      <c r="P37" s="8"/>
-      <c r="Q37" s="8"/>
-      <c r="R37" s="8"/>
-      <c r="S37" s="8"/>
-      <c r="T37" s="8"/>
-      <c r="U37" s="8"/>
-      <c r="V37" s="8"/>
-      <c r="W37" s="8"/>
-      <c r="X37" s="8"/>
-      <c r="Y37" s="8"/>
-      <c r="Z37" s="2"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="9"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="9"/>
+      <c r="M37" s="9"/>
+      <c r="N37" s="9"/>
+      <c r="O37" s="9"/>
+      <c r="P37" s="9"/>
+      <c r="Q37" s="9"/>
+      <c r="R37" s="9"/>
+      <c r="S37" s="9"/>
+      <c r="T37" s="9"/>
+      <c r="U37" s="9"/>
+      <c r="V37" s="9"/>
+      <c r="W37" s="9"/>
+      <c r="X37" s="9"/>
+      <c r="Y37" s="9"/>
+      <c r="Z37" s="10"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="B38" s="7">
+      <c r="B38" s="8">
         <v>0.0</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="C38" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="D38" s="8" t="s">
+      <c r="D38" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="E38" s="8" t="s">
+      <c r="E38" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8"/>
-      <c r="H38" s="8"/>
-      <c r="I38" s="8"/>
-      <c r="J38" s="8"/>
-      <c r="K38" s="8"/>
-      <c r="L38" s="8"/>
-      <c r="M38" s="8"/>
-      <c r="N38" s="8"/>
-      <c r="O38" s="8"/>
-      <c r="P38" s="8"/>
-      <c r="Q38" s="8"/>
-      <c r="R38" s="8"/>
-      <c r="S38" s="8"/>
-      <c r="T38" s="8"/>
-      <c r="U38" s="8"/>
-      <c r="V38" s="8"/>
-      <c r="W38" s="8"/>
-      <c r="X38" s="8"/>
-      <c r="Y38" s="8"/>
-      <c r="Z38" s="2"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="9"/>
+      <c r="I38" s="9"/>
+      <c r="J38" s="9"/>
+      <c r="K38" s="9"/>
+      <c r="L38" s="9"/>
+      <c r="M38" s="9"/>
+      <c r="N38" s="9"/>
+      <c r="O38" s="9"/>
+      <c r="P38" s="9"/>
+      <c r="Q38" s="9"/>
+      <c r="R38" s="9"/>
+      <c r="S38" s="9"/>
+      <c r="T38" s="9"/>
+      <c r="U38" s="9"/>
+      <c r="V38" s="9"/>
+      <c r="W38" s="9"/>
+      <c r="X38" s="9"/>
+      <c r="Y38" s="9"/>
+      <c r="Z38" s="10"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="6" t="s">
+      <c r="A39" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="B39" s="7">
+      <c r="B39" s="8">
         <v>0.0</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C39" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="D39" s="8" t="s">
+      <c r="D39" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="E39" s="8" t="s">
+      <c r="E39" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="F39" s="8"/>
-      <c r="G39" s="8"/>
-      <c r="H39" s="8"/>
-      <c r="I39" s="8"/>
-      <c r="J39" s="8"/>
-      <c r="K39" s="8"/>
-      <c r="L39" s="8"/>
-      <c r="M39" s="8"/>
-      <c r="N39" s="8"/>
-      <c r="O39" s="8"/>
-      <c r="P39" s="8"/>
-      <c r="Q39" s="8"/>
-      <c r="R39" s="8"/>
-      <c r="S39" s="8"/>
-      <c r="T39" s="8"/>
-      <c r="U39" s="8"/>
-      <c r="V39" s="8"/>
-      <c r="W39" s="8"/>
-      <c r="X39" s="8"/>
-      <c r="Y39" s="8"/>
-      <c r="Z39" s="2"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="9"/>
+      <c r="I39" s="9"/>
+      <c r="J39" s="9"/>
+      <c r="K39" s="9"/>
+      <c r="L39" s="9"/>
+      <c r="M39" s="9"/>
+      <c r="N39" s="9"/>
+      <c r="O39" s="9"/>
+      <c r="P39" s="9"/>
+      <c r="Q39" s="9"/>
+      <c r="R39" s="9"/>
+      <c r="S39" s="9"/>
+      <c r="T39" s="9"/>
+      <c r="U39" s="9"/>
+      <c r="V39" s="9"/>
+      <c r="W39" s="9"/>
+      <c r="X39" s="9"/>
+      <c r="Y39" s="9"/>
+      <c r="Z39" s="10"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="6" t="s">
+      <c r="A40" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="B40" s="7">
+      <c r="B40" s="8">
         <v>0.0</v>
       </c>
-      <c r="C40" s="8" t="s">
+      <c r="C40" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="D40" s="8" t="s">
+      <c r="D40" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="E40" s="8" t="s">
+      <c r="E40" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="F40" s="8"/>
-      <c r="G40" s="8"/>
-      <c r="H40" s="8"/>
-      <c r="I40" s="8"/>
-      <c r="J40" s="8"/>
-      <c r="K40" s="8"/>
-      <c r="L40" s="8"/>
-      <c r="M40" s="8"/>
-      <c r="N40" s="8"/>
-      <c r="O40" s="8"/>
-      <c r="P40" s="8"/>
-      <c r="Q40" s="8"/>
-      <c r="R40" s="8"/>
-      <c r="S40" s="8"/>
-      <c r="T40" s="8"/>
-      <c r="U40" s="8"/>
-      <c r="V40" s="8"/>
-      <c r="W40" s="8"/>
-      <c r="X40" s="8"/>
-      <c r="Y40" s="8"/>
-      <c r="Z40" s="2"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="9"/>
+      <c r="K40" s="9"/>
+      <c r="L40" s="9"/>
+      <c r="M40" s="9"/>
+      <c r="N40" s="9"/>
+      <c r="O40" s="9"/>
+      <c r="P40" s="9"/>
+      <c r="Q40" s="9"/>
+      <c r="R40" s="9"/>
+      <c r="S40" s="9"/>
+      <c r="T40" s="9"/>
+      <c r="U40" s="9"/>
+      <c r="V40" s="9"/>
+      <c r="W40" s="9"/>
+      <c r="X40" s="9"/>
+      <c r="Y40" s="9"/>
+      <c r="Z40" s="10"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="6" t="s">
+      <c r="A41" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="B41" s="7">
+      <c r="B41" s="8">
         <v>0.0</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="C41" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="D41" s="8" t="s">
+      <c r="D41" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="E41" s="8" t="s">
+      <c r="E41" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="F41" s="8"/>
-      <c r="G41" s="8"/>
-      <c r="H41" s="8"/>
-      <c r="I41" s="8"/>
-      <c r="J41" s="8"/>
-      <c r="K41" s="8"/>
-      <c r="L41" s="8"/>
-      <c r="M41" s="8"/>
-      <c r="N41" s="8"/>
-      <c r="O41" s="8"/>
-      <c r="P41" s="8"/>
-      <c r="Q41" s="8"/>
-      <c r="R41" s="8"/>
-      <c r="S41" s="8"/>
-      <c r="T41" s="8"/>
-      <c r="U41" s="8"/>
-      <c r="V41" s="8"/>
-      <c r="W41" s="8"/>
-      <c r="X41" s="8"/>
-      <c r="Y41" s="8"/>
-      <c r="Z41" s="2"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="9"/>
+      <c r="I41" s="9"/>
+      <c r="J41" s="9"/>
+      <c r="K41" s="9"/>
+      <c r="L41" s="9"/>
+      <c r="M41" s="9"/>
+      <c r="N41" s="9"/>
+      <c r="O41" s="9"/>
+      <c r="P41" s="9"/>
+      <c r="Q41" s="9"/>
+      <c r="R41" s="9"/>
+      <c r="S41" s="9"/>
+      <c r="T41" s="9"/>
+      <c r="U41" s="9"/>
+      <c r="V41" s="9"/>
+      <c r="W41" s="9"/>
+      <c r="X41" s="9"/>
+      <c r="Y41" s="9"/>
+      <c r="Z41" s="10"/>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="6" t="s">
+      <c r="A42" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="B42" s="7">
+      <c r="B42" s="8">
         <v>0.0</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="C42" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="D42" s="8" t="s">
+      <c r="D42" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="E42" s="8" t="s">
+      <c r="E42" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="F42" s="8"/>
-      <c r="G42" s="8"/>
-      <c r="H42" s="8"/>
-      <c r="I42" s="8"/>
-      <c r="J42" s="8"/>
-      <c r="K42" s="8"/>
-      <c r="L42" s="8"/>
-      <c r="M42" s="8"/>
-      <c r="N42" s="8"/>
-      <c r="O42" s="8"/>
-      <c r="P42" s="8"/>
-      <c r="Q42" s="8"/>
-      <c r="R42" s="8"/>
-      <c r="S42" s="8"/>
-      <c r="T42" s="8"/>
-      <c r="U42" s="8"/>
-      <c r="V42" s="8"/>
-      <c r="W42" s="8"/>
-      <c r="X42" s="8"/>
-      <c r="Y42" s="8"/>
-      <c r="Z42" s="2"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="9"/>
+      <c r="I42" s="9"/>
+      <c r="J42" s="9"/>
+      <c r="K42" s="9"/>
+      <c r="L42" s="9"/>
+      <c r="M42" s="9"/>
+      <c r="N42" s="9"/>
+      <c r="O42" s="9"/>
+      <c r="P42" s="9"/>
+      <c r="Q42" s="9"/>
+      <c r="R42" s="9"/>
+      <c r="S42" s="9"/>
+      <c r="T42" s="9"/>
+      <c r="U42" s="9"/>
+      <c r="V42" s="9"/>
+      <c r="W42" s="9"/>
+      <c r="X42" s="9"/>
+      <c r="Y42" s="9"/>
+      <c r="Z42" s="10"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="B43" s="7">
+      <c r="B43" s="8">
         <v>0.0</v>
       </c>
-      <c r="C43" s="8" t="s">
+      <c r="C43" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="D43" s="8" t="s">
+      <c r="D43" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="E43" s="8" t="s">
+      <c r="E43" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="F43" s="8"/>
-      <c r="G43" s="8"/>
-      <c r="H43" s="8"/>
-      <c r="I43" s="8"/>
-      <c r="J43" s="8"/>
-      <c r="K43" s="8"/>
-      <c r="L43" s="8"/>
-      <c r="M43" s="8"/>
-      <c r="N43" s="8"/>
-      <c r="O43" s="8"/>
-      <c r="P43" s="8"/>
-      <c r="Q43" s="8"/>
-      <c r="R43" s="8"/>
-      <c r="S43" s="8"/>
-      <c r="T43" s="8"/>
-      <c r="U43" s="8"/>
-      <c r="V43" s="8"/>
-      <c r="W43" s="8"/>
-      <c r="X43" s="8"/>
-      <c r="Y43" s="8"/>
-      <c r="Z43" s="2"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="9"/>
+      <c r="I43" s="9"/>
+      <c r="J43" s="9"/>
+      <c r="K43" s="9"/>
+      <c r="L43" s="9"/>
+      <c r="M43" s="9"/>
+      <c r="N43" s="9"/>
+      <c r="O43" s="9"/>
+      <c r="P43" s="9"/>
+      <c r="Q43" s="9"/>
+      <c r="R43" s="9"/>
+      <c r="S43" s="9"/>
+      <c r="T43" s="9"/>
+      <c r="U43" s="9"/>
+      <c r="V43" s="9"/>
+      <c r="W43" s="9"/>
+      <c r="X43" s="9"/>
+      <c r="Y43" s="9"/>
+      <c r="Z43" s="10"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="6" t="s">
+      <c r="A44" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="B44" s="7">
+      <c r="B44" s="8">
         <v>0.0</v>
       </c>
-      <c r="C44" s="8" t="s">
+      <c r="C44" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="D44" s="8" t="s">
+      <c r="D44" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="E44" s="8" t="s">
+      <c r="E44" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="F44" s="8"/>
-      <c r="G44" s="8"/>
-      <c r="H44" s="8"/>
-      <c r="I44" s="8"/>
-      <c r="J44" s="8"/>
-      <c r="K44" s="8"/>
-      <c r="L44" s="8"/>
-      <c r="M44" s="8"/>
-      <c r="N44" s="8"/>
-      <c r="O44" s="8"/>
-      <c r="P44" s="8"/>
-      <c r="Q44" s="8"/>
-      <c r="R44" s="8"/>
-      <c r="S44" s="8"/>
-      <c r="T44" s="8"/>
-      <c r="U44" s="8"/>
-      <c r="V44" s="8"/>
-      <c r="W44" s="8"/>
-      <c r="X44" s="8"/>
-      <c r="Y44" s="8"/>
-      <c r="Z44" s="2"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="9"/>
+      <c r="H44" s="9"/>
+      <c r="I44" s="9"/>
+      <c r="J44" s="9"/>
+      <c r="K44" s="9"/>
+      <c r="L44" s="9"/>
+      <c r="M44" s="9"/>
+      <c r="N44" s="9"/>
+      <c r="O44" s="9"/>
+      <c r="P44" s="9"/>
+      <c r="Q44" s="9"/>
+      <c r="R44" s="9"/>
+      <c r="S44" s="9"/>
+      <c r="T44" s="9"/>
+      <c r="U44" s="9"/>
+      <c r="V44" s="9"/>
+      <c r="W44" s="9"/>
+      <c r="X44" s="9"/>
+      <c r="Y44" s="9"/>
+      <c r="Z44" s="10"/>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="6" t="s">
+      <c r="A45" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="B45" s="7">
+      <c r="B45" s="8">
         <v>0.0</v>
       </c>
-      <c r="C45" s="8" t="s">
+      <c r="C45" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="D45" s="8" t="s">
+      <c r="D45" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="E45" s="8" t="s">
+      <c r="E45" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="F45" s="8"/>
-      <c r="G45" s="8"/>
-      <c r="H45" s="8"/>
-      <c r="I45" s="8"/>
-      <c r="J45" s="8"/>
-      <c r="K45" s="8"/>
-      <c r="L45" s="8"/>
-      <c r="M45" s="8"/>
-      <c r="N45" s="8"/>
-      <c r="O45" s="8"/>
-      <c r="P45" s="8"/>
-      <c r="Q45" s="8"/>
-      <c r="R45" s="8"/>
-      <c r="S45" s="8"/>
-      <c r="T45" s="8"/>
-      <c r="U45" s="8"/>
-      <c r="V45" s="8"/>
-      <c r="W45" s="8"/>
-      <c r="X45" s="8"/>
-      <c r="Y45" s="8"/>
-      <c r="Z45" s="2"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="9"/>
+      <c r="H45" s="9"/>
+      <c r="I45" s="9"/>
+      <c r="J45" s="9"/>
+      <c r="K45" s="9"/>
+      <c r="L45" s="9"/>
+      <c r="M45" s="9"/>
+      <c r="N45" s="9"/>
+      <c r="O45" s="9"/>
+      <c r="P45" s="9"/>
+      <c r="Q45" s="9"/>
+      <c r="R45" s="9"/>
+      <c r="S45" s="9"/>
+      <c r="T45" s="9"/>
+      <c r="U45" s="9"/>
+      <c r="V45" s="9"/>
+      <c r="W45" s="9"/>
+      <c r="X45" s="9"/>
+      <c r="Y45" s="9"/>
+      <c r="Z45" s="10"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="6" t="s">
+      <c r="A46" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="B46" s="7">
+      <c r="B46" s="8">
         <v>0.0</v>
       </c>
-      <c r="C46" s="8" t="s">
+      <c r="C46" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="D46" s="8" t="s">
+      <c r="D46" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="E46" s="8" t="s">
+      <c r="E46" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="F46" s="8"/>
-      <c r="G46" s="8"/>
-      <c r="H46" s="8"/>
-      <c r="I46" s="8"/>
-      <c r="J46" s="8"/>
-      <c r="K46" s="8"/>
-      <c r="L46" s="8"/>
-      <c r="M46" s="8"/>
-      <c r="N46" s="8"/>
-      <c r="O46" s="8"/>
-      <c r="P46" s="8"/>
-      <c r="Q46" s="8"/>
-      <c r="R46" s="8"/>
-      <c r="S46" s="8"/>
-      <c r="T46" s="8"/>
-      <c r="U46" s="8"/>
-      <c r="V46" s="8"/>
-      <c r="W46" s="8"/>
-      <c r="X46" s="8"/>
-      <c r="Y46" s="8"/>
-      <c r="Z46" s="2"/>
+      <c r="F46" s="9"/>
+      <c r="G46" s="9"/>
+      <c r="H46" s="9"/>
+      <c r="I46" s="9"/>
+      <c r="J46" s="9"/>
+      <c r="K46" s="9"/>
+      <c r="L46" s="9"/>
+      <c r="M46" s="9"/>
+      <c r="N46" s="9"/>
+      <c r="O46" s="9"/>
+      <c r="P46" s="9"/>
+      <c r="Q46" s="9"/>
+      <c r="R46" s="9"/>
+      <c r="S46" s="9"/>
+      <c r="T46" s="9"/>
+      <c r="U46" s="9"/>
+      <c r="V46" s="9"/>
+      <c r="W46" s="9"/>
+      <c r="X46" s="9"/>
+      <c r="Y46" s="9"/>
+      <c r="Z46" s="10"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="6" t="s">
+      <c r="A47" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="B47" s="7">
+      <c r="B47" s="8">
         <v>0.0</v>
       </c>
-      <c r="C47" s="8" t="s">
+      <c r="C47" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="D47" s="8" t="s">
+      <c r="D47" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="E47" s="8" t="s">
+      <c r="E47" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="F47" s="8"/>
-      <c r="G47" s="8"/>
-      <c r="H47" s="8"/>
-      <c r="I47" s="8"/>
-      <c r="J47" s="8"/>
-      <c r="K47" s="8"/>
-      <c r="L47" s="8"/>
-      <c r="M47" s="8"/>
-      <c r="N47" s="8"/>
-      <c r="O47" s="8"/>
-      <c r="P47" s="8"/>
-      <c r="Q47" s="8"/>
-      <c r="R47" s="8"/>
-      <c r="S47" s="8"/>
-      <c r="T47" s="8"/>
-      <c r="U47" s="8"/>
-      <c r="V47" s="8"/>
-      <c r="W47" s="8"/>
-      <c r="X47" s="8"/>
-      <c r="Y47" s="8"/>
-      <c r="Z47" s="2"/>
+      <c r="F47" s="9"/>
+      <c r="G47" s="9"/>
+      <c r="H47" s="9"/>
+      <c r="I47" s="9"/>
+      <c r="J47" s="9"/>
+      <c r="K47" s="9"/>
+      <c r="L47" s="9"/>
+      <c r="M47" s="9"/>
+      <c r="N47" s="9"/>
+      <c r="O47" s="9"/>
+      <c r="P47" s="9"/>
+      <c r="Q47" s="9"/>
+      <c r="R47" s="9"/>
+      <c r="S47" s="9"/>
+      <c r="T47" s="9"/>
+      <c r="U47" s="9"/>
+      <c r="V47" s="9"/>
+      <c r="W47" s="9"/>
+      <c r="X47" s="9"/>
+      <c r="Y47" s="9"/>
+      <c r="Z47" s="10"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="6" t="s">
+      <c r="A48" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="B48" s="7">
+      <c r="B48" s="8">
         <v>0.0</v>
       </c>
-      <c r="C48" s="8" t="s">
+      <c r="C48" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="D48" s="8" t="s">
+      <c r="D48" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="E48" s="8" t="s">
+      <c r="E48" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="F48" s="8"/>
-      <c r="G48" s="8"/>
-      <c r="H48" s="8"/>
-      <c r="I48" s="8"/>
-      <c r="J48" s="8"/>
-      <c r="K48" s="8"/>
-      <c r="L48" s="8"/>
-      <c r="M48" s="8"/>
-      <c r="N48" s="8"/>
-      <c r="O48" s="8"/>
-      <c r="P48" s="8"/>
-      <c r="Q48" s="8"/>
-      <c r="R48" s="8"/>
-      <c r="S48" s="8"/>
-      <c r="T48" s="8"/>
-      <c r="U48" s="8"/>
-      <c r="V48" s="8"/>
-      <c r="W48" s="8"/>
-      <c r="X48" s="8"/>
-      <c r="Y48" s="8"/>
-      <c r="Z48" s="2"/>
+      <c r="F48" s="9"/>
+      <c r="G48" s="9"/>
+      <c r="H48" s="9"/>
+      <c r="I48" s="9"/>
+      <c r="J48" s="9"/>
+      <c r="K48" s="9"/>
+      <c r="L48" s="9"/>
+      <c r="M48" s="9"/>
+      <c r="N48" s="9"/>
+      <c r="O48" s="9"/>
+      <c r="P48" s="9"/>
+      <c r="Q48" s="9"/>
+      <c r="R48" s="9"/>
+      <c r="S48" s="9"/>
+      <c r="T48" s="9"/>
+      <c r="U48" s="9"/>
+      <c r="V48" s="9"/>
+      <c r="W48" s="9"/>
+      <c r="X48" s="9"/>
+      <c r="Y48" s="9"/>
+      <c r="Z48" s="10"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="6" t="s">
+      <c r="A49" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="B49" s="7">
+      <c r="B49" s="8">
         <v>0.0</v>
       </c>
-      <c r="C49" s="8" t="s">
+      <c r="C49" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="D49" s="8" t="s">
+      <c r="D49" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="E49" s="8" t="s">
+      <c r="E49" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="F49" s="8"/>
-      <c r="G49" s="8"/>
-      <c r="H49" s="8"/>
-      <c r="I49" s="8"/>
-      <c r="J49" s="8"/>
-      <c r="K49" s="8"/>
-      <c r="L49" s="8"/>
-      <c r="M49" s="8"/>
-      <c r="N49" s="8"/>
-      <c r="O49" s="8"/>
-      <c r="P49" s="8"/>
-      <c r="Q49" s="8"/>
-      <c r="R49" s="8"/>
-      <c r="S49" s="8"/>
-      <c r="T49" s="8"/>
-      <c r="U49" s="8"/>
-      <c r="V49" s="8"/>
-      <c r="W49" s="8"/>
-      <c r="X49" s="8"/>
-      <c r="Y49" s="8"/>
-      <c r="Z49" s="2"/>
+      <c r="F49" s="9"/>
+      <c r="G49" s="9"/>
+      <c r="H49" s="9"/>
+      <c r="I49" s="9"/>
+      <c r="J49" s="9"/>
+      <c r="K49" s="9"/>
+      <c r="L49" s="9"/>
+      <c r="M49" s="9"/>
+      <c r="N49" s="9"/>
+      <c r="O49" s="9"/>
+      <c r="P49" s="9"/>
+      <c r="Q49" s="9"/>
+      <c r="R49" s="9"/>
+      <c r="S49" s="9"/>
+      <c r="T49" s="9"/>
+      <c r="U49" s="9"/>
+      <c r="V49" s="9"/>
+      <c r="W49" s="9"/>
+      <c r="X49" s="9"/>
+      <c r="Y49" s="9"/>
+      <c r="Z49" s="10"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="6" t="s">
+      <c r="A50" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="B50" s="7">
+      <c r="B50" s="8">
         <v>0.0</v>
       </c>
-      <c r="C50" s="8" t="s">
+      <c r="C50" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="D50" s="8" t="s">
+      <c r="D50" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="E50" s="8" t="s">
+      <c r="E50" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="F50" s="8"/>
-      <c r="G50" s="8"/>
-      <c r="H50" s="8"/>
-      <c r="I50" s="8"/>
-      <c r="J50" s="8"/>
-      <c r="K50" s="8"/>
-      <c r="L50" s="8"/>
-      <c r="M50" s="8"/>
-      <c r="N50" s="8"/>
-      <c r="O50" s="8"/>
-      <c r="P50" s="8"/>
-      <c r="Q50" s="8"/>
-      <c r="R50" s="8"/>
-      <c r="S50" s="8"/>
-      <c r="T50" s="8"/>
-      <c r="U50" s="8"/>
-      <c r="V50" s="8"/>
-      <c r="W50" s="8"/>
-      <c r="X50" s="8"/>
-      <c r="Y50" s="8"/>
-      <c r="Z50" s="2"/>
+      <c r="F50" s="9"/>
+      <c r="G50" s="9"/>
+      <c r="H50" s="9"/>
+      <c r="I50" s="9"/>
+      <c r="J50" s="9"/>
+      <c r="K50" s="9"/>
+      <c r="L50" s="9"/>
+      <c r="M50" s="9"/>
+      <c r="N50" s="9"/>
+      <c r="O50" s="9"/>
+      <c r="P50" s="9"/>
+      <c r="Q50" s="9"/>
+      <c r="R50" s="9"/>
+      <c r="S50" s="9"/>
+      <c r="T50" s="9"/>
+      <c r="U50" s="9"/>
+      <c r="V50" s="9"/>
+      <c r="W50" s="9"/>
+      <c r="X50" s="9"/>
+      <c r="Y50" s="9"/>
+      <c r="Z50" s="10"/>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="6" t="s">
+      <c r="A51" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="B51" s="7">
+      <c r="B51" s="8">
         <v>0.0</v>
       </c>
-      <c r="C51" s="8" t="s">
+      <c r="C51" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="D51" s="8" t="s">
+      <c r="D51" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="E51" s="8" t="s">
+      <c r="E51" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="F51" s="8"/>
-      <c r="G51" s="8"/>
-      <c r="H51" s="8"/>
-      <c r="I51" s="8"/>
-      <c r="J51" s="8"/>
-      <c r="K51" s="8"/>
-      <c r="L51" s="8"/>
-      <c r="M51" s="8"/>
-      <c r="N51" s="8"/>
-      <c r="O51" s="8"/>
-      <c r="P51" s="8"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
-      <c r="S51" s="8"/>
-      <c r="T51" s="8"/>
-      <c r="U51" s="8"/>
-      <c r="V51" s="8"/>
-      <c r="W51" s="8"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="8"/>
-      <c r="Z51" s="2"/>
+      <c r="F51" s="9"/>
+      <c r="G51" s="9"/>
+      <c r="H51" s="9"/>
+      <c r="I51" s="9"/>
+      <c r="J51" s="9"/>
+      <c r="K51" s="9"/>
+      <c r="L51" s="9"/>
+      <c r="M51" s="9"/>
+      <c r="N51" s="9"/>
+      <c r="O51" s="9"/>
+      <c r="P51" s="9"/>
+      <c r="Q51" s="9"/>
+      <c r="R51" s="9"/>
+      <c r="S51" s="9"/>
+      <c r="T51" s="9"/>
+      <c r="U51" s="9"/>
+      <c r="V51" s="9"/>
+      <c r="W51" s="9"/>
+      <c r="X51" s="9"/>
+      <c r="Y51" s="9"/>
+      <c r="Z51" s="10"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="6" t="s">
+      <c r="A52" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="B52" s="7">
+      <c r="B52" s="8">
         <v>0.0</v>
       </c>
-      <c r="C52" s="8" t="s">
+      <c r="C52" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="D52" s="8" t="s">
+      <c r="D52" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="E52" s="8" t="s">
+      <c r="E52" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="F52" s="8"/>
-      <c r="G52" s="8"/>
-      <c r="H52" s="8"/>
-      <c r="I52" s="8"/>
-      <c r="J52" s="8"/>
-      <c r="K52" s="8"/>
-      <c r="L52" s="8"/>
-      <c r="M52" s="8"/>
-      <c r="N52" s="8"/>
-      <c r="O52" s="8"/>
-      <c r="P52" s="8"/>
-      <c r="Q52" s="8"/>
-      <c r="R52" s="8"/>
-      <c r="S52" s="8"/>
-      <c r="T52" s="8"/>
-      <c r="U52" s="8"/>
-      <c r="V52" s="8"/>
-      <c r="W52" s="8"/>
-      <c r="X52" s="8"/>
-      <c r="Y52" s="8"/>
-      <c r="Z52" s="2"/>
+      <c r="F52" s="9"/>
+      <c r="G52" s="9"/>
+      <c r="H52" s="9"/>
+      <c r="I52" s="9"/>
+      <c r="J52" s="9"/>
+      <c r="K52" s="9"/>
+      <c r="L52" s="9"/>
+      <c r="M52" s="9"/>
+      <c r="N52" s="9"/>
+      <c r="O52" s="9"/>
+      <c r="P52" s="9"/>
+      <c r="Q52" s="9"/>
+      <c r="R52" s="9"/>
+      <c r="S52" s="9"/>
+      <c r="T52" s="9"/>
+      <c r="U52" s="9"/>
+      <c r="V52" s="9"/>
+      <c r="W52" s="9"/>
+      <c r="X52" s="9"/>
+      <c r="Y52" s="9"/>
+      <c r="Z52" s="10"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="6" t="s">
+      <c r="A53" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="B53" s="7">
+      <c r="B53" s="8">
         <v>0.0</v>
       </c>
-      <c r="C53" s="8" t="s">
+      <c r="C53" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="D53" s="8" t="s">
+      <c r="D53" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="E53" s="8" t="s">
+      <c r="E53" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="F53" s="8"/>
-      <c r="G53" s="8"/>
-      <c r="H53" s="8"/>
-      <c r="I53" s="8"/>
-      <c r="J53" s="8"/>
-      <c r="K53" s="8"/>
-      <c r="L53" s="8"/>
-      <c r="M53" s="8"/>
-      <c r="N53" s="8"/>
-      <c r="O53" s="8"/>
-      <c r="P53" s="8"/>
-      <c r="Q53" s="8"/>
-      <c r="R53" s="8"/>
-      <c r="S53" s="8"/>
-      <c r="T53" s="8"/>
-      <c r="U53" s="8"/>
-      <c r="V53" s="8"/>
-      <c r="W53" s="8"/>
-      <c r="X53" s="8"/>
-      <c r="Y53" s="8"/>
-      <c r="Z53" s="2"/>
+      <c r="F53" s="9"/>
+      <c r="G53" s="9"/>
+      <c r="H53" s="9"/>
+      <c r="I53" s="9"/>
+      <c r="J53" s="9"/>
+      <c r="K53" s="9"/>
+      <c r="L53" s="9"/>
+      <c r="M53" s="9"/>
+      <c r="N53" s="9"/>
+      <c r="O53" s="9"/>
+      <c r="P53" s="9"/>
+      <c r="Q53" s="9"/>
+      <c r="R53" s="9"/>
+      <c r="S53" s="9"/>
+      <c r="T53" s="9"/>
+      <c r="U53" s="9"/>
+      <c r="V53" s="9"/>
+      <c r="W53" s="9"/>
+      <c r="X53" s="9"/>
+      <c r="Y53" s="9"/>
+      <c r="Z53" s="10"/>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="6" t="s">
+      <c r="A54" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="B54" s="7">
+      <c r="B54" s="8">
         <v>0.0</v>
       </c>
-      <c r="C54" s="8" t="s">
+      <c r="C54" s="13" t="s">
         <v>214</v>
       </c>
-      <c r="D54" s="8" t="s">
+      <c r="D54" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="E54" s="8" t="s">
+      <c r="E54" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="F54" s="8"/>
-      <c r="G54" s="8"/>
-      <c r="H54" s="8"/>
-      <c r="I54" s="8"/>
-      <c r="J54" s="8"/>
-      <c r="K54" s="8"/>
-      <c r="L54" s="8"/>
-      <c r="M54" s="8"/>
-      <c r="N54" s="8"/>
-      <c r="O54" s="8"/>
-      <c r="P54" s="8"/>
-      <c r="Q54" s="8"/>
-      <c r="R54" s="8"/>
-      <c r="S54" s="8"/>
-      <c r="T54" s="8"/>
-      <c r="U54" s="8"/>
-      <c r="V54" s="8"/>
-      <c r="W54" s="8"/>
-      <c r="X54" s="8"/>
-      <c r="Y54" s="8"/>
-      <c r="Z54" s="2"/>
+      <c r="F54" s="9"/>
+      <c r="G54" s="9"/>
+      <c r="H54" s="9"/>
+      <c r="I54" s="9"/>
+      <c r="J54" s="9"/>
+      <c r="K54" s="9"/>
+      <c r="L54" s="9"/>
+      <c r="M54" s="9"/>
+      <c r="N54" s="9"/>
+      <c r="O54" s="9"/>
+      <c r="P54" s="9"/>
+      <c r="Q54" s="9"/>
+      <c r="R54" s="9"/>
+      <c r="S54" s="9"/>
+      <c r="T54" s="9"/>
+      <c r="U54" s="9"/>
+      <c r="V54" s="9"/>
+      <c r="W54" s="9"/>
+      <c r="X54" s="9"/>
+      <c r="Y54" s="9"/>
+      <c r="Z54" s="10"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="6" t="s">
+      <c r="A55" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="B55" s="7">
+      <c r="B55" s="8">
         <v>0.0</v>
       </c>
-      <c r="C55" s="8" t="s">
+      <c r="C55" s="13" t="s">
         <v>216</v>
       </c>
-      <c r="D55" s="8" t="s">
+      <c r="D55" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="E55" s="8" t="s">
+      <c r="E55" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="F55" s="8"/>
-      <c r="G55" s="8"/>
-      <c r="H55" s="8"/>
-      <c r="I55" s="8"/>
-      <c r="J55" s="8"/>
-      <c r="K55" s="8"/>
-      <c r="L55" s="8"/>
-      <c r="M55" s="8"/>
-      <c r="N55" s="8"/>
-      <c r="O55" s="8"/>
-      <c r="P55" s="8"/>
-      <c r="Q55" s="8"/>
-      <c r="R55" s="8"/>
-      <c r="S55" s="8"/>
-      <c r="T55" s="8"/>
-      <c r="U55" s="8"/>
-      <c r="V55" s="8"/>
-      <c r="W55" s="8"/>
-      <c r="X55" s="8"/>
-      <c r="Y55" s="8"/>
-      <c r="Z55" s="2"/>
+      <c r="F55" s="9"/>
+      <c r="G55" s="9"/>
+      <c r="H55" s="9"/>
+      <c r="I55" s="9"/>
+      <c r="J55" s="9"/>
+      <c r="K55" s="9"/>
+      <c r="L55" s="9"/>
+      <c r="M55" s="9"/>
+      <c r="N55" s="9"/>
+      <c r="O55" s="9"/>
+      <c r="P55" s="9"/>
+      <c r="Q55" s="9"/>
+      <c r="R55" s="9"/>
+      <c r="S55" s="9"/>
+      <c r="T55" s="9"/>
+      <c r="U55" s="9"/>
+      <c r="V55" s="9"/>
+      <c r="W55" s="9"/>
+      <c r="X55" s="9"/>
+      <c r="Y55" s="9"/>
+      <c r="Z55" s="10"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="6" t="s">
+      <c r="A56" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="B56" s="7">
+      <c r="B56" s="8">
         <v>0.0</v>
       </c>
-      <c r="C56" s="8" t="s">
+      <c r="C56" s="13" t="s">
         <v>220</v>
       </c>
-      <c r="D56" s="8" t="s">
+      <c r="D56" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="E56" s="8" t="s">
+      <c r="E56" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="F56" s="8"/>
-      <c r="G56" s="8"/>
-      <c r="H56" s="8"/>
-      <c r="I56" s="8"/>
-      <c r="J56" s="8"/>
-      <c r="K56" s="8"/>
-      <c r="L56" s="8"/>
-      <c r="M56" s="8"/>
-      <c r="N56" s="8"/>
-      <c r="O56" s="8"/>
-      <c r="P56" s="8"/>
-      <c r="Q56" s="8"/>
-      <c r="R56" s="8"/>
-      <c r="S56" s="8"/>
-      <c r="T56" s="8"/>
-      <c r="U56" s="8"/>
-      <c r="V56" s="8"/>
-      <c r="W56" s="8"/>
-      <c r="X56" s="8"/>
-      <c r="Y56" s="8"/>
-      <c r="Z56" s="2"/>
+      <c r="F56" s="9"/>
+      <c r="G56" s="9"/>
+      <c r="H56" s="9"/>
+      <c r="I56" s="9"/>
+      <c r="J56" s="9"/>
+      <c r="K56" s="9"/>
+      <c r="L56" s="9"/>
+      <c r="M56" s="9"/>
+      <c r="N56" s="9"/>
+      <c r="O56" s="9"/>
+      <c r="P56" s="9"/>
+      <c r="Q56" s="9"/>
+      <c r="R56" s="9"/>
+      <c r="S56" s="9"/>
+      <c r="T56" s="9"/>
+      <c r="U56" s="9"/>
+      <c r="V56" s="9"/>
+      <c r="W56" s="9"/>
+      <c r="X56" s="9"/>
+      <c r="Y56" s="9"/>
+      <c r="Z56" s="10"/>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="6" t="s">
+      <c r="A57" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="B57" s="7">
+      <c r="B57" s="8">
         <v>0.0</v>
       </c>
-      <c r="C57" s="8" t="s">
+      <c r="C57" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="D57" s="8" t="s">
+      <c r="D57" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="E57" s="8" t="s">
+      <c r="E57" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="F57" s="8"/>
-      <c r="G57" s="8"/>
-      <c r="H57" s="8"/>
-      <c r="I57" s="8"/>
-      <c r="J57" s="8"/>
-      <c r="K57" s="8"/>
-      <c r="L57" s="8"/>
-      <c r="M57" s="8"/>
-      <c r="N57" s="8"/>
-      <c r="O57" s="8"/>
-      <c r="P57" s="8"/>
-      <c r="Q57" s="8"/>
-      <c r="R57" s="8"/>
-      <c r="S57" s="8"/>
-      <c r="T57" s="8"/>
-      <c r="U57" s="8"/>
-      <c r="V57" s="8"/>
-      <c r="W57" s="8"/>
-      <c r="X57" s="8"/>
-      <c r="Y57" s="8"/>
-      <c r="Z57" s="2"/>
+      <c r="F57" s="9"/>
+      <c r="G57" s="9"/>
+      <c r="H57" s="9"/>
+      <c r="I57" s="9"/>
+      <c r="J57" s="9"/>
+      <c r="K57" s="9"/>
+      <c r="L57" s="9"/>
+      <c r="M57" s="9"/>
+      <c r="N57" s="9"/>
+      <c r="O57" s="9"/>
+      <c r="P57" s="9"/>
+      <c r="Q57" s="9"/>
+      <c r="R57" s="9"/>
+      <c r="S57" s="9"/>
+      <c r="T57" s="9"/>
+      <c r="U57" s="9"/>
+      <c r="V57" s="9"/>
+      <c r="W57" s="9"/>
+      <c r="X57" s="9"/>
+      <c r="Y57" s="9"/>
+      <c r="Z57" s="10"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="6" t="s">
+      <c r="A58" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="B58" s="7">
+      <c r="B58" s="8">
         <v>0.0</v>
       </c>
-      <c r="C58" s="8" t="s">
+      <c r="C58" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="D58" s="8" t="s">
+      <c r="D58" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="E58" s="8" t="s">
+      <c r="E58" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="F58" s="8"/>
-      <c r="G58" s="8"/>
-      <c r="H58" s="8"/>
-      <c r="I58" s="8"/>
-      <c r="J58" s="8"/>
-      <c r="K58" s="8"/>
-      <c r="L58" s="8"/>
-      <c r="M58" s="8"/>
-      <c r="N58" s="8"/>
-      <c r="O58" s="8"/>
-      <c r="P58" s="8"/>
-      <c r="Q58" s="8"/>
-      <c r="R58" s="8"/>
-      <c r="S58" s="8"/>
-      <c r="T58" s="8"/>
-      <c r="U58" s="8"/>
-      <c r="V58" s="8"/>
-      <c r="W58" s="8"/>
-      <c r="X58" s="8"/>
-      <c r="Y58" s="8"/>
-      <c r="Z58" s="2"/>
+      <c r="F58" s="9"/>
+      <c r="G58" s="9"/>
+      <c r="H58" s="9"/>
+      <c r="I58" s="9"/>
+      <c r="J58" s="9"/>
+      <c r="K58" s="9"/>
+      <c r="L58" s="9"/>
+      <c r="M58" s="9"/>
+      <c r="N58" s="9"/>
+      <c r="O58" s="9"/>
+      <c r="P58" s="9"/>
+      <c r="Q58" s="9"/>
+      <c r="R58" s="9"/>
+      <c r="S58" s="9"/>
+      <c r="T58" s="9"/>
+      <c r="U58" s="9"/>
+      <c r="V58" s="9"/>
+      <c r="W58" s="9"/>
+      <c r="X58" s="9"/>
+      <c r="Y58" s="9"/>
+      <c r="Z58" s="10"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="6" t="s">
+      <c r="A59" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="B59" s="7">
+      <c r="B59" s="8">
         <v>0.0</v>
       </c>
-      <c r="C59" s="8" t="s">
+      <c r="C59" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="D59" s="8" t="s">
+      <c r="D59" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="E59" s="8" t="s">
+      <c r="E59" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="F59" s="8"/>
-      <c r="G59" s="8"/>
-      <c r="H59" s="8"/>
-      <c r="I59" s="8"/>
-      <c r="J59" s="8"/>
-      <c r="K59" s="8"/>
-      <c r="L59" s="8"/>
-      <c r="M59" s="8"/>
-      <c r="N59" s="8"/>
-      <c r="O59" s="8"/>
-      <c r="P59" s="8"/>
-      <c r="Q59" s="8"/>
-      <c r="R59" s="8"/>
-      <c r="S59" s="8"/>
-      <c r="T59" s="8"/>
-      <c r="U59" s="8"/>
-      <c r="V59" s="8"/>
-      <c r="W59" s="8"/>
-      <c r="X59" s="8"/>
-      <c r="Y59" s="8"/>
-      <c r="Z59" s="2"/>
+      <c r="F59" s="9"/>
+      <c r="G59" s="9"/>
+      <c r="H59" s="9"/>
+      <c r="I59" s="9"/>
+      <c r="J59" s="9"/>
+      <c r="K59" s="9"/>
+      <c r="L59" s="9"/>
+      <c r="M59" s="9"/>
+      <c r="N59" s="9"/>
+      <c r="O59" s="9"/>
+      <c r="P59" s="9"/>
+      <c r="Q59" s="9"/>
+      <c r="R59" s="9"/>
+      <c r="S59" s="9"/>
+      <c r="T59" s="9"/>
+      <c r="U59" s="9"/>
+      <c r="V59" s="9"/>
+      <c r="W59" s="9"/>
+      <c r="X59" s="9"/>
+      <c r="Y59" s="9"/>
+      <c r="Z59" s="10"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="6" t="s">
+      <c r="A60" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="B60" s="7">
+      <c r="B60" s="12">
         <v>0.0</v>
       </c>
-      <c r="C60" s="8" t="s">
+      <c r="C60" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="D60" s="8" t="s">
+      <c r="D60" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="E60" s="8" t="s">
+      <c r="E60" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="F60" s="8"/>
-      <c r="G60" s="8"/>
-      <c r="H60" s="8"/>
-      <c r="I60" s="8"/>
-      <c r="J60" s="8"/>
-      <c r="K60" s="8"/>
-      <c r="L60" s="8"/>
-      <c r="M60" s="8"/>
-      <c r="N60" s="8"/>
-      <c r="O60" s="8"/>
-      <c r="P60" s="8"/>
-      <c r="Q60" s="8"/>
-      <c r="R60" s="8"/>
-      <c r="S60" s="8"/>
-      <c r="T60" s="8"/>
-      <c r="U60" s="8"/>
-      <c r="V60" s="8"/>
-      <c r="W60" s="8"/>
-      <c r="X60" s="8"/>
-      <c r="Y60" s="8"/>
-      <c r="Z60" s="2"/>
+      <c r="F60" s="9"/>
+      <c r="G60" s="9"/>
+      <c r="H60" s="9"/>
+      <c r="I60" s="9"/>
+      <c r="J60" s="9"/>
+      <c r="K60" s="9"/>
+      <c r="L60" s="9"/>
+      <c r="M60" s="9"/>
+      <c r="N60" s="9"/>
+      <c r="O60" s="9"/>
+      <c r="P60" s="9"/>
+      <c r="Q60" s="9"/>
+      <c r="R60" s="9"/>
+      <c r="S60" s="9"/>
+      <c r="T60" s="9"/>
+      <c r="U60" s="9"/>
+      <c r="V60" s="9"/>
+      <c r="W60" s="9"/>
+      <c r="X60" s="9"/>
+      <c r="Y60" s="9"/>
+      <c r="Z60" s="10"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="6" t="s">
+      <c r="A61" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="B61" s="7">
+      <c r="B61" s="8">
         <v>0.0</v>
       </c>
-      <c r="C61" s="8" t="s">
+      <c r="C61" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="D61" s="8" t="s">
+      <c r="D61" s="9" t="s">
         <v>241</v>
       </c>
-      <c r="E61" s="8" t="s">
+      <c r="E61" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="F61" s="8"/>
-      <c r="G61" s="8"/>
-      <c r="H61" s="8"/>
-      <c r="I61" s="8"/>
-      <c r="J61" s="8"/>
-      <c r="K61" s="8"/>
-      <c r="L61" s="8"/>
-      <c r="M61" s="8"/>
-      <c r="N61" s="8"/>
-      <c r="O61" s="8"/>
-      <c r="P61" s="8"/>
-      <c r="Q61" s="8"/>
-      <c r="R61" s="8"/>
-      <c r="S61" s="8"/>
-      <c r="T61" s="8"/>
-      <c r="U61" s="8"/>
-      <c r="V61" s="8"/>
-      <c r="W61" s="8"/>
-      <c r="X61" s="8"/>
-      <c r="Y61" s="8"/>
-      <c r="Z61" s="2"/>
+      <c r="F61" s="9"/>
+      <c r="G61" s="9"/>
+      <c r="H61" s="9"/>
+      <c r="I61" s="9"/>
+      <c r="J61" s="9"/>
+      <c r="K61" s="9"/>
+      <c r="L61" s="9"/>
+      <c r="M61" s="9"/>
+      <c r="N61" s="9"/>
+      <c r="O61" s="9"/>
+      <c r="P61" s="9"/>
+      <c r="Q61" s="9"/>
+      <c r="R61" s="9"/>
+      <c r="S61" s="9"/>
+      <c r="T61" s="9"/>
+      <c r="U61" s="9"/>
+      <c r="V61" s="9"/>
+      <c r="W61" s="9"/>
+      <c r="X61" s="9"/>
+      <c r="Y61" s="9"/>
+      <c r="Z61" s="10"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="6" t="s">
+      <c r="A62" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="B62" s="7">
+      <c r="B62" s="8">
         <v>0.0</v>
       </c>
-      <c r="C62" s="8" t="s">
+      <c r="C62" s="13" t="s">
         <v>244</v>
       </c>
-      <c r="D62" s="8" t="s">
+      <c r="D62" s="9" t="s">
         <v>245</v>
       </c>
-      <c r="E62" s="8" t="s">
+      <c r="E62" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="F62" s="8"/>
-      <c r="G62" s="8"/>
-      <c r="H62" s="8"/>
-      <c r="I62" s="8"/>
-      <c r="J62" s="8"/>
-      <c r="K62" s="8"/>
-      <c r="L62" s="8"/>
-      <c r="M62" s="8"/>
-      <c r="N62" s="8"/>
-      <c r="O62" s="8"/>
-      <c r="P62" s="8"/>
-      <c r="Q62" s="8"/>
-      <c r="R62" s="8"/>
-      <c r="S62" s="8"/>
-      <c r="T62" s="8"/>
-      <c r="U62" s="8"/>
-      <c r="V62" s="8"/>
-      <c r="W62" s="8"/>
-      <c r="X62" s="8"/>
-      <c r="Y62" s="8"/>
-      <c r="Z62" s="2"/>
+      <c r="F62" s="9"/>
+      <c r="G62" s="9"/>
+      <c r="H62" s="9"/>
+      <c r="I62" s="9"/>
+      <c r="J62" s="9"/>
+      <c r="K62" s="9"/>
+      <c r="L62" s="9"/>
+      <c r="M62" s="9"/>
+      <c r="N62" s="9"/>
+      <c r="O62" s="9"/>
+      <c r="P62" s="9"/>
+      <c r="Q62" s="9"/>
+      <c r="R62" s="9"/>
+      <c r="S62" s="9"/>
+      <c r="T62" s="9"/>
+      <c r="U62" s="9"/>
+      <c r="V62" s="9"/>
+      <c r="W62" s="9"/>
+      <c r="X62" s="9"/>
+      <c r="Y62" s="9"/>
+      <c r="Z62" s="10"/>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="6" t="s">
+      <c r="A63" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="B63" s="7">
+      <c r="B63" s="8">
         <v>0.0</v>
       </c>
-      <c r="C63" s="8" t="s">
+      <c r="C63" s="13" t="s">
         <v>248</v>
       </c>
-      <c r="D63" s="8" t="s">
+      <c r="D63" s="9" t="s">
         <v>249</v>
       </c>
-      <c r="E63" s="8" t="s">
+      <c r="E63" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="F63" s="8"/>
-      <c r="G63" s="8"/>
-      <c r="H63" s="8"/>
-      <c r="I63" s="8"/>
-      <c r="J63" s="8"/>
-      <c r="K63" s="8"/>
-      <c r="L63" s="8"/>
-      <c r="M63" s="8"/>
-      <c r="N63" s="8"/>
-      <c r="O63" s="8"/>
-      <c r="P63" s="8"/>
-      <c r="Q63" s="8"/>
-      <c r="R63" s="8"/>
-      <c r="S63" s="8"/>
-      <c r="T63" s="8"/>
-      <c r="U63" s="8"/>
-      <c r="V63" s="8"/>
-      <c r="W63" s="8"/>
-      <c r="X63" s="8"/>
-      <c r="Y63" s="8"/>
-      <c r="Z63" s="2"/>
+      <c r="F63" s="9"/>
+      <c r="G63" s="9"/>
+      <c r="H63" s="9"/>
+      <c r="I63" s="9"/>
+      <c r="J63" s="9"/>
+      <c r="K63" s="9"/>
+      <c r="L63" s="9"/>
+      <c r="M63" s="9"/>
+      <c r="N63" s="9"/>
+      <c r="O63" s="9"/>
+      <c r="P63" s="9"/>
+      <c r="Q63" s="9"/>
+      <c r="R63" s="9"/>
+      <c r="S63" s="9"/>
+      <c r="T63" s="9"/>
+      <c r="U63" s="9"/>
+      <c r="V63" s="9"/>
+      <c r="W63" s="9"/>
+      <c r="X63" s="9"/>
+      <c r="Y63" s="9"/>
+      <c r="Z63" s="10"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="13" t="s">
+      <c r="A64" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="B64" s="1">
+      <c r="B64" s="8">
         <v>0.0</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C64" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="D64" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="E64" s="1" t="s">
+      <c r="E64" s="9" t="s">
         <v>254</v>
       </c>
-      <c r="F64" s="1"/>
-      <c r="G64" s="1"/>
-      <c r="H64" s="1"/>
-      <c r="I64" s="1"/>
-      <c r="J64" s="1"/>
-      <c r="K64" s="1"/>
-      <c r="L64" s="1"/>
-      <c r="M64" s="1"/>
-      <c r="N64" s="1"/>
-      <c r="O64" s="1"/>
-      <c r="P64" s="1"/>
-      <c r="Q64" s="1"/>
-      <c r="R64" s="1"/>
-      <c r="S64" s="1"/>
-      <c r="T64" s="1"/>
-      <c r="U64" s="1"/>
-      <c r="V64" s="1"/>
-      <c r="W64" s="1"/>
-      <c r="X64" s="1"/>
-      <c r="Y64" s="1"/>
-      <c r="Z64" s="2"/>
+      <c r="F64" s="9"/>
+      <c r="G64" s="9"/>
+      <c r="H64" s="9"/>
+      <c r="I64" s="9"/>
+      <c r="J64" s="9"/>
+      <c r="K64" s="9"/>
+      <c r="L64" s="9"/>
+      <c r="M64" s="9"/>
+      <c r="N64" s="9"/>
+      <c r="O64" s="9"/>
+      <c r="P64" s="9"/>
+      <c r="Q64" s="9"/>
+      <c r="R64" s="9"/>
+      <c r="S64" s="9"/>
+      <c r="T64" s="9"/>
+      <c r="U64" s="9"/>
+      <c r="V64" s="9"/>
+      <c r="W64" s="9"/>
+      <c r="X64" s="9"/>
+      <c r="Y64" s="9"/>
+      <c r="Z64" s="10"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="14" t="s">
+      <c r="A65" s="16" t="s">
         <v>255</v>
       </c>
       <c r="B65" s="1">
         <v>0.0</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C65" s="17" t="s">
         <v>256</v>
       </c>
       <c r="D65" s="1" t="s">
@@ -3796,16 +3817,16 @@
       <c r="W65" s="1"/>
       <c r="X65" s="1"/>
       <c r="Y65" s="1"/>
-      <c r="Z65" s="2"/>
+      <c r="Z65" s="10"/>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="13" t="s">
+      <c r="A66" s="16" t="s">
         <v>259</v>
       </c>
       <c r="B66" s="1">
         <v>0.0</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C66" s="17" t="s">
         <v>260</v>
       </c>
       <c r="D66" s="1" t="s">
@@ -3834,251 +3855,251 @@
       <c r="W66" s="1"/>
       <c r="X66" s="1"/>
       <c r="Y66" s="1"/>
-      <c r="Z66" s="2"/>
+      <c r="Z66" s="10"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="6" t="s">
+      <c r="A67" s="16" t="s">
         <v>263</v>
       </c>
-      <c r="B67" s="7">
+      <c r="B67" s="1">
         <v>0.0</v>
       </c>
-      <c r="C67" s="8" t="s">
+      <c r="C67" s="17" t="s">
         <v>264</v>
       </c>
-      <c r="D67" s="8" t="s">
+      <c r="D67" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="E67" s="8" t="s">
+      <c r="E67" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="F67" s="8"/>
-      <c r="G67" s="8"/>
-      <c r="H67" s="8"/>
-      <c r="I67" s="8"/>
-      <c r="J67" s="8"/>
-      <c r="K67" s="8"/>
-      <c r="L67" s="8"/>
-      <c r="M67" s="8"/>
-      <c r="N67" s="8"/>
-      <c r="O67" s="8"/>
-      <c r="P67" s="8"/>
-      <c r="Q67" s="8"/>
-      <c r="R67" s="8"/>
-      <c r="S67" s="8"/>
-      <c r="T67" s="8"/>
-      <c r="U67" s="8"/>
-      <c r="V67" s="8"/>
-      <c r="W67" s="8"/>
-      <c r="X67" s="8"/>
-      <c r="Y67" s="8"/>
-      <c r="Z67" s="2"/>
+      <c r="F67" s="1"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1"/>
+      <c r="J67" s="1"/>
+      <c r="K67" s="1"/>
+      <c r="L67" s="1"/>
+      <c r="M67" s="1"/>
+      <c r="N67" s="1"/>
+      <c r="O67" s="1"/>
+      <c r="P67" s="1"/>
+      <c r="Q67" s="1"/>
+      <c r="R67" s="1"/>
+      <c r="S67" s="1"/>
+      <c r="T67" s="1"/>
+      <c r="U67" s="1"/>
+      <c r="V67" s="1"/>
+      <c r="W67" s="1"/>
+      <c r="X67" s="1"/>
+      <c r="Y67" s="1"/>
+      <c r="Z67" s="10"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="6" t="s">
+      <c r="A68" s="16" t="s">
         <v>267</v>
       </c>
-      <c r="B68" s="7">
+      <c r="B68" s="1">
         <v>0.0</v>
       </c>
-      <c r="C68" s="8" t="s">
+      <c r="C68" s="17" t="s">
         <v>268</v>
       </c>
-      <c r="D68" s="8" t="s">
+      <c r="D68" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="E68" s="8" t="s">
+      <c r="E68" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="F68" s="8"/>
-      <c r="G68" s="8"/>
-      <c r="H68" s="8"/>
-      <c r="I68" s="8"/>
-      <c r="J68" s="8"/>
-      <c r="K68" s="8"/>
-      <c r="L68" s="8"/>
-      <c r="M68" s="8"/>
-      <c r="N68" s="8"/>
-      <c r="O68" s="8"/>
-      <c r="P68" s="8"/>
-      <c r="Q68" s="8"/>
-      <c r="R68" s="8"/>
-      <c r="S68" s="8"/>
-      <c r="T68" s="8"/>
-      <c r="U68" s="8"/>
-      <c r="V68" s="8"/>
-      <c r="W68" s="8"/>
-      <c r="X68" s="8"/>
-      <c r="Y68" s="8"/>
-      <c r="Z68" s="2"/>
+      <c r="F68" s="1"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+      <c r="J68" s="1"/>
+      <c r="K68" s="1"/>
+      <c r="L68" s="1"/>
+      <c r="M68" s="1"/>
+      <c r="N68" s="1"/>
+      <c r="O68" s="1"/>
+      <c r="P68" s="1"/>
+      <c r="Q68" s="1"/>
+      <c r="R68" s="1"/>
+      <c r="S68" s="1"/>
+      <c r="T68" s="1"/>
+      <c r="U68" s="1"/>
+      <c r="V68" s="1"/>
+      <c r="W68" s="1"/>
+      <c r="X68" s="1"/>
+      <c r="Y68" s="1"/>
+      <c r="Z68" s="10"/>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="6" t="s">
+      <c r="A69" s="16" t="s">
         <v>271</v>
       </c>
-      <c r="B69" s="7">
+      <c r="B69" s="1">
         <v>0.0</v>
       </c>
-      <c r="C69" s="8" t="s">
+      <c r="C69" s="17" t="s">
         <v>272</v>
       </c>
-      <c r="D69" s="8" t="s">
+      <c r="D69" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="E69" s="8" t="s">
+      <c r="E69" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="F69" s="8"/>
-      <c r="G69" s="8"/>
-      <c r="H69" s="8"/>
-      <c r="I69" s="8"/>
-      <c r="J69" s="8"/>
-      <c r="K69" s="8"/>
-      <c r="L69" s="8"/>
-      <c r="M69" s="8"/>
-      <c r="N69" s="8"/>
-      <c r="O69" s="8"/>
-      <c r="P69" s="8"/>
-      <c r="Q69" s="8"/>
-      <c r="R69" s="8"/>
-      <c r="S69" s="8"/>
-      <c r="T69" s="8"/>
-      <c r="U69" s="8"/>
-      <c r="V69" s="8"/>
-      <c r="W69" s="8"/>
-      <c r="X69" s="8"/>
-      <c r="Y69" s="8"/>
-      <c r="Z69" s="2"/>
+      <c r="F69" s="1"/>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+      <c r="J69" s="1"/>
+      <c r="K69" s="1"/>
+      <c r="L69" s="1"/>
+      <c r="M69" s="1"/>
+      <c r="N69" s="1"/>
+      <c r="O69" s="1"/>
+      <c r="P69" s="1"/>
+      <c r="Q69" s="1"/>
+      <c r="R69" s="1"/>
+      <c r="S69" s="1"/>
+      <c r="T69" s="1"/>
+      <c r="U69" s="1"/>
+      <c r="V69" s="1"/>
+      <c r="W69" s="1"/>
+      <c r="X69" s="1"/>
+      <c r="Y69" s="1"/>
+      <c r="Z69" s="10"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="6" t="s">
+      <c r="A70" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="B70" s="7">
+      <c r="B70" s="8">
         <v>0.0</v>
       </c>
-      <c r="C70" s="8" t="s">
+      <c r="C70" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="D70" s="8" t="s">
+      <c r="D70" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="E70" s="8" t="s">
+      <c r="E70" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="F70" s="8"/>
-      <c r="G70" s="8"/>
-      <c r="H70" s="8"/>
-      <c r="I70" s="8"/>
-      <c r="J70" s="8"/>
-      <c r="K70" s="8"/>
-      <c r="L70" s="8"/>
-      <c r="M70" s="8"/>
-      <c r="N70" s="8"/>
-      <c r="O70" s="8"/>
-      <c r="P70" s="8"/>
-      <c r="Q70" s="8"/>
-      <c r="R70" s="8"/>
-      <c r="S70" s="8"/>
-      <c r="T70" s="8"/>
-      <c r="U70" s="8"/>
-      <c r="V70" s="8"/>
-      <c r="W70" s="8"/>
-      <c r="X70" s="8"/>
-      <c r="Y70" s="8"/>
-      <c r="Z70" s="2"/>
+      <c r="F70" s="9"/>
+      <c r="G70" s="9"/>
+      <c r="H70" s="9"/>
+      <c r="I70" s="9"/>
+      <c r="J70" s="9"/>
+      <c r="K70" s="9"/>
+      <c r="L70" s="9"/>
+      <c r="M70" s="9"/>
+      <c r="N70" s="9"/>
+      <c r="O70" s="9"/>
+      <c r="P70" s="9"/>
+      <c r="Q70" s="9"/>
+      <c r="R70" s="9"/>
+      <c r="S70" s="9"/>
+      <c r="T70" s="9"/>
+      <c r="U70" s="9"/>
+      <c r="V70" s="9"/>
+      <c r="W70" s="9"/>
+      <c r="X70" s="9"/>
+      <c r="Y70" s="9"/>
+      <c r="Z70" s="10"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="6" t="s">
+      <c r="A71" s="11" t="s">
         <v>279</v>
       </c>
-      <c r="B71" s="7">
+      <c r="B71" s="8">
         <v>0.0</v>
       </c>
-      <c r="C71" s="8" t="s">
+      <c r="C71" s="13" t="s">
         <v>280</v>
       </c>
-      <c r="D71" s="8" t="s">
+      <c r="D71" s="9" t="s">
         <v>281</v>
       </c>
-      <c r="E71" s="8" t="s">
+      <c r="E71" s="9" t="s">
         <v>282</v>
       </c>
-      <c r="F71" s="8"/>
-      <c r="G71" s="8"/>
-      <c r="H71" s="8"/>
-      <c r="I71" s="8"/>
-      <c r="J71" s="8"/>
-      <c r="K71" s="8"/>
-      <c r="L71" s="8"/>
-      <c r="M71" s="8"/>
-      <c r="N71" s="8"/>
-      <c r="O71" s="8"/>
-      <c r="P71" s="8"/>
-      <c r="Q71" s="8"/>
-      <c r="R71" s="8"/>
-      <c r="S71" s="8"/>
-      <c r="T71" s="8"/>
-      <c r="U71" s="8"/>
-      <c r="V71" s="8"/>
-      <c r="W71" s="8"/>
-      <c r="X71" s="8"/>
-      <c r="Y71" s="8"/>
-      <c r="Z71" s="2"/>
+      <c r="F71" s="9"/>
+      <c r="G71" s="9"/>
+      <c r="H71" s="9"/>
+      <c r="I71" s="9"/>
+      <c r="J71" s="9"/>
+      <c r="K71" s="9"/>
+      <c r="L71" s="9"/>
+      <c r="M71" s="9"/>
+      <c r="N71" s="9"/>
+      <c r="O71" s="9"/>
+      <c r="P71" s="9"/>
+      <c r="Q71" s="9"/>
+      <c r="R71" s="9"/>
+      <c r="S71" s="9"/>
+      <c r="T71" s="9"/>
+      <c r="U71" s="9"/>
+      <c r="V71" s="9"/>
+      <c r="W71" s="9"/>
+      <c r="X71" s="9"/>
+      <c r="Y71" s="9"/>
+      <c r="Z71" s="10"/>
     </row>
     <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="15" t="s">
+      <c r="A72" s="18" t="s">
         <v>283</v>
       </c>
-      <c r="B72" s="16">
+      <c r="B72" s="1">
         <v>0.0</v>
       </c>
       <c r="C72" s="17" t="s">
         <v>284</v>
       </c>
-      <c r="D72" s="17" t="s">
+      <c r="D72" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="E72" s="17" t="s">
+      <c r="E72" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="F72" s="17"/>
-      <c r="G72" s="17"/>
-      <c r="H72" s="17"/>
-      <c r="I72" s="17"/>
-      <c r="J72" s="17"/>
-      <c r="K72" s="17"/>
-      <c r="L72" s="17"/>
-      <c r="M72" s="17"/>
-      <c r="N72" s="17"/>
-      <c r="O72" s="17"/>
-      <c r="P72" s="17"/>
-      <c r="Q72" s="17"/>
-      <c r="R72" s="17"/>
-      <c r="S72" s="17"/>
-      <c r="T72" s="17"/>
-      <c r="U72" s="17"/>
-      <c r="V72" s="17"/>
-      <c r="W72" s="17"/>
-      <c r="X72" s="17"/>
-      <c r="Y72" s="17"/>
-      <c r="Z72" s="2"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1"/>
+      <c r="J72" s="1"/>
+      <c r="K72" s="1"/>
+      <c r="L72" s="1"/>
+      <c r="M72" s="1"/>
+      <c r="N72" s="1"/>
+      <c r="O72" s="1"/>
+      <c r="P72" s="1"/>
+      <c r="Q72" s="1"/>
+      <c r="R72" s="1"/>
+      <c r="S72" s="1"/>
+      <c r="T72" s="1"/>
+      <c r="U72" s="1"/>
+      <c r="V72" s="1"/>
+      <c r="W72" s="1"/>
+      <c r="X72" s="1"/>
+      <c r="Y72" s="1"/>
+      <c r="Z72" s="10"/>
     </row>
     <row r="73" ht="15.0" customHeight="1">
-      <c r="A73" s="13" t="s">
+      <c r="A73" s="16" t="s">
         <v>287</v>
       </c>
       <c r="B73" s="1">
         <v>0.0</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="C73" s="17" t="s">
         <v>288</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>151</v>
+        <v>289</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>152</v>
+        <v>290</v>
       </c>
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
@@ -4100,23 +4121,23 @@
       <c r="W73" s="1"/>
       <c r="X73" s="1"/>
       <c r="Y73" s="1"/>
-      <c r="Z73" s="2"/>
+      <c r="Z73" s="10"/>
     </row>
     <row r="74" ht="15.0" customHeight="1">
-      <c r="A74" s="13" t="s">
-        <v>289</v>
+      <c r="A74" s="18" t="s">
+        <v>291</v>
       </c>
       <c r="B74" s="1">
         <v>0.0</v>
       </c>
-      <c r="C74" s="1" t="s">
-        <v>290</v>
+      <c r="C74" s="17" t="s">
+        <v>292</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
@@ -4138,348 +4159,318 @@
       <c r="W74" s="1"/>
       <c r="X74" s="1"/>
       <c r="Y74" s="1"/>
-      <c r="Z74" s="2"/>
+      <c r="Z74" s="10"/>
     </row>
     <row r="75" ht="15.0" customHeight="1">
-      <c r="A75" s="13" t="s">
-        <v>293</v>
-      </c>
-      <c r="B75" s="1">
+      <c r="A75" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="B75" s="8">
         <v>0.0</v>
       </c>
-      <c r="C75" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="F75" s="1"/>
-      <c r="G75" s="1"/>
-      <c r="H75" s="1"/>
-      <c r="I75" s="1"/>
-      <c r="J75" s="1"/>
-      <c r="K75" s="1"/>
-      <c r="L75" s="1"/>
-      <c r="M75" s="1"/>
-      <c r="N75" s="1"/>
-      <c r="O75" s="1"/>
-      <c r="P75" s="1"/>
-      <c r="Q75" s="1"/>
-      <c r="R75" s="1"/>
-      <c r="S75" s="1"/>
-      <c r="T75" s="1"/>
-      <c r="U75" s="1"/>
-      <c r="V75" s="1"/>
-      <c r="W75" s="1"/>
-      <c r="X75" s="1"/>
-      <c r="Y75" s="1"/>
-      <c r="Z75" s="2"/>
+      <c r="C75" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="D75" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="E75" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="F75" s="9"/>
+      <c r="G75" s="9"/>
+      <c r="H75" s="9"/>
+      <c r="I75" s="9"/>
+      <c r="J75" s="9"/>
+      <c r="K75" s="9"/>
+      <c r="L75" s="9"/>
+      <c r="M75" s="9"/>
+      <c r="N75" s="9"/>
+      <c r="O75" s="9"/>
+      <c r="P75" s="9"/>
+      <c r="Q75" s="9"/>
+      <c r="R75" s="9"/>
+      <c r="S75" s="9"/>
+      <c r="T75" s="9"/>
+      <c r="U75" s="9"/>
+      <c r="V75" s="9"/>
+      <c r="W75" s="9"/>
+      <c r="X75" s="9"/>
+      <c r="Y75" s="9"/>
+      <c r="Z75" s="10"/>
     </row>
     <row r="76" ht="15.0" customHeight="1">
-      <c r="A76" s="13" t="s">
-        <v>295</v>
-      </c>
-      <c r="B76" s="1">
+      <c r="A76" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="B76" s="8">
         <v>0.0</v>
       </c>
-      <c r="C76" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="F76" s="1"/>
-      <c r="G76" s="1"/>
-      <c r="H76" s="1"/>
-      <c r="I76" s="1"/>
-      <c r="J76" s="1"/>
-      <c r="K76" s="1"/>
-      <c r="L76" s="1"/>
-      <c r="M76" s="1"/>
-      <c r="N76" s="1"/>
-      <c r="O76" s="1"/>
-      <c r="P76" s="1"/>
-      <c r="Q76" s="1"/>
-      <c r="R76" s="1"/>
-      <c r="S76" s="1"/>
-      <c r="T76" s="1"/>
-      <c r="U76" s="1"/>
-      <c r="V76" s="1"/>
-      <c r="W76" s="1"/>
-      <c r="X76" s="1"/>
-      <c r="Y76" s="1"/>
-      <c r="Z76" s="2"/>
+      <c r="C76" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="D76" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="E76" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="F76" s="9"/>
+      <c r="G76" s="9"/>
+      <c r="H76" s="9"/>
+      <c r="I76" s="9"/>
+      <c r="J76" s="9"/>
+      <c r="K76" s="9"/>
+      <c r="L76" s="9"/>
+      <c r="M76" s="9"/>
+      <c r="N76" s="9"/>
+      <c r="O76" s="9"/>
+      <c r="P76" s="9"/>
+      <c r="Q76" s="9"/>
+      <c r="R76" s="9"/>
+      <c r="S76" s="9"/>
+      <c r="T76" s="9"/>
+      <c r="U76" s="9"/>
+      <c r="V76" s="9"/>
+      <c r="W76" s="9"/>
+      <c r="X76" s="9"/>
+      <c r="Y76" s="9"/>
+      <c r="Z76" s="10"/>
     </row>
     <row r="77" ht="15.0" customHeight="1">
-      <c r="A77" s="13" t="s">
-        <v>299</v>
-      </c>
-      <c r="B77" s="1">
+      <c r="A77" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="B77" s="8">
         <v>0.0</v>
       </c>
-      <c r="C77" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="F77" s="1"/>
-      <c r="G77" s="1"/>
-      <c r="H77" s="1"/>
-      <c r="I77" s="1"/>
-      <c r="J77" s="1"/>
-      <c r="K77" s="1"/>
-      <c r="L77" s="1"/>
-      <c r="M77" s="1"/>
-      <c r="N77" s="1"/>
-      <c r="O77" s="1"/>
-      <c r="P77" s="1"/>
-      <c r="Q77" s="1"/>
-      <c r="R77" s="1"/>
-      <c r="S77" s="1"/>
-      <c r="T77" s="1"/>
-      <c r="U77" s="1"/>
-      <c r="V77" s="1"/>
-      <c r="W77" s="1"/>
-      <c r="X77" s="1"/>
-      <c r="Y77" s="1"/>
-      <c r="Z77" s="2"/>
+      <c r="C77" s="13" t="s">
+        <v>304</v>
+      </c>
+      <c r="D77" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="E77" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="F77" s="9"/>
+      <c r="G77" s="9"/>
+      <c r="H77" s="9"/>
+      <c r="I77" s="9"/>
+      <c r="J77" s="9"/>
+      <c r="K77" s="9"/>
+      <c r="L77" s="9"/>
+      <c r="M77" s="9"/>
+      <c r="N77" s="9"/>
+      <c r="O77" s="9"/>
+      <c r="P77" s="9"/>
+      <c r="Q77" s="9"/>
+      <c r="R77" s="9"/>
+      <c r="S77" s="9"/>
+      <c r="T77" s="9"/>
+      <c r="U77" s="9"/>
+      <c r="V77" s="9"/>
+      <c r="W77" s="9"/>
+      <c r="X77" s="9"/>
+      <c r="Y77" s="9"/>
+      <c r="Z77" s="10"/>
     </row>
     <row r="78" ht="15.0" customHeight="1">
-      <c r="A78" s="13" t="s">
-        <v>303</v>
-      </c>
-      <c r="B78" s="1">
+      <c r="A78" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="B78" s="8">
         <v>0.0</v>
       </c>
-      <c r="C78" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="F78" s="1"/>
-      <c r="G78" s="1"/>
-      <c r="H78" s="1"/>
-      <c r="I78" s="1"/>
-      <c r="J78" s="1"/>
-      <c r="K78" s="1"/>
-      <c r="L78" s="1"/>
-      <c r="M78" s="1"/>
-      <c r="N78" s="1"/>
-      <c r="O78" s="1"/>
-      <c r="P78" s="1"/>
-      <c r="Q78" s="1"/>
-      <c r="R78" s="1"/>
-      <c r="S78" s="1"/>
-      <c r="T78" s="1"/>
-      <c r="U78" s="1"/>
-      <c r="V78" s="1"/>
-      <c r="W78" s="1"/>
-      <c r="X78" s="1"/>
-      <c r="Y78" s="1"/>
-      <c r="Z78" s="2"/>
+      <c r="C78" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="D78" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="E78" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="F78" s="9"/>
+      <c r="G78" s="9"/>
+      <c r="H78" s="9"/>
+      <c r="I78" s="9"/>
+      <c r="J78" s="9"/>
+      <c r="K78" s="9"/>
+      <c r="L78" s="9"/>
+      <c r="M78" s="9"/>
+      <c r="N78" s="9"/>
+      <c r="O78" s="9"/>
+      <c r="P78" s="9"/>
+      <c r="Q78" s="9"/>
+      <c r="R78" s="9"/>
+      <c r="S78" s="9"/>
+      <c r="T78" s="9"/>
+      <c r="U78" s="9"/>
+      <c r="V78" s="9"/>
+      <c r="W78" s="9"/>
+      <c r="X78" s="9"/>
+      <c r="Y78" s="9"/>
+      <c r="Z78" s="10"/>
     </row>
     <row r="79" ht="15.0" customHeight="1">
-      <c r="A79" s="13" t="s">
-        <v>307</v>
-      </c>
-      <c r="B79" s="1">
+      <c r="A79" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="B79" s="8">
         <v>0.0</v>
       </c>
-      <c r="C79" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="F79" s="1"/>
-      <c r="G79" s="1"/>
-      <c r="H79" s="1"/>
-      <c r="I79" s="1"/>
-      <c r="J79" s="1"/>
-      <c r="K79" s="1"/>
-      <c r="L79" s="1"/>
-      <c r="M79" s="1"/>
-      <c r="N79" s="1"/>
-      <c r="O79" s="1"/>
-      <c r="P79" s="1"/>
-      <c r="Q79" s="1"/>
-      <c r="R79" s="1"/>
-      <c r="S79" s="1"/>
-      <c r="T79" s="1"/>
-      <c r="U79" s="1"/>
-      <c r="V79" s="1"/>
-      <c r="W79" s="1"/>
-      <c r="X79" s="1"/>
-      <c r="Y79" s="1"/>
-      <c r="Z79" s="2"/>
+      <c r="C79" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D79" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="E79" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="F79" s="9"/>
+      <c r="G79" s="9"/>
+      <c r="H79" s="9"/>
+      <c r="I79" s="9"/>
+      <c r="J79" s="9"/>
+      <c r="K79" s="9"/>
+      <c r="L79" s="9"/>
+      <c r="M79" s="9"/>
+      <c r="N79" s="9"/>
+      <c r="O79" s="9"/>
+      <c r="P79" s="9"/>
+      <c r="Q79" s="9"/>
+      <c r="R79" s="9"/>
+      <c r="S79" s="9"/>
+      <c r="T79" s="9"/>
+      <c r="U79" s="9"/>
+      <c r="V79" s="9"/>
+      <c r="W79" s="9"/>
+      <c r="X79" s="9"/>
+      <c r="Y79" s="9"/>
+      <c r="Z79" s="10"/>
     </row>
     <row r="80" ht="15.0" customHeight="1">
-      <c r="A80" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="B80" s="7">
+      <c r="A80" s="19" t="s">
+        <v>315</v>
+      </c>
+      <c r="B80" s="20">
         <v>0.0</v>
       </c>
-      <c r="C80" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="D80" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="E80" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="F80" s="8"/>
-      <c r="G80" s="8"/>
-      <c r="H80" s="8"/>
-      <c r="I80" s="8"/>
-      <c r="J80" s="8"/>
-      <c r="K80" s="8"/>
-      <c r="L80" s="8"/>
-      <c r="M80" s="8"/>
-      <c r="N80" s="8"/>
-      <c r="O80" s="8"/>
-      <c r="P80" s="8"/>
-      <c r="Q80" s="8"/>
-      <c r="R80" s="8"/>
-      <c r="S80" s="8"/>
-      <c r="T80" s="8"/>
-      <c r="U80" s="8"/>
-      <c r="V80" s="8"/>
-      <c r="W80" s="8"/>
-      <c r="X80" s="8"/>
-      <c r="Y80" s="8"/>
-      <c r="Z80" s="2"/>
+      <c r="C80" s="21" t="s">
+        <v>316</v>
+      </c>
+      <c r="D80" s="22" t="s">
+        <v>317</v>
+      </c>
+      <c r="E80" s="22" t="s">
+        <v>318</v>
+      </c>
+      <c r="F80" s="22"/>
+      <c r="G80" s="22"/>
+      <c r="H80" s="22"/>
+      <c r="I80" s="22"/>
+      <c r="J80" s="22"/>
+      <c r="K80" s="22"/>
+      <c r="L80" s="22"/>
+      <c r="M80" s="22"/>
+      <c r="N80" s="22"/>
+      <c r="O80" s="22"/>
+      <c r="P80" s="22"/>
+      <c r="Q80" s="22"/>
+      <c r="R80" s="22"/>
+      <c r="S80" s="22"/>
+      <c r="T80" s="22"/>
+      <c r="U80" s="22"/>
+      <c r="V80" s="22"/>
+      <c r="W80" s="22"/>
+      <c r="X80" s="22"/>
+      <c r="Y80" s="22"/>
+      <c r="Z80" s="23"/>
     </row>
     <row r="81" ht="15.0" customHeight="1">
-      <c r="A81" s="6" t="s">
-        <v>313</v>
-      </c>
-      <c r="B81" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="C81" s="8" t="s">
-        <v>314</v>
-      </c>
-      <c r="D81" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="E81" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="F81" s="8"/>
-      <c r="G81" s="8"/>
-      <c r="H81" s="8"/>
-      <c r="I81" s="8"/>
-      <c r="J81" s="8"/>
-      <c r="K81" s="8"/>
-      <c r="L81" s="8"/>
-      <c r="M81" s="8"/>
-      <c r="N81" s="8"/>
-      <c r="O81" s="8"/>
-      <c r="P81" s="8"/>
-      <c r="Q81" s="8"/>
-      <c r="R81" s="8"/>
-      <c r="S81" s="8"/>
-      <c r="T81" s="8"/>
-      <c r="U81" s="8"/>
-      <c r="V81" s="8"/>
-      <c r="W81" s="8"/>
-      <c r="X81" s="8"/>
-      <c r="Y81" s="8"/>
+      <c r="A81" s="1"/>
+      <c r="B81" s="1"/>
+      <c r="C81" s="1"/>
+      <c r="D81" s="1"/>
+      <c r="E81" s="1"/>
+      <c r="F81" s="1"/>
+      <c r="G81" s="1"/>
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
+      <c r="J81" s="1"/>
+      <c r="K81" s="1"/>
+      <c r="L81" s="1"/>
+      <c r="M81" s="1"/>
+      <c r="N81" s="1"/>
+      <c r="O81" s="1"/>
+      <c r="P81" s="1"/>
+      <c r="Q81" s="1"/>
+      <c r="R81" s="1"/>
+      <c r="S81" s="1"/>
+      <c r="T81" s="1"/>
+      <c r="U81" s="1"/>
+      <c r="V81" s="1"/>
+      <c r="W81" s="1"/>
+      <c r="X81" s="1"/>
+      <c r="Y81" s="1"/>
       <c r="Z81" s="2"/>
     </row>
     <row r="82" ht="15.0" customHeight="1">
-      <c r="A82" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="B82" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="C82" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D82" s="8" t="s">
-        <v>317</v>
-      </c>
-      <c r="E82" s="8" t="s">
-        <v>318</v>
-      </c>
-      <c r="F82" s="8"/>
-      <c r="G82" s="8"/>
-      <c r="H82" s="8"/>
-      <c r="I82" s="8"/>
-      <c r="J82" s="8"/>
-      <c r="K82" s="8"/>
-      <c r="L82" s="8"/>
-      <c r="M82" s="8"/>
-      <c r="N82" s="8"/>
-      <c r="O82" s="8"/>
-      <c r="P82" s="8"/>
-      <c r="Q82" s="8"/>
-      <c r="R82" s="8"/>
-      <c r="S82" s="8"/>
-      <c r="T82" s="8"/>
-      <c r="U82" s="8"/>
-      <c r="V82" s="8"/>
-      <c r="W82" s="8"/>
-      <c r="X82" s="8"/>
-      <c r="Y82" s="8"/>
+      <c r="A82" s="1"/>
+      <c r="B82" s="1"/>
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="1"/>
+      <c r="H82" s="1"/>
+      <c r="I82" s="1"/>
+      <c r="J82" s="1"/>
+      <c r="K82" s="1"/>
+      <c r="L82" s="1"/>
+      <c r="M82" s="1"/>
+      <c r="N82" s="1"/>
+      <c r="O82" s="1"/>
+      <c r="P82" s="1"/>
+      <c r="Q82" s="1"/>
+      <c r="R82" s="1"/>
+      <c r="S82" s="1"/>
+      <c r="T82" s="1"/>
+      <c r="U82" s="1"/>
+      <c r="V82" s="1"/>
+      <c r="W82" s="1"/>
+      <c r="X82" s="1"/>
+      <c r="Y82" s="1"/>
       <c r="Z82" s="2"/>
     </row>
     <row r="83" ht="15.0" customHeight="1">
-      <c r="A83" s="15" t="s">
-        <v>319</v>
-      </c>
-      <c r="B83" s="16">
-        <v>0.0</v>
-      </c>
-      <c r="C83" s="17" t="s">
-        <v>320</v>
-      </c>
-      <c r="D83" s="17" t="s">
-        <v>321</v>
-      </c>
-      <c r="E83" s="17" t="s">
-        <v>322</v>
-      </c>
-      <c r="F83" s="17"/>
-      <c r="G83" s="17"/>
-      <c r="H83" s="17"/>
-      <c r="I83" s="17"/>
-      <c r="J83" s="17"/>
-      <c r="K83" s="17"/>
-      <c r="L83" s="17"/>
-      <c r="M83" s="17"/>
-      <c r="N83" s="17"/>
-      <c r="O83" s="17"/>
-      <c r="P83" s="17"/>
-      <c r="Q83" s="17"/>
-      <c r="R83" s="17"/>
-      <c r="S83" s="17"/>
-      <c r="T83" s="17"/>
-      <c r="U83" s="17"/>
-      <c r="V83" s="17"/>
-      <c r="W83" s="17"/>
-      <c r="X83" s="17"/>
-      <c r="Y83" s="17"/>
+      <c r="A83" s="1"/>
+      <c r="B83" s="1"/>
+      <c r="C83" s="1"/>
+      <c r="D83" s="1"/>
+      <c r="E83" s="1"/>
+      <c r="F83" s="1"/>
+      <c r="G83" s="1"/>
+      <c r="H83" s="1"/>
+      <c r="I83" s="1"/>
+      <c r="J83" s="1"/>
+      <c r="K83" s="1"/>
+      <c r="L83" s="1"/>
+      <c r="M83" s="1"/>
+      <c r="N83" s="1"/>
+      <c r="O83" s="1"/>
+      <c r="P83" s="1"/>
+      <c r="Q83" s="1"/>
+      <c r="R83" s="1"/>
+      <c r="S83" s="1"/>
+      <c r="T83" s="1"/>
+      <c r="U83" s="1"/>
+      <c r="V83" s="1"/>
+      <c r="W83" s="1"/>
+      <c r="X83" s="1"/>
+      <c r="Y83" s="1"/>
       <c r="Z83" s="2"/>
     </row>
     <row r="84" ht="15.0" customHeight="1">
@@ -4567,7 +4558,7 @@
       <c r="Z86" s="2"/>
     </row>
     <row r="87" ht="15.0" customHeight="1">
-      <c r="A87" s="1"/>
+      <c r="A87" s="17"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
       <c r="D87" s="1"/>
@@ -4595,115 +4586,115 @@
       <c r="Z87" s="2"/>
     </row>
     <row r="88" ht="15.0" customHeight="1">
-      <c r="A88" s="1"/>
-      <c r="B88" s="1"/>
-      <c r="C88" s="1"/>
-      <c r="D88" s="1"/>
-      <c r="E88" s="1"/>
-      <c r="F88" s="1"/>
-      <c r="G88" s="1"/>
-      <c r="H88" s="1"/>
-      <c r="I88" s="1"/>
-      <c r="J88" s="1"/>
-      <c r="K88" s="1"/>
-      <c r="L88" s="1"/>
-      <c r="M88" s="1"/>
-      <c r="N88" s="1"/>
-      <c r="O88" s="1"/>
-      <c r="P88" s="1"/>
-      <c r="Q88" s="1"/>
-      <c r="R88" s="1"/>
-      <c r="S88" s="1"/>
-      <c r="T88" s="1"/>
-      <c r="U88" s="1"/>
-      <c r="V88" s="1"/>
-      <c r="W88" s="1"/>
-      <c r="X88" s="1"/>
-      <c r="Y88" s="1"/>
+      <c r="A88" s="9"/>
+      <c r="B88" s="8"/>
+      <c r="C88" s="9"/>
+      <c r="D88" s="9"/>
+      <c r="E88" s="9"/>
+      <c r="F88" s="9"/>
+      <c r="G88" s="9"/>
+      <c r="H88" s="9"/>
+      <c r="I88" s="9"/>
+      <c r="J88" s="9"/>
+      <c r="K88" s="9"/>
+      <c r="L88" s="9"/>
+      <c r="M88" s="9"/>
+      <c r="N88" s="9"/>
+      <c r="O88" s="9"/>
+      <c r="P88" s="9"/>
+      <c r="Q88" s="9"/>
+      <c r="R88" s="9"/>
+      <c r="S88" s="9"/>
+      <c r="T88" s="9"/>
+      <c r="U88" s="9"/>
+      <c r="V88" s="9"/>
+      <c r="W88" s="9"/>
+      <c r="X88" s="9"/>
+      <c r="Y88" s="9"/>
       <c r="Z88" s="2"/>
     </row>
     <row r="89" ht="15.0" customHeight="1">
-      <c r="A89" s="1"/>
-      <c r="B89" s="1"/>
-      <c r="C89" s="1"/>
-      <c r="D89" s="1"/>
-      <c r="E89" s="1"/>
-      <c r="F89" s="1"/>
-      <c r="G89" s="1"/>
-      <c r="H89" s="1"/>
-      <c r="I89" s="1"/>
-      <c r="J89" s="1"/>
-      <c r="K89" s="1"/>
-      <c r="L89" s="1"/>
-      <c r="M89" s="1"/>
-      <c r="N89" s="1"/>
-      <c r="O89" s="1"/>
-      <c r="P89" s="1"/>
-      <c r="Q89" s="1"/>
-      <c r="R89" s="1"/>
-      <c r="S89" s="1"/>
-      <c r="T89" s="1"/>
-      <c r="U89" s="1"/>
-      <c r="V89" s="1"/>
-      <c r="W89" s="1"/>
-      <c r="X89" s="1"/>
-      <c r="Y89" s="1"/>
+      <c r="A89" s="9"/>
+      <c r="B89" s="8"/>
+      <c r="C89" s="9"/>
+      <c r="D89" s="9"/>
+      <c r="E89" s="9"/>
+      <c r="F89" s="9"/>
+      <c r="G89" s="9"/>
+      <c r="H89" s="9"/>
+      <c r="I89" s="9"/>
+      <c r="J89" s="9"/>
+      <c r="K89" s="9"/>
+      <c r="L89" s="9"/>
+      <c r="M89" s="9"/>
+      <c r="N89" s="9"/>
+      <c r="O89" s="9"/>
+      <c r="P89" s="9"/>
+      <c r="Q89" s="9"/>
+      <c r="R89" s="9"/>
+      <c r="S89" s="9"/>
+      <c r="T89" s="9"/>
+      <c r="U89" s="9"/>
+      <c r="V89" s="9"/>
+      <c r="W89" s="9"/>
+      <c r="X89" s="9"/>
+      <c r="Y89" s="9"/>
       <c r="Z89" s="2"/>
     </row>
     <row r="90" ht="15.0" customHeight="1">
-      <c r="A90" s="1"/>
-      <c r="B90" s="1"/>
-      <c r="C90" s="1"/>
-      <c r="D90" s="1"/>
-      <c r="E90" s="1"/>
-      <c r="F90" s="1"/>
-      <c r="G90" s="1"/>
-      <c r="H90" s="1"/>
-      <c r="I90" s="1"/>
-      <c r="J90" s="1"/>
-      <c r="K90" s="1"/>
-      <c r="L90" s="1"/>
-      <c r="M90" s="1"/>
-      <c r="N90" s="1"/>
-      <c r="O90" s="1"/>
-      <c r="P90" s="1"/>
-      <c r="Q90" s="1"/>
-      <c r="R90" s="1"/>
-      <c r="S90" s="1"/>
-      <c r="T90" s="1"/>
-      <c r="U90" s="1"/>
-      <c r="V90" s="1"/>
-      <c r="W90" s="1"/>
-      <c r="X90" s="1"/>
-      <c r="Y90" s="1"/>
+      <c r="A90" s="9"/>
+      <c r="B90" s="8"/>
+      <c r="C90" s="9"/>
+      <c r="D90" s="9"/>
+      <c r="E90" s="9"/>
+      <c r="F90" s="9"/>
+      <c r="G90" s="9"/>
+      <c r="H90" s="9"/>
+      <c r="I90" s="9"/>
+      <c r="J90" s="9"/>
+      <c r="K90" s="9"/>
+      <c r="L90" s="9"/>
+      <c r="M90" s="9"/>
+      <c r="N90" s="9"/>
+      <c r="O90" s="9"/>
+      <c r="P90" s="9"/>
+      <c r="Q90" s="9"/>
+      <c r="R90" s="9"/>
+      <c r="S90" s="9"/>
+      <c r="T90" s="9"/>
+      <c r="U90" s="9"/>
+      <c r="V90" s="9"/>
+      <c r="W90" s="9"/>
+      <c r="X90" s="9"/>
+      <c r="Y90" s="9"/>
       <c r="Z90" s="2"/>
     </row>
     <row r="91" ht="15.0" customHeight="1">
-      <c r="A91" s="1"/>
-      <c r="B91" s="1"/>
-      <c r="C91" s="1"/>
-      <c r="D91" s="1"/>
-      <c r="E91" s="1"/>
-      <c r="F91" s="1"/>
-      <c r="G91" s="1"/>
-      <c r="H91" s="1"/>
-      <c r="I91" s="1"/>
-      <c r="J91" s="1"/>
-      <c r="K91" s="1"/>
-      <c r="L91" s="1"/>
-      <c r="M91" s="1"/>
-      <c r="N91" s="1"/>
-      <c r="O91" s="1"/>
-      <c r="P91" s="1"/>
-      <c r="Q91" s="1"/>
-      <c r="R91" s="1"/>
-      <c r="S91" s="1"/>
-      <c r="T91" s="1"/>
-      <c r="U91" s="1"/>
-      <c r="V91" s="1"/>
-      <c r="W91" s="1"/>
-      <c r="X91" s="1"/>
-      <c r="Y91" s="1"/>
+      <c r="A91" s="9"/>
+      <c r="B91" s="8"/>
+      <c r="C91" s="9"/>
+      <c r="D91" s="9"/>
+      <c r="E91" s="9"/>
+      <c r="F91" s="9"/>
+      <c r="G91" s="9"/>
+      <c r="H91" s="9"/>
+      <c r="I91" s="9"/>
+      <c r="J91" s="9"/>
+      <c r="K91" s="9"/>
+      <c r="L91" s="9"/>
+      <c r="M91" s="9"/>
+      <c r="N91" s="9"/>
+      <c r="O91" s="9"/>
+      <c r="P91" s="9"/>
+      <c r="Q91" s="9"/>
+      <c r="R91" s="9"/>
+      <c r="S91" s="9"/>
+      <c r="T91" s="9"/>
+      <c r="U91" s="9"/>
+      <c r="V91" s="9"/>
+      <c r="W91" s="9"/>
+      <c r="X91" s="9"/>
+      <c r="Y91" s="9"/>
       <c r="Z91" s="2"/>
     </row>
     <row r="92" ht="15.0" customHeight="1">
@@ -9747,227 +9738,227 @@
       <c r="Z271" s="2"/>
     </row>
     <row r="272" ht="15.0" customHeight="1">
-      <c r="A272" s="2"/>
-      <c r="B272" s="2"/>
-      <c r="C272" s="2"/>
-      <c r="D272" s="2"/>
-      <c r="E272" s="2"/>
-      <c r="F272" s="2"/>
-      <c r="G272" s="2"/>
-      <c r="H272" s="2"/>
-      <c r="I272" s="2"/>
-      <c r="J272" s="2"/>
-      <c r="K272" s="2"/>
-      <c r="L272" s="2"/>
-      <c r="M272" s="2"/>
-      <c r="N272" s="2"/>
-      <c r="O272" s="2"/>
-      <c r="P272" s="2"/>
-      <c r="Q272" s="2"/>
-      <c r="R272" s="2"/>
-      <c r="S272" s="2"/>
-      <c r="T272" s="2"/>
-      <c r="U272" s="2"/>
-      <c r="V272" s="2"/>
-      <c r="W272" s="2"/>
-      <c r="X272" s="2"/>
-      <c r="Y272" s="2"/>
+      <c r="A272" s="1"/>
+      <c r="B272" s="1"/>
+      <c r="C272" s="1"/>
+      <c r="D272" s="1"/>
+      <c r="E272" s="1"/>
+      <c r="F272" s="1"/>
+      <c r="G272" s="1"/>
+      <c r="H272" s="1"/>
+      <c r="I272" s="1"/>
+      <c r="J272" s="1"/>
+      <c r="K272" s="1"/>
+      <c r="L272" s="1"/>
+      <c r="M272" s="1"/>
+      <c r="N272" s="1"/>
+      <c r="O272" s="1"/>
+      <c r="P272" s="1"/>
+      <c r="Q272" s="1"/>
+      <c r="R272" s="1"/>
+      <c r="S272" s="1"/>
+      <c r="T272" s="1"/>
+      <c r="U272" s="1"/>
+      <c r="V272" s="1"/>
+      <c r="W272" s="1"/>
+      <c r="X272" s="1"/>
+      <c r="Y272" s="1"/>
       <c r="Z272" s="2"/>
     </row>
     <row r="273" ht="15.0" customHeight="1">
-      <c r="A273" s="2"/>
-      <c r="B273" s="2"/>
-      <c r="C273" s="2"/>
-      <c r="D273" s="2"/>
-      <c r="E273" s="2"/>
-      <c r="F273" s="2"/>
-      <c r="G273" s="2"/>
-      <c r="H273" s="2"/>
-      <c r="I273" s="2"/>
-      <c r="J273" s="2"/>
-      <c r="K273" s="2"/>
-      <c r="L273" s="2"/>
-      <c r="M273" s="2"/>
-      <c r="N273" s="2"/>
-      <c r="O273" s="2"/>
-      <c r="P273" s="2"/>
-      <c r="Q273" s="2"/>
-      <c r="R273" s="2"/>
-      <c r="S273" s="2"/>
-      <c r="T273" s="2"/>
-      <c r="U273" s="2"/>
-      <c r="V273" s="2"/>
-      <c r="W273" s="2"/>
-      <c r="X273" s="2"/>
-      <c r="Y273" s="2"/>
+      <c r="A273" s="1"/>
+      <c r="B273" s="1"/>
+      <c r="C273" s="1"/>
+      <c r="D273" s="1"/>
+      <c r="E273" s="1"/>
+      <c r="F273" s="1"/>
+      <c r="G273" s="1"/>
+      <c r="H273" s="1"/>
+      <c r="I273" s="1"/>
+      <c r="J273" s="1"/>
+      <c r="K273" s="1"/>
+      <c r="L273" s="1"/>
+      <c r="M273" s="1"/>
+      <c r="N273" s="1"/>
+      <c r="O273" s="1"/>
+      <c r="P273" s="1"/>
+      <c r="Q273" s="1"/>
+      <c r="R273" s="1"/>
+      <c r="S273" s="1"/>
+      <c r="T273" s="1"/>
+      <c r="U273" s="1"/>
+      <c r="V273" s="1"/>
+      <c r="W273" s="1"/>
+      <c r="X273" s="1"/>
+      <c r="Y273" s="1"/>
       <c r="Z273" s="2"/>
     </row>
     <row r="274" ht="15.0" customHeight="1">
-      <c r="A274" s="2"/>
-      <c r="B274" s="2"/>
-      <c r="C274" s="2"/>
-      <c r="D274" s="2"/>
-      <c r="E274" s="2"/>
-      <c r="F274" s="2"/>
-      <c r="G274" s="2"/>
-      <c r="H274" s="2"/>
-      <c r="I274" s="2"/>
-      <c r="J274" s="2"/>
-      <c r="K274" s="2"/>
-      <c r="L274" s="2"/>
-      <c r="M274" s="2"/>
-      <c r="N274" s="2"/>
-      <c r="O274" s="2"/>
-      <c r="P274" s="2"/>
-      <c r="Q274" s="2"/>
-      <c r="R274" s="2"/>
-      <c r="S274" s="2"/>
-      <c r="T274" s="2"/>
-      <c r="U274" s="2"/>
-      <c r="V274" s="2"/>
-      <c r="W274" s="2"/>
-      <c r="X274" s="2"/>
-      <c r="Y274" s="2"/>
+      <c r="A274" s="1"/>
+      <c r="B274" s="1"/>
+      <c r="C274" s="1"/>
+      <c r="D274" s="1"/>
+      <c r="E274" s="1"/>
+      <c r="F274" s="1"/>
+      <c r="G274" s="1"/>
+      <c r="H274" s="1"/>
+      <c r="I274" s="1"/>
+      <c r="J274" s="1"/>
+      <c r="K274" s="1"/>
+      <c r="L274" s="1"/>
+      <c r="M274" s="1"/>
+      <c r="N274" s="1"/>
+      <c r="O274" s="1"/>
+      <c r="P274" s="1"/>
+      <c r="Q274" s="1"/>
+      <c r="R274" s="1"/>
+      <c r="S274" s="1"/>
+      <c r="T274" s="1"/>
+      <c r="U274" s="1"/>
+      <c r="V274" s="1"/>
+      <c r="W274" s="1"/>
+      <c r="X274" s="1"/>
+      <c r="Y274" s="1"/>
       <c r="Z274" s="2"/>
     </row>
     <row r="275" ht="15.0" customHeight="1">
-      <c r="A275" s="2"/>
-      <c r="B275" s="2"/>
-      <c r="C275" s="2"/>
-      <c r="D275" s="2"/>
-      <c r="E275" s="2"/>
-      <c r="F275" s="2"/>
-      <c r="G275" s="2"/>
-      <c r="H275" s="2"/>
-      <c r="I275" s="2"/>
-      <c r="J275" s="2"/>
-      <c r="K275" s="2"/>
-      <c r="L275" s="2"/>
-      <c r="M275" s="2"/>
-      <c r="N275" s="2"/>
-      <c r="O275" s="2"/>
-      <c r="P275" s="2"/>
-      <c r="Q275" s="2"/>
-      <c r="R275" s="2"/>
-      <c r="S275" s="2"/>
-      <c r="T275" s="2"/>
-      <c r="U275" s="2"/>
-      <c r="V275" s="2"/>
-      <c r="W275" s="2"/>
-      <c r="X275" s="2"/>
-      <c r="Y275" s="2"/>
+      <c r="A275" s="1"/>
+      <c r="B275" s="1"/>
+      <c r="C275" s="1"/>
+      <c r="D275" s="1"/>
+      <c r="E275" s="1"/>
+      <c r="F275" s="1"/>
+      <c r="G275" s="1"/>
+      <c r="H275" s="1"/>
+      <c r="I275" s="1"/>
+      <c r="J275" s="1"/>
+      <c r="K275" s="1"/>
+      <c r="L275" s="1"/>
+      <c r="M275" s="1"/>
+      <c r="N275" s="1"/>
+      <c r="O275" s="1"/>
+      <c r="P275" s="1"/>
+      <c r="Q275" s="1"/>
+      <c r="R275" s="1"/>
+      <c r="S275" s="1"/>
+      <c r="T275" s="1"/>
+      <c r="U275" s="1"/>
+      <c r="V275" s="1"/>
+      <c r="W275" s="1"/>
+      <c r="X275" s="1"/>
+      <c r="Y275" s="1"/>
       <c r="Z275" s="2"/>
     </row>
     <row r="276" ht="15.0" customHeight="1">
-      <c r="A276" s="2"/>
-      <c r="B276" s="2"/>
-      <c r="C276" s="2"/>
-      <c r="D276" s="2"/>
-      <c r="E276" s="2"/>
-      <c r="F276" s="2"/>
-      <c r="G276" s="2"/>
-      <c r="H276" s="2"/>
-      <c r="I276" s="2"/>
-      <c r="J276" s="2"/>
-      <c r="K276" s="2"/>
-      <c r="L276" s="2"/>
-      <c r="M276" s="2"/>
-      <c r="N276" s="2"/>
-      <c r="O276" s="2"/>
-      <c r="P276" s="2"/>
-      <c r="Q276" s="2"/>
-      <c r="R276" s="2"/>
-      <c r="S276" s="2"/>
-      <c r="T276" s="2"/>
-      <c r="U276" s="2"/>
-      <c r="V276" s="2"/>
-      <c r="W276" s="2"/>
-      <c r="X276" s="2"/>
-      <c r="Y276" s="2"/>
+      <c r="A276" s="1"/>
+      <c r="B276" s="1"/>
+      <c r="C276" s="1"/>
+      <c r="D276" s="1"/>
+      <c r="E276" s="1"/>
+      <c r="F276" s="1"/>
+      <c r="G276" s="1"/>
+      <c r="H276" s="1"/>
+      <c r="I276" s="1"/>
+      <c r="J276" s="1"/>
+      <c r="K276" s="1"/>
+      <c r="L276" s="1"/>
+      <c r="M276" s="1"/>
+      <c r="N276" s="1"/>
+      <c r="O276" s="1"/>
+      <c r="P276" s="1"/>
+      <c r="Q276" s="1"/>
+      <c r="R276" s="1"/>
+      <c r="S276" s="1"/>
+      <c r="T276" s="1"/>
+      <c r="U276" s="1"/>
+      <c r="V276" s="1"/>
+      <c r="W276" s="1"/>
+      <c r="X276" s="1"/>
+      <c r="Y276" s="1"/>
       <c r="Z276" s="2"/>
     </row>
     <row r="277" ht="15.0" customHeight="1">
-      <c r="A277" s="2"/>
-      <c r="B277" s="2"/>
-      <c r="C277" s="2"/>
-      <c r="D277" s="2"/>
-      <c r="E277" s="2"/>
-      <c r="F277" s="2"/>
-      <c r="G277" s="2"/>
-      <c r="H277" s="2"/>
-      <c r="I277" s="2"/>
-      <c r="J277" s="2"/>
-      <c r="K277" s="2"/>
-      <c r="L277" s="2"/>
-      <c r="M277" s="2"/>
-      <c r="N277" s="2"/>
-      <c r="O277" s="2"/>
-      <c r="P277" s="2"/>
-      <c r="Q277" s="2"/>
-      <c r="R277" s="2"/>
-      <c r="S277" s="2"/>
-      <c r="T277" s="2"/>
-      <c r="U277" s="2"/>
-      <c r="V277" s="2"/>
-      <c r="W277" s="2"/>
-      <c r="X277" s="2"/>
-      <c r="Y277" s="2"/>
+      <c r="A277" s="1"/>
+      <c r="B277" s="1"/>
+      <c r="C277" s="1"/>
+      <c r="D277" s="1"/>
+      <c r="E277" s="1"/>
+      <c r="F277" s="1"/>
+      <c r="G277" s="1"/>
+      <c r="H277" s="1"/>
+      <c r="I277" s="1"/>
+      <c r="J277" s="1"/>
+      <c r="K277" s="1"/>
+      <c r="L277" s="1"/>
+      <c r="M277" s="1"/>
+      <c r="N277" s="1"/>
+      <c r="O277" s="1"/>
+      <c r="P277" s="1"/>
+      <c r="Q277" s="1"/>
+      <c r="R277" s="1"/>
+      <c r="S277" s="1"/>
+      <c r="T277" s="1"/>
+      <c r="U277" s="1"/>
+      <c r="V277" s="1"/>
+      <c r="W277" s="1"/>
+      <c r="X277" s="1"/>
+      <c r="Y277" s="1"/>
       <c r="Z277" s="2"/>
     </row>
     <row r="278" ht="15.0" customHeight="1">
-      <c r="A278" s="2"/>
-      <c r="B278" s="2"/>
-      <c r="C278" s="2"/>
-      <c r="D278" s="2"/>
-      <c r="E278" s="2"/>
-      <c r="F278" s="2"/>
-      <c r="G278" s="2"/>
-      <c r="H278" s="2"/>
-      <c r="I278" s="2"/>
-      <c r="J278" s="2"/>
-      <c r="K278" s="2"/>
-      <c r="L278" s="2"/>
-      <c r="M278" s="2"/>
-      <c r="N278" s="2"/>
-      <c r="O278" s="2"/>
-      <c r="P278" s="2"/>
-      <c r="Q278" s="2"/>
-      <c r="R278" s="2"/>
-      <c r="S278" s="2"/>
-      <c r="T278" s="2"/>
-      <c r="U278" s="2"/>
-      <c r="V278" s="2"/>
-      <c r="W278" s="2"/>
-      <c r="X278" s="2"/>
-      <c r="Y278" s="2"/>
+      <c r="A278" s="1"/>
+      <c r="B278" s="1"/>
+      <c r="C278" s="1"/>
+      <c r="D278" s="1"/>
+      <c r="E278" s="1"/>
+      <c r="F278" s="1"/>
+      <c r="G278" s="1"/>
+      <c r="H278" s="1"/>
+      <c r="I278" s="1"/>
+      <c r="J278" s="1"/>
+      <c r="K278" s="1"/>
+      <c r="L278" s="1"/>
+      <c r="M278" s="1"/>
+      <c r="N278" s="1"/>
+      <c r="O278" s="1"/>
+      <c r="P278" s="1"/>
+      <c r="Q278" s="1"/>
+      <c r="R278" s="1"/>
+      <c r="S278" s="1"/>
+      <c r="T278" s="1"/>
+      <c r="U278" s="1"/>
+      <c r="V278" s="1"/>
+      <c r="W278" s="1"/>
+      <c r="X278" s="1"/>
+      <c r="Y278" s="1"/>
       <c r="Z278" s="2"/>
     </row>
     <row r="279" ht="15.0" customHeight="1">
-      <c r="A279" s="2"/>
-      <c r="B279" s="2"/>
-      <c r="C279" s="2"/>
-      <c r="D279" s="2"/>
-      <c r="E279" s="2"/>
-      <c r="F279" s="2"/>
-      <c r="G279" s="2"/>
-      <c r="H279" s="2"/>
-      <c r="I279" s="2"/>
-      <c r="J279" s="2"/>
-      <c r="K279" s="2"/>
-      <c r="L279" s="2"/>
-      <c r="M279" s="2"/>
-      <c r="N279" s="2"/>
-      <c r="O279" s="2"/>
-      <c r="P279" s="2"/>
-      <c r="Q279" s="2"/>
-      <c r="R279" s="2"/>
-      <c r="S279" s="2"/>
-      <c r="T279" s="2"/>
-      <c r="U279" s="2"/>
-      <c r="V279" s="2"/>
-      <c r="W279" s="2"/>
-      <c r="X279" s="2"/>
-      <c r="Y279" s="2"/>
+      <c r="A279" s="1"/>
+      <c r="B279" s="1"/>
+      <c r="C279" s="1"/>
+      <c r="D279" s="1"/>
+      <c r="E279" s="1"/>
+      <c r="F279" s="1"/>
+      <c r="G279" s="1"/>
+      <c r="H279" s="1"/>
+      <c r="I279" s="1"/>
+      <c r="J279" s="1"/>
+      <c r="K279" s="1"/>
+      <c r="L279" s="1"/>
+      <c r="M279" s="1"/>
+      <c r="N279" s="1"/>
+      <c r="O279" s="1"/>
+      <c r="P279" s="1"/>
+      <c r="Q279" s="1"/>
+      <c r="R279" s="1"/>
+      <c r="S279" s="1"/>
+      <c r="T279" s="1"/>
+      <c r="U279" s="1"/>
+      <c r="V279" s="1"/>
+      <c r="W279" s="1"/>
+      <c r="X279" s="1"/>
+      <c r="Y279" s="1"/>
       <c r="Z279" s="2"/>
     </row>
     <row r="280" ht="15.0" customHeight="1">
@@ -10082,7 +10073,7 @@
       <c r="Y283" s="2"/>
       <c r="Z283" s="2"/>
     </row>
-    <row r="284" ht="15.75" customHeight="1">
+    <row r="284" ht="15.0" customHeight="1">
       <c r="A284" s="2"/>
       <c r="B284" s="2"/>
       <c r="C284" s="2"/>
@@ -10110,7 +10101,7 @@
       <c r="Y284" s="2"/>
       <c r="Z284" s="2"/>
     </row>
-    <row r="285" ht="15.75" customHeight="1">
+    <row r="285" ht="15.0" customHeight="1">
       <c r="A285" s="2"/>
       <c r="B285" s="2"/>
       <c r="C285" s="2"/>
@@ -10138,7 +10129,7 @@
       <c r="Y285" s="2"/>
       <c r="Z285" s="2"/>
     </row>
-    <row r="286" ht="15.75" customHeight="1">
+    <row r="286" ht="15.0" customHeight="1">
       <c r="A286" s="2"/>
       <c r="B286" s="2"/>
       <c r="C286" s="2"/>
@@ -10166,7 +10157,7 @@
       <c r="Y286" s="2"/>
       <c r="Z286" s="2"/>
     </row>
-    <row r="287" ht="15.75" customHeight="1">
+    <row r="287" ht="15.0" customHeight="1">
       <c r="A287" s="2"/>
       <c r="B287" s="2"/>
       <c r="C287" s="2"/>
@@ -10194,7 +10185,7 @@
       <c r="Y287" s="2"/>
       <c r="Z287" s="2"/>
     </row>
-    <row r="288" ht="15.75" customHeight="1">
+    <row r="288" ht="15.0" customHeight="1">
       <c r="A288" s="2"/>
       <c r="B288" s="2"/>
       <c r="C288" s="2"/>
@@ -10222,7 +10213,7 @@
       <c r="Y288" s="2"/>
       <c r="Z288" s="2"/>
     </row>
-    <row r="289" ht="15.75" customHeight="1">
+    <row r="289" ht="15.0" customHeight="1">
       <c r="A289" s="2"/>
       <c r="B289" s="2"/>
       <c r="C289" s="2"/>
@@ -10250,7 +10241,7 @@
       <c r="Y289" s="2"/>
       <c r="Z289" s="2"/>
     </row>
-    <row r="290" ht="15.75" customHeight="1">
+    <row r="290" ht="15.0" customHeight="1">
       <c r="A290" s="2"/>
       <c r="B290" s="2"/>
       <c r="C290" s="2"/>
@@ -10278,7 +10269,7 @@
       <c r="Y290" s="2"/>
       <c r="Z290" s="2"/>
     </row>
-    <row r="291" ht="15.75" customHeight="1">
+    <row r="291" ht="15.0" customHeight="1">
       <c r="A291" s="2"/>
       <c r="B291" s="2"/>
       <c r="C291" s="2"/>
@@ -30186,6 +30177,230 @@
       <c r="Y1001" s="2"/>
       <c r="Z1001" s="2"/>
     </row>
+    <row r="1002" ht="15.75" customHeight="1">
+      <c r="A1002" s="2"/>
+      <c r="B1002" s="2"/>
+      <c r="C1002" s="2"/>
+      <c r="D1002" s="2"/>
+      <c r="E1002" s="2"/>
+      <c r="F1002" s="2"/>
+      <c r="G1002" s="2"/>
+      <c r="H1002" s="2"/>
+      <c r="I1002" s="2"/>
+      <c r="J1002" s="2"/>
+      <c r="K1002" s="2"/>
+      <c r="L1002" s="2"/>
+      <c r="M1002" s="2"/>
+      <c r="N1002" s="2"/>
+      <c r="O1002" s="2"/>
+      <c r="P1002" s="2"/>
+      <c r="Q1002" s="2"/>
+      <c r="R1002" s="2"/>
+      <c r="S1002" s="2"/>
+      <c r="T1002" s="2"/>
+      <c r="U1002" s="2"/>
+      <c r="V1002" s="2"/>
+      <c r="W1002" s="2"/>
+      <c r="X1002" s="2"/>
+      <c r="Y1002" s="2"/>
+      <c r="Z1002" s="2"/>
+    </row>
+    <row r="1003" ht="15.75" customHeight="1">
+      <c r="A1003" s="2"/>
+      <c r="B1003" s="2"/>
+      <c r="C1003" s="2"/>
+      <c r="D1003" s="2"/>
+      <c r="E1003" s="2"/>
+      <c r="F1003" s="2"/>
+      <c r="G1003" s="2"/>
+      <c r="H1003" s="2"/>
+      <c r="I1003" s="2"/>
+      <c r="J1003" s="2"/>
+      <c r="K1003" s="2"/>
+      <c r="L1003" s="2"/>
+      <c r="M1003" s="2"/>
+      <c r="N1003" s="2"/>
+      <c r="O1003" s="2"/>
+      <c r="P1003" s="2"/>
+      <c r="Q1003" s="2"/>
+      <c r="R1003" s="2"/>
+      <c r="S1003" s="2"/>
+      <c r="T1003" s="2"/>
+      <c r="U1003" s="2"/>
+      <c r="V1003" s="2"/>
+      <c r="W1003" s="2"/>
+      <c r="X1003" s="2"/>
+      <c r="Y1003" s="2"/>
+      <c r="Z1003" s="2"/>
+    </row>
+    <row r="1004" ht="15.75" customHeight="1">
+      <c r="A1004" s="2"/>
+      <c r="B1004" s="2"/>
+      <c r="C1004" s="2"/>
+      <c r="D1004" s="2"/>
+      <c r="E1004" s="2"/>
+      <c r="F1004" s="2"/>
+      <c r="G1004" s="2"/>
+      <c r="H1004" s="2"/>
+      <c r="I1004" s="2"/>
+      <c r="J1004" s="2"/>
+      <c r="K1004" s="2"/>
+      <c r="L1004" s="2"/>
+      <c r="M1004" s="2"/>
+      <c r="N1004" s="2"/>
+      <c r="O1004" s="2"/>
+      <c r="P1004" s="2"/>
+      <c r="Q1004" s="2"/>
+      <c r="R1004" s="2"/>
+      <c r="S1004" s="2"/>
+      <c r="T1004" s="2"/>
+      <c r="U1004" s="2"/>
+      <c r="V1004" s="2"/>
+      <c r="W1004" s="2"/>
+      <c r="X1004" s="2"/>
+      <c r="Y1004" s="2"/>
+      <c r="Z1004" s="2"/>
+    </row>
+    <row r="1005" ht="15.75" customHeight="1">
+      <c r="A1005" s="2"/>
+      <c r="B1005" s="2"/>
+      <c r="C1005" s="2"/>
+      <c r="D1005" s="2"/>
+      <c r="E1005" s="2"/>
+      <c r="F1005" s="2"/>
+      <c r="G1005" s="2"/>
+      <c r="H1005" s="2"/>
+      <c r="I1005" s="2"/>
+      <c r="J1005" s="2"/>
+      <c r="K1005" s="2"/>
+      <c r="L1005" s="2"/>
+      <c r="M1005" s="2"/>
+      <c r="N1005" s="2"/>
+      <c r="O1005" s="2"/>
+      <c r="P1005" s="2"/>
+      <c r="Q1005" s="2"/>
+      <c r="R1005" s="2"/>
+      <c r="S1005" s="2"/>
+      <c r="T1005" s="2"/>
+      <c r="U1005" s="2"/>
+      <c r="V1005" s="2"/>
+      <c r="W1005" s="2"/>
+      <c r="X1005" s="2"/>
+      <c r="Y1005" s="2"/>
+      <c r="Z1005" s="2"/>
+    </row>
+    <row r="1006" ht="15.75" customHeight="1">
+      <c r="A1006" s="2"/>
+      <c r="B1006" s="2"/>
+      <c r="C1006" s="2"/>
+      <c r="D1006" s="2"/>
+      <c r="E1006" s="2"/>
+      <c r="F1006" s="2"/>
+      <c r="G1006" s="2"/>
+      <c r="H1006" s="2"/>
+      <c r="I1006" s="2"/>
+      <c r="J1006" s="2"/>
+      <c r="K1006" s="2"/>
+      <c r="L1006" s="2"/>
+      <c r="M1006" s="2"/>
+      <c r="N1006" s="2"/>
+      <c r="O1006" s="2"/>
+      <c r="P1006" s="2"/>
+      <c r="Q1006" s="2"/>
+      <c r="R1006" s="2"/>
+      <c r="S1006" s="2"/>
+      <c r="T1006" s="2"/>
+      <c r="U1006" s="2"/>
+      <c r="V1006" s="2"/>
+      <c r="W1006" s="2"/>
+      <c r="X1006" s="2"/>
+      <c r="Y1006" s="2"/>
+      <c r="Z1006" s="2"/>
+    </row>
+    <row r="1007" ht="15.75" customHeight="1">
+      <c r="A1007" s="2"/>
+      <c r="B1007" s="2"/>
+      <c r="C1007" s="2"/>
+      <c r="D1007" s="2"/>
+      <c r="E1007" s="2"/>
+      <c r="F1007" s="2"/>
+      <c r="G1007" s="2"/>
+      <c r="H1007" s="2"/>
+      <c r="I1007" s="2"/>
+      <c r="J1007" s="2"/>
+      <c r="K1007" s="2"/>
+      <c r="L1007" s="2"/>
+      <c r="M1007" s="2"/>
+      <c r="N1007" s="2"/>
+      <c r="O1007" s="2"/>
+      <c r="P1007" s="2"/>
+      <c r="Q1007" s="2"/>
+      <c r="R1007" s="2"/>
+      <c r="S1007" s="2"/>
+      <c r="T1007" s="2"/>
+      <c r="U1007" s="2"/>
+      <c r="V1007" s="2"/>
+      <c r="W1007" s="2"/>
+      <c r="X1007" s="2"/>
+      <c r="Y1007" s="2"/>
+      <c r="Z1007" s="2"/>
+    </row>
+    <row r="1008" ht="15.75" customHeight="1">
+      <c r="A1008" s="2"/>
+      <c r="B1008" s="2"/>
+      <c r="C1008" s="2"/>
+      <c r="D1008" s="2"/>
+      <c r="E1008" s="2"/>
+      <c r="F1008" s="2"/>
+      <c r="G1008" s="2"/>
+      <c r="H1008" s="2"/>
+      <c r="I1008" s="2"/>
+      <c r="J1008" s="2"/>
+      <c r="K1008" s="2"/>
+      <c r="L1008" s="2"/>
+      <c r="M1008" s="2"/>
+      <c r="N1008" s="2"/>
+      <c r="O1008" s="2"/>
+      <c r="P1008" s="2"/>
+      <c r="Q1008" s="2"/>
+      <c r="R1008" s="2"/>
+      <c r="S1008" s="2"/>
+      <c r="T1008" s="2"/>
+      <c r="U1008" s="2"/>
+      <c r="V1008" s="2"/>
+      <c r="W1008" s="2"/>
+      <c r="X1008" s="2"/>
+      <c r="Y1008" s="2"/>
+      <c r="Z1008" s="2"/>
+    </row>
+    <row r="1009" ht="15.75" customHeight="1">
+      <c r="A1009" s="2"/>
+      <c r="B1009" s="2"/>
+      <c r="C1009" s="2"/>
+      <c r="D1009" s="2"/>
+      <c r="E1009" s="2"/>
+      <c r="F1009" s="2"/>
+      <c r="G1009" s="2"/>
+      <c r="H1009" s="2"/>
+      <c r="I1009" s="2"/>
+      <c r="J1009" s="2"/>
+      <c r="K1009" s="2"/>
+      <c r="L1009" s="2"/>
+      <c r="M1009" s="2"/>
+      <c r="N1009" s="2"/>
+      <c r="O1009" s="2"/>
+      <c r="P1009" s="2"/>
+      <c r="Q1009" s="2"/>
+      <c r="R1009" s="2"/>
+      <c r="S1009" s="2"/>
+      <c r="T1009" s="2"/>
+      <c r="U1009" s="2"/>
+      <c r="V1009" s="2"/>
+      <c r="W1009" s="2"/>
+      <c r="X1009" s="2"/>
+      <c r="Y1009" s="2"/>
+      <c r="Z1009" s="2"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Templates/Tables/StringInfo/StrTable.xlsx
+++ b/Templates/Tables/StringInfo/StrTable.xlsx
@@ -1041,7 +1041,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1066,9 +1066,6 @@
     </xf>
     <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf borderId="3" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="3" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1301,7 +1298,7 @@
     <col customWidth="1" min="6" max="25" width="12.63"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.0" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1338,7 +1335,7 @@
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
     </row>
-    <row r="2" ht="15.0" customHeight="1">
+    <row r="2">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -1375,7 +1372,7 @@
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
     </row>
-    <row r="3" ht="15.0" customHeight="1">
+    <row r="3">
       <c r="A3" s="5" t="s">
         <v>9</v>
       </c>
@@ -1412,7 +1409,7 @@
       <c r="X3" s="7"/>
       <c r="Y3" s="7"/>
     </row>
-    <row r="4" ht="15.0" customHeight="1">
+    <row r="4">
       <c r="A4" s="5" t="s">
         <v>13</v>
       </c>
@@ -1449,7 +1446,7 @@
       <c r="X4" s="7"/>
       <c r="Y4" s="7"/>
     </row>
-    <row r="5" ht="15.0" customHeight="1">
+    <row r="5">
       <c r="A5" s="5" t="s">
         <v>17</v>
       </c>
@@ -1486,7 +1483,7 @@
       <c r="X5" s="7"/>
       <c r="Y5" s="7"/>
     </row>
-    <row r="6" ht="15.0" customHeight="1">
+    <row r="6">
       <c r="A6" s="5" t="s">
         <v>21</v>
       </c>
@@ -1523,7 +1520,7 @@
       <c r="X6" s="7"/>
       <c r="Y6" s="7"/>
     </row>
-    <row r="7" ht="15.0" customHeight="1">
+    <row r="7">
       <c r="A7" s="5" t="s">
         <v>25</v>
       </c>
@@ -1560,7 +1557,7 @@
       <c r="X7" s="7"/>
       <c r="Y7" s="7"/>
     </row>
-    <row r="8" ht="15.0" customHeight="1">
+    <row r="8">
       <c r="A8" s="5" t="s">
         <v>29</v>
       </c>
@@ -1597,7 +1594,7 @@
       <c r="X8" s="7"/>
       <c r="Y8" s="7"/>
     </row>
-    <row r="9" ht="15.0" customHeight="1">
+    <row r="9">
       <c r="A9" s="5" t="s">
         <v>33</v>
       </c>
@@ -1634,7 +1631,7 @@
       <c r="X9" s="7"/>
       <c r="Y9" s="7"/>
     </row>
-    <row r="10" ht="15.0" customHeight="1">
+    <row r="10">
       <c r="A10" s="5" t="s">
         <v>37</v>
       </c>
@@ -1671,7 +1668,7 @@
       <c r="X10" s="7"/>
       <c r="Y10" s="7"/>
     </row>
-    <row r="11" ht="15.0" customHeight="1">
+    <row r="11">
       <c r="A11" s="5" t="s">
         <v>41</v>
       </c>
@@ -1708,7 +1705,7 @@
       <c r="X11" s="7"/>
       <c r="Y11" s="7"/>
     </row>
-    <row r="12" ht="15.0" customHeight="1">
+    <row r="12">
       <c r="A12" s="5" t="s">
         <v>45</v>
       </c>
@@ -1745,7 +1742,7 @@
       <c r="X12" s="7"/>
       <c r="Y12" s="7"/>
     </row>
-    <row r="13" ht="15.0" customHeight="1">
+    <row r="13">
       <c r="A13" s="5" t="s">
         <v>49</v>
       </c>
@@ -1782,7 +1779,7 @@
       <c r="X13" s="7"/>
       <c r="Y13" s="7"/>
     </row>
-    <row r="14" ht="15.0" customHeight="1">
+    <row r="14">
       <c r="A14" s="5" t="s">
         <v>53</v>
       </c>
@@ -1819,7 +1816,7 @@
       <c r="X14" s="7"/>
       <c r="Y14" s="7"/>
     </row>
-    <row r="15" ht="15.0" customHeight="1">
+    <row r="15">
       <c r="A15" s="5" t="s">
         <v>57</v>
       </c>
@@ -1856,8 +1853,8 @@
       <c r="X15" s="7"/>
       <c r="Y15" s="7"/>
     </row>
-    <row r="16" ht="15.0" customHeight="1">
-      <c r="A16" s="9" t="s">
+    <row r="16">
+      <c r="A16" s="5" t="s">
         <v>61</v>
       </c>
       <c r="B16" s="6">
@@ -1893,7 +1890,7 @@
       <c r="X16" s="7"/>
       <c r="Y16" s="7"/>
     </row>
-    <row r="17" ht="15.0" customHeight="1">
+    <row r="17">
       <c r="A17" s="5" t="s">
         <v>65</v>
       </c>
@@ -1930,7 +1927,7 @@
       <c r="X17" s="7"/>
       <c r="Y17" s="7"/>
     </row>
-    <row r="18" ht="15.0" customHeight="1">
+    <row r="18">
       <c r="A18" s="5" t="s">
         <v>69</v>
       </c>
@@ -1967,7 +1964,7 @@
       <c r="X18" s="7"/>
       <c r="Y18" s="7"/>
     </row>
-    <row r="19" ht="15.0" customHeight="1">
+    <row r="19">
       <c r="A19" s="5" t="s">
         <v>73</v>
       </c>
@@ -2004,7 +2001,7 @@
       <c r="X19" s="7"/>
       <c r="Y19" s="7"/>
     </row>
-    <row r="20" ht="15.0" customHeight="1">
+    <row r="20">
       <c r="A20" s="5" t="s">
         <v>77</v>
       </c>
@@ -2041,7 +2038,7 @@
       <c r="X20" s="7"/>
       <c r="Y20" s="7"/>
     </row>
-    <row r="21" ht="15.0" customHeight="1">
+    <row r="21">
       <c r="A21" s="2" t="s">
         <v>81</v>
       </c>
@@ -2078,7 +2075,7 @@
       <c r="X21" s="4"/>
       <c r="Y21" s="4"/>
     </row>
-    <row r="22" ht="15.0" customHeight="1">
+    <row r="22">
       <c r="A22" s="5" t="s">
         <v>85</v>
       </c>
@@ -2115,7 +2112,7 @@
       <c r="X22" s="7"/>
       <c r="Y22" s="7"/>
     </row>
-    <row r="23" ht="15.0" customHeight="1">
+    <row r="23">
       <c r="A23" s="5" t="s">
         <v>89</v>
       </c>
@@ -2152,7 +2149,7 @@
       <c r="X23" s="7"/>
       <c r="Y23" s="7"/>
     </row>
-    <row r="24" ht="15.0" customHeight="1">
+    <row r="24">
       <c r="A24" s="5" t="s">
         <v>93</v>
       </c>
@@ -2189,7 +2186,7 @@
       <c r="X24" s="7"/>
       <c r="Y24" s="7"/>
     </row>
-    <row r="25" ht="15.0" customHeight="1">
+    <row r="25">
       <c r="A25" s="5" t="s">
         <v>97</v>
       </c>
@@ -2226,7 +2223,7 @@
       <c r="X25" s="7"/>
       <c r="Y25" s="7"/>
     </row>
-    <row r="26" ht="15.0" customHeight="1">
+    <row r="26">
       <c r="A26" s="5" t="s">
         <v>101</v>
       </c>
@@ -2263,7 +2260,7 @@
       <c r="X26" s="7"/>
       <c r="Y26" s="7"/>
     </row>
-    <row r="27" ht="15.0" customHeight="1">
+    <row r="27">
       <c r="A27" s="5" t="s">
         <v>105</v>
       </c>
@@ -2300,7 +2297,7 @@
       <c r="X27" s="7"/>
       <c r="Y27" s="7"/>
     </row>
-    <row r="28" ht="15.0" customHeight="1">
+    <row r="28">
       <c r="A28" s="5" t="s">
         <v>109</v>
       </c>
@@ -2337,7 +2334,7 @@
       <c r="X28" s="7"/>
       <c r="Y28" s="7"/>
     </row>
-    <row r="29" ht="15.0" customHeight="1">
+    <row r="29">
       <c r="A29" s="5" t="s">
         <v>113</v>
       </c>
@@ -2374,7 +2371,7 @@
       <c r="X29" s="7"/>
       <c r="Y29" s="7"/>
     </row>
-    <row r="30" ht="15.0" customHeight="1">
+    <row r="30">
       <c r="A30" s="5" t="s">
         <v>117</v>
       </c>
@@ -2411,7 +2408,7 @@
       <c r="X30" s="7"/>
       <c r="Y30" s="7"/>
     </row>
-    <row r="31" ht="15.0" customHeight="1">
+    <row r="31">
       <c r="A31" s="5" t="s">
         <v>121</v>
       </c>
@@ -2448,7 +2445,7 @@
       <c r="X31" s="7"/>
       <c r="Y31" s="7"/>
     </row>
-    <row r="32" ht="15.0" customHeight="1">
+    <row r="32">
       <c r="A32" s="5" t="s">
         <v>125</v>
       </c>
@@ -2485,7 +2482,7 @@
       <c r="X32" s="7"/>
       <c r="Y32" s="7"/>
     </row>
-    <row r="33" ht="15.0" customHeight="1">
+    <row r="33">
       <c r="A33" s="5" t="s">
         <v>129</v>
       </c>
@@ -2522,7 +2519,7 @@
       <c r="X33" s="7"/>
       <c r="Y33" s="7"/>
     </row>
-    <row r="34" ht="15.0" customHeight="1">
+    <row r="34">
       <c r="A34" s="5" t="s">
         <v>133</v>
       </c>
@@ -2559,7 +2556,7 @@
       <c r="X34" s="7"/>
       <c r="Y34" s="7"/>
     </row>
-    <row r="35" ht="15.0" customHeight="1">
+    <row r="35">
       <c r="A35" s="5" t="s">
         <v>137</v>
       </c>
@@ -2596,7 +2593,7 @@
       <c r="X35" s="7"/>
       <c r="Y35" s="7"/>
     </row>
-    <row r="36" ht="15.0" customHeight="1">
+    <row r="36">
       <c r="A36" s="5" t="s">
         <v>141</v>
       </c>
@@ -2633,7 +2630,7 @@
       <c r="X36" s="7"/>
       <c r="Y36" s="7"/>
     </row>
-    <row r="37" ht="15.0" customHeight="1">
+    <row r="37">
       <c r="A37" s="5" t="s">
         <v>145</v>
       </c>
@@ -2670,7 +2667,7 @@
       <c r="X37" s="7"/>
       <c r="Y37" s="7"/>
     </row>
-    <row r="38" ht="15.0" customHeight="1">
+    <row r="38">
       <c r="A38" s="5" t="s">
         <v>149</v>
       </c>
@@ -2707,7 +2704,7 @@
       <c r="X38" s="7"/>
       <c r="Y38" s="7"/>
     </row>
-    <row r="39" ht="15.0" customHeight="1">
+    <row r="39">
       <c r="A39" s="5" t="s">
         <v>153</v>
       </c>
@@ -2744,7 +2741,7 @@
       <c r="X39" s="7"/>
       <c r="Y39" s="7"/>
     </row>
-    <row r="40" ht="15.0" customHeight="1">
+    <row r="40">
       <c r="A40" s="5" t="s">
         <v>157</v>
       </c>
@@ -2781,7 +2778,7 @@
       <c r="X40" s="7"/>
       <c r="Y40" s="7"/>
     </row>
-    <row r="41" ht="15.0" customHeight="1">
+    <row r="41">
       <c r="A41" s="5" t="s">
         <v>161</v>
       </c>
@@ -2818,7 +2815,7 @@
       <c r="X41" s="7"/>
       <c r="Y41" s="7"/>
     </row>
-    <row r="42" ht="15.0" customHeight="1">
+    <row r="42">
       <c r="A42" s="5" t="s">
         <v>165</v>
       </c>
@@ -2855,7 +2852,7 @@
       <c r="X42" s="7"/>
       <c r="Y42" s="7"/>
     </row>
-    <row r="43" ht="15.0" customHeight="1">
+    <row r="43">
       <c r="A43" s="5" t="s">
         <v>169</v>
       </c>
@@ -2892,7 +2889,7 @@
       <c r="X43" s="7"/>
       <c r="Y43" s="7"/>
     </row>
-    <row r="44" ht="15.0" customHeight="1">
+    <row r="44">
       <c r="A44" s="5" t="s">
         <v>173</v>
       </c>
@@ -2929,7 +2926,7 @@
       <c r="X44" s="7"/>
       <c r="Y44" s="7"/>
     </row>
-    <row r="45" ht="15.0" customHeight="1">
+    <row r="45">
       <c r="A45" s="5" t="s">
         <v>177</v>
       </c>
@@ -2966,7 +2963,7 @@
       <c r="X45" s="7"/>
       <c r="Y45" s="7"/>
     </row>
-    <row r="46" ht="15.0" customHeight="1">
+    <row r="46">
       <c r="A46" s="5" t="s">
         <v>181</v>
       </c>
@@ -3003,7 +3000,7 @@
       <c r="X46" s="7"/>
       <c r="Y46" s="7"/>
     </row>
-    <row r="47" ht="15.0" customHeight="1">
+    <row r="47">
       <c r="A47" s="5" t="s">
         <v>185</v>
       </c>
@@ -3040,7 +3037,7 @@
       <c r="X47" s="7"/>
       <c r="Y47" s="7"/>
     </row>
-    <row r="48" ht="15.0" customHeight="1">
+    <row r="48">
       <c r="A48" s="5" t="s">
         <v>189</v>
       </c>
@@ -3077,7 +3074,7 @@
       <c r="X48" s="7"/>
       <c r="Y48" s="7"/>
     </row>
-    <row r="49" ht="15.0" customHeight="1">
+    <row r="49">
       <c r="A49" s="5" t="s">
         <v>193</v>
       </c>
@@ -3114,7 +3111,7 @@
       <c r="X49" s="7"/>
       <c r="Y49" s="7"/>
     </row>
-    <row r="50" ht="15.0" customHeight="1">
+    <row r="50">
       <c r="A50" s="5" t="s">
         <v>197</v>
       </c>
@@ -3151,7 +3148,7 @@
       <c r="X50" s="7"/>
       <c r="Y50" s="7"/>
     </row>
-    <row r="51" ht="15.0" customHeight="1">
+    <row r="51">
       <c r="A51" s="5" t="s">
         <v>201</v>
       </c>
@@ -3188,7 +3185,7 @@
       <c r="X51" s="7"/>
       <c r="Y51" s="7"/>
     </row>
-    <row r="52" ht="15.0" customHeight="1">
+    <row r="52">
       <c r="A52" s="5" t="s">
         <v>205</v>
       </c>
@@ -3225,7 +3222,7 @@
       <c r="X52" s="7"/>
       <c r="Y52" s="7"/>
     </row>
-    <row r="53" ht="15.0" customHeight="1">
+    <row r="53">
       <c r="A53" s="5" t="s">
         <v>209</v>
       </c>
@@ -3262,7 +3259,7 @@
       <c r="X53" s="7"/>
       <c r="Y53" s="7"/>
     </row>
-    <row r="54" ht="15.0" customHeight="1">
+    <row r="54">
       <c r="A54" s="5" t="s">
         <v>213</v>
       </c>
@@ -3299,7 +3296,7 @@
       <c r="X54" s="7"/>
       <c r="Y54" s="7"/>
     </row>
-    <row r="55" ht="15.0" customHeight="1">
+    <row r="55">
       <c r="A55" s="5" t="s">
         <v>215</v>
       </c>
@@ -3336,7 +3333,7 @@
       <c r="X55" s="7"/>
       <c r="Y55" s="7"/>
     </row>
-    <row r="56" ht="15.0" customHeight="1">
+    <row r="56">
       <c r="A56" s="5" t="s">
         <v>219</v>
       </c>
@@ -3373,7 +3370,7 @@
       <c r="X56" s="7"/>
       <c r="Y56" s="7"/>
     </row>
-    <row r="57" ht="15.0" customHeight="1">
+    <row r="57">
       <c r="A57" s="5" t="s">
         <v>223</v>
       </c>
@@ -3410,7 +3407,7 @@
       <c r="X57" s="7"/>
       <c r="Y57" s="7"/>
     </row>
-    <row r="58" ht="15.0" customHeight="1">
+    <row r="58">
       <c r="A58" s="5" t="s">
         <v>227</v>
       </c>
@@ -3447,7 +3444,7 @@
       <c r="X58" s="7"/>
       <c r="Y58" s="7"/>
     </row>
-    <row r="59" ht="15.0" customHeight="1">
+    <row r="59">
       <c r="A59" s="5" t="s">
         <v>231</v>
       </c>
@@ -3484,7 +3481,7 @@
       <c r="X59" s="7"/>
       <c r="Y59" s="7"/>
     </row>
-    <row r="60" ht="15.0" customHeight="1">
+    <row r="60">
       <c r="A60" s="5" t="s">
         <v>235</v>
       </c>
@@ -3521,7 +3518,7 @@
       <c r="X60" s="7"/>
       <c r="Y60" s="7"/>
     </row>
-    <row r="61" ht="15.0" customHeight="1">
+    <row r="61">
       <c r="A61" s="5" t="s">
         <v>239</v>
       </c>
@@ -3558,7 +3555,7 @@
       <c r="X61" s="7"/>
       <c r="Y61" s="7"/>
     </row>
-    <row r="62" ht="15.0" customHeight="1">
+    <row r="62">
       <c r="A62" s="5" t="s">
         <v>243</v>
       </c>
@@ -3595,7 +3592,7 @@
       <c r="X62" s="7"/>
       <c r="Y62" s="7"/>
     </row>
-    <row r="63" ht="15.0" customHeight="1">
+    <row r="63">
       <c r="A63" s="5" t="s">
         <v>247</v>
       </c>
@@ -3632,7 +3629,7 @@
       <c r="X63" s="7"/>
       <c r="Y63" s="7"/>
     </row>
-    <row r="64" ht="15.0" customHeight="1">
+    <row r="64">
       <c r="A64" s="5" t="s">
         <v>251</v>
       </c>
@@ -3669,8 +3666,8 @@
       <c r="X64" s="7"/>
       <c r="Y64" s="7"/>
     </row>
-    <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="10" t="s">
+    <row r="65">
+      <c r="A65" s="9" t="s">
         <v>255</v>
       </c>
       <c r="B65" s="1">
@@ -3706,8 +3703,8 @@
       <c r="X65" s="1"/>
       <c r="Y65" s="1"/>
     </row>
-    <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="10" t="s">
+    <row r="66">
+      <c r="A66" s="9" t="s">
         <v>259</v>
       </c>
       <c r="B66" s="1">
@@ -3743,8 +3740,8 @@
       <c r="X66" s="1"/>
       <c r="Y66" s="1"/>
     </row>
-    <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="10" t="s">
+    <row r="67">
+      <c r="A67" s="9" t="s">
         <v>263</v>
       </c>
       <c r="B67" s="1">
@@ -3780,8 +3777,8 @@
       <c r="X67" s="1"/>
       <c r="Y67" s="1"/>
     </row>
-    <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="10" t="s">
+    <row r="68">
+      <c r="A68" s="9" t="s">
         <v>267</v>
       </c>
       <c r="B68" s="1">
@@ -3817,8 +3814,8 @@
       <c r="X68" s="1"/>
       <c r="Y68" s="1"/>
     </row>
-    <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="10" t="s">
+    <row r="69">
+      <c r="A69" s="9" t="s">
         <v>271</v>
       </c>
       <c r="B69" s="1">
@@ -3854,7 +3851,7 @@
       <c r="X69" s="1"/>
       <c r="Y69" s="1"/>
     </row>
-    <row r="70" ht="15.0" customHeight="1">
+    <row r="70">
       <c r="A70" s="5" t="s">
         <v>275</v>
       </c>
@@ -3891,7 +3888,7 @@
       <c r="X70" s="7"/>
       <c r="Y70" s="7"/>
     </row>
-    <row r="71" ht="15.0" customHeight="1">
+    <row r="71">
       <c r="A71" s="5" t="s">
         <v>279</v>
       </c>
@@ -3928,8 +3925,8 @@
       <c r="X71" s="7"/>
       <c r="Y71" s="7"/>
     </row>
-    <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="10" t="s">
+    <row r="72">
+      <c r="A72" s="9" t="s">
         <v>283</v>
       </c>
       <c r="B72" s="1">
@@ -3965,8 +3962,8 @@
       <c r="X72" s="1"/>
       <c r="Y72" s="1"/>
     </row>
-    <row r="73" ht="15.0" customHeight="1">
-      <c r="A73" s="10" t="s">
+    <row r="73">
+      <c r="A73" s="9" t="s">
         <v>287</v>
       </c>
       <c r="B73" s="1">
@@ -4002,8 +3999,8 @@
       <c r="X73" s="1"/>
       <c r="Y73" s="1"/>
     </row>
-    <row r="74" ht="15.0" customHeight="1">
-      <c r="A74" s="10" t="s">
+    <row r="74">
+      <c r="A74" s="9" t="s">
         <v>291</v>
       </c>
       <c r="B74" s="1">
@@ -4039,7 +4036,7 @@
       <c r="X74" s="1"/>
       <c r="Y74" s="1"/>
     </row>
-    <row r="75" ht="15.0" customHeight="1">
+    <row r="75">
       <c r="A75" s="5" t="s">
         <v>295</v>
       </c>
@@ -4076,7 +4073,7 @@
       <c r="X75" s="7"/>
       <c r="Y75" s="7"/>
     </row>
-    <row r="76" ht="15.0" customHeight="1">
+    <row r="76">
       <c r="A76" s="5" t="s">
         <v>299</v>
       </c>
@@ -4113,7 +4110,7 @@
       <c r="X76" s="7"/>
       <c r="Y76" s="7"/>
     </row>
-    <row r="77" ht="15.0" customHeight="1">
+    <row r="77">
       <c r="A77" s="5" t="s">
         <v>303</v>
       </c>
@@ -4150,7 +4147,7 @@
       <c r="X77" s="7"/>
       <c r="Y77" s="7"/>
     </row>
-    <row r="78" ht="15.0" customHeight="1">
+    <row r="78">
       <c r="A78" s="5" t="s">
         <v>307</v>
       </c>
@@ -4187,7 +4184,7 @@
       <c r="X78" s="7"/>
       <c r="Y78" s="7"/>
     </row>
-    <row r="79" ht="15.0" customHeight="1">
+    <row r="79">
       <c r="A79" s="5" t="s">
         <v>311</v>
       </c>
@@ -4224,44 +4221,44 @@
       <c r="X79" s="7"/>
       <c r="Y79" s="7"/>
     </row>
-    <row r="80" ht="15.0" customHeight="1">
-      <c r="A80" s="11" t="s">
+    <row r="80">
+      <c r="A80" s="10" t="s">
         <v>315</v>
       </c>
-      <c r="B80" s="12">
+      <c r="B80" s="11">
         <v>0.0</v>
       </c>
-      <c r="C80" s="13" t="s">
+      <c r="C80" s="12" t="s">
         <v>316</v>
       </c>
-      <c r="D80" s="13" t="s">
+      <c r="D80" s="12" t="s">
         <v>317</v>
       </c>
-      <c r="E80" s="13" t="s">
+      <c r="E80" s="12" t="s">
         <v>318</v>
       </c>
-      <c r="F80" s="13"/>
-      <c r="G80" s="13"/>
-      <c r="H80" s="13"/>
-      <c r="I80" s="13"/>
-      <c r="J80" s="13"/>
-      <c r="K80" s="13"/>
-      <c r="L80" s="13"/>
-      <c r="M80" s="13"/>
-      <c r="N80" s="13"/>
-      <c r="O80" s="13"/>
-      <c r="P80" s="13"/>
-      <c r="Q80" s="13"/>
-      <c r="R80" s="13"/>
-      <c r="S80" s="13"/>
-      <c r="T80" s="13"/>
-      <c r="U80" s="13"/>
-      <c r="V80" s="13"/>
-      <c r="W80" s="13"/>
-      <c r="X80" s="13"/>
-      <c r="Y80" s="13"/>
-    </row>
-    <row r="81" ht="15.0" customHeight="1">
+      <c r="F80" s="12"/>
+      <c r="G80" s="12"/>
+      <c r="H80" s="12"/>
+      <c r="I80" s="12"/>
+      <c r="J80" s="12"/>
+      <c r="K80" s="12"/>
+      <c r="L80" s="12"/>
+      <c r="M80" s="12"/>
+      <c r="N80" s="12"/>
+      <c r="O80" s="12"/>
+      <c r="P80" s="12"/>
+      <c r="Q80" s="12"/>
+      <c r="R80" s="12"/>
+      <c r="S80" s="12"/>
+      <c r="T80" s="12"/>
+      <c r="U80" s="12"/>
+      <c r="V80" s="12"/>
+      <c r="W80" s="12"/>
+      <c r="X80" s="12"/>
+      <c r="Y80" s="12"/>
+    </row>
+    <row r="81">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -4288,7 +4285,7 @@
       <c r="X81" s="1"/>
       <c r="Y81" s="1"/>
     </row>
-    <row r="82" ht="15.0" customHeight="1">
+    <row r="82">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -4315,7 +4312,7 @@
       <c r="X82" s="1"/>
       <c r="Y82" s="1"/>
     </row>
-    <row r="83" ht="15.0" customHeight="1">
+    <row r="83">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -4342,7 +4339,7 @@
       <c r="X83" s="1"/>
       <c r="Y83" s="1"/>
     </row>
-    <row r="84" ht="15.0" customHeight="1">
+    <row r="84">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -4369,7 +4366,7 @@
       <c r="X84" s="1"/>
       <c r="Y84" s="1"/>
     </row>
-    <row r="85" ht="15.0" customHeight="1">
+    <row r="85">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -4396,7 +4393,7 @@
       <c r="X85" s="1"/>
       <c r="Y85" s="1"/>
     </row>
-    <row r="86" ht="15.0" customHeight="1">
+    <row r="86">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -4423,7 +4420,7 @@
       <c r="X86" s="1"/>
       <c r="Y86" s="1"/>
     </row>
-    <row r="87" ht="15.0" customHeight="1">
+    <row r="87">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -4450,7 +4447,7 @@
       <c r="X87" s="1"/>
       <c r="Y87" s="1"/>
     </row>
-    <row r="88" ht="15.0" customHeight="1">
+    <row r="88">
       <c r="A88" s="7"/>
       <c r="B88" s="6"/>
       <c r="C88" s="7"/>
@@ -4477,7 +4474,7 @@
       <c r="X88" s="7"/>
       <c r="Y88" s="7"/>
     </row>
-    <row r="89" ht="15.0" customHeight="1">
+    <row r="89">
       <c r="A89" s="7"/>
       <c r="B89" s="6"/>
       <c r="C89" s="7"/>
@@ -4504,7 +4501,7 @@
       <c r="X89" s="7"/>
       <c r="Y89" s="7"/>
     </row>
-    <row r="90" ht="15.0" customHeight="1">
+    <row r="90">
       <c r="A90" s="7"/>
       <c r="B90" s="6"/>
       <c r="C90" s="7"/>
@@ -4531,7 +4528,7 @@
       <c r="X90" s="7"/>
       <c r="Y90" s="7"/>
     </row>
-    <row r="91" ht="15.0" customHeight="1">
+    <row r="91">
       <c r="A91" s="7"/>
       <c r="B91" s="6"/>
       <c r="C91" s="7"/>
@@ -4558,7 +4555,7 @@
       <c r="X91" s="7"/>
       <c r="Y91" s="7"/>
     </row>
-    <row r="92" ht="15.0" customHeight="1">
+    <row r="92">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -4585,7 +4582,7 @@
       <c r="X92" s="1"/>
       <c r="Y92" s="1"/>
     </row>
-    <row r="93" ht="15.0" customHeight="1">
+    <row r="93">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -4612,7 +4609,7 @@
       <c r="X93" s="1"/>
       <c r="Y93" s="1"/>
     </row>
-    <row r="94" ht="15.0" customHeight="1">
+    <row r="94">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -4639,7 +4636,7 @@
       <c r="X94" s="1"/>
       <c r="Y94" s="1"/>
     </row>
-    <row r="95" ht="15.0" customHeight="1">
+    <row r="95">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -4666,7 +4663,7 @@
       <c r="X95" s="1"/>
       <c r="Y95" s="1"/>
     </row>
-    <row r="96" ht="15.0" customHeight="1">
+    <row r="96">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -4693,7 +4690,7 @@
       <c r="X96" s="1"/>
       <c r="Y96" s="1"/>
     </row>
-    <row r="97" ht="15.0" customHeight="1">
+    <row r="97">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -4720,7 +4717,7 @@
       <c r="X97" s="1"/>
       <c r="Y97" s="1"/>
     </row>
-    <row r="98" ht="15.0" customHeight="1">
+    <row r="98">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -4747,7 +4744,7 @@
       <c r="X98" s="1"/>
       <c r="Y98" s="1"/>
     </row>
-    <row r="99" ht="15.0" customHeight="1">
+    <row r="99">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -4774,7 +4771,7 @@
       <c r="X99" s="1"/>
       <c r="Y99" s="1"/>
     </row>
-    <row r="100" ht="15.0" customHeight="1">
+    <row r="100">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -4801,7 +4798,7 @@
       <c r="X100" s="1"/>
       <c r="Y100" s="1"/>
     </row>
-    <row r="101" ht="15.0" customHeight="1">
+    <row r="101">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -4828,7 +4825,7 @@
       <c r="X101" s="1"/>
       <c r="Y101" s="1"/>
     </row>
-    <row r="102" ht="15.0" customHeight="1">
+    <row r="102">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -4855,7 +4852,7 @@
       <c r="X102" s="1"/>
       <c r="Y102" s="1"/>
     </row>
-    <row r="103" ht="15.0" customHeight="1">
+    <row r="103">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -4882,7 +4879,7 @@
       <c r="X103" s="1"/>
       <c r="Y103" s="1"/>
     </row>
-    <row r="104" ht="15.0" customHeight="1">
+    <row r="104">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -4909,7 +4906,7 @@
       <c r="X104" s="1"/>
       <c r="Y104" s="1"/>
     </row>
-    <row r="105" ht="15.0" customHeight="1">
+    <row r="105">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -4936,7 +4933,7 @@
       <c r="X105" s="1"/>
       <c r="Y105" s="1"/>
     </row>
-    <row r="106" ht="15.0" customHeight="1">
+    <row r="106">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -4963,7 +4960,7 @@
       <c r="X106" s="1"/>
       <c r="Y106" s="1"/>
     </row>
-    <row r="107" ht="15.0" customHeight="1">
+    <row r="107">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -4990,7 +4987,7 @@
       <c r="X107" s="1"/>
       <c r="Y107" s="1"/>
     </row>
-    <row r="108" ht="15.0" customHeight="1">
+    <row r="108">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -5017,7 +5014,7 @@
       <c r="X108" s="1"/>
       <c r="Y108" s="1"/>
     </row>
-    <row r="109" ht="15.0" customHeight="1">
+    <row r="109">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -5044,7 +5041,7 @@
       <c r="X109" s="1"/>
       <c r="Y109" s="1"/>
     </row>
-    <row r="110" ht="15.0" customHeight="1">
+    <row r="110">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -5071,7 +5068,7 @@
       <c r="X110" s="1"/>
       <c r="Y110" s="1"/>
     </row>
-    <row r="111" ht="15.0" customHeight="1">
+    <row r="111">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -5098,7 +5095,7 @@
       <c r="X111" s="1"/>
       <c r="Y111" s="1"/>
     </row>
-    <row r="112" ht="15.0" customHeight="1">
+    <row r="112">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -5125,7 +5122,7 @@
       <c r="X112" s="1"/>
       <c r="Y112" s="1"/>
     </row>
-    <row r="113" ht="15.0" customHeight="1">
+    <row r="113">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -5152,7 +5149,7 @@
       <c r="X113" s="1"/>
       <c r="Y113" s="1"/>
     </row>
-    <row r="114" ht="15.0" customHeight="1">
+    <row r="114">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -5179,7 +5176,7 @@
       <c r="X114" s="1"/>
       <c r="Y114" s="1"/>
     </row>
-    <row r="115" ht="15.0" customHeight="1">
+    <row r="115">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -5206,7 +5203,7 @@
       <c r="X115" s="1"/>
       <c r="Y115" s="1"/>
     </row>
-    <row r="116" ht="15.0" customHeight="1">
+    <row r="116">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -5233,7 +5230,7 @@
       <c r="X116" s="1"/>
       <c r="Y116" s="1"/>
     </row>
-    <row r="117" ht="15.0" customHeight="1">
+    <row r="117">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -5260,7 +5257,7 @@
       <c r="X117" s="1"/>
       <c r="Y117" s="1"/>
     </row>
-    <row r="118" ht="15.0" customHeight="1">
+    <row r="118">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -5287,7 +5284,7 @@
       <c r="X118" s="1"/>
       <c r="Y118" s="1"/>
     </row>
-    <row r="119" ht="15.0" customHeight="1">
+    <row r="119">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -5314,7 +5311,7 @@
       <c r="X119" s="1"/>
       <c r="Y119" s="1"/>
     </row>
-    <row r="120" ht="15.0" customHeight="1">
+    <row r="120">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -5341,7 +5338,7 @@
       <c r="X120" s="1"/>
       <c r="Y120" s="1"/>
     </row>
-    <row r="121" ht="15.0" customHeight="1">
+    <row r="121">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -5368,7 +5365,7 @@
       <c r="X121" s="1"/>
       <c r="Y121" s="1"/>
     </row>
-    <row r="122" ht="15.0" customHeight="1">
+    <row r="122">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -5395,7 +5392,7 @@
       <c r="X122" s="1"/>
       <c r="Y122" s="1"/>
     </row>
-    <row r="123" ht="15.0" customHeight="1">
+    <row r="123">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -5422,7 +5419,7 @@
       <c r="X123" s="1"/>
       <c r="Y123" s="1"/>
     </row>
-    <row r="124" ht="15.0" customHeight="1">
+    <row r="124">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -5449,7 +5446,7 @@
       <c r="X124" s="1"/>
       <c r="Y124" s="1"/>
     </row>
-    <row r="125" ht="15.0" customHeight="1">
+    <row r="125">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -5476,7 +5473,7 @@
       <c r="X125" s="1"/>
       <c r="Y125" s="1"/>
     </row>
-    <row r="126" ht="15.0" customHeight="1">
+    <row r="126">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -5503,7 +5500,7 @@
       <c r="X126" s="1"/>
       <c r="Y126" s="1"/>
     </row>
-    <row r="127" ht="15.0" customHeight="1">
+    <row r="127">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -5530,7 +5527,7 @@
       <c r="X127" s="1"/>
       <c r="Y127" s="1"/>
     </row>
-    <row r="128" ht="15.0" customHeight="1">
+    <row r="128">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -5557,7 +5554,7 @@
       <c r="X128" s="1"/>
       <c r="Y128" s="1"/>
     </row>
-    <row r="129" ht="15.0" customHeight="1">
+    <row r="129">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -5584,7 +5581,7 @@
       <c r="X129" s="1"/>
       <c r="Y129" s="1"/>
     </row>
-    <row r="130" ht="15.0" customHeight="1">
+    <row r="130">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -5611,7 +5608,7 @@
       <c r="X130" s="1"/>
       <c r="Y130" s="1"/>
     </row>
-    <row r="131" ht="15.0" customHeight="1">
+    <row r="131">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -5638,7 +5635,7 @@
       <c r="X131" s="1"/>
       <c r="Y131" s="1"/>
     </row>
-    <row r="132" ht="15.0" customHeight="1">
+    <row r="132">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -5665,7 +5662,7 @@
       <c r="X132" s="1"/>
       <c r="Y132" s="1"/>
     </row>
-    <row r="133" ht="15.0" customHeight="1">
+    <row r="133">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -5692,7 +5689,7 @@
       <c r="X133" s="1"/>
       <c r="Y133" s="1"/>
     </row>
-    <row r="134" ht="15.0" customHeight="1">
+    <row r="134">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -5719,7 +5716,7 @@
       <c r="X134" s="1"/>
       <c r="Y134" s="1"/>
     </row>
-    <row r="135" ht="15.0" customHeight="1">
+    <row r="135">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -5746,7 +5743,7 @@
       <c r="X135" s="1"/>
       <c r="Y135" s="1"/>
     </row>
-    <row r="136" ht="15.0" customHeight="1">
+    <row r="136">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -5773,7 +5770,7 @@
       <c r="X136" s="1"/>
       <c r="Y136" s="1"/>
     </row>
-    <row r="137" ht="15.0" customHeight="1">
+    <row r="137">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -5800,7 +5797,7 @@
       <c r="X137" s="1"/>
       <c r="Y137" s="1"/>
     </row>
-    <row r="138" ht="15.0" customHeight="1">
+    <row r="138">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -5827,7 +5824,7 @@
       <c r="X138" s="1"/>
       <c r="Y138" s="1"/>
     </row>
-    <row r="139" ht="15.0" customHeight="1">
+    <row r="139">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -5854,7 +5851,7 @@
       <c r="X139" s="1"/>
       <c r="Y139" s="1"/>
     </row>
-    <row r="140" ht="15.0" customHeight="1">
+    <row r="140">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -5881,7 +5878,7 @@
       <c r="X140" s="1"/>
       <c r="Y140" s="1"/>
     </row>
-    <row r="141" ht="15.0" customHeight="1">
+    <row r="141">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -5908,7 +5905,7 @@
       <c r="X141" s="1"/>
       <c r="Y141" s="1"/>
     </row>
-    <row r="142" ht="15.0" customHeight="1">
+    <row r="142">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -5935,7 +5932,7 @@
       <c r="X142" s="1"/>
       <c r="Y142" s="1"/>
     </row>
-    <row r="143" ht="15.0" customHeight="1">
+    <row r="143">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -5962,7 +5959,7 @@
       <c r="X143" s="1"/>
       <c r="Y143" s="1"/>
     </row>
-    <row r="144" ht="15.0" customHeight="1">
+    <row r="144">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -5989,7 +5986,7 @@
       <c r="X144" s="1"/>
       <c r="Y144" s="1"/>
     </row>
-    <row r="145" ht="15.0" customHeight="1">
+    <row r="145">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -6016,7 +6013,7 @@
       <c r="X145" s="1"/>
       <c r="Y145" s="1"/>
     </row>
-    <row r="146" ht="15.0" customHeight="1">
+    <row r="146">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -6043,7 +6040,7 @@
       <c r="X146" s="1"/>
       <c r="Y146" s="1"/>
     </row>
-    <row r="147" ht="15.0" customHeight="1">
+    <row r="147">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -6070,7 +6067,7 @@
       <c r="X147" s="1"/>
       <c r="Y147" s="1"/>
     </row>
-    <row r="148" ht="15.0" customHeight="1">
+    <row r="148">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -6097,7 +6094,7 @@
       <c r="X148" s="1"/>
       <c r="Y148" s="1"/>
     </row>
-    <row r="149" ht="15.0" customHeight="1">
+    <row r="149">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -6124,7 +6121,7 @@
       <c r="X149" s="1"/>
       <c r="Y149" s="1"/>
     </row>
-    <row r="150" ht="15.0" customHeight="1">
+    <row r="150">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -6151,7 +6148,7 @@
       <c r="X150" s="1"/>
       <c r="Y150" s="1"/>
     </row>
-    <row r="151" ht="15.0" customHeight="1">
+    <row r="151">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -6178,7 +6175,7 @@
       <c r="X151" s="1"/>
       <c r="Y151" s="1"/>
     </row>
-    <row r="152" ht="15.0" customHeight="1">
+    <row r="152">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -6205,7 +6202,7 @@
       <c r="X152" s="1"/>
       <c r="Y152" s="1"/>
     </row>
-    <row r="153" ht="15.0" customHeight="1">
+    <row r="153">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -6232,7 +6229,7 @@
       <c r="X153" s="1"/>
       <c r="Y153" s="1"/>
     </row>
-    <row r="154" ht="15.0" customHeight="1">
+    <row r="154">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -6259,7 +6256,7 @@
       <c r="X154" s="1"/>
       <c r="Y154" s="1"/>
     </row>
-    <row r="155" ht="15.0" customHeight="1">
+    <row r="155">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -6286,7 +6283,7 @@
       <c r="X155" s="1"/>
       <c r="Y155" s="1"/>
     </row>
-    <row r="156" ht="15.0" customHeight="1">
+    <row r="156">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -6313,7 +6310,7 @@
       <c r="X156" s="1"/>
       <c r="Y156" s="1"/>
     </row>
-    <row r="157" ht="15.0" customHeight="1">
+    <row r="157">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -6340,7 +6337,7 @@
       <c r="X157" s="1"/>
       <c r="Y157" s="1"/>
     </row>
-    <row r="158" ht="15.0" customHeight="1">
+    <row r="158">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -6367,7 +6364,7 @@
       <c r="X158" s="1"/>
       <c r="Y158" s="1"/>
     </row>
-    <row r="159" ht="15.0" customHeight="1">
+    <row r="159">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -6394,7 +6391,7 @@
       <c r="X159" s="1"/>
       <c r="Y159" s="1"/>
     </row>
-    <row r="160" ht="15.0" customHeight="1">
+    <row r="160">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -6421,7 +6418,7 @@
       <c r="X160" s="1"/>
       <c r="Y160" s="1"/>
     </row>
-    <row r="161" ht="15.0" customHeight="1">
+    <row r="161">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -6448,7 +6445,7 @@
       <c r="X161" s="1"/>
       <c r="Y161" s="1"/>
     </row>
-    <row r="162" ht="15.0" customHeight="1">
+    <row r="162">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -6475,7 +6472,7 @@
       <c r="X162" s="1"/>
       <c r="Y162" s="1"/>
     </row>
-    <row r="163" ht="15.0" customHeight="1">
+    <row r="163">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -6502,7 +6499,7 @@
       <c r="X163" s="1"/>
       <c r="Y163" s="1"/>
     </row>
-    <row r="164" ht="15.0" customHeight="1">
+    <row r="164">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -6529,7 +6526,7 @@
       <c r="X164" s="1"/>
       <c r="Y164" s="1"/>
     </row>
-    <row r="165" ht="15.0" customHeight="1">
+    <row r="165">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -6556,7 +6553,7 @@
       <c r="X165" s="1"/>
       <c r="Y165" s="1"/>
     </row>
-    <row r="166" ht="15.0" customHeight="1">
+    <row r="166">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -6583,7 +6580,7 @@
       <c r="X166" s="1"/>
       <c r="Y166" s="1"/>
     </row>
-    <row r="167" ht="15.0" customHeight="1">
+    <row r="167">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -6610,7 +6607,7 @@
       <c r="X167" s="1"/>
       <c r="Y167" s="1"/>
     </row>
-    <row r="168" ht="15.0" customHeight="1">
+    <row r="168">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -6637,7 +6634,7 @@
       <c r="X168" s="1"/>
       <c r="Y168" s="1"/>
     </row>
-    <row r="169" ht="15.0" customHeight="1">
+    <row r="169">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -6664,7 +6661,7 @@
       <c r="X169" s="1"/>
       <c r="Y169" s="1"/>
     </row>
-    <row r="170" ht="15.0" customHeight="1">
+    <row r="170">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -6691,7 +6688,7 @@
       <c r="X170" s="1"/>
       <c r="Y170" s="1"/>
     </row>
-    <row r="171" ht="15.0" customHeight="1">
+    <row r="171">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -6718,7 +6715,7 @@
       <c r="X171" s="1"/>
       <c r="Y171" s="1"/>
     </row>
-    <row r="172" ht="15.0" customHeight="1">
+    <row r="172">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -6745,7 +6742,7 @@
       <c r="X172" s="1"/>
       <c r="Y172" s="1"/>
     </row>
-    <row r="173" ht="15.0" customHeight="1">
+    <row r="173">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -6772,7 +6769,7 @@
       <c r="X173" s="1"/>
       <c r="Y173" s="1"/>
     </row>
-    <row r="174" ht="15.0" customHeight="1">
+    <row r="174">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -6799,7 +6796,7 @@
       <c r="X174" s="1"/>
       <c r="Y174" s="1"/>
     </row>
-    <row r="175" ht="15.0" customHeight="1">
+    <row r="175">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -6826,7 +6823,7 @@
       <c r="X175" s="1"/>
       <c r="Y175" s="1"/>
     </row>
-    <row r="176" ht="15.0" customHeight="1">
+    <row r="176">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -6853,7 +6850,7 @@
       <c r="X176" s="1"/>
       <c r="Y176" s="1"/>
     </row>
-    <row r="177" ht="15.0" customHeight="1">
+    <row r="177">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -6880,7 +6877,7 @@
       <c r="X177" s="1"/>
       <c r="Y177" s="1"/>
     </row>
-    <row r="178" ht="15.0" customHeight="1">
+    <row r="178">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -6907,7 +6904,7 @@
       <c r="X178" s="1"/>
       <c r="Y178" s="1"/>
     </row>
-    <row r="179" ht="15.0" customHeight="1">
+    <row r="179">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -6934,7 +6931,7 @@
       <c r="X179" s="1"/>
       <c r="Y179" s="1"/>
     </row>
-    <row r="180" ht="15.0" customHeight="1">
+    <row r="180">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -6961,7 +6958,7 @@
       <c r="X180" s="1"/>
       <c r="Y180" s="1"/>
     </row>
-    <row r="181" ht="15.0" customHeight="1">
+    <row r="181">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -6988,7 +6985,7 @@
       <c r="X181" s="1"/>
       <c r="Y181" s="1"/>
     </row>
-    <row r="182" ht="15.0" customHeight="1">
+    <row r="182">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -7015,7 +7012,7 @@
       <c r="X182" s="1"/>
       <c r="Y182" s="1"/>
     </row>
-    <row r="183" ht="15.0" customHeight="1">
+    <row r="183">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -7042,7 +7039,7 @@
       <c r="X183" s="1"/>
       <c r="Y183" s="1"/>
     </row>
-    <row r="184" ht="15.0" customHeight="1">
+    <row r="184">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -7069,7 +7066,7 @@
       <c r="X184" s="1"/>
       <c r="Y184" s="1"/>
     </row>
-    <row r="185" ht="15.0" customHeight="1">
+    <row r="185">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -7096,7 +7093,7 @@
       <c r="X185" s="1"/>
       <c r="Y185" s="1"/>
     </row>
-    <row r="186" ht="15.0" customHeight="1">
+    <row r="186">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -7123,7 +7120,7 @@
       <c r="X186" s="1"/>
       <c r="Y186" s="1"/>
     </row>
-    <row r="187" ht="15.0" customHeight="1">
+    <row r="187">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -7150,7 +7147,7 @@
       <c r="X187" s="1"/>
       <c r="Y187" s="1"/>
     </row>
-    <row r="188" ht="15.0" customHeight="1">
+    <row r="188">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -7177,7 +7174,7 @@
       <c r="X188" s="1"/>
       <c r="Y188" s="1"/>
     </row>
-    <row r="189" ht="15.0" customHeight="1">
+    <row r="189">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -7204,7 +7201,7 @@
       <c r="X189" s="1"/>
       <c r="Y189" s="1"/>
     </row>
-    <row r="190" ht="15.0" customHeight="1">
+    <row r="190">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -7231,7 +7228,7 @@
       <c r="X190" s="1"/>
       <c r="Y190" s="1"/>
     </row>
-    <row r="191" ht="15.0" customHeight="1">
+    <row r="191">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -7258,7 +7255,7 @@
       <c r="X191" s="1"/>
       <c r="Y191" s="1"/>
     </row>
-    <row r="192" ht="15.0" customHeight="1">
+    <row r="192">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -7285,7 +7282,7 @@
       <c r="X192" s="1"/>
       <c r="Y192" s="1"/>
     </row>
-    <row r="193" ht="15.0" customHeight="1">
+    <row r="193">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -7312,7 +7309,7 @@
       <c r="X193" s="1"/>
       <c r="Y193" s="1"/>
     </row>
-    <row r="194" ht="15.0" customHeight="1">
+    <row r="194">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -7339,7 +7336,7 @@
       <c r="X194" s="1"/>
       <c r="Y194" s="1"/>
     </row>
-    <row r="195" ht="15.0" customHeight="1">
+    <row r="195">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -7366,7 +7363,7 @@
       <c r="X195" s="1"/>
       <c r="Y195" s="1"/>
     </row>
-    <row r="196" ht="15.0" customHeight="1">
+    <row r="196">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -7393,7 +7390,7 @@
       <c r="X196" s="1"/>
       <c r="Y196" s="1"/>
     </row>
-    <row r="197" ht="15.0" customHeight="1">
+    <row r="197">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -7420,7 +7417,7 @@
       <c r="X197" s="1"/>
       <c r="Y197" s="1"/>
     </row>
-    <row r="198" ht="15.0" customHeight="1">
+    <row r="198">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -7447,7 +7444,7 @@
       <c r="X198" s="1"/>
       <c r="Y198" s="1"/>
     </row>
-    <row r="199" ht="15.0" customHeight="1">
+    <row r="199">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -7474,7 +7471,7 @@
       <c r="X199" s="1"/>
       <c r="Y199" s="1"/>
     </row>
-    <row r="200" ht="15.0" customHeight="1">
+    <row r="200">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -7501,7 +7498,7 @@
       <c r="X200" s="1"/>
       <c r="Y200" s="1"/>
     </row>
-    <row r="201" ht="15.0" customHeight="1">
+    <row r="201">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -7528,7 +7525,7 @@
       <c r="X201" s="1"/>
       <c r="Y201" s="1"/>
     </row>
-    <row r="202" ht="15.0" customHeight="1">
+    <row r="202">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -7555,7 +7552,7 @@
       <c r="X202" s="1"/>
       <c r="Y202" s="1"/>
     </row>
-    <row r="203" ht="15.0" customHeight="1">
+    <row r="203">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -7582,7 +7579,7 @@
       <c r="X203" s="1"/>
       <c r="Y203" s="1"/>
     </row>
-    <row r="204" ht="15.0" customHeight="1">
+    <row r="204">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -7609,7 +7606,7 @@
       <c r="X204" s="1"/>
       <c r="Y204" s="1"/>
     </row>
-    <row r="205" ht="15.0" customHeight="1">
+    <row r="205">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -7636,7 +7633,7 @@
       <c r="X205" s="1"/>
       <c r="Y205" s="1"/>
     </row>
-    <row r="206" ht="15.0" customHeight="1">
+    <row r="206">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -7663,7 +7660,7 @@
       <c r="X206" s="1"/>
       <c r="Y206" s="1"/>
     </row>
-    <row r="207" ht="15.0" customHeight="1">
+    <row r="207">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -7690,7 +7687,7 @@
       <c r="X207" s="1"/>
       <c r="Y207" s="1"/>
     </row>
-    <row r="208" ht="15.0" customHeight="1">
+    <row r="208">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -7717,7 +7714,7 @@
       <c r="X208" s="1"/>
       <c r="Y208" s="1"/>
     </row>
-    <row r="209" ht="15.0" customHeight="1">
+    <row r="209">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -7744,7 +7741,7 @@
       <c r="X209" s="1"/>
       <c r="Y209" s="1"/>
     </row>
-    <row r="210" ht="15.0" customHeight="1">
+    <row r="210">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -7771,7 +7768,7 @@
       <c r="X210" s="1"/>
       <c r="Y210" s="1"/>
     </row>
-    <row r="211" ht="15.0" customHeight="1">
+    <row r="211">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -7798,7 +7795,7 @@
       <c r="X211" s="1"/>
       <c r="Y211" s="1"/>
     </row>
-    <row r="212" ht="15.0" customHeight="1">
+    <row r="212">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -7825,7 +7822,7 @@
       <c r="X212" s="1"/>
       <c r="Y212" s="1"/>
     </row>
-    <row r="213" ht="15.0" customHeight="1">
+    <row r="213">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -7852,7 +7849,7 @@
       <c r="X213" s="1"/>
       <c r="Y213" s="1"/>
     </row>
-    <row r="214" ht="15.0" customHeight="1">
+    <row r="214">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -7879,7 +7876,7 @@
       <c r="X214" s="1"/>
       <c r="Y214" s="1"/>
     </row>
-    <row r="215" ht="15.0" customHeight="1">
+    <row r="215">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -7906,7 +7903,7 @@
       <c r="X215" s="1"/>
       <c r="Y215" s="1"/>
     </row>
-    <row r="216" ht="15.0" customHeight="1">
+    <row r="216">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -7933,7 +7930,7 @@
       <c r="X216" s="1"/>
       <c r="Y216" s="1"/>
     </row>
-    <row r="217" ht="15.0" customHeight="1">
+    <row r="217">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -7960,7 +7957,7 @@
       <c r="X217" s="1"/>
       <c r="Y217" s="1"/>
     </row>
-    <row r="218" ht="15.0" customHeight="1">
+    <row r="218">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -7987,7 +7984,7 @@
       <c r="X218" s="1"/>
       <c r="Y218" s="1"/>
     </row>
-    <row r="219" ht="15.0" customHeight="1">
+    <row r="219">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -8014,7 +8011,7 @@
       <c r="X219" s="1"/>
       <c r="Y219" s="1"/>
     </row>
-    <row r="220" ht="15.0" customHeight="1">
+    <row r="220">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -8041,7 +8038,7 @@
       <c r="X220" s="1"/>
       <c r="Y220" s="1"/>
     </row>
-    <row r="221" ht="15.0" customHeight="1">
+    <row r="221">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -8068,7 +8065,7 @@
       <c r="X221" s="1"/>
       <c r="Y221" s="1"/>
     </row>
-    <row r="222" ht="15.0" customHeight="1">
+    <row r="222">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -8095,7 +8092,7 @@
       <c r="X222" s="1"/>
       <c r="Y222" s="1"/>
     </row>
-    <row r="223" ht="15.0" customHeight="1">
+    <row r="223">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -8122,7 +8119,7 @@
       <c r="X223" s="1"/>
       <c r="Y223" s="1"/>
     </row>
-    <row r="224" ht="15.0" customHeight="1">
+    <row r="224">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -8149,7 +8146,7 @@
       <c r="X224" s="1"/>
       <c r="Y224" s="1"/>
     </row>
-    <row r="225" ht="15.0" customHeight="1">
+    <row r="225">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -8176,7 +8173,7 @@
       <c r="X225" s="1"/>
       <c r="Y225" s="1"/>
     </row>
-    <row r="226" ht="15.0" customHeight="1">
+    <row r="226">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -8203,7 +8200,7 @@
       <c r="X226" s="1"/>
       <c r="Y226" s="1"/>
     </row>
-    <row r="227" ht="15.0" customHeight="1">
+    <row r="227">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -8230,7 +8227,7 @@
       <c r="X227" s="1"/>
       <c r="Y227" s="1"/>
     </row>
-    <row r="228" ht="15.0" customHeight="1">
+    <row r="228">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -8257,7 +8254,7 @@
       <c r="X228" s="1"/>
       <c r="Y228" s="1"/>
     </row>
-    <row r="229" ht="15.0" customHeight="1">
+    <row r="229">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -8284,7 +8281,7 @@
       <c r="X229" s="1"/>
       <c r="Y229" s="1"/>
     </row>
-    <row r="230" ht="15.0" customHeight="1">
+    <row r="230">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -8311,7 +8308,7 @@
       <c r="X230" s="1"/>
       <c r="Y230" s="1"/>
     </row>
-    <row r="231" ht="15.0" customHeight="1">
+    <row r="231">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -8338,7 +8335,7 @@
       <c r="X231" s="1"/>
       <c r="Y231" s="1"/>
     </row>
-    <row r="232" ht="15.0" customHeight="1">
+    <row r="232">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -8365,7 +8362,7 @@
       <c r="X232" s="1"/>
       <c r="Y232" s="1"/>
     </row>
-    <row r="233" ht="15.0" customHeight="1">
+    <row r="233">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -8392,7 +8389,7 @@
       <c r="X233" s="1"/>
       <c r="Y233" s="1"/>
     </row>
-    <row r="234" ht="15.0" customHeight="1">
+    <row r="234">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -8419,7 +8416,7 @@
       <c r="X234" s="1"/>
       <c r="Y234" s="1"/>
     </row>
-    <row r="235" ht="15.0" customHeight="1">
+    <row r="235">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -8446,7 +8443,7 @@
       <c r="X235" s="1"/>
       <c r="Y235" s="1"/>
     </row>
-    <row r="236" ht="15.0" customHeight="1">
+    <row r="236">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -8473,7 +8470,7 @@
       <c r="X236" s="1"/>
       <c r="Y236" s="1"/>
     </row>
-    <row r="237" ht="15.0" customHeight="1">
+    <row r="237">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -8500,7 +8497,7 @@
       <c r="X237" s="1"/>
       <c r="Y237" s="1"/>
     </row>
-    <row r="238" ht="15.0" customHeight="1">
+    <row r="238">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -8527,7 +8524,7 @@
       <c r="X238" s="1"/>
       <c r="Y238" s="1"/>
     </row>
-    <row r="239" ht="15.0" customHeight="1">
+    <row r="239">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -8554,7 +8551,7 @@
       <c r="X239" s="1"/>
       <c r="Y239" s="1"/>
     </row>
-    <row r="240" ht="15.0" customHeight="1">
+    <row r="240">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -8581,7 +8578,7 @@
       <c r="X240" s="1"/>
       <c r="Y240" s="1"/>
     </row>
-    <row r="241" ht="15.0" customHeight="1">
+    <row r="241">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -8608,7 +8605,7 @@
       <c r="X241" s="1"/>
       <c r="Y241" s="1"/>
     </row>
-    <row r="242" ht="15.0" customHeight="1">
+    <row r="242">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -8635,7 +8632,7 @@
       <c r="X242" s="1"/>
       <c r="Y242" s="1"/>
     </row>
-    <row r="243" ht="15.0" customHeight="1">
+    <row r="243">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -8662,7 +8659,7 @@
       <c r="X243" s="1"/>
       <c r="Y243" s="1"/>
     </row>
-    <row r="244" ht="15.0" customHeight="1">
+    <row r="244">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -8689,7 +8686,7 @@
       <c r="X244" s="1"/>
       <c r="Y244" s="1"/>
     </row>
-    <row r="245" ht="15.0" customHeight="1">
+    <row r="245">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -8716,7 +8713,7 @@
       <c r="X245" s="1"/>
       <c r="Y245" s="1"/>
     </row>
-    <row r="246" ht="15.0" customHeight="1">
+    <row r="246">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -8743,7 +8740,7 @@
       <c r="X246" s="1"/>
       <c r="Y246" s="1"/>
     </row>
-    <row r="247" ht="15.0" customHeight="1">
+    <row r="247">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -8770,7 +8767,7 @@
       <c r="X247" s="1"/>
       <c r="Y247" s="1"/>
     </row>
-    <row r="248" ht="15.0" customHeight="1">
+    <row r="248">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -8797,7 +8794,7 @@
       <c r="X248" s="1"/>
       <c r="Y248" s="1"/>
     </row>
-    <row r="249" ht="15.0" customHeight="1">
+    <row r="249">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -8824,7 +8821,7 @@
       <c r="X249" s="1"/>
       <c r="Y249" s="1"/>
     </row>
-    <row r="250" ht="15.0" customHeight="1">
+    <row r="250">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -8851,7 +8848,7 @@
       <c r="X250" s="1"/>
       <c r="Y250" s="1"/>
     </row>
-    <row r="251" ht="15.0" customHeight="1">
+    <row r="251">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -8878,7 +8875,7 @@
       <c r="X251" s="1"/>
       <c r="Y251" s="1"/>
     </row>
-    <row r="252" ht="15.0" customHeight="1">
+    <row r="252">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -8905,7 +8902,7 @@
       <c r="X252" s="1"/>
       <c r="Y252" s="1"/>
     </row>
-    <row r="253" ht="15.0" customHeight="1">
+    <row r="253">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -8932,7 +8929,7 @@
       <c r="X253" s="1"/>
       <c r="Y253" s="1"/>
     </row>
-    <row r="254" ht="15.0" customHeight="1">
+    <row r="254">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -8959,7 +8956,7 @@
       <c r="X254" s="1"/>
       <c r="Y254" s="1"/>
     </row>
-    <row r="255" ht="15.0" customHeight="1">
+    <row r="255">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -8986,7 +8983,7 @@
       <c r="X255" s="1"/>
       <c r="Y255" s="1"/>
     </row>
-    <row r="256" ht="15.0" customHeight="1">
+    <row r="256">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -9013,7 +9010,7 @@
       <c r="X256" s="1"/>
       <c r="Y256" s="1"/>
     </row>
-    <row r="257" ht="15.0" customHeight="1">
+    <row r="257">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -9040,7 +9037,7 @@
       <c r="X257" s="1"/>
       <c r="Y257" s="1"/>
     </row>
-    <row r="258" ht="15.0" customHeight="1">
+    <row r="258">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -9067,7 +9064,7 @@
       <c r="X258" s="1"/>
       <c r="Y258" s="1"/>
     </row>
-    <row r="259" ht="15.0" customHeight="1">
+    <row r="259">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -9094,7 +9091,7 @@
       <c r="X259" s="1"/>
       <c r="Y259" s="1"/>
     </row>
-    <row r="260" ht="15.0" customHeight="1">
+    <row r="260">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -9121,7 +9118,7 @@
       <c r="X260" s="1"/>
       <c r="Y260" s="1"/>
     </row>
-    <row r="261" ht="15.0" customHeight="1">
+    <row r="261">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -9148,7 +9145,7 @@
       <c r="X261" s="1"/>
       <c r="Y261" s="1"/>
     </row>
-    <row r="262" ht="15.0" customHeight="1">
+    <row r="262">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -9175,7 +9172,7 @@
       <c r="X262" s="1"/>
       <c r="Y262" s="1"/>
     </row>
-    <row r="263" ht="15.0" customHeight="1">
+    <row r="263">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -9202,7 +9199,7 @@
       <c r="X263" s="1"/>
       <c r="Y263" s="1"/>
     </row>
-    <row r="264" ht="15.0" customHeight="1">
+    <row r="264">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -9229,7 +9226,7 @@
       <c r="X264" s="1"/>
       <c r="Y264" s="1"/>
     </row>
-    <row r="265" ht="15.0" customHeight="1">
+    <row r="265">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -9256,7 +9253,7 @@
       <c r="X265" s="1"/>
       <c r="Y265" s="1"/>
     </row>
-    <row r="266" ht="15.0" customHeight="1">
+    <row r="266">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -9283,7 +9280,7 @@
       <c r="X266" s="1"/>
       <c r="Y266" s="1"/>
     </row>
-    <row r="267" ht="15.0" customHeight="1">
+    <row r="267">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -9310,7 +9307,7 @@
       <c r="X267" s="1"/>
       <c r="Y267" s="1"/>
     </row>
-    <row r="268" ht="15.0" customHeight="1">
+    <row r="268">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -9337,7 +9334,7 @@
       <c r="X268" s="1"/>
       <c r="Y268" s="1"/>
     </row>
-    <row r="269" ht="15.0" customHeight="1">
+    <row r="269">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -9364,7 +9361,7 @@
       <c r="X269" s="1"/>
       <c r="Y269" s="1"/>
     </row>
-    <row r="270" ht="15.0" customHeight="1">
+    <row r="270">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -9391,7 +9388,7 @@
       <c r="X270" s="1"/>
       <c r="Y270" s="1"/>
     </row>
-    <row r="271" ht="15.0" customHeight="1">
+    <row r="271">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -9418,7 +9415,7 @@
       <c r="X271" s="1"/>
       <c r="Y271" s="1"/>
     </row>
-    <row r="272" ht="15.0" customHeight="1">
+    <row r="272">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -9445,7 +9442,7 @@
       <c r="X272" s="1"/>
       <c r="Y272" s="1"/>
     </row>
-    <row r="273" ht="15.0" customHeight="1">
+    <row r="273">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -9472,7 +9469,7 @@
       <c r="X273" s="1"/>
       <c r="Y273" s="1"/>
     </row>
-    <row r="274" ht="15.0" customHeight="1">
+    <row r="274">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -9499,7 +9496,7 @@
       <c r="X274" s="1"/>
       <c r="Y274" s="1"/>
     </row>
-    <row r="275" ht="15.0" customHeight="1">
+    <row r="275">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
@@ -9526,7 +9523,7 @@
       <c r="X275" s="1"/>
       <c r="Y275" s="1"/>
     </row>
-    <row r="276" ht="15.0" customHeight="1">
+    <row r="276">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -9553,7 +9550,7 @@
       <c r="X276" s="1"/>
       <c r="Y276" s="1"/>
     </row>
-    <row r="277" ht="15.0" customHeight="1">
+    <row r="277">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
@@ -9580,7 +9577,7 @@
       <c r="X277" s="1"/>
       <c r="Y277" s="1"/>
     </row>
-    <row r="278" ht="15.0" customHeight="1">
+    <row r="278">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
@@ -9607,7 +9604,7 @@
       <c r="X278" s="1"/>
       <c r="Y278" s="1"/>
     </row>
-    <row r="279" ht="15.0" customHeight="1">
+    <row r="279">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -9634,7 +9631,7 @@
       <c r="X279" s="1"/>
       <c r="Y279" s="1"/>
     </row>
-    <row r="280" ht="15.0" customHeight="1">
+    <row r="280">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
@@ -9661,726 +9658,6 @@
       <c r="X280" s="1"/>
       <c r="Y280" s="1"/>
     </row>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
-    <row r="810" ht="15.75" customHeight="1"/>
-    <row r="811" ht="15.75" customHeight="1"/>
-    <row r="812" ht="15.75" customHeight="1"/>
-    <row r="813" ht="15.75" customHeight="1"/>
-    <row r="814" ht="15.75" customHeight="1"/>
-    <row r="815" ht="15.75" customHeight="1"/>
-    <row r="816" ht="15.75" customHeight="1"/>
-    <row r="817" ht="15.75" customHeight="1"/>
-    <row r="818" ht="15.75" customHeight="1"/>
-    <row r="819" ht="15.75" customHeight="1"/>
-    <row r="820" ht="15.75" customHeight="1"/>
-    <row r="821" ht="15.75" customHeight="1"/>
-    <row r="822" ht="15.75" customHeight="1"/>
-    <row r="823" ht="15.75" customHeight="1"/>
-    <row r="824" ht="15.75" customHeight="1"/>
-    <row r="825" ht="15.75" customHeight="1"/>
-    <row r="826" ht="15.75" customHeight="1"/>
-    <row r="827" ht="15.75" customHeight="1"/>
-    <row r="828" ht="15.75" customHeight="1"/>
-    <row r="829" ht="15.75" customHeight="1"/>
-    <row r="830" ht="15.75" customHeight="1"/>
-    <row r="831" ht="15.75" customHeight="1"/>
-    <row r="832" ht="15.75" customHeight="1"/>
-    <row r="833" ht="15.75" customHeight="1"/>
-    <row r="834" ht="15.75" customHeight="1"/>
-    <row r="835" ht="15.75" customHeight="1"/>
-    <row r="836" ht="15.75" customHeight="1"/>
-    <row r="837" ht="15.75" customHeight="1"/>
-    <row r="838" ht="15.75" customHeight="1"/>
-    <row r="839" ht="15.75" customHeight="1"/>
-    <row r="840" ht="15.75" customHeight="1"/>
-    <row r="841" ht="15.75" customHeight="1"/>
-    <row r="842" ht="15.75" customHeight="1"/>
-    <row r="843" ht="15.75" customHeight="1"/>
-    <row r="844" ht="15.75" customHeight="1"/>
-    <row r="845" ht="15.75" customHeight="1"/>
-    <row r="846" ht="15.75" customHeight="1"/>
-    <row r="847" ht="15.75" customHeight="1"/>
-    <row r="848" ht="15.75" customHeight="1"/>
-    <row r="849" ht="15.75" customHeight="1"/>
-    <row r="850" ht="15.75" customHeight="1"/>
-    <row r="851" ht="15.75" customHeight="1"/>
-    <row r="852" ht="15.75" customHeight="1"/>
-    <row r="853" ht="15.75" customHeight="1"/>
-    <row r="854" ht="15.75" customHeight="1"/>
-    <row r="855" ht="15.75" customHeight="1"/>
-    <row r="856" ht="15.75" customHeight="1"/>
-    <row r="857" ht="15.75" customHeight="1"/>
-    <row r="858" ht="15.75" customHeight="1"/>
-    <row r="859" ht="15.75" customHeight="1"/>
-    <row r="860" ht="15.75" customHeight="1"/>
-    <row r="861" ht="15.75" customHeight="1"/>
-    <row r="862" ht="15.75" customHeight="1"/>
-    <row r="863" ht="15.75" customHeight="1"/>
-    <row r="864" ht="15.75" customHeight="1"/>
-    <row r="865" ht="15.75" customHeight="1"/>
-    <row r="866" ht="15.75" customHeight="1"/>
-    <row r="867" ht="15.75" customHeight="1"/>
-    <row r="868" ht="15.75" customHeight="1"/>
-    <row r="869" ht="15.75" customHeight="1"/>
-    <row r="870" ht="15.75" customHeight="1"/>
-    <row r="871" ht="15.75" customHeight="1"/>
-    <row r="872" ht="15.75" customHeight="1"/>
-    <row r="873" ht="15.75" customHeight="1"/>
-    <row r="874" ht="15.75" customHeight="1"/>
-    <row r="875" ht="15.75" customHeight="1"/>
-    <row r="876" ht="15.75" customHeight="1"/>
-    <row r="877" ht="15.75" customHeight="1"/>
-    <row r="878" ht="15.75" customHeight="1"/>
-    <row r="879" ht="15.75" customHeight="1"/>
-    <row r="880" ht="15.75" customHeight="1"/>
-    <row r="881" ht="15.75" customHeight="1"/>
-    <row r="882" ht="15.75" customHeight="1"/>
-    <row r="883" ht="15.75" customHeight="1"/>
-    <row r="884" ht="15.75" customHeight="1"/>
-    <row r="885" ht="15.75" customHeight="1"/>
-    <row r="886" ht="15.75" customHeight="1"/>
-    <row r="887" ht="15.75" customHeight="1"/>
-    <row r="888" ht="15.75" customHeight="1"/>
-    <row r="889" ht="15.75" customHeight="1"/>
-    <row r="890" ht="15.75" customHeight="1"/>
-    <row r="891" ht="15.75" customHeight="1"/>
-    <row r="892" ht="15.75" customHeight="1"/>
-    <row r="893" ht="15.75" customHeight="1"/>
-    <row r="894" ht="15.75" customHeight="1"/>
-    <row r="895" ht="15.75" customHeight="1"/>
-    <row r="896" ht="15.75" customHeight="1"/>
-    <row r="897" ht="15.75" customHeight="1"/>
-    <row r="898" ht="15.75" customHeight="1"/>
-    <row r="899" ht="15.75" customHeight="1"/>
-    <row r="900" ht="15.75" customHeight="1"/>
-    <row r="901" ht="15.75" customHeight="1"/>
-    <row r="902" ht="15.75" customHeight="1"/>
-    <row r="903" ht="15.75" customHeight="1"/>
-    <row r="904" ht="15.75" customHeight="1"/>
-    <row r="905" ht="15.75" customHeight="1"/>
-    <row r="906" ht="15.75" customHeight="1"/>
-    <row r="907" ht="15.75" customHeight="1"/>
-    <row r="908" ht="15.75" customHeight="1"/>
-    <row r="909" ht="15.75" customHeight="1"/>
-    <row r="910" ht="15.75" customHeight="1"/>
-    <row r="911" ht="15.75" customHeight="1"/>
-    <row r="912" ht="15.75" customHeight="1"/>
-    <row r="913" ht="15.75" customHeight="1"/>
-    <row r="914" ht="15.75" customHeight="1"/>
-    <row r="915" ht="15.75" customHeight="1"/>
-    <row r="916" ht="15.75" customHeight="1"/>
-    <row r="917" ht="15.75" customHeight="1"/>
-    <row r="918" ht="15.75" customHeight="1"/>
-    <row r="919" ht="15.75" customHeight="1"/>
-    <row r="920" ht="15.75" customHeight="1"/>
-    <row r="921" ht="15.75" customHeight="1"/>
-    <row r="922" ht="15.75" customHeight="1"/>
-    <row r="923" ht="15.75" customHeight="1"/>
-    <row r="924" ht="15.75" customHeight="1"/>
-    <row r="925" ht="15.75" customHeight="1"/>
-    <row r="926" ht="15.75" customHeight="1"/>
-    <row r="927" ht="15.75" customHeight="1"/>
-    <row r="928" ht="15.75" customHeight="1"/>
-    <row r="929" ht="15.75" customHeight="1"/>
-    <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
-    <row r="935" ht="15.75" customHeight="1"/>
-    <row r="936" ht="15.75" customHeight="1"/>
-    <row r="937" ht="15.75" customHeight="1"/>
-    <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
-    <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
-    <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Templates/Tables/StringInfo/StrTable.xlsx
+++ b/Templates/Tables/StringInfo/StrTable.xlsx
@@ -1291,11 +1291,11 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="23.5"/>
-    <col customWidth="1" min="2" max="2" width="12.63"/>
-    <col customWidth="1" min="3" max="3" width="32.63"/>
+    <col customWidth="1" min="2" max="2" width="7.13"/>
+    <col customWidth="1" min="3" max="3" width="26.13"/>
     <col customWidth="1" min="4" max="4" width="85.88"/>
     <col customWidth="1" min="5" max="5" width="98.0"/>
-    <col customWidth="1" min="6" max="25" width="12.63"/>
+    <col customWidth="1" min="6" max="26" width="23.75"/>
   </cols>
   <sheetData>
     <row r="1">
